--- a/docs/BRUTAL-items-et-cartes.xlsx
+++ b/docs/BRUTAL-items-et-cartes.xlsx
@@ -63,7 +63,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -78,6 +78,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="009AA0A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004A9D52"/>
       </patternFill>
     </fill>
     <fill>
@@ -152,7 +157,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -175,14 +180,17 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -200,22 +208,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -584,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -675,19 +683,26 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Rare  (rare)</t>
+          <t xml:space="preserve">  Uncommon  (uncommon)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Epic  (epique)</t>
+          <t xml:space="preserve">  Rare  (rare)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Epic  (epique)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">  Legendary  (legendaire)</t>
         </is>
@@ -724,1536 +739,1536 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>BRUTAL — Items par type (cartes ajoutées au deck)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>Une ligne = une pièce d'équipement. Remplis les lignes vides pour proposer de nouveaux items.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>Nom</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="C3" s="11" t="inlineStr">
         <is>
           <t>Rareté</t>
         </is>
       </c>
-      <c r="D3" s="10" t="inlineStr">
+      <c r="D3" s="11" t="inlineStr">
         <is>
           <t>Nb cartes</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="E3" s="11" t="inlineStr">
         <is>
           <t>Carte 1</t>
         </is>
       </c>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="F3" s="11" t="inlineStr">
         <is>
           <t>Qté</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="G3" s="11" t="inlineStr">
         <is>
           <t>Carte 2</t>
         </is>
       </c>
-      <c r="H3" s="10" t="inlineStr">
+      <c r="H3" s="11" t="inlineStr">
         <is>
           <t>Qté</t>
         </is>
       </c>
-      <c r="I3" s="10" t="inlineStr">
+      <c r="I3" s="11" t="inlineStr">
         <is>
           <t>Carte 3</t>
         </is>
       </c>
-      <c r="J3" s="10" t="inlineStr">
+      <c r="J3" s="11" t="inlineStr">
         <is>
           <t>Qté</t>
         </is>
       </c>
-      <c r="K3" s="10" t="inlineStr">
+      <c r="K3" s="11" t="inlineStr">
         <is>
           <t>Carte 4</t>
         </is>
       </c>
-      <c r="L3" s="10" t="inlineStr">
+      <c r="L3" s="11" t="inlineStr">
         <is>
           <t>Qté</t>
         </is>
       </c>
-      <c r="M3" s="10" t="inlineStr">
+      <c r="M3" s="11" t="inlineStr">
         <is>
           <t>Notes / nouvelles cartes</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Armes — une main   (5)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Rusty Axe</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>hache-rouillee</t>
         </is>
       </c>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="D5" s="15" t="n">
+      <c r="D5" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="E5" s="16" t="inlineStr">
+      <c r="E5" s="17" t="inlineStr">
         <is>
           <t>Rusty Cleave</t>
         </is>
       </c>
-      <c r="F5" s="15" t="n">
+      <c r="F5" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="G5" s="16" t="n"/>
-      <c r="H5" s="16" t="n"/>
-      <c r="I5" s="16" t="n"/>
-      <c r="J5" s="16" t="n"/>
-      <c r="K5" s="16" t="n"/>
-      <c r="L5" s="16" t="n"/>
-      <c r="M5" s="16" t="n"/>
+      <c r="G5" s="17" t="n"/>
+      <c r="H5" s="17" t="n"/>
+      <c r="I5" s="17" t="n"/>
+      <c r="J5" s="17" t="n"/>
+      <c r="K5" s="17" t="n"/>
+      <c r="L5" s="17" t="n"/>
+      <c r="M5" s="17" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>Forge Hammer</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>marteau-de-forge</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="D6" s="15" t="n">
+      <c r="D6" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E6" s="17" t="inlineStr">
         <is>
           <t>Forge Smash</t>
         </is>
       </c>
-      <c r="F6" s="15" t="n">
+      <c r="F6" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="G6" s="16" t="n"/>
-      <c r="H6" s="16" t="n"/>
-      <c r="I6" s="16" t="n"/>
-      <c r="J6" s="16" t="n"/>
-      <c r="K6" s="16" t="n"/>
-      <c r="L6" s="16" t="n"/>
-      <c r="M6" s="16" t="n"/>
+      <c r="G6" s="17" t="n"/>
+      <c r="H6" s="17" t="n"/>
+      <c r="I6" s="17" t="n"/>
+      <c r="J6" s="17" t="n"/>
+      <c r="K6" s="17" t="n"/>
+      <c r="L6" s="17" t="n"/>
+      <c r="M6" s="17" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>Miner's Pick</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>pioche-de-mineur</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="D7" s="15" t="n">
+      <c r="D7" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E7" s="17" t="inlineStr">
         <is>
           <t>Pickaxe Jab</t>
         </is>
       </c>
-      <c r="F7" s="15" t="n">
+      <c r="F7" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="G7" s="16" t="n"/>
-      <c r="H7" s="16" t="n"/>
-      <c r="I7" s="16" t="n"/>
-      <c r="J7" s="16" t="n"/>
-      <c r="K7" s="16" t="n"/>
-      <c r="L7" s="16" t="n"/>
-      <c r="M7" s="16" t="n"/>
+      <c r="G7" s="17" t="n"/>
+      <c r="H7" s="17" t="n"/>
+      <c r="I7" s="17" t="n"/>
+      <c r="J7" s="17" t="n"/>
+      <c r="K7" s="17" t="n"/>
+      <c r="L7" s="17" t="n"/>
+      <c r="M7" s="17" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>Basilisk Fang</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>croc-de-basilic</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr">
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="D8" s="15" t="n">
+      <c r="D8" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>Venom Stab</t>
         </is>
       </c>
-      <c r="F8" s="15" t="n">
+      <c r="F8" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="G8" s="16" t="n"/>
-      <c r="H8" s="16" t="n"/>
-      <c r="I8" s="16" t="n"/>
-      <c r="J8" s="16" t="n"/>
-      <c r="K8" s="16" t="n"/>
-      <c r="L8" s="16" t="n"/>
-      <c r="M8" s="16" t="n"/>
+      <c r="G8" s="17" t="n"/>
+      <c r="H8" s="17" t="n"/>
+      <c r="I8" s="17" t="n"/>
+      <c r="J8" s="17" t="n"/>
+      <c r="K8" s="17" t="n"/>
+      <c r="L8" s="17" t="n"/>
+      <c r="M8" s="17" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>Magma Hammer</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>marteau-de-lave</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C9" s="19" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="D9" s="15" t="n">
+      <c r="D9" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t>Lava Hammer</t>
         </is>
       </c>
-      <c r="F9" s="15" t="n">
+      <c r="F9" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="G9" s="16" t="n"/>
-      <c r="H9" s="16" t="n"/>
-      <c r="I9" s="16" t="n"/>
-      <c r="J9" s="16" t="n"/>
-      <c r="K9" s="16" t="n"/>
-      <c r="L9" s="16" t="n"/>
-      <c r="M9" s="16" t="n"/>
+      <c r="G9" s="17" t="n"/>
+      <c r="H9" s="17" t="n"/>
+      <c r="I9" s="17" t="n"/>
+      <c r="J9" s="17" t="n"/>
+      <c r="K9" s="17" t="n"/>
+      <c r="L9" s="17" t="n"/>
+      <c r="M9" s="17" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="19" t="n"/>
-      <c r="B10" s="19" t="n"/>
-      <c r="C10" s="19" t="n"/>
-      <c r="D10" s="19" t="n"/>
-      <c r="E10" s="19" t="n"/>
-      <c r="F10" s="19" t="n"/>
-      <c r="G10" s="19" t="n"/>
-      <c r="H10" s="19" t="n"/>
-      <c r="I10" s="19" t="n"/>
-      <c r="J10" s="19" t="n"/>
-      <c r="K10" s="19" t="n"/>
-      <c r="L10" s="19" t="n"/>
-      <c r="M10" s="19" t="n"/>
+      <c r="A10" s="20" t="n"/>
+      <c r="B10" s="20" t="n"/>
+      <c r="C10" s="20" t="n"/>
+      <c r="D10" s="20" t="n"/>
+      <c r="E10" s="20" t="n"/>
+      <c r="F10" s="20" t="n"/>
+      <c r="G10" s="20" t="n"/>
+      <c r="H10" s="20" t="n"/>
+      <c r="I10" s="20" t="n"/>
+      <c r="J10" s="20" t="n"/>
+      <c r="K10" s="20" t="n"/>
+      <c r="L10" s="20" t="n"/>
+      <c r="M10" s="20" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="19" t="n"/>
-      <c r="B11" s="19" t="n"/>
-      <c r="C11" s="19" t="n"/>
-      <c r="D11" s="19" t="n"/>
-      <c r="E11" s="19" t="n"/>
-      <c r="F11" s="19" t="n"/>
-      <c r="G11" s="19" t="n"/>
-      <c r="H11" s="19" t="n"/>
-      <c r="I11" s="19" t="n"/>
-      <c r="J11" s="19" t="n"/>
-      <c r="K11" s="19" t="n"/>
-      <c r="L11" s="19" t="n"/>
-      <c r="M11" s="19" t="n"/>
+      <c r="A11" s="20" t="n"/>
+      <c r="B11" s="20" t="n"/>
+      <c r="C11" s="20" t="n"/>
+      <c r="D11" s="20" t="n"/>
+      <c r="E11" s="20" t="n"/>
+      <c r="F11" s="20" t="n"/>
+      <c r="G11" s="20" t="n"/>
+      <c r="H11" s="20" t="n"/>
+      <c r="I11" s="20" t="n"/>
+      <c r="J11" s="20" t="n"/>
+      <c r="K11" s="20" t="n"/>
+      <c r="L11" s="20" t="n"/>
+      <c r="M11" s="20" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="19" t="n"/>
-      <c r="B12" s="19" t="n"/>
-      <c r="C12" s="19" t="n"/>
-      <c r="D12" s="19" t="n"/>
-      <c r="E12" s="19" t="n"/>
-      <c r="F12" s="19" t="n"/>
-      <c r="G12" s="19" t="n"/>
-      <c r="H12" s="19" t="n"/>
-      <c r="I12" s="19" t="n"/>
-      <c r="J12" s="19" t="n"/>
-      <c r="K12" s="19" t="n"/>
-      <c r="L12" s="19" t="n"/>
-      <c r="M12" s="19" t="n"/>
+      <c r="A12" s="20" t="n"/>
+      <c r="B12" s="20" t="n"/>
+      <c r="C12" s="20" t="n"/>
+      <c r="D12" s="20" t="n"/>
+      <c r="E12" s="20" t="n"/>
+      <c r="F12" s="20" t="n"/>
+      <c r="G12" s="20" t="n"/>
+      <c r="H12" s="20" t="n"/>
+      <c r="I12" s="20" t="n"/>
+      <c r="J12" s="20" t="n"/>
+      <c r="K12" s="20" t="n"/>
+      <c r="L12" s="20" t="n"/>
+      <c r="M12" s="20" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="19" t="n"/>
-      <c r="B13" s="19" t="n"/>
-      <c r="C13" s="19" t="n"/>
-      <c r="D13" s="19" t="n"/>
-      <c r="E13" s="19" t="n"/>
-      <c r="F13" s="19" t="n"/>
-      <c r="G13" s="19" t="n"/>
-      <c r="H13" s="19" t="n"/>
-      <c r="I13" s="19" t="n"/>
-      <c r="J13" s="19" t="n"/>
-      <c r="K13" s="19" t="n"/>
-      <c r="L13" s="19" t="n"/>
-      <c r="M13" s="19" t="n"/>
+      <c r="A13" s="20" t="n"/>
+      <c r="B13" s="20" t="n"/>
+      <c r="C13" s="20" t="n"/>
+      <c r="D13" s="20" t="n"/>
+      <c r="E13" s="20" t="n"/>
+      <c r="F13" s="20" t="n"/>
+      <c r="G13" s="20" t="n"/>
+      <c r="H13" s="20" t="n"/>
+      <c r="I13" s="20" t="n"/>
+      <c r="J13" s="20" t="n"/>
+      <c r="K13" s="20" t="n"/>
+      <c r="L13" s="20" t="n"/>
+      <c r="M13" s="20" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="19" t="n"/>
-      <c r="B14" s="19" t="n"/>
-      <c r="C14" s="19" t="n"/>
-      <c r="D14" s="19" t="n"/>
-      <c r="E14" s="19" t="n"/>
-      <c r="F14" s="19" t="n"/>
-      <c r="G14" s="19" t="n"/>
-      <c r="H14" s="19" t="n"/>
-      <c r="I14" s="19" t="n"/>
-      <c r="J14" s="19" t="n"/>
-      <c r="K14" s="19" t="n"/>
-      <c r="L14" s="19" t="n"/>
-      <c r="M14" s="19" t="n"/>
+      <c r="A14" s="20" t="n"/>
+      <c r="B14" s="20" t="n"/>
+      <c r="C14" s="20" t="n"/>
+      <c r="D14" s="20" t="n"/>
+      <c r="E14" s="20" t="n"/>
+      <c r="F14" s="20" t="n"/>
+      <c r="G14" s="20" t="n"/>
+      <c r="H14" s="20" t="n"/>
+      <c r="I14" s="20" t="n"/>
+      <c r="J14" s="20" t="n"/>
+      <c r="K14" s="20" t="n"/>
+      <c r="L14" s="20" t="n"/>
+      <c r="M14" s="20" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="19" t="n"/>
-      <c r="B15" s="19" t="n"/>
-      <c r="C15" s="19" t="n"/>
-      <c r="D15" s="19" t="n"/>
-      <c r="E15" s="19" t="n"/>
-      <c r="F15" s="19" t="n"/>
-      <c r="G15" s="19" t="n"/>
-      <c r="H15" s="19" t="n"/>
-      <c r="I15" s="19" t="n"/>
-      <c r="J15" s="19" t="n"/>
-      <c r="K15" s="19" t="n"/>
-      <c r="L15" s="19" t="n"/>
-      <c r="M15" s="19" t="n"/>
+      <c r="A15" s="20" t="n"/>
+      <c r="B15" s="20" t="n"/>
+      <c r="C15" s="20" t="n"/>
+      <c r="D15" s="20" t="n"/>
+      <c r="E15" s="20" t="n"/>
+      <c r="F15" s="20" t="n"/>
+      <c r="G15" s="20" t="n"/>
+      <c r="H15" s="20" t="n"/>
+      <c r="I15" s="20" t="n"/>
+      <c r="J15" s="20" t="n"/>
+      <c r="K15" s="20" t="n"/>
+      <c r="L15" s="20" t="n"/>
+      <c r="M15" s="20" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>Armes — deux mains   (1)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>War Axe</t>
         </is>
       </c>
-      <c r="B18" s="13" t="inlineStr">
+      <c r="B18" s="14" t="inlineStr">
         <is>
           <t>hache-de-guerre</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C18" s="19" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="D18" s="15" t="n">
+      <c r="D18" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="E18" s="16" t="inlineStr">
+      <c r="E18" s="17" t="inlineStr">
         <is>
           <t>Pommel Strike</t>
         </is>
       </c>
-      <c r="F18" s="15" t="n">
+      <c r="F18" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="G18" s="16" t="inlineStr">
+      <c r="G18" s="17" t="inlineStr">
         <is>
           <t>Giant Swing</t>
         </is>
       </c>
-      <c r="H18" s="15" t="n">
+      <c r="H18" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="I18" s="16" t="inlineStr">
+      <c r="I18" s="17" t="inlineStr">
         <is>
           <t>Cleave</t>
         </is>
       </c>
-      <c r="J18" s="15" t="n">
+      <c r="J18" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="K18" s="16" t="n"/>
-      <c r="L18" s="16" t="n"/>
-      <c r="M18" s="16" t="n"/>
+      <c r="K18" s="17" t="n"/>
+      <c r="L18" s="17" t="n"/>
+      <c r="M18" s="17" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="19" t="n"/>
-      <c r="B19" s="19" t="n"/>
-      <c r="C19" s="19" t="n"/>
-      <c r="D19" s="19" t="n"/>
-      <c r="E19" s="19" t="n"/>
-      <c r="F19" s="19" t="n"/>
-      <c r="G19" s="19" t="n"/>
-      <c r="H19" s="19" t="n"/>
-      <c r="I19" s="19" t="n"/>
-      <c r="J19" s="19" t="n"/>
-      <c r="K19" s="19" t="n"/>
-      <c r="L19" s="19" t="n"/>
-      <c r="M19" s="19" t="n"/>
+      <c r="A19" s="20" t="n"/>
+      <c r="B19" s="20" t="n"/>
+      <c r="C19" s="20" t="n"/>
+      <c r="D19" s="20" t="n"/>
+      <c r="E19" s="20" t="n"/>
+      <c r="F19" s="20" t="n"/>
+      <c r="G19" s="20" t="n"/>
+      <c r="H19" s="20" t="n"/>
+      <c r="I19" s="20" t="n"/>
+      <c r="J19" s="20" t="n"/>
+      <c r="K19" s="20" t="n"/>
+      <c r="L19" s="20" t="n"/>
+      <c r="M19" s="20" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="19" t="n"/>
-      <c r="B20" s="19" t="n"/>
-      <c r="C20" s="19" t="n"/>
-      <c r="D20" s="19" t="n"/>
-      <c r="E20" s="19" t="n"/>
-      <c r="F20" s="19" t="n"/>
-      <c r="G20" s="19" t="n"/>
-      <c r="H20" s="19" t="n"/>
-      <c r="I20" s="19" t="n"/>
-      <c r="J20" s="19" t="n"/>
-      <c r="K20" s="19" t="n"/>
-      <c r="L20" s="19" t="n"/>
-      <c r="M20" s="19" t="n"/>
+      <c r="A20" s="20" t="n"/>
+      <c r="B20" s="20" t="n"/>
+      <c r="C20" s="20" t="n"/>
+      <c r="D20" s="20" t="n"/>
+      <c r="E20" s="20" t="n"/>
+      <c r="F20" s="20" t="n"/>
+      <c r="G20" s="20" t="n"/>
+      <c r="H20" s="20" t="n"/>
+      <c r="I20" s="20" t="n"/>
+      <c r="J20" s="20" t="n"/>
+      <c r="K20" s="20" t="n"/>
+      <c r="L20" s="20" t="n"/>
+      <c r="M20" s="20" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="19" t="n"/>
-      <c r="B21" s="19" t="n"/>
-      <c r="C21" s="19" t="n"/>
-      <c r="D21" s="19" t="n"/>
-      <c r="E21" s="19" t="n"/>
-      <c r="F21" s="19" t="n"/>
-      <c r="G21" s="19" t="n"/>
-      <c r="H21" s="19" t="n"/>
-      <c r="I21" s="19" t="n"/>
-      <c r="J21" s="19" t="n"/>
-      <c r="K21" s="19" t="n"/>
-      <c r="L21" s="19" t="n"/>
-      <c r="M21" s="19" t="n"/>
+      <c r="A21" s="20" t="n"/>
+      <c r="B21" s="20" t="n"/>
+      <c r="C21" s="20" t="n"/>
+      <c r="D21" s="20" t="n"/>
+      <c r="E21" s="20" t="n"/>
+      <c r="F21" s="20" t="n"/>
+      <c r="G21" s="20" t="n"/>
+      <c r="H21" s="20" t="n"/>
+      <c r="I21" s="20" t="n"/>
+      <c r="J21" s="20" t="n"/>
+      <c r="K21" s="20" t="n"/>
+      <c r="L21" s="20" t="n"/>
+      <c r="M21" s="20" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="19" t="n"/>
-      <c r="B22" s="19" t="n"/>
-      <c r="C22" s="19" t="n"/>
-      <c r="D22" s="19" t="n"/>
-      <c r="E22" s="19" t="n"/>
-      <c r="F22" s="19" t="n"/>
-      <c r="G22" s="19" t="n"/>
-      <c r="H22" s="19" t="n"/>
-      <c r="I22" s="19" t="n"/>
-      <c r="J22" s="19" t="n"/>
-      <c r="K22" s="19" t="n"/>
-      <c r="L22" s="19" t="n"/>
-      <c r="M22" s="19" t="n"/>
+      <c r="A22" s="20" t="n"/>
+      <c r="B22" s="20" t="n"/>
+      <c r="C22" s="20" t="n"/>
+      <c r="D22" s="20" t="n"/>
+      <c r="E22" s="20" t="n"/>
+      <c r="F22" s="20" t="n"/>
+      <c r="G22" s="20" t="n"/>
+      <c r="H22" s="20" t="n"/>
+      <c r="I22" s="20" t="n"/>
+      <c r="J22" s="20" t="n"/>
+      <c r="K22" s="20" t="n"/>
+      <c r="L22" s="20" t="n"/>
+      <c r="M22" s="20" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="19" t="n"/>
-      <c r="B23" s="19" t="n"/>
-      <c r="C23" s="19" t="n"/>
-      <c r="D23" s="19" t="n"/>
-      <c r="E23" s="19" t="n"/>
-      <c r="F23" s="19" t="n"/>
-      <c r="G23" s="19" t="n"/>
-      <c r="H23" s="19" t="n"/>
-      <c r="I23" s="19" t="n"/>
-      <c r="J23" s="19" t="n"/>
-      <c r="K23" s="19" t="n"/>
-      <c r="L23" s="19" t="n"/>
-      <c r="M23" s="19" t="n"/>
+      <c r="A23" s="20" t="n"/>
+      <c r="B23" s="20" t="n"/>
+      <c r="C23" s="20" t="n"/>
+      <c r="D23" s="20" t="n"/>
+      <c r="E23" s="20" t="n"/>
+      <c r="F23" s="20" t="n"/>
+      <c r="G23" s="20" t="n"/>
+      <c r="H23" s="20" t="n"/>
+      <c r="I23" s="20" t="n"/>
+      <c r="J23" s="20" t="n"/>
+      <c r="K23" s="20" t="n"/>
+      <c r="L23" s="20" t="n"/>
+      <c r="M23" s="20" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="19" t="n"/>
-      <c r="B24" s="19" t="n"/>
-      <c r="C24" s="19" t="n"/>
-      <c r="D24" s="19" t="n"/>
-      <c r="E24" s="19" t="n"/>
-      <c r="F24" s="19" t="n"/>
-      <c r="G24" s="19" t="n"/>
-      <c r="H24" s="19" t="n"/>
-      <c r="I24" s="19" t="n"/>
-      <c r="J24" s="19" t="n"/>
-      <c r="K24" s="19" t="n"/>
-      <c r="L24" s="19" t="n"/>
-      <c r="M24" s="19" t="n"/>
+      <c r="A24" s="20" t="n"/>
+      <c r="B24" s="20" t="n"/>
+      <c r="C24" s="20" t="n"/>
+      <c r="D24" s="20" t="n"/>
+      <c r="E24" s="20" t="n"/>
+      <c r="F24" s="20" t="n"/>
+      <c r="G24" s="20" t="n"/>
+      <c r="H24" s="20" t="n"/>
+      <c r="I24" s="20" t="n"/>
+      <c r="J24" s="20" t="n"/>
+      <c r="K24" s="20" t="n"/>
+      <c r="L24" s="20" t="n"/>
+      <c r="M24" s="20" t="n"/>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="A26" s="12" t="inlineStr">
         <is>
           <t>Boucliers (main 2nde)   (1)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="inlineStr">
+      <c r="A27" s="13" t="inlineStr">
         <is>
           <t>Tower Shield</t>
         </is>
       </c>
-      <c r="B27" s="13" t="inlineStr">
+      <c r="B27" s="14" t="inlineStr">
         <is>
           <t>bouclier-tour</t>
         </is>
       </c>
-      <c r="C27" s="18" t="inlineStr">
+      <c r="C27" s="19" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="D27" s="15" t="n">
+      <c r="D27" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="E27" s="16" t="inlineStr">
+      <c r="E27" s="17" t="inlineStr">
         <is>
           <t>Shield Wall</t>
         </is>
       </c>
-      <c r="F27" s="15" t="n">
+      <c r="F27" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="G27" s="16" t="inlineStr">
+      <c r="G27" s="17" t="inlineStr">
         <is>
           <t>Shield Bash</t>
         </is>
       </c>
-      <c r="H27" s="15" t="n">
+      <c r="H27" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="I27" s="16" t="n"/>
-      <c r="J27" s="16" t="n"/>
-      <c r="K27" s="16" t="n"/>
-      <c r="L27" s="16" t="n"/>
-      <c r="M27" s="16" t="n"/>
+      <c r="I27" s="17" t="n"/>
+      <c r="J27" s="17" t="n"/>
+      <c r="K27" s="17" t="n"/>
+      <c r="L27" s="17" t="n"/>
+      <c r="M27" s="17" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="19" t="n"/>
-      <c r="B28" s="19" t="n"/>
-      <c r="C28" s="19" t="n"/>
-      <c r="D28" s="19" t="n"/>
-      <c r="E28" s="19" t="n"/>
-      <c r="F28" s="19" t="n"/>
-      <c r="G28" s="19" t="n"/>
-      <c r="H28" s="19" t="n"/>
-      <c r="I28" s="19" t="n"/>
-      <c r="J28" s="19" t="n"/>
-      <c r="K28" s="19" t="n"/>
-      <c r="L28" s="19" t="n"/>
-      <c r="M28" s="19" t="n"/>
+      <c r="A28" s="20" t="n"/>
+      <c r="B28" s="20" t="n"/>
+      <c r="C28" s="20" t="n"/>
+      <c r="D28" s="20" t="n"/>
+      <c r="E28" s="20" t="n"/>
+      <c r="F28" s="20" t="n"/>
+      <c r="G28" s="20" t="n"/>
+      <c r="H28" s="20" t="n"/>
+      <c r="I28" s="20" t="n"/>
+      <c r="J28" s="20" t="n"/>
+      <c r="K28" s="20" t="n"/>
+      <c r="L28" s="20" t="n"/>
+      <c r="M28" s="20" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="19" t="n"/>
-      <c r="B29" s="19" t="n"/>
-      <c r="C29" s="19" t="n"/>
-      <c r="D29" s="19" t="n"/>
-      <c r="E29" s="19" t="n"/>
-      <c r="F29" s="19" t="n"/>
-      <c r="G29" s="19" t="n"/>
-      <c r="H29" s="19" t="n"/>
-      <c r="I29" s="19" t="n"/>
-      <c r="J29" s="19" t="n"/>
-      <c r="K29" s="19" t="n"/>
-      <c r="L29" s="19" t="n"/>
-      <c r="M29" s="19" t="n"/>
+      <c r="A29" s="20" t="n"/>
+      <c r="B29" s="20" t="n"/>
+      <c r="C29" s="20" t="n"/>
+      <c r="D29" s="20" t="n"/>
+      <c r="E29" s="20" t="n"/>
+      <c r="F29" s="20" t="n"/>
+      <c r="G29" s="20" t="n"/>
+      <c r="H29" s="20" t="n"/>
+      <c r="I29" s="20" t="n"/>
+      <c r="J29" s="20" t="n"/>
+      <c r="K29" s="20" t="n"/>
+      <c r="L29" s="20" t="n"/>
+      <c r="M29" s="20" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="19" t="n"/>
-      <c r="B30" s="19" t="n"/>
-      <c r="C30" s="19" t="n"/>
-      <c r="D30" s="19" t="n"/>
-      <c r="E30" s="19" t="n"/>
-      <c r="F30" s="19" t="n"/>
-      <c r="G30" s="19" t="n"/>
-      <c r="H30" s="19" t="n"/>
-      <c r="I30" s="19" t="n"/>
-      <c r="J30" s="19" t="n"/>
-      <c r="K30" s="19" t="n"/>
-      <c r="L30" s="19" t="n"/>
-      <c r="M30" s="19" t="n"/>
+      <c r="A30" s="20" t="n"/>
+      <c r="B30" s="20" t="n"/>
+      <c r="C30" s="20" t="n"/>
+      <c r="D30" s="20" t="n"/>
+      <c r="E30" s="20" t="n"/>
+      <c r="F30" s="20" t="n"/>
+      <c r="G30" s="20" t="n"/>
+      <c r="H30" s="20" t="n"/>
+      <c r="I30" s="20" t="n"/>
+      <c r="J30" s="20" t="n"/>
+      <c r="K30" s="20" t="n"/>
+      <c r="L30" s="20" t="n"/>
+      <c r="M30" s="20" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="19" t="n"/>
-      <c r="B31" s="19" t="n"/>
-      <c r="C31" s="19" t="n"/>
-      <c r="D31" s="19" t="n"/>
-      <c r="E31" s="19" t="n"/>
-      <c r="F31" s="19" t="n"/>
-      <c r="G31" s="19" t="n"/>
-      <c r="H31" s="19" t="n"/>
-      <c r="I31" s="19" t="n"/>
-      <c r="J31" s="19" t="n"/>
-      <c r="K31" s="19" t="n"/>
-      <c r="L31" s="19" t="n"/>
-      <c r="M31" s="19" t="n"/>
+      <c r="A31" s="20" t="n"/>
+      <c r="B31" s="20" t="n"/>
+      <c r="C31" s="20" t="n"/>
+      <c r="D31" s="20" t="n"/>
+      <c r="E31" s="20" t="n"/>
+      <c r="F31" s="20" t="n"/>
+      <c r="G31" s="20" t="n"/>
+      <c r="H31" s="20" t="n"/>
+      <c r="I31" s="20" t="n"/>
+      <c r="J31" s="20" t="n"/>
+      <c r="K31" s="20" t="n"/>
+      <c r="L31" s="20" t="n"/>
+      <c r="M31" s="20" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="19" t="n"/>
-      <c r="B32" s="19" t="n"/>
-      <c r="C32" s="19" t="n"/>
-      <c r="D32" s="19" t="n"/>
-      <c r="E32" s="19" t="n"/>
-      <c r="F32" s="19" t="n"/>
-      <c r="G32" s="19" t="n"/>
-      <c r="H32" s="19" t="n"/>
-      <c r="I32" s="19" t="n"/>
-      <c r="J32" s="19" t="n"/>
-      <c r="K32" s="19" t="n"/>
-      <c r="L32" s="19" t="n"/>
-      <c r="M32" s="19" t="n"/>
+      <c r="A32" s="20" t="n"/>
+      <c r="B32" s="20" t="n"/>
+      <c r="C32" s="20" t="n"/>
+      <c r="D32" s="20" t="n"/>
+      <c r="E32" s="20" t="n"/>
+      <c r="F32" s="20" t="n"/>
+      <c r="G32" s="20" t="n"/>
+      <c r="H32" s="20" t="n"/>
+      <c r="I32" s="20" t="n"/>
+      <c r="J32" s="20" t="n"/>
+      <c r="K32" s="20" t="n"/>
+      <c r="L32" s="20" t="n"/>
+      <c r="M32" s="20" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="19" t="n"/>
-      <c r="B33" s="19" t="n"/>
-      <c r="C33" s="19" t="n"/>
-      <c r="D33" s="19" t="n"/>
-      <c r="E33" s="19" t="n"/>
-      <c r="F33" s="19" t="n"/>
-      <c r="G33" s="19" t="n"/>
-      <c r="H33" s="19" t="n"/>
-      <c r="I33" s="19" t="n"/>
-      <c r="J33" s="19" t="n"/>
-      <c r="K33" s="19" t="n"/>
-      <c r="L33" s="19" t="n"/>
-      <c r="M33" s="19" t="n"/>
+      <c r="A33" s="20" t="n"/>
+      <c r="B33" s="20" t="n"/>
+      <c r="C33" s="20" t="n"/>
+      <c r="D33" s="20" t="n"/>
+      <c r="E33" s="20" t="n"/>
+      <c r="F33" s="20" t="n"/>
+      <c r="G33" s="20" t="n"/>
+      <c r="H33" s="20" t="n"/>
+      <c r="I33" s="20" t="n"/>
+      <c r="J33" s="20" t="n"/>
+      <c r="K33" s="20" t="n"/>
+      <c r="L33" s="20" t="n"/>
+      <c r="M33" s="20" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="11" t="inlineStr">
+      <c r="A35" s="12" t="inlineStr">
         <is>
           <t>Armures   (3)</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="12" t="inlineStr">
+      <c r="A36" s="13" t="inlineStr">
         <is>
           <t>Traveler's Garb</t>
         </is>
       </c>
-      <c r="B36" s="13" t="inlineStr">
+      <c r="B36" s="14" t="inlineStr">
         <is>
           <t>tenue-de-voyageur</t>
         </is>
       </c>
-      <c r="C36" s="14" t="inlineStr">
+      <c r="C36" s="15" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="D36" s="15" t="n">
+      <c r="D36" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="E36" s="16" t="n"/>
-      <c r="F36" s="16" t="n"/>
-      <c r="G36" s="16" t="n"/>
-      <c r="H36" s="16" t="n"/>
-      <c r="I36" s="16" t="n"/>
-      <c r="J36" s="16" t="n"/>
-      <c r="K36" s="16" t="n"/>
-      <c r="L36" s="16" t="n"/>
-      <c r="M36" s="16" t="n"/>
+      <c r="E36" s="17" t="n"/>
+      <c r="F36" s="17" t="n"/>
+      <c r="G36" s="17" t="n"/>
+      <c r="H36" s="17" t="n"/>
+      <c r="I36" s="17" t="n"/>
+      <c r="J36" s="17" t="n"/>
+      <c r="K36" s="17" t="n"/>
+      <c r="L36" s="17" t="n"/>
+      <c r="M36" s="17" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="12" t="inlineStr">
+      <c r="A37" s="13" t="inlineStr">
         <is>
           <t>Onyx Guard Plate</t>
         </is>
       </c>
-      <c r="B37" s="13" t="inlineStr">
+      <c r="B37" s="14" t="inlineStr">
         <is>
           <t>plate-onyx</t>
         </is>
       </c>
-      <c r="C37" s="17" t="inlineStr">
+      <c r="C37" s="18" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="D37" s="15" t="n">
+      <c r="D37" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="E37" s="16" t="inlineStr">
+      <c r="E37" s="17" t="inlineStr">
         <is>
           <t>Onyx Armor</t>
         </is>
       </c>
-      <c r="F37" s="15" t="n">
+      <c r="F37" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="G37" s="16" t="inlineStr">
+      <c r="G37" s="17" t="inlineStr">
         <is>
           <t>Dragon's Blaze</t>
         </is>
       </c>
-      <c r="H37" s="15" t="n">
+      <c r="H37" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="I37" s="16" t="inlineStr">
+      <c r="I37" s="17" t="inlineStr">
         <is>
           <t>Onyx Breath</t>
         </is>
       </c>
-      <c r="J37" s="15" t="n">
+      <c r="J37" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="K37" s="16" t="n"/>
-      <c r="L37" s="16" t="n"/>
-      <c r="M37" s="16" t="n"/>
+      <c r="K37" s="17" t="n"/>
+      <c r="L37" s="17" t="n"/>
+      <c r="M37" s="17" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="12" t="inlineStr">
+      <c r="A38" s="13" t="inlineStr">
         <is>
           <t>Forgemaster's Mail</t>
         </is>
       </c>
-      <c r="B38" s="13" t="inlineStr">
+      <c r="B38" s="14" t="inlineStr">
         <is>
           <t>maille-de-forge</t>
         </is>
       </c>
-      <c r="C38" s="17" t="inlineStr">
+      <c r="C38" s="18" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="D38" s="15" t="n">
+      <c r="D38" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="E38" s="16" t="inlineStr">
+      <c r="E38" s="17" t="inlineStr">
         <is>
           <t>Mail Armor</t>
         </is>
       </c>
-      <c r="F38" s="15" t="n">
+      <c r="F38" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="G38" s="16" t="inlineStr">
+      <c r="G38" s="17" t="inlineStr">
         <is>
           <t>Quench</t>
         </is>
       </c>
-      <c r="H38" s="15" t="n">
+      <c r="H38" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="I38" s="16" t="n"/>
-      <c r="J38" s="16" t="n"/>
-      <c r="K38" s="16" t="n"/>
-      <c r="L38" s="16" t="n"/>
-      <c r="M38" s="16" t="n"/>
+      <c r="I38" s="17" t="n"/>
+      <c r="J38" s="17" t="n"/>
+      <c r="K38" s="17" t="n"/>
+      <c r="L38" s="17" t="n"/>
+      <c r="M38" s="17" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="19" t="n"/>
-      <c r="B39" s="19" t="n"/>
-      <c r="C39" s="19" t="n"/>
-      <c r="D39" s="19" t="n"/>
-      <c r="E39" s="19" t="n"/>
-      <c r="F39" s="19" t="n"/>
-      <c r="G39" s="19" t="n"/>
-      <c r="H39" s="19" t="n"/>
-      <c r="I39" s="19" t="n"/>
-      <c r="J39" s="19" t="n"/>
-      <c r="K39" s="19" t="n"/>
-      <c r="L39" s="19" t="n"/>
-      <c r="M39" s="19" t="n"/>
+      <c r="A39" s="20" t="n"/>
+      <c r="B39" s="20" t="n"/>
+      <c r="C39" s="20" t="n"/>
+      <c r="D39" s="20" t="n"/>
+      <c r="E39" s="20" t="n"/>
+      <c r="F39" s="20" t="n"/>
+      <c r="G39" s="20" t="n"/>
+      <c r="H39" s="20" t="n"/>
+      <c r="I39" s="20" t="n"/>
+      <c r="J39" s="20" t="n"/>
+      <c r="K39" s="20" t="n"/>
+      <c r="L39" s="20" t="n"/>
+      <c r="M39" s="20" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="19" t="n"/>
-      <c r="B40" s="19" t="n"/>
-      <c r="C40" s="19" t="n"/>
-      <c r="D40" s="19" t="n"/>
-      <c r="E40" s="19" t="n"/>
-      <c r="F40" s="19" t="n"/>
-      <c r="G40" s="19" t="n"/>
-      <c r="H40" s="19" t="n"/>
-      <c r="I40" s="19" t="n"/>
-      <c r="J40" s="19" t="n"/>
-      <c r="K40" s="19" t="n"/>
-      <c r="L40" s="19" t="n"/>
-      <c r="M40" s="19" t="n"/>
+      <c r="A40" s="20" t="n"/>
+      <c r="B40" s="20" t="n"/>
+      <c r="C40" s="20" t="n"/>
+      <c r="D40" s="20" t="n"/>
+      <c r="E40" s="20" t="n"/>
+      <c r="F40" s="20" t="n"/>
+      <c r="G40" s="20" t="n"/>
+      <c r="H40" s="20" t="n"/>
+      <c r="I40" s="20" t="n"/>
+      <c r="J40" s="20" t="n"/>
+      <c r="K40" s="20" t="n"/>
+      <c r="L40" s="20" t="n"/>
+      <c r="M40" s="20" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="19" t="n"/>
-      <c r="B41" s="19" t="n"/>
-      <c r="C41" s="19" t="n"/>
-      <c r="D41" s="19" t="n"/>
-      <c r="E41" s="19" t="n"/>
-      <c r="F41" s="19" t="n"/>
-      <c r="G41" s="19" t="n"/>
-      <c r="H41" s="19" t="n"/>
-      <c r="I41" s="19" t="n"/>
-      <c r="J41" s="19" t="n"/>
-      <c r="K41" s="19" t="n"/>
-      <c r="L41" s="19" t="n"/>
-      <c r="M41" s="19" t="n"/>
+      <c r="A41" s="20" t="n"/>
+      <c r="B41" s="20" t="n"/>
+      <c r="C41" s="20" t="n"/>
+      <c r="D41" s="20" t="n"/>
+      <c r="E41" s="20" t="n"/>
+      <c r="F41" s="20" t="n"/>
+      <c r="G41" s="20" t="n"/>
+      <c r="H41" s="20" t="n"/>
+      <c r="I41" s="20" t="n"/>
+      <c r="J41" s="20" t="n"/>
+      <c r="K41" s="20" t="n"/>
+      <c r="L41" s="20" t="n"/>
+      <c r="M41" s="20" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="19" t="n"/>
-      <c r="B42" s="19" t="n"/>
-      <c r="C42" s="19" t="n"/>
-      <c r="D42" s="19" t="n"/>
-      <c r="E42" s="19" t="n"/>
-      <c r="F42" s="19" t="n"/>
-      <c r="G42" s="19" t="n"/>
-      <c r="H42" s="19" t="n"/>
-      <c r="I42" s="19" t="n"/>
-      <c r="J42" s="19" t="n"/>
-      <c r="K42" s="19" t="n"/>
-      <c r="L42" s="19" t="n"/>
-      <c r="M42" s="19" t="n"/>
+      <c r="A42" s="20" t="n"/>
+      <c r="B42" s="20" t="n"/>
+      <c r="C42" s="20" t="n"/>
+      <c r="D42" s="20" t="n"/>
+      <c r="E42" s="20" t="n"/>
+      <c r="F42" s="20" t="n"/>
+      <c r="G42" s="20" t="n"/>
+      <c r="H42" s="20" t="n"/>
+      <c r="I42" s="20" t="n"/>
+      <c r="J42" s="20" t="n"/>
+      <c r="K42" s="20" t="n"/>
+      <c r="L42" s="20" t="n"/>
+      <c r="M42" s="20" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="19" t="n"/>
-      <c r="B43" s="19" t="n"/>
-      <c r="C43" s="19" t="n"/>
-      <c r="D43" s="19" t="n"/>
-      <c r="E43" s="19" t="n"/>
-      <c r="F43" s="19" t="n"/>
-      <c r="G43" s="19" t="n"/>
-      <c r="H43" s="19" t="n"/>
-      <c r="I43" s="19" t="n"/>
-      <c r="J43" s="19" t="n"/>
-      <c r="K43" s="19" t="n"/>
-      <c r="L43" s="19" t="n"/>
-      <c r="M43" s="19" t="n"/>
+      <c r="A43" s="20" t="n"/>
+      <c r="B43" s="20" t="n"/>
+      <c r="C43" s="20" t="n"/>
+      <c r="D43" s="20" t="n"/>
+      <c r="E43" s="20" t="n"/>
+      <c r="F43" s="20" t="n"/>
+      <c r="G43" s="20" t="n"/>
+      <c r="H43" s="20" t="n"/>
+      <c r="I43" s="20" t="n"/>
+      <c r="J43" s="20" t="n"/>
+      <c r="K43" s="20" t="n"/>
+      <c r="L43" s="20" t="n"/>
+      <c r="M43" s="20" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="19" t="n"/>
-      <c r="B44" s="19" t="n"/>
-      <c r="C44" s="19" t="n"/>
-      <c r="D44" s="19" t="n"/>
-      <c r="E44" s="19" t="n"/>
-      <c r="F44" s="19" t="n"/>
-      <c r="G44" s="19" t="n"/>
-      <c r="H44" s="19" t="n"/>
-      <c r="I44" s="19" t="n"/>
-      <c r="J44" s="19" t="n"/>
-      <c r="K44" s="19" t="n"/>
-      <c r="L44" s="19" t="n"/>
-      <c r="M44" s="19" t="n"/>
+      <c r="A44" s="20" t="n"/>
+      <c r="B44" s="20" t="n"/>
+      <c r="C44" s="20" t="n"/>
+      <c r="D44" s="20" t="n"/>
+      <c r="E44" s="20" t="n"/>
+      <c r="F44" s="20" t="n"/>
+      <c r="G44" s="20" t="n"/>
+      <c r="H44" s="20" t="n"/>
+      <c r="I44" s="20" t="n"/>
+      <c r="J44" s="20" t="n"/>
+      <c r="K44" s="20" t="n"/>
+      <c r="L44" s="20" t="n"/>
+      <c r="M44" s="20" t="n"/>
     </row>
     <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="11" t="inlineStr">
+      <c r="A46" s="12" t="inlineStr">
         <is>
           <t>Colliers   (1)</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="12" t="inlineStr">
+      <c r="A47" s="13" t="inlineStr">
         <is>
           <t>Sapphire Amulet</t>
         </is>
       </c>
-      <c r="B47" s="13" t="inlineStr">
+      <c r="B47" s="14" t="inlineStr">
         <is>
           <t>collier-de-saphir</t>
         </is>
       </c>
-      <c r="C47" s="18" t="inlineStr">
+      <c r="C47" s="19" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="D47" s="15" t="n">
+      <c r="D47" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="E47" s="16" t="inlineStr">
+      <c r="E47" s="17" t="inlineStr">
         <is>
           <t>Sapphire Surge</t>
         </is>
       </c>
-      <c r="F47" s="15" t="n">
+      <c r="F47" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="G47" s="16" t="n"/>
-      <c r="H47" s="16" t="n"/>
-      <c r="I47" s="16" t="n"/>
-      <c r="J47" s="16" t="n"/>
-      <c r="K47" s="16" t="n"/>
-      <c r="L47" s="16" t="n"/>
-      <c r="M47" s="16" t="n"/>
+      <c r="G47" s="17" t="n"/>
+      <c r="H47" s="17" t="n"/>
+      <c r="I47" s="17" t="n"/>
+      <c r="J47" s="17" t="n"/>
+      <c r="K47" s="17" t="n"/>
+      <c r="L47" s="17" t="n"/>
+      <c r="M47" s="17" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="19" t="n"/>
-      <c r="B48" s="19" t="n"/>
-      <c r="C48" s="19" t="n"/>
-      <c r="D48" s="19" t="n"/>
-      <c r="E48" s="19" t="n"/>
-      <c r="F48" s="19" t="n"/>
-      <c r="G48" s="19" t="n"/>
-      <c r="H48" s="19" t="n"/>
-      <c r="I48" s="19" t="n"/>
-      <c r="J48" s="19" t="n"/>
-      <c r="K48" s="19" t="n"/>
-      <c r="L48" s="19" t="n"/>
-      <c r="M48" s="19" t="n"/>
+      <c r="A48" s="20" t="n"/>
+      <c r="B48" s="20" t="n"/>
+      <c r="C48" s="20" t="n"/>
+      <c r="D48" s="20" t="n"/>
+      <c r="E48" s="20" t="n"/>
+      <c r="F48" s="20" t="n"/>
+      <c r="G48" s="20" t="n"/>
+      <c r="H48" s="20" t="n"/>
+      <c r="I48" s="20" t="n"/>
+      <c r="J48" s="20" t="n"/>
+      <c r="K48" s="20" t="n"/>
+      <c r="L48" s="20" t="n"/>
+      <c r="M48" s="20" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="19" t="n"/>
-      <c r="B49" s="19" t="n"/>
-      <c r="C49" s="19" t="n"/>
-      <c r="D49" s="19" t="n"/>
-      <c r="E49" s="19" t="n"/>
-      <c r="F49" s="19" t="n"/>
-      <c r="G49" s="19" t="n"/>
-      <c r="H49" s="19" t="n"/>
-      <c r="I49" s="19" t="n"/>
-      <c r="J49" s="19" t="n"/>
-      <c r="K49" s="19" t="n"/>
-      <c r="L49" s="19" t="n"/>
-      <c r="M49" s="19" t="n"/>
+      <c r="A49" s="20" t="n"/>
+      <c r="B49" s="20" t="n"/>
+      <c r="C49" s="20" t="n"/>
+      <c r="D49" s="20" t="n"/>
+      <c r="E49" s="20" t="n"/>
+      <c r="F49" s="20" t="n"/>
+      <c r="G49" s="20" t="n"/>
+      <c r="H49" s="20" t="n"/>
+      <c r="I49" s="20" t="n"/>
+      <c r="J49" s="20" t="n"/>
+      <c r="K49" s="20" t="n"/>
+      <c r="L49" s="20" t="n"/>
+      <c r="M49" s="20" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="19" t="n"/>
-      <c r="B50" s="19" t="n"/>
-      <c r="C50" s="19" t="n"/>
-      <c r="D50" s="19" t="n"/>
-      <c r="E50" s="19" t="n"/>
-      <c r="F50" s="19" t="n"/>
-      <c r="G50" s="19" t="n"/>
-      <c r="H50" s="19" t="n"/>
-      <c r="I50" s="19" t="n"/>
-      <c r="J50" s="19" t="n"/>
-      <c r="K50" s="19" t="n"/>
-      <c r="L50" s="19" t="n"/>
-      <c r="M50" s="19" t="n"/>
+      <c r="A50" s="20" t="n"/>
+      <c r="B50" s="20" t="n"/>
+      <c r="C50" s="20" t="n"/>
+      <c r="D50" s="20" t="n"/>
+      <c r="E50" s="20" t="n"/>
+      <c r="F50" s="20" t="n"/>
+      <c r="G50" s="20" t="n"/>
+      <c r="H50" s="20" t="n"/>
+      <c r="I50" s="20" t="n"/>
+      <c r="J50" s="20" t="n"/>
+      <c r="K50" s="20" t="n"/>
+      <c r="L50" s="20" t="n"/>
+      <c r="M50" s="20" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="19" t="n"/>
-      <c r="B51" s="19" t="n"/>
-      <c r="C51" s="19" t="n"/>
-      <c r="D51" s="19" t="n"/>
-      <c r="E51" s="19" t="n"/>
-      <c r="F51" s="19" t="n"/>
-      <c r="G51" s="19" t="n"/>
-      <c r="H51" s="19" t="n"/>
-      <c r="I51" s="19" t="n"/>
-      <c r="J51" s="19" t="n"/>
-      <c r="K51" s="19" t="n"/>
-      <c r="L51" s="19" t="n"/>
-      <c r="M51" s="19" t="n"/>
+      <c r="A51" s="20" t="n"/>
+      <c r="B51" s="20" t="n"/>
+      <c r="C51" s="20" t="n"/>
+      <c r="D51" s="20" t="n"/>
+      <c r="E51" s="20" t="n"/>
+      <c r="F51" s="20" t="n"/>
+      <c r="G51" s="20" t="n"/>
+      <c r="H51" s="20" t="n"/>
+      <c r="I51" s="20" t="n"/>
+      <c r="J51" s="20" t="n"/>
+      <c r="K51" s="20" t="n"/>
+      <c r="L51" s="20" t="n"/>
+      <c r="M51" s="20" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="19" t="n"/>
-      <c r="B52" s="19" t="n"/>
-      <c r="C52" s="19" t="n"/>
-      <c r="D52" s="19" t="n"/>
-      <c r="E52" s="19" t="n"/>
-      <c r="F52" s="19" t="n"/>
-      <c r="G52" s="19" t="n"/>
-      <c r="H52" s="19" t="n"/>
-      <c r="I52" s="19" t="n"/>
-      <c r="J52" s="19" t="n"/>
-      <c r="K52" s="19" t="n"/>
-      <c r="L52" s="19" t="n"/>
-      <c r="M52" s="19" t="n"/>
+      <c r="A52" s="20" t="n"/>
+      <c r="B52" s="20" t="n"/>
+      <c r="C52" s="20" t="n"/>
+      <c r="D52" s="20" t="n"/>
+      <c r="E52" s="20" t="n"/>
+      <c r="F52" s="20" t="n"/>
+      <c r="G52" s="20" t="n"/>
+      <c r="H52" s="20" t="n"/>
+      <c r="I52" s="20" t="n"/>
+      <c r="J52" s="20" t="n"/>
+      <c r="K52" s="20" t="n"/>
+      <c r="L52" s="20" t="n"/>
+      <c r="M52" s="20" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="19" t="n"/>
-      <c r="B53" s="19" t="n"/>
-      <c r="C53" s="19" t="n"/>
-      <c r="D53" s="19" t="n"/>
-      <c r="E53" s="19" t="n"/>
-      <c r="F53" s="19" t="n"/>
-      <c r="G53" s="19" t="n"/>
-      <c r="H53" s="19" t="n"/>
-      <c r="I53" s="19" t="n"/>
-      <c r="J53" s="19" t="n"/>
-      <c r="K53" s="19" t="n"/>
-      <c r="L53" s="19" t="n"/>
-      <c r="M53" s="19" t="n"/>
+      <c r="A53" s="20" t="n"/>
+      <c r="B53" s="20" t="n"/>
+      <c r="C53" s="20" t="n"/>
+      <c r="D53" s="20" t="n"/>
+      <c r="E53" s="20" t="n"/>
+      <c r="F53" s="20" t="n"/>
+      <c r="G53" s="20" t="n"/>
+      <c r="H53" s="20" t="n"/>
+      <c r="I53" s="20" t="n"/>
+      <c r="J53" s="20" t="n"/>
+      <c r="K53" s="20" t="n"/>
+      <c r="L53" s="20" t="n"/>
+      <c r="M53" s="20" t="n"/>
     </row>
     <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="11" t="inlineStr">
+      <c r="A55" s="12" t="inlineStr">
         <is>
           <t>Bagues   (2)</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="12" t="inlineStr">
+      <c r="A56" s="13" t="inlineStr">
         <is>
           <t>Blood Ring</t>
         </is>
       </c>
-      <c r="B56" s="13" t="inlineStr">
+      <c r="B56" s="14" t="inlineStr">
         <is>
           <t>bague-de-sang</t>
         </is>
       </c>
-      <c r="C56" s="17" t="inlineStr">
+      <c r="C56" s="18" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="D56" s="15" t="n">
+      <c r="D56" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="E56" s="16" t="inlineStr">
+      <c r="E56" s="17" t="inlineStr">
         <is>
           <t>Bloodletting</t>
         </is>
       </c>
-      <c r="F56" s="15" t="n">
+      <c r="F56" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="G56" s="16" t="n"/>
-      <c r="H56" s="16" t="n"/>
-      <c r="I56" s="16" t="n"/>
-      <c r="J56" s="16" t="n"/>
-      <c r="K56" s="16" t="n"/>
-      <c r="L56" s="16" t="n"/>
-      <c r="M56" s="16" t="n"/>
+      <c r="G56" s="17" t="n"/>
+      <c r="H56" s="17" t="n"/>
+      <c r="I56" s="17" t="n"/>
+      <c r="J56" s="17" t="n"/>
+      <c r="K56" s="17" t="n"/>
+      <c r="L56" s="17" t="n"/>
+      <c r="M56" s="17" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="12" t="inlineStr">
+      <c r="A57" s="13" t="inlineStr">
         <is>
           <t>Frost Ring</t>
         </is>
       </c>
-      <c r="B57" s="13" t="inlineStr">
+      <c r="B57" s="14" t="inlineStr">
         <is>
           <t>anneau-de-givre</t>
         </is>
       </c>
-      <c r="C57" s="17" t="inlineStr">
+      <c r="C57" s="18" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="D57" s="15" t="n">
+      <c r="D57" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="E57" s="16" t="inlineStr">
+      <c r="E57" s="17" t="inlineStr">
         <is>
           <t>Frostbite</t>
         </is>
       </c>
-      <c r="F57" s="15" t="n">
+      <c r="F57" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="G57" s="16" t="n"/>
-      <c r="H57" s="16" t="n"/>
-      <c r="I57" s="16" t="n"/>
-      <c r="J57" s="16" t="n"/>
-      <c r="K57" s="16" t="n"/>
-      <c r="L57" s="16" t="n"/>
-      <c r="M57" s="16" t="n"/>
+      <c r="G57" s="17" t="n"/>
+      <c r="H57" s="17" t="n"/>
+      <c r="I57" s="17" t="n"/>
+      <c r="J57" s="17" t="n"/>
+      <c r="K57" s="17" t="n"/>
+      <c r="L57" s="17" t="n"/>
+      <c r="M57" s="17" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="19" t="n"/>
-      <c r="B58" s="19" t="n"/>
-      <c r="C58" s="19" t="n"/>
-      <c r="D58" s="19" t="n"/>
-      <c r="E58" s="19" t="n"/>
-      <c r="F58" s="19" t="n"/>
-      <c r="G58" s="19" t="n"/>
-      <c r="H58" s="19" t="n"/>
-      <c r="I58" s="19" t="n"/>
-      <c r="J58" s="19" t="n"/>
-      <c r="K58" s="19" t="n"/>
-      <c r="L58" s="19" t="n"/>
-      <c r="M58" s="19" t="n"/>
+      <c r="A58" s="20" t="n"/>
+      <c r="B58" s="20" t="n"/>
+      <c r="C58" s="20" t="n"/>
+      <c r="D58" s="20" t="n"/>
+      <c r="E58" s="20" t="n"/>
+      <c r="F58" s="20" t="n"/>
+      <c r="G58" s="20" t="n"/>
+      <c r="H58" s="20" t="n"/>
+      <c r="I58" s="20" t="n"/>
+      <c r="J58" s="20" t="n"/>
+      <c r="K58" s="20" t="n"/>
+      <c r="L58" s="20" t="n"/>
+      <c r="M58" s="20" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="19" t="n"/>
-      <c r="B59" s="19" t="n"/>
-      <c r="C59" s="19" t="n"/>
-      <c r="D59" s="19" t="n"/>
-      <c r="E59" s="19" t="n"/>
-      <c r="F59" s="19" t="n"/>
-      <c r="G59" s="19" t="n"/>
-      <c r="H59" s="19" t="n"/>
-      <c r="I59" s="19" t="n"/>
-      <c r="J59" s="19" t="n"/>
-      <c r="K59" s="19" t="n"/>
-      <c r="L59" s="19" t="n"/>
-      <c r="M59" s="19" t="n"/>
+      <c r="A59" s="20" t="n"/>
+      <c r="B59" s="20" t="n"/>
+      <c r="C59" s="20" t="n"/>
+      <c r="D59" s="20" t="n"/>
+      <c r="E59" s="20" t="n"/>
+      <c r="F59" s="20" t="n"/>
+      <c r="G59" s="20" t="n"/>
+      <c r="H59" s="20" t="n"/>
+      <c r="I59" s="20" t="n"/>
+      <c r="J59" s="20" t="n"/>
+      <c r="K59" s="20" t="n"/>
+      <c r="L59" s="20" t="n"/>
+      <c r="M59" s="20" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="19" t="n"/>
-      <c r="B60" s="19" t="n"/>
-      <c r="C60" s="19" t="n"/>
-      <c r="D60" s="19" t="n"/>
-      <c r="E60" s="19" t="n"/>
-      <c r="F60" s="19" t="n"/>
-      <c r="G60" s="19" t="n"/>
-      <c r="H60" s="19" t="n"/>
-      <c r="I60" s="19" t="n"/>
-      <c r="J60" s="19" t="n"/>
-      <c r="K60" s="19" t="n"/>
-      <c r="L60" s="19" t="n"/>
-      <c r="M60" s="19" t="n"/>
+      <c r="A60" s="20" t="n"/>
+      <c r="B60" s="20" t="n"/>
+      <c r="C60" s="20" t="n"/>
+      <c r="D60" s="20" t="n"/>
+      <c r="E60" s="20" t="n"/>
+      <c r="F60" s="20" t="n"/>
+      <c r="G60" s="20" t="n"/>
+      <c r="H60" s="20" t="n"/>
+      <c r="I60" s="20" t="n"/>
+      <c r="J60" s="20" t="n"/>
+      <c r="K60" s="20" t="n"/>
+      <c r="L60" s="20" t="n"/>
+      <c r="M60" s="20" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="19" t="n"/>
-      <c r="B61" s="19" t="n"/>
-      <c r="C61" s="19" t="n"/>
-      <c r="D61" s="19" t="n"/>
-      <c r="E61" s="19" t="n"/>
-      <c r="F61" s="19" t="n"/>
-      <c r="G61" s="19" t="n"/>
-      <c r="H61" s="19" t="n"/>
-      <c r="I61" s="19" t="n"/>
-      <c r="J61" s="19" t="n"/>
-      <c r="K61" s="19" t="n"/>
-      <c r="L61" s="19" t="n"/>
-      <c r="M61" s="19" t="n"/>
+      <c r="A61" s="20" t="n"/>
+      <c r="B61" s="20" t="n"/>
+      <c r="C61" s="20" t="n"/>
+      <c r="D61" s="20" t="n"/>
+      <c r="E61" s="20" t="n"/>
+      <c r="F61" s="20" t="n"/>
+      <c r="G61" s="20" t="n"/>
+      <c r="H61" s="20" t="n"/>
+      <c r="I61" s="20" t="n"/>
+      <c r="J61" s="20" t="n"/>
+      <c r="K61" s="20" t="n"/>
+      <c r="L61" s="20" t="n"/>
+      <c r="M61" s="20" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="19" t="n"/>
-      <c r="B62" s="19" t="n"/>
-      <c r="C62" s="19" t="n"/>
-      <c r="D62" s="19" t="n"/>
-      <c r="E62" s="19" t="n"/>
-      <c r="F62" s="19" t="n"/>
-      <c r="G62" s="19" t="n"/>
-      <c r="H62" s="19" t="n"/>
-      <c r="I62" s="19" t="n"/>
-      <c r="J62" s="19" t="n"/>
-      <c r="K62" s="19" t="n"/>
-      <c r="L62" s="19" t="n"/>
-      <c r="M62" s="19" t="n"/>
+      <c r="A62" s="20" t="n"/>
+      <c r="B62" s="20" t="n"/>
+      <c r="C62" s="20" t="n"/>
+      <c r="D62" s="20" t="n"/>
+      <c r="E62" s="20" t="n"/>
+      <c r="F62" s="20" t="n"/>
+      <c r="G62" s="20" t="n"/>
+      <c r="H62" s="20" t="n"/>
+      <c r="I62" s="20" t="n"/>
+      <c r="J62" s="20" t="n"/>
+      <c r="K62" s="20" t="n"/>
+      <c r="L62" s="20" t="n"/>
+      <c r="M62" s="20" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="19" t="n"/>
-      <c r="B63" s="19" t="n"/>
-      <c r="C63" s="19" t="n"/>
-      <c r="D63" s="19" t="n"/>
-      <c r="E63" s="19" t="n"/>
-      <c r="F63" s="19" t="n"/>
-      <c r="G63" s="19" t="n"/>
-      <c r="H63" s="19" t="n"/>
-      <c r="I63" s="19" t="n"/>
-      <c r="J63" s="19" t="n"/>
-      <c r="K63" s="19" t="n"/>
-      <c r="L63" s="19" t="n"/>
-      <c r="M63" s="19" t="n"/>
+      <c r="A63" s="20" t="n"/>
+      <c r="B63" s="20" t="n"/>
+      <c r="C63" s="20" t="n"/>
+      <c r="D63" s="20" t="n"/>
+      <c r="E63" s="20" t="n"/>
+      <c r="F63" s="20" t="n"/>
+      <c r="G63" s="20" t="n"/>
+      <c r="H63" s="20" t="n"/>
+      <c r="I63" s="20" t="n"/>
+      <c r="J63" s="20" t="n"/>
+      <c r="K63" s="20" t="n"/>
+      <c r="L63" s="20" t="n"/>
+      <c r="M63" s="20" t="n"/>
     </row>
     <row r="65" ht="20" customHeight="1">
-      <c r="A65" s="11" t="inlineStr">
+      <c r="A65" s="12" t="inlineStr">
         <is>
           <t>Gants   (1)</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="12" t="inlineStr">
+      <c r="A66" s="13" t="inlineStr">
         <is>
           <t>Miner's Gloves</t>
         </is>
       </c>
-      <c r="B66" s="13" t="inlineStr">
+      <c r="B66" s="14" t="inlineStr">
         <is>
           <t>gants-de-mineur</t>
         </is>
       </c>
-      <c r="C66" s="14" t="inlineStr">
+      <c r="C66" s="15" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="D66" s="15" t="n">
+      <c r="D66" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="E66" s="16" t="n"/>
-      <c r="F66" s="16" t="n"/>
-      <c r="G66" s="16" t="n"/>
-      <c r="H66" s="16" t="n"/>
-      <c r="I66" s="16" t="n"/>
-      <c r="J66" s="16" t="n"/>
-      <c r="K66" s="16" t="n"/>
-      <c r="L66" s="16" t="n"/>
-      <c r="M66" s="16" t="n"/>
+      <c r="E66" s="17" t="n"/>
+      <c r="F66" s="17" t="n"/>
+      <c r="G66" s="17" t="n"/>
+      <c r="H66" s="17" t="n"/>
+      <c r="I66" s="17" t="n"/>
+      <c r="J66" s="17" t="n"/>
+      <c r="K66" s="17" t="n"/>
+      <c r="L66" s="17" t="n"/>
+      <c r="M66" s="17" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="19" t="n"/>
-      <c r="B67" s="19" t="n"/>
-      <c r="C67" s="19" t="n"/>
-      <c r="D67" s="19" t="n"/>
-      <c r="E67" s="19" t="n"/>
-      <c r="F67" s="19" t="n"/>
-      <c r="G67" s="19" t="n"/>
-      <c r="H67" s="19" t="n"/>
-      <c r="I67" s="19" t="n"/>
-      <c r="J67" s="19" t="n"/>
-      <c r="K67" s="19" t="n"/>
-      <c r="L67" s="19" t="n"/>
-      <c r="M67" s="19" t="n"/>
+      <c r="A67" s="20" t="n"/>
+      <c r="B67" s="20" t="n"/>
+      <c r="C67" s="20" t="n"/>
+      <c r="D67" s="20" t="n"/>
+      <c r="E67" s="20" t="n"/>
+      <c r="F67" s="20" t="n"/>
+      <c r="G67" s="20" t="n"/>
+      <c r="H67" s="20" t="n"/>
+      <c r="I67" s="20" t="n"/>
+      <c r="J67" s="20" t="n"/>
+      <c r="K67" s="20" t="n"/>
+      <c r="L67" s="20" t="n"/>
+      <c r="M67" s="20" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="19" t="n"/>
-      <c r="B68" s="19" t="n"/>
-      <c r="C68" s="19" t="n"/>
-      <c r="D68" s="19" t="n"/>
-      <c r="E68" s="19" t="n"/>
-      <c r="F68" s="19" t="n"/>
-      <c r="G68" s="19" t="n"/>
-      <c r="H68" s="19" t="n"/>
-      <c r="I68" s="19" t="n"/>
-      <c r="J68" s="19" t="n"/>
-      <c r="K68" s="19" t="n"/>
-      <c r="L68" s="19" t="n"/>
-      <c r="M68" s="19" t="n"/>
+      <c r="A68" s="20" t="n"/>
+      <c r="B68" s="20" t="n"/>
+      <c r="C68" s="20" t="n"/>
+      <c r="D68" s="20" t="n"/>
+      <c r="E68" s="20" t="n"/>
+      <c r="F68" s="20" t="n"/>
+      <c r="G68" s="20" t="n"/>
+      <c r="H68" s="20" t="n"/>
+      <c r="I68" s="20" t="n"/>
+      <c r="J68" s="20" t="n"/>
+      <c r="K68" s="20" t="n"/>
+      <c r="L68" s="20" t="n"/>
+      <c r="M68" s="20" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="19" t="n"/>
-      <c r="B69" s="19" t="n"/>
-      <c r="C69" s="19" t="n"/>
-      <c r="D69" s="19" t="n"/>
-      <c r="E69" s="19" t="n"/>
-      <c r="F69" s="19" t="n"/>
-      <c r="G69" s="19" t="n"/>
-      <c r="H69" s="19" t="n"/>
-      <c r="I69" s="19" t="n"/>
-      <c r="J69" s="19" t="n"/>
-      <c r="K69" s="19" t="n"/>
-      <c r="L69" s="19" t="n"/>
-      <c r="M69" s="19" t="n"/>
+      <c r="A69" s="20" t="n"/>
+      <c r="B69" s="20" t="n"/>
+      <c r="C69" s="20" t="n"/>
+      <c r="D69" s="20" t="n"/>
+      <c r="E69" s="20" t="n"/>
+      <c r="F69" s="20" t="n"/>
+      <c r="G69" s="20" t="n"/>
+      <c r="H69" s="20" t="n"/>
+      <c r="I69" s="20" t="n"/>
+      <c r="J69" s="20" t="n"/>
+      <c r="K69" s="20" t="n"/>
+      <c r="L69" s="20" t="n"/>
+      <c r="M69" s="20" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="19" t="n"/>
-      <c r="B70" s="19" t="n"/>
-      <c r="C70" s="19" t="n"/>
-      <c r="D70" s="19" t="n"/>
-      <c r="E70" s="19" t="n"/>
-      <c r="F70" s="19" t="n"/>
-      <c r="G70" s="19" t="n"/>
-      <c r="H70" s="19" t="n"/>
-      <c r="I70" s="19" t="n"/>
-      <c r="J70" s="19" t="n"/>
-      <c r="K70" s="19" t="n"/>
-      <c r="L70" s="19" t="n"/>
-      <c r="M70" s="19" t="n"/>
+      <c r="A70" s="20" t="n"/>
+      <c r="B70" s="20" t="n"/>
+      <c r="C70" s="20" t="n"/>
+      <c r="D70" s="20" t="n"/>
+      <c r="E70" s="20" t="n"/>
+      <c r="F70" s="20" t="n"/>
+      <c r="G70" s="20" t="n"/>
+      <c r="H70" s="20" t="n"/>
+      <c r="I70" s="20" t="n"/>
+      <c r="J70" s="20" t="n"/>
+      <c r="K70" s="20" t="n"/>
+      <c r="L70" s="20" t="n"/>
+      <c r="M70" s="20" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="19" t="n"/>
-      <c r="B71" s="19" t="n"/>
-      <c r="C71" s="19" t="n"/>
-      <c r="D71" s="19" t="n"/>
-      <c r="E71" s="19" t="n"/>
-      <c r="F71" s="19" t="n"/>
-      <c r="G71" s="19" t="n"/>
-      <c r="H71" s="19" t="n"/>
-      <c r="I71" s="19" t="n"/>
-      <c r="J71" s="19" t="n"/>
-      <c r="K71" s="19" t="n"/>
-      <c r="L71" s="19" t="n"/>
-      <c r="M71" s="19" t="n"/>
+      <c r="A71" s="20" t="n"/>
+      <c r="B71" s="20" t="n"/>
+      <c r="C71" s="20" t="n"/>
+      <c r="D71" s="20" t="n"/>
+      <c r="E71" s="20" t="n"/>
+      <c r="F71" s="20" t="n"/>
+      <c r="G71" s="20" t="n"/>
+      <c r="H71" s="20" t="n"/>
+      <c r="I71" s="20" t="n"/>
+      <c r="J71" s="20" t="n"/>
+      <c r="K71" s="20" t="n"/>
+      <c r="L71" s="20" t="n"/>
+      <c r="M71" s="20" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="19" t="n"/>
-      <c r="B72" s="19" t="n"/>
-      <c r="C72" s="19" t="n"/>
-      <c r="D72" s="19" t="n"/>
-      <c r="E72" s="19" t="n"/>
-      <c r="F72" s="19" t="n"/>
-      <c r="G72" s="19" t="n"/>
-      <c r="H72" s="19" t="n"/>
-      <c r="I72" s="19" t="n"/>
-      <c r="J72" s="19" t="n"/>
-      <c r="K72" s="19" t="n"/>
-      <c r="L72" s="19" t="n"/>
-      <c r="M72" s="19" t="n"/>
+      <c r="A72" s="20" t="n"/>
+      <c r="B72" s="20" t="n"/>
+      <c r="C72" s="20" t="n"/>
+      <c r="D72" s="20" t="n"/>
+      <c r="E72" s="20" t="n"/>
+      <c r="F72" s="20" t="n"/>
+      <c r="G72" s="20" t="n"/>
+      <c r="H72" s="20" t="n"/>
+      <c r="I72" s="20" t="n"/>
+      <c r="J72" s="20" t="n"/>
+      <c r="K72" s="20" t="n"/>
+      <c r="L72" s="20" t="n"/>
+      <c r="M72" s="20" t="n"/>
     </row>
     <row r="74" ht="20" customHeight="1">
-      <c r="A74" s="11" t="inlineStr">
+      <c r="A74" s="12" t="inlineStr">
         <is>
           <t>Bottes   (1)</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="12" t="inlineStr">
+      <c r="A75" s="13" t="inlineStr">
         <is>
           <t>Swift Boots</t>
         </is>
       </c>
-      <c r="B75" s="13" t="inlineStr">
+      <c r="B75" s="14" t="inlineStr">
         <is>
           <t>bottes-vives</t>
         </is>
       </c>
-      <c r="C75" s="17" t="inlineStr">
+      <c r="C75" s="18" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="D75" s="15" t="n">
+      <c r="D75" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="E75" s="16" t="inlineStr">
+      <c r="E75" s="17" t="inlineStr">
         <is>
           <t>Quicken</t>
         </is>
       </c>
-      <c r="F75" s="15" t="n">
+      <c r="F75" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="G75" s="16" t="n"/>
-      <c r="H75" s="16" t="n"/>
-      <c r="I75" s="16" t="n"/>
-      <c r="J75" s="16" t="n"/>
-      <c r="K75" s="16" t="n"/>
-      <c r="L75" s="16" t="n"/>
-      <c r="M75" s="16" t="n"/>
+      <c r="G75" s="17" t="n"/>
+      <c r="H75" s="17" t="n"/>
+      <c r="I75" s="17" t="n"/>
+      <c r="J75" s="17" t="n"/>
+      <c r="K75" s="17" t="n"/>
+      <c r="L75" s="17" t="n"/>
+      <c r="M75" s="17" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="19" t="n"/>
-      <c r="B76" s="19" t="n"/>
-      <c r="C76" s="19" t="n"/>
-      <c r="D76" s="19" t="n"/>
-      <c r="E76" s="19" t="n"/>
-      <c r="F76" s="19" t="n"/>
-      <c r="G76" s="19" t="n"/>
-      <c r="H76" s="19" t="n"/>
-      <c r="I76" s="19" t="n"/>
-      <c r="J76" s="19" t="n"/>
-      <c r="K76" s="19" t="n"/>
-      <c r="L76" s="19" t="n"/>
-      <c r="M76" s="19" t="n"/>
+      <c r="A76" s="20" t="n"/>
+      <c r="B76" s="20" t="n"/>
+      <c r="C76" s="20" t="n"/>
+      <c r="D76" s="20" t="n"/>
+      <c r="E76" s="20" t="n"/>
+      <c r="F76" s="20" t="n"/>
+      <c r="G76" s="20" t="n"/>
+      <c r="H76" s="20" t="n"/>
+      <c r="I76" s="20" t="n"/>
+      <c r="J76" s="20" t="n"/>
+      <c r="K76" s="20" t="n"/>
+      <c r="L76" s="20" t="n"/>
+      <c r="M76" s="20" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="19" t="n"/>
-      <c r="B77" s="19" t="n"/>
-      <c r="C77" s="19" t="n"/>
-      <c r="D77" s="19" t="n"/>
-      <c r="E77" s="19" t="n"/>
-      <c r="F77" s="19" t="n"/>
-      <c r="G77" s="19" t="n"/>
-      <c r="H77" s="19" t="n"/>
-      <c r="I77" s="19" t="n"/>
-      <c r="J77" s="19" t="n"/>
-      <c r="K77" s="19" t="n"/>
-      <c r="L77" s="19" t="n"/>
-      <c r="M77" s="19" t="n"/>
+      <c r="A77" s="20" t="n"/>
+      <c r="B77" s="20" t="n"/>
+      <c r="C77" s="20" t="n"/>
+      <c r="D77" s="20" t="n"/>
+      <c r="E77" s="20" t="n"/>
+      <c r="F77" s="20" t="n"/>
+      <c r="G77" s="20" t="n"/>
+      <c r="H77" s="20" t="n"/>
+      <c r="I77" s="20" t="n"/>
+      <c r="J77" s="20" t="n"/>
+      <c r="K77" s="20" t="n"/>
+      <c r="L77" s="20" t="n"/>
+      <c r="M77" s="20" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="19" t="n"/>
-      <c r="B78" s="19" t="n"/>
-      <c r="C78" s="19" t="n"/>
-      <c r="D78" s="19" t="n"/>
-      <c r="E78" s="19" t="n"/>
-      <c r="F78" s="19" t="n"/>
-      <c r="G78" s="19" t="n"/>
-      <c r="H78" s="19" t="n"/>
-      <c r="I78" s="19" t="n"/>
-      <c r="J78" s="19" t="n"/>
-      <c r="K78" s="19" t="n"/>
-      <c r="L78" s="19" t="n"/>
-      <c r="M78" s="19" t="n"/>
+      <c r="A78" s="20" t="n"/>
+      <c r="B78" s="20" t="n"/>
+      <c r="C78" s="20" t="n"/>
+      <c r="D78" s="20" t="n"/>
+      <c r="E78" s="20" t="n"/>
+      <c r="F78" s="20" t="n"/>
+      <c r="G78" s="20" t="n"/>
+      <c r="H78" s="20" t="n"/>
+      <c r="I78" s="20" t="n"/>
+      <c r="J78" s="20" t="n"/>
+      <c r="K78" s="20" t="n"/>
+      <c r="L78" s="20" t="n"/>
+      <c r="M78" s="20" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="19" t="n"/>
-      <c r="B79" s="19" t="n"/>
-      <c r="C79" s="19" t="n"/>
-      <c r="D79" s="19" t="n"/>
-      <c r="E79" s="19" t="n"/>
-      <c r="F79" s="19" t="n"/>
-      <c r="G79" s="19" t="n"/>
-      <c r="H79" s="19" t="n"/>
-      <c r="I79" s="19" t="n"/>
-      <c r="J79" s="19" t="n"/>
-      <c r="K79" s="19" t="n"/>
-      <c r="L79" s="19" t="n"/>
-      <c r="M79" s="19" t="n"/>
+      <c r="A79" s="20" t="n"/>
+      <c r="B79" s="20" t="n"/>
+      <c r="C79" s="20" t="n"/>
+      <c r="D79" s="20" t="n"/>
+      <c r="E79" s="20" t="n"/>
+      <c r="F79" s="20" t="n"/>
+      <c r="G79" s="20" t="n"/>
+      <c r="H79" s="20" t="n"/>
+      <c r="I79" s="20" t="n"/>
+      <c r="J79" s="20" t="n"/>
+      <c r="K79" s="20" t="n"/>
+      <c r="L79" s="20" t="n"/>
+      <c r="M79" s="20" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="19" t="n"/>
-      <c r="B80" s="19" t="n"/>
-      <c r="C80" s="19" t="n"/>
-      <c r="D80" s="19" t="n"/>
-      <c r="E80" s="19" t="n"/>
-      <c r="F80" s="19" t="n"/>
-      <c r="G80" s="19" t="n"/>
-      <c r="H80" s="19" t="n"/>
-      <c r="I80" s="19" t="n"/>
-      <c r="J80" s="19" t="n"/>
-      <c r="K80" s="19" t="n"/>
-      <c r="L80" s="19" t="n"/>
-      <c r="M80" s="19" t="n"/>
+      <c r="A80" s="20" t="n"/>
+      <c r="B80" s="20" t="n"/>
+      <c r="C80" s="20" t="n"/>
+      <c r="D80" s="20" t="n"/>
+      <c r="E80" s="20" t="n"/>
+      <c r="F80" s="20" t="n"/>
+      <c r="G80" s="20" t="n"/>
+      <c r="H80" s="20" t="n"/>
+      <c r="I80" s="20" t="n"/>
+      <c r="J80" s="20" t="n"/>
+      <c r="K80" s="20" t="n"/>
+      <c r="L80" s="20" t="n"/>
+      <c r="M80" s="20" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="19" t="n"/>
-      <c r="B81" s="19" t="n"/>
-      <c r="C81" s="19" t="n"/>
-      <c r="D81" s="19" t="n"/>
-      <c r="E81" s="19" t="n"/>
-      <c r="F81" s="19" t="n"/>
-      <c r="G81" s="19" t="n"/>
-      <c r="H81" s="19" t="n"/>
-      <c r="I81" s="19" t="n"/>
-      <c r="J81" s="19" t="n"/>
-      <c r="K81" s="19" t="n"/>
-      <c r="L81" s="19" t="n"/>
-      <c r="M81" s="19" t="n"/>
+      <c r="A81" s="20" t="n"/>
+      <c r="B81" s="20" t="n"/>
+      <c r="C81" s="20" t="n"/>
+      <c r="D81" s="20" t="n"/>
+      <c r="E81" s="20" t="n"/>
+      <c r="F81" s="20" t="n"/>
+      <c r="G81" s="20" t="n"/>
+      <c r="H81" s="20" t="n"/>
+      <c r="I81" s="20" t="n"/>
+      <c r="J81" s="20" t="n"/>
+      <c r="K81" s="20" t="n"/>
+      <c r="L81" s="20" t="n"/>
+      <c r="M81" s="20" t="n"/>
     </row>
     <row r="83" ht="20" customHeight="1">
-      <c r="A83" s="11" t="inlineStr">
+      <c r="A83" s="12" t="inlineStr">
         <is>
           <t>Sacs   (1)</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="12" t="inlineStr">
+      <c r="A84" s="13" t="inlineStr">
         <is>
           <t>Leather Pouch</t>
         </is>
       </c>
-      <c r="B84" s="13" t="inlineStr">
+      <c r="B84" s="14" t="inlineStr">
         <is>
           <t>sac-en-cuir</t>
         </is>
       </c>
-      <c r="C84" s="14" t="inlineStr">
+      <c r="C84" s="15" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="D84" s="15" t="n">
+      <c r="D84" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="E84" s="16" t="n"/>
-      <c r="F84" s="16" t="n"/>
-      <c r="G84" s="16" t="n"/>
-      <c r="H84" s="16" t="n"/>
-      <c r="I84" s="16" t="n"/>
-      <c r="J84" s="16" t="n"/>
-      <c r="K84" s="16" t="n"/>
-      <c r="L84" s="16" t="n"/>
-      <c r="M84" s="16" t="n"/>
+      <c r="E84" s="17" t="n"/>
+      <c r="F84" s="17" t="n"/>
+      <c r="G84" s="17" t="n"/>
+      <c r="H84" s="17" t="n"/>
+      <c r="I84" s="17" t="n"/>
+      <c r="J84" s="17" t="n"/>
+      <c r="K84" s="17" t="n"/>
+      <c r="L84" s="17" t="n"/>
+      <c r="M84" s="17" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="19" t="n"/>
-      <c r="B85" s="19" t="n"/>
-      <c r="C85" s="19" t="n"/>
-      <c r="D85" s="19" t="n"/>
-      <c r="E85" s="19" t="n"/>
-      <c r="F85" s="19" t="n"/>
-      <c r="G85" s="19" t="n"/>
-      <c r="H85" s="19" t="n"/>
-      <c r="I85" s="19" t="n"/>
-      <c r="J85" s="19" t="n"/>
-      <c r="K85" s="19" t="n"/>
-      <c r="L85" s="19" t="n"/>
-      <c r="M85" s="19" t="n"/>
+      <c r="A85" s="20" t="n"/>
+      <c r="B85" s="20" t="n"/>
+      <c r="C85" s="20" t="n"/>
+      <c r="D85" s="20" t="n"/>
+      <c r="E85" s="20" t="n"/>
+      <c r="F85" s="20" t="n"/>
+      <c r="G85" s="20" t="n"/>
+      <c r="H85" s="20" t="n"/>
+      <c r="I85" s="20" t="n"/>
+      <c r="J85" s="20" t="n"/>
+      <c r="K85" s="20" t="n"/>
+      <c r="L85" s="20" t="n"/>
+      <c r="M85" s="20" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="19" t="n"/>
-      <c r="B86" s="19" t="n"/>
-      <c r="C86" s="19" t="n"/>
-      <c r="D86" s="19" t="n"/>
-      <c r="E86" s="19" t="n"/>
-      <c r="F86" s="19" t="n"/>
-      <c r="G86" s="19" t="n"/>
-      <c r="H86" s="19" t="n"/>
-      <c r="I86" s="19" t="n"/>
-      <c r="J86" s="19" t="n"/>
-      <c r="K86" s="19" t="n"/>
-      <c r="L86" s="19" t="n"/>
-      <c r="M86" s="19" t="n"/>
+      <c r="A86" s="20" t="n"/>
+      <c r="B86" s="20" t="n"/>
+      <c r="C86" s="20" t="n"/>
+      <c r="D86" s="20" t="n"/>
+      <c r="E86" s="20" t="n"/>
+      <c r="F86" s="20" t="n"/>
+      <c r="G86" s="20" t="n"/>
+      <c r="H86" s="20" t="n"/>
+      <c r="I86" s="20" t="n"/>
+      <c r="J86" s="20" t="n"/>
+      <c r="K86" s="20" t="n"/>
+      <c r="L86" s="20" t="n"/>
+      <c r="M86" s="20" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="19" t="n"/>
-      <c r="B87" s="19" t="n"/>
-      <c r="C87" s="19" t="n"/>
-      <c r="D87" s="19" t="n"/>
-      <c r="E87" s="19" t="n"/>
-      <c r="F87" s="19" t="n"/>
-      <c r="G87" s="19" t="n"/>
-      <c r="H87" s="19" t="n"/>
-      <c r="I87" s="19" t="n"/>
-      <c r="J87" s="19" t="n"/>
-      <c r="K87" s="19" t="n"/>
-      <c r="L87" s="19" t="n"/>
-      <c r="M87" s="19" t="n"/>
+      <c r="A87" s="20" t="n"/>
+      <c r="B87" s="20" t="n"/>
+      <c r="C87" s="20" t="n"/>
+      <c r="D87" s="20" t="n"/>
+      <c r="E87" s="20" t="n"/>
+      <c r="F87" s="20" t="n"/>
+      <c r="G87" s="20" t="n"/>
+      <c r="H87" s="20" t="n"/>
+      <c r="I87" s="20" t="n"/>
+      <c r="J87" s="20" t="n"/>
+      <c r="K87" s="20" t="n"/>
+      <c r="L87" s="20" t="n"/>
+      <c r="M87" s="20" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="19" t="n"/>
-      <c r="B88" s="19" t="n"/>
-      <c r="C88" s="19" t="n"/>
-      <c r="D88" s="19" t="n"/>
-      <c r="E88" s="19" t="n"/>
-      <c r="F88" s="19" t="n"/>
-      <c r="G88" s="19" t="n"/>
-      <c r="H88" s="19" t="n"/>
-      <c r="I88" s="19" t="n"/>
-      <c r="J88" s="19" t="n"/>
-      <c r="K88" s="19" t="n"/>
-      <c r="L88" s="19" t="n"/>
-      <c r="M88" s="19" t="n"/>
+      <c r="A88" s="20" t="n"/>
+      <c r="B88" s="20" t="n"/>
+      <c r="C88" s="20" t="n"/>
+      <c r="D88" s="20" t="n"/>
+      <c r="E88" s="20" t="n"/>
+      <c r="F88" s="20" t="n"/>
+      <c r="G88" s="20" t="n"/>
+      <c r="H88" s="20" t="n"/>
+      <c r="I88" s="20" t="n"/>
+      <c r="J88" s="20" t="n"/>
+      <c r="K88" s="20" t="n"/>
+      <c r="L88" s="20" t="n"/>
+      <c r="M88" s="20" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" s="19" t="n"/>
-      <c r="B89" s="19" t="n"/>
-      <c r="C89" s="19" t="n"/>
-      <c r="D89" s="19" t="n"/>
-      <c r="E89" s="19" t="n"/>
-      <c r="F89" s="19" t="n"/>
-      <c r="G89" s="19" t="n"/>
-      <c r="H89" s="19" t="n"/>
-      <c r="I89" s="19" t="n"/>
-      <c r="J89" s="19" t="n"/>
-      <c r="K89" s="19" t="n"/>
-      <c r="L89" s="19" t="n"/>
-      <c r="M89" s="19" t="n"/>
+      <c r="A89" s="20" t="n"/>
+      <c r="B89" s="20" t="n"/>
+      <c r="C89" s="20" t="n"/>
+      <c r="D89" s="20" t="n"/>
+      <c r="E89" s="20" t="n"/>
+      <c r="F89" s="20" t="n"/>
+      <c r="G89" s="20" t="n"/>
+      <c r="H89" s="20" t="n"/>
+      <c r="I89" s="20" t="n"/>
+      <c r="J89" s="20" t="n"/>
+      <c r="K89" s="20" t="n"/>
+      <c r="L89" s="20" t="n"/>
+      <c r="M89" s="20" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="19" t="n"/>
-      <c r="B90" s="19" t="n"/>
-      <c r="C90" s="19" t="n"/>
-      <c r="D90" s="19" t="n"/>
-      <c r="E90" s="19" t="n"/>
-      <c r="F90" s="19" t="n"/>
-      <c r="G90" s="19" t="n"/>
-      <c r="H90" s="19" t="n"/>
-      <c r="I90" s="19" t="n"/>
-      <c r="J90" s="19" t="n"/>
-      <c r="K90" s="19" t="n"/>
-      <c r="L90" s="19" t="n"/>
-      <c r="M90" s="19" t="n"/>
+      <c r="A90" s="20" t="n"/>
+      <c r="B90" s="20" t="n"/>
+      <c r="C90" s="20" t="n"/>
+      <c r="D90" s="20" t="n"/>
+      <c r="E90" s="20" t="n"/>
+      <c r="F90" s="20" t="n"/>
+      <c r="G90" s="20" t="n"/>
+      <c r="H90" s="20" t="n"/>
+      <c r="I90" s="20" t="n"/>
+      <c r="J90" s="20" t="n"/>
+      <c r="K90" s="20" t="n"/>
+      <c r="L90" s="20" t="n"/>
+      <c r="M90" s="20" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -2293,769 +2308,769 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>BRUTAL — Cartes existantes (référence pour composer des items)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>Nom</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C2" s="11" t="inlineStr">
         <is>
           <t>Coût (Chaleur)</t>
         </is>
       </c>
-      <c r="D2" s="10" t="inlineStr">
+      <c r="D2" s="11" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>AOE</t>
         </is>
       </c>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="F2" s="11" t="inlineStr">
         <is>
           <t>Donnée par</t>
         </is>
       </c>
-      <c r="G2" s="10" t="inlineStr">
+      <c r="G2" s="11" t="inlineStr">
         <is>
           <t>Effet</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="20" t="inlineStr">
+      <c r="A3" s="21" t="inlineStr">
         <is>
           <t>Bloodletting</t>
         </is>
       </c>
-      <c r="B3" s="21" t="inlineStr">
+      <c r="B3" s="22" t="inlineStr">
         <is>
           <t>coup-de-sang</t>
         </is>
       </c>
-      <c r="C3" s="15" t="n">
+      <c r="C3" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="22" t="inlineStr">
+      <c r="D3" s="23" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E3" s="15" t="inlineStr"/>
-      <c r="F3" s="16" t="inlineStr">
+      <c r="E3" s="16" t="inlineStr"/>
+      <c r="F3" s="17" t="inlineStr">
         <is>
           <t>Blood Ring</t>
         </is>
       </c>
-      <c r="G3" s="16" t="inlineStr">
+      <c r="G3" s="17" t="inlineStr">
         <is>
           <t>Deal 2 damage. Apply 2 Bleed (heals you each tick).</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="20" t="inlineStr">
+      <c r="A4" s="21" t="inlineStr">
         <is>
           <t>Cleave</t>
         </is>
       </c>
-      <c r="B4" s="21" t="inlineStr">
+      <c r="B4" s="22" t="inlineStr">
         <is>
           <t>couper-en-deux</t>
         </is>
       </c>
-      <c r="C4" s="15" t="n">
+      <c r="C4" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D4" s="22" t="inlineStr">
+      <c r="D4" s="23" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E4" s="15" t="inlineStr"/>
-      <c r="F4" s="16" t="inlineStr">
+      <c r="E4" s="16" t="inlineStr"/>
+      <c r="F4" s="17" t="inlineStr">
         <is>
           <t>War Axe</t>
         </is>
       </c>
-      <c r="G4" s="16" t="inlineStr">
+      <c r="G4" s="17" t="inlineStr">
         <is>
           <t>Deal 12 damage. If the target dies, deal 12 damage to the next enemy.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="20" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>Dragon's Blaze</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>embrasement-dragon</t>
         </is>
       </c>
-      <c r="C5" s="15" t="n">
+      <c r="C5" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="D5" s="22" t="inlineStr">
+      <c r="D5" s="23" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E5" s="15" t="inlineStr">
+      <c r="E5" s="16" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="F5" s="16" t="inlineStr">
+      <c r="F5" s="17" t="inlineStr">
         <is>
           <t>Onyx Guard Plate</t>
         </is>
       </c>
-      <c r="G5" s="16" t="inlineStr">
+      <c r="G5" s="17" t="inlineStr">
         <is>
           <t>Detonate all Burning: deal 2 damage per Burning on ALL enemies.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="inlineStr">
+      <c r="A6" s="21" t="inlineStr">
         <is>
           <t>Forge Smash</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>ecrasement</t>
         </is>
       </c>
-      <c r="C6" s="15" t="n">
+      <c r="C6" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D6" s="22" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr"/>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="E6" s="16" t="inlineStr"/>
+      <c r="F6" s="17" t="inlineStr">
         <is>
           <t>Forge Hammer</t>
         </is>
       </c>
-      <c r="G6" s="16" t="inlineStr">
+      <c r="G6" s="17" t="inlineStr">
         <is>
           <t>Deal 8 damage. Gain 3 Stone.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="A7" s="21" t="inlineStr">
         <is>
           <t>Frostbite</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>givre-lent</t>
         </is>
       </c>
-      <c r="C7" s="15" t="n">
+      <c r="C7" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="22" t="inlineStr">
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E7" s="15" t="inlineStr"/>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="E7" s="16" t="inlineStr"/>
+      <c r="F7" s="17" t="inlineStr">
         <is>
           <t>Frost Ring</t>
         </is>
       </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="G7" s="17" t="inlineStr">
         <is>
           <t>Deal 2 damage. Chill: -30% speed for 3 turns.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="21" t="inlineStr">
         <is>
           <t>Giant Swing</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>giant-swing</t>
         </is>
       </c>
-      <c r="C8" s="15" t="n">
+      <c r="C8" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="D8" s="22" t="inlineStr">
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E8" s="15" t="inlineStr">
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>War Axe</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="G8" s="17" t="inlineStr">
         <is>
           <t>Deal 9 damage to ALL enemies.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="20" t="inlineStr">
+      <c r="A9" s="21" t="inlineStr">
         <is>
           <t>Lava Hammer</t>
         </is>
       </c>
-      <c r="B9" s="21" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>coup-de-lave</t>
         </is>
       </c>
-      <c r="C9" s="15" t="n">
+      <c r="C9" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D9" s="22" t="inlineStr">
+      <c r="D9" s="23" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E9" s="15" t="inlineStr"/>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="E9" s="16" t="inlineStr"/>
+      <c r="F9" s="17" t="inlineStr">
         <is>
           <t>Magma Hammer</t>
         </is>
       </c>
-      <c r="G9" s="16" t="inlineStr">
+      <c r="G9" s="17" t="inlineStr">
         <is>
           <t>Deal 5 damage. Apply 4 Burning.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="inlineStr">
+      <c r="A10" s="21" t="inlineStr">
         <is>
           <t>Onyx Breath</t>
         </is>
       </c>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>souffle-onyx</t>
         </is>
       </c>
-      <c r="C10" s="15" t="n">
+      <c r="C10" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="D10" s="22" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E10" s="15" t="inlineStr">
+      <c r="E10" s="16" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>Onyx Guard Plate</t>
         </is>
       </c>
-      <c r="G10" s="16" t="inlineStr">
+      <c r="G10" s="17" t="inlineStr">
         <is>
           <t>Apply 8 Burning to ALL enemies.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="20" t="inlineStr">
+      <c r="A11" s="21" t="inlineStr">
         <is>
           <t>Pickaxe Jab</t>
         </is>
       </c>
-      <c r="B11" s="21" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>coup-de-pioche</t>
         </is>
       </c>
-      <c r="C11" s="15" t="n">
+      <c r="C11" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="22" t="inlineStr">
+      <c r="D11" s="23" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E11" s="15" t="inlineStr"/>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="E11" s="16" t="inlineStr"/>
+      <c r="F11" s="17" t="inlineStr">
         <is>
           <t>Miner's Pick</t>
         </is>
       </c>
-      <c r="G11" s="16" t="inlineStr">
+      <c r="G11" s="17" t="inlineStr">
         <is>
           <t>Deal 3 damage twice.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="inlineStr">
+      <c r="A12" s="21" t="inlineStr">
         <is>
           <t>Pommel Strike</t>
         </is>
       </c>
-      <c r="B12" s="21" t="inlineStr">
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>coup-de-pommeau</t>
         </is>
       </c>
-      <c r="C12" s="15" t="n">
+      <c r="C12" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D12" s="22" t="inlineStr">
+      <c r="D12" s="23" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E12" s="15" t="inlineStr"/>
-      <c r="F12" s="16" t="inlineStr">
+      <c r="E12" s="16" t="inlineStr"/>
+      <c r="F12" s="17" t="inlineStr">
         <is>
           <t>War Axe</t>
         </is>
       </c>
-      <c r="G12" s="16" t="inlineStr">
+      <c r="G12" s="17" t="inlineStr">
         <is>
           <t>Deal 4 damage. Stun the target for 1 turn.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="20" t="inlineStr">
+      <c r="A13" s="21" t="inlineStr">
         <is>
           <t>Punch</t>
         </is>
       </c>
-      <c r="B13" s="21" t="inlineStr">
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>coup-faible</t>
         </is>
       </c>
-      <c r="C13" s="15" t="n">
+      <c r="C13" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="22" t="inlineStr">
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E13" s="15" t="inlineStr"/>
-      <c r="F13" s="16" t="inlineStr">
+      <c r="E13" s="16" t="inlineStr"/>
+      <c r="F13" s="17" t="inlineStr">
         <is>
           <t>— (deck de base)</t>
         </is>
       </c>
-      <c r="G13" s="16" t="inlineStr">
+      <c r="G13" s="17" t="inlineStr">
         <is>
           <t>Deal 3 damage.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="inlineStr">
+      <c r="A14" s="21" t="inlineStr">
         <is>
           <t>Rusty Cleave</t>
         </is>
       </c>
-      <c r="B14" s="21" t="inlineStr">
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>coup-de-hache</t>
         </is>
       </c>
-      <c r="C14" s="15" t="n">
+      <c r="C14" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D14" s="22" t="inlineStr">
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E14" s="15" t="inlineStr"/>
-      <c r="F14" s="16" t="inlineStr">
+      <c r="E14" s="16" t="inlineStr"/>
+      <c r="F14" s="17" t="inlineStr">
         <is>
           <t>Rusty Axe</t>
         </is>
       </c>
-      <c r="G14" s="16" t="inlineStr">
+      <c r="G14" s="17" t="inlineStr">
         <is>
           <t>Deal 12 damage.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="20" t="inlineStr">
+      <c r="A15" s="21" t="inlineStr">
         <is>
           <t>Shield Bash</t>
         </is>
       </c>
-      <c r="B15" s="21" t="inlineStr">
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>coup-de-bouclier</t>
         </is>
       </c>
-      <c r="C15" s="15" t="n">
+      <c r="C15" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D15" s="22" t="inlineStr">
+      <c r="D15" s="23" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E15" s="15" t="inlineStr"/>
-      <c r="F15" s="16" t="inlineStr">
+      <c r="E15" s="16" t="inlineStr"/>
+      <c r="F15" s="17" t="inlineStr">
         <is>
           <t>Tower Shield</t>
         </is>
       </c>
-      <c r="G15" s="16" t="inlineStr">
+      <c r="G15" s="17" t="inlineStr">
         <is>
           <t>Deal 3 damage. Stun the enemy for 2 turns.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="20" t="inlineStr">
+      <c r="A16" s="21" t="inlineStr">
         <is>
           <t>Strike</t>
         </is>
       </c>
-      <c r="B16" s="21" t="inlineStr">
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>frappe</t>
         </is>
       </c>
-      <c r="C16" s="15" t="n">
+      <c r="C16" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="22" t="inlineStr">
+      <c r="D16" s="23" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E16" s="15" t="inlineStr"/>
-      <c r="F16" s="16" t="inlineStr">
+      <c r="E16" s="16" t="inlineStr"/>
+      <c r="F16" s="17" t="inlineStr">
         <is>
           <t>— (deck de base)</t>
         </is>
       </c>
-      <c r="G16" s="16" t="inlineStr">
+      <c r="G16" s="17" t="inlineStr">
         <is>
           <t>Deal 6 damage.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="20" t="inlineStr">
+      <c r="A17" s="21" t="inlineStr">
         <is>
           <t>Venom Stab</t>
         </is>
       </c>
-      <c r="B17" s="21" t="inlineStr">
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>coup-venimeux</t>
         </is>
       </c>
-      <c r="C17" s="15" t="n">
+      <c r="C17" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="22" t="inlineStr">
+      <c r="D17" s="23" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E17" s="15" t="inlineStr"/>
-      <c r="F17" s="16" t="inlineStr">
+      <c r="E17" s="16" t="inlineStr"/>
+      <c r="F17" s="17" t="inlineStr">
         <is>
           <t>Basilisk Fang</t>
         </is>
       </c>
-      <c r="G17" s="16" t="inlineStr">
+      <c r="G17" s="17" t="inlineStr">
         <is>
           <t>Deal 4 damage. Apply 4 Poison.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="20" t="inlineStr">
+      <c r="A18" s="21" t="inlineStr">
         <is>
           <t>Guard</t>
         </is>
       </c>
-      <c r="B18" s="21" t="inlineStr">
+      <c r="B18" s="22" t="inlineStr">
         <is>
           <t>garde</t>
         </is>
       </c>
-      <c r="C18" s="15" t="n">
+      <c r="C18" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="23" t="inlineStr">
+      <c r="D18" s="24" t="inlineStr">
         <is>
           <t>Défense</t>
         </is>
       </c>
-      <c r="E18" s="15" t="inlineStr"/>
-      <c r="F18" s="16" t="inlineStr">
+      <c r="E18" s="16" t="inlineStr"/>
+      <c r="F18" s="17" t="inlineStr">
         <is>
           <t>— (deck de base)</t>
         </is>
       </c>
-      <c r="G18" s="16" t="inlineStr">
+      <c r="G18" s="17" t="inlineStr">
         <is>
           <t>Gain 5 Stone.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="20" t="inlineStr">
+      <c r="A19" s="21" t="inlineStr">
         <is>
           <t>Hand Guard</t>
         </is>
       </c>
-      <c r="B19" s="21" t="inlineStr">
+      <c r="B19" s="22" t="inlineStr">
         <is>
           <t>garde-faible</t>
         </is>
       </c>
-      <c r="C19" s="15" t="n">
+      <c r="C19" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="23" t="inlineStr">
+      <c r="D19" s="24" t="inlineStr">
         <is>
           <t>Défense</t>
         </is>
       </c>
-      <c r="E19" s="15" t="inlineStr"/>
-      <c r="F19" s="16" t="inlineStr">
+      <c r="E19" s="16" t="inlineStr"/>
+      <c r="F19" s="17" t="inlineStr">
         <is>
           <t>— (deck de base)</t>
         </is>
       </c>
-      <c r="G19" s="16" t="inlineStr">
+      <c r="G19" s="17" t="inlineStr">
         <is>
           <t>Gain 3 Stone.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="20" t="inlineStr">
+      <c r="A20" s="21" t="inlineStr">
         <is>
           <t>Mail Armor</t>
         </is>
       </c>
-      <c r="B20" s="21" t="inlineStr">
+      <c r="B20" s="22" t="inlineStr">
         <is>
           <t>mail-armor</t>
         </is>
       </c>
-      <c r="C20" s="15" t="n">
+      <c r="C20" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="23" t="inlineStr">
+      <c r="D20" s="24" t="inlineStr">
         <is>
           <t>Défense</t>
         </is>
       </c>
-      <c r="E20" s="15" t="inlineStr"/>
-      <c r="F20" s="16" t="inlineStr">
+      <c r="E20" s="16" t="inlineStr"/>
+      <c r="F20" s="17" t="inlineStr">
         <is>
           <t>Forgemaster's Mail</t>
         </is>
       </c>
-      <c r="G20" s="16" t="inlineStr">
+      <c r="G20" s="17" t="inlineStr">
         <is>
           <t>Gain 5 Stone.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="20" t="inlineStr">
+      <c r="A21" s="21" t="inlineStr">
         <is>
           <t>Onyx Armor</t>
         </is>
       </c>
-      <c r="B21" s="21" t="inlineStr">
+      <c r="B21" s="22" t="inlineStr">
         <is>
           <t>onyx-armor</t>
         </is>
       </c>
-      <c r="C21" s="15" t="n">
+      <c r="C21" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D21" s="23" t="inlineStr">
+      <c r="D21" s="24" t="inlineStr">
         <is>
           <t>Défense</t>
         </is>
       </c>
-      <c r="E21" s="15" t="inlineStr"/>
-      <c r="F21" s="16" t="inlineStr">
+      <c r="E21" s="16" t="inlineStr"/>
+      <c r="F21" s="17" t="inlineStr">
         <is>
           <t>Onyx Guard Plate</t>
         </is>
       </c>
-      <c r="G21" s="16" t="inlineStr">
+      <c r="G21" s="17" t="inlineStr">
         <is>
           <t>Gain 15 Stone.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="20" t="inlineStr">
+      <c r="A22" s="21" t="inlineStr">
         <is>
           <t>Quench</t>
         </is>
       </c>
-      <c r="B22" s="21" t="inlineStr">
+      <c r="B22" s="22" t="inlineStr">
         <is>
           <t>trempe</t>
         </is>
       </c>
-      <c r="C22" s="15" t="n">
+      <c r="C22" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D22" s="23" t="inlineStr">
+      <c r="D22" s="24" t="inlineStr">
         <is>
           <t>Défense</t>
         </is>
       </c>
-      <c r="E22" s="15" t="inlineStr"/>
-      <c r="F22" s="16" t="inlineStr">
+      <c r="E22" s="16" t="inlineStr"/>
+      <c r="F22" s="17" t="inlineStr">
         <is>
           <t>Forgemaster's Mail</t>
         </is>
       </c>
-      <c r="G22" s="16" t="inlineStr">
+      <c r="G22" s="17" t="inlineStr">
         <is>
           <t>Spend all Forge Heat. Gain 4 Stone per Heat spent.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="20" t="inlineStr">
+      <c r="A23" s="21" t="inlineStr">
         <is>
           <t>Shield Wall</t>
         </is>
       </c>
-      <c r="B23" s="21" t="inlineStr">
+      <c r="B23" s="22" t="inlineStr">
         <is>
           <t>mur-bouclier</t>
         </is>
       </c>
-      <c r="C23" s="15" t="n">
+      <c r="C23" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="23" t="inlineStr">
+      <c r="D23" s="24" t="inlineStr">
         <is>
           <t>Défense</t>
         </is>
       </c>
-      <c r="E23" s="15" t="inlineStr"/>
-      <c r="F23" s="16" t="inlineStr">
+      <c r="E23" s="16" t="inlineStr"/>
+      <c r="F23" s="17" t="inlineStr">
         <is>
           <t>Tower Shield</t>
         </is>
       </c>
-      <c r="G23" s="16" t="inlineStr">
+      <c r="G23" s="17" t="inlineStr">
         <is>
           <t>Gain 5 Stone.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="20" t="inlineStr">
+      <c r="A24" s="21" t="inlineStr">
         <is>
           <t>Quicken</t>
         </is>
       </c>
-      <c r="B24" s="21" t="inlineStr">
+      <c r="B24" s="22" t="inlineStr">
         <is>
           <t>celerite-vive</t>
         </is>
       </c>
-      <c r="C24" s="15" t="n">
+      <c r="C24" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="24" t="inlineStr">
+      <c r="D24" s="25" t="inlineStr">
         <is>
           <t>Buff</t>
         </is>
       </c>
-      <c r="E24" s="15" t="inlineStr"/>
-      <c r="F24" s="16" t="inlineStr">
+      <c r="E24" s="16" t="inlineStr"/>
+      <c r="F24" s="17" t="inlineStr">
         <is>
           <t>Swift Boots</t>
         </is>
       </c>
-      <c r="G24" s="16" t="inlineStr">
+      <c r="G24" s="17" t="inlineStr">
         <is>
           <t>Haste: +30% attack speed for 3 turns.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="20" t="inlineStr">
+      <c r="A25" s="21" t="inlineStr">
         <is>
           <t>Sapphire Surge</t>
         </is>
       </c>
-      <c r="B25" s="21" t="inlineStr">
+      <c r="B25" s="22" t="inlineStr">
         <is>
           <t>surge-saphir</t>
         </is>
       </c>
-      <c r="C25" s="15" t="n">
+      <c r="C25" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D25" s="24" t="inlineStr">
+      <c r="D25" s="25" t="inlineStr">
         <is>
           <t>Buff</t>
         </is>
       </c>
-      <c r="E25" s="15" t="inlineStr"/>
-      <c r="F25" s="16" t="inlineStr">
+      <c r="E25" s="16" t="inlineStr"/>
+      <c r="F25" s="17" t="inlineStr">
         <is>
           <t>Sapphire Amulet</t>
         </is>
       </c>
-      <c r="G25" s="16" t="inlineStr">
+      <c r="G25" s="17" t="inlineStr">
         <is>
           <t>Gain 2 Forge Heat (energy).</t>
         </is>

--- a/docs/BRUTAL-items-et-cartes.xlsx
+++ b/docs/BRUTAL-items-et-cartes.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Lisez-moi" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Items" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Cartes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sets" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -157,7 +158,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -207,6 +208,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -592,7 +599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A18"/>
+  <dimension ref="A1:A22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -652,57 +659,81 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Important : une arme n'a PAS de « dégâts » propres</t>
+          <t>Effets HORS carte (sac, deux mains, set d'armure)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>La colonne « Effet hors-carte » (onglet Items) décrit ce qu'un objet apporte EN DEHORS de ses cartes : rangées de sac, arme à deux mains, appartenance à un set. Pour un nouvel objet, écris ici son effet hors-carte (ex. « +4 rangées de sac »).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Les SETS d'armure ont leur propre onglet « Sets » : un bonus s'active quand on porte TOUTES les pièces d'armure du set (l'arme ne compte pas). Propose un set sur une ligne vide.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Important : une arme n'a PAS de « dégâts » propres</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
           <t>Dans BRUTAL, tout le combat passe par les CARTES du deck — une arme/armure ne fait que fournir des cartes. C'est pourquoi ce tableau se concentre sur les cartes et leur quantité, pas sur un chiffre de dégâts.</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>Légende des raretés</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  Common  (commun)</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  Uncommon  (uncommon)</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">  Rare  (rare)</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Epic  (epique)</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">  Legendary  (legendaire)</t>
         </is>
@@ -720,7 +751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M90"/>
+  <dimension ref="A1:N96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -735,7 +766,8 @@
     <col width="6" customWidth="1" min="10" max="10"/>
     <col width="19" customWidth="1" min="11" max="11"/>
     <col width="6" customWidth="1" min="12" max="12"/>
-    <col width="40" customWidth="1" min="13" max="13"/>
+    <col width="26" customWidth="1" min="13" max="13"/>
+    <col width="40" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -814,6 +846,11 @@
         </is>
       </c>
       <c r="M3" s="11" t="inlineStr">
+        <is>
+          <t>Effet hors-carte</t>
+        </is>
+      </c>
+      <c r="N3" s="11" t="inlineStr">
         <is>
           <t>Notes / nouvelles cartes</t>
         </is>
@@ -859,7 +896,8 @@
       <c r="J5" s="17" t="n"/>
       <c r="K5" s="17" t="n"/>
       <c r="L5" s="17" t="n"/>
-      <c r="M5" s="17" t="n"/>
+      <c r="M5" s="18" t="inlineStr"/>
+      <c r="N5" s="17" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
@@ -872,9 +910,9 @@
           <t>marteau-de-forge</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
-        <is>
-          <t>Common</t>
+      <c r="C6" s="19" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="D6" s="16" t="n">
@@ -894,7 +932,8 @@
       <c r="J6" s="17" t="n"/>
       <c r="K6" s="17" t="n"/>
       <c r="L6" s="17" t="n"/>
-      <c r="M6" s="17" t="n"/>
+      <c r="M6" s="18" t="inlineStr"/>
+      <c r="N6" s="17" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
@@ -929,7 +968,8 @@
       <c r="J7" s="17" t="n"/>
       <c r="K7" s="17" t="n"/>
       <c r="L7" s="17" t="n"/>
-      <c r="M7" s="17" t="n"/>
+      <c r="M7" s="18" t="inlineStr"/>
+      <c r="N7" s="17" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
@@ -942,7 +982,7 @@
           <t>croc-de-basilic</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
@@ -964,7 +1004,8 @@
       <c r="J8" s="17" t="n"/>
       <c r="K8" s="17" t="n"/>
       <c r="L8" s="17" t="n"/>
-      <c r="M8" s="17" t="n"/>
+      <c r="M8" s="18" t="inlineStr"/>
+      <c r="N8" s="17" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
@@ -977,7 +1018,7 @@
           <t>marteau-de-lave</t>
         </is>
       </c>
-      <c r="C9" s="19" t="inlineStr">
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
@@ -999,102 +1040,109 @@
       <c r="J9" s="17" t="n"/>
       <c r="K9" s="17" t="n"/>
       <c r="L9" s="17" t="n"/>
-      <c r="M9" s="17" t="n"/>
+      <c r="M9" s="18" t="inlineStr"/>
+      <c r="N9" s="17" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="n"/>
-      <c r="B10" s="20" t="n"/>
-      <c r="C10" s="20" t="n"/>
-      <c r="D10" s="20" t="n"/>
-      <c r="E10" s="20" t="n"/>
-      <c r="F10" s="20" t="n"/>
-      <c r="G10" s="20" t="n"/>
-      <c r="H10" s="20" t="n"/>
-      <c r="I10" s="20" t="n"/>
-      <c r="J10" s="20" t="n"/>
-      <c r="K10" s="20" t="n"/>
-      <c r="L10" s="20" t="n"/>
-      <c r="M10" s="20" t="n"/>
+      <c r="A10" s="22" t="n"/>
+      <c r="B10" s="22" t="n"/>
+      <c r="C10" s="22" t="n"/>
+      <c r="D10" s="22" t="n"/>
+      <c r="E10" s="22" t="n"/>
+      <c r="F10" s="22" t="n"/>
+      <c r="G10" s="22" t="n"/>
+      <c r="H10" s="22" t="n"/>
+      <c r="I10" s="22" t="n"/>
+      <c r="J10" s="22" t="n"/>
+      <c r="K10" s="22" t="n"/>
+      <c r="L10" s="22" t="n"/>
+      <c r="M10" s="22" t="n"/>
+      <c r="N10" s="22" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="20" t="n"/>
-      <c r="B11" s="20" t="n"/>
-      <c r="C11" s="20" t="n"/>
-      <c r="D11" s="20" t="n"/>
-      <c r="E11" s="20" t="n"/>
-      <c r="F11" s="20" t="n"/>
-      <c r="G11" s="20" t="n"/>
-      <c r="H11" s="20" t="n"/>
-      <c r="I11" s="20" t="n"/>
-      <c r="J11" s="20" t="n"/>
-      <c r="K11" s="20" t="n"/>
-      <c r="L11" s="20" t="n"/>
-      <c r="M11" s="20" t="n"/>
+      <c r="A11" s="22" t="n"/>
+      <c r="B11" s="22" t="n"/>
+      <c r="C11" s="22" t="n"/>
+      <c r="D11" s="22" t="n"/>
+      <c r="E11" s="22" t="n"/>
+      <c r="F11" s="22" t="n"/>
+      <c r="G11" s="22" t="n"/>
+      <c r="H11" s="22" t="n"/>
+      <c r="I11" s="22" t="n"/>
+      <c r="J11" s="22" t="n"/>
+      <c r="K11" s="22" t="n"/>
+      <c r="L11" s="22" t="n"/>
+      <c r="M11" s="22" t="n"/>
+      <c r="N11" s="22" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="n"/>
-      <c r="B12" s="20" t="n"/>
-      <c r="C12" s="20" t="n"/>
-      <c r="D12" s="20" t="n"/>
-      <c r="E12" s="20" t="n"/>
-      <c r="F12" s="20" t="n"/>
-      <c r="G12" s="20" t="n"/>
-      <c r="H12" s="20" t="n"/>
-      <c r="I12" s="20" t="n"/>
-      <c r="J12" s="20" t="n"/>
-      <c r="K12" s="20" t="n"/>
-      <c r="L12" s="20" t="n"/>
-      <c r="M12" s="20" t="n"/>
+      <c r="A12" s="22" t="n"/>
+      <c r="B12" s="22" t="n"/>
+      <c r="C12" s="22" t="n"/>
+      <c r="D12" s="22" t="n"/>
+      <c r="E12" s="22" t="n"/>
+      <c r="F12" s="22" t="n"/>
+      <c r="G12" s="22" t="n"/>
+      <c r="H12" s="22" t="n"/>
+      <c r="I12" s="22" t="n"/>
+      <c r="J12" s="22" t="n"/>
+      <c r="K12" s="22" t="n"/>
+      <c r="L12" s="22" t="n"/>
+      <c r="M12" s="22" t="n"/>
+      <c r="N12" s="22" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="20" t="n"/>
-      <c r="B13" s="20" t="n"/>
-      <c r="C13" s="20" t="n"/>
-      <c r="D13" s="20" t="n"/>
-      <c r="E13" s="20" t="n"/>
-      <c r="F13" s="20" t="n"/>
-      <c r="G13" s="20" t="n"/>
-      <c r="H13" s="20" t="n"/>
-      <c r="I13" s="20" t="n"/>
-      <c r="J13" s="20" t="n"/>
-      <c r="K13" s="20" t="n"/>
-      <c r="L13" s="20" t="n"/>
-      <c r="M13" s="20" t="n"/>
+      <c r="A13" s="22" t="n"/>
+      <c r="B13" s="22" t="n"/>
+      <c r="C13" s="22" t="n"/>
+      <c r="D13" s="22" t="n"/>
+      <c r="E13" s="22" t="n"/>
+      <c r="F13" s="22" t="n"/>
+      <c r="G13" s="22" t="n"/>
+      <c r="H13" s="22" t="n"/>
+      <c r="I13" s="22" t="n"/>
+      <c r="J13" s="22" t="n"/>
+      <c r="K13" s="22" t="n"/>
+      <c r="L13" s="22" t="n"/>
+      <c r="M13" s="22" t="n"/>
+      <c r="N13" s="22" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="n"/>
-      <c r="B14" s="20" t="n"/>
-      <c r="C14" s="20" t="n"/>
-      <c r="D14" s="20" t="n"/>
-      <c r="E14" s="20" t="n"/>
-      <c r="F14" s="20" t="n"/>
-      <c r="G14" s="20" t="n"/>
-      <c r="H14" s="20" t="n"/>
-      <c r="I14" s="20" t="n"/>
-      <c r="J14" s="20" t="n"/>
-      <c r="K14" s="20" t="n"/>
-      <c r="L14" s="20" t="n"/>
-      <c r="M14" s="20" t="n"/>
+      <c r="A14" s="22" t="n"/>
+      <c r="B14" s="22" t="n"/>
+      <c r="C14" s="22" t="n"/>
+      <c r="D14" s="22" t="n"/>
+      <c r="E14" s="22" t="n"/>
+      <c r="F14" s="22" t="n"/>
+      <c r="G14" s="22" t="n"/>
+      <c r="H14" s="22" t="n"/>
+      <c r="I14" s="22" t="n"/>
+      <c r="J14" s="22" t="n"/>
+      <c r="K14" s="22" t="n"/>
+      <c r="L14" s="22" t="n"/>
+      <c r="M14" s="22" t="n"/>
+      <c r="N14" s="22" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="20" t="n"/>
-      <c r="B15" s="20" t="n"/>
-      <c r="C15" s="20" t="n"/>
-      <c r="D15" s="20" t="n"/>
-      <c r="E15" s="20" t="n"/>
-      <c r="F15" s="20" t="n"/>
-      <c r="G15" s="20" t="n"/>
-      <c r="H15" s="20" t="n"/>
-      <c r="I15" s="20" t="n"/>
-      <c r="J15" s="20" t="n"/>
-      <c r="K15" s="20" t="n"/>
-      <c r="L15" s="20" t="n"/>
-      <c r="M15" s="20" t="n"/>
+      <c r="A15" s="22" t="n"/>
+      <c r="B15" s="22" t="n"/>
+      <c r="C15" s="22" t="n"/>
+      <c r="D15" s="22" t="n"/>
+      <c r="E15" s="22" t="n"/>
+      <c r="F15" s="22" t="n"/>
+      <c r="G15" s="22" t="n"/>
+      <c r="H15" s="22" t="n"/>
+      <c r="I15" s="22" t="n"/>
+      <c r="J15" s="22" t="n"/>
+      <c r="K15" s="22" t="n"/>
+      <c r="L15" s="22" t="n"/>
+      <c r="M15" s="22" t="n"/>
+      <c r="N15" s="22" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>Armes — deux mains   (1)</t>
+          <t>Armes — deux mains   (2)</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1157,7 @@
           <t>hache-de-guerre</t>
         </is>
       </c>
-      <c r="C18" s="19" t="inlineStr">
+      <c r="C18" s="21" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
@@ -1143,1146 +1191,1477 @@
       </c>
       <c r="K18" s="17" t="n"/>
       <c r="L18" s="17" t="n"/>
-      <c r="M18" s="17" t="n"/>
+      <c r="M18" s="18" t="inlineStr">
+        <is>
+          <t>Deux mains</t>
+        </is>
+      </c>
+      <c r="N18" s="17" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="20" t="n"/>
-      <c r="B19" s="20" t="n"/>
-      <c r="C19" s="20" t="n"/>
-      <c r="D19" s="20" t="n"/>
-      <c r="E19" s="20" t="n"/>
-      <c r="F19" s="20" t="n"/>
-      <c r="G19" s="20" t="n"/>
-      <c r="H19" s="20" t="n"/>
-      <c r="I19" s="20" t="n"/>
-      <c r="J19" s="20" t="n"/>
-      <c r="K19" s="20" t="n"/>
-      <c r="L19" s="20" t="n"/>
-      <c r="M19" s="20" t="n"/>
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>Big Onyx Sword</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>epee-onyx</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="D19" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="E19" s="17" t="inlineStr">
+        <is>
+          <t>Onyx Radiance</t>
+        </is>
+      </c>
+      <c r="F19" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="17" t="inlineStr">
+        <is>
+          <t>Onyx Slash</t>
+        </is>
+      </c>
+      <c r="H19" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" s="17" t="inlineStr">
+        <is>
+          <t>Heat Rejection</t>
+        </is>
+      </c>
+      <c r="J19" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" s="17" t="n"/>
+      <c r="L19" s="17" t="n"/>
+      <c r="M19" s="18" t="inlineStr">
+        <is>
+          <t>Deux mains</t>
+        </is>
+      </c>
+      <c r="N19" s="17" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="20" t="n"/>
-      <c r="B20" s="20" t="n"/>
-      <c r="C20" s="20" t="n"/>
-      <c r="D20" s="20" t="n"/>
-      <c r="E20" s="20" t="n"/>
-      <c r="F20" s="20" t="n"/>
-      <c r="G20" s="20" t="n"/>
-      <c r="H20" s="20" t="n"/>
-      <c r="I20" s="20" t="n"/>
-      <c r="J20" s="20" t="n"/>
-      <c r="K20" s="20" t="n"/>
-      <c r="L20" s="20" t="n"/>
-      <c r="M20" s="20" t="n"/>
+      <c r="A20" s="22" t="n"/>
+      <c r="B20" s="22" t="n"/>
+      <c r="C20" s="22" t="n"/>
+      <c r="D20" s="22" t="n"/>
+      <c r="E20" s="22" t="n"/>
+      <c r="F20" s="22" t="n"/>
+      <c r="G20" s="22" t="n"/>
+      <c r="H20" s="22" t="n"/>
+      <c r="I20" s="22" t="n"/>
+      <c r="J20" s="22" t="n"/>
+      <c r="K20" s="22" t="n"/>
+      <c r="L20" s="22" t="n"/>
+      <c r="M20" s="22" t="n"/>
+      <c r="N20" s="22" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="20" t="n"/>
-      <c r="B21" s="20" t="n"/>
-      <c r="C21" s="20" t="n"/>
-      <c r="D21" s="20" t="n"/>
-      <c r="E21" s="20" t="n"/>
-      <c r="F21" s="20" t="n"/>
-      <c r="G21" s="20" t="n"/>
-      <c r="H21" s="20" t="n"/>
-      <c r="I21" s="20" t="n"/>
-      <c r="J21" s="20" t="n"/>
-      <c r="K21" s="20" t="n"/>
-      <c r="L21" s="20" t="n"/>
-      <c r="M21" s="20" t="n"/>
+      <c r="A21" s="22" t="n"/>
+      <c r="B21" s="22" t="n"/>
+      <c r="C21" s="22" t="n"/>
+      <c r="D21" s="22" t="n"/>
+      <c r="E21" s="22" t="n"/>
+      <c r="F21" s="22" t="n"/>
+      <c r="G21" s="22" t="n"/>
+      <c r="H21" s="22" t="n"/>
+      <c r="I21" s="22" t="n"/>
+      <c r="J21" s="22" t="n"/>
+      <c r="K21" s="22" t="n"/>
+      <c r="L21" s="22" t="n"/>
+      <c r="M21" s="22" t="n"/>
+      <c r="N21" s="22" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="20" t="n"/>
-      <c r="B22" s="20" t="n"/>
-      <c r="C22" s="20" t="n"/>
-      <c r="D22" s="20" t="n"/>
-      <c r="E22" s="20" t="n"/>
-      <c r="F22" s="20" t="n"/>
-      <c r="G22" s="20" t="n"/>
-      <c r="H22" s="20" t="n"/>
-      <c r="I22" s="20" t="n"/>
-      <c r="J22" s="20" t="n"/>
-      <c r="K22" s="20" t="n"/>
-      <c r="L22" s="20" t="n"/>
-      <c r="M22" s="20" t="n"/>
+      <c r="A22" s="22" t="n"/>
+      <c r="B22" s="22" t="n"/>
+      <c r="C22" s="22" t="n"/>
+      <c r="D22" s="22" t="n"/>
+      <c r="E22" s="22" t="n"/>
+      <c r="F22" s="22" t="n"/>
+      <c r="G22" s="22" t="n"/>
+      <c r="H22" s="22" t="n"/>
+      <c r="I22" s="22" t="n"/>
+      <c r="J22" s="22" t="n"/>
+      <c r="K22" s="22" t="n"/>
+      <c r="L22" s="22" t="n"/>
+      <c r="M22" s="22" t="n"/>
+      <c r="N22" s="22" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="20" t="n"/>
-      <c r="B23" s="20" t="n"/>
-      <c r="C23" s="20" t="n"/>
-      <c r="D23" s="20" t="n"/>
-      <c r="E23" s="20" t="n"/>
-      <c r="F23" s="20" t="n"/>
-      <c r="G23" s="20" t="n"/>
-      <c r="H23" s="20" t="n"/>
-      <c r="I23" s="20" t="n"/>
-      <c r="J23" s="20" t="n"/>
-      <c r="K23" s="20" t="n"/>
-      <c r="L23" s="20" t="n"/>
-      <c r="M23" s="20" t="n"/>
+      <c r="A23" s="22" t="n"/>
+      <c r="B23" s="22" t="n"/>
+      <c r="C23" s="22" t="n"/>
+      <c r="D23" s="22" t="n"/>
+      <c r="E23" s="22" t="n"/>
+      <c r="F23" s="22" t="n"/>
+      <c r="G23" s="22" t="n"/>
+      <c r="H23" s="22" t="n"/>
+      <c r="I23" s="22" t="n"/>
+      <c r="J23" s="22" t="n"/>
+      <c r="K23" s="22" t="n"/>
+      <c r="L23" s="22" t="n"/>
+      <c r="M23" s="22" t="n"/>
+      <c r="N23" s="22" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="20" t="n"/>
-      <c r="B24" s="20" t="n"/>
-      <c r="C24" s="20" t="n"/>
-      <c r="D24" s="20" t="n"/>
-      <c r="E24" s="20" t="n"/>
-      <c r="F24" s="20" t="n"/>
-      <c r="G24" s="20" t="n"/>
-      <c r="H24" s="20" t="n"/>
-      <c r="I24" s="20" t="n"/>
-      <c r="J24" s="20" t="n"/>
-      <c r="K24" s="20" t="n"/>
-      <c r="L24" s="20" t="n"/>
-      <c r="M24" s="20" t="n"/>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="12" t="inlineStr">
+      <c r="A24" s="22" t="n"/>
+      <c r="B24" s="22" t="n"/>
+      <c r="C24" s="22" t="n"/>
+      <c r="D24" s="22" t="n"/>
+      <c r="E24" s="22" t="n"/>
+      <c r="F24" s="22" t="n"/>
+      <c r="G24" s="22" t="n"/>
+      <c r="H24" s="22" t="n"/>
+      <c r="I24" s="22" t="n"/>
+      <c r="J24" s="22" t="n"/>
+      <c r="K24" s="22" t="n"/>
+      <c r="L24" s="22" t="n"/>
+      <c r="M24" s="22" t="n"/>
+      <c r="N24" s="22" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="22" t="n"/>
+      <c r="B25" s="22" t="n"/>
+      <c r="C25" s="22" t="n"/>
+      <c r="D25" s="22" t="n"/>
+      <c r="E25" s="22" t="n"/>
+      <c r="F25" s="22" t="n"/>
+      <c r="G25" s="22" t="n"/>
+      <c r="H25" s="22" t="n"/>
+      <c r="I25" s="22" t="n"/>
+      <c r="J25" s="22" t="n"/>
+      <c r="K25" s="22" t="n"/>
+      <c r="L25" s="22" t="n"/>
+      <c r="M25" s="22" t="n"/>
+      <c r="N25" s="22" t="n"/>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
         <is>
           <t>Boucliers (main 2nde)   (1)</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="13" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
         <is>
           <t>Tower Shield</t>
         </is>
       </c>
-      <c r="B27" s="14" t="inlineStr">
+      <c r="B28" s="14" t="inlineStr">
         <is>
           <t>bouclier-tour</t>
         </is>
       </c>
-      <c r="C27" s="19" t="inlineStr">
+      <c r="C28" s="21" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="D27" s="16" t="n">
+      <c r="D28" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="E27" s="17" t="inlineStr">
+      <c r="E28" s="17" t="inlineStr">
         <is>
           <t>Shield Wall</t>
         </is>
       </c>
-      <c r="F27" s="16" t="n">
+      <c r="F28" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="17" t="inlineStr">
+        <is>
+          <t>Shield Bash</t>
+        </is>
+      </c>
+      <c r="H28" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="G27" s="17" t="inlineStr">
-        <is>
-          <t>Shield Bash</t>
-        </is>
-      </c>
-      <c r="H27" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="I27" s="17" t="n"/>
-      <c r="J27" s="17" t="n"/>
-      <c r="K27" s="17" t="n"/>
-      <c r="L27" s="17" t="n"/>
-      <c r="M27" s="17" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="20" t="n"/>
-      <c r="B28" s="20" t="n"/>
-      <c r="C28" s="20" t="n"/>
-      <c r="D28" s="20" t="n"/>
-      <c r="E28" s="20" t="n"/>
-      <c r="F28" s="20" t="n"/>
-      <c r="G28" s="20" t="n"/>
-      <c r="H28" s="20" t="n"/>
-      <c r="I28" s="20" t="n"/>
-      <c r="J28" s="20" t="n"/>
-      <c r="K28" s="20" t="n"/>
-      <c r="L28" s="20" t="n"/>
-      <c r="M28" s="20" t="n"/>
+      <c r="I28" s="17" t="n"/>
+      <c r="J28" s="17" t="n"/>
+      <c r="K28" s="17" t="n"/>
+      <c r="L28" s="17" t="n"/>
+      <c r="M28" s="18" t="inlineStr"/>
+      <c r="N28" s="17" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="20" t="n"/>
-      <c r="B29" s="20" t="n"/>
-      <c r="C29" s="20" t="n"/>
-      <c r="D29" s="20" t="n"/>
-      <c r="E29" s="20" t="n"/>
-      <c r="F29" s="20" t="n"/>
-      <c r="G29" s="20" t="n"/>
-      <c r="H29" s="20" t="n"/>
-      <c r="I29" s="20" t="n"/>
-      <c r="J29" s="20" t="n"/>
-      <c r="K29" s="20" t="n"/>
-      <c r="L29" s="20" t="n"/>
-      <c r="M29" s="20" t="n"/>
+      <c r="A29" s="22" t="n"/>
+      <c r="B29" s="22" t="n"/>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="22" t="n"/>
+      <c r="E29" s="22" t="n"/>
+      <c r="F29" s="22" t="n"/>
+      <c r="G29" s="22" t="n"/>
+      <c r="H29" s="22" t="n"/>
+      <c r="I29" s="22" t="n"/>
+      <c r="J29" s="22" t="n"/>
+      <c r="K29" s="22" t="n"/>
+      <c r="L29" s="22" t="n"/>
+      <c r="M29" s="22" t="n"/>
+      <c r="N29" s="22" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="20" t="n"/>
-      <c r="B30" s="20" t="n"/>
-      <c r="C30" s="20" t="n"/>
-      <c r="D30" s="20" t="n"/>
-      <c r="E30" s="20" t="n"/>
-      <c r="F30" s="20" t="n"/>
-      <c r="G30" s="20" t="n"/>
-      <c r="H30" s="20" t="n"/>
-      <c r="I30" s="20" t="n"/>
-      <c r="J30" s="20" t="n"/>
-      <c r="K30" s="20" t="n"/>
-      <c r="L30" s="20" t="n"/>
-      <c r="M30" s="20" t="n"/>
+      <c r="A30" s="22" t="n"/>
+      <c r="B30" s="22" t="n"/>
+      <c r="C30" s="22" t="n"/>
+      <c r="D30" s="22" t="n"/>
+      <c r="E30" s="22" t="n"/>
+      <c r="F30" s="22" t="n"/>
+      <c r="G30" s="22" t="n"/>
+      <c r="H30" s="22" t="n"/>
+      <c r="I30" s="22" t="n"/>
+      <c r="J30" s="22" t="n"/>
+      <c r="K30" s="22" t="n"/>
+      <c r="L30" s="22" t="n"/>
+      <c r="M30" s="22" t="n"/>
+      <c r="N30" s="22" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="20" t="n"/>
-      <c r="B31" s="20" t="n"/>
-      <c r="C31" s="20" t="n"/>
-      <c r="D31" s="20" t="n"/>
-      <c r="E31" s="20" t="n"/>
-      <c r="F31" s="20" t="n"/>
-      <c r="G31" s="20" t="n"/>
-      <c r="H31" s="20" t="n"/>
-      <c r="I31" s="20" t="n"/>
-      <c r="J31" s="20" t="n"/>
-      <c r="K31" s="20" t="n"/>
-      <c r="L31" s="20" t="n"/>
-      <c r="M31" s="20" t="n"/>
+      <c r="A31" s="22" t="n"/>
+      <c r="B31" s="22" t="n"/>
+      <c r="C31" s="22" t="n"/>
+      <c r="D31" s="22" t="n"/>
+      <c r="E31" s="22" t="n"/>
+      <c r="F31" s="22" t="n"/>
+      <c r="G31" s="22" t="n"/>
+      <c r="H31" s="22" t="n"/>
+      <c r="I31" s="22" t="n"/>
+      <c r="J31" s="22" t="n"/>
+      <c r="K31" s="22" t="n"/>
+      <c r="L31" s="22" t="n"/>
+      <c r="M31" s="22" t="n"/>
+      <c r="N31" s="22" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="20" t="n"/>
-      <c r="B32" s="20" t="n"/>
-      <c r="C32" s="20" t="n"/>
-      <c r="D32" s="20" t="n"/>
-      <c r="E32" s="20" t="n"/>
-      <c r="F32" s="20" t="n"/>
-      <c r="G32" s="20" t="n"/>
-      <c r="H32" s="20" t="n"/>
-      <c r="I32" s="20" t="n"/>
-      <c r="J32" s="20" t="n"/>
-      <c r="K32" s="20" t="n"/>
-      <c r="L32" s="20" t="n"/>
-      <c r="M32" s="20" t="n"/>
+      <c r="A32" s="22" t="n"/>
+      <c r="B32" s="22" t="n"/>
+      <c r="C32" s="22" t="n"/>
+      <c r="D32" s="22" t="n"/>
+      <c r="E32" s="22" t="n"/>
+      <c r="F32" s="22" t="n"/>
+      <c r="G32" s="22" t="n"/>
+      <c r="H32" s="22" t="n"/>
+      <c r="I32" s="22" t="n"/>
+      <c r="J32" s="22" t="n"/>
+      <c r="K32" s="22" t="n"/>
+      <c r="L32" s="22" t="n"/>
+      <c r="M32" s="22" t="n"/>
+      <c r="N32" s="22" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="20" t="n"/>
-      <c r="B33" s="20" t="n"/>
-      <c r="C33" s="20" t="n"/>
-      <c r="D33" s="20" t="n"/>
-      <c r="E33" s="20" t="n"/>
-      <c r="F33" s="20" t="n"/>
-      <c r="G33" s="20" t="n"/>
-      <c r="H33" s="20" t="n"/>
-      <c r="I33" s="20" t="n"/>
-      <c r="J33" s="20" t="n"/>
-      <c r="K33" s="20" t="n"/>
-      <c r="L33" s="20" t="n"/>
-      <c r="M33" s="20" t="n"/>
-    </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="12" t="inlineStr">
+      <c r="A33" s="22" t="n"/>
+      <c r="B33" s="22" t="n"/>
+      <c r="C33" s="22" t="n"/>
+      <c r="D33" s="22" t="n"/>
+      <c r="E33" s="22" t="n"/>
+      <c r="F33" s="22" t="n"/>
+      <c r="G33" s="22" t="n"/>
+      <c r="H33" s="22" t="n"/>
+      <c r="I33" s="22" t="n"/>
+      <c r="J33" s="22" t="n"/>
+      <c r="K33" s="22" t="n"/>
+      <c r="L33" s="22" t="n"/>
+      <c r="M33" s="22" t="n"/>
+      <c r="N33" s="22" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="22" t="n"/>
+      <c r="B34" s="22" t="n"/>
+      <c r="C34" s="22" t="n"/>
+      <c r="D34" s="22" t="n"/>
+      <c r="E34" s="22" t="n"/>
+      <c r="F34" s="22" t="n"/>
+      <c r="G34" s="22" t="n"/>
+      <c r="H34" s="22" t="n"/>
+      <c r="I34" s="22" t="n"/>
+      <c r="J34" s="22" t="n"/>
+      <c r="K34" s="22" t="n"/>
+      <c r="L34" s="22" t="n"/>
+      <c r="M34" s="22" t="n"/>
+      <c r="N34" s="22" t="n"/>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
         <is>
           <t>Armures   (3)</t>
         </is>
       </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="13" t="inlineStr">
-        <is>
-          <t>Traveler's Garb</t>
-        </is>
-      </c>
-      <c r="B36" s="14" t="inlineStr">
-        <is>
-          <t>tenue-de-voyageur</t>
-        </is>
-      </c>
-      <c r="C36" s="15" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="D36" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" s="17" t="n"/>
-      <c r="F36" s="17" t="n"/>
-      <c r="G36" s="17" t="n"/>
-      <c r="H36" s="17" t="n"/>
-      <c r="I36" s="17" t="n"/>
-      <c r="J36" s="17" t="n"/>
-      <c r="K36" s="17" t="n"/>
-      <c r="L36" s="17" t="n"/>
-      <c r="M36" s="17" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="13" t="inlineStr">
         <is>
-          <t>Onyx Guard Plate</t>
+          <t>Traveler's Garb</t>
         </is>
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>plate-onyx</t>
-        </is>
-      </c>
-      <c r="C37" s="18" t="inlineStr">
-        <is>
-          <t>Rare</t>
+          <t>tenue-de-voyageur</t>
+        </is>
+      </c>
+      <c r="C37" s="15" t="inlineStr">
+        <is>
+          <t>Common</t>
         </is>
       </c>
       <c r="D37" s="16" t="n">
-        <v>6</v>
-      </c>
-      <c r="E37" s="17" t="inlineStr">
-        <is>
-          <t>Onyx Armor</t>
-        </is>
-      </c>
-      <c r="F37" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="G37" s="17" t="inlineStr">
-        <is>
-          <t>Dragon's Blaze</t>
-        </is>
-      </c>
-      <c r="H37" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="I37" s="17" t="inlineStr">
-        <is>
-          <t>Onyx Breath</t>
-        </is>
-      </c>
-      <c r="J37" s="16" t="n">
-        <v>2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E37" s="17" t="n"/>
+      <c r="F37" s="17" t="n"/>
+      <c r="G37" s="17" t="n"/>
+      <c r="H37" s="17" t="n"/>
+      <c r="I37" s="17" t="n"/>
+      <c r="J37" s="17" t="n"/>
       <c r="K37" s="17" t="n"/>
       <c r="L37" s="17" t="n"/>
-      <c r="M37" s="17" t="n"/>
+      <c r="M37" s="18" t="inlineStr"/>
+      <c r="N37" s="17" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>Forgemaster's Mail</t>
+          <t>Onyx Guard Plate</t>
         </is>
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t>maille-de-forge</t>
-        </is>
-      </c>
-      <c r="C38" s="18" t="inlineStr">
+          <t>plate-onyx</t>
+        </is>
+      </c>
+      <c r="C38" s="20" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
       <c r="D38" s="16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E38" s="17" t="inlineStr">
         <is>
-          <t>Mail Armor</t>
+          <t>Onyx Armor</t>
         </is>
       </c>
       <c r="F38" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G38" s="17" t="inlineStr">
         <is>
-          <t>Quench</t>
+          <t>Dragon's Blaze</t>
         </is>
       </c>
       <c r="H38" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="I38" s="17" t="n"/>
-      <c r="J38" s="17" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="I38" s="17" t="inlineStr">
+        <is>
+          <t>Onyx Breath</t>
+        </is>
+      </c>
+      <c r="J38" s="16" t="n">
+        <v>2</v>
+      </c>
       <c r="K38" s="17" t="n"/>
       <c r="L38" s="17" t="n"/>
-      <c r="M38" s="17" t="n"/>
+      <c r="M38" s="18" t="inlineStr">
+        <is>
+          <t>Défense 5  ·  Set : Onyx Set</t>
+        </is>
+      </c>
+      <c r="N38" s="17" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="20" t="n"/>
-      <c r="B39" s="20" t="n"/>
-      <c r="C39" s="20" t="n"/>
-      <c r="D39" s="20" t="n"/>
-      <c r="E39" s="20" t="n"/>
-      <c r="F39" s="20" t="n"/>
-      <c r="G39" s="20" t="n"/>
-      <c r="H39" s="20" t="n"/>
-      <c r="I39" s="20" t="n"/>
-      <c r="J39" s="20" t="n"/>
-      <c r="K39" s="20" t="n"/>
-      <c r="L39" s="20" t="n"/>
-      <c r="M39" s="20" t="n"/>
+      <c r="A39" s="13" t="inlineStr">
+        <is>
+          <t>Forgemaster's Mail</t>
+        </is>
+      </c>
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t>maille-de-forge</t>
+        </is>
+      </c>
+      <c r="C39" s="20" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D39" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="E39" s="17" t="inlineStr">
+        <is>
+          <t>Mail Armor</t>
+        </is>
+      </c>
+      <c r="F39" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="G39" s="17" t="inlineStr">
+        <is>
+          <t>Quench</t>
+        </is>
+      </c>
+      <c r="H39" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" s="17" t="n"/>
+      <c r="J39" s="17" t="n"/>
+      <c r="K39" s="17" t="n"/>
+      <c r="L39" s="17" t="n"/>
+      <c r="M39" s="18" t="inlineStr">
+        <is>
+          <t>Défense 3</t>
+        </is>
+      </c>
+      <c r="N39" s="17" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="20" t="n"/>
-      <c r="B40" s="20" t="n"/>
-      <c r="C40" s="20" t="n"/>
-      <c r="D40" s="20" t="n"/>
-      <c r="E40" s="20" t="n"/>
-      <c r="F40" s="20" t="n"/>
-      <c r="G40" s="20" t="n"/>
-      <c r="H40" s="20" t="n"/>
-      <c r="I40" s="20" t="n"/>
-      <c r="J40" s="20" t="n"/>
-      <c r="K40" s="20" t="n"/>
-      <c r="L40" s="20" t="n"/>
-      <c r="M40" s="20" t="n"/>
+      <c r="A40" s="22" t="n"/>
+      <c r="B40" s="22" t="n"/>
+      <c r="C40" s="22" t="n"/>
+      <c r="D40" s="22" t="n"/>
+      <c r="E40" s="22" t="n"/>
+      <c r="F40" s="22" t="n"/>
+      <c r="G40" s="22" t="n"/>
+      <c r="H40" s="22" t="n"/>
+      <c r="I40" s="22" t="n"/>
+      <c r="J40" s="22" t="n"/>
+      <c r="K40" s="22" t="n"/>
+      <c r="L40" s="22" t="n"/>
+      <c r="M40" s="22" t="n"/>
+      <c r="N40" s="22" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="20" t="n"/>
-      <c r="B41" s="20" t="n"/>
-      <c r="C41" s="20" t="n"/>
-      <c r="D41" s="20" t="n"/>
-      <c r="E41" s="20" t="n"/>
-      <c r="F41" s="20" t="n"/>
-      <c r="G41" s="20" t="n"/>
-      <c r="H41" s="20" t="n"/>
-      <c r="I41" s="20" t="n"/>
-      <c r="J41" s="20" t="n"/>
-      <c r="K41" s="20" t="n"/>
-      <c r="L41" s="20" t="n"/>
-      <c r="M41" s="20" t="n"/>
+      <c r="A41" s="22" t="n"/>
+      <c r="B41" s="22" t="n"/>
+      <c r="C41" s="22" t="n"/>
+      <c r="D41" s="22" t="n"/>
+      <c r="E41" s="22" t="n"/>
+      <c r="F41" s="22" t="n"/>
+      <c r="G41" s="22" t="n"/>
+      <c r="H41" s="22" t="n"/>
+      <c r="I41" s="22" t="n"/>
+      <c r="J41" s="22" t="n"/>
+      <c r="K41" s="22" t="n"/>
+      <c r="L41" s="22" t="n"/>
+      <c r="M41" s="22" t="n"/>
+      <c r="N41" s="22" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="20" t="n"/>
-      <c r="B42" s="20" t="n"/>
-      <c r="C42" s="20" t="n"/>
-      <c r="D42" s="20" t="n"/>
-      <c r="E42" s="20" t="n"/>
-      <c r="F42" s="20" t="n"/>
-      <c r="G42" s="20" t="n"/>
-      <c r="H42" s="20" t="n"/>
-      <c r="I42" s="20" t="n"/>
-      <c r="J42" s="20" t="n"/>
-      <c r="K42" s="20" t="n"/>
-      <c r="L42" s="20" t="n"/>
-      <c r="M42" s="20" t="n"/>
+      <c r="A42" s="22" t="n"/>
+      <c r="B42" s="22" t="n"/>
+      <c r="C42" s="22" t="n"/>
+      <c r="D42" s="22" t="n"/>
+      <c r="E42" s="22" t="n"/>
+      <c r="F42" s="22" t="n"/>
+      <c r="G42" s="22" t="n"/>
+      <c r="H42" s="22" t="n"/>
+      <c r="I42" s="22" t="n"/>
+      <c r="J42" s="22" t="n"/>
+      <c r="K42" s="22" t="n"/>
+      <c r="L42" s="22" t="n"/>
+      <c r="M42" s="22" t="n"/>
+      <c r="N42" s="22" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="20" t="n"/>
-      <c r="B43" s="20" t="n"/>
-      <c r="C43" s="20" t="n"/>
-      <c r="D43" s="20" t="n"/>
-      <c r="E43" s="20" t="n"/>
-      <c r="F43" s="20" t="n"/>
-      <c r="G43" s="20" t="n"/>
-      <c r="H43" s="20" t="n"/>
-      <c r="I43" s="20" t="n"/>
-      <c r="J43" s="20" t="n"/>
-      <c r="K43" s="20" t="n"/>
-      <c r="L43" s="20" t="n"/>
-      <c r="M43" s="20" t="n"/>
+      <c r="A43" s="22" t="n"/>
+      <c r="B43" s="22" t="n"/>
+      <c r="C43" s="22" t="n"/>
+      <c r="D43" s="22" t="n"/>
+      <c r="E43" s="22" t="n"/>
+      <c r="F43" s="22" t="n"/>
+      <c r="G43" s="22" t="n"/>
+      <c r="H43" s="22" t="n"/>
+      <c r="I43" s="22" t="n"/>
+      <c r="J43" s="22" t="n"/>
+      <c r="K43" s="22" t="n"/>
+      <c r="L43" s="22" t="n"/>
+      <c r="M43" s="22" t="n"/>
+      <c r="N43" s="22" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="20" t="n"/>
-      <c r="B44" s="20" t="n"/>
-      <c r="C44" s="20" t="n"/>
-      <c r="D44" s="20" t="n"/>
-      <c r="E44" s="20" t="n"/>
-      <c r="F44" s="20" t="n"/>
-      <c r="G44" s="20" t="n"/>
-      <c r="H44" s="20" t="n"/>
-      <c r="I44" s="20" t="n"/>
-      <c r="J44" s="20" t="n"/>
-      <c r="K44" s="20" t="n"/>
-      <c r="L44" s="20" t="n"/>
-      <c r="M44" s="20" t="n"/>
-    </row>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="12" t="inlineStr">
-        <is>
-          <t>Colliers   (1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="13" t="inlineStr">
+      <c r="A44" s="22" t="n"/>
+      <c r="B44" s="22" t="n"/>
+      <c r="C44" s="22" t="n"/>
+      <c r="D44" s="22" t="n"/>
+      <c r="E44" s="22" t="n"/>
+      <c r="F44" s="22" t="n"/>
+      <c r="G44" s="22" t="n"/>
+      <c r="H44" s="22" t="n"/>
+      <c r="I44" s="22" t="n"/>
+      <c r="J44" s="22" t="n"/>
+      <c r="K44" s="22" t="n"/>
+      <c r="L44" s="22" t="n"/>
+      <c r="M44" s="22" t="n"/>
+      <c r="N44" s="22" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="22" t="n"/>
+      <c r="B45" s="22" t="n"/>
+      <c r="C45" s="22" t="n"/>
+      <c r="D45" s="22" t="n"/>
+      <c r="E45" s="22" t="n"/>
+      <c r="F45" s="22" t="n"/>
+      <c r="G45" s="22" t="n"/>
+      <c r="H45" s="22" t="n"/>
+      <c r="I45" s="22" t="n"/>
+      <c r="J45" s="22" t="n"/>
+      <c r="K45" s="22" t="n"/>
+      <c r="L45" s="22" t="n"/>
+      <c r="M45" s="22" t="n"/>
+      <c r="N45" s="22" t="n"/>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="12" t="inlineStr">
+        <is>
+          <t>Colliers   (3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="13" t="inlineStr">
         <is>
           <t>Sapphire Amulet</t>
         </is>
       </c>
-      <c r="B47" s="14" t="inlineStr">
+      <c r="B48" s="14" t="inlineStr">
         <is>
           <t>collier-de-saphir</t>
         </is>
       </c>
-      <c r="C47" s="19" t="inlineStr">
+      <c r="C48" s="19" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D48" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" s="17" t="inlineStr">
+        <is>
+          <t>Sapphire Surge</t>
+        </is>
+      </c>
+      <c r="F48" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="17" t="n"/>
+      <c r="H48" s="17" t="n"/>
+      <c r="I48" s="17" t="n"/>
+      <c r="J48" s="17" t="n"/>
+      <c r="K48" s="17" t="n"/>
+      <c r="L48" s="17" t="n"/>
+      <c r="M48" s="18" t="inlineStr"/>
+      <c r="N48" s="17" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="13" t="inlineStr">
+        <is>
+          <t>Nice Sapphire Amulet</t>
+        </is>
+      </c>
+      <c r="B49" s="14" t="inlineStr">
+        <is>
+          <t>collier-de-saphir-fin</t>
+        </is>
+      </c>
+      <c r="C49" s="20" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D49" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E49" s="17" t="inlineStr">
+        <is>
+          <t>Sapphire Surge</t>
+        </is>
+      </c>
+      <c r="F49" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G49" s="17" t="n"/>
+      <c r="H49" s="17" t="n"/>
+      <c r="I49" s="17" t="n"/>
+      <c r="J49" s="17" t="n"/>
+      <c r="K49" s="17" t="n"/>
+      <c r="L49" s="17" t="n"/>
+      <c r="M49" s="18" t="inlineStr"/>
+      <c r="N49" s="17" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="13" t="inlineStr">
+        <is>
+          <t>Perfect Sapphire Amulet</t>
+        </is>
+      </c>
+      <c r="B50" s="14" t="inlineStr">
+        <is>
+          <t>collier-de-saphir-parfait</t>
+        </is>
+      </c>
+      <c r="C50" s="21" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="D47" s="16" t="n">
+      <c r="D50" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E50" s="17" t="inlineStr">
+        <is>
+          <t>Perfect Sapphire Surge</t>
+        </is>
+      </c>
+      <c r="F50" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="G50" s="17" t="n"/>
+      <c r="H50" s="17" t="n"/>
+      <c r="I50" s="17" t="n"/>
+      <c r="J50" s="17" t="n"/>
+      <c r="K50" s="17" t="n"/>
+      <c r="L50" s="17" t="n"/>
+      <c r="M50" s="18" t="inlineStr"/>
+      <c r="N50" s="17" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="22" t="n"/>
+      <c r="B51" s="22" t="n"/>
+      <c r="C51" s="22" t="n"/>
+      <c r="D51" s="22" t="n"/>
+      <c r="E51" s="22" t="n"/>
+      <c r="F51" s="22" t="n"/>
+      <c r="G51" s="22" t="n"/>
+      <c r="H51" s="22" t="n"/>
+      <c r="I51" s="22" t="n"/>
+      <c r="J51" s="22" t="n"/>
+      <c r="K51" s="22" t="n"/>
+      <c r="L51" s="22" t="n"/>
+      <c r="M51" s="22" t="n"/>
+      <c r="N51" s="22" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="22" t="n"/>
+      <c r="B52" s="22" t="n"/>
+      <c r="C52" s="22" t="n"/>
+      <c r="D52" s="22" t="n"/>
+      <c r="E52" s="22" t="n"/>
+      <c r="F52" s="22" t="n"/>
+      <c r="G52" s="22" t="n"/>
+      <c r="H52" s="22" t="n"/>
+      <c r="I52" s="22" t="n"/>
+      <c r="J52" s="22" t="n"/>
+      <c r="K52" s="22" t="n"/>
+      <c r="L52" s="22" t="n"/>
+      <c r="M52" s="22" t="n"/>
+      <c r="N52" s="22" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="22" t="n"/>
+      <c r="B53" s="22" t="n"/>
+      <c r="C53" s="22" t="n"/>
+      <c r="D53" s="22" t="n"/>
+      <c r="E53" s="22" t="n"/>
+      <c r="F53" s="22" t="n"/>
+      <c r="G53" s="22" t="n"/>
+      <c r="H53" s="22" t="n"/>
+      <c r="I53" s="22" t="n"/>
+      <c r="J53" s="22" t="n"/>
+      <c r="K53" s="22" t="n"/>
+      <c r="L53" s="22" t="n"/>
+      <c r="M53" s="22" t="n"/>
+      <c r="N53" s="22" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="22" t="n"/>
+      <c r="B54" s="22" t="n"/>
+      <c r="C54" s="22" t="n"/>
+      <c r="D54" s="22" t="n"/>
+      <c r="E54" s="22" t="n"/>
+      <c r="F54" s="22" t="n"/>
+      <c r="G54" s="22" t="n"/>
+      <c r="H54" s="22" t="n"/>
+      <c r="I54" s="22" t="n"/>
+      <c r="J54" s="22" t="n"/>
+      <c r="K54" s="22" t="n"/>
+      <c r="L54" s="22" t="n"/>
+      <c r="M54" s="22" t="n"/>
+      <c r="N54" s="22" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="22" t="n"/>
+      <c r="B55" s="22" t="n"/>
+      <c r="C55" s="22" t="n"/>
+      <c r="D55" s="22" t="n"/>
+      <c r="E55" s="22" t="n"/>
+      <c r="F55" s="22" t="n"/>
+      <c r="G55" s="22" t="n"/>
+      <c r="H55" s="22" t="n"/>
+      <c r="I55" s="22" t="n"/>
+      <c r="J55" s="22" t="n"/>
+      <c r="K55" s="22" t="n"/>
+      <c r="L55" s="22" t="n"/>
+      <c r="M55" s="22" t="n"/>
+      <c r="N55" s="22" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="22" t="n"/>
+      <c r="B56" s="22" t="n"/>
+      <c r="C56" s="22" t="n"/>
+      <c r="D56" s="22" t="n"/>
+      <c r="E56" s="22" t="n"/>
+      <c r="F56" s="22" t="n"/>
+      <c r="G56" s="22" t="n"/>
+      <c r="H56" s="22" t="n"/>
+      <c r="I56" s="22" t="n"/>
+      <c r="J56" s="22" t="n"/>
+      <c r="K56" s="22" t="n"/>
+      <c r="L56" s="22" t="n"/>
+      <c r="M56" s="22" t="n"/>
+      <c r="N56" s="22" t="n"/>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="12" t="inlineStr">
+        <is>
+          <t>Bagues   (2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="13" t="inlineStr">
+        <is>
+          <t>Blood Ring</t>
+        </is>
+      </c>
+      <c r="B59" s="14" t="inlineStr">
+        <is>
+          <t>bague-de-sang</t>
+        </is>
+      </c>
+      <c r="C59" s="19" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D59" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="E47" s="17" t="inlineStr">
-        <is>
-          <t>Sapphire Surge</t>
-        </is>
-      </c>
-      <c r="F47" s="16" t="n">
+      <c r="E59" s="17" t="inlineStr">
+        <is>
+          <t>Bloodletting</t>
+        </is>
+      </c>
+      <c r="F59" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="G47" s="17" t="n"/>
-      <c r="H47" s="17" t="n"/>
-      <c r="I47" s="17" t="n"/>
-      <c r="J47" s="17" t="n"/>
-      <c r="K47" s="17" t="n"/>
-      <c r="L47" s="17" t="n"/>
-      <c r="M47" s="17" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="20" t="n"/>
-      <c r="B48" s="20" t="n"/>
-      <c r="C48" s="20" t="n"/>
-      <c r="D48" s="20" t="n"/>
-      <c r="E48" s="20" t="n"/>
-      <c r="F48" s="20" t="n"/>
-      <c r="G48" s="20" t="n"/>
-      <c r="H48" s="20" t="n"/>
-      <c r="I48" s="20" t="n"/>
-      <c r="J48" s="20" t="n"/>
-      <c r="K48" s="20" t="n"/>
-      <c r="L48" s="20" t="n"/>
-      <c r="M48" s="20" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="20" t="n"/>
-      <c r="B49" s="20" t="n"/>
-      <c r="C49" s="20" t="n"/>
-      <c r="D49" s="20" t="n"/>
-      <c r="E49" s="20" t="n"/>
-      <c r="F49" s="20" t="n"/>
-      <c r="G49" s="20" t="n"/>
-      <c r="H49" s="20" t="n"/>
-      <c r="I49" s="20" t="n"/>
-      <c r="J49" s="20" t="n"/>
-      <c r="K49" s="20" t="n"/>
-      <c r="L49" s="20" t="n"/>
-      <c r="M49" s="20" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="20" t="n"/>
-      <c r="B50" s="20" t="n"/>
-      <c r="C50" s="20" t="n"/>
-      <c r="D50" s="20" t="n"/>
-      <c r="E50" s="20" t="n"/>
-      <c r="F50" s="20" t="n"/>
-      <c r="G50" s="20" t="n"/>
-      <c r="H50" s="20" t="n"/>
-      <c r="I50" s="20" t="n"/>
-      <c r="J50" s="20" t="n"/>
-      <c r="K50" s="20" t="n"/>
-      <c r="L50" s="20" t="n"/>
-      <c r="M50" s="20" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="20" t="n"/>
-      <c r="B51" s="20" t="n"/>
-      <c r="C51" s="20" t="n"/>
-      <c r="D51" s="20" t="n"/>
-      <c r="E51" s="20" t="n"/>
-      <c r="F51" s="20" t="n"/>
-      <c r="G51" s="20" t="n"/>
-      <c r="H51" s="20" t="n"/>
-      <c r="I51" s="20" t="n"/>
-      <c r="J51" s="20" t="n"/>
-      <c r="K51" s="20" t="n"/>
-      <c r="L51" s="20" t="n"/>
-      <c r="M51" s="20" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="20" t="n"/>
-      <c r="B52" s="20" t="n"/>
-      <c r="C52" s="20" t="n"/>
-      <c r="D52" s="20" t="n"/>
-      <c r="E52" s="20" t="n"/>
-      <c r="F52" s="20" t="n"/>
-      <c r="G52" s="20" t="n"/>
-      <c r="H52" s="20" t="n"/>
-      <c r="I52" s="20" t="n"/>
-      <c r="J52" s="20" t="n"/>
-      <c r="K52" s="20" t="n"/>
-      <c r="L52" s="20" t="n"/>
-      <c r="M52" s="20" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="20" t="n"/>
-      <c r="B53" s="20" t="n"/>
-      <c r="C53" s="20" t="n"/>
-      <c r="D53" s="20" t="n"/>
-      <c r="E53" s="20" t="n"/>
-      <c r="F53" s="20" t="n"/>
-      <c r="G53" s="20" t="n"/>
-      <c r="H53" s="20" t="n"/>
-      <c r="I53" s="20" t="n"/>
-      <c r="J53" s="20" t="n"/>
-      <c r="K53" s="20" t="n"/>
-      <c r="L53" s="20" t="n"/>
-      <c r="M53" s="20" t="n"/>
-    </row>
-    <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="12" t="inlineStr">
-        <is>
-          <t>Bagues   (2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="13" t="inlineStr">
-        <is>
-          <t>Blood Ring</t>
-        </is>
-      </c>
-      <c r="B56" s="14" t="inlineStr">
-        <is>
-          <t>bague-de-sang</t>
-        </is>
-      </c>
-      <c r="C56" s="18" t="inlineStr">
+      <c r="G59" s="17" t="n"/>
+      <c r="H59" s="17" t="n"/>
+      <c r="I59" s="17" t="n"/>
+      <c r="J59" s="17" t="n"/>
+      <c r="K59" s="17" t="n"/>
+      <c r="L59" s="17" t="n"/>
+      <c r="M59" s="18" t="inlineStr"/>
+      <c r="N59" s="17" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="13" t="inlineStr">
+        <is>
+          <t>Frost Ring</t>
+        </is>
+      </c>
+      <c r="B60" s="14" t="inlineStr">
+        <is>
+          <t>anneau-de-givre</t>
+        </is>
+      </c>
+      <c r="C60" s="19" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D60" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E60" s="17" t="inlineStr">
+        <is>
+          <t>Frostbite</t>
+        </is>
+      </c>
+      <c r="F60" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G60" s="17" t="n"/>
+      <c r="H60" s="17" t="n"/>
+      <c r="I60" s="17" t="n"/>
+      <c r="J60" s="17" t="n"/>
+      <c r="K60" s="17" t="n"/>
+      <c r="L60" s="17" t="n"/>
+      <c r="M60" s="18" t="inlineStr"/>
+      <c r="N60" s="17" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="22" t="n"/>
+      <c r="B61" s="22" t="n"/>
+      <c r="C61" s="22" t="n"/>
+      <c r="D61" s="22" t="n"/>
+      <c r="E61" s="22" t="n"/>
+      <c r="F61" s="22" t="n"/>
+      <c r="G61" s="22" t="n"/>
+      <c r="H61" s="22" t="n"/>
+      <c r="I61" s="22" t="n"/>
+      <c r="J61" s="22" t="n"/>
+      <c r="K61" s="22" t="n"/>
+      <c r="L61" s="22" t="n"/>
+      <c r="M61" s="22" t="n"/>
+      <c r="N61" s="22" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="22" t="n"/>
+      <c r="B62" s="22" t="n"/>
+      <c r="C62" s="22" t="n"/>
+      <c r="D62" s="22" t="n"/>
+      <c r="E62" s="22" t="n"/>
+      <c r="F62" s="22" t="n"/>
+      <c r="G62" s="22" t="n"/>
+      <c r="H62" s="22" t="n"/>
+      <c r="I62" s="22" t="n"/>
+      <c r="J62" s="22" t="n"/>
+      <c r="K62" s="22" t="n"/>
+      <c r="L62" s="22" t="n"/>
+      <c r="M62" s="22" t="n"/>
+      <c r="N62" s="22" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="22" t="n"/>
+      <c r="B63" s="22" t="n"/>
+      <c r="C63" s="22" t="n"/>
+      <c r="D63" s="22" t="n"/>
+      <c r="E63" s="22" t="n"/>
+      <c r="F63" s="22" t="n"/>
+      <c r="G63" s="22" t="n"/>
+      <c r="H63" s="22" t="n"/>
+      <c r="I63" s="22" t="n"/>
+      <c r="J63" s="22" t="n"/>
+      <c r="K63" s="22" t="n"/>
+      <c r="L63" s="22" t="n"/>
+      <c r="M63" s="22" t="n"/>
+      <c r="N63" s="22" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="22" t="n"/>
+      <c r="B64" s="22" t="n"/>
+      <c r="C64" s="22" t="n"/>
+      <c r="D64" s="22" t="n"/>
+      <c r="E64" s="22" t="n"/>
+      <c r="F64" s="22" t="n"/>
+      <c r="G64" s="22" t="n"/>
+      <c r="H64" s="22" t="n"/>
+      <c r="I64" s="22" t="n"/>
+      <c r="J64" s="22" t="n"/>
+      <c r="K64" s="22" t="n"/>
+      <c r="L64" s="22" t="n"/>
+      <c r="M64" s="22" t="n"/>
+      <c r="N64" s="22" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="22" t="n"/>
+      <c r="B65" s="22" t="n"/>
+      <c r="C65" s="22" t="n"/>
+      <c r="D65" s="22" t="n"/>
+      <c r="E65" s="22" t="n"/>
+      <c r="F65" s="22" t="n"/>
+      <c r="G65" s="22" t="n"/>
+      <c r="H65" s="22" t="n"/>
+      <c r="I65" s="22" t="n"/>
+      <c r="J65" s="22" t="n"/>
+      <c r="K65" s="22" t="n"/>
+      <c r="L65" s="22" t="n"/>
+      <c r="M65" s="22" t="n"/>
+      <c r="N65" s="22" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="22" t="n"/>
+      <c r="B66" s="22" t="n"/>
+      <c r="C66" s="22" t="n"/>
+      <c r="D66" s="22" t="n"/>
+      <c r="E66" s="22" t="n"/>
+      <c r="F66" s="22" t="n"/>
+      <c r="G66" s="22" t="n"/>
+      <c r="H66" s="22" t="n"/>
+      <c r="I66" s="22" t="n"/>
+      <c r="J66" s="22" t="n"/>
+      <c r="K66" s="22" t="n"/>
+      <c r="L66" s="22" t="n"/>
+      <c r="M66" s="22" t="n"/>
+      <c r="N66" s="22" t="n"/>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="12" t="inlineStr">
+        <is>
+          <t>Gants   (2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="13" t="inlineStr">
+        <is>
+          <t>Miner's Gloves</t>
+        </is>
+      </c>
+      <c r="B69" s="14" t="inlineStr">
+        <is>
+          <t>gants-de-mineur</t>
+        </is>
+      </c>
+      <c r="C69" s="15" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D69" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E69" s="17" t="inlineStr">
+        <is>
+          <t>Master's Hand</t>
+        </is>
+      </c>
+      <c r="F69" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G69" s="17" t="n"/>
+      <c r="H69" s="17" t="n"/>
+      <c r="I69" s="17" t="n"/>
+      <c r="J69" s="17" t="n"/>
+      <c r="K69" s="17" t="n"/>
+      <c r="L69" s="17" t="n"/>
+      <c r="M69" s="18" t="inlineStr"/>
+      <c r="N69" s="17" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="13" t="inlineStr">
+        <is>
+          <t>Onyx Glove</t>
+        </is>
+      </c>
+      <c r="B70" s="14" t="inlineStr">
+        <is>
+          <t>gants-onyx</t>
+        </is>
+      </c>
+      <c r="C70" s="21" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="D70" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="E70" s="17" t="inlineStr">
+        <is>
+          <t>Burning Hand</t>
+        </is>
+      </c>
+      <c r="F70" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G70" s="17" t="inlineStr">
+        <is>
+          <t>Onyx Fist</t>
+        </is>
+      </c>
+      <c r="H70" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="I70" s="17" t="n"/>
+      <c r="J70" s="17" t="n"/>
+      <c r="K70" s="17" t="n"/>
+      <c r="L70" s="17" t="n"/>
+      <c r="M70" s="18" t="inlineStr">
+        <is>
+          <t>Set : Onyx Set</t>
+        </is>
+      </c>
+      <c r="N70" s="17" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="22" t="n"/>
+      <c r="B71" s="22" t="n"/>
+      <c r="C71" s="22" t="n"/>
+      <c r="D71" s="22" t="n"/>
+      <c r="E71" s="22" t="n"/>
+      <c r="F71" s="22" t="n"/>
+      <c r="G71" s="22" t="n"/>
+      <c r="H71" s="22" t="n"/>
+      <c r="I71" s="22" t="n"/>
+      <c r="J71" s="22" t="n"/>
+      <c r="K71" s="22" t="n"/>
+      <c r="L71" s="22" t="n"/>
+      <c r="M71" s="22" t="n"/>
+      <c r="N71" s="22" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="22" t="n"/>
+      <c r="B72" s="22" t="n"/>
+      <c r="C72" s="22" t="n"/>
+      <c r="D72" s="22" t="n"/>
+      <c r="E72" s="22" t="n"/>
+      <c r="F72" s="22" t="n"/>
+      <c r="G72" s="22" t="n"/>
+      <c r="H72" s="22" t="n"/>
+      <c r="I72" s="22" t="n"/>
+      <c r="J72" s="22" t="n"/>
+      <c r="K72" s="22" t="n"/>
+      <c r="L72" s="22" t="n"/>
+      <c r="M72" s="22" t="n"/>
+      <c r="N72" s="22" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="22" t="n"/>
+      <c r="B73" s="22" t="n"/>
+      <c r="C73" s="22" t="n"/>
+      <c r="D73" s="22" t="n"/>
+      <c r="E73" s="22" t="n"/>
+      <c r="F73" s="22" t="n"/>
+      <c r="G73" s="22" t="n"/>
+      <c r="H73" s="22" t="n"/>
+      <c r="I73" s="22" t="n"/>
+      <c r="J73" s="22" t="n"/>
+      <c r="K73" s="22" t="n"/>
+      <c r="L73" s="22" t="n"/>
+      <c r="M73" s="22" t="n"/>
+      <c r="N73" s="22" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="22" t="n"/>
+      <c r="B74" s="22" t="n"/>
+      <c r="C74" s="22" t="n"/>
+      <c r="D74" s="22" t="n"/>
+      <c r="E74" s="22" t="n"/>
+      <c r="F74" s="22" t="n"/>
+      <c r="G74" s="22" t="n"/>
+      <c r="H74" s="22" t="n"/>
+      <c r="I74" s="22" t="n"/>
+      <c r="J74" s="22" t="n"/>
+      <c r="K74" s="22" t="n"/>
+      <c r="L74" s="22" t="n"/>
+      <c r="M74" s="22" t="n"/>
+      <c r="N74" s="22" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="22" t="n"/>
+      <c r="B75" s="22" t="n"/>
+      <c r="C75" s="22" t="n"/>
+      <c r="D75" s="22" t="n"/>
+      <c r="E75" s="22" t="n"/>
+      <c r="F75" s="22" t="n"/>
+      <c r="G75" s="22" t="n"/>
+      <c r="H75" s="22" t="n"/>
+      <c r="I75" s="22" t="n"/>
+      <c r="J75" s="22" t="n"/>
+      <c r="K75" s="22" t="n"/>
+      <c r="L75" s="22" t="n"/>
+      <c r="M75" s="22" t="n"/>
+      <c r="N75" s="22" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="22" t="n"/>
+      <c r="B76" s="22" t="n"/>
+      <c r="C76" s="22" t="n"/>
+      <c r="D76" s="22" t="n"/>
+      <c r="E76" s="22" t="n"/>
+      <c r="F76" s="22" t="n"/>
+      <c r="G76" s="22" t="n"/>
+      <c r="H76" s="22" t="n"/>
+      <c r="I76" s="22" t="n"/>
+      <c r="J76" s="22" t="n"/>
+      <c r="K76" s="22" t="n"/>
+      <c r="L76" s="22" t="n"/>
+      <c r="M76" s="22" t="n"/>
+      <c r="N76" s="22" t="n"/>
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="12" t="inlineStr">
+        <is>
+          <t>Bottes   (2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="13" t="inlineStr">
+        <is>
+          <t>Swift Boots</t>
+        </is>
+      </c>
+      <c r="B79" s="14" t="inlineStr">
+        <is>
+          <t>bottes-vives</t>
+        </is>
+      </c>
+      <c r="C79" s="20" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="D56" s="16" t="n">
+      <c r="D79" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="E56" s="17" t="inlineStr">
-        <is>
-          <t>Bloodletting</t>
-        </is>
-      </c>
-      <c r="F56" s="16" t="n">
+      <c r="E79" s="17" t="inlineStr">
+        <is>
+          <t>Quicken</t>
+        </is>
+      </c>
+      <c r="F79" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="G56" s="17" t="n"/>
-      <c r="H56" s="17" t="n"/>
-      <c r="I56" s="17" t="n"/>
-      <c r="J56" s="17" t="n"/>
-      <c r="K56" s="17" t="n"/>
-      <c r="L56" s="17" t="n"/>
-      <c r="M56" s="17" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="13" t="inlineStr">
-        <is>
-          <t>Frost Ring</t>
-        </is>
-      </c>
-      <c r="B57" s="14" t="inlineStr">
-        <is>
-          <t>anneau-de-givre</t>
-        </is>
-      </c>
-      <c r="C57" s="18" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="D57" s="16" t="n">
+      <c r="G79" s="17" t="n"/>
+      <c r="H79" s="17" t="n"/>
+      <c r="I79" s="17" t="n"/>
+      <c r="J79" s="17" t="n"/>
+      <c r="K79" s="17" t="n"/>
+      <c r="L79" s="17" t="n"/>
+      <c r="M79" s="18" t="inlineStr"/>
+      <c r="N79" s="17" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="13" t="inlineStr">
+        <is>
+          <t>Onyx Boots</t>
+        </is>
+      </c>
+      <c r="B80" s="14" t="inlineStr">
+        <is>
+          <t>bottes-onyx</t>
+        </is>
+      </c>
+      <c r="C80" s="21" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="D80" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E80" s="17" t="inlineStr">
+        <is>
+          <t>Burning Run</t>
+        </is>
+      </c>
+      <c r="F80" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" s="17" t="inlineStr">
+        <is>
+          <t>Flaming Kick</t>
+        </is>
+      </c>
+      <c r="H80" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="E57" s="17" t="inlineStr">
-        <is>
-          <t>Frostbite</t>
-        </is>
-      </c>
-      <c r="F57" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="G57" s="17" t="n"/>
-      <c r="H57" s="17" t="n"/>
-      <c r="I57" s="17" t="n"/>
-      <c r="J57" s="17" t="n"/>
-      <c r="K57" s="17" t="n"/>
-      <c r="L57" s="17" t="n"/>
-      <c r="M57" s="17" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="20" t="n"/>
-      <c r="B58" s="20" t="n"/>
-      <c r="C58" s="20" t="n"/>
-      <c r="D58" s="20" t="n"/>
-      <c r="E58" s="20" t="n"/>
-      <c r="F58" s="20" t="n"/>
-      <c r="G58" s="20" t="n"/>
-      <c r="H58" s="20" t="n"/>
-      <c r="I58" s="20" t="n"/>
-      <c r="J58" s="20" t="n"/>
-      <c r="K58" s="20" t="n"/>
-      <c r="L58" s="20" t="n"/>
-      <c r="M58" s="20" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="20" t="n"/>
-      <c r="B59" s="20" t="n"/>
-      <c r="C59" s="20" t="n"/>
-      <c r="D59" s="20" t="n"/>
-      <c r="E59" s="20" t="n"/>
-      <c r="F59" s="20" t="n"/>
-      <c r="G59" s="20" t="n"/>
-      <c r="H59" s="20" t="n"/>
-      <c r="I59" s="20" t="n"/>
-      <c r="J59" s="20" t="n"/>
-      <c r="K59" s="20" t="n"/>
-      <c r="L59" s="20" t="n"/>
-      <c r="M59" s="20" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="20" t="n"/>
-      <c r="B60" s="20" t="n"/>
-      <c r="C60" s="20" t="n"/>
-      <c r="D60" s="20" t="n"/>
-      <c r="E60" s="20" t="n"/>
-      <c r="F60" s="20" t="n"/>
-      <c r="G60" s="20" t="n"/>
-      <c r="H60" s="20" t="n"/>
-      <c r="I60" s="20" t="n"/>
-      <c r="J60" s="20" t="n"/>
-      <c r="K60" s="20" t="n"/>
-      <c r="L60" s="20" t="n"/>
-      <c r="M60" s="20" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="20" t="n"/>
-      <c r="B61" s="20" t="n"/>
-      <c r="C61" s="20" t="n"/>
-      <c r="D61" s="20" t="n"/>
-      <c r="E61" s="20" t="n"/>
-      <c r="F61" s="20" t="n"/>
-      <c r="G61" s="20" t="n"/>
-      <c r="H61" s="20" t="n"/>
-      <c r="I61" s="20" t="n"/>
-      <c r="J61" s="20" t="n"/>
-      <c r="K61" s="20" t="n"/>
-      <c r="L61" s="20" t="n"/>
-      <c r="M61" s="20" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="20" t="n"/>
-      <c r="B62" s="20" t="n"/>
-      <c r="C62" s="20" t="n"/>
-      <c r="D62" s="20" t="n"/>
-      <c r="E62" s="20" t="n"/>
-      <c r="F62" s="20" t="n"/>
-      <c r="G62" s="20" t="n"/>
-      <c r="H62" s="20" t="n"/>
-      <c r="I62" s="20" t="n"/>
-      <c r="J62" s="20" t="n"/>
-      <c r="K62" s="20" t="n"/>
-      <c r="L62" s="20" t="n"/>
-      <c r="M62" s="20" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="20" t="n"/>
-      <c r="B63" s="20" t="n"/>
-      <c r="C63" s="20" t="n"/>
-      <c r="D63" s="20" t="n"/>
-      <c r="E63" s="20" t="n"/>
-      <c r="F63" s="20" t="n"/>
-      <c r="G63" s="20" t="n"/>
-      <c r="H63" s="20" t="n"/>
-      <c r="I63" s="20" t="n"/>
-      <c r="J63" s="20" t="n"/>
-      <c r="K63" s="20" t="n"/>
-      <c r="L63" s="20" t="n"/>
-      <c r="M63" s="20" t="n"/>
-    </row>
-    <row r="65" ht="20" customHeight="1">
-      <c r="A65" s="12" t="inlineStr">
-        <is>
-          <t>Gants   (1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="13" t="inlineStr">
-        <is>
-          <t>Miner's Gloves</t>
-        </is>
-      </c>
-      <c r="B66" s="14" t="inlineStr">
-        <is>
-          <t>gants-de-mineur</t>
-        </is>
-      </c>
-      <c r="C66" s="15" t="inlineStr">
+      <c r="I80" s="17" t="n"/>
+      <c r="J80" s="17" t="n"/>
+      <c r="K80" s="17" t="n"/>
+      <c r="L80" s="17" t="n"/>
+      <c r="M80" s="18" t="inlineStr">
+        <is>
+          <t>Set : Onyx Set</t>
+        </is>
+      </c>
+      <c r="N80" s="17" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="22" t="n"/>
+      <c r="B81" s="22" t="n"/>
+      <c r="C81" s="22" t="n"/>
+      <c r="D81" s="22" t="n"/>
+      <c r="E81" s="22" t="n"/>
+      <c r="F81" s="22" t="n"/>
+      <c r="G81" s="22" t="n"/>
+      <c r="H81" s="22" t="n"/>
+      <c r="I81" s="22" t="n"/>
+      <c r="J81" s="22" t="n"/>
+      <c r="K81" s="22" t="n"/>
+      <c r="L81" s="22" t="n"/>
+      <c r="M81" s="22" t="n"/>
+      <c r="N81" s="22" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="22" t="n"/>
+      <c r="B82" s="22" t="n"/>
+      <c r="C82" s="22" t="n"/>
+      <c r="D82" s="22" t="n"/>
+      <c r="E82" s="22" t="n"/>
+      <c r="F82" s="22" t="n"/>
+      <c r="G82" s="22" t="n"/>
+      <c r="H82" s="22" t="n"/>
+      <c r="I82" s="22" t="n"/>
+      <c r="J82" s="22" t="n"/>
+      <c r="K82" s="22" t="n"/>
+      <c r="L82" s="22" t="n"/>
+      <c r="M82" s="22" t="n"/>
+      <c r="N82" s="22" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="22" t="n"/>
+      <c r="B83" s="22" t="n"/>
+      <c r="C83" s="22" t="n"/>
+      <c r="D83" s="22" t="n"/>
+      <c r="E83" s="22" t="n"/>
+      <c r="F83" s="22" t="n"/>
+      <c r="G83" s="22" t="n"/>
+      <c r="H83" s="22" t="n"/>
+      <c r="I83" s="22" t="n"/>
+      <c r="J83" s="22" t="n"/>
+      <c r="K83" s="22" t="n"/>
+      <c r="L83" s="22" t="n"/>
+      <c r="M83" s="22" t="n"/>
+      <c r="N83" s="22" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="22" t="n"/>
+      <c r="B84" s="22" t="n"/>
+      <c r="C84" s="22" t="n"/>
+      <c r="D84" s="22" t="n"/>
+      <c r="E84" s="22" t="n"/>
+      <c r="F84" s="22" t="n"/>
+      <c r="G84" s="22" t="n"/>
+      <c r="H84" s="22" t="n"/>
+      <c r="I84" s="22" t="n"/>
+      <c r="J84" s="22" t="n"/>
+      <c r="K84" s="22" t="n"/>
+      <c r="L84" s="22" t="n"/>
+      <c r="M84" s="22" t="n"/>
+      <c r="N84" s="22" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="22" t="n"/>
+      <c r="B85" s="22" t="n"/>
+      <c r="C85" s="22" t="n"/>
+      <c r="D85" s="22" t="n"/>
+      <c r="E85" s="22" t="n"/>
+      <c r="F85" s="22" t="n"/>
+      <c r="G85" s="22" t="n"/>
+      <c r="H85" s="22" t="n"/>
+      <c r="I85" s="22" t="n"/>
+      <c r="J85" s="22" t="n"/>
+      <c r="K85" s="22" t="n"/>
+      <c r="L85" s="22" t="n"/>
+      <c r="M85" s="22" t="n"/>
+      <c r="N85" s="22" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="22" t="n"/>
+      <c r="B86" s="22" t="n"/>
+      <c r="C86" s="22" t="n"/>
+      <c r="D86" s="22" t="n"/>
+      <c r="E86" s="22" t="n"/>
+      <c r="F86" s="22" t="n"/>
+      <c r="G86" s="22" t="n"/>
+      <c r="H86" s="22" t="n"/>
+      <c r="I86" s="22" t="n"/>
+      <c r="J86" s="22" t="n"/>
+      <c r="K86" s="22" t="n"/>
+      <c r="L86" s="22" t="n"/>
+      <c r="M86" s="22" t="n"/>
+      <c r="N86" s="22" t="n"/>
+    </row>
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="12" t="inlineStr">
+        <is>
+          <t>Sacs   (2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="13" t="inlineStr">
+        <is>
+          <t>Leather Pouch</t>
+        </is>
+      </c>
+      <c r="B89" s="14" t="inlineStr">
+        <is>
+          <t>sac-en-cuir</t>
+        </is>
+      </c>
+      <c r="C89" s="15" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="D66" s="16" t="n">
+      <c r="D89" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="E66" s="17" t="n"/>
-      <c r="F66" s="17" t="n"/>
-      <c r="G66" s="17" t="n"/>
-      <c r="H66" s="17" t="n"/>
-      <c r="I66" s="17" t="n"/>
-      <c r="J66" s="17" t="n"/>
-      <c r="K66" s="17" t="n"/>
-      <c r="L66" s="17" t="n"/>
-      <c r="M66" s="17" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="20" t="n"/>
-      <c r="B67" s="20" t="n"/>
-      <c r="C67" s="20" t="n"/>
-      <c r="D67" s="20" t="n"/>
-      <c r="E67" s="20" t="n"/>
-      <c r="F67" s="20" t="n"/>
-      <c r="G67" s="20" t="n"/>
-      <c r="H67" s="20" t="n"/>
-      <c r="I67" s="20" t="n"/>
-      <c r="J67" s="20" t="n"/>
-      <c r="K67" s="20" t="n"/>
-      <c r="L67" s="20" t="n"/>
-      <c r="M67" s="20" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="20" t="n"/>
-      <c r="B68" s="20" t="n"/>
-      <c r="C68" s="20" t="n"/>
-      <c r="D68" s="20" t="n"/>
-      <c r="E68" s="20" t="n"/>
-      <c r="F68" s="20" t="n"/>
-      <c r="G68" s="20" t="n"/>
-      <c r="H68" s="20" t="n"/>
-      <c r="I68" s="20" t="n"/>
-      <c r="J68" s="20" t="n"/>
-      <c r="K68" s="20" t="n"/>
-      <c r="L68" s="20" t="n"/>
-      <c r="M68" s="20" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="20" t="n"/>
-      <c r="B69" s="20" t="n"/>
-      <c r="C69" s="20" t="n"/>
-      <c r="D69" s="20" t="n"/>
-      <c r="E69" s="20" t="n"/>
-      <c r="F69" s="20" t="n"/>
-      <c r="G69" s="20" t="n"/>
-      <c r="H69" s="20" t="n"/>
-      <c r="I69" s="20" t="n"/>
-      <c r="J69" s="20" t="n"/>
-      <c r="K69" s="20" t="n"/>
-      <c r="L69" s="20" t="n"/>
-      <c r="M69" s="20" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="20" t="n"/>
-      <c r="B70" s="20" t="n"/>
-      <c r="C70" s="20" t="n"/>
-      <c r="D70" s="20" t="n"/>
-      <c r="E70" s="20" t="n"/>
-      <c r="F70" s="20" t="n"/>
-      <c r="G70" s="20" t="n"/>
-      <c r="H70" s="20" t="n"/>
-      <c r="I70" s="20" t="n"/>
-      <c r="J70" s="20" t="n"/>
-      <c r="K70" s="20" t="n"/>
-      <c r="L70" s="20" t="n"/>
-      <c r="M70" s="20" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="20" t="n"/>
-      <c r="B71" s="20" t="n"/>
-      <c r="C71" s="20" t="n"/>
-      <c r="D71" s="20" t="n"/>
-      <c r="E71" s="20" t="n"/>
-      <c r="F71" s="20" t="n"/>
-      <c r="G71" s="20" t="n"/>
-      <c r="H71" s="20" t="n"/>
-      <c r="I71" s="20" t="n"/>
-      <c r="J71" s="20" t="n"/>
-      <c r="K71" s="20" t="n"/>
-      <c r="L71" s="20" t="n"/>
-      <c r="M71" s="20" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="20" t="n"/>
-      <c r="B72" s="20" t="n"/>
-      <c r="C72" s="20" t="n"/>
-      <c r="D72" s="20" t="n"/>
-      <c r="E72" s="20" t="n"/>
-      <c r="F72" s="20" t="n"/>
-      <c r="G72" s="20" t="n"/>
-      <c r="H72" s="20" t="n"/>
-      <c r="I72" s="20" t="n"/>
-      <c r="J72" s="20" t="n"/>
-      <c r="K72" s="20" t="n"/>
-      <c r="L72" s="20" t="n"/>
-      <c r="M72" s="20" t="n"/>
-    </row>
-    <row r="74" ht="20" customHeight="1">
-      <c r="A74" s="12" t="inlineStr">
-        <is>
-          <t>Bottes   (1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="13" t="inlineStr">
-        <is>
-          <t>Swift Boots</t>
-        </is>
-      </c>
-      <c r="B75" s="14" t="inlineStr">
-        <is>
-          <t>bottes-vives</t>
-        </is>
-      </c>
-      <c r="C75" s="18" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="D75" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E75" s="17" t="inlineStr">
-        <is>
-          <t>Quicken</t>
-        </is>
-      </c>
-      <c r="F75" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="G75" s="17" t="n"/>
-      <c r="H75" s="17" t="n"/>
-      <c r="I75" s="17" t="n"/>
-      <c r="J75" s="17" t="n"/>
-      <c r="K75" s="17" t="n"/>
-      <c r="L75" s="17" t="n"/>
-      <c r="M75" s="17" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="20" t="n"/>
-      <c r="B76" s="20" t="n"/>
-      <c r="C76" s="20" t="n"/>
-      <c r="D76" s="20" t="n"/>
-      <c r="E76" s="20" t="n"/>
-      <c r="F76" s="20" t="n"/>
-      <c r="G76" s="20" t="n"/>
-      <c r="H76" s="20" t="n"/>
-      <c r="I76" s="20" t="n"/>
-      <c r="J76" s="20" t="n"/>
-      <c r="K76" s="20" t="n"/>
-      <c r="L76" s="20" t="n"/>
-      <c r="M76" s="20" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="20" t="n"/>
-      <c r="B77" s="20" t="n"/>
-      <c r="C77" s="20" t="n"/>
-      <c r="D77" s="20" t="n"/>
-      <c r="E77" s="20" t="n"/>
-      <c r="F77" s="20" t="n"/>
-      <c r="G77" s="20" t="n"/>
-      <c r="H77" s="20" t="n"/>
-      <c r="I77" s="20" t="n"/>
-      <c r="J77" s="20" t="n"/>
-      <c r="K77" s="20" t="n"/>
-      <c r="L77" s="20" t="n"/>
-      <c r="M77" s="20" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="20" t="n"/>
-      <c r="B78" s="20" t="n"/>
-      <c r="C78" s="20" t="n"/>
-      <c r="D78" s="20" t="n"/>
-      <c r="E78" s="20" t="n"/>
-      <c r="F78" s="20" t="n"/>
-      <c r="G78" s="20" t="n"/>
-      <c r="H78" s="20" t="n"/>
-      <c r="I78" s="20" t="n"/>
-      <c r="J78" s="20" t="n"/>
-      <c r="K78" s="20" t="n"/>
-      <c r="L78" s="20" t="n"/>
-      <c r="M78" s="20" t="n"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="20" t="n"/>
-      <c r="B79" s="20" t="n"/>
-      <c r="C79" s="20" t="n"/>
-      <c r="D79" s="20" t="n"/>
-      <c r="E79" s="20" t="n"/>
-      <c r="F79" s="20" t="n"/>
-      <c r="G79" s="20" t="n"/>
-      <c r="H79" s="20" t="n"/>
-      <c r="I79" s="20" t="n"/>
-      <c r="J79" s="20" t="n"/>
-      <c r="K79" s="20" t="n"/>
-      <c r="L79" s="20" t="n"/>
-      <c r="M79" s="20" t="n"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="20" t="n"/>
-      <c r="B80" s="20" t="n"/>
-      <c r="C80" s="20" t="n"/>
-      <c r="D80" s="20" t="n"/>
-      <c r="E80" s="20" t="n"/>
-      <c r="F80" s="20" t="n"/>
-      <c r="G80" s="20" t="n"/>
-      <c r="H80" s="20" t="n"/>
-      <c r="I80" s="20" t="n"/>
-      <c r="J80" s="20" t="n"/>
-      <c r="K80" s="20" t="n"/>
-      <c r="L80" s="20" t="n"/>
-      <c r="M80" s="20" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="20" t="n"/>
-      <c r="B81" s="20" t="n"/>
-      <c r="C81" s="20" t="n"/>
-      <c r="D81" s="20" t="n"/>
-      <c r="E81" s="20" t="n"/>
-      <c r="F81" s="20" t="n"/>
-      <c r="G81" s="20" t="n"/>
-      <c r="H81" s="20" t="n"/>
-      <c r="I81" s="20" t="n"/>
-      <c r="J81" s="20" t="n"/>
-      <c r="K81" s="20" t="n"/>
-      <c r="L81" s="20" t="n"/>
-      <c r="M81" s="20" t="n"/>
-    </row>
-    <row r="83" ht="20" customHeight="1">
-      <c r="A83" s="12" t="inlineStr">
-        <is>
-          <t>Sacs   (1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="13" t="inlineStr">
-        <is>
-          <t>Leather Pouch</t>
-        </is>
-      </c>
-      <c r="B84" s="14" t="inlineStr">
-        <is>
-          <t>sac-en-cuir</t>
-        </is>
-      </c>
-      <c r="C84" s="15" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="D84" s="16" t="n">
+      <c r="E89" s="17" t="n"/>
+      <c r="F89" s="17" t="n"/>
+      <c r="G89" s="17" t="n"/>
+      <c r="H89" s="17" t="n"/>
+      <c r="I89" s="17" t="n"/>
+      <c r="J89" s="17" t="n"/>
+      <c r="K89" s="17" t="n"/>
+      <c r="L89" s="17" t="n"/>
+      <c r="M89" s="18" t="inlineStr">
+        <is>
+          <t>+2 rangées de sac</t>
+        </is>
+      </c>
+      <c r="N89" s="17" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="13" t="inlineStr">
+        <is>
+          <t>Big Leather Pouch</t>
+        </is>
+      </c>
+      <c r="B90" s="14" t="inlineStr">
+        <is>
+          <t>grand-sac-en-cuir</t>
+        </is>
+      </c>
+      <c r="C90" s="19" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D90" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="E84" s="17" t="n"/>
-      <c r="F84" s="17" t="n"/>
-      <c r="G84" s="17" t="n"/>
-      <c r="H84" s="17" t="n"/>
-      <c r="I84" s="17" t="n"/>
-      <c r="J84" s="17" t="n"/>
-      <c r="K84" s="17" t="n"/>
-      <c r="L84" s="17" t="n"/>
-      <c r="M84" s="17" t="n"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="20" t="n"/>
-      <c r="B85" s="20" t="n"/>
-      <c r="C85" s="20" t="n"/>
-      <c r="D85" s="20" t="n"/>
-      <c r="E85" s="20" t="n"/>
-      <c r="F85" s="20" t="n"/>
-      <c r="G85" s="20" t="n"/>
-      <c r="H85" s="20" t="n"/>
-      <c r="I85" s="20" t="n"/>
-      <c r="J85" s="20" t="n"/>
-      <c r="K85" s="20" t="n"/>
-      <c r="L85" s="20" t="n"/>
-      <c r="M85" s="20" t="n"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="20" t="n"/>
-      <c r="B86" s="20" t="n"/>
-      <c r="C86" s="20" t="n"/>
-      <c r="D86" s="20" t="n"/>
-      <c r="E86" s="20" t="n"/>
-      <c r="F86" s="20" t="n"/>
-      <c r="G86" s="20" t="n"/>
-      <c r="H86" s="20" t="n"/>
-      <c r="I86" s="20" t="n"/>
-      <c r="J86" s="20" t="n"/>
-      <c r="K86" s="20" t="n"/>
-      <c r="L86" s="20" t="n"/>
-      <c r="M86" s="20" t="n"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="20" t="n"/>
-      <c r="B87" s="20" t="n"/>
-      <c r="C87" s="20" t="n"/>
-      <c r="D87" s="20" t="n"/>
-      <c r="E87" s="20" t="n"/>
-      <c r="F87" s="20" t="n"/>
-      <c r="G87" s="20" t="n"/>
-      <c r="H87" s="20" t="n"/>
-      <c r="I87" s="20" t="n"/>
-      <c r="J87" s="20" t="n"/>
-      <c r="K87" s="20" t="n"/>
-      <c r="L87" s="20" t="n"/>
-      <c r="M87" s="20" t="n"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="20" t="n"/>
-      <c r="B88" s="20" t="n"/>
-      <c r="C88" s="20" t="n"/>
-      <c r="D88" s="20" t="n"/>
-      <c r="E88" s="20" t="n"/>
-      <c r="F88" s="20" t="n"/>
-      <c r="G88" s="20" t="n"/>
-      <c r="H88" s="20" t="n"/>
-      <c r="I88" s="20" t="n"/>
-      <c r="J88" s="20" t="n"/>
-      <c r="K88" s="20" t="n"/>
-      <c r="L88" s="20" t="n"/>
-      <c r="M88" s="20" t="n"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="20" t="n"/>
-      <c r="B89" s="20" t="n"/>
-      <c r="C89" s="20" t="n"/>
-      <c r="D89" s="20" t="n"/>
-      <c r="E89" s="20" t="n"/>
-      <c r="F89" s="20" t="n"/>
-      <c r="G89" s="20" t="n"/>
-      <c r="H89" s="20" t="n"/>
-      <c r="I89" s="20" t="n"/>
-      <c r="J89" s="20" t="n"/>
-      <c r="K89" s="20" t="n"/>
-      <c r="L89" s="20" t="n"/>
-      <c r="M89" s="20" t="n"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="20" t="n"/>
-      <c r="B90" s="20" t="n"/>
-      <c r="C90" s="20" t="n"/>
-      <c r="D90" s="20" t="n"/>
-      <c r="E90" s="20" t="n"/>
-      <c r="F90" s="20" t="n"/>
-      <c r="G90" s="20" t="n"/>
-      <c r="H90" s="20" t="n"/>
-      <c r="I90" s="20" t="n"/>
-      <c r="J90" s="20" t="n"/>
-      <c r="K90" s="20" t="n"/>
-      <c r="L90" s="20" t="n"/>
-      <c r="M90" s="20" t="n"/>
+      <c r="E90" s="17" t="n"/>
+      <c r="F90" s="17" t="n"/>
+      <c r="G90" s="17" t="n"/>
+      <c r="H90" s="17" t="n"/>
+      <c r="I90" s="17" t="n"/>
+      <c r="J90" s="17" t="n"/>
+      <c r="K90" s="17" t="n"/>
+      <c r="L90" s="17" t="n"/>
+      <c r="M90" s="18" t="inlineStr">
+        <is>
+          <t>+3 rangées de sac</t>
+        </is>
+      </c>
+      <c r="N90" s="17" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="22" t="n"/>
+      <c r="B91" s="22" t="n"/>
+      <c r="C91" s="22" t="n"/>
+      <c r="D91" s="22" t="n"/>
+      <c r="E91" s="22" t="n"/>
+      <c r="F91" s="22" t="n"/>
+      <c r="G91" s="22" t="n"/>
+      <c r="H91" s="22" t="n"/>
+      <c r="I91" s="22" t="n"/>
+      <c r="J91" s="22" t="n"/>
+      <c r="K91" s="22" t="n"/>
+      <c r="L91" s="22" t="n"/>
+      <c r="M91" s="22" t="n"/>
+      <c r="N91" s="22" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="22" t="n"/>
+      <c r="B92" s="22" t="n"/>
+      <c r="C92" s="22" t="n"/>
+      <c r="D92" s="22" t="n"/>
+      <c r="E92" s="22" t="n"/>
+      <c r="F92" s="22" t="n"/>
+      <c r="G92" s="22" t="n"/>
+      <c r="H92" s="22" t="n"/>
+      <c r="I92" s="22" t="n"/>
+      <c r="J92" s="22" t="n"/>
+      <c r="K92" s="22" t="n"/>
+      <c r="L92" s="22" t="n"/>
+      <c r="M92" s="22" t="n"/>
+      <c r="N92" s="22" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="22" t="n"/>
+      <c r="B93" s="22" t="n"/>
+      <c r="C93" s="22" t="n"/>
+      <c r="D93" s="22" t="n"/>
+      <c r="E93" s="22" t="n"/>
+      <c r="F93" s="22" t="n"/>
+      <c r="G93" s="22" t="n"/>
+      <c r="H93" s="22" t="n"/>
+      <c r="I93" s="22" t="n"/>
+      <c r="J93" s="22" t="n"/>
+      <c r="K93" s="22" t="n"/>
+      <c r="L93" s="22" t="n"/>
+      <c r="M93" s="22" t="n"/>
+      <c r="N93" s="22" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="22" t="n"/>
+      <c r="B94" s="22" t="n"/>
+      <c r="C94" s="22" t="n"/>
+      <c r="D94" s="22" t="n"/>
+      <c r="E94" s="22" t="n"/>
+      <c r="F94" s="22" t="n"/>
+      <c r="G94" s="22" t="n"/>
+      <c r="H94" s="22" t="n"/>
+      <c r="I94" s="22" t="n"/>
+      <c r="J94" s="22" t="n"/>
+      <c r="K94" s="22" t="n"/>
+      <c r="L94" s="22" t="n"/>
+      <c r="M94" s="22" t="n"/>
+      <c r="N94" s="22" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="22" t="n"/>
+      <c r="B95" s="22" t="n"/>
+      <c r="C95" s="22" t="n"/>
+      <c r="D95" s="22" t="n"/>
+      <c r="E95" s="22" t="n"/>
+      <c r="F95" s="22" t="n"/>
+      <c r="G95" s="22" t="n"/>
+      <c r="H95" s="22" t="n"/>
+      <c r="I95" s="22" t="n"/>
+      <c r="J95" s="22" t="n"/>
+      <c r="K95" s="22" t="n"/>
+      <c r="L95" s="22" t="n"/>
+      <c r="M95" s="22" t="n"/>
+      <c r="N95" s="22" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="22" t="n"/>
+      <c r="B96" s="22" t="n"/>
+      <c r="C96" s="22" t="n"/>
+      <c r="D96" s="22" t="n"/>
+      <c r="E96" s="22" t="n"/>
+      <c r="F96" s="22" t="n"/>
+      <c r="G96" s="22" t="n"/>
+      <c r="H96" s="22" t="n"/>
+      <c r="I96" s="22" t="n"/>
+      <c r="J96" s="22" t="n"/>
+      <c r="K96" s="22" t="n"/>
+      <c r="L96" s="22" t="n"/>
+      <c r="M96" s="22" t="n"/>
+      <c r="N96" s="22" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A46:M46"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A74:M74"/>
-    <mergeCell ref="A17:M17"/>
-    <mergeCell ref="A35:M35"/>
-    <mergeCell ref="A4:M4"/>
-    <mergeCell ref="A26:M26"/>
-    <mergeCell ref="A55:M55"/>
-    <mergeCell ref="A83:M83"/>
-    <mergeCell ref="A65:M65"/>
-    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A17:N17"/>
+    <mergeCell ref="A27:N27"/>
+    <mergeCell ref="A88:N88"/>
+    <mergeCell ref="A4:N4"/>
+    <mergeCell ref="A78:N78"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A68:N68"/>
+    <mergeCell ref="A47:N47"/>
+    <mergeCell ref="A36:N36"/>
+    <mergeCell ref="A58:N58"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2295,7 +2674,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2352,12 +2731,12 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t>Bloodletting</t>
         </is>
       </c>
-      <c r="B3" s="22" t="inlineStr">
+      <c r="B3" s="24" t="inlineStr">
         <is>
           <t>coup-de-sang</t>
         </is>
@@ -2365,7 +2744,7 @@
       <c r="C3" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="23" t="inlineStr">
+      <c r="D3" s="25" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
@@ -2383,20 +2762,20 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="21" t="inlineStr">
-        <is>
-          <t>Cleave</t>
-        </is>
-      </c>
-      <c r="B4" s="22" t="inlineStr">
-        <is>
-          <t>couper-en-deux</t>
+      <c r="A4" s="23" t="inlineStr">
+        <is>
+          <t>Burning Hand</t>
+        </is>
+      </c>
+      <c r="B4" s="24" t="inlineStr">
+        <is>
+          <t>main-brulante</t>
         </is>
       </c>
       <c r="C4" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="D4" s="23" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="D4" s="25" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
@@ -2404,96 +2783,96 @@
       <c r="E4" s="16" t="inlineStr"/>
       <c r="F4" s="17" t="inlineStr">
         <is>
+          <t>Onyx Glove</t>
+        </is>
+      </c>
+      <c r="G4" s="17" t="inlineStr">
+        <is>
+          <t>Discard your hand. For each card discarded, apply 3 Burning to a random enemy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="23" t="inlineStr">
+        <is>
+          <t>Cleave</t>
+        </is>
+      </c>
+      <c r="B5" s="24" t="inlineStr">
+        <is>
+          <t>couper-en-deux</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="25" t="inlineStr">
+        <is>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="E5" s="16" t="inlineStr"/>
+      <c r="F5" s="17" t="inlineStr">
+        <is>
           <t>War Axe</t>
         </is>
       </c>
-      <c r="G4" s="17" t="inlineStr">
+      <c r="G5" s="17" t="inlineStr">
         <is>
           <t>Deal 12 damage. If the target dies, deal 12 damage to the next enemy.</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="21" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="23" t="inlineStr">
         <is>
           <t>Dragon's Blaze</t>
         </is>
       </c>
-      <c r="B5" s="22" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>embrasement-dragon</t>
         </is>
       </c>
-      <c r="C5" s="16" t="n">
+      <c r="C6" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="D5" s="23" t="inlineStr">
+      <c r="D6" s="25" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E5" s="16" t="inlineStr">
+      <c r="E6" s="16" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="F6" s="17" t="inlineStr">
         <is>
           <t>Onyx Guard Plate</t>
         </is>
       </c>
-      <c r="G5" s="17" t="inlineStr">
+      <c r="G6" s="17" t="inlineStr">
         <is>
           <t>Detonate all Burning: deal 2 damage per Burning on ALL enemies.</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="21" t="inlineStr">
-        <is>
-          <t>Forge Smash</t>
-        </is>
-      </c>
-      <c r="B6" s="22" t="inlineStr">
-        <is>
-          <t>ecrasement</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="D6" s="23" t="inlineStr">
-        <is>
-          <t>Attaque</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="inlineStr"/>
-      <c r="F6" s="17" t="inlineStr">
-        <is>
-          <t>Forge Hammer</t>
-        </is>
-      </c>
-      <c r="G6" s="17" t="inlineStr">
-        <is>
-          <t>Deal 8 damage. Gain 3 Stone.</t>
-        </is>
-      </c>
-    </row>
     <row r="7">
-      <c r="A7" s="21" t="inlineStr">
-        <is>
-          <t>Frostbite</t>
-        </is>
-      </c>
-      <c r="B7" s="22" t="inlineStr">
-        <is>
-          <t>givre-lent</t>
+      <c r="A7" s="23" t="inlineStr">
+        <is>
+          <t>Flaming Kick</t>
+        </is>
+      </c>
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>coup-de-pied-ardent</t>
         </is>
       </c>
       <c r="C7" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="23" t="inlineStr">
+      <c r="D7" s="25" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
@@ -2501,65 +2880,61 @@
       <c r="E7" s="16" t="inlineStr"/>
       <c r="F7" s="17" t="inlineStr">
         <is>
-          <t>Frost Ring</t>
+          <t>Onyx Boots</t>
         </is>
       </c>
       <c r="G7" s="17" t="inlineStr">
         <is>
-          <t>Deal 2 damage. Chill: -30% speed for 3 turns.</t>
+          <t>Move all Burning from the target to the enemy behind it.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="21" t="inlineStr">
-        <is>
-          <t>Giant Swing</t>
-        </is>
-      </c>
-      <c r="B8" s="22" t="inlineStr">
-        <is>
-          <t>giant-swing</t>
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>Forge Smash</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>ecrasement</t>
         </is>
       </c>
       <c r="C8" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="D8" s="23" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="D8" s="25" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
+      <c r="E8" s="16" t="inlineStr"/>
       <c r="F8" s="17" t="inlineStr">
         <is>
-          <t>War Axe</t>
+          <t>Forge Hammer</t>
         </is>
       </c>
       <c r="G8" s="17" t="inlineStr">
         <is>
-          <t>Deal 9 damage to ALL enemies.</t>
+          <t>Deal 8 damage. Gain 3 Stone.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="inlineStr">
-        <is>
-          <t>Lava Hammer</t>
-        </is>
-      </c>
-      <c r="B9" s="22" t="inlineStr">
-        <is>
-          <t>coup-de-lave</t>
+      <c r="A9" s="23" t="inlineStr">
+        <is>
+          <t>Frostbite</t>
+        </is>
+      </c>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>givre-lent</t>
         </is>
       </c>
       <c r="C9" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="D9" s="23" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="D9" s="25" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
@@ -2567,30 +2942,30 @@
       <c r="E9" s="16" t="inlineStr"/>
       <c r="F9" s="17" t="inlineStr">
         <is>
-          <t>Magma Hammer</t>
+          <t>Frost Ring</t>
         </is>
       </c>
       <c r="G9" s="17" t="inlineStr">
         <is>
-          <t>Deal 5 damage. Apply 4 Burning.</t>
+          <t>Deal 2 damage. Chill: -30% speed for 3 turns.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="21" t="inlineStr">
-        <is>
-          <t>Onyx Breath</t>
-        </is>
-      </c>
-      <c r="B10" s="22" t="inlineStr">
-        <is>
-          <t>souffle-onyx</t>
+      <c r="A10" s="23" t="inlineStr">
+        <is>
+          <t>Giant Swing</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>giant-swing</t>
         </is>
       </c>
       <c r="C10" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="D10" s="23" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="D10" s="25" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
@@ -2602,61 +2977,65 @@
       </c>
       <c r="F10" s="17" t="inlineStr">
         <is>
-          <t>Onyx Guard Plate</t>
+          <t>War Axe</t>
         </is>
       </c>
       <c r="G10" s="17" t="inlineStr">
         <is>
-          <t>Apply 8 Burning to ALL enemies.</t>
+          <t>Deal 9 damage to ALL enemies.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="inlineStr">
-        <is>
-          <t>Pickaxe Jab</t>
-        </is>
-      </c>
-      <c r="B11" s="22" t="inlineStr">
-        <is>
-          <t>coup-de-pioche</t>
+      <c r="A11" s="23" t="inlineStr">
+        <is>
+          <t>Heat Rejection</t>
+        </is>
+      </c>
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>rejet-chaleur</t>
         </is>
       </c>
       <c r="C11" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" s="23" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="D11" s="25" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E11" s="16" t="inlineStr"/>
+      <c r="E11" s="16" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t>Miner's Pick</t>
+          <t>Big Onyx Sword</t>
         </is>
       </c>
       <c r="G11" s="17" t="inlineStr">
         <is>
-          <t>Deal 3 damage twice.</t>
+          <t>Spend all Forge Heat. Apply 3 Burning per Heat spent to ALL enemies.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="21" t="inlineStr">
-        <is>
-          <t>Pommel Strike</t>
-        </is>
-      </c>
-      <c r="B12" s="22" t="inlineStr">
-        <is>
-          <t>coup-de-pommeau</t>
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>Lava Hammer</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>coup-de-lave</t>
         </is>
       </c>
       <c r="C12" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="23" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="D12" s="25" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
@@ -2664,61 +3043,65 @@
       <c r="E12" s="16" t="inlineStr"/>
       <c r="F12" s="17" t="inlineStr">
         <is>
-          <t>War Axe</t>
+          <t>Magma Hammer</t>
         </is>
       </c>
       <c r="G12" s="17" t="inlineStr">
         <is>
-          <t>Deal 4 damage. Stun the target for 1 turn.</t>
+          <t>Deal 5 damage. Apply 4 Burning.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="21" t="inlineStr">
-        <is>
-          <t>Punch</t>
-        </is>
-      </c>
-      <c r="B13" s="22" t="inlineStr">
-        <is>
-          <t>coup-faible</t>
+      <c r="A13" s="23" t="inlineStr">
+        <is>
+          <t>Onyx Breath</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>souffle-onyx</t>
         </is>
       </c>
       <c r="C13" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="23" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="D13" s="25" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E13" s="16" t="inlineStr"/>
+      <c r="E13" s="16" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t>— (deck de base)</t>
+          <t>Onyx Guard Plate</t>
         </is>
       </c>
       <c r="G13" s="17" t="inlineStr">
         <is>
-          <t>Deal 3 damage.</t>
+          <t>Apply 8 Burning to ALL enemies.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="21" t="inlineStr">
-        <is>
-          <t>Rusty Cleave</t>
-        </is>
-      </c>
-      <c r="B14" s="22" t="inlineStr">
-        <is>
-          <t>coup-de-hache</t>
+      <c r="A14" s="23" t="inlineStr">
+        <is>
+          <t>Onyx Fist</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>poing-onyx</t>
         </is>
       </c>
       <c r="C14" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="D14" s="23" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="D14" s="25" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
@@ -2726,61 +3109,65 @@
       <c r="E14" s="16" t="inlineStr"/>
       <c r="F14" s="17" t="inlineStr">
         <is>
-          <t>Rusty Axe</t>
+          <t>Onyx Glove</t>
         </is>
       </c>
       <c r="G14" s="17" t="inlineStr">
         <is>
-          <t>Deal 12 damage.</t>
+          <t>Gain 5 Stone. Deal 2 damage and apply 1 Burning.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="21" t="inlineStr">
-        <is>
-          <t>Shield Bash</t>
-        </is>
-      </c>
-      <c r="B15" s="22" t="inlineStr">
-        <is>
-          <t>coup-de-bouclier</t>
+      <c r="A15" s="23" t="inlineStr">
+        <is>
+          <t>Onyx Radiance</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>onyx-radiance</t>
         </is>
       </c>
       <c r="C15" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="25" t="inlineStr">
+        <is>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="E15" s="16" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="F15" s="17" t="inlineStr">
+        <is>
+          <t>Big Onyx Sword</t>
+        </is>
+      </c>
+      <c r="G15" s="17" t="inlineStr">
+        <is>
+          <t>Apply 2 Burning to ALL enemies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="23" t="inlineStr">
+        <is>
+          <t>Onyx Slash</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>onyx-slash</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D15" s="23" t="inlineStr">
-        <is>
-          <t>Attaque</t>
-        </is>
-      </c>
-      <c r="E15" s="16" t="inlineStr"/>
-      <c r="F15" s="17" t="inlineStr">
-        <is>
-          <t>Tower Shield</t>
-        </is>
-      </c>
-      <c r="G15" s="17" t="inlineStr">
-        <is>
-          <t>Deal 3 damage. Stun the enemy for 2 turns.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="21" t="inlineStr">
-        <is>
-          <t>Strike</t>
-        </is>
-      </c>
-      <c r="B16" s="22" t="inlineStr">
-        <is>
-          <t>frappe</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" s="23" t="inlineStr">
+      <c r="D16" s="25" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
@@ -2788,30 +3175,30 @@
       <c r="E16" s="16" t="inlineStr"/>
       <c r="F16" s="17" t="inlineStr">
         <is>
-          <t>— (deck de base)</t>
+          <t>Big Onyx Sword</t>
         </is>
       </c>
       <c r="G16" s="17" t="inlineStr">
         <is>
-          <t>Deal 6 damage.</t>
+          <t>Deal 12 damage and 4 Burning. The enemy behind takes half (6 damage, 2 Burning).</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="21" t="inlineStr">
-        <is>
-          <t>Venom Stab</t>
-        </is>
-      </c>
-      <c r="B17" s="22" t="inlineStr">
-        <is>
-          <t>coup-venimeux</t>
+      <c r="A17" s="23" t="inlineStr">
+        <is>
+          <t>Pickaxe Jab</t>
+        </is>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>coup-de-pioche</t>
         </is>
       </c>
       <c r="C17" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="23" t="inlineStr">
+      <c r="D17" s="25" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
@@ -2819,63 +3206,63 @@
       <c r="E17" s="16" t="inlineStr"/>
       <c r="F17" s="17" t="inlineStr">
         <is>
-          <t>Basilisk Fang</t>
+          <t>Miner's Pick</t>
         </is>
       </c>
       <c r="G17" s="17" t="inlineStr">
         <is>
-          <t>Deal 4 damage. Apply 4 Poison.</t>
+          <t>Deal 3 damage twice.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="21" t="inlineStr">
-        <is>
-          <t>Guard</t>
-        </is>
-      </c>
-      <c r="B18" s="22" t="inlineStr">
-        <is>
-          <t>garde</t>
+      <c r="A18" s="23" t="inlineStr">
+        <is>
+          <t>Pommel Strike</t>
+        </is>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>coup-de-pommeau</t>
         </is>
       </c>
       <c r="C18" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="24" t="inlineStr">
-        <is>
-          <t>Défense</t>
+      <c r="D18" s="25" t="inlineStr">
+        <is>
+          <t>Attaque</t>
         </is>
       </c>
       <c r="E18" s="16" t="inlineStr"/>
       <c r="F18" s="17" t="inlineStr">
         <is>
-          <t>— (deck de base)</t>
+          <t>War Axe</t>
         </is>
       </c>
       <c r="G18" s="17" t="inlineStr">
         <is>
-          <t>Gain 5 Stone.</t>
+          <t>Deal 4 damage. Stun the target for 1 turn.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="21" t="inlineStr">
-        <is>
-          <t>Hand Guard</t>
-        </is>
-      </c>
-      <c r="B19" s="22" t="inlineStr">
-        <is>
-          <t>garde-faible</t>
+      <c r="A19" s="23" t="inlineStr">
+        <is>
+          <t>Punch</t>
+        </is>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>coup-faible</t>
         </is>
       </c>
       <c r="C19" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" s="24" t="inlineStr">
-        <is>
-          <t>Défense</t>
+        <v>0</v>
+      </c>
+      <c r="D19" s="25" t="inlineStr">
+        <is>
+          <t>Attaque</t>
         </is>
       </c>
       <c r="E19" s="16" t="inlineStr"/>
@@ -2886,191 +3273,470 @@
       </c>
       <c r="G19" s="17" t="inlineStr">
         <is>
-          <t>Gain 3 Stone.</t>
+          <t>Deal 3 damage.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="21" t="inlineStr">
-        <is>
-          <t>Mail Armor</t>
-        </is>
-      </c>
-      <c r="B20" s="22" t="inlineStr">
-        <is>
-          <t>mail-armor</t>
+      <c r="A20" s="23" t="inlineStr">
+        <is>
+          <t>Rusty Cleave</t>
+        </is>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>coup-de-hache</t>
         </is>
       </c>
       <c r="C20" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" s="24" t="inlineStr">
-        <is>
-          <t>Défense</t>
+        <v>2</v>
+      </c>
+      <c r="D20" s="25" t="inlineStr">
+        <is>
+          <t>Attaque</t>
         </is>
       </c>
       <c r="E20" s="16" t="inlineStr"/>
       <c r="F20" s="17" t="inlineStr">
         <is>
-          <t>Forgemaster's Mail</t>
+          <t>Rusty Axe</t>
         </is>
       </c>
       <c r="G20" s="17" t="inlineStr">
         <is>
-          <t>Gain 5 Stone.</t>
+          <t>Deal 12 damage.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="21" t="inlineStr">
-        <is>
-          <t>Onyx Armor</t>
-        </is>
-      </c>
-      <c r="B21" s="22" t="inlineStr">
-        <is>
-          <t>onyx-armor</t>
+      <c r="A21" s="23" t="inlineStr">
+        <is>
+          <t>Shield Bash</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>coup-de-bouclier</t>
         </is>
       </c>
       <c r="C21" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D21" s="24" t="inlineStr">
-        <is>
-          <t>Défense</t>
+      <c r="D21" s="25" t="inlineStr">
+        <is>
+          <t>Attaque</t>
         </is>
       </c>
       <c r="E21" s="16" t="inlineStr"/>
       <c r="F21" s="17" t="inlineStr">
         <is>
-          <t>Onyx Guard Plate</t>
+          <t>Tower Shield</t>
         </is>
       </c>
       <c r="G21" s="17" t="inlineStr">
         <is>
-          <t>Gain 15 Stone.</t>
+          <t>Deal 3 damage. Stun the enemy for 2 turns.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="21" t="inlineStr">
-        <is>
-          <t>Quench</t>
-        </is>
-      </c>
-      <c r="B22" s="22" t="inlineStr">
-        <is>
-          <t>trempe</t>
+      <c r="A22" s="23" t="inlineStr">
+        <is>
+          <t>Strike</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>frappe</t>
         </is>
       </c>
       <c r="C22" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="24" t="inlineStr">
-        <is>
-          <t>Défense</t>
+        <v>1</v>
+      </c>
+      <c r="D22" s="25" t="inlineStr">
+        <is>
+          <t>Attaque</t>
         </is>
       </c>
       <c r="E22" s="16" t="inlineStr"/>
       <c r="F22" s="17" t="inlineStr">
         <is>
-          <t>Forgemaster's Mail</t>
+          <t>— (deck de base)</t>
         </is>
       </c>
       <c r="G22" s="17" t="inlineStr">
         <is>
-          <t>Spend all Forge Heat. Gain 4 Stone per Heat spent.</t>
+          <t>Deal 6 damage.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="21" t="inlineStr">
-        <is>
-          <t>Shield Wall</t>
-        </is>
-      </c>
-      <c r="B23" s="22" t="inlineStr">
-        <is>
-          <t>mur-bouclier</t>
+      <c r="A23" s="23" t="inlineStr">
+        <is>
+          <t>Venom Stab</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>coup-venimeux</t>
         </is>
       </c>
       <c r="C23" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="24" t="inlineStr">
-        <is>
-          <t>Défense</t>
+      <c r="D23" s="25" t="inlineStr">
+        <is>
+          <t>Attaque</t>
         </is>
       </c>
       <c r="E23" s="16" t="inlineStr"/>
       <c r="F23" s="17" t="inlineStr">
         <is>
-          <t>Tower Shield</t>
+          <t>Basilisk Fang</t>
         </is>
       </c>
       <c r="G23" s="17" t="inlineStr">
         <is>
-          <t>Gain 5 Stone.</t>
+          <t>Deal 4 damage. Apply 4 Poison.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="21" t="inlineStr">
-        <is>
-          <t>Quicken</t>
-        </is>
-      </c>
-      <c r="B24" s="22" t="inlineStr">
-        <is>
-          <t>celerite-vive</t>
+      <c r="A24" s="23" t="inlineStr">
+        <is>
+          <t>Guard</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>garde</t>
         </is>
       </c>
       <c r="C24" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="25" t="inlineStr">
-        <is>
-          <t>Buff</t>
+      <c r="D24" s="26" t="inlineStr">
+        <is>
+          <t>Défense</t>
         </is>
       </c>
       <c r="E24" s="16" t="inlineStr"/>
       <c r="F24" s="17" t="inlineStr">
         <is>
-          <t>Swift Boots</t>
+          <t>— (deck de base)</t>
         </is>
       </c>
       <c r="G24" s="17" t="inlineStr">
         <is>
-          <t>Haste: +30% attack speed for 3 turns.</t>
+          <t>Gain 5 Stone.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="21" t="inlineStr">
-        <is>
-          <t>Sapphire Surge</t>
-        </is>
-      </c>
-      <c r="B25" s="22" t="inlineStr">
-        <is>
-          <t>surge-saphir</t>
+      <c r="A25" s="23" t="inlineStr">
+        <is>
+          <t>Hand Guard</t>
+        </is>
+      </c>
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>garde-faible</t>
         </is>
       </c>
       <c r="C25" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="25" t="inlineStr">
-        <is>
-          <t>Buff</t>
+        <v>1</v>
+      </c>
+      <c r="D25" s="26" t="inlineStr">
+        <is>
+          <t>Défense</t>
         </is>
       </c>
       <c r="E25" s="16" t="inlineStr"/>
       <c r="F25" s="17" t="inlineStr">
         <is>
-          <t>Sapphire Amulet</t>
+          <t>— (deck de base)</t>
         </is>
       </c>
       <c r="G25" s="17" t="inlineStr">
+        <is>
+          <t>Gain 3 Stone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="23" t="inlineStr">
+        <is>
+          <t>Mail Armor</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>mail-armor</t>
+        </is>
+      </c>
+      <c r="C26" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="26" t="inlineStr">
+        <is>
+          <t>Défense</t>
+        </is>
+      </c>
+      <c r="E26" s="16" t="inlineStr"/>
+      <c r="F26" s="17" t="inlineStr">
+        <is>
+          <t>Forgemaster's Mail</t>
+        </is>
+      </c>
+      <c r="G26" s="17" t="inlineStr">
+        <is>
+          <t>Gain 5 Stone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="23" t="inlineStr">
+        <is>
+          <t>Onyx Armor</t>
+        </is>
+      </c>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>onyx-armor</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" s="26" t="inlineStr">
+        <is>
+          <t>Défense</t>
+        </is>
+      </c>
+      <c r="E27" s="16" t="inlineStr"/>
+      <c r="F27" s="17" t="inlineStr">
+        <is>
+          <t>Onyx Guard Plate</t>
+        </is>
+      </c>
+      <c r="G27" s="17" t="inlineStr">
+        <is>
+          <t>Gain 15 Stone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="23" t="inlineStr">
+        <is>
+          <t>Quench</t>
+        </is>
+      </c>
+      <c r="B28" s="24" t="inlineStr">
+        <is>
+          <t>trempe</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="26" t="inlineStr">
+        <is>
+          <t>Défense</t>
+        </is>
+      </c>
+      <c r="E28" s="16" t="inlineStr"/>
+      <c r="F28" s="17" t="inlineStr">
+        <is>
+          <t>Forgemaster's Mail</t>
+        </is>
+      </c>
+      <c r="G28" s="17" t="inlineStr">
+        <is>
+          <t>Spend all Forge Heat. Gain 4 Stone per Heat spent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="23" t="inlineStr">
+        <is>
+          <t>Shield Wall</t>
+        </is>
+      </c>
+      <c r="B29" s="24" t="inlineStr">
+        <is>
+          <t>mur-bouclier</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="26" t="inlineStr">
+        <is>
+          <t>Défense</t>
+        </is>
+      </c>
+      <c r="E29" s="16" t="inlineStr"/>
+      <c r="F29" s="17" t="inlineStr">
+        <is>
+          <t>Tower Shield</t>
+        </is>
+      </c>
+      <c r="G29" s="17" t="inlineStr">
+        <is>
+          <t>Gain 5 Stone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="23" t="inlineStr">
+        <is>
+          <t>Burning Run</t>
+        </is>
+      </c>
+      <c r="B30" s="24" t="inlineStr">
+        <is>
+          <t>course-ardente</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" s="27" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="E30" s="16" t="inlineStr"/>
+      <c r="F30" s="17" t="inlineStr">
+        <is>
+          <t>Onyx Boots</t>
+        </is>
+      </c>
+      <c r="G30" s="17" t="inlineStr">
+        <is>
+          <t>Haste for as many turns as your current Forge Heat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="23" t="inlineStr">
+        <is>
+          <t>Master's Hand</t>
+        </is>
+      </c>
+      <c r="B31" s="24" t="inlineStr">
+        <is>
+          <t>main-de-maitre</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="27" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="E31" s="16" t="inlineStr"/>
+      <c r="F31" s="17" t="inlineStr">
+        <is>
+          <t>Miner's Gloves</t>
+        </is>
+      </c>
+      <c r="G31" s="17" t="inlineStr">
+        <is>
+          <t>Draw 2 cards.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="23" t="inlineStr">
+        <is>
+          <t>Perfect Sapphire Surge</t>
+        </is>
+      </c>
+      <c r="B32" s="24" t="inlineStr">
+        <is>
+          <t>surge-saphir-parfait</t>
+        </is>
+      </c>
+      <c r="C32" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="27" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="E32" s="16" t="inlineStr"/>
+      <c r="F32" s="17" t="inlineStr">
+        <is>
+          <t>Perfect Sapphire Amulet</t>
+        </is>
+      </c>
+      <c r="G32" s="17" t="inlineStr">
+        <is>
+          <t>Gain 3 Forge Heat (energy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="23" t="inlineStr">
+        <is>
+          <t>Quicken</t>
+        </is>
+      </c>
+      <c r="B33" s="24" t="inlineStr">
+        <is>
+          <t>celerite-vive</t>
+        </is>
+      </c>
+      <c r="C33" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="27" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="E33" s="16" t="inlineStr"/>
+      <c r="F33" s="17" t="inlineStr">
+        <is>
+          <t>Swift Boots</t>
+        </is>
+      </c>
+      <c r="G33" s="17" t="inlineStr">
+        <is>
+          <t>Haste: +30% attack speed for 3 turns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="23" t="inlineStr">
+        <is>
+          <t>Sapphire Surge</t>
+        </is>
+      </c>
+      <c r="B34" s="24" t="inlineStr">
+        <is>
+          <t>surge-saphir</t>
+        </is>
+      </c>
+      <c r="C34" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="27" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="E34" s="16" t="inlineStr"/>
+      <c r="F34" s="17" t="inlineStr">
+        <is>
+          <t>Sapphire Amulet, Nice Sapphire Amulet</t>
+        </is>
+      </c>
+      <c r="G34" s="17" t="inlineStr">
         <is>
           <t>Gain 2 Forge Heat (energy).</t>
         </is>
@@ -3082,4 +3748,123 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="007C2D12"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>BRUTAL — Sets d'armure (bonus de panoplie, hors cartes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>Le bonus s'active quand TOUTES les pièces sont équipées en même temps (l'arme n'est pas requise). Écris un nouveau set sur une ligne vide.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>Pièces requises (armure seulement)</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>Déclencheur</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>Bonus</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="23" t="inlineStr">
+        <is>
+          <t>Onyx Set</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>Onyx Guard Plate  +  Onyx Glove  +  Onyx Boots</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>Quand le héros est frappé en mêlée</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>When hit by a melee attack, the attacker takes 1 Burning (no spread).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="22" t="n"/>
+      <c r="B5" s="22" t="n"/>
+      <c r="C5" s="22" t="n"/>
+      <c r="D5" s="22" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="22" t="n"/>
+      <c r="B6" s="22" t="n"/>
+      <c r="C6" s="22" t="n"/>
+      <c r="D6" s="22" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="22" t="n"/>
+      <c r="B7" s="22" t="n"/>
+      <c r="C7" s="22" t="n"/>
+      <c r="D7" s="22" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="22" t="n"/>
+      <c r="B8" s="22" t="n"/>
+      <c r="C8" s="22" t="n"/>
+      <c r="D8" s="22" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="22" t="n"/>
+      <c r="B9" s="22" t="n"/>
+      <c r="C9" s="22" t="n"/>
+      <c r="D9" s="22" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="22" t="n"/>
+      <c r="B10" s="22" t="n"/>
+      <c r="C10" s="22" t="n"/>
+      <c r="D10" s="22" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/BRUTAL-items-et-cartes.xlsx
+++ b/docs/BRUTAL-items-et-cartes.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,6 +62,9 @@
     <font>
       <color rgb="00888888"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <color rgb="00888888"/>
     </font>
   </fonts>
   <fills count="14">
@@ -158,7 +161,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -226,6 +229,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -600,7 +606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -704,156 +710,173 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
+          <t>Rareté des cartes (onglet « Cartes »)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>La couleur de rareté d'une carte = celle de l'objet LE MOINS rare qui la débloque (ex. « Strike » est Common car des armes communes la donnent). Calculée automatiquement à la génération — c'est PUREMENT indicatif pour s'y retrouver, cette rareté n'existe pas dans le jeu. « — » = carte du deck de base (donnée par aucun objet).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
           <t>Légende des raretés</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  Common  (commun)</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  Uncommon  (uncommon)</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">  Rare  (rare)</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Epic  (epique)</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">  Legendary  (legendaire)</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="9" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>Tableau de référence pour garder une certaine balance</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>Rareté</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>Nb de cartes</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>Dégât / énergie</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>Armure / énergie</t>
         </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="C26" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="D26" s="2" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="C27" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="D27" s="2" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="C28" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="D28" s="2" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Legendary</t>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="D30" s="2" t="n">
         <v>8</v>
-      </c>
-      <c r="C30" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="D30" s="2" t="n">
-        <v>18</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>Armes à deux mains : ×1,5 sur dégât et armure/énergie (moins de cartes), souvent via des sorts chers en énergie.</t>
         </is>
@@ -2854,16 +2877,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="6" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="62" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="62" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -2896,15 +2920,20 @@
       </c>
       <c r="E2" s="12" t="inlineStr">
         <is>
+          <t>Rareté</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
           <t>AOE</t>
         </is>
       </c>
-      <c r="F2" s="12" t="inlineStr">
+      <c r="G2" s="12" t="inlineStr">
         <is>
           <t>Donnée par</t>
         </is>
       </c>
-      <c r="G2" s="12" t="inlineStr">
+      <c r="H2" s="12" t="inlineStr">
         <is>
           <t>Effet</t>
         </is>
@@ -2929,17 +2958,22 @@
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E3" s="17" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F3" s="17" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="F3" s="18" t="inlineStr">
+      <c r="G3" s="18" t="inlineStr">
         <is>
           <t>Magma Hammer</t>
         </is>
       </c>
-      <c r="G3" s="18" t="inlineStr">
+      <c r="H3" s="18" t="inlineStr">
         <is>
           <t>Apply 10 Burning to ALL enemies. Already-burning enemies take double, then their Burning is forged into Stone for you.</t>
         </is>
@@ -2964,13 +2998,18 @@
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E4" s="17" t="inlineStr"/>
-      <c r="F4" s="18" t="inlineStr">
+      <c r="E4" s="20" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F4" s="17" t="inlineStr"/>
+      <c r="G4" s="18" t="inlineStr">
         <is>
           <t>Blood Ring</t>
         </is>
       </c>
-      <c r="G4" s="18" t="inlineStr">
+      <c r="H4" s="18" t="inlineStr">
         <is>
           <t>Deal 3 damage + current Bleed stacks as bonus damage. Apply 3 Bleed (stacks don't reset).</t>
         </is>
@@ -2995,13 +3034,18 @@
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E5" s="17" t="inlineStr"/>
-      <c r="F5" s="18" t="inlineStr">
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F5" s="17" t="inlineStr"/>
+      <c r="G5" s="18" t="inlineStr">
         <is>
           <t>Onyx Glove</t>
         </is>
       </c>
-      <c r="G5" s="18" t="inlineStr">
+      <c r="H5" s="18" t="inlineStr">
         <is>
           <t>Discard your hand. For each card discarded, apply 3 Burning to a random enemy.</t>
         </is>
@@ -3026,13 +3070,18 @@
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E6" s="17" t="inlineStr"/>
-      <c r="F6" s="18" t="inlineStr">
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F6" s="17" t="inlineStr"/>
+      <c r="G6" s="18" t="inlineStr">
         <is>
           <t>War Axe</t>
         </is>
       </c>
-      <c r="G6" s="18" t="inlineStr">
+      <c r="H6" s="18" t="inlineStr">
         <is>
           <t>Deal 20 damage. If the target dies, deal 15 damage to the next enemy.</t>
         </is>
@@ -3057,17 +3106,22 @@
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E7" s="17" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F7" s="17" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="F7" s="18" t="inlineStr">
+      <c r="G7" s="18" t="inlineStr">
         <is>
           <t>Magma Hammer, Onyx Guard Plate</t>
         </is>
       </c>
-      <c r="G7" s="18" t="inlineStr">
+      <c r="H7" s="18" t="inlineStr">
         <is>
           <t>Detonate all Burning: deal 2 damage per Burning on ALL enemies.</t>
         </is>
@@ -3092,13 +3146,18 @@
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E8" s="17" t="inlineStr"/>
-      <c r="F8" s="18" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F8" s="17" t="inlineStr"/>
+      <c r="G8" s="18" t="inlineStr">
         <is>
           <t>Magma Hammer</t>
         </is>
       </c>
-      <c r="G8" s="18" t="inlineStr">
+      <c r="H8" s="18" t="inlineStr">
         <is>
           <t>Deal 12 damage. Apply 3 Burning.</t>
         </is>
@@ -3123,13 +3182,18 @@
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E9" s="17" t="inlineStr"/>
-      <c r="F9" s="18" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F9" s="17" t="inlineStr"/>
+      <c r="G9" s="18" t="inlineStr">
         <is>
           <t>Onyx Boots</t>
         </is>
       </c>
-      <c r="G9" s="18" t="inlineStr">
+      <c r="H9" s="18" t="inlineStr">
         <is>
           <t>Move all Burning from the target to the enemy behind it.</t>
         </is>
@@ -3154,13 +3218,18 @@
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E10" s="17" t="inlineStr"/>
-      <c r="F10" s="18" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F10" s="17" t="inlineStr"/>
+      <c r="G10" s="18" t="inlineStr">
         <is>
           <t>Forge Hammer</t>
         </is>
       </c>
-      <c r="G10" s="18" t="inlineStr">
+      <c r="H10" s="18" t="inlineStr">
         <is>
           <t>Deal 10 damage. Gain 8 Stone.</t>
         </is>
@@ -3185,13 +3254,18 @@
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E11" s="17" t="inlineStr"/>
-      <c r="F11" s="18" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F11" s="17" t="inlineStr"/>
+      <c r="G11" s="18" t="inlineStr">
         <is>
           <t>Frost Ring</t>
         </is>
       </c>
-      <c r="G11" s="18" t="inlineStr">
+      <c r="H11" s="18" t="inlineStr">
         <is>
           <t>Deal 2 damage. Chill: -30% speed for 3 turns.</t>
         </is>
@@ -3216,17 +3290,22 @@
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E12" s="17" t="inlineStr">
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F12" s="17" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="F12" s="18" t="inlineStr">
+      <c r="G12" s="18" t="inlineStr">
         <is>
           <t>War Axe</t>
         </is>
       </c>
-      <c r="G12" s="18" t="inlineStr">
+      <c r="H12" s="18" t="inlineStr">
         <is>
           <t>Deal 16 damage to ALL enemies. Apply 2 Bleed to ALL enemies.</t>
         </is>
@@ -3251,17 +3330,22 @@
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E13" s="17" t="inlineStr">
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F13" s="17" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="F13" s="18" t="inlineStr">
+      <c r="G13" s="18" t="inlineStr">
         <is>
           <t>Big Onyx Sword</t>
         </is>
       </c>
-      <c r="G13" s="18" t="inlineStr">
+      <c r="H13" s="18" t="inlineStr">
         <is>
           <t>Spend all Forge Heat. Apply 8 Burning per Heat spent to ALL enemies.</t>
         </is>
@@ -3286,13 +3370,18 @@
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E14" s="17" t="inlineStr"/>
-      <c r="F14" s="18" t="inlineStr">
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F14" s="17" t="inlineStr"/>
+      <c r="G14" s="18" t="inlineStr">
         <is>
           <t>Magma Hammer</t>
         </is>
       </c>
-      <c r="G14" s="18" t="inlineStr">
+      <c r="H14" s="18" t="inlineStr">
         <is>
           <t>Deal 28 damage. Apply 4 Burning.</t>
         </is>
@@ -3317,17 +3406,22 @@
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E15" s="17" t="inlineStr">
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F15" s="17" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="F15" s="18" t="inlineStr">
+      <c r="G15" s="18" t="inlineStr">
         <is>
           <t>Onyx Guard Plate</t>
         </is>
       </c>
-      <c r="G15" s="18" t="inlineStr">
+      <c r="H15" s="18" t="inlineStr">
         <is>
           <t>Apply 8 Burning to ALL enemies.</t>
         </is>
@@ -3352,13 +3446,18 @@
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E16" s="17" t="inlineStr"/>
-      <c r="F16" s="18" t="inlineStr">
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F16" s="17" t="inlineStr"/>
+      <c r="G16" s="18" t="inlineStr">
         <is>
           <t>Onyx Glove</t>
         </is>
       </c>
-      <c r="G16" s="18" t="inlineStr">
+      <c r="H16" s="18" t="inlineStr">
         <is>
           <t>Gain 5 Stone. Deal 2 damage and apply 1 Burning.</t>
         </is>
@@ -3383,17 +3482,22 @@
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E17" s="17" t="inlineStr">
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F17" s="17" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="F17" s="18" t="inlineStr">
+      <c r="G17" s="18" t="inlineStr">
         <is>
           <t>Big Onyx Sword</t>
         </is>
       </c>
-      <c r="G17" s="18" t="inlineStr">
+      <c r="H17" s="18" t="inlineStr">
         <is>
           <t>Apply 8 Burning to ALL enemies.</t>
         </is>
@@ -3418,13 +3522,18 @@
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E18" s="17" t="inlineStr"/>
-      <c r="F18" s="18" t="inlineStr">
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F18" s="17" t="inlineStr"/>
+      <c r="G18" s="18" t="inlineStr">
         <is>
           <t>Big Onyx Sword</t>
         </is>
       </c>
-      <c r="G18" s="18" t="inlineStr">
+      <c r="H18" s="18" t="inlineStr">
         <is>
           <t>Deal 26 damage and 4 Burning. The enemy behind takes half (13 damage, 2 Burning).</t>
         </is>
@@ -3449,13 +3558,18 @@
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E19" s="17" t="inlineStr"/>
-      <c r="F19" s="18" t="inlineStr">
+      <c r="E19" s="16" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F19" s="17" t="inlineStr"/>
+      <c r="G19" s="18" t="inlineStr">
         <is>
           <t>Miner's Pick</t>
         </is>
       </c>
-      <c r="G19" s="18" t="inlineStr">
+      <c r="H19" s="18" t="inlineStr">
         <is>
           <t>Deal 3 damage twice. If the target dies, hit a random other enemy for 3.</t>
         </is>
@@ -3480,17 +3594,22 @@
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E20" s="17" t="inlineStr">
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F20" s="17" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="F20" s="18" t="inlineStr">
+      <c r="G20" s="18" t="inlineStr">
         <is>
           <t>Basilisk Fang</t>
         </is>
       </c>
-      <c r="G20" s="18" t="inlineStr">
+      <c r="H20" s="18" t="inlineStr">
         <is>
           <t>Hit ALL enemies 3 times for 3 damage. Apply 1 Poison per hit (2 if the enemy was already poisoned).</t>
         </is>
@@ -3515,13 +3634,18 @@
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E21" s="17" t="inlineStr"/>
-      <c r="F21" s="18" t="inlineStr">
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F21" s="17" t="inlineStr"/>
+      <c r="G21" s="18" t="inlineStr">
         <is>
           <t>War Axe</t>
         </is>
       </c>
-      <c r="G21" s="18" t="inlineStr">
+      <c r="H21" s="18" t="inlineStr">
         <is>
           <t>Deal 16 damage. Stun the target for 2 turns.</t>
         </is>
@@ -3546,13 +3670,18 @@
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E22" s="17" t="inlineStr"/>
-      <c r="F22" s="18" t="inlineStr">
+      <c r="E22" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="17" t="inlineStr"/>
+      <c r="G22" s="18" t="inlineStr">
         <is>
           <t>— (deck de base)</t>
         </is>
       </c>
-      <c r="G22" s="18" t="inlineStr">
+      <c r="H22" s="18" t="inlineStr">
         <is>
           <t>Deal 3 damage.</t>
         </is>
@@ -3577,13 +3706,18 @@
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E23" s="17" t="inlineStr"/>
-      <c r="F23" s="18" t="inlineStr">
+      <c r="E23" s="16" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F23" s="17" t="inlineStr"/>
+      <c r="G23" s="18" t="inlineStr">
         <is>
           <t>Rusty Axe</t>
         </is>
       </c>
-      <c r="G23" s="18" t="inlineStr">
+      <c r="H23" s="18" t="inlineStr">
         <is>
           <t>Deal 6 damage to the target and 4 damage to each adjacent enemy.</t>
         </is>
@@ -3608,13 +3742,18 @@
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E24" s="17" t="inlineStr"/>
-      <c r="F24" s="18" t="inlineStr">
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F24" s="17" t="inlineStr"/>
+      <c r="G24" s="18" t="inlineStr">
         <is>
           <t>Tower Shield</t>
         </is>
       </c>
-      <c r="G24" s="18" t="inlineStr">
+      <c r="H24" s="18" t="inlineStr">
         <is>
           <t>Deal 3 damage. Stun the enemy for 2 turns.</t>
         </is>
@@ -3639,13 +3778,18 @@
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E25" s="17" t="inlineStr"/>
-      <c r="F25" s="18" t="inlineStr">
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F25" s="17" t="inlineStr"/>
+      <c r="G25" s="18" t="inlineStr">
         <is>
           <t>Forge Hammer</t>
         </is>
       </c>
-      <c r="G25" s="18" t="inlineStr">
+      <c r="H25" s="18" t="inlineStr">
         <is>
           <t>Deal 15 damage. Each adjacent enemy has a 50% chance to take 5 Burning.</t>
         </is>
@@ -3670,13 +3814,18 @@
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E26" s="17" t="inlineStr"/>
-      <c r="F26" s="18" t="inlineStr">
+      <c r="E26" s="16" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F26" s="17" t="inlineStr"/>
+      <c r="G26" s="18" t="inlineStr">
         <is>
           <t>Rusty Axe, Forge Hammer, Miner's Pick</t>
         </is>
       </c>
-      <c r="G26" s="18" t="inlineStr">
+      <c r="H26" s="18" t="inlineStr">
         <is>
           <t>Deal 6 damage.</t>
         </is>
@@ -3701,13 +3850,18 @@
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E27" s="17" t="inlineStr"/>
-      <c r="F27" s="18" t="inlineStr">
+      <c r="E27" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F27" s="17" t="inlineStr"/>
+      <c r="G27" s="18" t="inlineStr">
         <is>
           <t>Basilisk Fang</t>
         </is>
       </c>
-      <c r="G27" s="18" t="inlineStr">
+      <c r="H27" s="18" t="inlineStr">
         <is>
           <t>Deal 4 damage. Apply 4 Poison.</t>
         </is>
@@ -3732,13 +3886,18 @@
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E28" s="17" t="inlineStr"/>
-      <c r="F28" s="18" t="inlineStr">
+      <c r="E28" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F28" s="17" t="inlineStr"/>
+      <c r="G28" s="18" t="inlineStr">
         <is>
           <t>Basilisk Fang</t>
         </is>
       </c>
-      <c r="G28" s="18" t="inlineStr">
+      <c r="H28" s="18" t="inlineStr">
         <is>
           <t>Deal 18 damage. Doubled if the target has a negative status.</t>
         </is>
@@ -3758,18 +3917,23 @@
       <c r="C29" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="27" t="inlineStr">
+      <c r="D29" s="28" t="inlineStr">
         <is>
           <t>Défense</t>
         </is>
       </c>
-      <c r="E29" s="17" t="inlineStr"/>
-      <c r="F29" s="18" t="inlineStr">
+      <c r="E29" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F29" s="17" t="inlineStr"/>
+      <c r="G29" s="18" t="inlineStr">
         <is>
           <t>— (deck de base)</t>
         </is>
       </c>
-      <c r="G29" s="18" t="inlineStr">
+      <c r="H29" s="18" t="inlineStr">
         <is>
           <t>Gain 5 Stone.</t>
         </is>
@@ -3789,18 +3953,23 @@
       <c r="C30" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="27" t="inlineStr">
+      <c r="D30" s="28" t="inlineStr">
         <is>
           <t>Défense</t>
         </is>
       </c>
-      <c r="E30" s="17" t="inlineStr"/>
-      <c r="F30" s="18" t="inlineStr">
+      <c r="E30" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F30" s="17" t="inlineStr"/>
+      <c r="G30" s="18" t="inlineStr">
         <is>
           <t>— (deck de base)</t>
         </is>
       </c>
-      <c r="G30" s="18" t="inlineStr">
+      <c r="H30" s="18" t="inlineStr">
         <is>
           <t>Gain 3 Stone.</t>
         </is>
@@ -3820,18 +3989,23 @@
       <c r="C31" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="D31" s="27" t="inlineStr">
+      <c r="D31" s="28" t="inlineStr">
         <is>
           <t>Défense</t>
         </is>
       </c>
-      <c r="E31" s="17" t="inlineStr"/>
-      <c r="F31" s="18" t="inlineStr">
+      <c r="E31" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F31" s="17" t="inlineStr"/>
+      <c r="G31" s="18" t="inlineStr">
         <is>
           <t>Forgemaster's Mail</t>
         </is>
       </c>
-      <c r="G31" s="18" t="inlineStr">
+      <c r="H31" s="18" t="inlineStr">
         <is>
           <t>Gain 5 Stone.</t>
         </is>
@@ -3851,18 +4025,23 @@
       <c r="C32" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="D32" s="27" t="inlineStr">
+      <c r="D32" s="28" t="inlineStr">
         <is>
           <t>Défense</t>
         </is>
       </c>
-      <c r="E32" s="17" t="inlineStr"/>
-      <c r="F32" s="18" t="inlineStr">
+      <c r="E32" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F32" s="17" t="inlineStr"/>
+      <c r="G32" s="18" t="inlineStr">
         <is>
           <t>Onyx Guard Plate</t>
         </is>
       </c>
-      <c r="G32" s="18" t="inlineStr">
+      <c r="H32" s="18" t="inlineStr">
         <is>
           <t>Gain 15 Stone.</t>
         </is>
@@ -3882,18 +4061,23 @@
       <c r="C33" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="D33" s="27" t="inlineStr">
+      <c r="D33" s="28" t="inlineStr">
         <is>
           <t>Défense</t>
         </is>
       </c>
-      <c r="E33" s="17" t="inlineStr"/>
-      <c r="F33" s="18" t="inlineStr">
+      <c r="E33" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F33" s="17" t="inlineStr"/>
+      <c r="G33" s="18" t="inlineStr">
         <is>
           <t>Forgemaster's Mail</t>
         </is>
       </c>
-      <c r="G33" s="18" t="inlineStr">
+      <c r="H33" s="18" t="inlineStr">
         <is>
           <t>Spend all Forge Heat. Gain 4 Stone per Heat spent.</t>
         </is>
@@ -3913,18 +4097,23 @@
       <c r="C34" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="D34" s="27" t="inlineStr">
+      <c r="D34" s="28" t="inlineStr">
         <is>
           <t>Défense</t>
         </is>
       </c>
-      <c r="E34" s="17" t="inlineStr"/>
-      <c r="F34" s="18" t="inlineStr">
+      <c r="E34" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F34" s="17" t="inlineStr"/>
+      <c r="G34" s="18" t="inlineStr">
         <is>
           <t>Tower Shield</t>
         </is>
       </c>
-      <c r="G34" s="18" t="inlineStr">
+      <c r="H34" s="18" t="inlineStr">
         <is>
           <t>Gain 5 Stone.</t>
         </is>
@@ -3944,18 +4133,23 @@
       <c r="C35" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="D35" s="28" t="inlineStr">
+      <c r="D35" s="29" t="inlineStr">
         <is>
           <t>Buff</t>
         </is>
       </c>
-      <c r="E35" s="17" t="inlineStr"/>
-      <c r="F35" s="18" t="inlineStr">
+      <c r="E35" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F35" s="17" t="inlineStr"/>
+      <c r="G35" s="18" t="inlineStr">
         <is>
           <t>Onyx Boots</t>
         </is>
       </c>
-      <c r="G35" s="18" t="inlineStr">
+      <c r="H35" s="18" t="inlineStr">
         <is>
           <t>Haste for as many turns as your current Forge Heat.</t>
         </is>
@@ -3975,18 +4169,23 @@
       <c r="C36" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="D36" s="28" t="inlineStr">
+      <c r="D36" s="29" t="inlineStr">
         <is>
           <t>Buff</t>
         </is>
       </c>
-      <c r="E36" s="17" t="inlineStr"/>
-      <c r="F36" s="18" t="inlineStr">
+      <c r="E36" s="16" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F36" s="17" t="inlineStr"/>
+      <c r="G36" s="18" t="inlineStr">
         <is>
           <t>Miner's Gloves</t>
         </is>
       </c>
-      <c r="G36" s="18" t="inlineStr">
+      <c r="H36" s="18" t="inlineStr">
         <is>
           <t>Draw 2 cards.</t>
         </is>
@@ -4006,18 +4205,23 @@
       <c r="C37" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="D37" s="28" t="inlineStr">
+      <c r="D37" s="29" t="inlineStr">
         <is>
           <t>Buff</t>
         </is>
       </c>
-      <c r="E37" s="17" t="inlineStr"/>
-      <c r="F37" s="18" t="inlineStr">
+      <c r="E37" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F37" s="17" t="inlineStr"/>
+      <c r="G37" s="18" t="inlineStr">
         <is>
           <t>Big Onyx Sword</t>
         </is>
       </c>
-      <c r="G37" s="18" t="inlineStr">
+      <c r="H37" s="18" t="inlineStr">
         <is>
           <t>Gain 5 Forge Heat (energy).</t>
         </is>
@@ -4037,18 +4241,23 @@
       <c r="C38" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="D38" s="28" t="inlineStr">
+      <c r="D38" s="29" t="inlineStr">
         <is>
           <t>Buff</t>
         </is>
       </c>
-      <c r="E38" s="17" t="inlineStr"/>
-      <c r="F38" s="18" t="inlineStr">
+      <c r="E38" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F38" s="17" t="inlineStr"/>
+      <c r="G38" s="18" t="inlineStr">
         <is>
           <t>Perfect Sapphire Amulet</t>
         </is>
       </c>
-      <c r="G38" s="18" t="inlineStr">
+      <c r="H38" s="18" t="inlineStr">
         <is>
           <t>Gain 3 Forge Heat (energy).</t>
         </is>
@@ -4068,18 +4277,23 @@
       <c r="C39" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="D39" s="28" t="inlineStr">
+      <c r="D39" s="29" t="inlineStr">
         <is>
           <t>Buff</t>
         </is>
       </c>
-      <c r="E39" s="17" t="inlineStr"/>
-      <c r="F39" s="18" t="inlineStr">
+      <c r="E39" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F39" s="17" t="inlineStr"/>
+      <c r="G39" s="18" t="inlineStr">
         <is>
           <t>Swift Boots</t>
         </is>
       </c>
-      <c r="G39" s="18" t="inlineStr">
+      <c r="H39" s="18" t="inlineStr">
         <is>
           <t>Haste: +30% attack speed for 3 turns.</t>
         </is>
@@ -4099,18 +4313,23 @@
       <c r="C40" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="D40" s="28" t="inlineStr">
+      <c r="D40" s="29" t="inlineStr">
         <is>
           <t>Buff</t>
         </is>
       </c>
-      <c r="E40" s="17" t="inlineStr"/>
-      <c r="F40" s="18" t="inlineStr">
+      <c r="E40" s="20" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F40" s="17" t="inlineStr"/>
+      <c r="G40" s="18" t="inlineStr">
         <is>
           <t>Sapphire Amulet, Nice Sapphire Amulet</t>
         </is>
       </c>
-      <c r="G40" s="18" t="inlineStr">
+      <c r="H40" s="18" t="inlineStr">
         <is>
           <t>Gain 2 Forge Heat (energy).</t>
         </is>
@@ -4118,7 +4337,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/BRUTAL-items-et-cartes.xlsx
+++ b/docs/BRUTAL-items-et-cartes.xlsx
@@ -1567,21 +1567,21 @@
           <t>bouclier-tour</t>
         </is>
       </c>
-      <c r="C28" s="22" t="inlineStr">
-        <is>
-          <t>Epic</t>
+      <c r="C28" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
         </is>
       </c>
       <c r="D28" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E28" s="18" t="inlineStr">
+        <is>
+          <t>Shield Wall</t>
+        </is>
+      </c>
+      <c r="F28" s="17" t="n">
         <v>3</v>
-      </c>
-      <c r="E28" s="18" t="inlineStr">
-        <is>
-          <t>Shield Wall</t>
-        </is>
-      </c>
-      <c r="F28" s="17" t="n">
-        <v>1</v>
       </c>
       <c r="G28" s="18" t="inlineStr">
         <is>
@@ -1591,8 +1591,14 @@
       <c r="H28" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="I28" s="18" t="n"/>
-      <c r="J28" s="18" t="n"/>
+      <c r="I28" s="18" t="inlineStr">
+        <is>
+          <t>Stacking Shield</t>
+        </is>
+      </c>
+      <c r="J28" s="17" t="n">
+        <v>1</v>
+      </c>
       <c r="K28" s="18" t="n"/>
       <c r="L28" s="18" t="n"/>
       <c r="M28" s="19" t="inlineStr"/>
@@ -1718,12 +1724,24 @@
         </is>
       </c>
       <c r="D37" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" s="18" t="n"/>
-      <c r="F37" s="18" t="n"/>
-      <c r="G37" s="18" t="n"/>
-      <c r="H37" s="18" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="E37" s="18" t="inlineStr">
+        <is>
+          <t>Light Armor</t>
+        </is>
+      </c>
+      <c r="F37" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="G37" s="18" t="inlineStr">
+        <is>
+          <t>Free Movement</t>
+        </is>
+      </c>
+      <c r="H37" s="17" t="n">
+        <v>1</v>
+      </c>
       <c r="I37" s="18" t="n"/>
       <c r="J37" s="18" t="n"/>
       <c r="K37" s="18" t="n"/>
@@ -1748,7 +1766,7 @@
         </is>
       </c>
       <c r="D38" s="17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E38" s="18" t="inlineStr">
         <is>
@@ -1756,7 +1774,7 @@
         </is>
       </c>
       <c r="F38" s="17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G38" s="18" t="inlineStr">
         <is>
@@ -1764,7 +1782,7 @@
         </is>
       </c>
       <c r="H38" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I38" s="18" t="inlineStr">
         <is>
@@ -1774,11 +1792,17 @@
       <c r="J38" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="K38" s="18" t="n"/>
-      <c r="L38" s="18" t="n"/>
+      <c r="K38" s="18" t="inlineStr">
+        <is>
+          <t>All Should Be Fire</t>
+        </is>
+      </c>
+      <c r="L38" s="17" t="n">
+        <v>1</v>
+      </c>
       <c r="M38" s="19" t="inlineStr">
         <is>
-          <t>Défense 5  ·  Set : Onyx Set</t>
+          <t>Set : Onyx Set</t>
         </is>
       </c>
       <c r="N38" s="18" t="n"/>
@@ -1800,7 +1824,7 @@
         </is>
       </c>
       <c r="D39" s="17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E39" s="18" t="inlineStr">
         <is>
@@ -1818,15 +1842,17 @@
       <c r="H39" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="I39" s="18" t="n"/>
-      <c r="J39" s="18" t="n"/>
+      <c r="I39" s="18" t="inlineStr">
+        <is>
+          <t>Heavy Armor</t>
+        </is>
+      </c>
+      <c r="J39" s="17" t="n">
+        <v>2</v>
+      </c>
       <c r="K39" s="18" t="n"/>
       <c r="L39" s="18" t="n"/>
-      <c r="M39" s="19" t="inlineStr">
-        <is>
-          <t>Défense 3</t>
-        </is>
-      </c>
+      <c r="M39" s="19" t="inlineStr"/>
       <c r="N39" s="18" t="n"/>
     </row>
     <row r="40">
@@ -2877,7 +2903,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2942,16 +2968,16 @@
     <row r="3">
       <c r="A3" s="24" t="inlineStr">
         <is>
-          <t>Armor Forging</t>
+          <t>All Should Be Fire</t>
         </is>
       </c>
       <c r="B3" s="25" t="inlineStr">
         <is>
-          <t>forgeage-d-armure</t>
+          <t>tout-en-feu</t>
         </is>
       </c>
       <c r="C3" s="17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D3" s="26" t="inlineStr">
         <is>
@@ -2970,176 +2996,176 @@
       </c>
       <c r="G3" s="18" t="inlineStr">
         <is>
-          <t>Magma Hammer</t>
+          <t>Onyx Guard Plate</t>
         </is>
       </c>
       <c r="H3" s="18" t="inlineStr">
         <is>
-          <t>Apply 10 Burning to ALL enemies. Already-burning enemies take double, then their Burning is forged into Stone for you.</t>
+          <t>Convert ALL enemy statuses (positive and negative) to Burning, then double the Burning.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="24" t="inlineStr">
         <is>
-          <t>Bloodletting</t>
+          <t>Armor Forging</t>
         </is>
       </c>
       <c r="B4" s="25" t="inlineStr">
         <is>
-          <t>coup-de-sang</t>
+          <t>forgeage-d-armure</t>
         </is>
       </c>
       <c r="C4" s="17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D4" s="26" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E4" s="20" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="F4" s="17" t="inlineStr"/>
+      <c r="E4" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F4" s="17" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
       <c r="G4" s="18" t="inlineStr">
         <is>
-          <t>Blood Ring</t>
+          <t>Magma Hammer</t>
         </is>
       </c>
       <c r="H4" s="18" t="inlineStr">
         <is>
-          <t>Deal 3 damage + current Bleed stacks as bonus damage. Apply 3 Bleed (stacks don't reset).</t>
+          <t>Apply 10 Burning to ALL enemies. Already-burning enemies take double, then their Burning is forged into Stone for you.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="24" t="inlineStr">
         <is>
-          <t>Burning Hand</t>
+          <t>Bloodletting</t>
         </is>
       </c>
       <c r="B5" s="25" t="inlineStr">
         <is>
-          <t>main-brulante</t>
+          <t>coup-de-sang</t>
         </is>
       </c>
       <c r="C5" s="17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" s="26" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E5" s="22" t="inlineStr">
-        <is>
-          <t>Epic</t>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="F5" s="17" t="inlineStr"/>
       <c r="G5" s="18" t="inlineStr">
         <is>
-          <t>Onyx Glove</t>
+          <t>Blood Ring</t>
         </is>
       </c>
       <c r="H5" s="18" t="inlineStr">
         <is>
-          <t>Discard your hand. For each card discarded, apply 3 Burning to a random enemy.</t>
+          <t>Deal 3 damage + current Bleed stacks as bonus damage. Apply 3 Bleed (stacks don't reset).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="24" t="inlineStr">
         <is>
-          <t>Cleave</t>
+          <t>Burning Hand</t>
         </is>
       </c>
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>couper-en-deux</t>
+          <t>main-brulante</t>
         </is>
       </c>
       <c r="C6" s="17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D6" s="26" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr">
-        <is>
-          <t>Rare</t>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
         </is>
       </c>
       <c r="F6" s="17" t="inlineStr"/>
       <c r="G6" s="18" t="inlineStr">
         <is>
-          <t>War Axe</t>
+          <t>Onyx Glove</t>
         </is>
       </c>
       <c r="H6" s="18" t="inlineStr">
         <is>
-          <t>Deal 20 damage. If the target dies, deal 15 damage to the next enemy.</t>
+          <t>Discard your hand. For each card discarded, apply 8 Burning to a random enemy.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="24" t="inlineStr">
         <is>
-          <t>Dragon's Blaze</t>
+          <t>Cleave</t>
         </is>
       </c>
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>embrasement-dragon</t>
+          <t>couper-en-deux</t>
         </is>
       </c>
       <c r="C7" s="17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D7" s="26" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E7" s="22" t="inlineStr">
-        <is>
-          <t>Epic</t>
-        </is>
-      </c>
-      <c r="F7" s="17" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F7" s="17" t="inlineStr"/>
       <c r="G7" s="18" t="inlineStr">
         <is>
-          <t>Magma Hammer, Onyx Guard Plate</t>
+          <t>War Axe</t>
         </is>
       </c>
       <c r="H7" s="18" t="inlineStr">
         <is>
-          <t>Detonate all Burning: deal 2 damage per Burning on ALL enemies.</t>
+          <t>Deal 20 damage. If the target dies, deal 15 damage to the next enemy.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="24" t="inlineStr">
         <is>
-          <t>Fire Strike</t>
+          <t>Dragon's Blaze</t>
         </is>
       </c>
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>feu-frappe</t>
+          <t>embrasement-dragon</t>
         </is>
       </c>
       <c r="C8" s="17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D8" s="26" t="inlineStr">
         <is>
@@ -3151,27 +3177,31 @@
           <t>Epic</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr"/>
+      <c r="F8" s="17" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
       <c r="G8" s="18" t="inlineStr">
         <is>
-          <t>Magma Hammer</t>
+          <t>Magma Hammer, Onyx Guard Plate</t>
         </is>
       </c>
       <c r="H8" s="18" t="inlineStr">
         <is>
-          <t>Deal 12 damage. Apply 3 Burning.</t>
+          <t>Detonate all Burning: deal 2 damage per Burning on ALL enemies.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="24" t="inlineStr">
         <is>
-          <t>Flaming Kick</t>
+          <t>Fire Strike</t>
         </is>
       </c>
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>coup-de-pied-ardent</t>
+          <t>feu-frappe</t>
         </is>
       </c>
       <c r="C9" s="17" t="n">
@@ -3190,64 +3220,64 @@
       <c r="F9" s="17" t="inlineStr"/>
       <c r="G9" s="18" t="inlineStr">
         <is>
-          <t>Onyx Boots</t>
+          <t>Magma Hammer</t>
         </is>
       </c>
       <c r="H9" s="18" t="inlineStr">
         <is>
-          <t>Move all Burning from the target to the enemy behind it.</t>
+          <t>Deal 12 damage. Apply 3 Burning.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="24" t="inlineStr">
         <is>
-          <t>Forge Smash</t>
+          <t>Flaming Kick</t>
         </is>
       </c>
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>ecrasement</t>
+          <t>coup-de-pied-ardent</t>
         </is>
       </c>
       <c r="C10" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" s="26" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E10" s="20" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
         </is>
       </c>
       <c r="F10" s="17" t="inlineStr"/>
       <c r="G10" s="18" t="inlineStr">
         <is>
-          <t>Forge Hammer</t>
+          <t>Onyx Boots</t>
         </is>
       </c>
       <c r="H10" s="18" t="inlineStr">
         <is>
-          <t>Deal 10 damage. Gain 8 Stone.</t>
+          <t>Move all Burning from the target to the enemy behind it.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="24" t="inlineStr">
         <is>
-          <t>Frostbite</t>
+          <t>Forge Smash</t>
         </is>
       </c>
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>givre-lent</t>
+          <t>ecrasement</t>
         </is>
       </c>
       <c r="C11" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" s="26" t="inlineStr">
         <is>
@@ -3262,77 +3292,73 @@
       <c r="F11" s="17" t="inlineStr"/>
       <c r="G11" s="18" t="inlineStr">
         <is>
-          <t>Frost Ring</t>
+          <t>Forge Hammer</t>
         </is>
       </c>
       <c r="H11" s="18" t="inlineStr">
         <is>
-          <t>Deal 2 damage. Chill: -30% speed for 3 turns.</t>
+          <t>Deal 10 damage. Gain 8 Stone.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="24" t="inlineStr">
         <is>
-          <t>Giant Swing</t>
+          <t>Frostbite</t>
         </is>
       </c>
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>giant-swing</t>
+          <t>givre-lent</t>
         </is>
       </c>
       <c r="C12" s="17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D12" s="26" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E12" s="21" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="F12" s="17" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F12" s="17" t="inlineStr"/>
       <c r="G12" s="18" t="inlineStr">
         <is>
-          <t>War Axe</t>
+          <t>Frost Ring</t>
         </is>
       </c>
       <c r="H12" s="18" t="inlineStr">
         <is>
-          <t>Deal 16 damage to ALL enemies. Apply 2 Bleed to ALL enemies.</t>
+          <t>Deal 5 damage. Chill: -30% speed for 3 turns.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="24" t="inlineStr">
         <is>
-          <t>Heat Rejection</t>
+          <t>Giant Swing</t>
         </is>
       </c>
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>rejet-chaleur</t>
+          <t>giant-swing</t>
         </is>
       </c>
       <c r="C13" s="17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D13" s="26" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E13" s="22" t="inlineStr">
-        <is>
-          <t>Epic</t>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
         </is>
       </c>
       <c r="F13" s="17" t="inlineStr">
@@ -3342,28 +3368,28 @@
       </c>
       <c r="G13" s="18" t="inlineStr">
         <is>
-          <t>Big Onyx Sword</t>
+          <t>War Axe</t>
         </is>
       </c>
       <c r="H13" s="18" t="inlineStr">
         <is>
-          <t>Spend all Forge Heat. Apply 8 Burning per Heat spent to ALL enemies.</t>
+          <t>Deal 16 damage to ALL enemies. Apply 2 Bleed to ALL enemies.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="24" t="inlineStr">
         <is>
-          <t>Lava Hammer</t>
+          <t>Heat Rejection</t>
         </is>
       </c>
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>coup-de-lave</t>
+          <t>rejet-chaleur</t>
         </is>
       </c>
       <c r="C14" s="17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D14" s="26" t="inlineStr">
         <is>
@@ -3375,31 +3401,35 @@
           <t>Epic</t>
         </is>
       </c>
-      <c r="F14" s="17" t="inlineStr"/>
+      <c r="F14" s="17" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
       <c r="G14" s="18" t="inlineStr">
         <is>
-          <t>Magma Hammer</t>
+          <t>Big Onyx Sword</t>
         </is>
       </c>
       <c r="H14" s="18" t="inlineStr">
         <is>
-          <t>Deal 28 damage. Apply 4 Burning.</t>
+          <t>Spend all Forge Heat. Apply 8 Burning per Heat spent to ALL enemies.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="24" t="inlineStr">
         <is>
-          <t>Onyx Breath</t>
+          <t>Lava Hammer</t>
         </is>
       </c>
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>souffle-onyx</t>
+          <t>coup-de-lave</t>
         </is>
       </c>
       <c r="C15" s="17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D15" s="26" t="inlineStr">
         <is>
@@ -3411,35 +3441,31 @@
           <t>Epic</t>
         </is>
       </c>
-      <c r="F15" s="17" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
+      <c r="F15" s="17" t="inlineStr"/>
       <c r="G15" s="18" t="inlineStr">
         <is>
-          <t>Onyx Guard Plate</t>
+          <t>Magma Hammer</t>
         </is>
       </c>
       <c r="H15" s="18" t="inlineStr">
         <is>
-          <t>Apply 8 Burning to ALL enemies.</t>
+          <t>Deal 28 damage. Apply 4 Burning.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="24" t="inlineStr">
         <is>
-          <t>Onyx Fist</t>
+          <t>Onyx Breath</t>
         </is>
       </c>
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>poing-onyx</t>
+          <t>souffle-onyx</t>
         </is>
       </c>
       <c r="C16" s="17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D16" s="26" t="inlineStr">
         <is>
@@ -3451,27 +3477,31 @@
           <t>Epic</t>
         </is>
       </c>
-      <c r="F16" s="17" t="inlineStr"/>
+      <c r="F16" s="17" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
       <c r="G16" s="18" t="inlineStr">
         <is>
-          <t>Onyx Glove</t>
+          <t>Onyx Guard Plate</t>
         </is>
       </c>
       <c r="H16" s="18" t="inlineStr">
         <is>
-          <t>Gain 5 Stone. Deal 2 damage and apply 1 Burning.</t>
+          <t>Apply 20 Burning to ALL enemies.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="24" t="inlineStr">
         <is>
-          <t>Onyx Radiance</t>
+          <t>Onyx Fist</t>
         </is>
       </c>
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>onyx-radiance</t>
+          <t>poing-onyx</t>
         </is>
       </c>
       <c r="C17" s="17" t="n">
@@ -3487,35 +3517,31 @@
           <t>Epic</t>
         </is>
       </c>
-      <c r="F17" s="17" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
+      <c r="F17" s="17" t="inlineStr"/>
       <c r="G17" s="18" t="inlineStr">
         <is>
-          <t>Big Onyx Sword</t>
+          <t>Onyx Glove</t>
         </is>
       </c>
       <c r="H17" s="18" t="inlineStr">
         <is>
-          <t>Apply 8 Burning to ALL enemies.</t>
+          <t>Gain 10 Stone. Deal 10 damage and apply 3 Burning.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="24" t="inlineStr">
         <is>
-          <t>Onyx Slash</t>
+          <t>Onyx Radiance</t>
         </is>
       </c>
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>onyx-slash</t>
+          <t>onyx-radiance</t>
         </is>
       </c>
       <c r="C18" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" s="26" t="inlineStr">
         <is>
@@ -3527,7 +3553,11 @@
           <t>Epic</t>
         </is>
       </c>
-      <c r="F18" s="17" t="inlineStr"/>
+      <c r="F18" s="17" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
       <c r="G18" s="18" t="inlineStr">
         <is>
           <t>Big Onyx Sword</t>
@@ -3535,99 +3565,95 @@
       </c>
       <c r="H18" s="18" t="inlineStr">
         <is>
-          <t>Deal 26 damage and 4 Burning. The enemy behind takes half (13 damage, 2 Burning).</t>
+          <t>Apply 8 Burning to ALL enemies.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="24" t="inlineStr">
         <is>
-          <t>Pickaxe Jab</t>
+          <t>Onyx Slash</t>
         </is>
       </c>
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>coup-de-pioche</t>
+          <t>onyx-slash</t>
         </is>
       </c>
       <c r="C19" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19" s="26" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E19" s="16" t="inlineStr">
-        <is>
-          <t>Common</t>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
         </is>
       </c>
       <c r="F19" s="17" t="inlineStr"/>
       <c r="G19" s="18" t="inlineStr">
         <is>
-          <t>Miner's Pick</t>
+          <t>Big Onyx Sword</t>
         </is>
       </c>
       <c r="H19" s="18" t="inlineStr">
         <is>
-          <t>Deal 3 damage twice. If the target dies, hit a random other enemy for 3.</t>
+          <t>Deal 26 damage and 4 Burning. The enemy behind takes half (13 damage, 2 Burning).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="24" t="inlineStr">
         <is>
-          <t>Poison Dance</t>
+          <t>Pickaxe Jab</t>
         </is>
       </c>
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>danse-empoisonnee</t>
+          <t>coup-de-pioche</t>
         </is>
       </c>
       <c r="C20" s="17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D20" s="26" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E20" s="21" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="F20" s="17" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
+      <c r="E20" s="16" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F20" s="17" t="inlineStr"/>
       <c r="G20" s="18" t="inlineStr">
         <is>
-          <t>Basilisk Fang</t>
+          <t>Miner's Pick</t>
         </is>
       </c>
       <c r="H20" s="18" t="inlineStr">
         <is>
-          <t>Hit ALL enemies 3 times for 3 damage. Apply 1 Poison per hit (2 if the enemy was already poisoned).</t>
+          <t>Deal 3 damage twice. If the target dies, hit a random other enemy for 3.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="24" t="inlineStr">
         <is>
-          <t>Pommel Strike</t>
+          <t>Poison Dance</t>
         </is>
       </c>
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>coup-de-pommeau</t>
+          <t>danse-empoisonnee</t>
         </is>
       </c>
       <c r="C21" s="17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D21" s="26" t="inlineStr">
         <is>
@@ -3639,99 +3665,103 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="F21" s="17" t="inlineStr"/>
+      <c r="F21" s="17" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
       <c r="G21" s="18" t="inlineStr">
         <is>
-          <t>War Axe</t>
+          <t>Basilisk Fang</t>
         </is>
       </c>
       <c r="H21" s="18" t="inlineStr">
         <is>
-          <t>Deal 16 damage. Stun the target for 2 turns.</t>
+          <t>Hit ALL enemies 3 times for 3 damage. Apply 1 Poison per hit (2 if the enemy was already poisoned).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="24" t="inlineStr">
         <is>
-          <t>Punch</t>
+          <t>Pommel Strike</t>
         </is>
       </c>
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>coup-faible</t>
+          <t>coup-de-pommeau</t>
         </is>
       </c>
       <c r="C22" s="17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22" s="26" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E22" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="E22" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
         </is>
       </c>
       <c r="F22" s="17" t="inlineStr"/>
       <c r="G22" s="18" t="inlineStr">
         <is>
-          <t>— (deck de base)</t>
+          <t>War Axe</t>
         </is>
       </c>
       <c r="H22" s="18" t="inlineStr">
         <is>
-          <t>Deal 3 damage.</t>
+          <t>Deal 16 damage. Stun the target for 2 turns.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="24" t="inlineStr">
         <is>
-          <t>Rusty Cleave</t>
+          <t>Punch</t>
         </is>
       </c>
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>coup-de-hache</t>
+          <t>coup-faible</t>
         </is>
       </c>
       <c r="C23" s="17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D23" s="26" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E23" s="16" t="inlineStr">
-        <is>
-          <t>Common</t>
+      <c r="E23" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="17" t="inlineStr"/>
       <c r="G23" s="18" t="inlineStr">
         <is>
-          <t>Rusty Axe</t>
+          <t>— (deck de base)</t>
         </is>
       </c>
       <c r="H23" s="18" t="inlineStr">
         <is>
-          <t>Deal 6 damage to the target and 4 damage to each adjacent enemy.</t>
+          <t>Deal 3 damage.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="24" t="inlineStr">
         <is>
-          <t>Shield Bash</t>
+          <t>Rusty Cleave</t>
         </is>
       </c>
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>coup-de-bouclier</t>
+          <t>coup-de-hache</t>
         </is>
       </c>
       <c r="C24" s="17" t="n">
@@ -3742,104 +3772,104 @@
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E24" s="22" t="inlineStr">
-        <is>
-          <t>Epic</t>
+      <c r="E24" s="16" t="inlineStr">
+        <is>
+          <t>Common</t>
         </is>
       </c>
       <c r="F24" s="17" t="inlineStr"/>
       <c r="G24" s="18" t="inlineStr">
         <is>
-          <t>Tower Shield</t>
+          <t>Rusty Axe</t>
         </is>
       </c>
       <c r="H24" s="18" t="inlineStr">
         <is>
-          <t>Deal 3 damage. Stun the enemy for 2 turns.</t>
+          <t>Deal 6 damage to the target and 4 damage to each adjacent enemy.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="24" t="inlineStr">
         <is>
-          <t>Splash Strike</t>
+          <t>Shield Bash</t>
         </is>
       </c>
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>eclaboussure-de-frappe</t>
+          <t>coup-de-bouclier</t>
         </is>
       </c>
       <c r="C25" s="17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D25" s="26" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E25" s="20" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
+      <c r="E25" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
         </is>
       </c>
       <c r="F25" s="17" t="inlineStr"/>
       <c r="G25" s="18" t="inlineStr">
         <is>
-          <t>Forge Hammer</t>
+          <t>Tower Shield</t>
         </is>
       </c>
       <c r="H25" s="18" t="inlineStr">
         <is>
-          <t>Deal 15 damage. Each adjacent enemy has a 50% chance to take 5 Burning.</t>
+          <t>Deal 10 damage. Stun the enemy for 3 turns.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="24" t="inlineStr">
         <is>
-          <t>Strike</t>
+          <t>Splash Strike</t>
         </is>
       </c>
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>frappe</t>
+          <t>eclaboussure-de-frappe</t>
         </is>
       </c>
       <c r="C26" s="17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D26" s="26" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E26" s="16" t="inlineStr">
-        <is>
-          <t>Common</t>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="F26" s="17" t="inlineStr"/>
       <c r="G26" s="18" t="inlineStr">
         <is>
-          <t>Rusty Axe, Forge Hammer, Miner's Pick</t>
+          <t>Forge Hammer</t>
         </is>
       </c>
       <c r="H26" s="18" t="inlineStr">
         <is>
-          <t>Deal 6 damage.</t>
+          <t>Deal 15 damage. Each adjacent enemy has a 50% chance to take 5 Burning.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="24" t="inlineStr">
         <is>
-          <t>Venom Stab</t>
+          <t>Strike</t>
         </is>
       </c>
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>coup-venimeux</t>
+          <t>frappe</t>
         </is>
       </c>
       <c r="C27" s="17" t="n">
@@ -3850,36 +3880,36 @@
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E27" s="21" t="inlineStr">
-        <is>
-          <t>Rare</t>
+      <c r="E27" s="16" t="inlineStr">
+        <is>
+          <t>Common</t>
         </is>
       </c>
       <c r="F27" s="17" t="inlineStr"/>
       <c r="G27" s="18" t="inlineStr">
         <is>
-          <t>Basilisk Fang</t>
+          <t>Rusty Axe, Forge Hammer, Miner's Pick</t>
         </is>
       </c>
       <c r="H27" s="18" t="inlineStr">
         <is>
-          <t>Deal 4 damage. Apply 4 Poison.</t>
+          <t>Deal 6 damage.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="24" t="inlineStr">
         <is>
-          <t>Wound Opening</t>
+          <t>Venom Stab</t>
         </is>
       </c>
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>ouverture-des-plaies</t>
+          <t>coup-venimeux</t>
         </is>
       </c>
       <c r="C28" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" s="26" t="inlineStr">
         <is>
@@ -3899,55 +3929,55 @@
       </c>
       <c r="H28" s="18" t="inlineStr">
         <is>
-          <t>Deal 18 damage. Doubled if the target has a negative status.</t>
+          <t>Deal 4 damage. Apply 4 Poison.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="24" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Wound Opening</t>
         </is>
       </c>
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>garde</t>
+          <t>ouverture-des-plaies</t>
         </is>
       </c>
       <c r="C29" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" s="28" t="inlineStr">
-        <is>
-          <t>Défense</t>
-        </is>
-      </c>
-      <c r="E29" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>2</v>
+      </c>
+      <c r="D29" s="26" t="inlineStr">
+        <is>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="E29" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
         </is>
       </c>
       <c r="F29" s="17" t="inlineStr"/>
       <c r="G29" s="18" t="inlineStr">
         <is>
-          <t>— (deck de base)</t>
+          <t>Basilisk Fang</t>
         </is>
       </c>
       <c r="H29" s="18" t="inlineStr">
         <is>
-          <t>Gain 5 Stone.</t>
+          <t>Deal 18 damage. Doubled if the target has a negative status.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="24" t="inlineStr">
         <is>
-          <t>Hand Guard</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>garde-faible</t>
+          <t>garde</t>
         </is>
       </c>
       <c r="C30" s="17" t="n">
@@ -3971,19 +4001,19 @@
       </c>
       <c r="H30" s="18" t="inlineStr">
         <is>
-          <t>Gain 3 Stone.</t>
+          <t>Gain 5 Stone.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="24" t="inlineStr">
         <is>
-          <t>Mail Armor</t>
+          <t>Hand Guard</t>
         </is>
       </c>
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>mail-armor</t>
+          <t>garde-faible</t>
         </is>
       </c>
       <c r="C31" s="17" t="n">
@@ -3994,32 +4024,32 @@
           <t>Défense</t>
         </is>
       </c>
-      <c r="E31" s="21" t="inlineStr">
-        <is>
-          <t>Rare</t>
+      <c r="E31" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="F31" s="17" t="inlineStr"/>
       <c r="G31" s="18" t="inlineStr">
         <is>
-          <t>Forgemaster's Mail</t>
+          <t>— (deck de base)</t>
         </is>
       </c>
       <c r="H31" s="18" t="inlineStr">
         <is>
-          <t>Gain 5 Stone.</t>
+          <t>Gain 3 Stone.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="24" t="inlineStr">
         <is>
-          <t>Onyx Armor</t>
+          <t>Heavy Armor</t>
         </is>
       </c>
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>onyx-armor</t>
+          <t>armure-lourde</t>
         </is>
       </c>
       <c r="C32" s="17" t="n">
@@ -4030,68 +4060,68 @@
           <t>Défense</t>
         </is>
       </c>
-      <c r="E32" s="22" t="inlineStr">
-        <is>
-          <t>Epic</t>
+      <c r="E32" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
         </is>
       </c>
       <c r="F32" s="17" t="inlineStr"/>
       <c r="G32" s="18" t="inlineStr">
         <is>
-          <t>Onyx Guard Plate</t>
+          <t>Forgemaster's Mail</t>
         </is>
       </c>
       <c r="H32" s="18" t="inlineStr">
         <is>
-          <t>Gain 15 Stone.</t>
+          <t>Gain 20 Stone.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="24" t="inlineStr">
         <is>
-          <t>Quench</t>
+          <t>Light Armor</t>
         </is>
       </c>
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>trempe</t>
+          <t>armure-legere</t>
         </is>
       </c>
       <c r="C33" s="17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D33" s="28" t="inlineStr">
         <is>
           <t>Défense</t>
         </is>
       </c>
-      <c r="E33" s="21" t="inlineStr">
-        <is>
-          <t>Rare</t>
+      <c r="E33" s="16" t="inlineStr">
+        <is>
+          <t>Common</t>
         </is>
       </c>
       <c r="F33" s="17" t="inlineStr"/>
       <c r="G33" s="18" t="inlineStr">
         <is>
-          <t>Forgemaster's Mail</t>
+          <t>Traveler's Garb</t>
         </is>
       </c>
       <c r="H33" s="18" t="inlineStr">
         <is>
-          <t>Spend all Forge Heat. Gain 4 Stone per Heat spent.</t>
+          <t>Gain 5 Stone.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="24" t="inlineStr">
         <is>
-          <t>Shield Wall</t>
+          <t>Mail Armor</t>
         </is>
       </c>
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>mur-bouclier</t>
+          <t>mail-armor</t>
         </is>
       </c>
       <c r="C34" s="17" t="n">
@@ -4102,40 +4132,40 @@
           <t>Défense</t>
         </is>
       </c>
-      <c r="E34" s="22" t="inlineStr">
-        <is>
-          <t>Epic</t>
+      <c r="E34" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
         </is>
       </c>
       <c r="F34" s="17" t="inlineStr"/>
       <c r="G34" s="18" t="inlineStr">
         <is>
-          <t>Tower Shield</t>
+          <t>Forgemaster's Mail</t>
         </is>
       </c>
       <c r="H34" s="18" t="inlineStr">
         <is>
-          <t>Gain 5 Stone.</t>
+          <t>Gain 7 Stone for every enemy still alive.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="24" t="inlineStr">
         <is>
-          <t>Burning Run</t>
+          <t>Onyx Armor</t>
         </is>
       </c>
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>course-ardente</t>
+          <t>onyx-armor</t>
         </is>
       </c>
       <c r="C35" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="D35" s="29" t="inlineStr">
-        <is>
-          <t>Buff</t>
+      <c r="D35" s="28" t="inlineStr">
+        <is>
+          <t>Défense</t>
         </is>
       </c>
       <c r="E35" s="22" t="inlineStr">
@@ -4146,190 +4176,370 @@
       <c r="F35" s="17" t="inlineStr"/>
       <c r="G35" s="18" t="inlineStr">
         <is>
-          <t>Onyx Boots</t>
+          <t>Onyx Guard Plate</t>
         </is>
       </c>
       <c r="H35" s="18" t="inlineStr">
         <is>
-          <t>Haste for as many turns as your current Forge Heat.</t>
+          <t>Gain 30 Stone.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="24" t="inlineStr">
         <is>
-          <t>Master's Hand</t>
+          <t>Quench</t>
         </is>
       </c>
       <c r="B36" s="25" t="inlineStr">
         <is>
-          <t>main-de-maitre</t>
+          <t>trempe</t>
         </is>
       </c>
       <c r="C36" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D36" s="29" t="inlineStr">
-        <is>
-          <t>Buff</t>
-        </is>
-      </c>
-      <c r="E36" s="16" t="inlineStr">
-        <is>
-          <t>Common</t>
+        <v>0</v>
+      </c>
+      <c r="D36" s="28" t="inlineStr">
+        <is>
+          <t>Défense</t>
+        </is>
+      </c>
+      <c r="E36" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
         </is>
       </c>
       <c r="F36" s="17" t="inlineStr"/>
       <c r="G36" s="18" t="inlineStr">
         <is>
-          <t>Miner's Gloves</t>
+          <t>Forgemaster's Mail</t>
         </is>
       </c>
       <c r="H36" s="18" t="inlineStr">
         <is>
-          <t>Draw 2 cards.</t>
+          <t>Spend all Forge Heat. Gain 10 Stone per Heat spent.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="24" t="inlineStr">
         <is>
-          <t>Onyx Overheat</t>
+          <t>Shield Wall</t>
         </is>
       </c>
       <c r="B37" s="25" t="inlineStr">
         <is>
-          <t>onyx-overheat</t>
+          <t>mur-bouclier</t>
         </is>
       </c>
       <c r="C37" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" s="29" t="inlineStr">
-        <is>
-          <t>Buff</t>
-        </is>
-      </c>
-      <c r="E37" s="22" t="inlineStr">
-        <is>
-          <t>Epic</t>
+        <v>1</v>
+      </c>
+      <c r="D37" s="28" t="inlineStr">
+        <is>
+          <t>Défense</t>
+        </is>
+      </c>
+      <c r="E37" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
         </is>
       </c>
       <c r="F37" s="17" t="inlineStr"/>
       <c r="G37" s="18" t="inlineStr">
         <is>
-          <t>Big Onyx Sword</t>
+          <t>Tower Shield</t>
         </is>
       </c>
       <c r="H37" s="18" t="inlineStr">
         <is>
-          <t>Gain 5 Forge Heat (energy).</t>
+          <t>Gain 10 Stone.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="24" t="inlineStr">
         <is>
-          <t>Perfect Sapphire Surge</t>
+          <t>Stacking Shield</t>
         </is>
       </c>
       <c r="B38" s="25" t="inlineStr">
         <is>
-          <t>surge-saphir-parfait</t>
+          <t>bouclier-empilant</t>
         </is>
       </c>
       <c r="C38" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" s="29" t="inlineStr">
-        <is>
-          <t>Buff</t>
-        </is>
-      </c>
-      <c r="E38" s="22" t="inlineStr">
-        <is>
-          <t>Epic</t>
+        <v>4</v>
+      </c>
+      <c r="D38" s="28" t="inlineStr">
+        <is>
+          <t>Défense</t>
+        </is>
+      </c>
+      <c r="E38" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
         </is>
       </c>
       <c r="F38" s="17" t="inlineStr"/>
       <c r="G38" s="18" t="inlineStr">
         <is>
-          <t>Perfect Sapphire Amulet</t>
+          <t>Tower Shield</t>
         </is>
       </c>
       <c r="H38" s="18" t="inlineStr">
         <is>
-          <t>Gain 3 Forge Heat (energy).</t>
+          <t>Double your current Stone.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="24" t="inlineStr">
         <is>
-          <t>Quicken</t>
+          <t>Burning Run</t>
         </is>
       </c>
       <c r="B39" s="25" t="inlineStr">
         <is>
-          <t>celerite-vive</t>
+          <t>course-ardente</t>
         </is>
       </c>
       <c r="C39" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D39" s="29" t="inlineStr">
         <is>
           <t>Buff</t>
         </is>
       </c>
-      <c r="E39" s="21" t="inlineStr">
-        <is>
-          <t>Rare</t>
+      <c r="E39" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
         </is>
       </c>
       <c r="F39" s="17" t="inlineStr"/>
       <c r="G39" s="18" t="inlineStr">
         <is>
-          <t>Swift Boots</t>
+          <t>Onyx Boots</t>
         </is>
       </c>
       <c r="H39" s="18" t="inlineStr">
         <is>
-          <t>Haste: +30% attack speed for 3 turns.</t>
+          <t>Haste for as many turns as your current Forge Heat.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="24" t="inlineStr">
         <is>
-          <t>Sapphire Surge</t>
+          <t>Free Movement</t>
         </is>
       </c>
       <c r="B40" s="25" t="inlineStr">
         <is>
-          <t>surge-saphir</t>
+          <t>mouvement-degage</t>
         </is>
       </c>
       <c r="C40" s="17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D40" s="29" t="inlineStr">
         <is>
           <t>Buff</t>
         </is>
       </c>
-      <c r="E40" s="20" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
+      <c r="E40" s="16" t="inlineStr">
+        <is>
+          <t>Common</t>
         </is>
       </c>
       <c r="F40" s="17" t="inlineStr"/>
       <c r="G40" s="18" t="inlineStr">
         <is>
+          <t>Traveler's Garb</t>
+        </is>
+      </c>
+      <c r="H40" s="18" t="inlineStr">
+        <is>
+          <t>Haste for 5 of your turns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="24" t="inlineStr">
+        <is>
+          <t>Master's Hand</t>
+        </is>
+      </c>
+      <c r="B41" s="25" t="inlineStr">
+        <is>
+          <t>main-de-maitre</t>
+        </is>
+      </c>
+      <c r="C41" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" s="29" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="E41" s="16" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F41" s="17" t="inlineStr"/>
+      <c r="G41" s="18" t="inlineStr">
+        <is>
+          <t>Miner's Gloves</t>
+        </is>
+      </c>
+      <c r="H41" s="18" t="inlineStr">
+        <is>
+          <t>Draw 2 cards.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="24" t="inlineStr">
+        <is>
+          <t>Onyx Overheat</t>
+        </is>
+      </c>
+      <c r="B42" s="25" t="inlineStr">
+        <is>
+          <t>onyx-overheat</t>
+        </is>
+      </c>
+      <c r="C42" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="29" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="E42" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F42" s="17" t="inlineStr"/>
+      <c r="G42" s="18" t="inlineStr">
+        <is>
+          <t>Big Onyx Sword</t>
+        </is>
+      </c>
+      <c r="H42" s="18" t="inlineStr">
+        <is>
+          <t>Gain 5 Forge Heat (energy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="24" t="inlineStr">
+        <is>
+          <t>Perfect Sapphire Surge</t>
+        </is>
+      </c>
+      <c r="B43" s="25" t="inlineStr">
+        <is>
+          <t>surge-saphir-parfait</t>
+        </is>
+      </c>
+      <c r="C43" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="29" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="E43" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F43" s="17" t="inlineStr"/>
+      <c r="G43" s="18" t="inlineStr">
+        <is>
+          <t>Perfect Sapphire Amulet</t>
+        </is>
+      </c>
+      <c r="H43" s="18" t="inlineStr">
+        <is>
+          <t>Gain 3 Forge Heat (energy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="24" t="inlineStr">
+        <is>
+          <t>Quicken</t>
+        </is>
+      </c>
+      <c r="B44" s="25" t="inlineStr">
+        <is>
+          <t>celerite-vive</t>
+        </is>
+      </c>
+      <c r="C44" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" s="29" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="E44" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F44" s="17" t="inlineStr"/>
+      <c r="G44" s="18" t="inlineStr">
+        <is>
+          <t>Swift Boots</t>
+        </is>
+      </c>
+      <c r="H44" s="18" t="inlineStr">
+        <is>
+          <t>Haste: +30% attack speed for 3 turns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="24" t="inlineStr">
+        <is>
+          <t>Sapphire Surge</t>
+        </is>
+      </c>
+      <c r="B45" s="25" t="inlineStr">
+        <is>
+          <t>surge-saphir</t>
+        </is>
+      </c>
+      <c r="C45" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="29" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="E45" s="20" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F45" s="17" t="inlineStr"/>
+      <c r="G45" s="18" t="inlineStr">
+        <is>
           <t>Sapphire Amulet, Nice Sapphire Amulet</t>
         </is>
       </c>
-      <c r="H40" s="18" t="inlineStr">
+      <c r="H45" s="18" t="inlineStr">
         <is>
           <t>Gain 2 Forge Heat (energy).</t>
         </is>

--- a/docs/BRUTAL-items-et-cartes.xlsx
+++ b/docs/BRUTAL-items-et-cartes.xlsx
@@ -161,7 +161,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -226,6 +226,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -894,7 +897,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N96"/>
+  <dimension ref="A1:N106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1703,7 +1706,7 @@
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t>Armures   (3)</t>
+          <t>Armures   (4)</t>
         </is>
       </c>
     </row>
@@ -1852,24 +1855,64 @@
       </c>
       <c r="K39" s="18" t="n"/>
       <c r="L39" s="18" t="n"/>
-      <c r="M39" s="19" t="inlineStr"/>
+      <c r="M39" s="19" t="inlineStr">
+        <is>
+          <t>Set : Mail Set</t>
+        </is>
+      </c>
       <c r="N39" s="18" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="23" t="n"/>
-      <c r="B40" s="23" t="n"/>
-      <c r="C40" s="23" t="n"/>
-      <c r="D40" s="23" t="n"/>
-      <c r="E40" s="23" t="n"/>
-      <c r="F40" s="23" t="n"/>
-      <c r="G40" s="23" t="n"/>
-      <c r="H40" s="23" t="n"/>
-      <c r="I40" s="23" t="n"/>
-      <c r="J40" s="23" t="n"/>
-      <c r="K40" s="23" t="n"/>
-      <c r="L40" s="23" t="n"/>
-      <c r="M40" s="23" t="n"/>
-      <c r="N40" s="23" t="n"/>
+      <c r="A40" s="14" t="inlineStr">
+        <is>
+          <t>Crusader Plate</t>
+        </is>
+      </c>
+      <c r="B40" s="15" t="inlineStr">
+        <is>
+          <t>plate-croise</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D40" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E40" s="18" t="inlineStr">
+        <is>
+          <t>Radiant Strike</t>
+        </is>
+      </c>
+      <c r="F40" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G40" s="18" t="inlineStr">
+        <is>
+          <t>Sacred Ground</t>
+        </is>
+      </c>
+      <c r="H40" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="I40" s="18" t="inlineStr">
+        <is>
+          <t>Blinding Flash</t>
+        </is>
+      </c>
+      <c r="J40" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K40" s="18" t="n"/>
+      <c r="L40" s="18" t="n"/>
+      <c r="M40" s="19" t="inlineStr">
+        <is>
+          <t>Set : Crusader Set</t>
+        </is>
+      </c>
+      <c r="N40" s="18" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="23" t="n"/>
@@ -1951,67 +1994,47 @@
       <c r="M45" s="23" t="n"/>
       <c r="N45" s="23" t="n"/>
     </row>
-    <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="13" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="23" t="n"/>
+      <c r="B46" s="23" t="n"/>
+      <c r="C46" s="23" t="n"/>
+      <c r="D46" s="23" t="n"/>
+      <c r="E46" s="23" t="n"/>
+      <c r="F46" s="23" t="n"/>
+      <c r="G46" s="23" t="n"/>
+      <c r="H46" s="23" t="n"/>
+      <c r="I46" s="23" t="n"/>
+      <c r="J46" s="23" t="n"/>
+      <c r="K46" s="23" t="n"/>
+      <c r="L46" s="23" t="n"/>
+      <c r="M46" s="23" t="n"/>
+      <c r="N46" s="23" t="n"/>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="13" t="inlineStr">
         <is>
           <t>Colliers   (3)</t>
         </is>
       </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="14" t="inlineStr">
-        <is>
-          <t>Sapphire Amulet</t>
-        </is>
-      </c>
-      <c r="B48" s="15" t="inlineStr">
-        <is>
-          <t>collier-de-saphir</t>
-        </is>
-      </c>
-      <c r="C48" s="20" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="D48" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E48" s="18" t="inlineStr">
-        <is>
-          <t>Sapphire Surge</t>
-        </is>
-      </c>
-      <c r="F48" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G48" s="18" t="n"/>
-      <c r="H48" s="18" t="n"/>
-      <c r="I48" s="18" t="n"/>
-      <c r="J48" s="18" t="n"/>
-      <c r="K48" s="18" t="n"/>
-      <c r="L48" s="18" t="n"/>
-      <c r="M48" s="19" t="inlineStr"/>
-      <c r="N48" s="18" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="14" t="inlineStr">
         <is>
-          <t>Nice Sapphire Amulet</t>
+          <t>Sapphire Amulet</t>
         </is>
       </c>
       <c r="B49" s="15" t="inlineStr">
         <is>
-          <t>collier-de-saphir-fin</t>
-        </is>
-      </c>
-      <c r="C49" s="21" t="inlineStr">
-        <is>
-          <t>Rare</t>
+          <t>collier-de-saphir</t>
+        </is>
+      </c>
+      <c r="C49" s="20" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="D49" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E49" s="18" t="inlineStr">
         <is>
@@ -2019,7 +2042,7 @@
         </is>
       </c>
       <c r="F49" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G49" s="18" t="n"/>
       <c r="H49" s="18" t="n"/>
@@ -2033,29 +2056,29 @@
     <row r="50">
       <c r="A50" s="14" t="inlineStr">
         <is>
-          <t>Perfect Sapphire Amulet</t>
+          <t>Nice Sapphire Amulet</t>
         </is>
       </c>
       <c r="B50" s="15" t="inlineStr">
         <is>
-          <t>collier-de-saphir-parfait</t>
-        </is>
-      </c>
-      <c r="C50" s="22" t="inlineStr">
-        <is>
-          <t>Epic</t>
+          <t>collier-de-saphir-fin</t>
+        </is>
+      </c>
+      <c r="C50" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
         </is>
       </c>
       <c r="D50" s="17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E50" s="18" t="inlineStr">
         <is>
-          <t>Perfect Sapphire Surge</t>
+          <t>Sapphire Surge</t>
         </is>
       </c>
       <c r="F50" s="17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G50" s="18" t="n"/>
       <c r="H50" s="18" t="n"/>
@@ -2067,20 +2090,40 @@
       <c r="N50" s="18" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="23" t="n"/>
-      <c r="B51" s="23" t="n"/>
-      <c r="C51" s="23" t="n"/>
-      <c r="D51" s="23" t="n"/>
-      <c r="E51" s="23" t="n"/>
-      <c r="F51" s="23" t="n"/>
-      <c r="G51" s="23" t="n"/>
-      <c r="H51" s="23" t="n"/>
-      <c r="I51" s="23" t="n"/>
-      <c r="J51" s="23" t="n"/>
-      <c r="K51" s="23" t="n"/>
-      <c r="L51" s="23" t="n"/>
-      <c r="M51" s="23" t="n"/>
-      <c r="N51" s="23" t="n"/>
+      <c r="A51" s="14" t="inlineStr">
+        <is>
+          <t>Perfect Sapphire Amulet</t>
+        </is>
+      </c>
+      <c r="B51" s="15" t="inlineStr">
+        <is>
+          <t>collier-de-saphir-parfait</t>
+        </is>
+      </c>
+      <c r="C51" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="D51" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E51" s="18" t="inlineStr">
+        <is>
+          <t>Perfect Sapphire Surge</t>
+        </is>
+      </c>
+      <c r="F51" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="G51" s="18" t="n"/>
+      <c r="H51" s="18" t="n"/>
+      <c r="I51" s="18" t="n"/>
+      <c r="J51" s="18" t="n"/>
+      <c r="K51" s="18" t="n"/>
+      <c r="L51" s="18" t="n"/>
+      <c r="M51" s="19" t="inlineStr"/>
+      <c r="N51" s="18" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="23" t="n"/>
@@ -2162,58 +2205,38 @@
       <c r="M56" s="23" t="n"/>
       <c r="N56" s="23" t="n"/>
     </row>
-    <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="13" t="inlineStr">
-        <is>
-          <t>Bagues   (2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="14" t="inlineStr">
-        <is>
-          <t>Blood Ring</t>
-        </is>
-      </c>
-      <c r="B59" s="15" t="inlineStr">
-        <is>
-          <t>bague-de-sang</t>
-        </is>
-      </c>
-      <c r="C59" s="20" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="D59" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="E59" s="18" t="inlineStr">
-        <is>
-          <t>Bloodletting</t>
-        </is>
-      </c>
-      <c r="F59" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="G59" s="18" t="n"/>
-      <c r="H59" s="18" t="n"/>
-      <c r="I59" s="18" t="n"/>
-      <c r="J59" s="18" t="n"/>
-      <c r="K59" s="18" t="n"/>
-      <c r="L59" s="18" t="n"/>
-      <c r="M59" s="19" t="inlineStr"/>
-      <c r="N59" s="18" t="n"/>
+    <row r="57">
+      <c r="A57" s="23" t="n"/>
+      <c r="B57" s="23" t="n"/>
+      <c r="C57" s="23" t="n"/>
+      <c r="D57" s="23" t="n"/>
+      <c r="E57" s="23" t="n"/>
+      <c r="F57" s="23" t="n"/>
+      <c r="G57" s="23" t="n"/>
+      <c r="H57" s="23" t="n"/>
+      <c r="I57" s="23" t="n"/>
+      <c r="J57" s="23" t="n"/>
+      <c r="K57" s="23" t="n"/>
+      <c r="L57" s="23" t="n"/>
+      <c r="M57" s="23" t="n"/>
+      <c r="N57" s="23" t="n"/>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="13" t="inlineStr">
+        <is>
+          <t>Bagues   (3)</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="14" t="inlineStr">
         <is>
-          <t>Frost Ring</t>
+          <t>Blood Ring</t>
         </is>
       </c>
       <c r="B60" s="15" t="inlineStr">
         <is>
-          <t>anneau-de-givre</t>
+          <t>bague-de-sang</t>
         </is>
       </c>
       <c r="C60" s="20" t="inlineStr">
@@ -2226,7 +2249,7 @@
       </c>
       <c r="E60" s="18" t="inlineStr">
         <is>
-          <t>Frostbite</t>
+          <t>Bloodletting</t>
         </is>
       </c>
       <c r="F60" s="17" t="n">
@@ -2242,36 +2265,76 @@
       <c r="N60" s="18" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="23" t="n"/>
-      <c r="B61" s="23" t="n"/>
-      <c r="C61" s="23" t="n"/>
-      <c r="D61" s="23" t="n"/>
-      <c r="E61" s="23" t="n"/>
-      <c r="F61" s="23" t="n"/>
-      <c r="G61" s="23" t="n"/>
-      <c r="H61" s="23" t="n"/>
-      <c r="I61" s="23" t="n"/>
-      <c r="J61" s="23" t="n"/>
-      <c r="K61" s="23" t="n"/>
-      <c r="L61" s="23" t="n"/>
-      <c r="M61" s="23" t="n"/>
-      <c r="N61" s="23" t="n"/>
+      <c r="A61" s="14" t="inlineStr">
+        <is>
+          <t>Frost Ring</t>
+        </is>
+      </c>
+      <c r="B61" s="15" t="inlineStr">
+        <is>
+          <t>anneau-de-givre</t>
+        </is>
+      </c>
+      <c r="C61" s="20" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D61" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E61" s="18" t="inlineStr">
+        <is>
+          <t>Frostbite</t>
+        </is>
+      </c>
+      <c r="F61" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G61" s="18" t="n"/>
+      <c r="H61" s="18" t="n"/>
+      <c r="I61" s="18" t="n"/>
+      <c r="J61" s="18" t="n"/>
+      <c r="K61" s="18" t="n"/>
+      <c r="L61" s="18" t="n"/>
+      <c r="M61" s="19" t="inlineStr"/>
+      <c r="N61" s="18" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="23" t="n"/>
-      <c r="B62" s="23" t="n"/>
-      <c r="C62" s="23" t="n"/>
-      <c r="D62" s="23" t="n"/>
-      <c r="E62" s="23" t="n"/>
-      <c r="F62" s="23" t="n"/>
-      <c r="G62" s="23" t="n"/>
-      <c r="H62" s="23" t="n"/>
-      <c r="I62" s="23" t="n"/>
-      <c r="J62" s="23" t="n"/>
-      <c r="K62" s="23" t="n"/>
-      <c r="L62" s="23" t="n"/>
-      <c r="M62" s="23" t="n"/>
-      <c r="N62" s="23" t="n"/>
+      <c r="A62" s="14" t="inlineStr">
+        <is>
+          <t>Perfect Frost Ring</t>
+        </is>
+      </c>
+      <c r="B62" s="15" t="inlineStr">
+        <is>
+          <t>anneau-de-givre-parfait</t>
+        </is>
+      </c>
+      <c r="C62" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D62" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E62" s="18" t="inlineStr">
+        <is>
+          <t>Frost Cascade</t>
+        </is>
+      </c>
+      <c r="F62" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G62" s="18" t="n"/>
+      <c r="H62" s="18" t="n"/>
+      <c r="I62" s="18" t="n"/>
+      <c r="J62" s="18" t="n"/>
+      <c r="K62" s="18" t="n"/>
+      <c r="L62" s="18" t="n"/>
+      <c r="M62" s="19" t="inlineStr"/>
+      <c r="N62" s="18" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="23" t="n"/>
@@ -2337,158 +2400,230 @@
       <c r="M66" s="23" t="n"/>
       <c r="N66" s="23" t="n"/>
     </row>
-    <row r="68" ht="20" customHeight="1">
-      <c r="A68" s="13" t="inlineStr">
-        <is>
-          <t>Gants   (2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="14" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="23" t="n"/>
+      <c r="B67" s="23" t="n"/>
+      <c r="C67" s="23" t="n"/>
+      <c r="D67" s="23" t="n"/>
+      <c r="E67" s="23" t="n"/>
+      <c r="F67" s="23" t="n"/>
+      <c r="G67" s="23" t="n"/>
+      <c r="H67" s="23" t="n"/>
+      <c r="I67" s="23" t="n"/>
+      <c r="J67" s="23" t="n"/>
+      <c r="K67" s="23" t="n"/>
+      <c r="L67" s="23" t="n"/>
+      <c r="M67" s="23" t="n"/>
+      <c r="N67" s="23" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="23" t="n"/>
+      <c r="B68" s="23" t="n"/>
+      <c r="C68" s="23" t="n"/>
+      <c r="D68" s="23" t="n"/>
+      <c r="E68" s="23" t="n"/>
+      <c r="F68" s="23" t="n"/>
+      <c r="G68" s="23" t="n"/>
+      <c r="H68" s="23" t="n"/>
+      <c r="I68" s="23" t="n"/>
+      <c r="J68" s="23" t="n"/>
+      <c r="K68" s="23" t="n"/>
+      <c r="L68" s="23" t="n"/>
+      <c r="M68" s="23" t="n"/>
+      <c r="N68" s="23" t="n"/>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="13" t="inlineStr">
+        <is>
+          <t>Gants   (4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="14" t="inlineStr">
         <is>
           <t>Miner's Gloves</t>
         </is>
       </c>
-      <c r="B69" s="15" t="inlineStr">
+      <c r="B71" s="15" t="inlineStr">
         <is>
           <t>gants-de-mineur</t>
         </is>
       </c>
-      <c r="C69" s="16" t="inlineStr">
+      <c r="C71" s="16" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="D69" s="17" t="n">
+      <c r="D71" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="E69" s="18" t="inlineStr">
+      <c r="E71" s="18" t="inlineStr">
         <is>
           <t>Master's Hand</t>
         </is>
       </c>
-      <c r="F69" s="17" t="n">
+      <c r="F71" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="G69" s="18" t="n"/>
-      <c r="H69" s="18" t="n"/>
-      <c r="I69" s="18" t="n"/>
-      <c r="J69" s="18" t="n"/>
-      <c r="K69" s="18" t="n"/>
-      <c r="L69" s="18" t="n"/>
-      <c r="M69" s="19" t="inlineStr"/>
-      <c r="N69" s="18" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="14" t="inlineStr">
+      <c r="G71" s="18" t="n"/>
+      <c r="H71" s="18" t="n"/>
+      <c r="I71" s="18" t="n"/>
+      <c r="J71" s="18" t="n"/>
+      <c r="K71" s="18" t="n"/>
+      <c r="L71" s="18" t="n"/>
+      <c r="M71" s="19" t="inlineStr"/>
+      <c r="N71" s="18" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="14" t="inlineStr">
         <is>
           <t>Onyx Glove</t>
         </is>
       </c>
-      <c r="B70" s="15" t="inlineStr">
+      <c r="B72" s="15" t="inlineStr">
         <is>
           <t>gants-onyx</t>
         </is>
       </c>
-      <c r="C70" s="22" t="inlineStr">
+      <c r="C72" s="22" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="D70" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="E70" s="18" t="inlineStr">
+      <c r="D72" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E72" s="18" t="inlineStr">
         <is>
           <t>Burning Hand</t>
         </is>
       </c>
-      <c r="F70" s="17" t="n">
+      <c r="F72" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="G70" s="18" t="inlineStr">
+      <c r="G72" s="18" t="inlineStr">
         <is>
           <t>Onyx Fist</t>
         </is>
       </c>
-      <c r="H70" s="17" t="n">
+      <c r="H72" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="I70" s="18" t="n"/>
-      <c r="J70" s="18" t="n"/>
-      <c r="K70" s="18" t="n"/>
-      <c r="L70" s="18" t="n"/>
-      <c r="M70" s="19" t="inlineStr">
+      <c r="I72" s="18" t="inlineStr">
+        <is>
+          <t>Forge from Ashes</t>
+        </is>
+      </c>
+      <c r="J72" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K72" s="18" t="n"/>
+      <c r="L72" s="18" t="n"/>
+      <c r="M72" s="19" t="inlineStr">
         <is>
           <t>Set : Onyx Set</t>
         </is>
       </c>
-      <c r="N70" s="18" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="23" t="n"/>
-      <c r="B71" s="23" t="n"/>
-      <c r="C71" s="23" t="n"/>
-      <c r="D71" s="23" t="n"/>
-      <c r="E71" s="23" t="n"/>
-      <c r="F71" s="23" t="n"/>
-      <c r="G71" s="23" t="n"/>
-      <c r="H71" s="23" t="n"/>
-      <c r="I71" s="23" t="n"/>
-      <c r="J71" s="23" t="n"/>
-      <c r="K71" s="23" t="n"/>
-      <c r="L71" s="23" t="n"/>
-      <c r="M71" s="23" t="n"/>
-      <c r="N71" s="23" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="23" t="n"/>
-      <c r="B72" s="23" t="n"/>
-      <c r="C72" s="23" t="n"/>
-      <c r="D72" s="23" t="n"/>
-      <c r="E72" s="23" t="n"/>
-      <c r="F72" s="23" t="n"/>
-      <c r="G72" s="23" t="n"/>
-      <c r="H72" s="23" t="n"/>
-      <c r="I72" s="23" t="n"/>
-      <c r="J72" s="23" t="n"/>
-      <c r="K72" s="23" t="n"/>
-      <c r="L72" s="23" t="n"/>
-      <c r="M72" s="23" t="n"/>
-      <c r="N72" s="23" t="n"/>
+      <c r="N72" s="18" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="23" t="n"/>
-      <c r="B73" s="23" t="n"/>
-      <c r="C73" s="23" t="n"/>
-      <c r="D73" s="23" t="n"/>
-      <c r="E73" s="23" t="n"/>
-      <c r="F73" s="23" t="n"/>
-      <c r="G73" s="23" t="n"/>
-      <c r="H73" s="23" t="n"/>
-      <c r="I73" s="23" t="n"/>
-      <c r="J73" s="23" t="n"/>
-      <c r="K73" s="23" t="n"/>
-      <c r="L73" s="23" t="n"/>
-      <c r="M73" s="23" t="n"/>
-      <c r="N73" s="23" t="n"/>
+      <c r="A73" s="14" t="inlineStr">
+        <is>
+          <t>Mail Glove</t>
+        </is>
+      </c>
+      <c r="B73" s="15" t="inlineStr">
+        <is>
+          <t>gants-de-maille</t>
+        </is>
+      </c>
+      <c r="C73" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D73" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E73" s="18" t="inlineStr">
+        <is>
+          <t>Master's Hand</t>
+        </is>
+      </c>
+      <c r="F73" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G73" s="18" t="inlineStr">
+        <is>
+          <t>Outnumbered</t>
+        </is>
+      </c>
+      <c r="H73" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I73" s="18" t="inlineStr">
+        <is>
+          <t>Mail Advantage</t>
+        </is>
+      </c>
+      <c r="J73" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K73" s="18" t="n"/>
+      <c r="L73" s="18" t="n"/>
+      <c r="M73" s="19" t="inlineStr">
+        <is>
+          <t>Set : Mail Set</t>
+        </is>
+      </c>
+      <c r="N73" s="18" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="23" t="n"/>
-      <c r="B74" s="23" t="n"/>
-      <c r="C74" s="23" t="n"/>
-      <c r="D74" s="23" t="n"/>
-      <c r="E74" s="23" t="n"/>
-      <c r="F74" s="23" t="n"/>
-      <c r="G74" s="23" t="n"/>
-      <c r="H74" s="23" t="n"/>
-      <c r="I74" s="23" t="n"/>
-      <c r="J74" s="23" t="n"/>
-      <c r="K74" s="23" t="n"/>
-      <c r="L74" s="23" t="n"/>
-      <c r="M74" s="23" t="n"/>
-      <c r="N74" s="23" t="n"/>
+      <c r="A74" s="14" t="inlineStr">
+        <is>
+          <t>Crusader Gauntlets</t>
+        </is>
+      </c>
+      <c r="B74" s="15" t="inlineStr">
+        <is>
+          <t>gants-croise</t>
+        </is>
+      </c>
+      <c r="C74" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D74" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E74" s="18" t="inlineStr">
+        <is>
+          <t>Lumen Jab</t>
+        </is>
+      </c>
+      <c r="F74" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G74" s="18" t="inlineStr">
+        <is>
+          <t>Halo Burst</t>
+        </is>
+      </c>
+      <c r="H74" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I74" s="18" t="n"/>
+      <c r="J74" s="18" t="n"/>
+      <c r="K74" s="18" t="n"/>
+      <c r="L74" s="18" t="n"/>
+      <c r="M74" s="19" t="inlineStr">
+        <is>
+          <t>Set : Crusader Set</t>
+        </is>
+      </c>
+      <c r="N74" s="18" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="23" t="n"/>
@@ -2522,265 +2657,338 @@
       <c r="M76" s="23" t="n"/>
       <c r="N76" s="23" t="n"/>
     </row>
-    <row r="78" ht="20" customHeight="1">
-      <c r="A78" s="13" t="inlineStr">
-        <is>
-          <t>Bottes   (2)</t>
-        </is>
-      </c>
+    <row r="77">
+      <c r="A77" s="23" t="n"/>
+      <c r="B77" s="23" t="n"/>
+      <c r="C77" s="23" t="n"/>
+      <c r="D77" s="23" t="n"/>
+      <c r="E77" s="23" t="n"/>
+      <c r="F77" s="23" t="n"/>
+      <c r="G77" s="23" t="n"/>
+      <c r="H77" s="23" t="n"/>
+      <c r="I77" s="23" t="n"/>
+      <c r="J77" s="23" t="n"/>
+      <c r="K77" s="23" t="n"/>
+      <c r="L77" s="23" t="n"/>
+      <c r="M77" s="23" t="n"/>
+      <c r="N77" s="23" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="23" t="n"/>
+      <c r="B78" s="23" t="n"/>
+      <c r="C78" s="23" t="n"/>
+      <c r="D78" s="23" t="n"/>
+      <c r="E78" s="23" t="n"/>
+      <c r="F78" s="23" t="n"/>
+      <c r="G78" s="23" t="n"/>
+      <c r="H78" s="23" t="n"/>
+      <c r="I78" s="23" t="n"/>
+      <c r="J78" s="23" t="n"/>
+      <c r="K78" s="23" t="n"/>
+      <c r="L78" s="23" t="n"/>
+      <c r="M78" s="23" t="n"/>
+      <c r="N78" s="23" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="14" t="inlineStr">
+      <c r="A79" s="23" t="n"/>
+      <c r="B79" s="23" t="n"/>
+      <c r="C79" s="23" t="n"/>
+      <c r="D79" s="23" t="n"/>
+      <c r="E79" s="23" t="n"/>
+      <c r="F79" s="23" t="n"/>
+      <c r="G79" s="23" t="n"/>
+      <c r="H79" s="23" t="n"/>
+      <c r="I79" s="23" t="n"/>
+      <c r="J79" s="23" t="n"/>
+      <c r="K79" s="23" t="n"/>
+      <c r="L79" s="23" t="n"/>
+      <c r="M79" s="23" t="n"/>
+      <c r="N79" s="23" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="23" t="n"/>
+      <c r="B80" s="23" t="n"/>
+      <c r="C80" s="23" t="n"/>
+      <c r="D80" s="23" t="n"/>
+      <c r="E80" s="23" t="n"/>
+      <c r="F80" s="23" t="n"/>
+      <c r="G80" s="23" t="n"/>
+      <c r="H80" s="23" t="n"/>
+      <c r="I80" s="23" t="n"/>
+      <c r="J80" s="23" t="n"/>
+      <c r="K80" s="23" t="n"/>
+      <c r="L80" s="23" t="n"/>
+      <c r="M80" s="23" t="n"/>
+      <c r="N80" s="23" t="n"/>
+    </row>
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="13" t="inlineStr">
+        <is>
+          <t>Bottes   (4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="14" t="inlineStr">
         <is>
           <t>Swift Boots</t>
         </is>
       </c>
-      <c r="B79" s="15" t="inlineStr">
+      <c r="B83" s="15" t="inlineStr">
         <is>
           <t>bottes-vives</t>
         </is>
       </c>
-      <c r="C79" s="21" t="inlineStr">
+      <c r="C83" s="20" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D83" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E83" s="18" t="inlineStr">
+        <is>
+          <t>Quicken</t>
+        </is>
+      </c>
+      <c r="F83" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="G83" s="18" t="inlineStr">
+        <is>
+          <t>Second Wind</t>
+        </is>
+      </c>
+      <c r="H83" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I83" s="18" t="n"/>
+      <c r="J83" s="18" t="n"/>
+      <c r="K83" s="18" t="n"/>
+      <c r="L83" s="18" t="n"/>
+      <c r="M83" s="19" t="inlineStr"/>
+      <c r="N83" s="18" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="14" t="inlineStr">
+        <is>
+          <t>Onyx Boots</t>
+        </is>
+      </c>
+      <c r="B84" s="15" t="inlineStr">
+        <is>
+          <t>bottes-onyx</t>
+        </is>
+      </c>
+      <c r="C84" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="D84" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E84" s="18" t="inlineStr">
+        <is>
+          <t>Burning Run</t>
+        </is>
+      </c>
+      <c r="F84" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" s="18" t="inlineStr">
+        <is>
+          <t>Flaming Kick</t>
+        </is>
+      </c>
+      <c r="H84" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I84" s="18" t="inlineStr">
+        <is>
+          <t>Fire Boost</t>
+        </is>
+      </c>
+      <c r="J84" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K84" s="18" t="inlineStr">
+        <is>
+          <t>Boost</t>
+        </is>
+      </c>
+      <c r="L84" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M84" s="19" t="inlineStr">
+        <is>
+          <t>Set : Onyx Set</t>
+        </is>
+      </c>
+      <c r="N84" s="18" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="14" t="inlineStr">
+        <is>
+          <t>Mail Boots</t>
+        </is>
+      </c>
+      <c r="B85" s="15" t="inlineStr">
+        <is>
+          <t>bottes-de-maille</t>
+        </is>
+      </c>
+      <c r="C85" s="21" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="D79" s="17" t="n">
+      <c r="D85" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E85" s="18" t="inlineStr">
+        <is>
+          <t>Quicken</t>
+        </is>
+      </c>
+      <c r="F85" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="E79" s="18" t="inlineStr">
-        <is>
-          <t>Quicken</t>
-        </is>
-      </c>
-      <c r="F79" s="17" t="n">
+      <c r="G85" s="18" t="inlineStr">
+        <is>
+          <t>Mail Advantage</t>
+        </is>
+      </c>
+      <c r="H85" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I85" s="18" t="inlineStr">
+        <is>
+          <t>Boost</t>
+        </is>
+      </c>
+      <c r="J85" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="G79" s="18" t="n"/>
-      <c r="H79" s="18" t="n"/>
-      <c r="I79" s="18" t="n"/>
-      <c r="J79" s="18" t="n"/>
-      <c r="K79" s="18" t="n"/>
-      <c r="L79" s="18" t="n"/>
-      <c r="M79" s="19" t="inlineStr"/>
-      <c r="N79" s="18" t="n"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="14" t="inlineStr">
-        <is>
-          <t>Onyx Boots</t>
-        </is>
-      </c>
-      <c r="B80" s="15" t="inlineStr">
-        <is>
-          <t>bottes-onyx</t>
-        </is>
-      </c>
-      <c r="C80" s="22" t="inlineStr">
-        <is>
-          <t>Epic</t>
-        </is>
-      </c>
-      <c r="D80" s="17" t="n">
+      <c r="K85" s="18" t="n"/>
+      <c r="L85" s="18" t="n"/>
+      <c r="M85" s="19" t="inlineStr">
+        <is>
+          <t>Set : Mail Set</t>
+        </is>
+      </c>
+      <c r="N85" s="18" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="14" t="inlineStr">
+        <is>
+          <t>Crusader Greaves</t>
+        </is>
+      </c>
+      <c r="B86" s="15" t="inlineStr">
+        <is>
+          <t>bottes-croise</t>
+        </is>
+      </c>
+      <c r="C86" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D86" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="E80" s="18" t="inlineStr">
-        <is>
-          <t>Burning Run</t>
-        </is>
-      </c>
-      <c r="F80" s="17" t="n">
+      <c r="E86" s="18" t="inlineStr">
+        <is>
+          <t>Crusader's Charge</t>
+        </is>
+      </c>
+      <c r="F86" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="G80" s="18" t="inlineStr">
-        <is>
-          <t>Flaming Kick</t>
-        </is>
-      </c>
-      <c r="H80" s="17" t="n">
+      <c r="G86" s="18" t="inlineStr">
+        <is>
+          <t>Dazzling Kick</t>
+        </is>
+      </c>
+      <c r="H86" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="I80" s="18" t="n"/>
-      <c r="J80" s="18" t="n"/>
-      <c r="K80" s="18" t="n"/>
-      <c r="L80" s="18" t="n"/>
-      <c r="M80" s="19" t="inlineStr">
-        <is>
-          <t>Set : Onyx Set</t>
-        </is>
-      </c>
-      <c r="N80" s="18" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="23" t="n"/>
-      <c r="B81" s="23" t="n"/>
-      <c r="C81" s="23" t="n"/>
-      <c r="D81" s="23" t="n"/>
-      <c r="E81" s="23" t="n"/>
-      <c r="F81" s="23" t="n"/>
-      <c r="G81" s="23" t="n"/>
-      <c r="H81" s="23" t="n"/>
-      <c r="I81" s="23" t="n"/>
-      <c r="J81" s="23" t="n"/>
-      <c r="K81" s="23" t="n"/>
-      <c r="L81" s="23" t="n"/>
-      <c r="M81" s="23" t="n"/>
-      <c r="N81" s="23" t="n"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="23" t="n"/>
-      <c r="B82" s="23" t="n"/>
-      <c r="C82" s="23" t="n"/>
-      <c r="D82" s="23" t="n"/>
-      <c r="E82" s="23" t="n"/>
-      <c r="F82" s="23" t="n"/>
-      <c r="G82" s="23" t="n"/>
-      <c r="H82" s="23" t="n"/>
-      <c r="I82" s="23" t="n"/>
-      <c r="J82" s="23" t="n"/>
-      <c r="K82" s="23" t="n"/>
-      <c r="L82" s="23" t="n"/>
-      <c r="M82" s="23" t="n"/>
-      <c r="N82" s="23" t="n"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="23" t="n"/>
-      <c r="B83" s="23" t="n"/>
-      <c r="C83" s="23" t="n"/>
-      <c r="D83" s="23" t="n"/>
-      <c r="E83" s="23" t="n"/>
-      <c r="F83" s="23" t="n"/>
-      <c r="G83" s="23" t="n"/>
-      <c r="H83" s="23" t="n"/>
-      <c r="I83" s="23" t="n"/>
-      <c r="J83" s="23" t="n"/>
-      <c r="K83" s="23" t="n"/>
-      <c r="L83" s="23" t="n"/>
-      <c r="M83" s="23" t="n"/>
-      <c r="N83" s="23" t="n"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="23" t="n"/>
-      <c r="B84" s="23" t="n"/>
-      <c r="C84" s="23" t="n"/>
-      <c r="D84" s="23" t="n"/>
-      <c r="E84" s="23" t="n"/>
-      <c r="F84" s="23" t="n"/>
-      <c r="G84" s="23" t="n"/>
-      <c r="H84" s="23" t="n"/>
-      <c r="I84" s="23" t="n"/>
-      <c r="J84" s="23" t="n"/>
-      <c r="K84" s="23" t="n"/>
-      <c r="L84" s="23" t="n"/>
-      <c r="M84" s="23" t="n"/>
-      <c r="N84" s="23" t="n"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="23" t="n"/>
-      <c r="B85" s="23" t="n"/>
-      <c r="C85" s="23" t="n"/>
-      <c r="D85" s="23" t="n"/>
-      <c r="E85" s="23" t="n"/>
-      <c r="F85" s="23" t="n"/>
-      <c r="G85" s="23" t="n"/>
-      <c r="H85" s="23" t="n"/>
-      <c r="I85" s="23" t="n"/>
-      <c r="J85" s="23" t="n"/>
-      <c r="K85" s="23" t="n"/>
-      <c r="L85" s="23" t="n"/>
-      <c r="M85" s="23" t="n"/>
-      <c r="N85" s="23" t="n"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="23" t="n"/>
-      <c r="B86" s="23" t="n"/>
-      <c r="C86" s="23" t="n"/>
-      <c r="D86" s="23" t="n"/>
-      <c r="E86" s="23" t="n"/>
-      <c r="F86" s="23" t="n"/>
-      <c r="G86" s="23" t="n"/>
-      <c r="H86" s="23" t="n"/>
-      <c r="I86" s="23" t="n"/>
-      <c r="J86" s="23" t="n"/>
-      <c r="K86" s="23" t="n"/>
-      <c r="L86" s="23" t="n"/>
-      <c r="M86" s="23" t="n"/>
-      <c r="N86" s="23" t="n"/>
-    </row>
-    <row r="88" ht="20" customHeight="1">
-      <c r="A88" s="13" t="inlineStr">
-        <is>
-          <t>Sacs   (2)</t>
-        </is>
-      </c>
+      <c r="I86" s="18" t="n"/>
+      <c r="J86" s="18" t="n"/>
+      <c r="K86" s="18" t="n"/>
+      <c r="L86" s="18" t="n"/>
+      <c r="M86" s="19" t="inlineStr">
+        <is>
+          <t>Set : Crusader Set</t>
+        </is>
+      </c>
+      <c r="N86" s="18" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="23" t="n"/>
+      <c r="B87" s="23" t="n"/>
+      <c r="C87" s="23" t="n"/>
+      <c r="D87" s="23" t="n"/>
+      <c r="E87" s="23" t="n"/>
+      <c r="F87" s="23" t="n"/>
+      <c r="G87" s="23" t="n"/>
+      <c r="H87" s="23" t="n"/>
+      <c r="I87" s="23" t="n"/>
+      <c r="J87" s="23" t="n"/>
+      <c r="K87" s="23" t="n"/>
+      <c r="L87" s="23" t="n"/>
+      <c r="M87" s="23" t="n"/>
+      <c r="N87" s="23" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="23" t="n"/>
+      <c r="B88" s="23" t="n"/>
+      <c r="C88" s="23" t="n"/>
+      <c r="D88" s="23" t="n"/>
+      <c r="E88" s="23" t="n"/>
+      <c r="F88" s="23" t="n"/>
+      <c r="G88" s="23" t="n"/>
+      <c r="H88" s="23" t="n"/>
+      <c r="I88" s="23" t="n"/>
+      <c r="J88" s="23" t="n"/>
+      <c r="K88" s="23" t="n"/>
+      <c r="L88" s="23" t="n"/>
+      <c r="M88" s="23" t="n"/>
+      <c r="N88" s="23" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" s="14" t="inlineStr">
-        <is>
-          <t>Leather Pouch</t>
-        </is>
-      </c>
-      <c r="B89" s="15" t="inlineStr">
-        <is>
-          <t>sac-en-cuir</t>
-        </is>
-      </c>
-      <c r="C89" s="16" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="D89" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E89" s="18" t="n"/>
-      <c r="F89" s="18" t="n"/>
-      <c r="G89" s="18" t="n"/>
-      <c r="H89" s="18" t="n"/>
-      <c r="I89" s="18" t="n"/>
-      <c r="J89" s="18" t="n"/>
-      <c r="K89" s="18" t="n"/>
-      <c r="L89" s="18" t="n"/>
-      <c r="M89" s="19" t="inlineStr">
-        <is>
-          <t>+2 rangées de sac</t>
-        </is>
-      </c>
-      <c r="N89" s="18" t="n"/>
+      <c r="A89" s="23" t="n"/>
+      <c r="B89" s="23" t="n"/>
+      <c r="C89" s="23" t="n"/>
+      <c r="D89" s="23" t="n"/>
+      <c r="E89" s="23" t="n"/>
+      <c r="F89" s="23" t="n"/>
+      <c r="G89" s="23" t="n"/>
+      <c r="H89" s="23" t="n"/>
+      <c r="I89" s="23" t="n"/>
+      <c r="J89" s="23" t="n"/>
+      <c r="K89" s="23" t="n"/>
+      <c r="L89" s="23" t="n"/>
+      <c r="M89" s="23" t="n"/>
+      <c r="N89" s="23" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="14" t="inlineStr">
-        <is>
-          <t>Big Leather Pouch</t>
-        </is>
-      </c>
-      <c r="B90" s="15" t="inlineStr">
-        <is>
-          <t>grand-sac-en-cuir</t>
-        </is>
-      </c>
-      <c r="C90" s="20" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="D90" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E90" s="18" t="n"/>
-      <c r="F90" s="18" t="n"/>
-      <c r="G90" s="18" t="n"/>
-      <c r="H90" s="18" t="n"/>
-      <c r="I90" s="18" t="n"/>
-      <c r="J90" s="18" t="n"/>
-      <c r="K90" s="18" t="n"/>
-      <c r="L90" s="18" t="n"/>
-      <c r="M90" s="19" t="inlineStr">
-        <is>
-          <t>+3 rangées de sac</t>
-        </is>
-      </c>
-      <c r="N90" s="18" t="n"/>
+      <c r="A90" s="23" t="n"/>
+      <c r="B90" s="23" t="n"/>
+      <c r="C90" s="23" t="n"/>
+      <c r="D90" s="23" t="n"/>
+      <c r="E90" s="23" t="n"/>
+      <c r="F90" s="23" t="n"/>
+      <c r="G90" s="23" t="n"/>
+      <c r="H90" s="23" t="n"/>
+      <c r="I90" s="23" t="n"/>
+      <c r="J90" s="23" t="n"/>
+      <c r="K90" s="23" t="n"/>
+      <c r="L90" s="23" t="n"/>
+      <c r="M90" s="23" t="n"/>
+      <c r="N90" s="23" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="23" t="n"/>
@@ -2814,82 +3022,325 @@
       <c r="M92" s="23" t="n"/>
       <c r="N92" s="23" t="n"/>
     </row>
-    <row r="93">
-      <c r="A93" s="23" t="n"/>
-      <c r="B93" s="23" t="n"/>
-      <c r="C93" s="23" t="n"/>
-      <c r="D93" s="23" t="n"/>
-      <c r="E93" s="23" t="n"/>
-      <c r="F93" s="23" t="n"/>
-      <c r="G93" s="23" t="n"/>
-      <c r="H93" s="23" t="n"/>
-      <c r="I93" s="23" t="n"/>
-      <c r="J93" s="23" t="n"/>
-      <c r="K93" s="23" t="n"/>
-      <c r="L93" s="23" t="n"/>
-      <c r="M93" s="23" t="n"/>
-      <c r="N93" s="23" t="n"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="23" t="n"/>
-      <c r="B94" s="23" t="n"/>
-      <c r="C94" s="23" t="n"/>
-      <c r="D94" s="23" t="n"/>
-      <c r="E94" s="23" t="n"/>
-      <c r="F94" s="23" t="n"/>
-      <c r="G94" s="23" t="n"/>
-      <c r="H94" s="23" t="n"/>
-      <c r="I94" s="23" t="n"/>
-      <c r="J94" s="23" t="n"/>
-      <c r="K94" s="23" t="n"/>
-      <c r="L94" s="23" t="n"/>
-      <c r="M94" s="23" t="n"/>
-      <c r="N94" s="23" t="n"/>
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="13" t="inlineStr">
+        <is>
+          <t>Sacs   (6)</t>
+        </is>
+      </c>
     </row>
     <row r="95">
-      <c r="A95" s="23" t="n"/>
-      <c r="B95" s="23" t="n"/>
-      <c r="C95" s="23" t="n"/>
-      <c r="D95" s="23" t="n"/>
-      <c r="E95" s="23" t="n"/>
-      <c r="F95" s="23" t="n"/>
-      <c r="G95" s="23" t="n"/>
-      <c r="H95" s="23" t="n"/>
-      <c r="I95" s="23" t="n"/>
-      <c r="J95" s="23" t="n"/>
-      <c r="K95" s="23" t="n"/>
-      <c r="L95" s="23" t="n"/>
-      <c r="M95" s="23" t="n"/>
-      <c r="N95" s="23" t="n"/>
+      <c r="A95" s="14" t="inlineStr">
+        <is>
+          <t>Leather Pouch</t>
+        </is>
+      </c>
+      <c r="B95" s="15" t="inlineStr">
+        <is>
+          <t>sac-en-cuir</t>
+        </is>
+      </c>
+      <c r="C95" s="16" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D95" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" s="18" t="n"/>
+      <c r="F95" s="18" t="n"/>
+      <c r="G95" s="18" t="n"/>
+      <c r="H95" s="18" t="n"/>
+      <c r="I95" s="18" t="n"/>
+      <c r="J95" s="18" t="n"/>
+      <c r="K95" s="18" t="n"/>
+      <c r="L95" s="18" t="n"/>
+      <c r="M95" s="19" t="inlineStr">
+        <is>
+          <t>+1 rangées de sac</t>
+        </is>
+      </c>
+      <c r="N95" s="18" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" s="23" t="n"/>
-      <c r="B96" s="23" t="n"/>
-      <c r="C96" s="23" t="n"/>
-      <c r="D96" s="23" t="n"/>
-      <c r="E96" s="23" t="n"/>
-      <c r="F96" s="23" t="n"/>
-      <c r="G96" s="23" t="n"/>
-      <c r="H96" s="23" t="n"/>
-      <c r="I96" s="23" t="n"/>
-      <c r="J96" s="23" t="n"/>
-      <c r="K96" s="23" t="n"/>
-      <c r="L96" s="23" t="n"/>
-      <c r="M96" s="23" t="n"/>
-      <c r="N96" s="23" t="n"/>
+      <c r="A96" s="14" t="inlineStr">
+        <is>
+          <t>Big Leather Pouch</t>
+        </is>
+      </c>
+      <c r="B96" s="15" t="inlineStr">
+        <is>
+          <t>grand-sac-en-cuir</t>
+        </is>
+      </c>
+      <c r="C96" s="20" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D96" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" s="18" t="n"/>
+      <c r="F96" s="18" t="n"/>
+      <c r="G96" s="18" t="n"/>
+      <c r="H96" s="18" t="n"/>
+      <c r="I96" s="18" t="n"/>
+      <c r="J96" s="18" t="n"/>
+      <c r="K96" s="18" t="n"/>
+      <c r="L96" s="18" t="n"/>
+      <c r="M96" s="19" t="inlineStr">
+        <is>
+          <t>+2 rangées de sac</t>
+        </is>
+      </c>
+      <c r="N96" s="18" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="14" t="inlineStr">
+        <is>
+          <t>Huge Leather Pouch</t>
+        </is>
+      </c>
+      <c r="B97" s="15" t="inlineStr">
+        <is>
+          <t>enorme-sac-en-cuir</t>
+        </is>
+      </c>
+      <c r="C97" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D97" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" s="18" t="n"/>
+      <c r="F97" s="18" t="n"/>
+      <c r="G97" s="18" t="n"/>
+      <c r="H97" s="18" t="n"/>
+      <c r="I97" s="18" t="n"/>
+      <c r="J97" s="18" t="n"/>
+      <c r="K97" s="18" t="n"/>
+      <c r="L97" s="18" t="n"/>
+      <c r="M97" s="19" t="inlineStr">
+        <is>
+          <t>+3 rangées de sac</t>
+        </is>
+      </c>
+      <c r="N97" s="18" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="14" t="inlineStr">
+        <is>
+          <t>Backpack</t>
+        </is>
+      </c>
+      <c r="B98" s="15" t="inlineStr">
+        <is>
+          <t>sac-a-dos</t>
+        </is>
+      </c>
+      <c r="C98" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D98" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" s="18" t="n"/>
+      <c r="F98" s="18" t="n"/>
+      <c r="G98" s="18" t="n"/>
+      <c r="H98" s="18" t="n"/>
+      <c r="I98" s="18" t="n"/>
+      <c r="J98" s="18" t="n"/>
+      <c r="K98" s="18" t="n"/>
+      <c r="L98" s="18" t="n"/>
+      <c r="M98" s="19" t="inlineStr">
+        <is>
+          <t>+4 rangées de sac</t>
+        </is>
+      </c>
+      <c r="N98" s="18" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="14" t="inlineStr">
+        <is>
+          <t>Bottomless Bag</t>
+        </is>
+      </c>
+      <c r="B99" s="15" t="inlineStr">
+        <is>
+          <t>sac-sans-fond</t>
+        </is>
+      </c>
+      <c r="C99" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="D99" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" s="18" t="n"/>
+      <c r="F99" s="18" t="n"/>
+      <c r="G99" s="18" t="n"/>
+      <c r="H99" s="18" t="n"/>
+      <c r="I99" s="18" t="n"/>
+      <c r="J99" s="18" t="n"/>
+      <c r="K99" s="18" t="n"/>
+      <c r="L99" s="18" t="n"/>
+      <c r="M99" s="19" t="inlineStr">
+        <is>
+          <t>+6 rangées de sac</t>
+        </is>
+      </c>
+      <c r="N99" s="18" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="14" t="inlineStr">
+        <is>
+          <t>Master Miner's Bag</t>
+        </is>
+      </c>
+      <c r="B100" s="15" t="inlineStr">
+        <is>
+          <t>sac-maitre-mineur</t>
+        </is>
+      </c>
+      <c r="C100" s="24" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="D100" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" s="18" t="n"/>
+      <c r="F100" s="18" t="n"/>
+      <c r="G100" s="18" t="n"/>
+      <c r="H100" s="18" t="n"/>
+      <c r="I100" s="18" t="n"/>
+      <c r="J100" s="18" t="n"/>
+      <c r="K100" s="18" t="n"/>
+      <c r="L100" s="18" t="n"/>
+      <c r="M100" s="19" t="inlineStr">
+        <is>
+          <t>+10 rangées de sac</t>
+        </is>
+      </c>
+      <c r="N100" s="18" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="23" t="n"/>
+      <c r="B101" s="23" t="n"/>
+      <c r="C101" s="23" t="n"/>
+      <c r="D101" s="23" t="n"/>
+      <c r="E101" s="23" t="n"/>
+      <c r="F101" s="23" t="n"/>
+      <c r="G101" s="23" t="n"/>
+      <c r="H101" s="23" t="n"/>
+      <c r="I101" s="23" t="n"/>
+      <c r="J101" s="23" t="n"/>
+      <c r="K101" s="23" t="n"/>
+      <c r="L101" s="23" t="n"/>
+      <c r="M101" s="23" t="n"/>
+      <c r="N101" s="23" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="23" t="n"/>
+      <c r="B102" s="23" t="n"/>
+      <c r="C102" s="23" t="n"/>
+      <c r="D102" s="23" t="n"/>
+      <c r="E102" s="23" t="n"/>
+      <c r="F102" s="23" t="n"/>
+      <c r="G102" s="23" t="n"/>
+      <c r="H102" s="23" t="n"/>
+      <c r="I102" s="23" t="n"/>
+      <c r="J102" s="23" t="n"/>
+      <c r="K102" s="23" t="n"/>
+      <c r="L102" s="23" t="n"/>
+      <c r="M102" s="23" t="n"/>
+      <c r="N102" s="23" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="23" t="n"/>
+      <c r="B103" s="23" t="n"/>
+      <c r="C103" s="23" t="n"/>
+      <c r="D103" s="23" t="n"/>
+      <c r="E103" s="23" t="n"/>
+      <c r="F103" s="23" t="n"/>
+      <c r="G103" s="23" t="n"/>
+      <c r="H103" s="23" t="n"/>
+      <c r="I103" s="23" t="n"/>
+      <c r="J103" s="23" t="n"/>
+      <c r="K103" s="23" t="n"/>
+      <c r="L103" s="23" t="n"/>
+      <c r="M103" s="23" t="n"/>
+      <c r="N103" s="23" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="23" t="n"/>
+      <c r="B104" s="23" t="n"/>
+      <c r="C104" s="23" t="n"/>
+      <c r="D104" s="23" t="n"/>
+      <c r="E104" s="23" t="n"/>
+      <c r="F104" s="23" t="n"/>
+      <c r="G104" s="23" t="n"/>
+      <c r="H104" s="23" t="n"/>
+      <c r="I104" s="23" t="n"/>
+      <c r="J104" s="23" t="n"/>
+      <c r="K104" s="23" t="n"/>
+      <c r="L104" s="23" t="n"/>
+      <c r="M104" s="23" t="n"/>
+      <c r="N104" s="23" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="23" t="n"/>
+      <c r="B105" s="23" t="n"/>
+      <c r="C105" s="23" t="n"/>
+      <c r="D105" s="23" t="n"/>
+      <c r="E105" s="23" t="n"/>
+      <c r="F105" s="23" t="n"/>
+      <c r="G105" s="23" t="n"/>
+      <c r="H105" s="23" t="n"/>
+      <c r="I105" s="23" t="n"/>
+      <c r="J105" s="23" t="n"/>
+      <c r="K105" s="23" t="n"/>
+      <c r="L105" s="23" t="n"/>
+      <c r="M105" s="23" t="n"/>
+      <c r="N105" s="23" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="23" t="n"/>
+      <c r="B106" s="23" t="n"/>
+      <c r="C106" s="23" t="n"/>
+      <c r="D106" s="23" t="n"/>
+      <c r="E106" s="23" t="n"/>
+      <c r="F106" s="23" t="n"/>
+      <c r="G106" s="23" t="n"/>
+      <c r="H106" s="23" t="n"/>
+      <c r="I106" s="23" t="n"/>
+      <c r="J106" s="23" t="n"/>
+      <c r="K106" s="23" t="n"/>
+      <c r="L106" s="23" t="n"/>
+      <c r="M106" s="23" t="n"/>
+      <c r="N106" s="23" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="A17:N17"/>
+    <mergeCell ref="A70:N70"/>
     <mergeCell ref="A27:N27"/>
-    <mergeCell ref="A88:N88"/>
+    <mergeCell ref="A94:N94"/>
     <mergeCell ref="A4:N4"/>
-    <mergeCell ref="A78:N78"/>
+    <mergeCell ref="A48:N48"/>
     <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A68:N68"/>
-    <mergeCell ref="A47:N47"/>
+    <mergeCell ref="A59:N59"/>
+    <mergeCell ref="A82:N82"/>
     <mergeCell ref="A36:N36"/>
-    <mergeCell ref="A58:N58"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2903,7 +3354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2966,12 +3417,12 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="24" t="inlineStr">
+      <c r="A3" s="25" t="inlineStr">
         <is>
           <t>All Should Be Fire</t>
         </is>
       </c>
-      <c r="B3" s="25" t="inlineStr">
+      <c r="B3" s="26" t="inlineStr">
         <is>
           <t>tout-en-feu</t>
         </is>
@@ -2979,7 +3430,7 @@
       <c r="C3" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="D3" s="26" t="inlineStr">
+      <c r="D3" s="27" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
@@ -3006,12 +3457,12 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>Armor Forging</t>
         </is>
       </c>
-      <c r="B4" s="25" t="inlineStr">
+      <c r="B4" s="26" t="inlineStr">
         <is>
           <t>forgeage-d-armure</t>
         </is>
@@ -3019,7 +3470,7 @@
       <c r="C4" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="D4" s="26" t="inlineStr">
+      <c r="D4" s="27" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
@@ -3046,518 +3497,518 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
+        <is>
+          <t>Blinding Flash</t>
+        </is>
+      </c>
+      <c r="B5" s="26" t="inlineStr">
+        <is>
+          <t>eclair-aveuglant</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" s="27" t="inlineStr">
+        <is>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F5" s="17" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="G5" s="18" t="inlineStr">
+        <is>
+          <t>Crusader Plate</t>
+        </is>
+      </c>
+      <c r="H5" s="18" t="inlineStr">
+        <is>
+          <t>Apply 2 Confusion to ALL enemies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="25" t="inlineStr">
         <is>
           <t>Bloodletting</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B6" s="26" t="inlineStr">
         <is>
           <t>coup-de-sang</t>
         </is>
       </c>
-      <c r="C5" s="17" t="n">
+      <c r="C6" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="26" t="inlineStr">
+      <c r="D6" s="27" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E5" s="20" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="F5" s="17" t="inlineStr"/>
-      <c r="G5" s="18" t="inlineStr">
-        <is>
-          <t>Blood Ring</t>
-        </is>
-      </c>
-      <c r="H5" s="18" t="inlineStr">
-        <is>
-          <t>Deal 3 damage + current Bleed stacks as bonus damage. Apply 3 Bleed (stacks don't reset).</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="24" t="inlineStr">
-        <is>
-          <t>Burning Hand</t>
-        </is>
-      </c>
-      <c r="B6" s="25" t="inlineStr">
-        <is>
-          <t>main-brulante</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="26" t="inlineStr">
-        <is>
-          <t>Attaque</t>
-        </is>
-      </c>
-      <c r="E6" s="22" t="inlineStr">
-        <is>
-          <t>Epic</t>
         </is>
       </c>
       <c r="F6" s="17" t="inlineStr"/>
       <c r="G6" s="18" t="inlineStr">
         <is>
-          <t>Onyx Glove</t>
+          <t>Blood Ring</t>
         </is>
       </c>
       <c r="H6" s="18" t="inlineStr">
         <is>
-          <t>Discard your hand. For each card discarded, apply 8 Burning to a random enemy.</t>
+          <t>Deal 3 damage + current Bleed stacks as bonus damage. Apply 3 Bleed (stacks don't reset).</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="24" t="inlineStr">
-        <is>
-          <t>Cleave</t>
-        </is>
-      </c>
-      <c r="B7" s="25" t="inlineStr">
-        <is>
-          <t>couper-en-deux</t>
+      <c r="A7" s="25" t="inlineStr">
+        <is>
+          <t>Burning Hand</t>
+        </is>
+      </c>
+      <c r="B7" s="26" t="inlineStr">
+        <is>
+          <t>main-brulante</t>
         </is>
       </c>
       <c r="C7" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D7" s="26" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="D7" s="27" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E7" s="21" t="inlineStr">
-        <is>
-          <t>Rare</t>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
         </is>
       </c>
       <c r="F7" s="17" t="inlineStr"/>
       <c r="G7" s="18" t="inlineStr">
         <is>
+          <t>Onyx Glove</t>
+        </is>
+      </c>
+      <c r="H7" s="18" t="inlineStr">
+        <is>
+          <t>Discard your hand. For each card discarded, apply 8 Burning to a random enemy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="25" t="inlineStr">
+        <is>
+          <t>Cleave</t>
+        </is>
+      </c>
+      <c r="B8" s="26" t="inlineStr">
+        <is>
+          <t>couper-en-deux</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="27" t="inlineStr">
+        <is>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F8" s="17" t="inlineStr"/>
+      <c r="G8" s="18" t="inlineStr">
+        <is>
           <t>War Axe</t>
         </is>
       </c>
-      <c r="H7" s="18" t="inlineStr">
+      <c r="H8" s="18" t="inlineStr">
         <is>
           <t>Deal 20 damage. If the target dies, deal 15 damage to the next enemy.</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="24" t="inlineStr">
-        <is>
-          <t>Dragon's Blaze</t>
-        </is>
-      </c>
-      <c r="B8" s="25" t="inlineStr">
-        <is>
-          <t>embrasement-dragon</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="D8" s="26" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="25" t="inlineStr">
+        <is>
+          <t>Dazzling Kick</t>
+        </is>
+      </c>
+      <c r="B9" s="26" t="inlineStr">
+        <is>
+          <t>coup-eblouissant</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" s="27" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E8" s="22" t="inlineStr">
-        <is>
-          <t>Epic</t>
-        </is>
-      </c>
-      <c r="F8" s="17" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="G8" s="18" t="inlineStr">
-        <is>
-          <t>Magma Hammer, Onyx Guard Plate</t>
-        </is>
-      </c>
-      <c r="H8" s="18" t="inlineStr">
-        <is>
-          <t>Detonate all Burning: deal 2 damage per Burning on ALL enemies.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="24" t="inlineStr">
-        <is>
-          <t>Fire Strike</t>
-        </is>
-      </c>
-      <c r="B9" s="25" t="inlineStr">
-        <is>
-          <t>feu-frappe</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="26" t="inlineStr">
-        <is>
-          <t>Attaque</t>
-        </is>
-      </c>
-      <c r="E9" s="22" t="inlineStr">
-        <is>
-          <t>Epic</t>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
         </is>
       </c>
       <c r="F9" s="17" t="inlineStr"/>
       <c r="G9" s="18" t="inlineStr">
         <is>
-          <t>Magma Hammer</t>
+          <t>Crusader Greaves</t>
         </is>
       </c>
       <c r="H9" s="18" t="inlineStr">
         <is>
-          <t>Deal 12 damage. Apply 3 Burning.</t>
+          <t>Deal 10 damage. Apply 3 Confusion.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="24" t="inlineStr">
-        <is>
-          <t>Flaming Kick</t>
-        </is>
-      </c>
-      <c r="B10" s="25" t="inlineStr">
-        <is>
-          <t>coup-de-pied-ardent</t>
+      <c r="A10" s="25" t="inlineStr">
+        <is>
+          <t>Dragon's Blaze</t>
+        </is>
+      </c>
+      <c r="B10" s="26" t="inlineStr">
+        <is>
+          <t>embrasement-dragon</t>
         </is>
       </c>
       <c r="C10" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" s="27" t="inlineStr">
+        <is>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F10" s="17" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="G10" s="18" t="inlineStr">
+        <is>
+          <t>Magma Hammer, Onyx Guard Plate</t>
+        </is>
+      </c>
+      <c r="H10" s="18" t="inlineStr">
+        <is>
+          <t>Detonate all Burning: deal 2 damage per Burning on ALL enemies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="25" t="inlineStr">
+        <is>
+          <t>Fire Strike</t>
+        </is>
+      </c>
+      <c r="B11" s="26" t="inlineStr">
+        <is>
+          <t>feu-frappe</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="26" t="inlineStr">
+      <c r="D11" s="27" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E10" s="22" t="inlineStr">
+      <c r="E11" s="22" t="inlineStr">
         <is>
           <t>Epic</t>
-        </is>
-      </c>
-      <c r="F10" s="17" t="inlineStr"/>
-      <c r="G10" s="18" t="inlineStr">
-        <is>
-          <t>Onyx Boots</t>
-        </is>
-      </c>
-      <c r="H10" s="18" t="inlineStr">
-        <is>
-          <t>Move all Burning from the target to the enemy behind it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="24" t="inlineStr">
-        <is>
-          <t>Forge Smash</t>
-        </is>
-      </c>
-      <c r="B11" s="25" t="inlineStr">
-        <is>
-          <t>ecrasement</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" s="26" t="inlineStr">
-        <is>
-          <t>Attaque</t>
-        </is>
-      </c>
-      <c r="E11" s="20" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
         </is>
       </c>
       <c r="F11" s="17" t="inlineStr"/>
       <c r="G11" s="18" t="inlineStr">
         <is>
-          <t>Forge Hammer</t>
+          <t>Magma Hammer</t>
         </is>
       </c>
       <c r="H11" s="18" t="inlineStr">
         <is>
-          <t>Deal 10 damage. Gain 8 Stone.</t>
+          <t>Deal 12 damage. Apply 3 Burning.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="24" t="inlineStr">
-        <is>
-          <t>Frostbite</t>
-        </is>
-      </c>
-      <c r="B12" s="25" t="inlineStr">
-        <is>
-          <t>givre-lent</t>
+      <c r="A12" s="25" t="inlineStr">
+        <is>
+          <t>Flaming Kick</t>
+        </is>
+      </c>
+      <c r="B12" s="26" t="inlineStr">
+        <is>
+          <t>coup-de-pied-ardent</t>
         </is>
       </c>
       <c r="C12" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="D12" s="26" t="inlineStr">
+      <c r="D12" s="27" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E12" s="20" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
         </is>
       </c>
       <c r="F12" s="17" t="inlineStr"/>
       <c r="G12" s="18" t="inlineStr">
         <is>
-          <t>Frost Ring</t>
+          <t>Onyx Boots</t>
         </is>
       </c>
       <c r="H12" s="18" t="inlineStr">
         <is>
-          <t>Deal 5 damage. Chill: -30% speed for 3 turns.</t>
+          <t>Move all Burning from the target to the enemy behind it.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="24" t="inlineStr">
-        <is>
-          <t>Giant Swing</t>
-        </is>
-      </c>
-      <c r="B13" s="25" t="inlineStr">
-        <is>
-          <t>giant-swing</t>
+      <c r="A13" s="25" t="inlineStr">
+        <is>
+          <t>Forge Smash</t>
+        </is>
+      </c>
+      <c r="B13" s="26" t="inlineStr">
+        <is>
+          <t>ecrasement</t>
         </is>
       </c>
       <c r="C13" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="D13" s="26" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="D13" s="27" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E13" s="21" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F13" s="17" t="inlineStr"/>
+      <c r="G13" s="18" t="inlineStr">
+        <is>
+          <t>Forge Hammer</t>
+        </is>
+      </c>
+      <c r="H13" s="18" t="inlineStr">
+        <is>
+          <t>Deal 10 damage. Gain 8 Stone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="25" t="inlineStr">
+        <is>
+          <t>Frost Cascade</t>
+        </is>
+      </c>
+      <c r="B14" s="26" t="inlineStr">
+        <is>
+          <t>gel-cascade</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="27" t="inlineStr">
+        <is>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="F13" s="17" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="G13" s="18" t="inlineStr">
-        <is>
-          <t>War Axe</t>
-        </is>
-      </c>
-      <c r="H13" s="18" t="inlineStr">
-        <is>
-          <t>Deal 16 damage to ALL enemies. Apply 2 Bleed to ALL enemies.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="24" t="inlineStr">
-        <is>
-          <t>Heat Rejection</t>
-        </is>
-      </c>
-      <c r="B14" s="25" t="inlineStr">
-        <is>
-          <t>rejet-chaleur</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="26" t="inlineStr">
+      <c r="F14" s="17" t="inlineStr"/>
+      <c r="G14" s="18" t="inlineStr">
+        <is>
+          <t>Perfect Frost Ring</t>
+        </is>
+      </c>
+      <c r="H14" s="18" t="inlineStr">
+        <is>
+          <t>Deal 8 damage and apply 3 Chill. If the target was already chilled, cascade the same hit to the next enemy, and so on.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="25" t="inlineStr">
+        <is>
+          <t>Frostbite</t>
+        </is>
+      </c>
+      <c r="B15" s="26" t="inlineStr">
+        <is>
+          <t>givre-lent</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="27" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E14" s="22" t="inlineStr">
-        <is>
-          <t>Epic</t>
-        </is>
-      </c>
-      <c r="F14" s="17" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="G14" s="18" t="inlineStr">
-        <is>
-          <t>Big Onyx Sword</t>
-        </is>
-      </c>
-      <c r="H14" s="18" t="inlineStr">
-        <is>
-          <t>Spend all Forge Heat. Apply 8 Burning per Heat spent to ALL enemies.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="24" t="inlineStr">
-        <is>
-          <t>Lava Hammer</t>
-        </is>
-      </c>
-      <c r="B15" s="25" t="inlineStr">
-        <is>
-          <t>coup-de-lave</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D15" s="26" t="inlineStr">
-        <is>
-          <t>Attaque</t>
-        </is>
-      </c>
-      <c r="E15" s="22" t="inlineStr">
-        <is>
-          <t>Epic</t>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="F15" s="17" t="inlineStr"/>
       <c r="G15" s="18" t="inlineStr">
         <is>
-          <t>Magma Hammer</t>
+          <t>Frost Ring</t>
         </is>
       </c>
       <c r="H15" s="18" t="inlineStr">
         <is>
-          <t>Deal 28 damage. Apply 4 Burning.</t>
+          <t>Deal 5 damage. Chill: -30% speed for 3 turns.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="24" t="inlineStr">
-        <is>
-          <t>Onyx Breath</t>
-        </is>
-      </c>
-      <c r="B16" s="25" t="inlineStr">
-        <is>
-          <t>souffle-onyx</t>
+      <c r="A16" s="25" t="inlineStr">
+        <is>
+          <t>Giant Swing</t>
+        </is>
+      </c>
+      <c r="B16" s="26" t="inlineStr">
+        <is>
+          <t>giant-swing</t>
         </is>
       </c>
       <c r="C16" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D16" s="26" t="inlineStr">
+      <c r="D16" s="27" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E16" s="22" t="inlineStr">
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F16" s="17" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="G16" s="18" t="inlineStr">
+        <is>
+          <t>War Axe</t>
+        </is>
+      </c>
+      <c r="H16" s="18" t="inlineStr">
+        <is>
+          <t>Deal 16 damage to ALL enemies. Apply 2 Bleed to ALL enemies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="25" t="inlineStr">
+        <is>
+          <t>Halo Burst</t>
+        </is>
+      </c>
+      <c r="B17" s="26" t="inlineStr">
+        <is>
+          <t>eclat-de-halo</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" s="27" t="inlineStr">
+        <is>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F17" s="17" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="G17" s="18" t="inlineStr">
+        <is>
+          <t>Crusader Gauntlets</t>
+        </is>
+      </c>
+      <c r="H17" s="18" t="inlineStr">
+        <is>
+          <t>Deal 6 damage to ALL enemies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="25" t="inlineStr">
+        <is>
+          <t>Heat Rejection</t>
+        </is>
+      </c>
+      <c r="B18" s="26" t="inlineStr">
+        <is>
+          <t>rejet-chaleur</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="27" t="inlineStr">
+        <is>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="F16" s="17" t="inlineStr">
+      <c r="F18" s="17" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="G16" s="18" t="inlineStr">
-        <is>
-          <t>Onyx Guard Plate</t>
-        </is>
-      </c>
-      <c r="H16" s="18" t="inlineStr">
-        <is>
-          <t>Apply 20 Burning to ALL enemies.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="24" t="inlineStr">
-        <is>
-          <t>Onyx Fist</t>
-        </is>
-      </c>
-      <c r="B17" s="25" t="inlineStr">
-        <is>
-          <t>poing-onyx</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" s="26" t="inlineStr">
-        <is>
-          <t>Attaque</t>
-        </is>
-      </c>
-      <c r="E17" s="22" t="inlineStr">
-        <is>
-          <t>Epic</t>
-        </is>
-      </c>
-      <c r="F17" s="17" t="inlineStr"/>
-      <c r="G17" s="18" t="inlineStr">
-        <is>
-          <t>Onyx Glove</t>
-        </is>
-      </c>
-      <c r="H17" s="18" t="inlineStr">
-        <is>
-          <t>Gain 10 Stone. Deal 10 damage and apply 3 Burning.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="24" t="inlineStr">
-        <is>
-          <t>Onyx Radiance</t>
-        </is>
-      </c>
-      <c r="B18" s="25" t="inlineStr">
-        <is>
-          <t>onyx-radiance</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="26" t="inlineStr">
-        <is>
-          <t>Attaque</t>
-        </is>
-      </c>
-      <c r="E18" s="22" t="inlineStr">
-        <is>
-          <t>Epic</t>
-        </is>
-      </c>
-      <c r="F18" s="17" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
       <c r="G18" s="18" t="inlineStr">
         <is>
           <t>Big Onyx Sword</t>
@@ -3565,25 +4016,25 @@
       </c>
       <c r="H18" s="18" t="inlineStr">
         <is>
-          <t>Apply 8 Burning to ALL enemies.</t>
+          <t>Spend all Forge Heat. Apply 8 Burning per Heat spent to ALL enemies.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="24" t="inlineStr">
-        <is>
-          <t>Onyx Slash</t>
-        </is>
-      </c>
-      <c r="B19" s="25" t="inlineStr">
-        <is>
-          <t>onyx-slash</t>
+      <c r="A19" s="25" t="inlineStr">
+        <is>
+          <t>Lava Hammer</t>
+        </is>
+      </c>
+      <c r="B19" s="26" t="inlineStr">
+        <is>
+          <t>coup-de-lave</t>
         </is>
       </c>
       <c r="C19" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="D19" s="26" t="inlineStr">
+      <c r="D19" s="27" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
@@ -3596,73 +4047,73 @@
       <c r="F19" s="17" t="inlineStr"/>
       <c r="G19" s="18" t="inlineStr">
         <is>
-          <t>Big Onyx Sword</t>
+          <t>Magma Hammer</t>
         </is>
       </c>
       <c r="H19" s="18" t="inlineStr">
         <is>
-          <t>Deal 26 damage and 4 Burning. The enemy behind takes half (13 damage, 2 Burning).</t>
+          <t>Deal 28 damage. Apply 4 Burning.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="24" t="inlineStr">
-        <is>
-          <t>Pickaxe Jab</t>
-        </is>
-      </c>
-      <c r="B20" s="25" t="inlineStr">
-        <is>
-          <t>coup-de-pioche</t>
+      <c r="A20" s="25" t="inlineStr">
+        <is>
+          <t>Lumen Jab</t>
+        </is>
+      </c>
+      <c r="B20" s="26" t="inlineStr">
+        <is>
+          <t>coup-de-lumiere</t>
         </is>
       </c>
       <c r="C20" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="26" t="inlineStr">
+      <c r="D20" s="27" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E20" s="16" t="inlineStr">
-        <is>
-          <t>Common</t>
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
         </is>
       </c>
       <c r="F20" s="17" t="inlineStr"/>
       <c r="G20" s="18" t="inlineStr">
         <is>
-          <t>Miner's Pick</t>
+          <t>Crusader Gauntlets</t>
         </is>
       </c>
       <c r="H20" s="18" t="inlineStr">
         <is>
-          <t>Deal 3 damage twice. If the target dies, hit a random other enemy for 3.</t>
+          <t>Deal 8 damage. Apply 1 Confusion.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="24" t="inlineStr">
-        <is>
-          <t>Poison Dance</t>
-        </is>
-      </c>
-      <c r="B21" s="25" t="inlineStr">
-        <is>
-          <t>danse-empoisonnee</t>
+      <c r="A21" s="25" t="inlineStr">
+        <is>
+          <t>Onyx Breath</t>
+        </is>
+      </c>
+      <c r="B21" s="26" t="inlineStr">
+        <is>
+          <t>souffle-onyx</t>
         </is>
       </c>
       <c r="C21" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D21" s="26" t="inlineStr">
+      <c r="D21" s="27" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E21" s="21" t="inlineStr">
-        <is>
-          <t>Rare</t>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
         </is>
       </c>
       <c r="F21" s="17" t="inlineStr">
@@ -3672,282 +4123,290 @@
       </c>
       <c r="G21" s="18" t="inlineStr">
         <is>
-          <t>Basilisk Fang</t>
+          <t>Onyx Guard Plate</t>
         </is>
       </c>
       <c r="H21" s="18" t="inlineStr">
         <is>
-          <t>Hit ALL enemies 3 times for 3 damage. Apply 1 Poison per hit (2 if the enemy was already poisoned).</t>
+          <t>Apply 20 Burning to ALL enemies.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="24" t="inlineStr">
-        <is>
-          <t>Pommel Strike</t>
-        </is>
-      </c>
-      <c r="B22" s="25" t="inlineStr">
-        <is>
-          <t>coup-de-pommeau</t>
+      <c r="A22" s="25" t="inlineStr">
+        <is>
+          <t>Onyx Fist</t>
+        </is>
+      </c>
+      <c r="B22" s="26" t="inlineStr">
+        <is>
+          <t>poing-onyx</t>
         </is>
       </c>
       <c r="C22" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="26" t="inlineStr">
+      <c r="D22" s="27" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E22" s="21" t="inlineStr">
-        <is>
-          <t>Rare</t>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
         </is>
       </c>
       <c r="F22" s="17" t="inlineStr"/>
       <c r="G22" s="18" t="inlineStr">
         <is>
-          <t>War Axe</t>
+          <t>Onyx Glove</t>
         </is>
       </c>
       <c r="H22" s="18" t="inlineStr">
         <is>
-          <t>Deal 16 damage. Stun the target for 2 turns.</t>
+          <t>Gain 10 Stone. Deal 10 damage and apply 3 Burning.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="24" t="inlineStr">
-        <is>
-          <t>Punch</t>
-        </is>
-      </c>
-      <c r="B23" s="25" t="inlineStr">
-        <is>
-          <t>coup-faible</t>
+      <c r="A23" s="25" t="inlineStr">
+        <is>
+          <t>Onyx Radiance</t>
+        </is>
+      </c>
+      <c r="B23" s="26" t="inlineStr">
+        <is>
+          <t>onyx-radiance</t>
         </is>
       </c>
       <c r="C23" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="26" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="D23" s="27" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E23" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="17" t="inlineStr"/>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F23" s="17" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
       <c r="G23" s="18" t="inlineStr">
         <is>
-          <t>— (deck de base)</t>
+          <t>Big Onyx Sword</t>
         </is>
       </c>
       <c r="H23" s="18" t="inlineStr">
         <is>
-          <t>Deal 3 damage.</t>
+          <t>Apply 8 Burning to ALL enemies.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="24" t="inlineStr">
-        <is>
-          <t>Rusty Cleave</t>
-        </is>
-      </c>
-      <c r="B24" s="25" t="inlineStr">
-        <is>
-          <t>coup-de-hache</t>
+      <c r="A24" s="25" t="inlineStr">
+        <is>
+          <t>Onyx Slash</t>
+        </is>
+      </c>
+      <c r="B24" s="26" t="inlineStr">
+        <is>
+          <t>onyx-slash</t>
         </is>
       </c>
       <c r="C24" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="D24" s="26" t="inlineStr">
+      <c r="D24" s="27" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E24" s="16" t="inlineStr">
-        <is>
-          <t>Common</t>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
         </is>
       </c>
       <c r="F24" s="17" t="inlineStr"/>
       <c r="G24" s="18" t="inlineStr">
         <is>
-          <t>Rusty Axe</t>
+          <t>Big Onyx Sword</t>
         </is>
       </c>
       <c r="H24" s="18" t="inlineStr">
         <is>
-          <t>Deal 6 damage to the target and 4 damage to each adjacent enemy.</t>
+          <t>Deal 26 damage and 4 Burning. The enemy behind takes half (13 damage, 2 Burning).</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="24" t="inlineStr">
-        <is>
-          <t>Shield Bash</t>
-        </is>
-      </c>
-      <c r="B25" s="25" t="inlineStr">
-        <is>
-          <t>coup-de-bouclier</t>
+      <c r="A25" s="25" t="inlineStr">
+        <is>
+          <t>Pickaxe Jab</t>
+        </is>
+      </c>
+      <c r="B25" s="26" t="inlineStr">
+        <is>
+          <t>coup-de-pioche</t>
         </is>
       </c>
       <c r="C25" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D25" s="26" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="D25" s="27" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E25" s="21" t="inlineStr">
-        <is>
-          <t>Rare</t>
+      <c r="E25" s="16" t="inlineStr">
+        <is>
+          <t>Common</t>
         </is>
       </c>
       <c r="F25" s="17" t="inlineStr"/>
       <c r="G25" s="18" t="inlineStr">
         <is>
-          <t>Tower Shield</t>
+          <t>Miner's Pick</t>
         </is>
       </c>
       <c r="H25" s="18" t="inlineStr">
         <is>
-          <t>Deal 10 damage. Stun the enemy for 3 turns.</t>
+          <t>Deal 3 damage twice. If the target dies, hit a random other enemy for 3.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="24" t="inlineStr">
-        <is>
-          <t>Splash Strike</t>
-        </is>
-      </c>
-      <c r="B26" s="25" t="inlineStr">
-        <is>
-          <t>eclaboussure-de-frappe</t>
+      <c r="A26" s="25" t="inlineStr">
+        <is>
+          <t>Poison Dance</t>
+        </is>
+      </c>
+      <c r="B26" s="26" t="inlineStr">
+        <is>
+          <t>danse-empoisonnee</t>
         </is>
       </c>
       <c r="C26" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D26" s="26" t="inlineStr">
+      <c r="D26" s="27" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E26" s="20" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="F26" s="17" t="inlineStr"/>
+      <c r="E26" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F26" s="17" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
       <c r="G26" s="18" t="inlineStr">
         <is>
-          <t>Forge Hammer</t>
+          <t>Basilisk Fang</t>
         </is>
       </c>
       <c r="H26" s="18" t="inlineStr">
         <is>
-          <t>Deal 15 damage. Each adjacent enemy has a 50% chance to take 5 Burning.</t>
+          <t>Hit ALL enemies 3 times for 3 damage. Apply 1 Poison per hit (2 if the enemy was already poisoned).</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="24" t="inlineStr">
-        <is>
-          <t>Strike</t>
-        </is>
-      </c>
-      <c r="B27" s="25" t="inlineStr">
-        <is>
-          <t>frappe</t>
+      <c r="A27" s="25" t="inlineStr">
+        <is>
+          <t>Pommel Strike</t>
+        </is>
+      </c>
+      <c r="B27" s="26" t="inlineStr">
+        <is>
+          <t>coup-de-pommeau</t>
         </is>
       </c>
       <c r="C27" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="26" t="inlineStr">
+      <c r="D27" s="27" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E27" s="16" t="inlineStr">
-        <is>
-          <t>Common</t>
+      <c r="E27" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
         </is>
       </c>
       <c r="F27" s="17" t="inlineStr"/>
       <c r="G27" s="18" t="inlineStr">
         <is>
-          <t>Rusty Axe, Forge Hammer, Miner's Pick</t>
+          <t>War Axe</t>
         </is>
       </c>
       <c r="H27" s="18" t="inlineStr">
         <is>
-          <t>Deal 6 damage.</t>
+          <t>Deal 16 damage. Stun the target for 2 turns.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="24" t="inlineStr">
-        <is>
-          <t>Venom Stab</t>
-        </is>
-      </c>
-      <c r="B28" s="25" t="inlineStr">
-        <is>
-          <t>coup-venimeux</t>
+      <c r="A28" s="25" t="inlineStr">
+        <is>
+          <t>Punch</t>
+        </is>
+      </c>
+      <c r="B28" s="26" t="inlineStr">
+        <is>
+          <t>coup-faible</t>
         </is>
       </c>
       <c r="C28" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" s="26" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="D28" s="27" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E28" s="21" t="inlineStr">
-        <is>
-          <t>Rare</t>
+      <c r="E28" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="F28" s="17" t="inlineStr"/>
       <c r="G28" s="18" t="inlineStr">
         <is>
-          <t>Basilisk Fang</t>
+          <t>— (deck de base)</t>
         </is>
       </c>
       <c r="H28" s="18" t="inlineStr">
         <is>
-          <t>Deal 4 damage. Apply 4 Poison.</t>
+          <t>Deal 3 damage.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="24" t="inlineStr">
-        <is>
-          <t>Wound Opening</t>
-        </is>
-      </c>
-      <c r="B29" s="25" t="inlineStr">
-        <is>
-          <t>ouverture-des-plaies</t>
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>Radiant Strike</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="inlineStr">
+        <is>
+          <t>frappe-radiante</t>
         </is>
       </c>
       <c r="C29" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="D29" s="26" t="inlineStr">
+      <c r="D29" s="27" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
@@ -3960,140 +4419,140 @@
       <c r="F29" s="17" t="inlineStr"/>
       <c r="G29" s="18" t="inlineStr">
         <is>
-          <t>Basilisk Fang</t>
+          <t>Crusader Plate</t>
         </is>
       </c>
       <c r="H29" s="18" t="inlineStr">
         <is>
-          <t>Deal 18 damage. Doubled if the target has a negative status.</t>
+          <t>Deal 14 damage. Apply 2 Confusion.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="24" t="inlineStr">
-        <is>
-          <t>Guard</t>
-        </is>
-      </c>
-      <c r="B30" s="25" t="inlineStr">
-        <is>
-          <t>garde</t>
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>Rusty Cleave</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="inlineStr">
+        <is>
+          <t>coup-de-hache</t>
         </is>
       </c>
       <c r="C30" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" s="28" t="inlineStr">
-        <is>
-          <t>Défense</t>
-        </is>
-      </c>
-      <c r="E30" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>2</v>
+      </c>
+      <c r="D30" s="27" t="inlineStr">
+        <is>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="E30" s="16" t="inlineStr">
+        <is>
+          <t>Common</t>
         </is>
       </c>
       <c r="F30" s="17" t="inlineStr"/>
       <c r="G30" s="18" t="inlineStr">
         <is>
-          <t>— (deck de base)</t>
+          <t>Rusty Axe</t>
         </is>
       </c>
       <c r="H30" s="18" t="inlineStr">
         <is>
-          <t>Gain 5 Stone.</t>
+          <t>Deal 6 damage to the target and 4 damage to each adjacent enemy.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="24" t="inlineStr">
-        <is>
-          <t>Hand Guard</t>
-        </is>
-      </c>
-      <c r="B31" s="25" t="inlineStr">
-        <is>
-          <t>garde-faible</t>
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>Shield Bash</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="inlineStr">
+        <is>
+          <t>coup-de-bouclier</t>
         </is>
       </c>
       <c r="C31" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D31" s="28" t="inlineStr">
-        <is>
-          <t>Défense</t>
-        </is>
-      </c>
-      <c r="E31" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>2</v>
+      </c>
+      <c r="D31" s="27" t="inlineStr">
+        <is>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="E31" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
         </is>
       </c>
       <c r="F31" s="17" t="inlineStr"/>
       <c r="G31" s="18" t="inlineStr">
         <is>
-          <t>— (deck de base)</t>
+          <t>Tower Shield</t>
         </is>
       </c>
       <c r="H31" s="18" t="inlineStr">
         <is>
-          <t>Gain 3 Stone.</t>
+          <t>Deal 10 damage. Stun the enemy for 3 turns.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="24" t="inlineStr">
-        <is>
-          <t>Heavy Armor</t>
-        </is>
-      </c>
-      <c r="B32" s="25" t="inlineStr">
-        <is>
-          <t>armure-lourde</t>
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>Splash Strike</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="inlineStr">
+        <is>
+          <t>eclaboussure-de-frappe</t>
         </is>
       </c>
       <c r="C32" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D32" s="28" t="inlineStr">
-        <is>
-          <t>Défense</t>
-        </is>
-      </c>
-      <c r="E32" s="21" t="inlineStr">
-        <is>
-          <t>Rare</t>
+        <v>3</v>
+      </c>
+      <c r="D32" s="27" t="inlineStr">
+        <is>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="E32" s="20" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="F32" s="17" t="inlineStr"/>
       <c r="G32" s="18" t="inlineStr">
         <is>
-          <t>Forgemaster's Mail</t>
+          <t>Forge Hammer</t>
         </is>
       </c>
       <c r="H32" s="18" t="inlineStr">
         <is>
-          <t>Gain 20 Stone.</t>
+          <t>Deal 15 damage. Each adjacent enemy has a 50% chance to take 5 Burning.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="24" t="inlineStr">
-        <is>
-          <t>Light Armor</t>
-        </is>
-      </c>
-      <c r="B33" s="25" t="inlineStr">
-        <is>
-          <t>armure-legere</t>
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>Strike</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="inlineStr">
+        <is>
+          <t>frappe</t>
         </is>
       </c>
       <c r="C33" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="D33" s="28" t="inlineStr">
-        <is>
-          <t>Défense</t>
+      <c r="D33" s="27" t="inlineStr">
+        <is>
+          <t>Attaque</t>
         </is>
       </c>
       <c r="E33" s="16" t="inlineStr">
@@ -4104,32 +4563,32 @@
       <c r="F33" s="17" t="inlineStr"/>
       <c r="G33" s="18" t="inlineStr">
         <is>
-          <t>Traveler's Garb</t>
+          <t>Rusty Axe, Forge Hammer, Miner's Pick</t>
         </is>
       </c>
       <c r="H33" s="18" t="inlineStr">
         <is>
-          <t>Gain 5 Stone.</t>
+          <t>Deal 6 damage.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="24" t="inlineStr">
-        <is>
-          <t>Mail Armor</t>
-        </is>
-      </c>
-      <c r="B34" s="25" t="inlineStr">
-        <is>
-          <t>mail-armor</t>
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>Venom Stab</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="inlineStr">
+        <is>
+          <t>coup-venimeux</t>
         </is>
       </c>
       <c r="C34" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="D34" s="28" t="inlineStr">
-        <is>
-          <t>Défense</t>
+      <c r="D34" s="27" t="inlineStr">
+        <is>
+          <t>Attaque</t>
         </is>
       </c>
       <c r="E34" s="21" t="inlineStr">
@@ -4140,138 +4599,138 @@
       <c r="F34" s="17" t="inlineStr"/>
       <c r="G34" s="18" t="inlineStr">
         <is>
-          <t>Forgemaster's Mail</t>
+          <t>Basilisk Fang</t>
         </is>
       </c>
       <c r="H34" s="18" t="inlineStr">
         <is>
-          <t>Gain 7 Stone for every enemy still alive.</t>
+          <t>Deal 4 damage. Apply 4 Poison.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="24" t="inlineStr">
-        <is>
-          <t>Onyx Armor</t>
-        </is>
-      </c>
-      <c r="B35" s="25" t="inlineStr">
-        <is>
-          <t>onyx-armor</t>
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>Wound Opening</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="inlineStr">
+        <is>
+          <t>ouverture-des-plaies</t>
         </is>
       </c>
       <c r="C35" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="D35" s="28" t="inlineStr">
-        <is>
-          <t>Défense</t>
-        </is>
-      </c>
-      <c r="E35" s="22" t="inlineStr">
-        <is>
-          <t>Epic</t>
+      <c r="D35" s="27" t="inlineStr">
+        <is>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="E35" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
         </is>
       </c>
       <c r="F35" s="17" t="inlineStr"/>
       <c r="G35" s="18" t="inlineStr">
         <is>
-          <t>Onyx Guard Plate</t>
+          <t>Basilisk Fang</t>
         </is>
       </c>
       <c r="H35" s="18" t="inlineStr">
         <is>
-          <t>Gain 30 Stone.</t>
+          <t>Deal 18 damage. Doubled if the target has a negative status.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="24" t="inlineStr">
-        <is>
-          <t>Quench</t>
-        </is>
-      </c>
-      <c r="B36" s="25" t="inlineStr">
-        <is>
-          <t>trempe</t>
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>Guard</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="inlineStr">
+        <is>
+          <t>garde</t>
         </is>
       </c>
       <c r="C36" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" s="28" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="D36" s="29" t="inlineStr">
         <is>
           <t>Défense</t>
         </is>
       </c>
-      <c r="E36" s="21" t="inlineStr">
-        <is>
-          <t>Rare</t>
+      <c r="E36" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="F36" s="17" t="inlineStr"/>
       <c r="G36" s="18" t="inlineStr">
         <is>
-          <t>Forgemaster's Mail</t>
+          <t>— (deck de base)</t>
         </is>
       </c>
       <c r="H36" s="18" t="inlineStr">
         <is>
-          <t>Spend all Forge Heat. Gain 10 Stone per Heat spent.</t>
+          <t>Gain 5 Stone.</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="24" t="inlineStr">
-        <is>
-          <t>Shield Wall</t>
-        </is>
-      </c>
-      <c r="B37" s="25" t="inlineStr">
-        <is>
-          <t>mur-bouclier</t>
+      <c r="A37" s="25" t="inlineStr">
+        <is>
+          <t>Hand Guard</t>
+        </is>
+      </c>
+      <c r="B37" s="26" t="inlineStr">
+        <is>
+          <t>garde-faible</t>
         </is>
       </c>
       <c r="C37" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="D37" s="28" t="inlineStr">
+      <c r="D37" s="29" t="inlineStr">
         <is>
           <t>Défense</t>
         </is>
       </c>
-      <c r="E37" s="21" t="inlineStr">
-        <is>
-          <t>Rare</t>
+      <c r="E37" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="F37" s="17" t="inlineStr"/>
       <c r="G37" s="18" t="inlineStr">
         <is>
-          <t>Tower Shield</t>
+          <t>— (deck de base)</t>
         </is>
       </c>
       <c r="H37" s="18" t="inlineStr">
         <is>
-          <t>Gain 10 Stone.</t>
+          <t>Gain 3 Stone.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="24" t="inlineStr">
-        <is>
-          <t>Stacking Shield</t>
-        </is>
-      </c>
-      <c r="B38" s="25" t="inlineStr">
-        <is>
-          <t>bouclier-empilant</t>
+      <c r="A38" s="25" t="inlineStr">
+        <is>
+          <t>Heavy Armor</t>
+        </is>
+      </c>
+      <c r="B38" s="26" t="inlineStr">
+        <is>
+          <t>armure-lourde</t>
         </is>
       </c>
       <c r="C38" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="D38" s="28" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="D38" s="29" t="inlineStr">
         <is>
           <t>Défense</t>
         </is>
@@ -4284,132 +4743,132 @@
       <c r="F38" s="17" t="inlineStr"/>
       <c r="G38" s="18" t="inlineStr">
         <is>
-          <t>Tower Shield</t>
+          <t>Forgemaster's Mail</t>
         </is>
       </c>
       <c r="H38" s="18" t="inlineStr">
         <is>
-          <t>Double your current Stone.</t>
+          <t>Gain 20 Stone.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="24" t="inlineStr">
-        <is>
-          <t>Burning Run</t>
-        </is>
-      </c>
-      <c r="B39" s="25" t="inlineStr">
-        <is>
-          <t>course-ardente</t>
+      <c r="A39" s="25" t="inlineStr">
+        <is>
+          <t>Light Armor</t>
+        </is>
+      </c>
+      <c r="B39" s="26" t="inlineStr">
+        <is>
+          <t>armure-legere</t>
         </is>
       </c>
       <c r="C39" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D39" s="29" t="inlineStr">
         <is>
-          <t>Buff</t>
-        </is>
-      </c>
-      <c r="E39" s="22" t="inlineStr">
-        <is>
-          <t>Epic</t>
+          <t>Défense</t>
+        </is>
+      </c>
+      <c r="E39" s="16" t="inlineStr">
+        <is>
+          <t>Common</t>
         </is>
       </c>
       <c r="F39" s="17" t="inlineStr"/>
       <c r="G39" s="18" t="inlineStr">
         <is>
-          <t>Onyx Boots</t>
+          <t>Traveler's Garb</t>
         </is>
       </c>
       <c r="H39" s="18" t="inlineStr">
         <is>
-          <t>Haste for as many turns as your current Forge Heat.</t>
+          <t>Gain 5 Stone.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="24" t="inlineStr">
-        <is>
-          <t>Free Movement</t>
-        </is>
-      </c>
-      <c r="B40" s="25" t="inlineStr">
-        <is>
-          <t>mouvement-degage</t>
+      <c r="A40" s="25" t="inlineStr">
+        <is>
+          <t>Mail Armor</t>
+        </is>
+      </c>
+      <c r="B40" s="26" t="inlineStr">
+        <is>
+          <t>mail-armor</t>
         </is>
       </c>
       <c r="C40" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D40" s="29" t="inlineStr">
         <is>
-          <t>Buff</t>
-        </is>
-      </c>
-      <c r="E40" s="16" t="inlineStr">
-        <is>
-          <t>Common</t>
+          <t>Défense</t>
+        </is>
+      </c>
+      <c r="E40" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
         </is>
       </c>
       <c r="F40" s="17" t="inlineStr"/>
       <c r="G40" s="18" t="inlineStr">
         <is>
-          <t>Traveler's Garb</t>
+          <t>Forgemaster's Mail</t>
         </is>
       </c>
       <c r="H40" s="18" t="inlineStr">
         <is>
-          <t>Haste for 5 of your turns.</t>
+          <t>Gain 7 Stone for every enemy still alive.</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="24" t="inlineStr">
-        <is>
-          <t>Master's Hand</t>
-        </is>
-      </c>
-      <c r="B41" s="25" t="inlineStr">
-        <is>
-          <t>main-de-maitre</t>
+      <c r="A41" s="25" t="inlineStr">
+        <is>
+          <t>Onyx Armor</t>
+        </is>
+      </c>
+      <c r="B41" s="26" t="inlineStr">
+        <is>
+          <t>onyx-armor</t>
         </is>
       </c>
       <c r="C41" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D41" s="29" t="inlineStr">
         <is>
-          <t>Buff</t>
-        </is>
-      </c>
-      <c r="E41" s="16" t="inlineStr">
-        <is>
-          <t>Common</t>
+          <t>Défense</t>
+        </is>
+      </c>
+      <c r="E41" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
         </is>
       </c>
       <c r="F41" s="17" t="inlineStr"/>
       <c r="G41" s="18" t="inlineStr">
         <is>
-          <t>Miner's Gloves</t>
+          <t>Onyx Guard Plate</t>
         </is>
       </c>
       <c r="H41" s="18" t="inlineStr">
         <is>
-          <t>Draw 2 cards.</t>
+          <t>Gain 30 Stone.</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="24" t="inlineStr">
-        <is>
-          <t>Onyx Overheat</t>
-        </is>
-      </c>
-      <c r="B42" s="25" t="inlineStr">
-        <is>
-          <t>onyx-overheat</t>
+      <c r="A42" s="25" t="inlineStr">
+        <is>
+          <t>Quench</t>
+        </is>
+      </c>
+      <c r="B42" s="26" t="inlineStr">
+        <is>
+          <t>trempe</t>
         </is>
       </c>
       <c r="C42" s="17" t="n">
@@ -4417,71 +4876,71 @@
       </c>
       <c r="D42" s="29" t="inlineStr">
         <is>
-          <t>Buff</t>
-        </is>
-      </c>
-      <c r="E42" s="22" t="inlineStr">
-        <is>
-          <t>Epic</t>
+          <t>Défense</t>
+        </is>
+      </c>
+      <c r="E42" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
         </is>
       </c>
       <c r="F42" s="17" t="inlineStr"/>
       <c r="G42" s="18" t="inlineStr">
         <is>
-          <t>Big Onyx Sword</t>
+          <t>Forgemaster's Mail</t>
         </is>
       </c>
       <c r="H42" s="18" t="inlineStr">
         <is>
-          <t>Gain 5 Forge Heat (energy).</t>
+          <t>Spend all Forge Heat. Gain 10 Stone per Heat spent.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="24" t="inlineStr">
-        <is>
-          <t>Perfect Sapphire Surge</t>
-        </is>
-      </c>
-      <c r="B43" s="25" t="inlineStr">
-        <is>
-          <t>surge-saphir-parfait</t>
+      <c r="A43" s="25" t="inlineStr">
+        <is>
+          <t>Sacred Ground</t>
+        </is>
+      </c>
+      <c r="B43" s="26" t="inlineStr">
+        <is>
+          <t>terre-sacree</t>
         </is>
       </c>
       <c r="C43" s="17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D43" s="29" t="inlineStr">
         <is>
-          <t>Buff</t>
-        </is>
-      </c>
-      <c r="E43" s="22" t="inlineStr">
-        <is>
-          <t>Epic</t>
+          <t>Défense</t>
+        </is>
+      </c>
+      <c r="E43" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
         </is>
       </c>
       <c r="F43" s="17" t="inlineStr"/>
       <c r="G43" s="18" t="inlineStr">
         <is>
-          <t>Perfect Sapphire Amulet</t>
+          <t>Crusader Plate</t>
         </is>
       </c>
       <c r="H43" s="18" t="inlineStr">
         <is>
-          <t>Gain 3 Forge Heat (energy).</t>
+          <t>Gain 18 Stone.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="24" t="inlineStr">
-        <is>
-          <t>Quicken</t>
-        </is>
-      </c>
-      <c r="B44" s="25" t="inlineStr">
-        <is>
-          <t>celerite-vive</t>
+      <c r="A44" s="25" t="inlineStr">
+        <is>
+          <t>Shield Wall</t>
+        </is>
+      </c>
+      <c r="B44" s="26" t="inlineStr">
+        <is>
+          <t>mur-bouclier</t>
         </is>
       </c>
       <c r="C44" s="17" t="n">
@@ -4489,7 +4948,7 @@
       </c>
       <c r="D44" s="29" t="inlineStr">
         <is>
-          <t>Buff</t>
+          <t>Défense</t>
         </is>
       </c>
       <c r="E44" s="21" t="inlineStr">
@@ -4500,48 +4959,552 @@
       <c r="F44" s="17" t="inlineStr"/>
       <c r="G44" s="18" t="inlineStr">
         <is>
-          <t>Swift Boots</t>
+          <t>Tower Shield</t>
         </is>
       </c>
       <c r="H44" s="18" t="inlineStr">
         <is>
-          <t>Haste: +30% attack speed for 3 turns.</t>
+          <t>Gain 10 Stone.</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="24" t="inlineStr">
-        <is>
-          <t>Sapphire Surge</t>
-        </is>
-      </c>
-      <c r="B45" s="25" t="inlineStr">
-        <is>
-          <t>surge-saphir</t>
+      <c r="A45" s="25" t="inlineStr">
+        <is>
+          <t>Stacking Shield</t>
+        </is>
+      </c>
+      <c r="B45" s="26" t="inlineStr">
+        <is>
+          <t>bouclier-empilant</t>
         </is>
       </c>
       <c r="C45" s="17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D45" s="29" t="inlineStr">
         <is>
-          <t>Buff</t>
-        </is>
-      </c>
-      <c r="E45" s="20" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
+          <t>Défense</t>
+        </is>
+      </c>
+      <c r="E45" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
         </is>
       </c>
       <c r="F45" s="17" t="inlineStr"/>
       <c r="G45" s="18" t="inlineStr">
         <is>
+          <t>Tower Shield</t>
+        </is>
+      </c>
+      <c r="H45" s="18" t="inlineStr">
+        <is>
+          <t>Double your current Stone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="25" t="inlineStr">
+        <is>
+          <t>Boost</t>
+        </is>
+      </c>
+      <c r="B46" s="26" t="inlineStr">
+        <is>
+          <t>boost</t>
+        </is>
+      </c>
+      <c r="C46" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="30" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="E46" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F46" s="17" t="inlineStr"/>
+      <c r="G46" s="18" t="inlineStr">
+        <is>
+          <t>Onyx Boots, Mail Boots</t>
+        </is>
+      </c>
+      <c r="H46" s="18" t="inlineStr">
+        <is>
+          <t>Gain 3 Forge Heat (energy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="25" t="inlineStr">
+        <is>
+          <t>Burning Run</t>
+        </is>
+      </c>
+      <c r="B47" s="26" t="inlineStr">
+        <is>
+          <t>course-ardente</t>
+        </is>
+      </c>
+      <c r="C47" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D47" s="30" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="E47" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F47" s="17" t="inlineStr"/>
+      <c r="G47" s="18" t="inlineStr">
+        <is>
+          <t>Onyx Boots</t>
+        </is>
+      </c>
+      <c r="H47" s="18" t="inlineStr">
+        <is>
+          <t>Haste for as many turns as your current Forge Heat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="25" t="inlineStr">
+        <is>
+          <t>Crusader's Charge</t>
+        </is>
+      </c>
+      <c r="B48" s="26" t="inlineStr">
+        <is>
+          <t>charge-du-croise</t>
+        </is>
+      </c>
+      <c r="C48" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" s="30" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="E48" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F48" s="17" t="inlineStr"/>
+      <c r="G48" s="18" t="inlineStr">
+        <is>
+          <t>Crusader Greaves</t>
+        </is>
+      </c>
+      <c r="H48" s="18" t="inlineStr">
+        <is>
+          <t>Haste: +30% attack speed for 3 turns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="25" t="inlineStr">
+        <is>
+          <t>Fire Boost</t>
+        </is>
+      </c>
+      <c r="B49" s="26" t="inlineStr">
+        <is>
+          <t>boost-feu</t>
+        </is>
+      </c>
+      <c r="C49" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" s="30" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="E49" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F49" s="17" t="inlineStr"/>
+      <c r="G49" s="18" t="inlineStr">
+        <is>
+          <t>Onyx Boots</t>
+        </is>
+      </c>
+      <c r="H49" s="18" t="inlineStr">
+        <is>
+          <t>Convert 4 of your own Burning into 2 Forge Heat. No effect below 4 Burning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="25" t="inlineStr">
+        <is>
+          <t>Forge from Ashes</t>
+        </is>
+      </c>
+      <c r="B50" s="26" t="inlineStr">
+        <is>
+          <t>forge-des-cendres</t>
+        </is>
+      </c>
+      <c r="C50" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D50" s="30" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="E50" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F50" s="17" t="inlineStr"/>
+      <c r="G50" s="18" t="inlineStr">
+        <is>
+          <t>Onyx Glove</t>
+        </is>
+      </c>
+      <c r="H50" s="18" t="inlineStr">
+        <is>
+          <t>Discard your hand and draw that many cards.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="25" t="inlineStr">
+        <is>
+          <t>Free Movement</t>
+        </is>
+      </c>
+      <c r="B51" s="26" t="inlineStr">
+        <is>
+          <t>mouvement-degage</t>
+        </is>
+      </c>
+      <c r="C51" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D51" s="30" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="E51" s="16" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F51" s="17" t="inlineStr"/>
+      <c r="G51" s="18" t="inlineStr">
+        <is>
+          <t>Traveler's Garb</t>
+        </is>
+      </c>
+      <c r="H51" s="18" t="inlineStr">
+        <is>
+          <t>Haste for 5 of your turns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="25" t="inlineStr">
+        <is>
+          <t>Mail Advantage</t>
+        </is>
+      </c>
+      <c r="B52" s="26" t="inlineStr">
+        <is>
+          <t>avantage-maille</t>
+        </is>
+      </c>
+      <c r="C52" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" s="30" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="E52" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F52" s="17" t="inlineStr"/>
+      <c r="G52" s="18" t="inlineStr">
+        <is>
+          <t>Mail Glove, Mail Boots</t>
+        </is>
+      </c>
+      <c r="H52" s="18" t="inlineStr">
+        <is>
+          <t>Gain 8 Stone and Haste for 2 turns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="25" t="inlineStr">
+        <is>
+          <t>Master's Hand</t>
+        </is>
+      </c>
+      <c r="B53" s="26" t="inlineStr">
+        <is>
+          <t>main-de-maitre</t>
+        </is>
+      </c>
+      <c r="C53" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" s="30" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="E53" s="16" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F53" s="17" t="inlineStr"/>
+      <c r="G53" s="18" t="inlineStr">
+        <is>
+          <t>Miner's Gloves, Mail Glove</t>
+        </is>
+      </c>
+      <c r="H53" s="18" t="inlineStr">
+        <is>
+          <t>Draw 2 cards.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="25" t="inlineStr">
+        <is>
+          <t>Onyx Overheat</t>
+        </is>
+      </c>
+      <c r="B54" s="26" t="inlineStr">
+        <is>
+          <t>onyx-overheat</t>
+        </is>
+      </c>
+      <c r="C54" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="30" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="E54" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F54" s="17" t="inlineStr"/>
+      <c r="G54" s="18" t="inlineStr">
+        <is>
+          <t>Big Onyx Sword</t>
+        </is>
+      </c>
+      <c r="H54" s="18" t="inlineStr">
+        <is>
+          <t>Gain 5 Forge Heat (energy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="25" t="inlineStr">
+        <is>
+          <t>Outnumbered</t>
+        </is>
+      </c>
+      <c r="B55" s="26" t="inlineStr">
+        <is>
+          <t>surnombre</t>
+        </is>
+      </c>
+      <c r="C55" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D55" s="30" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="E55" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F55" s="17" t="inlineStr"/>
+      <c r="G55" s="18" t="inlineStr">
+        <is>
+          <t>Mail Glove</t>
+        </is>
+      </c>
+      <c r="H55" s="18" t="inlineStr">
+        <is>
+          <t>Draw 1 card per living enemy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="25" t="inlineStr">
+        <is>
+          <t>Perfect Sapphire Surge</t>
+        </is>
+      </c>
+      <c r="B56" s="26" t="inlineStr">
+        <is>
+          <t>surge-saphir-parfait</t>
+        </is>
+      </c>
+      <c r="C56" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="30" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="E56" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F56" s="17" t="inlineStr"/>
+      <c r="G56" s="18" t="inlineStr">
+        <is>
+          <t>Perfect Sapphire Amulet</t>
+        </is>
+      </c>
+      <c r="H56" s="18" t="inlineStr">
+        <is>
+          <t>Gain 3 Forge Heat (energy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="25" t="inlineStr">
+        <is>
+          <t>Quicken</t>
+        </is>
+      </c>
+      <c r="B57" s="26" t="inlineStr">
+        <is>
+          <t>celerite-vive</t>
+        </is>
+      </c>
+      <c r="C57" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" s="30" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="E57" s="20" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F57" s="17" t="inlineStr"/>
+      <c r="G57" s="18" t="inlineStr">
+        <is>
+          <t>Swift Boots, Mail Boots</t>
+        </is>
+      </c>
+      <c r="H57" s="18" t="inlineStr">
+        <is>
+          <t>Haste: +30% attack speed for 3 turns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="25" t="inlineStr">
+        <is>
+          <t>Sapphire Surge</t>
+        </is>
+      </c>
+      <c r="B58" s="26" t="inlineStr">
+        <is>
+          <t>surge-saphir</t>
+        </is>
+      </c>
+      <c r="C58" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" s="30" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="E58" s="20" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F58" s="17" t="inlineStr"/>
+      <c r="G58" s="18" t="inlineStr">
+        <is>
           <t>Sapphire Amulet, Nice Sapphire Amulet</t>
         </is>
       </c>
-      <c r="H45" s="18" t="inlineStr">
+      <c r="H58" s="18" t="inlineStr">
         <is>
           <t>Gain 2 Forge Heat (energy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="25" t="inlineStr">
+        <is>
+          <t>Second Wind</t>
+        </is>
+      </c>
+      <c r="B59" s="26" t="inlineStr">
+        <is>
+          <t>second-souffle</t>
+        </is>
+      </c>
+      <c r="C59" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="30" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="E59" s="20" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F59" s="17" t="inlineStr"/>
+      <c r="G59" s="18" t="inlineStr">
+        <is>
+          <t>Swift Boots</t>
+        </is>
+      </c>
+      <c r="H59" s="18" t="inlineStr">
+        <is>
+          <t>Trade 5 Haste turns for 3 Forge Heat. No effect below 5 Haste.</t>
         </is>
       </c>
     </row>
@@ -4560,7 +5523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4606,7 +5569,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>Onyx Set</t>
         </is>
@@ -4628,16 +5591,48 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="23" t="n"/>
-      <c r="B5" s="23" t="n"/>
-      <c r="C5" s="23" t="n"/>
-      <c r="D5" s="23" t="n"/>
+      <c r="A5" s="25" t="inlineStr">
+        <is>
+          <t>Mail Set</t>
+        </is>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>Forgemaster's Mail  +  Mail Glove  +  Mail Boots</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>En début de combat</t>
+        </is>
+      </c>
+      <c r="D5" s="18" t="inlineStr">
+        <is>
+          <t>At the start of combat, gain 10 Stone per enemy faced.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="23" t="n"/>
-      <c r="B6" s="23" t="n"/>
-      <c r="C6" s="23" t="n"/>
-      <c r="D6" s="23" t="n"/>
+      <c r="A6" s="25" t="inlineStr">
+        <is>
+          <t>Crusader Set</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>Crusader Plate  +  Crusader Gauntlets  +  Crusader Greaves</t>
+        </is>
+      </c>
+      <c r="C6" s="18" t="inlineStr">
+        <is>
+          <t>Quand le héros est frappé en mêlée</t>
+        </is>
+      </c>
+      <c r="D6" s="18" t="inlineStr">
+        <is>
+          <t>When hit by a melee attack, the attacker is Dazzled (1 Confusion).</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="23" t="n"/>
@@ -4662,6 +5657,18 @@
       <c r="B10" s="23" t="n"/>
       <c r="C10" s="23" t="n"/>
       <c r="D10" s="23" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="23" t="n"/>
+      <c r="B11" s="23" t="n"/>
+      <c r="C11" s="23" t="n"/>
+      <c r="D11" s="23" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="23" t="n"/>
+      <c r="B12" s="23" t="n"/>
+      <c r="C12" s="23" t="n"/>
+      <c r="D12" s="23" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/docs/BRUTAL-items-et-cartes.xlsx
+++ b/docs/BRUTAL-items-et-cartes.xlsx
@@ -897,7 +897,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N106"/>
+  <dimension ref="A1:N109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1706,7 +1706,7 @@
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t>Armures   (4)</t>
+          <t>Armures   (5)</t>
         </is>
       </c>
     </row>
@@ -1915,20 +1915,56 @@
       <c r="N40" s="18" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="23" t="n"/>
-      <c r="B41" s="23" t="n"/>
-      <c r="C41" s="23" t="n"/>
-      <c r="D41" s="23" t="n"/>
-      <c r="E41" s="23" t="n"/>
-      <c r="F41" s="23" t="n"/>
-      <c r="G41" s="23" t="n"/>
-      <c r="H41" s="23" t="n"/>
-      <c r="I41" s="23" t="n"/>
-      <c r="J41" s="23" t="n"/>
-      <c r="K41" s="23" t="n"/>
-      <c r="L41" s="23" t="n"/>
-      <c r="M41" s="23" t="n"/>
-      <c r="N41" s="23" t="n"/>
+      <c r="A41" s="14" t="inlineStr">
+        <is>
+          <t>Blood Plate</t>
+        </is>
+      </c>
+      <c r="B41" s="15" t="inlineStr">
+        <is>
+          <t>plate-sang</t>
+        </is>
+      </c>
+      <c r="C41" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="D41" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="E41" s="18" t="inlineStr">
+        <is>
+          <t>Crimson Carve</t>
+        </is>
+      </c>
+      <c r="F41" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="G41" s="18" t="inlineStr">
+        <is>
+          <t>Sanguine Guard</t>
+        </is>
+      </c>
+      <c r="H41" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I41" s="18" t="inlineStr">
+        <is>
+          <t>Bloodbath</t>
+        </is>
+      </c>
+      <c r="J41" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K41" s="18" t="n"/>
+      <c r="L41" s="18" t="n"/>
+      <c r="M41" s="19" t="inlineStr">
+        <is>
+          <t>Set : Blood Set</t>
+        </is>
+      </c>
+      <c r="N41" s="18" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="23" t="n"/>
@@ -2010,67 +2046,47 @@
       <c r="M46" s="23" t="n"/>
       <c r="N46" s="23" t="n"/>
     </row>
-    <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="13" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="23" t="n"/>
+      <c r="B47" s="23" t="n"/>
+      <c r="C47" s="23" t="n"/>
+      <c r="D47" s="23" t="n"/>
+      <c r="E47" s="23" t="n"/>
+      <c r="F47" s="23" t="n"/>
+      <c r="G47" s="23" t="n"/>
+      <c r="H47" s="23" t="n"/>
+      <c r="I47" s="23" t="n"/>
+      <c r="J47" s="23" t="n"/>
+      <c r="K47" s="23" t="n"/>
+      <c r="L47" s="23" t="n"/>
+      <c r="M47" s="23" t="n"/>
+      <c r="N47" s="23" t="n"/>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="13" t="inlineStr">
         <is>
           <t>Colliers   (3)</t>
         </is>
       </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="14" t="inlineStr">
-        <is>
-          <t>Sapphire Amulet</t>
-        </is>
-      </c>
-      <c r="B49" s="15" t="inlineStr">
-        <is>
-          <t>collier-de-saphir</t>
-        </is>
-      </c>
-      <c r="C49" s="20" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="D49" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E49" s="18" t="inlineStr">
-        <is>
-          <t>Sapphire Surge</t>
-        </is>
-      </c>
-      <c r="F49" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G49" s="18" t="n"/>
-      <c r="H49" s="18" t="n"/>
-      <c r="I49" s="18" t="n"/>
-      <c r="J49" s="18" t="n"/>
-      <c r="K49" s="18" t="n"/>
-      <c r="L49" s="18" t="n"/>
-      <c r="M49" s="19" t="inlineStr"/>
-      <c r="N49" s="18" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="14" t="inlineStr">
         <is>
-          <t>Nice Sapphire Amulet</t>
+          <t>Sapphire Amulet</t>
         </is>
       </c>
       <c r="B50" s="15" t="inlineStr">
         <is>
-          <t>collier-de-saphir-fin</t>
-        </is>
-      </c>
-      <c r="C50" s="21" t="inlineStr">
-        <is>
-          <t>Rare</t>
+          <t>collier-de-saphir</t>
+        </is>
+      </c>
+      <c r="C50" s="20" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="D50" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E50" s="18" t="inlineStr">
         <is>
@@ -2078,7 +2094,7 @@
         </is>
       </c>
       <c r="F50" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G50" s="18" t="n"/>
       <c r="H50" s="18" t="n"/>
@@ -2092,29 +2108,29 @@
     <row r="51">
       <c r="A51" s="14" t="inlineStr">
         <is>
-          <t>Perfect Sapphire Amulet</t>
+          <t>Nice Sapphire Amulet</t>
         </is>
       </c>
       <c r="B51" s="15" t="inlineStr">
         <is>
-          <t>collier-de-saphir-parfait</t>
-        </is>
-      </c>
-      <c r="C51" s="22" t="inlineStr">
-        <is>
-          <t>Epic</t>
+          <t>collier-de-saphir-fin</t>
+        </is>
+      </c>
+      <c r="C51" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
         </is>
       </c>
       <c r="D51" s="17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E51" s="18" t="inlineStr">
         <is>
-          <t>Perfect Sapphire Surge</t>
+          <t>Sapphire Surge</t>
         </is>
       </c>
       <c r="F51" s="17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G51" s="18" t="n"/>
       <c r="H51" s="18" t="n"/>
@@ -2126,20 +2142,40 @@
       <c r="N51" s="18" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="23" t="n"/>
-      <c r="B52" s="23" t="n"/>
-      <c r="C52" s="23" t="n"/>
-      <c r="D52" s="23" t="n"/>
-      <c r="E52" s="23" t="n"/>
-      <c r="F52" s="23" t="n"/>
-      <c r="G52" s="23" t="n"/>
-      <c r="H52" s="23" t="n"/>
-      <c r="I52" s="23" t="n"/>
-      <c r="J52" s="23" t="n"/>
-      <c r="K52" s="23" t="n"/>
-      <c r="L52" s="23" t="n"/>
-      <c r="M52" s="23" t="n"/>
-      <c r="N52" s="23" t="n"/>
+      <c r="A52" s="14" t="inlineStr">
+        <is>
+          <t>Perfect Sapphire Amulet</t>
+        </is>
+      </c>
+      <c r="B52" s="15" t="inlineStr">
+        <is>
+          <t>collier-de-saphir-parfait</t>
+        </is>
+      </c>
+      <c r="C52" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="D52" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E52" s="18" t="inlineStr">
+        <is>
+          <t>Perfect Sapphire Surge</t>
+        </is>
+      </c>
+      <c r="F52" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="G52" s="18" t="n"/>
+      <c r="H52" s="18" t="n"/>
+      <c r="I52" s="18" t="n"/>
+      <c r="J52" s="18" t="n"/>
+      <c r="K52" s="18" t="n"/>
+      <c r="L52" s="18" t="n"/>
+      <c r="M52" s="19" t="inlineStr"/>
+      <c r="N52" s="18" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="23" t="n"/>
@@ -2221,58 +2257,38 @@
       <c r="M57" s="23" t="n"/>
       <c r="N57" s="23" t="n"/>
     </row>
-    <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="13" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="23" t="n"/>
+      <c r="B58" s="23" t="n"/>
+      <c r="C58" s="23" t="n"/>
+      <c r="D58" s="23" t="n"/>
+      <c r="E58" s="23" t="n"/>
+      <c r="F58" s="23" t="n"/>
+      <c r="G58" s="23" t="n"/>
+      <c r="H58" s="23" t="n"/>
+      <c r="I58" s="23" t="n"/>
+      <c r="J58" s="23" t="n"/>
+      <c r="K58" s="23" t="n"/>
+      <c r="L58" s="23" t="n"/>
+      <c r="M58" s="23" t="n"/>
+      <c r="N58" s="23" t="n"/>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="13" t="inlineStr">
         <is>
           <t>Bagues   (3)</t>
         </is>
       </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="14" t="inlineStr">
-        <is>
-          <t>Blood Ring</t>
-        </is>
-      </c>
-      <c r="B60" s="15" t="inlineStr">
-        <is>
-          <t>bague-de-sang</t>
-        </is>
-      </c>
-      <c r="C60" s="20" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="D60" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="E60" s="18" t="inlineStr">
-        <is>
-          <t>Bloodletting</t>
-        </is>
-      </c>
-      <c r="F60" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="G60" s="18" t="n"/>
-      <c r="H60" s="18" t="n"/>
-      <c r="I60" s="18" t="n"/>
-      <c r="J60" s="18" t="n"/>
-      <c r="K60" s="18" t="n"/>
-      <c r="L60" s="18" t="n"/>
-      <c r="M60" s="19" t="inlineStr"/>
-      <c r="N60" s="18" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="14" t="inlineStr">
         <is>
-          <t>Frost Ring</t>
+          <t>Blood Ring</t>
         </is>
       </c>
       <c r="B61" s="15" t="inlineStr">
         <is>
-          <t>anneau-de-givre</t>
+          <t>bague-de-sang</t>
         </is>
       </c>
       <c r="C61" s="20" t="inlineStr">
@@ -2285,7 +2301,7 @@
       </c>
       <c r="E61" s="18" t="inlineStr">
         <is>
-          <t>Frostbite</t>
+          <t>Bloodletting</t>
         </is>
       </c>
       <c r="F61" s="17" t="n">
@@ -2303,17 +2319,17 @@
     <row r="62">
       <c r="A62" s="14" t="inlineStr">
         <is>
-          <t>Perfect Frost Ring</t>
+          <t>Frost Ring</t>
         </is>
       </c>
       <c r="B62" s="15" t="inlineStr">
         <is>
-          <t>anneau-de-givre-parfait</t>
-        </is>
-      </c>
-      <c r="C62" s="21" t="inlineStr">
-        <is>
-          <t>Rare</t>
+          <t>anneau-de-givre</t>
+        </is>
+      </c>
+      <c r="C62" s="20" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="D62" s="17" t="n">
@@ -2321,7 +2337,7 @@
       </c>
       <c r="E62" s="18" t="inlineStr">
         <is>
-          <t>Frost Cascade</t>
+          <t>Frostbite</t>
         </is>
       </c>
       <c r="F62" s="17" t="n">
@@ -2337,20 +2353,40 @@
       <c r="N62" s="18" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="23" t="n"/>
-      <c r="B63" s="23" t="n"/>
-      <c r="C63" s="23" t="n"/>
-      <c r="D63" s="23" t="n"/>
-      <c r="E63" s="23" t="n"/>
-      <c r="F63" s="23" t="n"/>
-      <c r="G63" s="23" t="n"/>
-      <c r="H63" s="23" t="n"/>
-      <c r="I63" s="23" t="n"/>
-      <c r="J63" s="23" t="n"/>
-      <c r="K63" s="23" t="n"/>
-      <c r="L63" s="23" t="n"/>
-      <c r="M63" s="23" t="n"/>
-      <c r="N63" s="23" t="n"/>
+      <c r="A63" s="14" t="inlineStr">
+        <is>
+          <t>Perfect Frost Ring</t>
+        </is>
+      </c>
+      <c r="B63" s="15" t="inlineStr">
+        <is>
+          <t>anneau-de-givre-parfait</t>
+        </is>
+      </c>
+      <c r="C63" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D63" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E63" s="18" t="inlineStr">
+        <is>
+          <t>Frost Cascade</t>
+        </is>
+      </c>
+      <c r="F63" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G63" s="18" t="n"/>
+      <c r="H63" s="18" t="n"/>
+      <c r="I63" s="18" t="n"/>
+      <c r="J63" s="18" t="n"/>
+      <c r="K63" s="18" t="n"/>
+      <c r="L63" s="18" t="n"/>
+      <c r="M63" s="19" t="inlineStr"/>
+      <c r="N63" s="18" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="23" t="n"/>
@@ -2432,123 +2468,87 @@
       <c r="M68" s="23" t="n"/>
       <c r="N68" s="23" t="n"/>
     </row>
-    <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="13" t="inlineStr">
-        <is>
-          <t>Gants   (4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="14" t="inlineStr">
-        <is>
-          <t>Miner's Gloves</t>
-        </is>
-      </c>
-      <c r="B71" s="15" t="inlineStr">
-        <is>
-          <t>gants-de-mineur</t>
-        </is>
-      </c>
-      <c r="C71" s="16" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="D71" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="E71" s="18" t="inlineStr">
-        <is>
-          <t>Master's Hand</t>
-        </is>
-      </c>
-      <c r="F71" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="G71" s="18" t="n"/>
-      <c r="H71" s="18" t="n"/>
-      <c r="I71" s="18" t="n"/>
-      <c r="J71" s="18" t="n"/>
-      <c r="K71" s="18" t="n"/>
-      <c r="L71" s="18" t="n"/>
-      <c r="M71" s="19" t="inlineStr"/>
-      <c r="N71" s="18" t="n"/>
+    <row r="69">
+      <c r="A69" s="23" t="n"/>
+      <c r="B69" s="23" t="n"/>
+      <c r="C69" s="23" t="n"/>
+      <c r="D69" s="23" t="n"/>
+      <c r="E69" s="23" t="n"/>
+      <c r="F69" s="23" t="n"/>
+      <c r="G69" s="23" t="n"/>
+      <c r="H69" s="23" t="n"/>
+      <c r="I69" s="23" t="n"/>
+      <c r="J69" s="23" t="n"/>
+      <c r="K69" s="23" t="n"/>
+      <c r="L69" s="23" t="n"/>
+      <c r="M69" s="23" t="n"/>
+      <c r="N69" s="23" t="n"/>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="13" t="inlineStr">
+        <is>
+          <t>Gants   (5)</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="14" t="inlineStr">
         <is>
-          <t>Onyx Glove</t>
+          <t>Miner's Gloves</t>
         </is>
       </c>
       <c r="B72" s="15" t="inlineStr">
         <is>
-          <t>gants-onyx</t>
-        </is>
-      </c>
-      <c r="C72" s="22" t="inlineStr">
-        <is>
-          <t>Epic</t>
+          <t>gants-de-mineur</t>
+        </is>
+      </c>
+      <c r="C72" s="16" t="inlineStr">
+        <is>
+          <t>Common</t>
         </is>
       </c>
       <c r="D72" s="17" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E72" s="18" t="inlineStr">
         <is>
-          <t>Burning Hand</t>
+          <t>Master's Hand</t>
         </is>
       </c>
       <c r="F72" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="G72" s="18" t="inlineStr">
-        <is>
-          <t>Onyx Fist</t>
-        </is>
-      </c>
-      <c r="H72" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="I72" s="18" t="inlineStr">
-        <is>
-          <t>Forge from Ashes</t>
-        </is>
-      </c>
-      <c r="J72" s="17" t="n">
-        <v>2</v>
-      </c>
+      <c r="G72" s="18" t="n"/>
+      <c r="H72" s="18" t="n"/>
+      <c r="I72" s="18" t="n"/>
+      <c r="J72" s="18" t="n"/>
       <c r="K72" s="18" t="n"/>
       <c r="L72" s="18" t="n"/>
-      <c r="M72" s="19" t="inlineStr">
-        <is>
-          <t>Set : Onyx Set</t>
-        </is>
-      </c>
+      <c r="M72" s="19" t="inlineStr"/>
       <c r="N72" s="18" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="14" t="inlineStr">
         <is>
-          <t>Mail Glove</t>
+          <t>Onyx Glove</t>
         </is>
       </c>
       <c r="B73" s="15" t="inlineStr">
         <is>
-          <t>gants-de-maille</t>
-        </is>
-      </c>
-      <c r="C73" s="21" t="inlineStr">
-        <is>
-          <t>Rare</t>
+          <t>gants-onyx</t>
+        </is>
+      </c>
+      <c r="C73" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
         </is>
       </c>
       <c r="D73" s="17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E73" s="18" t="inlineStr">
         <is>
-          <t>Master's Hand</t>
+          <t>Burning Hand</t>
         </is>
       </c>
       <c r="F73" s="17" t="n">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="G73" s="18" t="inlineStr">
         <is>
-          <t>Outnumbered</t>
+          <t>Onyx Fist</t>
         </is>
       </c>
       <c r="H73" s="17" t="n">
@@ -2564,17 +2564,17 @@
       </c>
       <c r="I73" s="18" t="inlineStr">
         <is>
-          <t>Mail Advantage</t>
+          <t>Forge from Ashes</t>
         </is>
       </c>
       <c r="J73" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K73" s="18" t="n"/>
       <c r="L73" s="18" t="n"/>
       <c r="M73" s="19" t="inlineStr">
         <is>
-          <t>Set : Mail Set</t>
+          <t>Set : Onyx Set</t>
         </is>
       </c>
       <c r="N73" s="18" t="n"/>
@@ -2582,12 +2582,12 @@
     <row r="74">
       <c r="A74" s="14" t="inlineStr">
         <is>
-          <t>Crusader Gauntlets</t>
+          <t>Mail Glove</t>
         </is>
       </c>
       <c r="B74" s="15" t="inlineStr">
         <is>
-          <t>gants-croise</t>
+          <t>gants-de-maille</t>
         </is>
       </c>
       <c r="C74" s="21" t="inlineStr">
@@ -2596,11 +2596,11 @@
         </is>
       </c>
       <c r="D74" s="17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E74" s="18" t="inlineStr">
         <is>
-          <t>Lumen Jab</t>
+          <t>Master's Hand</t>
         </is>
       </c>
       <c r="F74" s="17" t="n">
@@ -2608,54 +2608,120 @@
       </c>
       <c r="G74" s="18" t="inlineStr">
         <is>
-          <t>Halo Burst</t>
+          <t>Outnumbered</t>
         </is>
       </c>
       <c r="H74" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I74" s="18" t="inlineStr">
+        <is>
+          <t>Mail Advantage</t>
+        </is>
+      </c>
+      <c r="J74" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="I74" s="18" t="n"/>
-      <c r="J74" s="18" t="n"/>
       <c r="K74" s="18" t="n"/>
       <c r="L74" s="18" t="n"/>
       <c r="M74" s="19" t="inlineStr">
         <is>
+          <t>Set : Mail Set</t>
+        </is>
+      </c>
+      <c r="N74" s="18" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="14" t="inlineStr">
+        <is>
+          <t>Crusader Gauntlets</t>
+        </is>
+      </c>
+      <c r="B75" s="15" t="inlineStr">
+        <is>
+          <t>gants-croise</t>
+        </is>
+      </c>
+      <c r="C75" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D75" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E75" s="18" t="inlineStr">
+        <is>
+          <t>Lumen Jab</t>
+        </is>
+      </c>
+      <c r="F75" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G75" s="18" t="inlineStr">
+        <is>
+          <t>Halo Burst</t>
+        </is>
+      </c>
+      <c r="H75" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I75" s="18" t="n"/>
+      <c r="J75" s="18" t="n"/>
+      <c r="K75" s="18" t="n"/>
+      <c r="L75" s="18" t="n"/>
+      <c r="M75" s="19" t="inlineStr">
+        <is>
           <t>Set : Crusader Set</t>
         </is>
       </c>
-      <c r="N74" s="18" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="23" t="n"/>
-      <c r="B75" s="23" t="n"/>
-      <c r="C75" s="23" t="n"/>
-      <c r="D75" s="23" t="n"/>
-      <c r="E75" s="23" t="n"/>
-      <c r="F75" s="23" t="n"/>
-      <c r="G75" s="23" t="n"/>
-      <c r="H75" s="23" t="n"/>
-      <c r="I75" s="23" t="n"/>
-      <c r="J75" s="23" t="n"/>
-      <c r="K75" s="23" t="n"/>
-      <c r="L75" s="23" t="n"/>
-      <c r="M75" s="23" t="n"/>
-      <c r="N75" s="23" t="n"/>
+      <c r="N75" s="18" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="23" t="n"/>
-      <c r="B76" s="23" t="n"/>
-      <c r="C76" s="23" t="n"/>
-      <c r="D76" s="23" t="n"/>
-      <c r="E76" s="23" t="n"/>
-      <c r="F76" s="23" t="n"/>
-      <c r="G76" s="23" t="n"/>
-      <c r="H76" s="23" t="n"/>
-      <c r="I76" s="23" t="n"/>
-      <c r="J76" s="23" t="n"/>
-      <c r="K76" s="23" t="n"/>
-      <c r="L76" s="23" t="n"/>
-      <c r="M76" s="23" t="n"/>
-      <c r="N76" s="23" t="n"/>
+      <c r="A76" s="14" t="inlineStr">
+        <is>
+          <t>Blood Gauntlets</t>
+        </is>
+      </c>
+      <c r="B76" s="15" t="inlineStr">
+        <is>
+          <t>gants-sang</t>
+        </is>
+      </c>
+      <c r="C76" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="D76" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E76" s="18" t="inlineStr">
+        <is>
+          <t>Open Veins</t>
+        </is>
+      </c>
+      <c r="F76" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G76" s="18" t="inlineStr">
+        <is>
+          <t>Contagion</t>
+        </is>
+      </c>
+      <c r="H76" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I76" s="18" t="n"/>
+      <c r="J76" s="18" t="n"/>
+      <c r="K76" s="18" t="n"/>
+      <c r="L76" s="18" t="n"/>
+      <c r="M76" s="19" t="inlineStr">
+        <is>
+          <t>Set : Blood Set</t>
+        </is>
+      </c>
+      <c r="N76" s="18" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="23" t="n"/>
@@ -2721,131 +2787,63 @@
       <c r="M80" s="23" t="n"/>
       <c r="N80" s="23" t="n"/>
     </row>
-    <row r="82" ht="20" customHeight="1">
-      <c r="A82" s="13" t="inlineStr">
-        <is>
-          <t>Bottes   (4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="14" t="inlineStr">
-        <is>
-          <t>Swift Boots</t>
-        </is>
-      </c>
-      <c r="B83" s="15" t="inlineStr">
-        <is>
-          <t>bottes-vives</t>
-        </is>
-      </c>
-      <c r="C83" s="20" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="D83" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="E83" s="18" t="inlineStr">
-        <is>
-          <t>Quicken</t>
-        </is>
-      </c>
-      <c r="F83" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="G83" s="18" t="inlineStr">
-        <is>
-          <t>Second Wind</t>
-        </is>
-      </c>
-      <c r="H83" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="I83" s="18" t="n"/>
-      <c r="J83" s="18" t="n"/>
-      <c r="K83" s="18" t="n"/>
-      <c r="L83" s="18" t="n"/>
-      <c r="M83" s="19" t="inlineStr"/>
-      <c r="N83" s="18" t="n"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="14" t="inlineStr">
-        <is>
-          <t>Onyx Boots</t>
-        </is>
-      </c>
-      <c r="B84" s="15" t="inlineStr">
-        <is>
-          <t>bottes-onyx</t>
-        </is>
-      </c>
-      <c r="C84" s="22" t="inlineStr">
-        <is>
-          <t>Epic</t>
-        </is>
-      </c>
-      <c r="D84" s="17" t="n">
-        <v>6</v>
-      </c>
-      <c r="E84" s="18" t="inlineStr">
-        <is>
-          <t>Burning Run</t>
-        </is>
-      </c>
-      <c r="F84" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G84" s="18" t="inlineStr">
-        <is>
-          <t>Flaming Kick</t>
-        </is>
-      </c>
-      <c r="H84" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="I84" s="18" t="inlineStr">
-        <is>
-          <t>Fire Boost</t>
-        </is>
-      </c>
-      <c r="J84" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K84" s="18" t="inlineStr">
-        <is>
-          <t>Boost</t>
-        </is>
-      </c>
-      <c r="L84" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="M84" s="19" t="inlineStr">
-        <is>
-          <t>Set : Onyx Set</t>
-        </is>
-      </c>
-      <c r="N84" s="18" t="n"/>
+    <row r="81">
+      <c r="A81" s="23" t="n"/>
+      <c r="B81" s="23" t="n"/>
+      <c r="C81" s="23" t="n"/>
+      <c r="D81" s="23" t="n"/>
+      <c r="E81" s="23" t="n"/>
+      <c r="F81" s="23" t="n"/>
+      <c r="G81" s="23" t="n"/>
+      <c r="H81" s="23" t="n"/>
+      <c r="I81" s="23" t="n"/>
+      <c r="J81" s="23" t="n"/>
+      <c r="K81" s="23" t="n"/>
+      <c r="L81" s="23" t="n"/>
+      <c r="M81" s="23" t="n"/>
+      <c r="N81" s="23" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="23" t="n"/>
+      <c r="B82" s="23" t="n"/>
+      <c r="C82" s="23" t="n"/>
+      <c r="D82" s="23" t="n"/>
+      <c r="E82" s="23" t="n"/>
+      <c r="F82" s="23" t="n"/>
+      <c r="G82" s="23" t="n"/>
+      <c r="H82" s="23" t="n"/>
+      <c r="I82" s="23" t="n"/>
+      <c r="J82" s="23" t="n"/>
+      <c r="K82" s="23" t="n"/>
+      <c r="L82" s="23" t="n"/>
+      <c r="M82" s="23" t="n"/>
+      <c r="N82" s="23" t="n"/>
+    </row>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="13" t="inlineStr">
+        <is>
+          <t>Bottes   (5)</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="14" t="inlineStr">
         <is>
-          <t>Mail Boots</t>
+          <t>Swift Boots</t>
         </is>
       </c>
       <c r="B85" s="15" t="inlineStr">
         <is>
-          <t>bottes-de-maille</t>
-        </is>
-      </c>
-      <c r="C85" s="21" t="inlineStr">
-        <is>
-          <t>Rare</t>
+          <t>bottes-vives</t>
+        </is>
+      </c>
+      <c r="C85" s="20" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="D85" s="17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E85" s="18" t="inlineStr">
         <is>
@@ -2853,55 +2851,45 @@
         </is>
       </c>
       <c r="F85" s="17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G85" s="18" t="inlineStr">
         <is>
-          <t>Mail Advantage</t>
+          <t>Second Wind</t>
         </is>
       </c>
       <c r="H85" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="I85" s="18" t="inlineStr">
-        <is>
-          <t>Boost</t>
-        </is>
-      </c>
-      <c r="J85" s="17" t="n">
-        <v>2</v>
-      </c>
+      <c r="I85" s="18" t="n"/>
+      <c r="J85" s="18" t="n"/>
       <c r="K85" s="18" t="n"/>
       <c r="L85" s="18" t="n"/>
-      <c r="M85" s="19" t="inlineStr">
-        <is>
-          <t>Set : Mail Set</t>
-        </is>
-      </c>
+      <c r="M85" s="19" t="inlineStr"/>
       <c r="N85" s="18" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="14" t="inlineStr">
         <is>
-          <t>Crusader Greaves</t>
+          <t>Onyx Boots</t>
         </is>
       </c>
       <c r="B86" s="15" t="inlineStr">
         <is>
-          <t>bottes-croise</t>
-        </is>
-      </c>
-      <c r="C86" s="21" t="inlineStr">
-        <is>
-          <t>Rare</t>
+          <t>bottes-onyx</t>
+        </is>
+      </c>
+      <c r="C86" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
         </is>
       </c>
       <c r="D86" s="17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E86" s="18" t="inlineStr">
         <is>
-          <t>Crusader's Charge</t>
+          <t>Burning Run</t>
         </is>
       </c>
       <c r="F86" s="17" t="n">
@@ -2909,70 +2897,178 @@
       </c>
       <c r="G86" s="18" t="inlineStr">
         <is>
+          <t>Flaming Kick</t>
+        </is>
+      </c>
+      <c r="H86" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I86" s="18" t="inlineStr">
+        <is>
+          <t>Fire Boost</t>
+        </is>
+      </c>
+      <c r="J86" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K86" s="18" t="inlineStr">
+        <is>
+          <t>Boost</t>
+        </is>
+      </c>
+      <c r="L86" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M86" s="19" t="inlineStr">
+        <is>
+          <t>Set : Onyx Set</t>
+        </is>
+      </c>
+      <c r="N86" s="18" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="14" t="inlineStr">
+        <is>
+          <t>Mail Boots</t>
+        </is>
+      </c>
+      <c r="B87" s="15" t="inlineStr">
+        <is>
+          <t>bottes-de-maille</t>
+        </is>
+      </c>
+      <c r="C87" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D87" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E87" s="18" t="inlineStr">
+        <is>
+          <t>Quicken</t>
+        </is>
+      </c>
+      <c r="F87" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G87" s="18" t="inlineStr">
+        <is>
+          <t>Mail Advantage</t>
+        </is>
+      </c>
+      <c r="H87" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I87" s="18" t="inlineStr">
+        <is>
+          <t>Boost</t>
+        </is>
+      </c>
+      <c r="J87" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K87" s="18" t="n"/>
+      <c r="L87" s="18" t="n"/>
+      <c r="M87" s="19" t="inlineStr">
+        <is>
+          <t>Set : Mail Set</t>
+        </is>
+      </c>
+      <c r="N87" s="18" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="14" t="inlineStr">
+        <is>
+          <t>Crusader Greaves</t>
+        </is>
+      </c>
+      <c r="B88" s="15" t="inlineStr">
+        <is>
+          <t>bottes-croise</t>
+        </is>
+      </c>
+      <c r="C88" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D88" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E88" s="18" t="inlineStr">
+        <is>
+          <t>Crusader's Charge</t>
+        </is>
+      </c>
+      <c r="F88" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" s="18" t="inlineStr">
+        <is>
           <t>Dazzling Kick</t>
         </is>
       </c>
-      <c r="H86" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="I86" s="18" t="n"/>
-      <c r="J86" s="18" t="n"/>
-      <c r="K86" s="18" t="n"/>
-      <c r="L86" s="18" t="n"/>
-      <c r="M86" s="19" t="inlineStr">
+      <c r="H88" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I88" s="18" t="n"/>
+      <c r="J88" s="18" t="n"/>
+      <c r="K88" s="18" t="n"/>
+      <c r="L88" s="18" t="n"/>
+      <c r="M88" s="19" t="inlineStr">
         <is>
           <t>Set : Crusader Set</t>
         </is>
       </c>
-      <c r="N86" s="18" t="n"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="23" t="n"/>
-      <c r="B87" s="23" t="n"/>
-      <c r="C87" s="23" t="n"/>
-      <c r="D87" s="23" t="n"/>
-      <c r="E87" s="23" t="n"/>
-      <c r="F87" s="23" t="n"/>
-      <c r="G87" s="23" t="n"/>
-      <c r="H87" s="23" t="n"/>
-      <c r="I87" s="23" t="n"/>
-      <c r="J87" s="23" t="n"/>
-      <c r="K87" s="23" t="n"/>
-      <c r="L87" s="23" t="n"/>
-      <c r="M87" s="23" t="n"/>
-      <c r="N87" s="23" t="n"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="23" t="n"/>
-      <c r="B88" s="23" t="n"/>
-      <c r="C88" s="23" t="n"/>
-      <c r="D88" s="23" t="n"/>
-      <c r="E88" s="23" t="n"/>
-      <c r="F88" s="23" t="n"/>
-      <c r="G88" s="23" t="n"/>
-      <c r="H88" s="23" t="n"/>
-      <c r="I88" s="23" t="n"/>
-      <c r="J88" s="23" t="n"/>
-      <c r="K88" s="23" t="n"/>
-      <c r="L88" s="23" t="n"/>
-      <c r="M88" s="23" t="n"/>
-      <c r="N88" s="23" t="n"/>
+      <c r="N88" s="18" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" s="23" t="n"/>
-      <c r="B89" s="23" t="n"/>
-      <c r="C89" s="23" t="n"/>
-      <c r="D89" s="23" t="n"/>
-      <c r="E89" s="23" t="n"/>
-      <c r="F89" s="23" t="n"/>
-      <c r="G89" s="23" t="n"/>
-      <c r="H89" s="23" t="n"/>
-      <c r="I89" s="23" t="n"/>
-      <c r="J89" s="23" t="n"/>
-      <c r="K89" s="23" t="n"/>
-      <c r="L89" s="23" t="n"/>
-      <c r="M89" s="23" t="n"/>
-      <c r="N89" s="23" t="n"/>
+      <c r="A89" s="14" t="inlineStr">
+        <is>
+          <t>Blood Greaves</t>
+        </is>
+      </c>
+      <c r="B89" s="15" t="inlineStr">
+        <is>
+          <t>bottes-sang</t>
+        </is>
+      </c>
+      <c r="C89" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="D89" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E89" s="18" t="inlineStr">
+        <is>
+          <t>Hemorrhage</t>
+        </is>
+      </c>
+      <c r="F89" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G89" s="18" t="inlineStr">
+        <is>
+          <t>Blood Rush</t>
+        </is>
+      </c>
+      <c r="H89" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I89" s="18" t="n"/>
+      <c r="J89" s="18" t="n"/>
+      <c r="K89" s="18" t="n"/>
+      <c r="L89" s="18" t="n"/>
+      <c r="M89" s="19" t="inlineStr">
+        <is>
+          <t>Set : Blood Set</t>
+        </is>
+      </c>
+      <c r="N89" s="18" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="23" t="n"/>
@@ -3022,129 +3118,75 @@
       <c r="M92" s="23" t="n"/>
       <c r="N92" s="23" t="n"/>
     </row>
-    <row r="94" ht="20" customHeight="1">
-      <c r="A94" s="13" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="23" t="n"/>
+      <c r="B93" s="23" t="n"/>
+      <c r="C93" s="23" t="n"/>
+      <c r="D93" s="23" t="n"/>
+      <c r="E93" s="23" t="n"/>
+      <c r="F93" s="23" t="n"/>
+      <c r="G93" s="23" t="n"/>
+      <c r="H93" s="23" t="n"/>
+      <c r="I93" s="23" t="n"/>
+      <c r="J93" s="23" t="n"/>
+      <c r="K93" s="23" t="n"/>
+      <c r="L93" s="23" t="n"/>
+      <c r="M93" s="23" t="n"/>
+      <c r="N93" s="23" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="23" t="n"/>
+      <c r="B94" s="23" t="n"/>
+      <c r="C94" s="23" t="n"/>
+      <c r="D94" s="23" t="n"/>
+      <c r="E94" s="23" t="n"/>
+      <c r="F94" s="23" t="n"/>
+      <c r="G94" s="23" t="n"/>
+      <c r="H94" s="23" t="n"/>
+      <c r="I94" s="23" t="n"/>
+      <c r="J94" s="23" t="n"/>
+      <c r="K94" s="23" t="n"/>
+      <c r="L94" s="23" t="n"/>
+      <c r="M94" s="23" t="n"/>
+      <c r="N94" s="23" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="23" t="n"/>
+      <c r="B95" s="23" t="n"/>
+      <c r="C95" s="23" t="n"/>
+      <c r="D95" s="23" t="n"/>
+      <c r="E95" s="23" t="n"/>
+      <c r="F95" s="23" t="n"/>
+      <c r="G95" s="23" t="n"/>
+      <c r="H95" s="23" t="n"/>
+      <c r="I95" s="23" t="n"/>
+      <c r="J95" s="23" t="n"/>
+      <c r="K95" s="23" t="n"/>
+      <c r="L95" s="23" t="n"/>
+      <c r="M95" s="23" t="n"/>
+      <c r="N95" s="23" t="n"/>
+    </row>
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97" s="13" t="inlineStr">
         <is>
           <t>Sacs   (6)</t>
         </is>
       </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="14" t="inlineStr">
-        <is>
-          <t>Leather Pouch</t>
-        </is>
-      </c>
-      <c r="B95" s="15" t="inlineStr">
-        <is>
-          <t>sac-en-cuir</t>
-        </is>
-      </c>
-      <c r="C95" s="16" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="D95" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E95" s="18" t="n"/>
-      <c r="F95" s="18" t="n"/>
-      <c r="G95" s="18" t="n"/>
-      <c r="H95" s="18" t="n"/>
-      <c r="I95" s="18" t="n"/>
-      <c r="J95" s="18" t="n"/>
-      <c r="K95" s="18" t="n"/>
-      <c r="L95" s="18" t="n"/>
-      <c r="M95" s="19" t="inlineStr">
-        <is>
-          <t>+1 rangées de sac</t>
-        </is>
-      </c>
-      <c r="N95" s="18" t="n"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="14" t="inlineStr">
-        <is>
-          <t>Big Leather Pouch</t>
-        </is>
-      </c>
-      <c r="B96" s="15" t="inlineStr">
-        <is>
-          <t>grand-sac-en-cuir</t>
-        </is>
-      </c>
-      <c r="C96" s="20" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="D96" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E96" s="18" t="n"/>
-      <c r="F96" s="18" t="n"/>
-      <c r="G96" s="18" t="n"/>
-      <c r="H96" s="18" t="n"/>
-      <c r="I96" s="18" t="n"/>
-      <c r="J96" s="18" t="n"/>
-      <c r="K96" s="18" t="n"/>
-      <c r="L96" s="18" t="n"/>
-      <c r="M96" s="19" t="inlineStr">
-        <is>
-          <t>+2 rangées de sac</t>
-        </is>
-      </c>
-      <c r="N96" s="18" t="n"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="14" t="inlineStr">
-        <is>
-          <t>Huge Leather Pouch</t>
-        </is>
-      </c>
-      <c r="B97" s="15" t="inlineStr">
-        <is>
-          <t>enorme-sac-en-cuir</t>
-        </is>
-      </c>
-      <c r="C97" s="21" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="D97" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E97" s="18" t="n"/>
-      <c r="F97" s="18" t="n"/>
-      <c r="G97" s="18" t="n"/>
-      <c r="H97" s="18" t="n"/>
-      <c r="I97" s="18" t="n"/>
-      <c r="J97" s="18" t="n"/>
-      <c r="K97" s="18" t="n"/>
-      <c r="L97" s="18" t="n"/>
-      <c r="M97" s="19" t="inlineStr">
-        <is>
-          <t>+3 rangées de sac</t>
-        </is>
-      </c>
-      <c r="N97" s="18" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="14" t="inlineStr">
         <is>
-          <t>Backpack</t>
+          <t>Leather Pouch</t>
         </is>
       </c>
       <c r="B98" s="15" t="inlineStr">
         <is>
-          <t>sac-a-dos</t>
-        </is>
-      </c>
-      <c r="C98" s="21" t="inlineStr">
-        <is>
-          <t>Rare</t>
+          <t>sac-en-cuir</t>
+        </is>
+      </c>
+      <c r="C98" s="16" t="inlineStr">
+        <is>
+          <t>Common</t>
         </is>
       </c>
       <c r="D98" s="17" t="n">
@@ -3160,7 +3202,7 @@
       <c r="L98" s="18" t="n"/>
       <c r="M98" s="19" t="inlineStr">
         <is>
-          <t>+4 rangées de sac</t>
+          <t>+1 rangées de sac</t>
         </is>
       </c>
       <c r="N98" s="18" t="n"/>
@@ -3168,17 +3210,17 @@
     <row r="99">
       <c r="A99" s="14" t="inlineStr">
         <is>
-          <t>Bottomless Bag</t>
+          <t>Big Leather Pouch</t>
         </is>
       </c>
       <c r="B99" s="15" t="inlineStr">
         <is>
-          <t>sac-sans-fond</t>
-        </is>
-      </c>
-      <c r="C99" s="22" t="inlineStr">
-        <is>
-          <t>Epic</t>
+          <t>grand-sac-en-cuir</t>
+        </is>
+      </c>
+      <c r="C99" s="20" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="D99" s="17" t="n">
@@ -3194,7 +3236,7 @@
       <c r="L99" s="18" t="n"/>
       <c r="M99" s="19" t="inlineStr">
         <is>
-          <t>+6 rangées de sac</t>
+          <t>+2 rangées de sac</t>
         </is>
       </c>
       <c r="N99" s="18" t="n"/>
@@ -3202,17 +3244,17 @@
     <row r="100">
       <c r="A100" s="14" t="inlineStr">
         <is>
-          <t>Master Miner's Bag</t>
+          <t>Huge Leather Pouch</t>
         </is>
       </c>
       <c r="B100" s="15" t="inlineStr">
         <is>
-          <t>sac-maitre-mineur</t>
-        </is>
-      </c>
-      <c r="C100" s="24" t="inlineStr">
-        <is>
-          <t>Legendary</t>
+          <t>enorme-sac-en-cuir</t>
+        </is>
+      </c>
+      <c r="C100" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
         </is>
       </c>
       <c r="D100" s="17" t="n">
@@ -3228,58 +3270,112 @@
       <c r="L100" s="18" t="n"/>
       <c r="M100" s="19" t="inlineStr">
         <is>
+          <t>+3 rangées de sac</t>
+        </is>
+      </c>
+      <c r="N100" s="18" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="14" t="inlineStr">
+        <is>
+          <t>Backpack</t>
+        </is>
+      </c>
+      <c r="B101" s="15" t="inlineStr">
+        <is>
+          <t>sac-a-dos</t>
+        </is>
+      </c>
+      <c r="C101" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D101" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" s="18" t="n"/>
+      <c r="F101" s="18" t="n"/>
+      <c r="G101" s="18" t="n"/>
+      <c r="H101" s="18" t="n"/>
+      <c r="I101" s="18" t="n"/>
+      <c r="J101" s="18" t="n"/>
+      <c r="K101" s="18" t="n"/>
+      <c r="L101" s="18" t="n"/>
+      <c r="M101" s="19" t="inlineStr">
+        <is>
+          <t>+4 rangées de sac</t>
+        </is>
+      </c>
+      <c r="N101" s="18" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="14" t="inlineStr">
+        <is>
+          <t>Bottomless Bag</t>
+        </is>
+      </c>
+      <c r="B102" s="15" t="inlineStr">
+        <is>
+          <t>sac-sans-fond</t>
+        </is>
+      </c>
+      <c r="C102" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="D102" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" s="18" t="n"/>
+      <c r="F102" s="18" t="n"/>
+      <c r="G102" s="18" t="n"/>
+      <c r="H102" s="18" t="n"/>
+      <c r="I102" s="18" t="n"/>
+      <c r="J102" s="18" t="n"/>
+      <c r="K102" s="18" t="n"/>
+      <c r="L102" s="18" t="n"/>
+      <c r="M102" s="19" t="inlineStr">
+        <is>
+          <t>+6 rangées de sac</t>
+        </is>
+      </c>
+      <c r="N102" s="18" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="14" t="inlineStr">
+        <is>
+          <t>Master Miner's Bag</t>
+        </is>
+      </c>
+      <c r="B103" s="15" t="inlineStr">
+        <is>
+          <t>sac-maitre-mineur</t>
+        </is>
+      </c>
+      <c r="C103" s="24" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="D103" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" s="18" t="n"/>
+      <c r="F103" s="18" t="n"/>
+      <c r="G103" s="18" t="n"/>
+      <c r="H103" s="18" t="n"/>
+      <c r="I103" s="18" t="n"/>
+      <c r="J103" s="18" t="n"/>
+      <c r="K103" s="18" t="n"/>
+      <c r="L103" s="18" t="n"/>
+      <c r="M103" s="19" t="inlineStr">
+        <is>
           <t>+10 rangées de sac</t>
         </is>
       </c>
-      <c r="N100" s="18" t="n"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="23" t="n"/>
-      <c r="B101" s="23" t="n"/>
-      <c r="C101" s="23" t="n"/>
-      <c r="D101" s="23" t="n"/>
-      <c r="E101" s="23" t="n"/>
-      <c r="F101" s="23" t="n"/>
-      <c r="G101" s="23" t="n"/>
-      <c r="H101" s="23" t="n"/>
-      <c r="I101" s="23" t="n"/>
-      <c r="J101" s="23" t="n"/>
-      <c r="K101" s="23" t="n"/>
-      <c r="L101" s="23" t="n"/>
-      <c r="M101" s="23" t="n"/>
-      <c r="N101" s="23" t="n"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="23" t="n"/>
-      <c r="B102" s="23" t="n"/>
-      <c r="C102" s="23" t="n"/>
-      <c r="D102" s="23" t="n"/>
-      <c r="E102" s="23" t="n"/>
-      <c r="F102" s="23" t="n"/>
-      <c r="G102" s="23" t="n"/>
-      <c r="H102" s="23" t="n"/>
-      <c r="I102" s="23" t="n"/>
-      <c r="J102" s="23" t="n"/>
-      <c r="K102" s="23" t="n"/>
-      <c r="L102" s="23" t="n"/>
-      <c r="M102" s="23" t="n"/>
-      <c r="N102" s="23" t="n"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="23" t="n"/>
-      <c r="B103" s="23" t="n"/>
-      <c r="C103" s="23" t="n"/>
-      <c r="D103" s="23" t="n"/>
-      <c r="E103" s="23" t="n"/>
-      <c r="F103" s="23" t="n"/>
-      <c r="G103" s="23" t="n"/>
-      <c r="H103" s="23" t="n"/>
-      <c r="I103" s="23" t="n"/>
-      <c r="J103" s="23" t="n"/>
-      <c r="K103" s="23" t="n"/>
-      <c r="L103" s="23" t="n"/>
-      <c r="M103" s="23" t="n"/>
-      <c r="N103" s="23" t="n"/>
+      <c r="N103" s="18" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="23" t="n"/>
@@ -3329,17 +3425,65 @@
       <c r="M106" s="23" t="n"/>
       <c r="N106" s="23" t="n"/>
     </row>
+    <row r="107">
+      <c r="A107" s="23" t="n"/>
+      <c r="B107" s="23" t="n"/>
+      <c r="C107" s="23" t="n"/>
+      <c r="D107" s="23" t="n"/>
+      <c r="E107" s="23" t="n"/>
+      <c r="F107" s="23" t="n"/>
+      <c r="G107" s="23" t="n"/>
+      <c r="H107" s="23" t="n"/>
+      <c r="I107" s="23" t="n"/>
+      <c r="J107" s="23" t="n"/>
+      <c r="K107" s="23" t="n"/>
+      <c r="L107" s="23" t="n"/>
+      <c r="M107" s="23" t="n"/>
+      <c r="N107" s="23" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="23" t="n"/>
+      <c r="B108" s="23" t="n"/>
+      <c r="C108" s="23" t="n"/>
+      <c r="D108" s="23" t="n"/>
+      <c r="E108" s="23" t="n"/>
+      <c r="F108" s="23" t="n"/>
+      <c r="G108" s="23" t="n"/>
+      <c r="H108" s="23" t="n"/>
+      <c r="I108" s="23" t="n"/>
+      <c r="J108" s="23" t="n"/>
+      <c r="K108" s="23" t="n"/>
+      <c r="L108" s="23" t="n"/>
+      <c r="M108" s="23" t="n"/>
+      <c r="N108" s="23" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="23" t="n"/>
+      <c r="B109" s="23" t="n"/>
+      <c r="C109" s="23" t="n"/>
+      <c r="D109" s="23" t="n"/>
+      <c r="E109" s="23" t="n"/>
+      <c r="F109" s="23" t="n"/>
+      <c r="G109" s="23" t="n"/>
+      <c r="H109" s="23" t="n"/>
+      <c r="I109" s="23" t="n"/>
+      <c r="J109" s="23" t="n"/>
+      <c r="K109" s="23" t="n"/>
+      <c r="L109" s="23" t="n"/>
+      <c r="M109" s="23" t="n"/>
+      <c r="N109" s="23" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="A17:N17"/>
-    <mergeCell ref="A70:N70"/>
     <mergeCell ref="A27:N27"/>
-    <mergeCell ref="A94:N94"/>
     <mergeCell ref="A4:N4"/>
-    <mergeCell ref="A48:N48"/>
     <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A59:N59"/>
-    <mergeCell ref="A82:N82"/>
+    <mergeCell ref="A60:N60"/>
+    <mergeCell ref="A97:N97"/>
+    <mergeCell ref="A71:N71"/>
+    <mergeCell ref="A49:N49"/>
+    <mergeCell ref="A84:N84"/>
     <mergeCell ref="A36:N36"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -3354,7 +3498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:H66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3539,120 +3683,124 @@
     <row r="6">
       <c r="A6" s="25" t="inlineStr">
         <is>
-          <t>Bloodletting</t>
+          <t>Bloodbath</t>
         </is>
       </c>
       <c r="B6" s="26" t="inlineStr">
         <is>
-          <t>coup-de-sang</t>
+          <t>bain-de-sang</t>
         </is>
       </c>
       <c r="C6" s="17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D6" s="27" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E6" s="20" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="F6" s="17" t="inlineStr"/>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F6" s="17" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
       <c r="G6" s="18" t="inlineStr">
         <is>
-          <t>Blood Ring</t>
+          <t>Blood Plate</t>
         </is>
       </c>
       <c r="H6" s="18" t="inlineStr">
         <is>
-          <t>Deal 3 damage + current Bleed stacks as bonus damage. Apply 3 Bleed (stacks don't reset).</t>
+          <t>Apply 5 Bleed to ALL enemies.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="25" t="inlineStr">
         <is>
-          <t>Burning Hand</t>
+          <t>Bloodletting</t>
         </is>
       </c>
       <c r="B7" s="26" t="inlineStr">
         <is>
-          <t>main-brulante</t>
+          <t>coup-de-sang</t>
         </is>
       </c>
       <c r="C7" s="17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" s="27" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E7" s="22" t="inlineStr">
-        <is>
-          <t>Epic</t>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="F7" s="17" t="inlineStr"/>
       <c r="G7" s="18" t="inlineStr">
         <is>
-          <t>Onyx Glove</t>
+          <t>Blood Ring</t>
         </is>
       </c>
       <c r="H7" s="18" t="inlineStr">
         <is>
-          <t>Discard your hand. For each card discarded, apply 8 Burning to a random enemy.</t>
+          <t>Deal 3 damage + current Bleed stacks as bonus damage. Apply 3 Bleed (stacks don't reset).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="25" t="inlineStr">
         <is>
-          <t>Cleave</t>
+          <t>Burning Hand</t>
         </is>
       </c>
       <c r="B8" s="26" t="inlineStr">
         <is>
-          <t>couper-en-deux</t>
+          <t>main-brulante</t>
         </is>
       </c>
       <c r="C8" s="17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D8" s="27" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E8" s="21" t="inlineStr">
-        <is>
-          <t>Rare</t>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
         </is>
       </c>
       <c r="F8" s="17" t="inlineStr"/>
       <c r="G8" s="18" t="inlineStr">
         <is>
-          <t>War Axe</t>
+          <t>Onyx Glove</t>
         </is>
       </c>
       <c r="H8" s="18" t="inlineStr">
         <is>
-          <t>Deal 20 damage. If the target dies, deal 15 damage to the next enemy.</t>
+          <t>Discard your hand. For each card discarded, apply 8 Burning to a random enemy.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="25" t="inlineStr">
         <is>
-          <t>Dazzling Kick</t>
+          <t>Cleave</t>
         </is>
       </c>
       <c r="B9" s="26" t="inlineStr">
         <is>
-          <t>coup-eblouissant</t>
+          <t>couper-en-deux</t>
         </is>
       </c>
       <c r="C9" s="17" t="n">
@@ -3671,28 +3819,28 @@
       <c r="F9" s="17" t="inlineStr"/>
       <c r="G9" s="18" t="inlineStr">
         <is>
-          <t>Crusader Greaves</t>
+          <t>War Axe</t>
         </is>
       </c>
       <c r="H9" s="18" t="inlineStr">
         <is>
-          <t>Deal 10 damage. Apply 3 Confusion.</t>
+          <t>Deal 20 damage. If the target dies, deal 15 damage to the next enemy.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="25" t="inlineStr">
         <is>
-          <t>Dragon's Blaze</t>
+          <t>Contagion</t>
         </is>
       </c>
       <c r="B10" s="26" t="inlineStr">
         <is>
-          <t>embrasement-dragon</t>
+          <t>contagion</t>
         </is>
       </c>
       <c r="C10" s="17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D10" s="27" t="inlineStr">
         <is>
@@ -3704,35 +3852,31 @@
           <t>Epic</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
+      <c r="F10" s="17" t="inlineStr"/>
       <c r="G10" s="18" t="inlineStr">
         <is>
-          <t>Magma Hammer, Onyx Guard Plate</t>
+          <t>Blood Gauntlets</t>
         </is>
       </c>
       <c r="H10" s="18" t="inlineStr">
         <is>
-          <t>Detonate all Burning: deal 2 damage per Burning on ALL enemies.</t>
+          <t>Deal 6 damage. Both adjacent enemies gain Bleed equal to the target's Bleed.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="25" t="inlineStr">
         <is>
-          <t>Fire Strike</t>
+          <t>Crimson Carve</t>
         </is>
       </c>
       <c r="B11" s="26" t="inlineStr">
         <is>
-          <t>feu-frappe</t>
+          <t>carve-cramoisi</t>
         </is>
       </c>
       <c r="C11" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" s="27" t="inlineStr">
         <is>
@@ -3747,132 +3891,136 @@
       <c r="F11" s="17" t="inlineStr"/>
       <c r="G11" s="18" t="inlineStr">
         <is>
-          <t>Magma Hammer</t>
+          <t>Blood Plate</t>
         </is>
       </c>
       <c r="H11" s="18" t="inlineStr">
         <is>
-          <t>Deal 12 damage. Apply 3 Burning.</t>
+          <t>Deal 12 damage. Apply 4 Bleed.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="25" t="inlineStr">
         <is>
-          <t>Flaming Kick</t>
+          <t>Dazzling Kick</t>
         </is>
       </c>
       <c r="B12" s="26" t="inlineStr">
         <is>
-          <t>coup-de-pied-ardent</t>
+          <t>coup-eblouissant</t>
         </is>
       </c>
       <c r="C12" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" s="27" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E12" s="22" t="inlineStr">
-        <is>
-          <t>Epic</t>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
         </is>
       </c>
       <c r="F12" s="17" t="inlineStr"/>
       <c r="G12" s="18" t="inlineStr">
         <is>
-          <t>Onyx Boots</t>
+          <t>Crusader Greaves</t>
         </is>
       </c>
       <c r="H12" s="18" t="inlineStr">
         <is>
-          <t>Move all Burning from the target to the enemy behind it.</t>
+          <t>Deal 10 damage. Apply 3 Confusion.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="25" t="inlineStr">
         <is>
-          <t>Forge Smash</t>
+          <t>Dragon's Blaze</t>
         </is>
       </c>
       <c r="B13" s="26" t="inlineStr">
         <is>
-          <t>ecrasement</t>
+          <t>embrasement-dragon</t>
         </is>
       </c>
       <c r="C13" s="17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D13" s="27" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E13" s="20" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="F13" s="17" t="inlineStr"/>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F13" s="17" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
       <c r="G13" s="18" t="inlineStr">
         <is>
-          <t>Forge Hammer</t>
+          <t>Magma Hammer, Onyx Guard Plate</t>
         </is>
       </c>
       <c r="H13" s="18" t="inlineStr">
         <is>
-          <t>Deal 10 damage. Gain 8 Stone.</t>
+          <t>Detonate all Burning: deal 2 damage per Burning on ALL enemies.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="25" t="inlineStr">
         <is>
-          <t>Frost Cascade</t>
+          <t>Fire Strike</t>
         </is>
       </c>
       <c r="B14" s="26" t="inlineStr">
         <is>
-          <t>gel-cascade</t>
+          <t>feu-frappe</t>
         </is>
       </c>
       <c r="C14" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" s="27" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E14" s="21" t="inlineStr">
-        <is>
-          <t>Rare</t>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
         </is>
       </c>
       <c r="F14" s="17" t="inlineStr"/>
       <c r="G14" s="18" t="inlineStr">
         <is>
-          <t>Perfect Frost Ring</t>
+          <t>Magma Hammer</t>
         </is>
       </c>
       <c r="H14" s="18" t="inlineStr">
         <is>
-          <t>Deal 8 damage and apply 3 Chill. If the target was already chilled, cascade the same hit to the next enemy, and so on.</t>
+          <t>Deal 12 damage. Apply 3 Burning.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="25" t="inlineStr">
         <is>
-          <t>Frostbite</t>
+          <t>Flaming Kick</t>
         </is>
       </c>
       <c r="B15" s="26" t="inlineStr">
         <is>
-          <t>givre-lent</t>
+          <t>coup-de-pied-ardent</t>
         </is>
       </c>
       <c r="C15" s="17" t="n">
@@ -3883,72 +4031,68 @@
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E15" s="20" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
         </is>
       </c>
       <c r="F15" s="17" t="inlineStr"/>
       <c r="G15" s="18" t="inlineStr">
         <is>
-          <t>Frost Ring</t>
+          <t>Onyx Boots</t>
         </is>
       </c>
       <c r="H15" s="18" t="inlineStr">
         <is>
-          <t>Deal 5 damage. Chill: -30% speed for 3 turns.</t>
+          <t>Move all Burning from the target to the enemy behind it.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="25" t="inlineStr">
         <is>
-          <t>Giant Swing</t>
+          <t>Forge Smash</t>
         </is>
       </c>
       <c r="B16" s="26" t="inlineStr">
         <is>
-          <t>giant-swing</t>
+          <t>ecrasement</t>
         </is>
       </c>
       <c r="C16" s="17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16" s="27" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E16" s="21" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="F16" s="17" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F16" s="17" t="inlineStr"/>
       <c r="G16" s="18" t="inlineStr">
         <is>
-          <t>War Axe</t>
+          <t>Forge Hammer</t>
         </is>
       </c>
       <c r="H16" s="18" t="inlineStr">
         <is>
-          <t>Deal 16 damage to ALL enemies. Apply 2 Bleed to ALL enemies.</t>
+          <t>Deal 10 damage. Gain 8 Stone.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="25" t="inlineStr">
         <is>
-          <t>Halo Burst</t>
+          <t>Frost Cascade</t>
         </is>
       </c>
       <c r="B17" s="26" t="inlineStr">
         <is>
-          <t>eclat-de-halo</t>
+          <t>gel-cascade</t>
         </is>
       </c>
       <c r="C17" s="17" t="n">
@@ -3964,111 +4108,107 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="F17" s="17" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
+      <c r="F17" s="17" t="inlineStr"/>
       <c r="G17" s="18" t="inlineStr">
         <is>
-          <t>Crusader Gauntlets</t>
+          <t>Perfect Frost Ring</t>
         </is>
       </c>
       <c r="H17" s="18" t="inlineStr">
         <is>
-          <t>Deal 6 damage to ALL enemies.</t>
+          <t>Deal 8 damage and apply 3 Chill. If the target was already chilled, cascade the same hit to the next enemy, and so on.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="25" t="inlineStr">
         <is>
-          <t>Heat Rejection</t>
+          <t>Frostbite</t>
         </is>
       </c>
       <c r="B18" s="26" t="inlineStr">
         <is>
-          <t>rejet-chaleur</t>
+          <t>givre-lent</t>
         </is>
       </c>
       <c r="C18" s="17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18" s="27" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E18" s="22" t="inlineStr">
-        <is>
-          <t>Epic</t>
-        </is>
-      </c>
-      <c r="F18" s="17" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F18" s="17" t="inlineStr"/>
       <c r="G18" s="18" t="inlineStr">
         <is>
-          <t>Big Onyx Sword</t>
+          <t>Frost Ring</t>
         </is>
       </c>
       <c r="H18" s="18" t="inlineStr">
         <is>
-          <t>Spend all Forge Heat. Apply 8 Burning per Heat spent to ALL enemies.</t>
+          <t>Deal 5 damage. Chill: -30% speed for 3 turns.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="25" t="inlineStr">
         <is>
-          <t>Lava Hammer</t>
+          <t>Giant Swing</t>
         </is>
       </c>
       <c r="B19" s="26" t="inlineStr">
         <is>
-          <t>coup-de-lave</t>
+          <t>giant-swing</t>
         </is>
       </c>
       <c r="C19" s="17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D19" s="27" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E19" s="22" t="inlineStr">
-        <is>
-          <t>Epic</t>
-        </is>
-      </c>
-      <c r="F19" s="17" t="inlineStr"/>
+      <c r="E19" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F19" s="17" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
       <c r="G19" s="18" t="inlineStr">
         <is>
-          <t>Magma Hammer</t>
+          <t>War Axe</t>
         </is>
       </c>
       <c r="H19" s="18" t="inlineStr">
         <is>
-          <t>Deal 28 damage. Apply 4 Burning.</t>
+          <t>Deal 16 damage to ALL enemies. Apply 2 Bleed to ALL enemies.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="25" t="inlineStr">
         <is>
-          <t>Lumen Jab</t>
+          <t>Halo Burst</t>
         </is>
       </c>
       <c r="B20" s="26" t="inlineStr">
         <is>
-          <t>coup-de-lumiere</t>
+          <t>eclat-de-halo</t>
         </is>
       </c>
       <c r="C20" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" s="27" t="inlineStr">
         <is>
@@ -4080,7 +4220,11 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="F20" s="17" t="inlineStr"/>
+      <c r="F20" s="17" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
       <c r="G20" s="18" t="inlineStr">
         <is>
           <t>Crusader Gauntlets</t>
@@ -4088,23 +4232,23 @@
       </c>
       <c r="H20" s="18" t="inlineStr">
         <is>
-          <t>Deal 8 damage. Apply 1 Confusion.</t>
+          <t>Deal 6 damage to ALL enemies.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="25" t="inlineStr">
         <is>
-          <t>Onyx Breath</t>
+          <t>Heat Rejection</t>
         </is>
       </c>
       <c r="B21" s="26" t="inlineStr">
         <is>
-          <t>souffle-onyx</t>
+          <t>rejet-chaleur</t>
         </is>
       </c>
       <c r="C21" s="17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D21" s="27" t="inlineStr">
         <is>
@@ -4123,28 +4267,28 @@
       </c>
       <c r="G21" s="18" t="inlineStr">
         <is>
-          <t>Onyx Guard Plate</t>
+          <t>Big Onyx Sword</t>
         </is>
       </c>
       <c r="H21" s="18" t="inlineStr">
         <is>
-          <t>Apply 20 Burning to ALL enemies.</t>
+          <t>Spend all Forge Heat. Apply 8 Burning per Heat spent to ALL enemies.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="25" t="inlineStr">
         <is>
-          <t>Onyx Fist</t>
+          <t>Hemorrhage</t>
         </is>
       </c>
       <c r="B22" s="26" t="inlineStr">
         <is>
-          <t>poing-onyx</t>
+          <t>hemorragie</t>
         </is>
       </c>
       <c r="C22" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" s="27" t="inlineStr">
         <is>
@@ -4159,28 +4303,28 @@
       <c r="F22" s="17" t="inlineStr"/>
       <c r="G22" s="18" t="inlineStr">
         <is>
-          <t>Onyx Glove</t>
+          <t>Blood Greaves</t>
         </is>
       </c>
       <c r="H22" s="18" t="inlineStr">
         <is>
-          <t>Gain 10 Stone. Deal 10 damage and apply 3 Burning.</t>
+          <t>Consume all the target's Bleed: deal 3 damage per Bleed consumed.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="25" t="inlineStr">
         <is>
-          <t>Onyx Radiance</t>
+          <t>Lava Hammer</t>
         </is>
       </c>
       <c r="B23" s="26" t="inlineStr">
         <is>
-          <t>onyx-radiance</t>
+          <t>coup-de-lave</t>
         </is>
       </c>
       <c r="C23" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" s="27" t="inlineStr">
         <is>
@@ -4192,143 +4336,139 @@
           <t>Epic</t>
         </is>
       </c>
-      <c r="F23" s="17" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
+      <c r="F23" s="17" t="inlineStr"/>
       <c r="G23" s="18" t="inlineStr">
         <is>
-          <t>Big Onyx Sword</t>
+          <t>Magma Hammer</t>
         </is>
       </c>
       <c r="H23" s="18" t="inlineStr">
         <is>
-          <t>Apply 8 Burning to ALL enemies.</t>
+          <t>Deal 28 damage. Apply 4 Burning.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="25" t="inlineStr">
         <is>
-          <t>Onyx Slash</t>
+          <t>Lumen Jab</t>
         </is>
       </c>
       <c r="B24" s="26" t="inlineStr">
         <is>
-          <t>onyx-slash</t>
+          <t>coup-de-lumiere</t>
         </is>
       </c>
       <c r="C24" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D24" s="27" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E24" s="22" t="inlineStr">
-        <is>
-          <t>Epic</t>
+      <c r="E24" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
         </is>
       </c>
       <c r="F24" s="17" t="inlineStr"/>
       <c r="G24" s="18" t="inlineStr">
         <is>
-          <t>Big Onyx Sword</t>
+          <t>Crusader Gauntlets</t>
         </is>
       </c>
       <c r="H24" s="18" t="inlineStr">
         <is>
-          <t>Deal 26 damage and 4 Burning. The enemy behind takes half (13 damage, 2 Burning).</t>
+          <t>Deal 8 damage. Apply 1 Confusion.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="25" t="inlineStr">
         <is>
-          <t>Pickaxe Jab</t>
+          <t>Onyx Breath</t>
         </is>
       </c>
       <c r="B25" s="26" t="inlineStr">
         <is>
-          <t>coup-de-pioche</t>
+          <t>souffle-onyx</t>
         </is>
       </c>
       <c r="C25" s="17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D25" s="27" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E25" s="16" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="F25" s="17" t="inlineStr"/>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F25" s="17" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
       <c r="G25" s="18" t="inlineStr">
         <is>
-          <t>Miner's Pick</t>
+          <t>Onyx Guard Plate</t>
         </is>
       </c>
       <c r="H25" s="18" t="inlineStr">
         <is>
-          <t>Deal 3 damage twice. If the target dies, hit a random other enemy for 3.</t>
+          <t>Apply 20 Burning to ALL enemies.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="25" t="inlineStr">
         <is>
-          <t>Poison Dance</t>
+          <t>Onyx Fist</t>
         </is>
       </c>
       <c r="B26" s="26" t="inlineStr">
         <is>
-          <t>danse-empoisonnee</t>
+          <t>poing-onyx</t>
         </is>
       </c>
       <c r="C26" s="17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D26" s="27" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E26" s="21" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="F26" s="17" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F26" s="17" t="inlineStr"/>
       <c r="G26" s="18" t="inlineStr">
         <is>
-          <t>Basilisk Fang</t>
+          <t>Onyx Glove</t>
         </is>
       </c>
       <c r="H26" s="18" t="inlineStr">
         <is>
-          <t>Hit ALL enemies 3 times for 3 damage. Apply 1 Poison per hit (2 if the enemy was already poisoned).</t>
+          <t>Gain 10 Stone. Deal 10 damage and apply 3 Burning.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="25" t="inlineStr">
         <is>
-          <t>Pommel Strike</t>
+          <t>Onyx Radiance</t>
         </is>
       </c>
       <c r="B27" s="26" t="inlineStr">
         <is>
-          <t>coup-de-pommeau</t>
+          <t>onyx-radiance</t>
         </is>
       </c>
       <c r="C27" s="17" t="n">
@@ -4339,108 +4479,112 @@
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E27" s="21" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="F27" s="17" t="inlineStr"/>
+      <c r="E27" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F27" s="17" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
       <c r="G27" s="18" t="inlineStr">
         <is>
-          <t>War Axe</t>
+          <t>Big Onyx Sword</t>
         </is>
       </c>
       <c r="H27" s="18" t="inlineStr">
         <is>
-          <t>Deal 16 damage. Stun the target for 2 turns.</t>
+          <t>Apply 8 Burning to ALL enemies.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="25" t="inlineStr">
         <is>
-          <t>Punch</t>
+          <t>Onyx Slash</t>
         </is>
       </c>
       <c r="B28" s="26" t="inlineStr">
         <is>
-          <t>coup-faible</t>
+          <t>onyx-slash</t>
         </is>
       </c>
       <c r="C28" s="17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D28" s="27" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E28" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="E28" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
         </is>
       </c>
       <c r="F28" s="17" t="inlineStr"/>
       <c r="G28" s="18" t="inlineStr">
         <is>
-          <t>— (deck de base)</t>
+          <t>Big Onyx Sword</t>
         </is>
       </c>
       <c r="H28" s="18" t="inlineStr">
         <is>
-          <t>Deal 3 damage.</t>
+          <t>Deal 26 damage and 4 Burning. The enemy behind takes half (13 damage, 2 Burning).</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="25" t="inlineStr">
         <is>
-          <t>Radiant Strike</t>
+          <t>Open Veins</t>
         </is>
       </c>
       <c r="B29" s="26" t="inlineStr">
         <is>
-          <t>frappe-radiante</t>
+          <t>ouvrir-les-veines</t>
         </is>
       </c>
       <c r="C29" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D29" s="27" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E29" s="21" t="inlineStr">
-        <is>
-          <t>Rare</t>
+      <c r="E29" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
         </is>
       </c>
       <c r="F29" s="17" t="inlineStr"/>
       <c r="G29" s="18" t="inlineStr">
         <is>
-          <t>Crusader Plate</t>
+          <t>Blood Gauntlets</t>
         </is>
       </c>
       <c r="H29" s="18" t="inlineStr">
         <is>
-          <t>Deal 14 damage. Apply 2 Confusion.</t>
+          <t>Deal 4 damage. Apply 5 Bleed.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="25" t="inlineStr">
         <is>
-          <t>Rusty Cleave</t>
+          <t>Pickaxe Jab</t>
         </is>
       </c>
       <c r="B30" s="26" t="inlineStr">
         <is>
-          <t>coup-de-hache</t>
+          <t>coup-de-pioche</t>
         </is>
       </c>
       <c r="C30" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30" s="27" t="inlineStr">
         <is>
@@ -4455,28 +4599,28 @@
       <c r="F30" s="17" t="inlineStr"/>
       <c r="G30" s="18" t="inlineStr">
         <is>
-          <t>Rusty Axe</t>
+          <t>Miner's Pick</t>
         </is>
       </c>
       <c r="H30" s="18" t="inlineStr">
         <is>
-          <t>Deal 6 damage to the target and 4 damage to each adjacent enemy.</t>
+          <t>Deal 3 damage twice. If the target dies, hit a random other enemy for 3.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="25" t="inlineStr">
         <is>
-          <t>Shield Bash</t>
+          <t>Poison Dance</t>
         </is>
       </c>
       <c r="B31" s="26" t="inlineStr">
         <is>
-          <t>coup-de-bouclier</t>
+          <t>danse-empoisonnee</t>
         </is>
       </c>
       <c r="C31" s="17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D31" s="27" t="inlineStr">
         <is>
@@ -4488,103 +4632,107 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="F31" s="17" t="inlineStr"/>
+      <c r="F31" s="17" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
       <c r="G31" s="18" t="inlineStr">
         <is>
-          <t>Tower Shield</t>
+          <t>Basilisk Fang</t>
         </is>
       </c>
       <c r="H31" s="18" t="inlineStr">
         <is>
-          <t>Deal 10 damage. Stun the enemy for 3 turns.</t>
+          <t>Hit ALL enemies 3 times for 3 damage. Apply 1 Poison per hit (2 if the enemy was already poisoned).</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="25" t="inlineStr">
         <is>
-          <t>Splash Strike</t>
+          <t>Pommel Strike</t>
         </is>
       </c>
       <c r="B32" s="26" t="inlineStr">
         <is>
-          <t>eclaboussure-de-frappe</t>
+          <t>coup-de-pommeau</t>
         </is>
       </c>
       <c r="C32" s="17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D32" s="27" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E32" s="20" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
+      <c r="E32" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
         </is>
       </c>
       <c r="F32" s="17" t="inlineStr"/>
       <c r="G32" s="18" t="inlineStr">
         <is>
-          <t>Forge Hammer</t>
+          <t>War Axe</t>
         </is>
       </c>
       <c r="H32" s="18" t="inlineStr">
         <is>
-          <t>Deal 15 damage. Each adjacent enemy has a 50% chance to take 5 Burning.</t>
+          <t>Deal 16 damage. Stun the target for 2 turns.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="25" t="inlineStr">
         <is>
-          <t>Strike</t>
+          <t>Punch</t>
         </is>
       </c>
       <c r="B33" s="26" t="inlineStr">
         <is>
-          <t>frappe</t>
+          <t>coup-faible</t>
         </is>
       </c>
       <c r="C33" s="17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D33" s="27" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E33" s="16" t="inlineStr">
-        <is>
-          <t>Common</t>
+      <c r="E33" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="F33" s="17" t="inlineStr"/>
       <c r="G33" s="18" t="inlineStr">
         <is>
-          <t>Rusty Axe, Forge Hammer, Miner's Pick</t>
+          <t>— (deck de base)</t>
         </is>
       </c>
       <c r="H33" s="18" t="inlineStr">
         <is>
-          <t>Deal 6 damage.</t>
+          <t>Deal 3 damage.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="25" t="inlineStr">
         <is>
-          <t>Venom Stab</t>
+          <t>Radiant Strike</t>
         </is>
       </c>
       <c r="B34" s="26" t="inlineStr">
         <is>
-          <t>coup-venimeux</t>
+          <t>frappe-radiante</t>
         </is>
       </c>
       <c r="C34" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D34" s="27" t="inlineStr">
         <is>
@@ -4599,24 +4747,24 @@
       <c r="F34" s="17" t="inlineStr"/>
       <c r="G34" s="18" t="inlineStr">
         <is>
-          <t>Basilisk Fang</t>
+          <t>Crusader Plate</t>
         </is>
       </c>
       <c r="H34" s="18" t="inlineStr">
         <is>
-          <t>Deal 4 damage. Apply 4 Poison.</t>
+          <t>Deal 14 damage. Apply 2 Confusion.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="25" t="inlineStr">
         <is>
-          <t>Wound Opening</t>
+          <t>Rusty Cleave</t>
         </is>
       </c>
       <c r="B35" s="26" t="inlineStr">
         <is>
-          <t>ouverture-des-plaies</t>
+          <t>coup-de-hache</t>
         </is>
       </c>
       <c r="C35" s="17" t="n">
@@ -4627,184 +4775,184 @@
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E35" s="21" t="inlineStr">
-        <is>
-          <t>Rare</t>
+      <c r="E35" s="16" t="inlineStr">
+        <is>
+          <t>Common</t>
         </is>
       </c>
       <c r="F35" s="17" t="inlineStr"/>
       <c r="G35" s="18" t="inlineStr">
         <is>
-          <t>Basilisk Fang</t>
+          <t>Rusty Axe</t>
         </is>
       </c>
       <c r="H35" s="18" t="inlineStr">
         <is>
-          <t>Deal 18 damage. Doubled if the target has a negative status.</t>
+          <t>Deal 6 damage to the target and 4 damage to each adjacent enemy.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="25" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Shield Bash</t>
         </is>
       </c>
       <c r="B36" s="26" t="inlineStr">
         <is>
-          <t>garde</t>
+          <t>coup-de-bouclier</t>
         </is>
       </c>
       <c r="C36" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D36" s="29" t="inlineStr">
-        <is>
-          <t>Défense</t>
-        </is>
-      </c>
-      <c r="E36" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>2</v>
+      </c>
+      <c r="D36" s="27" t="inlineStr">
+        <is>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="E36" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
         </is>
       </c>
       <c r="F36" s="17" t="inlineStr"/>
       <c r="G36" s="18" t="inlineStr">
         <is>
-          <t>— (deck de base)</t>
+          <t>Tower Shield</t>
         </is>
       </c>
       <c r="H36" s="18" t="inlineStr">
         <is>
-          <t>Gain 5 Stone.</t>
+          <t>Deal 10 damage. Stun the enemy for 3 turns.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="25" t="inlineStr">
         <is>
-          <t>Hand Guard</t>
+          <t>Splash Strike</t>
         </is>
       </c>
       <c r="B37" s="26" t="inlineStr">
         <is>
-          <t>garde-faible</t>
+          <t>eclaboussure-de-frappe</t>
         </is>
       </c>
       <c r="C37" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D37" s="29" t="inlineStr">
-        <is>
-          <t>Défense</t>
-        </is>
-      </c>
-      <c r="E37" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>3</v>
+      </c>
+      <c r="D37" s="27" t="inlineStr">
+        <is>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="E37" s="20" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="F37" s="17" t="inlineStr"/>
       <c r="G37" s="18" t="inlineStr">
         <is>
-          <t>— (deck de base)</t>
+          <t>Forge Hammer</t>
         </is>
       </c>
       <c r="H37" s="18" t="inlineStr">
         <is>
-          <t>Gain 3 Stone.</t>
+          <t>Deal 15 damage. Each adjacent enemy has a 50% chance to take 5 Burning.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="25" t="inlineStr">
         <is>
-          <t>Heavy Armor</t>
+          <t>Strike</t>
         </is>
       </c>
       <c r="B38" s="26" t="inlineStr">
         <is>
-          <t>armure-lourde</t>
+          <t>frappe</t>
         </is>
       </c>
       <c r="C38" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D38" s="29" t="inlineStr">
-        <is>
-          <t>Défense</t>
-        </is>
-      </c>
-      <c r="E38" s="21" t="inlineStr">
-        <is>
-          <t>Rare</t>
+        <v>1</v>
+      </c>
+      <c r="D38" s="27" t="inlineStr">
+        <is>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="E38" s="16" t="inlineStr">
+        <is>
+          <t>Common</t>
         </is>
       </c>
       <c r="F38" s="17" t="inlineStr"/>
       <c r="G38" s="18" t="inlineStr">
         <is>
-          <t>Forgemaster's Mail</t>
+          <t>Rusty Axe, Forge Hammer, Miner's Pick</t>
         </is>
       </c>
       <c r="H38" s="18" t="inlineStr">
         <is>
-          <t>Gain 20 Stone.</t>
+          <t>Deal 6 damage.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="25" t="inlineStr">
         <is>
-          <t>Light Armor</t>
+          <t>Venom Stab</t>
         </is>
       </c>
       <c r="B39" s="26" t="inlineStr">
         <is>
-          <t>armure-legere</t>
+          <t>coup-venimeux</t>
         </is>
       </c>
       <c r="C39" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="D39" s="29" t="inlineStr">
-        <is>
-          <t>Défense</t>
-        </is>
-      </c>
-      <c r="E39" s="16" t="inlineStr">
-        <is>
-          <t>Common</t>
+      <c r="D39" s="27" t="inlineStr">
+        <is>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="E39" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
         </is>
       </c>
       <c r="F39" s="17" t="inlineStr"/>
       <c r="G39" s="18" t="inlineStr">
         <is>
-          <t>Traveler's Garb</t>
+          <t>Basilisk Fang</t>
         </is>
       </c>
       <c r="H39" s="18" t="inlineStr">
         <is>
-          <t>Gain 5 Stone.</t>
+          <t>Deal 4 damage. Apply 4 Poison.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="25" t="inlineStr">
         <is>
-          <t>Mail Armor</t>
+          <t>Wound Opening</t>
         </is>
       </c>
       <c r="B40" s="26" t="inlineStr">
         <is>
-          <t>mail-armor</t>
+          <t>ouverture-des-plaies</t>
         </is>
       </c>
       <c r="C40" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D40" s="29" t="inlineStr">
-        <is>
-          <t>Défense</t>
+        <v>2</v>
+      </c>
+      <c r="D40" s="27" t="inlineStr">
+        <is>
+          <t>Attaque</t>
         </is>
       </c>
       <c r="E40" s="21" t="inlineStr">
@@ -4815,96 +4963,96 @@
       <c r="F40" s="17" t="inlineStr"/>
       <c r="G40" s="18" t="inlineStr">
         <is>
-          <t>Forgemaster's Mail</t>
+          <t>Basilisk Fang</t>
         </is>
       </c>
       <c r="H40" s="18" t="inlineStr">
         <is>
-          <t>Gain 7 Stone for every enemy still alive.</t>
+          <t>Deal 18 damage. Doubled if the target has a negative status.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="25" t="inlineStr">
         <is>
-          <t>Onyx Armor</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="B41" s="26" t="inlineStr">
         <is>
-          <t>onyx-armor</t>
+          <t>garde</t>
         </is>
       </c>
       <c r="C41" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D41" s="29" t="inlineStr">
         <is>
           <t>Défense</t>
         </is>
       </c>
-      <c r="E41" s="22" t="inlineStr">
-        <is>
-          <t>Epic</t>
+      <c r="E41" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="F41" s="17" t="inlineStr"/>
       <c r="G41" s="18" t="inlineStr">
         <is>
-          <t>Onyx Guard Plate</t>
+          <t>— (deck de base)</t>
         </is>
       </c>
       <c r="H41" s="18" t="inlineStr">
         <is>
-          <t>Gain 30 Stone.</t>
+          <t>Gain 5 Stone.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="25" t="inlineStr">
         <is>
-          <t>Quench</t>
+          <t>Hand Guard</t>
         </is>
       </c>
       <c r="B42" s="26" t="inlineStr">
         <is>
-          <t>trempe</t>
+          <t>garde-faible</t>
         </is>
       </c>
       <c r="C42" s="17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D42" s="29" t="inlineStr">
         <is>
           <t>Défense</t>
         </is>
       </c>
-      <c r="E42" s="21" t="inlineStr">
-        <is>
-          <t>Rare</t>
+      <c r="E42" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="F42" s="17" t="inlineStr"/>
       <c r="G42" s="18" t="inlineStr">
         <is>
-          <t>Forgemaster's Mail</t>
+          <t>— (deck de base)</t>
         </is>
       </c>
       <c r="H42" s="18" t="inlineStr">
         <is>
-          <t>Spend all Forge Heat. Gain 10 Stone per Heat spent.</t>
+          <t>Gain 3 Stone.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="25" t="inlineStr">
         <is>
-          <t>Sacred Ground</t>
+          <t>Heavy Armor</t>
         </is>
       </c>
       <c r="B43" s="26" t="inlineStr">
         <is>
-          <t>terre-sacree</t>
+          <t>armure-lourde</t>
         </is>
       </c>
       <c r="C43" s="17" t="n">
@@ -4923,24 +5071,24 @@
       <c r="F43" s="17" t="inlineStr"/>
       <c r="G43" s="18" t="inlineStr">
         <is>
-          <t>Crusader Plate</t>
+          <t>Forgemaster's Mail</t>
         </is>
       </c>
       <c r="H43" s="18" t="inlineStr">
         <is>
-          <t>Gain 18 Stone.</t>
+          <t>Gain 20 Stone.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="25" t="inlineStr">
         <is>
-          <t>Shield Wall</t>
+          <t>Light Armor</t>
         </is>
       </c>
       <c r="B44" s="26" t="inlineStr">
         <is>
-          <t>mur-bouclier</t>
+          <t>armure-legere</t>
         </is>
       </c>
       <c r="C44" s="17" t="n">
@@ -4951,36 +5099,36 @@
           <t>Défense</t>
         </is>
       </c>
-      <c r="E44" s="21" t="inlineStr">
-        <is>
-          <t>Rare</t>
+      <c r="E44" s="16" t="inlineStr">
+        <is>
+          <t>Common</t>
         </is>
       </c>
       <c r="F44" s="17" t="inlineStr"/>
       <c r="G44" s="18" t="inlineStr">
         <is>
-          <t>Tower Shield</t>
+          <t>Traveler's Garb</t>
         </is>
       </c>
       <c r="H44" s="18" t="inlineStr">
         <is>
-          <t>Gain 10 Stone.</t>
+          <t>Gain 5 Stone.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="25" t="inlineStr">
         <is>
-          <t>Stacking Shield</t>
+          <t>Mail Armor</t>
         </is>
       </c>
       <c r="B45" s="26" t="inlineStr">
         <is>
-          <t>bouclier-empilant</t>
+          <t>mail-armor</t>
         </is>
       </c>
       <c r="C45" s="17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D45" s="29" t="inlineStr">
         <is>
@@ -4995,104 +5143,104 @@
       <c r="F45" s="17" t="inlineStr"/>
       <c r="G45" s="18" t="inlineStr">
         <is>
-          <t>Tower Shield</t>
+          <t>Forgemaster's Mail</t>
         </is>
       </c>
       <c r="H45" s="18" t="inlineStr">
         <is>
-          <t>Double your current Stone.</t>
+          <t>Gain 7 Stone for every enemy still alive.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="25" t="inlineStr">
         <is>
-          <t>Boost</t>
+          <t>Onyx Armor</t>
         </is>
       </c>
       <c r="B46" s="26" t="inlineStr">
         <is>
-          <t>boost</t>
+          <t>onyx-armor</t>
         </is>
       </c>
       <c r="C46" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D46" s="30" t="inlineStr">
-        <is>
-          <t>Buff</t>
-        </is>
-      </c>
-      <c r="E46" s="21" t="inlineStr">
-        <is>
-          <t>Rare</t>
+        <v>2</v>
+      </c>
+      <c r="D46" s="29" t="inlineStr">
+        <is>
+          <t>Défense</t>
+        </is>
+      </c>
+      <c r="E46" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
         </is>
       </c>
       <c r="F46" s="17" t="inlineStr"/>
       <c r="G46" s="18" t="inlineStr">
         <is>
-          <t>Onyx Boots, Mail Boots</t>
+          <t>Onyx Guard Plate</t>
         </is>
       </c>
       <c r="H46" s="18" t="inlineStr">
         <is>
-          <t>Gain 3 Forge Heat (energy).</t>
+          <t>Gain 30 Stone.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="25" t="inlineStr">
         <is>
-          <t>Burning Run</t>
+          <t>Quench</t>
         </is>
       </c>
       <c r="B47" s="26" t="inlineStr">
         <is>
-          <t>course-ardente</t>
+          <t>trempe</t>
         </is>
       </c>
       <c r="C47" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D47" s="30" t="inlineStr">
-        <is>
-          <t>Buff</t>
-        </is>
-      </c>
-      <c r="E47" s="22" t="inlineStr">
-        <is>
-          <t>Epic</t>
+        <v>0</v>
+      </c>
+      <c r="D47" s="29" t="inlineStr">
+        <is>
+          <t>Défense</t>
+        </is>
+      </c>
+      <c r="E47" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
         </is>
       </c>
       <c r="F47" s="17" t="inlineStr"/>
       <c r="G47" s="18" t="inlineStr">
         <is>
-          <t>Onyx Boots</t>
+          <t>Forgemaster's Mail</t>
         </is>
       </c>
       <c r="H47" s="18" t="inlineStr">
         <is>
-          <t>Haste for as many turns as your current Forge Heat.</t>
+          <t>Spend all Forge Heat. Gain 10 Stone per Heat spent.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="25" t="inlineStr">
         <is>
-          <t>Crusader's Charge</t>
+          <t>Sacred Ground</t>
         </is>
       </c>
       <c r="B48" s="26" t="inlineStr">
         <is>
-          <t>charge-du-croise</t>
+          <t>terre-sacree</t>
         </is>
       </c>
       <c r="C48" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D48" s="30" t="inlineStr">
-        <is>
-          <t>Buff</t>
+        <v>2</v>
+      </c>
+      <c r="D48" s="29" t="inlineStr">
+        <is>
+          <t>Défense</t>
         </is>
       </c>
       <c r="E48" s="21" t="inlineStr">
@@ -5103,32 +5251,32 @@
       <c r="F48" s="17" t="inlineStr"/>
       <c r="G48" s="18" t="inlineStr">
         <is>
-          <t>Crusader Greaves</t>
+          <t>Crusader Plate</t>
         </is>
       </c>
       <c r="H48" s="18" t="inlineStr">
         <is>
-          <t>Haste: +30% attack speed for 3 turns.</t>
+          <t>Gain 18 Stone.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="25" t="inlineStr">
         <is>
-          <t>Fire Boost</t>
+          <t>Sanguine Guard</t>
         </is>
       </c>
       <c r="B49" s="26" t="inlineStr">
         <is>
-          <t>boost-feu</t>
+          <t>garde-sanguine</t>
         </is>
       </c>
       <c r="C49" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D49" s="30" t="inlineStr">
-        <is>
-          <t>Buff</t>
+        <v>2</v>
+      </c>
+      <c r="D49" s="29" t="inlineStr">
+        <is>
+          <t>Défense</t>
         </is>
       </c>
       <c r="E49" s="22" t="inlineStr">
@@ -5139,96 +5287,96 @@
       <c r="F49" s="17" t="inlineStr"/>
       <c r="G49" s="18" t="inlineStr">
         <is>
-          <t>Onyx Boots</t>
+          <t>Blood Plate</t>
         </is>
       </c>
       <c r="H49" s="18" t="inlineStr">
         <is>
-          <t>Convert 4 of your own Burning into 2 Forge Heat. No effect below 4 Burning.</t>
+          <t>Gain 1 Stone per Bleed among ALL enemies.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="25" t="inlineStr">
         <is>
-          <t>Forge from Ashes</t>
+          <t>Shield Wall</t>
         </is>
       </c>
       <c r="B50" s="26" t="inlineStr">
         <is>
-          <t>forge-des-cendres</t>
+          <t>mur-bouclier</t>
         </is>
       </c>
       <c r="C50" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D50" s="30" t="inlineStr">
-        <is>
-          <t>Buff</t>
-        </is>
-      </c>
-      <c r="E50" s="22" t="inlineStr">
-        <is>
-          <t>Epic</t>
+        <v>1</v>
+      </c>
+      <c r="D50" s="29" t="inlineStr">
+        <is>
+          <t>Défense</t>
+        </is>
+      </c>
+      <c r="E50" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
         </is>
       </c>
       <c r="F50" s="17" t="inlineStr"/>
       <c r="G50" s="18" t="inlineStr">
         <is>
-          <t>Onyx Glove</t>
+          <t>Tower Shield</t>
         </is>
       </c>
       <c r="H50" s="18" t="inlineStr">
         <is>
-          <t>Discard your hand and draw that many cards.</t>
+          <t>Gain 10 Stone.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="25" t="inlineStr">
         <is>
-          <t>Free Movement</t>
+          <t>Stacking Shield</t>
         </is>
       </c>
       <c r="B51" s="26" t="inlineStr">
         <is>
-          <t>mouvement-degage</t>
+          <t>bouclier-empilant</t>
         </is>
       </c>
       <c r="C51" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D51" s="30" t="inlineStr">
-        <is>
-          <t>Buff</t>
-        </is>
-      </c>
-      <c r="E51" s="16" t="inlineStr">
-        <is>
-          <t>Common</t>
+        <v>4</v>
+      </c>
+      <c r="D51" s="29" t="inlineStr">
+        <is>
+          <t>Défense</t>
+        </is>
+      </c>
+      <c r="E51" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
         </is>
       </c>
       <c r="F51" s="17" t="inlineStr"/>
       <c r="G51" s="18" t="inlineStr">
         <is>
-          <t>Traveler's Garb</t>
+          <t>Tower Shield</t>
         </is>
       </c>
       <c r="H51" s="18" t="inlineStr">
         <is>
-          <t>Haste for 5 of your turns.</t>
+          <t>Double your current Stone.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="25" t="inlineStr">
         <is>
-          <t>Mail Advantage</t>
+          <t>Blood Rush</t>
         </is>
       </c>
       <c r="B52" s="26" t="inlineStr">
         <is>
-          <t>avantage-maille</t>
+          <t>ruee-de-sang</t>
         </is>
       </c>
       <c r="C52" s="17" t="n">
@@ -5239,72 +5387,72 @@
           <t>Buff</t>
         </is>
       </c>
-      <c r="E52" s="21" t="inlineStr">
-        <is>
-          <t>Rare</t>
+      <c r="E52" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
         </is>
       </c>
       <c r="F52" s="17" t="inlineStr"/>
       <c r="G52" s="18" t="inlineStr">
         <is>
-          <t>Mail Glove, Mail Boots</t>
+          <t>Blood Greaves</t>
         </is>
       </c>
       <c r="H52" s="18" t="inlineStr">
         <is>
-          <t>Gain 8 Stone and Haste for 2 turns.</t>
+          <t>Gain 1 Forge Heat per 4 Bleed among ALL enemies.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="25" t="inlineStr">
         <is>
-          <t>Master's Hand</t>
+          <t>Boost</t>
         </is>
       </c>
       <c r="B53" s="26" t="inlineStr">
         <is>
-          <t>main-de-maitre</t>
+          <t>boost</t>
         </is>
       </c>
       <c r="C53" s="17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D53" s="30" t="inlineStr">
         <is>
           <t>Buff</t>
         </is>
       </c>
-      <c r="E53" s="16" t="inlineStr">
-        <is>
-          <t>Common</t>
+      <c r="E53" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
         </is>
       </c>
       <c r="F53" s="17" t="inlineStr"/>
       <c r="G53" s="18" t="inlineStr">
         <is>
-          <t>Miner's Gloves, Mail Glove</t>
+          <t>Onyx Boots, Mail Boots</t>
         </is>
       </c>
       <c r="H53" s="18" t="inlineStr">
         <is>
-          <t>Draw 2 cards.</t>
+          <t>Gain 3 Forge Heat (energy).</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="25" t="inlineStr">
         <is>
-          <t>Onyx Overheat</t>
+          <t>Burning Run</t>
         </is>
       </c>
       <c r="B54" s="26" t="inlineStr">
         <is>
-          <t>onyx-overheat</t>
+          <t>course-ardente</t>
         </is>
       </c>
       <c r="C54" s="17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D54" s="30" t="inlineStr">
         <is>
@@ -5319,28 +5467,28 @@
       <c r="F54" s="17" t="inlineStr"/>
       <c r="G54" s="18" t="inlineStr">
         <is>
-          <t>Big Onyx Sword</t>
+          <t>Onyx Boots</t>
         </is>
       </c>
       <c r="H54" s="18" t="inlineStr">
         <is>
-          <t>Gain 5 Forge Heat (energy).</t>
+          <t>Haste for as many turns as your current Forge Heat.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="25" t="inlineStr">
         <is>
-          <t>Outnumbered</t>
+          <t>Crusader's Charge</t>
         </is>
       </c>
       <c r="B55" s="26" t="inlineStr">
         <is>
-          <t>surnombre</t>
+          <t>charge-du-croise</t>
         </is>
       </c>
       <c r="C55" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D55" s="30" t="inlineStr">
         <is>
@@ -5355,28 +5503,28 @@
       <c r="F55" s="17" t="inlineStr"/>
       <c r="G55" s="18" t="inlineStr">
         <is>
-          <t>Mail Glove</t>
+          <t>Crusader Greaves</t>
         </is>
       </c>
       <c r="H55" s="18" t="inlineStr">
         <is>
-          <t>Draw 1 card per living enemy.</t>
+          <t>Haste: +30% attack speed for 3 turns.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="25" t="inlineStr">
         <is>
-          <t>Perfect Sapphire Surge</t>
+          <t>Fire Boost</t>
         </is>
       </c>
       <c r="B56" s="26" t="inlineStr">
         <is>
-          <t>surge-saphir-parfait</t>
+          <t>boost-feu</t>
         </is>
       </c>
       <c r="C56" s="17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D56" s="30" t="inlineStr">
         <is>
@@ -5391,118 +5539,370 @@
       <c r="F56" s="17" t="inlineStr"/>
       <c r="G56" s="18" t="inlineStr">
         <is>
-          <t>Perfect Sapphire Amulet</t>
+          <t>Onyx Boots</t>
         </is>
       </c>
       <c r="H56" s="18" t="inlineStr">
         <is>
-          <t>Gain 3 Forge Heat (energy).</t>
+          <t>Convert 4 of your own Burning into 2 Forge Heat. No effect below 4 Burning.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="25" t="inlineStr">
         <is>
-          <t>Quicken</t>
+          <t>Forge from Ashes</t>
         </is>
       </c>
       <c r="B57" s="26" t="inlineStr">
         <is>
-          <t>celerite-vive</t>
+          <t>forge-des-cendres</t>
         </is>
       </c>
       <c r="C57" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D57" s="30" t="inlineStr">
         <is>
           <t>Buff</t>
         </is>
       </c>
-      <c r="E57" s="20" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
+      <c r="E57" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
         </is>
       </c>
       <c r="F57" s="17" t="inlineStr"/>
       <c r="G57" s="18" t="inlineStr">
         <is>
-          <t>Swift Boots, Mail Boots</t>
+          <t>Onyx Glove</t>
         </is>
       </c>
       <c r="H57" s="18" t="inlineStr">
         <is>
-          <t>Haste: +30% attack speed for 3 turns.</t>
+          <t>Discard your hand and draw that many cards.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="25" t="inlineStr">
         <is>
-          <t>Sapphire Surge</t>
+          <t>Free Movement</t>
         </is>
       </c>
       <c r="B58" s="26" t="inlineStr">
         <is>
-          <t>surge-saphir</t>
+          <t>mouvement-degage</t>
         </is>
       </c>
       <c r="C58" s="17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D58" s="30" t="inlineStr">
         <is>
           <t>Buff</t>
         </is>
       </c>
-      <c r="E58" s="20" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
+      <c r="E58" s="16" t="inlineStr">
+        <is>
+          <t>Common</t>
         </is>
       </c>
       <c r="F58" s="17" t="inlineStr"/>
       <c r="G58" s="18" t="inlineStr">
         <is>
-          <t>Sapphire Amulet, Nice Sapphire Amulet</t>
+          <t>Traveler's Garb</t>
         </is>
       </c>
       <c r="H58" s="18" t="inlineStr">
         <is>
-          <t>Gain 2 Forge Heat (energy).</t>
+          <t>Haste for 5 of your turns.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="25" t="inlineStr">
         <is>
-          <t>Second Wind</t>
+          <t>Mail Advantage</t>
         </is>
       </c>
       <c r="B59" s="26" t="inlineStr">
         <is>
-          <t>second-souffle</t>
+          <t>avantage-maille</t>
         </is>
       </c>
       <c r="C59" s="17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D59" s="30" t="inlineStr">
         <is>
           <t>Buff</t>
         </is>
       </c>
-      <c r="E59" s="20" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
+      <c r="E59" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
         </is>
       </c>
       <c r="F59" s="17" t="inlineStr"/>
       <c r="G59" s="18" t="inlineStr">
         <is>
+          <t>Mail Glove, Mail Boots</t>
+        </is>
+      </c>
+      <c r="H59" s="18" t="inlineStr">
+        <is>
+          <t>Gain 8 Stone and Haste for 2 turns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="25" t="inlineStr">
+        <is>
+          <t>Master's Hand</t>
+        </is>
+      </c>
+      <c r="B60" s="26" t="inlineStr">
+        <is>
+          <t>main-de-maitre</t>
+        </is>
+      </c>
+      <c r="C60" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" s="30" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="E60" s="16" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F60" s="17" t="inlineStr"/>
+      <c r="G60" s="18" t="inlineStr">
+        <is>
+          <t>Miner's Gloves, Mail Glove</t>
+        </is>
+      </c>
+      <c r="H60" s="18" t="inlineStr">
+        <is>
+          <t>Draw 2 cards.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="25" t="inlineStr">
+        <is>
+          <t>Onyx Overheat</t>
+        </is>
+      </c>
+      <c r="B61" s="26" t="inlineStr">
+        <is>
+          <t>onyx-overheat</t>
+        </is>
+      </c>
+      <c r="C61" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" s="30" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="E61" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F61" s="17" t="inlineStr"/>
+      <c r="G61" s="18" t="inlineStr">
+        <is>
+          <t>Big Onyx Sword</t>
+        </is>
+      </c>
+      <c r="H61" s="18" t="inlineStr">
+        <is>
+          <t>Gain 5 Forge Heat (energy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="25" t="inlineStr">
+        <is>
+          <t>Outnumbered</t>
+        </is>
+      </c>
+      <c r="B62" s="26" t="inlineStr">
+        <is>
+          <t>surnombre</t>
+        </is>
+      </c>
+      <c r="C62" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D62" s="30" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="E62" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F62" s="17" t="inlineStr"/>
+      <c r="G62" s="18" t="inlineStr">
+        <is>
+          <t>Mail Glove</t>
+        </is>
+      </c>
+      <c r="H62" s="18" t="inlineStr">
+        <is>
+          <t>Draw 1 card per living enemy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="25" t="inlineStr">
+        <is>
+          <t>Perfect Sapphire Surge</t>
+        </is>
+      </c>
+      <c r="B63" s="26" t="inlineStr">
+        <is>
+          <t>surge-saphir-parfait</t>
+        </is>
+      </c>
+      <c r="C63" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" s="30" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="E63" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F63" s="17" t="inlineStr"/>
+      <c r="G63" s="18" t="inlineStr">
+        <is>
+          <t>Perfect Sapphire Amulet</t>
+        </is>
+      </c>
+      <c r="H63" s="18" t="inlineStr">
+        <is>
+          <t>Gain 3 Forge Heat (energy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="25" t="inlineStr">
+        <is>
+          <t>Quicken</t>
+        </is>
+      </c>
+      <c r="B64" s="26" t="inlineStr">
+        <is>
+          <t>celerite-vive</t>
+        </is>
+      </c>
+      <c r="C64" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" s="30" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="E64" s="20" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F64" s="17" t="inlineStr"/>
+      <c r="G64" s="18" t="inlineStr">
+        <is>
+          <t>Swift Boots, Mail Boots</t>
+        </is>
+      </c>
+      <c r="H64" s="18" t="inlineStr">
+        <is>
+          <t>Haste: +30% attack speed for 3 turns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="25" t="inlineStr">
+        <is>
+          <t>Sapphire Surge</t>
+        </is>
+      </c>
+      <c r="B65" s="26" t="inlineStr">
+        <is>
+          <t>surge-saphir</t>
+        </is>
+      </c>
+      <c r="C65" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" s="30" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="E65" s="20" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F65" s="17" t="inlineStr"/>
+      <c r="G65" s="18" t="inlineStr">
+        <is>
+          <t>Sapphire Amulet, Nice Sapphire Amulet</t>
+        </is>
+      </c>
+      <c r="H65" s="18" t="inlineStr">
+        <is>
+          <t>Gain 2 Forge Heat (energy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="25" t="inlineStr">
+        <is>
+          <t>Second Wind</t>
+        </is>
+      </c>
+      <c r="B66" s="26" t="inlineStr">
+        <is>
+          <t>second-souffle</t>
+        </is>
+      </c>
+      <c r="C66" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" s="30" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="E66" s="20" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F66" s="17" t="inlineStr"/>
+      <c r="G66" s="18" t="inlineStr">
+        <is>
           <t>Swift Boots</t>
         </is>
       </c>
-      <c r="H59" s="18" t="inlineStr">
+      <c r="H66" s="18" t="inlineStr">
         <is>
           <t>Trade 5 Haste turns for 3 Forge Heat. No effect below 5 Haste.</t>
         </is>
@@ -5523,7 +5923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5635,10 +6035,26 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="23" t="n"/>
-      <c r="B7" s="23" t="n"/>
-      <c r="C7" s="23" t="n"/>
-      <c r="D7" s="23" t="n"/>
+      <c r="A7" s="25" t="inlineStr">
+        <is>
+          <t>Blood Set</t>
+        </is>
+      </c>
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>Blood Plate  +  Blood Gauntlets  +  Blood Greaves</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>Quand un combo de saignement inflige des dégâts bonus</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="inlineStr">
+        <is>
+          <t>When a Bleed combo deals bonus damage, heal the hero for that amount.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="23" t="n"/>
@@ -5669,6 +6085,12 @@
       <c r="B12" s="23" t="n"/>
       <c r="C12" s="23" t="n"/>
       <c r="D12" s="23" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="23" t="n"/>
+      <c r="B13" s="23" t="n"/>
+      <c r="C13" s="23" t="n"/>
+      <c r="D13" s="23" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/docs/BRUTAL-items-et-cartes.xlsx
+++ b/docs/BRUTAL-items-et-cartes.xlsx
@@ -1925,13 +1925,13 @@
           <t>plate-sang</t>
         </is>
       </c>
-      <c r="C41" s="22" t="inlineStr">
-        <is>
-          <t>Epic</t>
+      <c r="C41" s="20" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="D41" s="17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E41" s="18" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="J41" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K41" s="18" t="n"/>
       <c r="L41" s="18" t="n"/>
@@ -2688,9 +2688,9 @@
           <t>gants-sang</t>
         </is>
       </c>
-      <c r="C76" s="22" t="inlineStr">
-        <is>
-          <t>Epic</t>
+      <c r="C76" s="20" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="D76" s="17" t="n">
@@ -3035,9 +3035,9 @@
           <t>bottes-sang</t>
         </is>
       </c>
-      <c r="C89" s="22" t="inlineStr">
-        <is>
-          <t>Epic</t>
+      <c r="C89" s="20" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="D89" s="17" t="n">
@@ -3699,9 +3699,9 @@
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E6" s="22" t="inlineStr">
-        <is>
-          <t>Epic</t>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="F6" s="17" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="H6" s="18" t="inlineStr">
         <is>
-          <t>Apply 5 Bleed to ALL enemies.</t>
+          <t>Apply 4 Bleed to ALL enemies.</t>
         </is>
       </c>
     </row>
@@ -3847,9 +3847,9 @@
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E10" s="22" t="inlineStr">
-        <is>
-          <t>Epic</t>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="F10" s="17" t="inlineStr"/>
@@ -3860,7 +3860,7 @@
       </c>
       <c r="H10" s="18" t="inlineStr">
         <is>
-          <t>Deal 6 damage. Both adjacent enemies gain Bleed equal to the target's Bleed.</t>
+          <t>Deal 5 damage. Both adjacent enemies gain Bleed equal to the target's Bleed.</t>
         </is>
       </c>
     </row>
@@ -3883,9 +3883,9 @@
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E11" s="22" t="inlineStr">
-        <is>
-          <t>Epic</t>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="F11" s="17" t="inlineStr"/>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="H11" s="18" t="inlineStr">
         <is>
-          <t>Deal 12 damage. Apply 4 Bleed.</t>
+          <t>Deal 9 damage. Apply 3 Bleed.</t>
         </is>
       </c>
     </row>
@@ -4295,9 +4295,9 @@
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E22" s="22" t="inlineStr">
-        <is>
-          <t>Epic</t>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="F22" s="17" t="inlineStr"/>
@@ -4308,7 +4308,7 @@
       </c>
       <c r="H22" s="18" t="inlineStr">
         <is>
-          <t>Consume all the target's Bleed: deal 3 damage per Bleed consumed.</t>
+          <t>Consume all the target's Bleed: deal 2 damage per Bleed consumed.</t>
         </is>
       </c>
     </row>
@@ -4555,9 +4555,9 @@
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E29" s="22" t="inlineStr">
-        <is>
-          <t>Epic</t>
+      <c r="E29" s="20" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="F29" s="17" t="inlineStr"/>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="H29" s="18" t="inlineStr">
         <is>
-          <t>Deal 4 damage. Apply 5 Bleed.</t>
+          <t>Deal 3 damage. Apply 4 Bleed.</t>
         </is>
       </c>
     </row>
@@ -5279,9 +5279,9 @@
           <t>Défense</t>
         </is>
       </c>
-      <c r="E49" s="22" t="inlineStr">
-        <is>
-          <t>Epic</t>
+      <c r="E49" s="20" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="F49" s="17" t="inlineStr"/>
@@ -5387,9 +5387,9 @@
           <t>Buff</t>
         </is>
       </c>
-      <c r="E52" s="22" t="inlineStr">
-        <is>
-          <t>Epic</t>
+      <c r="E52" s="20" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="F52" s="17" t="inlineStr"/>
@@ -5400,7 +5400,7 @@
       </c>
       <c r="H52" s="18" t="inlineStr">
         <is>
-          <t>Gain 1 Forge Heat per 4 Bleed among ALL enemies.</t>
+          <t>Gain 1 Forge Heat per 5 Bleed among ALL enemies.</t>
         </is>
       </c>
     </row>

--- a/docs/BRUTAL-items-et-cartes.xlsx
+++ b/docs/BRUTAL-items-et-cartes.xlsx
@@ -672,14 +672,14 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Effets HORS carte (sac, deux mains, set d'armure)</t>
+          <t>Effets HORS carte (armure de départ, sac, deux mains, set d'armure)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>La colonne « Effet hors-carte » (onglet Items) décrit ce qu'un objet apporte EN DEHORS de ses cartes : rangées de sac, arme à deux mains, appartenance à un set. Pour un nouvel objet, écris ici son effet hors-carte (ex. « +4 rangées de sac »).</t>
+          <t>La colonne « Effet hors-carte » (onglet Items) décrit ce qu'un objet apporte EN DEHORS de ses cartes : armure (Pierre) donnée en début de combat, rangées de sac, arme à deux mains, passif propre, appartenance à un set. Pour un nouvel objet, écris ici son effet hors-carte (ex. « Ajoute 12 d'armure en début de combat », « +4 rangées de sac »).</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,11 @@
       </c>
       <c r="K28" s="18" t="n"/>
       <c r="L28" s="18" t="n"/>
-      <c r="M28" s="19" t="inlineStr"/>
+      <c r="M28" s="19" t="inlineStr">
+        <is>
+          <t>When hit by a melee attack, gain 2 Stone.</t>
+        </is>
+      </c>
       <c r="N28" s="18" t="n"/>
     </row>
     <row r="29">
@@ -1749,7 +1753,11 @@
       <c r="J37" s="18" t="n"/>
       <c r="K37" s="18" t="n"/>
       <c r="L37" s="18" t="n"/>
-      <c r="M37" s="19" t="inlineStr"/>
+      <c r="M37" s="19" t="inlineStr">
+        <is>
+          <t>Ajoute 8 d'armure en début de combat</t>
+        </is>
+      </c>
       <c r="N37" s="18" t="n"/>
     </row>
     <row r="38">
@@ -1805,7 +1813,7 @@
       </c>
       <c r="M38" s="19" t="inlineStr">
         <is>
-          <t>Set : Onyx Set</t>
+          <t>Ajoute 30 d'armure en début de combat  ·  Set : Onyx Set</t>
         </is>
       </c>
       <c r="N38" s="18" t="n"/>
@@ -1857,7 +1865,7 @@
       <c r="L39" s="18" t="n"/>
       <c r="M39" s="19" t="inlineStr">
         <is>
-          <t>Set : Mail Set</t>
+          <t>Ajoute 22 d'armure en début de combat  ·  Set : Mail Set</t>
         </is>
       </c>
       <c r="N39" s="18" t="n"/>
@@ -1909,7 +1917,7 @@
       <c r="L40" s="18" t="n"/>
       <c r="M40" s="19" t="inlineStr">
         <is>
-          <t>Set : Crusader Set</t>
+          <t>Ajoute 15 d'armure en début de combat  ·  Set : Crusader Set</t>
         </is>
       </c>
       <c r="N40" s="18" t="n"/>
@@ -1961,7 +1969,7 @@
       <c r="L41" s="18" t="n"/>
       <c r="M41" s="19" t="inlineStr">
         <is>
-          <t>Set : Blood Set</t>
+          <t>Ajoute 12 d'armure en début de combat  ·  Set : Blood Set</t>
         </is>
       </c>
       <c r="N41" s="18" t="n"/>

--- a/docs/BRUTAL-items-et-cartes.xlsx
+++ b/docs/BRUTAL-items-et-cartes.xlsx
@@ -1813,7 +1813,7 @@
       </c>
       <c r="M38" s="19" t="inlineStr">
         <is>
-          <t>Ajoute 30 d'armure en début de combat  ·  Set : Onyx Set</t>
+          <t>Ajoute 36 d'armure en début de combat  ·  Set : Onyx Set</t>
         </is>
       </c>
       <c r="N38" s="18" t="n"/>
@@ -1891,15 +1891,15 @@
       </c>
       <c r="E40" s="18" t="inlineStr">
         <is>
-          <t>Radiant Strike</t>
+          <t>Heavy Armor</t>
         </is>
       </c>
       <c r="F40" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G40" s="18" t="inlineStr">
         <is>
-          <t>Sacred Ground</t>
+          <t>Armor of light</t>
         </is>
       </c>
       <c r="H40" s="17" t="n">
@@ -1913,11 +1913,17 @@
       <c r="J40" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="K40" s="18" t="n"/>
-      <c r="L40" s="18" t="n"/>
+      <c r="K40" s="18" t="inlineStr">
+        <is>
+          <t>Holy light</t>
+        </is>
+      </c>
+      <c r="L40" s="17" t="n">
+        <v>1</v>
+      </c>
       <c r="M40" s="19" t="inlineStr">
         <is>
-          <t>Ajoute 15 d'armure en début de combat  ·  Set : Crusader Set</t>
+          <t>Ajoute 30 d'armure en début de combat  ·  Set : Crusader Set</t>
         </is>
       </c>
       <c r="N40" s="18" t="n"/>
@@ -1933,9 +1939,9 @@
           <t>plate-sang</t>
         </is>
       </c>
-      <c r="C41" s="20" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
+      <c r="C41" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
         </is>
       </c>
       <c r="D41" s="17" t="n">
@@ -1943,11 +1949,11 @@
       </c>
       <c r="E41" s="18" t="inlineStr">
         <is>
-          <t>Crimson Carve</t>
+          <t>Heavy Armor</t>
         </is>
       </c>
       <c r="F41" s="17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G41" s="18" t="inlineStr">
         <is>
@@ -1965,11 +1971,17 @@
       <c r="J41" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="K41" s="18" t="n"/>
-      <c r="L41" s="18" t="n"/>
+      <c r="K41" s="18" t="inlineStr">
+        <is>
+          <t>Drink blood</t>
+        </is>
+      </c>
+      <c r="L41" s="17" t="n">
+        <v>1</v>
+      </c>
       <c r="M41" s="19" t="inlineStr">
         <is>
-          <t>Ajoute 12 d'armure en début de combat  ·  Set : Blood Set</t>
+          <t>Ajoute 20 d'armure en début de combat  ·  Set : Blood Set</t>
         </is>
       </c>
       <c r="N41" s="18" t="n"/>
@@ -2656,11 +2668,11 @@
         </is>
       </c>
       <c r="D75" s="17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E75" s="18" t="inlineStr">
         <is>
-          <t>Lumen Jab</t>
+          <t>Master's Hand</t>
         </is>
       </c>
       <c r="F75" s="17" t="n">
@@ -2674,8 +2686,14 @@
       <c r="H75" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="I75" s="18" t="n"/>
-      <c r="J75" s="18" t="n"/>
+      <c r="I75" s="18" t="inlineStr">
+        <is>
+          <t>Lay on Hands</t>
+        </is>
+      </c>
+      <c r="J75" s="17" t="n">
+        <v>2</v>
+      </c>
       <c r="K75" s="18" t="n"/>
       <c r="L75" s="18" t="n"/>
       <c r="M75" s="19" t="inlineStr">
@@ -2696,13 +2714,13 @@
           <t>gants-sang</t>
         </is>
       </c>
-      <c r="C76" s="20" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
+      <c r="C76" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
         </is>
       </c>
       <c r="D76" s="17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E76" s="18" t="inlineStr">
         <is>
@@ -2720,8 +2738,14 @@
       <c r="H76" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="I76" s="18" t="n"/>
-      <c r="J76" s="18" t="n"/>
+      <c r="I76" s="18" t="inlineStr">
+        <is>
+          <t>Blood Absorption</t>
+        </is>
+      </c>
+      <c r="J76" s="17" t="n">
+        <v>1</v>
+      </c>
       <c r="K76" s="18" t="n"/>
       <c r="L76" s="18" t="n"/>
       <c r="M76" s="19" t="inlineStr">
@@ -2873,7 +2897,11 @@
       <c r="J85" s="18" t="n"/>
       <c r="K85" s="18" t="n"/>
       <c r="L85" s="18" t="n"/>
-      <c r="M85" s="19" t="inlineStr"/>
+      <c r="M85" s="19" t="inlineStr">
+        <is>
+          <t>+15% célérité, +3 move speed</t>
+        </is>
+      </c>
       <c r="N85" s="18" t="n"/>
     </row>
     <row r="86">
@@ -2929,7 +2957,7 @@
       </c>
       <c r="M86" s="19" t="inlineStr">
         <is>
-          <t>Set : Onyx Set</t>
+          <t>+30% célérité, +8 move speed  ·  Set : Onyx Set</t>
         </is>
       </c>
       <c r="N86" s="18" t="n"/>
@@ -2981,7 +3009,7 @@
       <c r="L87" s="18" t="n"/>
       <c r="M87" s="19" t="inlineStr">
         <is>
-          <t>Set : Mail Set</t>
+          <t>+20% célérité, +5 move speed  ·  Set : Mail Set</t>
         </is>
       </c>
       <c r="N87" s="18" t="n"/>
@@ -3003,11 +3031,11 @@
         </is>
       </c>
       <c r="D88" s="17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E88" s="18" t="inlineStr">
         <is>
-          <t>Crusader's Charge</t>
+          <t>Quicken</t>
         </is>
       </c>
       <c r="F88" s="17" t="n">
@@ -3015,19 +3043,25 @@
       </c>
       <c r="G88" s="18" t="inlineStr">
         <is>
-          <t>Dazzling Kick</t>
+          <t>Kick of light</t>
         </is>
       </c>
       <c r="H88" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="I88" s="18" t="n"/>
-      <c r="J88" s="18" t="n"/>
+      <c r="I88" s="18" t="inlineStr">
+        <is>
+          <t>Boost</t>
+        </is>
+      </c>
+      <c r="J88" s="17" t="n">
+        <v>2</v>
+      </c>
       <c r="K88" s="18" t="n"/>
       <c r="L88" s="18" t="n"/>
       <c r="M88" s="19" t="inlineStr">
         <is>
-          <t>Set : Crusader Set</t>
+          <t>+20% célérité, +5 move speed  ·  Set : Crusader Set</t>
         </is>
       </c>
       <c r="N88" s="18" t="n"/>
@@ -3043,21 +3077,21 @@
           <t>bottes-sang</t>
         </is>
       </c>
-      <c r="C89" s="20" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
+      <c r="C89" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
         </is>
       </c>
       <c r="D89" s="17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E89" s="18" t="inlineStr">
         <is>
-          <t>Hemorrhage</t>
+          <t>Blood Slide</t>
         </is>
       </c>
       <c r="F89" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G89" s="18" t="inlineStr">
         <is>
@@ -3067,13 +3101,25 @@
       <c r="H89" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="I89" s="18" t="n"/>
-      <c r="J89" s="18" t="n"/>
-      <c r="K89" s="18" t="n"/>
-      <c r="L89" s="18" t="n"/>
+      <c r="I89" s="18" t="inlineStr">
+        <is>
+          <t>Quicken</t>
+        </is>
+      </c>
+      <c r="J89" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K89" s="18" t="inlineStr">
+        <is>
+          <t>Boost</t>
+        </is>
+      </c>
+      <c r="L89" s="17" t="n">
+        <v>1</v>
+      </c>
       <c r="M89" s="19" t="inlineStr">
         <is>
-          <t>Set : Blood Set</t>
+          <t>+20% célérité, +5 move speed  ·  Set : Blood Set</t>
         </is>
       </c>
       <c r="N89" s="18" t="n"/>
@@ -3506,7 +3552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H66"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3660,7 +3706,7 @@
         </is>
       </c>
       <c r="C5" s="17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D5" s="27" t="inlineStr">
         <is>
@@ -3691,25 +3737,25 @@
     <row r="6">
       <c r="A6" s="25" t="inlineStr">
         <is>
-          <t>Bloodbath</t>
+          <t>Blood Slide</t>
         </is>
       </c>
       <c r="B6" s="26" t="inlineStr">
         <is>
-          <t>bain-de-sang</t>
+          <t>glissade-sur-sang</t>
         </is>
       </c>
       <c r="C6" s="17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" s="27" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E6" s="20" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
         </is>
       </c>
       <c r="F6" s="17" t="inlineStr">
@@ -3719,132 +3765,136 @@
       </c>
       <c r="G6" s="18" t="inlineStr">
         <is>
-          <t>Blood Plate</t>
+          <t>Blood Greaves</t>
         </is>
       </c>
       <c r="H6" s="18" t="inlineStr">
         <is>
-          <t>Apply 4 Bleed to ALL enemies.</t>
+          <t>Stun for 2 turns every enemy that has Bleed.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="25" t="inlineStr">
         <is>
-          <t>Bloodletting</t>
+          <t>Bloodbath</t>
         </is>
       </c>
       <c r="B7" s="26" t="inlineStr">
         <is>
-          <t>coup-de-sang</t>
+          <t>bain-de-sang</t>
         </is>
       </c>
       <c r="C7" s="17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D7" s="27" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E7" s="20" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="F7" s="17" t="inlineStr"/>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F7" s="17" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
       <c r="G7" s="18" t="inlineStr">
         <is>
-          <t>Blood Ring</t>
+          <t>Blood Plate</t>
         </is>
       </c>
       <c r="H7" s="18" t="inlineStr">
         <is>
-          <t>Deal 3 damage + current Bleed stacks as bonus damage. Apply 3 Bleed (stacks don't reset).</t>
+          <t>Take 10 damage. Apply 5 Bleed to ALL enemies.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="25" t="inlineStr">
         <is>
-          <t>Burning Hand</t>
+          <t>Bloodletting</t>
         </is>
       </c>
       <c r="B8" s="26" t="inlineStr">
         <is>
-          <t>main-brulante</t>
+          <t>coup-de-sang</t>
         </is>
       </c>
       <c r="C8" s="17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" s="27" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E8" s="22" t="inlineStr">
-        <is>
-          <t>Epic</t>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="F8" s="17" t="inlineStr"/>
       <c r="G8" s="18" t="inlineStr">
         <is>
-          <t>Onyx Glove</t>
+          <t>Blood Ring</t>
         </is>
       </c>
       <c r="H8" s="18" t="inlineStr">
         <is>
-          <t>Discard your hand. For each card discarded, apply 8 Burning to a random enemy.</t>
+          <t>Deal 3 damage + current Bleed stacks as bonus damage. Apply 3 Bleed (stacks don't reset).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="25" t="inlineStr">
         <is>
-          <t>Cleave</t>
+          <t>Burning Hand</t>
         </is>
       </c>
       <c r="B9" s="26" t="inlineStr">
         <is>
-          <t>couper-en-deux</t>
+          <t>main-brulante</t>
         </is>
       </c>
       <c r="C9" s="17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D9" s="27" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E9" s="21" t="inlineStr">
-        <is>
-          <t>Rare</t>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
         </is>
       </c>
       <c r="F9" s="17" t="inlineStr"/>
       <c r="G9" s="18" t="inlineStr">
         <is>
-          <t>War Axe</t>
+          <t>Onyx Glove</t>
         </is>
       </c>
       <c r="H9" s="18" t="inlineStr">
         <is>
-          <t>Deal 20 damage. If the target dies, deal 15 damage to the next enemy.</t>
+          <t>Discard your hand. For each card discarded, apply 8 Burning to a random enemy.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="25" t="inlineStr">
         <is>
-          <t>Contagion</t>
+          <t>Cleave</t>
         </is>
       </c>
       <c r="B10" s="26" t="inlineStr">
         <is>
-          <t>contagion</t>
+          <t>couper-en-deux</t>
         </is>
       </c>
       <c r="C10" s="17" t="n">
@@ -3855,32 +3905,32 @@
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E10" s="20" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
         </is>
       </c>
       <c r="F10" s="17" t="inlineStr"/>
       <c r="G10" s="18" t="inlineStr">
         <is>
-          <t>Blood Gauntlets</t>
+          <t>War Axe</t>
         </is>
       </c>
       <c r="H10" s="18" t="inlineStr">
         <is>
-          <t>Deal 5 damage. Both adjacent enemies gain Bleed equal to the target's Bleed.</t>
+          <t>Deal 20 damage. If the target dies, deal 15 damage to the next enemy.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="25" t="inlineStr">
         <is>
-          <t>Crimson Carve</t>
+          <t>Contagion</t>
         </is>
       </c>
       <c r="B11" s="26" t="inlineStr">
         <is>
-          <t>carve-cramoisi</t>
+          <t>contagion</t>
         </is>
       </c>
       <c r="C11" s="17" t="n">
@@ -3891,81 +3941,85 @@
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E11" s="20" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
         </is>
       </c>
       <c r="F11" s="17" t="inlineStr"/>
       <c r="G11" s="18" t="inlineStr">
         <is>
-          <t>Blood Plate</t>
+          <t>Blood Gauntlets</t>
         </is>
       </c>
       <c r="H11" s="18" t="inlineStr">
         <is>
-          <t>Deal 9 damage. Apply 3 Bleed.</t>
+          <t>Both adjacent enemies match the target's Bleed.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="25" t="inlineStr">
         <is>
-          <t>Dazzling Kick</t>
+          <t>Dragon's Blaze</t>
         </is>
       </c>
       <c r="B12" s="26" t="inlineStr">
         <is>
-          <t>coup-eblouissant</t>
+          <t>embrasement-dragon</t>
         </is>
       </c>
       <c r="C12" s="17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D12" s="27" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E12" s="21" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="F12" s="17" t="inlineStr"/>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F12" s="17" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
       <c r="G12" s="18" t="inlineStr">
         <is>
-          <t>Crusader Greaves</t>
+          <t>Magma Hammer, Onyx Guard Plate</t>
         </is>
       </c>
       <c r="H12" s="18" t="inlineStr">
         <is>
-          <t>Deal 10 damage. Apply 3 Confusion.</t>
+          <t>Detonate all Burning: deal 2 damage per Burning on ALL enemies.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="25" t="inlineStr">
         <is>
-          <t>Dragon's Blaze</t>
+          <t>Drink blood</t>
         </is>
       </c>
       <c r="B13" s="26" t="inlineStr">
         <is>
-          <t>embrasement-dragon</t>
+          <t>boire-le-sang</t>
         </is>
       </c>
       <c r="C13" s="17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D13" s="27" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E13" s="22" t="inlineStr">
-        <is>
-          <t>Epic</t>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
         </is>
       </c>
       <c r="F13" s="17" t="inlineStr">
@@ -3975,12 +4029,12 @@
       </c>
       <c r="G13" s="18" t="inlineStr">
         <is>
-          <t>Magma Hammer, Onyx Guard Plate</t>
+          <t>Blood Plate</t>
         </is>
       </c>
       <c r="H13" s="18" t="inlineStr">
         <is>
-          <t>Detonate all Burning: deal 2 damage per Burning on ALL enemies.</t>
+          <t>Lose 20 HP. Deal 10 damage and 1 Bleed to ALL enemies. Heal 20 HP per enemy killed by this.</t>
         </is>
       </c>
     </row>
@@ -4216,7 +4270,7 @@
         </is>
       </c>
       <c r="C20" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" s="27" t="inlineStr">
         <is>
@@ -4240,7 +4294,7 @@
       </c>
       <c r="H20" s="18" t="inlineStr">
         <is>
-          <t>Deal 6 damage to ALL enemies.</t>
+          <t>Apply 1 more Confusion to each already-confused enemy.</t>
         </is>
       </c>
     </row>
@@ -4287,36 +4341,36 @@
     <row r="22">
       <c r="A22" s="25" t="inlineStr">
         <is>
-          <t>Hemorrhage</t>
+          <t>Kick of light</t>
         </is>
       </c>
       <c r="B22" s="26" t="inlineStr">
         <is>
-          <t>hemorragie</t>
+          <t>coup-de-lumiere</t>
         </is>
       </c>
       <c r="C22" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22" s="27" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E22" s="20" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
+      <c r="E22" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
         </is>
       </c>
       <c r="F22" s="17" t="inlineStr"/>
       <c r="G22" s="18" t="inlineStr">
         <is>
-          <t>Blood Greaves</t>
+          <t>Crusader Greaves</t>
         </is>
       </c>
       <c r="H22" s="18" t="inlineStr">
         <is>
-          <t>Consume all the target's Bleed: deal 2 damage per Bleed consumed.</t>
+          <t>Deal 6 damage. Apply 1 Confusion.</t>
         </is>
       </c>
     </row>
@@ -4359,52 +4413,56 @@
     <row r="24">
       <c r="A24" s="25" t="inlineStr">
         <is>
-          <t>Lumen Jab</t>
+          <t>Onyx Breath</t>
         </is>
       </c>
       <c r="B24" s="26" t="inlineStr">
         <is>
-          <t>coup-de-lumiere</t>
+          <t>souffle-onyx</t>
         </is>
       </c>
       <c r="C24" s="17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D24" s="27" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E24" s="21" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="F24" s="17" t="inlineStr"/>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F24" s="17" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
       <c r="G24" s="18" t="inlineStr">
         <is>
-          <t>Crusader Gauntlets</t>
+          <t>Onyx Guard Plate</t>
         </is>
       </c>
       <c r="H24" s="18" t="inlineStr">
         <is>
-          <t>Deal 8 damage. Apply 1 Confusion.</t>
+          <t>Apply 20 Burning to ALL enemies.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="25" t="inlineStr">
         <is>
-          <t>Onyx Breath</t>
+          <t>Onyx Fist</t>
         </is>
       </c>
       <c r="B25" s="26" t="inlineStr">
         <is>
-          <t>souffle-onyx</t>
+          <t>poing-onyx</t>
         </is>
       </c>
       <c r="C25" s="17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D25" s="27" t="inlineStr">
         <is>
@@ -4416,31 +4474,27 @@
           <t>Epic</t>
         </is>
       </c>
-      <c r="F25" s="17" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
+      <c r="F25" s="17" t="inlineStr"/>
       <c r="G25" s="18" t="inlineStr">
         <is>
-          <t>Onyx Guard Plate</t>
+          <t>Onyx Glove</t>
         </is>
       </c>
       <c r="H25" s="18" t="inlineStr">
         <is>
-          <t>Apply 20 Burning to ALL enemies.</t>
+          <t>Gain 10 Stone. Deal 10 damage and apply 3 Burning.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="25" t="inlineStr">
         <is>
-          <t>Onyx Fist</t>
+          <t>Onyx Radiance</t>
         </is>
       </c>
       <c r="B26" s="26" t="inlineStr">
         <is>
-          <t>poing-onyx</t>
+          <t>onyx-radiance</t>
         </is>
       </c>
       <c r="C26" s="17" t="n">
@@ -4456,31 +4510,35 @@
           <t>Epic</t>
         </is>
       </c>
-      <c r="F26" s="17" t="inlineStr"/>
+      <c r="F26" s="17" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
       <c r="G26" s="18" t="inlineStr">
         <is>
-          <t>Onyx Glove</t>
+          <t>Big Onyx Sword</t>
         </is>
       </c>
       <c r="H26" s="18" t="inlineStr">
         <is>
-          <t>Gain 10 Stone. Deal 10 damage and apply 3 Burning.</t>
+          <t>Apply 8 Burning to ALL enemies.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="25" t="inlineStr">
         <is>
-          <t>Onyx Radiance</t>
+          <t>Onyx Slash</t>
         </is>
       </c>
       <c r="B27" s="26" t="inlineStr">
         <is>
-          <t>onyx-radiance</t>
+          <t>onyx-slash</t>
         </is>
       </c>
       <c r="C27" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27" s="27" t="inlineStr">
         <is>
@@ -4492,11 +4550,7 @@
           <t>Epic</t>
         </is>
       </c>
-      <c r="F27" s="17" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
+      <c r="F27" s="17" t="inlineStr"/>
       <c r="G27" s="18" t="inlineStr">
         <is>
           <t>Big Onyx Sword</t>
@@ -4504,55 +4558,55 @@
       </c>
       <c r="H27" s="18" t="inlineStr">
         <is>
-          <t>Apply 8 Burning to ALL enemies.</t>
+          <t>Deal 26 damage and 4 Burning. The enemy behind takes half (13 damage, 2 Burning).</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="25" t="inlineStr">
         <is>
-          <t>Onyx Slash</t>
+          <t>Open Veins</t>
         </is>
       </c>
       <c r="B28" s="26" t="inlineStr">
         <is>
-          <t>onyx-slash</t>
+          <t>ouvrir-les-veines</t>
         </is>
       </c>
       <c r="C28" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" s="27" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E28" s="22" t="inlineStr">
-        <is>
-          <t>Epic</t>
+      <c r="E28" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
         </is>
       </c>
       <c r="F28" s="17" t="inlineStr"/>
       <c r="G28" s="18" t="inlineStr">
         <is>
-          <t>Big Onyx Sword</t>
+          <t>Blood Gauntlets</t>
         </is>
       </c>
       <c r="H28" s="18" t="inlineStr">
         <is>
-          <t>Deal 26 damage and 4 Burning. The enemy behind takes half (13 damage, 2 Burning).</t>
+          <t>Take 10 damage. Apply 4 Bleed.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="25" t="inlineStr">
         <is>
-          <t>Open Veins</t>
+          <t>Pickaxe Jab</t>
         </is>
       </c>
       <c r="B29" s="26" t="inlineStr">
         <is>
-          <t>ouvrir-les-veines</t>
+          <t>coup-de-pioche</t>
         </is>
       </c>
       <c r="C29" s="17" t="n">
@@ -4563,72 +4617,76 @@
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E29" s="20" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
+      <c r="E29" s="16" t="inlineStr">
+        <is>
+          <t>Common</t>
         </is>
       </c>
       <c r="F29" s="17" t="inlineStr"/>
       <c r="G29" s="18" t="inlineStr">
         <is>
-          <t>Blood Gauntlets</t>
+          <t>Miner's Pick</t>
         </is>
       </c>
       <c r="H29" s="18" t="inlineStr">
         <is>
-          <t>Deal 3 damage. Apply 4 Bleed.</t>
+          <t>Deal 3 damage twice. If the target dies, hit a random other enemy for 3.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="25" t="inlineStr">
         <is>
-          <t>Pickaxe Jab</t>
+          <t>Poison Dance</t>
         </is>
       </c>
       <c r="B30" s="26" t="inlineStr">
         <is>
-          <t>coup-de-pioche</t>
+          <t>danse-empoisonnee</t>
         </is>
       </c>
       <c r="C30" s="17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D30" s="27" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E30" s="16" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="F30" s="17" t="inlineStr"/>
+      <c r="E30" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F30" s="17" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
       <c r="G30" s="18" t="inlineStr">
         <is>
-          <t>Miner's Pick</t>
+          <t>Basilisk Fang</t>
         </is>
       </c>
       <c r="H30" s="18" t="inlineStr">
         <is>
-          <t>Deal 3 damage twice. If the target dies, hit a random other enemy for 3.</t>
+          <t>Hit ALL enemies 3 times for 3 damage. Apply 1 Poison per hit (2 if the enemy was already poisoned).</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="25" t="inlineStr">
         <is>
-          <t>Poison Dance</t>
+          <t>Pommel Strike</t>
         </is>
       </c>
       <c r="B31" s="26" t="inlineStr">
         <is>
-          <t>danse-empoisonnee</t>
+          <t>coup-de-pommeau</t>
         </is>
       </c>
       <c r="C31" s="17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D31" s="27" t="inlineStr">
         <is>
@@ -4640,71 +4698,67 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="F31" s="17" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
+      <c r="F31" s="17" t="inlineStr"/>
       <c r="G31" s="18" t="inlineStr">
         <is>
-          <t>Basilisk Fang</t>
+          <t>War Axe</t>
         </is>
       </c>
       <c r="H31" s="18" t="inlineStr">
         <is>
-          <t>Hit ALL enemies 3 times for 3 damage. Apply 1 Poison per hit (2 if the enemy was already poisoned).</t>
+          <t>Deal 16 damage. Stun the target for 2 turns.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="25" t="inlineStr">
         <is>
-          <t>Pommel Strike</t>
+          <t>Punch</t>
         </is>
       </c>
       <c r="B32" s="26" t="inlineStr">
         <is>
-          <t>coup-de-pommeau</t>
+          <t>coup-faible</t>
         </is>
       </c>
       <c r="C32" s="17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D32" s="27" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E32" s="21" t="inlineStr">
-        <is>
-          <t>Rare</t>
+      <c r="E32" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="F32" s="17" t="inlineStr"/>
       <c r="G32" s="18" t="inlineStr">
         <is>
-          <t>War Axe</t>
+          <t>— (deck de base)</t>
         </is>
       </c>
       <c r="H32" s="18" t="inlineStr">
         <is>
-          <t>Deal 16 damage. Stun the target for 2 turns.</t>
+          <t>Deal 3 damage.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="25" t="inlineStr">
         <is>
-          <t>Punch</t>
+          <t>Radiant Strike</t>
         </is>
       </c>
       <c r="B33" s="26" t="inlineStr">
         <is>
-          <t>coup-faible</t>
+          <t>frappe-radiante</t>
         </is>
       </c>
       <c r="C33" s="17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D33" s="27" t="inlineStr">
         <is>
@@ -4719,24 +4773,24 @@
       <c r="F33" s="17" t="inlineStr"/>
       <c r="G33" s="18" t="inlineStr">
         <is>
-          <t>— (deck de base)</t>
+          <t>— (non équipée)</t>
         </is>
       </c>
       <c r="H33" s="18" t="inlineStr">
         <is>
-          <t>Deal 3 damage.</t>
+          <t>Deal 14 damage. Apply 2 Confusion.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="25" t="inlineStr">
         <is>
-          <t>Radiant Strike</t>
+          <t>Rusty Cleave</t>
         </is>
       </c>
       <c r="B34" s="26" t="inlineStr">
         <is>
-          <t>frappe-radiante</t>
+          <t>coup-de-hache</t>
         </is>
       </c>
       <c r="C34" s="17" t="n">
@@ -4747,32 +4801,32 @@
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E34" s="21" t="inlineStr">
-        <is>
-          <t>Rare</t>
+      <c r="E34" s="16" t="inlineStr">
+        <is>
+          <t>Common</t>
         </is>
       </c>
       <c r="F34" s="17" t="inlineStr"/>
       <c r="G34" s="18" t="inlineStr">
         <is>
-          <t>Crusader Plate</t>
+          <t>Rusty Axe</t>
         </is>
       </c>
       <c r="H34" s="18" t="inlineStr">
         <is>
-          <t>Deal 14 damage. Apply 2 Confusion.</t>
+          <t>Deal 6 damage to the target and 4 damage to each adjacent enemy.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="25" t="inlineStr">
         <is>
-          <t>Rusty Cleave</t>
+          <t>Shield Bash</t>
         </is>
       </c>
       <c r="B35" s="26" t="inlineStr">
         <is>
-          <t>coup-de-hache</t>
+          <t>coup-de-bouclier</t>
         </is>
       </c>
       <c r="C35" s="17" t="n">
@@ -4783,104 +4837,104 @@
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E35" s="16" t="inlineStr">
-        <is>
-          <t>Common</t>
+      <c r="E35" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
         </is>
       </c>
       <c r="F35" s="17" t="inlineStr"/>
       <c r="G35" s="18" t="inlineStr">
         <is>
-          <t>Rusty Axe</t>
+          <t>Tower Shield</t>
         </is>
       </c>
       <c r="H35" s="18" t="inlineStr">
         <is>
-          <t>Deal 6 damage to the target and 4 damage to each adjacent enemy.</t>
+          <t>Deal 10 damage. Stun the enemy for 3 turns.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="25" t="inlineStr">
         <is>
-          <t>Shield Bash</t>
+          <t>Splash Strike</t>
         </is>
       </c>
       <c r="B36" s="26" t="inlineStr">
         <is>
-          <t>coup-de-bouclier</t>
+          <t>eclaboussure-de-frappe</t>
         </is>
       </c>
       <c r="C36" s="17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D36" s="27" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E36" s="21" t="inlineStr">
-        <is>
-          <t>Rare</t>
+      <c r="E36" s="20" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="F36" s="17" t="inlineStr"/>
       <c r="G36" s="18" t="inlineStr">
         <is>
-          <t>Tower Shield</t>
+          <t>Forge Hammer</t>
         </is>
       </c>
       <c r="H36" s="18" t="inlineStr">
         <is>
-          <t>Deal 10 damage. Stun the enemy for 3 turns.</t>
+          <t>Deal 15 damage. Each adjacent enemy has a 50% chance to take 5 Burning.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="25" t="inlineStr">
         <is>
-          <t>Splash Strike</t>
+          <t>Strike</t>
         </is>
       </c>
       <c r="B37" s="26" t="inlineStr">
         <is>
-          <t>eclaboussure-de-frappe</t>
+          <t>frappe</t>
         </is>
       </c>
       <c r="C37" s="17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D37" s="27" t="inlineStr">
         <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E37" s="20" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
+      <c r="E37" s="16" t="inlineStr">
+        <is>
+          <t>Common</t>
         </is>
       </c>
       <c r="F37" s="17" t="inlineStr"/>
       <c r="G37" s="18" t="inlineStr">
         <is>
-          <t>Forge Hammer</t>
+          <t>Rusty Axe, Forge Hammer, Miner's Pick</t>
         </is>
       </c>
       <c r="H37" s="18" t="inlineStr">
         <is>
-          <t>Deal 15 damage. Each adjacent enemy has a 50% chance to take 5 Burning.</t>
+          <t>Deal 6 damage.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="25" t="inlineStr">
         <is>
-          <t>Strike</t>
+          <t>Venom Stab</t>
         </is>
       </c>
       <c r="B38" s="26" t="inlineStr">
         <is>
-          <t>frappe</t>
+          <t>coup-venimeux</t>
         </is>
       </c>
       <c r="C38" s="17" t="n">
@@ -4891,36 +4945,36 @@
           <t>Attaque</t>
         </is>
       </c>
-      <c r="E38" s="16" t="inlineStr">
-        <is>
-          <t>Common</t>
+      <c r="E38" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
         </is>
       </c>
       <c r="F38" s="17" t="inlineStr"/>
       <c r="G38" s="18" t="inlineStr">
         <is>
-          <t>Rusty Axe, Forge Hammer, Miner's Pick</t>
+          <t>Basilisk Fang</t>
         </is>
       </c>
       <c r="H38" s="18" t="inlineStr">
         <is>
-          <t>Deal 6 damage.</t>
+          <t>Deal 4 damage. Apply 4 Poison.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="25" t="inlineStr">
         <is>
-          <t>Venom Stab</t>
+          <t>Wound Opening</t>
         </is>
       </c>
       <c r="B39" s="26" t="inlineStr">
         <is>
-          <t>coup-venimeux</t>
+          <t>ouverture-des-plaies</t>
         </is>
       </c>
       <c r="C39" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D39" s="27" t="inlineStr">
         <is>
@@ -4940,27 +4994,27 @@
       </c>
       <c r="H39" s="18" t="inlineStr">
         <is>
-          <t>Deal 4 damage. Apply 4 Poison.</t>
+          <t>Deal 18 damage. Doubled if the target has a negative status.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="25" t="inlineStr">
         <is>
-          <t>Wound Opening</t>
+          <t>Armor of light</t>
         </is>
       </c>
       <c r="B40" s="26" t="inlineStr">
         <is>
-          <t>ouverture-des-plaies</t>
+          <t>armure-de-lumiere</t>
         </is>
       </c>
       <c r="C40" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D40" s="27" t="inlineStr">
-        <is>
-          <t>Attaque</t>
+        <v>1</v>
+      </c>
+      <c r="D40" s="29" t="inlineStr">
+        <is>
+          <t>Défense</t>
         </is>
       </c>
       <c r="E40" s="21" t="inlineStr">
@@ -4971,12 +5025,12 @@
       <c r="F40" s="17" t="inlineStr"/>
       <c r="G40" s="18" t="inlineStr">
         <is>
-          <t>Basilisk Fang</t>
+          <t>Crusader Plate</t>
         </is>
       </c>
       <c r="H40" s="18" t="inlineStr">
         <is>
-          <t>Deal 18 damage. Doubled if the target has a negative status.</t>
+          <t>Gain 6 Stone. Dazzle the nearest enemy (2 Confusion).</t>
         </is>
       </c>
     </row>
@@ -5007,7 +5061,7 @@
       <c r="F41" s="17" t="inlineStr"/>
       <c r="G41" s="18" t="inlineStr">
         <is>
-          <t>— (deck de base)</t>
+          <t>— (non équipée)</t>
         </is>
       </c>
       <c r="H41" s="18" t="inlineStr">
@@ -5079,7 +5133,7 @@
       <c r="F43" s="17" t="inlineStr"/>
       <c r="G43" s="18" t="inlineStr">
         <is>
-          <t>Forgemaster's Mail</t>
+          <t>Forgemaster's Mail, Crusader Plate, Blood Plate</t>
         </is>
       </c>
       <c r="H43" s="18" t="inlineStr">
@@ -5091,48 +5145,48 @@
     <row r="44">
       <c r="A44" s="25" t="inlineStr">
         <is>
-          <t>Light Armor</t>
+          <t>Holy light</t>
         </is>
       </c>
       <c r="B44" s="26" t="inlineStr">
         <is>
-          <t>armure-legere</t>
+          <t>lumiere-sacree</t>
         </is>
       </c>
       <c r="C44" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D44" s="29" t="inlineStr">
         <is>
           <t>Défense</t>
         </is>
       </c>
-      <c r="E44" s="16" t="inlineStr">
-        <is>
-          <t>Common</t>
+      <c r="E44" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
         </is>
       </c>
       <c r="F44" s="17" t="inlineStr"/>
       <c r="G44" s="18" t="inlineStr">
         <is>
-          <t>Traveler's Garb</t>
+          <t>Crusader Plate</t>
         </is>
       </c>
       <c r="H44" s="18" t="inlineStr">
         <is>
-          <t>Gain 5 Stone.</t>
+          <t>Heal 30 HP.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="25" t="inlineStr">
         <is>
-          <t>Mail Armor</t>
+          <t>Light Armor</t>
         </is>
       </c>
       <c r="B45" s="26" t="inlineStr">
         <is>
-          <t>mail-armor</t>
+          <t>armure-legere</t>
         </is>
       </c>
       <c r="C45" s="17" t="n">
@@ -5143,108 +5197,108 @@
           <t>Défense</t>
         </is>
       </c>
-      <c r="E45" s="21" t="inlineStr">
-        <is>
-          <t>Rare</t>
+      <c r="E45" s="16" t="inlineStr">
+        <is>
+          <t>Common</t>
         </is>
       </c>
       <c r="F45" s="17" t="inlineStr"/>
       <c r="G45" s="18" t="inlineStr">
         <is>
-          <t>Forgemaster's Mail</t>
+          <t>Traveler's Garb</t>
         </is>
       </c>
       <c r="H45" s="18" t="inlineStr">
         <is>
-          <t>Gain 7 Stone for every enemy still alive.</t>
+          <t>Gain 5 Stone.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="25" t="inlineStr">
         <is>
-          <t>Onyx Armor</t>
+          <t>Mail Armor</t>
         </is>
       </c>
       <c r="B46" s="26" t="inlineStr">
         <is>
-          <t>onyx-armor</t>
+          <t>mail-armor</t>
         </is>
       </c>
       <c r="C46" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D46" s="29" t="inlineStr">
         <is>
           <t>Défense</t>
         </is>
       </c>
-      <c r="E46" s="22" t="inlineStr">
-        <is>
-          <t>Epic</t>
+      <c r="E46" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
         </is>
       </c>
       <c r="F46" s="17" t="inlineStr"/>
       <c r="G46" s="18" t="inlineStr">
         <is>
-          <t>Onyx Guard Plate</t>
+          <t>Forgemaster's Mail</t>
         </is>
       </c>
       <c r="H46" s="18" t="inlineStr">
         <is>
-          <t>Gain 30 Stone.</t>
+          <t>Gain 7 Stone for every enemy still alive.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="25" t="inlineStr">
         <is>
-          <t>Quench</t>
+          <t>Onyx Armor</t>
         </is>
       </c>
       <c r="B47" s="26" t="inlineStr">
         <is>
-          <t>trempe</t>
+          <t>onyx-armor</t>
         </is>
       </c>
       <c r="C47" s="17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D47" s="29" t="inlineStr">
         <is>
           <t>Défense</t>
         </is>
       </c>
-      <c r="E47" s="21" t="inlineStr">
-        <is>
-          <t>Rare</t>
+      <c r="E47" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
         </is>
       </c>
       <c r="F47" s="17" t="inlineStr"/>
       <c r="G47" s="18" t="inlineStr">
         <is>
-          <t>Forgemaster's Mail</t>
+          <t>Onyx Guard Plate</t>
         </is>
       </c>
       <c r="H47" s="18" t="inlineStr">
         <is>
-          <t>Spend all Forge Heat. Gain 10 Stone per Heat spent.</t>
+          <t>Gain 30 Stone.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="25" t="inlineStr">
         <is>
-          <t>Sacred Ground</t>
+          <t>Quench</t>
         </is>
       </c>
       <c r="B48" s="26" t="inlineStr">
         <is>
-          <t>terre-sacree</t>
+          <t>trempe</t>
         </is>
       </c>
       <c r="C48" s="17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D48" s="29" t="inlineStr">
         <is>
@@ -5259,12 +5313,12 @@
       <c r="F48" s="17" t="inlineStr"/>
       <c r="G48" s="18" t="inlineStr">
         <is>
-          <t>Crusader Plate</t>
+          <t>Forgemaster's Mail</t>
         </is>
       </c>
       <c r="H48" s="18" t="inlineStr">
         <is>
-          <t>Gain 18 Stone.</t>
+          <t>Spend all Forge Heat. Gain 10 Stone per Heat spent.</t>
         </is>
       </c>
     </row>
@@ -5280,16 +5334,16 @@
         </is>
       </c>
       <c r="C49" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D49" s="29" t="inlineStr">
         <is>
           <t>Défense</t>
         </is>
       </c>
-      <c r="E49" s="20" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
+      <c r="E49" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
         </is>
       </c>
       <c r="F49" s="17" t="inlineStr"/>
@@ -5300,7 +5354,7 @@
       </c>
       <c r="H49" s="18" t="inlineStr">
         <is>
-          <t>Gain 1 Stone per Bleed among ALL enemies.</t>
+          <t>Per Bleed among ALL enemies: gain 3 Stone and heal 2 HP.</t>
         </is>
       </c>
     </row>
@@ -5379,48 +5433,48 @@
     <row r="52">
       <c r="A52" s="25" t="inlineStr">
         <is>
-          <t>Blood Rush</t>
+          <t>Blood Absorption</t>
         </is>
       </c>
       <c r="B52" s="26" t="inlineStr">
         <is>
-          <t>ruee-de-sang</t>
+          <t>absorption-de-sang</t>
         </is>
       </c>
       <c r="C52" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D52" s="30" t="inlineStr">
         <is>
           <t>Buff</t>
         </is>
       </c>
-      <c r="E52" s="20" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
+      <c r="E52" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
         </is>
       </c>
       <c r="F52" s="17" t="inlineStr"/>
       <c r="G52" s="18" t="inlineStr">
         <is>
-          <t>Blood Greaves</t>
+          <t>Blood Gauntlets</t>
         </is>
       </c>
       <c r="H52" s="18" t="inlineStr">
         <is>
-          <t>Gain 1 Forge Heat per 5 Bleed among ALL enemies.</t>
+          <t>Heal 5 HP per Bleed among ALL enemies, then remove all their Bleed.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="25" t="inlineStr">
         <is>
-          <t>Boost</t>
+          <t>Blood Rush</t>
         </is>
       </c>
       <c r="B53" s="26" t="inlineStr">
         <is>
-          <t>boost</t>
+          <t>ruee-de-sang</t>
         </is>
       </c>
       <c r="C53" s="17" t="n">
@@ -5439,84 +5493,84 @@
       <c r="F53" s="17" t="inlineStr"/>
       <c r="G53" s="18" t="inlineStr">
         <is>
-          <t>Onyx Boots, Mail Boots</t>
+          <t>Blood Greaves</t>
         </is>
       </c>
       <c r="H53" s="18" t="inlineStr">
         <is>
-          <t>Gain 3 Forge Heat (energy).</t>
+          <t>Gain 1 Forge Heat per 5 Bleed among ALL enemies.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="25" t="inlineStr">
         <is>
-          <t>Burning Run</t>
+          <t>Boost</t>
         </is>
       </c>
       <c r="B54" s="26" t="inlineStr">
         <is>
-          <t>course-ardente</t>
+          <t>boost</t>
         </is>
       </c>
       <c r="C54" s="17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D54" s="30" t="inlineStr">
         <is>
           <t>Buff</t>
         </is>
       </c>
-      <c r="E54" s="22" t="inlineStr">
-        <is>
-          <t>Epic</t>
+      <c r="E54" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
         </is>
       </c>
       <c r="F54" s="17" t="inlineStr"/>
       <c r="G54" s="18" t="inlineStr">
         <is>
-          <t>Onyx Boots</t>
+          <t>Onyx Boots, Mail Boots, Crusader Greaves, Blood Greaves</t>
         </is>
       </c>
       <c r="H54" s="18" t="inlineStr">
         <is>
-          <t>Haste for as many turns as your current Forge Heat.</t>
+          <t>Gain 3 Forge Heat (energy).</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="25" t="inlineStr">
         <is>
-          <t>Crusader's Charge</t>
+          <t>Burning Run</t>
         </is>
       </c>
       <c r="B55" s="26" t="inlineStr">
         <is>
-          <t>charge-du-croise</t>
+          <t>course-ardente</t>
         </is>
       </c>
       <c r="C55" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D55" s="30" t="inlineStr">
         <is>
           <t>Buff</t>
         </is>
       </c>
-      <c r="E55" s="21" t="inlineStr">
-        <is>
-          <t>Rare</t>
+      <c r="E55" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
         </is>
       </c>
       <c r="F55" s="17" t="inlineStr"/>
       <c r="G55" s="18" t="inlineStr">
         <is>
-          <t>Crusader Greaves</t>
+          <t>Onyx Boots</t>
         </is>
       </c>
       <c r="H55" s="18" t="inlineStr">
         <is>
-          <t>Haste: +30% attack speed for 3 turns.</t>
+          <t>Haste for as many turns as your current Forge Heat.</t>
         </is>
       </c>
     </row>
@@ -5631,12 +5685,12 @@
     <row r="59">
       <c r="A59" s="25" t="inlineStr">
         <is>
-          <t>Mail Advantage</t>
+          <t>Lay on Hands</t>
         </is>
       </c>
       <c r="B59" s="26" t="inlineStr">
         <is>
-          <t>avantage-maille</t>
+          <t>imposition-des-mains</t>
         </is>
       </c>
       <c r="C59" s="17" t="n">
@@ -5655,24 +5709,24 @@
       <c r="F59" s="17" t="inlineStr"/>
       <c r="G59" s="18" t="inlineStr">
         <is>
-          <t>Mail Glove, Mail Boots</t>
+          <t>Crusader Gauntlets</t>
         </is>
       </c>
       <c r="H59" s="18" t="inlineStr">
         <is>
-          <t>Gain 8 Stone and Haste for 2 turns.</t>
+          <t>Remove one random negative status from the hero.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="25" t="inlineStr">
         <is>
-          <t>Master's Hand</t>
+          <t>Mail Advantage</t>
         </is>
       </c>
       <c r="B60" s="26" t="inlineStr">
         <is>
-          <t>main-de-maitre</t>
+          <t>avantage-maille</t>
         </is>
       </c>
       <c r="C60" s="17" t="n">
@@ -5683,180 +5737,180 @@
           <t>Buff</t>
         </is>
       </c>
-      <c r="E60" s="16" t="inlineStr">
-        <is>
-          <t>Common</t>
+      <c r="E60" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
         </is>
       </c>
       <c r="F60" s="17" t="inlineStr"/>
       <c r="G60" s="18" t="inlineStr">
         <is>
-          <t>Miner's Gloves, Mail Glove</t>
+          <t>Mail Glove, Mail Boots</t>
         </is>
       </c>
       <c r="H60" s="18" t="inlineStr">
         <is>
-          <t>Draw 2 cards.</t>
+          <t>Gain 8 Stone and Haste for 2 turns.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="25" t="inlineStr">
         <is>
-          <t>Onyx Overheat</t>
+          <t>Master's Hand</t>
         </is>
       </c>
       <c r="B61" s="26" t="inlineStr">
         <is>
-          <t>onyx-overheat</t>
+          <t>main-de-maitre</t>
         </is>
       </c>
       <c r="C61" s="17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D61" s="30" t="inlineStr">
         <is>
           <t>Buff</t>
         </is>
       </c>
-      <c r="E61" s="22" t="inlineStr">
-        <is>
-          <t>Epic</t>
+      <c r="E61" s="16" t="inlineStr">
+        <is>
+          <t>Common</t>
         </is>
       </c>
       <c r="F61" s="17" t="inlineStr"/>
       <c r="G61" s="18" t="inlineStr">
         <is>
-          <t>Big Onyx Sword</t>
+          <t>Miner's Gloves, Mail Glove, Crusader Gauntlets</t>
         </is>
       </c>
       <c r="H61" s="18" t="inlineStr">
         <is>
-          <t>Gain 5 Forge Heat (energy).</t>
+          <t>Draw 2 cards.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="25" t="inlineStr">
         <is>
-          <t>Outnumbered</t>
+          <t>Onyx Overheat</t>
         </is>
       </c>
       <c r="B62" s="26" t="inlineStr">
         <is>
-          <t>surnombre</t>
+          <t>onyx-overheat</t>
         </is>
       </c>
       <c r="C62" s="17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D62" s="30" t="inlineStr">
         <is>
           <t>Buff</t>
         </is>
       </c>
-      <c r="E62" s="21" t="inlineStr">
-        <is>
-          <t>Rare</t>
+      <c r="E62" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
         </is>
       </c>
       <c r="F62" s="17" t="inlineStr"/>
       <c r="G62" s="18" t="inlineStr">
         <is>
-          <t>Mail Glove</t>
+          <t>Big Onyx Sword</t>
         </is>
       </c>
       <c r="H62" s="18" t="inlineStr">
         <is>
-          <t>Draw 1 card per living enemy.</t>
+          <t>Gain 5 Forge Heat (energy).</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="25" t="inlineStr">
         <is>
-          <t>Perfect Sapphire Surge</t>
+          <t>Outnumbered</t>
         </is>
       </c>
       <c r="B63" s="26" t="inlineStr">
         <is>
-          <t>surge-saphir-parfait</t>
+          <t>surnombre</t>
         </is>
       </c>
       <c r="C63" s="17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D63" s="30" t="inlineStr">
         <is>
           <t>Buff</t>
         </is>
       </c>
-      <c r="E63" s="22" t="inlineStr">
-        <is>
-          <t>Epic</t>
+      <c r="E63" s="21" t="inlineStr">
+        <is>
+          <t>Rare</t>
         </is>
       </c>
       <c r="F63" s="17" t="inlineStr"/>
       <c r="G63" s="18" t="inlineStr">
         <is>
-          <t>Perfect Sapphire Amulet</t>
+          <t>Mail Glove</t>
         </is>
       </c>
       <c r="H63" s="18" t="inlineStr">
         <is>
-          <t>Gain 3 Forge Heat (energy).</t>
+          <t>Draw 1 card per living enemy.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="25" t="inlineStr">
         <is>
-          <t>Quicken</t>
+          <t>Perfect Sapphire Surge</t>
         </is>
       </c>
       <c r="B64" s="26" t="inlineStr">
         <is>
-          <t>celerite-vive</t>
+          <t>surge-saphir-parfait</t>
         </is>
       </c>
       <c r="C64" s="17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D64" s="30" t="inlineStr">
         <is>
           <t>Buff</t>
         </is>
       </c>
-      <c r="E64" s="20" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
+      <c r="E64" s="22" t="inlineStr">
+        <is>
+          <t>Epic</t>
         </is>
       </c>
       <c r="F64" s="17" t="inlineStr"/>
       <c r="G64" s="18" t="inlineStr">
         <is>
-          <t>Swift Boots, Mail Boots</t>
+          <t>Perfect Sapphire Amulet</t>
         </is>
       </c>
       <c r="H64" s="18" t="inlineStr">
         <is>
-          <t>Haste: +30% attack speed for 3 turns.</t>
+          <t>Gain 3 Forge Heat (energy).</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="25" t="inlineStr">
         <is>
-          <t>Sapphire Surge</t>
+          <t>Quicken</t>
         </is>
       </c>
       <c r="B65" s="26" t="inlineStr">
         <is>
-          <t>surge-saphir</t>
+          <t>celerite-vive</t>
         </is>
       </c>
       <c r="C65" s="17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D65" s="30" t="inlineStr">
         <is>
@@ -5871,24 +5925,24 @@
       <c r="F65" s="17" t="inlineStr"/>
       <c r="G65" s="18" t="inlineStr">
         <is>
-          <t>Sapphire Amulet, Nice Sapphire Amulet</t>
+          <t>Swift Boots, Mail Boots, Crusader Greaves, Blood Greaves</t>
         </is>
       </c>
       <c r="H65" s="18" t="inlineStr">
         <is>
-          <t>Gain 2 Forge Heat (energy).</t>
+          <t>Haste: +30% attack speed for 3 turns.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="25" t="inlineStr">
         <is>
-          <t>Second Wind</t>
+          <t>Sapphire Surge</t>
         </is>
       </c>
       <c r="B66" s="26" t="inlineStr">
         <is>
-          <t>second-souffle</t>
+          <t>surge-saphir</t>
         </is>
       </c>
       <c r="C66" s="17" t="n">
@@ -5907,10 +5961,46 @@
       <c r="F66" s="17" t="inlineStr"/>
       <c r="G66" s="18" t="inlineStr">
         <is>
+          <t>Sapphire Amulet, Nice Sapphire Amulet</t>
+        </is>
+      </c>
+      <c r="H66" s="18" t="inlineStr">
+        <is>
+          <t>Gain 2 Forge Heat (energy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="25" t="inlineStr">
+        <is>
+          <t>Second Wind</t>
+        </is>
+      </c>
+      <c r="B67" s="26" t="inlineStr">
+        <is>
+          <t>second-souffle</t>
+        </is>
+      </c>
+      <c r="C67" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" s="30" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="E67" s="20" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F67" s="17" t="inlineStr"/>
+      <c r="G67" s="18" t="inlineStr">
+        <is>
           <t>Swift Boots</t>
         </is>
       </c>
-      <c r="H66" s="18" t="inlineStr">
+      <c r="H67" s="18" t="inlineStr">
         <is>
           <t>Trade 5 Haste turns for 3 Forge Heat. No effect below 5 Haste.</t>
         </is>
@@ -6038,7 +6128,7 @@
       </c>
       <c r="D6" s="18" t="inlineStr">
         <is>
-          <t>When hit by a melee attack, the attacker is Dazzled (1 Confusion).</t>
+          <t>When hit by a melee attack, the attacker has a 50% chance to be Dazzled (1 Confusion).</t>
         </is>
       </c>
     </row>

--- a/docs/BRUTAL-items-et-cartes.xlsx
+++ b/docs/BRUTAL-items-et-cartes.xlsx
@@ -7371,7 +7371,7 @@
         <v>290</v>
       </c>
       <c r="F96" s="13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G96" s="13" t="s">
         <v>73</v>

--- a/docs/BRUTAL-items-et-cartes.xlsx
+++ b/docs/BRUTAL-items-et-cartes.xlsx
@@ -3608,10 +3608,14 @@
       </c>
       <c r="B59" s="15" t="inlineStr">
         <is>
-          <t>Opening wounds</t>
-        </is>
-      </c>
-      <c r="C59" s="15" t="n"/>
+          <t>Opening Wounds</t>
+        </is>
+      </c>
+      <c r="C59" s="15" t="inlineStr">
+        <is>
+          <t>ouvrir-les-plaies</t>
+        </is>
+      </c>
       <c r="D59" s="15" t="n">
         <v>2</v>
       </c>
@@ -7523,7 +7527,11 @@
           <t>Get ahead</t>
         </is>
       </c>
-      <c r="C147" s="15" t="n"/>
+      <c r="C147" s="15" t="inlineStr">
+        <is>
+          <t>prendre-l-avance</t>
+        </is>
+      </c>
       <c r="D147" s="15" t="n">
         <v>2</v>
       </c>
@@ -7550,7 +7558,7 @@
       </c>
       <c r="J147" s="16" t="inlineStr">
         <is>
-          <t>Gagne 3 haste et stun l'ennemi selectioné pendant 3 tours</t>
+          <t>Gain 3 Haste. Stun the target for 3 turns.</t>
         </is>
       </c>
     </row>
@@ -8201,7 +8209,7 @@
         </is>
       </c>
       <c r="D163" s="21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E163" s="21" t="inlineStr">
         <is>
@@ -8226,7 +8234,7 @@
       </c>
       <c r="J163" s="22" t="inlineStr">
         <is>
-          <t>Discard your hand and draw that many cards.</t>
+          <t>Discard your hand and draw double the discarded cards.</t>
         </is>
       </c>
     </row>

--- a/docs/BRUTAL-items-et-cartes.xlsx
+++ b/docs/BRUTAL-items-et-cartes.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -83,8 +83,12 @@
       <color rgb="FF006B5E"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF1B4D1B"/>
+    </font>
   </fonts>
-  <fills count="28">
+  <fills count="30">
     <fill>
       <patternFill/>
     </fill>
@@ -221,6 +225,16 @@
         <fgColor rgb="FF40E0D0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF63BE7B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF08080"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -249,7 +263,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -358,6 +372,15 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="27" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1026,7 +1049,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J171"/>
+  <dimension ref="A1:K171"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" style="57" min="1" max="1"/>
@@ -1039,6 +1062,7 @@
     <col width="6" customWidth="1" style="57" min="8" max="8"/>
     <col width="42" customWidth="1" style="57" min="9" max="9"/>
     <col width="58" customWidth="1" style="57" min="10" max="10"/>
+    <col width="8" customWidth="1" style="57" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="21.95" customHeight="1" s="57">
@@ -1097,6 +1121,11 @@
       <c r="J2" s="10" t="inlineStr">
         <is>
           <t>Effet</t>
+        </is>
+      </c>
+      <c r="K2" s="58" t="inlineStr">
+        <is>
+          <t>Visuel</t>
         </is>
       </c>
     </row>
@@ -1115,6 +1144,7 @@
       <c r="H3" s="12" t="n"/>
       <c r="I3" s="12" t="n"/>
       <c r="J3" s="12" t="n"/>
+      <c r="K3" s="11" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1" s="57">
       <c r="A4" s="13" t="inlineStr">
@@ -1161,6 +1191,11 @@
           <t>Deal 3 damage.</t>
         </is>
       </c>
+      <c r="K4" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="57">
       <c r="A5" s="13" t="inlineStr">
@@ -1207,6 +1242,11 @@
           <t>Deal 4 damage twice.</t>
         </is>
       </c>
+      <c r="K5" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="57">
       <c r="A6" s="13" t="inlineStr">
@@ -1253,6 +1293,11 @@
           <t>Deal 12 damage.</t>
         </is>
       </c>
+      <c r="K6" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="57">
       <c r="A7" s="13" t="inlineStr">
@@ -1299,6 +1344,11 @@
           <t>Deal 3 damage twice. If the target dies, hit a random other enemy for 3.</t>
         </is>
       </c>
+      <c r="K7" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="57">
       <c r="A8" s="13" t="inlineStr">
@@ -1345,6 +1395,11 @@
           <t>Deal 7 damage to the target and the enemy behind it.</t>
         </is>
       </c>
+      <c r="K8" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="57">
       <c r="A9" s="13" t="inlineStr">
@@ -1391,6 +1446,11 @@
           <t>Deal 6 damage to the target and 4 damage to each adjacent enemy.</t>
         </is>
       </c>
+      <c r="K9" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="57">
       <c r="A10" s="13" t="inlineStr">
@@ -1437,6 +1497,11 @@
           <t>Deal 8 damage.</t>
         </is>
       </c>
+      <c r="K10" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="57">
       <c r="A11" s="13" t="inlineStr">
@@ -1483,6 +1548,11 @@
           <t>Deal 20 damage.</t>
         </is>
       </c>
+      <c r="K11" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="57">
       <c r="A12" s="13" t="inlineStr">
@@ -1529,6 +1599,11 @@
           <t>Deal 6 damage.</t>
         </is>
       </c>
+      <c r="K12" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="57">
       <c r="A13" s="15" t="inlineStr">
@@ -1575,6 +1650,11 @@
           <t>Deal 20 damage.</t>
         </is>
       </c>
+      <c r="K13" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="57">
       <c r="A14" s="15" t="inlineStr">
@@ -1621,6 +1701,11 @@
           <t>Deal 9 damage.</t>
         </is>
       </c>
+      <c r="K14" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="57">
       <c r="A15" s="15" t="inlineStr">
@@ -1667,6 +1752,11 @@
           <t>Deal 18 damage. Doubled if you have 6+ Strength.</t>
         </is>
       </c>
+      <c r="K15" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="57">
       <c r="A16" s="15" t="inlineStr">
@@ -1713,6 +1803,11 @@
           <t>Deal 10 damage. Doubled if the target is below 50% HP.</t>
         </is>
       </c>
+      <c r="K16" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="57">
       <c r="A17" s="15" t="inlineStr">
@@ -1759,6 +1854,11 @@
           <t>Deal 3 damage three times.</t>
         </is>
       </c>
+      <c r="K17" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="57">
       <c r="A18" s="15" t="inlineStr">
@@ -1805,6 +1905,11 @@
           <t>Deal 12 damage to the target and the enemy behind it.</t>
         </is>
       </c>
+      <c r="K18" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="57">
       <c r="A19" s="15" t="inlineStr">
@@ -1851,6 +1956,11 @@
           <t>Deal 14 damage. Lose 4 HP.</t>
         </is>
       </c>
+      <c r="K19" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="57">
       <c r="A20" s="15" t="inlineStr">
@@ -1897,6 +2007,11 @@
           <t>Deal 5 damage three times.</t>
         </is>
       </c>
+      <c r="K20" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="57">
       <c r="A21" s="15" t="inlineStr">
@@ -1943,6 +2058,11 @@
           <t>Deal 14 damage to the target and 6 to each adjacent enemy.</t>
         </is>
       </c>
+      <c r="K21" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="57">
       <c r="A22" s="15" t="inlineStr">
@@ -1993,6 +2113,11 @@
           <t>Deal 8 damage to ALL enemies. Et ajoute 2 saignement</t>
         </is>
       </c>
+      <c r="K22" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="57">
       <c r="A23" s="17" t="inlineStr">
@@ -2039,6 +2164,11 @@
           <t>Deal 30 damage. If the target dies, deal 15 damage to the next enemy.</t>
         </is>
       </c>
+      <c r="K23" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="57">
       <c r="A24" s="17" t="inlineStr">
@@ -2085,6 +2215,11 @@
           <t>Deal 16 damage. Doubled if the target has a negative status.</t>
         </is>
       </c>
+      <c r="K24" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="17.1" customHeight="1" s="57">
       <c r="A25" s="21" t="inlineStr">
@@ -2129,6 +2264,11 @@
       <c r="J25" s="21" t="inlineStr">
         <is>
           <t>Deal 30 damage. Doubled if the target is below 50% HP.</t>
+        </is>
+      </c>
+      <c r="K25" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
         </is>
       </c>
     </row>
@@ -2147,6 +2287,7 @@
       <c r="H26" s="20" t="n"/>
       <c r="I26" s="20" t="n"/>
       <c r="J26" s="20" t="n"/>
+      <c r="K26" s="19" t="n"/>
     </row>
     <row r="27" ht="15" customHeight="1" s="57">
       <c r="A27" s="13" t="inlineStr">
@@ -2193,6 +2334,11 @@
           <t>Deal 4 damage. Apply 2 Burning.</t>
         </is>
       </c>
+      <c r="K27" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="57">
       <c r="A28" s="13" t="inlineStr">
@@ -2239,6 +2385,11 @@
           <t>Remove 3 Burning from yourself.</t>
         </is>
       </c>
+      <c r="K28" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="57">
       <c r="A29" s="15" t="inlineStr">
@@ -2289,6 +2440,11 @@
           <t>Deal 5 damage and apply 3 Burning to ALL enemies.</t>
         </is>
       </c>
+      <c r="K29" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="15" customHeight="1" s="57">
       <c r="A30" s="15" t="inlineStr">
@@ -2335,6 +2491,11 @@
           <t>Deal 6 damage. Apply 3 Burning.</t>
         </is>
       </c>
+      <c r="K30" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="57">
       <c r="A31" s="15" t="inlineStr">
@@ -2381,6 +2542,11 @@
           <t>Deal 15 damage. Each adjacent enemy has a 50% chance to take 5 Burning.</t>
         </is>
       </c>
+      <c r="K31" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="57">
       <c r="A32" s="21" t="inlineStr">
@@ -2431,6 +2597,11 @@
           <t>Convert ALL enemy statuses (positive and negative) to Burning, then double the Burning.</t>
         </is>
       </c>
+      <c r="K32" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="15" customHeight="1" s="57">
       <c r="A33" s="21" t="inlineStr">
@@ -2481,6 +2652,11 @@
           <t>Apply 10 Burning to ALL enemies. Already-burning enemies take double, then their Burning is forged into Stone for you.</t>
         </is>
       </c>
+      <c r="K33" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="15" customHeight="1" s="57">
       <c r="A34" s="21" t="inlineStr">
@@ -2527,6 +2703,11 @@
           <t>Discard your hand. For each card discarded, apply 8 Burning to a random enemy.</t>
         </is>
       </c>
+      <c r="K34" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="15" customHeight="1" s="57">
       <c r="A35" s="21" t="inlineStr">
@@ -2573,6 +2754,11 @@
           <t>Haste for as many turns as your current Forge Heat.</t>
         </is>
       </c>
+      <c r="K35" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="15" customHeight="1" s="57">
       <c r="A36" s="21" t="inlineStr">
@@ -2623,6 +2809,11 @@
           <t>Detonate all Burning: deal 2 damage per Burning on ALL enemies.</t>
         </is>
       </c>
+      <c r="K36" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="15" customHeight="1" s="57">
       <c r="A37" s="21" t="inlineStr">
@@ -2669,6 +2860,11 @@
           <t>Convert 4 of your own Burning into 2 Forge Heat. No effect below 4 Burning.</t>
         </is>
       </c>
+      <c r="K37" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="57">
       <c r="A38" s="21" t="inlineStr">
@@ -2715,6 +2911,11 @@
           <t>Deal 12 damage. Apply 3 Burning.</t>
         </is>
       </c>
+      <c r="K38" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="57">
       <c r="A39" s="21" t="inlineStr">
@@ -2761,6 +2962,11 @@
           <t>Move all Burning from the target to the enemy behind it.</t>
         </is>
       </c>
+      <c r="K39" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="15" customHeight="1" s="57">
       <c r="A40" s="21" t="inlineStr">
@@ -2811,6 +3017,11 @@
           <t>Spend all Forge Heat. Apply 8 Burning per Heat spent to ALL enemies.</t>
         </is>
       </c>
+      <c r="K40" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="57">
       <c r="A41" s="21" t="inlineStr">
@@ -2857,6 +3068,11 @@
           <t>Deal 28 damage. Apply 4 Burning.</t>
         </is>
       </c>
+      <c r="K41" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="57">
       <c r="A42" s="21" t="inlineStr">
@@ -2907,6 +3123,11 @@
           <t>Apply 20 Burning to ALL enemies.</t>
         </is>
       </c>
+      <c r="K42" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="57">
       <c r="A43" s="21" t="inlineStr">
@@ -2953,6 +3174,11 @@
           <t>Gain 10 Stone. Deal 10 damage and apply 3 Burning.</t>
         </is>
       </c>
+      <c r="K43" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="57">
       <c r="A44" s="21" t="inlineStr">
@@ -3003,6 +3229,11 @@
           <t>Apply 8 Burning to ALL enemies.</t>
         </is>
       </c>
+      <c r="K44" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="17.1" customHeight="1" s="57">
       <c r="A45" s="21" t="inlineStr">
@@ -3047,6 +3278,11 @@
       <c r="J45" s="22" t="inlineStr">
         <is>
           <t>Deal 26 damage and 4 Burning. The enemy behind takes half (13 damage, 2 Burning).</t>
+        </is>
+      </c>
+      <c r="K45" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
         </is>
       </c>
     </row>
@@ -3065,6 +3301,7 @@
       <c r="H46" s="24" t="n"/>
       <c r="I46" s="24" t="n"/>
       <c r="J46" s="24" t="n"/>
+      <c r="K46" s="23" t="n"/>
     </row>
     <row r="47" ht="15" customHeight="1" s="57">
       <c r="A47" s="13" t="inlineStr">
@@ -3115,6 +3352,11 @@
           <t>Apply 2 Poison to ALL enemies.</t>
         </is>
       </c>
+      <c r="K47" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="15" customHeight="1" s="57">
       <c r="A48" s="13" t="inlineStr">
@@ -3161,6 +3403,11 @@
           <t>Deal 3 damage. Apply 4 Poison.</t>
         </is>
       </c>
+      <c r="K48" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="15" customHeight="1" s="57">
       <c r="A49" s="15" t="inlineStr">
@@ -3211,6 +3458,11 @@
           <t>Apply 6 Poison to ALL enemies.</t>
         </is>
       </c>
+      <c r="K49" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="15" customHeight="1" s="57">
       <c r="A50" s="15" t="inlineStr">
@@ -3257,6 +3509,11 @@
           <t>Deal 5 damage. Apply 5 Poison.</t>
         </is>
       </c>
+      <c r="K50" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="15" customHeight="1" s="57">
       <c r="A51" s="17" t="inlineStr">
@@ -3307,6 +3564,11 @@
           <t>Hit ALL enemies 3 times for 3 damage. Apply 1 Poison per hit (2 if the enemy was already poisoned).</t>
         </is>
       </c>
+      <c r="K51" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="15" customHeight="1" s="57">
       <c r="A52" s="17" t="inlineStr">
@@ -3353,6 +3615,11 @@
           <t>Inflige autant de degat physique que de dose de poison active sur la cible et au ennemi adjacent a la cible. Ajoute 2 poison aux cibles touché par cette carte.</t>
         </is>
       </c>
+      <c r="K52" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="17.1" customHeight="1" s="57">
       <c r="A53" s="17" t="inlineStr">
@@ -3397,6 +3664,11 @@
       <c r="J53" s="18" t="inlineStr">
         <is>
           <t>Deal 6 damage. Apply 4 Poison.</t>
+        </is>
+      </c>
+      <c r="K53" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
         </is>
       </c>
     </row>
@@ -3415,6 +3687,7 @@
       <c r="H54" s="26" t="n"/>
       <c r="I54" s="26" t="n"/>
       <c r="J54" s="26" t="n"/>
+      <c r="K54" s="25" t="n"/>
     </row>
     <row r="55" ht="15" customHeight="1" s="57">
       <c r="A55" s="13" t="inlineStr">
@@ -3461,6 +3734,11 @@
           <t>Deal 5 damage. Apply 2 Bleed.</t>
         </is>
       </c>
+      <c r="K55" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="15" customHeight="1" s="57">
       <c r="A56" s="15" t="inlineStr">
@@ -3507,6 +3785,11 @@
           <t>Deal 3 damage. Apply 3 Bleed (stacks don't reset).</t>
         </is>
       </c>
+      <c r="K56" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="15" customHeight="1" s="57">
       <c r="A57" s="15" t="inlineStr">
@@ -3553,6 +3836,11 @@
           <t>Deal 5 damage, apply 3 Bleed, and heal 3 HP.</t>
         </is>
       </c>
+      <c r="K57" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="15" customHeight="1" s="57">
       <c r="A58" s="15" t="inlineStr">
@@ -3599,6 +3887,11 @@
           <t>Deal 6 damage. Apply 4 Bleed.</t>
         </is>
       </c>
+      <c r="K58" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="15" customHeight="1" s="57">
       <c r="A59" s="15" t="inlineStr">
@@ -3645,6 +3938,11 @@
           <t>Deal 15 damage. Apply 4 bleed.</t>
         </is>
       </c>
+      <c r="K59" s="60" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="15" customHeight="1" s="57">
       <c r="A60" s="15" t="inlineStr">
@@ -3695,6 +3993,11 @@
           <t>Deal 6 damage and apply 2 Bleed to ALL enemies.</t>
         </is>
       </c>
+      <c r="K60" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="15" customHeight="1" s="57">
       <c r="A61" s="17" t="inlineStr">
@@ -3741,6 +4044,11 @@
           <t>Heal 5 HP per Bleed among ALL enemies, then remove all their Bleed.</t>
         </is>
       </c>
+      <c r="K61" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="15" customHeight="1" s="57">
       <c r="A62" s="17" t="inlineStr">
@@ -3787,6 +4095,11 @@
           <t>Gain 1 Forge Heat per 5 Bleed among ALL enemies.</t>
         </is>
       </c>
+      <c r="K62" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="15" customHeight="1" s="57">
       <c r="A63" s="17" t="inlineStr">
@@ -3837,6 +4150,11 @@
           <t>Stun for 2 turns every enemy that has Bleed.</t>
         </is>
       </c>
+      <c r="K63" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="15" customHeight="1" s="57">
       <c r="A64" s="17" t="inlineStr">
@@ -3887,6 +4205,11 @@
           <t>Take 10 damage. Apply 5 Bleed to ALL enemies.</t>
         </is>
       </c>
+      <c r="K64" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="15" customHeight="1" s="57">
       <c r="A65" s="17" t="inlineStr">
@@ -3933,6 +4256,11 @@
           <t>Both adjacent enemies match the target's Bleed.</t>
         </is>
       </c>
+      <c r="K65" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="15" customHeight="1" s="57">
       <c r="A66" s="17" t="inlineStr">
@@ -3983,6 +4311,11 @@
           <t>Lose 20 HP. Deal 10 damage and 1 Bleed to ALL enemies. Heal 20 HP per enemy killed by this.</t>
         </is>
       </c>
+      <c r="K66" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="15" customHeight="1" s="57">
       <c r="A67" s="17" t="inlineStr">
@@ -4033,6 +4366,11 @@
           <t>Deal 16 damage to ALL enemies. Apply 2 Bleed to ALL enemies.</t>
         </is>
       </c>
+      <c r="K67" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="15" customHeight="1" s="57">
       <c r="A68" s="17" t="inlineStr">
@@ -4079,6 +4417,11 @@
           <t>Take 10 damage. Apply 4 Bleed on an ennemi target.</t>
         </is>
       </c>
+      <c r="K68" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="15" customHeight="1" s="57">
       <c r="A69" s="17" t="inlineStr">
@@ -4125,6 +4468,11 @@
           <t>Per Bleed among ALL enemies: gain 3 Stone and heal 2 HP.</t>
         </is>
       </c>
+      <c r="K69" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="15" customHeight="1" s="57">
       <c r="A70" s="21" t="inlineStr">
@@ -4171,6 +4519,11 @@
           <t>Deal 14 damage. Apply 3 Bleed.</t>
         </is>
       </c>
+      <c r="K70" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="17.1" customHeight="1" s="57">
       <c r="A71" s="21" t="inlineStr">
@@ -4219,6 +4572,11 @@
       <c r="J71" s="21" t="inlineStr">
         <is>
           <t>Deal 20 damage and apply 3 Bleed to ALL enemies.</t>
+        </is>
+      </c>
+      <c r="K71" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
         </is>
       </c>
     </row>
@@ -4237,6 +4595,7 @@
       <c r="H72" s="28" t="n"/>
       <c r="I72" s="28" t="n"/>
       <c r="J72" s="28" t="n"/>
+      <c r="K72" s="27" t="n"/>
     </row>
     <row r="73" ht="15" customHeight="1" s="57">
       <c r="A73" s="13" t="inlineStr">
@@ -4283,6 +4642,11 @@
           <t>Deal 5 damage. Chill: -30% speed for 2 turns.</t>
         </is>
       </c>
+      <c r="K73" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="15" customHeight="1" s="57">
       <c r="A74" s="15" t="inlineStr">
@@ -4333,6 +4697,11 @@
           <t>Chill ALL enemies (-30% speed for 3 turns).</t>
         </is>
       </c>
+      <c r="K74" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="15" customHeight="1" s="57">
       <c r="A75" s="15" t="inlineStr">
@@ -4379,6 +4748,11 @@
           <t>Deal 5 damage. Chill: -30% speed for 3 turns.</t>
         </is>
       </c>
+      <c r="K75" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="15" customHeight="1" s="57">
       <c r="A76" s="16" t="inlineStr">
@@ -4425,6 +4799,11 @@
           <t>Deal 10 damage. Chill: -30% speed for 2 turns.</t>
         </is>
       </c>
+      <c r="K76" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="15" customHeight="1" s="57">
       <c r="A77" s="15" t="inlineStr">
@@ -4471,6 +4850,11 @@
           <t>Deal 8 damage, +5 more if the target is Chilled.</t>
         </is>
       </c>
+      <c r="K77" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="17.1" customHeight="1" s="57">
       <c r="A78" s="17" t="inlineStr">
@@ -4515,6 +4899,11 @@
       <c r="J78" s="18" t="inlineStr">
         <is>
           <t>Deal 8 damage and apply 3 Chill. If the target was already chilled, cascade the same hit to the next enemy, and so on.</t>
+        </is>
+      </c>
+      <c r="K78" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
         </is>
       </c>
     </row>
@@ -4533,6 +4922,7 @@
       <c r="H79" s="30" t="n"/>
       <c r="I79" s="30" t="n"/>
       <c r="J79" s="30" t="n"/>
+      <c r="K79" s="29" t="n"/>
     </row>
     <row r="80" ht="15" customHeight="1" s="57">
       <c r="A80" s="13" t="inlineStr">
@@ -4579,6 +4969,11 @@
           <t>Deal 14 damage. Apply 2 Confusion.</t>
         </is>
       </c>
+      <c r="K80" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="15" customHeight="1" s="57">
       <c r="A81" s="13" t="inlineStr">
@@ -4625,6 +5020,11 @@
           <t>Apply 2 Confusion to the target.</t>
         </is>
       </c>
+      <c r="K81" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="15" customHeight="1" s="57">
       <c r="A82" s="15" t="inlineStr">
@@ -4671,6 +5071,11 @@
           <t>Steal a random buff from the target enemy and apply it to yourself.</t>
         </is>
       </c>
+      <c r="K82" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="15" customHeight="1" s="57">
       <c r="A83" s="17" t="inlineStr">
@@ -4717,6 +5122,11 @@
           <t>Gain 6 Stone. Apply 2 confusion to the nearest enemy.</t>
         </is>
       </c>
+      <c r="K83" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="15" customHeight="1" s="57">
       <c r="A84" s="17" t="inlineStr">
@@ -4767,6 +5177,11 @@
           <t>Apply 2 Confusion to ALL enemies.</t>
         </is>
       </c>
+      <c r="K84" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="15" customHeight="1" s="57">
       <c r="A85" s="17" t="inlineStr">
@@ -4817,6 +5232,11 @@
           <t>Apply 1 more Confusion to each already-confused enemy.</t>
         </is>
       </c>
+      <c r="K85" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="15" customHeight="1" s="57">
       <c r="A86" s="17" t="inlineStr">
@@ -4863,6 +5283,11 @@
           <t>Deal 10 damage. Apply 1 Confusion.</t>
         </is>
       </c>
+      <c r="K86" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="15" customHeight="1" s="57">
       <c r="A87" s="17" t="inlineStr">
@@ -4909,6 +5334,11 @@
           <t>Deal 12 damage. Stun the target for 1 turns.</t>
         </is>
       </c>
+      <c r="K87" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="15" customHeight="1" s="57">
       <c r="A88" s="17" t="inlineStr">
@@ -4955,6 +5385,11 @@
           <t>Deal 40 damage. Stun the target for 2 turn.</t>
         </is>
       </c>
+      <c r="K88" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="15" customHeight="1" s="57">
       <c r="A89" s="17" t="inlineStr">
@@ -5001,6 +5436,11 @@
           <t>Deal 8 damage. Stun the enemy for 3 turns.</t>
         </is>
       </c>
+      <c r="K89" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="17.1" customHeight="1" s="57">
       <c r="A90" s="17" t="inlineStr">
@@ -5049,6 +5489,11 @@
       <c r="J90" s="18" t="inlineStr">
         <is>
           <t>Deal 10 damage to ALL enemies. If you have 20+ Stone, stun them all for 1 turn.</t>
+        </is>
+      </c>
+      <c r="K90" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
         </is>
       </c>
     </row>
@@ -5067,6 +5512,7 @@
       <c r="H91" s="32" t="n"/>
       <c r="I91" s="32" t="n"/>
       <c r="J91" s="32" t="n"/>
+      <c r="K91" s="31" t="n"/>
     </row>
     <row r="92" ht="15" customHeight="1" s="57">
       <c r="A92" s="13" t="inlineStr">
@@ -5113,6 +5559,11 @@
           <t>Gain 3 Stone.</t>
         </is>
       </c>
+      <c r="K92" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="15" customHeight="1" s="57">
       <c r="A93" s="13" t="inlineStr">
@@ -5159,6 +5610,11 @@
           <t>Gain 5 Stone.</t>
         </is>
       </c>
+      <c r="K93" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="15" customHeight="1" s="57">
       <c r="A94" s="13" t="inlineStr">
@@ -5205,6 +5661,11 @@
           <t>Gain 8 Stone.</t>
         </is>
       </c>
+      <c r="K94" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="15" customHeight="1" s="57">
       <c r="A95" s="13" t="inlineStr">
@@ -5251,6 +5712,11 @@
           <t>Gain 6 Stone.</t>
         </is>
       </c>
+      <c r="K95" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="15" customHeight="1" s="57">
       <c r="A96" s="13" t="inlineStr">
@@ -5297,6 +5763,11 @@
           <t>Gain 9 Stone.</t>
         </is>
       </c>
+      <c r="K96" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="15" customHeight="1" s="57">
       <c r="A97" s="15" t="inlineStr">
@@ -5343,6 +5814,11 @@
           <t>Gain 12 Stone and 3 Regen.</t>
         </is>
       </c>
+      <c r="K97" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="15" customHeight="1" s="57">
       <c r="A98" s="15" t="inlineStr">
@@ -5389,6 +5865,11 @@
           <t>Gain 12 Stone.</t>
         </is>
       </c>
+      <c r="K98" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="15" customHeight="1" s="57">
       <c r="A99" s="15" t="inlineStr">
@@ -5435,6 +5916,11 @@
           <t>Deal damage equal to your Stone, then gain 8 Stone.</t>
         </is>
       </c>
+      <c r="K99" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="15" customHeight="1" s="57">
       <c r="A100" s="15" t="inlineStr">
@@ -5481,6 +5967,11 @@
           <t>Deal 10 damage. Gain 8 Stone.</t>
         </is>
       </c>
+      <c r="K100" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="15" customHeight="1" s="57">
       <c r="A101" s="15" t="inlineStr">
@@ -5527,6 +6018,11 @@
           <t>Gain 18 Stone.</t>
         </is>
       </c>
+      <c r="K101" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="15" customHeight="1" s="57">
       <c r="A102" s="15" t="inlineStr">
@@ -5573,6 +6069,11 @@
           <t>Gain 23 Stone. Counts as three Stone cards for Stone Age combos.</t>
         </is>
       </c>
+      <c r="K102" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="15" customHeight="1" s="57">
       <c r="A103" s="15" t="inlineStr">
@@ -5619,6 +6120,11 @@
           <t>Gain 4 Riposte: reflect melee damage you take back to the attacker. Lose 1 per trigger.</t>
         </is>
       </c>
+      <c r="K103" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="15" customHeight="1" s="57">
       <c r="A104" s="15" t="inlineStr">
@@ -5665,6 +6171,11 @@
           <t>Gain 10 Stone.</t>
         </is>
       </c>
+      <c r="K104" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="15" customHeight="1" s="57">
       <c r="A105" s="15" t="inlineStr">
@@ -5711,6 +6222,11 @@
           <t>Gain 7 Stone.</t>
         </is>
       </c>
+      <c r="K105" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="15" customHeight="1" s="57">
       <c r="A106" s="15" t="inlineStr">
@@ -5757,6 +6273,11 @@
           <t>Gain 1 Stone for each Stone card played this combat (Many Stone counts as 3).</t>
         </is>
       </c>
+      <c r="K106" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="15" customHeight="1" s="57">
       <c r="A107" s="15" t="inlineStr">
@@ -5803,6 +6324,11 @@
           <t>Deal damage equal to your current Stone.</t>
         </is>
       </c>
+      <c r="K107" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="15" customHeight="1" s="57">
       <c r="A108" s="15" t="inlineStr">
@@ -5849,6 +6375,11 @@
           <t xml:space="preserve">Gain 12 Stone. </t>
         </is>
       </c>
+      <c r="K108" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="15" customHeight="1" s="57">
       <c r="A109" s="17" t="inlineStr">
@@ -5895,6 +6426,11 @@
           <t>Gain 22 Stone.</t>
         </is>
       </c>
+      <c r="K109" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="15" customHeight="1" s="57">
       <c r="A110" s="17" t="inlineStr">
@@ -5941,6 +6477,11 @@
           <t>Gain 8 Stone and Haste for 2 turns.</t>
         </is>
       </c>
+      <c r="K110" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="15" customHeight="1" s="57">
       <c r="A111" s="17" t="inlineStr">
@@ -5987,6 +6528,11 @@
           <t>Gain 7 Stone for every enemy still alive.</t>
         </is>
       </c>
+      <c r="K111" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="15" customHeight="1" s="57">
       <c r="A112" s="17" t="inlineStr">
@@ -6033,6 +6579,11 @@
           <t>Spend all Forge Heat. Gain 10 Stone per Heat spent.</t>
         </is>
       </c>
+      <c r="K112" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="15" customHeight="1" s="57">
       <c r="A113" s="17" t="inlineStr">
@@ -6079,6 +6630,11 @@
           <t>Double your current Stone.</t>
         </is>
       </c>
+      <c r="K113" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="15" customHeight="1" s="57">
       <c r="A114" s="17" t="inlineStr">
@@ -6125,6 +6681,11 @@
           <t>Deal damage equal to your Stone, then gain 10 Stone.</t>
         </is>
       </c>
+      <c r="K114" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="17.1" customHeight="1" s="57">
       <c r="A115" s="21" t="inlineStr">
@@ -6171,6 +6732,11 @@
           <t>Gain 30 Stone.</t>
         </is>
       </c>
+      <c r="K115" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="15" customHeight="1" s="57">
       <c r="A116" s="13" t="inlineStr">
@@ -6215,6 +6781,11 @@
       <c r="J116" s="14" t="inlineStr">
         <is>
           <t>Gain 2 Stone.</t>
+        </is>
+      </c>
+      <c r="K116" s="60" t="inlineStr">
+        <is>
+          <t>✗</t>
         </is>
       </c>
     </row>
@@ -6233,6 +6804,7 @@
       <c r="H117" s="34" t="n"/>
       <c r="I117" s="34" t="n"/>
       <c r="J117" s="34" t="n"/>
+      <c r="K117" s="33" t="n"/>
     </row>
     <row r="118" ht="15" customHeight="1" s="57">
       <c r="A118" s="13" t="inlineStr">
@@ -6279,6 +6851,11 @@
           <t>Gain 3 Regen. Each turn: heal that many HP, then lose 1 Regen.</t>
         </is>
       </c>
+      <c r="K118" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="15" customHeight="1" s="57">
       <c r="A119" s="15" t="inlineStr">
@@ -6325,6 +6902,11 @@
           <t>Consume the target's Bleed: heal that many HP. Gain 1 Forge Heat.</t>
         </is>
       </c>
+      <c r="K119" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="15" customHeight="1" s="57">
       <c r="A120" s="15" t="inlineStr">
@@ -6371,6 +6953,11 @@
           <t>Deal 12 damage. Remove a random buff from the target; if one was removed, gain 4 Regen.</t>
         </is>
       </c>
+      <c r="K120" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="15" customHeight="1" s="57">
       <c r="A121" s="15" t="inlineStr">
@@ -6421,6 +7008,11 @@
           <t>Deal 6 damage to ALL enemies. Heal 4 HP per enemy hit.</t>
         </is>
       </c>
+      <c r="K121" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="15" customHeight="1" s="57">
       <c r="A122" s="17" t="inlineStr">
@@ -6467,6 +7059,11 @@
           <t>Heal 30 HP.</t>
         </is>
       </c>
+      <c r="K122" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="15" customHeight="1" s="57">
       <c r="A123" s="17" t="inlineStr">
@@ -6513,6 +7110,11 @@
           <t>Remove a random buff from the target. If one was removed, gain 4 Regen.</t>
         </is>
       </c>
+      <c r="K123" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="17.1" customHeight="1" s="57">
       <c r="A124" s="21" t="inlineStr">
@@ -6559,6 +7161,11 @@
           <t>Heal 10 HP per enemy that has Bleed.</t>
         </is>
       </c>
+      <c r="K124" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="15" customHeight="1" s="57">
       <c r="A125" s="21" t="inlineStr">
@@ -6603,6 +7210,11 @@
       <c r="J125" s="22" t="inlineStr">
         <is>
           <t>Deal 15 damage. If the target dies, gain 4 Strength and heal 20 HP.</t>
+        </is>
+      </c>
+      <c r="K125" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
         </is>
       </c>
     </row>
@@ -6621,6 +7233,7 @@
       <c r="H126" s="36" t="n"/>
       <c r="I126" s="36" t="n"/>
       <c r="J126" s="36" t="n"/>
+      <c r="K126" s="35" t="n"/>
     </row>
     <row r="127" ht="15" customHeight="1" s="57">
       <c r="A127" s="13" t="inlineStr">
@@ -6667,6 +7280,11 @@
           <t>Gain 0 to 3 Forge Heat at random.</t>
         </is>
       </c>
+      <c r="K127" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="15" customHeight="1" s="57">
       <c r="A128" s="13" t="inlineStr">
@@ -6713,6 +7331,11 @@
           <t>Gain 1 Forge Heat (energy).</t>
         </is>
       </c>
+      <c r="K128" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="15" customHeight="1" s="57">
       <c r="A129" s="15" t="inlineStr">
@@ -6759,6 +7382,11 @@
           <t>Deal 6 damage. Gain 2 Forge Heat.</t>
         </is>
       </c>
+      <c r="K129" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="15" customHeight="1" s="57">
       <c r="A130" s="15" t="inlineStr">
@@ -6809,6 +7437,11 @@
           <t>Deal 4 damage to ALL enemies. Gain 2 Forge Heat.</t>
         </is>
       </c>
+      <c r="K130" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="15" customHeight="1" s="57">
       <c r="A131" s="15" t="inlineStr">
@@ -6855,6 +7488,11 @@
           <t>Gain 3 Forge Heat (energy).</t>
         </is>
       </c>
+      <c r="K131" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="132" ht="15" customHeight="1" s="57">
       <c r="A132" s="15" t="inlineStr">
@@ -6901,6 +7539,11 @@
           <t>Draw 1 card. Gain 2 Forge Heat.</t>
         </is>
       </c>
+      <c r="K132" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="15" customHeight="1" s="57">
       <c r="A133" s="15" t="inlineStr">
@@ -6947,6 +7590,11 @@
           <t>Gain 1 Forge Heat per 8 Stone cards played this combat (min 1, max 6).</t>
         </is>
       </c>
+      <c r="K133" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="15" customHeight="1" s="57">
       <c r="A134" s="15" t="inlineStr">
@@ -6993,6 +7641,11 @@
           <t>Gain 4 Forge Heat (energy).</t>
         </is>
       </c>
+      <c r="K134" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="135" ht="15" customHeight="1" s="57">
       <c r="A135" s="15" t="inlineStr">
@@ -7039,6 +7692,11 @@
           <t>Gain 1 to 5 Forge Heat at random.</t>
         </is>
       </c>
+      <c r="K135" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="136" ht="15" customHeight="1" s="57">
       <c r="A136" s="15" t="inlineStr">
@@ -7085,6 +7743,11 @@
           <t>Gain 2 Forge Heat (energy).</t>
         </is>
       </c>
+      <c r="K136" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="137" ht="15" customHeight="1" s="57">
       <c r="A137" s="15" t="inlineStr">
@@ -7131,6 +7794,11 @@
           <t>Trade 5 Haste turns for 3 Forge Heat. No effect below 5 Haste.</t>
         </is>
       </c>
+      <c r="K137" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="138" ht="17.1" customHeight="1" s="57">
       <c r="A138" s="21" t="inlineStr">
@@ -7177,6 +7845,11 @@
           <t>Gain 5 Forge Heat (energy).</t>
         </is>
       </c>
+      <c r="K138" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="139" ht="15" customHeight="1" s="57">
       <c r="A139" s="21" t="inlineStr">
@@ -7221,6 +7894,11 @@
       <c r="J139" s="22" t="inlineStr">
         <is>
           <t>Gain 3 Forge Heat (energy).</t>
+        </is>
+      </c>
+      <c r="K139" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
         </is>
       </c>
     </row>
@@ -7239,6 +7917,7 @@
       <c r="H140" s="38" t="n"/>
       <c r="I140" s="38" t="n"/>
       <c r="J140" s="38" t="n"/>
+      <c r="K140" s="37" t="n"/>
     </row>
     <row r="141" ht="15" customHeight="1" s="57">
       <c r="A141" s="13" t="inlineStr">
@@ -7285,6 +7964,11 @@
           <t>Gain 2 Haste.</t>
         </is>
       </c>
+      <c r="K141" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="142" ht="15" customHeight="1" s="57">
       <c r="A142" s="13" t="inlineStr">
@@ -7331,6 +8015,11 @@
           <t>Haste for 4 of your turns.</t>
         </is>
       </c>
+      <c r="K142" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="143" ht="15" customHeight="1" s="57">
       <c r="A143" s="13" t="inlineStr">
@@ -7377,6 +8066,11 @@
           <t>Each of your turns, gain 1 permanent Haste (it builds up all combat). Stacks when replayed.</t>
         </is>
       </c>
+      <c r="K143" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="144" ht="15" customHeight="1" s="57">
       <c r="A144" s="15" t="inlineStr">
@@ -7423,6 +8117,11 @@
           <t>Haste for 3 turns. Draw 1 card.</t>
         </is>
       </c>
+      <c r="K144" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="145" ht="17.1" customHeight="1" s="57">
       <c r="A145" s="15" t="inlineStr">
@@ -7469,6 +8168,11 @@
           <t>Gain 4 Haste. Each stack: +5% speed. Lose 1 per turn.</t>
         </is>
       </c>
+      <c r="K145" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="146" ht="17.1" customHeight="1" s="57">
       <c r="A146" s="15" t="inlineStr">
@@ -7515,6 +8219,11 @@
           <t>Take an extra turn right after this one.</t>
         </is>
       </c>
+      <c r="K146" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="147" ht="15" customHeight="1" s="57">
       <c r="A147" s="15" t="inlineStr">
@@ -7561,6 +8270,11 @@
           <t>Gain 3 Haste. Stun the target for 3 turns.</t>
         </is>
       </c>
+      <c r="K147" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="148" ht="15" customHeight="1" s="57">
       <c r="A148" s="13" t="inlineStr">
@@ -7605,6 +8319,11 @@
       <c r="J148" s="14" t="inlineStr">
         <is>
           <t>Gain 2 Haste.</t>
+        </is>
+      </c>
+      <c r="K148" s="60" t="inlineStr">
+        <is>
+          <t>✗</t>
         </is>
       </c>
     </row>
@@ -7623,6 +8342,7 @@
       <c r="H149" s="40" t="n"/>
       <c r="I149" s="40" t="n"/>
       <c r="J149" s="40" t="n"/>
+      <c r="K149" s="39" t="n"/>
     </row>
     <row r="150" ht="15" customHeight="1" s="57">
       <c r="A150" s="13" t="inlineStr">
@@ -7669,6 +8389,11 @@
           <t>Gain 2 Strength (+2 damage to every attack this combat).</t>
         </is>
       </c>
+      <c r="K150" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="151" ht="15" customHeight="1" s="57">
       <c r="A151" s="15" t="inlineStr">
@@ -7715,6 +8440,11 @@
           <t>Gain 3 Strength.</t>
         </is>
       </c>
+      <c r="K151" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="152" ht="15" customHeight="1" s="57">
       <c r="A152" s="15" t="inlineStr">
@@ -7761,6 +8491,11 @@
           <t>Deal 14 damage. Gain 3 Strength.</t>
         </is>
       </c>
+      <c r="K152" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="153" ht="17.1" customHeight="1" s="57">
       <c r="A153" s="15" t="inlineStr">
@@ -7807,6 +8542,11 @@
           <t>Gain 4 Strength.</t>
         </is>
       </c>
+      <c r="K153" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="154" ht="15" customHeight="1" s="57">
       <c r="A154" s="15" t="inlineStr">
@@ -7853,6 +8593,11 @@
           <t>Gain 4 Strength. Draw 2 cards.</t>
         </is>
       </c>
+      <c r="K154" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="155" ht="15" customHeight="1" s="57">
       <c r="A155" s="15" t="inlineStr">
@@ -7897,6 +8642,11 @@
       <c r="J155" s="16" t="inlineStr">
         <is>
           <t>Gain 3 Strength. Draw 1 card.</t>
+        </is>
+      </c>
+      <c r="K155" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
         </is>
       </c>
     </row>
@@ -7915,6 +8665,7 @@
       <c r="H156" s="42" t="n"/>
       <c r="I156" s="42" t="n"/>
       <c r="J156" s="42" t="n"/>
+      <c r="K156" s="41" t="n"/>
     </row>
     <row r="157" ht="15" customHeight="1" s="57">
       <c r="A157" s="13" t="inlineStr">
@@ -7961,6 +8712,11 @@
           <t>Draw 2 cards.</t>
         </is>
       </c>
+      <c r="K157" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="158" ht="15" customHeight="1" s="57">
       <c r="A158" s="13" t="inlineStr">
@@ -8007,6 +8763,11 @@
           <t>Draw 1 card. Gain Stone equal to twice its cost.</t>
         </is>
       </c>
+      <c r="K158" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="159" ht="15" customHeight="1" s="57">
       <c r="A159" s="15" t="inlineStr">
@@ -8053,6 +8814,11 @@
           <t>Draw 3 cards. Keep those costing less than 3 Forge Heat, discard the rest.</t>
         </is>
       </c>
+      <c r="K159" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="160" ht="15" customHeight="1" s="57">
       <c r="A160" s="15" t="inlineStr">
@@ -8099,6 +8865,11 @@
           <t>Draw 1 card per 6 Stone cards played this combat (min 1, max 6).</t>
         </is>
       </c>
+      <c r="K160" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="161" ht="15" customHeight="1" s="57">
       <c r="A161" s="15" t="inlineStr">
@@ -8145,6 +8916,11 @@
           <t>Draw 2 cards. Gain 1 Forge Heat.</t>
         </is>
       </c>
+      <c r="K161" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="162" ht="15" customHeight="1" s="57">
       <c r="A162" s="17" t="inlineStr">
@@ -8191,6 +8967,11 @@
           <t>Draw 1 card per living enemy.</t>
         </is>
       </c>
+      <c r="K162" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="163" ht="15" customHeight="1" s="57">
       <c r="A163" s="21" t="inlineStr">
@@ -8237,6 +9018,11 @@
           <t>Discard your hand and draw double the discarded cards.</t>
         </is>
       </c>
+      <c r="K163" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
     </row>
     <row r="164" ht="15" customHeight="1" s="57">
       <c r="A164" s="13" t="inlineStr">
@@ -8281,6 +9067,11 @@
       <c r="J164" s="14" t="inlineStr">
         <is>
           <t>Discard 1 card, then draw 1.</t>
+        </is>
+      </c>
+      <c r="K164" s="60" t="inlineStr">
+        <is>
+          <t>✗</t>
         </is>
       </c>
     </row>

--- a/docs/BRUTAL-items-et-cartes.xlsx
+++ b/docs/BRUTAL-items-et-cartes.xlsx
@@ -6783,9 +6783,9 @@
           <t>Gain 2 Stone.</t>
         </is>
       </c>
-      <c r="K116" s="60" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="K116" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
         </is>
       </c>
     </row>
@@ -8321,9 +8321,9 @@
           <t>Gain 2 Haste.</t>
         </is>
       </c>
-      <c r="K148" s="60" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="K148" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
         </is>
       </c>
     </row>
@@ -9069,9 +9069,9 @@
           <t>Discard 1 card, then draw 1.</t>
         </is>
       </c>
-      <c r="K164" s="60" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="K164" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
         </is>
       </c>
     </row>

--- a/docs/BRUTAL-items-et-cartes.xlsx
+++ b/docs/BRUTAL-items-et-cartes.xlsx
@@ -3938,9 +3938,9 @@
           <t>Deal 15 damage. Apply 4 bleed.</t>
         </is>
       </c>
-      <c r="K59" s="60" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="K59" s="59" t="inlineStr">
+        <is>
+          <t>✔</t>
         </is>
       </c>
     </row>

--- a/docs/BRUTAL-items-et-cartes.xlsx
+++ b/docs/BRUTAL-items-et-cartes.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Items" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Sets" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Effets" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Recettes" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -21,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -87,8 +88,20 @@
       <b val="1"/>
       <color rgb="FF1B4D1B"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="30">
+  <fills count="49">
     <fill>
       <patternFill/>
     </fill>
@@ -235,8 +248,103 @@
         <fgColor rgb="FFF08080"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00b9b2a6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00c0703a"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="003a3a42"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008a857c"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007a5230"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00cdd2d6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00e8c54f"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002fa86a"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002a4bbf"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="009a5fd0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008fa0ad"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0018a558"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00d12f4a"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002f6fd1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00bfe6f0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00acc6d4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001a1a22"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00f6e6a0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00fff2d9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -259,11 +367,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00cccccc"/>
+      </left>
+      <right style="thin">
+        <color rgb="00cccccc"/>
+      </right>
+      <top style="thin">
+        <color rgb="00cccccc"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00cccccc"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -379,6 +501,68 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="31" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="32" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="36" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="37" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="38" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="39" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="40" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="41" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="42" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="43" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="44" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="45" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="46" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="47" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="48" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="48" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -14910,4 +15094,2671 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F217"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" style="57" min="1" max="1"/>
+    <col width="14" customWidth="1" style="57" min="2" max="2"/>
+    <col width="14" customWidth="1" style="57" min="3" max="3"/>
+    <col width="14" customWidth="1" style="57" min="4" max="4"/>
+    <col width="14" customWidth="1" style="57" min="5" max="5"/>
+    <col width="14" customWidth="1" style="57" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="61" t="inlineStr">
+        <is>
+          <t>RECETTES DE CRAFT — SOURCE ÉDITABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="62" t="inlineStr">
+        <is>
+          <t>Édite les grilles ci-dessous, puis lance : python3 outils/importer_recettes.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="62" t="inlineStr">
+        <is>
+          <t>Un bloc = une arme. Ligne « ARME » = en-tête. Dessous : la grille (codes 2 lettres, case vide = rien).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="63" t="inlineStr">
+        <is>
+          <t>CODES :</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="B6" s="62" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="C6" s="65" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="D6" s="62" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="E6" s="66" t="inlineStr">
+        <is>
+          <t>Co</t>
+        </is>
+      </c>
+      <c r="F6" s="62" t="inlineStr">
+        <is>
+          <t>Coal</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="67" t="inlineStr">
+        <is>
+          <t>St</t>
+        </is>
+      </c>
+      <c r="B7" s="62" t="inlineStr">
+        <is>
+          <t>Cut Stone</t>
+        </is>
+      </c>
+      <c r="C7" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="D7" s="62" t="inlineStr">
+        <is>
+          <t>Wood</t>
+        </is>
+      </c>
+      <c r="E7" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="F7" s="62" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="70" t="inlineStr">
+        <is>
+          <t>Au</t>
+        </is>
+      </c>
+      <c r="B8" s="62" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="C8" s="71" t="inlineStr">
+        <is>
+          <t>Ma</t>
+        </is>
+      </c>
+      <c r="D8" s="62" t="inlineStr">
+        <is>
+          <t>Malachite</t>
+        </is>
+      </c>
+      <c r="E8" s="72" t="inlineStr">
+        <is>
+          <t>La</t>
+        </is>
+      </c>
+      <c r="F8" s="62" t="inlineStr">
+        <is>
+          <t>Lapis</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="73" t="inlineStr">
+        <is>
+          <t>Am</t>
+        </is>
+      </c>
+      <c r="B9" s="62" t="inlineStr">
+        <is>
+          <t>Amethyst</t>
+        </is>
+      </c>
+      <c r="C9" s="74" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+      <c r="D9" s="62" t="inlineStr">
+        <is>
+          <t>Titanium</t>
+        </is>
+      </c>
+      <c r="E9" s="75" t="inlineStr">
+        <is>
+          <t>Em</t>
+        </is>
+      </c>
+      <c r="F9" s="62" t="inlineStr">
+        <is>
+          <t>Emerald</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="76" t="inlineStr">
+        <is>
+          <t>Ru</t>
+        </is>
+      </c>
+      <c r="B10" s="62" t="inlineStr">
+        <is>
+          <t>Ruby</t>
+        </is>
+      </c>
+      <c r="C10" s="77" t="inlineStr">
+        <is>
+          <t>Sa</t>
+        </is>
+      </c>
+      <c r="D10" s="62" t="inlineStr">
+        <is>
+          <t>Sapphire</t>
+        </is>
+      </c>
+      <c r="E10" s="78" t="inlineStr">
+        <is>
+          <t>Di</t>
+        </is>
+      </c>
+      <c r="F10" s="62" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="79" t="inlineStr">
+        <is>
+          <t>Mi</t>
+        </is>
+      </c>
+      <c r="B11" s="62" t="inlineStr">
+        <is>
+          <t>Mithril</t>
+        </is>
+      </c>
+      <c r="C11" s="80" t="inlineStr">
+        <is>
+          <t>On</t>
+        </is>
+      </c>
+      <c r="D11" s="62" t="inlineStr">
+        <is>
+          <t>Onyx</t>
+        </is>
+      </c>
+      <c r="E11" s="81" t="inlineStr">
+        <is>
+          <t>Su</t>
+        </is>
+      </c>
+      <c r="F11" s="62" t="inlineStr">
+        <is>
+          <t>Sunstone</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B13" s="82" t="inlineStr">
+        <is>
+          <t>epee-courte</t>
+        </is>
+      </c>
+      <c r="C13" s="83" t="inlineStr">
+        <is>
+          <t>Short Sword</t>
+        </is>
+      </c>
+      <c r="D13" s="83" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="E13" s="83" t="inlineStr">
+        <is>
+          <t>lame</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="84" t="n"/>
+      <c r="C14" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="D14" s="84" t="n"/>
+    </row>
+    <row r="15">
+      <c r="B15" s="65" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="C15" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="D15" s="65" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="84" t="n"/>
+      <c r="C16" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="D16" s="84" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B18" s="82" t="inlineStr">
+        <is>
+          <t>gourdin</t>
+        </is>
+      </c>
+      <c r="C18" s="83" t="inlineStr">
+        <is>
+          <t>Wooden Club</t>
+        </is>
+      </c>
+      <c r="D18" s="83" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="E18" s="83" t="inlineStr">
+        <is>
+          <t>bois/contondant</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="C19" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="C20" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="84" t="n"/>
+      <c r="C21" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B23" s="82" t="inlineStr">
+        <is>
+          <t>lance</t>
+        </is>
+      </c>
+      <c r="C23" s="83" t="inlineStr">
+        <is>
+          <t>Spear</t>
+        </is>
+      </c>
+      <c r="D23" s="83" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="E23" s="83" t="inlineStr">
+        <is>
+          <t>perforant</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="84" t="n"/>
+      <c r="C24" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="D24" s="84" t="n"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="84" t="n"/>
+      <c r="C25" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="D25" s="84" t="n"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="84" t="n"/>
+      <c r="C26" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="D26" s="84" t="n"/>
+    </row>
+    <row r="27">
+      <c r="B27" s="84" t="n"/>
+      <c r="C27" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="D27" s="84" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B29" s="82" t="inlineStr">
+        <is>
+          <t>hachette</t>
+        </is>
+      </c>
+      <c r="C29" s="83" t="inlineStr">
+        <is>
+          <t>Hatchet</t>
+        </is>
+      </c>
+      <c r="D29" s="83" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="E29" s="83" t="inlineStr">
+        <is>
+          <t>hache</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="C30" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="C31" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="84" t="n"/>
+      <c r="C32" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B34" s="82" t="inlineStr">
+        <is>
+          <t>masse</t>
+        </is>
+      </c>
+      <c r="C34" s="83" t="inlineStr">
+        <is>
+          <t>Mace</t>
+        </is>
+      </c>
+      <c r="D34" s="83" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="E34" s="83" t="inlineStr">
+        <is>
+          <t>contondant</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="67" t="inlineStr">
+        <is>
+          <t>St</t>
+        </is>
+      </c>
+      <c r="C35" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="D35" s="67" t="inlineStr">
+        <is>
+          <t>St</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="84" t="n"/>
+      <c r="C36" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="D36" s="84" t="n"/>
+    </row>
+    <row r="37">
+      <c r="B37" s="84" t="n"/>
+      <c r="C37" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="D37" s="84" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B39" s="82" t="inlineStr">
+        <is>
+          <t>dague-rouillee</t>
+        </is>
+      </c>
+      <c r="C39" s="83" t="inlineStr">
+        <is>
+          <t>Rusty Dagger</t>
+        </is>
+      </c>
+      <c r="D39" s="83" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="E39" s="83" t="inlineStr">
+        <is>
+          <t>dague</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B44" s="82" t="inlineStr">
+        <is>
+          <t>couteau-serpent</t>
+        </is>
+      </c>
+      <c r="C44" s="83" t="inlineStr">
+        <is>
+          <t>Serpent Knife</t>
+        </is>
+      </c>
+      <c r="D44" s="83" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="E44" s="83" t="inlineStr">
+        <is>
+          <t>poison/dague</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="84" t="n"/>
+      <c r="C45" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="C46" s="84" t="n"/>
+    </row>
+    <row r="47">
+      <c r="B47" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="C47" s="84" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B49" s="82" t="inlineStr">
+        <is>
+          <t>pic-de-glace</t>
+        </is>
+      </c>
+      <c r="C49" s="83" t="inlineStr">
+        <is>
+          <t>Ice Pick</t>
+        </is>
+      </c>
+      <c r="D49" s="83" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="E49" s="83" t="inlineStr">
+        <is>
+          <t>glace</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="C50" s="65" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="D50" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="84" t="n"/>
+      <c r="C51" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="D51" s="84" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B53" s="82" t="inlineStr">
+        <is>
+          <t>torche</t>
+        </is>
+      </c>
+      <c r="C53" s="83" t="inlineStr">
+        <is>
+          <t>Torch</t>
+        </is>
+      </c>
+      <c r="D53" s="83" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="E53" s="83" t="inlineStr">
+        <is>
+          <t>feu</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="66" t="inlineStr">
+        <is>
+          <t>Co</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B58" s="82" t="inlineStr">
+        <is>
+          <t>couteau-dentele</t>
+        </is>
+      </c>
+      <c r="C58" s="83" t="inlineStr">
+        <is>
+          <t>Serrated Knife</t>
+        </is>
+      </c>
+      <c r="D58" s="83" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="E58" s="83" t="inlineStr">
+        <is>
+          <t>saignement</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="C59" s="65" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="65" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="C60" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="84" t="n"/>
+      <c r="C61" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B63" s="82" t="inlineStr">
+        <is>
+          <t>couperet</t>
+        </is>
+      </c>
+      <c r="C63" s="83" t="inlineStr">
+        <is>
+          <t>Cleaver</t>
+        </is>
+      </c>
+      <c r="D63" s="83" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="E63" s="83" t="inlineStr">
+        <is>
+          <t>saignement</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="C64" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="C65" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="84" t="n"/>
+      <c r="C66" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B68" s="82" t="inlineStr">
+        <is>
+          <t>epee-entrainement</t>
+        </is>
+      </c>
+      <c r="C68" s="83" t="inlineStr">
+        <is>
+          <t>Training Sword</t>
+        </is>
+      </c>
+      <c r="D68" s="83" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="E68" s="83" t="inlineStr">
+        <is>
+          <t>entraînement</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="84" t="n"/>
+      <c r="C69" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="D69" s="84" t="n"/>
+    </row>
+    <row r="70">
+      <c r="B70" s="65" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="C70" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="D70" s="65" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="84" t="n"/>
+      <c r="C71" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="D71" s="84" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B73" s="82" t="inlineStr">
+        <is>
+          <t>baton</t>
+        </is>
+      </c>
+      <c r="C73" s="83" t="inlineStr">
+        <is>
+          <t>Quarterstaff</t>
+        </is>
+      </c>
+      <c r="D73" s="83" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="E73" s="83" t="inlineStr">
+        <is>
+          <t>dextérité/bois</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B79" s="82" t="inlineStr">
+        <is>
+          <t>fourche</t>
+        </is>
+      </c>
+      <c r="C79" s="83" t="inlineStr">
+        <is>
+          <t>Pitchfork</t>
+        </is>
+      </c>
+      <c r="D79" s="83" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="E79" s="83" t="inlineStr">
+        <is>
+          <t>perforant/bois</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="C80" s="65" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="D80" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" s="84" t="n"/>
+      <c r="C81" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="D81" s="84" t="n"/>
+    </row>
+    <row r="82">
+      <c r="B82" s="84" t="n"/>
+      <c r="C82" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="D82" s="84" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B84" s="82" t="inlineStr">
+        <is>
+          <t>hache-rouillee</t>
+        </is>
+      </c>
+      <c r="C84" s="83" t="inlineStr">
+        <is>
+          <t>Rusty Axe</t>
+        </is>
+      </c>
+      <c r="D84" s="83" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="E84" s="83" t="inlineStr">
+        <is>
+          <t>hache/brute</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="C85" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="C86" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" s="84" t="n"/>
+      <c r="C87" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" s="84" t="n"/>
+      <c r="C88" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B90" s="82" t="inlineStr">
+        <is>
+          <t>pioche-de-mineur</t>
+        </is>
+      </c>
+      <c r="C90" s="83" t="inlineStr">
+        <is>
+          <t>Miner's Pick</t>
+        </is>
+      </c>
+      <c r="D90" s="83" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="E90" s="83" t="inlineStr">
+        <is>
+          <t>pioche</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="C91" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="D91" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" s="84" t="n"/>
+      <c r="C92" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="D92" s="84" t="n"/>
+    </row>
+    <row r="93">
+      <c r="B93" s="84" t="n"/>
+      <c r="C93" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="D93" s="84" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B95" s="82" t="inlineStr">
+        <is>
+          <t>marteau-de-forge</t>
+        </is>
+      </c>
+      <c r="C95" s="83" t="inlineStr">
+        <is>
+          <t>Forge Hammer</t>
+        </is>
+      </c>
+      <c r="D95" s="83" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="E95" s="83" t="inlineStr">
+        <is>
+          <t>forge</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="C96" s="66" t="inlineStr">
+        <is>
+          <t>Co</t>
+        </is>
+      </c>
+      <c r="D96" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="C97" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="D97" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" s="84" t="n"/>
+      <c r="C98" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="D98" s="84" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B100" s="82" t="inlineStr">
+        <is>
+          <t>epee-large</t>
+        </is>
+      </c>
+      <c r="C100" s="83" t="inlineStr">
+        <is>
+          <t>Claymore</t>
+        </is>
+      </c>
+      <c r="D100" s="83" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="E100" s="83" t="inlineStr">
+        <is>
+          <t>force 2M</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" s="84" t="n"/>
+      <c r="C101" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="D101" s="84" t="n"/>
+    </row>
+    <row r="102">
+      <c r="B102" s="84" t="n"/>
+      <c r="C102" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="D102" s="84" t="n"/>
+    </row>
+    <row r="103">
+      <c r="B103" s="84" t="n"/>
+      <c r="C103" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="D103" s="84" t="n"/>
+    </row>
+    <row r="104">
+      <c r="B104" s="70" t="inlineStr">
+        <is>
+          <t>Au</t>
+        </is>
+      </c>
+      <c r="C104" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="D104" s="70" t="inlineStr">
+        <is>
+          <t>Au</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" s="84" t="n"/>
+      <c r="C105" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="D105" s="84" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B107" s="82" t="inlineStr">
+        <is>
+          <t>hallebarde</t>
+        </is>
+      </c>
+      <c r="C107" s="83" t="inlineStr">
+        <is>
+          <t>Halberd</t>
+        </is>
+      </c>
+      <c r="D107" s="83" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="E107" s="83" t="inlineStr">
+        <is>
+          <t>allonge/glace</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" s="84" t="n"/>
+      <c r="C108" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="D108" s="72" t="inlineStr">
+        <is>
+          <t>La</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" s="84" t="n"/>
+      <c r="C109" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="D109" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" s="84" t="n"/>
+      <c r="C110" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="D110" s="84" t="n"/>
+    </row>
+    <row r="111">
+      <c r="B111" s="84" t="n"/>
+      <c r="C111" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="D111" s="84" t="n"/>
+    </row>
+    <row r="112">
+      <c r="B112" s="84" t="n"/>
+      <c r="C112" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="D112" s="84" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B114" s="82" t="inlineStr">
+        <is>
+          <t>dague-venin</t>
+        </is>
+      </c>
+      <c r="C114" s="83" t="inlineStr">
+        <is>
+          <t>Venomfang Dagger</t>
+        </is>
+      </c>
+      <c r="D114" s="83" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="E114" s="83" t="inlineStr">
+        <is>
+          <t>poison</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" s="75" t="inlineStr">
+        <is>
+          <t>Em</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B120" s="82" t="inlineStr">
+        <is>
+          <t>lame-de-givre</t>
+        </is>
+      </c>
+      <c r="C120" s="83" t="inlineStr">
+        <is>
+          <t>Frostbrand</t>
+        </is>
+      </c>
+      <c r="D120" s="83" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="E120" s="83" t="inlineStr">
+        <is>
+          <t>glace</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" s="84" t="n"/>
+      <c r="C121" s="72" t="inlineStr">
+        <is>
+          <t>La</t>
+        </is>
+      </c>
+      <c r="D121" s="84" t="n"/>
+    </row>
+    <row r="122">
+      <c r="B122" s="84" t="n"/>
+      <c r="C122" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="D122" s="84" t="n"/>
+    </row>
+    <row r="123">
+      <c r="B123" s="70" t="inlineStr">
+        <is>
+          <t>Au</t>
+        </is>
+      </c>
+      <c r="C123" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="D123" s="70" t="inlineStr">
+        <is>
+          <t>Au</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" s="84" t="n"/>
+      <c r="C124" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="D124" s="84" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B126" s="82" t="inlineStr">
+        <is>
+          <t>lame-de-braise</t>
+        </is>
+      </c>
+      <c r="C126" s="83" t="inlineStr">
+        <is>
+          <t>Emberblade</t>
+        </is>
+      </c>
+      <c r="D126" s="83" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="E126" s="83" t="inlineStr">
+        <is>
+          <t>feu</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" s="76" t="inlineStr">
+        <is>
+          <t>Ru</t>
+        </is>
+      </c>
+      <c r="C127" s="84" t="n"/>
+      <c r="D127" s="76" t="inlineStr">
+        <is>
+          <t>Ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" s="84" t="n"/>
+      <c r="C128" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="D128" s="84" t="n"/>
+    </row>
+    <row r="129">
+      <c r="B129" s="84" t="n"/>
+      <c r="C129" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="D129" s="84" t="n"/>
+    </row>
+    <row r="130">
+      <c r="B130" s="84" t="n"/>
+      <c r="C130" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="D130" s="84" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B132" s="82" t="inlineStr">
+        <is>
+          <t>hache-faucheuse</t>
+        </is>
+      </c>
+      <c r="C132" s="83" t="inlineStr">
+        <is>
+          <t>Reaver Axe</t>
+        </is>
+      </c>
+      <c r="D132" s="83" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="E132" s="83" t="inlineStr">
+        <is>
+          <t>saignement</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="B133" s="76" t="inlineStr">
+        <is>
+          <t>Ru</t>
+        </is>
+      </c>
+      <c r="C133" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="D133" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="B134" s="84" t="n"/>
+      <c r="C134" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="D134" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="B135" s="84" t="n"/>
+      <c r="C135" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="D135" s="84" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B137" s="82" t="inlineStr">
+        <is>
+          <t>hache-berserk</t>
+        </is>
+      </c>
+      <c r="C137" s="83" t="inlineStr">
+        <is>
+          <t>Berserker Axe</t>
+        </is>
+      </c>
+      <c r="D137" s="83" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="E137" s="83" t="inlineStr">
+        <is>
+          <t>brute/fureur</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="B138" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="C138" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="D138" s="76" t="inlineStr">
+        <is>
+          <t>Ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="B139" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="C139" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="D139" s="84" t="n"/>
+    </row>
+    <row r="140">
+      <c r="B140" s="84" t="n"/>
+      <c r="C140" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="D140" s="84" t="n"/>
+    </row>
+    <row r="141">
+      <c r="B141" s="84" t="n"/>
+      <c r="C141" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="D141" s="84" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B143" s="82" t="inlineStr">
+        <is>
+          <t>marteau-guerre</t>
+        </is>
+      </c>
+      <c r="C143" s="83" t="inlineStr">
+        <is>
+          <t>Warhammer</t>
+        </is>
+      </c>
+      <c r="D143" s="83" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="E143" s="83" t="inlineStr">
+        <is>
+          <t>pierre/brute</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="B144" s="67" t="inlineStr">
+        <is>
+          <t>St</t>
+        </is>
+      </c>
+      <c r="C144" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="D144" s="67" t="inlineStr">
+        <is>
+          <t>St</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="B145" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="C145" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="D145" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="B146" s="84" t="n"/>
+      <c r="C146" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="D146" s="84" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B148" s="82" t="inlineStr">
+        <is>
+          <t>dagues-jumelles</t>
+        </is>
+      </c>
+      <c r="C148" s="83" t="inlineStr">
+        <is>
+          <t>Twin Daggers</t>
+        </is>
+      </c>
+      <c r="D148" s="83" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="E148" s="83" t="inlineStr">
+        <is>
+          <t>dextérité</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="B149" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="C149" s="84" t="n"/>
+      <c r="D149" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="B150" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="C150" s="84" t="n"/>
+      <c r="D150" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="B151" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="C151" s="84" t="n"/>
+      <c r="D151" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B153" s="82" t="inlineStr">
+        <is>
+          <t>lame-bourreau</t>
+        </is>
+      </c>
+      <c r="C153" s="83" t="inlineStr">
+        <is>
+          <t>Executioner's Blade</t>
+        </is>
+      </c>
+      <c r="D153" s="83" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="E153" s="83" t="inlineStr">
+        <is>
+          <t>exécution</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="B154" s="84" t="n"/>
+      <c r="C154" s="73" t="inlineStr">
+        <is>
+          <t>Am</t>
+        </is>
+      </c>
+      <c r="D154" s="84" t="n"/>
+    </row>
+    <row r="155">
+      <c r="B155" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="C155" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="D155" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="B156" s="84" t="n"/>
+      <c r="C156" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="D156" s="84" t="n"/>
+    </row>
+    <row r="157">
+      <c r="B157" s="84" t="n"/>
+      <c r="C157" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="D157" s="84" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B159" s="82" t="inlineStr">
+        <is>
+          <t>baguette-cristal</t>
+        </is>
+      </c>
+      <c r="C159" s="83" t="inlineStr">
+        <is>
+          <t>Crystal Wand</t>
+        </is>
+      </c>
+      <c r="D159" s="83" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="E159" s="83" t="inlineStr">
+        <is>
+          <t>arcane</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="B160" s="70" t="inlineStr">
+        <is>
+          <t>Au</t>
+        </is>
+      </c>
+      <c r="C160" s="73" t="inlineStr">
+        <is>
+          <t>Am</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="B161" s="84" t="n"/>
+      <c r="C161" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="B162" s="84" t="n"/>
+      <c r="C162" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B164" s="82" t="inlineStr">
+        <is>
+          <t>fleau-cloute</t>
+        </is>
+      </c>
+      <c r="C164" s="83" t="inlineStr">
+        <is>
+          <t>Spiked Flail</t>
+        </is>
+      </c>
+      <c r="D164" s="83" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="E164" s="83" t="inlineStr">
+        <is>
+          <t>brute/moulinet</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="B165" s="67" t="inlineStr">
+        <is>
+          <t>St</t>
+        </is>
+      </c>
+      <c r="C165" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="B166" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="C166" s="67" t="inlineStr">
+        <is>
+          <t>St</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="B167" s="84" t="n"/>
+      <c r="C167" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="B168" s="84" t="n"/>
+      <c r="C168" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B170" s="82" t="inlineStr">
+        <is>
+          <t>marteau-de-pierre</t>
+        </is>
+      </c>
+      <c r="C170" s="83" t="inlineStr">
+        <is>
+          <t>Stone Hammer</t>
+        </is>
+      </c>
+      <c r="D170" s="83" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="E170" s="83" t="inlineStr">
+        <is>
+          <t>pierre</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="B171" s="67" t="inlineStr">
+        <is>
+          <t>St</t>
+        </is>
+      </c>
+      <c r="C171" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="D171" s="67" t="inlineStr">
+        <is>
+          <t>St</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="B172" s="67" t="inlineStr">
+        <is>
+          <t>St</t>
+        </is>
+      </c>
+      <c r="C172" s="67" t="inlineStr">
+        <is>
+          <t>St</t>
+        </is>
+      </c>
+      <c r="D172" s="67" t="inlineStr">
+        <is>
+          <t>St</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="B173" s="84" t="n"/>
+      <c r="C173" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="D173" s="84" t="n"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B175" s="82" t="inlineStr">
+        <is>
+          <t>epee-sacree</t>
+        </is>
+      </c>
+      <c r="C175" s="83" t="inlineStr">
+        <is>
+          <t>Holy Sword</t>
+        </is>
+      </c>
+      <c r="D175" s="83" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="E175" s="83" t="inlineStr">
+        <is>
+          <t>sacré</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="B176" s="84" t="n"/>
+      <c r="C176" s="70" t="inlineStr">
+        <is>
+          <t>Au</t>
+        </is>
+      </c>
+      <c r="D176" s="84" t="n"/>
+    </row>
+    <row r="177">
+      <c r="B177" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="C177" s="70" t="inlineStr">
+        <is>
+          <t>Au</t>
+        </is>
+      </c>
+      <c r="D177" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="B178" s="84" t="n"/>
+      <c r="C178" s="70" t="inlineStr">
+        <is>
+          <t>Au</t>
+        </is>
+      </c>
+      <c r="D178" s="84" t="n"/>
+    </row>
+    <row r="179">
+      <c r="B179" s="84" t="n"/>
+      <c r="C179" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="D179" s="84" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B181" s="82" t="inlineStr">
+        <is>
+          <t>croc-de-basilic</t>
+        </is>
+      </c>
+      <c r="C181" s="83" t="inlineStr">
+        <is>
+          <t>Basilisk Fang</t>
+        </is>
+      </c>
+      <c r="D181" s="83" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="E181" s="83" t="inlineStr">
+        <is>
+          <t>poison</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="B182" s="84" t="n"/>
+      <c r="C182" s="75" t="inlineStr">
+        <is>
+          <t>Em</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="B183" s="71" t="inlineStr">
+        <is>
+          <t>Ma</t>
+        </is>
+      </c>
+      <c r="C183" s="75" t="inlineStr">
+        <is>
+          <t>Em</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="B184" s="84" t="n"/>
+      <c r="C184" s="71" t="inlineStr">
+        <is>
+          <t>Ma</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="B185" s="84" t="n"/>
+      <c r="C185" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B187" s="82" t="inlineStr">
+        <is>
+          <t>hache-de-guerre</t>
+        </is>
+      </c>
+      <c r="C187" s="83" t="inlineStr">
+        <is>
+          <t>War Axe</t>
+        </is>
+      </c>
+      <c r="D187" s="83" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="E187" s="83" t="inlineStr">
+        <is>
+          <t>brute 2M</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="B188" s="84" t="n"/>
+      <c r="C188" s="74" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+      <c r="D188" s="74" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="B189" s="74" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+      <c r="C189" s="74" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+      <c r="D189" s="74" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="B190" s="74" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+      <c r="C190" s="74" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+      <c r="D190" s="84" t="n"/>
+    </row>
+    <row r="191">
+      <c r="B191" s="84" t="n"/>
+      <c r="C191" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="D191" s="84" t="n"/>
+    </row>
+    <row r="192">
+      <c r="B192" s="84" t="n"/>
+      <c r="C192" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="D192" s="84" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B194" s="82" t="inlineStr">
+        <is>
+          <t>marteau-de-siege</t>
+        </is>
+      </c>
+      <c r="C194" s="83" t="inlineStr">
+        <is>
+          <t>Siege Maul</t>
+        </is>
+      </c>
+      <c r="D194" s="83" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="E194" s="83" t="inlineStr">
+        <is>
+          <t>pierre/tank 2M</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="B195" s="74" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+      <c r="C195" s="74" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+      <c r="D195" s="74" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="B196" s="74" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+      <c r="C196" s="67" t="inlineStr">
+        <is>
+          <t>St</t>
+        </is>
+      </c>
+      <c r="D196" s="74" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="B197" s="84" t="n"/>
+      <c r="C197" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="D197" s="84" t="n"/>
+    </row>
+    <row r="198">
+      <c r="B198" s="84" t="n"/>
+      <c r="C198" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="D198" s="84" t="n"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B200" s="82" t="inlineStr">
+        <is>
+          <t>marteau-de-lave</t>
+        </is>
+      </c>
+      <c r="C200" s="83" t="inlineStr">
+        <is>
+          <t>Magma Hammer</t>
+        </is>
+      </c>
+      <c r="D200" s="83" t="inlineStr">
+        <is>
+          <t>epique</t>
+        </is>
+      </c>
+      <c r="E200" s="83" t="inlineStr">
+        <is>
+          <t>feu/lave</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="B201" s="66" t="inlineStr">
+        <is>
+          <t>Co</t>
+        </is>
+      </c>
+      <c r="C201" s="76" t="inlineStr">
+        <is>
+          <t>Ru</t>
+        </is>
+      </c>
+      <c r="D201" s="66" t="inlineStr">
+        <is>
+          <t>Co</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="B202" s="76" t="inlineStr">
+        <is>
+          <t>Ru</t>
+        </is>
+      </c>
+      <c r="C202" s="79" t="inlineStr">
+        <is>
+          <t>Mi</t>
+        </is>
+      </c>
+      <c r="D202" s="76" t="inlineStr">
+        <is>
+          <t>Ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="B203" s="84" t="n"/>
+      <c r="C203" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="D203" s="84" t="n"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B205" s="82" t="inlineStr">
+        <is>
+          <t>epee-onyx</t>
+        </is>
+      </c>
+      <c r="C205" s="83" t="inlineStr">
+        <is>
+          <t>Big Onyx Sword</t>
+        </is>
+      </c>
+      <c r="D205" s="83" t="inlineStr">
+        <is>
+          <t>epique</t>
+        </is>
+      </c>
+      <c r="E205" s="83" t="inlineStr">
+        <is>
+          <t>onyx 2M</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="B206" s="84" t="n"/>
+      <c r="C206" s="80" t="inlineStr">
+        <is>
+          <t>On</t>
+        </is>
+      </c>
+      <c r="D206" s="84" t="n"/>
+    </row>
+    <row r="207">
+      <c r="B207" s="84" t="n"/>
+      <c r="C207" s="80" t="inlineStr">
+        <is>
+          <t>On</t>
+        </is>
+      </c>
+      <c r="D207" s="84" t="n"/>
+    </row>
+    <row r="208">
+      <c r="B208" s="79" t="inlineStr">
+        <is>
+          <t>Mi</t>
+        </is>
+      </c>
+      <c r="C208" s="80" t="inlineStr">
+        <is>
+          <t>On</t>
+        </is>
+      </c>
+      <c r="D208" s="79" t="inlineStr">
+        <is>
+          <t>Mi</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="B209" s="84" t="n"/>
+      <c r="C209" s="80" t="inlineStr">
+        <is>
+          <t>On</t>
+        </is>
+      </c>
+      <c r="D209" s="84" t="n"/>
+    </row>
+    <row r="210">
+      <c r="B210" s="84" t="n"/>
+      <c r="C210" s="74" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+      <c r="D210" s="84" t="n"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B212" s="82" t="inlineStr">
+        <is>
+          <t>grande-faux</t>
+        </is>
+      </c>
+      <c r="C212" s="83" t="inlineStr">
+        <is>
+          <t>Great Scythe</t>
+        </is>
+      </c>
+      <c r="D212" s="83" t="inlineStr">
+        <is>
+          <t>epique</t>
+        </is>
+      </c>
+      <c r="E212" s="83" t="inlineStr">
+        <is>
+          <t>saignement/mort 2M</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="B213" s="80" t="inlineStr">
+        <is>
+          <t>On</t>
+        </is>
+      </c>
+      <c r="C213" s="80" t="inlineStr">
+        <is>
+          <t>On</t>
+        </is>
+      </c>
+      <c r="D213" s="76" t="inlineStr">
+        <is>
+          <t>Ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="B214" s="79" t="inlineStr">
+        <is>
+          <t>Mi</t>
+        </is>
+      </c>
+      <c r="C214" s="84" t="n"/>
+      <c r="D214" s="84" t="n"/>
+    </row>
+    <row r="215">
+      <c r="B215" s="79" t="inlineStr">
+        <is>
+          <t>Mi</t>
+        </is>
+      </c>
+      <c r="C215" s="84" t="n"/>
+      <c r="D215" s="84" t="n"/>
+    </row>
+    <row r="216">
+      <c r="B216" s="79" t="inlineStr">
+        <is>
+          <t>Mi</t>
+        </is>
+      </c>
+      <c r="C216" s="84" t="n"/>
+      <c r="D216" s="84" t="n"/>
+    </row>
+    <row r="217">
+      <c r="B217" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="C217" s="84" t="n"/>
+      <c r="D217" s="84" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/BRUTAL-items-et-cartes.xlsx
+++ b/docs/BRUTAL-items-et-cartes.xlsx
@@ -15102,15 +15102,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F217"/>
+  <dimension ref="A1:F553"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" style="57" min="1" max="1"/>
-    <col width="14" customWidth="1" style="57" min="2" max="2"/>
-    <col width="14" customWidth="1" style="57" min="3" max="3"/>
-    <col width="14" customWidth="1" style="57" min="4" max="4"/>
-    <col width="14" customWidth="1" style="57" min="5" max="5"/>
-    <col width="14" customWidth="1" style="57" min="6" max="6"/>
+    <col width="14" customWidth="1" style="57" min="1" max="1"/>
+    <col width="16" customWidth="1" style="57" min="2" max="2"/>
+    <col width="16" customWidth="1" style="57" min="3" max="3"/>
+    <col width="16" customWidth="1" style="57" min="4" max="4"/>
+    <col width="16" customWidth="1" style="57" min="5" max="5"/>
+    <col width="16" customWidth="1" style="57" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15130,7 +15130,7 @@
     <row r="3">
       <c r="A3" s="62" t="inlineStr">
         <is>
-          <t>Un bloc = une arme. Ligne « ARME » = en-tête. Dessous : la grille (codes 2 lettres, case vide = rien).</t>
+          <t>Un bloc = un objet. Ligne « ARME » = en-tête (id, nom, rareté, thème). Dessous : la grille (codes 2 lettres ; case vide = rien).</t>
         </is>
       </c>
     </row>
@@ -17757,6 +17757,4183 @@
       </c>
       <c r="C217" s="84" t="n"/>
       <c r="D217" s="84" t="n"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B219" s="82" t="inlineStr">
+        <is>
+          <t>armure-cuir</t>
+        </is>
+      </c>
+      <c r="C219" s="83" t="inlineStr">
+        <is>
+          <t>Leather Armor</t>
+        </is>
+      </c>
+      <c r="D219" s="83" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="E219" s="83" t="inlineStr">
+        <is>
+          <t>cuir</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="B220" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="C220" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="D220" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="B221" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="C221" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="D221" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B223" s="82" t="inlineStr">
+        <is>
+          <t>gilet-rembourre</t>
+        </is>
+      </c>
+      <c r="C223" s="83" t="inlineStr">
+        <is>
+          <t>Padded Vest</t>
+        </is>
+      </c>
+      <c r="D223" s="83" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="E223" s="83" t="inlineStr">
+        <is>
+          <t>matelassé</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="B224" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="C224" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="D224" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="B225" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="C225" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="D225" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B227" s="82" t="inlineStr">
+        <is>
+          <t>cotte-mailles</t>
+        </is>
+      </c>
+      <c r="C227" s="83" t="inlineStr">
+        <is>
+          <t>Chainmail</t>
+        </is>
+      </c>
+      <c r="D227" s="83" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="E227" s="83" t="inlineStr">
+        <is>
+          <t>mailles</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="B228" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="C228" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="D228" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="B229" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="C229" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="D229" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B231" s="82" t="inlineStr">
+        <is>
+          <t>armure-peau</t>
+        </is>
+      </c>
+      <c r="C231" s="83" t="inlineStr">
+        <is>
+          <t>Hide Armor</t>
+        </is>
+      </c>
+      <c r="D231" s="83" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="E231" s="83" t="inlineStr">
+        <is>
+          <t>peau</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="B232" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="C232" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="D232" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="B233" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="C233" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="D233" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B235" s="82" t="inlineStr">
+        <is>
+          <t>tenue-de-voyageur</t>
+        </is>
+      </c>
+      <c r="C235" s="83" t="inlineStr">
+        <is>
+          <t>Traveler's Garb</t>
+        </is>
+      </c>
+      <c r="D235" s="83" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="E235" s="83" t="inlineStr">
+        <is>
+          <t>léger</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="B236" s="65" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="C236" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="D236" s="65" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="B237" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="C237" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="D237" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B239" s="82" t="inlineStr">
+        <is>
+          <t>plaque-de-fer</t>
+        </is>
+      </c>
+      <c r="C239" s="83" t="inlineStr">
+        <is>
+          <t>Basic Iron Plate</t>
+        </is>
+      </c>
+      <c r="D239" s="83" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="E239" s="83" t="inlineStr">
+        <is>
+          <t>plaque</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="B240" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="C240" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="D240" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="B241" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="C241" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="D241" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="B242" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="C242" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="D242" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B244" s="82" t="inlineStr">
+        <is>
+          <t>armure-cloutee</t>
+        </is>
+      </c>
+      <c r="C244" s="83" t="inlineStr">
+        <is>
+          <t>Spiked Armor</t>
+        </is>
+      </c>
+      <c r="D244" s="83" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="E244" s="83" t="inlineStr">
+        <is>
+          <t>cloutée</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="B245" s="67" t="inlineStr">
+        <is>
+          <t>St</t>
+        </is>
+      </c>
+      <c r="C245" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="D245" s="67" t="inlineStr">
+        <is>
+          <t>St</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="B246" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="C246" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="D246" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="B247" s="67" t="inlineStr">
+        <is>
+          <t>St</t>
+        </is>
+      </c>
+      <c r="C247" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="D247" s="67" t="inlineStr">
+        <is>
+          <t>St</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B249" s="82" t="inlineStr">
+        <is>
+          <t>peau-berserk</t>
+        </is>
+      </c>
+      <c r="C249" s="83" t="inlineStr">
+        <is>
+          <t>Berserker Hide</t>
+        </is>
+      </c>
+      <c r="D249" s="83" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="E249" s="83" t="inlineStr">
+        <is>
+          <t>rage/sang</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="B250" s="76" t="inlineStr">
+        <is>
+          <t>Ru</t>
+        </is>
+      </c>
+      <c r="C250" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="D250" s="76" t="inlineStr">
+        <is>
+          <t>Ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="B251" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="C251" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="D251" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B253" s="82" t="inlineStr">
+        <is>
+          <t>armure-stone-age</t>
+        </is>
+      </c>
+      <c r="C253" s="83" t="inlineStr">
+        <is>
+          <t>Stone Armor</t>
+        </is>
+      </c>
+      <c r="D253" s="83" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="E253" s="83" t="inlineStr">
+        <is>
+          <t>pierre (set)</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="B254" s="67" t="inlineStr">
+        <is>
+          <t>St</t>
+        </is>
+      </c>
+      <c r="C254" s="67" t="inlineStr">
+        <is>
+          <t>St</t>
+        </is>
+      </c>
+      <c r="D254" s="67" t="inlineStr">
+        <is>
+          <t>St</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="B255" s="67" t="inlineStr">
+        <is>
+          <t>St</t>
+        </is>
+      </c>
+      <c r="C255" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="D255" s="67" t="inlineStr">
+        <is>
+          <t>St</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B257" s="82" t="inlineStr">
+        <is>
+          <t>plate-croise</t>
+        </is>
+      </c>
+      <c r="C257" s="83" t="inlineStr">
+        <is>
+          <t>Crusader Plate</t>
+        </is>
+      </c>
+      <c r="D257" s="83" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="E257" s="83" t="inlineStr">
+        <is>
+          <t>sacré</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="B258" s="70" t="inlineStr">
+        <is>
+          <t>Au</t>
+        </is>
+      </c>
+      <c r="C258" s="74" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+      <c r="D258" s="70" t="inlineStr">
+        <is>
+          <t>Au</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="B259" s="74" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+      <c r="C259" s="74" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+      <c r="D259" s="74" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="B260" s="70" t="inlineStr">
+        <is>
+          <t>Au</t>
+        </is>
+      </c>
+      <c r="C260" s="74" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+      <c r="D260" s="70" t="inlineStr">
+        <is>
+          <t>Au</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B262" s="82" t="inlineStr">
+        <is>
+          <t>plate-sang</t>
+        </is>
+      </c>
+      <c r="C262" s="83" t="inlineStr">
+        <is>
+          <t>Blood Plate</t>
+        </is>
+      </c>
+      <c r="D262" s="83" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="E262" s="83" t="inlineStr">
+        <is>
+          <t>sang</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="B263" s="76" t="inlineStr">
+        <is>
+          <t>Ru</t>
+        </is>
+      </c>
+      <c r="C263" s="74" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+      <c r="D263" s="76" t="inlineStr">
+        <is>
+          <t>Ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="B264" s="74" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+      <c r="C264" s="74" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+      <c r="D264" s="74" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="B265" s="76" t="inlineStr">
+        <is>
+          <t>Ru</t>
+        </is>
+      </c>
+      <c r="C265" s="74" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+      <c r="D265" s="76" t="inlineStr">
+        <is>
+          <t>Ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B267" s="82" t="inlineStr">
+        <is>
+          <t>maille-de-forge</t>
+        </is>
+      </c>
+      <c r="C267" s="83" t="inlineStr">
+        <is>
+          <t>Forgemaster's Mail</t>
+        </is>
+      </c>
+      <c r="D267" s="83" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="E267" s="83" t="inlineStr">
+        <is>
+          <t>forge</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="B268" s="74" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+      <c r="C268" s="66" t="inlineStr">
+        <is>
+          <t>Co</t>
+        </is>
+      </c>
+      <c r="D268" s="74" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="B269" s="66" t="inlineStr">
+        <is>
+          <t>Co</t>
+        </is>
+      </c>
+      <c r="C269" s="70" t="inlineStr">
+        <is>
+          <t>Au</t>
+        </is>
+      </c>
+      <c r="D269" s="66" t="inlineStr">
+        <is>
+          <t>Co</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="B270" s="74" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+      <c r="C270" s="66" t="inlineStr">
+        <is>
+          <t>Co</t>
+        </is>
+      </c>
+      <c r="D270" s="74" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B272" s="82" t="inlineStr">
+        <is>
+          <t>plate-onyx</t>
+        </is>
+      </c>
+      <c r="C272" s="83" t="inlineStr">
+        <is>
+          <t>Onyx Guard Plate</t>
+        </is>
+      </c>
+      <c r="D272" s="83" t="inlineStr">
+        <is>
+          <t>epique</t>
+        </is>
+      </c>
+      <c r="E272" s="83" t="inlineStr">
+        <is>
+          <t>onyx</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="B273" s="80" t="inlineStr">
+        <is>
+          <t>On</t>
+        </is>
+      </c>
+      <c r="C273" s="79" t="inlineStr">
+        <is>
+          <t>Mi</t>
+        </is>
+      </c>
+      <c r="D273" s="80" t="inlineStr">
+        <is>
+          <t>On</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="B274" s="79" t="inlineStr">
+        <is>
+          <t>Mi</t>
+        </is>
+      </c>
+      <c r="C274" s="80" t="inlineStr">
+        <is>
+          <t>On</t>
+        </is>
+      </c>
+      <c r="D274" s="79" t="inlineStr">
+        <is>
+          <t>Mi</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="B275" s="80" t="inlineStr">
+        <is>
+          <t>On</t>
+        </is>
+      </c>
+      <c r="C275" s="79" t="inlineStr">
+        <is>
+          <t>Mi</t>
+        </is>
+      </c>
+      <c r="D275" s="80" t="inlineStr">
+        <is>
+          <t>On</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B277" s="82" t="inlineStr">
+        <is>
+          <t>bottes-usees</t>
+        </is>
+      </c>
+      <c r="C277" s="83" t="inlineStr">
+        <is>
+          <t>Worn Boots</t>
+        </is>
+      </c>
+      <c r="D277" s="83" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="E277" s="83" t="inlineStr">
+        <is>
+          <t>usé</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="B278" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="C278" s="84" t="n"/>
+    </row>
+    <row r="279">
+      <c r="B279" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="C279" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B281" s="82" t="inlineStr">
+        <is>
+          <t>bottes-cuir</t>
+        </is>
+      </c>
+      <c r="C281" s="83" t="inlineStr">
+        <is>
+          <t>Leather Boots</t>
+        </is>
+      </c>
+      <c r="D281" s="83" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="E281" s="83" t="inlineStr">
+        <is>
+          <t>cuir</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="B282" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="C282" s="84" t="n"/>
+    </row>
+    <row r="283">
+      <c r="B283" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="C283" s="84" t="n"/>
+    </row>
+    <row r="284">
+      <c r="B284" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="C284" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B286" s="82" t="inlineStr">
+        <is>
+          <t>bottes-voyage</t>
+        </is>
+      </c>
+      <c r="C286" s="83" t="inlineStr">
+        <is>
+          <t>Traveler Boots</t>
+        </is>
+      </c>
+      <c r="D286" s="83" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="E286" s="83" t="inlineStr">
+        <is>
+          <t>voyage</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="B287" s="65" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="C287" s="84" t="n"/>
+    </row>
+    <row r="288">
+      <c r="B288" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="C288" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B290" s="82" t="inlineStr">
+        <is>
+          <t>sandales</t>
+        </is>
+      </c>
+      <c r="C290" s="83" t="inlineStr">
+        <is>
+          <t>Sandals</t>
+        </is>
+      </c>
+      <c r="D290" s="83" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="E290" s="83" t="inlineStr">
+        <is>
+          <t>léger</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="B291" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="C291" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B293" s="82" t="inlineStr">
+        <is>
+          <t>bottes-rapides</t>
+        </is>
+      </c>
+      <c r="C293" s="83" t="inlineStr">
+        <is>
+          <t>Swift Striders</t>
+        </is>
+      </c>
+      <c r="D293" s="83" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="E293" s="83" t="inlineStr">
+        <is>
+          <t>vitesse</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="B294" s="75" t="inlineStr">
+        <is>
+          <t>Em</t>
+        </is>
+      </c>
+      <c r="C294" s="84" t="n"/>
+    </row>
+    <row r="295">
+      <c r="B295" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="C295" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B297" s="82" t="inlineStr">
+        <is>
+          <t>bottes-pierre</t>
+        </is>
+      </c>
+      <c r="C297" s="83" t="inlineStr">
+        <is>
+          <t>Stonetread Boots</t>
+        </is>
+      </c>
+      <c r="D297" s="83" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="E297" s="83" t="inlineStr">
+        <is>
+          <t>pierre</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="B298" s="67" t="inlineStr">
+        <is>
+          <t>St</t>
+        </is>
+      </c>
+      <c r="C298" s="84" t="n"/>
+    </row>
+    <row r="299">
+      <c r="B299" s="67" t="inlineStr">
+        <is>
+          <t>St</t>
+        </is>
+      </c>
+      <c r="C299" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B301" s="82" t="inlineStr">
+        <is>
+          <t>bottes-braise</t>
+        </is>
+      </c>
+      <c r="C301" s="83" t="inlineStr">
+        <is>
+          <t>Ember Striders</t>
+        </is>
+      </c>
+      <c r="D301" s="83" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="E301" s="83" t="inlineStr">
+        <is>
+          <t>feu</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="B302" s="76" t="inlineStr">
+        <is>
+          <t>Ru</t>
+        </is>
+      </c>
+      <c r="C302" s="84" t="n"/>
+    </row>
+    <row r="303">
+      <c r="B303" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="C303" s="66" t="inlineStr">
+        <is>
+          <t>Co</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B305" s="82" t="inlineStr">
+        <is>
+          <t>bottes-stone-age</t>
+        </is>
+      </c>
+      <c r="C305" s="83" t="inlineStr">
+        <is>
+          <t>Stone Boots</t>
+        </is>
+      </c>
+      <c r="D305" s="83" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="E305" s="83" t="inlineStr">
+        <is>
+          <t>pierre (set)</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="B306" s="67" t="inlineStr">
+        <is>
+          <t>St</t>
+        </is>
+      </c>
+      <c r="C306" s="67" t="inlineStr">
+        <is>
+          <t>St</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="B307" s="67" t="inlineStr">
+        <is>
+          <t>St</t>
+        </is>
+      </c>
+      <c r="C307" s="84" t="n"/>
+    </row>
+    <row r="309">
+      <c r="A309" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B309" s="82" t="inlineStr">
+        <is>
+          <t>bottes-vives</t>
+        </is>
+      </c>
+      <c r="C309" s="83" t="inlineStr">
+        <is>
+          <t>Swift Boots</t>
+        </is>
+      </c>
+      <c r="D309" s="83" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="E309" s="83" t="inlineStr">
+        <is>
+          <t>vitesse</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="B310" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="C310" s="75" t="inlineStr">
+        <is>
+          <t>Em</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="B311" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="C311" s="84" t="n"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B313" s="82" t="inlineStr">
+        <is>
+          <t>bottes-de-maille</t>
+        </is>
+      </c>
+      <c r="C313" s="83" t="inlineStr">
+        <is>
+          <t>Mail Boots</t>
+        </is>
+      </c>
+      <c r="D313" s="83" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="E313" s="83" t="inlineStr">
+        <is>
+          <t>mailles</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="B314" s="74" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+      <c r="C314" s="74" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="B315" s="74" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+      <c r="C315" s="84" t="n"/>
+    </row>
+    <row r="316">
+      <c r="B316" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="C316" s="84" t="n"/>
+    </row>
+    <row r="318">
+      <c r="A318" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B318" s="82" t="inlineStr">
+        <is>
+          <t>bottes-croise</t>
+        </is>
+      </c>
+      <c r="C318" s="83" t="inlineStr">
+        <is>
+          <t>Crusader Greaves</t>
+        </is>
+      </c>
+      <c r="D318" s="83" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="E318" s="83" t="inlineStr">
+        <is>
+          <t>sacré</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="B319" s="70" t="inlineStr">
+        <is>
+          <t>Au</t>
+        </is>
+      </c>
+      <c r="C319" s="74" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="B320" s="74" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+      <c r="C320" s="84" t="n"/>
+    </row>
+    <row r="321">
+      <c r="B321" s="74" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+      <c r="C321" s="84" t="n"/>
+    </row>
+    <row r="323">
+      <c r="A323" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B323" s="82" t="inlineStr">
+        <is>
+          <t>bottes-sang</t>
+        </is>
+      </c>
+      <c r="C323" s="83" t="inlineStr">
+        <is>
+          <t>Blood Greaves</t>
+        </is>
+      </c>
+      <c r="D323" s="83" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="E323" s="83" t="inlineStr">
+        <is>
+          <t>sang</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="B324" s="76" t="inlineStr">
+        <is>
+          <t>Ru</t>
+        </is>
+      </c>
+      <c r="C324" s="74" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="B325" s="74" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+      <c r="C325" s="84" t="n"/>
+    </row>
+    <row r="326">
+      <c r="B326" s="74" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+      <c r="C326" s="84" t="n"/>
+    </row>
+    <row r="328">
+      <c r="A328" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B328" s="82" t="inlineStr">
+        <is>
+          <t>bottes-onyx</t>
+        </is>
+      </c>
+      <c r="C328" s="83" t="inlineStr">
+        <is>
+          <t>Onyx Boots</t>
+        </is>
+      </c>
+      <c r="D328" s="83" t="inlineStr">
+        <is>
+          <t>epique</t>
+        </is>
+      </c>
+      <c r="E328" s="83" t="inlineStr">
+        <is>
+          <t>onyx</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="B329" s="80" t="inlineStr">
+        <is>
+          <t>On</t>
+        </is>
+      </c>
+      <c r="C329" s="79" t="inlineStr">
+        <is>
+          <t>Mi</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="B330" s="80" t="inlineStr">
+        <is>
+          <t>On</t>
+        </is>
+      </c>
+      <c r="C330" s="84" t="n"/>
+    </row>
+    <row r="331">
+      <c r="B331" s="79" t="inlineStr">
+        <is>
+          <t>Mi</t>
+        </is>
+      </c>
+      <c r="C331" s="84" t="n"/>
+    </row>
+    <row r="333">
+      <c r="A333" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B333" s="82" t="inlineStr">
+        <is>
+          <t>gants-tissu</t>
+        </is>
+      </c>
+      <c r="C333" s="83" t="inlineStr">
+        <is>
+          <t>Cloth Gloves</t>
+        </is>
+      </c>
+      <c r="D333" s="83" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="E333" s="83" t="inlineStr">
+        <is>
+          <t>tissu</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="B334" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="C334" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="B335" s="84" t="n"/>
+      <c r="C335" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B337" s="82" t="inlineStr">
+        <is>
+          <t>gants-travail</t>
+        </is>
+      </c>
+      <c r="C337" s="83" t="inlineStr">
+        <is>
+          <t>Work Gloves</t>
+        </is>
+      </c>
+      <c r="D337" s="83" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="E337" s="83" t="inlineStr">
+        <is>
+          <t>travail</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="B338" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="C338" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="B339" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="C339" s="84" t="n"/>
+    </row>
+    <row r="341">
+      <c r="A341" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B341" s="82" t="inlineStr">
+        <is>
+          <t>gants-cuir</t>
+        </is>
+      </c>
+      <c r="C341" s="83" t="inlineStr">
+        <is>
+          <t>Leather Gloves</t>
+        </is>
+      </c>
+      <c r="D341" s="83" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="E341" s="83" t="inlineStr">
+        <is>
+          <t>cuir</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="B342" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="C342" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="B343" s="84" t="n"/>
+      <c r="C343" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B345" s="82" t="inlineStr">
+        <is>
+          <t>gants-cloutes</t>
+        </is>
+      </c>
+      <c r="C345" s="83" t="inlineStr">
+        <is>
+          <t>Studded Gloves</t>
+        </is>
+      </c>
+      <c r="D345" s="83" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="E345" s="83" t="inlineStr">
+        <is>
+          <t>clous</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="B346" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="C346" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="B347" s="66" t="inlineStr">
+        <is>
+          <t>Co</t>
+        </is>
+      </c>
+      <c r="C347" s="84" t="n"/>
+    </row>
+    <row r="349">
+      <c r="A349" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B349" s="82" t="inlineStr">
+        <is>
+          <t>gants-de-mineur</t>
+        </is>
+      </c>
+      <c r="C349" s="83" t="inlineStr">
+        <is>
+          <t>Miner's Gloves</t>
+        </is>
+      </c>
+      <c r="D349" s="83" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="E349" s="83" t="inlineStr">
+        <is>
+          <t>mine</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="B350" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="C350" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="B351" s="84" t="n"/>
+      <c r="C351" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B353" s="82" t="inlineStr">
+        <is>
+          <t>gants-voleur</t>
+        </is>
+      </c>
+      <c r="C353" s="83" t="inlineStr">
+        <is>
+          <t>Thief's Gloves</t>
+        </is>
+      </c>
+      <c r="D353" s="83" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="E353" s="83" t="inlineStr">
+        <is>
+          <t>agile</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="B354" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="C354" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="B355" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="C355" s="84" t="n"/>
+    </row>
+    <row r="357">
+      <c r="A357" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B357" s="82" t="inlineStr">
+        <is>
+          <t>gantelets</t>
+        </is>
+      </c>
+      <c r="C357" s="83" t="inlineStr">
+        <is>
+          <t>Gauntlets</t>
+        </is>
+      </c>
+      <c r="D357" s="83" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="E357" s="83" t="inlineStr">
+        <is>
+          <t>force</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="B358" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="C358" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="B359" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="C359" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B361" s="82" t="inlineStr">
+        <is>
+          <t>gants-venin</t>
+        </is>
+      </c>
+      <c r="C361" s="83" t="inlineStr">
+        <is>
+          <t>Venom Gloves</t>
+        </is>
+      </c>
+      <c r="D361" s="83" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="E361" s="83" t="inlineStr">
+        <is>
+          <t>poison</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="B362" s="75" t="inlineStr">
+        <is>
+          <t>Em</t>
+        </is>
+      </c>
+      <c r="C362" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="B363" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="C363" s="84" t="n"/>
+    </row>
+    <row r="365">
+      <c r="A365" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B365" s="82" t="inlineStr">
+        <is>
+          <t>gants-stone-age</t>
+        </is>
+      </c>
+      <c r="C365" s="83" t="inlineStr">
+        <is>
+          <t>Stone Glove</t>
+        </is>
+      </c>
+      <c r="D365" s="83" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="E365" s="83" t="inlineStr">
+        <is>
+          <t>pierre (set)</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="B366" s="67" t="inlineStr">
+        <is>
+          <t>St</t>
+        </is>
+      </c>
+      <c r="C366" s="67" t="inlineStr">
+        <is>
+          <t>St</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="B367" s="67" t="inlineStr">
+        <is>
+          <t>St</t>
+        </is>
+      </c>
+      <c r="C367" s="67" t="inlineStr">
+        <is>
+          <t>St</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B369" s="82" t="inlineStr">
+        <is>
+          <t>gants-chance</t>
+        </is>
+      </c>
+      <c r="C369" s="83" t="inlineStr">
+        <is>
+          <t>Lucky Glove</t>
+        </is>
+      </c>
+      <c r="D369" s="83" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="E369" s="83" t="inlineStr">
+        <is>
+          <t>chance</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="B370" s="70" t="inlineStr">
+        <is>
+          <t>Au</t>
+        </is>
+      </c>
+      <c r="C370" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="B371" s="84" t="n"/>
+      <c r="C371" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B373" s="82" t="inlineStr">
+        <is>
+          <t>gants-de-maille</t>
+        </is>
+      </c>
+      <c r="C373" s="83" t="inlineStr">
+        <is>
+          <t>Mail Glove</t>
+        </is>
+      </c>
+      <c r="D373" s="83" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="E373" s="83" t="inlineStr">
+        <is>
+          <t>mailles</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="B374" s="74" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+      <c r="C374" s="74" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="B375" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="C375" s="84" t="n"/>
+    </row>
+    <row r="377">
+      <c r="A377" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B377" s="82" t="inlineStr">
+        <is>
+          <t>gants-croise</t>
+        </is>
+      </c>
+      <c r="C377" s="83" t="inlineStr">
+        <is>
+          <t>Crusader Gauntlets</t>
+        </is>
+      </c>
+      <c r="D377" s="83" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="E377" s="83" t="inlineStr">
+        <is>
+          <t>sacré</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="B378" s="70" t="inlineStr">
+        <is>
+          <t>Au</t>
+        </is>
+      </c>
+      <c r="C378" s="74" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="B379" s="74" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+      <c r="C379" s="74" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B381" s="82" t="inlineStr">
+        <is>
+          <t>gants-sang</t>
+        </is>
+      </c>
+      <c r="C381" s="83" t="inlineStr">
+        <is>
+          <t>Blood Gauntlets</t>
+        </is>
+      </c>
+      <c r="D381" s="83" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="E381" s="83" t="inlineStr">
+        <is>
+          <t>sang</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="B382" s="76" t="inlineStr">
+        <is>
+          <t>Ru</t>
+        </is>
+      </c>
+      <c r="C382" s="74" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="B383" s="74" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+      <c r="C383" s="74" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B385" s="82" t="inlineStr">
+        <is>
+          <t>gants-onyx</t>
+        </is>
+      </c>
+      <c r="C385" s="83" t="inlineStr">
+        <is>
+          <t>Onyx Glove</t>
+        </is>
+      </c>
+      <c r="D385" s="83" t="inlineStr">
+        <is>
+          <t>epique</t>
+        </is>
+      </c>
+      <c r="E385" s="83" t="inlineStr">
+        <is>
+          <t>onyx</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="B386" s="80" t="inlineStr">
+        <is>
+          <t>On</t>
+        </is>
+      </c>
+      <c r="C386" s="80" t="inlineStr">
+        <is>
+          <t>On</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="B387" s="79" t="inlineStr">
+        <is>
+          <t>Mi</t>
+        </is>
+      </c>
+      <c r="C387" s="84" t="n"/>
+    </row>
+    <row r="389">
+      <c r="A389" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B389" s="82" t="inlineStr">
+        <is>
+          <t>anneau-etincelle</t>
+        </is>
+      </c>
+      <c r="C389" s="83" t="inlineStr">
+        <is>
+          <t>Spark Ring</t>
+        </is>
+      </c>
+      <c r="D389" s="83" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="E389" s="83" t="inlineStr">
+        <is>
+          <t>foudre</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="B390" s="65" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="C390" s="72" t="inlineStr">
+        <is>
+          <t>La</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B392" s="82" t="inlineStr">
+        <is>
+          <t>anneau-venin</t>
+        </is>
+      </c>
+      <c r="C392" s="83" t="inlineStr">
+        <is>
+          <t>Venom Ring</t>
+        </is>
+      </c>
+      <c r="D392" s="83" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="E392" s="83" t="inlineStr">
+        <is>
+          <t>poison</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="B393" s="75" t="inlineStr">
+        <is>
+          <t>Em</t>
+        </is>
+      </c>
+      <c r="C393" s="65" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B395" s="82" t="inlineStr">
+        <is>
+          <t>anneau-braise</t>
+        </is>
+      </c>
+      <c r="C395" s="83" t="inlineStr">
+        <is>
+          <t>Ember Ring</t>
+        </is>
+      </c>
+      <c r="D395" s="83" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="E395" s="83" t="inlineStr">
+        <is>
+          <t>feu</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="B396" s="65" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="B397" s="76" t="inlineStr">
+        <is>
+          <t>Ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B399" s="82" t="inlineStr">
+        <is>
+          <t>anneau-frimas</t>
+        </is>
+      </c>
+      <c r="C399" s="83" t="inlineStr">
+        <is>
+          <t>Frost Band</t>
+        </is>
+      </c>
+      <c r="D399" s="83" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="E399" s="83" t="inlineStr">
+        <is>
+          <t>glace</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="B400" s="72" t="inlineStr">
+        <is>
+          <t>La</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="B401" s="65" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B403" s="82" t="inlineStr">
+        <is>
+          <t>anneau-saignant</t>
+        </is>
+      </c>
+      <c r="C403" s="83" t="inlineStr">
+        <is>
+          <t>Bleeding Ring</t>
+        </is>
+      </c>
+      <c r="D403" s="83" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="E403" s="83" t="inlineStr">
+        <is>
+          <t>sang</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="B404" s="76" t="inlineStr">
+        <is>
+          <t>Ru</t>
+        </is>
+      </c>
+      <c r="C404" s="65" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B406" s="82" t="inlineStr">
+        <is>
+          <t>anneau-force</t>
+        </is>
+      </c>
+      <c r="C406" s="83" t="inlineStr">
+        <is>
+          <t>Power Ring</t>
+        </is>
+      </c>
+      <c r="D406" s="83" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="E406" s="83" t="inlineStr">
+        <is>
+          <t>force</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="B407" s="65" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="C407" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B409" s="82" t="inlineStr">
+        <is>
+          <t>anneau-pierre</t>
+        </is>
+      </c>
+      <c r="C409" s="83" t="inlineStr">
+        <is>
+          <t>Stone Ring</t>
+        </is>
+      </c>
+      <c r="D409" s="83" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="E409" s="83" t="inlineStr">
+        <is>
+          <t>pierre</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="B410" s="67" t="inlineStr">
+        <is>
+          <t>St</t>
+        </is>
+      </c>
+      <c r="C410" s="65" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B412" s="82" t="inlineStr">
+        <is>
+          <t>anneau-agile</t>
+        </is>
+      </c>
+      <c r="C412" s="83" t="inlineStr">
+        <is>
+          <t>Nimble Ring</t>
+        </is>
+      </c>
+      <c r="D412" s="83" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="E412" s="83" t="inlineStr">
+        <is>
+          <t>agile</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="B413" s="65" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="B414" s="75" t="inlineStr">
+        <is>
+          <t>Em</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B416" s="82" t="inlineStr">
+        <is>
+          <t>anneau-vigueur</t>
+        </is>
+      </c>
+      <c r="C416" s="83" t="inlineStr">
+        <is>
+          <t>Vigor Ring</t>
+        </is>
+      </c>
+      <c r="D416" s="83" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="E416" s="83" t="inlineStr">
+        <is>
+          <t>vigueur</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="B417" s="71" t="inlineStr">
+        <is>
+          <t>Ma</t>
+        </is>
+      </c>
+      <c r="C417" s="65" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B419" s="82" t="inlineStr">
+        <is>
+          <t>anneau-de-fer</t>
+        </is>
+      </c>
+      <c r="C419" s="83" t="inlineStr">
+        <is>
+          <t>Iron Ring</t>
+        </is>
+      </c>
+      <c r="D419" s="83" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="E419" s="83" t="inlineStr">
+        <is>
+          <t>fer</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="B420" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="C420" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="B421" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="C421" s="84" t="n"/>
+    </row>
+    <row r="423">
+      <c r="A423" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B423" s="82" t="inlineStr">
+        <is>
+          <t>bague-de-sang</t>
+        </is>
+      </c>
+      <c r="C423" s="83" t="inlineStr">
+        <is>
+          <t>Blood Ring</t>
+        </is>
+      </c>
+      <c r="D423" s="83" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="E423" s="83" t="inlineStr">
+        <is>
+          <t>sang</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="B424" s="76" t="inlineStr">
+        <is>
+          <t>Ru</t>
+        </is>
+      </c>
+      <c r="C424" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="B425" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="C425" s="84" t="n"/>
+    </row>
+    <row r="427">
+      <c r="A427" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B427" s="82" t="inlineStr">
+        <is>
+          <t>anneau-de-givre</t>
+        </is>
+      </c>
+      <c r="C427" s="83" t="inlineStr">
+        <is>
+          <t>Frost Ring</t>
+        </is>
+      </c>
+      <c r="D427" s="83" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="E427" s="83" t="inlineStr">
+        <is>
+          <t>glace</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="B428" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="B429" s="72" t="inlineStr">
+        <is>
+          <t>La</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="B430" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B432" s="82" t="inlineStr">
+        <is>
+          <t>anneau-toxique</t>
+        </is>
+      </c>
+      <c r="C432" s="83" t="inlineStr">
+        <is>
+          <t>Toxic Ring</t>
+        </is>
+      </c>
+      <c r="D432" s="83" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="E432" s="83" t="inlineStr">
+        <is>
+          <t>poison</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="B433" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="B434" s="75" t="inlineStr">
+        <is>
+          <t>Em</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="B435" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B437" s="82" t="inlineStr">
+        <is>
+          <t>anneau-puissance</t>
+        </is>
+      </c>
+      <c r="C437" s="83" t="inlineStr">
+        <is>
+          <t>Ring of Might</t>
+        </is>
+      </c>
+      <c r="D437" s="83" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="E437" s="83" t="inlineStr">
+        <is>
+          <t>force</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="B438" s="74" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+      <c r="C438" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="B439" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="C439" s="84" t="n"/>
+    </row>
+    <row r="441">
+      <c r="A441" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B441" s="82" t="inlineStr">
+        <is>
+          <t>sceau-givre</t>
+        </is>
+      </c>
+      <c r="C441" s="83" t="inlineStr">
+        <is>
+          <t>Frost Signet</t>
+        </is>
+      </c>
+      <c r="D441" s="83" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="E441" s="83" t="inlineStr">
+        <is>
+          <t>glace</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="B442" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="C442" s="72" t="inlineStr">
+        <is>
+          <t>La</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="B443" s="84" t="n"/>
+      <c r="C443" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B445" s="82" t="inlineStr">
+        <is>
+          <t>anneau-soif-sang</t>
+        </is>
+      </c>
+      <c r="C445" s="83" t="inlineStr">
+        <is>
+          <t>Bloodthirst Ring</t>
+        </is>
+      </c>
+      <c r="D445" s="83" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="E445" s="83" t="inlineStr">
+        <is>
+          <t>sang</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="B446" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="C446" s="76" t="inlineStr">
+        <is>
+          <t>Ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="B447" s="84" t="n"/>
+      <c r="C447" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B449" s="82" t="inlineStr">
+        <is>
+          <t>anneau-forge</t>
+        </is>
+      </c>
+      <c r="C449" s="83" t="inlineStr">
+        <is>
+          <t>Forge Ring</t>
+        </is>
+      </c>
+      <c r="D449" s="83" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="E449" s="83" t="inlineStr">
+        <is>
+          <t>forge</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="B450" s="70" t="inlineStr">
+        <is>
+          <t>Au</t>
+        </is>
+      </c>
+      <c r="C450" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="B451" s="66" t="inlineStr">
+        <is>
+          <t>Co</t>
+        </is>
+      </c>
+      <c r="C451" s="84" t="n"/>
+    </row>
+    <row r="453">
+      <c r="A453" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B453" s="82" t="inlineStr">
+        <is>
+          <t>anneau-de-givre-parfait</t>
+        </is>
+      </c>
+      <c r="C453" s="83" t="inlineStr">
+        <is>
+          <t>Perfect Frost Ring</t>
+        </is>
+      </c>
+      <c r="D453" s="83" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="E453" s="83" t="inlineStr">
+        <is>
+          <t>glace</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="B454" s="72" t="inlineStr">
+        <is>
+          <t>La</t>
+        </is>
+      </c>
+      <c r="C454" s="70" t="inlineStr">
+        <is>
+          <t>Au</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="B455" s="70" t="inlineStr">
+        <is>
+          <t>Au</t>
+        </is>
+      </c>
+      <c r="C455" s="72" t="inlineStr">
+        <is>
+          <t>La</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B457" s="82" t="inlineStr">
+        <is>
+          <t>collier-cuivre</t>
+        </is>
+      </c>
+      <c r="C457" s="83" t="inlineStr">
+        <is>
+          <t>Copper Amulet</t>
+        </is>
+      </c>
+      <c r="D457" s="83" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="E457" s="83" t="inlineStr">
+        <is>
+          <t>foudre</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="B458" s="65" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="C458" s="65" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="D458" s="65" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="B459" s="84" t="n"/>
+      <c r="C459" s="72" t="inlineStr">
+        <is>
+          <t>La</t>
+        </is>
+      </c>
+      <c r="D459" s="84" t="n"/>
+    </row>
+    <row r="461">
+      <c r="A461" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B461" s="82" t="inlineStr">
+        <is>
+          <t>pendentif-quartz</t>
+        </is>
+      </c>
+      <c r="C461" s="83" t="inlineStr">
+        <is>
+          <t>Quartz Pendant</t>
+        </is>
+      </c>
+      <c r="D461" s="83" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="E461" s="83" t="inlineStr">
+        <is>
+          <t>quartz</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="B462" s="65" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="C462" s="65" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="B463" s="84" t="n"/>
+      <c r="C463" s="67" t="inlineStr">
+        <is>
+          <t>St</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B465" s="82" t="inlineStr">
+        <is>
+          <t>charme-os</t>
+        </is>
+      </c>
+      <c r="C465" s="83" t="inlineStr">
+        <is>
+          <t>Bone Charm</t>
+        </is>
+      </c>
+      <c r="D465" s="83" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="E465" s="83" t="inlineStr">
+        <is>
+          <t>os</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="B466" s="65" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="C466" s="65" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="B467" s="66" t="inlineStr">
+        <is>
+          <t>Co</t>
+        </is>
+      </c>
+      <c r="C467" s="84" t="n"/>
+    </row>
+    <row r="469">
+      <c r="A469" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B469" s="82" t="inlineStr">
+        <is>
+          <t>pendentif-chaud</t>
+        </is>
+      </c>
+      <c r="C469" s="83" t="inlineStr">
+        <is>
+          <t>Spark Pendant</t>
+        </is>
+      </c>
+      <c r="D469" s="83" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="E469" s="83" t="inlineStr">
+        <is>
+          <t>feu</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="B470" s="65" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="B471" s="65" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="B472" s="76" t="inlineStr">
+        <is>
+          <t>Ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B474" s="82" t="inlineStr">
+        <is>
+          <t>porte-bonheur</t>
+        </is>
+      </c>
+      <c r="C474" s="83" t="inlineStr">
+        <is>
+          <t>Lucky Charm</t>
+        </is>
+      </c>
+      <c r="D474" s="83" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="E474" s="83" t="inlineStr">
+        <is>
+          <t>chance</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="B475" s="65" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="C475" s="70" t="inlineStr">
+        <is>
+          <t>Au</t>
+        </is>
+      </c>
+      <c r="D475" s="65" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B477" s="82" t="inlineStr">
+        <is>
+          <t>pendentif-energie</t>
+        </is>
+      </c>
+      <c r="C477" s="83" t="inlineStr">
+        <is>
+          <t>Energizing Pendant</t>
+        </is>
+      </c>
+      <c r="D477" s="83" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="E477" s="83" t="inlineStr">
+        <is>
+          <t>énergie</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="B478" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="C478" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="D478" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="B479" s="84" t="n"/>
+      <c r="C479" s="72" t="inlineStr">
+        <is>
+          <t>La</t>
+        </is>
+      </c>
+      <c r="D479" s="84" t="n"/>
+    </row>
+    <row r="481">
+      <c r="A481" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B481" s="82" t="inlineStr">
+        <is>
+          <t>collier-concentration</t>
+        </is>
+      </c>
+      <c r="C481" s="83" t="inlineStr">
+        <is>
+          <t>Amulet of Focus</t>
+        </is>
+      </c>
+      <c r="D481" s="83" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="E481" s="83" t="inlineStr">
+        <is>
+          <t>arcane</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="B482" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="C482" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="B483" s="84" t="n"/>
+      <c r="C483" s="73" t="inlineStr">
+        <is>
+          <t>Am</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B485" s="82" t="inlineStr">
+        <is>
+          <t>pendentif-vampire</t>
+        </is>
+      </c>
+      <c r="C485" s="83" t="inlineStr">
+        <is>
+          <t>Vampiric Pendant</t>
+        </is>
+      </c>
+      <c r="D485" s="83" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="E485" s="83" t="inlineStr">
+        <is>
+          <t>sang/drain</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="B486" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="B487" s="76" t="inlineStr">
+        <is>
+          <t>Ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="B488" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B490" s="82" t="inlineStr">
+        <is>
+          <t>collier-de-saphir</t>
+        </is>
+      </c>
+      <c r="C490" s="83" t="inlineStr">
+        <is>
+          <t>Sapphire Amulet</t>
+        </is>
+      </c>
+      <c r="D490" s="83" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="E490" s="83" t="inlineStr">
+        <is>
+          <t>saphir</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="B491" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="C491" s="77" t="inlineStr">
+        <is>
+          <t>Sa</t>
+        </is>
+      </c>
+      <c r="D491" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B493" s="82" t="inlineStr">
+        <is>
+          <t>collier-de-saphir-fin</t>
+        </is>
+      </c>
+      <c r="C493" s="83" t="inlineStr">
+        <is>
+          <t>Nice Sapphire Amulet</t>
+        </is>
+      </c>
+      <c r="D493" s="83" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="E493" s="83" t="inlineStr">
+        <is>
+          <t>saphir</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="B494" s="77" t="inlineStr">
+        <is>
+          <t>Sa</t>
+        </is>
+      </c>
+      <c r="C494" s="70" t="inlineStr">
+        <is>
+          <t>Au</t>
+        </is>
+      </c>
+      <c r="D494" s="77" t="inlineStr">
+        <is>
+          <t>Sa</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B496" s="82" t="inlineStr">
+        <is>
+          <t>collier-de-saphir-parfait</t>
+        </is>
+      </c>
+      <c r="C496" s="83" t="inlineStr">
+        <is>
+          <t>Perfect Sapphire Amulet</t>
+        </is>
+      </c>
+      <c r="D496" s="83" t="inlineStr">
+        <is>
+          <t>epique</t>
+        </is>
+      </c>
+      <c r="E496" s="83" t="inlineStr">
+        <is>
+          <t>saphir</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="B497" s="77" t="inlineStr">
+        <is>
+          <t>Sa</t>
+        </is>
+      </c>
+      <c r="C497" s="78" t="inlineStr">
+        <is>
+          <t>Di</t>
+        </is>
+      </c>
+      <c r="D497" s="77" t="inlineStr">
+        <is>
+          <t>Sa</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="B498" s="84" t="n"/>
+      <c r="C498" s="77" t="inlineStr">
+        <is>
+          <t>Sa</t>
+        </is>
+      </c>
+      <c r="D498" s="84" t="n"/>
+    </row>
+    <row r="500">
+      <c r="A500" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B500" s="82" t="inlineStr">
+        <is>
+          <t>bouclier-bois</t>
+        </is>
+      </c>
+      <c r="C500" s="83" t="inlineStr">
+        <is>
+          <t>Wooden Shield</t>
+        </is>
+      </c>
+      <c r="D500" s="83" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="E500" s="83" t="inlineStr">
+        <is>
+          <t>bois</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="B501" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="C501" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="B502" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="C502" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="B503" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="C503" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B505" s="82" t="inlineStr">
+        <is>
+          <t>targe</t>
+        </is>
+      </c>
+      <c r="C505" s="83" t="inlineStr">
+        <is>
+          <t>Buckler</t>
+        </is>
+      </c>
+      <c r="D505" s="83" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="E505" s="83" t="inlineStr">
+        <is>
+          <t>petit bouclier</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="B506" s="65" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="C506" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="B507" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="C507" s="65" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B509" s="82" t="inlineStr">
+        <is>
+          <t>grimoire</t>
+        </is>
+      </c>
+      <c r="C509" s="83" t="inlineStr">
+        <is>
+          <t>Spellbook</t>
+        </is>
+      </c>
+      <c r="D509" s="83" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="E509" s="83" t="inlineStr">
+        <is>
+          <t>arcane/livre</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="B510" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="C510" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="B511" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="C511" s="72" t="inlineStr">
+        <is>
+          <t>La</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B513" s="82" t="inlineStr">
+        <is>
+          <t>fanal</t>
+        </is>
+      </c>
+      <c r="C513" s="83" t="inlineStr">
+        <is>
+          <t>Hand Torch</t>
+        </is>
+      </c>
+      <c r="D513" s="83" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="E513" s="83" t="inlineStr">
+        <is>
+          <t>feu</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="B514" s="66" t="inlineStr">
+        <is>
+          <t>Co</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="B515" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="B516" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B518" s="82" t="inlineStr">
+        <is>
+          <t>sceptre-apprenti</t>
+        </is>
+      </c>
+      <c r="C518" s="83" t="inlineStr">
+        <is>
+          <t>Apprentice Scepter</t>
+        </is>
+      </c>
+      <c r="D518" s="83" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="E518" s="83" t="inlineStr">
+        <is>
+          <t>sceptre</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="B519" s="65" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="B520" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="B521" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B523" s="82" t="inlineStr">
+        <is>
+          <t>grimoire-soin</t>
+        </is>
+      </c>
+      <c r="C523" s="83" t="inlineStr">
+        <is>
+          <t>Healing Book</t>
+        </is>
+      </c>
+      <c r="D523" s="83" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="E523" s="83" t="inlineStr">
+        <is>
+          <t>soin/livre</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="B524" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="C524" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="B525" s="71" t="inlineStr">
+        <is>
+          <t>Ma</t>
+        </is>
+      </c>
+      <c r="C525" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B527" s="82" t="inlineStr">
+        <is>
+          <t>bouclier-renforce</t>
+        </is>
+      </c>
+      <c r="C527" s="83" t="inlineStr">
+        <is>
+          <t>Reinforced Shield</t>
+        </is>
+      </c>
+      <c r="D527" s="83" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="E527" s="83" t="inlineStr">
+        <is>
+          <t>renforcé</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="B528" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="C528" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="B529" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="C529" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="B530" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="C530" s="64" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B532" s="82" t="inlineStr">
+        <is>
+          <t>grimoire-flammes</t>
+        </is>
+      </c>
+      <c r="C532" s="83" t="inlineStr">
+        <is>
+          <t>Grimoire of Flames</t>
+        </is>
+      </c>
+      <c r="D532" s="83" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="E532" s="83" t="inlineStr">
+        <is>
+          <t>feu/livre</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="B533" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="C533" s="76" t="inlineStr">
+        <is>
+          <t>Ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="B534" s="76" t="inlineStr">
+        <is>
+          <t>Ru</t>
+        </is>
+      </c>
+      <c r="C534" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B536" s="82" t="inlineStr">
+        <is>
+          <t>sceptre-commandement</t>
+        </is>
+      </c>
+      <c r="C536" s="83" t="inlineStr">
+        <is>
+          <t>Scepter of Command</t>
+        </is>
+      </c>
+      <c r="D536" s="83" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="E536" s="83" t="inlineStr">
+        <is>
+          <t>commandement</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="B537" s="70" t="inlineStr">
+        <is>
+          <t>Au</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="B538" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="B539" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B541" s="82" t="inlineStr">
+        <is>
+          <t>bouclier-protecteur</t>
+        </is>
+      </c>
+      <c r="C541" s="83" t="inlineStr">
+        <is>
+          <t>Warding Shield</t>
+        </is>
+      </c>
+      <c r="D541" s="83" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="E541" s="83" t="inlineStr">
+        <is>
+          <t>protection</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="B542" s="72" t="inlineStr">
+        <is>
+          <t>La</t>
+        </is>
+      </c>
+      <c r="C542" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="B543" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="C543" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="B544" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="C544" s="72" t="inlineStr">
+        <is>
+          <t>La</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B546" s="82" t="inlineStr">
+        <is>
+          <t>grimoire-puissance</t>
+        </is>
+      </c>
+      <c r="C546" s="83" t="inlineStr">
+        <is>
+          <t>Tome of Power</t>
+        </is>
+      </c>
+      <c r="D546" s="83" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="E546" s="83" t="inlineStr">
+        <is>
+          <t>arcane/livre</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="B547" s="73" t="inlineStr">
+        <is>
+          <t>Am</t>
+        </is>
+      </c>
+      <c r="C547" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="B548" s="68" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="C548" s="73" t="inlineStr">
+        <is>
+          <t>Am</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="82" t="inlineStr">
+        <is>
+          <t>ARME</t>
+        </is>
+      </c>
+      <c r="B550" s="82" t="inlineStr">
+        <is>
+          <t>bouclier-tour</t>
+        </is>
+      </c>
+      <c r="C550" s="83" t="inlineStr">
+        <is>
+          <t>Tower Shield</t>
+        </is>
+      </c>
+      <c r="D550" s="83" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="E550" s="83" t="inlineStr">
+        <is>
+          <t>tour</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="B551" s="74" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+      <c r="C551" s="74" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="B552" s="74" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+      <c r="C552" s="74" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="B553" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="C553" s="69" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/BRUTAL-items-et-cartes.xlsx
+++ b/docs/BRUTAL-items-et-cartes.xlsx
@@ -13,6 +13,7 @@
     <sheet name="Sets" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Effets" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Recettes" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Valeurs" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -22,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -100,8 +101,12 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <name val="Consolas"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="49">
+  <fills count="54">
     <fill>
       <patternFill/>
     </fill>
@@ -343,6 +348,31 @@
         <fgColor rgb="00fff2d9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00e8e8e8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00d6ecd6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00d6e4f6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ecdcf4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00f6e8cc"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -385,7 +415,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -564,6 +594,26 @@
     <xf numFmtId="0" fontId="13" fillId="48" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="50" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="52" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -21938,4 +21988,2554 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D130"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" style="57" min="1" max="1"/>
+    <col width="26" customWidth="1" style="57" min="2" max="2"/>
+    <col width="12" customWidth="1" style="57" min="3" max="3"/>
+    <col width="12" customWidth="1" style="57" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="61" t="inlineStr">
+        <is>
+          <t>VALEUR DES OBJETS — SOURCE ÉDITABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="62" t="inlineStr">
+        <is>
+          <t>Édite la colonne « Valeur » (D), puis lance : python3 outils/importer_valeurs.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="62" t="inlineStr">
+        <is>
+          <t>Cible par rareté : Common 400 · Uncommon 2 000 · Rare 10 000 · Epic 80 000 · Legendary 250 000 (± semé)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="62" t="inlineStr">
+        <is>
+          <t>Le prix de VENTE (marchand −25 %, HV −10 à −20 %) découle de cette valeur dans le jeu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="85" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B6" s="85" t="inlineStr">
+        <is>
+          <t>Nom</t>
+        </is>
+      </c>
+      <c r="C6" s="85" t="inlineStr">
+        <is>
+          <t>Rareté</t>
+        </is>
+      </c>
+      <c r="D6" s="85" t="inlineStr">
+        <is>
+          <t>Valeur</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="86" t="inlineStr">
+        <is>
+          <t>couperet</t>
+        </is>
+      </c>
+      <c r="B7" s="87" t="inlineStr">
+        <is>
+          <t>Cleaver</t>
+        </is>
+      </c>
+      <c r="C7" s="88" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D7" s="85" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="86" t="inlineStr">
+        <is>
+          <t>hachette</t>
+        </is>
+      </c>
+      <c r="B8" s="87" t="inlineStr">
+        <is>
+          <t>Hatchet</t>
+        </is>
+      </c>
+      <c r="C8" s="88" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D8" s="85" t="n">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="86" t="inlineStr">
+        <is>
+          <t>pic-de-glace</t>
+        </is>
+      </c>
+      <c r="B9" s="87" t="inlineStr">
+        <is>
+          <t>Ice Pick</t>
+        </is>
+      </c>
+      <c r="C9" s="88" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D9" s="85" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="86" t="inlineStr">
+        <is>
+          <t>masse</t>
+        </is>
+      </c>
+      <c r="B10" s="87" t="inlineStr">
+        <is>
+          <t>Mace</t>
+        </is>
+      </c>
+      <c r="C10" s="88" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D10" s="85" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="86" t="inlineStr">
+        <is>
+          <t>pioche-de-mineur</t>
+        </is>
+      </c>
+      <c r="B11" s="87" t="inlineStr">
+        <is>
+          <t>Miner's Pick</t>
+        </is>
+      </c>
+      <c r="C11" s="88" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D11" s="85" t="n">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="86" t="inlineStr">
+        <is>
+          <t>fourche</t>
+        </is>
+      </c>
+      <c r="B12" s="87" t="inlineStr">
+        <is>
+          <t>Pitchfork</t>
+        </is>
+      </c>
+      <c r="C12" s="88" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D12" s="85" t="n">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="86" t="inlineStr">
+        <is>
+          <t>baton</t>
+        </is>
+      </c>
+      <c r="B13" s="87" t="inlineStr">
+        <is>
+          <t>Quarterstaff</t>
+        </is>
+      </c>
+      <c r="C13" s="88" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D13" s="85" t="n">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="86" t="inlineStr">
+        <is>
+          <t>hache-rouillee</t>
+        </is>
+      </c>
+      <c r="B14" s="87" t="inlineStr">
+        <is>
+          <t>Rusty Axe</t>
+        </is>
+      </c>
+      <c r="C14" s="88" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D14" s="85" t="n">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="86" t="inlineStr">
+        <is>
+          <t>dague-rouillee</t>
+        </is>
+      </c>
+      <c r="B15" s="87" t="inlineStr">
+        <is>
+          <t>Rusty Dagger</t>
+        </is>
+      </c>
+      <c r="C15" s="88" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D15" s="85" t="n">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="86" t="inlineStr">
+        <is>
+          <t>couteau-serpent</t>
+        </is>
+      </c>
+      <c r="B16" s="87" t="inlineStr">
+        <is>
+          <t>Serpent Knife</t>
+        </is>
+      </c>
+      <c r="C16" s="88" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D16" s="85" t="n">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="86" t="inlineStr">
+        <is>
+          <t>couteau-dentele</t>
+        </is>
+      </c>
+      <c r="B17" s="87" t="inlineStr">
+        <is>
+          <t>Serrated Knife</t>
+        </is>
+      </c>
+      <c r="C17" s="88" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D17" s="85" t="n">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="86" t="inlineStr">
+        <is>
+          <t>epee-courte</t>
+        </is>
+      </c>
+      <c r="B18" s="87" t="inlineStr">
+        <is>
+          <t>Short Sword</t>
+        </is>
+      </c>
+      <c r="C18" s="88" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D18" s="85" t="n">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="86" t="inlineStr">
+        <is>
+          <t>lance</t>
+        </is>
+      </c>
+      <c r="B19" s="87" t="inlineStr">
+        <is>
+          <t>Spear</t>
+        </is>
+      </c>
+      <c r="C19" s="88" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D19" s="85" t="n">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="86" t="inlineStr">
+        <is>
+          <t>torche</t>
+        </is>
+      </c>
+      <c r="B20" s="87" t="inlineStr">
+        <is>
+          <t>Torch</t>
+        </is>
+      </c>
+      <c r="C20" s="88" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D20" s="85" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="86" t="inlineStr">
+        <is>
+          <t>epee-entrainement</t>
+        </is>
+      </c>
+      <c r="B21" s="87" t="inlineStr">
+        <is>
+          <t>Training Sword</t>
+        </is>
+      </c>
+      <c r="C21" s="88" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D21" s="85" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="86" t="inlineStr">
+        <is>
+          <t>gourdin</t>
+        </is>
+      </c>
+      <c r="B22" s="87" t="inlineStr">
+        <is>
+          <t>Wooden Club</t>
+        </is>
+      </c>
+      <c r="C22" s="88" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D22" s="85" t="n">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="86" t="inlineStr">
+        <is>
+          <t>cotte-mailles</t>
+        </is>
+      </c>
+      <c r="B23" s="87" t="inlineStr">
+        <is>
+          <t>Chainmail</t>
+        </is>
+      </c>
+      <c r="C23" s="88" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D23" s="85" t="n">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="86" t="inlineStr">
+        <is>
+          <t>armure-peau</t>
+        </is>
+      </c>
+      <c r="B24" s="87" t="inlineStr">
+        <is>
+          <t>Hide Armor</t>
+        </is>
+      </c>
+      <c r="C24" s="88" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D24" s="85" t="n">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="86" t="inlineStr">
+        <is>
+          <t>armure-cuir</t>
+        </is>
+      </c>
+      <c r="B25" s="87" t="inlineStr">
+        <is>
+          <t>Leather Armor</t>
+        </is>
+      </c>
+      <c r="C25" s="88" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D25" s="85" t="n">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="86" t="inlineStr">
+        <is>
+          <t>gilet-rembourre</t>
+        </is>
+      </c>
+      <c r="B26" s="87" t="inlineStr">
+        <is>
+          <t>Padded Vest</t>
+        </is>
+      </c>
+      <c r="C26" s="88" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D26" s="85" t="n">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="86" t="inlineStr">
+        <is>
+          <t>tenue-de-voyageur</t>
+        </is>
+      </c>
+      <c r="B27" s="87" t="inlineStr">
+        <is>
+          <t>Traveler's Garb</t>
+        </is>
+      </c>
+      <c r="C27" s="88" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D27" s="85" t="n">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="86" t="inlineStr">
+        <is>
+          <t>anneau-saignant</t>
+        </is>
+      </c>
+      <c r="B28" s="87" t="inlineStr">
+        <is>
+          <t>Bleeding Ring</t>
+        </is>
+      </c>
+      <c r="C28" s="88" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D28" s="85" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="86" t="inlineStr">
+        <is>
+          <t>anneau-braise</t>
+        </is>
+      </c>
+      <c r="B29" s="87" t="inlineStr">
+        <is>
+          <t>Ember Ring</t>
+        </is>
+      </c>
+      <c r="C29" s="88" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D29" s="85" t="n">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="86" t="inlineStr">
+        <is>
+          <t>anneau-frimas</t>
+        </is>
+      </c>
+      <c r="B30" s="87" t="inlineStr">
+        <is>
+          <t>Frost Band</t>
+        </is>
+      </c>
+      <c r="C30" s="88" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D30" s="85" t="n">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="86" t="inlineStr">
+        <is>
+          <t>anneau-agile</t>
+        </is>
+      </c>
+      <c r="B31" s="87" t="inlineStr">
+        <is>
+          <t>Nimble Ring</t>
+        </is>
+      </c>
+      <c r="C31" s="88" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D31" s="85" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="86" t="inlineStr">
+        <is>
+          <t>anneau-force</t>
+        </is>
+      </c>
+      <c r="B32" s="87" t="inlineStr">
+        <is>
+          <t>Power Ring</t>
+        </is>
+      </c>
+      <c r="C32" s="88" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D32" s="85" t="n">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="86" t="inlineStr">
+        <is>
+          <t>anneau-etincelle</t>
+        </is>
+      </c>
+      <c r="B33" s="87" t="inlineStr">
+        <is>
+          <t>Spark Ring</t>
+        </is>
+      </c>
+      <c r="C33" s="88" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D33" s="85" t="n">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="86" t="inlineStr">
+        <is>
+          <t>anneau-pierre</t>
+        </is>
+      </c>
+      <c r="B34" s="87" t="inlineStr">
+        <is>
+          <t>Stone Ring</t>
+        </is>
+      </c>
+      <c r="C34" s="88" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D34" s="85" t="n">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="86" t="inlineStr">
+        <is>
+          <t>anneau-venin</t>
+        </is>
+      </c>
+      <c r="B35" s="87" t="inlineStr">
+        <is>
+          <t>Venom Ring</t>
+        </is>
+      </c>
+      <c r="C35" s="88" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D35" s="85" t="n">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="86" t="inlineStr">
+        <is>
+          <t>anneau-vigueur</t>
+        </is>
+      </c>
+      <c r="B36" s="87" t="inlineStr">
+        <is>
+          <t>Vigor Ring</t>
+        </is>
+      </c>
+      <c r="C36" s="88" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D36" s="85" t="n">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="86" t="inlineStr">
+        <is>
+          <t>bottes-cuir</t>
+        </is>
+      </c>
+      <c r="B37" s="87" t="inlineStr">
+        <is>
+          <t>Leather Boots</t>
+        </is>
+      </c>
+      <c r="C37" s="88" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D37" s="85" t="n">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="86" t="inlineStr">
+        <is>
+          <t>sandales</t>
+        </is>
+      </c>
+      <c r="B38" s="87" t="inlineStr">
+        <is>
+          <t>Sandals</t>
+        </is>
+      </c>
+      <c r="C38" s="88" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D38" s="85" t="n">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="86" t="inlineStr">
+        <is>
+          <t>bottes-voyage</t>
+        </is>
+      </c>
+      <c r="B39" s="87" t="inlineStr">
+        <is>
+          <t>Traveler Boots</t>
+        </is>
+      </c>
+      <c r="C39" s="88" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D39" s="85" t="n">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="86" t="inlineStr">
+        <is>
+          <t>bottes-usees</t>
+        </is>
+      </c>
+      <c r="B40" s="87" t="inlineStr">
+        <is>
+          <t>Worn Boots</t>
+        </is>
+      </c>
+      <c r="C40" s="88" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D40" s="85" t="n">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="86" t="inlineStr">
+        <is>
+          <t>sceptre-apprenti</t>
+        </is>
+      </c>
+      <c r="B41" s="87" t="inlineStr">
+        <is>
+          <t>Apprentice Scepter</t>
+        </is>
+      </c>
+      <c r="C41" s="88" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D41" s="85" t="n">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="86" t="inlineStr">
+        <is>
+          <t>targe</t>
+        </is>
+      </c>
+      <c r="B42" s="87" t="inlineStr">
+        <is>
+          <t>Buckler</t>
+        </is>
+      </c>
+      <c r="C42" s="88" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D42" s="85" t="n">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="86" t="inlineStr">
+        <is>
+          <t>fanal</t>
+        </is>
+      </c>
+      <c r="B43" s="87" t="inlineStr">
+        <is>
+          <t>Hand Torch</t>
+        </is>
+      </c>
+      <c r="C43" s="88" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D43" s="85" t="n">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="86" t="inlineStr">
+        <is>
+          <t>grimoire-soin</t>
+        </is>
+      </c>
+      <c r="B44" s="87" t="inlineStr">
+        <is>
+          <t>Healing Book</t>
+        </is>
+      </c>
+      <c r="C44" s="88" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D44" s="85" t="n">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="86" t="inlineStr">
+        <is>
+          <t>grimoire</t>
+        </is>
+      </c>
+      <c r="B45" s="87" t="inlineStr">
+        <is>
+          <t>Spellbook</t>
+        </is>
+      </c>
+      <c r="C45" s="88" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D45" s="85" t="n">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="86" t="inlineStr">
+        <is>
+          <t>bouclier-bois</t>
+        </is>
+      </c>
+      <c r="B46" s="87" t="inlineStr">
+        <is>
+          <t>Wooden Shield</t>
+        </is>
+      </c>
+      <c r="C46" s="88" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D46" s="85" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="86" t="inlineStr">
+        <is>
+          <t>charme-os</t>
+        </is>
+      </c>
+      <c r="B47" s="87" t="inlineStr">
+        <is>
+          <t>Bone Charm</t>
+        </is>
+      </c>
+      <c r="C47" s="88" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D47" s="85" t="n">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="86" t="inlineStr">
+        <is>
+          <t>collier-cuivre</t>
+        </is>
+      </c>
+      <c r="B48" s="87" t="inlineStr">
+        <is>
+          <t>Copper Amulet</t>
+        </is>
+      </c>
+      <c r="C48" s="88" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D48" s="85" t="n">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="86" t="inlineStr">
+        <is>
+          <t>porte-bonheur</t>
+        </is>
+      </c>
+      <c r="B49" s="87" t="inlineStr">
+        <is>
+          <t>Lucky Charm</t>
+        </is>
+      </c>
+      <c r="C49" s="88" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D49" s="85" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="86" t="inlineStr">
+        <is>
+          <t>pendentif-quartz</t>
+        </is>
+      </c>
+      <c r="B50" s="87" t="inlineStr">
+        <is>
+          <t>Quartz Pendant</t>
+        </is>
+      </c>
+      <c r="C50" s="88" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D50" s="85" t="n">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="86" t="inlineStr">
+        <is>
+          <t>pendentif-chaud</t>
+        </is>
+      </c>
+      <c r="B51" s="87" t="inlineStr">
+        <is>
+          <t>Spark Pendant</t>
+        </is>
+      </c>
+      <c r="C51" s="88" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D51" s="85" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="86" t="inlineStr">
+        <is>
+          <t>gants-tissu</t>
+        </is>
+      </c>
+      <c r="B52" s="87" t="inlineStr">
+        <is>
+          <t>Cloth Gloves</t>
+        </is>
+      </c>
+      <c r="C52" s="88" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D52" s="85" t="n">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="86" t="inlineStr">
+        <is>
+          <t>gants-cuir</t>
+        </is>
+      </c>
+      <c r="B53" s="87" t="inlineStr">
+        <is>
+          <t>Leather Gloves</t>
+        </is>
+      </c>
+      <c r="C53" s="88" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D53" s="85" t="n">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="86" t="inlineStr">
+        <is>
+          <t>gants-de-mineur</t>
+        </is>
+      </c>
+      <c r="B54" s="87" t="inlineStr">
+        <is>
+          <t>Miner's Gloves</t>
+        </is>
+      </c>
+      <c r="C54" s="88" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D54" s="85" t="n">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="86" t="inlineStr">
+        <is>
+          <t>gants-cloutes</t>
+        </is>
+      </c>
+      <c r="B55" s="87" t="inlineStr">
+        <is>
+          <t>Studded Gloves</t>
+        </is>
+      </c>
+      <c r="C55" s="88" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D55" s="85" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="86" t="inlineStr">
+        <is>
+          <t>gants-travail</t>
+        </is>
+      </c>
+      <c r="B56" s="87" t="inlineStr">
+        <is>
+          <t>Work Gloves</t>
+        </is>
+      </c>
+      <c r="C56" s="88" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D56" s="85" t="n">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="86" t="inlineStr">
+        <is>
+          <t>sac-en-cuir</t>
+        </is>
+      </c>
+      <c r="B57" s="87" t="inlineStr">
+        <is>
+          <t>Leather Pouch</t>
+        </is>
+      </c>
+      <c r="C57" s="88" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D57" s="85" t="n">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="86" t="inlineStr">
+        <is>
+          <t>hache-berserk</t>
+        </is>
+      </c>
+      <c r="B58" s="87" t="inlineStr">
+        <is>
+          <t>Berserker Axe</t>
+        </is>
+      </c>
+      <c r="C58" s="89" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D58" s="85" t="n">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="86" t="inlineStr">
+        <is>
+          <t>epee-large</t>
+        </is>
+      </c>
+      <c r="B59" s="87" t="inlineStr">
+        <is>
+          <t>Claymore</t>
+        </is>
+      </c>
+      <c r="C59" s="89" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D59" s="85" t="n">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="86" t="inlineStr">
+        <is>
+          <t>baguette-cristal</t>
+        </is>
+      </c>
+      <c r="B60" s="87" t="inlineStr">
+        <is>
+          <t>Crystal Wand</t>
+        </is>
+      </c>
+      <c r="C60" s="89" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D60" s="85" t="n">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="86" t="inlineStr">
+        <is>
+          <t>lame-de-braise</t>
+        </is>
+      </c>
+      <c r="B61" s="87" t="inlineStr">
+        <is>
+          <t>Emberblade</t>
+        </is>
+      </c>
+      <c r="C61" s="89" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D61" s="85" t="n">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="86" t="inlineStr">
+        <is>
+          <t>lame-bourreau</t>
+        </is>
+      </c>
+      <c r="B62" s="87" t="inlineStr">
+        <is>
+          <t>Executioner's Blade</t>
+        </is>
+      </c>
+      <c r="C62" s="89" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D62" s="85" t="n">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="86" t="inlineStr">
+        <is>
+          <t>marteau-de-forge</t>
+        </is>
+      </c>
+      <c r="B63" s="87" t="inlineStr">
+        <is>
+          <t>Forge Hammer</t>
+        </is>
+      </c>
+      <c r="C63" s="89" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D63" s="85" t="n">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="86" t="inlineStr">
+        <is>
+          <t>lame-de-givre</t>
+        </is>
+      </c>
+      <c r="B64" s="87" t="inlineStr">
+        <is>
+          <t>Frostbrand</t>
+        </is>
+      </c>
+      <c r="C64" s="89" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D64" s="85" t="n">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="86" t="inlineStr">
+        <is>
+          <t>hallebarde</t>
+        </is>
+      </c>
+      <c r="B65" s="87" t="inlineStr">
+        <is>
+          <t>Halberd</t>
+        </is>
+      </c>
+      <c r="C65" s="89" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D65" s="85" t="n">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="86" t="inlineStr">
+        <is>
+          <t>epee-sacree</t>
+        </is>
+      </c>
+      <c r="B66" s="87" t="inlineStr">
+        <is>
+          <t>Holy Sword</t>
+        </is>
+      </c>
+      <c r="C66" s="89" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D66" s="85" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="86" t="inlineStr">
+        <is>
+          <t>hache-faucheuse</t>
+        </is>
+      </c>
+      <c r="B67" s="87" t="inlineStr">
+        <is>
+          <t>Reaver Axe</t>
+        </is>
+      </c>
+      <c r="C67" s="89" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D67" s="85" t="n">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="86" t="inlineStr">
+        <is>
+          <t>fleau-cloute</t>
+        </is>
+      </c>
+      <c r="B68" s="87" t="inlineStr">
+        <is>
+          <t>Spiked Flail</t>
+        </is>
+      </c>
+      <c r="C68" s="89" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D68" s="85" t="n">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="86" t="inlineStr">
+        <is>
+          <t>marteau-de-pierre</t>
+        </is>
+      </c>
+      <c r="B69" s="87" t="inlineStr">
+        <is>
+          <t>Stone Hammer</t>
+        </is>
+      </c>
+      <c r="C69" s="89" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D69" s="85" t="n">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="86" t="inlineStr">
+        <is>
+          <t>dagues-jumelles</t>
+        </is>
+      </c>
+      <c r="B70" s="87" t="inlineStr">
+        <is>
+          <t>Twin Daggers</t>
+        </is>
+      </c>
+      <c r="C70" s="89" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D70" s="85" t="n">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="86" t="inlineStr">
+        <is>
+          <t>dague-venin</t>
+        </is>
+      </c>
+      <c r="B71" s="87" t="inlineStr">
+        <is>
+          <t>Venomfang Dagger</t>
+        </is>
+      </c>
+      <c r="C71" s="89" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D71" s="85" t="n">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="86" t="inlineStr">
+        <is>
+          <t>marteau-guerre</t>
+        </is>
+      </c>
+      <c r="B72" s="87" t="inlineStr">
+        <is>
+          <t>Warhammer</t>
+        </is>
+      </c>
+      <c r="C72" s="89" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D72" s="85" t="n">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="86" t="inlineStr">
+        <is>
+          <t>plaque-de-fer</t>
+        </is>
+      </c>
+      <c r="B73" s="87" t="inlineStr">
+        <is>
+          <t>Basic Iron Plate</t>
+        </is>
+      </c>
+      <c r="C73" s="89" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D73" s="85" t="n">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="86" t="inlineStr">
+        <is>
+          <t>peau-berserk</t>
+        </is>
+      </c>
+      <c r="B74" s="87" t="inlineStr">
+        <is>
+          <t>Berserker Hide</t>
+        </is>
+      </c>
+      <c r="C74" s="89" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D74" s="85" t="n">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="86" t="inlineStr">
+        <is>
+          <t>armure-stone-age</t>
+        </is>
+      </c>
+      <c r="B75" s="87" t="inlineStr">
+        <is>
+          <t>Stone Armor</t>
+        </is>
+      </c>
+      <c r="C75" s="89" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D75" s="85" t="n">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="86" t="inlineStr">
+        <is>
+          <t>bague-de-sang</t>
+        </is>
+      </c>
+      <c r="B76" s="87" t="inlineStr">
+        <is>
+          <t>Blood Ring</t>
+        </is>
+      </c>
+      <c r="C76" s="89" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D76" s="85" t="n">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="86" t="inlineStr">
+        <is>
+          <t>anneau-soif-sang</t>
+        </is>
+      </c>
+      <c r="B77" s="87" t="inlineStr">
+        <is>
+          <t>Bloodthirst Ring</t>
+        </is>
+      </c>
+      <c r="C77" s="89" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D77" s="85" t="n">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="86" t="inlineStr">
+        <is>
+          <t>anneau-forge</t>
+        </is>
+      </c>
+      <c r="B78" s="87" t="inlineStr">
+        <is>
+          <t>Forge Ring</t>
+        </is>
+      </c>
+      <c r="C78" s="89" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D78" s="85" t="n">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="86" t="inlineStr">
+        <is>
+          <t>anneau-de-givre</t>
+        </is>
+      </c>
+      <c r="B79" s="87" t="inlineStr">
+        <is>
+          <t>Frost Ring</t>
+        </is>
+      </c>
+      <c r="C79" s="89" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D79" s="85" t="n">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="86" t="inlineStr">
+        <is>
+          <t>sceau-givre</t>
+        </is>
+      </c>
+      <c r="B80" s="87" t="inlineStr">
+        <is>
+          <t>Frost Signet</t>
+        </is>
+      </c>
+      <c r="C80" s="89" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D80" s="85" t="n">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="86" t="inlineStr">
+        <is>
+          <t>anneau-de-fer</t>
+        </is>
+      </c>
+      <c r="B81" s="87" t="inlineStr">
+        <is>
+          <t>Iron Ring</t>
+        </is>
+      </c>
+      <c r="C81" s="89" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D81" s="85" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="86" t="inlineStr">
+        <is>
+          <t>anneau-puissance</t>
+        </is>
+      </c>
+      <c r="B82" s="87" t="inlineStr">
+        <is>
+          <t>Ring of Might</t>
+        </is>
+      </c>
+      <c r="C82" s="89" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D82" s="85" t="n">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="86" t="inlineStr">
+        <is>
+          <t>anneau-toxique</t>
+        </is>
+      </c>
+      <c r="B83" s="87" t="inlineStr">
+        <is>
+          <t>Toxic Ring</t>
+        </is>
+      </c>
+      <c r="C83" s="89" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D83" s="85" t="n">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="86" t="inlineStr">
+        <is>
+          <t>bottes-braise</t>
+        </is>
+      </c>
+      <c r="B84" s="87" t="inlineStr">
+        <is>
+          <t>Ember Striders</t>
+        </is>
+      </c>
+      <c r="C84" s="89" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D84" s="85" t="n">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="86" t="inlineStr">
+        <is>
+          <t>bottes-stone-age</t>
+        </is>
+      </c>
+      <c r="B85" s="87" t="inlineStr">
+        <is>
+          <t>Stone Boots</t>
+        </is>
+      </c>
+      <c r="C85" s="89" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D85" s="85" t="n">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="86" t="inlineStr">
+        <is>
+          <t>bottes-pierre</t>
+        </is>
+      </c>
+      <c r="B86" s="87" t="inlineStr">
+        <is>
+          <t>Stonetread Boots</t>
+        </is>
+      </c>
+      <c r="C86" s="89" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D86" s="85" t="n">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="86" t="inlineStr">
+        <is>
+          <t>bottes-vives</t>
+        </is>
+      </c>
+      <c r="B87" s="87" t="inlineStr">
+        <is>
+          <t>Swift Boots</t>
+        </is>
+      </c>
+      <c r="C87" s="89" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D87" s="85" t="n">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="86" t="inlineStr">
+        <is>
+          <t>bottes-rapides</t>
+        </is>
+      </c>
+      <c r="B88" s="87" t="inlineStr">
+        <is>
+          <t>Swift Striders</t>
+        </is>
+      </c>
+      <c r="C88" s="89" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D88" s="85" t="n">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="86" t="inlineStr">
+        <is>
+          <t>grimoire-flammes</t>
+        </is>
+      </c>
+      <c r="B89" s="87" t="inlineStr">
+        <is>
+          <t>Grimoire of Flames</t>
+        </is>
+      </c>
+      <c r="C89" s="89" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D89" s="85" t="n">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="86" t="inlineStr">
+        <is>
+          <t>bouclier-renforce</t>
+        </is>
+      </c>
+      <c r="B90" s="87" t="inlineStr">
+        <is>
+          <t>Reinforced Shield</t>
+        </is>
+      </c>
+      <c r="C90" s="89" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D90" s="85" t="n">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="86" t="inlineStr">
+        <is>
+          <t>sceptre-commandement</t>
+        </is>
+      </c>
+      <c r="B91" s="87" t="inlineStr">
+        <is>
+          <t>Scepter of Command</t>
+        </is>
+      </c>
+      <c r="C91" s="89" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D91" s="85" t="n">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="86" t="inlineStr">
+        <is>
+          <t>grimoire-puissance</t>
+        </is>
+      </c>
+      <c r="B92" s="87" t="inlineStr">
+        <is>
+          <t>Tome of Power</t>
+        </is>
+      </c>
+      <c r="C92" s="89" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D92" s="85" t="n">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="86" t="inlineStr">
+        <is>
+          <t>collier-concentration</t>
+        </is>
+      </c>
+      <c r="B93" s="87" t="inlineStr">
+        <is>
+          <t>Amulet of Focus</t>
+        </is>
+      </c>
+      <c r="C93" s="89" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D93" s="85" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="86" t="inlineStr">
+        <is>
+          <t>pendentif-energie</t>
+        </is>
+      </c>
+      <c r="B94" s="87" t="inlineStr">
+        <is>
+          <t>Energizing Pendant</t>
+        </is>
+      </c>
+      <c r="C94" s="89" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D94" s="85" t="n">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="86" t="inlineStr">
+        <is>
+          <t>collier-de-saphir</t>
+        </is>
+      </c>
+      <c r="B95" s="87" t="inlineStr">
+        <is>
+          <t>Sapphire Amulet</t>
+        </is>
+      </c>
+      <c r="C95" s="89" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D95" s="85" t="n">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="86" t="inlineStr">
+        <is>
+          <t>pendentif-vampire</t>
+        </is>
+      </c>
+      <c r="B96" s="87" t="inlineStr">
+        <is>
+          <t>Vampiric Pendant</t>
+        </is>
+      </c>
+      <c r="C96" s="89" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D96" s="85" t="n">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="86" t="inlineStr">
+        <is>
+          <t>gantelets</t>
+        </is>
+      </c>
+      <c r="B97" s="87" t="inlineStr">
+        <is>
+          <t>Gauntlets</t>
+        </is>
+      </c>
+      <c r="C97" s="89" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D97" s="85" t="n">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="86" t="inlineStr">
+        <is>
+          <t>gants-chance</t>
+        </is>
+      </c>
+      <c r="B98" s="87" t="inlineStr">
+        <is>
+          <t>Lucky Glove</t>
+        </is>
+      </c>
+      <c r="C98" s="89" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D98" s="85" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="86" t="inlineStr">
+        <is>
+          <t>gants-stone-age</t>
+        </is>
+      </c>
+      <c r="B99" s="87" t="inlineStr">
+        <is>
+          <t>Stone Glove</t>
+        </is>
+      </c>
+      <c r="C99" s="89" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D99" s="85" t="n">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="86" t="inlineStr">
+        <is>
+          <t>gants-voleur</t>
+        </is>
+      </c>
+      <c r="B100" s="87" t="inlineStr">
+        <is>
+          <t>Thief's Gloves</t>
+        </is>
+      </c>
+      <c r="C100" s="89" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D100" s="85" t="n">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="86" t="inlineStr">
+        <is>
+          <t>gants-venin</t>
+        </is>
+      </c>
+      <c r="B101" s="87" t="inlineStr">
+        <is>
+          <t>Venom Gloves</t>
+        </is>
+      </c>
+      <c r="C101" s="89" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D101" s="85" t="n">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="86" t="inlineStr">
+        <is>
+          <t>grand-sac-en-cuir</t>
+        </is>
+      </c>
+      <c r="B102" s="87" t="inlineStr">
+        <is>
+          <t>Big Leather Pouch</t>
+        </is>
+      </c>
+      <c r="C102" s="89" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D102" s="85" t="n">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="86" t="inlineStr">
+        <is>
+          <t>croc-de-basilic</t>
+        </is>
+      </c>
+      <c r="B103" s="87" t="inlineStr">
+        <is>
+          <t>Basilisk Fang</t>
+        </is>
+      </c>
+      <c r="C103" s="90" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D103" s="85" t="n">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="86" t="inlineStr">
+        <is>
+          <t>marteau-de-siege</t>
+        </is>
+      </c>
+      <c r="B104" s="87" t="inlineStr">
+        <is>
+          <t>Siege Maul</t>
+        </is>
+      </c>
+      <c r="C104" s="90" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D104" s="85" t="n">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="86" t="inlineStr">
+        <is>
+          <t>hache-de-guerre</t>
+        </is>
+      </c>
+      <c r="B105" s="87" t="inlineStr">
+        <is>
+          <t>War Axe</t>
+        </is>
+      </c>
+      <c r="C105" s="90" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D105" s="85" t="n">
+        <v>8100</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="86" t="inlineStr">
+        <is>
+          <t>plate-sang</t>
+        </is>
+      </c>
+      <c r="B106" s="87" t="inlineStr">
+        <is>
+          <t>Blood Plate</t>
+        </is>
+      </c>
+      <c r="C106" s="90" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D106" s="85" t="n">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="86" t="inlineStr">
+        <is>
+          <t>plate-croise</t>
+        </is>
+      </c>
+      <c r="B107" s="87" t="inlineStr">
+        <is>
+          <t>Crusader Plate</t>
+        </is>
+      </c>
+      <c r="C107" s="90" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D107" s="85" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="86" t="inlineStr">
+        <is>
+          <t>maille-de-forge</t>
+        </is>
+      </c>
+      <c r="B108" s="87" t="inlineStr">
+        <is>
+          <t>Forgemaster's Mail</t>
+        </is>
+      </c>
+      <c r="C108" s="90" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D108" s="85" t="n">
+        <v>8100</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="86" t="inlineStr">
+        <is>
+          <t>anneau-de-givre-parfait</t>
+        </is>
+      </c>
+      <c r="B109" s="87" t="inlineStr">
+        <is>
+          <t>Perfect Frost Ring</t>
+        </is>
+      </c>
+      <c r="C109" s="90" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D109" s="85" t="n">
+        <v>8300</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="86" t="inlineStr">
+        <is>
+          <t>bottes-sang</t>
+        </is>
+      </c>
+      <c r="B110" s="87" t="inlineStr">
+        <is>
+          <t>Blood Greaves</t>
+        </is>
+      </c>
+      <c r="C110" s="90" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D110" s="85" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="86" t="inlineStr">
+        <is>
+          <t>bottes-croise</t>
+        </is>
+      </c>
+      <c r="B111" s="87" t="inlineStr">
+        <is>
+          <t>Crusader Greaves</t>
+        </is>
+      </c>
+      <c r="C111" s="90" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D111" s="85" t="n">
+        <v>9900</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="86" t="inlineStr">
+        <is>
+          <t>bottes-de-maille</t>
+        </is>
+      </c>
+      <c r="B112" s="87" t="inlineStr">
+        <is>
+          <t>Mail Boots</t>
+        </is>
+      </c>
+      <c r="C112" s="90" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D112" s="85" t="n">
+        <v>8900</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="86" t="inlineStr">
+        <is>
+          <t>collier-de-saphir-fin</t>
+        </is>
+      </c>
+      <c r="B113" s="87" t="inlineStr">
+        <is>
+          <t>Nice Sapphire Amulet</t>
+        </is>
+      </c>
+      <c r="C113" s="90" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D113" s="85" t="n">
+        <v>8600</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="86" t="inlineStr">
+        <is>
+          <t>gants-sang</t>
+        </is>
+      </c>
+      <c r="B114" s="87" t="inlineStr">
+        <is>
+          <t>Blood Gauntlets</t>
+        </is>
+      </c>
+      <c r="C114" s="90" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D114" s="85" t="n">
+        <v>9200</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="86" t="inlineStr">
+        <is>
+          <t>gants-croise</t>
+        </is>
+      </c>
+      <c r="B115" s="87" t="inlineStr">
+        <is>
+          <t>Crusader Gauntlets</t>
+        </is>
+      </c>
+      <c r="C115" s="90" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D115" s="85" t="n">
+        <v>8400</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="86" t="inlineStr">
+        <is>
+          <t>gants-de-maille</t>
+        </is>
+      </c>
+      <c r="B116" s="87" t="inlineStr">
+        <is>
+          <t>Mail Glove</t>
+        </is>
+      </c>
+      <c r="C116" s="90" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D116" s="85" t="n">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="86" t="inlineStr">
+        <is>
+          <t>sac-a-dos</t>
+        </is>
+      </c>
+      <c r="B117" s="87" t="inlineStr">
+        <is>
+          <t>Backpack</t>
+        </is>
+      </c>
+      <c r="C117" s="90" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D117" s="85" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="86" t="inlineStr">
+        <is>
+          <t>enorme-sac-en-cuir</t>
+        </is>
+      </c>
+      <c r="B118" s="87" t="inlineStr">
+        <is>
+          <t>Huge Leather Pouch</t>
+        </is>
+      </c>
+      <c r="C118" s="90" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D118" s="85" t="n">
+        <v>9400</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="86" t="inlineStr">
+        <is>
+          <t>chevaliere-ancienne</t>
+        </is>
+      </c>
+      <c r="B119" s="87" t="inlineStr">
+        <is>
+          <t>Ancient Signet</t>
+        </is>
+      </c>
+      <c r="C119" s="90" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D119" s="85" t="n">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="86" t="inlineStr">
+        <is>
+          <t>calice-cristal</t>
+        </is>
+      </c>
+      <c r="B120" s="87" t="inlineStr">
+        <is>
+          <t>Crystal Chalice</t>
+        </is>
+      </c>
+      <c r="C120" s="90" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D120" s="85" t="n">
+        <v>9900</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="86" t="inlineStr">
+        <is>
+          <t>idole-doree</t>
+        </is>
+      </c>
+      <c r="B121" s="87" t="inlineStr">
+        <is>
+          <t>Gilded Idol</t>
+        </is>
+      </c>
+      <c r="C121" s="90" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D121" s="85" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="86" t="inlineStr">
+        <is>
+          <t>epee-onyx</t>
+        </is>
+      </c>
+      <c r="B122" s="87" t="inlineStr">
+        <is>
+          <t>Big Onyx Sword</t>
+        </is>
+      </c>
+      <c r="C122" s="91" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="D122" s="85" t="n">
+        <v>64000</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="86" t="inlineStr">
+        <is>
+          <t>grande-faux</t>
+        </is>
+      </c>
+      <c r="B123" s="87" t="inlineStr">
+        <is>
+          <t>Great Scythe</t>
+        </is>
+      </c>
+      <c r="C123" s="91" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="D123" s="85" t="n">
+        <v>88000</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="86" t="inlineStr">
+        <is>
+          <t>marteau-de-lave</t>
+        </is>
+      </c>
+      <c r="B124" s="87" t="inlineStr">
+        <is>
+          <t>Magma Hammer</t>
+        </is>
+      </c>
+      <c r="C124" s="91" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="D124" s="85" t="n">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="86" t="inlineStr">
+        <is>
+          <t>plate-onyx</t>
+        </is>
+      </c>
+      <c r="B125" s="87" t="inlineStr">
+        <is>
+          <t>Onyx Guard Plate</t>
+        </is>
+      </c>
+      <c r="C125" s="91" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="D125" s="85" t="n">
+        <v>65000</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="86" t="inlineStr">
+        <is>
+          <t>bottes-onyx</t>
+        </is>
+      </c>
+      <c r="B126" s="87" t="inlineStr">
+        <is>
+          <t>Onyx Boots</t>
+        </is>
+      </c>
+      <c r="C126" s="91" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="D126" s="85" t="n">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="86" t="inlineStr">
+        <is>
+          <t>collier-de-saphir-parfait</t>
+        </is>
+      </c>
+      <c r="B127" s="87" t="inlineStr">
+        <is>
+          <t>Perfect Sapphire Amulet</t>
+        </is>
+      </c>
+      <c r="C127" s="91" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="D127" s="85" t="n">
+        <v>84000</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="86" t="inlineStr">
+        <is>
+          <t>gants-onyx</t>
+        </is>
+      </c>
+      <c r="B128" s="87" t="inlineStr">
+        <is>
+          <t>Onyx Glove</t>
+        </is>
+      </c>
+      <c r="C128" s="91" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="D128" s="85" t="n">
+        <v>82000</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="86" t="inlineStr">
+        <is>
+          <t>sac-sans-fond</t>
+        </is>
+      </c>
+      <c r="B129" s="87" t="inlineStr">
+        <is>
+          <t>Bottomless Bag</t>
+        </is>
+      </c>
+      <c r="C129" s="91" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="D129" s="85" t="n">
+        <v>94000</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="86" t="inlineStr">
+        <is>
+          <t>sac-maitre-mineur</t>
+        </is>
+      </c>
+      <c r="B130" s="87" t="inlineStr">
+        <is>
+          <t>Master Miner's Bag</t>
+        </is>
+      </c>
+      <c r="C130" s="92" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="D130" s="85" t="n">
+        <v>290000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/BRUTAL-items-et-cartes.xlsx
+++ b/docs/BRUTAL-items-et-cartes.xlsx
@@ -14,6 +14,7 @@
     <sheet name="Effets" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Recettes" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Valeurs" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Ressources" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -24538,4 +24539,405 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" style="57" min="1" max="1"/>
+    <col width="16" customWidth="1" style="57" min="2" max="2"/>
+    <col width="8" customWidth="1" style="57" min="3" max="3"/>
+    <col width="12" customWidth="1" style="57" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="61" t="inlineStr">
+        <is>
+          <t>VALEUR DES RESSOURCES — SOURCE ÉDITABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="62" t="inlineStr">
+        <is>
+          <t>Édite la colonne « Valeur » (D), puis lance : python3 outils/importer_valeurs.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="62" t="inlineStr">
+        <is>
+          <t>Valeur = prix de BASE au marché (le marché la fait ensuite fluctuer). Ce sont les prix ACTUELS, à ajuster librement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="85" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B6" s="85" t="inlineStr">
+        <is>
+          <t>Nom</t>
+        </is>
+      </c>
+      <c r="C6" s="85" t="inlineStr">
+        <is>
+          <t>Rang</t>
+        </is>
+      </c>
+      <c r="D6" s="85" t="inlineStr">
+        <is>
+          <t>Valeur</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="86" t="inlineStr">
+        <is>
+          <t>pierre-taillee</t>
+        </is>
+      </c>
+      <c r="B7" s="87" t="inlineStr">
+        <is>
+          <t>Cut Stone</t>
+        </is>
+      </c>
+      <c r="C7" s="88" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="85" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="86" t="inlineStr">
+        <is>
+          <t>charbon</t>
+        </is>
+      </c>
+      <c r="B8" s="87" t="inlineStr">
+        <is>
+          <t>Coal</t>
+        </is>
+      </c>
+      <c r="C8" s="88" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="85" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="86" t="inlineStr">
+        <is>
+          <t>cuivre</t>
+        </is>
+      </c>
+      <c r="B9" s="87" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="C9" s="88" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" s="85" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="86" t="inlineStr">
+        <is>
+          <t>fer</t>
+        </is>
+      </c>
+      <c r="B10" s="87" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="C10" s="88" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" s="85" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="86" t="inlineStr">
+        <is>
+          <t>argent</t>
+        </is>
+      </c>
+      <c r="B11" s="87" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="C11" s="89" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" s="85" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="86" t="inlineStr">
+        <is>
+          <t>or</t>
+        </is>
+      </c>
+      <c r="B12" s="87" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="C12" s="89" t="n">
+        <v>6</v>
+      </c>
+      <c r="D12" s="85" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="86" t="inlineStr">
+        <is>
+          <t>malachite</t>
+        </is>
+      </c>
+      <c r="B13" s="87" t="inlineStr">
+        <is>
+          <t>Malachite</t>
+        </is>
+      </c>
+      <c r="C13" s="90" t="n">
+        <v>7</v>
+      </c>
+      <c r="D13" s="85" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="86" t="inlineStr">
+        <is>
+          <t>lapis</t>
+        </is>
+      </c>
+      <c r="B14" s="87" t="inlineStr">
+        <is>
+          <t>Lapis Lazuli</t>
+        </is>
+      </c>
+      <c r="C14" s="90" t="n">
+        <v>7</v>
+      </c>
+      <c r="D14" s="85" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="86" t="inlineStr">
+        <is>
+          <t>amethyste</t>
+        </is>
+      </c>
+      <c r="B15" s="87" t="inlineStr">
+        <is>
+          <t>Amethyst</t>
+        </is>
+      </c>
+      <c r="C15" s="90" t="n">
+        <v>7</v>
+      </c>
+      <c r="D15" s="85" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="86" t="inlineStr">
+        <is>
+          <t>titane</t>
+        </is>
+      </c>
+      <c r="B16" s="87" t="inlineStr">
+        <is>
+          <t>Titanium</t>
+        </is>
+      </c>
+      <c r="C16" s="90" t="n">
+        <v>8</v>
+      </c>
+      <c r="D16" s="85" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="86" t="inlineStr">
+        <is>
+          <t>emeraude</t>
+        </is>
+      </c>
+      <c r="B17" s="87" t="inlineStr">
+        <is>
+          <t>Emerald</t>
+        </is>
+      </c>
+      <c r="C17" s="90" t="n">
+        <v>9</v>
+      </c>
+      <c r="D17" s="85" t="n">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="86" t="inlineStr">
+        <is>
+          <t>rubis</t>
+        </is>
+      </c>
+      <c r="B18" s="87" t="inlineStr">
+        <is>
+          <t>Ruby</t>
+        </is>
+      </c>
+      <c r="C18" s="90" t="n">
+        <v>9</v>
+      </c>
+      <c r="D18" s="85" t="n">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="86" t="inlineStr">
+        <is>
+          <t>saphir</t>
+        </is>
+      </c>
+      <c r="B19" s="87" t="inlineStr">
+        <is>
+          <t>Sapphire</t>
+        </is>
+      </c>
+      <c r="C19" s="91" t="n">
+        <v>10</v>
+      </c>
+      <c r="D19" s="85" t="n">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="86" t="inlineStr">
+        <is>
+          <t>diamant</t>
+        </is>
+      </c>
+      <c r="B20" s="87" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="C20" s="91" t="n">
+        <v>11</v>
+      </c>
+      <c r="D20" s="85" t="n">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="86" t="inlineStr">
+        <is>
+          <t>mithril</t>
+        </is>
+      </c>
+      <c r="B21" s="87" t="inlineStr">
+        <is>
+          <t>Mithril</t>
+        </is>
+      </c>
+      <c r="C21" s="91" t="n">
+        <v>11</v>
+      </c>
+      <c r="D21" s="85" t="n">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="86" t="inlineStr">
+        <is>
+          <t>onyx</t>
+        </is>
+      </c>
+      <c r="B22" s="87" t="inlineStr">
+        <is>
+          <t>Onyx</t>
+        </is>
+      </c>
+      <c r="C22" s="91" t="n">
+        <v>12</v>
+      </c>
+      <c r="D22" s="85" t="n">
+        <v>1928</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="86" t="inlineStr">
+        <is>
+          <t>pierre-solaire</t>
+        </is>
+      </c>
+      <c r="B23" s="87" t="inlineStr">
+        <is>
+          <t>Sunstone</t>
+        </is>
+      </c>
+      <c r="C23" s="91" t="n">
+        <v>12</v>
+      </c>
+      <c r="D23" s="85" t="n">
+        <v>1928</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="86" t="inlineStr">
+        <is>
+          <t>bois</t>
+        </is>
+      </c>
+      <c r="B24" s="87" t="inlineStr">
+        <is>
+          <t>Wood</t>
+        </is>
+      </c>
+      <c r="C24" s="88" t="inlineStr"/>
+      <c r="D24" s="85" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="86" t="inlineStr">
+        <is>
+          <t>cuir</t>
+        </is>
+      </c>
+      <c r="B25" s="87" t="inlineStr">
+        <is>
+          <t>Leather</t>
+        </is>
+      </c>
+      <c r="C25" s="88" t="inlineStr"/>
+      <c r="D25" s="85" t="n">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/BRUTAL-items-et-cartes.xlsx
+++ b/docs/BRUTAL-items-et-cartes.xlsx
@@ -24547,7 +24547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="57" min="1" max="1"/>
@@ -24937,6 +24937,70 @@
         <v>7</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="86" t="inlineStr">
+        <is>
+          <t>cuir-epais</t>
+        </is>
+      </c>
+      <c r="B26" s="87" t="inlineStr">
+        <is>
+          <t>Thick Leather</t>
+        </is>
+      </c>
+      <c r="C26" s="89" t="inlineStr"/>
+      <c r="D26" s="85" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="86" t="inlineStr">
+        <is>
+          <t>cuir-etrange</t>
+        </is>
+      </c>
+      <c r="B27" s="87" t="inlineStr">
+        <is>
+          <t>Strange Leather</t>
+        </is>
+      </c>
+      <c r="C27" s="90" t="inlineStr"/>
+      <c r="D27" s="85" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="86" t="inlineStr">
+        <is>
+          <t>bois-sombre</t>
+        </is>
+      </c>
+      <c r="B28" s="87" t="inlineStr">
+        <is>
+          <t>Dark Wood</t>
+        </is>
+      </c>
+      <c r="C28" s="89" t="inlineStr"/>
+      <c r="D28" s="85" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="86" t="inlineStr">
+        <is>
+          <t>bois-enchante</t>
+        </is>
+      </c>
+      <c r="B29" s="87" t="inlineStr">
+        <is>
+          <t>Enchanted Wood</t>
+        </is>
+      </c>
+      <c r="C29" s="90" t="inlineStr"/>
+      <c r="D29" s="85" t="n">
+        <v>120</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/BRUTAL-items-et-cartes.xlsx
+++ b/docs/BRUTAL-items-et-cartes.xlsx
@@ -15,6 +15,8 @@
     <sheet name="Valeurs" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Ressources" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Recettes" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Profondeurs" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Profondeurs-chances" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -24,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="16">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -106,8 +108,16 @@
       <name val="Consolas"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="59">
+  <fills count="60">
     <fill>
       <patternFill/>
     </fill>
@@ -399,6 +409,11 @@
         <fgColor rgb="007a5a86"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E2A22"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -441,7 +456,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -656,6 +671,8 @@
     <xf numFmtId="0" fontId="14" fillId="58" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="59" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1318,6 +1335,73 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" style="57" min="1" max="1"/>
+    <col width="12" customWidth="1" style="57" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="98" t="inlineStr">
+        <is>
+          <t>CHANCE DE RARETÉ par CHOIX de loot (en %) — doit sommer à 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="99" t="inlineStr">
+        <is>
+          <t>rarete</t>
+        </is>
+      </c>
+      <c r="B3" s="99" t="inlineStr">
+        <is>
+          <t>Chance (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>normale</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>epique</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -25098,4 +25182,216 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" style="57" min="1" max="1"/>
+    <col width="22" customWidth="1" style="57" min="2" max="2"/>
+    <col width="12" customWidth="1" style="57" min="3" max="3"/>
+    <col width="12" customWidth="1" style="57" min="4" max="4"/>
+    <col width="10" customWidth="1" style="57" min="5" max="5"/>
+    <col width="8" customWidth="1" style="57" min="6" max="6"/>
+    <col width="8" customWidth="1" style="57" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="98" t="inlineStr">
+        <is>
+          <t>LOOTS DE PROFONDEUR — buffs de « run » (SOURCE ÉDITABLE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>À chaque étage des profondeurs, on choisit UN loot parmi 2 (ou +). Les buffs s'accumulent</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>toute la descente et sont perdus en ressortant. Édite les valeurs, puis : python3 outils/importer_profondeur.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Effets reconnus : force (dégâts perm. en combat) · gold (or versé si on sort VIVANT) · celerite (% vitesse combat) · armure (armure au début du combat)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="99" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B6" s="99" t="inlineStr">
+        <is>
+          <t>Nom</t>
+        </is>
+      </c>
+      <c r="C6" s="99" t="inlineStr">
+        <is>
+          <t>Effet</t>
+        </is>
+      </c>
+      <c r="D6" s="99" t="inlineStr">
+        <is>
+          <t>Icône (hex)</t>
+        </is>
+      </c>
+      <c r="E6" s="99" t="inlineStr">
+        <is>
+          <t>Normale</t>
+        </is>
+      </c>
+      <c r="F6" s="99" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="G6" s="99" t="inlineStr">
+        <is>
+          <t>Épique</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>pierre-force</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Strength Stone</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>force</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>#d9542a</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>tresor-gold</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Gold Hoard</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>gold</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>#e0b64e</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100</v>
+      </c>
+      <c r="F8" t="n">
+        <v>200</v>
+      </c>
+      <c r="G8" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>pierre-celerite</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Celerity Stone</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>celerite</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>#5fb0e8</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" t="n">
+        <v>20</v>
+      </c>
+      <c r="G9" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>plaque-renforcement</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Reinforcement Plate</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>armure</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>#9cd3ff</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" t="n">
+        <v>20</v>
+      </c>
+      <c r="G10" t="n">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/BRUTAL-items-et-cartes.xlsx
+++ b/docs/BRUTAL-items-et-cartes.xlsx
@@ -25190,7 +25190,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="57" min="1" max="1"/>
@@ -25391,6 +25391,37 @@
         <v>50</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>portail-profondeur</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Depth Portal</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>porte</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>#5fd08a</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/BRUTAL-items-et-cartes.xlsx
+++ b/docs/BRUTAL-items-et-cartes.xlsx
@@ -17,6 +17,7 @@
     <sheet name="Recettes" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Profondeurs" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Profondeurs-chances" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Monstres" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -26,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -116,8 +117,13 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00808080"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="60">
+  <fills count="61">
     <fill>
       <patternFill/>
     </fill>
@@ -414,6 +420,11 @@
         <fgColor rgb="002E2A22"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -456,7 +467,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -673,6 +684,8 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="59" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="60" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1402,6 +1415,258 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="57" min="1" max="1"/>
+    <col width="20" customWidth="1" style="57" min="2" max="2"/>
+    <col width="8" customWidth="1" style="57" min="3" max="3"/>
+    <col width="12" customWidth="1" style="57" min="4" max="4"/>
+    <col width="7" customWidth="1" style="57" min="5" max="5"/>
+    <col width="9" customWidth="1" style="57" min="6" max="6"/>
+    <col width="7" customWidth="1" style="57" min="7" max="7"/>
+    <col width="9" customWidth="1" style="57" min="8" max="8"/>
+    <col width="52" customWidth="1" style="57" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="100" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="100" t="inlineStr">
+        <is>
+          <t>nom</t>
+        </is>
+      </c>
+      <c r="C1" s="100" t="inlineStr">
+        <is>
+          <t>niveau</t>
+        </is>
+      </c>
+      <c r="D1" s="100" t="inlineStr">
+        <is>
+          <t>famille</t>
+        </is>
+      </c>
+      <c r="E1" s="100" t="inlineStr">
+        <is>
+          <t>pv</t>
+        </is>
+      </c>
+      <c r="F1" s="100" t="inlineStr">
+        <is>
+          <t>attaque</t>
+        </is>
+      </c>
+      <c r="G1" s="100" t="inlineStr">
+        <is>
+          <t>xp</t>
+        </is>
+      </c>
+      <c r="H1" s="100" t="inlineStr">
+        <is>
+          <t>vitesse</t>
+        </is>
+      </c>
+      <c r="I1" s="100" t="inlineStr">
+        <is>
+          <t>actions</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="101" t="inlineStr">
+        <is>
+          <t>identifiant (ne pas changer)</t>
+        </is>
+      </c>
+      <c r="B2" s="101" t="inlineStr">
+        <is>
+          <t>nom affiché (anglais)</t>
+        </is>
+      </c>
+      <c r="C2" s="101" t="inlineStr">
+        <is>
+          <t>niveau (→ or lâché)</t>
+        </is>
+      </c>
+      <c r="D2" s="101" t="inlineStr">
+        <is>
+          <t>gobelin / animal / (vide)</t>
+        </is>
+      </c>
+      <c r="E2" s="101" t="inlineStr">
+        <is>
+          <t>points de vie</t>
+        </is>
+      </c>
+      <c r="F2" s="101" t="inlineStr">
+        <is>
+          <t>dégâts par coup</t>
+        </is>
+      </c>
+      <c r="G2" s="101" t="inlineStr">
+        <is>
+          <t>XP donnée à la mort</t>
+        </is>
+      </c>
+      <c r="H2" s="101" t="inlineStr">
+        <is>
+          <t>vitesse d'initiative ET d'animation (grand = rapide)</t>
+        </is>
+      </c>
+      <c r="I2" s="101" t="inlineStr">
+        <is>
+          <t>actions spéciales : type:valeur:poids séparés par | (types: attaque, soigner, haste-allie). Vide = attaque simple.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>gobelin</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Cave Goblin</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>gobelin</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>24</v>
+      </c>
+      <c r="F3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>gobelin-vif</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Goblin Skirmisher</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>gobelin</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H4" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>gobelin-chaman</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Goblin Shaman</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>gobelin</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>14</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>12</v>
+      </c>
+      <c r="H5" t="n">
+        <v>7</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>soigner:10:50 | haste-allie:2:30 | attaque:2:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ogre-masque</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Masked Ogre</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>animal</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>58</v>
+      </c>
+      <c r="F6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G6" t="n">
+        <v>24</v>
+      </c>
+      <c r="H6" t="n">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/docs/BRUTAL-items-et-cartes.xlsx
+++ b/docs/BRUTAL-items-et-cartes.xlsx
@@ -18,6 +18,7 @@
     <sheet name="Profondeurs" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Profondeurs-chances" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="Monstres" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Héros" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -1667,6 +1668,162 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" style="57" min="1" max="1"/>
+    <col width="9" customWidth="1" style="57" min="2" max="2"/>
+    <col width="54" customWidth="1" style="57" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="100" t="inlineStr">
+        <is>
+          <t>clé</t>
+        </is>
+      </c>
+      <c r="B1" s="100" t="inlineStr">
+        <is>
+          <t>valeur</t>
+        </is>
+      </c>
+      <c r="C1" s="100" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>pv</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>40</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Vie de base (avant talents/équipement)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>vitesseMarche</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>160</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Vitesse de déplacement en exploration (pixels/seconde)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>vitesseCombat</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Vitesse d'initiative en combat (ATB, agilité de base)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>chaleurDepart</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Chaleur de forge au début d'un combat</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>chaleurRecharge</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Chaleur regagnée à chaque tour</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>chaleurSeuil</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Seuil de surchauffe de la forge</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>chaleurMax</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>8</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Chaleur maximale</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>mainMax</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Nombre maximum de cartes en main</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/docs/BRUTAL-items-et-cartes.xlsx
+++ b/docs/BRUTAL-items-et-cartes.xlsx
@@ -1422,7 +1422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" style="57" min="1" max="1"/>
@@ -1434,6 +1434,7 @@
     <col width="7" customWidth="1" style="57" min="7" max="7"/>
     <col width="9" customWidth="1" style="57" min="8" max="8"/>
     <col width="52" customWidth="1" style="57" min="9" max="9"/>
+    <col width="42" customWidth="1" style="57" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1482,6 +1483,11 @@
           <t>actions</t>
         </is>
       </c>
+      <c r="J1" s="100" t="inlineStr">
+        <is>
+          <t>grand</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="101" t="inlineStr">
@@ -1529,6 +1535,11 @@
           <t>actions spéciales : type:valeur:poids séparés par | (types: attaque, soigner, haste-allie). Vide = attaque simple.</t>
         </is>
       </c>
+      <c r="J2" s="101" t="inlineStr">
+        <is>
+          <t>met 1 si le monstre est GRAND (occupe 2 places, pop plus rare). Vide = normal.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1661,6 +1672,9 @@
       </c>
       <c r="H6" t="n">
         <v>6</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docs/BRUTAL-items-et-cartes.xlsx
+++ b/docs/BRUTAL-items-et-cartes.xlsx
@@ -788,6 +788,23 @@
 </comments>
 </file>
 
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>BRUTAL</author>
+  </authors>
+  <commentList>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>Total que les cartes de l'item devraient fournir (outils/resumer_cartes.py) :
+somme des cibles de chaque carte × sa quantité — dégâts pour une arme, armure
+pour une armure. Entre parenthèses : nb de cartes de l'item vs cible de la rareté.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1870,7 +1887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L171"/>
+  <dimension ref="A1:M171"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" style="100" min="1" max="1"/>
@@ -10751,7 +10768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F141"/>
+  <dimension ref="A1:H141"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" style="100" min="1" max="1"/>
@@ -10759,6 +10776,7 @@
     <col width="11" customWidth="1" style="100" min="4" max="4"/>
     <col width="71.5703125" customWidth="1" style="100" min="5" max="5"/>
     <col width="52" customWidth="1" style="100" min="6" max="6"/>
+    <col width="30" customWidth="1" style="100" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="21.95" customHeight="1" s="100">
@@ -10790,6 +10808,11 @@
       <c r="F1" s="10" t="inlineStr">
         <is>
           <t>Effet hors-carte / spécial</t>
+        </is>
+      </c>
+      <c r="G1" s="101" t="inlineStr">
+        <is>
+          <t>Total visé (barème)</t>
         </is>
       </c>
     </row>
@@ -10832,6 +10855,11 @@
         </is>
       </c>
       <c r="F3" s="14" t="n"/>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>≈ 25 dégâts  (4 cartes/5 visées)</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="100">
       <c r="A4" s="13" t="inlineStr">
@@ -10860,6 +10888,11 @@
         </is>
       </c>
       <c r="F4" s="14" t="n"/>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>≈ 20 dégâts  (4 cartes/5 visées)</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="100">
       <c r="A5" s="13" t="inlineStr">
@@ -10888,6 +10921,11 @@
         </is>
       </c>
       <c r="F5" s="14" t="n"/>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>≈ 20 dégâts  (4 cartes/5 visées)</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="100">
       <c r="A6" s="13" t="inlineStr">
@@ -10916,6 +10954,11 @@
         </is>
       </c>
       <c r="F6" s="14" t="n"/>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>≈ 35 dégâts  ·  ≈ 6 armure  (5 cartes/5 visées)</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="100">
       <c r="A7" s="13" t="inlineStr">
@@ -10944,6 +10987,11 @@
         </is>
       </c>
       <c r="F7" s="14" t="n"/>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>≈ 25 dégâts  (5 cartes/5 visées)</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="100">
       <c r="A8" s="13" t="inlineStr">
@@ -10972,6 +11020,11 @@
         </is>
       </c>
       <c r="F8" s="14" t="n"/>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>≈ 25 dégâts  ·  ≈ 3 armure  (4 cartes/5 visées)</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="100">
       <c r="A9" s="13" t="inlineStr">
@@ -11000,6 +11053,11 @@
         </is>
       </c>
       <c r="F9" s="14" t="n"/>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>≈ 10 dégâts  ·  ≈ 6 armure  (5 cartes/5 visées · 1 buff)</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="100">
       <c r="A10" s="13" t="inlineStr">
@@ -11028,6 +11086,11 @@
         </is>
       </c>
       <c r="F10" s="14" t="n"/>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>≈ 35 dégâts  (5 cartes/5 visées)</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="100">
       <c r="A11" s="13" t="inlineStr">
@@ -11056,6 +11119,11 @@
         </is>
       </c>
       <c r="F11" s="14" t="n"/>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>≈ 20 dégâts  (4 cartes/5 visées)</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="100">
       <c r="A12" s="13" t="inlineStr">
@@ -11084,6 +11152,11 @@
         </is>
       </c>
       <c r="F12" s="14" t="n"/>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>≈ 20 dégâts  (4 cartes/5 visées)</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="100">
       <c r="A13" s="13" t="inlineStr">
@@ -11112,6 +11185,11 @@
         </is>
       </c>
       <c r="F13" s="14" t="n"/>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>≈ 20 dégâts  (4 cartes/5 visées)</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="100">
       <c r="A14" s="13" t="inlineStr">
@@ -11140,6 +11218,11 @@
         </is>
       </c>
       <c r="F14" s="14" t="n"/>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>≈ 25 dégâts  (5 cartes/5 visées)</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="100">
       <c r="A15" s="13" t="inlineStr">
@@ -11168,6 +11251,11 @@
         </is>
       </c>
       <c r="F15" s="14" t="n"/>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>≈ 35 dégâts  (5 cartes/5 visées)</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="100">
       <c r="A16" s="13" t="inlineStr">
@@ -11196,6 +11284,11 @@
         </is>
       </c>
       <c r="F16" s="14" t="n"/>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>≈ 20 dégâts  (4 cartes/5 visées)</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="100">
       <c r="A17" s="13" t="inlineStr">
@@ -11224,6 +11317,11 @@
         </is>
       </c>
       <c r="F17" s="14" t="n"/>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>≈ 15 dégâts  (4 cartes/5 visées · 1 buff)</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="100">
       <c r="A18" s="13" t="inlineStr">
@@ -11252,6 +11350,11 @@
         </is>
       </c>
       <c r="F18" s="14" t="n"/>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>≈ 25 dégâts  ·  ≈ 3 armure  (5 cartes/5 visées)</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="100">
       <c r="A19" s="15" t="inlineStr">
@@ -11280,6 +11383,11 @@
         </is>
       </c>
       <c r="F19" s="16" t="n"/>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>≈ 29 dégâts  (5 cartes/6 visées · 1 buff)</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="100">
       <c r="A20" s="16" t="inlineStr">
@@ -11312,6 +11420,11 @@
           <t>Deux mains</t>
         </is>
       </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>≈ 72 dégâts  (8 cartes/6 visées · 3 buff)</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="100">
       <c r="A21" s="15" t="inlineStr">
@@ -11340,6 +11453,11 @@
         </is>
       </c>
       <c r="F21" s="16" t="n"/>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>≈ 24 dégâts  (4 cartes/6 visées · 1 buff)</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="100">
       <c r="A22" s="15" t="inlineStr">
@@ -11368,6 +11486,11 @@
         </is>
       </c>
       <c r="F22" s="16" t="n"/>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>≈ 23 dégâts  (4 cartes/6 visées)</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="100">
       <c r="A23" s="15" t="inlineStr">
@@ -11396,6 +11519,11 @@
         </is>
       </c>
       <c r="F23" s="16" t="n"/>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>≈ 55 dégâts  (5 cartes/6 visées)</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="100">
       <c r="A24" s="15" t="inlineStr">
@@ -11424,6 +11552,11 @@
         </is>
       </c>
       <c r="F24" s="16" t="n"/>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>≈ 82 dégâts  (6 cartes/6 visées)</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="100">
       <c r="A25" s="15" t="inlineStr">
@@ -11452,6 +11585,11 @@
         </is>
       </c>
       <c r="F25" s="16" t="n"/>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>≈ 31 dégâts  (4 cartes/6 visées)</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="100">
       <c r="A26" s="15" t="inlineStr">
@@ -11484,6 +11622,11 @@
           <t>Deux mains</t>
         </is>
       </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>≈ 132 dégâts  ·  ≈ 7,5 armure  (9 cartes/6 visées)</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="100">
       <c r="A27" s="15" t="inlineStr">
@@ -11512,6 +11655,11 @@
         </is>
       </c>
       <c r="F27" s="16" t="n"/>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>≈ 42 dégâts  (5 cartes/6 visées · 1 buff)</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="100">
       <c r="A28" s="15" t="inlineStr">
@@ -11540,6 +11688,11 @@
         </is>
       </c>
       <c r="F28" s="16" t="n"/>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>≈ 23 dégâts  (4 cartes/6 visées)</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="100">
       <c r="A29" s="15" t="inlineStr">
@@ -11568,6 +11721,11 @@
         </is>
       </c>
       <c r="F29" s="16" t="n"/>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>≈ 53 dégâts  (5 cartes/6 visées)</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="15" customHeight="1" s="100">
       <c r="A30" s="15" t="inlineStr">
@@ -11596,6 +11754,11 @@
         </is>
       </c>
       <c r="F30" s="16" t="n"/>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>≈ 40 dégâts  ·  ≈ 6 armure  (5 cartes/6 visées)</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="100">
       <c r="A31" s="15" t="inlineStr">
@@ -11628,6 +11791,11 @@
           <t>Combo: Twin combo: +3 permanent Strength if the same Twin Daggers are in your off-hand.</t>
         </is>
       </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>≈ 37 dégâts  (5 cartes/6 visées)</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="100">
       <c r="A32" s="15" t="inlineStr">
@@ -11656,6 +11824,11 @@
         </is>
       </c>
       <c r="F32" s="16" t="n"/>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>≈ 23 dégâts  (4 cartes/6 visées)</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="15" customHeight="1" s="100">
       <c r="A33" s="15" t="inlineStr">
@@ -11684,6 +11857,11 @@
         </is>
       </c>
       <c r="F33" s="16" t="n"/>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>≈ 48 dégâts  ·  ≈ 6 armure  (5 cartes/6 visées)</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="15" customHeight="1" s="100">
       <c r="A34" s="17" t="inlineStr">
@@ -11716,6 +11894,11 @@
           <t>Combo: Twin fang: +5 permanent Strength if another dagger is in your off-hand.</t>
         </is>
       </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>≈ 168 dégâts  (10 cartes/6 visées · 1 non listée)</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="15" customHeight="1" s="100">
       <c r="A35" s="17" t="inlineStr">
@@ -11748,6 +11931,11 @@
           <t>Deux mains, Bonsu passif de 2 stone par tours (permanent tant que l'arme est équipée).</t>
         </is>
       </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>≈ 306 dégâts  ·  ≈ 24 armure  (8 cartes/6 visées · 1 buff)</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="15" customHeight="1" s="100">
       <c r="A36" s="17" t="inlineStr">
@@ -11780,6 +11968,11 @@
           <t>Deux mains</t>
         </is>
       </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>≈ 252 dégâts  (6 cartes/6 visées)</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="15" customHeight="1" s="100">
       <c r="A37" s="21" t="inlineStr">
@@ -11812,6 +12005,11 @@
           <t>Deux mains</t>
         </is>
       </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>≈ 204 dégâts  (7 cartes/7 visées · 2 buff)</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="100">
       <c r="A38" s="53" t="inlineStr">
@@ -11844,6 +12042,11 @@
           <t>Deux mains</t>
         </is>
       </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>≈ 357 dégâts  (8 cartes/7 visées · 1 buff)</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="100">
       <c r="A39" s="21" t="inlineStr">
@@ -11872,6 +12075,11 @@
         </is>
       </c>
       <c r="F39" s="22" t="n"/>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>≈ 272 dégâts  (7 cartes/7 visées)</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="17.1" customHeight="1" s="100">
       <c r="A40" s="47" t="inlineStr">
@@ -11912,6 +12120,11 @@
         </is>
       </c>
       <c r="F41" s="14" t="n"/>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>aucun dégât/armure  (2 cartes/5 visées · 2 buff)</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="100">
       <c r="A42" s="13" t="inlineStr">
@@ -11940,6 +12153,11 @@
         </is>
       </c>
       <c r="F42" s="14" t="n"/>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>≈ 3 armure  (2 cartes/5 visées · 1 buff)</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="100">
       <c r="A43" s="13" t="inlineStr">
@@ -11968,6 +12186,11 @@
         </is>
       </c>
       <c r="F43" s="14" t="n"/>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>≈ 20 dégâts  (3 cartes/5 visées)</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="100">
       <c r="A44" s="13" t="inlineStr">
@@ -11996,6 +12219,11 @@
         </is>
       </c>
       <c r="F44" s="14" t="n"/>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>aucun dégât/armure  (3 cartes/5 visées · 3 buff)</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="15" customHeight="1" s="100">
       <c r="A45" s="13" t="inlineStr">
@@ -12024,6 +12252,11 @@
         </is>
       </c>
       <c r="F45" s="14" t="n"/>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>aucun dégât/armure  (2 cartes/5 visées · 2 buff)</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="15" customHeight="1" s="100">
       <c r="A46" s="13" t="inlineStr">
@@ -12052,6 +12285,11 @@
         </is>
       </c>
       <c r="F46" s="14" t="n"/>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>≈ 9 armure  (3 cartes/5 visées)</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="15" customHeight="1" s="100">
       <c r="A47" s="15" t="inlineStr">
@@ -12080,6 +12318,11 @@
         </is>
       </c>
       <c r="F47" s="16" t="n"/>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>≈ 26 dégâts  (3 cartes/6 visées)</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="15" customHeight="1" s="100">
       <c r="A48" s="15" t="inlineStr">
@@ -12108,6 +12351,11 @@
         </is>
       </c>
       <c r="F48" s="16" t="n"/>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>≈ 14 armure  (4 cartes/6 visées)</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="15" customHeight="1" s="100">
       <c r="A49" s="15" t="inlineStr">
@@ -12136,6 +12384,11 @@
         </is>
       </c>
       <c r="F49" s="16" t="n"/>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>aucun dégât/armure  (2 cartes/6 visées · 2 buff)</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="15" customHeight="1" s="100">
       <c r="A50" s="15" t="inlineStr">
@@ -12164,6 +12417,11 @@
         </is>
       </c>
       <c r="F50" s="16" t="n"/>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>≈ 16 dégâts  (3 cartes/6 visées · 2 buff)</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="15" customHeight="1" s="100">
       <c r="A51" s="15" t="inlineStr">
@@ -12196,6 +12454,11 @@
           <t>When hit by a melee attack, the attacker takes 2 damage.</t>
         </is>
       </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>≈ 16 armure  (3 cartes/6 visées)</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="15" customHeight="1" s="100">
       <c r="A52" s="17" t="inlineStr">
@@ -12226,6 +12489,11 @@
       <c r="F52" s="18" t="inlineStr">
         <is>
           <t>When hit by a melee attack, gain 2 Stone.</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>≈ 48 dégâts  ·  ≈ 47 armure  (6 cartes/6 visées)</t>
         </is>
       </c>
     </row>
@@ -12272,6 +12540,11 @@
           <t>Armure début: 8</t>
         </is>
       </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>≈ 14 armure  (4 cartes/5 visées)</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="15" customHeight="1" s="100">
       <c r="A55" s="13" t="inlineStr">
@@ -12304,6 +12577,11 @@
           <t>Armure début: 6</t>
         </is>
       </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>≈ 3 armure  (2 cartes/5 visées · 1 buff)</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="15" customHeight="1" s="100">
       <c r="A56" s="13" t="inlineStr">
@@ -12336,6 +12614,11 @@
           <t>Armure début: 6</t>
         </is>
       </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>≈ 9 armure  (3 cartes/5 visées)</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="15" customHeight="1" s="100">
       <c r="A57" s="13" t="inlineStr">
@@ -12368,6 +12651,11 @@
           <t>Armure début: 6</t>
         </is>
       </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>≈ 6 armure  (4 cartes/5 visées · 2 buff)</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="15" customHeight="1" s="100">
       <c r="A58" s="13" t="inlineStr">
@@ -12400,6 +12688,11 @@
           <t>Armure début: 8</t>
         </is>
       </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>≈ 9 armure  (4 cartes/5 visées · 1 buff)</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="15" customHeight="1" s="100">
       <c r="A59" s="15" t="inlineStr">
@@ -12432,6 +12725,11 @@
           <t>Armure début: 15</t>
         </is>
       </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>≈ 30 armure  (4 cartes/6 visées)</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="15" customHeight="1" s="100">
       <c r="A60" s="15" t="inlineStr">
@@ -12464,6 +12762,11 @@
           <t>Armure début: 4</t>
         </is>
       </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>≈ 5 armure  (4 cartes/6 visées · 3 buff)</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="15" customHeight="1" s="100">
       <c r="A61" s="15" t="inlineStr">
@@ -12496,6 +12799,11 @@
           <t>Armure début: 10  ·  When hit by a melee attack, the attacker takes 2 damage.</t>
         </is>
       </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>≈ 25 armure  (4 cartes/6 visées)</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="15" customHeight="1" s="100">
       <c r="A62" s="15" t="inlineStr">
@@ -12528,6 +12836,11 @@
           <t>Armure début: 12  ·  Set: Stone Age Set</t>
         </is>
       </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>≈ 85 armure  (10 cartes/6 visées)</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="15" customHeight="1" s="100">
       <c r="A63" s="17" t="inlineStr">
@@ -12560,6 +12873,11 @@
           <t>Armure début: 20 - +4 stone a chaque tour (permanent)  ·  Set: Blood Set</t>
         </is>
       </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>≈ 60 dégâts  ·  ≈ 48 armure  (6 cartes/6 visées)</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="15" customHeight="1" s="100">
       <c r="A64" s="17" t="inlineStr">
@@ -12592,6 +12910,11 @@
           <t>Armure début: 30 - +6 stone a chaque tour (permanent)  ·  Set: Crusader Set</t>
         </is>
       </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>≈ 60 dégâts  ·  ≈ 56 armure  (6 cartes/6 visées)</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="15" customHeight="1" s="100">
       <c r="A65" s="17" t="inlineStr">
@@ -12624,6 +12947,11 @@
           <t>Armure début: 22 - +5 stone a chaque tour (permanent)  ·  Set: Mail Set</t>
         </is>
       </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>≈ 56 armure  (6 cartes/6 visées · 1 buff)</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="15" customHeight="1" s="100">
       <c r="A66" s="21" t="inlineStr">
@@ -12654,6 +12982,11 @@
       <c r="F66" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">Armure début: 36 - +10 stone a chaque tour (permanent) ·  Set: Onyx Set </t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>≈ 204 dégâts  ·  ≈ 72 armure  (7 cartes/7 visées)</t>
         </is>
       </c>
     </row>
@@ -12696,6 +13029,11 @@
         </is>
       </c>
       <c r="F68" s="14" t="n"/>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>≈ 10 dégâts  (2 cartes/5 visées)</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="15" customHeight="1" s="100">
       <c r="A69" s="13" t="inlineStr">
@@ -12724,6 +13062,11 @@
         </is>
       </c>
       <c r="F69" s="14" t="n"/>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>aucun dégât/armure  (1 carte/5 visées · 1 buff)</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="15" customHeight="1" s="100">
       <c r="A70" s="13" t="inlineStr">
@@ -12752,6 +13095,11 @@
         </is>
       </c>
       <c r="F70" s="14" t="n"/>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>aucun dégât/armure  (2 cartes/5 visées · 2 buff)</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="15" customHeight="1" s="100">
       <c r="A71" s="13" t="inlineStr">
@@ -12780,6 +13128,11 @@
         </is>
       </c>
       <c r="F71" s="14" t="n"/>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>aucun dégât/armure  (2 cartes/5 visées · 2 buff)</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="15" customHeight="1" s="100">
       <c r="A72" s="13" t="inlineStr">
@@ -12808,6 +13161,11 @@
         </is>
       </c>
       <c r="F72" s="14" t="n"/>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>≈ 5 dégâts  (2 cartes/5 visées · 1 buff)</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="15" customHeight="1" s="100">
       <c r="A73" s="15" t="inlineStr">
@@ -12836,6 +13194,11 @@
         </is>
       </c>
       <c r="F73" s="16" t="n"/>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>aucun dégât/armure  (2 cartes/6 visées · 2 buff)</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="15" customHeight="1" s="100">
       <c r="A74" s="15" t="inlineStr">
@@ -12864,6 +13227,11 @@
         </is>
       </c>
       <c r="F74" s="16" t="n"/>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>aucun dégât/armure  (2 cartes/6 visées · 2 buff)</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="15" customHeight="1" s="100">
       <c r="A75" s="15" t="inlineStr">
@@ -12892,6 +13260,11 @@
         </is>
       </c>
       <c r="F75" s="16" t="n"/>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>aucun dégât/armure  (1 carte/6 visées · 1 buff)</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="15" customHeight="1" s="100">
       <c r="A76" s="15" t="inlineStr">
@@ -12920,6 +13293,11 @@
         </is>
       </c>
       <c r="F76" s="16" t="n"/>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>≈ 13 dégâts  (2 cartes/6 visées)</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="15" customHeight="1" s="100">
       <c r="A77" s="17" t="inlineStr">
@@ -12948,6 +13326,11 @@
         </is>
       </c>
       <c r="F77" s="18" t="n"/>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>aucun dégât/armure  (2 cartes/6 visées · 2 buff)</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="15" customHeight="1" s="100">
       <c r="A78" s="21" t="inlineStr">
@@ -12976,6 +13359,11 @@
         </is>
       </c>
       <c r="F78" s="22" t="n"/>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>aucun dégât/armure  (3 cartes/7 visées · 3 buff)</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="17.1" customHeight="1" s="100">
       <c r="A79" s="47" t="inlineStr">
@@ -13016,6 +13404,11 @@
         </is>
       </c>
       <c r="F80" s="14" t="n"/>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>≈ 10 dégâts  (2 cartes/5 visées)</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="15" customHeight="1" s="100">
       <c r="A81" s="13" t="inlineStr">
@@ -13044,6 +13437,11 @@
         </is>
       </c>
       <c r="F81" s="14" t="n"/>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>≈ 10 dégâts  (2 cartes/5 visées)</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="15" customHeight="1" s="100">
       <c r="A82" s="13" t="inlineStr">
@@ -13072,6 +13470,11 @@
         </is>
       </c>
       <c r="F82" s="14" t="n"/>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>≈ 10 dégâts  (2 cartes/5 visées)</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="15" customHeight="1" s="100">
       <c r="A83" s="13" t="inlineStr">
@@ -13100,6 +13503,11 @@
         </is>
       </c>
       <c r="F83" s="14" t="n"/>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>aucun dégât/armure  (2 cartes/5 visées · 2 buff)</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="15" customHeight="1" s="100">
       <c r="A84" s="13" t="inlineStr">
@@ -13128,6 +13536,11 @@
         </is>
       </c>
       <c r="F84" s="14" t="n"/>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>aucun dégât/armure  (2 cartes/5 visées · 2 buff)</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="15" customHeight="1" s="100">
       <c r="A85" s="13" t="inlineStr">
@@ -13156,6 +13569,11 @@
         </is>
       </c>
       <c r="F85" s="14" t="n"/>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>aucun dégât/armure  (2 cartes/5 visées · 2 buff)</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="15" customHeight="1" s="100">
       <c r="A86" s="13" t="inlineStr">
@@ -13184,6 +13602,11 @@
         </is>
       </c>
       <c r="F86" s="14" t="n"/>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>≈ 6 armure  (2 cartes/5 visées)</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="15" customHeight="1" s="100">
       <c r="A87" s="13" t="inlineStr">
@@ -13212,6 +13635,11 @@
         </is>
       </c>
       <c r="F87" s="14" t="n"/>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>≈ 10 dégâts  (2 cartes/5 visées)</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="15" customHeight="1" s="100">
       <c r="A88" s="13" t="inlineStr">
@@ -13240,6 +13668,11 @@
         </is>
       </c>
       <c r="F88" s="14" t="n"/>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>≈ 3 armure  (2 cartes/5 visées · 1 buff)</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="15" customHeight="1" s="100">
       <c r="A89" s="15" t="inlineStr">
@@ -13268,6 +13701,11 @@
         </is>
       </c>
       <c r="F89" s="16" t="n"/>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>≈ 16 dégâts  (2 cartes/6 visées)</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="15" customHeight="1" s="100">
       <c r="A90" s="15" t="inlineStr">
@@ -13296,6 +13734,11 @@
         </is>
       </c>
       <c r="F90" s="16" t="n"/>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>≈ 13 dégâts  (2 cartes/6 visées)</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="15" customHeight="1" s="100">
       <c r="A91" s="15" t="inlineStr">
@@ -13324,6 +13767,11 @@
         </is>
       </c>
       <c r="F91" s="16" t="n"/>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>aucun dégât/armure  (2 cartes/6 visées · 2 buff)</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="15" customHeight="1" s="100">
       <c r="A92" s="15" t="inlineStr">
@@ -13352,6 +13800,11 @@
         </is>
       </c>
       <c r="F92" s="16" t="n"/>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>≈ 16 dégâts  (2 cartes/6 visées)</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="15" customHeight="1" s="100">
       <c r="A93" s="15" t="inlineStr">
@@ -13380,6 +13833,11 @@
         </is>
       </c>
       <c r="F93" s="16" t="n"/>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>≈ 21 dégâts  (2 cartes/6 visées)</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="15" customHeight="1" s="100">
       <c r="A94" s="15" t="inlineStr">
@@ -13408,6 +13866,11 @@
         </is>
       </c>
       <c r="F94" s="16" t="n"/>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>≈ 6 armure  (2 cartes/6 visées)</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="15" customHeight="1" s="100">
       <c r="A95" s="15" t="inlineStr">
@@ -13436,6 +13899,11 @@
         </is>
       </c>
       <c r="F95" s="16" t="n"/>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>aucun dégât/armure  (2 cartes/6 visées · 2 buff)</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="15" customHeight="1" s="100">
       <c r="A96" s="15" t="inlineStr">
@@ -13464,6 +13932,11 @@
         </is>
       </c>
       <c r="F96" s="16" t="n"/>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>≈ 21 dégâts  (2 cartes/6 visées)</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="15" customHeight="1" s="100">
       <c r="A97" s="17" t="inlineStr">
@@ -13492,6 +13965,11 @@
         </is>
       </c>
       <c r="F97" s="18" t="n"/>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>≈ 48 dégâts  (2 cartes/6 visées)</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="17.1" customHeight="1" s="100">
       <c r="A98" s="47" t="inlineStr">
@@ -13532,6 +14010,11 @@
         </is>
       </c>
       <c r="F99" s="14" t="n"/>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>aucun dégât/armure  (2 cartes/5 visées · 2 buff)</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="15" customHeight="1" s="100">
       <c r="A100" s="13" t="inlineStr">
@@ -13560,6 +14043,11 @@
         </is>
       </c>
       <c r="F100" s="14" t="n"/>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>≈ 3 armure  (2 cartes/5 visées · 1 buff)</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="15" customHeight="1" s="100">
       <c r="A101" s="13" t="inlineStr">
@@ -13588,6 +14076,11 @@
         </is>
       </c>
       <c r="F101" s="14" t="n"/>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>aucun dégât/armure  (2 cartes/5 visées · 2 buff)</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="15" customHeight="1" s="100">
       <c r="A102" s="13" t="inlineStr">
@@ -13616,6 +14109,11 @@
         </is>
       </c>
       <c r="F102" s="14" t="n"/>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>≈ 10 dégâts  (2 cartes/5 visées)</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="15" customHeight="1" s="100">
       <c r="A103" s="13" t="inlineStr">
@@ -13644,6 +14142,11 @@
         </is>
       </c>
       <c r="F103" s="14" t="n"/>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>≈ 5 dégâts  (2 cartes/5 visées · 1 buff)</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="15" customHeight="1" s="100">
       <c r="A104" s="15" t="inlineStr">
@@ -13672,6 +14175,11 @@
         </is>
       </c>
       <c r="F104" s="16" t="n"/>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>≈ 16 dégâts  ·  ≈ 3 armure  (2 cartes/6 visées)</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="15" customHeight="1" s="100">
       <c r="A105" s="15" t="inlineStr">
@@ -13700,6 +14208,11 @@
         </is>
       </c>
       <c r="F105" s="16" t="n"/>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>aucun dégât/armure  (3 cartes/6 visées · 3 buff)</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="15" customHeight="1" s="100">
       <c r="A106" s="15" t="inlineStr">
@@ -13732,6 +14245,11 @@
           <t>Set: Stone Age Set</t>
         </is>
       </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>≈ 30 armure  (5 cartes/6 visées · 1 buff)</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="15" customHeight="1" s="100">
       <c r="A107" s="15" t="inlineStr">
@@ -13760,6 +14278,11 @@
         </is>
       </c>
       <c r="F107" s="16" t="n"/>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>aucun dégât/armure  (2 cartes/6 visées · 2 buff)</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="15" customHeight="1" s="100">
       <c r="A108" s="15" t="inlineStr">
@@ -13788,6 +14311,11 @@
         </is>
       </c>
       <c r="F108" s="16" t="n"/>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>≈ 10 dégâts  (2 cartes/6 visées)</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="15" customHeight="1" s="100">
       <c r="A109" s="17" t="inlineStr">
@@ -13820,6 +14348,11 @@
           <t>Set: Blood Set</t>
         </is>
       </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>≈ 72 dégâts  (5 cartes/6 visées · 1 buff)</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="15" customHeight="1" s="100">
       <c r="A110" s="17" t="inlineStr">
@@ -13852,6 +14385,11 @@
           <t>Set: Crusader Set</t>
         </is>
       </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>≈ 12 dégâts  (5 cartes/6 visées · 4 buff)</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="15" customHeight="1" s="100">
       <c r="A111" s="17" t="inlineStr">
@@ -13884,6 +14422,11 @@
           <t>Set: Mail Set</t>
         </is>
       </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>aucun dégât/armure  (5 cartes/6 visées · 5 buff)</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="15" customHeight="1" s="100">
       <c r="A112" s="21" t="inlineStr">
@@ -13914,6 +14457,11 @@
       <c r="F112" s="22" t="inlineStr">
         <is>
           <t>Set: Onyx Set</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>≈ 34 dégâts  (6 cartes/7 visées · 4 buff)</t>
         </is>
       </c>
     </row>
@@ -13960,6 +14508,11 @@
           <t>+3 Agilité  ·  +10% déplacement</t>
         </is>
       </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>aucun dégât/armure  (2 cartes/5 visées · 2 buff)</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="15" customHeight="1" s="100">
       <c r="A115" s="13" t="inlineStr">
@@ -13992,6 +14545,11 @@
           <t>+2 Agilité  ·  +8% déplacement</t>
         </is>
       </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>aucun dégât/armure  (2 cartes/5 visées · 2 buff)</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="15" customHeight="1" s="100">
       <c r="A116" s="13" t="inlineStr">
@@ -14024,6 +14582,11 @@
           <t>+3 Agilité  ·  +15% déplacement</t>
         </is>
       </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>aucun dégât/armure  (2 cartes/5 visées · 2 buff)</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="15" customHeight="1" s="100">
       <c r="A117" s="13" t="inlineStr">
@@ -14056,6 +14619,11 @@
           <t>+1 Agilité  ·  +5% déplacement</t>
         </is>
       </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>aucun dégât/armure  (1 carte/5 visées · 1 buff)</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="15" customHeight="1" s="100">
       <c r="A118" s="15" t="inlineStr">
@@ -14088,6 +14656,11 @@
           <t>+6 Agilité  ·  +15% déplacement</t>
         </is>
       </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>≈ 5 dégâts  (2 cartes/6 visées · 1 buff)</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="15" customHeight="1" s="100">
       <c r="A119" s="15" t="inlineStr">
@@ -14120,6 +14693,11 @@
           <t>+3 Agilité  ·  +6% déplacement  ·  Set: Stone Age Set</t>
         </is>
       </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>≈ 30 armure  (5 cartes/6 visées · 1 buff)</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="15" customHeight="1" s="100">
       <c r="A120" s="15" t="inlineStr">
@@ -14152,6 +14730,11 @@
           <t>+4 Agilité  ·  +8% déplacement</t>
         </is>
       </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>≈ 24 dégâts  ·  ≈ 3 armure  (2 cartes/6 visées)</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="15" customHeight="1" s="100">
       <c r="A121" s="15" t="inlineStr">
@@ -14184,6 +14767,11 @@
           <t>+7 Agilité  ·  +20% déplacement</t>
         </is>
       </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>aucun dégât/armure  (4 cartes/6 visées · 4 buff)</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="15" customHeight="1" s="100">
       <c r="A122" s="15" t="inlineStr">
@@ -14216,6 +14804,11 @@
           <t>+8 Agilité  ·  +30% déplacement</t>
         </is>
       </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>aucun dégât/armure  (2 cartes/6 visées · 2 buff)</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="15" customHeight="1" s="100">
       <c r="A123" s="17" t="inlineStr">
@@ -14248,6 +14841,11 @@
           <t>+12 Agilité  ·  +25% déplacement  ·  Set: Blood Set</t>
         </is>
       </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>≈ 24 dégâts  (5 cartes/6 visées · 4 buff)</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="15" customHeight="1" s="100">
       <c r="A124" s="17" t="inlineStr">
@@ -14280,6 +14878,11 @@
           <t>+12 Agilité  ·  +25% déplacement  ·  Set: Crusader Set</t>
         </is>
       </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>≈ 24 dégâts  (5 cartes/6 visées · 3 buff)</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="15" customHeight="1" s="100">
       <c r="A125" s="17" t="inlineStr">
@@ -14312,6 +14915,11 @@
           <t>+10 Agilité  ·  +15% déplacement  ·  Set: Mail Set</t>
         </is>
       </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>aucun dégât/armure  (5 cartes/6 visées · 5 buff)</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="15" customHeight="1" s="100">
       <c r="A126" s="21" t="inlineStr">
@@ -14342,6 +14950,11 @@
       <c r="F126" s="22" t="inlineStr">
         <is>
           <t>+18 Agilité  ·  +50% déplacement  ·  Set: Onyx Set</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>≈ 17 dégâts  (6 cartes/7 visées · 5 buff)</t>
         </is>
       </c>
     </row>
@@ -14388,6 +15001,11 @@
           <t>+1 rangées de sac</t>
         </is>
       </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>aucun dégât/armure  (0 carte/5 visées)</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="15" customHeight="1" s="100">
       <c r="A129" s="15" t="inlineStr">
@@ -14420,6 +15038,11 @@
           <t>+2 rangées de sac</t>
         </is>
       </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>aucun dégât/armure  (0 carte/6 visées)</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="15" customHeight="1" s="100">
       <c r="A130" s="17" t="inlineStr">
@@ -14452,6 +15075,11 @@
           <t>+4 rangées de sac</t>
         </is>
       </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>aucun dégât/armure  (0 carte/6 visées)</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="15" customHeight="1" s="100">
       <c r="A131" s="17" t="inlineStr">
@@ -14484,6 +15112,11 @@
           <t>+3 rangées de sac</t>
         </is>
       </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>aucun dégât/armure  (0 carte/6 visées)</t>
+        </is>
+      </c>
     </row>
     <row r="132" ht="15" customHeight="1" s="100">
       <c r="A132" s="21" t="inlineStr">
@@ -14516,6 +15149,11 @@
           <t>+6 rangées de sac</t>
         </is>
       </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>aucun dégât/armure  (0 carte/7 visées)</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="15" customHeight="1" s="100">
       <c r="A133" s="49" t="inlineStr">
@@ -14546,6 +15184,11 @@
       <c r="F133" s="50" t="inlineStr">
         <is>
           <t>+10 rangées de sac</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>aucun dégât/armure  (0 carte/8 visées)</t>
         </is>
       </c>
     </row>
@@ -14615,6 +15258,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 

--- a/docs/BRUTAL-items-et-cartes.xlsx
+++ b/docs/BRUTAL-items-et-cartes.xlsx
@@ -3,8 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="480" yWindow="0" windowWidth="28320" windowHeight="18900" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-60780" yWindow="1230" windowWidth="28320" windowHeight="18900" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-60090" yWindow="1920" windowWidth="35040" windowHeight="18900" tabRatio="600" firstSheet="0" activeTab="10" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Lisez-moi" sheetId="1" state="visible" r:id="rId1"/>
@@ -28,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -132,6 +131,11 @@
       <i val="1"/>
       <color rgb="FF808080"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
@@ -477,7 +481,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -691,9 +695,13 @@
     <xf numFmtId="0" fontId="17" fillId="58" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="59" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="27" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1098,11 +1106,11 @@
   <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col width="100" customWidth="1" style="100" min="1" max="1"/>
-    <col width="18" customWidth="1" style="100" min="2" max="4"/>
+    <col width="100" customWidth="1" style="102" min="1" max="1"/>
+    <col width="18" customWidth="1" style="102" min="2" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" s="100">
+    <row r="1" ht="24" customHeight="1" s="102">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>BRUTAL — Catalogue des items &amp; cartes</t>
@@ -1119,7 +1127,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="45" customHeight="1" s="100">
+    <row r="4" ht="45" customHeight="1" s="102">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Lister proprement tout l'équipement actuel (onglet « Items »), rangé par type, avec les cartes que chaque pièce ajoute au deck et leur quantité. Sers-toi des lignes vides sous chaque type pour me proposer de nouvelles armes / armures.</t>
@@ -1136,14 +1144,14 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1" s="100">
+    <row r="7" ht="30" customHeight="1" s="102">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>1) Va dans l'onglet « Items », sous le bon type.  2) Remplis une ligne vide : Nom, Rareté, puis pour chaque carte son Nom et sa Quantité (colonnes Carte 1/Qté, Carte 2/Qté…).</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="45" customHeight="1" s="100">
+    <row r="8" ht="45" customHeight="1" s="102">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>3) Si une carte EXISTE déjà, prends son nom dans l'onglet « Cartes » (référence).  Si tu inventes une NOUVELLE carte, écris son nom dans une colonne Carte et décris son effet (dégâts, Pierre, Poison, coût en Chaleur…) dans la colonne « Notes ».</t>
@@ -1160,14 +1168,14 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1" s="100">
+    <row r="11" ht="60" customHeight="1" s="102">
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>La colonne « Effet hors-carte » (onglet Items) décrit ce qu'un objet apporte EN DEHORS de ses cartes : armure (Pierre) donnée en début de combat, rangées de sac, arme à deux mains, passif propre, appartenance à un set. Pour un nouvel objet, écris ici son effet hors-carte (ex. « Ajoute 12 d'armure en début de combat », « +4 rangées de sac »).</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1" s="100">
+    <row r="12" ht="30" customHeight="1" s="102">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Les SETS d'armure ont leur propre onglet « Sets » : un bonus s'active quand on porte TOUTES les pièces d'armure du set (l'arme ne compte pas). Propose un set sur une ligne vide.</t>
@@ -1184,7 +1192,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1" s="100">
+    <row r="15" ht="30" customHeight="1" s="102">
       <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Dans BRUTAL, tout le combat passe par les CARTES du deck — une arme/armure ne fait que fournir des cartes. C'est pourquoi ce tableau se concentre sur les cartes et leur quantité, pas sur un chiffre de dégâts.</t>
@@ -1201,7 +1209,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1" s="100">
+    <row r="18" ht="60" customHeight="1" s="102">
       <c r="A18" s="2" t="inlineStr">
         <is>
           <t>La couleur de rareté d'une carte = celle de l'objet LE MOINS rare qui la débloque (ex. « Strike » est Common car des armes communes la donnent). Calculée automatiquement à la génération — c'est PUREMENT indicatif pour s'y retrouver, cette rareté n'existe pas dans le jeu. « — » = carte du deck de base (donnée par aucun objet).</t>
@@ -1218,7 +1226,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="30" customHeight="1" s="100">
+    <row r="21" ht="30" customHeight="1" s="102">
       <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Les items et cartes récemment ajoutés (à relire/valider) sont surlignés en jaune dans les onglets « Items » et « Cartes ». Une fois que tu les as validés, dis-le moi et je retire le surlignage.</t>
@@ -1313,7 +1321,7 @@
         <v>5</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
@@ -1329,7 +1337,7 @@
         <v>8</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34">
@@ -1345,7 +1353,7 @@
         <v>12</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35">
@@ -1361,7 +1369,7 @@
         <v>17</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="36">
@@ -1377,10 +1385,10 @@
         <v>25</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="37" ht="30" customHeight="1" s="100">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1" s="102">
       <c r="A37" s="2" t="inlineStr">
         <is>
           <t>Armes à deux mains : ×1,5 sur dégât et armure/énergie (moins de cartes), souvent via des sorts chers en énergie.</t>
@@ -1401,11 +1409,11 @@
   <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" style="100" min="1" max="1"/>
-    <col width="12" customWidth="1" style="100" min="2" max="2"/>
+    <col width="14" customWidth="1" style="102" min="1" max="1"/>
+    <col width="12" customWidth="1" style="102" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25" customHeight="1" s="100">
+    <row r="1" ht="17.25" customHeight="1" s="102">
       <c r="A1" s="95" t="inlineStr">
         <is>
           <t>CHANCE DE RARETÉ par CHOIX de loot (en %) — doit sommer à 100</t>
@@ -1468,16 +1476,16 @@
   <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" style="100" min="1" max="1"/>
-    <col width="20" customWidth="1" style="100" min="2" max="2"/>
-    <col width="8" customWidth="1" style="100" min="3" max="3"/>
-    <col width="12" customWidth="1" style="100" min="4" max="4"/>
-    <col width="7" customWidth="1" style="100" min="5" max="5"/>
-    <col width="9" customWidth="1" style="100" min="6" max="6"/>
-    <col width="7" customWidth="1" style="100" min="7" max="7"/>
-    <col width="9" customWidth="1" style="100" min="8" max="8"/>
-    <col width="52" customWidth="1" style="100" min="9" max="9"/>
-    <col width="42" customWidth="1" style="100" min="10" max="10"/>
+    <col width="16" customWidth="1" style="102" min="1" max="1"/>
+    <col width="20" customWidth="1" style="102" min="2" max="2"/>
+    <col width="8" customWidth="1" style="102" min="3" max="3"/>
+    <col width="12" customWidth="1" style="102" min="4" max="4"/>
+    <col width="7" customWidth="1" style="102" min="5" max="5"/>
+    <col width="9" customWidth="1" style="102" min="6" max="6"/>
+    <col width="7" customWidth="1" style="102" min="7" max="7"/>
+    <col width="9" customWidth="1" style="102" min="8" max="8"/>
+    <col width="52" customWidth="1" style="102" min="9" max="9"/>
+    <col width="42" customWidth="1" style="102" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1607,13 +1615,13 @@
         <v>24</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G3" t="n">
         <v>6</v>
       </c>
       <c r="H3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -1638,14 +1646,21 @@
       <c r="E4" t="n">
         <v>16</v>
       </c>
-      <c r="F4" t="n">
-        <v>3</v>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2x2</t>
+        </is>
       </c>
       <c r="G4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H4" t="n">
-        <v>18</v>
+        <v>11</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>applique 1 poisson par attaque (2x attaque = 2 poisons)</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -1660,7 +1675,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1668,13 +1683,13 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H5" t="n">
         <v>7</v>
@@ -1705,16 +1720,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="F6" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="G6" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="H6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1734,9 +1749,9 @@
   <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" style="100" min="1" max="1"/>
-    <col width="9" customWidth="1" style="100" min="2" max="2"/>
-    <col width="54" customWidth="1" style="100" min="3" max="3"/>
+    <col width="18" customWidth="1" style="102" min="1" max="1"/>
+    <col width="9" customWidth="1" style="102" min="2" max="2"/>
+    <col width="54" customWidth="1" style="102" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1763,7 +1778,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1793,7 +1808,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1890,28 +1905,28 @@
   <dimension ref="A1:M171"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" style="100" min="1" max="1"/>
-    <col width="24" customWidth="1" style="100" min="2" max="2"/>
-    <col width="22" customWidth="1" style="100" min="3" max="3"/>
-    <col width="7" customWidth="1" style="100" min="4" max="4"/>
-    <col width="9" customWidth="1" style="100" min="5" max="5"/>
-    <col width="11" customWidth="1" style="100" min="6" max="6"/>
-    <col width="8" customWidth="1" style="100" min="7" max="7"/>
-    <col width="6" customWidth="1" style="100" min="8" max="8"/>
-    <col width="42" customWidth="1" style="100" min="9" max="9"/>
-    <col width="58" customWidth="1" style="100" min="10" max="10"/>
-    <col width="8" customWidth="1" style="100" min="11" max="11"/>
-    <col width="26" customWidth="1" style="100" min="12" max="12"/>
+    <col width="13" customWidth="1" style="102" min="1" max="1"/>
+    <col width="24" customWidth="1" style="102" min="2" max="2"/>
+    <col width="22" customWidth="1" style="102" min="3" max="3"/>
+    <col width="7" customWidth="1" style="102" min="4" max="4"/>
+    <col width="9" customWidth="1" style="102" min="5" max="5"/>
+    <col width="11" customWidth="1" style="102" min="6" max="6"/>
+    <col width="8" customWidth="1" style="102" min="7" max="7"/>
+    <col width="6" customWidth="1" style="102" min="8" max="8"/>
+    <col width="42" customWidth="1" style="102" min="9" max="9"/>
+    <col width="58" customWidth="1" style="102" min="10" max="10"/>
+    <col width="8" customWidth="1" style="102" min="11" max="11"/>
+    <col width="26" customWidth="1" style="102" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21.95" customHeight="1" s="100">
-      <c r="A1" s="99" t="inlineStr">
+    <row r="1" ht="21.95" customHeight="1" s="102">
+      <c r="A1" s="101" t="inlineStr">
         <is>
           <t xml:space="preserve">  Lignes turquoise = ajouts récents à relire (4 armes 2 mains + leurs cartes).</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="17.1" customHeight="1" s="100">
+    <row r="2" ht="17.1" customHeight="1" s="102">
       <c r="A2" s="10" t="inlineStr">
         <is>
           <t>Famille</t>
@@ -1967,13 +1982,13 @@
           <t>Visuel</t>
         </is>
       </c>
-      <c r="L2" s="101" t="inlineStr">
+      <c r="L2" s="103" t="inlineStr">
         <is>
           <t>Cible (barème)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="100">
+    <row r="3" ht="15" customHeight="1" s="102">
       <c r="A3" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  ▸ DÉGÂTS</t>
@@ -1990,7 +2005,7 @@
       <c r="J3" s="12" t="n"/>
       <c r="K3" s="11" t="n"/>
     </row>
-    <row r="4" ht="15" customHeight="1" s="100">
+    <row r="4" ht="15" customHeight="1" s="102">
       <c r="A4" s="13" t="inlineStr">
         <is>
           <t>Dégâts</t>
@@ -2032,7 +2047,7 @@
       </c>
       <c r="J4" s="14" t="inlineStr">
         <is>
-          <t>Deal 3 damage.</t>
+          <t>Deal 2 damage.</t>
         </is>
       </c>
       <c r="K4" s="57" t="inlineStr">
@@ -2046,7 +2061,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="100">
+    <row r="5" ht="15" customHeight="1" s="102">
       <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Dégâts</t>
@@ -2088,7 +2103,7 @@
       </c>
       <c r="J5" s="14" t="inlineStr">
         <is>
-          <t>Deal 4 damage twice.</t>
+          <t>Deal 3 damage twice.</t>
         </is>
       </c>
       <c r="K5" s="57" t="inlineStr">
@@ -2102,7 +2117,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="100">
+    <row r="6" ht="15" customHeight="1" s="102">
       <c r="A6" s="13" t="inlineStr">
         <is>
           <t>Dégâts</t>
@@ -2158,7 +2173,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="100">
+    <row r="7" ht="15" customHeight="1" s="102">
       <c r="A7" s="13" t="inlineStr">
         <is>
           <t>Dégâts</t>
@@ -2214,7 +2229,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="100">
+    <row r="8" ht="15" customHeight="1" s="102">
       <c r="A8" s="13" t="inlineStr">
         <is>
           <t>Dégâts</t>
@@ -2256,7 +2271,7 @@
       </c>
       <c r="J8" s="14" t="inlineStr">
         <is>
-          <t>Deal 7 damage to the target and the enemy behind it.</t>
+          <t>Deal 6 damage to the target and the enemy behind it.</t>
         </is>
       </c>
       <c r="K8" s="57" t="inlineStr">
@@ -2270,7 +2285,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="100">
+    <row r="9" ht="15" customHeight="1" s="102">
       <c r="A9" s="13" t="inlineStr">
         <is>
           <t>Dégâts</t>
@@ -2326,7 +2341,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="100">
+    <row r="10" ht="15" customHeight="1" s="102">
       <c r="A10" s="13" t="inlineStr">
         <is>
           <t>Dégâts</t>
@@ -2368,7 +2383,7 @@
       </c>
       <c r="J10" s="14" t="inlineStr">
         <is>
-          <t>Deal 8 damage.</t>
+          <t>Deal 7 damage.</t>
         </is>
       </c>
       <c r="K10" s="57" t="inlineStr">
@@ -2382,7 +2397,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="100">
+    <row r="11" ht="15" customHeight="1" s="102">
       <c r="A11" s="13" t="inlineStr">
         <is>
           <t>Dégâts</t>
@@ -2438,7 +2453,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="100">
+    <row r="12" ht="15" customHeight="1" s="102">
       <c r="A12" s="13" t="inlineStr">
         <is>
           <t>Dégâts</t>
@@ -2480,7 +2495,7 @@
       </c>
       <c r="J12" s="14" t="inlineStr">
         <is>
-          <t>Deal 6 damage.</t>
+          <t>Deal 5 damage.</t>
         </is>
       </c>
       <c r="K12" s="57" t="inlineStr">
@@ -2494,7 +2509,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="100">
+    <row r="13" ht="15" customHeight="1" s="102">
       <c r="A13" s="15" t="inlineStr">
         <is>
           <t>Dégâts</t>
@@ -2550,7 +2565,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="100">
+    <row r="14" ht="15" customHeight="1" s="102">
       <c r="A14" s="15" t="inlineStr">
         <is>
           <t>Dégâts</t>
@@ -2592,7 +2607,7 @@
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>Deal 9 damage.</t>
+          <t>Deal 8 damage.</t>
         </is>
       </c>
       <c r="K14" s="57" t="inlineStr">
@@ -2606,7 +2621,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="100">
+    <row r="15" ht="15" customHeight="1" s="102">
       <c r="A15" s="15" t="inlineStr">
         <is>
           <t>Dégâts</t>
@@ -2662,7 +2677,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="100">
+    <row r="16" ht="15" customHeight="1" s="102">
       <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Dégâts</t>
@@ -2704,7 +2719,7 @@
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>Deal 10 damage. Doubled if the target is below 50% HP.</t>
+          <t>Deal 12 damage. Doubled if the target is below 50% HP.</t>
         </is>
       </c>
       <c r="K16" s="57" t="inlineStr">
@@ -2718,7 +2733,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="100">
+    <row r="17" ht="15" customHeight="1" s="102">
       <c r="A17" s="15" t="inlineStr">
         <is>
           <t>Dégâts</t>
@@ -2774,7 +2789,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="100">
+    <row r="18" ht="15" customHeight="1" s="102">
       <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Dégâts</t>
@@ -2816,7 +2831,7 @@
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>Deal 12 damage to the target and the enemy behind it.</t>
+          <t>Deal 10 damage to the target and the enemy behind it.</t>
         </is>
       </c>
       <c r="K18" s="57" t="inlineStr">
@@ -2830,7 +2845,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="100">
+    <row r="19" ht="15" customHeight="1" s="102">
       <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Dégâts</t>
@@ -2886,7 +2901,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="100">
+    <row r="20" ht="15" customHeight="1" s="102">
       <c r="A20" s="15" t="inlineStr">
         <is>
           <t>Dégâts</t>
@@ -2928,7 +2943,7 @@
       </c>
       <c r="J20" s="15" t="inlineStr">
         <is>
-          <t>Deal 5 damage three times.</t>
+          <t>Deal 4 damage three times.</t>
         </is>
       </c>
       <c r="K20" s="57" t="inlineStr">
@@ -2942,7 +2957,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="100">
+    <row r="21" ht="15" customHeight="1" s="102">
       <c r="A21" s="15" t="inlineStr">
         <is>
           <t>Dégâts</t>
@@ -2959,7 +2974,7 @@
         </is>
       </c>
       <c r="D21" s="15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21" s="15" t="inlineStr">
         <is>
@@ -2984,7 +2999,7 @@
       </c>
       <c r="J21" s="15" t="inlineStr">
         <is>
-          <t>Deal 14 damage to the target and 6 to each adjacent enemy.</t>
+          <t>Deal 16 damage to the target and 10 to each adjacent enemy.</t>
         </is>
       </c>
       <c r="K21" s="57" t="inlineStr">
@@ -2994,11 +3009,11 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>≈ 12 dégâts  (1×8×1,5)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1" s="100">
+          <t>≈ 24 dégâts  (2×8×1,5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1" s="102">
       <c r="A22" s="15" t="inlineStr">
         <is>
           <t>Dégâts</t>
@@ -3058,7 +3073,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" s="100">
+    <row r="23" ht="15" customHeight="1" s="102">
       <c r="A23" s="17" t="inlineStr">
         <is>
           <t>Dégâts</t>
@@ -3100,7 +3115,7 @@
       </c>
       <c r="J23" s="18" t="inlineStr">
         <is>
-          <t>Deal 30 damage. If the target dies, deal 15 damage to the next enemy.</t>
+          <t>Deal 50 damage. If the target dies, deal 24 damage to the next enemy.</t>
         </is>
       </c>
       <c r="K23" s="57" t="inlineStr">
@@ -3114,7 +3129,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" s="100">
+    <row r="24" ht="15" customHeight="1" s="102">
       <c r="A24" s="17" t="inlineStr">
         <is>
           <t>Dégâts</t>
@@ -3170,7 +3185,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="17.1" customHeight="1" s="100">
+    <row r="25" ht="17.1" customHeight="1" s="102">
       <c r="A25" s="21" t="inlineStr">
         <is>
           <t>Dégâts</t>
@@ -3212,7 +3227,7 @@
       </c>
       <c r="J25" s="21" t="inlineStr">
         <is>
-          <t>Deal 30 damage. Doubled if the target is below 50% HP.</t>
+          <t>Deal 42 damage. Doubled if the target is below 50% HP.</t>
         </is>
       </c>
       <c r="K25" s="57" t="inlineStr">
@@ -3226,7 +3241,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" s="100">
+    <row r="26" ht="15" customHeight="1" s="102">
       <c r="A26" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  ▸ FEU</t>
@@ -3243,7 +3258,7 @@
       <c r="J26" s="20" t="n"/>
       <c r="K26" s="19" t="n"/>
     </row>
-    <row r="27" ht="15" customHeight="1" s="100">
+    <row r="27" ht="15" customHeight="1" s="102">
       <c r="A27" s="13" t="inlineStr">
         <is>
           <t>Feu</t>
@@ -3285,7 +3300,7 @@
       </c>
       <c r="J27" s="14" t="inlineStr">
         <is>
-          <t>Deal 4 damage. Apply 2 Burning.</t>
+          <t>Deal 3 damage. Apply 2 Burning.</t>
         </is>
       </c>
       <c r="K27" s="57" t="inlineStr">
@@ -3299,7 +3314,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" s="100">
+    <row r="28" ht="15" customHeight="1" s="102">
       <c r="A28" s="13" t="inlineStr">
         <is>
           <t>Feu</t>
@@ -3355,7 +3370,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" s="100">
+    <row r="29" ht="15" customHeight="1" s="102">
       <c r="A29" s="15" t="inlineStr">
         <is>
           <t>Feu</t>
@@ -3401,7 +3416,7 @@
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
-          <t>Deal 5 damage and apply 3 Burning to ALL enemies.</t>
+          <t>Deal 8 damage and apply 3 Burning to ALL enemies.</t>
         </is>
       </c>
       <c r="K29" s="57" t="inlineStr">
@@ -3415,7 +3430,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1" s="100">
+    <row r="30" ht="15" customHeight="1" s="102">
       <c r="A30" s="15" t="inlineStr">
         <is>
           <t>Feu</t>
@@ -3471,7 +3486,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1" s="100">
+    <row r="31" ht="15" customHeight="1" s="102">
       <c r="A31" s="15" t="inlineStr">
         <is>
           <t>Feu</t>
@@ -3513,7 +3528,7 @@
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
-          <t>Deal 15 damage. Each adjacent enemy has a 50% chance to take 5 Burning.</t>
+          <t>Deal 18 damage. Each adjacent enemy and the target has a 50% chance to take 4 Burning.</t>
         </is>
       </c>
       <c r="K31" s="57" t="inlineStr">
@@ -3527,7 +3542,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1" s="100">
+    <row r="32" ht="15" customHeight="1" s="102">
       <c r="A32" s="21" t="inlineStr">
         <is>
           <t>Feu</t>
@@ -3587,7 +3602,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1" s="100">
+    <row r="33" ht="15" customHeight="1" s="102">
       <c r="A33" s="21" t="inlineStr">
         <is>
           <t>Feu</t>
@@ -3647,7 +3662,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1" s="100">
+    <row r="34" ht="15" customHeight="1" s="102">
       <c r="A34" s="21" t="inlineStr">
         <is>
           <t>Feu</t>
@@ -3703,7 +3718,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1" s="100">
+    <row r="35" ht="15" customHeight="1" s="102">
       <c r="A35" s="21" t="inlineStr">
         <is>
           <t>Feu</t>
@@ -3745,7 +3760,7 @@
       </c>
       <c r="J35" s="22" t="inlineStr">
         <is>
-          <t>Haste for as many turns as your current Forge Heat.</t>
+          <t>gain 3 Haste for as many as your current Forge Heat.</t>
         </is>
       </c>
       <c r="K35" s="57" t="inlineStr">
@@ -3759,7 +3774,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1" s="100">
+    <row r="36" ht="15" customHeight="1" s="102">
       <c r="A36" s="21" t="inlineStr">
         <is>
           <t>Feu</t>
@@ -3805,7 +3820,7 @@
       </c>
       <c r="J36" s="22" t="inlineStr">
         <is>
-          <t>Detonate all Burning: deal 2 damage per Burning on ALL enemies.</t>
+          <t>Detonate all Burning: deal 5 damage per Burning on ALL enemies.</t>
         </is>
       </c>
       <c r="K36" s="57" t="inlineStr">
@@ -3819,7 +3834,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="15" customHeight="1" s="100">
+    <row r="37" ht="15" customHeight="1" s="102">
       <c r="A37" s="21" t="inlineStr">
         <is>
           <t>Feu</t>
@@ -3861,7 +3876,7 @@
       </c>
       <c r="J37" s="22" t="inlineStr">
         <is>
-          <t>Convert 4 of your own Burning into 2 Forge Heat. No effect below 4 Burning.</t>
+          <t>Convertis jusque 5 effet de brulure sur soit en 3 point d'energie.</t>
         </is>
       </c>
       <c r="K37" s="57" t="inlineStr">
@@ -3875,7 +3890,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="15" customHeight="1" s="100">
+    <row r="38" ht="15" customHeight="1" s="102">
       <c r="A38" s="21" t="inlineStr">
         <is>
           <t>Feu</t>
@@ -3917,7 +3932,7 @@
       </c>
       <c r="J38" s="22" t="inlineStr">
         <is>
-          <t>Deal 12 damage. Apply 3 Burning.</t>
+          <t>Deal 15 damage. Apply 4 Burning.</t>
         </is>
       </c>
       <c r="K38" s="57" t="inlineStr">
@@ -3931,7 +3946,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="15" customHeight="1" s="100">
+    <row r="39" ht="15" customHeight="1" s="102">
       <c r="A39" s="21" t="inlineStr">
         <is>
           <t>Feu</t>
@@ -3948,7 +3963,7 @@
         </is>
       </c>
       <c r="D39" s="21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E39" s="21" t="inlineStr">
         <is>
@@ -3983,11 +3998,11 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>≈ 17 dégâts  (1×17)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="15" customHeight="1" s="100">
+          <t>gratuite (0 énergie) — hors barème</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1" s="102">
       <c r="A40" s="21" t="inlineStr">
         <is>
           <t>Feu</t>
@@ -4033,7 +4048,7 @@
       </c>
       <c r="J40" s="22" t="inlineStr">
         <is>
-          <t>Spend all Forge Heat. Apply 8 Burning per Heat spent to ALL enemies.</t>
+          <t>Spend all Forge Heat. Apply 7 Burning per Heat spent to ALL enemies.</t>
         </is>
       </c>
       <c r="K40" s="57" t="inlineStr">
@@ -4047,7 +4062,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="15" customHeight="1" s="100">
+    <row r="41" ht="15" customHeight="1" s="102">
       <c r="A41" s="21" t="inlineStr">
         <is>
           <t>Feu</t>
@@ -4089,7 +4104,7 @@
       </c>
       <c r="J41" s="22" t="inlineStr">
         <is>
-          <t>Deal 28 damage. Apply 4 Burning.</t>
+          <t>Deal 30 damage. Apply 6 Burning.</t>
         </is>
       </c>
       <c r="K41" s="57" t="inlineStr">
@@ -4103,7 +4118,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="15" customHeight="1" s="100">
+    <row r="42" ht="15" customHeight="1" s="102">
       <c r="A42" s="21" t="inlineStr">
         <is>
           <t>Feu</t>
@@ -4163,7 +4178,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="15" customHeight="1" s="100">
+    <row r="43" ht="15" customHeight="1" s="102">
       <c r="A43" s="21" t="inlineStr">
         <is>
           <t>Feu</t>
@@ -4219,7 +4234,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="15" customHeight="1" s="100">
+    <row r="44" ht="15" customHeight="1" s="102">
       <c r="A44" s="21" t="inlineStr">
         <is>
           <t>Feu</t>
@@ -4265,7 +4280,7 @@
       </c>
       <c r="J44" s="22" t="inlineStr">
         <is>
-          <t>Apply 8 Burning to ALL enemies.</t>
+          <t>Apply 10 Burning to ALL enemies.</t>
         </is>
       </c>
       <c r="K44" s="57" t="inlineStr">
@@ -4279,7 +4294,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="17.1" customHeight="1" s="100">
+    <row r="45" ht="17.1" customHeight="1" s="102">
       <c r="A45" s="21" t="inlineStr">
         <is>
           <t>Feu</t>
@@ -4321,7 +4336,7 @@
       </c>
       <c r="J45" s="22" t="inlineStr">
         <is>
-          <t>Deal 26 damage and 4 Burning. The enemy behind takes half (13 damage, 2 Burning).</t>
+          <t>Deal 40 damage and 6 Burning. The enemy behind takes half (13 damage, 2 Burning).</t>
         </is>
       </c>
       <c r="K45" s="57" t="inlineStr">
@@ -4335,7 +4350,7 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="15" customHeight="1" s="100">
+    <row r="46" ht="15" customHeight="1" s="102">
       <c r="A46" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  ▸ POISON</t>
@@ -4352,7 +4367,7 @@
       <c r="J46" s="24" t="n"/>
       <c r="K46" s="23" t="n"/>
     </row>
-    <row r="47" ht="15" customHeight="1" s="100">
+    <row r="47" ht="15" customHeight="1" s="102">
       <c r="A47" s="13" t="inlineStr">
         <is>
           <t>Poison</t>
@@ -4412,7 +4427,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="15" customHeight="1" s="100">
+    <row r="48" ht="15" customHeight="1" s="102">
       <c r="A48" s="13" t="inlineStr">
         <is>
           <t>Poison</t>
@@ -4454,7 +4469,7 @@
       </c>
       <c r="J48" s="14" t="inlineStr">
         <is>
-          <t>Deal 3 damage. Apply 4 Poison.</t>
+          <t>Deal 3 damage. Apply 3 Poison.</t>
         </is>
       </c>
       <c r="K48" s="57" t="inlineStr">
@@ -4468,7 +4483,7 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="15" customHeight="1" s="100">
+    <row r="49" ht="15" customHeight="1" s="102">
       <c r="A49" s="15" t="inlineStr">
         <is>
           <t>Poison</t>
@@ -4514,7 +4529,7 @@
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>Apply 6 Poison to ALL enemies.</t>
+          <t>Apply 7 Poison to ALL enemies.</t>
         </is>
       </c>
       <c r="K49" s="57" t="inlineStr">
@@ -4528,7 +4543,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="15" customHeight="1" s="100">
+    <row r="50" ht="15" customHeight="1" s="102">
       <c r="A50" s="15" t="inlineStr">
         <is>
           <t>Poison</t>
@@ -4584,7 +4599,7 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="15" customHeight="1" s="100">
+    <row r="51" ht="15" customHeight="1" s="102">
       <c r="A51" s="17" t="inlineStr">
         <is>
           <t>Poison</t>
@@ -4630,7 +4645,7 @@
       </c>
       <c r="J51" s="18" t="inlineStr">
         <is>
-          <t>Hit ALL enemies 3 times for 3 damage. Apply 1 Poison per hit (2 if the enemy was already poisoned).</t>
+          <t>Hit ALL enemies 3 times for 6 damage. Apply 2 Poison per hit (4 if the enemy was already poisoned).</t>
         </is>
       </c>
       <c r="K51" s="57" t="inlineStr">
@@ -4644,7 +4659,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="15" customHeight="1" s="100">
+    <row r="52" ht="15" customHeight="1" s="102">
       <c r="A52" s="17" t="inlineStr">
         <is>
           <t>Poison</t>
@@ -4686,7 +4701,7 @@
       </c>
       <c r="J52" s="18" t="inlineStr">
         <is>
-          <t>Inflige autant de degat physique que de dose de poison active sur la cible et au ennemi adjacent a la cible. Ajoute 2 poison aux cibles touché par cette carte.</t>
+          <t>Inflige autant de degat physique que de dose de poison active sur la cible et au ennemi adjacent a la cible. Ajoute 5 poison aux cibles touché par cette carte.</t>
         </is>
       </c>
       <c r="K52" s="57" t="inlineStr">
@@ -4700,7 +4715,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="17.1" customHeight="1" s="100">
+    <row r="53" ht="17.1" customHeight="1" s="102">
       <c r="A53" s="17" t="inlineStr">
         <is>
           <t>Poison</t>
@@ -4742,7 +4757,7 @@
       </c>
       <c r="J53" s="18" t="inlineStr">
         <is>
-          <t>Deal 6 damage. Apply 4 Poison.</t>
+          <t>Deal 10 damage. Apply 5 Poison.</t>
         </is>
       </c>
       <c r="K53" s="57" t="inlineStr">
@@ -4756,7 +4771,7 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="15" customHeight="1" s="100">
+    <row r="54" ht="15" customHeight="1" s="102">
       <c r="A54" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  ▸ SAIGNEMENT</t>
@@ -4773,7 +4788,7 @@
       <c r="J54" s="26" t="n"/>
       <c r="K54" s="25" t="n"/>
     </row>
-    <row r="55" ht="15" customHeight="1" s="100">
+    <row r="55" ht="15" customHeight="1" s="102">
       <c r="A55" s="13" t="inlineStr">
         <is>
           <t>Saignement</t>
@@ -4815,7 +4830,7 @@
       </c>
       <c r="J55" s="14" t="inlineStr">
         <is>
-          <t>Deal 5 damage. Apply 2 Bleed.</t>
+          <t>Deal 4 damage. Apply 2 Bleed.</t>
         </is>
       </c>
       <c r="K55" s="57" t="inlineStr">
@@ -4829,7 +4844,7 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="15" customHeight="1" s="100">
+    <row r="56" ht="15" customHeight="1" s="102">
       <c r="A56" s="15" t="inlineStr">
         <is>
           <t>Saignement</t>
@@ -4871,7 +4886,7 @@
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
-          <t>Deal 3 damage. Apply 3 Bleed (stacks don't reset).</t>
+          <t>Deal 6 damage. Apply 3 Bleed.</t>
         </is>
       </c>
       <c r="K56" s="57" t="inlineStr">
@@ -4885,7 +4900,7 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="15" customHeight="1" s="100">
+    <row r="57" ht="15" customHeight="1" s="102">
       <c r="A57" s="15" t="inlineStr">
         <is>
           <t>Saignement</t>
@@ -4927,7 +4942,7 @@
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>Deal 5 damage, apply 3 Bleed, and heal 3 HP.</t>
+          <t>Deal 3 damage, apply 3 Bleed, and heal d'autant que la cible a de bleed actif.</t>
         </is>
       </c>
       <c r="K57" s="57" t="inlineStr">
@@ -4941,7 +4956,7 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="15" customHeight="1" s="100">
+    <row r="58" ht="15" customHeight="1" s="102">
       <c r="A58" s="15" t="inlineStr">
         <is>
           <t>Saignement</t>
@@ -4997,7 +5012,7 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="15" customHeight="1" s="100">
+    <row r="59" ht="15" customHeight="1" s="102">
       <c r="A59" s="15" t="inlineStr">
         <is>
           <t>Saignement</t>
@@ -5039,7 +5054,7 @@
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
-          <t>Deal 15 damage. Apply 4 bleed.</t>
+          <t>Deal 22 damage. Apply 5 bleed.</t>
         </is>
       </c>
       <c r="K59" s="57" t="inlineStr">
@@ -5053,7 +5068,7 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="15" customHeight="1" s="100">
+    <row r="60" ht="15" customHeight="1" s="102">
       <c r="A60" s="15" t="inlineStr">
         <is>
           <t>Saignement</t>
@@ -5099,7 +5114,7 @@
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
-          <t>Deal 6 damage and apply 2 Bleed to ALL enemies.</t>
+          <t>Deal 7 damage and apply 3 Bleed to ALL enemies.</t>
         </is>
       </c>
       <c r="K60" s="57" t="inlineStr">
@@ -5113,7 +5128,7 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="15" customHeight="1" s="100">
+    <row r="61" ht="15" customHeight="1" s="102">
       <c r="A61" s="17" t="inlineStr">
         <is>
           <t>Saignement</t>
@@ -5169,7 +5184,7 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="15" customHeight="1" s="100">
+    <row r="62" ht="15" customHeight="1" s="102">
       <c r="A62" s="17" t="inlineStr">
         <is>
           <t>Saignement</t>
@@ -5225,7 +5240,7 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="15" customHeight="1" s="100">
+    <row r="63" ht="15" customHeight="1" s="102">
       <c r="A63" s="17" t="inlineStr">
         <is>
           <t>Saignement</t>
@@ -5285,7 +5300,7 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="15" customHeight="1" s="100">
+    <row r="64" ht="15" customHeight="1" s="102">
       <c r="A64" s="17" t="inlineStr">
         <is>
           <t>Saignement</t>
@@ -5331,7 +5346,7 @@
       </c>
       <c r="J64" s="18" t="inlineStr">
         <is>
-          <t>Take 10 damage. Apply 5 Bleed to ALL enemies.</t>
+          <t>Take 20 damage. Apply 10 Bleed to ALL enemies.</t>
         </is>
       </c>
       <c r="K64" s="57" t="inlineStr">
@@ -5345,7 +5360,7 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="15" customHeight="1" s="100">
+    <row r="65" ht="15" customHeight="1" s="102">
       <c r="A65" s="17" t="inlineStr">
         <is>
           <t>Saignement</t>
@@ -5401,7 +5416,7 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="15" customHeight="1" s="100">
+    <row r="66" ht="15" customHeight="1" s="102">
       <c r="A66" s="17" t="inlineStr">
         <is>
           <t>Saignement</t>
@@ -5447,7 +5462,7 @@
       </c>
       <c r="J66" s="18" t="inlineStr">
         <is>
-          <t>Lose 20 HP. Deal 10 damage and 1 Bleed to ALL enemies. Heal 20 HP per enemy killed by this.</t>
+          <t>Lose 20 HP. Deal 16 damage and 3 Bleed to ALL enemies. Heal 20 HP per enemy killed by this.</t>
         </is>
       </c>
       <c r="K66" s="57" t="inlineStr">
@@ -5461,7 +5476,7 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1" s="100">
+    <row r="67" ht="15" customHeight="1" s="102">
       <c r="A67" s="17" t="inlineStr">
         <is>
           <t>Saignement</t>
@@ -5507,7 +5522,7 @@
       </c>
       <c r="J67" s="18" t="inlineStr">
         <is>
-          <t>Deal 16 damage to ALL enemies. Apply 2 Bleed to ALL enemies.</t>
+          <t>Deal 24 damage to ALL enemies. Apply 4 Bleed to ALL enemies.</t>
         </is>
       </c>
       <c r="K67" s="57" t="inlineStr">
@@ -5521,7 +5536,7 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="15" customHeight="1" s="100">
+    <row r="68" ht="15" customHeight="1" s="102">
       <c r="A68" s="17" t="inlineStr">
         <is>
           <t>Saignement</t>
@@ -5563,7 +5578,7 @@
       </c>
       <c r="J68" s="18" t="inlineStr">
         <is>
-          <t>Take 10 damage. Apply 4 Bleed on an ennemi target.</t>
+          <t>Take 10 damage. Apply 10 Bleed on an ennemi target.</t>
         </is>
       </c>
       <c r="K68" s="57" t="inlineStr">
@@ -5577,7 +5592,7 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="15" customHeight="1" s="100">
+    <row r="69" ht="15" customHeight="1" s="102">
       <c r="A69" s="17" t="inlineStr">
         <is>
           <t>Saignement</t>
@@ -5619,7 +5634,7 @@
       </c>
       <c r="J69" s="18" t="inlineStr">
         <is>
-          <t>Per Bleed among ALL enemies: gain 3 Stone and heal 2 HP.</t>
+          <t>Per Bleed among ALL enemies: gain 2 Stone and heal 5 HP.</t>
         </is>
       </c>
       <c r="K69" s="57" t="inlineStr">
@@ -5629,11 +5644,11 @@
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>≈ 8 armure  (1×8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="15" customHeight="1" s="100">
+          <t>≈ 9 armure  (1×9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="15" customHeight="1" s="102">
       <c r="A70" s="21" t="inlineStr">
         <is>
           <t>Saignement</t>
@@ -5675,7 +5690,7 @@
       </c>
       <c r="J70" s="21" t="inlineStr">
         <is>
-          <t>Deal 14 damage. Apply 3 Bleed.</t>
+          <t>Deal 20 damage. Apply 8 Bleed.</t>
         </is>
       </c>
       <c r="K70" s="57" t="inlineStr">
@@ -5689,7 +5704,7 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="17.1" customHeight="1" s="100">
+    <row r="71" ht="17.1" customHeight="1" s="102">
       <c r="A71" s="21" t="inlineStr">
         <is>
           <t>Saignement</t>
@@ -5735,7 +5750,7 @@
       </c>
       <c r="J71" s="21" t="inlineStr">
         <is>
-          <t>Deal 20 damage and apply 3 Bleed to ALL enemies.</t>
+          <t>Deal 35 damage and apply 5 Bleed to ALL enemies.</t>
         </is>
       </c>
       <c r="K71" s="57" t="inlineStr">
@@ -5749,7 +5764,7 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="15" customHeight="1" s="100">
+    <row r="72" ht="15" customHeight="1" s="102">
       <c r="A72" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  ▸ GEL</t>
@@ -5766,7 +5781,7 @@
       <c r="J72" s="28" t="n"/>
       <c r="K72" s="27" t="n"/>
     </row>
-    <row r="73" ht="15" customHeight="1" s="100">
+    <row r="73" ht="15" customHeight="1" s="102">
       <c r="A73" s="13" t="inlineStr">
         <is>
           <t>Gel</t>
@@ -5808,7 +5823,7 @@
       </c>
       <c r="J73" s="14" t="inlineStr">
         <is>
-          <t>Deal 5 damage. Chill: -30% speed for 2 turns.</t>
+          <t>Deal 4 damage. Apply 2 chill</t>
         </is>
       </c>
       <c r="K73" s="57" t="inlineStr">
@@ -5822,7 +5837,7 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="15" customHeight="1" s="100">
+    <row r="74" ht="15" customHeight="1" s="102">
       <c r="A74" s="15" t="inlineStr">
         <is>
           <t>Gel</t>
@@ -5868,7 +5883,7 @@
       </c>
       <c r="J74" s="16" t="inlineStr">
         <is>
-          <t>Chill ALL enemies (-30% speed for 3 turns).</t>
+          <t>Apply 3 chill on all ennemy</t>
         </is>
       </c>
       <c r="K74" s="57" t="inlineStr">
@@ -5882,7 +5897,7 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="15" customHeight="1" s="100">
+    <row r="75" ht="15" customHeight="1" s="102">
       <c r="A75" s="15" t="inlineStr">
         <is>
           <t>Gel</t>
@@ -5924,7 +5939,7 @@
       </c>
       <c r="J75" s="16" t="inlineStr">
         <is>
-          <t>Deal 5 damage. Chill: -30% speed for 3 turns.</t>
+          <t>Deal 6 damage. Apply 4 chill</t>
         </is>
       </c>
       <c r="K75" s="57" t="inlineStr">
@@ -5938,7 +5953,7 @@
         </is>
       </c>
     </row>
-    <row r="76" ht="15" customHeight="1" s="100">
+    <row r="76" ht="15" customHeight="1" s="102">
       <c r="A76" s="16" t="inlineStr">
         <is>
           <t>Gel</t>
@@ -5980,7 +5995,7 @@
       </c>
       <c r="J76" s="16" t="inlineStr">
         <is>
-          <t>Deal 10 damage. Chill: -30% speed for 2 turns.</t>
+          <t>Deal 11 damage. Apply 3 chill</t>
         </is>
       </c>
       <c r="K76" s="57" t="inlineStr">
@@ -5994,7 +6009,7 @@
         </is>
       </c>
     </row>
-    <row r="77" ht="15" customHeight="1" s="100">
+    <row r="77" ht="15" customHeight="1" s="102">
       <c r="A77" s="15" t="inlineStr">
         <is>
           <t>Gel</t>
@@ -6036,7 +6051,7 @@
       </c>
       <c r="J77" s="16" t="inlineStr">
         <is>
-          <t>Deal 8 damage, +5 more if the target is Chilled.</t>
+          <t>Deal 12 damage, +8 more if the target is Chilled.</t>
         </is>
       </c>
       <c r="K77" s="57" t="inlineStr">
@@ -6050,7 +6065,7 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="17.1" customHeight="1" s="100">
+    <row r="78" ht="17.1" customHeight="1" s="102">
       <c r="A78" s="17" t="inlineStr">
         <is>
           <t>Gel</t>
@@ -6092,7 +6107,7 @@
       </c>
       <c r="J78" s="18" t="inlineStr">
         <is>
-          <t>Deal 8 damage and apply 3 Chill. If the target was already chilled, cascade the same hit to the next enemy, and so on.</t>
+          <t>Deal 16 damage and apply 7 Chill. If the target was already chilled, cascade the same hit to the next enemy, and so on.</t>
         </is>
       </c>
       <c r="K78" s="57" t="inlineStr">
@@ -6106,7 +6121,7 @@
         </is>
       </c>
     </row>
-    <row r="79" ht="15" customHeight="1" s="100">
+    <row r="79" ht="15" customHeight="1" s="102">
       <c r="A79" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  ▸ CONTRÔLE</t>
@@ -6123,7 +6138,7 @@
       <c r="J79" s="30" t="n"/>
       <c r="K79" s="29" t="n"/>
     </row>
-    <row r="80" ht="15" customHeight="1" s="100">
+    <row r="80" ht="15" customHeight="1" s="102">
       <c r="A80" s="13" t="inlineStr">
         <is>
           <t>Contrôle</t>
@@ -6165,7 +6180,7 @@
       </c>
       <c r="J80" s="14" t="inlineStr">
         <is>
-          <t>Deal 14 damage. Apply 2 Confusion.</t>
+          <t>Deal 8 damage. Apply 1 Confusion.</t>
         </is>
       </c>
       <c r="K80" s="57" t="inlineStr">
@@ -6179,7 +6194,7 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="15" customHeight="1" s="100">
+    <row r="81" ht="15" customHeight="1" s="102">
       <c r="A81" s="13" t="inlineStr">
         <is>
           <t>Contrôle</t>
@@ -6235,7 +6250,7 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="15" customHeight="1" s="100">
+    <row r="82" ht="15" customHeight="1" s="102">
       <c r="A82" s="15" t="inlineStr">
         <is>
           <t>Contrôle</t>
@@ -6291,7 +6306,7 @@
         </is>
       </c>
     </row>
-    <row r="83" ht="15" customHeight="1" s="100">
+    <row r="83" ht="15" customHeight="1" s="102">
       <c r="A83" s="17" t="inlineStr">
         <is>
           <t>Contrôle</t>
@@ -6333,7 +6348,7 @@
       </c>
       <c r="J83" s="18" t="inlineStr">
         <is>
-          <t>Gain 6 Stone. Apply 2 confusion to the nearest enemy.</t>
+          <t>Gain 6 Stone. Apply 1 confusion to the nearest enemy.</t>
         </is>
       </c>
       <c r="K83" s="57" t="inlineStr">
@@ -6343,11 +6358,11 @@
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>≈ 8 armure  (1×8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="15" customHeight="1" s="100">
+          <t>≈ 9 armure  (1×9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="15" customHeight="1" s="102">
       <c r="A84" s="17" t="inlineStr">
         <is>
           <t>Contrôle</t>
@@ -6407,7 +6422,7 @@
         </is>
       </c>
     </row>
-    <row r="85" ht="15" customHeight="1" s="100">
+    <row r="85" ht="15" customHeight="1" s="102">
       <c r="A85" s="17" t="inlineStr">
         <is>
           <t>Contrôle</t>
@@ -6467,7 +6482,7 @@
         </is>
       </c>
     </row>
-    <row r="86" ht="15" customHeight="1" s="100">
+    <row r="86" ht="15" customHeight="1" s="102">
       <c r="A86" s="17" t="inlineStr">
         <is>
           <t>Contrôle</t>
@@ -6523,7 +6538,7 @@
         </is>
       </c>
     </row>
-    <row r="87" ht="15" customHeight="1" s="100">
+    <row r="87" ht="15" customHeight="1" s="102">
       <c r="A87" s="17" t="inlineStr">
         <is>
           <t>Contrôle</t>
@@ -6579,7 +6594,7 @@
         </is>
       </c>
     </row>
-    <row r="88" ht="15" customHeight="1" s="100">
+    <row r="88" ht="15" customHeight="1" s="102">
       <c r="A88" s="17" t="inlineStr">
         <is>
           <t>Contrôle</t>
@@ -6621,7 +6636,7 @@
       </c>
       <c r="J88" s="18" t="inlineStr">
         <is>
-          <t>Deal 40 damage. Stun the target for 2 turn.</t>
+          <t>Deal 50 damage. Stun the target for 2 turn.</t>
         </is>
       </c>
       <c r="K88" s="57" t="inlineStr">
@@ -6635,7 +6650,7 @@
         </is>
       </c>
     </row>
-    <row r="89" ht="15" customHeight="1" s="100">
+    <row r="89" ht="15" customHeight="1" s="102">
       <c r="A89" s="17" t="inlineStr">
         <is>
           <t>Contrôle</t>
@@ -6691,7 +6706,7 @@
         </is>
       </c>
     </row>
-    <row r="90" ht="17.1" customHeight="1" s="100">
+    <row r="90" ht="17.1" customHeight="1" s="102">
       <c r="A90" s="17" t="inlineStr">
         <is>
           <t>Contrôle</t>
@@ -6737,7 +6752,7 @@
       </c>
       <c r="J90" s="18" t="inlineStr">
         <is>
-          <t>Deal 10 damage to ALL enemies. If you have 20+ Stone, stun them all for 1 turn.</t>
+          <t>Deal 15 damage to ALL enemies. If you have 20+ Stone, stun them all for 1 turn.</t>
         </is>
       </c>
       <c r="K90" s="57" t="inlineStr">
@@ -6751,7 +6766,7 @@
         </is>
       </c>
     </row>
-    <row r="91" ht="15" customHeight="1" s="100">
+    <row r="91" ht="15" customHeight="1" s="102">
       <c r="A91" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  ▸ PIERRE</t>
@@ -6768,7 +6783,7 @@
       <c r="J91" s="32" t="n"/>
       <c r="K91" s="31" t="n"/>
     </row>
-    <row r="92" ht="15" customHeight="1" s="100">
+    <row r="92" ht="15" customHeight="1" s="102">
       <c r="A92" s="13" t="inlineStr">
         <is>
           <t>Pierre</t>
@@ -6810,7 +6825,7 @@
       </c>
       <c r="J92" s="14" t="inlineStr">
         <is>
-          <t>Gain 3 Stone.</t>
+          <t>Gain 2 Stone.</t>
         </is>
       </c>
       <c r="K92" s="57" t="inlineStr">
@@ -6824,7 +6839,7 @@
         </is>
       </c>
     </row>
-    <row r="93" ht="15" customHeight="1" s="100">
+    <row r="93" ht="15" customHeight="1" s="102">
       <c r="A93" s="13" t="inlineStr">
         <is>
           <t>Pierre</t>
@@ -6866,7 +6881,7 @@
       </c>
       <c r="J93" s="14" t="inlineStr">
         <is>
-          <t>Gain 5 Stone.</t>
+          <t>Gain 4 Stone.</t>
         </is>
       </c>
       <c r="K93" s="57" t="inlineStr">
@@ -6876,11 +6891,11 @@
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>≈ 3 armure  (1×3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="15" customHeight="1" s="100">
+          <t>≈ 4 armure  (1×4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="15" customHeight="1" s="102">
       <c r="A94" s="13" t="inlineStr">
         <is>
           <t>Pierre</t>
@@ -6922,7 +6937,7 @@
       </c>
       <c r="J94" s="14" t="inlineStr">
         <is>
-          <t>Gain 8 Stone.</t>
+          <t>Gain 5 Stone.</t>
         </is>
       </c>
       <c r="K94" s="57" t="inlineStr">
@@ -6932,11 +6947,11 @@
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>≈ 3 armure  (1×3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="15" customHeight="1" s="100">
+          <t>≈ 4 armure  (1×4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="15" customHeight="1" s="102">
       <c r="A95" s="13" t="inlineStr">
         <is>
           <t>Pierre</t>
@@ -6978,7 +6993,7 @@
       </c>
       <c r="J95" s="14" t="inlineStr">
         <is>
-          <t>Gain 6 Stone.</t>
+          <t>Gain 5 Stone.</t>
         </is>
       </c>
       <c r="K95" s="57" t="inlineStr">
@@ -6988,11 +7003,11 @@
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>≈ 3 armure  (1×3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="15" customHeight="1" s="100">
+          <t>≈ 4 armure  (1×4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="15" customHeight="1" s="102">
       <c r="A96" s="13" t="inlineStr">
         <is>
           <t>Pierre</t>
@@ -7034,7 +7049,7 @@
       </c>
       <c r="J96" s="14" t="inlineStr">
         <is>
-          <t>Gain 9 Stone.</t>
+          <t>Gain 6 Stone.</t>
         </is>
       </c>
       <c r="K96" s="57" t="inlineStr">
@@ -7044,11 +7059,11 @@
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>≈ 5 armure  (1×5)</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="15" customHeight="1" s="100">
+          <t>≈ 6 armure  (1×6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="15" customHeight="1" s="102">
       <c r="A97" s="15" t="inlineStr">
         <is>
           <t>Pierre</t>
@@ -7090,7 +7105,7 @@
       </c>
       <c r="J97" s="16" t="inlineStr">
         <is>
-          <t>Gain 12 Stone and 3 Regen.</t>
+          <t>Gain 10 Stone and 3 Regen.</t>
         </is>
       </c>
       <c r="K97" s="57" t="inlineStr">
@@ -7100,11 +7115,11 @@
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>≈ 10 armure  (2×5)</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="15" customHeight="1" s="100">
+          <t>≈ 12 armure  (2×6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="15" customHeight="1" s="102">
       <c r="A98" s="15" t="inlineStr">
         <is>
           <t>Pierre</t>
@@ -7146,7 +7161,7 @@
       </c>
       <c r="J98" s="16" t="inlineStr">
         <is>
-          <t>Gain 12 Stone.</t>
+          <t>Gain 9 Stone.</t>
         </is>
       </c>
       <c r="K98" s="57" t="inlineStr">
@@ -7156,11 +7171,11 @@
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>≈ 7,5 armure  (1×5×1,5)</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="15" customHeight="1" s="100">
+          <t>≈ 9 armure  (1×6×1,5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="15" customHeight="1" s="102">
       <c r="A99" s="15" t="inlineStr">
         <is>
           <t>Pierre</t>
@@ -7202,7 +7217,7 @@
       </c>
       <c r="J99" s="16" t="inlineStr">
         <is>
-          <t>Deal damage equal to your Stone, then gain 8 Stone.</t>
+          <t>Deal damage equal to your Stone, then gain 5 Stone.</t>
         </is>
       </c>
       <c r="K99" s="57" t="inlineStr">
@@ -7216,7 +7231,7 @@
         </is>
       </c>
     </row>
-    <row r="100" ht="15" customHeight="1" s="100">
+    <row r="100" ht="15" customHeight="1" s="102">
       <c r="A100" s="15" t="inlineStr">
         <is>
           <t>Pierre</t>
@@ -7258,7 +7273,7 @@
       </c>
       <c r="J100" s="16" t="inlineStr">
         <is>
-          <t>Deal 10 damage. Gain 8 Stone.</t>
+          <t>Deal 10 damage. Gain 5 Stone.</t>
         </is>
       </c>
       <c r="K100" s="57" t="inlineStr">
@@ -7272,7 +7287,7 @@
         </is>
       </c>
     </row>
-    <row r="101" ht="15" customHeight="1" s="100">
+    <row r="101" ht="15" customHeight="1" s="102">
       <c r="A101" s="15" t="inlineStr">
         <is>
           <t>Pierre</t>
@@ -7314,7 +7329,7 @@
       </c>
       <c r="J101" s="16" t="inlineStr">
         <is>
-          <t>Gain 18 Stone.</t>
+          <t>Gain 14 Stone.</t>
         </is>
       </c>
       <c r="K101" s="57" t="inlineStr">
@@ -7324,11 +7339,11 @@
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>≈ 10 armure  (2×5)</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="15" customHeight="1" s="100">
+          <t>≈ 12 armure  (2×6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="15" customHeight="1" s="102">
       <c r="A102" s="15" t="inlineStr">
         <is>
           <t>Pierre</t>
@@ -7370,7 +7385,7 @@
       </c>
       <c r="J102" s="16" t="inlineStr">
         <is>
-          <t>Gain 23 Stone. Counts as three Stone cards for Stone Age combos.</t>
+          <t>Gain 17 Stone. Counts as three Stone cards for Stone Age combos.</t>
         </is>
       </c>
       <c r="K102" s="57" t="inlineStr">
@@ -7380,11 +7395,11 @@
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>≈ 15 armure  (3×5)</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="15" customHeight="1" s="100">
+          <t>≈ 18 armure  (3×6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="15" customHeight="1" s="102">
       <c r="A103" s="15" t="inlineStr">
         <is>
           <t>Pierre</t>
@@ -7426,7 +7441,7 @@
       </c>
       <c r="J103" s="16" t="inlineStr">
         <is>
-          <t>Gain 4 Riposte: reflect melee damage you take back to the attacker. Lose 1 per trigger.</t>
+          <t>Gain 3 Riposte: reflect melee damage you take back to the attacker. Lose 1 per trigger.</t>
         </is>
       </c>
       <c r="K103" s="57" t="inlineStr">
@@ -7436,11 +7451,11 @@
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>≈ 10 armure  (2×5)</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="15" customHeight="1" s="100">
+          <t>≈ 12 armure  (2×6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="15" customHeight="1" s="102">
       <c r="A104" s="15" t="inlineStr">
         <is>
           <t>Pierre</t>
@@ -7482,7 +7497,7 @@
       </c>
       <c r="J104" s="16" t="inlineStr">
         <is>
-          <t>Gain 10 Stone.</t>
+          <t>Gain 9 Stone.</t>
         </is>
       </c>
       <c r="K104" s="57" t="inlineStr">
@@ -7492,11 +7507,11 @@
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>≈ 5 armure  (1×5)</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="15" customHeight="1" s="100">
+          <t>≈ 6 armure  (1×6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="15" customHeight="1" s="102">
       <c r="A105" s="15" t="inlineStr">
         <is>
           <t>Pierre</t>
@@ -7538,7 +7553,7 @@
       </c>
       <c r="J105" s="16" t="inlineStr">
         <is>
-          <t>Gain 7 Stone.</t>
+          <t>Gain 5 Stone.</t>
         </is>
       </c>
       <c r="K105" s="57" t="inlineStr">
@@ -7548,11 +7563,11 @@
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>≈ 5 armure  (1×5)</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="15" customHeight="1" s="100">
+          <t>≈ 6 armure  (1×6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="15" customHeight="1" s="102">
       <c r="A106" s="15" t="inlineStr">
         <is>
           <t>Pierre</t>
@@ -7604,11 +7619,11 @@
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>≈ 10 armure  (2×5)</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="15" customHeight="1" s="100">
+          <t>≈ 12 armure  (2×6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="15" customHeight="1" s="102">
       <c r="A107" s="15" t="inlineStr">
         <is>
           <t>Pierre</t>
@@ -7664,7 +7679,7 @@
         </is>
       </c>
     </row>
-    <row r="108" ht="15" customHeight="1" s="100">
+    <row r="108" ht="15" customHeight="1" s="102">
       <c r="A108" s="15" t="inlineStr">
         <is>
           <t>Pierre</t>
@@ -7706,7 +7721,7 @@
       </c>
       <c r="J108" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gain 12 Stone. </t>
+          <t xml:space="preserve">Gain 10 Stone. </t>
         </is>
       </c>
       <c r="K108" s="57" t="inlineStr">
@@ -7716,11 +7731,11 @@
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>≈ 12 armure  (1×8×1,5)</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="15" customHeight="1" s="100">
+          <t>≈ 13,5 armure  (1×9×1,5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="15" customHeight="1" s="102">
       <c r="A109" s="17" t="inlineStr">
         <is>
           <t>Pierre</t>
@@ -7762,7 +7777,7 @@
       </c>
       <c r="J109" s="18" t="inlineStr">
         <is>
-          <t>Gain 22 Stone.</t>
+          <t>Gain 20 Stone.</t>
         </is>
       </c>
       <c r="K109" s="57" t="inlineStr">
@@ -7772,11 +7787,11 @@
       </c>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>≈ 16 armure  (2×8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="15" customHeight="1" s="100">
+          <t>≈ 18 armure  (2×9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="15" customHeight="1" s="102">
       <c r="A110" s="17" t="inlineStr">
         <is>
           <t>Pierre</t>
@@ -7818,7 +7833,7 @@
       </c>
       <c r="J110" s="18" t="inlineStr">
         <is>
-          <t>Gain 8 Stone and Haste for 2 turns.</t>
+          <t>Gain 6 Stone and 2 haste.</t>
         </is>
       </c>
       <c r="K110" s="57" t="inlineStr">
@@ -7832,7 +7847,7 @@
         </is>
       </c>
     </row>
-    <row r="111" ht="15" customHeight="1" s="100">
+    <row r="111" ht="15" customHeight="1" s="102">
       <c r="A111" s="17" t="inlineStr">
         <is>
           <t>Pierre</t>
@@ -7874,7 +7889,7 @@
       </c>
       <c r="J111" s="18" t="inlineStr">
         <is>
-          <t>Gain 7 Stone for every enemy still alive.</t>
+          <t>Gain 5 Stone for every enemy still alive.</t>
         </is>
       </c>
       <c r="K111" s="57" t="inlineStr">
@@ -7884,11 +7899,11 @@
       </c>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>≈ 8 armure  (1×8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="15" customHeight="1" s="100">
+          <t>≈ 9 armure  (1×9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="15" customHeight="1" s="102">
       <c r="A112" s="17" t="inlineStr">
         <is>
           <t>Pierre</t>
@@ -7930,7 +7945,7 @@
       </c>
       <c r="J112" s="18" t="inlineStr">
         <is>
-          <t>Spend all Forge Heat. Gain 10 Stone per Heat spent.</t>
+          <t>Spend all Forge Heat. Gain 9 Stone per Heat spent.</t>
         </is>
       </c>
       <c r="K112" s="57" t="inlineStr">
@@ -7944,7 +7959,7 @@
         </is>
       </c>
     </row>
-    <row r="113" ht="15" customHeight="1" s="100">
+    <row r="113" ht="15" customHeight="1" s="102">
       <c r="A113" s="17" t="inlineStr">
         <is>
           <t>Pierre</t>
@@ -7996,11 +8011,11 @@
       </c>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>≈ 32 armure  (4×8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="15" customHeight="1" s="100">
+          <t>≈ 36 armure  (4×9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="15" customHeight="1" s="102">
       <c r="A114" s="17" t="inlineStr">
         <is>
           <t>Pierre</t>
@@ -8056,7 +8071,7 @@
         </is>
       </c>
     </row>
-    <row r="115" ht="17.1" customHeight="1" s="100">
+    <row r="115" ht="17.1" customHeight="1" s="102">
       <c r="A115" s="21" t="inlineStr">
         <is>
           <t>Pierre</t>
@@ -8108,11 +8123,11 @@
       </c>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>≈ 24 armure  (2×12)</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="15" customHeight="1" s="100">
+          <t>≈ 28 armure  (2×14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="15" customHeight="1" s="102">
       <c r="A116" s="13" t="inlineStr">
         <is>
           <t>Pierre</t>
@@ -8154,7 +8169,7 @@
       </c>
       <c r="J116" s="14" t="inlineStr">
         <is>
-          <t>Gain 2 Stone.</t>
+          <t>Gain 1 Stone.</t>
         </is>
       </c>
       <c r="K116" s="57" t="inlineStr">
@@ -8168,7 +8183,7 @@
         </is>
       </c>
     </row>
-    <row r="117" ht="15" customHeight="1" s="100">
+    <row r="117" ht="15" customHeight="1" s="102">
       <c r="A117" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">  ▸ SOIN</t>
@@ -8185,7 +8200,7 @@
       <c r="J117" s="34" t="n"/>
       <c r="K117" s="33" t="n"/>
     </row>
-    <row r="118" ht="15" customHeight="1" s="100">
+    <row r="118" ht="15" customHeight="1" s="102">
       <c r="A118" s="13" t="inlineStr">
         <is>
           <t>Soin</t>
@@ -8227,7 +8242,7 @@
       </c>
       <c r="J118" s="14" t="inlineStr">
         <is>
-          <t>Gain 3 Regen. Each turn: heal that many HP, then lose 1 Regen.</t>
+          <t>Gain 3 Regen.</t>
         </is>
       </c>
       <c r="K118" s="57" t="inlineStr">
@@ -8241,7 +8256,7 @@
         </is>
       </c>
     </row>
-    <row r="119" ht="15" customHeight="1" s="100">
+    <row r="119" ht="15" customHeight="1" s="102">
       <c r="A119" s="15" t="inlineStr">
         <is>
           <t>Soin</t>
@@ -8297,7 +8312,7 @@
         </is>
       </c>
     </row>
-    <row r="120" ht="15" customHeight="1" s="100">
+    <row r="120" ht="15" customHeight="1" s="102">
       <c r="A120" s="15" t="inlineStr">
         <is>
           <t>Soin</t>
@@ -8339,7 +8354,7 @@
       </c>
       <c r="J120" s="16" t="inlineStr">
         <is>
-          <t>Deal 12 damage. Remove a random buff from the target; if one was removed, gain 4 Regen.</t>
+          <t>Deal 10 damage. Remove a random buff from the target; if one was removed, gain 4 Regen.</t>
         </is>
       </c>
       <c r="K120" s="57" t="inlineStr">
@@ -8353,7 +8368,7 @@
         </is>
       </c>
     </row>
-    <row r="121" ht="15" customHeight="1" s="100">
+    <row r="121" ht="15" customHeight="1" s="102">
       <c r="A121" s="15" t="inlineStr">
         <is>
           <t>Soin</t>
@@ -8399,7 +8414,7 @@
       </c>
       <c r="J121" s="16" t="inlineStr">
         <is>
-          <t>Deal 6 damage to ALL enemies. Heal 4 HP per enemy hit.</t>
+          <t>Deal 7 damage to ALL enemies. Heal 4 HP per enemy hit.</t>
         </is>
       </c>
       <c r="K121" s="57" t="inlineStr">
@@ -8413,7 +8428,7 @@
         </is>
       </c>
     </row>
-    <row r="122" ht="15" customHeight="1" s="100">
+    <row r="122" ht="15" customHeight="1" s="102">
       <c r="A122" s="17" t="inlineStr">
         <is>
           <t>Soin</t>
@@ -8455,7 +8470,7 @@
       </c>
       <c r="J122" s="18" t="inlineStr">
         <is>
-          <t>Heal 30 HP.</t>
+          <t>Heal 20 HP.</t>
         </is>
       </c>
       <c r="K122" s="57" t="inlineStr">
@@ -8465,11 +8480,11 @@
       </c>
       <c r="L122" s="2" t="inlineStr">
         <is>
-          <t>≈ 16 armure  (2×8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="15" customHeight="1" s="100">
+          <t>≈ 18 armure  (2×9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="15" customHeight="1" s="102">
       <c r="A123" s="17" t="inlineStr">
         <is>
           <t>Soin</t>
@@ -8511,7 +8526,7 @@
       </c>
       <c r="J123" s="18" t="inlineStr">
         <is>
-          <t>Remove a random buff from the target. If one was removed, gain 4 Regen.</t>
+          <t>Remove a random buff from the target. If one was removed, gain 5 Regen.</t>
         </is>
       </c>
       <c r="K123" s="57" t="inlineStr">
@@ -8525,7 +8540,7 @@
         </is>
       </c>
     </row>
-    <row r="124" ht="17.1" customHeight="1" s="100">
+    <row r="124" ht="17.1" customHeight="1" s="102">
       <c r="A124" s="21" t="inlineStr">
         <is>
           <t>Soin</t>
@@ -8567,7 +8582,7 @@
       </c>
       <c r="J124" s="22" t="inlineStr">
         <is>
-          <t>Heal 10 HP per enemy that has Bleed.</t>
+          <t>Heal 15 HP per enemy that has Bleed.</t>
         </is>
       </c>
       <c r="K124" s="57" t="inlineStr">
@@ -8581,7 +8596,7 @@
         </is>
       </c>
     </row>
-    <row r="125" ht="15" customHeight="1" s="100">
+    <row r="125" ht="15" customHeight="1" s="102">
       <c r="A125" s="21" t="inlineStr">
         <is>
           <t>Soin</t>
@@ -8623,7 +8638,7 @@
       </c>
       <c r="J125" s="22" t="inlineStr">
         <is>
-          <t>Deal 15 damage. If the target dies, gain 4 Strength and heal 20 HP.</t>
+          <t>Deal 50 damage. If the target dies, gain 5 Strength and heal 10 HP.</t>
         </is>
       </c>
       <c r="K125" s="57" t="inlineStr">
@@ -8637,7 +8652,7 @@
         </is>
       </c>
     </row>
-    <row r="126" ht="15" customHeight="1" s="100">
+    <row r="126" ht="15" customHeight="1" s="102">
       <c r="A126" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">  ▸ ÉNERGIE</t>
@@ -8654,7 +8669,7 @@
       <c r="J126" s="36" t="n"/>
       <c r="K126" s="35" t="n"/>
     </row>
-    <row r="127" ht="15" customHeight="1" s="100">
+    <row r="127" ht="15" customHeight="1" s="102">
       <c r="A127" s="13" t="inlineStr">
         <is>
           <t>Énergie</t>
@@ -8710,7 +8725,7 @@
         </is>
       </c>
     </row>
-    <row r="128" ht="15" customHeight="1" s="100">
+    <row r="128" ht="15" customHeight="1" s="102">
       <c r="A128" s="13" t="inlineStr">
         <is>
           <t>Énergie</t>
@@ -8766,7 +8781,7 @@
         </is>
       </c>
     </row>
-    <row r="129" ht="15" customHeight="1" s="100">
+    <row r="129" ht="15" customHeight="1" s="102">
       <c r="A129" s="15" t="inlineStr">
         <is>
           <t>Énergie</t>
@@ -8822,7 +8837,7 @@
         </is>
       </c>
     </row>
-    <row r="130" ht="15" customHeight="1" s="100">
+    <row r="130" ht="15" customHeight="1" s="102">
       <c r="A130" s="15" t="inlineStr">
         <is>
           <t>Énergie</t>
@@ -8882,7 +8897,7 @@
         </is>
       </c>
     </row>
-    <row r="131" ht="15" customHeight="1" s="100">
+    <row r="131" ht="15" customHeight="1" s="102">
       <c r="A131" s="15" t="inlineStr">
         <is>
           <t>Énergie</t>
@@ -8938,7 +8953,7 @@
         </is>
       </c>
     </row>
-    <row r="132" ht="15" customHeight="1" s="100">
+    <row r="132" ht="15" customHeight="1" s="102">
       <c r="A132" s="15" t="inlineStr">
         <is>
           <t>Énergie</t>
@@ -8994,7 +9009,7 @@
         </is>
       </c>
     </row>
-    <row r="133" ht="15" customHeight="1" s="100">
+    <row r="133" ht="15" customHeight="1" s="102">
       <c r="A133" s="15" t="inlineStr">
         <is>
           <t>Énergie</t>
@@ -9050,7 +9065,7 @@
         </is>
       </c>
     </row>
-    <row r="134" ht="15" customHeight="1" s="100">
+    <row r="134" ht="15" customHeight="1" s="102">
       <c r="A134" s="15" t="inlineStr">
         <is>
           <t>Énergie</t>
@@ -9106,7 +9121,7 @@
         </is>
       </c>
     </row>
-    <row r="135" ht="15" customHeight="1" s="100">
+    <row r="135" ht="15" customHeight="1" s="102">
       <c r="A135" s="15" t="inlineStr">
         <is>
           <t>Énergie</t>
@@ -9148,7 +9163,7 @@
       </c>
       <c r="J135" s="16" t="inlineStr">
         <is>
-          <t>Gain 1 to 5 Forge Heat at random.</t>
+          <t>Gain 1 to 6 Forge Heat at random.</t>
         </is>
       </c>
       <c r="K135" s="57" t="inlineStr">
@@ -9162,7 +9177,7 @@
         </is>
       </c>
     </row>
-    <row r="136" ht="15" customHeight="1" s="100">
+    <row r="136" ht="15" customHeight="1" s="102">
       <c r="A136" s="15" t="inlineStr">
         <is>
           <t>Énergie</t>
@@ -9218,7 +9233,7 @@
         </is>
       </c>
     </row>
-    <row r="137" ht="15" customHeight="1" s="100">
+    <row r="137" ht="15" customHeight="1" s="102">
       <c r="A137" s="15" t="inlineStr">
         <is>
           <t>Énergie</t>
@@ -9260,7 +9275,7 @@
       </c>
       <c r="J137" s="16" t="inlineStr">
         <is>
-          <t>Trade 5 Haste turns for 3 Forge Heat. No effect below 5 Haste.</t>
+          <t>Trade 5 Haste for 4 Forge Heat. No effect below 5 Haste.</t>
         </is>
       </c>
       <c r="K137" s="57" t="inlineStr">
@@ -9274,7 +9289,7 @@
         </is>
       </c>
     </row>
-    <row r="138" ht="17.1" customHeight="1" s="100">
+    <row r="138" ht="17.1" customHeight="1" s="102">
       <c r="A138" s="21" t="inlineStr">
         <is>
           <t>Énergie</t>
@@ -9316,7 +9331,7 @@
       </c>
       <c r="J138" s="22" t="inlineStr">
         <is>
-          <t>Gain 5 Forge Heat (energy).</t>
+          <t>Gain 4 Forge Heat (energy).</t>
         </is>
       </c>
       <c r="K138" s="57" t="inlineStr">
@@ -9330,7 +9345,7 @@
         </is>
       </c>
     </row>
-    <row r="139" ht="15" customHeight="1" s="100">
+    <row r="139" ht="15" customHeight="1" s="102">
       <c r="A139" s="21" t="inlineStr">
         <is>
           <t>Énergie</t>
@@ -9386,7 +9401,7 @@
         </is>
       </c>
     </row>
-    <row r="140" ht="15" customHeight="1" s="100">
+    <row r="140" ht="15" customHeight="1" s="102">
       <c r="A140" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">  ▸ HÂTE</t>
@@ -9403,7 +9418,7 @@
       <c r="J140" s="38" t="n"/>
       <c r="K140" s="37" t="n"/>
     </row>
-    <row r="141" ht="15" customHeight="1" s="100">
+    <row r="141" ht="15" customHeight="1" s="102">
       <c r="A141" s="13" t="inlineStr">
         <is>
           <t>Hâte</t>
@@ -9459,7 +9474,7 @@
         </is>
       </c>
     </row>
-    <row r="142" ht="15" customHeight="1" s="100">
+    <row r="142" ht="15" customHeight="1" s="102">
       <c r="A142" s="13" t="inlineStr">
         <is>
           <t>Hâte</t>
@@ -9501,7 +9516,7 @@
       </c>
       <c r="J142" s="14" t="inlineStr">
         <is>
-          <t>Haste for 4 of your turns.</t>
+          <t>Gain 4 Haste.</t>
         </is>
       </c>
       <c r="K142" s="57" t="inlineStr">
@@ -9515,7 +9530,7 @@
         </is>
       </c>
     </row>
-    <row r="143" ht="15" customHeight="1" s="100">
+    <row r="143" ht="15" customHeight="1" s="102">
       <c r="A143" s="13" t="inlineStr">
         <is>
           <t>Hâte</t>
@@ -9557,7 +9572,7 @@
       </c>
       <c r="J143" s="14" t="inlineStr">
         <is>
-          <t>Each of your turns, gain 1 permanent Haste (it builds up all combat). Stacks when replayed.</t>
+          <t>Each of your turns, gain 1 Haste (it builds up all combat). Stacks when replayed.</t>
         </is>
       </c>
       <c r="K143" s="57" t="inlineStr">
@@ -9571,7 +9586,7 @@
         </is>
       </c>
     </row>
-    <row r="144" ht="15" customHeight="1" s="100">
+    <row r="144" ht="15" customHeight="1" s="102">
       <c r="A144" s="15" t="inlineStr">
         <is>
           <t>Hâte</t>
@@ -9613,7 +9628,7 @@
       </c>
       <c r="J144" s="16" t="inlineStr">
         <is>
-          <t>Haste for 3 turns. Draw 1 card.</t>
+          <t>Gain 3 Haste and Draw 1 card.</t>
         </is>
       </c>
       <c r="K144" s="57" t="inlineStr">
@@ -9627,7 +9642,7 @@
         </is>
       </c>
     </row>
-    <row r="145" ht="17.1" customHeight="1" s="100">
+    <row r="145" ht="17.1" customHeight="1" s="102">
       <c r="A145" s="15" t="inlineStr">
         <is>
           <t>Hâte</t>
@@ -9669,7 +9684,7 @@
       </c>
       <c r="J145" s="16" t="inlineStr">
         <is>
-          <t>Gain 4 Haste. Each stack: +5% speed. Lose 1 per turn.</t>
+          <t>Gain 4 Haste.</t>
         </is>
       </c>
       <c r="K145" s="57" t="inlineStr">
@@ -9683,7 +9698,7 @@
         </is>
       </c>
     </row>
-    <row r="146" ht="17.1" customHeight="1" s="100">
+    <row r="146" ht="17.1" customHeight="1" s="102">
       <c r="A146" s="15" t="inlineStr">
         <is>
           <t>Hâte</t>
@@ -9739,7 +9754,7 @@
         </is>
       </c>
     </row>
-    <row r="147" ht="15" customHeight="1" s="100">
+    <row r="147" ht="15" customHeight="1" s="102">
       <c r="A147" s="15" t="inlineStr">
         <is>
           <t>Hâte</t>
@@ -9795,7 +9810,7 @@
         </is>
       </c>
     </row>
-    <row r="148" ht="15" customHeight="1" s="100">
+    <row r="148" ht="15" customHeight="1" s="102">
       <c r="A148" s="13" t="inlineStr">
         <is>
           <t>Hâte</t>
@@ -9851,7 +9866,7 @@
         </is>
       </c>
     </row>
-    <row r="149" ht="15" customHeight="1" s="100">
+    <row r="149" ht="15" customHeight="1" s="102">
       <c r="A149" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve">  ▸ FORCE</t>
@@ -9868,7 +9883,7 @@
       <c r="J149" s="40" t="n"/>
       <c r="K149" s="39" t="n"/>
     </row>
-    <row r="150" ht="15" customHeight="1" s="100">
+    <row r="150" ht="15" customHeight="1" s="102">
       <c r="A150" s="13" t="inlineStr">
         <is>
           <t>Force</t>
@@ -9910,7 +9925,7 @@
       </c>
       <c r="J150" s="14" t="inlineStr">
         <is>
-          <t>Gain 2 Strength (+2 damage to every attack this combat).</t>
+          <t>Gain 2 Strength.</t>
         </is>
       </c>
       <c r="K150" s="57" t="inlineStr">
@@ -9924,7 +9939,7 @@
         </is>
       </c>
     </row>
-    <row r="151" ht="15" customHeight="1" s="100">
+    <row r="151" ht="15" customHeight="1" s="102">
       <c r="A151" s="15" t="inlineStr">
         <is>
           <t>Force</t>
@@ -9980,7 +9995,7 @@
         </is>
       </c>
     </row>
-    <row r="152" ht="15" customHeight="1" s="100">
+    <row r="152" ht="15" customHeight="1" s="102">
       <c r="A152" s="15" t="inlineStr">
         <is>
           <t>Force</t>
@@ -10022,7 +10037,7 @@
       </c>
       <c r="J152" s="16" t="inlineStr">
         <is>
-          <t>Deal 14 damage. Gain 3 Strength.</t>
+          <t>Deal 10 damage. Gain 3 Strength.</t>
         </is>
       </c>
       <c r="K152" s="57" t="inlineStr">
@@ -10036,7 +10051,7 @@
         </is>
       </c>
     </row>
-    <row r="153" ht="17.1" customHeight="1" s="100">
+    <row r="153" ht="17.1" customHeight="1" s="102">
       <c r="A153" s="15" t="inlineStr">
         <is>
           <t>Force</t>
@@ -10053,7 +10068,7 @@
         </is>
       </c>
       <c r="D153" s="15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E153" s="15" t="inlineStr">
         <is>
@@ -10078,7 +10093,7 @@
       </c>
       <c r="J153" s="16" t="inlineStr">
         <is>
-          <t>Gain 4 Strength.</t>
+          <t>Gain 6 Strength.</t>
         </is>
       </c>
       <c r="K153" s="57" t="inlineStr">
@@ -10092,7 +10107,7 @@
         </is>
       </c>
     </row>
-    <row r="154" ht="15" customHeight="1" s="100">
+    <row r="154" ht="15" customHeight="1" s="102">
       <c r="A154" s="15" t="inlineStr">
         <is>
           <t>Force</t>
@@ -10134,7 +10149,7 @@
       </c>
       <c r="J154" s="16" t="inlineStr">
         <is>
-          <t>Gain 4 Strength. Draw 2 cards.</t>
+          <t>Gain 2 Strength. Draw 2 cards.</t>
         </is>
       </c>
       <c r="K154" s="57" t="inlineStr">
@@ -10148,7 +10163,7 @@
         </is>
       </c>
     </row>
-    <row r="155" ht="15" customHeight="1" s="100">
+    <row r="155" ht="15" customHeight="1" s="102">
       <c r="A155" s="15" t="inlineStr">
         <is>
           <t>Force</t>
@@ -10204,7 +10219,7 @@
         </is>
       </c>
     </row>
-    <row r="156" ht="15" customHeight="1" s="100">
+    <row r="156" ht="15" customHeight="1" s="102">
       <c r="A156" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">  ▸ PIOCHE</t>
@@ -10221,7 +10236,7 @@
       <c r="J156" s="42" t="n"/>
       <c r="K156" s="41" t="n"/>
     </row>
-    <row r="157" ht="15" customHeight="1" s="100">
+    <row r="157" ht="15" customHeight="1" s="102">
       <c r="A157" s="13" t="inlineStr">
         <is>
           <t>Pioche</t>
@@ -10277,7 +10292,7 @@
         </is>
       </c>
     </row>
-    <row r="158" ht="15" customHeight="1" s="100">
+    <row r="158" ht="15" customHeight="1" s="102">
       <c r="A158" s="13" t="inlineStr">
         <is>
           <t>Pioche</t>
@@ -10333,7 +10348,7 @@
         </is>
       </c>
     </row>
-    <row r="159" ht="15" customHeight="1" s="100">
+    <row r="159" ht="15" customHeight="1" s="102">
       <c r="A159" s="15" t="inlineStr">
         <is>
           <t>Pioche</t>
@@ -10389,7 +10404,7 @@
         </is>
       </c>
     </row>
-    <row r="160" ht="15" customHeight="1" s="100">
+    <row r="160" ht="15" customHeight="1" s="102">
       <c r="A160" s="15" t="inlineStr">
         <is>
           <t>Pioche</t>
@@ -10445,7 +10460,7 @@
         </is>
       </c>
     </row>
-    <row r="161" ht="15" customHeight="1" s="100">
+    <row r="161" ht="15" customHeight="1" s="102">
       <c r="A161" s="15" t="inlineStr">
         <is>
           <t>Pioche</t>
@@ -10487,7 +10502,7 @@
       </c>
       <c r="J161" s="16" t="inlineStr">
         <is>
-          <t>Draw 2 cards. Gain 1 Forge Heat.</t>
+          <t>Draw 2 cards. Gain 2 Forge Heat.</t>
         </is>
       </c>
       <c r="K161" s="57" t="inlineStr">
@@ -10501,7 +10516,7 @@
         </is>
       </c>
     </row>
-    <row r="162" ht="15" customHeight="1" s="100">
+    <row r="162" ht="15" customHeight="1" s="102">
       <c r="A162" s="17" t="inlineStr">
         <is>
           <t>Pioche</t>
@@ -10518,7 +10533,7 @@
         </is>
       </c>
       <c r="D162" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E162" s="17" t="inlineStr">
         <is>
@@ -10557,7 +10572,7 @@
         </is>
       </c>
     </row>
-    <row r="163" ht="15" customHeight="1" s="100">
+    <row r="163" ht="15" customHeight="1" s="102">
       <c r="A163" s="21" t="inlineStr">
         <is>
           <t>Pioche</t>
@@ -10613,7 +10628,7 @@
         </is>
       </c>
     </row>
-    <row r="164" ht="15" customHeight="1" s="100">
+    <row r="164" ht="15" customHeight="1" s="102">
       <c r="A164" s="13" t="inlineStr">
         <is>
           <t>Pioche</t>
@@ -10669,7 +10684,7 @@
         </is>
       </c>
     </row>
-    <row r="165" ht="15" customHeight="1" s="100">
+    <row r="165" ht="15" customHeight="1" s="102">
       <c r="A165" s="55" t="n"/>
       <c r="B165" s="55" t="n"/>
       <c r="C165" s="55" t="n"/>
@@ -10681,7 +10696,7 @@
       <c r="I165" s="55" t="n"/>
       <c r="J165" s="55" t="n"/>
     </row>
-    <row r="166" ht="15" customHeight="1" s="100">
+    <row r="166" ht="15" customHeight="1" s="102">
       <c r="A166" s="55" t="n"/>
       <c r="B166" s="55" t="n"/>
       <c r="C166" s="55" t="n"/>
@@ -10693,7 +10708,7 @@
       <c r="I166" s="55" t="n"/>
       <c r="J166" s="55" t="n"/>
     </row>
-    <row r="167" ht="15" customHeight="1" s="100">
+    <row r="167" ht="15" customHeight="1" s="102">
       <c r="A167" s="55" t="n"/>
       <c r="B167" s="55" t="n"/>
       <c r="C167" s="55" t="n"/>
@@ -10705,7 +10720,7 @@
       <c r="I167" s="55" t="n"/>
       <c r="J167" s="55" t="n"/>
     </row>
-    <row r="168" ht="15" customHeight="1" s="100">
+    <row r="168" ht="15" customHeight="1" s="102">
       <c r="A168" s="55" t="n"/>
       <c r="B168" s="55" t="n"/>
       <c r="C168" s="55" t="n"/>
@@ -10771,15 +10786,15 @@
   <dimension ref="A1:H141"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" style="100" min="1" max="1"/>
-    <col width="24" customWidth="1" style="100" min="2" max="3"/>
-    <col width="11" customWidth="1" style="100" min="4" max="4"/>
-    <col width="71.5703125" customWidth="1" style="100" min="5" max="5"/>
-    <col width="52" customWidth="1" style="100" min="6" max="6"/>
-    <col width="30" customWidth="1" style="100" min="7" max="7"/>
+    <col width="16" customWidth="1" style="102" min="1" max="1"/>
+    <col width="24" customWidth="1" style="102" min="2" max="3"/>
+    <col width="11" customWidth="1" style="102" min="4" max="4"/>
+    <col width="71.5703125" customWidth="1" style="102" min="5" max="5"/>
+    <col width="52" customWidth="1" style="102" min="6" max="6"/>
+    <col width="30" customWidth="1" style="102" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21.95" customHeight="1" s="100">
+    <row r="1" ht="21.95" customHeight="1" s="102">
       <c r="A1" s="10" t="inlineStr">
         <is>
           <t>Catégorie</t>
@@ -10810,13 +10825,13 @@
           <t>Effet hors-carte / spécial</t>
         </is>
       </c>
-      <c r="G1" s="101" t="inlineStr">
+      <c r="G1" s="103" t="inlineStr">
         <is>
           <t>Total visé (barème)</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="17.1" customHeight="1" s="100">
+    <row r="2" ht="17.1" customHeight="1" s="102">
       <c r="A2" s="47" t="inlineStr">
         <is>
           <t xml:space="preserve">  ▸ ARMES</t>
@@ -10828,7 +10843,7 @@
       <c r="E2" s="48" t="n"/>
       <c r="F2" s="48" t="n"/>
     </row>
-    <row r="3" ht="15" customHeight="1" s="100">
+    <row r="3" ht="15" customHeight="1" s="102">
       <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Armes</t>
@@ -10861,7 +10876,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="100">
+    <row r="4" ht="15" customHeight="1" s="102">
       <c r="A4" s="13" t="inlineStr">
         <is>
           <t>Armes</t>
@@ -10894,7 +10909,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="100">
+    <row r="5" ht="15" customHeight="1" s="102">
       <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Armes</t>
@@ -10927,7 +10942,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="100">
+    <row r="6" ht="15" customHeight="1" s="102">
       <c r="A6" s="13" t="inlineStr">
         <is>
           <t>Armes</t>
@@ -10956,11 +10971,11 @@
       <c r="F6" s="14" t="n"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>≈ 35 dégâts  ·  ≈ 6 armure  (5 cartes/5 visées)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="100">
+          <t>≈ 35 dégâts  ·  ≈ 8 armure  (5 cartes/5 visées)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1" s="102">
       <c r="A7" s="13" t="inlineStr">
         <is>
           <t>Armes</t>
@@ -10993,7 +11008,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="100">
+    <row r="8" ht="15" customHeight="1" s="102">
       <c r="A8" s="13" t="inlineStr">
         <is>
           <t>Armes</t>
@@ -11022,11 +11037,11 @@
       <c r="F8" s="14" t="n"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>≈ 25 dégâts  ·  ≈ 3 armure  (4 cartes/5 visées)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="100">
+          <t>≈ 25 dégâts  ·  ≈ 4 armure  (4 cartes/5 visées)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="102">
       <c r="A9" s="13" t="inlineStr">
         <is>
           <t>Armes</t>
@@ -11055,11 +11070,11 @@
       <c r="F9" s="14" t="n"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>≈ 10 dégâts  ·  ≈ 6 armure  (5 cartes/5 visées · 1 buff)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="100">
+          <t>≈ 10 dégâts  ·  ≈ 8 armure  (5 cartes/5 visées · 1 buff)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1" s="102">
       <c r="A10" s="13" t="inlineStr">
         <is>
           <t>Armes</t>
@@ -11092,7 +11107,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="100">
+    <row r="11" ht="15" customHeight="1" s="102">
       <c r="A11" s="13" t="inlineStr">
         <is>
           <t>Armes</t>
@@ -11125,7 +11140,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="100">
+    <row r="12" ht="15" customHeight="1" s="102">
       <c r="A12" s="13" t="inlineStr">
         <is>
           <t>Armes</t>
@@ -11158,7 +11173,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="100">
+    <row r="13" ht="15" customHeight="1" s="102">
       <c r="A13" s="13" t="inlineStr">
         <is>
           <t>Armes</t>
@@ -11191,7 +11206,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="100">
+    <row r="14" ht="15" customHeight="1" s="102">
       <c r="A14" s="13" t="inlineStr">
         <is>
           <t>Armes</t>
@@ -11224,7 +11239,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="100">
+    <row r="15" ht="15" customHeight="1" s="102">
       <c r="A15" s="13" t="inlineStr">
         <is>
           <t>Armes</t>
@@ -11257,7 +11272,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="100">
+    <row r="16" ht="15" customHeight="1" s="102">
       <c r="A16" s="13" t="inlineStr">
         <is>
           <t>Armes</t>
@@ -11290,7 +11305,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="100">
+    <row r="17" ht="15" customHeight="1" s="102">
       <c r="A17" s="13" t="inlineStr">
         <is>
           <t>Armes</t>
@@ -11323,7 +11338,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="100">
+    <row r="18" ht="15" customHeight="1" s="102">
       <c r="A18" s="13" t="inlineStr">
         <is>
           <t>Armes</t>
@@ -11352,11 +11367,11 @@
       <c r="F18" s="14" t="n"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>≈ 25 dégâts  ·  ≈ 3 armure  (5 cartes/5 visées)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1" s="100">
+          <t>≈ 25 dégâts  ·  ≈ 4 armure  (5 cartes/5 visées)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1" s="102">
       <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Armes</t>
@@ -11389,7 +11404,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="100">
+    <row r="20" ht="15" customHeight="1" s="102">
       <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Armes</t>
@@ -11422,11 +11437,11 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>≈ 72 dégâts  (8 cartes/6 visées · 3 buff)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="100">
+          <t>≈ 96 dégâts  (8 cartes/6 visées · 3 buff)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1" s="102">
       <c r="A21" s="15" t="inlineStr">
         <is>
           <t>Armes</t>
@@ -11459,7 +11474,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="100">
+    <row r="22" ht="15" customHeight="1" s="102">
       <c r="A22" s="15" t="inlineStr">
         <is>
           <t>Armes</t>
@@ -11492,7 +11507,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" s="100">
+    <row r="23" ht="15" customHeight="1" s="102">
       <c r="A23" s="15" t="inlineStr">
         <is>
           <t>Armes</t>
@@ -11525,7 +11540,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" s="100">
+    <row r="24" ht="15" customHeight="1" s="102">
       <c r="A24" s="15" t="inlineStr">
         <is>
           <t>Armes</t>
@@ -11558,7 +11573,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" s="100">
+    <row r="25" ht="15" customHeight="1" s="102">
       <c r="A25" s="15" t="inlineStr">
         <is>
           <t>Armes</t>
@@ -11591,7 +11606,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" s="100">
+    <row r="26" ht="15" customHeight="1" s="102">
       <c r="A26" s="15" t="inlineStr">
         <is>
           <t>Armes</t>
@@ -11624,11 +11639,11 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>≈ 132 dégâts  ·  ≈ 7,5 armure  (9 cartes/6 visées)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="100">
+          <t>≈ 132 dégâts  ·  ≈ 9 armure  (9 cartes/6 visées)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1" s="102">
       <c r="A27" s="15" t="inlineStr">
         <is>
           <t>Armes</t>
@@ -11661,7 +11676,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" s="100">
+    <row r="28" ht="15" customHeight="1" s="102">
       <c r="A28" s="15" t="inlineStr">
         <is>
           <t>Armes</t>
@@ -11694,7 +11709,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" s="100">
+    <row r="29" ht="15" customHeight="1" s="102">
       <c r="A29" s="15" t="inlineStr">
         <is>
           <t>Armes</t>
@@ -11727,7 +11742,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1" s="100">
+    <row r="30" ht="15" customHeight="1" s="102">
       <c r="A30" s="15" t="inlineStr">
         <is>
           <t>Armes</t>
@@ -11756,11 +11771,11 @@
       <c r="F30" s="16" t="n"/>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>≈ 40 dégâts  ·  ≈ 6 armure  (5 cartes/6 visées)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1" s="100">
+          <t>≈ 40 dégâts  ·  ≈ 8 armure  (5 cartes/6 visées)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1" s="102">
       <c r="A31" s="15" t="inlineStr">
         <is>
           <t>Armes</t>
@@ -11797,7 +11812,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1" s="100">
+    <row r="32" ht="15" customHeight="1" s="102">
       <c r="A32" s="15" t="inlineStr">
         <is>
           <t>Armes</t>
@@ -11830,7 +11845,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1" s="100">
+    <row r="33" ht="15" customHeight="1" s="102">
       <c r="A33" s="15" t="inlineStr">
         <is>
           <t>Armes</t>
@@ -11859,11 +11874,11 @@
       <c r="F33" s="16" t="n"/>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>≈ 48 dégâts  ·  ≈ 6 armure  (5 cartes/6 visées)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1" s="100">
+          <t>≈ 48 dégâts  ·  ≈ 8 armure  (5 cartes/6 visées)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1" s="102">
       <c r="A34" s="17" t="inlineStr">
         <is>
           <t>Armes</t>
@@ -11900,7 +11915,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1" s="100">
+    <row r="35" ht="15" customHeight="1" s="102">
       <c r="A35" s="17" t="inlineStr">
         <is>
           <t>Armes</t>
@@ -11933,11 +11948,11 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>≈ 306 dégâts  ·  ≈ 24 armure  (8 cartes/6 visées · 1 buff)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="15" customHeight="1" s="100">
+          <t>≈ 306 dégâts  ·  ≈ 27 armure  (8 cartes/6 visées · 1 buff)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1" s="102">
       <c r="A36" s="17" t="inlineStr">
         <is>
           <t>Armes</t>
@@ -11974,7 +11989,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="15" customHeight="1" s="100">
+    <row r="37" ht="15" customHeight="1" s="102">
       <c r="A37" s="21" t="inlineStr">
         <is>
           <t>Armes</t>
@@ -12011,7 +12026,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="15" customHeight="1" s="100">
+    <row r="38" ht="15" customHeight="1" s="102">
       <c r="A38" s="53" t="inlineStr">
         <is>
           <t>Armes</t>
@@ -12048,7 +12063,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="15" customHeight="1" s="100">
+    <row r="39" ht="15" customHeight="1" s="102">
       <c r="A39" s="21" t="inlineStr">
         <is>
           <t>Armes</t>
@@ -12081,7 +12096,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="17.1" customHeight="1" s="100">
+    <row r="40" ht="17.1" customHeight="1" s="102">
       <c r="A40" s="47" t="inlineStr">
         <is>
           <t xml:space="preserve">  ▸ MAIN SECONDE / OFF-HAND</t>
@@ -12093,7 +12108,7 @@
       <c r="E40" s="48" t="n"/>
       <c r="F40" s="48" t="n"/>
     </row>
-    <row r="41" ht="15" customHeight="1" s="100">
+    <row r="41" ht="15" customHeight="1" s="102">
       <c r="A41" s="13" t="inlineStr">
         <is>
           <t>Main seconde / Off-hand</t>
@@ -12126,7 +12141,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="15" customHeight="1" s="100">
+    <row r="42" ht="15" customHeight="1" s="102">
       <c r="A42" s="13" t="inlineStr">
         <is>
           <t>Main seconde / Off-hand</t>
@@ -12155,11 +12170,11 @@
       <c r="F42" s="14" t="n"/>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>≈ 3 armure  (2 cartes/5 visées · 1 buff)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="15" customHeight="1" s="100">
+          <t>≈ 4 armure  (2 cartes/5 visées · 1 buff)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="15" customHeight="1" s="102">
       <c r="A43" s="13" t="inlineStr">
         <is>
           <t>Main seconde / Off-hand</t>
@@ -12192,7 +12207,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="15" customHeight="1" s="100">
+    <row r="44" ht="15" customHeight="1" s="102">
       <c r="A44" s="13" t="inlineStr">
         <is>
           <t>Main seconde / Off-hand</t>
@@ -12225,7 +12240,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="15" customHeight="1" s="100">
+    <row r="45" ht="15" customHeight="1" s="102">
       <c r="A45" s="13" t="inlineStr">
         <is>
           <t>Main seconde / Off-hand</t>
@@ -12258,7 +12273,7 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="15" customHeight="1" s="100">
+    <row r="46" ht="15" customHeight="1" s="102">
       <c r="A46" s="13" t="inlineStr">
         <is>
           <t>Main seconde / Off-hand</t>
@@ -12287,11 +12302,11 @@
       <c r="F46" s="14" t="n"/>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>≈ 9 armure  (3 cartes/5 visées)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="15" customHeight="1" s="100">
+          <t>≈ 12 armure  (3 cartes/5 visées)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="15" customHeight="1" s="102">
       <c r="A47" s="15" t="inlineStr">
         <is>
           <t>Main seconde / Off-hand</t>
@@ -12324,7 +12339,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="15" customHeight="1" s="100">
+    <row r="48" ht="15" customHeight="1" s="102">
       <c r="A48" s="15" t="inlineStr">
         <is>
           <t>Main seconde / Off-hand</t>
@@ -12353,11 +12368,11 @@
       <c r="F48" s="16" t="n"/>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>≈ 14 armure  (4 cartes/6 visées)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="15" customHeight="1" s="100">
+          <t>≈ 18 armure  (4 cartes/6 visées)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="15" customHeight="1" s="102">
       <c r="A49" s="15" t="inlineStr">
         <is>
           <t>Main seconde / Off-hand</t>
@@ -12390,7 +12405,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="15" customHeight="1" s="100">
+    <row r="50" ht="15" customHeight="1" s="102">
       <c r="A50" s="15" t="inlineStr">
         <is>
           <t>Main seconde / Off-hand</t>
@@ -12423,7 +12438,7 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="15" customHeight="1" s="100">
+    <row r="51" ht="15" customHeight="1" s="102">
       <c r="A51" s="15" t="inlineStr">
         <is>
           <t>Main seconde / Off-hand</t>
@@ -12456,11 +12471,11 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>≈ 16 armure  (3 cartes/6 visées)</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="15" customHeight="1" s="100">
+          <t>≈ 20 armure  (3 cartes/6 visées)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="15" customHeight="1" s="102">
       <c r="A52" s="17" t="inlineStr">
         <is>
           <t>Main seconde / Off-hand</t>
@@ -12488,16 +12503,16 @@
       </c>
       <c r="F52" s="18" t="inlineStr">
         <is>
-          <t>When hit by a melee attack, gain 2 Stone.</t>
+          <t>When hit by a melee attack, gain 3 Stone.</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>≈ 48 dégâts  ·  ≈ 47 armure  (6 cartes/6 visées)</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="17.1" customHeight="1" s="100">
+          <t>≈ 48 dégâts  ·  ≈ 54 armure  (6 cartes/6 visées)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="17.1" customHeight="1" s="102">
       <c r="A53" s="47" t="inlineStr">
         <is>
           <t xml:space="preserve">  ▸ ARMURES</t>
@@ -12509,7 +12524,7 @@
       <c r="E53" s="48" t="n"/>
       <c r="F53" s="48" t="n"/>
     </row>
-    <row r="54" ht="15" customHeight="1" s="100">
+    <row r="54" ht="15" customHeight="1" s="102">
       <c r="A54" s="13" t="inlineStr">
         <is>
           <t>Armures</t>
@@ -12542,11 +12557,11 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>≈ 14 armure  (4 cartes/5 visées)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="15" customHeight="1" s="100">
+          <t>≈ 18 armure  (4 cartes/5 visées)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="15" customHeight="1" s="102">
       <c r="A55" s="13" t="inlineStr">
         <is>
           <t>Armures</t>
@@ -12579,11 +12594,11 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>≈ 3 armure  (2 cartes/5 visées · 1 buff)</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="15" customHeight="1" s="100">
+          <t>≈ 4 armure  (2 cartes/5 visées · 1 buff)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="15" customHeight="1" s="102">
       <c r="A56" s="13" t="inlineStr">
         <is>
           <t>Armures</t>
@@ -12616,11 +12631,11 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>≈ 9 armure  (3 cartes/5 visées)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="15" customHeight="1" s="100">
+          <t>≈ 12 armure  (3 cartes/5 visées)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="15" customHeight="1" s="102">
       <c r="A57" s="13" t="inlineStr">
         <is>
           <t>Armures</t>
@@ -12653,11 +12668,11 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>≈ 6 armure  (4 cartes/5 visées · 2 buff)</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="15" customHeight="1" s="100">
+          <t>≈ 8 armure  (4 cartes/5 visées · 2 buff)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="15" customHeight="1" s="102">
       <c r="A58" s="13" t="inlineStr">
         <is>
           <t>Armures</t>
@@ -12690,11 +12705,11 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>≈ 9 armure  (4 cartes/5 visées · 1 buff)</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="15" customHeight="1" s="100">
+          <t>≈ 12 armure  (4 cartes/5 visées · 1 buff)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="15" customHeight="1" s="102">
       <c r="A59" s="15" t="inlineStr">
         <is>
           <t>Armures</t>
@@ -12727,238 +12742,238 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
+          <t>≈ 36 armure  (4 cartes/6 visées)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="15" customHeight="1" s="102">
+      <c r="A60" s="15" t="inlineStr">
+        <is>
+          <t>Armures</t>
+        </is>
+      </c>
+      <c r="B60" s="15" t="inlineStr">
+        <is>
+          <t>Berserker Hide</t>
+        </is>
+      </c>
+      <c r="C60" s="15" t="inlineStr">
+        <is>
+          <t>peau-berserk</t>
+        </is>
+      </c>
+      <c r="D60" s="15" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="E60" s="16" t="inlineStr">
+        <is>
+          <t>Rage×1, Standard Armor×1, Unstoppable×1, Free Movement×1</t>
+        </is>
+      </c>
+      <c r="F60" s="16" t="inlineStr">
+        <is>
+          <t>Armure début: 4</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>≈ 6 armure  (4 cartes/6 visées · 3 buff)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="15" customHeight="1" s="102">
+      <c r="A61" s="15" t="inlineStr">
+        <is>
+          <t>Armures</t>
+        </is>
+      </c>
+      <c r="B61" s="15" t="inlineStr">
+        <is>
+          <t>Spiked Armor</t>
+        </is>
+      </c>
+      <c r="C61" s="15" t="inlineStr">
+        <is>
+          <t>armure-cloutee</t>
+        </is>
+      </c>
+      <c r="D61" s="15" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="E61" s="16" t="inlineStr">
+        <is>
+          <t>Standard Armor×3, Rebound×1</t>
+        </is>
+      </c>
+      <c r="F61" s="16" t="inlineStr">
+        <is>
+          <t>Armure début: 10  ·  When hit by a melee attack, the attacker takes 2 damage.</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
           <t>≈ 30 armure  (4 cartes/6 visées)</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="15" customHeight="1" s="100">
-      <c r="A60" s="15" t="inlineStr">
+    <row r="62" ht="15" customHeight="1" s="102">
+      <c r="A62" s="15" t="inlineStr">
         <is>
           <t>Armures</t>
         </is>
       </c>
-      <c r="B60" s="15" t="inlineStr">
-        <is>
-          <t>Berserker Hide</t>
-        </is>
-      </c>
-      <c r="C60" s="15" t="inlineStr">
-        <is>
-          <t>peau-berserk</t>
-        </is>
-      </c>
-      <c r="D60" s="15" t="inlineStr">
+      <c r="B62" s="15" t="inlineStr">
+        <is>
+          <t>Stone Armor</t>
+        </is>
+      </c>
+      <c r="C62" s="15" t="inlineStr">
+        <is>
+          <t>armure-stone-age</t>
+        </is>
+      </c>
+      <c r="D62" s="15" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E60" s="16" t="inlineStr">
-        <is>
-          <t>Rage×1, Standard Armor×1, Unstoppable×1, Free Movement×1</t>
-        </is>
-      </c>
-      <c r="F60" s="16" t="inlineStr">
-        <is>
-          <t>Armure début: 4</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>≈ 5 armure  (4 cartes/6 visées · 3 buff)</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="15" customHeight="1" s="100">
-      <c r="A61" s="15" t="inlineStr">
+      <c r="E62" s="16" t="inlineStr">
+        <is>
+          <t>Stone×6, Many Stone×3, Stone Coagulation×1</t>
+        </is>
+      </c>
+      <c r="F62" s="16" t="inlineStr">
+        <is>
+          <t>Armure début: 12  ·  Set: Stone Age Set</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>≈ 102 armure  (10 cartes/6 visées)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="15" customHeight="1" s="102">
+      <c r="A63" s="17" t="inlineStr">
         <is>
           <t>Armures</t>
         </is>
       </c>
-      <c r="B61" s="15" t="inlineStr">
-        <is>
-          <t>Spiked Armor</t>
-        </is>
-      </c>
-      <c r="C61" s="15" t="inlineStr">
-        <is>
-          <t>armure-cloutee</t>
-        </is>
-      </c>
-      <c r="D61" s="15" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="E61" s="16" t="inlineStr">
-        <is>
-          <t>Standard Armor×3, Rebound×1</t>
-        </is>
-      </c>
-      <c r="F61" s="16" t="inlineStr">
-        <is>
-          <t>Armure début: 10  ·  When hit by a melee attack, the attacker takes 2 damage.</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>≈ 25 armure  (4 cartes/6 visées)</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="15" customHeight="1" s="100">
-      <c r="A62" s="15" t="inlineStr">
+      <c r="B63" s="17" t="inlineStr">
+        <is>
+          <t>Blood Plate</t>
+        </is>
+      </c>
+      <c r="C63" s="17" t="inlineStr">
+        <is>
+          <t>plate-sang</t>
+        </is>
+      </c>
+      <c r="D63" s="17" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="E63" s="18" t="inlineStr">
+        <is>
+          <t>Heavy Armor×2, Sanguine Guard×2, Bloodbath×1, Drink blood×1</t>
+        </is>
+      </c>
+      <c r="F63" s="18" t="inlineStr">
+        <is>
+          <t>Armure début: 20 - +3 stone a chaque tour (permanent)  ·  Set: Blood Set</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>≈ 60 dégâts  ·  ≈ 54 armure  (6 cartes/6 visées)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="15" customHeight="1" s="102">
+      <c r="A64" s="17" t="inlineStr">
         <is>
           <t>Armures</t>
         </is>
       </c>
-      <c r="B62" s="15" t="inlineStr">
-        <is>
-          <t>Stone Armor</t>
-        </is>
-      </c>
-      <c r="C62" s="15" t="inlineStr">
-        <is>
-          <t>armure-stone-age</t>
-        </is>
-      </c>
-      <c r="D62" s="15" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="E62" s="16" t="inlineStr">
-        <is>
-          <t>Stone×6, Many Stone×3, Stone Coagulation×1</t>
-        </is>
-      </c>
-      <c r="F62" s="16" t="inlineStr">
-        <is>
-          <t>Armure début: 12  ·  Set: Stone Age Set</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>≈ 85 armure  (10 cartes/6 visées)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="15" customHeight="1" s="100">
-      <c r="A63" s="17" t="inlineStr">
+      <c r="B64" s="17" t="inlineStr">
+        <is>
+          <t>Crusader Plate</t>
+        </is>
+      </c>
+      <c r="C64" s="17" t="inlineStr">
+        <is>
+          <t>plate-croise</t>
+        </is>
+      </c>
+      <c r="D64" s="17" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="E64" s="18" t="inlineStr">
+        <is>
+          <t>Heavy Armor×1, Armor of light×3, Blinding Flash×1, Holy light×1</t>
+        </is>
+      </c>
+      <c r="F64" s="18" t="inlineStr">
+        <is>
+          <t>Armure début: 30 - +5 stone a chaque tour (permanent)  ·  Set: Crusader Set</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>≈ 60 dégâts  ·  ≈ 63 armure  (6 cartes/6 visées)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="15" customHeight="1" s="102">
+      <c r="A65" s="17" t="inlineStr">
         <is>
           <t>Armures</t>
         </is>
       </c>
-      <c r="B63" s="17" t="inlineStr">
-        <is>
-          <t>Blood Plate</t>
-        </is>
-      </c>
-      <c r="C63" s="17" t="inlineStr">
-        <is>
-          <t>plate-sang</t>
-        </is>
-      </c>
-      <c r="D63" s="17" t="inlineStr">
+      <c r="B65" s="17" t="inlineStr">
+        <is>
+          <t>Forgemaster's Mail</t>
+        </is>
+      </c>
+      <c r="C65" s="17" t="inlineStr">
+        <is>
+          <t>maille-de-forge</t>
+        </is>
+      </c>
+      <c r="D65" s="17" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="E63" s="18" t="inlineStr">
-        <is>
-          <t>Heavy Armor×2, Sanguine Guard×2, Bloodbath×1, Drink blood×1</t>
-        </is>
-      </c>
-      <c r="F63" s="18" t="inlineStr">
-        <is>
-          <t>Armure début: 20 - +4 stone a chaque tour (permanent)  ·  Set: Blood Set</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t>≈ 60 dégâts  ·  ≈ 48 armure  (6 cartes/6 visées)</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="15" customHeight="1" s="100">
-      <c r="A64" s="17" t="inlineStr">
+      <c r="E65" s="18" t="inlineStr">
+        <is>
+          <t>Mail Armor×3, Quench×1, Heavy Armor×2</t>
+        </is>
+      </c>
+      <c r="F65" s="18" t="inlineStr">
+        <is>
+          <t>Armure début: 22 - +4 stone a chaque tour (permanent)  ·  Set: Mail Set</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>≈ 63 armure  (6 cartes/6 visées · 1 buff)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="15" customHeight="1" s="102">
+      <c r="A66" s="21" t="inlineStr">
         <is>
           <t>Armures</t>
         </is>
       </c>
-      <c r="B64" s="17" t="inlineStr">
-        <is>
-          <t>Crusader Plate</t>
-        </is>
-      </c>
-      <c r="C64" s="17" t="inlineStr">
-        <is>
-          <t>plate-croise</t>
-        </is>
-      </c>
-      <c r="D64" s="17" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="E64" s="18" t="inlineStr">
-        <is>
-          <t>Heavy Armor×1, Armor of light×3, Blinding Flash×1, Holy light×1</t>
-        </is>
-      </c>
-      <c r="F64" s="18" t="inlineStr">
-        <is>
-          <t>Armure début: 30 - +6 stone a chaque tour (permanent)  ·  Set: Crusader Set</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>≈ 60 dégâts  ·  ≈ 56 armure  (6 cartes/6 visées)</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="15" customHeight="1" s="100">
-      <c r="A65" s="17" t="inlineStr">
-        <is>
-          <t>Armures</t>
-        </is>
-      </c>
-      <c r="B65" s="17" t="inlineStr">
-        <is>
-          <t>Forgemaster's Mail</t>
-        </is>
-      </c>
-      <c r="C65" s="17" t="inlineStr">
-        <is>
-          <t>maille-de-forge</t>
-        </is>
-      </c>
-      <c r="D65" s="17" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="E65" s="18" t="inlineStr">
-        <is>
-          <t>Mail Armor×3, Quench×1, Heavy Armor×2</t>
-        </is>
-      </c>
-      <c r="F65" s="18" t="inlineStr">
-        <is>
-          <t>Armure début: 22 - +5 stone a chaque tour (permanent)  ·  Set: Mail Set</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="inlineStr">
-        <is>
-          <t>≈ 56 armure  (6 cartes/6 visées · 1 buff)</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="15" customHeight="1" s="100">
-      <c r="A66" s="21" t="inlineStr">
-        <is>
-          <t>Armures</t>
-        </is>
-      </c>
       <c r="B66" s="21" t="inlineStr">
         <is>
           <t>Onyx Guard Plate</t>
@@ -12981,16 +12996,16 @@
       </c>
       <c r="F66" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Armure début: 36 - +10 stone a chaque tour (permanent) ·  Set: Onyx Set </t>
+          <t xml:space="preserve">Armure début: 36 - +8 stone a chaque tour (permanent) ·  Set: Onyx Set </t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>≈ 204 dégâts  ·  ≈ 72 armure  (7 cartes/7 visées)</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="17.1" customHeight="1" s="100">
+          <t>≈ 204 dégâts  ·  ≈ 84 armure  (7 cartes/7 visées)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="17.1" customHeight="1" s="102">
       <c r="A67" s="47" t="inlineStr">
         <is>
           <t xml:space="preserve">  ▸ COLLIERS</t>
@@ -13002,7 +13017,7 @@
       <c r="E67" s="48" t="n"/>
       <c r="F67" s="48" t="n"/>
     </row>
-    <row r="68" ht="15" customHeight="1" s="100">
+    <row r="68" ht="15" customHeight="1" s="102">
       <c r="A68" s="13" t="inlineStr">
         <is>
           <t>Colliers</t>
@@ -13035,7 +13050,7 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="15" customHeight="1" s="100">
+    <row r="69" ht="15" customHeight="1" s="102">
       <c r="A69" s="13" t="inlineStr">
         <is>
           <t>Colliers</t>
@@ -13068,7 +13083,7 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="15" customHeight="1" s="100">
+    <row r="70" ht="15" customHeight="1" s="102">
       <c r="A70" s="13" t="inlineStr">
         <is>
           <t>Colliers</t>
@@ -13101,7 +13116,7 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="15" customHeight="1" s="100">
+    <row r="71" ht="15" customHeight="1" s="102">
       <c r="A71" s="13" t="inlineStr">
         <is>
           <t>Colliers</t>
@@ -13134,7 +13149,7 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="15" customHeight="1" s="100">
+    <row r="72" ht="15" customHeight="1" s="102">
       <c r="A72" s="13" t="inlineStr">
         <is>
           <t>Colliers</t>
@@ -13167,7 +13182,7 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="15" customHeight="1" s="100">
+    <row r="73" ht="15" customHeight="1" s="102">
       <c r="A73" s="15" t="inlineStr">
         <is>
           <t>Colliers</t>
@@ -13200,7 +13215,7 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="15" customHeight="1" s="100">
+    <row r="74" ht="15" customHeight="1" s="102">
       <c r="A74" s="15" t="inlineStr">
         <is>
           <t>Colliers</t>
@@ -13233,7 +13248,7 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="15" customHeight="1" s="100">
+    <row r="75" ht="15" customHeight="1" s="102">
       <c r="A75" s="15" t="inlineStr">
         <is>
           <t>Colliers</t>
@@ -13266,7 +13281,7 @@
         </is>
       </c>
     </row>
-    <row r="76" ht="15" customHeight="1" s="100">
+    <row r="76" ht="15" customHeight="1" s="102">
       <c r="A76" s="15" t="inlineStr">
         <is>
           <t>Colliers</t>
@@ -13299,7 +13314,7 @@
         </is>
       </c>
     </row>
-    <row r="77" ht="15" customHeight="1" s="100">
+    <row r="77" ht="15" customHeight="1" s="102">
       <c r="A77" s="17" t="inlineStr">
         <is>
           <t>Colliers</t>
@@ -13332,7 +13347,7 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="15" customHeight="1" s="100">
+    <row r="78" ht="15" customHeight="1" s="102">
       <c r="A78" s="21" t="inlineStr">
         <is>
           <t>Colliers</t>
@@ -13365,7 +13380,7 @@
         </is>
       </c>
     </row>
-    <row r="79" ht="17.1" customHeight="1" s="100">
+    <row r="79" ht="17.1" customHeight="1" s="102">
       <c r="A79" s="47" t="inlineStr">
         <is>
           <t xml:space="preserve">  ▸ BAGUES</t>
@@ -13377,7 +13392,7 @@
       <c r="E79" s="48" t="n"/>
       <c r="F79" s="48" t="n"/>
     </row>
-    <row r="80" ht="15" customHeight="1" s="100">
+    <row r="80" ht="15" customHeight="1" s="102">
       <c r="A80" s="13" t="inlineStr">
         <is>
           <t>Bagues</t>
@@ -13410,7 +13425,7 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="15" customHeight="1" s="100">
+    <row r="81" ht="15" customHeight="1" s="102">
       <c r="A81" s="13" t="inlineStr">
         <is>
           <t>Bagues</t>
@@ -13443,7 +13458,7 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="15" customHeight="1" s="100">
+    <row r="82" ht="15" customHeight="1" s="102">
       <c r="A82" s="13" t="inlineStr">
         <is>
           <t>Bagues</t>
@@ -13476,7 +13491,7 @@
         </is>
       </c>
     </row>
-    <row r="83" ht="15" customHeight="1" s="100">
+    <row r="83" ht="15" customHeight="1" s="102">
       <c r="A83" s="13" t="inlineStr">
         <is>
           <t>Bagues</t>
@@ -13509,7 +13524,7 @@
         </is>
       </c>
     </row>
-    <row r="84" ht="15" customHeight="1" s="100">
+    <row r="84" ht="15" customHeight="1" s="102">
       <c r="A84" s="13" t="inlineStr">
         <is>
           <t>Bagues</t>
@@ -13542,7 +13557,7 @@
         </is>
       </c>
     </row>
-    <row r="85" ht="15" customHeight="1" s="100">
+    <row r="85" ht="15" customHeight="1" s="102">
       <c r="A85" s="13" t="inlineStr">
         <is>
           <t>Bagues</t>
@@ -13575,7 +13590,7 @@
         </is>
       </c>
     </row>
-    <row r="86" ht="15" customHeight="1" s="100">
+    <row r="86" ht="15" customHeight="1" s="102">
       <c r="A86" s="13" t="inlineStr">
         <is>
           <t>Bagues</t>
@@ -13604,11 +13619,11 @@
       <c r="F86" s="14" t="n"/>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>≈ 6 armure  (2 cartes/5 visées)</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="15" customHeight="1" s="100">
+          <t>≈ 8 armure  (2 cartes/5 visées)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="15" customHeight="1" s="102">
       <c r="A87" s="13" t="inlineStr">
         <is>
           <t>Bagues</t>
@@ -13641,7 +13656,7 @@
         </is>
       </c>
     </row>
-    <row r="88" ht="15" customHeight="1" s="100">
+    <row r="88" ht="15" customHeight="1" s="102">
       <c r="A88" s="13" t="inlineStr">
         <is>
           <t>Bagues</t>
@@ -13670,11 +13685,11 @@
       <c r="F88" s="14" t="n"/>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>≈ 3 armure  (2 cartes/5 visées · 1 buff)</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="15" customHeight="1" s="100">
+          <t>≈ 4 armure  (2 cartes/5 visées · 1 buff)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="15" customHeight="1" s="102">
       <c r="A89" s="15" t="inlineStr">
         <is>
           <t>Bagues</t>
@@ -13707,7 +13722,7 @@
         </is>
       </c>
     </row>
-    <row r="90" ht="15" customHeight="1" s="100">
+    <row r="90" ht="15" customHeight="1" s="102">
       <c r="A90" s="15" t="inlineStr">
         <is>
           <t>Bagues</t>
@@ -13740,7 +13755,7 @@
         </is>
       </c>
     </row>
-    <row r="91" ht="15" customHeight="1" s="100">
+    <row r="91" ht="15" customHeight="1" s="102">
       <c r="A91" s="15" t="inlineStr">
         <is>
           <t>Bagues</t>
@@ -13773,7 +13788,7 @@
         </is>
       </c>
     </row>
-    <row r="92" ht="15" customHeight="1" s="100">
+    <row r="92" ht="15" customHeight="1" s="102">
       <c r="A92" s="15" t="inlineStr">
         <is>
           <t>Bagues</t>
@@ -13806,7 +13821,7 @@
         </is>
       </c>
     </row>
-    <row r="93" ht="15" customHeight="1" s="100">
+    <row r="93" ht="15" customHeight="1" s="102">
       <c r="A93" s="15" t="inlineStr">
         <is>
           <t>Bagues</t>
@@ -13839,7 +13854,7 @@
         </is>
       </c>
     </row>
-    <row r="94" ht="15" customHeight="1" s="100">
+    <row r="94" ht="15" customHeight="1" s="102">
       <c r="A94" s="15" t="inlineStr">
         <is>
           <t>Bagues</t>
@@ -13868,11 +13883,11 @@
       <c r="F94" s="16" t="n"/>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>≈ 6 armure  (2 cartes/6 visées)</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="15" customHeight="1" s="100">
+          <t>≈ 8 armure  (2 cartes/6 visées)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="15" customHeight="1" s="102">
       <c r="A95" s="15" t="inlineStr">
         <is>
           <t>Bagues</t>
@@ -13905,7 +13920,7 @@
         </is>
       </c>
     </row>
-    <row r="96" ht="15" customHeight="1" s="100">
+    <row r="96" ht="15" customHeight="1" s="102">
       <c r="A96" s="15" t="inlineStr">
         <is>
           <t>Bagues</t>
@@ -13938,7 +13953,7 @@
         </is>
       </c>
     </row>
-    <row r="97" ht="15" customHeight="1" s="100">
+    <row r="97" ht="15" customHeight="1" s="102">
       <c r="A97" s="17" t="inlineStr">
         <is>
           <t>Bagues</t>
@@ -13971,7 +13986,7 @@
         </is>
       </c>
     </row>
-    <row r="98" ht="17.1" customHeight="1" s="100">
+    <row r="98" ht="17.1" customHeight="1" s="102">
       <c r="A98" s="47" t="inlineStr">
         <is>
           <t xml:space="preserve">  ▸ GANTS</t>
@@ -13983,7 +13998,7 @@
       <c r="E98" s="48" t="n"/>
       <c r="F98" s="48" t="n"/>
     </row>
-    <row r="99" ht="15" customHeight="1" s="100">
+    <row r="99" ht="15" customHeight="1" s="102">
       <c r="A99" s="13" t="inlineStr">
         <is>
           <t>Gants</t>
@@ -14016,7 +14031,7 @@
         </is>
       </c>
     </row>
-    <row r="100" ht="15" customHeight="1" s="100">
+    <row r="100" ht="15" customHeight="1" s="102">
       <c r="A100" s="13" t="inlineStr">
         <is>
           <t>Gants</t>
@@ -14045,11 +14060,11 @@
       <c r="F100" s="14" t="n"/>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>≈ 3 armure  (2 cartes/5 visées · 1 buff)</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="15" customHeight="1" s="100">
+          <t>≈ 4 armure  (2 cartes/5 visées · 1 buff)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="15" customHeight="1" s="102">
       <c r="A101" s="13" t="inlineStr">
         <is>
           <t>Gants</t>
@@ -14082,7 +14097,7 @@
         </is>
       </c>
     </row>
-    <row r="102" ht="15" customHeight="1" s="100">
+    <row r="102" ht="15" customHeight="1" s="102">
       <c r="A102" s="13" t="inlineStr">
         <is>
           <t>Gants</t>
@@ -14115,7 +14130,7 @@
         </is>
       </c>
     </row>
-    <row r="103" ht="15" customHeight="1" s="100">
+    <row r="103" ht="15" customHeight="1" s="102">
       <c r="A103" s="13" t="inlineStr">
         <is>
           <t>Gants</t>
@@ -14148,7 +14163,7 @@
         </is>
       </c>
     </row>
-    <row r="104" ht="15" customHeight="1" s="100">
+    <row r="104" ht="15" customHeight="1" s="102">
       <c r="A104" s="15" t="inlineStr">
         <is>
           <t>Gants</t>
@@ -14177,11 +14192,11 @@
       <c r="F104" s="16" t="n"/>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>≈ 16 dégâts  ·  ≈ 3 armure  (2 cartes/6 visées)</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="15" customHeight="1" s="100">
+          <t>≈ 16 dégâts  ·  ≈ 4 armure  (2 cartes/6 visées)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="15" customHeight="1" s="102">
       <c r="A105" s="15" t="inlineStr">
         <is>
           <t>Gants</t>
@@ -14214,7 +14229,7 @@
         </is>
       </c>
     </row>
-    <row r="106" ht="15" customHeight="1" s="100">
+    <row r="106" ht="15" customHeight="1" s="102">
       <c r="A106" s="15" t="inlineStr">
         <is>
           <t>Gants</t>
@@ -14247,11 +14262,11 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>≈ 30 armure  (5 cartes/6 visées · 1 buff)</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="15" customHeight="1" s="100">
+          <t>≈ 36 armure  (5 cartes/6 visées · 1 buff)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="15" customHeight="1" s="102">
       <c r="A107" s="15" t="inlineStr">
         <is>
           <t>Gants</t>
@@ -14284,7 +14299,7 @@
         </is>
       </c>
     </row>
-    <row r="108" ht="15" customHeight="1" s="100">
+    <row r="108" ht="15" customHeight="1" s="102">
       <c r="A108" s="15" t="inlineStr">
         <is>
           <t>Gants</t>
@@ -14317,7 +14332,7 @@
         </is>
       </c>
     </row>
-    <row r="109" ht="15" customHeight="1" s="100">
+    <row r="109" ht="15" customHeight="1" s="102">
       <c r="A109" s="17" t="inlineStr">
         <is>
           <t>Gants</t>
@@ -14354,7 +14369,7 @@
         </is>
       </c>
     </row>
-    <row r="110" ht="15" customHeight="1" s="100">
+    <row r="110" ht="15" customHeight="1" s="102">
       <c r="A110" s="17" t="inlineStr">
         <is>
           <t>Gants</t>
@@ -14391,7 +14406,7 @@
         </is>
       </c>
     </row>
-    <row r="111" ht="15" customHeight="1" s="100">
+    <row r="111" ht="15" customHeight="1" s="102">
       <c r="A111" s="17" t="inlineStr">
         <is>
           <t>Gants</t>
@@ -14428,7 +14443,7 @@
         </is>
       </c>
     </row>
-    <row r="112" ht="15" customHeight="1" s="100">
+    <row r="112" ht="15" customHeight="1" s="102">
       <c r="A112" s="21" t="inlineStr">
         <is>
           <t>Gants</t>
@@ -14465,7 +14480,7 @@
         </is>
       </c>
     </row>
-    <row r="113" ht="17.1" customHeight="1" s="100">
+    <row r="113" ht="17.1" customHeight="1" s="102">
       <c r="A113" s="47" t="inlineStr">
         <is>
           <t xml:space="preserve">  ▸ BOTTES</t>
@@ -14477,7 +14492,7 @@
       <c r="E113" s="48" t="n"/>
       <c r="F113" s="48" t="n"/>
     </row>
-    <row r="114" ht="15" customHeight="1" s="100">
+    <row r="114" ht="15" customHeight="1" s="102">
       <c r="A114" s="13" t="inlineStr">
         <is>
           <t>Bottes</t>
@@ -14514,7 +14529,7 @@
         </is>
       </c>
     </row>
-    <row r="115" ht="15" customHeight="1" s="100">
+    <row r="115" ht="15" customHeight="1" s="102">
       <c r="A115" s="13" t="inlineStr">
         <is>
           <t>Bottes</t>
@@ -14551,7 +14566,7 @@
         </is>
       </c>
     </row>
-    <row r="116" ht="15" customHeight="1" s="100">
+    <row r="116" ht="15" customHeight="1" s="102">
       <c r="A116" s="13" t="inlineStr">
         <is>
           <t>Bottes</t>
@@ -14588,7 +14603,7 @@
         </is>
       </c>
     </row>
-    <row r="117" ht="15" customHeight="1" s="100">
+    <row r="117" ht="15" customHeight="1" s="102">
       <c r="A117" s="13" t="inlineStr">
         <is>
           <t>Bottes</t>
@@ -14625,7 +14640,7 @@
         </is>
       </c>
     </row>
-    <row r="118" ht="15" customHeight="1" s="100">
+    <row r="118" ht="15" customHeight="1" s="102">
       <c r="A118" s="15" t="inlineStr">
         <is>
           <t>Bottes</t>
@@ -14662,7 +14677,7 @@
         </is>
       </c>
     </row>
-    <row r="119" ht="15" customHeight="1" s="100">
+    <row r="119" ht="15" customHeight="1" s="102">
       <c r="A119" s="15" t="inlineStr">
         <is>
           <t>Bottes</t>
@@ -14695,11 +14710,11 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>≈ 30 armure  (5 cartes/6 visées · 1 buff)</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="15" customHeight="1" s="100">
+          <t>≈ 36 armure  (5 cartes/6 visées · 1 buff)</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="15" customHeight="1" s="102">
       <c r="A120" s="15" t="inlineStr">
         <is>
           <t>Bottes</t>
@@ -14732,11 +14747,11 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>≈ 24 dégâts  ·  ≈ 3 armure  (2 cartes/6 visées)</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="15" customHeight="1" s="100">
+          <t>≈ 24 dégâts  ·  ≈ 4 armure  (2 cartes/6 visées)</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="15" customHeight="1" s="102">
       <c r="A121" s="15" t="inlineStr">
         <is>
           <t>Bottes</t>
@@ -14773,7 +14788,7 @@
         </is>
       </c>
     </row>
-    <row r="122" ht="15" customHeight="1" s="100">
+    <row r="122" ht="15" customHeight="1" s="102">
       <c r="A122" s="15" t="inlineStr">
         <is>
           <t>Bottes</t>
@@ -14810,7 +14825,7 @@
         </is>
       </c>
     </row>
-    <row r="123" ht="15" customHeight="1" s="100">
+    <row r="123" ht="15" customHeight="1" s="102">
       <c r="A123" s="17" t="inlineStr">
         <is>
           <t>Bottes</t>
@@ -14847,7 +14862,7 @@
         </is>
       </c>
     </row>
-    <row r="124" ht="15" customHeight="1" s="100">
+    <row r="124" ht="15" customHeight="1" s="102">
       <c r="A124" s="17" t="inlineStr">
         <is>
           <t>Bottes</t>
@@ -14884,7 +14899,7 @@
         </is>
       </c>
     </row>
-    <row r="125" ht="15" customHeight="1" s="100">
+    <row r="125" ht="15" customHeight="1" s="102">
       <c r="A125" s="17" t="inlineStr">
         <is>
           <t>Bottes</t>
@@ -14921,7 +14936,7 @@
         </is>
       </c>
     </row>
-    <row r="126" ht="15" customHeight="1" s="100">
+    <row r="126" ht="15" customHeight="1" s="102">
       <c r="A126" s="21" t="inlineStr">
         <is>
           <t>Bottes</t>
@@ -14947,18 +14962,18 @@
           <t>Burning Run×1, Flaming Kick×1, Fire Boost×2, Boost×2</t>
         </is>
       </c>
-      <c r="F126" s="22" t="inlineStr">
-        <is>
-          <t>+18 Agilité  ·  +50% déplacement  ·  Set: Onyx Set</t>
+      <c r="F126" s="100" t="inlineStr">
+        <is>
+          <t>+18 Agilité  ·  +40% déplacement  ·  Set: Onyx Set</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>≈ 17 dégâts  (6 cartes/7 visées · 5 buff)</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="17.1" customHeight="1" s="100">
+          <t>aucun dégât/armure  (6 cartes/7 visées · 6 buff)</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="17.1" customHeight="1" s="102">
       <c r="A127" s="47" t="inlineStr">
         <is>
           <t xml:space="preserve">  ▸ SACS</t>
@@ -14970,7 +14985,7 @@
       <c r="E127" s="48" t="n"/>
       <c r="F127" s="48" t="n"/>
     </row>
-    <row r="128" ht="15" customHeight="1" s="100">
+    <row r="128" ht="15" customHeight="1" s="102">
       <c r="A128" s="13" t="inlineStr">
         <is>
           <t>Sacs</t>
@@ -15007,7 +15022,7 @@
         </is>
       </c>
     </row>
-    <row r="129" ht="15" customHeight="1" s="100">
+    <row r="129" ht="15" customHeight="1" s="102">
       <c r="A129" s="15" t="inlineStr">
         <is>
           <t>Sacs</t>
@@ -15044,7 +15059,7 @@
         </is>
       </c>
     </row>
-    <row r="130" ht="15" customHeight="1" s="100">
+    <row r="130" ht="15" customHeight="1" s="102">
       <c r="A130" s="17" t="inlineStr">
         <is>
           <t>Sacs</t>
@@ -15081,7 +15096,7 @@
         </is>
       </c>
     </row>
-    <row r="131" ht="15" customHeight="1" s="100">
+    <row r="131" ht="15" customHeight="1" s="102">
       <c r="A131" s="17" t="inlineStr">
         <is>
           <t>Sacs</t>
@@ -15118,7 +15133,7 @@
         </is>
       </c>
     </row>
-    <row r="132" ht="15" customHeight="1" s="100">
+    <row r="132" ht="15" customHeight="1" s="102">
       <c r="A132" s="21" t="inlineStr">
         <is>
           <t>Sacs</t>
@@ -15155,7 +15170,7 @@
         </is>
       </c>
     </row>
-    <row r="133" ht="15" customHeight="1" s="100">
+    <row r="133" ht="15" customHeight="1" s="102">
       <c r="A133" s="49" t="inlineStr">
         <is>
           <t>Sacs</t>
@@ -15192,7 +15207,7 @@
         </is>
       </c>
     </row>
-    <row r="134" ht="15" customHeight="1" s="100">
+    <row r="134" ht="15" customHeight="1" s="102">
       <c r="A134" s="55" t="n"/>
       <c r="B134" s="55" t="n"/>
       <c r="C134" s="55" t="n"/>
@@ -15200,7 +15215,7 @@
       <c r="E134" s="55" t="n"/>
       <c r="F134" s="55" t="n"/>
     </row>
-    <row r="135" ht="15" customHeight="1" s="100">
+    <row r="135" ht="15" customHeight="1" s="102">
       <c r="A135" s="55" t="n"/>
       <c r="B135" s="55" t="n"/>
       <c r="C135" s="55" t="n"/>
@@ -15208,7 +15223,7 @@
       <c r="E135" s="55" t="n"/>
       <c r="F135" s="55" t="n"/>
     </row>
-    <row r="136" ht="15" customHeight="1" s="100">
+    <row r="136" ht="15" customHeight="1" s="102">
       <c r="A136" s="55" t="n"/>
       <c r="B136" s="55" t="n"/>
       <c r="C136" s="55" t="n"/>
@@ -15216,7 +15231,7 @@
       <c r="E136" s="55" t="n"/>
       <c r="F136" s="55" t="n"/>
     </row>
-    <row r="137" ht="15" customHeight="1" s="100">
+    <row r="137" ht="15" customHeight="1" s="102">
       <c r="A137" s="55" t="n"/>
       <c r="B137" s="55" t="n"/>
       <c r="C137" s="55" t="n"/>
@@ -15224,7 +15239,7 @@
       <c r="E137" s="55" t="n"/>
       <c r="F137" s="55" t="n"/>
     </row>
-    <row r="138" ht="15" customHeight="1" s="100">
+    <row r="138" ht="15" customHeight="1" s="102">
       <c r="A138" s="55" t="n"/>
       <c r="B138" s="55" t="n"/>
       <c r="C138" s="55" t="n"/>
@@ -15232,7 +15247,7 @@
       <c r="E138" s="55" t="n"/>
       <c r="F138" s="55" t="n"/>
     </row>
-    <row r="139" ht="15" customHeight="1" s="100">
+    <row r="139" ht="15" customHeight="1" s="102">
       <c r="A139" s="55" t="n"/>
       <c r="B139" s="55" t="n"/>
       <c r="C139" s="55" t="n"/>
@@ -15240,7 +15255,7 @@
       <c r="E139" s="55" t="n"/>
       <c r="F139" s="55" t="n"/>
     </row>
-    <row r="140" ht="15" customHeight="1" s="100">
+    <row r="140" ht="15" customHeight="1" s="102">
       <c r="A140" s="55" t="n"/>
       <c r="B140" s="55" t="n"/>
       <c r="C140" s="55" t="n"/>
@@ -15248,7 +15263,7 @@
       <c r="E140" s="55" t="n"/>
       <c r="F140" s="55" t="n"/>
     </row>
-    <row r="141" ht="15" customHeight="1" s="100">
+    <row r="141" ht="15" customHeight="1" s="102">
       <c r="A141" s="55" t="n"/>
       <c r="B141" s="55" t="n"/>
       <c r="C141" s="55" t="n"/>
@@ -15271,10 +15286,10 @@
   <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" style="100" min="1" max="1"/>
-    <col width="46" customWidth="1" style="100" min="2" max="2"/>
-    <col width="22" customWidth="1" style="100" min="3" max="3"/>
-    <col width="60" customWidth="1" style="100" min="4" max="4"/>
+    <col width="20" customWidth="1" style="102" min="1" max="1"/>
+    <col width="46" customWidth="1" style="102" min="2" max="2"/>
+    <col width="22" customWidth="1" style="102" min="3" max="3"/>
+    <col width="60" customWidth="1" style="102" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15313,7 +15328,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1" s="100">
+    <row r="5" ht="30" customHeight="1" s="102">
       <c r="A5" s="44" t="inlineStr">
         <is>
           <t>Onyx Set</t>
@@ -15335,7 +15350,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1" s="100">
+    <row r="6" ht="30" customHeight="1" s="102">
       <c r="A6" s="44" t="inlineStr">
         <is>
           <t>Mail Set</t>
@@ -15353,11 +15368,11 @@
       </c>
       <c r="D6" s="44" t="inlineStr">
         <is>
-          <t>At the start of combat, gain 10 Stone per enemy faced.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1" s="100">
+          <t>At the start of combat, gain 8 Stone per enemy faced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1" s="102">
       <c r="A7" s="44" t="inlineStr">
         <is>
           <t>Crusader Set</t>
@@ -15379,7 +15394,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1" s="100">
+    <row r="8" ht="30" customHeight="1" s="102">
       <c r="A8" s="44" t="inlineStr">
         <is>
           <t>Blood Set</t>
@@ -15397,11 +15412,11 @@
       </c>
       <c r="D8" s="44" t="inlineStr">
         <is>
-          <t>When a Bleed combo deals bonus damage, heal the hero for that amount.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1" s="100">
+          <t>When a Bleed combo deals bonus damage, heal the hero for half of that amount.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1" s="102">
       <c r="A9" s="44" t="inlineStr">
         <is>
           <t>Stone Age Set</t>
@@ -15437,13 +15452,13 @@
   <dimension ref="A1:D87"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" style="100" min="1" max="1"/>
-    <col width="22" customWidth="1" style="100" min="2" max="2"/>
-    <col width="78" customWidth="1" style="100" min="3" max="3"/>
-    <col width="24" customWidth="1" style="100" min="4" max="4"/>
+    <col width="24" customWidth="1" style="102" min="1" max="1"/>
+    <col width="22" customWidth="1" style="102" min="2" max="2"/>
+    <col width="78" customWidth="1" style="102" min="3" max="3"/>
+    <col width="24" customWidth="1" style="102" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" s="100">
+    <row r="1" ht="30" customHeight="1" s="102">
       <c r="A1" s="43" t="inlineStr">
         <is>
           <t>BRUTAL — Effets disponibles dans le code</t>
@@ -15453,7 +15468,7 @@
       <c r="C1" s="43" t="n"/>
       <c r="D1" s="43" t="n"/>
     </row>
-    <row r="2" ht="60" customHeight="1" s="100">
+    <row r="2" ht="60" customHeight="1" s="102">
       <c r="A2" s="44" t="inlineStr">
         <is>
           <t>Récapitulatif de tous les types d'effets implémentés dans jeu/systems/combat.js. Tenu à jour à chaque nouvelle version.</t>
@@ -15501,7 +15516,7 @@
       <c r="C5" s="46" t="n"/>
       <c r="D5" s="46" t="n"/>
     </row>
-    <row r="6" ht="30" customHeight="1" s="100">
+    <row r="6" ht="30" customHeight="1" s="102">
       <c r="A6" s="44" t="inlineStr">
         <is>
           <t>degats</t>
@@ -15523,7 +15538,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1" s="100">
+    <row r="7" ht="30" customHeight="1" s="102">
       <c r="A7" s="44" t="inlineStr">
         <is>
           <t>pierre</t>
@@ -15545,7 +15560,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1" s="100">
+    <row r="8" ht="30" customHeight="1" s="102">
       <c r="A8" s="44" t="inlineStr">
         <is>
           <t>auto-degats</t>
@@ -15567,7 +15582,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1" s="100">
+    <row r="9" ht="30" customHeight="1" s="102">
       <c r="A9" s="44" t="inlineStr">
         <is>
           <t>soin-heros</t>
@@ -15589,7 +15604,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1" s="100">
+    <row r="10" ht="30" customHeight="1" s="102">
       <c r="A10" s="44" t="inlineStr">
         <is>
           <t>doublerPierre</t>
@@ -15611,7 +15626,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1" s="100">
+    <row r="11" ht="30" customHeight="1" s="102">
       <c r="A11" s="44" t="inlineStr">
         <is>
           <t>pierre-vers-degats</t>
@@ -15643,7 +15658,7 @@
       <c r="C12" s="46" t="n"/>
       <c r="D12" s="46" t="n"/>
     </row>
-    <row r="13" ht="30" customHeight="1" s="100">
+    <row r="13" ht="30" customHeight="1" s="102">
       <c r="A13" s="44" t="inlineStr">
         <is>
           <t>poison</t>
@@ -15665,7 +15680,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1" s="100">
+    <row r="14" ht="30" customHeight="1" s="102">
       <c r="A14" s="44" t="inlineStr">
         <is>
           <t>feu</t>
@@ -15687,7 +15702,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1" s="100">
+    <row r="15" ht="30" customHeight="1" s="102">
       <c r="A15" s="44" t="inlineStr">
         <is>
           <t>sang</t>
@@ -15709,7 +15724,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1" s="100">
+    <row r="16" ht="30" customHeight="1" s="102">
       <c r="A16" s="44" t="inlineStr">
         <is>
           <t>lenteur</t>
@@ -15731,7 +15746,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1" s="100">
+    <row r="17" ht="30" customHeight="1" s="102">
       <c r="A17" s="44" t="inlineStr">
         <is>
           <t>embrasement</t>
@@ -15753,7 +15768,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1" s="100">
+    <row r="18" ht="30" customHeight="1" s="102">
       <c r="A18" s="44" t="inlineStr">
         <is>
           <t>confusion</t>
@@ -15775,7 +15790,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1" s="100">
+    <row r="19" ht="30" customHeight="1" s="102">
       <c r="A19" s="44" t="inlineStr">
         <is>
           <t>stun</t>
@@ -15807,7 +15822,7 @@
       <c r="C20" s="46" t="n"/>
       <c r="D20" s="46" t="n"/>
     </row>
-    <row r="21" ht="30" customHeight="1" s="100">
+    <row r="21" ht="30" customHeight="1" s="102">
       <c r="A21" s="44" t="inlineStr">
         <is>
           <t>celerite</t>
@@ -15829,7 +15844,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="30" customHeight="1" s="100">
+    <row r="22" ht="30" customHeight="1" s="102">
       <c r="A22" s="44" t="inlineStr">
         <is>
           <t>regen</t>
@@ -15851,7 +15866,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="30" customHeight="1" s="100">
+    <row r="23" ht="30" customHeight="1" s="102">
       <c r="A23" s="44" t="inlineStr">
         <is>
           <t>force</t>
@@ -15873,7 +15888,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="24" customHeight="1" s="100">
+    <row r="24" ht="24" customHeight="1" s="102">
       <c r="A24" s="46" t="inlineStr">
         <is>
           <t>── ÉNERGIE (CHALEUR DE FORGE) ──</t>
@@ -15883,7 +15898,7 @@
       <c r="C24" s="46" t="n"/>
       <c r="D24" s="46" t="n"/>
     </row>
-    <row r="25" ht="30" customHeight="1" s="100">
+    <row r="25" ht="30" customHeight="1" s="102">
       <c r="A25" s="44" t="inlineStr">
         <is>
           <t>chaleur</t>
@@ -15905,7 +15920,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="30" customHeight="1" s="100">
+    <row r="26" ht="30" customHeight="1" s="102">
       <c r="A26" s="44" t="inlineStr">
         <is>
           <t>trempe</t>
@@ -15927,7 +15942,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="30" customHeight="1" s="100">
+    <row r="27" ht="30" customHeight="1" s="102">
       <c r="A27" s="44" t="inlineStr">
         <is>
           <t>celerite-chaleur</t>
@@ -15949,7 +15964,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="30" customHeight="1" s="100">
+    <row r="28" ht="30" customHeight="1" s="102">
       <c r="A28" s="44" t="inlineStr">
         <is>
           <t>celerite-vers-energie</t>
@@ -15971,7 +15986,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="30" customHeight="1" s="100">
+    <row r="29" ht="30" customHeight="1" s="102">
       <c r="A29" s="44" t="inlineStr">
         <is>
           <t>feu-vers-energie</t>
@@ -15993,7 +16008,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="30" customHeight="1" s="100">
+    <row r="30" ht="30" customHeight="1" s="102">
       <c r="A30" s="44" t="inlineStr">
         <is>
           <t>rejet-chaleur</t>
@@ -16025,7 +16040,7 @@
       <c r="C31" s="46" t="n"/>
       <c r="D31" s="46" t="n"/>
     </row>
-    <row r="32" ht="30" customHeight="1" s="100">
+    <row r="32" ht="30" customHeight="1" s="102">
       <c r="A32" s="44" t="inlineStr">
         <is>
           <t>piocher</t>
@@ -16047,7 +16062,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="30" customHeight="1" s="100">
+    <row r="33" ht="30" customHeight="1" s="102">
       <c r="A33" s="44" t="inlineStr">
         <is>
           <t>piocher-par-ennemi</t>
@@ -16069,7 +16084,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="30" customHeight="1" s="100">
+    <row r="34" ht="30" customHeight="1" s="102">
       <c r="A34" s="44" t="inlineStr">
         <is>
           <t>defausse-brulante</t>
@@ -16091,7 +16106,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="30" customHeight="1" s="100">
+    <row r="35" ht="30" customHeight="1" s="102">
       <c r="A35" s="44" t="inlineStr">
         <is>
           <t>refaire-main</t>
@@ -16113,7 +16128,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="24" customHeight="1" s="100">
+    <row r="36" ht="24" customHeight="1" s="102">
       <c r="A36" s="46" t="inlineStr">
         <is>
           <t>── EFFETS SPÉCIAUX OFFENSIFS ──</t>
@@ -16123,7 +16138,7 @@
       <c r="C36" s="46" t="n"/>
       <c r="D36" s="46" t="n"/>
     </row>
-    <row r="37" ht="30" customHeight="1" s="100">
+    <row r="37" ht="30" customHeight="1" s="102">
       <c r="A37" s="44" t="inlineStr">
         <is>
           <t>cleave-adjacent</t>
@@ -16145,7 +16160,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="30" customHeight="1" s="100">
+    <row r="38" ht="30" customHeight="1" s="102">
       <c r="A38" s="44" t="inlineStr">
         <is>
           <t>coup-de-grace</t>
@@ -16167,7 +16182,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="30" customHeight="1" s="100">
+    <row r="39" ht="30" customHeight="1" s="102">
       <c r="A39" s="44" t="inlineStr">
         <is>
           <t>rebond</t>
@@ -16189,7 +16204,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="30" customHeight="1" s="100">
+    <row r="40" ht="30" customHeight="1" s="102">
       <c r="A40" s="44" t="inlineStr">
         <is>
           <t>pierre-par-ennemi</t>
@@ -16211,7 +16226,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="30" customHeight="1" s="100">
+    <row r="41" ht="30" customHeight="1" s="102">
       <c r="A41" s="44" t="inlineStr">
         <is>
           <t>degats-si-gel</t>
@@ -16233,7 +16248,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="30" customHeight="1" s="100">
+    <row r="42" ht="30" customHeight="1" s="102">
       <c r="A42" s="44" t="inlineStr">
         <is>
           <t>degats-si-faible</t>
@@ -16255,7 +16270,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="30" customHeight="1" s="100">
+    <row r="43" ht="30" customHeight="1" s="102">
       <c r="A43" s="44" t="inlineStr">
         <is>
           <t>degats-execution</t>
@@ -16277,7 +16292,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="30" customHeight="1" s="100">
+    <row r="44" ht="30" customHeight="1" s="102">
       <c r="A44" s="44" t="inlineStr">
         <is>
           <t>danse-poison</t>
@@ -16299,7 +16314,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="30" customHeight="1" s="100">
+    <row r="45" ht="30" customHeight="1" s="102">
       <c r="A45" s="44" t="inlineStr">
         <is>
           <t>brulure-adjacent</t>
@@ -16321,7 +16336,7 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="30" customHeight="1" s="100">
+    <row r="46" ht="30" customHeight="1" s="102">
       <c r="A46" s="44" t="inlineStr">
         <is>
           <t>eclaboussure</t>
@@ -16343,7 +16358,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="24" customHeight="1" s="100">
+    <row r="47" ht="24" customHeight="1" s="102">
       <c r="A47" s="46" t="inlineStr">
         <is>
           <t>── MÉCANIQUES SAIGNEMENT ──</t>
@@ -16353,7 +16368,7 @@
       <c r="C47" s="46" t="n"/>
       <c r="D47" s="46" t="n"/>
     </row>
-    <row r="48" ht="30" customHeight="1" s="100">
+    <row r="48" ht="30" customHeight="1" s="102">
       <c r="A48" s="44" t="inlineStr">
         <is>
           <t>pierre-par-sang</t>
@@ -16375,7 +16390,7 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="30" customHeight="1" s="100">
+    <row r="49" ht="30" customHeight="1" s="102">
       <c r="A49" s="44" t="inlineStr">
         <is>
           <t>soin-par-sang</t>
@@ -16397,7 +16412,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="30" customHeight="1" s="100">
+    <row r="50" ht="30" customHeight="1" s="102">
       <c r="A50" s="44" t="inlineStr">
         <is>
           <t>absorption-sang</t>
@@ -16419,7 +16434,7 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="30" customHeight="1" s="100">
+    <row r="51" ht="30" customHeight="1" s="102">
       <c r="A51" s="44" t="inlineStr">
         <is>
           <t>chaleur-par-sang</t>
@@ -16441,7 +16456,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="30" customHeight="1" s="100">
+    <row r="52" ht="30" customHeight="1" s="102">
       <c r="A52" s="44" t="inlineStr">
         <is>
           <t>stun-si-sang</t>
@@ -16463,7 +16478,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="30" customHeight="1" s="100">
+    <row r="53" ht="30" customHeight="1" s="102">
       <c r="A53" s="44" t="inlineStr">
         <is>
           <t>contagion</t>
@@ -16485,7 +16500,7 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="30" customHeight="1" s="100">
+    <row r="54" ht="30" customHeight="1" s="102">
       <c r="A54" s="44" t="inlineStr">
         <is>
           <t>boire-le-sang</t>
@@ -16517,7 +16532,7 @@
       <c r="C55" s="46" t="n"/>
       <c r="D55" s="46" t="n"/>
     </row>
-    <row r="56" ht="30" customHeight="1" s="100">
+    <row r="56" ht="30" customHeight="1" s="102">
       <c r="A56" s="44" t="inlineStr">
         <is>
           <t>tout-en-feu</t>
@@ -16539,7 +16554,7 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="30" customHeight="1" s="100">
+    <row r="57" ht="30" customHeight="1" s="102">
       <c r="A57" s="44" t="inlineStr">
         <is>
           <t>transfert-feu</t>
@@ -16561,7 +16576,7 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="30" customHeight="1" s="100">
+    <row r="58" ht="30" customHeight="1" s="102">
       <c r="A58" s="44" t="inlineStr">
         <is>
           <t>forgeage</t>
@@ -16583,7 +16598,7 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="24" customHeight="1" s="100">
+    <row r="59" ht="24" customHeight="1" s="102">
       <c r="A59" s="46" t="inlineStr">
         <is>
           <t>── MÉCANIQUES CONFUSION ──</t>
@@ -16593,7 +16608,7 @@
       <c r="C59" s="46" t="n"/>
       <c r="D59" s="46" t="n"/>
     </row>
-    <row r="60" ht="30" customHeight="1" s="100">
+    <row r="60" ht="30" customHeight="1" s="102">
       <c r="A60" s="44" t="inlineStr">
         <is>
           <t>confusion-proche</t>
@@ -16615,7 +16630,7 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="30" customHeight="1" s="100">
+    <row r="61" ht="30" customHeight="1" s="102">
       <c r="A61" s="44" t="inlineStr">
         <is>
           <t>confusion-si-confus</t>
@@ -16637,7 +16652,7 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="30" customHeight="1" s="100">
+    <row r="62" ht="30" customHeight="1" s="102">
       <c r="A62" s="44" t="inlineStr">
         <is>
           <t>purifier-hero</t>
@@ -16669,7 +16684,7 @@
       <c r="C63" s="46" t="n"/>
       <c r="D63" s="46" t="n"/>
     </row>
-    <row r="64" ht="30" customHeight="1" s="100">
+    <row r="64" ht="30" customHeight="1" s="102">
       <c r="A64" s="44" t="inlineStr">
         <is>
           <t>gel-cascade</t>
@@ -16691,7 +16706,7 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="24" customHeight="1" s="100">
+    <row r="66" ht="24" customHeight="1" s="102">
       <c r="A66" s="46" t="inlineStr">
         <is>
           <t>── NOUVELLES MÉCANIQUES (révision Excel juin) ──</t>
@@ -16701,7 +16716,7 @@
       <c r="C66" s="46" t="n"/>
       <c r="D66" s="46" t="n"/>
     </row>
-    <row r="67" ht="30" customHeight="1" s="100">
+    <row r="67" ht="30" customHeight="1" s="102">
       <c r="A67" s="44" t="inlineStr">
         <is>
           <t>drain-sang</t>
@@ -16723,7 +16738,7 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="30" customHeight="1" s="100">
+    <row r="68" ht="30" customHeight="1" s="102">
       <c r="A68" s="44" t="inlineStr">
         <is>
           <t>supprimer-bonus</t>
@@ -16745,7 +16760,7 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="30" customHeight="1" s="100">
+    <row r="69" ht="30" customHeight="1" s="102">
       <c r="A69" s="44" t="inlineStr">
         <is>
           <t>voler-bonus</t>
@@ -16767,7 +16782,7 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="30" customHeight="1" s="100">
+    <row r="70" ht="30" customHeight="1" s="102">
       <c r="A70" s="44" t="inlineStr">
         <is>
           <t>piocher-pierre</t>
@@ -16789,7 +16804,7 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="30" customHeight="1" s="100">
+    <row r="71" ht="30" customHeight="1" s="102">
       <c r="A71" s="44" t="inlineStr">
         <is>
           <t>retirer-feu-hero</t>
@@ -16811,7 +16826,7 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="30" customHeight="1" s="100">
+    <row r="72" ht="30" customHeight="1" s="102">
       <c r="A72" s="44" t="inlineStr">
         <is>
           <t>chaleur-aleatoire</t>
@@ -16833,7 +16848,7 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="30" customHeight="1" s="100">
+    <row r="73" ht="30" customHeight="1" s="102">
       <c r="A73" s="44" t="inlineStr">
         <is>
           <t>pioche-filtre</t>
@@ -16855,7 +16870,7 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="30" customHeight="1" s="100">
+    <row r="74" ht="30" customHeight="1" s="102">
       <c r="A74" s="44" t="inlineStr">
         <is>
           <t>degats-soin-cible</t>
@@ -16877,7 +16892,7 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="30" customHeight="1" s="100">
+    <row r="75" ht="30" customHeight="1" s="102">
       <c r="A75" s="44" t="inlineStr">
         <is>
           <t>celerite-par-tour</t>
@@ -16899,7 +16914,7 @@
         </is>
       </c>
     </row>
-    <row r="76" ht="30" customHeight="1" s="100">
+    <row r="76" ht="30" customHeight="1" s="102">
       <c r="A76" s="44" t="inlineStr">
         <is>
           <t>riposte</t>
@@ -16921,7 +16936,7 @@
         </is>
       </c>
     </row>
-    <row r="77" ht="30" customHeight="1" s="100">
+    <row r="77" ht="30" customHeight="1" s="102">
       <c r="A77" s="44" t="inlineStr">
         <is>
           <t>tour-bonus</t>
@@ -16943,7 +16958,7 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="30" customHeight="1" s="100">
+    <row r="78" ht="30" customHeight="1" s="102">
       <c r="A78" s="44" t="inlineStr">
         <is>
           <t>compteur-pierre</t>
@@ -16965,7 +16980,7 @@
         </is>
       </c>
     </row>
-    <row r="79" ht="30" customHeight="1" s="100">
+    <row r="79" ht="30" customHeight="1" s="102">
       <c r="A79" s="44" t="inlineStr">
         <is>
           <t>pierre-par-compteur</t>
@@ -16987,7 +17002,7 @@
         </is>
       </c>
     </row>
-    <row r="80" ht="30" customHeight="1" s="100">
+    <row r="80" ht="30" customHeight="1" s="102">
       <c r="A80" s="44" t="inlineStr">
         <is>
           <t>piocher-par-compteur</t>
@@ -17009,7 +17024,7 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="30" customHeight="1" s="100">
+    <row r="81" ht="30" customHeight="1" s="102">
       <c r="A81" s="44" t="inlineStr">
         <is>
           <t>chaleur-par-compteur</t>
@@ -17031,7 +17046,7 @@
         </is>
       </c>
     </row>
-    <row r="83" ht="24" customHeight="1" s="100">
+    <row r="83" ht="24" customHeight="1" s="102">
       <c r="A83" s="46" t="inlineStr">
         <is>
           <t>── COMBOS ARMES 2 MAINS ──</t>
@@ -17041,7 +17056,7 @@
       <c r="C83" s="46" t="n"/>
       <c r="D83" s="46" t="n"/>
     </row>
-    <row r="84" ht="30" customHeight="1" s="100">
+    <row r="84" ht="30" customHeight="1" s="102">
       <c r="A84" s="44" t="inlineStr">
         <is>
           <t>degats-si-force</t>
@@ -17063,7 +17078,7 @@
         </is>
       </c>
     </row>
-    <row r="85" ht="30" customHeight="1" s="100">
+    <row r="85" ht="30" customHeight="1" s="102">
       <c r="A85" s="44" t="inlineStr">
         <is>
           <t>stun-si-pierre</t>
@@ -17085,7 +17100,7 @@
         </is>
       </c>
     </row>
-    <row r="86" ht="30" customHeight="1" s="100">
+    <row r="86" ht="30" customHeight="1" s="102">
       <c r="A86" s="44" t="inlineStr">
         <is>
           <t>soin-par-ennemi-saignant</t>
@@ -17107,7 +17122,7 @@
         </is>
       </c>
     </row>
-    <row r="87" ht="30" customHeight="1" s="100">
+    <row r="87" ht="30" customHeight="1" s="102">
       <c r="A87" s="44" t="inlineStr">
         <is>
           <t>recompense-mort</t>
@@ -17143,12 +17158,12 @@
   <dimension ref="A1:D130"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" style="100" min="1" max="1"/>
-    <col width="26" customWidth="1" style="100" min="2" max="2"/>
-    <col width="12" customWidth="1" style="100" min="3" max="4"/>
+    <col width="24" customWidth="1" style="102" min="1" max="1"/>
+    <col width="26" customWidth="1" style="102" min="2" max="2"/>
+    <col width="12" customWidth="1" style="102" min="3" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.75" customHeight="1" s="100">
+    <row r="1" ht="18.75" customHeight="1" s="102">
       <c r="A1" s="58" t="inlineStr">
         <is>
           <t>VALEUR DES OBJETS — SOURCE ÉDITABLE</t>
@@ -19692,13 +19707,13 @@
   <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" style="100" min="1" max="1"/>
-    <col width="16" customWidth="1" style="100" min="2" max="2"/>
-    <col width="8" customWidth="1" style="100" min="3" max="3"/>
-    <col width="12" customWidth="1" style="100" min="4" max="4"/>
+    <col width="18" customWidth="1" style="102" min="1" max="1"/>
+    <col width="16" customWidth="1" style="102" min="2" max="2"/>
+    <col width="8" customWidth="1" style="102" min="3" max="3"/>
+    <col width="12" customWidth="1" style="102" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.75" customHeight="1" s="100">
+    <row r="1" ht="18.75" customHeight="1" s="102">
       <c r="A1" s="58" t="inlineStr">
         <is>
           <t>VALEUR DES RESSOURCES — SOURCE ÉDITABLE</t>
@@ -19756,7 +19771,7 @@
         <v>1</v>
       </c>
       <c r="D7" s="82" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -19774,7 +19789,7 @@
         <v>2</v>
       </c>
       <c r="D8" s="82" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
@@ -19792,7 +19807,7 @@
         <v>3</v>
       </c>
       <c r="D9" s="82" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10">
@@ -19810,7 +19825,7 @@
         <v>4</v>
       </c>
       <c r="D10" s="82" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11">
@@ -19828,7 +19843,7 @@
         <v>5</v>
       </c>
       <c r="D11" s="82" t="n">
-        <v>31</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12">
@@ -19846,7 +19861,7 @@
         <v>6</v>
       </c>
       <c r="D12" s="82" t="n">
-        <v>57</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -19864,7 +19879,7 @@
         <v>7</v>
       </c>
       <c r="D13" s="82" t="n">
-        <v>102</v>
+        <v>250</v>
       </c>
     </row>
     <row r="14">
@@ -19882,7 +19897,7 @@
         <v>7</v>
       </c>
       <c r="D14" s="82" t="n">
-        <v>102</v>
+        <v>320</v>
       </c>
     </row>
     <row r="15">
@@ -19900,7 +19915,7 @@
         <v>7</v>
       </c>
       <c r="D15" s="82" t="n">
-        <v>102</v>
+        <v>450</v>
       </c>
     </row>
     <row r="16">
@@ -19918,7 +19933,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="82" t="n">
-        <v>184</v>
+        <v>500</v>
       </c>
     </row>
     <row r="17">
@@ -19936,7 +19951,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="82" t="n">
-        <v>331</v>
+        <v>600</v>
       </c>
     </row>
     <row r="18">
@@ -19954,7 +19969,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="82" t="n">
-        <v>331</v>
+        <v>800</v>
       </c>
     </row>
     <row r="19">
@@ -19972,7 +19987,7 @@
         <v>10</v>
       </c>
       <c r="D19" s="82" t="n">
-        <v>595</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="20">
@@ -19990,7 +20005,7 @@
         <v>11</v>
       </c>
       <c r="D20" s="82" t="n">
-        <v>1071</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="21">
@@ -20008,7 +20023,7 @@
         <v>11</v>
       </c>
       <c r="D21" s="82" t="n">
-        <v>1071</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="22">
@@ -20026,7 +20041,7 @@
         <v>12</v>
       </c>
       <c r="D22" s="82" t="n">
-        <v>1928</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="23">
@@ -20044,7 +20059,7 @@
         <v>12</v>
       </c>
       <c r="D23" s="82" t="n">
-        <v>1928</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="24">
@@ -20060,7 +20075,7 @@
       </c>
       <c r="C24" s="85" t="n"/>
       <c r="D24" s="82" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25">
@@ -20076,7 +20091,7 @@
       </c>
       <c r="C25" s="85" t="n"/>
       <c r="D25" s="82" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26">
@@ -20092,7 +20107,7 @@
       </c>
       <c r="C26" s="86" t="n"/>
       <c r="D26" s="82" t="n">
-        <v>40</v>
+        <v>250</v>
       </c>
     </row>
     <row r="27">
@@ -20108,7 +20123,7 @@
       </c>
       <c r="C27" s="87" t="n"/>
       <c r="D27" s="82" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="28">
@@ -20124,7 +20139,7 @@
       </c>
       <c r="C28" s="86" t="n"/>
       <c r="D28" s="82" t="n">
-        <v>35</v>
+        <v>250</v>
       </c>
     </row>
     <row r="29">
@@ -20140,7 +20155,7 @@
       </c>
       <c r="C29" s="87" t="n"/>
       <c r="D29" s="82" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
     </row>
   </sheetData>
@@ -20157,11 +20172,11 @@
   <dimension ref="A1:F555"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" style="100" min="1" max="1"/>
-    <col width="16" customWidth="1" style="100" min="2" max="6"/>
+    <col width="18" customWidth="1" style="102" min="1" max="1"/>
+    <col width="16" customWidth="1" style="102" min="2" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.75" customHeight="1" s="100">
+    <row r="1" ht="18.75" customHeight="1" s="102">
       <c r="A1" s="58" t="inlineStr">
         <is>
           <t>RECETTES DE CRAFT — SOURCE ÉDITABLE</t>
@@ -27048,16 +27063,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" style="100" min="1" max="2"/>
-    <col width="12" customWidth="1" style="100" min="3" max="4"/>
-    <col width="10" customWidth="1" style="100" min="5" max="5"/>
-    <col width="8" customWidth="1" style="100" min="6" max="7"/>
+    <col width="22" customWidth="1" style="102" min="1" max="2"/>
+    <col width="12" customWidth="1" style="102" min="3" max="4"/>
+    <col width="10" customWidth="1" style="102" min="5" max="5"/>
+    <col width="8" customWidth="1" style="102" min="6" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25" customHeight="1" s="100">
+    <row r="1" ht="17.25" customHeight="1" s="102">
       <c r="A1" s="95" t="inlineStr">
         <is>
           <t>LOOTS DE PROFONDEUR — buffs de « run » (SOURCE ÉDITABLE)</t>
@@ -27150,7 +27165,7 @@
         <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -27178,10 +27193,10 @@
         <v>100</v>
       </c>
       <c r="F8" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="G8" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row r="9">
@@ -27197,7 +27212,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>celerite</t>
+          <t>agilité</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -27206,13 +27221,18 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>40</v>
+        <v>4</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Augmente l'agilité</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -27267,14 +27287,100 @@
           <t>#5fd08a</t>
         </is>
       </c>
-      <c r="E11" t="n">
-        <v>1</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
       </c>
       <c r="F11" t="n">
         <v>1</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Onde de tranquilité</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>pop-monstre</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
         <v>1</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Si choisis il n'y a pas de pop de monstre a cette étage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>poussière de rubis</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Soigne</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>20</v>
+      </c>
+      <c r="F13" t="n">
+        <v>40</v>
+      </c>
+      <c r="G13" t="n">
+        <v>80</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Soigne d'autant de hp directement</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Lucky stone</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>% de chance augmenté</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" t="n">
+        <v>6</v>
+      </c>
+      <c r="G14" t="n">
+        <v>12</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Ca augmente le % de minerais a l'étage actuel.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/docs/BRUTAL-items-et-cartes.xlsx
+++ b/docs/BRUTAL-items-et-cartes.xlsx
@@ -1278,7 +1278,6 @@
         </is>
       </c>
     </row>
-    <row r="29"/>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
@@ -1473,7 +1472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" style="102" min="1" max="1"/>
@@ -1486,6 +1485,7 @@
     <col width="9" customWidth="1" style="102" min="8" max="8"/>
     <col width="52" customWidth="1" style="102" min="9" max="9"/>
     <col width="42" customWidth="1" style="102" min="10" max="10"/>
+    <col width="26" customWidth="1" style="102" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1539,6 +1539,11 @@
           <t>grand</t>
         </is>
       </c>
+      <c r="K1" s="103" t="inlineStr">
+        <is>
+          <t>zone de pop</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="98" t="inlineStr">
@@ -1591,6 +1596,11 @@
           <t>met 1 si le monstre est GRAND (occupe 2 places, pop plus rare). Vide = normal.</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>où le monstre apparaît : « Eastern + profondeur » (surface est + mine) ou « Profondeur » (mine uniquement, étage 2+)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1623,6 +1633,11 @@
       <c r="H3" t="n">
         <v>6</v>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Eastern + profondeur</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1662,6 +1677,11 @@
           <t>applique 1 poisson par attaque (2x attaque = 2 poisons)</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Eastern + profondeur</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1699,6 +1719,11 @@
           <t>soigner:10:50 | haste-allie:2:30 | attaque:2:20</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Eastern + profondeur</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1733,6 +1758,503 @@
       </c>
       <c r="J6" t="n">
         <v>1</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Eastern + profondeur</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>orc-rodeur</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Orc Rogue</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>orc</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>40</v>
+      </c>
+      <c r="F7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G7" t="n">
+        <v>22</v>
+      </c>
+      <c r="H7" t="n">
+        <v>15</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>frappe 2× par tour (attaqueHits 2)</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Profondeur (mine, étage 2+)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>orc-guerrier</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Orc Warrior</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>orc</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>75</v>
+      </c>
+      <c r="F8" t="n">
+        <v>12</v>
+      </c>
+      <c r="G8" t="n">
+        <v>30</v>
+      </c>
+      <c r="H8" t="n">
+        <v>8</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Profondeur (mine, étage 2+)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>orc-guerriere</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Orc Warmaiden</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>orc</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>60</v>
+      </c>
+      <c r="F9" t="n">
+        <v>16</v>
+      </c>
+      <c r="G9" t="n">
+        <v>34</v>
+      </c>
+      <c r="H9" t="n">
+        <v>9</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Profondeur (mine, étage 2+)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>orc-brute</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Orc Berserker</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>orc</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>95</v>
+      </c>
+      <c r="F10" t="n">
+        <v>20</v>
+      </c>
+      <c r="G10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H10" t="n">
+        <v>6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Profondeur (mine, étage 2+)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>orc-chamane</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Orc Shaman</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>orc</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>45</v>
+      </c>
+      <c r="F11" t="n">
+        <v>6</v>
+      </c>
+      <c r="G11" t="n">
+        <v>36</v>
+      </c>
+      <c r="H11" t="n">
+        <v>7</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>soigner:12:45 | haste-allie:2:30 | attaque:6:25</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Profondeur (mine, étage 2+)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>blob-vert</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Green Slime</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>blob</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>55</v>
+      </c>
+      <c r="F12" t="n">
+        <v>8</v>
+      </c>
+      <c r="G12" t="n">
+        <v>24</v>
+      </c>
+      <c r="H12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1 poison par coup</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Profondeur (mine, étage 2+)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>blob-jaune</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ochre Slime</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>blob</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>50</v>
+      </c>
+      <c r="F13" t="n">
+        <v>8</v>
+      </c>
+      <c r="G13" t="n">
+        <v>24</v>
+      </c>
+      <c r="H13" t="n">
+        <v>4</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>poison par coup (acide, 3)</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Profondeur (mine, étage 2+)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>blob-rouge</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Crimson Slime</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>blob</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>80</v>
+      </c>
+      <c r="F14" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" t="n">
+        <v>30</v>
+      </c>
+      <c r="H14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>tanky</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Profondeur (mine, étage 2+)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>blob-bleu</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Azure Slime</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>blob</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>65</v>
+      </c>
+      <c r="F15" t="n">
+        <v>10</v>
+      </c>
+      <c r="G15" t="n">
+        <v>30</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>piquants</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Profondeur (mine, étage 2+)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>molosse</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Dire Hound</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>animal</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>40</v>
+      </c>
+      <c r="F16" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" t="n">
+        <v>22</v>
+      </c>
+      <c r="H16" t="n">
+        <v>16</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>rapide</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Profondeur (mine, étage 2+)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>molosse-feu</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ember Hound</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>4</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>animal</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>45</v>
+      </c>
+      <c r="F17" t="n">
+        <v>12</v>
+      </c>
+      <c r="G17" t="n">
+        <v>28</v>
+      </c>
+      <c r="H17" t="n">
+        <v>15</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>rapide, feu</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Profondeur (mine, étage 2+)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>molosse-sombre</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Shadow Hound</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>4</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>animal</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>42</v>
+      </c>
+      <c r="F18" t="n">
+        <v>11</v>
+      </c>
+      <c r="G18" t="n">
+        <v>26</v>
+      </c>
+      <c r="H18" t="n">
+        <v>17</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>rapide</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Profondeur (mine, étage 2+)</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1902,7 +2424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M171"/>
+  <dimension ref="A1:L171"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" style="102" min="1" max="1"/>
@@ -10783,7 +11305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H141"/>
+  <dimension ref="A1:G141"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" style="102" min="1" max="1"/>

--- a/docs/BRUTAL-items-et-cartes.xlsx
+++ b/docs/BRUTAL-items-et-cartes.xlsx
@@ -18,6 +18,7 @@
     <sheet name="Profondeurs-chances" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="Monstres" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="Héros" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Général" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -27,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="21">
+  <fonts count="26">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -140,8 +141,31 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00555555"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+    </font>
   </fonts>
-  <fills count="60">
+  <fills count="62">
     <fill>
       <patternFill/>
     </fill>
@@ -438,8 +462,18 @@
         <fgColor rgb="FFD9E1F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002F5496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -477,11 +511,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="104">
+  <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -702,6 +750,22 @@
     <xf numFmtId="0" fontId="10" fillId="27" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="60" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="61" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="61" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1472,7 +1536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" style="102" min="1" max="1"/>
@@ -2254,6 +2318,501 @@
       <c r="K18" t="inlineStr">
         <is>
           <t>Profondeur (mine, étage 2+)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>warrior-mushroom1</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Toadstool Lancer</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>3</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>mushroom</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>50</v>
+      </c>
+      <c r="F19" t="n">
+        <v>8</v>
+      </c>
+      <c r="G19" t="n">
+        <v>22</v>
+      </c>
+      <c r="H19" t="n">
+        <v>8</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Profondeur (mine, étage 2+)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>warrior-mushroom2</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Fungal Knight</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>mushroom</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>85</v>
+      </c>
+      <c r="F20" t="n">
+        <v>11</v>
+      </c>
+      <c r="G20" t="n">
+        <v>30</v>
+      </c>
+      <c r="H20" t="n">
+        <v>7</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Profondeur (mine, étage 2+)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>white-katana-mushroom</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Myconid Ronin</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>4</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>mushroom</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>45</v>
+      </c>
+      <c r="F21" t="n">
+        <v>7</v>
+      </c>
+      <c r="G21" t="n">
+        <v>30</v>
+      </c>
+      <c r="H21" t="n">
+        <v>18</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>frappe 2× par tour (attaqueHits 2)</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Profondeur (mine, étage 2+)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>black-mushroom-specialist</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Deathcap Reaper</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>5</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>mushroom</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>90</v>
+      </c>
+      <c r="F22" t="n">
+        <v>18</v>
+      </c>
+      <c r="G22" t="n">
+        <v>44</v>
+      </c>
+      <c r="H22" t="n">
+        <v>9</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Profondeur (mine, étage 2+)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>mage-mushroom</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Myconid Sage</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>4</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>mushroom</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>40</v>
+      </c>
+      <c r="F23" t="n">
+        <v>5</v>
+      </c>
+      <c r="G23" t="n">
+        <v>34</v>
+      </c>
+      <c r="H23" t="n">
+        <v>7</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>soigner:12:45 | haste-allie:2:30 | attaque:5:25</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Profondeur (mine, étage 2+)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>king-mushroom</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Mushroom King</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>6</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>mushroom</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>140</v>
+      </c>
+      <c r="F24" t="n">
+        <v>16</v>
+      </c>
+      <c r="G24" t="n">
+        <v>70</v>
+      </c>
+      <c r="H24" t="n">
+        <v>6</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>soigner:18:40 | haste-allie:2:30 | attaque:16:30</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Profondeur (mine, étage 2+)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>bear</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Cave Bear</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>4</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>animal</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>90</v>
+      </c>
+      <c r="F25" t="n">
+        <v>14</v>
+      </c>
+      <c r="G25" t="n">
+        <v>32</v>
+      </c>
+      <c r="H25" t="n">
+        <v>8</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>en meute avec les molosses</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Profondeur (mine, étage 2+)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>bones-bear</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Bonehide Bear</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>5</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>animal</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100</v>
+      </c>
+      <c r="F26" t="n">
+        <v>16</v>
+      </c>
+      <c r="G26" t="n">
+        <v>44</v>
+      </c>
+      <c r="H26" t="n">
+        <v>9</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>en meute avec les molosses</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Profondeur (mine, étage 2+)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>armor-bear</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Armored War-Bear</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>6</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>animal</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>150</v>
+      </c>
+      <c r="F27" t="n">
+        <v>20</v>
+      </c>
+      <c r="G27" t="n">
+        <v>60</v>
+      </c>
+      <c r="H27" t="n">
+        <v>6</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>en meute avec les molosses</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Profondeur (mine, étage 2+)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>lapin-stage1</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>White Rabbit</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>7</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>lapin</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>13</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>stade 1 GENTIL : n'attaque pas ; le tuer le fait ÉVOLUER (pas dans l'Excel : voir code)</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Rencontre spéciale rare (mine, étage 4+, seul)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>lapin-stage2</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Feral Hare</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>7</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>lapin</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>55</v>
+      </c>
+      <c r="F29" t="n">
+        <v>9</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>20</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>stade 2 : frappe 2× (attaqueHits 2) ; évolue en stade 3</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Rencontre spéciale (évolution)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>lapin-stage3</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Bloodfang Horror</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>10</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>lapin</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>150</v>
+      </c>
+      <c r="F30" t="n">
+        <v>17</v>
+      </c>
+      <c r="G30" t="n">
+        <v>130</v>
+      </c>
+      <c r="H30" t="n">
+        <v>26</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>stade 3 : frappe 2× ; gros or (niv 10) + 2% Ring of Luck</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Rencontre spéciale (stade final)</t>
         </is>
       </c>
     </row>
@@ -2410,6 +2969,863 @@
       <c r="C9" t="inlineStr">
         <is>
           <t>Nombre maximum de cartes en main</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" style="102" min="1" max="1"/>
+    <col width="34" customWidth="1" style="102" min="2" max="2"/>
+    <col width="16" customWidth="1" style="102" min="3" max="3"/>
+    <col width="62" customWidth="1" style="102" min="4" max="4"/>
+    <col width="22" customWidth="1" style="102" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="105" t="inlineStr">
+        <is>
+          <t>RÉGLAGES GÉNÉRAUX — valeurs secondaires d'équilibrage</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="106" t="inlineStr">
+        <is>
+          <t>Réglages « secondaires » du jeu, regroupés ici pour t'y retrouver. Ajuste la colonne « Valeur » ; dis-moi et je les applique dans le code (colonne « Où »). Pas d'importer auto : je les reporte à la main.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="107" t="inlineStr">
+        <is>
+          <t>Domaine</t>
+        </is>
+      </c>
+      <c r="B4" s="107" t="inlineStr">
+        <is>
+          <t>Réglage</t>
+        </is>
+      </c>
+      <c r="C4" s="107" t="inlineStr">
+        <is>
+          <t>Valeur</t>
+        </is>
+      </c>
+      <c r="D4" s="107" t="inlineStr">
+        <is>
+          <t>Explication (à quoi ça sert)</t>
+        </is>
+      </c>
+      <c r="E4" s="107" t="inlineStr">
+        <is>
+          <t>Où (fichier)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="108" t="inlineStr">
+        <is>
+          <t>MORT &amp; CACHES DE BUTIN PERDU</t>
+        </is>
+      </c>
+      <c r="B5" s="109" t="n"/>
+      <c r="C5" s="109" t="n"/>
+      <c r="D5" s="109" t="n"/>
+      <c r="E5" s="109" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="110" t="inlineStr">
+        <is>
+          <t>Mort</t>
+        </is>
+      </c>
+      <c r="B6" s="110" t="inlineStr">
+        <is>
+          <t>Perte d'XP</t>
+        </is>
+      </c>
+      <c r="C6" s="111" t="inlineStr">
+        <is>
+          <t>50 %</t>
+        </is>
+      </c>
+      <c r="D6" s="110" t="inlineStr">
+        <is>
+          <t>Part de la barre d'XP EN COURS perdue à la mort (jamais un niveau).</t>
+        </is>
+      </c>
+      <c r="E6" s="110" t="inlineStr">
+        <is>
+          <t>systems/mort.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="110" t="inlineStr">
+        <is>
+          <t>Mort</t>
+        </is>
+      </c>
+      <c r="B7" s="110" t="inlineStr">
+        <is>
+          <t>Perte d'objets du sac</t>
+        </is>
+      </c>
+      <c r="C7" s="111" t="inlineStr">
+        <is>
+          <t>50 %</t>
+        </is>
+      </c>
+      <c r="D7" s="110" t="inlineStr">
+        <is>
+          <t>Part des objets du sac perdus AU HASARD (l'équipement porté est épargné).</t>
+        </is>
+      </c>
+      <c r="E7" s="110" t="inlineStr">
+        <is>
+          <t>systems/mort.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="110" t="inlineStr">
+        <is>
+          <t>Mort</t>
+        </is>
+      </c>
+      <c r="B8" s="110" t="inlineStr">
+        <is>
+          <t>Perte d'or</t>
+        </is>
+      </c>
+      <c r="C8" s="111" t="inlineStr">
+        <is>
+          <t>30 %</t>
+        </is>
+      </c>
+      <c r="D8" s="110" t="inlineStr">
+        <is>
+          <t>Part de la bourse perdue à la mort.</t>
+        </is>
+      </c>
+      <c r="E8" s="110" t="inlineStr">
+        <is>
+          <t>systems/mort.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="110" t="inlineStr">
+        <is>
+          <t>Mort</t>
+        </is>
+      </c>
+      <c r="B9" s="110" t="inlineStr">
+        <is>
+          <t>Chance de retrouver une cache</t>
+        </is>
+      </c>
+      <c r="C9" s="111" t="inlineStr">
+        <is>
+          <t>1 %</t>
+        </is>
+      </c>
+      <c r="D9" s="110" t="inlineStr">
+        <is>
+          <t>Proba, PAR cache perdue et PAR étage de mine, de la voir resurgir (ramassable).</t>
+        </is>
+      </c>
+      <c r="E9" s="110" t="inlineStr">
+        <is>
+          <t>systems/mort.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="108" t="inlineStr">
+        <is>
+          <t>LAPIN BLANC (rencontre spéciale)</t>
+        </is>
+      </c>
+      <c r="B10" s="109" t="n"/>
+      <c r="C10" s="109" t="n"/>
+      <c r="D10" s="109" t="n"/>
+      <c r="E10" s="109" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="110" t="inlineStr">
+        <is>
+          <t>Lapin</t>
+        </is>
+      </c>
+      <c r="B11" s="110" t="inlineStr">
+        <is>
+          <t>Chance d'apparition</t>
+        </is>
+      </c>
+      <c r="C11" s="111" t="inlineStr">
+        <is>
+          <t>4 %</t>
+        </is>
+      </c>
+      <c r="D11" s="110" t="inlineStr">
+        <is>
+          <t>Proba qu'une rencontre en mine (étage 4+) soit un lapin plutôt qu'un groupe normal.</t>
+        </is>
+      </c>
+      <c r="E11" s="110" t="inlineStr">
+        <is>
+          <t>principal.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="110" t="inlineStr">
+        <is>
+          <t>Lapin</t>
+        </is>
+      </c>
+      <c r="B12" s="110" t="inlineStr">
+        <is>
+          <t>Étage minimum</t>
+        </is>
+      </c>
+      <c r="C12" s="111" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D12" s="110" t="inlineStr">
+        <is>
+          <t>Profondeur mini pour croiser le lapin.</t>
+        </is>
+      </c>
+      <c r="E12" s="110" t="inlineStr">
+        <is>
+          <t>principal.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="110" t="inlineStr">
+        <is>
+          <t>Lapin</t>
+        </is>
+      </c>
+      <c r="B13" s="110" t="inlineStr">
+        <is>
+          <t>Taille du groupe</t>
+        </is>
+      </c>
+      <c r="C13" s="111" t="inlineStr">
+        <is>
+          <t>70 / 22 / 8 %</t>
+        </is>
+      </c>
+      <c r="D13" s="110" t="inlineStr">
+        <is>
+          <t>Proba d'avoir 1 / 2 / 3 lapins ensemble (jamais mêlés à d'autres créatures).</t>
+        </is>
+      </c>
+      <c r="E13" s="110" t="inlineStr">
+        <is>
+          <t>principal.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="110" t="inlineStr">
+        <is>
+          <t>Lapin</t>
+        </is>
+      </c>
+      <c r="B14" s="110" t="inlineStr">
+        <is>
+          <t>Fuite — stade 1 (gentil)</t>
+        </is>
+      </c>
+      <c r="C14" s="111" t="inlineStr">
+        <is>
+          <t>100 %</t>
+        </is>
+      </c>
+      <c r="D14" s="110" t="inlineStr">
+        <is>
+          <t>Chance de fuir tant qu'il est gentil (réussit toujours).</t>
+        </is>
+      </c>
+      <c r="E14" s="110" t="inlineStr">
+        <is>
+          <t>ui/combat.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="110" t="inlineStr">
+        <is>
+          <t>Lapin</t>
+        </is>
+      </c>
+      <c r="B15" s="110" t="inlineStr">
+        <is>
+          <t>Fuite — stade 2 (enragé)</t>
+        </is>
+      </c>
+      <c r="C15" s="111" t="inlineStr">
+        <is>
+          <t>35 %</t>
+        </is>
+      </c>
+      <c r="D15" s="110" t="inlineStr">
+        <is>
+          <t>Chance de fuir une fois enragé.</t>
+        </is>
+      </c>
+      <c r="E15" s="110" t="inlineStr">
+        <is>
+          <t>ui/combat.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="110" t="inlineStr">
+        <is>
+          <t>Lapin</t>
+        </is>
+      </c>
+      <c r="B16" s="110" t="inlineStr">
+        <is>
+          <t>Fuite — stade 3 (monstre)</t>
+        </is>
+      </c>
+      <c r="C16" s="111" t="inlineStr">
+        <is>
+          <t>7 %</t>
+        </is>
+      </c>
+      <c r="D16" s="110" t="inlineStr">
+        <is>
+          <t>Chance de fuir le stade final (quasi impossible).</t>
+        </is>
+      </c>
+      <c r="E16" s="110" t="inlineStr">
+        <is>
+          <t>ui/combat.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="110" t="inlineStr">
+        <is>
+          <t>Lapin</t>
+        </is>
+      </c>
+      <c r="B17" s="110" t="inlineStr">
+        <is>
+          <t>Taille à l'écran (st. 1/2/3)</t>
+        </is>
+      </c>
+      <c r="C17" s="111" t="inlineStr">
+        <is>
+          <t>×0.667 / ×0.667 / ×1.25</t>
+        </is>
+      </c>
+      <c r="D17" s="110" t="inlineStr">
+        <is>
+          <t>Facteur d'affichage des sprites (tailleRel) : gentils plus petits, monstre plus grand.</t>
+        </is>
+      </c>
+      <c r="E17" s="110" t="inlineStr">
+        <is>
+          <t>data/ennemis.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="108" t="inlineStr">
+        <is>
+          <t>MINAGE &amp; RING OF LUCK</t>
+        </is>
+      </c>
+      <c r="B18" s="109" t="n"/>
+      <c r="C18" s="109" t="n"/>
+      <c r="D18" s="109" t="n"/>
+      <c r="E18" s="109" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="110" t="inlineStr">
+        <is>
+          <t>Minage</t>
+        </is>
+      </c>
+      <c r="B19" s="110" t="inlineStr">
+        <is>
+          <t>Ring of Luck : double butin</t>
+        </is>
+      </c>
+      <c r="C19" s="111" t="inlineStr">
+        <is>
+          <t>50 %</t>
+        </is>
+      </c>
+      <c r="D19" s="110" t="inlineStr">
+        <is>
+          <t>Chance de DOUBLER le minerai d'un coup de pioche (item Ring of Luck).</t>
+        </is>
+      </c>
+      <c r="E19" s="110" t="inlineStr">
+        <is>
+          <t>data/items.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="110" t="inlineStr">
+        <is>
+          <t>Minage</t>
+        </is>
+      </c>
+      <c r="B20" s="110" t="inlineStr">
+        <is>
+          <t>Bonus minerai par rareté</t>
+        </is>
+      </c>
+      <c r="C20" s="111" t="inlineStr">
+        <is>
+          <t>10 / 15 / 20 / 25 / 35 %</t>
+        </is>
+      </c>
+      <c r="D20" s="110" t="inlineStr">
+        <is>
+          <t>Chance d'un minerai bonus par coup selon la rareté (commun → légendaire).</t>
+        </is>
+      </c>
+      <c r="E20" s="110" t="inlineStr">
+        <is>
+          <t>principal.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="110" t="inlineStr">
+        <is>
+          <t>Minage</t>
+        </is>
+      </c>
+      <c r="B21" s="110" t="inlineStr">
+        <is>
+          <t>Durée d'un coup de pioche</t>
+        </is>
+      </c>
+      <c r="C21" s="111" t="inlineStr">
+        <is>
+          <t>0.55 s</t>
+        </is>
+      </c>
+      <c r="D21" s="110" t="inlineStr">
+        <is>
+          <t>Temps de base d'un coup (divisé par la vitesse de la pioche équipée).</t>
+        </is>
+      </c>
+      <c r="E21" s="110" t="inlineStr">
+        <is>
+          <t>principal.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="110" t="inlineStr">
+        <is>
+          <t>Minage</t>
+        </is>
+      </c>
+      <c r="B22" s="110" t="inlineStr">
+        <is>
+          <t>Veines par étage</t>
+        </is>
+      </c>
+      <c r="C22" s="111" t="inlineStr">
+        <is>
+          <t>3 à 6</t>
+        </is>
+      </c>
+      <c r="D22" s="110" t="inlineStr">
+        <is>
+          <t>Nombre de filons posés dans les salles d'un étage de mine.</t>
+        </is>
+      </c>
+      <c r="E22" s="110" t="inlineStr">
+        <is>
+          <t>world/mine.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="108" t="inlineStr">
+        <is>
+          <t>LUCKY DELVER (talent forge — caverne de chance)</t>
+        </is>
+      </c>
+      <c r="B23" s="109" t="n"/>
+      <c r="C23" s="109" t="n"/>
+      <c r="D23" s="109" t="n"/>
+      <c r="E23" s="109" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="110" t="inlineStr">
+        <is>
+          <t>Caverne</t>
+        </is>
+      </c>
+      <c r="B24" s="110" t="inlineStr">
+        <is>
+          <t>Chance d'apparition</t>
+        </is>
+      </c>
+      <c r="C24" s="111" t="inlineStr">
+        <is>
+          <t>22 %</t>
+        </is>
+      </c>
+      <c r="D24" s="110" t="inlineStr">
+        <is>
+          <t>Proba, par descente éligible (étage 3+), de tomber sur une caverne de chance.</t>
+        </is>
+      </c>
+      <c r="E24" s="110" t="inlineStr">
+        <is>
+          <t>principal.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="110" t="inlineStr">
+        <is>
+          <t>Caverne</t>
+        </is>
+      </c>
+      <c r="B25" s="110" t="inlineStr">
+        <is>
+          <t>Bonus de minerais</t>
+        </is>
+      </c>
+      <c r="C25" s="111" t="inlineStr">
+        <is>
+          <t>+220 %</t>
+        </is>
+      </c>
+      <c r="D25" s="110" t="inlineStr">
+        <is>
+          <t>Boost du nombre de veines dans une caverne de chance.</t>
+        </is>
+      </c>
+      <c r="E25" s="110" t="inlineStr">
+        <is>
+          <t>principal.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="110" t="inlineStr">
+        <is>
+          <t>Caverne</t>
+        </is>
+      </c>
+      <c r="B26" s="110" t="inlineStr">
+        <is>
+          <t>Taux de rencontre</t>
+        </is>
+      </c>
+      <c r="C26" s="111" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="D26" s="110" t="inlineStr">
+        <is>
+          <t>Fréquence des combats dans une caverne (vs 0.3 normal → quasi zéro monstre).</t>
+        </is>
+      </c>
+      <c r="E26" s="110" t="inlineStr">
+        <is>
+          <t>principal.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="108" t="inlineStr">
+        <is>
+          <t>BANQUE</t>
+        </is>
+      </c>
+      <c r="B27" s="109" t="n"/>
+      <c r="C27" s="109" t="n"/>
+      <c r="D27" s="109" t="n"/>
+      <c r="E27" s="109" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="110" t="inlineStr">
+        <is>
+          <t>Banque</t>
+        </is>
+      </c>
+      <c r="B28" s="110" t="inlineStr">
+        <is>
+          <t>Rendement du coffre-fort</t>
+        </is>
+      </c>
+      <c r="C28" s="111" t="inlineStr">
+        <is>
+          <t>0.2 % / jour</t>
+        </is>
+      </c>
+      <c r="D28" s="110" t="inlineStr">
+        <is>
+          <t>Intérêt composé du dépôt SÛR (par jour de jeu).</t>
+        </is>
+      </c>
+      <c r="E28" s="110" t="inlineStr">
+        <is>
+          <t>data/banque.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="108" t="inlineStr">
+        <is>
+          <t>RENCONTRES &amp; GROUPES DE MONSTRES</t>
+        </is>
+      </c>
+      <c r="B29" s="109" t="n"/>
+      <c r="C29" s="109" t="n"/>
+      <c r="D29" s="109" t="n"/>
+      <c r="E29" s="109" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="110" t="inlineStr">
+        <is>
+          <t>Mine</t>
+        </is>
+      </c>
+      <c r="B30" s="110" t="inlineStr">
+        <is>
+          <t>Taux de rencontre</t>
+        </is>
+      </c>
+      <c r="C30" s="111" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="D30" s="110" t="inlineStr">
+        <is>
+          <t>Fréquence de base des combats en explorant une mine.</t>
+        </is>
+      </c>
+      <c r="E30" s="110" t="inlineStr">
+        <is>
+          <t>world/mine.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="110" t="inlineStr">
+        <is>
+          <t>Mine</t>
+        </is>
+      </c>
+      <c r="B31" s="110" t="inlineStr">
+        <is>
+          <t>Étage « monstres profonds »</t>
+        </is>
+      </c>
+      <c r="C31" s="111" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D31" s="110" t="inlineStr">
+        <is>
+          <t>Étage mini où apparaissent orcs / blobs / molosses / ours / champignons.</t>
+        </is>
+      </c>
+      <c r="E31" s="110" t="inlineStr">
+        <is>
+          <t>world/mine.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="110" t="inlineStr">
+        <is>
+          <t>Mine</t>
+        </is>
+      </c>
+      <c r="B32" s="110" t="inlineStr">
+        <is>
+          <t>Chance de biome (thème)</t>
+        </is>
+      </c>
+      <c r="C32" s="111" t="inlineStr">
+        <is>
+          <t>40 %</t>
+        </is>
+      </c>
+      <c r="D32" s="110" t="inlineStr">
+        <is>
+          <t>Proba qu'un étage éligible soit à thème (cristal / glace / lave…).</t>
+        </is>
+      </c>
+      <c r="E32" s="110" t="inlineStr">
+        <is>
+          <t>world/mine.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="110" t="inlineStr">
+        <is>
+          <t>Groupes</t>
+        </is>
+      </c>
+      <c r="B33" s="110" t="inlineStr">
+        <is>
+          <t>Taille des groupes</t>
+        </is>
+      </c>
+      <c r="C33" s="111" t="inlineStr">
+        <is>
+          <t>30 / 30 / 20 / 15 / 5 %</t>
+        </is>
+      </c>
+      <c r="D33" s="110" t="inlineStr">
+        <is>
+          <t>Proba d'un groupe de 1 / 2 / 3 / 4 / 5 emplacements.</t>
+        </is>
+      </c>
+      <c r="E33" s="110" t="inlineStr">
+        <is>
+          <t>data/ennemis.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="110" t="inlineStr">
+        <is>
+          <t>Groupes</t>
+        </is>
+      </c>
+      <c r="B34" s="110" t="inlineStr">
+        <is>
+          <t>Facteur de niveau</t>
+        </is>
+      </c>
+      <c r="C34" s="111" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D34" s="110" t="inlineStr">
+        <is>
+          <t>Un niveau de monstre en plus = ~2× plus rare dans le tirage.</t>
+        </is>
+      </c>
+      <c r="E34" s="110" t="inlineStr">
+        <is>
+          <t>data/ennemis.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="110" t="inlineStr">
+        <is>
+          <t>Groupes</t>
+        </is>
+      </c>
+      <c r="B35" s="110" t="inlineStr">
+        <is>
+          <t>Rareté d'un « grand » (petit grp)</t>
+        </is>
+      </c>
+      <c r="C35" s="111" t="inlineStr">
+        <is>
+          <t>×0.5</t>
+        </is>
+      </c>
+      <c r="D35" s="110" t="inlineStr">
+        <is>
+          <t>Poids d'un grand monstre dans un petit groupe (plus rare).</t>
+        </is>
+      </c>
+      <c r="E35" s="110" t="inlineStr">
+        <is>
+          <t>data/ennemis.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="110" t="inlineStr">
+        <is>
+          <t>Groupes</t>
+        </is>
+      </c>
+      <c r="B36" s="110" t="inlineStr">
+        <is>
+          <t>Bonus d'un « grand » (gros grp)</t>
+        </is>
+      </c>
+      <c r="C36" s="111" t="inlineStr">
+        <is>
+          <t>×3</t>
+        </is>
+      </c>
+      <c r="D36" s="110" t="inlineStr">
+        <is>
+          <t>Poids d'un grand dans un gros groupe (favorisé).</t>
+        </is>
+      </c>
+      <c r="E36" s="110" t="inlineStr">
+        <is>
+          <t>data/ennemis.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="110" t="inlineStr">
+        <is>
+          <t>Combat</t>
+        </is>
+      </c>
+      <c r="B37" s="110" t="inlineStr">
+        <is>
+          <t>Fuite selon nb d'ennemis</t>
+        </is>
+      </c>
+      <c r="C37" s="111" t="inlineStr">
+        <is>
+          <t>50 / 33 / 25 / 25 / 20 %</t>
+        </is>
+      </c>
+      <c r="D37" s="110" t="inlineStr">
+        <is>
+          <t>Chance de fuir un combat normal selon le nombre d'ennemis (1 à 5).</t>
+        </is>
+      </c>
+      <c r="E37" s="110" t="inlineStr">
+        <is>
+          <t>ui/combat.js</t>
         </is>
       </c>
     </row>
@@ -11305,7 +12721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G141"/>
+  <dimension ref="A1:G142"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" style="102" min="1" max="1"/>
@@ -14509,49 +15925,49 @@
       </c>
     </row>
     <row r="98" ht="17.1" customHeight="1" s="102">
-      <c r="A98" s="47" t="inlineStr">
+      <c r="A98" s="17" t="inlineStr">
+        <is>
+          <t>Bagues</t>
+        </is>
+      </c>
+      <c r="B98" s="17" t="inlineStr">
+        <is>
+          <t>Ring of Luck</t>
+        </is>
+      </c>
+      <c r="C98" s="17" t="inlineStr">
+        <is>
+          <t>ring-of-luck</t>
+        </is>
+      </c>
+      <c r="D98" s="17" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="E98" s="18" t="inlineStr">
+        <is>
+          <t>(cartes à venir)</t>
+        </is>
+      </c>
+      <c r="F98" s="18" t="inlineStr">
+        <is>
+          <t>50% de doubler le butin d'un coup de minage (souterrains)</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="n"/>
+    </row>
+    <row r="99" ht="15" customHeight="1" s="102">
+      <c r="A99" s="47" t="inlineStr">
         <is>
           <t xml:space="preserve">  ▸ GANTS</t>
         </is>
       </c>
-      <c r="B98" s="48" t="n"/>
-      <c r="C98" s="48" t="n"/>
-      <c r="D98" s="48" t="n"/>
-      <c r="E98" s="48" t="n"/>
-      <c r="F98" s="48" t="n"/>
-    </row>
-    <row r="99" ht="15" customHeight="1" s="102">
-      <c r="A99" s="13" t="inlineStr">
-        <is>
-          <t>Gants</t>
-        </is>
-      </c>
-      <c r="B99" s="13" t="inlineStr">
-        <is>
-          <t>Cloth Gloves</t>
-        </is>
-      </c>
-      <c r="C99" s="13" t="inlineStr">
-        <is>
-          <t>gants-tissu</t>
-        </is>
-      </c>
-      <c r="D99" s="13" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="E99" s="14" t="inlineStr">
-        <is>
-          <t>Nimble Hands×2</t>
-        </is>
-      </c>
-      <c r="F99" s="14" t="n"/>
-      <c r="G99" s="2" t="inlineStr">
-        <is>
-          <t>aucun dégât/armure  (2 cartes/5 visées · 2 buff)</t>
-        </is>
-      </c>
+      <c r="B99" s="48" t="n"/>
+      <c r="C99" s="48" t="n"/>
+      <c r="D99" s="48" t="n"/>
+      <c r="E99" s="48" t="n"/>
+      <c r="F99" s="48" t="n"/>
     </row>
     <row r="100" ht="15" customHeight="1" s="102">
       <c r="A100" s="13" t="inlineStr">
@@ -14561,12 +15977,12 @@
       </c>
       <c r="B100" s="13" t="inlineStr">
         <is>
-          <t>Leather Gloves</t>
+          <t>Cloth Gloves</t>
         </is>
       </c>
       <c r="C100" s="13" t="inlineStr">
         <is>
-          <t>gants-cuir</t>
+          <t>gants-tissu</t>
         </is>
       </c>
       <c r="D100" s="13" t="inlineStr">
@@ -14576,13 +15992,13 @@
       </c>
       <c r="E100" s="14" t="inlineStr">
         <is>
-          <t>Nimble Hands×1, Guard×1</t>
+          <t>Nimble Hands×2</t>
         </is>
       </c>
       <c r="F100" s="14" t="n"/>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>≈ 4 armure  (2 cartes/5 visées · 1 buff)</t>
+          <t>aucun dégât/armure  (2 cartes/5 visées · 2 buff)</t>
         </is>
       </c>
     </row>
@@ -14594,12 +16010,12 @@
       </c>
       <c r="B101" s="13" t="inlineStr">
         <is>
-          <t>Miner's Gloves</t>
+          <t>Leather Gloves</t>
         </is>
       </c>
       <c r="C101" s="13" t="inlineStr">
         <is>
-          <t>gants-de-mineur</t>
+          <t>gants-cuir</t>
         </is>
       </c>
       <c r="D101" s="13" t="inlineStr">
@@ -14609,13 +16025,13 @@
       </c>
       <c r="E101" s="14" t="inlineStr">
         <is>
-          <t>Master's Hand×2</t>
+          <t>Nimble Hands×1, Guard×1</t>
         </is>
       </c>
       <c r="F101" s="14" t="n"/>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>aucun dégât/armure  (2 cartes/5 visées · 2 buff)</t>
+          <t>≈ 4 armure  (2 cartes/5 visées · 1 buff)</t>
         </is>
       </c>
     </row>
@@ -14627,12 +16043,12 @@
       </c>
       <c r="B102" s="13" t="inlineStr">
         <is>
-          <t>Studded Gloves</t>
+          <t>Miner's Gloves</t>
         </is>
       </c>
       <c r="C102" s="13" t="inlineStr">
         <is>
-          <t>gants-cloutes</t>
+          <t>gants-de-mineur</t>
         </is>
       </c>
       <c r="D102" s="13" t="inlineStr">
@@ -14642,13 +16058,13 @@
       </c>
       <c r="E102" s="14" t="inlineStr">
         <is>
-          <t>Strike×1, Gash×1</t>
+          <t>Master's Hand×2</t>
         </is>
       </c>
       <c r="F102" s="14" t="n"/>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>≈ 10 dégâts  (2 cartes/5 visées)</t>
+          <t>aucun dégât/armure  (2 cartes/5 visées · 2 buff)</t>
         </is>
       </c>
     </row>
@@ -14660,12 +16076,12 @@
       </c>
       <c r="B103" s="13" t="inlineStr">
         <is>
-          <t>Work Gloves</t>
+          <t>Studded Gloves</t>
         </is>
       </c>
       <c r="C103" s="13" t="inlineStr">
         <is>
-          <t>gants-travail</t>
+          <t>gants-cloutes</t>
         </is>
       </c>
       <c r="D103" s="13" t="inlineStr">
@@ -14675,46 +16091,46 @@
       </c>
       <c r="E103" s="14" t="inlineStr">
         <is>
-          <t>Master's Hand×1, Strike×1</t>
+          <t>Strike×1, Gash×1</t>
         </is>
       </c>
       <c r="F103" s="14" t="n"/>
       <c r="G103" s="2" t="inlineStr">
         <is>
+          <t>≈ 10 dégâts  (2 cartes/5 visées)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="15" customHeight="1" s="102">
+      <c r="A104" s="13" t="inlineStr">
+        <is>
+          <t>Gants</t>
+        </is>
+      </c>
+      <c r="B104" s="13" t="inlineStr">
+        <is>
+          <t>Work Gloves</t>
+        </is>
+      </c>
+      <c r="C104" s="13" t="inlineStr">
+        <is>
+          <t>gants-travail</t>
+        </is>
+      </c>
+      <c r="D104" s="13" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E104" s="14" t="inlineStr">
+        <is>
+          <t>Master's Hand×1, Strike×1</t>
+        </is>
+      </c>
+      <c r="F104" s="14" t="n"/>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
           <t>≈ 5 dégâts  (2 cartes/5 visées · 1 buff)</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="15" customHeight="1" s="102">
-      <c r="A104" s="15" t="inlineStr">
-        <is>
-          <t>Gants</t>
-        </is>
-      </c>
-      <c r="B104" s="15" t="inlineStr">
-        <is>
-          <t>Gauntlets</t>
-        </is>
-      </c>
-      <c r="C104" s="15" t="inlineStr">
-        <is>
-          <t>gantelets</t>
-        </is>
-      </c>
-      <c r="D104" s="15" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="E104" s="16" t="inlineStr">
-        <is>
-          <t>Power Strike×1, Guard×1</t>
-        </is>
-      </c>
-      <c r="F104" s="16" t="n"/>
-      <c r="G104" s="2" t="inlineStr">
-        <is>
-          <t>≈ 16 dégâts  ·  ≈ 4 armure  (2 cartes/6 visées)</t>
         </is>
       </c>
     </row>
@@ -14726,12 +16142,12 @@
       </c>
       <c r="B105" s="15" t="inlineStr">
         <is>
-          <t>Lucky Glove</t>
+          <t>Gauntlets</t>
         </is>
       </c>
       <c r="C105" s="15" t="inlineStr">
         <is>
-          <t>gants-chance</t>
+          <t>gantelets</t>
         </is>
       </c>
       <c r="D105" s="15" t="inlineStr">
@@ -14741,13 +16157,13 @@
       </c>
       <c r="E105" s="16" t="inlineStr">
         <is>
-          <t>Roll 1 Dice×1, Roll 2 Dice×1, Lucky Draw×1</t>
+          <t>Power Strike×1, Guard×1</t>
         </is>
       </c>
       <c r="F105" s="16" t="n"/>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>aucun dégât/armure  (3 cartes/6 visées · 3 buff)</t>
+          <t>≈ 16 dégâts  ·  ≈ 4 armure  (2 cartes/6 visées)</t>
         </is>
       </c>
     </row>
@@ -14759,12 +16175,12 @@
       </c>
       <c r="B106" s="15" t="inlineStr">
         <is>
-          <t>Stone Glove</t>
+          <t>Lucky Glove</t>
         </is>
       </c>
       <c r="C106" s="15" t="inlineStr">
         <is>
-          <t>gants-stone-age</t>
+          <t>gants-chance</t>
         </is>
       </c>
       <c r="D106" s="15" t="inlineStr">
@@ -14774,17 +16190,13 @@
       </c>
       <c r="E106" s="16" t="inlineStr">
         <is>
-          <t>Stone×3, Many Stone×1, Pebble Sale×1</t>
-        </is>
-      </c>
-      <c r="F106" s="16" t="inlineStr">
-        <is>
-          <t>Set: Stone Age Set</t>
-        </is>
-      </c>
+          <t>Roll 1 Dice×1, Roll 2 Dice×1, Lucky Draw×1</t>
+        </is>
+      </c>
+      <c r="F106" s="16" t="n"/>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>≈ 36 armure  (5 cartes/6 visées · 1 buff)</t>
+          <t>aucun dégât/armure  (3 cartes/6 visées · 3 buff)</t>
         </is>
       </c>
     </row>
@@ -14796,12 +16208,12 @@
       </c>
       <c r="B107" s="15" t="inlineStr">
         <is>
-          <t>Thief's Gloves</t>
+          <t>Stone Glove</t>
         </is>
       </c>
       <c r="C107" s="15" t="inlineStr">
         <is>
-          <t>gants-voleur</t>
+          <t>gants-stone-age</t>
         </is>
       </c>
       <c r="D107" s="15" t="inlineStr">
@@ -14811,13 +16223,17 @@
       </c>
       <c r="E107" s="16" t="inlineStr">
         <is>
-          <t>Sleight×1, Gimme That×1</t>
-        </is>
-      </c>
-      <c r="F107" s="16" t="n"/>
+          <t>Stone×3, Many Stone×1, Pebble Sale×1</t>
+        </is>
+      </c>
+      <c r="F107" s="16" t="inlineStr">
+        <is>
+          <t>Set: Stone Age Set</t>
+        </is>
+      </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>aucun dégât/armure  (2 cartes/6 visées · 2 buff)</t>
+          <t>≈ 36 armure  (5 cartes/6 visées · 1 buff)</t>
         </is>
       </c>
     </row>
@@ -14829,12 +16245,12 @@
       </c>
       <c r="B108" s="15" t="inlineStr">
         <is>
-          <t>Venom Gloves</t>
+          <t>Thief's Gloves</t>
         </is>
       </c>
       <c r="C108" s="15" t="inlineStr">
         <is>
-          <t>gants-venin</t>
+          <t>gants-voleur</t>
         </is>
       </c>
       <c r="D108" s="15" t="inlineStr">
@@ -14844,50 +16260,46 @@
       </c>
       <c r="E108" s="16" t="inlineStr">
         <is>
-          <t>Poison Coat×1, Poison Dart×1</t>
+          <t>Sleight×1, Gimme That×1</t>
         </is>
       </c>
       <c r="F108" s="16" t="n"/>
       <c r="G108" s="2" t="inlineStr">
         <is>
+          <t>aucun dégât/armure  (2 cartes/6 visées · 2 buff)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="15" customHeight="1" s="102">
+      <c r="A109" s="15" t="inlineStr">
+        <is>
+          <t>Gants</t>
+        </is>
+      </c>
+      <c r="B109" s="15" t="inlineStr">
+        <is>
+          <t>Venom Gloves</t>
+        </is>
+      </c>
+      <c r="C109" s="15" t="inlineStr">
+        <is>
+          <t>gants-venin</t>
+        </is>
+      </c>
+      <c r="D109" s="15" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="E109" s="16" t="inlineStr">
+        <is>
+          <t>Poison Coat×1, Poison Dart×1</t>
+        </is>
+      </c>
+      <c r="F109" s="16" t="n"/>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
           <t>≈ 10 dégâts  (2 cartes/6 visées)</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="15" customHeight="1" s="102">
-      <c r="A109" s="17" t="inlineStr">
-        <is>
-          <t>Gants</t>
-        </is>
-      </c>
-      <c r="B109" s="17" t="inlineStr">
-        <is>
-          <t>Blood Gauntlets</t>
-        </is>
-      </c>
-      <c r="C109" s="17" t="inlineStr">
-        <is>
-          <t>gants-sang</t>
-        </is>
-      </c>
-      <c r="D109" s="17" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="E109" s="18" t="inlineStr">
-        <is>
-          <t>Open Veins×2, Contagion×2, Blood Absorption×1</t>
-        </is>
-      </c>
-      <c r="F109" s="18" t="inlineStr">
-        <is>
-          <t>Set: Blood Set</t>
-        </is>
-      </c>
-      <c r="G109" s="2" t="inlineStr">
-        <is>
-          <t>≈ 72 dégâts  (5 cartes/6 visées · 1 buff)</t>
         </is>
       </c>
     </row>
@@ -14899,12 +16311,12 @@
       </c>
       <c r="B110" s="17" t="inlineStr">
         <is>
-          <t>Crusader Gauntlets</t>
+          <t>Blood Gauntlets</t>
         </is>
       </c>
       <c r="C110" s="17" t="inlineStr">
         <is>
-          <t>gants-croise</t>
+          <t>gants-sang</t>
         </is>
       </c>
       <c r="D110" s="17" t="inlineStr">
@@ -14914,17 +16326,17 @@
       </c>
       <c r="E110" s="18" t="inlineStr">
         <is>
-          <t>Master's Hand×2, Halo Burst×1, Lay on Hands×2</t>
+          <t>Open Veins×2, Contagion×2, Blood Absorption×1</t>
         </is>
       </c>
       <c r="F110" s="18" t="inlineStr">
         <is>
-          <t>Set: Crusader Set</t>
+          <t>Set: Blood Set</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>≈ 12 dégâts  (5 cartes/6 visées · 4 buff)</t>
+          <t>≈ 72 dégâts  (5 cartes/6 visées · 1 buff)</t>
         </is>
       </c>
     </row>
@@ -14936,120 +16348,120 @@
       </c>
       <c r="B111" s="17" t="inlineStr">
         <is>
+          <t>Crusader Gauntlets</t>
+        </is>
+      </c>
+      <c r="C111" s="17" t="inlineStr">
+        <is>
+          <t>gants-croise</t>
+        </is>
+      </c>
+      <c r="D111" s="17" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="E111" s="18" t="inlineStr">
+        <is>
+          <t>Master's Hand×2, Halo Burst×1, Lay on Hands×2</t>
+        </is>
+      </c>
+      <c r="F111" s="18" t="inlineStr">
+        <is>
+          <t>Set: Crusader Set</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>≈ 12 dégâts  (5 cartes/6 visées · 4 buff)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="15" customHeight="1" s="102">
+      <c r="A112" s="17" t="inlineStr">
+        <is>
+          <t>Gants</t>
+        </is>
+      </c>
+      <c r="B112" s="17" t="inlineStr">
+        <is>
           <t>Mail Glove</t>
         </is>
       </c>
-      <c r="C111" s="17" t="inlineStr">
+      <c r="C112" s="17" t="inlineStr">
         <is>
           <t>gants-de-maille</t>
         </is>
       </c>
-      <c r="D111" s="17" t="inlineStr">
+      <c r="D112" s="17" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="E111" s="18" t="inlineStr">
+      <c r="E112" s="18" t="inlineStr">
         <is>
           <t>Master's Hand×2, Outnumbered×2, Mail Advantage×1</t>
         </is>
       </c>
-      <c r="F111" s="18" t="inlineStr">
+      <c r="F112" s="18" t="inlineStr">
         <is>
           <t>Set: Mail Set</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr">
         <is>
           <t>aucun dégât/armure  (5 cartes/6 visées · 5 buff)</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="15" customHeight="1" s="102">
-      <c r="A112" s="21" t="inlineStr">
+    <row r="113" ht="17.1" customHeight="1" s="102">
+      <c r="A113" s="21" t="inlineStr">
         <is>
           <t>Gants</t>
         </is>
       </c>
-      <c r="B112" s="21" t="inlineStr">
+      <c r="B113" s="21" t="inlineStr">
         <is>
           <t>Onyx Glove</t>
         </is>
       </c>
-      <c r="C112" s="21" t="inlineStr">
+      <c r="C113" s="21" t="inlineStr">
         <is>
           <t>gants-onyx</t>
         </is>
       </c>
-      <c r="D112" s="21" t="inlineStr">
+      <c r="D113" s="21" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="E112" s="22" t="inlineStr">
+      <c r="E113" s="22" t="inlineStr">
         <is>
           <t>Burning Hand×2, Onyx Fist×2, Forge from Ashes×2</t>
         </is>
       </c>
-      <c r="F112" s="22" t="inlineStr">
+      <c r="F113" s="22" t="inlineStr">
         <is>
           <t>Set: Onyx Set</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr">
         <is>
           <t>≈ 34 dégâts  (6 cartes/7 visées · 4 buff)</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="17.1" customHeight="1" s="102">
-      <c r="A113" s="47" t="inlineStr">
+    <row r="114" ht="15" customHeight="1" s="102">
+      <c r="A114" s="47" t="inlineStr">
         <is>
           <t xml:space="preserve">  ▸ BOTTES</t>
         </is>
       </c>
-      <c r="B113" s="48" t="n"/>
-      <c r="C113" s="48" t="n"/>
-      <c r="D113" s="48" t="n"/>
-      <c r="E113" s="48" t="n"/>
-      <c r="F113" s="48" t="n"/>
-    </row>
-    <row r="114" ht="15" customHeight="1" s="102">
-      <c r="A114" s="13" t="inlineStr">
-        <is>
-          <t>Bottes</t>
-        </is>
-      </c>
-      <c r="B114" s="13" t="inlineStr">
-        <is>
-          <t>Leather Boots</t>
-        </is>
-      </c>
-      <c r="C114" s="13" t="inlineStr">
-        <is>
-          <t>bottes-cuir</t>
-        </is>
-      </c>
-      <c r="D114" s="13" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="E114" s="14" t="inlineStr">
-        <is>
-          <t>Acceleration×2</t>
-        </is>
-      </c>
-      <c r="F114" s="14" t="inlineStr">
-        <is>
-          <t>+3 Agilité  ·  +10% déplacement</t>
-        </is>
-      </c>
-      <c r="G114" s="2" t="inlineStr">
-        <is>
-          <t>aucun dégât/armure  (2 cartes/5 visées · 2 buff)</t>
-        </is>
-      </c>
+      <c r="B114" s="48" t="n"/>
+      <c r="C114" s="48" t="n"/>
+      <c r="D114" s="48" t="n"/>
+      <c r="E114" s="48" t="n"/>
+      <c r="F114" s="48" t="n"/>
     </row>
     <row r="115" ht="15" customHeight="1" s="102">
       <c r="A115" s="13" t="inlineStr">
@@ -15059,12 +16471,12 @@
       </c>
       <c r="B115" s="13" t="inlineStr">
         <is>
-          <t>Sandals</t>
+          <t>Leather Boots</t>
         </is>
       </c>
       <c r="C115" s="13" t="inlineStr">
         <is>
-          <t>sandales</t>
+          <t>bottes-cuir</t>
         </is>
       </c>
       <c r="D115" s="13" t="inlineStr">
@@ -15074,12 +16486,12 @@
       </c>
       <c r="E115" s="14" t="inlineStr">
         <is>
-          <t>Acceleration×1, Fresh Wind×1</t>
+          <t>Acceleration×2</t>
         </is>
       </c>
       <c r="F115" s="14" t="inlineStr">
         <is>
-          <t>+2 Agilité  ·  +8% déplacement</t>
+          <t>+3 Agilité  ·  +10% déplacement</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
@@ -15096,12 +16508,12 @@
       </c>
       <c r="B116" s="13" t="inlineStr">
         <is>
-          <t>Traveler Boots</t>
+          <t>Sandals</t>
         </is>
       </c>
       <c r="C116" s="13" t="inlineStr">
         <is>
-          <t>bottes-voyage</t>
+          <t>sandales</t>
         </is>
       </c>
       <c r="D116" s="13" t="inlineStr">
@@ -15111,12 +16523,12 @@
       </c>
       <c r="E116" s="14" t="inlineStr">
         <is>
-          <t>Acceleration×1, Long Run×1</t>
+          <t>Acceleration×1, Fresh Wind×1</t>
         </is>
       </c>
       <c r="F116" s="14" t="inlineStr">
         <is>
-          <t>+3 Agilité  ·  +15% déplacement</t>
+          <t>+2 Agilité  ·  +8% déplacement</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
@@ -15133,69 +16545,69 @@
       </c>
       <c r="B117" s="13" t="inlineStr">
         <is>
+          <t>Traveler Boots</t>
+        </is>
+      </c>
+      <c r="C117" s="13" t="inlineStr">
+        <is>
+          <t>bottes-voyage</t>
+        </is>
+      </c>
+      <c r="D117" s="13" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E117" s="14" t="inlineStr">
+        <is>
+          <t>Acceleration×1, Long Run×1</t>
+        </is>
+      </c>
+      <c r="F117" s="14" t="inlineStr">
+        <is>
+          <t>+3 Agilité  ·  +15% déplacement</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>aucun dégât/armure  (2 cartes/5 visées · 2 buff)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="15" customHeight="1" s="102">
+      <c r="A118" s="13" t="inlineStr">
+        <is>
+          <t>Bottes</t>
+        </is>
+      </c>
+      <c r="B118" s="13" t="inlineStr">
+        <is>
           <t>Worn Boots</t>
         </is>
       </c>
-      <c r="C117" s="13" t="inlineStr">
+      <c r="C118" s="13" t="inlineStr">
         <is>
           <t>bottes-usees</t>
         </is>
       </c>
-      <c r="D117" s="13" t="inlineStr">
+      <c r="D118" s="13" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="E117" s="14" t="inlineStr">
+      <c r="E118" s="14" t="inlineStr">
         <is>
           <t>Acceleration×1</t>
         </is>
       </c>
-      <c r="F117" s="14" t="inlineStr">
+      <c r="F118" s="14" t="inlineStr">
         <is>
           <t>+1 Agilité  ·  +5% déplacement</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr">
         <is>
           <t>aucun dégât/armure  (1 carte/5 visées · 1 buff)</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="15" customHeight="1" s="102">
-      <c r="A118" s="15" t="inlineStr">
-        <is>
-          <t>Bottes</t>
-        </is>
-      </c>
-      <c r="B118" s="15" t="inlineStr">
-        <is>
-          <t>Ember Striders</t>
-        </is>
-      </c>
-      <c r="C118" s="15" t="inlineStr">
-        <is>
-          <t>bottes-braise</t>
-        </is>
-      </c>
-      <c r="D118" s="15" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="E118" s="16" t="inlineStr">
-        <is>
-          <t>Ember×1, Quicken×1</t>
-        </is>
-      </c>
-      <c r="F118" s="16" t="inlineStr">
-        <is>
-          <t>+6 Agilité  ·  +15% déplacement</t>
-        </is>
-      </c>
-      <c r="G118" s="2" t="inlineStr">
-        <is>
-          <t>≈ 5 dégâts  (2 cartes/6 visées · 1 buff)</t>
         </is>
       </c>
     </row>
@@ -15207,12 +16619,12 @@
       </c>
       <c r="B119" s="15" t="inlineStr">
         <is>
-          <t>Stone Boots</t>
+          <t>Ember Striders</t>
         </is>
       </c>
       <c r="C119" s="15" t="inlineStr">
         <is>
-          <t>bottes-stone-age</t>
+          <t>bottes-braise</t>
         </is>
       </c>
       <c r="D119" s="15" t="inlineStr">
@@ -15222,17 +16634,17 @@
       </c>
       <c r="E119" s="16" t="inlineStr">
         <is>
-          <t>Stone×3, Many Stone×1, Melt Stones×1</t>
+          <t>Ember×1, Quicken×1</t>
         </is>
       </c>
       <c r="F119" s="16" t="inlineStr">
         <is>
-          <t>+3 Agilité  ·  +6% déplacement  ·  Set: Stone Age Set</t>
+          <t>+6 Agilité  ·  +15% déplacement</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>≈ 36 armure  (5 cartes/6 visées · 1 buff)</t>
+          <t>≈ 5 dégâts  (2 cartes/6 visées · 1 buff)</t>
         </is>
       </c>
     </row>
@@ -15244,12 +16656,12 @@
       </c>
       <c r="B120" s="15" t="inlineStr">
         <is>
-          <t>Stonetread Boots</t>
+          <t>Stone Boots</t>
         </is>
       </c>
       <c r="C120" s="15" t="inlineStr">
         <is>
-          <t>bottes-pierre</t>
+          <t>bottes-stone-age</t>
         </is>
       </c>
       <c r="D120" s="15" t="inlineStr">
@@ -15259,17 +16671,17 @@
       </c>
       <c r="E120" s="16" t="inlineStr">
         <is>
-          <t>Stone Fist×1, Guard×1</t>
+          <t>Stone×3, Many Stone×1, Melt Stones×1</t>
         </is>
       </c>
       <c r="F120" s="16" t="inlineStr">
         <is>
-          <t>+4 Agilité  ·  +8% déplacement</t>
+          <t>+3 Agilité  ·  +6% déplacement  ·  Set: Stone Age Set</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>≈ 24 dégâts  ·  ≈ 4 armure  (2 cartes/6 visées)</t>
+          <t>≈ 36 armure  (5 cartes/6 visées · 1 buff)</t>
         </is>
       </c>
     </row>
@@ -15281,12 +16693,12 @@
       </c>
       <c r="B121" s="15" t="inlineStr">
         <is>
-          <t>Swift Boots</t>
+          <t>Stonetread Boots</t>
         </is>
       </c>
       <c r="C121" s="15" t="inlineStr">
         <is>
-          <t>bottes-vives</t>
+          <t>bottes-pierre</t>
         </is>
       </c>
       <c r="D121" s="15" t="inlineStr">
@@ -15296,17 +16708,17 @@
       </c>
       <c r="E121" s="16" t="inlineStr">
         <is>
-          <t>Quicken×3, Second breath×1</t>
+          <t>Stone Fist×1, Guard×1</t>
         </is>
       </c>
       <c r="F121" s="16" t="inlineStr">
         <is>
-          <t>+7 Agilité  ·  +20% déplacement</t>
+          <t>+4 Agilité  ·  +8% déplacement</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>aucun dégât/armure  (4 cartes/6 visées · 4 buff)</t>
+          <t>≈ 24 dégâts  ·  ≈ 4 armure  (2 cartes/6 visées)</t>
         </is>
       </c>
     </row>
@@ -15318,69 +16730,69 @@
       </c>
       <c r="B122" s="15" t="inlineStr">
         <is>
+          <t>Swift Boots</t>
+        </is>
+      </c>
+      <c r="C122" s="15" t="inlineStr">
+        <is>
+          <t>bottes-vives</t>
+        </is>
+      </c>
+      <c r="D122" s="15" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="E122" s="16" t="inlineStr">
+        <is>
+          <t>Quicken×3, Second breath×1</t>
+        </is>
+      </c>
+      <c r="F122" s="16" t="inlineStr">
+        <is>
+          <t>+7 Agilité  ·  +20% déplacement</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>aucun dégât/armure  (4 cartes/6 visées · 4 buff)</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="15" customHeight="1" s="102">
+      <c r="A123" s="15" t="inlineStr">
+        <is>
+          <t>Bottes</t>
+        </is>
+      </c>
+      <c r="B123" s="15" t="inlineStr">
+        <is>
           <t>Swift Striders</t>
         </is>
       </c>
-      <c r="C122" s="15" t="inlineStr">
+      <c r="C123" s="15" t="inlineStr">
         <is>
           <t>bottes-rapides</t>
         </is>
       </c>
-      <c r="D122" s="15" t="inlineStr">
+      <c r="D123" s="15" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E122" s="16" t="inlineStr">
+      <c r="E123" s="16" t="inlineStr">
         <is>
           <t>Dash×1, Quicken×1</t>
         </is>
       </c>
-      <c r="F122" s="16" t="inlineStr">
+      <c r="F123" s="16" t="inlineStr">
         <is>
           <t>+8 Agilité  ·  +30% déplacement</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr">
         <is>
           <t>aucun dégât/armure  (2 cartes/6 visées · 2 buff)</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="15" customHeight="1" s="102">
-      <c r="A123" s="17" t="inlineStr">
-        <is>
-          <t>Bottes</t>
-        </is>
-      </c>
-      <c r="B123" s="17" t="inlineStr">
-        <is>
-          <t>Blood Greaves</t>
-        </is>
-      </c>
-      <c r="C123" s="17" t="inlineStr">
-        <is>
-          <t>bottes-sang</t>
-        </is>
-      </c>
-      <c r="D123" s="17" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="E123" s="18" t="inlineStr">
-        <is>
-          <t>Blood Slide×1, Blood Rush×2, Quicken×1, Boost×1</t>
-        </is>
-      </c>
-      <c r="F123" s="18" t="inlineStr">
-        <is>
-          <t>+12 Agilité  ·  +25% déplacement  ·  Set: Blood Set</t>
-        </is>
-      </c>
-      <c r="G123" s="2" t="inlineStr">
-        <is>
-          <t>≈ 24 dégâts  (5 cartes/6 visées · 4 buff)</t>
         </is>
       </c>
     </row>
@@ -15392,12 +16804,12 @@
       </c>
       <c r="B124" s="17" t="inlineStr">
         <is>
-          <t>Crusader Greaves</t>
+          <t>Blood Greaves</t>
         </is>
       </c>
       <c r="C124" s="17" t="inlineStr">
         <is>
-          <t>bottes-croise</t>
+          <t>bottes-sang</t>
         </is>
       </c>
       <c r="D124" s="17" t="inlineStr">
@@ -15407,17 +16819,17 @@
       </c>
       <c r="E124" s="18" t="inlineStr">
         <is>
-          <t>Quicken×1, Kick of light×2, Boost×2</t>
+          <t>Blood Slide×1, Blood Rush×2, Quicken×1, Boost×1</t>
         </is>
       </c>
       <c r="F124" s="18" t="inlineStr">
         <is>
-          <t>+12 Agilité  ·  +25% déplacement  ·  Set: Crusader Set</t>
+          <t>+12 Agilité  ·  +25% déplacement  ·  Set: Blood Set</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>≈ 24 dégâts  (5 cartes/6 visées · 3 buff)</t>
+          <t>≈ 24 dégâts  (5 cartes/6 visées · 4 buff)</t>
         </is>
       </c>
     </row>
@@ -15429,187 +16841,187 @@
       </c>
       <c r="B125" s="17" t="inlineStr">
         <is>
+          <t>Crusader Greaves</t>
+        </is>
+      </c>
+      <c r="C125" s="17" t="inlineStr">
+        <is>
+          <t>bottes-croise</t>
+        </is>
+      </c>
+      <c r="D125" s="17" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="E125" s="18" t="inlineStr">
+        <is>
+          <t>Quicken×1, Kick of light×2, Boost×2</t>
+        </is>
+      </c>
+      <c r="F125" s="18" t="inlineStr">
+        <is>
+          <t>+12 Agilité  ·  +25% déplacement  ·  Set: Crusader Set</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>≈ 24 dégâts  (5 cartes/6 visées · 3 buff)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="15" customHeight="1" s="102">
+      <c r="A126" s="17" t="inlineStr">
+        <is>
+          <t>Bottes</t>
+        </is>
+      </c>
+      <c r="B126" s="17" t="inlineStr">
+        <is>
           <t>Mail Boots</t>
         </is>
       </c>
-      <c r="C125" s="17" t="inlineStr">
+      <c r="C126" s="17" t="inlineStr">
         <is>
           <t>bottes-de-maille</t>
         </is>
       </c>
-      <c r="D125" s="17" t="inlineStr">
+      <c r="D126" s="17" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="E125" s="18" t="inlineStr">
+      <c r="E126" s="18" t="inlineStr">
         <is>
           <t>Quicken×2, Mail Advantage×1, Boost×2</t>
         </is>
       </c>
-      <c r="F125" s="18" t="inlineStr">
+      <c r="F126" s="18" t="inlineStr">
         <is>
           <t>+10 Agilité  ·  +15% déplacement  ·  Set: Mail Set</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr">
         <is>
           <t>aucun dégât/armure  (5 cartes/6 visées · 5 buff)</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="15" customHeight="1" s="102">
-      <c r="A126" s="21" t="inlineStr">
+    <row r="127" ht="17.1" customHeight="1" s="102">
+      <c r="A127" s="21" t="inlineStr">
         <is>
           <t>Bottes</t>
         </is>
       </c>
-      <c r="B126" s="21" t="inlineStr">
+      <c r="B127" s="21" t="inlineStr">
         <is>
           <t>Onyx Boots</t>
         </is>
       </c>
-      <c r="C126" s="21" t="inlineStr">
+      <c r="C127" s="21" t="inlineStr">
         <is>
           <t>bottes-onyx</t>
         </is>
       </c>
-      <c r="D126" s="21" t="inlineStr">
+      <c r="D127" s="21" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="E126" s="22" t="inlineStr">
+      <c r="E127" s="22" t="inlineStr">
         <is>
           <t>Burning Run×1, Flaming Kick×1, Fire Boost×2, Boost×2</t>
         </is>
       </c>
-      <c r="F126" s="100" t="inlineStr">
+      <c r="F127" s="100" t="inlineStr">
         <is>
           <t>+18 Agilité  ·  +40% déplacement  ·  Set: Onyx Set</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr">
         <is>
           <t>aucun dégât/armure  (6 cartes/7 visées · 6 buff)</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="17.1" customHeight="1" s="102">
-      <c r="A127" s="47" t="inlineStr">
+    <row r="128" ht="15" customHeight="1" s="102">
+      <c r="A128" s="47" t="inlineStr">
         <is>
           <t xml:space="preserve">  ▸ SACS</t>
         </is>
       </c>
-      <c r="B127" s="48" t="n"/>
-      <c r="C127" s="48" t="n"/>
-      <c r="D127" s="48" t="n"/>
-      <c r="E127" s="48" t="n"/>
-      <c r="F127" s="48" t="n"/>
-    </row>
-    <row r="128" ht="15" customHeight="1" s="102">
-      <c r="A128" s="13" t="inlineStr">
+      <c r="B128" s="48" t="n"/>
+      <c r="C128" s="48" t="n"/>
+      <c r="D128" s="48" t="n"/>
+      <c r="E128" s="48" t="n"/>
+      <c r="F128" s="48" t="n"/>
+    </row>
+    <row r="129" ht="15" customHeight="1" s="102">
+      <c r="A129" s="13" t="inlineStr">
         <is>
           <t>Sacs</t>
         </is>
       </c>
-      <c r="B128" s="13" t="inlineStr">
+      <c r="B129" s="13" t="inlineStr">
         <is>
           <t>Leather Pouch</t>
         </is>
       </c>
-      <c r="C128" s="13" t="inlineStr">
+      <c r="C129" s="13" t="inlineStr">
         <is>
           <t>sac-en-cuir</t>
         </is>
       </c>
-      <c r="D128" s="13" t="inlineStr">
+      <c r="D129" s="13" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="E128" s="14" t="inlineStr">
+      <c r="E129" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F128" s="14" t="inlineStr">
+      <c r="F129" s="14" t="inlineStr">
         <is>
           <t>+1 rangées de sac</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr">
         <is>
           <t>aucun dégât/armure  (0 carte/5 visées)</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="15" customHeight="1" s="102">
-      <c r="A129" s="15" t="inlineStr">
+    <row r="130" ht="15" customHeight="1" s="102">
+      <c r="A130" s="15" t="inlineStr">
         <is>
           <t>Sacs</t>
         </is>
       </c>
-      <c r="B129" s="15" t="inlineStr">
+      <c r="B130" s="15" t="inlineStr">
         <is>
           <t>Big Leather Pouch</t>
         </is>
       </c>
-      <c r="C129" s="15" t="inlineStr">
+      <c r="C130" s="15" t="inlineStr">
         <is>
           <t>grand-sac-en-cuir</t>
         </is>
       </c>
-      <c r="D129" s="15" t="inlineStr">
+      <c r="D130" s="15" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E129" s="16" t="inlineStr">
+      <c r="E130" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F129" s="16" t="inlineStr">
+      <c r="F130" s="16" t="inlineStr">
         <is>
           <t>+2 rangées de sac</t>
-        </is>
-      </c>
-      <c r="G129" s="2" t="inlineStr">
-        <is>
-          <t>aucun dégât/armure  (0 carte/6 visées)</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="15" customHeight="1" s="102">
-      <c r="A130" s="17" t="inlineStr">
-        <is>
-          <t>Sacs</t>
-        </is>
-      </c>
-      <c r="B130" s="17" t="inlineStr">
-        <is>
-          <t>Backpack</t>
-        </is>
-      </c>
-      <c r="C130" s="17" t="inlineStr">
-        <is>
-          <t>sac-a-dos</t>
-        </is>
-      </c>
-      <c r="D130" s="17" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="E130" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F130" s="18" t="inlineStr">
-        <is>
-          <t>+4 rangées de sac</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
@@ -15626,116 +17038,145 @@
       </c>
       <c r="B131" s="17" t="inlineStr">
         <is>
+          <t>Backpack</t>
+        </is>
+      </c>
+      <c r="C131" s="17" t="inlineStr">
+        <is>
+          <t>sac-a-dos</t>
+        </is>
+      </c>
+      <c r="D131" s="17" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="E131" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F131" s="18" t="inlineStr">
+        <is>
+          <t>+4 rangées de sac</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>aucun dégât/armure  (0 carte/6 visées)</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="15" customHeight="1" s="102">
+      <c r="A132" s="17" t="inlineStr">
+        <is>
+          <t>Sacs</t>
+        </is>
+      </c>
+      <c r="B132" s="17" t="inlineStr">
+        <is>
           <t>Huge Leather Pouch</t>
         </is>
       </c>
-      <c r="C131" s="17" t="inlineStr">
+      <c r="C132" s="17" t="inlineStr">
         <is>
           <t>enorme-sac-en-cuir</t>
         </is>
       </c>
-      <c r="D131" s="17" t="inlineStr">
+      <c r="D132" s="17" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="E131" s="18" t="inlineStr">
+      <c r="E132" s="18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F131" s="18" t="inlineStr">
+      <c r="F132" s="18" t="inlineStr">
         <is>
           <t>+3 rangées de sac</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr">
         <is>
           <t>aucun dégât/armure  (0 carte/6 visées)</t>
         </is>
       </c>
     </row>
-    <row r="132" ht="15" customHeight="1" s="102">
-      <c r="A132" s="21" t="inlineStr">
+    <row r="133" ht="15" customHeight="1" s="102">
+      <c r="A133" s="21" t="inlineStr">
         <is>
           <t>Sacs</t>
         </is>
       </c>
-      <c r="B132" s="21" t="inlineStr">
+      <c r="B133" s="21" t="inlineStr">
         <is>
           <t>Bottomless Bag</t>
         </is>
       </c>
-      <c r="C132" s="21" t="inlineStr">
+      <c r="C133" s="21" t="inlineStr">
         <is>
           <t>sac-sans-fond</t>
         </is>
       </c>
-      <c r="D132" s="21" t="inlineStr">
+      <c r="D133" s="21" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="E132" s="22" t="inlineStr">
+      <c r="E133" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F132" s="22" t="inlineStr">
+      <c r="F133" s="22" t="inlineStr">
         <is>
           <t>+6 rangées de sac</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr">
         <is>
           <t>aucun dégât/armure  (0 carte/7 visées)</t>
         </is>
       </c>
     </row>
-    <row r="133" ht="15" customHeight="1" s="102">
-      <c r="A133" s="49" t="inlineStr">
+    <row r="134" ht="15" customHeight="1" s="102">
+      <c r="A134" s="49" t="inlineStr">
         <is>
           <t>Sacs</t>
         </is>
       </c>
-      <c r="B133" s="49" t="inlineStr">
+      <c r="B134" s="49" t="inlineStr">
         <is>
           <t>Master Miner's Bag</t>
         </is>
       </c>
-      <c r="C133" s="49" t="inlineStr">
+      <c r="C134" s="49" t="inlineStr">
         <is>
           <t>sac-maitre-mineur</t>
         </is>
       </c>
-      <c r="D133" s="49" t="inlineStr">
+      <c r="D134" s="49" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="E133" s="50" t="inlineStr">
+      <c r="E134" s="50" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F133" s="50" t="inlineStr">
+      <c r="F134" s="50" t="inlineStr">
         <is>
           <t>+10 rangées de sac</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr">
         <is>
           <t>aucun dégât/armure  (0 carte/8 visées)</t>
         </is>
       </c>
-    </row>
-    <row r="134" ht="15" customHeight="1" s="102">
-      <c r="A134" s="55" t="n"/>
-      <c r="B134" s="55" t="n"/>
-      <c r="C134" s="55" t="n"/>
-      <c r="D134" s="55" t="n"/>
-      <c r="E134" s="55" t="n"/>
-      <c r="F134" s="55" t="n"/>
     </row>
     <row r="135" ht="15" customHeight="1" s="102">
       <c r="A135" s="55" t="n"/>
@@ -15792,6 +17233,14 @@
       <c r="D141" s="55" t="n"/>
       <c r="E141" s="55" t="n"/>
       <c r="F141" s="55" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="55" t="n"/>
+      <c r="B142" s="55" t="n"/>
+      <c r="C142" s="55" t="n"/>
+      <c r="D142" s="55" t="n"/>
+      <c r="E142" s="55" t="n"/>
+      <c r="F142" s="55" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17677,7 +19126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D130"/>
+  <dimension ref="A1:D131"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="102" min="1" max="1"/>
@@ -19798,12 +21247,12 @@
     <row r="110">
       <c r="A110" s="83" t="inlineStr">
         <is>
-          <t>bottes-sang</t>
+          <t>ring-of-luck</t>
         </is>
       </c>
       <c r="B110" s="84" t="inlineStr">
         <is>
-          <t>Blood Greaves</t>
+          <t>Ring of Luck</t>
         </is>
       </c>
       <c r="C110" s="87" t="inlineStr">
@@ -19811,19 +21260,19 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="D110" s="82" t="n">
-        <v>10000</v>
+      <c r="D110" s="104" t="n">
+        <v>11000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="83" t="inlineStr">
         <is>
-          <t>bottes-croise</t>
+          <t>bottes-sang</t>
         </is>
       </c>
       <c r="B111" s="84" t="inlineStr">
         <is>
-          <t>Crusader Greaves</t>
+          <t>Blood Greaves</t>
         </is>
       </c>
       <c r="C111" s="87" t="inlineStr">
@@ -19832,18 +21281,18 @@
         </is>
       </c>
       <c r="D111" s="82" t="n">
-        <v>9900</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="83" t="inlineStr">
         <is>
-          <t>bottes-de-maille</t>
+          <t>bottes-croise</t>
         </is>
       </c>
       <c r="B112" s="84" t="inlineStr">
         <is>
-          <t>Mail Boots</t>
+          <t>Crusader Greaves</t>
         </is>
       </c>
       <c r="C112" s="87" t="inlineStr">
@@ -19852,18 +21301,18 @@
         </is>
       </c>
       <c r="D112" s="82" t="n">
-        <v>8900</v>
+        <v>9900</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="83" t="inlineStr">
         <is>
-          <t>collier-de-saphir-fin</t>
+          <t>bottes-de-maille</t>
         </is>
       </c>
       <c r="B113" s="84" t="inlineStr">
         <is>
-          <t>Nice Sapphire Amulet</t>
+          <t>Mail Boots</t>
         </is>
       </c>
       <c r="C113" s="87" t="inlineStr">
@@ -19872,18 +21321,18 @@
         </is>
       </c>
       <c r="D113" s="82" t="n">
-        <v>8600</v>
+        <v>8900</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="83" t="inlineStr">
         <is>
-          <t>gants-sang</t>
+          <t>collier-de-saphir-fin</t>
         </is>
       </c>
       <c r="B114" s="84" t="inlineStr">
         <is>
-          <t>Blood Gauntlets</t>
+          <t>Nice Sapphire Amulet</t>
         </is>
       </c>
       <c r="C114" s="87" t="inlineStr">
@@ -19892,18 +21341,18 @@
         </is>
       </c>
       <c r="D114" s="82" t="n">
-        <v>9200</v>
+        <v>8600</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="83" t="inlineStr">
         <is>
-          <t>gants-croise</t>
+          <t>gants-sang</t>
         </is>
       </c>
       <c r="B115" s="84" t="inlineStr">
         <is>
-          <t>Crusader Gauntlets</t>
+          <t>Blood Gauntlets</t>
         </is>
       </c>
       <c r="C115" s="87" t="inlineStr">
@@ -19912,18 +21361,18 @@
         </is>
       </c>
       <c r="D115" s="82" t="n">
-        <v>8400</v>
+        <v>9200</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="83" t="inlineStr">
         <is>
-          <t>gants-de-maille</t>
+          <t>gants-croise</t>
         </is>
       </c>
       <c r="B116" s="84" t="inlineStr">
         <is>
-          <t>Mail Glove</t>
+          <t>Crusader Gauntlets</t>
         </is>
       </c>
       <c r="C116" s="87" t="inlineStr">
@@ -19932,18 +21381,18 @@
         </is>
       </c>
       <c r="D116" s="82" t="n">
-        <v>9000</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="83" t="inlineStr">
         <is>
-          <t>sac-a-dos</t>
+          <t>gants-de-maille</t>
         </is>
       </c>
       <c r="B117" s="84" t="inlineStr">
         <is>
-          <t>Backpack</t>
+          <t>Mail Glove</t>
         </is>
       </c>
       <c r="C117" s="87" t="inlineStr">
@@ -19952,18 +21401,18 @@
         </is>
       </c>
       <c r="D117" s="82" t="n">
-        <v>10000</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="83" t="inlineStr">
         <is>
-          <t>enorme-sac-en-cuir</t>
+          <t>sac-a-dos</t>
         </is>
       </c>
       <c r="B118" s="84" t="inlineStr">
         <is>
-          <t>Huge Leather Pouch</t>
+          <t>Backpack</t>
         </is>
       </c>
       <c r="C118" s="87" t="inlineStr">
@@ -19972,18 +21421,18 @@
         </is>
       </c>
       <c r="D118" s="82" t="n">
-        <v>9400</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="83" t="inlineStr">
         <is>
-          <t>chevaliere-ancienne</t>
+          <t>enorme-sac-en-cuir</t>
         </is>
       </c>
       <c r="B119" s="84" t="inlineStr">
         <is>
-          <t>Ancient Signet</t>
+          <t>Huge Leather Pouch</t>
         </is>
       </c>
       <c r="C119" s="87" t="inlineStr">
@@ -19992,18 +21441,18 @@
         </is>
       </c>
       <c r="D119" s="82" t="n">
-        <v>12000</v>
+        <v>9400</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="83" t="inlineStr">
         <is>
-          <t>calice-cristal</t>
+          <t>chevaliere-ancienne</t>
         </is>
       </c>
       <c r="B120" s="84" t="inlineStr">
         <is>
-          <t>Crystal Chalice</t>
+          <t>Ancient Signet</t>
         </is>
       </c>
       <c r="C120" s="87" t="inlineStr">
@@ -20012,18 +21461,18 @@
         </is>
       </c>
       <c r="D120" s="82" t="n">
-        <v>9900</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="83" t="inlineStr">
         <is>
-          <t>idole-doree</t>
+          <t>calice-cristal</t>
         </is>
       </c>
       <c r="B121" s="84" t="inlineStr">
         <is>
-          <t>Gilded Idol</t>
+          <t>Crystal Chalice</t>
         </is>
       </c>
       <c r="C121" s="87" t="inlineStr">
@@ -20032,38 +21481,38 @@
         </is>
       </c>
       <c r="D121" s="82" t="n">
-        <v>10000</v>
+        <v>9900</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="83" t="inlineStr">
         <is>
-          <t>epee-onyx</t>
+          <t>idole-doree</t>
         </is>
       </c>
       <c r="B122" s="84" t="inlineStr">
         <is>
-          <t>Big Onyx Sword</t>
-        </is>
-      </c>
-      <c r="C122" s="88" t="inlineStr">
-        <is>
-          <t>Epic</t>
+          <t>Gilded Idol</t>
+        </is>
+      </c>
+      <c r="C122" s="87" t="inlineStr">
+        <is>
+          <t>Rare</t>
         </is>
       </c>
       <c r="D122" s="82" t="n">
-        <v>64000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="83" t="inlineStr">
         <is>
-          <t>grande-faux</t>
+          <t>epee-onyx</t>
         </is>
       </c>
       <c r="B123" s="84" t="inlineStr">
         <is>
-          <t>Great Scythe</t>
+          <t>Big Onyx Sword</t>
         </is>
       </c>
       <c r="C123" s="88" t="inlineStr">
@@ -20072,18 +21521,18 @@
         </is>
       </c>
       <c r="D123" s="82" t="n">
-        <v>88000</v>
+        <v>64000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="83" t="inlineStr">
         <is>
-          <t>marteau-de-lave</t>
+          <t>grande-faux</t>
         </is>
       </c>
       <c r="B124" s="84" t="inlineStr">
         <is>
-          <t>Magma Hammer</t>
+          <t>Great Scythe</t>
         </is>
       </c>
       <c r="C124" s="88" t="inlineStr">
@@ -20092,18 +21541,18 @@
         </is>
       </c>
       <c r="D124" s="82" t="n">
-        <v>80000</v>
+        <v>88000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="83" t="inlineStr">
         <is>
-          <t>plate-onyx</t>
+          <t>marteau-de-lave</t>
         </is>
       </c>
       <c r="B125" s="84" t="inlineStr">
         <is>
-          <t>Onyx Guard Plate</t>
+          <t>Magma Hammer</t>
         </is>
       </c>
       <c r="C125" s="88" t="inlineStr">
@@ -20112,18 +21561,18 @@
         </is>
       </c>
       <c r="D125" s="82" t="n">
-        <v>65000</v>
+        <v>80000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="83" t="inlineStr">
         <is>
-          <t>bottes-onyx</t>
+          <t>plate-onyx</t>
         </is>
       </c>
       <c r="B126" s="84" t="inlineStr">
         <is>
-          <t>Onyx Boots</t>
+          <t>Onyx Guard Plate</t>
         </is>
       </c>
       <c r="C126" s="88" t="inlineStr">
@@ -20132,18 +21581,18 @@
         </is>
       </c>
       <c r="D126" s="82" t="n">
-        <v>70000</v>
+        <v>65000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="83" t="inlineStr">
         <is>
-          <t>collier-de-saphir-parfait</t>
+          <t>bottes-onyx</t>
         </is>
       </c>
       <c r="B127" s="84" t="inlineStr">
         <is>
-          <t>Perfect Sapphire Amulet</t>
+          <t>Onyx Boots</t>
         </is>
       </c>
       <c r="C127" s="88" t="inlineStr">
@@ -20152,18 +21601,18 @@
         </is>
       </c>
       <c r="D127" s="82" t="n">
-        <v>84000</v>
+        <v>70000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="83" t="inlineStr">
         <is>
-          <t>gants-onyx</t>
+          <t>collier-de-saphir-parfait</t>
         </is>
       </c>
       <c r="B128" s="84" t="inlineStr">
         <is>
-          <t>Onyx Glove</t>
+          <t>Perfect Sapphire Amulet</t>
         </is>
       </c>
       <c r="C128" s="88" t="inlineStr">
@@ -20172,18 +21621,18 @@
         </is>
       </c>
       <c r="D128" s="82" t="n">
-        <v>82000</v>
+        <v>84000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="83" t="inlineStr">
         <is>
-          <t>sac-sans-fond</t>
+          <t>gants-onyx</t>
         </is>
       </c>
       <c r="B129" s="84" t="inlineStr">
         <is>
-          <t>Bottomless Bag</t>
+          <t>Onyx Glove</t>
         </is>
       </c>
       <c r="C129" s="88" t="inlineStr">
@@ -20192,26 +21641,46 @@
         </is>
       </c>
       <c r="D129" s="82" t="n">
-        <v>94000</v>
+        <v>82000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="83" t="inlineStr">
         <is>
+          <t>sac-sans-fond</t>
+        </is>
+      </c>
+      <c r="B130" s="84" t="inlineStr">
+        <is>
+          <t>Bottomless Bag</t>
+        </is>
+      </c>
+      <c r="C130" s="88" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="D130" s="82" t="n">
+        <v>94000</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="83" t="inlineStr">
+        <is>
           <t>sac-maitre-mineur</t>
         </is>
       </c>
-      <c r="B130" s="84" t="inlineStr">
+      <c r="B131" s="84" t="inlineStr">
         <is>
           <t>Master Miner's Bag</t>
         </is>
       </c>
-      <c r="C130" s="89" t="inlineStr">
+      <c r="C131" s="89" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="D130" s="82" t="n">
+      <c r="D131" s="82" t="n">
         <v>290000</v>
       </c>
     </row>

--- a/docs/BRUTAL-items-et-cartes.xlsx
+++ b/docs/BRUTAL-items-et-cartes.xlsx
@@ -28,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -164,8 +164,13 @@
       <b val="1"/>
       <color rgb="001F3864"/>
     </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00555555"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="62">
+  <fills count="68">
     <fill>
       <patternFill/>
     </fill>
@@ -472,8 +477,38 @@
         <fgColor rgb="004472C4"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="006E8B3D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007A4A2B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="003E7C7C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008A5A2B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007A5AA0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A03030"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -525,11 +560,25 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D0D0D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D0D0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="112">
+  <cellXfs count="128">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -766,6 +815,30 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="60" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="62" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="62" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="63" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="63" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="64" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="64" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="65" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="65" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="66" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="66" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="67" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="67" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1536,1283 +1609,1490 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:L36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" style="102" min="1" max="1"/>
+    <col width="24" customWidth="1" style="102" min="1" max="1"/>
     <col width="20" customWidth="1" style="102" min="2" max="2"/>
     <col width="8" customWidth="1" style="102" min="3" max="3"/>
-    <col width="12" customWidth="1" style="102" min="4" max="4"/>
+    <col width="11" customWidth="1" style="102" min="4" max="4"/>
     <col width="7" customWidth="1" style="102" min="5" max="5"/>
-    <col width="9" customWidth="1" style="102" min="6" max="6"/>
+    <col width="10" customWidth="1" style="102" min="6" max="6"/>
     <col width="7" customWidth="1" style="102" min="7" max="7"/>
     <col width="9" customWidth="1" style="102" min="8" max="8"/>
-    <col width="52" customWidth="1" style="102" min="9" max="9"/>
-    <col width="42" customWidth="1" style="102" min="10" max="10"/>
-    <col width="26" customWidth="1" style="102" min="11" max="11"/>
+    <col width="26" customWidth="1" style="102" min="9" max="9"/>
+    <col width="8" customWidth="1" style="102" min="10" max="10"/>
+    <col width="30" customWidth="1" style="102" min="11" max="11"/>
+    <col width="34" customWidth="1" style="102" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="97" t="inlineStr">
+      <c r="A1" s="112" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" s="97" t="inlineStr">
+      <c r="B1" s="112" t="inlineStr">
         <is>
           <t>nom</t>
         </is>
       </c>
-      <c r="C1" s="97" t="inlineStr">
+      <c r="C1" s="112" t="inlineStr">
         <is>
           <t>niveau</t>
         </is>
       </c>
-      <c r="D1" s="97" t="inlineStr">
+      <c r="D1" s="112" t="inlineStr">
         <is>
           <t>famille</t>
         </is>
       </c>
-      <c r="E1" s="97" t="inlineStr">
+      <c r="E1" s="112" t="inlineStr">
         <is>
           <t>pv</t>
         </is>
       </c>
-      <c r="F1" s="97" t="inlineStr">
+      <c r="F1" s="112" t="inlineStr">
         <is>
           <t>attaque</t>
         </is>
       </c>
-      <c r="G1" s="97" t="inlineStr">
+      <c r="G1" s="112" t="inlineStr">
         <is>
           <t>xp</t>
         </is>
       </c>
-      <c r="H1" s="97" t="inlineStr">
+      <c r="H1" s="112" t="inlineStr">
         <is>
           <t>vitesse</t>
         </is>
       </c>
-      <c r="I1" s="97" t="inlineStr">
-        <is>
-          <t>actions</t>
-        </is>
-      </c>
-      <c r="J1" s="97" t="inlineStr">
+      <c r="I1" s="112" t="inlineStr">
+        <is>
+          <t>actions spéciales</t>
+        </is>
+      </c>
+      <c r="J1" s="112" t="inlineStr">
         <is>
           <t>grand</t>
         </is>
       </c>
-      <c r="K1" s="103" t="inlineStr">
+      <c r="K1" s="112" t="inlineStr">
         <is>
           <t>zone de pop</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="98" t="inlineStr">
+      <c r="L1" s="112" t="inlineStr">
+        <is>
+          <t>passif / note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="54" customHeight="1" s="102">
+      <c r="A2" s="113" t="inlineStr">
         <is>
           <t>identifiant (ne pas changer)</t>
         </is>
       </c>
-      <c r="B2" s="98" t="inlineStr">
+      <c r="B2" s="113" t="inlineStr">
         <is>
           <t>nom affiché (anglais)</t>
         </is>
       </c>
-      <c r="C2" s="98" t="inlineStr">
+      <c r="C2" s="113" t="inlineStr">
         <is>
           <t>niveau (→ or lâché)</t>
         </is>
       </c>
-      <c r="D2" s="98" t="inlineStr">
-        <is>
-          <t>gobelin / animal / (vide)</t>
-        </is>
-      </c>
-      <c r="E2" s="98" t="inlineStr">
+      <c r="D2" s="113" t="inlineStr">
+        <is>
+          <t>gobelin / orc / blob / animal / mushroom / lapin</t>
+        </is>
+      </c>
+      <c r="E2" s="113" t="inlineStr">
         <is>
           <t>points de vie</t>
         </is>
       </c>
-      <c r="F2" s="98" t="inlineStr">
-        <is>
-          <t>dégâts par coup</t>
-        </is>
-      </c>
-      <c r="G2" s="98" t="inlineStr">
-        <is>
-          <t>XP donnée à la mort</t>
-        </is>
-      </c>
-      <c r="H2" s="98" t="inlineStr">
-        <is>
-          <t>vitesse d'initiative ET d'animation (grand = rapide)</t>
-        </is>
-      </c>
-      <c r="I2" s="98" t="inlineStr">
-        <is>
-          <t>actions spéciales : type:valeur:poids séparés par | (types: attaque, soigner, haste-allie). Vide = attaque simple.</t>
-        </is>
-      </c>
-      <c r="J2" s="98" t="inlineStr">
-        <is>
-          <t>met 1 si le monstre est GRAND (occupe 2 places, pop plus rare). Vide = normal.</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>où le monstre apparaît : « Eastern + profondeur » (surface est + mine) ou « Profondeur » (mine uniquement, étage 2+)</t>
+      <c r="F2" s="113" t="inlineStr">
+        <is>
+          <t>dégâts par coup. Multi-coups : « NxM » = N dégâts × M coups (ex. 2x2)</t>
+        </is>
+      </c>
+      <c r="G2" s="113" t="inlineStr">
+        <is>
+          <t>XP à la mort</t>
+        </is>
+      </c>
+      <c r="H2" s="113" t="inlineStr">
+        <is>
+          <t>vitesse d'initiative ET d'animation</t>
+        </is>
+      </c>
+      <c r="I2" s="113" t="inlineStr">
+        <is>
+          <t>attaques spéciales, UNE PAR LIGNE : « Libellé valeur (chance%) ». Libellés : Soin, Hâte alliés, Attaque. Les % somment à 100. Vide = attaque simple.</t>
+        </is>
+      </c>
+      <c r="J2" s="113" t="inlineStr">
+        <is>
+          <t>1 si GRAND (occupe 2 places, pop plus rare)</t>
+        </is>
+      </c>
+      <c r="K2" s="113" t="inlineStr">
+        <is>
+          <t>où il apparaît</t>
+        </is>
+      </c>
+      <c r="L2" s="113" t="inlineStr">
+        <is>
+          <t>passif / mémo (poison, meute…) — NON lu par l'importer, purement informatif</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="114" t="inlineStr">
+        <is>
+          <t>▸ GOBELINS</t>
+        </is>
+      </c>
+      <c r="B3" s="115" t="n"/>
+      <c r="C3" s="115" t="n"/>
+      <c r="D3" s="115" t="n"/>
+      <c r="E3" s="115" t="n"/>
+      <c r="F3" s="115" t="n"/>
+      <c r="G3" s="115" t="n"/>
+      <c r="H3" s="115" t="n"/>
+      <c r="I3" s="115" t="n"/>
+      <c r="J3" s="115" t="n"/>
+      <c r="K3" s="115" t="n"/>
+      <c r="L3" s="115" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="116" t="inlineStr">
+        <is>
+          <t>gobelin-vif</t>
+        </is>
+      </c>
+      <c r="B4" s="116" t="inlineStr">
+        <is>
+          <t>Goblin Skirmisher</t>
+        </is>
+      </c>
+      <c r="C4" s="117" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="116" t="inlineStr">
         <is>
           <t>gobelin</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="E4" s="117" t="n">
+        <v>16</v>
+      </c>
+      <c r="F4" s="117" t="inlineStr">
+        <is>
+          <t>2x2</t>
+        </is>
+      </c>
+      <c r="G4" s="117" t="n">
+        <v>8</v>
+      </c>
+      <c r="H4" s="117" t="n">
+        <v>11</v>
+      </c>
+      <c r="I4" s="116" t="inlineStr"/>
+      <c r="J4" s="117" t="n"/>
+      <c r="K4" s="116" t="inlineStr">
+        <is>
+          <t>Eastern + profondeur</t>
+        </is>
+      </c>
+      <c r="L4" s="116" t="inlineStr">
+        <is>
+          <t>1 poison par coup</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="116" t="inlineStr">
+        <is>
+          <t>gobelin</t>
+        </is>
+      </c>
+      <c r="B5" s="116" t="inlineStr">
         <is>
           <t>Cave Goblin</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C5" s="117" t="n">
         <v>1</v>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D5" s="116" t="inlineStr">
         <is>
           <t>gobelin</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E5" s="117" t="n">
         <v>24</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F5" s="117" t="n">
         <v>5</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G5" s="117" t="n">
         <v>6</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H5" s="117" t="n">
         <v>6</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="I5" s="116" t="inlineStr"/>
+      <c r="J5" s="117" t="n"/>
+      <c r="K5" s="116" t="inlineStr">
         <is>
           <t>Eastern + profondeur</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>gobelin-vif</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Goblin Skirmisher</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
+      <c r="L5" s="116" t="inlineStr"/>
+    </row>
+    <row r="6" ht="59" customHeight="1" s="102">
+      <c r="A6" s="116" t="inlineStr">
+        <is>
+          <t>gobelin-chaman</t>
+        </is>
+      </c>
+      <c r="B6" s="116" t="inlineStr">
+        <is>
+          <t>Goblin Shaman</t>
+        </is>
+      </c>
+      <c r="C6" s="117" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="116" t="inlineStr">
+        <is>
+          <t>gobelin</t>
+        </is>
+      </c>
+      <c r="E6" s="117" t="n">
+        <v>20</v>
+      </c>
+      <c r="F6" s="117" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" s="117" t="n">
+        <v>20</v>
+      </c>
+      <c r="H6" s="117" t="n">
+        <v>7</v>
+      </c>
+      <c r="I6" s="116" t="inlineStr">
+        <is>
+          <t>Soin 10 (50%)
+Hâte alliés 2 (30%)
+Attaque 2 (20%)</t>
+        </is>
+      </c>
+      <c r="J6" s="117" t="n"/>
+      <c r="K6" s="116" t="inlineStr">
+        <is>
+          <t>Eastern + profondeur</t>
+        </is>
+      </c>
+      <c r="L6" s="116" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="118" t="inlineStr">
+        <is>
+          <t>▸ ORCS</t>
+        </is>
+      </c>
+      <c r="B7" s="119" t="n"/>
+      <c r="C7" s="119" t="n"/>
+      <c r="D7" s="119" t="n"/>
+      <c r="E7" s="119" t="n"/>
+      <c r="F7" s="119" t="n"/>
+      <c r="G7" s="119" t="n"/>
+      <c r="H7" s="119" t="n"/>
+      <c r="I7" s="119" t="n"/>
+      <c r="J7" s="119" t="n"/>
+      <c r="K7" s="119" t="n"/>
+      <c r="L7" s="119" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="116" t="inlineStr">
+        <is>
+          <t>orc-rodeur</t>
+        </is>
+      </c>
+      <c r="B8" s="116" t="inlineStr">
+        <is>
+          <t>Orc Rogue</t>
+        </is>
+      </c>
+      <c r="C8" s="117" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" s="116" t="inlineStr">
+        <is>
+          <t>orc</t>
+        </is>
+      </c>
+      <c r="E8" s="117" t="n">
+        <v>40</v>
+      </c>
+      <c r="F8" s="117" t="inlineStr">
+        <is>
+          <t>6x2</t>
+        </is>
+      </c>
+      <c r="G8" s="117" t="n">
+        <v>22</v>
+      </c>
+      <c r="H8" s="117" t="n">
+        <v>15</v>
+      </c>
+      <c r="I8" s="116" t="inlineStr"/>
+      <c r="J8" s="117" t="n"/>
+      <c r="K8" s="116" t="inlineStr">
+        <is>
+          <t>Profondeur (mine, étage 2+)</t>
+        </is>
+      </c>
+      <c r="L8" s="116" t="inlineStr"/>
+    </row>
+    <row r="9" ht="59" customHeight="1" s="102">
+      <c r="A9" s="116" t="inlineStr">
+        <is>
+          <t>orc-chamane</t>
+        </is>
+      </c>
+      <c r="B9" s="116" t="inlineStr">
+        <is>
+          <t>Orc Shaman</t>
+        </is>
+      </c>
+      <c r="C9" s="117" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" s="116" t="inlineStr">
+        <is>
+          <t>orc</t>
+        </is>
+      </c>
+      <c r="E9" s="117" t="n">
+        <v>45</v>
+      </c>
+      <c r="F9" s="117" t="n">
+        <v>6</v>
+      </c>
+      <c r="G9" s="117" t="n">
+        <v>36</v>
+      </c>
+      <c r="H9" s="117" t="n">
+        <v>7</v>
+      </c>
+      <c r="I9" s="116" t="inlineStr">
+        <is>
+          <t>Soin 12 (45%)
+Hâte alliés 2 (30%)
+Attaque 6 (25%)</t>
+        </is>
+      </c>
+      <c r="J9" s="117" t="n"/>
+      <c r="K9" s="116" t="inlineStr">
+        <is>
+          <t>Profondeur (mine, étage 2+)</t>
+        </is>
+      </c>
+      <c r="L9" s="116" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="116" t="inlineStr">
+        <is>
+          <t>orc-guerriere</t>
+        </is>
+      </c>
+      <c r="B10" s="116" t="inlineStr">
+        <is>
+          <t>Orc Warmaiden</t>
+        </is>
+      </c>
+      <c r="C10" s="117" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" s="116" t="inlineStr">
+        <is>
+          <t>orc</t>
+        </is>
+      </c>
+      <c r="E10" s="117" t="n">
+        <v>60</v>
+      </c>
+      <c r="F10" s="117" t="n">
+        <v>16</v>
+      </c>
+      <c r="G10" s="117" t="n">
+        <v>34</v>
+      </c>
+      <c r="H10" s="117" t="n">
+        <v>9</v>
+      </c>
+      <c r="I10" s="116" t="inlineStr"/>
+      <c r="J10" s="117" t="n"/>
+      <c r="K10" s="116" t="inlineStr">
+        <is>
+          <t>Profondeur (mine, étage 2+)</t>
+        </is>
+      </c>
+      <c r="L10" s="116" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="116" t="inlineStr">
+        <is>
+          <t>orc-guerrier</t>
+        </is>
+      </c>
+      <c r="B11" s="116" t="inlineStr">
+        <is>
+          <t>Orc Warrior</t>
+        </is>
+      </c>
+      <c r="C11" s="117" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" s="116" t="inlineStr">
+        <is>
+          <t>orc</t>
+        </is>
+      </c>
+      <c r="E11" s="117" t="n">
+        <v>75</v>
+      </c>
+      <c r="F11" s="117" t="n">
+        <v>12</v>
+      </c>
+      <c r="G11" s="117" t="n">
+        <v>30</v>
+      </c>
+      <c r="H11" s="117" t="n">
+        <v>8</v>
+      </c>
+      <c r="I11" s="116" t="inlineStr"/>
+      <c r="J11" s="117" t="n"/>
+      <c r="K11" s="116" t="inlineStr">
+        <is>
+          <t>Profondeur (mine, étage 2+)</t>
+        </is>
+      </c>
+      <c r="L11" s="116" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="116" t="inlineStr">
+        <is>
+          <t>orc-brute</t>
+        </is>
+      </c>
+      <c r="B12" s="116" t="inlineStr">
+        <is>
+          <t>Orc Berserker</t>
+        </is>
+      </c>
+      <c r="C12" s="117" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" s="116" t="inlineStr">
+        <is>
+          <t>orc</t>
+        </is>
+      </c>
+      <c r="E12" s="117" t="n">
+        <v>95</v>
+      </c>
+      <c r="F12" s="117" t="n">
+        <v>20</v>
+      </c>
+      <c r="G12" s="117" t="n">
+        <v>44</v>
+      </c>
+      <c r="H12" s="117" t="n">
+        <v>6</v>
+      </c>
+      <c r="I12" s="116" t="inlineStr"/>
+      <c r="J12" s="117" t="n">
         <v>1</v>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>gobelin</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
+      <c r="K12" s="116" t="inlineStr">
+        <is>
+          <t>Profondeur (mine, étage 2+)</t>
+        </is>
+      </c>
+      <c r="L12" s="116" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="120" t="inlineStr">
+        <is>
+          <t>▸ BLOBS (limons)</t>
+        </is>
+      </c>
+      <c r="B13" s="121" t="n"/>
+      <c r="C13" s="121" t="n"/>
+      <c r="D13" s="121" t="n"/>
+      <c r="E13" s="121" t="n"/>
+      <c r="F13" s="121" t="n"/>
+      <c r="G13" s="121" t="n"/>
+      <c r="H13" s="121" t="n"/>
+      <c r="I13" s="121" t="n"/>
+      <c r="J13" s="121" t="n"/>
+      <c r="K13" s="121" t="n"/>
+      <c r="L13" s="121" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="116" t="inlineStr">
+        <is>
+          <t>blob-jaune</t>
+        </is>
+      </c>
+      <c r="B14" s="116" t="inlineStr">
+        <is>
+          <t>Ochre Slime</t>
+        </is>
+      </c>
+      <c r="C14" s="117" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" s="116" t="inlineStr">
+        <is>
+          <t>blob</t>
+        </is>
+      </c>
+      <c r="E14" s="117" t="n">
+        <v>50</v>
+      </c>
+      <c r="F14" s="117" t="n">
+        <v>8</v>
+      </c>
+      <c r="G14" s="117" t="n">
+        <v>24</v>
+      </c>
+      <c r="H14" s="117" t="n">
+        <v>4</v>
+      </c>
+      <c r="I14" s="116" t="inlineStr"/>
+      <c r="J14" s="117" t="n"/>
+      <c r="K14" s="116" t="inlineStr">
+        <is>
+          <t>Profondeur (mine, étage 2+)</t>
+        </is>
+      </c>
+      <c r="L14" s="116" t="inlineStr">
+        <is>
+          <t>3 poison par coup (acide)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="116" t="inlineStr">
+        <is>
+          <t>blob-vert</t>
+        </is>
+      </c>
+      <c r="B15" s="116" t="inlineStr">
+        <is>
+          <t>Green Slime</t>
+        </is>
+      </c>
+      <c r="C15" s="117" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" s="116" t="inlineStr">
+        <is>
+          <t>blob</t>
+        </is>
+      </c>
+      <c r="E15" s="117" t="n">
+        <v>55</v>
+      </c>
+      <c r="F15" s="117" t="n">
+        <v>8</v>
+      </c>
+      <c r="G15" s="117" t="n">
+        <v>24</v>
+      </c>
+      <c r="H15" s="117" t="n">
+        <v>4</v>
+      </c>
+      <c r="I15" s="116" t="inlineStr"/>
+      <c r="J15" s="117" t="n"/>
+      <c r="K15" s="116" t="inlineStr">
+        <is>
+          <t>Profondeur (mine, étage 2+)</t>
+        </is>
+      </c>
+      <c r="L15" s="116" t="inlineStr">
+        <is>
+          <t>2 poison par coup</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="116" t="inlineStr">
+        <is>
+          <t>blob-bleu</t>
+        </is>
+      </c>
+      <c r="B16" s="116" t="inlineStr">
+        <is>
+          <t>Azure Slime</t>
+        </is>
+      </c>
+      <c r="C16" s="117" t="n">
+        <v>4</v>
+      </c>
+      <c r="D16" s="116" t="inlineStr">
+        <is>
+          <t>blob</t>
+        </is>
+      </c>
+      <c r="E16" s="117" t="n">
+        <v>65</v>
+      </c>
+      <c r="F16" s="117" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" s="117" t="n">
+        <v>30</v>
+      </c>
+      <c r="H16" s="117" t="n">
+        <v>4</v>
+      </c>
+      <c r="I16" s="116" t="inlineStr"/>
+      <c r="J16" s="117" t="n"/>
+      <c r="K16" s="116" t="inlineStr">
+        <is>
+          <t>Profondeur (mine, étage 2+)</t>
+        </is>
+      </c>
+      <c r="L16" s="116" t="inlineStr">
+        <is>
+          <t>piquants</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="116" t="inlineStr">
+        <is>
+          <t>blob-rouge</t>
+        </is>
+      </c>
+      <c r="B17" s="116" t="inlineStr">
+        <is>
+          <t>Crimson Slime</t>
+        </is>
+      </c>
+      <c r="C17" s="117" t="n">
+        <v>4</v>
+      </c>
+      <c r="D17" s="116" t="inlineStr">
+        <is>
+          <t>blob</t>
+        </is>
+      </c>
+      <c r="E17" s="117" t="n">
+        <v>80</v>
+      </c>
+      <c r="F17" s="117" t="n">
+        <v>10</v>
+      </c>
+      <c r="G17" s="117" t="n">
+        <v>30</v>
+      </c>
+      <c r="H17" s="117" t="n">
+        <v>4</v>
+      </c>
+      <c r="I17" s="116" t="inlineStr"/>
+      <c r="J17" s="117" t="n"/>
+      <c r="K17" s="116" t="inlineStr">
+        <is>
+          <t>Profondeur (mine, étage 2+)</t>
+        </is>
+      </c>
+      <c r="L17" s="116" t="inlineStr">
+        <is>
+          <t>très résistant</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="122" t="inlineStr">
+        <is>
+          <t>▸ ANIMAUX (bêtes — lâchent du cuir)</t>
+        </is>
+      </c>
+      <c r="B18" s="123" t="n"/>
+      <c r="C18" s="123" t="n"/>
+      <c r="D18" s="123" t="n"/>
+      <c r="E18" s="123" t="n"/>
+      <c r="F18" s="123" t="n"/>
+      <c r="G18" s="123" t="n"/>
+      <c r="H18" s="123" t="n"/>
+      <c r="I18" s="123" t="n"/>
+      <c r="J18" s="123" t="n"/>
+      <c r="K18" s="123" t="n"/>
+      <c r="L18" s="123" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="116" t="inlineStr">
+        <is>
+          <t>molosse</t>
+        </is>
+      </c>
+      <c r="B19" s="116" t="inlineStr">
+        <is>
+          <t>Dire Hound</t>
+        </is>
+      </c>
+      <c r="C19" s="117" t="n">
+        <v>3</v>
+      </c>
+      <c r="D19" s="116" t="inlineStr">
+        <is>
+          <t>animal</t>
+        </is>
+      </c>
+      <c r="E19" s="117" t="n">
+        <v>40</v>
+      </c>
+      <c r="F19" s="117" t="n">
+        <v>10</v>
+      </c>
+      <c r="G19" s="117" t="n">
+        <v>22</v>
+      </c>
+      <c r="H19" s="117" t="n">
         <v>16</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2x2</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
+      <c r="I19" s="116" t="inlineStr"/>
+      <c r="J19" s="117" t="n"/>
+      <c r="K19" s="116" t="inlineStr">
+        <is>
+          <t>Profondeur (mine, étage 2+)</t>
+        </is>
+      </c>
+      <c r="L19" s="116" t="inlineStr">
+        <is>
+          <t>rapide ; en meute</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="116" t="inlineStr">
+        <is>
+          <t>ogre-masque</t>
+        </is>
+      </c>
+      <c r="B20" s="116" t="inlineStr">
+        <is>
+          <t>Masked Ogre</t>
+        </is>
+      </c>
+      <c r="C20" s="117" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" s="116" t="inlineStr">
+        <is>
+          <t>animal</t>
+        </is>
+      </c>
+      <c r="E20" s="117" t="n">
+        <v>80</v>
+      </c>
+      <c r="F20" s="117" t="n">
+        <v>30</v>
+      </c>
+      <c r="G20" s="117" t="n">
+        <v>60</v>
+      </c>
+      <c r="H20" s="117" t="n">
+        <v>5</v>
+      </c>
+      <c r="I20" s="116" t="inlineStr"/>
+      <c r="J20" s="117" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" s="116" t="inlineStr">
+        <is>
+          <t>Eastern + profondeur</t>
+        </is>
+      </c>
+      <c r="L20" s="116" t="inlineStr">
+        <is>
+          <t>pic de difficulté</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="116" t="inlineStr">
+        <is>
+          <t>molosse-sombre</t>
+        </is>
+      </c>
+      <c r="B21" s="116" t="inlineStr">
+        <is>
+          <t>Shadow Hound</t>
+        </is>
+      </c>
+      <c r="C21" s="117" t="n">
+        <v>4</v>
+      </c>
+      <c r="D21" s="116" t="inlineStr">
+        <is>
+          <t>animal</t>
+        </is>
+      </c>
+      <c r="E21" s="117" t="n">
+        <v>42</v>
+      </c>
+      <c r="F21" s="117" t="n">
+        <v>11</v>
+      </c>
+      <c r="G21" s="117" t="n">
+        <v>26</v>
+      </c>
+      <c r="H21" s="117" t="n">
+        <v>17</v>
+      </c>
+      <c r="I21" s="116" t="inlineStr"/>
+      <c r="J21" s="117" t="n"/>
+      <c r="K21" s="116" t="inlineStr">
+        <is>
+          <t>Profondeur (mine, étage 2+)</t>
+        </is>
+      </c>
+      <c r="L21" s="116" t="inlineStr">
+        <is>
+          <t>rapide ; en meute</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="116" t="inlineStr">
+        <is>
+          <t>molosse-feu</t>
+        </is>
+      </c>
+      <c r="B22" s="116" t="inlineStr">
+        <is>
+          <t>Ember Hound</t>
+        </is>
+      </c>
+      <c r="C22" s="117" t="n">
+        <v>4</v>
+      </c>
+      <c r="D22" s="116" t="inlineStr">
+        <is>
+          <t>animal</t>
+        </is>
+      </c>
+      <c r="E22" s="117" t="n">
+        <v>45</v>
+      </c>
+      <c r="F22" s="117" t="n">
+        <v>12</v>
+      </c>
+      <c r="G22" s="117" t="n">
+        <v>28</v>
+      </c>
+      <c r="H22" s="117" t="n">
+        <v>15</v>
+      </c>
+      <c r="I22" s="116" t="inlineStr"/>
+      <c r="J22" s="117" t="n"/>
+      <c r="K22" s="116" t="inlineStr">
+        <is>
+          <t>Profondeur (mine, étage 2+)</t>
+        </is>
+      </c>
+      <c r="L22" s="116" t="inlineStr">
+        <is>
+          <t>rapide, feu ; en meute</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="116" t="inlineStr">
+        <is>
+          <t>bear</t>
+        </is>
+      </c>
+      <c r="B23" s="116" t="inlineStr">
+        <is>
+          <t>Cave Bear</t>
+        </is>
+      </c>
+      <c r="C23" s="117" t="n">
+        <v>4</v>
+      </c>
+      <c r="D23" s="116" t="inlineStr">
+        <is>
+          <t>animal</t>
+        </is>
+      </c>
+      <c r="E23" s="117" t="n">
+        <v>90</v>
+      </c>
+      <c r="F23" s="117" t="n">
+        <v>14</v>
+      </c>
+      <c r="G23" s="117" t="n">
+        <v>32</v>
+      </c>
+      <c r="H23" s="117" t="n">
         <v>8</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I23" s="116" t="inlineStr"/>
+      <c r="J23" s="117" t="n"/>
+      <c r="K23" s="116" t="inlineStr">
+        <is>
+          <t>Profondeur (mine, étage 2+)</t>
+        </is>
+      </c>
+      <c r="L23" s="116" t="inlineStr">
+        <is>
+          <t>en meute avec les molosses</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="116" t="inlineStr">
+        <is>
+          <t>bones-bear</t>
+        </is>
+      </c>
+      <c r="B24" s="116" t="inlineStr">
+        <is>
+          <t>Bonehide Bear</t>
+        </is>
+      </c>
+      <c r="C24" s="117" t="n">
+        <v>5</v>
+      </c>
+      <c r="D24" s="116" t="inlineStr">
+        <is>
+          <t>animal</t>
+        </is>
+      </c>
+      <c r="E24" s="117" t="n">
+        <v>100</v>
+      </c>
+      <c r="F24" s="117" t="n">
+        <v>16</v>
+      </c>
+      <c r="G24" s="117" t="n">
+        <v>44</v>
+      </c>
+      <c r="H24" s="117" t="n">
+        <v>9</v>
+      </c>
+      <c r="I24" s="116" t="inlineStr"/>
+      <c r="J24" s="117" t="n"/>
+      <c r="K24" s="116" t="inlineStr">
+        <is>
+          <t>Profondeur (mine, étage 2+)</t>
+        </is>
+      </c>
+      <c r="L24" s="116" t="inlineStr">
+        <is>
+          <t>en meute avec les molosses</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="116" t="inlineStr">
+        <is>
+          <t>armor-bear</t>
+        </is>
+      </c>
+      <c r="B25" s="116" t="inlineStr">
+        <is>
+          <t>Armored War-Bear</t>
+        </is>
+      </c>
+      <c r="C25" s="117" t="n">
+        <v>6</v>
+      </c>
+      <c r="D25" s="116" t="inlineStr">
+        <is>
+          <t>animal</t>
+        </is>
+      </c>
+      <c r="E25" s="117" t="n">
+        <v>150</v>
+      </c>
+      <c r="F25" s="117" t="n">
+        <v>20</v>
+      </c>
+      <c r="G25" s="117" t="n">
+        <v>60</v>
+      </c>
+      <c r="H25" s="117" t="n">
+        <v>6</v>
+      </c>
+      <c r="I25" s="116" t="inlineStr"/>
+      <c r="J25" s="117" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" s="116" t="inlineStr">
+        <is>
+          <t>Profondeur (mine, étage 2+)</t>
+        </is>
+      </c>
+      <c r="L25" s="116" t="inlineStr">
+        <is>
+          <t>en meute avec les molosses</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="124" t="inlineStr">
+        <is>
+          <t>▸ CHAMPIGNONS</t>
+        </is>
+      </c>
+      <c r="B26" s="125" t="n"/>
+      <c r="C26" s="125" t="n"/>
+      <c r="D26" s="125" t="n"/>
+      <c r="E26" s="125" t="n"/>
+      <c r="F26" s="125" t="n"/>
+      <c r="G26" s="125" t="n"/>
+      <c r="H26" s="125" t="n"/>
+      <c r="I26" s="125" t="n"/>
+      <c r="J26" s="125" t="n"/>
+      <c r="K26" s="125" t="n"/>
+      <c r="L26" s="125" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="116" t="inlineStr">
+        <is>
+          <t>warrior-mushroom1</t>
+        </is>
+      </c>
+      <c r="B27" s="116" t="inlineStr">
+        <is>
+          <t>Toadstool Lancer</t>
+        </is>
+      </c>
+      <c r="C27" s="117" t="n">
+        <v>3</v>
+      </c>
+      <c r="D27" s="116" t="inlineStr">
+        <is>
+          <t>mushroom</t>
+        </is>
+      </c>
+      <c r="E27" s="117" t="n">
+        <v>50</v>
+      </c>
+      <c r="F27" s="117" t="n">
+        <v>8</v>
+      </c>
+      <c r="G27" s="117" t="n">
+        <v>22</v>
+      </c>
+      <c r="H27" s="117" t="n">
+        <v>8</v>
+      </c>
+      <c r="I27" s="116" t="inlineStr"/>
+      <c r="J27" s="117" t="n"/>
+      <c r="K27" s="116" t="inlineStr">
+        <is>
+          <t>Profondeur (mine, étage 2+)</t>
+        </is>
+      </c>
+      <c r="L27" s="116" t="inlineStr"/>
+    </row>
+    <row r="28" ht="59" customHeight="1" s="102">
+      <c r="A28" s="116" t="inlineStr">
+        <is>
+          <t>mage-mushroom</t>
+        </is>
+      </c>
+      <c r="B28" s="116" t="inlineStr">
+        <is>
+          <t>Myconid Sage</t>
+        </is>
+      </c>
+      <c r="C28" s="117" t="n">
+        <v>4</v>
+      </c>
+      <c r="D28" s="116" t="inlineStr">
+        <is>
+          <t>mushroom</t>
+        </is>
+      </c>
+      <c r="E28" s="117" t="n">
+        <v>40</v>
+      </c>
+      <c r="F28" s="117" t="n">
+        <v>5</v>
+      </c>
+      <c r="G28" s="117" t="n">
+        <v>34</v>
+      </c>
+      <c r="H28" s="117" t="n">
+        <v>7</v>
+      </c>
+      <c r="I28" s="116" t="inlineStr">
+        <is>
+          <t>Soin 12 (45%)
+Hâte alliés 2 (30%)
+Attaque 5 (25%)</t>
+        </is>
+      </c>
+      <c r="J28" s="117" t="n"/>
+      <c r="K28" s="116" t="inlineStr">
+        <is>
+          <t>Profondeur (mine, étage 2+)</t>
+        </is>
+      </c>
+      <c r="L28" s="116" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="116" t="inlineStr">
+        <is>
+          <t>white-katana-mushroom</t>
+        </is>
+      </c>
+      <c r="B29" s="116" t="inlineStr">
+        <is>
+          <t>Myconid Ronin</t>
+        </is>
+      </c>
+      <c r="C29" s="117" t="n">
+        <v>4</v>
+      </c>
+      <c r="D29" s="116" t="inlineStr">
+        <is>
+          <t>mushroom</t>
+        </is>
+      </c>
+      <c r="E29" s="117" t="n">
+        <v>45</v>
+      </c>
+      <c r="F29" s="117" t="inlineStr">
+        <is>
+          <t>7x2</t>
+        </is>
+      </c>
+      <c r="G29" s="117" t="n">
+        <v>30</v>
+      </c>
+      <c r="H29" s="117" t="n">
+        <v>18</v>
+      </c>
+      <c r="I29" s="116" t="inlineStr"/>
+      <c r="J29" s="117" t="n"/>
+      <c r="K29" s="116" t="inlineStr">
+        <is>
+          <t>Profondeur (mine, étage 2+)</t>
+        </is>
+      </c>
+      <c r="L29" s="116" t="inlineStr">
+        <is>
+          <t>deux katanas</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="116" t="inlineStr">
+        <is>
+          <t>warrior-mushroom2</t>
+        </is>
+      </c>
+      <c r="B30" s="116" t="inlineStr">
+        <is>
+          <t>Fungal Knight</t>
+        </is>
+      </c>
+      <c r="C30" s="117" t="n">
+        <v>4</v>
+      </c>
+      <c r="D30" s="116" t="inlineStr">
+        <is>
+          <t>mushroom</t>
+        </is>
+      </c>
+      <c r="E30" s="117" t="n">
+        <v>85</v>
+      </c>
+      <c r="F30" s="117" t="n">
         <v>11</v>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>applique 1 poisson par attaque (2x attaque = 2 poisons)</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Eastern + profondeur</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>gobelin-chaman</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Goblin Shaman</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>gobelin</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
+      <c r="G30" s="117" t="n">
+        <v>30</v>
+      </c>
+      <c r="H30" s="117" t="n">
+        <v>7</v>
+      </c>
+      <c r="I30" s="116" t="inlineStr"/>
+      <c r="J30" s="117" t="n"/>
+      <c r="K30" s="116" t="inlineStr">
+        <is>
+          <t>Profondeur (mine, étage 2+)</t>
+        </is>
+      </c>
+      <c r="L30" s="116" t="inlineStr">
+        <is>
+          <t>épée + bouclier</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="116" t="inlineStr">
+        <is>
+          <t>black-mushroom-specialist</t>
+        </is>
+      </c>
+      <c r="B31" s="116" t="inlineStr">
+        <is>
+          <t>Deathcap Reaper</t>
+        </is>
+      </c>
+      <c r="C31" s="117" t="n">
+        <v>5</v>
+      </c>
+      <c r="D31" s="116" t="inlineStr">
+        <is>
+          <t>mushroom</t>
+        </is>
+      </c>
+      <c r="E31" s="117" t="n">
+        <v>90</v>
+      </c>
+      <c r="F31" s="117" t="n">
+        <v>18</v>
+      </c>
+      <c r="G31" s="117" t="n">
+        <v>44</v>
+      </c>
+      <c r="H31" s="117" t="n">
+        <v>9</v>
+      </c>
+      <c r="I31" s="116" t="inlineStr"/>
+      <c r="J31" s="117" t="n"/>
+      <c r="K31" s="116" t="inlineStr">
+        <is>
+          <t>Profondeur (mine, étage 2+)</t>
+        </is>
+      </c>
+      <c r="L31" s="116" t="inlineStr">
+        <is>
+          <t>grosse hallebarde</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="59" customHeight="1" s="102">
+      <c r="A32" s="116" t="inlineStr">
+        <is>
+          <t>king-mushroom</t>
+        </is>
+      </c>
+      <c r="B32" s="116" t="inlineStr">
+        <is>
+          <t>Mushroom King</t>
+        </is>
+      </c>
+      <c r="C32" s="117" t="n">
+        <v>6</v>
+      </c>
+      <c r="D32" s="116" t="inlineStr">
+        <is>
+          <t>mushroom</t>
+        </is>
+      </c>
+      <c r="E32" s="117" t="n">
+        <v>140</v>
+      </c>
+      <c r="F32" s="117" t="n">
+        <v>16</v>
+      </c>
+      <c r="G32" s="117" t="n">
+        <v>70</v>
+      </c>
+      <c r="H32" s="117" t="n">
+        <v>6</v>
+      </c>
+      <c r="I32" s="116" t="inlineStr">
+        <is>
+          <t>Soin 18 (40%)
+Hâte alliés 2 (30%)
+Attaque 16 (30%)</t>
+        </is>
+      </c>
+      <c r="J32" s="117" t="n">
+        <v>1</v>
+      </c>
+      <c r="K32" s="116" t="inlineStr">
+        <is>
+          <t>Profondeur (mine, étage 2+)</t>
+        </is>
+      </c>
+      <c r="L32" s="116" t="inlineStr">
+        <is>
+          <t>boss</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="126" t="inlineStr">
+        <is>
+          <t>▸ LAPIN BLANC (rencontre spéciale, évolutif)</t>
+        </is>
+      </c>
+      <c r="B33" s="127" t="n"/>
+      <c r="C33" s="127" t="n"/>
+      <c r="D33" s="127" t="n"/>
+      <c r="E33" s="127" t="n"/>
+      <c r="F33" s="127" t="n"/>
+      <c r="G33" s="127" t="n"/>
+      <c r="H33" s="127" t="n"/>
+      <c r="I33" s="127" t="n"/>
+      <c r="J33" s="127" t="n"/>
+      <c r="K33" s="127" t="n"/>
+      <c r="L33" s="127" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="116" t="inlineStr">
+        <is>
+          <t>lapin-stage1</t>
+        </is>
+      </c>
+      <c r="B34" s="116" t="inlineStr">
+        <is>
+          <t>White Rabbit</t>
+        </is>
+      </c>
+      <c r="C34" s="117" t="n">
+        <v>7</v>
+      </c>
+      <c r="D34" s="116" t="inlineStr">
+        <is>
+          <t>lapin</t>
+        </is>
+      </c>
+      <c r="E34" s="117" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="117" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="117" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="117" t="n">
+        <v>13</v>
+      </c>
+      <c r="I34" s="116" t="inlineStr"/>
+      <c r="J34" s="117" t="n"/>
+      <c r="K34" s="116" t="inlineStr">
+        <is>
+          <t>Rencontre spéciale rare (mine, étage 4+, seul/entre lapins)</t>
+        </is>
+      </c>
+      <c r="L34" s="116" t="inlineStr">
+        <is>
+          <t>stade 1 GENTIL : n'attaque pas ; le tuer le fait ÉVOLUER</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="116" t="inlineStr">
+        <is>
+          <t>lapin-stage2</t>
+        </is>
+      </c>
+      <c r="B35" s="116" t="inlineStr">
+        <is>
+          <t>Feral Hare</t>
+        </is>
+      </c>
+      <c r="C35" s="117" t="n">
+        <v>7</v>
+      </c>
+      <c r="D35" s="116" t="inlineStr">
+        <is>
+          <t>lapin</t>
+        </is>
+      </c>
+      <c r="E35" s="117" t="n">
+        <v>55</v>
+      </c>
+      <c r="F35" s="117" t="inlineStr">
+        <is>
+          <t>9x2</t>
+        </is>
+      </c>
+      <c r="G35" s="117" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="117" t="n">
         <v>20</v>
       </c>
-      <c r="F5" t="n">
-        <v>4</v>
-      </c>
-      <c r="G5" t="n">
-        <v>20</v>
-      </c>
-      <c r="H5" t="n">
-        <v>7</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>soigner:10:50 | haste-allie:2:30 | attaque:2:20</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Eastern + profondeur</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>ogre-masque</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Masked Ogre</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>3</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>animal</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>80</v>
-      </c>
-      <c r="F6" t="n">
-        <v>30</v>
-      </c>
-      <c r="G6" t="n">
-        <v>60</v>
-      </c>
-      <c r="H6" t="n">
-        <v>5</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Eastern + profondeur</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>orc-rodeur</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Orc Rogue</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>orc</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>40</v>
-      </c>
-      <c r="F7" t="n">
-        <v>6</v>
-      </c>
-      <c r="G7" t="n">
-        <v>22</v>
-      </c>
-      <c r="H7" t="n">
-        <v>15</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>frappe 2× par tour (attaqueHits 2)</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Profondeur (mine, étage 2+)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>orc-guerrier</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Orc Warrior</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>orc</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>75</v>
-      </c>
-      <c r="F8" t="n">
-        <v>12</v>
-      </c>
-      <c r="G8" t="n">
-        <v>30</v>
-      </c>
-      <c r="H8" t="n">
-        <v>8</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Profondeur (mine, étage 2+)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>orc-guerriere</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Orc Warmaiden</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>4</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>orc</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>60</v>
-      </c>
-      <c r="F9" t="n">
-        <v>16</v>
-      </c>
-      <c r="G9" t="n">
-        <v>34</v>
-      </c>
-      <c r="H9" t="n">
-        <v>9</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Profondeur (mine, étage 2+)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>orc-brute</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Orc Berserker</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>5</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>orc</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>95</v>
-      </c>
-      <c r="F10" t="n">
-        <v>20</v>
-      </c>
-      <c r="G10" t="n">
-        <v>44</v>
-      </c>
-      <c r="H10" t="n">
-        <v>6</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Profondeur (mine, étage 2+)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>orc-chamane</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Orc Shaman</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>4</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>orc</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>45</v>
-      </c>
-      <c r="F11" t="n">
-        <v>6</v>
-      </c>
-      <c r="G11" t="n">
-        <v>36</v>
-      </c>
-      <c r="H11" t="n">
-        <v>7</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>soigner:12:45 | haste-allie:2:30 | attaque:6:25</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Profondeur (mine, étage 2+)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>blob-vert</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Green Slime</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>3</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>blob</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>55</v>
-      </c>
-      <c r="F12" t="n">
-        <v>8</v>
-      </c>
-      <c r="G12" t="n">
-        <v>24</v>
-      </c>
-      <c r="H12" t="n">
-        <v>4</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1 poison par coup</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Profondeur (mine, étage 2+)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>blob-jaune</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Ochre Slime</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>3</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>blob</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>50</v>
-      </c>
-      <c r="F13" t="n">
-        <v>8</v>
-      </c>
-      <c r="G13" t="n">
-        <v>24</v>
-      </c>
-      <c r="H13" t="n">
-        <v>4</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>poison par coup (acide, 3)</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Profondeur (mine, étage 2+)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>blob-rouge</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Crimson Slime</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>4</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>blob</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>80</v>
-      </c>
-      <c r="F14" t="n">
+      <c r="I35" s="116" t="inlineStr"/>
+      <c r="J35" s="117" t="n"/>
+      <c r="K35" s="116" t="inlineStr">
+        <is>
+          <t>Rencontre spéciale (évolution)</t>
+        </is>
+      </c>
+      <c r="L35" s="116" t="inlineStr">
+        <is>
+          <t>stade 2 : évolue en stade 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="116" t="inlineStr">
+        <is>
+          <t>lapin-stage3</t>
+        </is>
+      </c>
+      <c r="B36" s="116" t="inlineStr">
+        <is>
+          <t>Bloodfang Horror</t>
+        </is>
+      </c>
+      <c r="C36" s="117" t="n">
         <v>10</v>
       </c>
-      <c r="G14" t="n">
-        <v>30</v>
-      </c>
-      <c r="H14" t="n">
-        <v>4</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>tanky</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Profondeur (mine, étage 2+)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>blob-bleu</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Azure Slime</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>4</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>blob</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>65</v>
-      </c>
-      <c r="F15" t="n">
-        <v>10</v>
-      </c>
-      <c r="G15" t="n">
-        <v>30</v>
-      </c>
-      <c r="H15" t="n">
-        <v>4</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>piquants</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Profondeur (mine, étage 2+)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>molosse</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Dire Hound</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>3</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>animal</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>40</v>
-      </c>
-      <c r="F16" t="n">
-        <v>10</v>
-      </c>
-      <c r="G16" t="n">
-        <v>22</v>
-      </c>
-      <c r="H16" t="n">
-        <v>16</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>rapide</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Profondeur (mine, étage 2+)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>molosse-feu</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Ember Hound</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>4</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>animal</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>45</v>
-      </c>
-      <c r="F17" t="n">
-        <v>12</v>
-      </c>
-      <c r="G17" t="n">
-        <v>28</v>
-      </c>
-      <c r="H17" t="n">
-        <v>15</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>rapide, feu</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Profondeur (mine, étage 2+)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>molosse-sombre</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Shadow Hound</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>4</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>animal</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>42</v>
-      </c>
-      <c r="F18" t="n">
-        <v>11</v>
-      </c>
-      <c r="G18" t="n">
+      <c r="D36" s="116" t="inlineStr">
+        <is>
+          <t>lapin</t>
+        </is>
+      </c>
+      <c r="E36" s="117" t="n">
+        <v>150</v>
+      </c>
+      <c r="F36" s="117" t="inlineStr">
+        <is>
+          <t>17x2</t>
+        </is>
+      </c>
+      <c r="G36" s="117" t="n">
+        <v>130</v>
+      </c>
+      <c r="H36" s="117" t="n">
         <v>26</v>
       </c>
-      <c r="H18" t="n">
-        <v>17</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>rapide</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Profondeur (mine, étage 2+)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>warrior-mushroom1</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Toadstool Lancer</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>3</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>mushroom</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>50</v>
-      </c>
-      <c r="F19" t="n">
-        <v>8</v>
-      </c>
-      <c r="G19" t="n">
-        <v>22</v>
-      </c>
-      <c r="H19" t="n">
-        <v>8</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Profondeur (mine, étage 2+)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>warrior-mushroom2</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Fungal Knight</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>4</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>mushroom</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>85</v>
-      </c>
-      <c r="F20" t="n">
-        <v>11</v>
-      </c>
-      <c r="G20" t="n">
-        <v>30</v>
-      </c>
-      <c r="H20" t="n">
-        <v>7</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Profondeur (mine, étage 2+)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>white-katana-mushroom</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Myconid Ronin</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>4</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>mushroom</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>45</v>
-      </c>
-      <c r="F21" t="n">
-        <v>7</v>
-      </c>
-      <c r="G21" t="n">
-        <v>30</v>
-      </c>
-      <c r="H21" t="n">
-        <v>18</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>frappe 2× par tour (attaqueHits 2)</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>Profondeur (mine, étage 2+)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>black-mushroom-specialist</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Deathcap Reaper</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>5</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>mushroom</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>90</v>
-      </c>
-      <c r="F22" t="n">
-        <v>18</v>
-      </c>
-      <c r="G22" t="n">
-        <v>44</v>
-      </c>
-      <c r="H22" t="n">
-        <v>9</v>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>Profondeur (mine, étage 2+)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>mage-mushroom</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Myconid Sage</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>4</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>mushroom</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>40</v>
-      </c>
-      <c r="F23" t="n">
-        <v>5</v>
-      </c>
-      <c r="G23" t="n">
-        <v>34</v>
-      </c>
-      <c r="H23" t="n">
-        <v>7</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>soigner:12:45 | haste-allie:2:30 | attaque:5:25</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Profondeur (mine, étage 2+)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>king-mushroom</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Mushroom King</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>6</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>mushroom</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>140</v>
-      </c>
-      <c r="F24" t="n">
-        <v>16</v>
-      </c>
-      <c r="G24" t="n">
-        <v>70</v>
-      </c>
-      <c r="H24" t="n">
-        <v>6</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>soigner:18:40 | haste-allie:2:30 | attaque:16:30</t>
-        </is>
-      </c>
-      <c r="J24" t="n">
-        <v>1</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Profondeur (mine, étage 2+)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>bear</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Cave Bear</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>4</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>animal</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>90</v>
-      </c>
-      <c r="F25" t="n">
-        <v>14</v>
-      </c>
-      <c r="G25" t="n">
-        <v>32</v>
-      </c>
-      <c r="H25" t="n">
-        <v>8</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>en meute avec les molosses</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>Profondeur (mine, étage 2+)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>bones-bear</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Bonehide Bear</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>5</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>animal</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>100</v>
-      </c>
-      <c r="F26" t="n">
-        <v>16</v>
-      </c>
-      <c r="G26" t="n">
-        <v>44</v>
-      </c>
-      <c r="H26" t="n">
-        <v>9</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>en meute avec les molosses</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>Profondeur (mine, étage 2+)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>armor-bear</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Armored War-Bear</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>6</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>animal</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>150</v>
-      </c>
-      <c r="F27" t="n">
-        <v>20</v>
-      </c>
-      <c r="G27" t="n">
-        <v>60</v>
-      </c>
-      <c r="H27" t="n">
-        <v>6</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>en meute avec les molosses</t>
-        </is>
-      </c>
-      <c r="J27" t="n">
-        <v>1</v>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>Profondeur (mine, étage 2+)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>lapin-stage1</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>White Rabbit</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>7</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>lapin</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="n">
-        <v>13</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>stade 1 GENTIL : n'attaque pas ; le tuer le fait ÉVOLUER (pas dans l'Excel : voir code)</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>Rencontre spéciale rare (mine, étage 4+, seul)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>lapin-stage2</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Feral Hare</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>7</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>lapin</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>55</v>
-      </c>
-      <c r="F29" t="n">
-        <v>9</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="n">
-        <v>20</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>stade 2 : frappe 2× (attaqueHits 2) ; évolue en stade 3</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>Rencontre spéciale (évolution)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>lapin-stage3</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Bloodfang Horror</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>10</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>lapin</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>150</v>
-      </c>
-      <c r="F30" t="n">
-        <v>17</v>
-      </c>
-      <c r="G30" t="n">
-        <v>130</v>
-      </c>
-      <c r="H30" t="n">
-        <v>26</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>stade 3 : frappe 2× ; gros or (niv 10) + 2% Ring of Luck</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
+      <c r="I36" s="116" t="inlineStr"/>
+      <c r="J36" s="117" t="n"/>
+      <c r="K36" s="116" t="inlineStr">
         <is>
           <t>Rencontre spéciale (stade final)</t>
+        </is>
+      </c>
+      <c r="L36" s="116" t="inlineStr">
+        <is>
+          <t>stade 3 : gros or (niv 10) + 2% Ring of Luck</t>
         </is>
       </c>
     </row>

--- a/docs/BRUTAL-items-et-cartes.xlsx
+++ b/docs/BRUTAL-items-et-cartes.xlsx
@@ -1731,7 +1731,7 @@
       </c>
       <c r="I2" s="113" t="inlineStr">
         <is>
-          <t>attaques spéciales, UNE PAR LIGNE : « Libellé valeur (chance%) ». Libellés : Soin, Hâte alliés, Attaque. Les % somment à 100. Vide = attaque simple.</t>
+          <t>attaques spéciales, UNE PAR LIGNE : « Libellé valeur (chance%) ». Libellés : Soin, Hâte alliés, Attaque. Les % sont des chances ABSOLUES et n'ont PAS besoin de sommer à 100 : la part restante = attaque de BASE. Vide = attaque de base à 100%.</t>
         </is>
       </c>
       <c r="J2" s="113" t="inlineStr">

--- a/docs/BRUTAL-items-et-cartes.xlsx
+++ b/docs/BRUTAL-items-et-cartes.xlsx
@@ -3263,7 +3263,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" style="102" min="1" max="1"/>
@@ -3287,6 +3287,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="107" t="inlineStr">
         <is>
@@ -3753,69 +3754,69 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="108" t="inlineStr">
-        <is>
-          <t>LUCKY DELVER (talent forge — caverne de chance)</t>
-        </is>
-      </c>
-      <c r="B23" s="109" t="n"/>
-      <c r="C23" s="109" t="n"/>
-      <c r="D23" s="109" t="n"/>
-      <c r="E23" s="109" t="n"/>
+      <c r="A23" s="110" t="inlineStr">
+        <is>
+          <t>Minage</t>
+        </is>
+      </c>
+      <c r="B23" s="110" t="inlineStr">
+        <is>
+          <t>Taille de pile de base</t>
+        </is>
+      </c>
+      <c r="C23" s="111" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D23" s="110" t="inlineStr">
+        <is>
+          <t>Nombre max de minerais par pile SANS talent (avant : 10).</t>
+        </is>
+      </c>
+      <c r="E23" s="110" t="inlineStr">
+        <is>
+          <t>data/items.js + inventaire.js</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="110" t="inlineStr">
         <is>
-          <t>Caverne</t>
+          <t>Minage</t>
         </is>
       </c>
       <c r="B24" s="110" t="inlineStr">
         <is>
-          <t>Chance d'apparition</t>
+          <t>Talent « Ore Hauler » (par rang)</t>
         </is>
       </c>
       <c r="C24" s="111" t="inlineStr">
         <is>
-          <t>22 %</t>
+          <t>+5 (×5 rangs → 30)</t>
         </is>
       </c>
       <c r="D24" s="110" t="inlineStr">
         <is>
-          <t>Proba, par descente éligible (étage 3+), de tomber sur une caverne de chance.</t>
+          <t>Chaque rang du talent forge agrandit les piles de +5 (5 rangs → 30/pile).</t>
         </is>
       </c>
       <c r="E24" s="110" t="inlineStr">
         <is>
-          <t>principal.js</t>
+          <t>data/talents.js</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="110" t="inlineStr">
-        <is>
-          <t>Caverne</t>
-        </is>
-      </c>
-      <c r="B25" s="110" t="inlineStr">
-        <is>
-          <t>Bonus de minerais</t>
-        </is>
-      </c>
-      <c r="C25" s="111" t="inlineStr">
-        <is>
-          <t>+220 %</t>
-        </is>
-      </c>
-      <c r="D25" s="110" t="inlineStr">
-        <is>
-          <t>Boost du nombre de veines dans une caverne de chance.</t>
-        </is>
-      </c>
-      <c r="E25" s="110" t="inlineStr">
-        <is>
-          <t>principal.js</t>
-        </is>
-      </c>
+      <c r="A25" s="108" t="inlineStr">
+        <is>
+          <t>LUCKY DELVER (talent forge — caverne de chance)</t>
+        </is>
+      </c>
+      <c r="B25" s="109" t="n"/>
+      <c r="C25" s="109" t="n"/>
+      <c r="D25" s="109" t="n"/>
+      <c r="E25" s="109" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="110" t="inlineStr">
@@ -3825,17 +3826,17 @@
       </c>
       <c r="B26" s="110" t="inlineStr">
         <is>
-          <t>Taux de rencontre</t>
+          <t>Chance d'apparition</t>
         </is>
       </c>
       <c r="C26" s="111" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>22 %</t>
         </is>
       </c>
       <c r="D26" s="110" t="inlineStr">
         <is>
-          <t>Fréquence des combats dans une caverne (vs 0.3 normal → quasi zéro monstre).</t>
+          <t>Proba, par descente éligible (étage 3+), de tomber sur une caverne de chance.</t>
         </is>
       </c>
       <c r="E26" s="110" t="inlineStr">
@@ -3845,47 +3846,63 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="108" t="inlineStr">
-        <is>
-          <t>BANQUE</t>
-        </is>
-      </c>
-      <c r="B27" s="109" t="n"/>
-      <c r="C27" s="109" t="n"/>
-      <c r="D27" s="109" t="n"/>
-      <c r="E27" s="109" t="n"/>
+      <c r="A27" s="110" t="inlineStr">
+        <is>
+          <t>Caverne</t>
+        </is>
+      </c>
+      <c r="B27" s="110" t="inlineStr">
+        <is>
+          <t>Bonus de minerais</t>
+        </is>
+      </c>
+      <c r="C27" s="111" t="inlineStr">
+        <is>
+          <t>+220 %</t>
+        </is>
+      </c>
+      <c r="D27" s="110" t="inlineStr">
+        <is>
+          <t>Boost du nombre de veines dans une caverne de chance.</t>
+        </is>
+      </c>
+      <c r="E27" s="110" t="inlineStr">
+        <is>
+          <t>principal.js</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="110" t="inlineStr">
         <is>
-          <t>Banque</t>
+          <t>Caverne</t>
         </is>
       </c>
       <c r="B28" s="110" t="inlineStr">
         <is>
-          <t>Rendement du coffre-fort</t>
+          <t>Taux de rencontre</t>
         </is>
       </c>
       <c r="C28" s="111" t="inlineStr">
         <is>
-          <t>0.2 % / jour</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="D28" s="110" t="inlineStr">
         <is>
-          <t>Intérêt composé du dépôt SÛR (par jour de jeu).</t>
+          <t>Fréquence des combats dans une caverne (vs 0.3 normal → quasi zéro monstre).</t>
         </is>
       </c>
       <c r="E28" s="110" t="inlineStr">
         <is>
-          <t>data/banque.js</t>
+          <t>principal.js</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="108" t="inlineStr">
         <is>
-          <t>RENCONTRES &amp; GROUPES DE MONSTRES</t>
+          <t>BANQUE</t>
         </is>
       </c>
       <c r="B29" s="109" t="n"/>
@@ -3896,56 +3913,40 @@
     <row r="30">
       <c r="A30" s="110" t="inlineStr">
         <is>
-          <t>Mine</t>
+          <t>Banque</t>
         </is>
       </c>
       <c r="B30" s="110" t="inlineStr">
         <is>
-          <t>Taux de rencontre</t>
+          <t>Rendement du coffre-fort</t>
         </is>
       </c>
       <c r="C30" s="111" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2 % / jour</t>
         </is>
       </c>
       <c r="D30" s="110" t="inlineStr">
         <is>
-          <t>Fréquence de base des combats en explorant une mine.</t>
+          <t>Intérêt composé du dépôt SÛR (par jour de jeu).</t>
         </is>
       </c>
       <c r="E30" s="110" t="inlineStr">
         <is>
-          <t>world/mine.js</t>
+          <t>data/banque.js</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="110" t="inlineStr">
-        <is>
-          <t>Mine</t>
-        </is>
-      </c>
-      <c r="B31" s="110" t="inlineStr">
-        <is>
-          <t>Étage « monstres profonds »</t>
-        </is>
-      </c>
-      <c r="C31" s="111" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D31" s="110" t="inlineStr">
-        <is>
-          <t>Étage mini où apparaissent orcs / blobs / molosses / ours / champignons.</t>
-        </is>
-      </c>
-      <c r="E31" s="110" t="inlineStr">
-        <is>
-          <t>world/mine.js</t>
-        </is>
-      </c>
+      <c r="A31" s="108" t="inlineStr">
+        <is>
+          <t>RENCONTRES &amp; GROUPES DE MONSTRES</t>
+        </is>
+      </c>
+      <c r="B31" s="109" t="n"/>
+      <c r="C31" s="109" t="n"/>
+      <c r="D31" s="109" t="n"/>
+      <c r="E31" s="109" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="110" t="inlineStr">
@@ -3955,17 +3956,17 @@
       </c>
       <c r="B32" s="110" t="inlineStr">
         <is>
-          <t>Chance de biome (thème)</t>
+          <t>Taux de rencontre</t>
         </is>
       </c>
       <c r="C32" s="111" t="inlineStr">
         <is>
-          <t>40 %</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="D32" s="110" t="inlineStr">
         <is>
-          <t>Proba qu'un étage éligible soit à thème (cristal / glace / lave…).</t>
+          <t>Fréquence de base des combats en explorant une mine.</t>
         </is>
       </c>
       <c r="E32" s="110" t="inlineStr">
@@ -3977,54 +3978,54 @@
     <row r="33">
       <c r="A33" s="110" t="inlineStr">
         <is>
-          <t>Groupes</t>
+          <t>Mine</t>
         </is>
       </c>
       <c r="B33" s="110" t="inlineStr">
         <is>
-          <t>Taille des groupes</t>
+          <t>Étage « monstres profonds »</t>
         </is>
       </c>
       <c r="C33" s="111" t="inlineStr">
         <is>
-          <t>30 / 30 / 20 / 15 / 5 %</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D33" s="110" t="inlineStr">
         <is>
-          <t>Proba d'un groupe de 1 / 2 / 3 / 4 / 5 emplacements.</t>
+          <t>Étage mini où apparaissent orcs / blobs / molosses / ours / champignons.</t>
         </is>
       </c>
       <c r="E33" s="110" t="inlineStr">
         <is>
-          <t>data/ennemis.js</t>
+          <t>world/mine.js</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="110" t="inlineStr">
         <is>
-          <t>Groupes</t>
+          <t>Mine</t>
         </is>
       </c>
       <c r="B34" s="110" t="inlineStr">
         <is>
-          <t>Facteur de niveau</t>
+          <t>Chance de biome (thème)</t>
         </is>
       </c>
       <c r="C34" s="111" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>40 %</t>
         </is>
       </c>
       <c r="D34" s="110" t="inlineStr">
         <is>
-          <t>Un niveau de monstre en plus = ~2× plus rare dans le tirage.</t>
+          <t>Proba qu'un étage éligible soit à thème (cristal / glace / lave…).</t>
         </is>
       </c>
       <c r="E34" s="110" t="inlineStr">
         <is>
-          <t>data/ennemis.js</t>
+          <t>world/mine.js</t>
         </is>
       </c>
     </row>
@@ -4036,17 +4037,17 @@
       </c>
       <c r="B35" s="110" t="inlineStr">
         <is>
-          <t>Rareté d'un « grand » (petit grp)</t>
+          <t>Taille des groupes</t>
         </is>
       </c>
       <c r="C35" s="111" t="inlineStr">
         <is>
-          <t>×0.5</t>
+          <t>30 / 30 / 20 / 15 / 5 %</t>
         </is>
       </c>
       <c r="D35" s="110" t="inlineStr">
         <is>
-          <t>Poids d'un grand monstre dans un petit groupe (plus rare).</t>
+          <t>Proba d'un groupe de 1 / 2 / 3 / 4 / 5 emplacements.</t>
         </is>
       </c>
       <c r="E35" s="110" t="inlineStr">
@@ -4063,17 +4064,17 @@
       </c>
       <c r="B36" s="110" t="inlineStr">
         <is>
-          <t>Bonus d'un « grand » (gros grp)</t>
+          <t>Facteur de niveau</t>
         </is>
       </c>
       <c r="C36" s="111" t="inlineStr">
         <is>
-          <t>×3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D36" s="110" t="inlineStr">
         <is>
-          <t>Poids d'un grand dans un gros groupe (favorisé).</t>
+          <t>Un niveau de monstre en plus = ~2× plus rare dans le tirage.</t>
         </is>
       </c>
       <c r="E36" s="110" t="inlineStr">
@@ -4085,25 +4086,79 @@
     <row r="37">
       <c r="A37" s="110" t="inlineStr">
         <is>
+          <t>Groupes</t>
+        </is>
+      </c>
+      <c r="B37" s="110" t="inlineStr">
+        <is>
+          <t>Rareté d'un « grand » (petit grp)</t>
+        </is>
+      </c>
+      <c r="C37" s="111" t="inlineStr">
+        <is>
+          <t>×0.5</t>
+        </is>
+      </c>
+      <c r="D37" s="110" t="inlineStr">
+        <is>
+          <t>Poids d'un grand monstre dans un petit groupe (plus rare).</t>
+        </is>
+      </c>
+      <c r="E37" s="110" t="inlineStr">
+        <is>
+          <t>data/ennemis.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="110" t="inlineStr">
+        <is>
+          <t>Groupes</t>
+        </is>
+      </c>
+      <c r="B38" s="110" t="inlineStr">
+        <is>
+          <t>Bonus d'un « grand » (gros grp)</t>
+        </is>
+      </c>
+      <c r="C38" s="111" t="inlineStr">
+        <is>
+          <t>×3</t>
+        </is>
+      </c>
+      <c r="D38" s="110" t="inlineStr">
+        <is>
+          <t>Poids d'un grand dans un gros groupe (favorisé).</t>
+        </is>
+      </c>
+      <c r="E38" s="110" t="inlineStr">
+        <is>
+          <t>data/ennemis.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="110" t="inlineStr">
+        <is>
           <t>Combat</t>
         </is>
       </c>
-      <c r="B37" s="110" t="inlineStr">
+      <c r="B39" s="110" t="inlineStr">
         <is>
           <t>Fuite selon nb d'ennemis</t>
         </is>
       </c>
-      <c r="C37" s="111" t="inlineStr">
+      <c r="C39" s="111" t="inlineStr">
         <is>
           <t>50 / 33 / 25 / 25 / 20 %</t>
         </is>
       </c>
-      <c r="D37" s="110" t="inlineStr">
+      <c r="D39" s="110" t="inlineStr">
         <is>
           <t>Chance de fuir un combat normal selon le nombre d'ennemis (1 à 5).</t>
         </is>
       </c>
-      <c r="E37" s="110" t="inlineStr">
+      <c r="E39" s="110" t="inlineStr">
         <is>
           <t>ui/combat.js</t>
         </is>

--- a/docs/BRUTAL-items-et-cartes.xlsx
+++ b/docs/BRUTAL-items-et-cartes.xlsx
@@ -1609,7 +1609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L36"/>
+  <dimension ref="A1:L41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="102" min="1" max="1"/>
@@ -3093,6 +3093,206 @@
       <c r="L36" s="116" t="inlineStr">
         <is>
           <t>stade 3 : gros or (niv 10) + 2% Ring of Luck</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="126" t="inlineStr">
+        <is>
+          <t>▸ TOUR DE SIÈGE (boss unique + son équipage, spawnOnly)</t>
+        </is>
+      </c>
+      <c r="B37" s="127" t="n"/>
+      <c r="C37" s="127" t="n"/>
+      <c r="D37" s="127" t="n"/>
+      <c r="E37" s="127" t="n"/>
+      <c r="F37" s="127" t="n"/>
+      <c r="G37" s="127" t="n"/>
+      <c r="H37" s="127" t="n"/>
+      <c r="I37" s="127" t="n"/>
+      <c r="J37" s="127" t="n"/>
+      <c r="K37" s="127" t="n"/>
+      <c r="L37" s="127" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="116" t="inlineStr">
+        <is>
+          <t>tour-de-siege-gobeline</t>
+        </is>
+      </c>
+      <c r="B38" s="116" t="inlineStr">
+        <is>
+          <t>Goblin Siege Tower</t>
+        </is>
+      </c>
+      <c r="C38" s="117" t="n">
+        <v>8</v>
+      </c>
+      <c r="D38" s="116" t="inlineStr">
+        <is>
+          <t>gobelin</t>
+        </is>
+      </c>
+      <c r="E38" s="117" t="n">
+        <v>220</v>
+      </c>
+      <c r="F38" s="117" t="n">
+        <v>16</v>
+      </c>
+      <c r="G38" s="117" t="n">
+        <v>120</v>
+      </c>
+      <c r="H38" s="117" t="n">
+        <v>5</v>
+      </c>
+      <c r="I38" s="116" t="n"/>
+      <c r="J38" s="117" t="n">
+        <v>1</v>
+      </c>
+      <c r="K38" s="116" t="inlineStr">
+        <is>
+          <t>Rencontre spéciale (mine, étage 5+, TOUJOURS seule)</t>
+        </is>
+      </c>
+      <c r="L38" s="116" t="inlineStr">
+        <is>
+          <t>boss unique ; à sa mort se DISLOQUE en son équipage (Kaboom + 3 de siège + porte-étendard)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="116" t="inlineStr">
+        <is>
+          <t>gobelin-kaboom</t>
+        </is>
+      </c>
+      <c r="B39" s="116" t="inlineStr">
+        <is>
+          <t>Goblin Kaboom</t>
+        </is>
+      </c>
+      <c r="C39" s="117" t="n">
+        <v>6</v>
+      </c>
+      <c r="D39" s="116" t="inlineStr">
+        <is>
+          <t>gobelin</t>
+        </is>
+      </c>
+      <c r="E39" s="117" t="n">
+        <v>20</v>
+      </c>
+      <c r="F39" s="117" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="117" t="n">
+        <v>20</v>
+      </c>
+      <c r="H39" s="117" t="n">
+        <v>4</v>
+      </c>
+      <c r="I39" s="116" t="n"/>
+      <c r="J39" s="117" t="n"/>
+      <c r="K39" s="116" t="inlineStr">
+        <is>
+          <t>Équipage de la tour (n'apparaît QUE de sa mort)</t>
+        </is>
+      </c>
+      <c r="L39" s="116" t="inlineStr">
+        <is>
+          <t>longue mèche (2 tours) puis EXPLOSE pour 100 et meurt — dégâts en code (explose)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="116" t="inlineStr">
+        <is>
+          <t>gobelin-de-siege</t>
+        </is>
+      </c>
+      <c r="B40" s="116" t="inlineStr">
+        <is>
+          <t>Siege Goblin</t>
+        </is>
+      </c>
+      <c r="C40" s="117" t="n">
+        <v>3</v>
+      </c>
+      <c r="D40" s="116" t="inlineStr">
+        <is>
+          <t>gobelin</t>
+        </is>
+      </c>
+      <c r="E40" s="117" t="n">
+        <v>24</v>
+      </c>
+      <c r="F40" s="117" t="n">
+        <v>7</v>
+      </c>
+      <c r="G40" s="117" t="n">
+        <v>8</v>
+      </c>
+      <c r="H40" s="117" t="n">
+        <v>9</v>
+      </c>
+      <c r="I40" s="116" t="n"/>
+      <c r="J40" s="117" t="n"/>
+      <c r="K40" s="116" t="inlineStr">
+        <is>
+          <t>Équipage de la tour (n'apparaît QUE de sa mort)</t>
+        </is>
+      </c>
+      <c r="L40" s="116" t="inlineStr">
+        <is>
+          <t>juste son épée ; rapide mais fragile</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="116" t="inlineStr">
+        <is>
+          <t>gobelin-de-siege-etandart</t>
+        </is>
+      </c>
+      <c r="B41" s="116" t="inlineStr">
+        <is>
+          <t>Siege Standard-Bearer</t>
+        </is>
+      </c>
+      <c r="C41" s="117" t="n">
+        <v>6</v>
+      </c>
+      <c r="D41" s="116" t="inlineStr">
+        <is>
+          <t>gobelin</t>
+        </is>
+      </c>
+      <c r="E41" s="117" t="n">
+        <v>55</v>
+      </c>
+      <c r="F41" s="117" t="n">
+        <v>5</v>
+      </c>
+      <c r="G41" s="117" t="n">
+        <v>24</v>
+      </c>
+      <c r="H41" s="117" t="n">
+        <v>7</v>
+      </c>
+      <c r="I41" s="116" t="inlineStr">
+        <is>
+          <t>Bannière 2 (100%)</t>
+        </is>
+      </c>
+      <c r="J41" s="117" t="n"/>
+      <c r="K41" s="116" t="inlineStr">
+        <is>
+          <t>Équipage de la tour (n'apparaît QUE de sa mort)</t>
+        </is>
+      </c>
+      <c r="L41" s="116" t="inlineStr">
+        <is>
+          <t>buffe les alliés : +2 Hâte ET +2 dégâts par tour (le +dégâts est en code : buffDegats)</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3487,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="107" t="inlineStr">
         <is>

--- a/docs/BRUTAL-items-et-cartes.xlsx
+++ b/docs/BRUTAL-items-et-cartes.xlsx
@@ -2668,7 +2668,11 @@
       <c r="I26" s="125" t="n"/>
       <c r="J26" s="125" t="n"/>
       <c r="K26" s="125" t="n"/>
-      <c r="L26" s="125" t="n"/>
+      <c r="L26" s="125" t="inlineStr">
+        <is>
+          <t>PASSIF DE FAMILLE — Force collective : +1 dégât/coup par champignon vivant (le Roi compte pour +5), partagé par tous ; recalculé à chaque mort. Réglages dans l'onglet Général.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="116" t="inlineStr">
@@ -3463,7 +3467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" style="102" min="1" max="1"/>
@@ -4360,6 +4364,98 @@
       <c r="E39" s="110" t="inlineStr">
         <is>
           <t>ui/combat.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="108" t="inlineStr">
+        <is>
+          <t>PASSIFS DE FAMILLE (monstres)</t>
+        </is>
+      </c>
+      <c r="B40" s="109" t="n"/>
+      <c r="C40" s="109" t="n"/>
+      <c r="D40" s="109" t="n"/>
+      <c r="E40" s="109" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="110" t="inlineStr">
+        <is>
+          <t>Champignons</t>
+        </is>
+      </c>
+      <c r="B41" s="110" t="inlineStr">
+        <is>
+          <t>Force collective : par champignon</t>
+        </is>
+      </c>
+      <c r="C41" s="111" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
+      <c r="D41" s="110" t="inlineStr">
+        <is>
+          <t>Chaque champignon VIVANT en combat donne +1 de Force (dégâts, à chaque coup) à TOUS les champignons. Recalculé à chaque mort : un champignon qui tombe retire son apport.</t>
+        </is>
+      </c>
+      <c r="E41" s="110" t="inlineStr">
+        <is>
+          <t>systems/combat.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="110" t="inlineStr">
+        <is>
+          <t>Champignons</t>
+        </is>
+      </c>
+      <c r="B42" s="110" t="inlineStr">
+        <is>
+          <t>Force collective : apport du Roi</t>
+        </is>
+      </c>
+      <c r="C42" s="111" t="inlineStr">
+        <is>
+          <t>+5</t>
+        </is>
+      </c>
+      <c r="D42" s="110" t="inlineStr">
+        <is>
+          <t>Le Roi champignon compte pour +5 (au lieu de +1) dans la Force collective des champignons.</t>
+        </is>
+      </c>
+      <c r="E42" s="110" t="inlineStr">
+        <is>
+          <t>systems/combat.js + data/ennemis.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="110" t="inlineStr">
+        <is>
+          <t>Champignons</t>
+        </is>
+      </c>
+      <c r="B43" s="110" t="inlineStr">
+        <is>
+          <t>Rois par combat</t>
+        </is>
+      </c>
+      <c r="C43" s="111" t="inlineStr">
+        <is>
+          <t>1 max</t>
+        </is>
+      </c>
+      <c r="D43" s="110" t="inlineStr">
+        <is>
+          <t>Il ne peut y avoir qu'UN seul Roi champignon par rencontre (garde-fou dans le tirage de groupe).</t>
+        </is>
+      </c>
+      <c r="E43" s="110" t="inlineStr">
+        <is>
+          <t>data/ennemis.js</t>
         </is>
       </c>
     </row>

--- a/docs/BRUTAL-items-et-cartes.xlsx
+++ b/docs/BRUTAL-items-et-cartes.xlsx
@@ -1609,7 +1609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="102" min="1" max="1"/>
@@ -3297,6 +3297,162 @@
       <c r="L41" s="116" t="inlineStr">
         <is>
           <t>buffe les alliés : +2 Hâte ET +2 dégâts par tour (le +dégâts est en code : buffDegats)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="126" t="inlineStr">
+        <is>
+          <t>▸ GOBELIN BLINDÉ (grand + son duo, spawnOnly)</t>
+        </is>
+      </c>
+      <c r="B42" s="127" t="n"/>
+      <c r="C42" s="127" t="n"/>
+      <c r="D42" s="127" t="n"/>
+      <c r="E42" s="127" t="n"/>
+      <c r="F42" s="127" t="n"/>
+      <c r="G42" s="127" t="n"/>
+      <c r="H42" s="127" t="n"/>
+      <c r="I42" s="127" t="n"/>
+      <c r="J42" s="127" t="n"/>
+      <c r="K42" s="127" t="n"/>
+      <c r="L42" s="127" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="116" t="inlineStr">
+        <is>
+          <t>gobelin-blinde</t>
+        </is>
+      </c>
+      <c r="B43" s="116" t="inlineStr">
+        <is>
+          <t>Armored Goblin</t>
+        </is>
+      </c>
+      <c r="C43" s="117" t="n">
+        <v>6</v>
+      </c>
+      <c r="D43" s="116" t="inlineStr">
+        <is>
+          <t>gobelin</t>
+        </is>
+      </c>
+      <c r="E43" s="117" t="n">
+        <v>10</v>
+      </c>
+      <c r="F43" s="117" t="n">
+        <v>10</v>
+      </c>
+      <c r="G43" s="117" t="n">
+        <v>40</v>
+      </c>
+      <c r="H43" s="117" t="n">
+        <v>6</v>
+      </c>
+      <c r="I43" s="116" t="n"/>
+      <c r="J43" s="117" t="n">
+        <v>1</v>
+      </c>
+      <c r="K43" s="116" t="inlineStr">
+        <is>
+          <t>Profondeur (mine, étage 2+), dans les groupes gobelins</t>
+        </is>
+      </c>
+      <c r="L43" s="116" t="inlineStr">
+        <is>
+          <t>GRAND. Commence avec 50 de BOUCLIER (absorbe avant les PV, cf. Général). À sa mort se disloque en 2 gobelins sur ses 2 places : bouclier à GAUCHE, masse à DROITE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="116" t="inlineStr">
+        <is>
+          <t>gobelin-sans-blindage1</t>
+        </is>
+      </c>
+      <c r="B44" s="116" t="inlineStr">
+        <is>
+          <t>Mace Goblin</t>
+        </is>
+      </c>
+      <c r="C44" s="117" t="n">
+        <v>5</v>
+      </c>
+      <c r="D44" s="116" t="inlineStr">
+        <is>
+          <t>gobelin</t>
+        </is>
+      </c>
+      <c r="E44" s="117" t="n">
+        <v>34</v>
+      </c>
+      <c r="F44" s="117" t="n">
+        <v>14</v>
+      </c>
+      <c r="G44" s="117" t="n">
+        <v>18</v>
+      </c>
+      <c r="H44" s="117" t="n">
+        <v>10</v>
+      </c>
+      <c r="I44" s="116" t="n"/>
+      <c r="J44" s="117" t="n"/>
+      <c r="K44" s="116" t="inlineStr">
+        <is>
+          <t>Duo du Gobelin blindé (n'apparaît QUE de sa mort)</t>
+        </is>
+      </c>
+      <c r="L44" s="116" t="inlineStr">
+        <is>
+          <t>ATTAQUANT : gros dégâts, aucune défense. À droite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="116" t="inlineStr">
+        <is>
+          <t>gobelin-sans-blindage2</t>
+        </is>
+      </c>
+      <c r="B45" s="116" t="inlineStr">
+        <is>
+          <t>Shield Goblin</t>
+        </is>
+      </c>
+      <c r="C45" s="117" t="n">
+        <v>5</v>
+      </c>
+      <c r="D45" s="116" t="inlineStr">
+        <is>
+          <t>gobelin</t>
+        </is>
+      </c>
+      <c r="E45" s="117" t="n">
+        <v>40</v>
+      </c>
+      <c r="F45" s="117" t="n">
+        <v>4</v>
+      </c>
+      <c r="G45" s="117" t="n">
+        <v>18</v>
+      </c>
+      <c r="H45" s="117" t="n">
+        <v>8</v>
+      </c>
+      <c r="I45" s="116" t="inlineStr">
+        <is>
+          <t>Bouclier alliés 8 (100%)</t>
+        </is>
+      </c>
+      <c r="J45" s="117" t="n"/>
+      <c r="K45" s="116" t="inlineStr">
+        <is>
+          <t>Duo du Gobelin blindé (n'apparaît QUE de sa mort)</t>
+        </is>
+      </c>
+      <c r="L45" s="116" t="inlineStr">
+        <is>
+          <t>DÉFENSEUR : 15 de bouclier perso (cf. Général) + donne du bouclier aux alliés chaque tour. À gauche. Synergie tank + dégâts.</t>
         </is>
       </c>
     </row>
@@ -3467,7 +3623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" style="102" min="1" max="1"/>
@@ -4456,6 +4612,125 @@
       <c r="E43" s="110" t="inlineStr">
         <is>
           <t>data/ennemis.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="108" t="inlineStr">
+        <is>
+          <t>GOBELIN BLINDÉ (bouclier ennemi + duo)</t>
+        </is>
+      </c>
+      <c r="B44" s="109" t="n"/>
+      <c r="C44" s="109" t="n"/>
+      <c r="D44" s="109" t="n"/>
+      <c r="E44" s="109" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="110" t="inlineStr">
+        <is>
+          <t>Gobelin blindé</t>
+        </is>
+      </c>
+      <c r="B45" s="110" t="inlineStr">
+        <is>
+          <t>Bouclier de départ</t>
+        </is>
+      </c>
+      <c r="C45" s="111" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D45" s="110" t="inlineStr">
+        <is>
+          <t>BOUCLIER du Gobelin blindé : absorbe les dégâts avant ses PV (comme la Pierre du héros). Sous le bouclier il n'a que 10 PV.</t>
+        </is>
+      </c>
+      <c r="E45" s="110" t="inlineStr">
+        <is>
+          <t>data/ennemis.js (bouclierDepart)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="110" t="inlineStr">
+        <is>
+          <t>Gobelin blindé</t>
+        </is>
+      </c>
+      <c r="B46" s="110" t="inlineStr">
+        <is>
+          <t>PV sous le bouclier</t>
+        </is>
+      </c>
+      <c r="C46" s="111" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D46" s="110" t="inlineStr">
+        <is>
+          <t>Points de vie réels une fois le bouclier tombé.</t>
+        </is>
+      </c>
+      <c r="E46" s="110" t="inlineStr">
+        <is>
+          <t>data/ennemis.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="110" t="inlineStr">
+        <is>
+          <t>Gobelin défenseur</t>
+        </is>
+      </c>
+      <c r="B47" s="110" t="inlineStr">
+        <is>
+          <t>Bouclier de départ</t>
+        </is>
+      </c>
+      <c r="C47" s="111" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D47" s="110" t="inlineStr">
+        <is>
+          <t>Garde personnelle du gobelin porteur de bouclier (défenseur), une fois sorti de l'armure.</t>
+        </is>
+      </c>
+      <c r="E47" s="110" t="inlineStr">
+        <is>
+          <t>data/ennemis.js (bouclierDepart)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="110" t="inlineStr">
+        <is>
+          <t>Gobelin défenseur</t>
+        </is>
+      </c>
+      <c r="B48" s="110" t="inlineStr">
+        <is>
+          <t>Bouclier donné aux alliés / tour</t>
+        </is>
+      </c>
+      <c r="C48" s="111" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D48" s="110" t="inlineStr">
+        <is>
+          <t>Bouclier que le défenseur donne à ses alliés vivants à chaque tour (protège l'attaquant → synergie tank + dégâts).</t>
+        </is>
+      </c>
+      <c r="E48" s="110" t="inlineStr">
+        <is>
+          <t>data/ennemis.js (actions) + systems/combat.js</t>
         </is>
       </c>
     </row>

--- a/docs/BRUTAL-items-et-cartes.xlsx
+++ b/docs/BRUTAL-items-et-cartes.xlsx
@@ -1609,7 +1609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L45"/>
+  <dimension ref="A1:L46"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="102" min="1" max="1"/>
@@ -3453,6 +3453,53 @@
       <c r="L45" s="116" t="inlineStr">
         <is>
           <t>DÉFENSEUR : 15 de bouclier perso (cf. Général) + donne du bouclier aux alliés chaque tour. À gauche. Synergie tank + dégâts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>fou-du-roi</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>The King's Fool</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>10</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>fou</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>200</v>
+      </c>
+      <c r="H46" t="n">
+        <v>14</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Marché (500/2000/10000 🪙) ; fuite après 1 tour du héros ; vol 200 🪙 si touché</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>TOUTES les profondeurs — 0,1 % par rencontre (tirage dédié, hors pool de zone)</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Rencontre-énigme : ne frappe jamais. Tué = butin garanti (5000 🪙 + 10 rubis/émeraude/saphir/diamant + 1 onyx + 1 sunstone) et ne revient plus. 3e paiement = cadeau (50000 XP, 10 onyx, 10 sunstone, 20 bois enchanté, 20 cuir étrange).</t>
         </is>
       </c>
     </row>

--- a/docs/BRUTAL-items-et-cartes.xlsx
+++ b/docs/BRUTAL-items-et-cartes.xlsx
@@ -3489,7 +3489,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Marché (500/2000/10000 🪙) ; fuite après 1 tour du héros ; vol 200 🪙 si touché</t>
+          <t>Marché (500/2000/10000 🪙) ; fuit après 1 tour du héros ; vol 200 🪙 si touché ; RANCUNE (après cadeau) : ne fuit plus et frappe à 60</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Rencontre-énigme : ne frappe jamais. Tué = butin garanti (5000 🪙 + 10 rubis/émeraude/saphir/diamant + 1 onyx + 1 sunstone) et ne revient plus. 3e paiement = cadeau (50000 XP, 10 onyx, 10 sunstone, 20 bois enchanté, 20 cuir étrange).</t>
+          <t>Rencontre-énigme : ne frappe JAMAIS tant qu'il marchande (il fuit avant). SEULE exception, la rancune (rencontre d'après le cadeau) : il reste et attaque à 60. Tué = butin garanti (5000 🪙 + 10 rubis/émeraude/saphir/diamant + 1 onyx + 1 sunstone) et ne revient plus. 3e paiement = cadeau (50000 XP, 10 onyx, 10 sunstone, 20 bois enchanté, 20 cuir étrange).</t>
         </is>
       </c>
     </row>

--- a/docs/BRUTAL-items-et-cartes.xlsx
+++ b/docs/BRUTAL-items-et-cartes.xlsx
@@ -3670,7 +3670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" style="102" min="1" max="1"/>
@@ -3694,6 +3694,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="107" t="inlineStr">
         <is>
@@ -4546,94 +4547,94 @@
     <row r="39">
       <c r="A39" s="110" t="inlineStr">
         <is>
-          <t>Combat</t>
+          <t>Groupes</t>
         </is>
       </c>
       <c r="B39" s="110" t="inlineStr">
         <is>
-          <t>Fuite selon nb d'ennemis</t>
+          <t>Meneur de la rencontre</t>
         </is>
       </c>
       <c r="C39" s="111" t="inlineStr">
         <is>
-          <t>50 / 33 / 25 / 25 / 20 %</t>
+          <t>1 monstre du bon niveau</t>
         </is>
       </c>
       <c r="D39" s="110" t="inlineStr">
         <is>
-          <t>Chance de fuir un combat normal selon le nombre d'ennemis (1 à 5).</t>
+          <t>Chaque rencontre part d'UN monstre tiré dans la fourchette de niveau de l'étage. C'est lui qui fixe la famille du groupe, et il en fait toujours partie.</t>
         </is>
       </c>
       <c r="E39" s="110" t="inlineStr">
         <is>
-          <t>ui/combat.js</t>
+          <t>data/ennemis.js</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="108" t="inlineStr">
-        <is>
-          <t>PASSIFS DE FAMILLE (monstres)</t>
-        </is>
-      </c>
-      <c r="B40" s="109" t="n"/>
-      <c r="C40" s="109" t="n"/>
-      <c r="D40" s="109" t="n"/>
-      <c r="E40" s="109" t="n"/>
+      <c r="A40" s="110" t="inlineStr">
+        <is>
+          <t>Groupes</t>
+        </is>
+      </c>
+      <c r="B40" s="110" t="inlineStr">
+        <is>
+          <t>Compagnons : niveau autorisé</t>
+        </is>
+      </c>
+      <c r="C40" s="111" t="inlineStr">
+        <is>
+          <t>≤ haut de la fourchette</t>
+        </is>
+      </c>
+      <c r="D40" s="110" t="inlineStr">
+        <is>
+          <t>Les compagnons sont de la même famille que le meneur. Jamais au-dessus de la fourchette de l'étage (le combat resterait jouable), mais EN DESSOUS c'est permis — pour la variété. Plus un compagnon est loin du niveau du meneur, plus il est rare (même facteur 2).</t>
+        </is>
+      </c>
+      <c r="E40" s="110" t="inlineStr">
+        <is>
+          <t>data/ennemis.js</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="110" t="inlineStr">
         <is>
-          <t>Champignons</t>
+          <t>Combat</t>
         </is>
       </c>
       <c r="B41" s="110" t="inlineStr">
         <is>
-          <t>Force collective : par champignon</t>
+          <t>Fuite selon nb d'ennemis</t>
         </is>
       </c>
       <c r="C41" s="111" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>50 / 33 / 25 / 25 / 20 %</t>
         </is>
       </c>
       <c r="D41" s="110" t="inlineStr">
         <is>
-          <t>Chaque champignon VIVANT en combat donne +1 de Force (dégâts, à chaque coup) à TOUS les champignons. Recalculé à chaque mort : un champignon qui tombe retire son apport.</t>
+          <t>Chance de fuir un combat normal selon le nombre d'ennemis (1 à 5).</t>
         </is>
       </c>
       <c r="E41" s="110" t="inlineStr">
         <is>
-          <t>systems/combat.js</t>
+          <t>ui/combat.js</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="110" t="inlineStr">
-        <is>
-          <t>Champignons</t>
-        </is>
-      </c>
-      <c r="B42" s="110" t="inlineStr">
-        <is>
-          <t>Force collective : apport du Roi</t>
-        </is>
-      </c>
-      <c r="C42" s="111" t="inlineStr">
-        <is>
-          <t>+5</t>
-        </is>
-      </c>
-      <c r="D42" s="110" t="inlineStr">
-        <is>
-          <t>Le Roi champignon compte pour +5 (au lieu de +1) dans la Force collective des champignons.</t>
-        </is>
-      </c>
-      <c r="E42" s="110" t="inlineStr">
-        <is>
-          <t>systems/combat.js + data/ennemis.js</t>
-        </is>
-      </c>
+      <c r="A42" s="108" t="inlineStr">
+        <is>
+          <t>PASSIFS DE FAMILLE (monstres)</t>
+        </is>
+      </c>
+      <c r="B42" s="109" t="n"/>
+      <c r="C42" s="109" t="n"/>
+      <c r="D42" s="109" t="n"/>
+      <c r="E42" s="109" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="110" t="inlineStr">
@@ -4643,94 +4644,94 @@
       </c>
       <c r="B43" s="110" t="inlineStr">
         <is>
-          <t>Rois par combat</t>
+          <t>Force collective : par champignon</t>
         </is>
       </c>
       <c r="C43" s="111" t="inlineStr">
         <is>
-          <t>1 max</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="D43" s="110" t="inlineStr">
         <is>
-          <t>Il ne peut y avoir qu'UN seul Roi champignon par rencontre (garde-fou dans le tirage de groupe).</t>
+          <t>Chaque champignon VIVANT en combat donne +1 de Force (dégâts, à chaque coup) à TOUS les champignons. Recalculé à chaque mort : un champignon qui tombe retire son apport.</t>
         </is>
       </c>
       <c r="E43" s="110" t="inlineStr">
         <is>
-          <t>data/ennemis.js</t>
+          <t>systems/combat.js</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="108" t="inlineStr">
-        <is>
-          <t>GOBELIN BLINDÉ (bouclier ennemi + duo)</t>
-        </is>
-      </c>
-      <c r="B44" s="109" t="n"/>
-      <c r="C44" s="109" t="n"/>
-      <c r="D44" s="109" t="n"/>
-      <c r="E44" s="109" t="n"/>
+      <c r="A44" s="110" t="inlineStr">
+        <is>
+          <t>Champignons</t>
+        </is>
+      </c>
+      <c r="B44" s="110" t="inlineStr">
+        <is>
+          <t>Force collective : apport du Roi</t>
+        </is>
+      </c>
+      <c r="C44" s="111" t="inlineStr">
+        <is>
+          <t>+5</t>
+        </is>
+      </c>
+      <c r="D44" s="110" t="inlineStr">
+        <is>
+          <t>Le Roi champignon compte pour +5 (au lieu de +1) dans la Force collective des champignons.</t>
+        </is>
+      </c>
+      <c r="E44" s="110" t="inlineStr">
+        <is>
+          <t>systems/combat.js + data/ennemis.js</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="110" t="inlineStr">
         <is>
-          <t>Gobelin blindé</t>
+          <t>Champignons</t>
         </is>
       </c>
       <c r="B45" s="110" t="inlineStr">
         <is>
-          <t>Bouclier de départ</t>
+          <t>Rois par combat</t>
         </is>
       </c>
       <c r="C45" s="111" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1 max</t>
         </is>
       </c>
       <c r="D45" s="110" t="inlineStr">
         <is>
-          <t>BOUCLIER du Gobelin blindé : absorbe les dégâts avant ses PV (comme la Pierre du héros). Sous le bouclier il n'a que 10 PV.</t>
+          <t>Il ne peut y avoir qu'UN seul Roi champignon par rencontre (garde-fou dans le tirage de groupe).</t>
         </is>
       </c>
       <c r="E45" s="110" t="inlineStr">
         <is>
-          <t>data/ennemis.js (bouclierDepart)</t>
+          <t>data/ennemis.js</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="110" t="inlineStr">
-        <is>
-          <t>Gobelin blindé</t>
-        </is>
-      </c>
-      <c r="B46" s="110" t="inlineStr">
-        <is>
-          <t>PV sous le bouclier</t>
-        </is>
-      </c>
-      <c r="C46" s="111" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D46" s="110" t="inlineStr">
-        <is>
-          <t>Points de vie réels une fois le bouclier tombé.</t>
-        </is>
-      </c>
-      <c r="E46" s="110" t="inlineStr">
-        <is>
-          <t>data/ennemis.js</t>
-        </is>
-      </c>
+      <c r="A46" s="108" t="inlineStr">
+        <is>
+          <t>GOBELIN BLINDÉ (bouclier ennemi + duo)</t>
+        </is>
+      </c>
+      <c r="B46" s="109" t="n"/>
+      <c r="C46" s="109" t="n"/>
+      <c r="D46" s="109" t="n"/>
+      <c r="E46" s="109" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="110" t="inlineStr">
         <is>
-          <t>Gobelin défenseur</t>
+          <t>Gobelin blindé</t>
         </is>
       </c>
       <c r="B47" s="110" t="inlineStr">
@@ -4740,12 +4741,12 @@
       </c>
       <c r="C47" s="111" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D47" s="110" t="inlineStr">
         <is>
-          <t>Garde personnelle du gobelin porteur de bouclier (défenseur), une fois sorti de l'armure.</t>
+          <t>BOUCLIER du Gobelin blindé : absorbe les dégâts avant ses PV (comme la Pierre du héros). Sous le bouclier il n'a que 10 PV.</t>
         </is>
       </c>
       <c r="E47" s="110" t="inlineStr">
@@ -4757,25 +4758,79 @@
     <row r="48">
       <c r="A48" s="110" t="inlineStr">
         <is>
+          <t>Gobelin blindé</t>
+        </is>
+      </c>
+      <c r="B48" s="110" t="inlineStr">
+        <is>
+          <t>PV sous le bouclier</t>
+        </is>
+      </c>
+      <c r="C48" s="111" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D48" s="110" t="inlineStr">
+        <is>
+          <t>Points de vie réels une fois le bouclier tombé.</t>
+        </is>
+      </c>
+      <c r="E48" s="110" t="inlineStr">
+        <is>
+          <t>data/ennemis.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="110" t="inlineStr">
+        <is>
           <t>Gobelin défenseur</t>
         </is>
       </c>
-      <c r="B48" s="110" t="inlineStr">
+      <c r="B49" s="110" t="inlineStr">
+        <is>
+          <t>Bouclier de départ</t>
+        </is>
+      </c>
+      <c r="C49" s="111" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D49" s="110" t="inlineStr">
+        <is>
+          <t>Garde personnelle du gobelin porteur de bouclier (défenseur), une fois sorti de l'armure.</t>
+        </is>
+      </c>
+      <c r="E49" s="110" t="inlineStr">
+        <is>
+          <t>data/ennemis.js (bouclierDepart)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="110" t="inlineStr">
+        <is>
+          <t>Gobelin défenseur</t>
+        </is>
+      </c>
+      <c r="B50" s="110" t="inlineStr">
         <is>
           <t>Bouclier donné aux alliés / tour</t>
         </is>
       </c>
-      <c r="C48" s="111" t="inlineStr">
+      <c r="C50" s="111" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D48" s="110" t="inlineStr">
+      <c r="D50" s="110" t="inlineStr">
         <is>
           <t>Bouclier que le défenseur donne à ses alliés vivants à chaque tour (protège l'attaquant → synergie tank + dégâts).</t>
         </is>
       </c>
-      <c r="E48" s="110" t="inlineStr">
+      <c r="E50" s="110" t="inlineStr">
         <is>
           <t>data/ennemis.js (actions) + systems/combat.js</t>
         </is>

--- a/docs/BRUTAL-items-et-cartes.xlsx
+++ b/docs/BRUTAL-items-et-cartes.xlsx
@@ -4894,7 +4894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" style="146" min="1" max="1"/>
@@ -5850,25 +5850,65 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="148" t="n"/>
-      <c r="B42" s="149" t="n"/>
-      <c r="C42" s="149" t="n"/>
-      <c r="D42" s="149" t="n"/>
-      <c r="E42" s="149" t="n"/>
+      <c r="A42" s="150" t="inlineStr">
+        <is>
+          <t>Combat</t>
+        </is>
+      </c>
+      <c r="B42" s="150" t="inlineStr">
+        <is>
+          <t>Hâte : bonus de vitesse</t>
+        </is>
+      </c>
+      <c r="C42" s="151" t="inlineStr">
+        <is>
+          <t>×1,30</t>
+        </is>
+      </c>
+      <c r="D42" s="150" t="inlineStr">
+        <is>
+          <t>Bonus FIXE tant qu'il reste au moins un tick de Hâte (héros ET monstres). Ne dépend PAS du nombre de ticks : ils ne font que la durée.</t>
+        </is>
+      </c>
+      <c r="E42" s="150" t="inlineStr">
+        <is>
+          <t>systems/combat.js</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="150" t="n"/>
-      <c r="B43" s="150" t="n"/>
-      <c r="C43" s="151" t="n"/>
-      <c r="D43" s="150" t="n"/>
-      <c r="E43" s="150" t="n"/>
+      <c r="A43" s="150" t="inlineStr">
+        <is>
+          <t>Combat</t>
+        </is>
+      </c>
+      <c r="B43" s="150" t="inlineStr">
+        <is>
+          <t>Hâte : seuil du tour bonus</t>
+        </is>
+      </c>
+      <c r="C43" s="151" t="inlineStr">
+        <is>
+          <t>8 ticks</t>
+        </is>
+      </c>
+      <c r="D43" s="150" t="inlineStr">
+        <is>
+          <t>À 8 ticks accumulés, le combattant rejoue immédiatement — et ça lui coûte 8 ticks (le surplus reste). Baisser ce seuil = plus de tours d'affilée.</t>
+        </is>
+      </c>
+      <c r="E43" s="150" t="inlineStr">
+        <is>
+          <t>systems/combat.js</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="150" t="n"/>
-      <c r="B44" s="150" t="n"/>
-      <c r="C44" s="151" t="n"/>
-      <c r="D44" s="150" t="n"/>
-      <c r="E44" s="150" t="n"/>
+      <c r="A44" s="148" t="n"/>
+      <c r="B44" s="149" t="n"/>
+      <c r="C44" s="149" t="n"/>
+      <c r="D44" s="149" t="n"/>
+      <c r="E44" s="149" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="150" t="n"/>
@@ -5878,11 +5918,11 @@
       <c r="E45" s="150" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="148" t="n"/>
-      <c r="B46" s="149" t="n"/>
-      <c r="C46" s="149" t="n"/>
-      <c r="D46" s="149" t="n"/>
-      <c r="E46" s="149" t="n"/>
+      <c r="A46" s="150" t="n"/>
+      <c r="B46" s="150" t="n"/>
+      <c r="C46" s="151" t="n"/>
+      <c r="D46" s="150" t="n"/>
+      <c r="E46" s="150" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="150" t="n"/>
@@ -5892,11 +5932,11 @@
       <c r="E47" s="150" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="150" t="n"/>
-      <c r="B48" s="150" t="n"/>
-      <c r="C48" s="151" t="n"/>
-      <c r="D48" s="150" t="n"/>
-      <c r="E48" s="150" t="n"/>
+      <c r="A48" s="148" t="n"/>
+      <c r="B48" s="149" t="n"/>
+      <c r="C48" s="149" t="n"/>
+      <c r="D48" s="149" t="n"/>
+      <c r="E48" s="149" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="150" t="n"/>
@@ -5911,6 +5951,20 @@
       <c r="C50" s="151" t="n"/>
       <c r="D50" s="150" t="n"/>
       <c r="E50" s="150" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="150" t="n"/>
+      <c r="B51" s="150" t="n"/>
+      <c r="C51" s="151" t="n"/>
+      <c r="D51" s="150" t="n"/>
+      <c r="E51" s="150" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="150" t="n"/>
+      <c r="B52" s="150" t="n"/>
+      <c r="C52" s="151" t="n"/>
+      <c r="D52" s="150" t="n"/>
+      <c r="E52" s="150" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -19889,7 +19943,7 @@
       </c>
       <c r="C21" s="44" t="inlineStr">
         <is>
-          <t>N ticks. Chaque tick = +5% vitesse. −1 tick par tour du héros.</t>
+          <t>N ticks. Tant qu'il reste AU MOINS un tick : +30 % de vitesse (bonus FIXE, jamais plus quel que soit le nombre de ticks). −1 tick par tour. À 8 ticks : un tour bonus, qui coûte ces 8 ticks.</t>
         </is>
       </c>
       <c r="D21" s="44" t="inlineStr">
@@ -20760,6 +20814,7 @@
         </is>
       </c>
     </row>
+    <row r="65"/>
     <row r="66" ht="24" customHeight="1" s="146">
       <c r="A66" s="46" t="inlineStr">
         <is>
@@ -21100,6 +21155,7 @@
         </is>
       </c>
     </row>
+    <row r="82"/>
     <row r="83" ht="24" customHeight="1" s="146">
       <c r="A83" s="46" t="inlineStr">
         <is>

--- a/docs/BRUTAL-items-et-cartes.xlsx
+++ b/docs/BRUTAL-items-et-cartes.xlsx
@@ -4918,7 +4918,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="103" t="inlineStr">
         <is>
@@ -5977,7 +5976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L171"/>
+  <dimension ref="A1:L174"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" style="146" min="1" max="1"/>
@@ -14772,7 +14771,11 @@
       <c r="J165" s="55" t="n"/>
     </row>
     <row r="166" ht="15" customHeight="1" s="146">
-      <c r="A166" s="55" t="n"/>
+      <c r="A166" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸ FORCE BRUTE (set du Barbare)</t>
+        </is>
+      </c>
       <c r="B166" s="55" t="n"/>
       <c r="C166" s="55" t="n"/>
       <c r="D166" s="55" t="n"/>
@@ -14784,64 +14787,424 @@
       <c r="J166" s="55" t="n"/>
     </row>
     <row r="167" ht="15" customHeight="1" s="146">
-      <c r="A167" s="55" t="n"/>
-      <c r="B167" s="55" t="n"/>
-      <c r="C167" s="55" t="n"/>
-      <c r="D167" s="55" t="n"/>
-      <c r="E167" s="55" t="n"/>
-      <c r="F167" s="55" t="n"/>
-      <c r="G167" s="55" t="n"/>
-      <c r="H167" s="55" t="n"/>
-      <c r="I167" s="55" t="n"/>
-      <c r="J167" s="55" t="n"/>
+      <c r="A167" s="13" t="inlineStr">
+        <is>
+          <t>Force brute</t>
+        </is>
+      </c>
+      <c r="B167" s="13" t="inlineStr">
+        <is>
+          <t>War Cry</t>
+        </is>
+      </c>
+      <c r="C167" s="13" t="inlineStr">
+        <is>
+          <t>cri-de-guerre</t>
+        </is>
+      </c>
+      <c r="D167" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E167" s="13" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="F167" s="13" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="G167" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H167" s="13" t="inlineStr"/>
+      <c r="I167" s="14" t="inlineStr">
+        <is>
+          <t>Barbarian Harness ×2, Barbarian Boots ×1</t>
+        </is>
+      </c>
+      <c r="J167" s="14" t="inlineStr">
+        <is>
+          <t>Gain 4 Strength.</t>
+        </is>
+      </c>
+      <c r="K167" s="57" t="inlineStr"/>
+      <c r="L167" s="2" t="inlineStr">
+        <is>
+          <t>set barbare — 1er jet</t>
+        </is>
+      </c>
     </row>
     <row r="168" ht="15" customHeight="1" s="146">
-      <c r="A168" s="55" t="n"/>
-      <c r="B168" s="55" t="n"/>
-      <c r="C168" s="55" t="n"/>
-      <c r="D168" s="55" t="n"/>
-      <c r="E168" s="55" t="n"/>
-      <c r="F168" s="55" t="n"/>
-      <c r="G168" s="55" t="n"/>
-      <c r="H168" s="55" t="n"/>
-      <c r="I168" s="55" t="n"/>
-      <c r="J168" s="55" t="n"/>
+      <c r="A168" s="13" t="inlineStr">
+        <is>
+          <t>Force brute</t>
+        </is>
+      </c>
+      <c r="B168" s="13" t="inlineStr">
+        <is>
+          <t>Beast Hide</t>
+        </is>
+      </c>
+      <c r="C168" s="13" t="inlineStr">
+        <is>
+          <t>peau-de-fauve</t>
+        </is>
+      </c>
+      <c r="D168" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E168" s="13" t="inlineStr">
+        <is>
+          <t>Défense</t>
+        </is>
+      </c>
+      <c r="F168" s="13" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="G168" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H168" s="13" t="inlineStr"/>
+      <c r="I168" s="14" t="inlineStr">
+        <is>
+          <t>Barbarian Harness ×2</t>
+        </is>
+      </c>
+      <c r="J168" s="14" t="inlineStr">
+        <is>
+          <t>Gain 9 Stone.</t>
+        </is>
+      </c>
+      <c r="K168" s="57" t="inlineStr"/>
+      <c r="L168" s="2" t="inlineStr">
+        <is>
+          <t>9 armure / 1 chaleur</t>
+        </is>
+      </c>
     </row>
     <row r="169">
-      <c r="A169" s="55" t="n"/>
-      <c r="B169" s="55" t="n"/>
-      <c r="C169" s="55" t="n"/>
-      <c r="D169" s="55" t="n"/>
-      <c r="E169" s="55" t="n"/>
-      <c r="F169" s="55" t="n"/>
-      <c r="G169" s="55" t="n"/>
-      <c r="H169" s="55" t="n"/>
-      <c r="I169" s="55" t="n"/>
-      <c r="J169" s="55" t="n"/>
+      <c r="A169" s="13" t="inlineStr">
+        <is>
+          <t>Force brute</t>
+        </is>
+      </c>
+      <c r="B169" s="13" t="inlineStr">
+        <is>
+          <t>Reckless Charge</t>
+        </is>
+      </c>
+      <c r="C169" s="13" t="inlineStr">
+        <is>
+          <t>charge-brutale</t>
+        </is>
+      </c>
+      <c r="D169" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E169" s="13" t="inlineStr">
+        <is>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="F169" s="13" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="G169" s="13" t="inlineStr">
+        <is>
+          <t>Mêlée</t>
+        </is>
+      </c>
+      <c r="H169" s="13" t="inlineStr"/>
+      <c r="I169" s="14" t="inlineStr">
+        <is>
+          <t>Barbarian Harness ×1, Barbarian Boots ×2</t>
+        </is>
+      </c>
+      <c r="J169" s="14" t="inlineStr">
+        <is>
+          <t>Deal 10 damage. Lose 3 HP.</t>
+        </is>
+      </c>
+      <c r="K169" s="57" t="inlineStr"/>
+      <c r="L169" s="2" t="inlineStr">
+        <is>
+          <t>10 dégâts / 1 chaleur (coût en PV)</t>
+        </is>
+      </c>
     </row>
     <row r="170">
-      <c r="A170" s="55" t="n"/>
-      <c r="B170" s="55" t="n"/>
-      <c r="C170" s="55" t="n"/>
-      <c r="D170" s="55" t="n"/>
-      <c r="E170" s="55" t="n"/>
-      <c r="F170" s="55" t="n"/>
-      <c r="G170" s="55" t="n"/>
-      <c r="H170" s="55" t="n"/>
-      <c r="I170" s="55" t="n"/>
-      <c r="J170" s="55" t="n"/>
+      <c r="A170" s="13" t="inlineStr">
+        <is>
+          <t>Force brute</t>
+        </is>
+      </c>
+      <c r="B170" s="13" t="inlineStr">
+        <is>
+          <t>Titan Blow</t>
+        </is>
+      </c>
+      <c r="C170" s="13" t="inlineStr">
+        <is>
+          <t>frappe-titanesque</t>
+        </is>
+      </c>
+      <c r="D170" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E170" s="13" t="inlineStr">
+        <is>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="F170" s="13" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="G170" s="13" t="inlineStr">
+        <is>
+          <t>Mêlée</t>
+        </is>
+      </c>
+      <c r="H170" s="13" t="inlineStr"/>
+      <c r="I170" s="14" t="inlineStr">
+        <is>
+          <t>Barbarian Harness ×1</t>
+        </is>
+      </c>
+      <c r="J170" s="14" t="inlineStr">
+        <is>
+          <t>Deal 14 damage. Doubled if your Strength is 15 or more.</t>
+        </is>
+      </c>
+      <c r="K170" s="57" t="inlineStr"/>
+      <c r="L170" s="2" t="inlineStr">
+        <is>
+          <t>14 ou 28 / 3 chaleur</t>
+        </is>
+      </c>
     </row>
     <row r="171">
-      <c r="A171" s="55" t="n"/>
-      <c r="B171" s="55" t="n"/>
-      <c r="C171" s="55" t="n"/>
-      <c r="D171" s="55" t="n"/>
-      <c r="E171" s="55" t="n"/>
-      <c r="F171" s="55" t="n"/>
-      <c r="G171" s="55" t="n"/>
-      <c r="H171" s="55" t="n"/>
-      <c r="I171" s="55" t="n"/>
-      <c r="J171" s="55" t="n"/>
+      <c r="A171" s="13" t="inlineStr">
+        <is>
+          <t>Force brute</t>
+        </is>
+      </c>
+      <c r="B171" s="13" t="inlineStr">
+        <is>
+          <t>Maul Swing</t>
+        </is>
+      </c>
+      <c r="C171" s="13" t="inlineStr">
+        <is>
+          <t>coup-de-massue</t>
+        </is>
+      </c>
+      <c r="D171" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E171" s="13" t="inlineStr">
+        <is>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="F171" s="13" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="G171" s="13" t="inlineStr">
+        <is>
+          <t>Mêlée</t>
+        </is>
+      </c>
+      <c r="H171" s="13" t="inlineStr"/>
+      <c r="I171" s="14" t="inlineStr">
+        <is>
+          <t>Barbarian Bracers ×2</t>
+        </is>
+      </c>
+      <c r="J171" s="14" t="inlineStr">
+        <is>
+          <t>Deal 12 damage.</t>
+        </is>
+      </c>
+      <c r="K171" s="57" t="inlineStr"/>
+      <c r="L171" s="2" t="inlineStr">
+        <is>
+          <t>12 dégâts / 2 chaleur</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="13" t="inlineStr">
+        <is>
+          <t>Force brute</t>
+        </is>
+      </c>
+      <c r="B172" s="13" t="inlineStr">
+        <is>
+          <t>Whirlwind</t>
+        </is>
+      </c>
+      <c r="C172" s="13" t="inlineStr">
+        <is>
+          <t>moulinet</t>
+        </is>
+      </c>
+      <c r="D172" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E172" s="13" t="inlineStr">
+        <is>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="F172" s="13" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="G172" s="13" t="inlineStr">
+        <is>
+          <t>Mêlée</t>
+        </is>
+      </c>
+      <c r="H172" s="13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I172" s="14" t="inlineStr">
+        <is>
+          <t>Barbarian Bracers ×2</t>
+        </is>
+      </c>
+      <c r="J172" s="14" t="inlineStr">
+        <is>
+          <t>Deal 8 damage. Both neighbours take 8.</t>
+        </is>
+      </c>
+      <c r="K172" s="57" t="inlineStr"/>
+      <c r="L172" s="2" t="inlineStr">
+        <is>
+          <t>jusqu'à 24 / 2 chaleur</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="13" t="inlineStr">
+        <is>
+          <t>Force brute</t>
+        </is>
+      </c>
+      <c r="B173" s="13" t="inlineStr">
+        <is>
+          <t>Bloodlust</t>
+        </is>
+      </c>
+      <c r="C173" s="13" t="inlineStr">
+        <is>
+          <t>curee</t>
+        </is>
+      </c>
+      <c r="D173" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E173" s="13" t="inlineStr">
+        <is>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="F173" s="13" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="G173" s="13" t="inlineStr">
+        <is>
+          <t>Mêlée</t>
+        </is>
+      </c>
+      <c r="H173" s="13" t="inlineStr"/>
+      <c r="I173" s="14" t="inlineStr">
+        <is>
+          <t>Barbarian Bracers ×2</t>
+        </is>
+      </c>
+      <c r="J173" s="14" t="inlineStr">
+        <is>
+          <t>Deal 6 damage. If the target dies, gain 5 Strength and heal 5 HP.</t>
+        </is>
+      </c>
+      <c r="K173" s="57" t="inlineStr"/>
+      <c r="L173" s="2" t="inlineStr">
+        <is>
+          <t>6 dégâts + prime d'exécution</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="13" t="inlineStr">
+        <is>
+          <t>Force brute</t>
+        </is>
+      </c>
+      <c r="B174" s="13" t="inlineStr">
+        <is>
+          <t>Stomp</t>
+        </is>
+      </c>
+      <c r="C174" s="13" t="inlineStr">
+        <is>
+          <t>pietinement</t>
+        </is>
+      </c>
+      <c r="D174" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E174" s="13" t="inlineStr">
+        <is>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="F174" s="13" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="G174" s="13" t="inlineStr">
+        <is>
+          <t>Mêlée</t>
+        </is>
+      </c>
+      <c r="H174" s="13" t="inlineStr"/>
+      <c r="I174" s="14" t="inlineStr">
+        <is>
+          <t>Barbarian Boots ×2</t>
+        </is>
+      </c>
+      <c r="J174" s="14" t="inlineStr">
+        <is>
+          <t>Deal 7 damage. Gain 2 Strength.</t>
+        </is>
+      </c>
+      <c r="K174" s="57" t="inlineStr"/>
+      <c r="L174" s="2" t="inlineStr">
+        <is>
+          <t>7 dégâts / 1 chaleur</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -19324,7 +19687,11 @@
       <c r="F135" s="55" t="n"/>
     </row>
     <row r="136" ht="15" customHeight="1" s="146">
-      <c r="A136" s="55" t="n"/>
+      <c r="A136" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸ SET DU BARBARE (rare — 1er jet, à réviser)</t>
+        </is>
+      </c>
       <c r="B136" s="55" t="n"/>
       <c r="C136" s="55" t="n"/>
       <c r="D136" s="55" t="n"/>
@@ -19332,28 +19699,115 @@
       <c r="F136" s="55" t="n"/>
     </row>
     <row r="137" ht="15" customHeight="1" s="146">
-      <c r="A137" s="55" t="n"/>
-      <c r="B137" s="55" t="n"/>
-      <c r="C137" s="55" t="n"/>
-      <c r="D137" s="55" t="n"/>
-      <c r="E137" s="55" t="n"/>
-      <c r="F137" s="55" t="n"/>
+      <c r="A137" s="49" t="inlineStr">
+        <is>
+          <t>Armures</t>
+        </is>
+      </c>
+      <c r="B137" s="49" t="inlineStr">
+        <is>
+          <t>Barbarian Harness</t>
+        </is>
+      </c>
+      <c r="C137" s="49" t="inlineStr">
+        <is>
+          <t>plastron-barbare</t>
+        </is>
+      </c>
+      <c r="D137" s="49" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="E137" s="50" t="inlineStr">
+        <is>
+          <t>Beast Hide×2, War Cry×2, Reckless Charge×1, Titan Blow×1</t>
+        </is>
+      </c>
+      <c r="F137" s="50" t="inlineStr">
+        <is>
+          <t>Armure début: 15  ·  Set: Barbarian Set</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>≈ 24 dégâts  ·  ≈ 18 armure  (6 cartes/6 visées · 2 buff)</t>
+        </is>
+      </c>
     </row>
     <row r="138" ht="15" customHeight="1" s="146">
-      <c r="A138" s="55" t="n"/>
-      <c r="B138" s="55" t="n"/>
-      <c r="C138" s="55" t="n"/>
-      <c r="D138" s="55" t="n"/>
-      <c r="E138" s="55" t="n"/>
-      <c r="F138" s="55" t="n"/>
+      <c r="A138" s="49" t="inlineStr">
+        <is>
+          <t>Gants</t>
+        </is>
+      </c>
+      <c r="B138" s="49" t="inlineStr">
+        <is>
+          <t>Barbarian Bracers</t>
+        </is>
+      </c>
+      <c r="C138" s="49" t="inlineStr">
+        <is>
+          <t>brassards-barbare</t>
+        </is>
+      </c>
+      <c r="D138" s="49" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="E138" s="50" t="inlineStr">
+        <is>
+          <t>Maul Swing×2, Whirlwind×2, Bloodlust×2</t>
+        </is>
+      </c>
+      <c r="F138" s="50" t="inlineStr">
+        <is>
+          <t>Set: Barbarian Set</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>≈ 60 dégâts  (6 cartes/6 visées)</t>
+        </is>
+      </c>
     </row>
     <row r="139" ht="15" customHeight="1" s="146">
-      <c r="A139" s="55" t="n"/>
-      <c r="B139" s="55" t="n"/>
-      <c r="C139" s="55" t="n"/>
-      <c r="D139" s="55" t="n"/>
-      <c r="E139" s="55" t="n"/>
-      <c r="F139" s="55" t="n"/>
+      <c r="A139" s="49" t="inlineStr">
+        <is>
+          <t>Bottes</t>
+        </is>
+      </c>
+      <c r="B139" s="49" t="inlineStr">
+        <is>
+          <t>Barbarian Boots</t>
+        </is>
+      </c>
+      <c r="C139" s="49" t="inlineStr">
+        <is>
+          <t>bottes-barbare</t>
+        </is>
+      </c>
+      <c r="D139" s="49" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="E139" s="50" t="inlineStr">
+        <is>
+          <t>Stomp×2, Reckless Charge×2, War Cry×1, Boost×1</t>
+        </is>
+      </c>
+      <c r="F139" s="50" t="inlineStr">
+        <is>
+          <t>+100 Agilité  ·  +20% déplacement  ·  Set: Barbarian Set</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>≈ 34 dégâts  (6 cartes/6 visées · 2 buff)</t>
+        </is>
+      </c>
     </row>
     <row r="140" ht="15" customHeight="1" s="146">
       <c r="A140" s="55" t="n"/>
@@ -19391,7 +19845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" style="146" min="1" max="1"/>
@@ -19543,6 +19997,28 @@
       <c r="D9" s="44" t="inlineStr">
         <is>
           <t>Every 10 Stone cards played in a combat, stun ALL enemies for 1 turn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="44" t="inlineStr">
+        <is>
+          <t>Barbarian Set</t>
+        </is>
+      </c>
+      <c r="B10" s="44" t="inlineStr">
+        <is>
+          <t>Barbarian Harness  +  Barbarian Bracers  +  Barbarian Boots</t>
+        </is>
+      </c>
+      <c r="C10" s="44" t="inlineStr">
+        <is>
+          <t>Début de combat + à chaque ennemi tué</t>
+        </is>
+      </c>
+      <c r="D10" s="44" t="inlineStr">
+        <is>
+          <t>+5 Strength for the whole fight. Each enemy slain grants +5 more Strength, until the end of the fight.</t>
         </is>
       </c>
     </row>
@@ -20814,7 +21290,6 @@
         </is>
       </c>
     </row>
-    <row r="65"/>
     <row r="66" ht="24" customHeight="1" s="146">
       <c r="A66" s="46" t="inlineStr">
         <is>
@@ -21155,7 +21630,6 @@
         </is>
       </c>
     </row>
-    <row r="82"/>
     <row r="83" ht="24" customHeight="1" s="146">
       <c r="A83" s="46" t="inlineStr">
         <is>

--- a/docs/BRUTAL-items-et-cartes.xlsx
+++ b/docs/BRUTAL-items-et-cartes.xlsx
@@ -5976,7 +5976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L174"/>
+  <dimension ref="A1:L185"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" style="146" min="1" max="1"/>
@@ -15206,6 +15206,495 @@
         </is>
       </c>
     </row>
+    <row r="176">
+      <c r="A176" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸ JUGEMENT (set béni par Dunïr)</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="13" t="inlineStr">
+        <is>
+          <t>Jugement</t>
+        </is>
+      </c>
+      <c r="B177" s="13" t="inlineStr">
+        <is>
+          <t>Judgement</t>
+        </is>
+      </c>
+      <c r="C177" s="13" t="inlineStr">
+        <is>
+          <t>jugement</t>
+        </is>
+      </c>
+      <c r="D177" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E177" s="13" t="inlineStr">
+        <is>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="F177" s="13" t="inlineStr">
+        <is>
+          <t>Épique</t>
+        </is>
+      </c>
+      <c r="G177" s="13" t="inlineStr">
+        <is>
+          <t>Mêlée</t>
+        </is>
+      </c>
+      <c r="H177" s="13" t="inlineStr"/>
+      <c r="I177" s="14" t="inlineStr">
+        <is>
+          <t>Plate ×1, Gauntlets ×2, Sabatons ×2</t>
+        </is>
+      </c>
+      <c r="J177" s="14" t="inlineStr">
+        <is>
+          <t>Deal 6 damage. Apply 3 Judgement.</t>
+        </is>
+      </c>
+      <c r="K177" s="57" t="inlineStr"/>
+      <c r="L177" s="2" t="inlineStr">
+        <is>
+          <t>set Dunïr — 1er jet</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="13" t="inlineStr">
+        <is>
+          <t>Jugement</t>
+        </is>
+      </c>
+      <c r="B178" s="13" t="inlineStr">
+        <is>
+          <t>Seal of Dunir</t>
+        </is>
+      </c>
+      <c r="C178" s="13" t="inlineStr">
+        <is>
+          <t>sceau-de-dunir</t>
+        </is>
+      </c>
+      <c r="D178" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E178" s="13" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="F178" s="13" t="inlineStr">
+        <is>
+          <t>Épique</t>
+        </is>
+      </c>
+      <c r="G178" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H178" s="13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I178" s="14" t="inlineStr">
+        <is>
+          <t>Plate ×1</t>
+        </is>
+      </c>
+      <c r="J178" s="14" t="inlineStr">
+        <is>
+          <t>Apply 2 Judgement to ALL enemies.</t>
+        </is>
+      </c>
+      <c r="K178" s="57" t="inlineStr"/>
+      <c r="L178" s="2" t="inlineStr">
+        <is>
+          <t>pose le terrain des reports</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="13" t="inlineStr">
+        <is>
+          <t>Jugement</t>
+        </is>
+      </c>
+      <c r="B179" s="13" t="inlineStr">
+        <is>
+          <t>Hammer of Light</t>
+        </is>
+      </c>
+      <c r="C179" s="13" t="inlineStr">
+        <is>
+          <t>marteau-de-lumiere</t>
+        </is>
+      </c>
+      <c r="D179" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E179" s="13" t="inlineStr">
+        <is>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="F179" s="13" t="inlineStr">
+        <is>
+          <t>Épique</t>
+        </is>
+      </c>
+      <c r="G179" s="13" t="inlineStr">
+        <is>
+          <t>Mêlée</t>
+        </is>
+      </c>
+      <c r="H179" s="13" t="inlineStr"/>
+      <c r="I179" s="14" t="inlineStr">
+        <is>
+          <t>Gauntlets ×2, Sabatons ×1</t>
+        </is>
+      </c>
+      <c r="J179" s="14" t="inlineStr">
+        <is>
+          <t>Deal 17 damage.</t>
+        </is>
+      </c>
+      <c r="K179" s="57" t="inlineStr"/>
+      <c r="L179" s="2" t="inlineStr">
+        <is>
+          <t>17 dégâts / 2 chaleur</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="13" t="inlineStr">
+        <is>
+          <t>Jugement</t>
+        </is>
+      </c>
+      <c r="B180" s="13" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+      <c r="C180" s="13" t="inlineStr">
+        <is>
+          <t>verdict</t>
+        </is>
+      </c>
+      <c r="D180" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E180" s="13" t="inlineStr">
+        <is>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="F180" s="13" t="inlineStr">
+        <is>
+          <t>Épique</t>
+        </is>
+      </c>
+      <c r="G180" s="13" t="inlineStr">
+        <is>
+          <t>Mêlée</t>
+        </is>
+      </c>
+      <c r="H180" s="13" t="inlineStr"/>
+      <c r="I180" s="14" t="inlineStr">
+        <is>
+          <t>Plate ×1</t>
+        </is>
+      </c>
+      <c r="J180" s="14" t="inlineStr">
+        <is>
+          <t>Deal 10 damage. Apply 5 Judgement.</t>
+        </is>
+      </c>
+      <c r="K180" s="57" t="inlineStr"/>
+      <c r="L180" s="2" t="inlineStr">
+        <is>
+          <t>le gros investissement</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="13" t="inlineStr">
+        <is>
+          <t>Jugement</t>
+        </is>
+      </c>
+      <c r="B181" s="13" t="inlineStr">
+        <is>
+          <t>Sentence</t>
+        </is>
+      </c>
+      <c r="C181" s="13" t="inlineStr">
+        <is>
+          <t>sentence</t>
+        </is>
+      </c>
+      <c r="D181" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E181" s="13" t="inlineStr">
+        <is>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="F181" s="13" t="inlineStr">
+        <is>
+          <t>Épique</t>
+        </is>
+      </c>
+      <c r="G181" s="13" t="inlineStr">
+        <is>
+          <t>Mêlée</t>
+        </is>
+      </c>
+      <c r="H181" s="13" t="inlineStr"/>
+      <c r="I181" s="14" t="inlineStr">
+        <is>
+          <t>Gauntlets ×2</t>
+        </is>
+      </c>
+      <c r="J181" s="14" t="inlineStr">
+        <is>
+          <t>Deal 3 damage per Judgement on the target.</t>
+        </is>
+      </c>
+      <c r="K181" s="57" t="inlineStr"/>
+      <c r="L181" s="2" t="inlineStr">
+        <is>
+          <t>encaisse le verdict</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="13" t="inlineStr">
+        <is>
+          <t>Jugement</t>
+        </is>
+      </c>
+      <c r="B182" s="13" t="inlineStr">
+        <is>
+          <t>Gilded Guard</t>
+        </is>
+      </c>
+      <c r="C182" s="13" t="inlineStr">
+        <is>
+          <t>garde-doree</t>
+        </is>
+      </c>
+      <c r="D182" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E182" s="13" t="inlineStr">
+        <is>
+          <t>Défense</t>
+        </is>
+      </c>
+      <c r="F182" s="13" t="inlineStr">
+        <is>
+          <t>Épique</t>
+        </is>
+      </c>
+      <c r="G182" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H182" s="13" t="inlineStr"/>
+      <c r="I182" s="14" t="inlineStr">
+        <is>
+          <t>Plate ×2, Sabatons ×1</t>
+        </is>
+      </c>
+      <c r="J182" s="14" t="inlineStr">
+        <is>
+          <t>Gain 14 Stone.</t>
+        </is>
+      </c>
+      <c r="K182" s="57" t="inlineStr"/>
+      <c r="L182" s="2" t="inlineStr">
+        <is>
+          <t>14 armure / 1 chaleur</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="13" t="inlineStr">
+        <is>
+          <t>Jugement</t>
+        </is>
+      </c>
+      <c r="B183" s="13" t="inlineStr">
+        <is>
+          <t>Hand of Dunir</t>
+        </is>
+      </c>
+      <c r="C183" s="13" t="inlineStr">
+        <is>
+          <t>main-de-dunir</t>
+        </is>
+      </c>
+      <c r="D183" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E183" s="13" t="inlineStr">
+        <is>
+          <t>Défense</t>
+        </is>
+      </c>
+      <c r="F183" s="13" t="inlineStr">
+        <is>
+          <t>Épique</t>
+        </is>
+      </c>
+      <c r="G183" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H183" s="13" t="inlineStr"/>
+      <c r="I183" s="14" t="inlineStr">
+        <is>
+          <t>Plate ×2</t>
+        </is>
+      </c>
+      <c r="J183" s="14" t="inlineStr">
+        <is>
+          <t>Gain 12 Stone. Heal 6 HP.</t>
+        </is>
+      </c>
+      <c r="K183" s="57" t="inlineStr"/>
+      <c r="L183" s="2" t="inlineStr">
+        <is>
+          <t>12 armure + 6 PV / 2 chaleur</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="13" t="inlineStr">
+        <is>
+          <t>Jugement</t>
+        </is>
+      </c>
+      <c r="B184" s="13" t="inlineStr">
+        <is>
+          <t>Golden Dawn</t>
+        </is>
+      </c>
+      <c r="C184" s="13" t="inlineStr">
+        <is>
+          <t>aube-doree</t>
+        </is>
+      </c>
+      <c r="D184" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E184" s="13" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="F184" s="13" t="inlineStr">
+        <is>
+          <t>Épique</t>
+        </is>
+      </c>
+      <c r="G184" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H184" s="13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I184" s="14" t="inlineStr">
+        <is>
+          <t>Sabatons ×2</t>
+        </is>
+      </c>
+      <c r="J184" s="14" t="inlineStr">
+        <is>
+          <t>Gain 3 Haste. Apply 1 Judgement to ALL enemies.</t>
+        </is>
+      </c>
+      <c r="K184" s="57" t="inlineStr"/>
+      <c r="L184" s="2" t="inlineStr">
+        <is>
+          <t>tempo + jugement de masse</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="13" t="inlineStr">
+        <is>
+          <t>Jugement</t>
+        </is>
+      </c>
+      <c r="B185" s="13" t="inlineStr">
+        <is>
+          <t>Skyfall Hammer</t>
+        </is>
+      </c>
+      <c r="C185" s="13" t="inlineStr">
+        <is>
+          <t>martel-du-ciel</t>
+        </is>
+      </c>
+      <c r="D185" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E185" s="13" t="inlineStr">
+        <is>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="F185" s="13" t="inlineStr">
+        <is>
+          <t>Épique</t>
+        </is>
+      </c>
+      <c r="G185" s="13" t="inlineStr">
+        <is>
+          <t>Mêlée</t>
+        </is>
+      </c>
+      <c r="H185" s="13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I185" s="14" t="inlineStr">
+        <is>
+          <t>Gauntlets ×1</t>
+        </is>
+      </c>
+      <c r="J185" s="14" t="inlineStr">
+        <is>
+          <t>Deal 12 damage. Both neighbours take 12.</t>
+        </is>
+      </c>
+      <c r="K185" s="57" t="inlineStr"/>
+      <c r="L185" s="2" t="inlineStr">
+        <is>
+          <t>enchaîne les reports</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
@@ -15221,7 +15710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G142"/>
+  <dimension ref="A1:G144"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" style="146" min="1" max="1"/>
@@ -19818,7 +20307,11 @@
       <c r="F140" s="55" t="n"/>
     </row>
     <row r="141" ht="15" customHeight="1" s="146">
-      <c r="A141" s="55" t="n"/>
+      <c r="A141" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸ SET BÉNI PAR DUNÏR (épique — 1er jet, à réviser)</t>
+        </is>
+      </c>
       <c r="B141" s="55" t="n"/>
       <c r="C141" s="55" t="n"/>
       <c r="D141" s="55" t="n"/>
@@ -19826,12 +20319,115 @@
       <c r="F141" s="55" t="n"/>
     </row>
     <row r="142">
-      <c r="A142" s="55" t="n"/>
-      <c r="B142" s="55" t="n"/>
-      <c r="C142" s="55" t="n"/>
-      <c r="D142" s="55" t="n"/>
-      <c r="E142" s="55" t="n"/>
-      <c r="F142" s="55" t="n"/>
+      <c r="A142" s="49" t="inlineStr">
+        <is>
+          <t>Armures</t>
+        </is>
+      </c>
+      <c r="B142" s="49" t="inlineStr">
+        <is>
+          <t>Dunir's Blessed Plate</t>
+        </is>
+      </c>
+      <c r="C142" s="49" t="inlineStr">
+        <is>
+          <t>plastron-dunir</t>
+        </is>
+      </c>
+      <c r="D142" s="49" t="inlineStr">
+        <is>
+          <t>Épique</t>
+        </is>
+      </c>
+      <c r="E142" s="50" t="inlineStr">
+        <is>
+          <t>Gilded Guard×2, Hand of Dunir×2, Seal of Dunir×1, Verdict×1, Judgement×1</t>
+        </is>
+      </c>
+      <c r="F142" s="50" t="inlineStr">
+        <is>
+          <t>Armure début: 40  ·  +6 Pierre à chaque tour  ·  Craft: pierre solaire + or  ·  Set: Dunir's Blessing</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>≈ 16 dégâts  ·  ≈ 52 armure  ·  12 PV  (7 cartes/7 visées)</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="49" t="inlineStr">
+        <is>
+          <t>Gants</t>
+        </is>
+      </c>
+      <c r="B143" s="49" t="inlineStr">
+        <is>
+          <t>Dunir's Blessed Gauntlets</t>
+        </is>
+      </c>
+      <c r="C143" s="49" t="inlineStr">
+        <is>
+          <t>gantelets-dunir</t>
+        </is>
+      </c>
+      <c r="D143" s="49" t="inlineStr">
+        <is>
+          <t>Épique</t>
+        </is>
+      </c>
+      <c r="E143" s="50" t="inlineStr">
+        <is>
+          <t>Judgement×2, Hammer of Light×2, Sentence×2, Skyfall Hammer×1</t>
+        </is>
+      </c>
+      <c r="F143" s="50" t="inlineStr">
+        <is>
+          <t>Craft: pierre solaire + or + mithril  ·  Set: Dunir's Blessing</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>≈ 82 dégâts  (7 cartes/7 visées)</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="49" t="inlineStr">
+        <is>
+          <t>Bottes</t>
+        </is>
+      </c>
+      <c r="B144" s="49" t="inlineStr">
+        <is>
+          <t>Dunir's Blessed Sabatons</t>
+        </is>
+      </c>
+      <c r="C144" s="49" t="inlineStr">
+        <is>
+          <t>solerets-dunir</t>
+        </is>
+      </c>
+      <c r="D144" s="49" t="inlineStr">
+        <is>
+          <t>Épique</t>
+        </is>
+      </c>
+      <c r="E144" s="50" t="inlineStr">
+        <is>
+          <t>Golden Dawn×2, Judgement×2, Hammer of Light×1, Gilded Guard×1, Boost×1</t>
+        </is>
+      </c>
+      <c r="F144" s="50" t="inlineStr">
+        <is>
+          <t>+160 Agilité  ·  +30% déplacement  ·  Craft: pierre solaire + or + mithril  ·  Set: Dunir's Blessing</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>≈ 29 dégâts  ·  ≈ 14 armure  (7 cartes/7 visées · 3 buff)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -19845,7 +20441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" style="146" min="1" max="1"/>
@@ -20019,6 +20615,28 @@
       <c r="D10" s="44" t="inlineStr">
         <is>
           <t>+5 Strength for the whole fight. Each enemy slain grants +5 more Strength, until the end of the fight.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="44" t="inlineStr">
+        <is>
+          <t>Dunir's Blessing</t>
+        </is>
+      </c>
+      <c r="B11" s="44" t="inlineStr">
+        <is>
+          <t>Dunir's Blessed Plate  +  Dunir's Blessed Gauntlets  +  Dunir's Blessed Sabatons</t>
+        </is>
+      </c>
+      <c r="C11" s="44" t="inlineStr">
+        <is>
+          <t>Début de combat + à chaque ennemi jugé qui meurt</t>
+        </is>
+      </c>
+      <c r="D11" s="44" t="inlineStr">
+        <is>
+          <t>At the start of combat, every enemy takes 2 Judgement. When a judged enemy dies, its whole Judgement passes to every enemy still standing.</t>
         </is>
       </c>
     </row>
@@ -20033,7 +20651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D87"/>
+  <dimension ref="A1:D88"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="146" min="1" max="1"/>
@@ -21725,6 +22343,28 @@
       <c r="D87" s="44" t="inlineStr">
         <is>
           <t>force, soin</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="44" t="inlineStr">
+        <is>
+          <t>jugement</t>
+        </is>
+      </c>
+      <c r="B88" s="44" t="inlineStr">
+        <is>
+          <t>Jugement (⚖)</t>
+        </is>
+      </c>
+      <c r="C88" s="44" t="inlineStr">
+        <is>
+          <t>Posé sur un ennemi. Ne fait AUCUN dégât et ne s'écoule JAMAIS : il augmente de N chaque blessure que cet ennemi subit (toute source). Set béni par Dunïr : à la mort d'un ennemi jugé, tout son Jugement passe aux survivants.</t>
+        </is>
+      </c>
+      <c r="D88" s="44" t="inlineStr">
+        <is>
+          <t>valeur: N</t>
         </is>
       </c>
     </row>

--- a/docs/BRUTAL-items-et-cartes.xlsx
+++ b/docs/BRUTAL-items-et-cartes.xlsx
@@ -20464,6 +20464,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="47" t="inlineStr">
         <is>
@@ -20631,12 +20632,12 @@
       </c>
       <c r="C11" s="44" t="inlineStr">
         <is>
-          <t>Début de combat + à chaque ennemi jugé qui meurt</t>
+          <t>Début de combat + à chaque ennemi jugé qui meurt (dispersion aléatoire)</t>
         </is>
       </c>
       <c r="D11" s="44" t="inlineStr">
         <is>
-          <t>At the start of combat, every enemy takes 2 Judgement. When a judged enemy dies, its whole Judgement passes to every enemy still standing.</t>
+          <t>At the start of combat, every enemy takes 2 Judgement. When a judged enemy dies, its Judgement scatters at random among the enemies still standing.</t>
         </is>
       </c>
     </row>
@@ -21908,6 +21909,7 @@
         </is>
       </c>
     </row>
+    <row r="65"/>
     <row r="66" ht="24" customHeight="1" s="146">
       <c r="A66" s="46" t="inlineStr">
         <is>
@@ -22248,6 +22250,7 @@
         </is>
       </c>
     </row>
+    <row r="82"/>
     <row r="83" ht="24" customHeight="1" s="146">
       <c r="A83" s="46" t="inlineStr">
         <is>
@@ -22359,7 +22362,7 @@
       </c>
       <c r="C88" s="44" t="inlineStr">
         <is>
-          <t>Posé sur un ennemi. Ne fait AUCUN dégât et ne s'écoule JAMAIS : il augmente de N chaque blessure que cet ennemi subit (toute source). Set béni par Dunïr : à la mort d'un ennemi jugé, tout son Jugement passe aux survivants.</t>
+          <t>Posé sur un ennemi. Ne fait AUCUN dégât et ne s'écoule JAMAIS : il augmente de N chaque blessure que cet ennemi subit (toute source). Set béni par Dunïr : à la mort d'un ennemi jugé, son Jugement se DISPERSE au hasard entre les survivants (total conservé).</t>
         </is>
       </c>
       <c r="D88" s="44" t="inlineStr">

--- a/docs/BRUTAL-items-et-cartes.xlsx
+++ b/docs/BRUTAL-items-et-cartes.xlsx
@@ -1249,7 +1249,7 @@
     <author>BRUTAL</author>
   </authors>
   <commentList>
-    <comment ref="G1" authorId="0" shapeId="0">
+    <comment ref="P1" authorId="0" shapeId="0">
       <text>
         <t>Total que les cartes de l'item devraient fournir (outils/resumer_cartes.py) :
 somme des cibles de chaque carte × sa quantité — dégâts pour une arme, armure
@@ -1597,7 +1597,7 @@
     <row r="7" ht="30" customHeight="1" s="140">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>1) Va dans l'onglet « Items », sous le bon type.  2) Remplis une ligne vide : Nom, Rareté, puis pour chaque carte son Nom et sa Quantité (colonnes Carte 1/Qté, Carte 2/Qté…).</t>
+          <t>1) Va dans l'onglet « Items », sous le bon type.  2) Remplis une ligne vide : Nom, ID, Rareté, puis UNE CARTE PAR CELLULE dans les colonnes « Carte 1 » à « Carte 10 » — une carte en double s'écrit deux fois, dans deux cellules. Fini les listes à virgules illisibles.</t>
         </is>
       </c>
     </row>
@@ -15716,15 +15716,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G150"/>
+  <dimension ref="A1:P150"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" style="140" min="1" max="1"/>
     <col width="24" customWidth="1" style="140" min="2" max="3"/>
     <col width="11" customWidth="1" style="140" min="4" max="4"/>
-    <col width="71.5703125" customWidth="1" style="140" min="5" max="5"/>
-    <col width="52" customWidth="1" style="140" min="6" max="6"/>
-    <col width="30" customWidth="1" style="140" min="7" max="7"/>
+    <col width="20" customWidth="1" style="140" min="5" max="5"/>
+    <col width="20" customWidth="1" style="140" min="6" max="6"/>
+    <col width="20" customWidth="1" style="140" min="7" max="7"/>
+    <col width="20" customWidth="1" style="140" min="8" max="8"/>
+    <col width="20" customWidth="1" style="140" min="9" max="9"/>
+    <col width="20" customWidth="1" style="140" min="10" max="10"/>
+    <col width="20" customWidth="1" style="140" min="11" max="11"/>
+    <col width="20" customWidth="1" style="140" min="12" max="12"/>
+    <col width="20" customWidth="1" style="140" min="13" max="13"/>
+    <col width="20" customWidth="1" style="140" min="14" max="14"/>
+    <col width="52" customWidth="1" style="140" min="15" max="15"/>
+    <col width="46" customWidth="1" style="140" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="21.95" customHeight="1" s="140">
@@ -15750,15 +15759,60 @@
       </c>
       <c r="E1" s="10" t="inlineStr">
         <is>
-          <t>Cartes (×qté)</t>
+          <t>Carte 1</t>
         </is>
       </c>
       <c r="F1" s="10" t="inlineStr">
         <is>
+          <t>Carte 2</t>
+        </is>
+      </c>
+      <c r="G1" s="10" t="inlineStr">
+        <is>
+          <t>Carte 3</t>
+        </is>
+      </c>
+      <c r="H1" s="10" t="inlineStr">
+        <is>
+          <t>Carte 4</t>
+        </is>
+      </c>
+      <c r="I1" s="10" t="inlineStr">
+        <is>
+          <t>Carte 5</t>
+        </is>
+      </c>
+      <c r="J1" s="10" t="inlineStr">
+        <is>
+          <t>Carte 6</t>
+        </is>
+      </c>
+      <c r="K1" s="10" t="inlineStr">
+        <is>
+          <t>Carte 7</t>
+        </is>
+      </c>
+      <c r="L1" s="10" t="inlineStr">
+        <is>
+          <t>Carte 8</t>
+        </is>
+      </c>
+      <c r="M1" s="10" t="inlineStr">
+        <is>
+          <t>Carte 9</t>
+        </is>
+      </c>
+      <c r="N1" s="10" t="inlineStr">
+        <is>
+          <t>Carte 10</t>
+        </is>
+      </c>
+      <c r="O1" s="10" t="inlineStr">
+        <is>
           <t>Effet hors-carte / spécial</t>
         </is>
       </c>
-      <c r="G1" s="94" t="inlineStr">
+      <c r="P1" s="94" t="inlineStr">
         <is>
           <t>Total visé (barème)</t>
         </is>
@@ -15774,7 +15828,7 @@
       <c r="C2" s="48" t="n"/>
       <c r="D2" s="48" t="n"/>
       <c r="E2" s="48" t="n"/>
-      <c r="F2" s="48" t="n"/>
+      <c r="O2" s="48" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1" s="140">
       <c r="A3" s="142" t="inlineStr">
@@ -15799,11 +15853,26 @@
       </c>
       <c r="E3" s="143" t="inlineStr">
         <is>
-          <t>Gash×1, Heavy Blow×1, Strike×2</t>
-        </is>
-      </c>
-      <c r="F3" s="143" t="n"/>
-      <c r="G3" s="2" t="inlineStr">
+          <t>Gash</t>
+        </is>
+      </c>
+      <c r="F3" s="143" t="inlineStr">
+        <is>
+          <t>Heavy Blow</t>
+        </is>
+      </c>
+      <c r="G3" s="143" t="inlineStr">
+        <is>
+          <t>Strike</t>
+        </is>
+      </c>
+      <c r="H3" s="143" t="inlineStr">
+        <is>
+          <t>Strike</t>
+        </is>
+      </c>
+      <c r="O3" s="143" t="n"/>
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>≈ 25 dégâts  (4 cartes/5 visées)</t>
         </is>
@@ -15832,11 +15901,26 @@
       </c>
       <c r="E4" s="143" t="inlineStr">
         <is>
-          <t>Double Strike×2, Strike×2</t>
-        </is>
-      </c>
-      <c r="F4" s="143" t="n"/>
-      <c r="G4" s="2" t="inlineStr">
+          <t>Double Strike</t>
+        </is>
+      </c>
+      <c r="F4" s="143" t="inlineStr">
+        <is>
+          <t>Double Strike</t>
+        </is>
+      </c>
+      <c r="G4" s="143" t="inlineStr">
+        <is>
+          <t>Strike</t>
+        </is>
+      </c>
+      <c r="H4" s="143" t="inlineStr">
+        <is>
+          <t>Strike</t>
+        </is>
+      </c>
+      <c r="O4" s="143" t="n"/>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>≈ 20 dégâts  (4 cartes/5 visées)</t>
         </is>
@@ -15865,11 +15949,26 @@
       </c>
       <c r="E5" s="143" t="inlineStr">
         <is>
-          <t>Ice Shard×2, Strike×2</t>
-        </is>
-      </c>
-      <c r="F5" s="143" t="n"/>
-      <c r="G5" s="2" t="inlineStr">
+          <t>Ice Shard</t>
+        </is>
+      </c>
+      <c r="F5" s="143" t="inlineStr">
+        <is>
+          <t>Ice Shard</t>
+        </is>
+      </c>
+      <c r="G5" s="143" t="inlineStr">
+        <is>
+          <t>Strike</t>
+        </is>
+      </c>
+      <c r="H5" s="143" t="inlineStr">
+        <is>
+          <t>Strike</t>
+        </is>
+      </c>
+      <c r="O5" s="143" t="n"/>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>≈ 20 dégâts  (4 cartes/5 visées)</t>
         </is>
@@ -15898,11 +15997,31 @@
       </c>
       <c r="E6" s="143" t="inlineStr">
         <is>
-          <t>Heavy Blow×2, Guard×2, Smash×1</t>
-        </is>
-      </c>
-      <c r="F6" s="143" t="n"/>
-      <c r="G6" s="2" t="inlineStr">
+          <t>Heavy Blow</t>
+        </is>
+      </c>
+      <c r="F6" s="143" t="inlineStr">
+        <is>
+          <t>Heavy Blow</t>
+        </is>
+      </c>
+      <c r="G6" s="143" t="inlineStr">
+        <is>
+          <t>Guard</t>
+        </is>
+      </c>
+      <c r="H6" s="143" t="inlineStr">
+        <is>
+          <t>Guard</t>
+        </is>
+      </c>
+      <c r="I6" s="143" t="inlineStr">
+        <is>
+          <t>Smash</t>
+        </is>
+      </c>
+      <c r="O6" s="143" t="n"/>
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>≈ 35 dégâts  ·  ≈ 8 armure  (5 cartes/5 visées)</t>
         </is>
@@ -15931,11 +16050,31 @@
       </c>
       <c r="E7" s="143" t="inlineStr">
         <is>
-          <t>Pickaxe Jab×2, Strike×3</t>
-        </is>
-      </c>
-      <c r="F7" s="143" t="n"/>
-      <c r="G7" s="2" t="inlineStr">
+          <t>Pickaxe Jab</t>
+        </is>
+      </c>
+      <c r="F7" s="143" t="inlineStr">
+        <is>
+          <t>Pickaxe Jab</t>
+        </is>
+      </c>
+      <c r="G7" s="143" t="inlineStr">
+        <is>
+          <t>Strike</t>
+        </is>
+      </c>
+      <c r="H7" s="143" t="inlineStr">
+        <is>
+          <t>Strike</t>
+        </is>
+      </c>
+      <c r="I7" s="143" t="inlineStr">
+        <is>
+          <t>Strike</t>
+        </is>
+      </c>
+      <c r="O7" s="143" t="n"/>
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>≈ 25 dégâts  (5 cartes/5 visées)</t>
         </is>
@@ -15964,11 +16103,26 @@
       </c>
       <c r="E8" s="143" t="inlineStr">
         <is>
-          <t>Pierce×2, Gash×1, Guard×1</t>
-        </is>
-      </c>
-      <c r="F8" s="143" t="n"/>
-      <c r="G8" s="2" t="inlineStr">
+          <t>Pierce</t>
+        </is>
+      </c>
+      <c r="F8" s="143" t="inlineStr">
+        <is>
+          <t>Pierce</t>
+        </is>
+      </c>
+      <c r="G8" s="143" t="inlineStr">
+        <is>
+          <t>Gash</t>
+        </is>
+      </c>
+      <c r="H8" s="143" t="inlineStr">
+        <is>
+          <t>Guard</t>
+        </is>
+      </c>
+      <c r="O8" s="143" t="n"/>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>≈ 25 dégâts  ·  ≈ 4 armure  (4 cartes/5 visées)</t>
         </is>
@@ -15997,11 +16151,31 @@
       </c>
       <c r="E9" s="143" t="inlineStr">
         <is>
-          <t>Strike×2, Guard×2, Nimble Hands×1</t>
-        </is>
-      </c>
-      <c r="F9" s="143" t="n"/>
-      <c r="G9" s="2" t="inlineStr">
+          <t>Strike</t>
+        </is>
+      </c>
+      <c r="F9" s="143" t="inlineStr">
+        <is>
+          <t>Strike</t>
+        </is>
+      </c>
+      <c r="G9" s="143" t="inlineStr">
+        <is>
+          <t>Guard</t>
+        </is>
+      </c>
+      <c r="H9" s="143" t="inlineStr">
+        <is>
+          <t>Guard</t>
+        </is>
+      </c>
+      <c r="I9" s="143" t="inlineStr">
+        <is>
+          <t>Nimble Hands</t>
+        </is>
+      </c>
+      <c r="O9" s="143" t="n"/>
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>≈ 10 dégâts  ·  ≈ 8 armure  (5 cartes/5 visées · 1 buff)</t>
         </is>
@@ -16030,11 +16204,31 @@
       </c>
       <c r="E10" s="143" t="inlineStr">
         <is>
-          <t>Rusty Cleave×2, Strike×3</t>
-        </is>
-      </c>
-      <c r="F10" s="143" t="n"/>
-      <c r="G10" s="2" t="inlineStr">
+          <t>Rusty Cleave</t>
+        </is>
+      </c>
+      <c r="F10" s="143" t="inlineStr">
+        <is>
+          <t>Rusty Cleave</t>
+        </is>
+      </c>
+      <c r="G10" s="143" t="inlineStr">
+        <is>
+          <t>Strike</t>
+        </is>
+      </c>
+      <c r="H10" s="143" t="inlineStr">
+        <is>
+          <t>Strike</t>
+        </is>
+      </c>
+      <c r="I10" s="143" t="inlineStr">
+        <is>
+          <t>Strike</t>
+        </is>
+      </c>
+      <c r="O10" s="143" t="n"/>
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>≈ 35 dégâts  (5 cartes/5 visées)</t>
         </is>
@@ -16063,11 +16257,26 @@
       </c>
       <c r="E11" s="143" t="inlineStr">
         <is>
-          <t>Poison Dart×2, Strike×2</t>
-        </is>
-      </c>
-      <c r="F11" s="143" t="n"/>
-      <c r="G11" s="2" t="inlineStr">
+          <t>Poison Dart</t>
+        </is>
+      </c>
+      <c r="F11" s="143" t="inlineStr">
+        <is>
+          <t>Poison Dart</t>
+        </is>
+      </c>
+      <c r="G11" s="143" t="inlineStr">
+        <is>
+          <t>Strike</t>
+        </is>
+      </c>
+      <c r="H11" s="143" t="inlineStr">
+        <is>
+          <t>Strike</t>
+        </is>
+      </c>
+      <c r="O11" s="143" t="n"/>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>≈ 20 dégâts  (4 cartes/5 visées)</t>
         </is>
@@ -16096,11 +16305,26 @@
       </c>
       <c r="E12" s="143" t="inlineStr">
         <is>
-          <t>Poison Dart×3, Slash×1</t>
-        </is>
-      </c>
-      <c r="F12" s="143" t="n"/>
-      <c r="G12" s="2" t="inlineStr">
+          <t>Poison Dart</t>
+        </is>
+      </c>
+      <c r="F12" s="143" t="inlineStr">
+        <is>
+          <t>Poison Dart</t>
+        </is>
+      </c>
+      <c r="G12" s="143" t="inlineStr">
+        <is>
+          <t>Poison Dart</t>
+        </is>
+      </c>
+      <c r="H12" s="143" t="inlineStr">
+        <is>
+          <t>Slash</t>
+        </is>
+      </c>
+      <c r="O12" s="143" t="n"/>
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>≈ 20 dégâts  (4 cartes/5 visées)</t>
         </is>
@@ -16129,11 +16353,26 @@
       </c>
       <c r="E13" s="143" t="inlineStr">
         <is>
-          <t>Gash×2, Strike×2</t>
-        </is>
-      </c>
-      <c r="F13" s="143" t="n"/>
-      <c r="G13" s="2" t="inlineStr">
+          <t>Gash</t>
+        </is>
+      </c>
+      <c r="F13" s="143" t="inlineStr">
+        <is>
+          <t>Gash</t>
+        </is>
+      </c>
+      <c r="G13" s="143" t="inlineStr">
+        <is>
+          <t>Strike</t>
+        </is>
+      </c>
+      <c r="H13" s="143" t="inlineStr">
+        <is>
+          <t>Strike</t>
+        </is>
+      </c>
+      <c r="O13" s="143" t="n"/>
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>≈ 20 dégâts  (4 cartes/5 visées)</t>
         </is>
@@ -16162,11 +16401,31 @@
       </c>
       <c r="E14" s="143" t="inlineStr">
         <is>
-          <t>Slash×2, Strike×3</t>
-        </is>
-      </c>
-      <c r="F14" s="143" t="n"/>
-      <c r="G14" s="2" t="inlineStr">
+          <t>Slash</t>
+        </is>
+      </c>
+      <c r="F14" s="143" t="inlineStr">
+        <is>
+          <t>Slash</t>
+        </is>
+      </c>
+      <c r="G14" s="143" t="inlineStr">
+        <is>
+          <t>Strike</t>
+        </is>
+      </c>
+      <c r="H14" s="143" t="inlineStr">
+        <is>
+          <t>Strike</t>
+        </is>
+      </c>
+      <c r="I14" s="143" t="inlineStr">
+        <is>
+          <t>Strike</t>
+        </is>
+      </c>
+      <c r="O14" s="143" t="n"/>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>≈ 25 dégâts  (5 cartes/5 visées)</t>
         </is>
@@ -16195,11 +16454,31 @@
       </c>
       <c r="E15" s="143" t="inlineStr">
         <is>
-          <t>Slash×1, Strike×2, Pierce×2</t>
-        </is>
-      </c>
-      <c r="F15" s="143" t="n"/>
-      <c r="G15" s="2" t="inlineStr">
+          <t>Slash</t>
+        </is>
+      </c>
+      <c r="F15" s="143" t="inlineStr">
+        <is>
+          <t>Strike</t>
+        </is>
+      </c>
+      <c r="G15" s="143" t="inlineStr">
+        <is>
+          <t>Strike</t>
+        </is>
+      </c>
+      <c r="H15" s="143" t="inlineStr">
+        <is>
+          <t>Pierce</t>
+        </is>
+      </c>
+      <c r="I15" s="143" t="inlineStr">
+        <is>
+          <t>Pierce</t>
+        </is>
+      </c>
+      <c r="O15" s="143" t="n"/>
+      <c r="P15" s="2" t="inlineStr">
         <is>
           <t>≈ 35 dégâts  (5 cartes/5 visées)</t>
         </is>
@@ -16228,11 +16507,26 @@
       </c>
       <c r="E16" s="143" t="inlineStr">
         <is>
-          <t>Ember×2, Strike×2</t>
-        </is>
-      </c>
-      <c r="F16" s="143" t="n"/>
-      <c r="G16" s="2" t="inlineStr">
+          <t>Ember</t>
+        </is>
+      </c>
+      <c r="F16" s="143" t="inlineStr">
+        <is>
+          <t>Ember</t>
+        </is>
+      </c>
+      <c r="G16" s="143" t="inlineStr">
+        <is>
+          <t>Strike</t>
+        </is>
+      </c>
+      <c r="H16" s="143" t="inlineStr">
+        <is>
+          <t>Strike</t>
+        </is>
+      </c>
+      <c r="O16" s="143" t="n"/>
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>≈ 20 dégâts  (4 cartes/5 visées)</t>
         </is>
@@ -16261,11 +16555,26 @@
       </c>
       <c r="E17" s="143" t="inlineStr">
         <is>
-          <t>Flex×1, Strike×3</t>
-        </is>
-      </c>
-      <c r="F17" s="143" t="n"/>
-      <c r="G17" s="2" t="inlineStr">
+          <t>Flex</t>
+        </is>
+      </c>
+      <c r="F17" s="143" t="inlineStr">
+        <is>
+          <t>Strike</t>
+        </is>
+      </c>
+      <c r="G17" s="143" t="inlineStr">
+        <is>
+          <t>Strike</t>
+        </is>
+      </c>
+      <c r="H17" s="143" t="inlineStr">
+        <is>
+          <t>Strike</t>
+        </is>
+      </c>
+      <c r="O17" s="143" t="n"/>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>≈ 15 dégâts  (4 cartes/5 visées · 1 buff)</t>
         </is>
@@ -16294,11 +16603,31 @@
       </c>
       <c r="E18" s="143" t="inlineStr">
         <is>
-          <t>Heavy Blow×1, Strike×3, Guard×1</t>
-        </is>
-      </c>
-      <c r="F18" s="143" t="n"/>
-      <c r="G18" s="2" t="inlineStr">
+          <t>Heavy Blow</t>
+        </is>
+      </c>
+      <c r="F18" s="143" t="inlineStr">
+        <is>
+          <t>Strike</t>
+        </is>
+      </c>
+      <c r="G18" s="143" t="inlineStr">
+        <is>
+          <t>Strike</t>
+        </is>
+      </c>
+      <c r="H18" s="143" t="inlineStr">
+        <is>
+          <t>Strike</t>
+        </is>
+      </c>
+      <c r="I18" s="143" t="inlineStr">
+        <is>
+          <t>Guard</t>
+        </is>
+      </c>
+      <c r="O18" s="143" t="n"/>
+      <c r="P18" s="2" t="inlineStr">
         <is>
           <t>≈ 25 dégâts  ·  ≈ 4 armure  (5 cartes/5 visées)</t>
         </is>
@@ -16325,13 +16654,33 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E19" s="146" t="inlineStr">
-        <is>
-          <t>Reckless Swing×2, Flex×1, Slash×1, Big Strike×1</t>
-        </is>
-      </c>
-      <c r="F19" s="146" t="n"/>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="E19" s="143" t="inlineStr">
+        <is>
+          <t>Reckless Swing</t>
+        </is>
+      </c>
+      <c r="F19" s="143" t="inlineStr">
+        <is>
+          <t>Reckless Swing</t>
+        </is>
+      </c>
+      <c r="G19" s="143" t="inlineStr">
+        <is>
+          <t>Flex</t>
+        </is>
+      </c>
+      <c r="H19" s="143" t="inlineStr">
+        <is>
+          <t>Slash</t>
+        </is>
+      </c>
+      <c r="I19" s="143" t="inlineStr">
+        <is>
+          <t>Big Strike</t>
+        </is>
+      </c>
+      <c r="O19" s="146" t="n"/>
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>≈ 29 dégâts  (5 cartes/6 visées · 1 buff)</t>
         </is>
@@ -16358,17 +16707,47 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E20" s="146" t="inlineStr">
-        <is>
-          <t>Wide Slash×2, Steel Flurry×2, Warrior's Momentum×1, Decisive Strike×1,Empowerx1,Get aheadx1</t>
-        </is>
-      </c>
-      <c r="F20" s="146" t="inlineStr">
+      <c r="E20" s="143" t="inlineStr">
+        <is>
+          <t>Wide Slash</t>
+        </is>
+      </c>
+      <c r="F20" s="143" t="inlineStr">
+        <is>
+          <t>Wide Slash</t>
+        </is>
+      </c>
+      <c r="G20" s="143" t="inlineStr">
+        <is>
+          <t>Steel Flurry</t>
+        </is>
+      </c>
+      <c r="H20" s="143" t="inlineStr">
+        <is>
+          <t>Steel Flurry</t>
+        </is>
+      </c>
+      <c r="I20" s="143" t="inlineStr">
+        <is>
+          <t>Warrior's Momentum</t>
+        </is>
+      </c>
+      <c r="J20" s="143" t="inlineStr">
+        <is>
+          <t>Decisive Strike</t>
+        </is>
+      </c>
+      <c r="K20" s="143" t="inlineStr">
+        <is>
+          <t>Get ahead</t>
+        </is>
+      </c>
+      <c r="O20" s="146" t="inlineStr">
         <is>
           <t>Deux mains</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>≈ 96 dégâts  (8 cartes/6 visées · 3 buff)</t>
         </is>
@@ -16395,13 +16774,28 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E21" s="146" t="inlineStr">
-        <is>
-          <t>Arcane Bolt×2, Spark×1, Big Strike×1</t>
-        </is>
-      </c>
-      <c r="F21" s="146" t="n"/>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="E21" s="143" t="inlineStr">
+        <is>
+          <t>Arcane Bolt</t>
+        </is>
+      </c>
+      <c r="F21" s="143" t="inlineStr">
+        <is>
+          <t>Arcane Bolt</t>
+        </is>
+      </c>
+      <c r="G21" s="143" t="inlineStr">
+        <is>
+          <t>Spark</t>
+        </is>
+      </c>
+      <c r="H21" s="143" t="inlineStr">
+        <is>
+          <t>Big Strike</t>
+        </is>
+      </c>
+      <c r="O21" s="146" t="n"/>
+      <c r="P21" s="2" t="inlineStr">
         <is>
           <t>≈ 24 dégâts  (4 cartes/6 visées · 1 buff)</t>
         </is>
@@ -16428,13 +16822,28 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E22" s="146" t="inlineStr">
-        <is>
-          <t>Flame Slash×1, Ember×2, Slash×1</t>
-        </is>
-      </c>
-      <c r="F22" s="146" t="n"/>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="E22" s="143" t="inlineStr">
+        <is>
+          <t>Flame Slash</t>
+        </is>
+      </c>
+      <c r="F22" s="143" t="inlineStr">
+        <is>
+          <t>Ember</t>
+        </is>
+      </c>
+      <c r="G22" s="143" t="inlineStr">
+        <is>
+          <t>Ember</t>
+        </is>
+      </c>
+      <c r="H22" s="143" t="inlineStr">
+        <is>
+          <t>Slash</t>
+        </is>
+      </c>
+      <c r="O22" s="146" t="n"/>
+      <c r="P22" s="2" t="inlineStr">
         <is>
           <t>≈ 23 dégâts  (4 cartes/6 visées)</t>
         </is>
@@ -16461,13 +16870,33 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E23" s="146" t="inlineStr">
-        <is>
-          <t>Execute×2, Heavy Blow×1, Slash×1, Big Strike×1</t>
-        </is>
-      </c>
-      <c r="F23" s="146" t="n"/>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="E23" s="143" t="inlineStr">
+        <is>
+          <t>Execute</t>
+        </is>
+      </c>
+      <c r="F23" s="143" t="inlineStr">
+        <is>
+          <t>Execute</t>
+        </is>
+      </c>
+      <c r="G23" s="143" t="inlineStr">
+        <is>
+          <t>Heavy Blow</t>
+        </is>
+      </c>
+      <c r="H23" s="143" t="inlineStr">
+        <is>
+          <t>Slash</t>
+        </is>
+      </c>
+      <c r="I23" s="143" t="inlineStr">
+        <is>
+          <t>Big Strike</t>
+        </is>
+      </c>
+      <c r="O23" s="146" t="n"/>
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>≈ 55 dégâts  (5 cartes/6 visées)</t>
         </is>
@@ -16494,13 +16923,38 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E24" s="146" t="inlineStr">
-        <is>
-          <t>Forge Smash×3, Strike×2, Splash Strike×1</t>
-        </is>
-      </c>
-      <c r="F24" s="146" t="n"/>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="E24" s="143" t="inlineStr">
+        <is>
+          <t>Forge Smash</t>
+        </is>
+      </c>
+      <c r="F24" s="143" t="inlineStr">
+        <is>
+          <t>Forge Smash</t>
+        </is>
+      </c>
+      <c r="G24" s="143" t="inlineStr">
+        <is>
+          <t>Forge Smash</t>
+        </is>
+      </c>
+      <c r="H24" s="143" t="inlineStr">
+        <is>
+          <t>Strike</t>
+        </is>
+      </c>
+      <c r="I24" s="143" t="inlineStr">
+        <is>
+          <t>Strike</t>
+        </is>
+      </c>
+      <c r="J24" s="143" t="inlineStr">
+        <is>
+          <t>Splash Strike</t>
+        </is>
+      </c>
+      <c r="O24" s="146" t="n"/>
+      <c r="P24" s="2" t="inlineStr">
         <is>
           <t>≈ 82 dégâts  (6 cartes/6 visées)</t>
         </is>
@@ -16527,13 +16981,28 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E25" s="146" t="inlineStr">
-        <is>
-          <t>Shatter×1, Ice Shard×2, Slash×1</t>
-        </is>
-      </c>
-      <c r="F25" s="146" t="n"/>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="E25" s="143" t="inlineStr">
+        <is>
+          <t>Shatter</t>
+        </is>
+      </c>
+      <c r="F25" s="143" t="inlineStr">
+        <is>
+          <t>Ice Shard</t>
+        </is>
+      </c>
+      <c r="G25" s="143" t="inlineStr">
+        <is>
+          <t>Ice Shard</t>
+        </is>
+      </c>
+      <c r="H25" s="143" t="inlineStr">
+        <is>
+          <t>Slash</t>
+        </is>
+      </c>
+      <c r="O25" s="146" t="n"/>
+      <c r="P25" s="2" t="inlineStr">
         <is>
           <t>≈ 31 dégâts  (4 cartes/6 visées)</t>
         </is>
@@ -16560,17 +17029,52 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E26" s="146" t="inlineStr">
-        <is>
-          <t>Pike Thrust×3, Wide Sweep×2, Hooking Strike×2, Bracing Stance×1, Opening woundsx1</t>
-        </is>
-      </c>
-      <c r="F26" s="146" t="inlineStr">
+      <c r="E26" s="143" t="inlineStr">
+        <is>
+          <t>Pike Thrust</t>
+        </is>
+      </c>
+      <c r="F26" s="143" t="inlineStr">
+        <is>
+          <t>Pike Thrust</t>
+        </is>
+      </c>
+      <c r="G26" s="143" t="inlineStr">
+        <is>
+          <t>Opening Wounds</t>
+        </is>
+      </c>
+      <c r="H26" s="143" t="inlineStr">
+        <is>
+          <t>Wide Sweep</t>
+        </is>
+      </c>
+      <c r="I26" s="143" t="inlineStr">
+        <is>
+          <t>Wide Sweep</t>
+        </is>
+      </c>
+      <c r="J26" s="143" t="inlineStr">
+        <is>
+          <t>Hooking Strike</t>
+        </is>
+      </c>
+      <c r="K26" s="143" t="inlineStr">
+        <is>
+          <t>Hooking Strike</t>
+        </is>
+      </c>
+      <c r="L26" s="143" t="inlineStr">
+        <is>
+          <t>Bracing Stance</t>
+        </is>
+      </c>
+      <c r="O26" s="146" t="inlineStr">
         <is>
           <t>Deux mains</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>≈ 132 dégâts  ·  ≈ 9 armure  (9 cartes/6 visées)</t>
         </is>
@@ -16597,13 +17101,33 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E27" s="146" t="inlineStr">
-        <is>
-          <t>Regenerate×1, Healing Cleave×1, Glory Strike×1, Slash×2</t>
-        </is>
-      </c>
-      <c r="F27" s="146" t="n"/>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="E27" s="143" t="inlineStr">
+        <is>
+          <t>Regenerate</t>
+        </is>
+      </c>
+      <c r="F27" s="143" t="inlineStr">
+        <is>
+          <t>Healing Cleave</t>
+        </is>
+      </c>
+      <c r="G27" s="143" t="inlineStr">
+        <is>
+          <t>Glory Strike</t>
+        </is>
+      </c>
+      <c r="H27" s="143" t="inlineStr">
+        <is>
+          <t>Slash</t>
+        </is>
+      </c>
+      <c r="I27" s="143" t="inlineStr">
+        <is>
+          <t>Slash</t>
+        </is>
+      </c>
+      <c r="O27" s="146" t="n"/>
+      <c r="P27" s="2" t="inlineStr">
         <is>
           <t>≈ 42 dégâts  (5 cartes/6 visées · 1 buff)</t>
         </is>
@@ -16630,13 +17154,28 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E28" s="146" t="inlineStr">
-        <is>
-          <t>Rend×1, Gash×2, Slash×1</t>
-        </is>
-      </c>
-      <c r="F28" s="146" t="n"/>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="E28" s="143" t="inlineStr">
+        <is>
+          <t>Rend</t>
+        </is>
+      </c>
+      <c r="F28" s="143" t="inlineStr">
+        <is>
+          <t>Gash</t>
+        </is>
+      </c>
+      <c r="G28" s="143" t="inlineStr">
+        <is>
+          <t>Gash</t>
+        </is>
+      </c>
+      <c r="H28" s="143" t="inlineStr">
+        <is>
+          <t>Slash</t>
+        </is>
+      </c>
+      <c r="O28" s="146" t="n"/>
+      <c r="P28" s="2" t="inlineStr">
         <is>
           <t>≈ 23 dégâts  (4 cartes/6 visées)</t>
         </is>
@@ -16663,13 +17202,33 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E29" s="146" t="inlineStr">
-        <is>
-          <t>Whirl×2, Gash×1, Big Strike×2</t>
-        </is>
-      </c>
-      <c r="F29" s="146" t="n"/>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="E29" s="143" t="inlineStr">
+        <is>
+          <t>Whirl</t>
+        </is>
+      </c>
+      <c r="F29" s="143" t="inlineStr">
+        <is>
+          <t>Whirl</t>
+        </is>
+      </c>
+      <c r="G29" s="143" t="inlineStr">
+        <is>
+          <t>Gash</t>
+        </is>
+      </c>
+      <c r="H29" s="143" t="inlineStr">
+        <is>
+          <t>Big Strike</t>
+        </is>
+      </c>
+      <c r="I29" s="143" t="inlineStr">
+        <is>
+          <t>Big Strike</t>
+        </is>
+      </c>
+      <c r="O29" s="146" t="n"/>
+      <c r="P29" s="2" t="inlineStr">
         <is>
           <t>≈ 53 dégâts  (5 cartes/6 visées)</t>
         </is>
@@ -16696,13 +17255,33 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E30" s="146" t="inlineStr">
-        <is>
-          <t>Stone Fist×1, Iron Wall×2, Big Strike×2</t>
-        </is>
-      </c>
-      <c r="F30" s="146" t="n"/>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="E30" s="143" t="inlineStr">
+        <is>
+          <t>Stone Fist</t>
+        </is>
+      </c>
+      <c r="F30" s="143" t="inlineStr">
+        <is>
+          <t>Iron Wall</t>
+        </is>
+      </c>
+      <c r="G30" s="143" t="inlineStr">
+        <is>
+          <t>Iron Wall</t>
+        </is>
+      </c>
+      <c r="H30" s="143" t="inlineStr">
+        <is>
+          <t>Big Strike</t>
+        </is>
+      </c>
+      <c r="I30" s="143" t="inlineStr">
+        <is>
+          <t>Big Strike</t>
+        </is>
+      </c>
+      <c r="O30" s="146" t="n"/>
+      <c r="P30" s="2" t="inlineStr">
         <is>
           <t>≈ 40 dégâts  ·  ≈ 8 armure  (5 cartes/6 visées)</t>
         </is>
@@ -16729,17 +17308,37 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E31" s="146" t="inlineStr">
-        <is>
-          <t>Flurry×2, Double Strike×1, Big Strike×2</t>
-        </is>
-      </c>
-      <c r="F31" s="146" t="inlineStr">
+      <c r="E31" s="143" t="inlineStr">
+        <is>
+          <t>Flurry</t>
+        </is>
+      </c>
+      <c r="F31" s="143" t="inlineStr">
+        <is>
+          <t>Flurry</t>
+        </is>
+      </c>
+      <c r="G31" s="143" t="inlineStr">
+        <is>
+          <t>Double Strike</t>
+        </is>
+      </c>
+      <c r="H31" s="143" t="inlineStr">
+        <is>
+          <t>Big Strike</t>
+        </is>
+      </c>
+      <c r="I31" s="143" t="inlineStr">
+        <is>
+          <t>Big Strike</t>
+        </is>
+      </c>
+      <c r="O31" s="146" t="inlineStr">
         <is>
           <t>Combo: Twin combo: +3 permanent Strength if the same Twin Daggers are in your off-hand.</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="P31" s="2" t="inlineStr">
         <is>
           <t>≈ 37 dégâts  (5 cartes/6 visées)</t>
         </is>
@@ -16766,13 +17365,28 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E32" s="146" t="inlineStr">
-        <is>
-          <t>Venom Spit×1, Poison Dart×2, Slash×1</t>
-        </is>
-      </c>
-      <c r="F32" s="146" t="n"/>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="E32" s="143" t="inlineStr">
+        <is>
+          <t>Venom Spit</t>
+        </is>
+      </c>
+      <c r="F32" s="143" t="inlineStr">
+        <is>
+          <t>Poison Dart</t>
+        </is>
+      </c>
+      <c r="G32" s="143" t="inlineStr">
+        <is>
+          <t>Poison Dart</t>
+        </is>
+      </c>
+      <c r="H32" s="143" t="inlineStr">
+        <is>
+          <t>Slash</t>
+        </is>
+      </c>
+      <c r="O32" s="146" t="n"/>
+      <c r="P32" s="2" t="inlineStr">
         <is>
           <t>≈ 23 dégâts  (4 cartes/6 visées)</t>
         </is>
@@ -16799,13 +17413,33 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E33" s="146" t="inlineStr">
-        <is>
-          <t>Earthshatter×1, Big Smash×1, Iron Wall×2, Big Strike×1</t>
-        </is>
-      </c>
-      <c r="F33" s="146" t="n"/>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="E33" s="143" t="inlineStr">
+        <is>
+          <t>Earthshatter</t>
+        </is>
+      </c>
+      <c r="F33" s="143" t="inlineStr">
+        <is>
+          <t>Big Smash</t>
+        </is>
+      </c>
+      <c r="G33" s="143" t="inlineStr">
+        <is>
+          <t>Iron Wall</t>
+        </is>
+      </c>
+      <c r="H33" s="143" t="inlineStr">
+        <is>
+          <t>Iron Wall</t>
+        </is>
+      </c>
+      <c r="I33" s="143" t="inlineStr">
+        <is>
+          <t>Big Strike</t>
+        </is>
+      </c>
+      <c r="O33" s="146" t="n"/>
+      <c r="P33" s="2" t="inlineStr">
         <is>
           <t>≈ 48 dégâts  ·  ≈ 8 armure  (5 cartes/6 visées)</t>
         </is>
@@ -16832,17 +17466,62 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="E34" s="149" t="inlineStr">
-        <is>
-          <t>Venom Stab×6, Poison Dance×2, weaknesses exploitation×1,Explosion Of Poisonx1</t>
-        </is>
-      </c>
-      <c r="F34" s="149" t="inlineStr">
+      <c r="E34" s="143" t="inlineStr">
+        <is>
+          <t>Venom Stab</t>
+        </is>
+      </c>
+      <c r="F34" s="143" t="inlineStr">
+        <is>
+          <t>Venom Stab</t>
+        </is>
+      </c>
+      <c r="G34" s="143" t="inlineStr">
+        <is>
+          <t>Venom Stab</t>
+        </is>
+      </c>
+      <c r="H34" s="143" t="inlineStr">
+        <is>
+          <t>Venom Stab</t>
+        </is>
+      </c>
+      <c r="I34" s="143" t="inlineStr">
+        <is>
+          <t>Venom Stab</t>
+        </is>
+      </c>
+      <c r="J34" s="143" t="inlineStr">
+        <is>
+          <t>Venom Stab</t>
+        </is>
+      </c>
+      <c r="K34" s="143" t="inlineStr">
+        <is>
+          <t>Poison Dance</t>
+        </is>
+      </c>
+      <c r="L34" s="143" t="inlineStr">
+        <is>
+          <t>Poison Dance</t>
+        </is>
+      </c>
+      <c r="M34" s="143" t="inlineStr">
+        <is>
+          <t>Weakness Exploitation</t>
+        </is>
+      </c>
+      <c r="N34" s="143" t="inlineStr">
+        <is>
+          <t>Explosion Of Poison</t>
+        </is>
+      </c>
+      <c r="O34" s="149" t="inlineStr">
         <is>
           <t>Combo: Twin fang: +5 permanent Strength if another dagger is in your off-hand.</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="P34" s="2" t="inlineStr">
         <is>
           <t>≈ 168 dégâts  (10 cartes/6 visées · 1 non listée)</t>
         </is>
@@ -16869,17 +17548,47 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="E35" s="149" t="inlineStr">
-        <is>
-          <t>Bulwark×2, Seismic Slam×2, Stonestrike×2, Tremor×1, Get aheadx1</t>
-        </is>
-      </c>
-      <c r="F35" s="149" t="inlineStr">
+      <c r="E35" s="143" t="inlineStr">
+        <is>
+          <t>Bulwark</t>
+        </is>
+      </c>
+      <c r="F35" s="143" t="inlineStr">
+        <is>
+          <t>Bulwark</t>
+        </is>
+      </c>
+      <c r="G35" s="143" t="inlineStr">
+        <is>
+          <t>Seismic Slam</t>
+        </is>
+      </c>
+      <c r="H35" s="143" t="inlineStr">
+        <is>
+          <t>Seismic Slam</t>
+        </is>
+      </c>
+      <c r="I35" s="143" t="inlineStr">
+        <is>
+          <t>Stonestrike</t>
+        </is>
+      </c>
+      <c r="J35" s="143" t="inlineStr">
+        <is>
+          <t>Stonestrike</t>
+        </is>
+      </c>
+      <c r="K35" s="143" t="inlineStr">
+        <is>
+          <t>Tremor</t>
+        </is>
+      </c>
+      <c r="O35" s="149" t="inlineStr">
         <is>
           <t>Deux mains, Bonsu passif de 2 stone par tours (permanent tant que l'arme est équipée).</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="P35" s="2" t="inlineStr">
         <is>
           <t>≈ 306 dégâts  ·  ≈ 27 armure  (8 cartes/6 visées · 1 buff)</t>
         </is>
@@ -16906,17 +17615,42 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="E36" s="149" t="inlineStr">
-        <is>
-          <t>Pommel Strike×2, Giant Swing×2, Cleave in half×2</t>
-        </is>
-      </c>
-      <c r="F36" s="149" t="inlineStr">
+      <c r="E36" s="143" t="inlineStr">
+        <is>
+          <t>Pommel Strike</t>
+        </is>
+      </c>
+      <c r="F36" s="143" t="inlineStr">
+        <is>
+          <t>Pommel Strike</t>
+        </is>
+      </c>
+      <c r="G36" s="143" t="inlineStr">
+        <is>
+          <t>Giant Swing</t>
+        </is>
+      </c>
+      <c r="H36" s="143" t="inlineStr">
+        <is>
+          <t>Giant Swing</t>
+        </is>
+      </c>
+      <c r="I36" s="143" t="inlineStr">
+        <is>
+          <t>Cleave</t>
+        </is>
+      </c>
+      <c r="J36" s="143" t="inlineStr">
+        <is>
+          <t>Cleave</t>
+        </is>
+      </c>
+      <c r="O36" s="149" t="inlineStr">
         <is>
           <t>Deux mains</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="P36" s="2" t="inlineStr">
         <is>
           <t>≈ 252 dégâts  (6 cartes/6 visées)</t>
         </is>
@@ -16943,17 +17677,47 @@
           <t>Epic</t>
         </is>
       </c>
-      <c r="E37" s="152" t="inlineStr">
-        <is>
-          <t>Onyx Radiance×2, Onyx Slash×3, Heat Rejection×1, Onyx Overheat×1</t>
-        </is>
-      </c>
-      <c r="F37" s="152" t="inlineStr">
+      <c r="E37" s="143" t="inlineStr">
+        <is>
+          <t>Onyx Radiance</t>
+        </is>
+      </c>
+      <c r="F37" s="143" t="inlineStr">
+        <is>
+          <t>Onyx Radiance</t>
+        </is>
+      </c>
+      <c r="G37" s="143" t="inlineStr">
+        <is>
+          <t>Onyx Slash</t>
+        </is>
+      </c>
+      <c r="H37" s="143" t="inlineStr">
+        <is>
+          <t>Onyx Slash</t>
+        </is>
+      </c>
+      <c r="I37" s="143" t="inlineStr">
+        <is>
+          <t>Onyx Slash</t>
+        </is>
+      </c>
+      <c r="J37" s="143" t="inlineStr">
+        <is>
+          <t>Heat Rejection</t>
+        </is>
+      </c>
+      <c r="K37" s="143" t="inlineStr">
+        <is>
+          <t>Onyx Overheat</t>
+        </is>
+      </c>
+      <c r="O37" s="152" t="inlineStr">
         <is>
           <t>Deux mains</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="P37" s="2" t="inlineStr">
         <is>
           <t>≈ 204 dégâts  (7 cartes/7 visées · 2 buff)</t>
         </is>
@@ -16980,17 +17744,52 @@
           <t>Epic</t>
         </is>
       </c>
-      <c r="E38" s="157" t="inlineStr">
-        <is>
-          <t>Grim Scythe×3, Reaping Arc×2, Death Sentence×1, Harvest×1, Soul Reap×1</t>
-        </is>
-      </c>
-      <c r="F38" s="157" t="inlineStr">
+      <c r="E38" s="143" t="inlineStr">
+        <is>
+          <t>Grim Scythe</t>
+        </is>
+      </c>
+      <c r="F38" s="143" t="inlineStr">
+        <is>
+          <t>Grim Scythe</t>
+        </is>
+      </c>
+      <c r="G38" s="143" t="inlineStr">
+        <is>
+          <t>Grim Scythe</t>
+        </is>
+      </c>
+      <c r="H38" s="143" t="inlineStr">
+        <is>
+          <t>Reaping Arc</t>
+        </is>
+      </c>
+      <c r="I38" s="143" t="inlineStr">
+        <is>
+          <t>Reaping Arc</t>
+        </is>
+      </c>
+      <c r="J38" s="143" t="inlineStr">
+        <is>
+          <t>Death Sentence</t>
+        </is>
+      </c>
+      <c r="K38" s="143" t="inlineStr">
+        <is>
+          <t>Harvest</t>
+        </is>
+      </c>
+      <c r="L38" s="143" t="inlineStr">
+        <is>
+          <t>Soul Reap</t>
+        </is>
+      </c>
+      <c r="O38" s="157" t="inlineStr">
         <is>
           <t>Deux mains</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="P38" s="2" t="inlineStr">
         <is>
           <t>≈ 357 dégâts  (8 cartes/7 visées · 1 buff)</t>
         </is>
@@ -17017,13 +17816,43 @@
           <t>Epic</t>
         </is>
       </c>
-      <c r="E39" s="152" t="inlineStr">
-        <is>
-          <t>Lava Hammer×3, Armor Forging×1, Dragon's Blaze×1, Fire Strike×2</t>
-        </is>
-      </c>
-      <c r="F39" s="152" t="n"/>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="E39" s="143" t="inlineStr">
+        <is>
+          <t>Lava Hammer</t>
+        </is>
+      </c>
+      <c r="F39" s="143" t="inlineStr">
+        <is>
+          <t>Lava Hammer</t>
+        </is>
+      </c>
+      <c r="G39" s="143" t="inlineStr">
+        <is>
+          <t>Lava Hammer</t>
+        </is>
+      </c>
+      <c r="H39" s="143" t="inlineStr">
+        <is>
+          <t>Armor Forging</t>
+        </is>
+      </c>
+      <c r="I39" s="143" t="inlineStr">
+        <is>
+          <t>Dragon's Blaze</t>
+        </is>
+      </c>
+      <c r="J39" s="143" t="inlineStr">
+        <is>
+          <t>Fire Strike</t>
+        </is>
+      </c>
+      <c r="K39" s="143" t="inlineStr">
+        <is>
+          <t>Fire Strike</t>
+        </is>
+      </c>
+      <c r="O39" s="152" t="n"/>
+      <c r="P39" s="2" t="inlineStr">
         <is>
           <t>≈ 272 dégâts  (7 cartes/7 visées)</t>
         </is>
@@ -17039,7 +17868,7 @@
       <c r="C40" s="48" t="n"/>
       <c r="D40" s="48" t="n"/>
       <c r="E40" s="48" t="n"/>
-      <c r="F40" s="48" t="n"/>
+      <c r="O40" s="48" t="n"/>
     </row>
     <row r="41" ht="15" customHeight="1" s="140">
       <c r="A41" s="142" t="inlineStr">
@@ -17064,11 +17893,16 @@
       </c>
       <c r="E41" s="143" t="inlineStr">
         <is>
-          <t>Flex×1, Spark×1</t>
-        </is>
-      </c>
-      <c r="F41" s="143" t="n"/>
-      <c r="G41" s="2" t="inlineStr">
+          <t>Flex</t>
+        </is>
+      </c>
+      <c r="F41" s="143" t="inlineStr">
+        <is>
+          <t>Spark</t>
+        </is>
+      </c>
+      <c r="O41" s="143" t="n"/>
+      <c r="P41" s="2" t="inlineStr">
         <is>
           <t>aucun dégât/armure  (2 cartes/5 visées · 2 buff)</t>
         </is>
@@ -17097,11 +17931,16 @@
       </c>
       <c r="E42" s="143" t="inlineStr">
         <is>
-          <t>Guard×1, Nimble Hands×1</t>
-        </is>
-      </c>
-      <c r="F42" s="143" t="n"/>
-      <c r="G42" s="2" t="inlineStr">
+          <t>Guard</t>
+        </is>
+      </c>
+      <c r="F42" s="143" t="inlineStr">
+        <is>
+          <t>Nimble Hands</t>
+        </is>
+      </c>
+      <c r="O42" s="143" t="n"/>
+      <c r="P42" s="2" t="inlineStr">
         <is>
           <t>≈ 4 armure  (2 cartes/5 visées · 1 buff)</t>
         </is>
@@ -17130,11 +17969,21 @@
       </c>
       <c r="E43" s="143" t="inlineStr">
         <is>
-          <t>Ember×2, Bright Flame×1</t>
-        </is>
-      </c>
-      <c r="F43" s="143" t="n"/>
-      <c r="G43" s="2" t="inlineStr">
+          <t>Ember</t>
+        </is>
+      </c>
+      <c r="F43" s="143" t="inlineStr">
+        <is>
+          <t>Ember</t>
+        </is>
+      </c>
+      <c r="G43" s="143" t="inlineStr">
+        <is>
+          <t>Bright Flame</t>
+        </is>
+      </c>
+      <c r="O43" s="143" t="n"/>
+      <c r="P43" s="2" t="inlineStr">
         <is>
           <t>≈ 20 dégâts  (3 cartes/5 visées)</t>
         </is>
@@ -17163,11 +18012,21 @@
       </c>
       <c r="E44" s="143" t="inlineStr">
         <is>
-          <t>Regenerate×2, Nimble Hands×1</t>
-        </is>
-      </c>
-      <c r="F44" s="143" t="n"/>
-      <c r="G44" s="2" t="inlineStr">
+          <t>Regenerate</t>
+        </is>
+      </c>
+      <c r="F44" s="143" t="inlineStr">
+        <is>
+          <t>Regenerate</t>
+        </is>
+      </c>
+      <c r="G44" s="143" t="inlineStr">
+        <is>
+          <t>Nimble Hands</t>
+        </is>
+      </c>
+      <c r="O44" s="143" t="n"/>
+      <c r="P44" s="2" t="inlineStr">
         <is>
           <t>aucun dégât/armure  (3 cartes/5 visées · 3 buff)</t>
         </is>
@@ -17196,11 +18055,16 @@
       </c>
       <c r="E45" s="143" t="inlineStr">
         <is>
-          <t>Spark×1, Nimble Hands×1</t>
-        </is>
-      </c>
-      <c r="F45" s="143" t="n"/>
-      <c r="G45" s="2" t="inlineStr">
+          <t>Spark</t>
+        </is>
+      </c>
+      <c r="F45" s="143" t="inlineStr">
+        <is>
+          <t>Nimble Hands</t>
+        </is>
+      </c>
+      <c r="O45" s="143" t="n"/>
+      <c r="P45" s="2" t="inlineStr">
         <is>
           <t>aucun dégât/armure  (2 cartes/5 visées · 2 buff)</t>
         </is>
@@ -17229,11 +18093,21 @@
       </c>
       <c r="E46" s="143" t="inlineStr">
         <is>
-          <t>Guard×2, Iron Wall×1</t>
-        </is>
-      </c>
-      <c r="F46" s="143" t="n"/>
-      <c r="G46" s="2" t="inlineStr">
+          <t>Guard</t>
+        </is>
+      </c>
+      <c r="F46" s="143" t="inlineStr">
+        <is>
+          <t>Guard</t>
+        </is>
+      </c>
+      <c r="G46" s="143" t="inlineStr">
+        <is>
+          <t>Iron Wall</t>
+        </is>
+      </c>
+      <c r="O46" s="143" t="n"/>
+      <c r="P46" s="2" t="inlineStr">
         <is>
           <t>≈ 12 armure  (3 cartes/5 visées)</t>
         </is>
@@ -17260,13 +18134,23 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E47" s="146" t="inlineStr">
-        <is>
-          <t>Fireball×1, Ember×2</t>
-        </is>
-      </c>
-      <c r="F47" s="146" t="n"/>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="E47" s="143" t="inlineStr">
+        <is>
+          <t>Fireball</t>
+        </is>
+      </c>
+      <c r="F47" s="143" t="inlineStr">
+        <is>
+          <t>Ember</t>
+        </is>
+      </c>
+      <c r="G47" s="143" t="inlineStr">
+        <is>
+          <t>Ember</t>
+        </is>
+      </c>
+      <c r="O47" s="146" t="n"/>
+      <c r="P47" s="2" t="inlineStr">
         <is>
           <t>≈ 26 dégâts  (3 cartes/6 visées)</t>
         </is>
@@ -17293,13 +18177,28 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E48" s="146" t="inlineStr">
-        <is>
-          <t>Iron Wall×3, Shield Wall×1</t>
-        </is>
-      </c>
-      <c r="F48" s="146" t="n"/>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="E48" s="143" t="inlineStr">
+        <is>
+          <t>Iron Wall</t>
+        </is>
+      </c>
+      <c r="F48" s="143" t="inlineStr">
+        <is>
+          <t>Iron Wall</t>
+        </is>
+      </c>
+      <c r="G48" s="143" t="inlineStr">
+        <is>
+          <t>Iron Wall</t>
+        </is>
+      </c>
+      <c r="H48" s="143" t="inlineStr">
+        <is>
+          <t>Shield Wall</t>
+        </is>
+      </c>
+      <c r="O48" s="146" t="n"/>
+      <c r="P48" s="2" t="inlineStr">
         <is>
           <t>≈ 18 armure  (4 cartes/6 visées)</t>
         </is>
@@ -17326,13 +18225,18 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E49" s="146" t="inlineStr">
-        <is>
-          <t>Rally×1, Flex×1</t>
-        </is>
-      </c>
-      <c r="F49" s="146" t="n"/>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="E49" s="143" t="inlineStr">
+        <is>
+          <t>Rally</t>
+        </is>
+      </c>
+      <c r="F49" s="143" t="inlineStr">
+        <is>
+          <t>Flex</t>
+        </is>
+      </c>
+      <c r="O49" s="146" t="n"/>
+      <c r="P49" s="2" t="inlineStr">
         <is>
           <t>aucun dégât/armure  (2 cartes/6 visées · 2 buff)</t>
         </is>
@@ -17359,13 +18263,23 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E50" s="146" t="inlineStr">
-        <is>
-          <t>Arcane Surge×1, Spark×1, Nimble Hands×1</t>
-        </is>
-      </c>
-      <c r="F50" s="146" t="n"/>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="E50" s="143" t="inlineStr">
+        <is>
+          <t>Arcane Surge</t>
+        </is>
+      </c>
+      <c r="F50" s="143" t="inlineStr">
+        <is>
+          <t>Spark</t>
+        </is>
+      </c>
+      <c r="G50" s="143" t="inlineStr">
+        <is>
+          <t>Nimble Hands</t>
+        </is>
+      </c>
+      <c r="O50" s="146" t="n"/>
+      <c r="P50" s="2" t="inlineStr">
         <is>
           <t>≈ 16 dégâts  (3 cartes/6 visées · 2 buff)</t>
         </is>
@@ -17392,17 +18306,27 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E51" s="146" t="inlineStr">
-        <is>
-          <t>Aegis×1, Iron Wall×1, Guard×1</t>
-        </is>
-      </c>
-      <c r="F51" s="146" t="inlineStr">
+      <c r="E51" s="143" t="inlineStr">
+        <is>
+          <t>Aegis</t>
+        </is>
+      </c>
+      <c r="F51" s="143" t="inlineStr">
+        <is>
+          <t>Iron Wall</t>
+        </is>
+      </c>
+      <c r="G51" s="143" t="inlineStr">
+        <is>
+          <t>Guard</t>
+        </is>
+      </c>
+      <c r="O51" s="146" t="inlineStr">
         <is>
           <t>When hit by a melee attack, the attacker takes 2 damage.</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="P51" s="2" t="inlineStr">
         <is>
           <t>≈ 20 armure  (3 cartes/6 visées)</t>
         </is>
@@ -17429,17 +18353,42 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="E52" s="149" t="inlineStr">
-        <is>
-          <t>Shield Wall×3, Shield Bash×2, Stacking Shield×1</t>
-        </is>
-      </c>
-      <c r="F52" s="149" t="inlineStr">
+      <c r="E52" s="143" t="inlineStr">
+        <is>
+          <t>Shield Wall</t>
+        </is>
+      </c>
+      <c r="F52" s="143" t="inlineStr">
+        <is>
+          <t>Shield Wall</t>
+        </is>
+      </c>
+      <c r="G52" s="143" t="inlineStr">
+        <is>
+          <t>Shield Wall</t>
+        </is>
+      </c>
+      <c r="H52" s="143" t="inlineStr">
+        <is>
+          <t>Shield Bash</t>
+        </is>
+      </c>
+      <c r="I52" s="143" t="inlineStr">
+        <is>
+          <t>Shield Bash</t>
+        </is>
+      </c>
+      <c r="J52" s="143" t="inlineStr">
+        <is>
+          <t>Stacking Shield</t>
+        </is>
+      </c>
+      <c r="O52" s="149" t="inlineStr">
         <is>
           <t>When hit by a melee attack, gain 3 Stone.</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="P52" s="2" t="inlineStr">
         <is>
           <t>≈ 48 dégâts  ·  ≈ 54 armure  (6 cartes/6 visées)</t>
         </is>
@@ -17455,7 +18404,7 @@
       <c r="C53" s="48" t="n"/>
       <c r="D53" s="48" t="n"/>
       <c r="E53" s="48" t="n"/>
-      <c r="F53" s="48" t="n"/>
+      <c r="O53" s="48" t="n"/>
     </row>
     <row r="54" ht="15" customHeight="1" s="140">
       <c r="A54" s="142" t="inlineStr">
@@ -17480,15 +18429,30 @@
       </c>
       <c r="E54" s="143" t="inlineStr">
         <is>
-          <t>Light Armor×3, Standard Armor×1</t>
+          <t>Light Armor</t>
         </is>
       </c>
       <c r="F54" s="143" t="inlineStr">
         <is>
+          <t>Light Armor</t>
+        </is>
+      </c>
+      <c r="G54" s="143" t="inlineStr">
+        <is>
+          <t>Light Armor</t>
+        </is>
+      </c>
+      <c r="H54" s="143" t="inlineStr">
+        <is>
+          <t>Standard Armor</t>
+        </is>
+      </c>
+      <c r="O54" s="143" t="inlineStr">
+        <is>
           <t>Armure début: 8</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="P54" s="2" t="inlineStr">
         <is>
           <t>≈ 18 armure  (4 cartes/5 visées)</t>
         </is>
@@ -17517,15 +18481,20 @@
       </c>
       <c r="E55" s="143" t="inlineStr">
         <is>
-          <t>Guard×1, Regenerate×1</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="F55" s="143" t="inlineStr">
         <is>
+          <t>Regenerate</t>
+        </is>
+      </c>
+      <c r="O55" s="143" t="inlineStr">
+        <is>
           <t>Armure début: 6</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="P55" s="2" t="inlineStr">
         <is>
           <t>≈ 4 armure  (2 cartes/5 visées · 1 buff)</t>
         </is>
@@ -17554,15 +18523,25 @@
       </c>
       <c r="E56" s="143" t="inlineStr">
         <is>
-          <t>Guard×2, Iron Wall×1</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="F56" s="143" t="inlineStr">
         <is>
+          <t>Guard</t>
+        </is>
+      </c>
+      <c r="G56" s="143" t="inlineStr">
+        <is>
+          <t>Iron Wall</t>
+        </is>
+      </c>
+      <c r="O56" s="143" t="inlineStr">
+        <is>
           <t>Armure début: 6</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="P56" s="2" t="inlineStr">
         <is>
           <t>≈ 12 armure  (3 cartes/5 visées)</t>
         </is>
@@ -17591,15 +18570,30 @@
       </c>
       <c r="E57" s="143" t="inlineStr">
         <is>
-          <t>Light Armor×2, Free Movement×1, Flex×1</t>
+          <t>Light Armor</t>
         </is>
       </c>
       <c r="F57" s="143" t="inlineStr">
         <is>
+          <t>Light Armor</t>
+        </is>
+      </c>
+      <c r="G57" s="143" t="inlineStr">
+        <is>
+          <t>Free Movement</t>
+        </is>
+      </c>
+      <c r="H57" s="143" t="inlineStr">
+        <is>
+          <t>Flex</t>
+        </is>
+      </c>
+      <c r="O57" s="143" t="inlineStr">
+        <is>
           <t>Armure début: 6</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="P57" s="2" t="inlineStr">
         <is>
           <t>≈ 8 armure  (4 cartes/5 visées · 2 buff)</t>
         </is>
@@ -17628,15 +18622,30 @@
       </c>
       <c r="E58" s="143" t="inlineStr">
         <is>
-          <t>Light Armor×3, Free Movement×1</t>
+          <t>Light Armor</t>
         </is>
       </c>
       <c r="F58" s="143" t="inlineStr">
         <is>
+          <t>Light Armor</t>
+        </is>
+      </c>
+      <c r="G58" s="143" t="inlineStr">
+        <is>
+          <t>Light Armor</t>
+        </is>
+      </c>
+      <c r="H58" s="143" t="inlineStr">
+        <is>
+          <t>Free Movement</t>
+        </is>
+      </c>
+      <c r="O58" s="143" t="inlineStr">
+        <is>
           <t>Armure début: 8</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="P58" s="2" t="inlineStr">
         <is>
           <t>≈ 12 armure  (4 cartes/5 visées · 1 buff)</t>
         </is>
@@ -17663,17 +18672,32 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E59" s="146" t="inlineStr">
-        <is>
-          <t>Fortify×1, Standard Armor×2, Rebound×1</t>
-        </is>
-      </c>
-      <c r="F59" s="146" t="inlineStr">
+      <c r="E59" s="143" t="inlineStr">
+        <is>
+          <t>Fortify</t>
+        </is>
+      </c>
+      <c r="F59" s="143" t="inlineStr">
+        <is>
+          <t>Standard Armor</t>
+        </is>
+      </c>
+      <c r="G59" s="143" t="inlineStr">
+        <is>
+          <t>Standard Armor</t>
+        </is>
+      </c>
+      <c r="H59" s="143" t="inlineStr">
+        <is>
+          <t>Rebound</t>
+        </is>
+      </c>
+      <c r="O59" s="146" t="inlineStr">
         <is>
           <t>Armure début: 15</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="P59" s="2" t="inlineStr">
         <is>
           <t>≈ 36 armure  (4 cartes/6 visées)</t>
         </is>
@@ -17700,17 +18724,32 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E60" s="146" t="inlineStr">
-        <is>
-          <t>Rage×1, Standard Armor×1, Unstoppable×1, Free Movement×1</t>
-        </is>
-      </c>
-      <c r="F60" s="146" t="inlineStr">
+      <c r="E60" s="143" t="inlineStr">
+        <is>
+          <t>Rage</t>
+        </is>
+      </c>
+      <c r="F60" s="143" t="inlineStr">
+        <is>
+          <t>Standard Armor</t>
+        </is>
+      </c>
+      <c r="G60" s="143" t="inlineStr">
+        <is>
+          <t>Unstoppable</t>
+        </is>
+      </c>
+      <c r="H60" s="143" t="inlineStr">
+        <is>
+          <t>Free Movement</t>
+        </is>
+      </c>
+      <c r="O60" s="146" t="inlineStr">
         <is>
           <t>Armure début: 4</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="P60" s="2" t="inlineStr">
         <is>
           <t>≈ 6 armure  (4 cartes/6 visées · 3 buff)</t>
         </is>
@@ -17737,17 +18776,32 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E61" s="146" t="inlineStr">
-        <is>
-          <t>Standard Armor×3, Rebound×1</t>
-        </is>
-      </c>
-      <c r="F61" s="146" t="inlineStr">
+      <c r="E61" s="143" t="inlineStr">
+        <is>
+          <t>Standard Armor</t>
+        </is>
+      </c>
+      <c r="F61" s="143" t="inlineStr">
+        <is>
+          <t>Standard Armor</t>
+        </is>
+      </c>
+      <c r="G61" s="143" t="inlineStr">
+        <is>
+          <t>Standard Armor</t>
+        </is>
+      </c>
+      <c r="H61" s="143" t="inlineStr">
+        <is>
+          <t>Rebound</t>
+        </is>
+      </c>
+      <c r="O61" s="146" t="inlineStr">
         <is>
           <t>Armure début: 10  ·  When hit by a melee attack, the attacker takes 2 damage.</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="P61" s="2" t="inlineStr">
         <is>
           <t>≈ 30 armure  (4 cartes/6 visées)</t>
         </is>
@@ -17774,17 +18828,62 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E62" s="146" t="inlineStr">
-        <is>
-          <t>Stone×6, Many Stone×3, Stone Coagulation×1</t>
-        </is>
-      </c>
-      <c r="F62" s="146" t="inlineStr">
+      <c r="E62" s="143" t="inlineStr">
+        <is>
+          <t>Stone</t>
+        </is>
+      </c>
+      <c r="F62" s="143" t="inlineStr">
+        <is>
+          <t>Stone</t>
+        </is>
+      </c>
+      <c r="G62" s="143" t="inlineStr">
+        <is>
+          <t>Stone</t>
+        </is>
+      </c>
+      <c r="H62" s="143" t="inlineStr">
+        <is>
+          <t>Stone</t>
+        </is>
+      </c>
+      <c r="I62" s="143" t="inlineStr">
+        <is>
+          <t>Stone</t>
+        </is>
+      </c>
+      <c r="J62" s="143" t="inlineStr">
+        <is>
+          <t>Stone</t>
+        </is>
+      </c>
+      <c r="K62" s="143" t="inlineStr">
+        <is>
+          <t>Many Stone</t>
+        </is>
+      </c>
+      <c r="L62" s="143" t="inlineStr">
+        <is>
+          <t>Many Stone</t>
+        </is>
+      </c>
+      <c r="M62" s="143" t="inlineStr">
+        <is>
+          <t>Many Stone</t>
+        </is>
+      </c>
+      <c r="N62" s="143" t="inlineStr">
+        <is>
+          <t>Stone Coagulation</t>
+        </is>
+      </c>
+      <c r="O62" s="146" t="inlineStr">
         <is>
           <t>Armure début: 12  ·  Set: Stone Age Set</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="P62" s="2" t="inlineStr">
         <is>
           <t>≈ 102 armure  (10 cartes/6 visées)</t>
         </is>
@@ -17811,17 +18910,42 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="E63" s="149" t="inlineStr">
-        <is>
-          <t>Heavy Armor×2, Sanguine Guard×2, Bloodbath×1, Drink blood×1</t>
-        </is>
-      </c>
-      <c r="F63" s="149" t="inlineStr">
+      <c r="E63" s="143" t="inlineStr">
+        <is>
+          <t>Heavy Armor</t>
+        </is>
+      </c>
+      <c r="F63" s="143" t="inlineStr">
+        <is>
+          <t>Heavy Armor</t>
+        </is>
+      </c>
+      <c r="G63" s="143" t="inlineStr">
+        <is>
+          <t>Sanguine Guard</t>
+        </is>
+      </c>
+      <c r="H63" s="143" t="inlineStr">
+        <is>
+          <t>Sanguine Guard</t>
+        </is>
+      </c>
+      <c r="I63" s="143" t="inlineStr">
+        <is>
+          <t>Bloodbath</t>
+        </is>
+      </c>
+      <c r="J63" s="143" t="inlineStr">
+        <is>
+          <t>Drink blood</t>
+        </is>
+      </c>
+      <c r="O63" s="149" t="inlineStr">
         <is>
           <t>Armure début: 20 - +3 stone a chaque tour (permanent)  ·  Set: Blood Set</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="P63" s="2" t="inlineStr">
         <is>
           <t>≈ 60 dégâts  ·  ≈ 54 armure  (6 cartes/6 visées)</t>
         </is>
@@ -17848,17 +18972,42 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="E64" s="149" t="inlineStr">
-        <is>
-          <t>Heavy Armor×1, Armor of light×3, Blinding Flash×1, Holy light×1</t>
-        </is>
-      </c>
-      <c r="F64" s="149" t="inlineStr">
+      <c r="E64" s="143" t="inlineStr">
+        <is>
+          <t>Heavy Armor</t>
+        </is>
+      </c>
+      <c r="F64" s="143" t="inlineStr">
+        <is>
+          <t>Armor of light</t>
+        </is>
+      </c>
+      <c r="G64" s="143" t="inlineStr">
+        <is>
+          <t>Armor of light</t>
+        </is>
+      </c>
+      <c r="H64" s="143" t="inlineStr">
+        <is>
+          <t>Armor of light</t>
+        </is>
+      </c>
+      <c r="I64" s="143" t="inlineStr">
+        <is>
+          <t>Blinding Flash</t>
+        </is>
+      </c>
+      <c r="J64" s="143" t="inlineStr">
+        <is>
+          <t>Holy light</t>
+        </is>
+      </c>
+      <c r="O64" s="149" t="inlineStr">
         <is>
           <t>Armure début: 30 - +5 stone a chaque tour (permanent)  ·  Set: Crusader Set</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="P64" s="2" t="inlineStr">
         <is>
           <t>≈ 60 dégâts  ·  ≈ 63 armure  (6 cartes/6 visées)</t>
         </is>
@@ -17885,17 +19034,42 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="E65" s="149" t="inlineStr">
-        <is>
-          <t>Beast Hide×2, War Cry×2, Reckless Charge×1, Titan Blow×1</t>
-        </is>
-      </c>
-      <c r="F65" s="149" t="inlineStr">
+      <c r="E65" s="143" t="inlineStr">
+        <is>
+          <t>Beast Hide</t>
+        </is>
+      </c>
+      <c r="F65" s="143" t="inlineStr">
+        <is>
+          <t>Beast Hide</t>
+        </is>
+      </c>
+      <c r="G65" s="143" t="inlineStr">
+        <is>
+          <t>War Cry</t>
+        </is>
+      </c>
+      <c r="H65" s="143" t="inlineStr">
+        <is>
+          <t>War Cry</t>
+        </is>
+      </c>
+      <c r="I65" s="143" t="inlineStr">
+        <is>
+          <t>Reckless Charge</t>
+        </is>
+      </c>
+      <c r="J65" s="143" t="inlineStr">
+        <is>
+          <t>Titan Blow</t>
+        </is>
+      </c>
+      <c r="O65" s="149" t="inlineStr">
         <is>
           <t>Armure début: 15  ·  Set: Barbarian Set</t>
         </is>
       </c>
-      <c r="G65" s="2" t="n"/>
+      <c r="P65" s="2" t="n"/>
     </row>
     <row r="66" ht="15" customHeight="1" s="140">
       <c r="A66" s="148" t="inlineStr">
@@ -17918,17 +19092,42 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="E66" s="149" t="inlineStr">
-        <is>
-          <t>Mail Armor×3, Quench×1, Heavy Armor×2</t>
-        </is>
-      </c>
-      <c r="F66" s="149" t="inlineStr">
+      <c r="E66" s="143" t="inlineStr">
+        <is>
+          <t>Mail Armor</t>
+        </is>
+      </c>
+      <c r="F66" s="143" t="inlineStr">
+        <is>
+          <t>Mail Armor</t>
+        </is>
+      </c>
+      <c r="G66" s="143" t="inlineStr">
+        <is>
+          <t>Mail Armor</t>
+        </is>
+      </c>
+      <c r="H66" s="143" t="inlineStr">
+        <is>
+          <t>Quench</t>
+        </is>
+      </c>
+      <c r="I66" s="143" t="inlineStr">
+        <is>
+          <t>Heavy Armor</t>
+        </is>
+      </c>
+      <c r="J66" s="143" t="inlineStr">
+        <is>
+          <t>Heavy Armor</t>
+        </is>
+      </c>
+      <c r="O66" s="149" t="inlineStr">
         <is>
           <t>Armure début: 22 - +4 stone a chaque tour (permanent)  ·  Set: Mail Set</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="P66" s="2" t="inlineStr">
         <is>
           <t>≈ 63 armure  (6 cartes/6 visées · 1 buff)</t>
         </is>
@@ -17955,17 +19154,47 @@
           <t>Épique</t>
         </is>
       </c>
-      <c r="E67" s="152" t="inlineStr">
-        <is>
-          <t>Gilded Guard×2, Hand of Dunir×2, Seal of Dunir×1, Verdict×1, Judgement×1</t>
-        </is>
-      </c>
-      <c r="F67" s="152" t="inlineStr">
+      <c r="E67" s="143" t="inlineStr">
+        <is>
+          <t>Gilded Guard</t>
+        </is>
+      </c>
+      <c r="F67" s="143" t="inlineStr">
+        <is>
+          <t>Gilded Guard</t>
+        </is>
+      </c>
+      <c r="G67" s="143" t="inlineStr">
+        <is>
+          <t>Hand of Dunir</t>
+        </is>
+      </c>
+      <c r="H67" s="143" t="inlineStr">
+        <is>
+          <t>Hand of Dunir</t>
+        </is>
+      </c>
+      <c r="I67" s="143" t="inlineStr">
+        <is>
+          <t>Seal of Dunir</t>
+        </is>
+      </c>
+      <c r="J67" s="143" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+      <c r="K67" s="143" t="inlineStr">
+        <is>
+          <t>Judgement</t>
+        </is>
+      </c>
+      <c r="O67" s="152" t="inlineStr">
         <is>
           <t>Armure début: 40  ·  +6 Pierre à chaque tour  ·  Craft: pierre solaire + or  ·  Set: Dunir's Blessing</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="P67" s="2" t="inlineStr">
         <is>
           <t>≈ 16 dégâts  ·  ≈ 52 armure  ·  12 PV  (7 cartes/7 visées)</t>
         </is>
@@ -17992,17 +19221,47 @@
           <t>Epic</t>
         </is>
       </c>
-      <c r="E68" s="152" t="inlineStr">
-        <is>
-          <t>Onyx Armor×3, Dragon's Blaze×1, Onyx Breath×2, All Should Be Fire×1</t>
-        </is>
-      </c>
-      <c r="F68" s="152" t="inlineStr">
+      <c r="E68" s="143" t="inlineStr">
+        <is>
+          <t>Onyx Armor</t>
+        </is>
+      </c>
+      <c r="F68" s="143" t="inlineStr">
+        <is>
+          <t>Onyx Armor</t>
+        </is>
+      </c>
+      <c r="G68" s="143" t="inlineStr">
+        <is>
+          <t>Onyx Armor</t>
+        </is>
+      </c>
+      <c r="H68" s="143" t="inlineStr">
+        <is>
+          <t>Dragon's Blaze</t>
+        </is>
+      </c>
+      <c r="I68" s="143" t="inlineStr">
+        <is>
+          <t>Onyx Breath</t>
+        </is>
+      </c>
+      <c r="J68" s="143" t="inlineStr">
+        <is>
+          <t>Onyx Breath</t>
+        </is>
+      </c>
+      <c r="K68" s="143" t="inlineStr">
+        <is>
+          <t>All Should Be Fire</t>
+        </is>
+      </c>
+      <c r="O68" s="152" t="inlineStr">
         <is>
           <t xml:space="preserve">Armure début: 36 - +8 stone a chaque tour (permanent) ·  Set: Onyx Set </t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="P68" s="2" t="inlineStr">
         <is>
           <t>≈ 204 dégâts  ·  ≈ 84 armure  (7 cartes/7 visées)</t>
         </is>
@@ -18018,7 +19277,7 @@
       <c r="C69" s="48" t="n"/>
       <c r="D69" s="48" t="n"/>
       <c r="E69" s="48" t="n"/>
-      <c r="F69" s="48" t="n"/>
+      <c r="O69" s="48" t="n"/>
     </row>
     <row r="70" ht="15" customHeight="1" s="140">
       <c r="A70" s="142" t="inlineStr">
@@ -18043,11 +19302,16 @@
       </c>
       <c r="E70" s="143" t="inlineStr">
         <is>
-          <t>Gash×1, Poison Coat×1</t>
-        </is>
-      </c>
-      <c r="F70" s="143" t="n"/>
-      <c r="G70" s="2" t="inlineStr">
+          <t>Gash</t>
+        </is>
+      </c>
+      <c r="F70" s="143" t="inlineStr">
+        <is>
+          <t>Poison Coat</t>
+        </is>
+      </c>
+      <c r="O70" s="143" t="n"/>
+      <c r="P70" s="2" t="inlineStr">
         <is>
           <t>≈ 10 dégâts  (2 cartes/5 visées)</t>
         </is>
@@ -18076,11 +19340,11 @@
       </c>
       <c r="E71" s="143" t="inlineStr">
         <is>
-          <t>Spark×1</t>
-        </is>
-      </c>
-      <c r="F71" s="143" t="n"/>
-      <c r="G71" s="2" t="inlineStr">
+          <t>Spark</t>
+        </is>
+      </c>
+      <c r="O71" s="143" t="n"/>
+      <c r="P71" s="2" t="inlineStr">
         <is>
           <t>aucun dégât/armure  (1 carte/5 visées · 1 buff)</t>
         </is>
@@ -18109,11 +19373,16 @@
       </c>
       <c r="E72" s="143" t="inlineStr">
         <is>
-          <t>Nimble Hands×1, Roll 1 Dice×1</t>
-        </is>
-      </c>
-      <c r="F72" s="143" t="n"/>
-      <c r="G72" s="2" t="inlineStr">
+          <t>Nimble Hands</t>
+        </is>
+      </c>
+      <c r="F72" s="143" t="inlineStr">
+        <is>
+          <t>Roll 1 Dice</t>
+        </is>
+      </c>
+      <c r="O72" s="143" t="n"/>
+      <c r="P72" s="2" t="inlineStr">
         <is>
           <t>aucun dégât/armure  (2 cartes/5 visées · 2 buff)</t>
         </is>
@@ -18142,11 +19411,16 @@
       </c>
       <c r="E73" s="143" t="inlineStr">
         <is>
-          <t>Spark×1, Nimble Hands×1</t>
-        </is>
-      </c>
-      <c r="F73" s="143" t="n"/>
-      <c r="G73" s="2" t="inlineStr">
+          <t>Spark</t>
+        </is>
+      </c>
+      <c r="F73" s="143" t="inlineStr">
+        <is>
+          <t>Nimble Hands</t>
+        </is>
+      </c>
+      <c r="O73" s="143" t="n"/>
+      <c r="P73" s="2" t="inlineStr">
         <is>
           <t>aucun dégât/armure  (2 cartes/5 visées · 2 buff)</t>
         </is>
@@ -18175,11 +19449,16 @@
       </c>
       <c r="E74" s="143" t="inlineStr">
         <is>
-          <t>Ember×1, Spark×1</t>
-        </is>
-      </c>
-      <c r="F74" s="143" t="n"/>
-      <c r="G74" s="2" t="inlineStr">
+          <t>Ember</t>
+        </is>
+      </c>
+      <c r="F74" s="143" t="inlineStr">
+        <is>
+          <t>Spark</t>
+        </is>
+      </c>
+      <c r="O74" s="143" t="n"/>
+      <c r="P74" s="2" t="inlineStr">
         <is>
           <t>≈ 5 dégâts  (2 cartes/5 visées · 1 buff)</t>
         </is>
@@ -18206,13 +19485,18 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E75" s="146" t="inlineStr">
-        <is>
-          <t>Focus×1, Nimble Hands×1</t>
-        </is>
-      </c>
-      <c r="F75" s="146" t="n"/>
-      <c r="G75" s="2" t="inlineStr">
+      <c r="E75" s="143" t="inlineStr">
+        <is>
+          <t>Focus</t>
+        </is>
+      </c>
+      <c r="F75" s="143" t="inlineStr">
+        <is>
+          <t>Nimble Hands</t>
+        </is>
+      </c>
+      <c r="O75" s="146" t="n"/>
+      <c r="P75" s="2" t="inlineStr">
         <is>
           <t>aucun dégât/armure  (2 cartes/6 visées · 2 buff)</t>
         </is>
@@ -18239,13 +19523,18 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E76" s="146" t="inlineStr">
-        <is>
-          <t>Boost×1, Spark×1</t>
-        </is>
-      </c>
-      <c r="F76" s="146" t="n"/>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="E76" s="143" t="inlineStr">
+        <is>
+          <t>Boost</t>
+        </is>
+      </c>
+      <c r="F76" s="143" t="inlineStr">
+        <is>
+          <t>Spark</t>
+        </is>
+      </c>
+      <c r="O76" s="146" t="n"/>
+      <c r="P76" s="2" t="inlineStr">
         <is>
           <t>aucun dégât/armure  (2 cartes/6 visées · 2 buff)</t>
         </is>
@@ -18272,13 +19561,13 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E77" s="146" t="inlineStr">
-        <is>
-          <t>Sapphire Surge×1</t>
-        </is>
-      </c>
-      <c r="F77" s="146" t="n"/>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="E77" s="143" t="inlineStr">
+        <is>
+          <t>Sapphire Surge</t>
+        </is>
+      </c>
+      <c r="O77" s="146" t="n"/>
+      <c r="P77" s="2" t="inlineStr">
         <is>
           <t>aucun dégât/armure  (1 carte/6 visées · 1 buff)</t>
         </is>
@@ -18305,13 +19594,18 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E78" s="146" t="inlineStr">
-        <is>
-          <t>Drain×1, Gash×1</t>
-        </is>
-      </c>
-      <c r="F78" s="146" t="n"/>
-      <c r="G78" s="2" t="inlineStr">
+      <c r="E78" s="143" t="inlineStr">
+        <is>
+          <t>Drain</t>
+        </is>
+      </c>
+      <c r="F78" s="143" t="inlineStr">
+        <is>
+          <t>Gash</t>
+        </is>
+      </c>
+      <c r="O78" s="146" t="n"/>
+      <c r="P78" s="2" t="inlineStr">
         <is>
           <t>≈ 13 dégâts  (2 cartes/6 visées)</t>
         </is>
@@ -18338,13 +19632,18 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="E79" s="149" t="inlineStr">
-        <is>
-          <t>Sapphire Surge×2</t>
-        </is>
-      </c>
-      <c r="F79" s="149" t="n"/>
-      <c r="G79" s="2" t="inlineStr">
+      <c r="E79" s="143" t="inlineStr">
+        <is>
+          <t>Sapphire Surge</t>
+        </is>
+      </c>
+      <c r="F79" s="143" t="inlineStr">
+        <is>
+          <t>Sapphire Surge</t>
+        </is>
+      </c>
+      <c r="O79" s="149" t="n"/>
+      <c r="P79" s="2" t="inlineStr">
         <is>
           <t>aucun dégât/armure  (2 cartes/6 visées · 2 buff)</t>
         </is>
@@ -18371,13 +19670,23 @@
           <t>Epic</t>
         </is>
       </c>
-      <c r="E80" s="152" t="inlineStr">
-        <is>
-          <t>Perfect Sapphire Surge×3</t>
-        </is>
-      </c>
-      <c r="F80" s="152" t="n"/>
-      <c r="G80" s="2" t="inlineStr">
+      <c r="E80" s="143" t="inlineStr">
+        <is>
+          <t>Perfect Sapphire Surge</t>
+        </is>
+      </c>
+      <c r="F80" s="143" t="inlineStr">
+        <is>
+          <t>Perfect Sapphire Surge</t>
+        </is>
+      </c>
+      <c r="G80" s="143" t="inlineStr">
+        <is>
+          <t>Perfect Sapphire Surge</t>
+        </is>
+      </c>
+      <c r="O80" s="152" t="n"/>
+      <c r="P80" s="2" t="inlineStr">
         <is>
           <t>aucun dégât/armure  (3 cartes/7 visées · 3 buff)</t>
         </is>
@@ -18393,7 +19702,7 @@
       <c r="C81" s="48" t="n"/>
       <c r="D81" s="48" t="n"/>
       <c r="E81" s="48" t="n"/>
-      <c r="F81" s="48" t="n"/>
+      <c r="O81" s="48" t="n"/>
     </row>
     <row r="82" ht="15" customHeight="1" s="140">
       <c r="A82" s="142" t="inlineStr">
@@ -18418,11 +19727,16 @@
       </c>
       <c r="E82" s="143" t="inlineStr">
         <is>
-          <t>Gash×2</t>
-        </is>
-      </c>
-      <c r="F82" s="143" t="n"/>
-      <c r="G82" s="2" t="inlineStr">
+          <t>Gash</t>
+        </is>
+      </c>
+      <c r="F82" s="143" t="inlineStr">
+        <is>
+          <t>Gash</t>
+        </is>
+      </c>
+      <c r="O82" s="143" t="n"/>
+      <c r="P82" s="2" t="inlineStr">
         <is>
           <t>≈ 10 dégâts  (2 cartes/5 visées)</t>
         </is>
@@ -18451,11 +19765,16 @@
       </c>
       <c r="E83" s="143" t="inlineStr">
         <is>
-          <t>Ember×2</t>
-        </is>
-      </c>
-      <c r="F83" s="143" t="n"/>
-      <c r="G83" s="2" t="inlineStr">
+          <t>Ember</t>
+        </is>
+      </c>
+      <c r="F83" s="143" t="inlineStr">
+        <is>
+          <t>Ember</t>
+        </is>
+      </c>
+      <c r="O83" s="143" t="n"/>
+      <c r="P83" s="2" t="inlineStr">
         <is>
           <t>≈ 10 dégâts  (2 cartes/5 visées)</t>
         </is>
@@ -18484,11 +19803,16 @@
       </c>
       <c r="E84" s="143" t="inlineStr">
         <is>
-          <t>Ice Shard×2</t>
-        </is>
-      </c>
-      <c r="F84" s="143" t="n"/>
-      <c r="G84" s="2" t="inlineStr">
+          <t>Ice Shard</t>
+        </is>
+      </c>
+      <c r="F84" s="143" t="inlineStr">
+        <is>
+          <t>Ice Shard</t>
+        </is>
+      </c>
+      <c r="O84" s="143" t="n"/>
+      <c r="P84" s="2" t="inlineStr">
         <is>
           <t>≈ 10 dégâts  (2 cartes/5 visées)</t>
         </is>
@@ -18517,11 +19841,16 @@
       </c>
       <c r="E85" s="143" t="inlineStr">
         <is>
-          <t>Nimble Hands×2</t>
-        </is>
-      </c>
-      <c r="F85" s="143" t="n"/>
-      <c r="G85" s="2" t="inlineStr">
+          <t>Nimble Hands</t>
+        </is>
+      </c>
+      <c r="F85" s="143" t="inlineStr">
+        <is>
+          <t>Nimble Hands</t>
+        </is>
+      </c>
+      <c r="O85" s="143" t="n"/>
+      <c r="P85" s="2" t="inlineStr">
         <is>
           <t>aucun dégât/armure  (2 cartes/5 visées · 2 buff)</t>
         </is>
@@ -18550,11 +19879,16 @@
       </c>
       <c r="E86" s="143" t="inlineStr">
         <is>
-          <t>Flex×2</t>
-        </is>
-      </c>
-      <c r="F86" s="143" t="n"/>
-      <c r="G86" s="2" t="inlineStr">
+          <t>Flex</t>
+        </is>
+      </c>
+      <c r="F86" s="143" t="inlineStr">
+        <is>
+          <t>Flex</t>
+        </is>
+      </c>
+      <c r="O86" s="143" t="n"/>
+      <c r="P86" s="2" t="inlineStr">
         <is>
           <t>aucun dégât/armure  (2 cartes/5 visées · 2 buff)</t>
         </is>
@@ -18583,11 +19917,16 @@
       </c>
       <c r="E87" s="143" t="inlineStr">
         <is>
-          <t>Spark×2</t>
-        </is>
-      </c>
-      <c r="F87" s="143" t="n"/>
-      <c r="G87" s="2" t="inlineStr">
+          <t>Spark</t>
+        </is>
+      </c>
+      <c r="F87" s="143" t="inlineStr">
+        <is>
+          <t>Spark</t>
+        </is>
+      </c>
+      <c r="O87" s="143" t="n"/>
+      <c r="P87" s="2" t="inlineStr">
         <is>
           <t>aucun dégât/armure  (2 cartes/5 visées · 2 buff)</t>
         </is>
@@ -18616,11 +19955,16 @@
       </c>
       <c r="E88" s="143" t="inlineStr">
         <is>
-          <t>Iron Wall×2</t>
-        </is>
-      </c>
-      <c r="F88" s="143" t="n"/>
-      <c r="G88" s="2" t="inlineStr">
+          <t>Iron Wall</t>
+        </is>
+      </c>
+      <c r="F88" s="143" t="inlineStr">
+        <is>
+          <t>Iron Wall</t>
+        </is>
+      </c>
+      <c r="O88" s="143" t="n"/>
+      <c r="P88" s="2" t="inlineStr">
         <is>
           <t>≈ 8 armure  (2 cartes/5 visées)</t>
         </is>
@@ -18649,11 +19993,16 @@
       </c>
       <c r="E89" s="143" t="inlineStr">
         <is>
-          <t>Poison Dart×2</t>
-        </is>
-      </c>
-      <c r="F89" s="143" t="n"/>
-      <c r="G89" s="2" t="inlineStr">
+          <t>Poison Dart</t>
+        </is>
+      </c>
+      <c r="F89" s="143" t="inlineStr">
+        <is>
+          <t>Poison Dart</t>
+        </is>
+      </c>
+      <c r="O89" s="143" t="n"/>
+      <c r="P89" s="2" t="inlineStr">
         <is>
           <t>≈ 10 dégâts  (2 cartes/5 visées)</t>
         </is>
@@ -18682,11 +20031,16 @@
       </c>
       <c r="E90" s="143" t="inlineStr">
         <is>
-          <t>Regenerate×1, Guard×1</t>
-        </is>
-      </c>
-      <c r="F90" s="143" t="n"/>
-      <c r="G90" s="2" t="inlineStr">
+          <t>Regenerate</t>
+        </is>
+      </c>
+      <c r="F90" s="143" t="inlineStr">
+        <is>
+          <t>Guard</t>
+        </is>
+      </c>
+      <c r="O90" s="143" t="n"/>
+      <c r="P90" s="2" t="inlineStr">
         <is>
           <t>≈ 4 armure  (2 cartes/5 visées · 1 buff)</t>
         </is>
@@ -18713,13 +20067,18 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E91" s="146" t="inlineStr">
-        <is>
-          <t>Bloodletting×2</t>
-        </is>
-      </c>
-      <c r="F91" s="146" t="n"/>
-      <c r="G91" s="2" t="inlineStr">
+      <c r="E91" s="143" t="inlineStr">
+        <is>
+          <t>Bloodletting</t>
+        </is>
+      </c>
+      <c r="F91" s="143" t="inlineStr">
+        <is>
+          <t>Bloodletting</t>
+        </is>
+      </c>
+      <c r="O91" s="146" t="n"/>
+      <c r="P91" s="2" t="inlineStr">
         <is>
           <t>≈ 16 dégâts  (2 cartes/6 visées)</t>
         </is>
@@ -18746,13 +20105,18 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E92" s="146" t="inlineStr">
-        <is>
-          <t>Bloodthirst×1, Gash×1</t>
-        </is>
-      </c>
-      <c r="F92" s="146" t="n"/>
-      <c r="G92" s="2" t="inlineStr">
+      <c r="E92" s="143" t="inlineStr">
+        <is>
+          <t>Bloodthirst</t>
+        </is>
+      </c>
+      <c r="F92" s="143" t="inlineStr">
+        <is>
+          <t>Gash</t>
+        </is>
+      </c>
+      <c r="O92" s="146" t="n"/>
+      <c r="P92" s="2" t="inlineStr">
         <is>
           <t>≈ 13 dégâts  (2 cartes/6 visées)</t>
         </is>
@@ -18779,13 +20143,18 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E93" s="146" t="inlineStr">
-        <is>
-          <t>Overclock×1, Spark×1</t>
-        </is>
-      </c>
-      <c r="F93" s="146" t="n"/>
-      <c r="G93" s="2" t="inlineStr">
+      <c r="E93" s="143" t="inlineStr">
+        <is>
+          <t>Overclock</t>
+        </is>
+      </c>
+      <c r="F93" s="143" t="inlineStr">
+        <is>
+          <t>Spark</t>
+        </is>
+      </c>
+      <c r="O93" s="146" t="n"/>
+      <c r="P93" s="2" t="inlineStr">
         <is>
           <t>aucun dégât/armure  (2 cartes/6 visées · 2 buff)</t>
         </is>
@@ -18812,13 +20181,18 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E94" s="146" t="inlineStr">
-        <is>
-          <t>Frostbite×2</t>
-        </is>
-      </c>
-      <c r="F94" s="146" t="n"/>
-      <c r="G94" s="2" t="inlineStr">
+      <c r="E94" s="143" t="inlineStr">
+        <is>
+          <t>Frostbite</t>
+        </is>
+      </c>
+      <c r="F94" s="143" t="inlineStr">
+        <is>
+          <t>Frostbite</t>
+        </is>
+      </c>
+      <c r="O94" s="146" t="n"/>
+      <c r="P94" s="2" t="inlineStr">
         <is>
           <t>≈ 16 dégâts  (2 cartes/6 visées)</t>
         </is>
@@ -18845,13 +20219,18 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E95" s="146" t="inlineStr">
-        <is>
-          <t>Frost Nova×1, Ice Shard×1</t>
-        </is>
-      </c>
-      <c r="F95" s="146" t="n"/>
-      <c r="G95" s="2" t="inlineStr">
+      <c r="E95" s="143" t="inlineStr">
+        <is>
+          <t>Frost Nova</t>
+        </is>
+      </c>
+      <c r="F95" s="143" t="inlineStr">
+        <is>
+          <t>Ice Shard</t>
+        </is>
+      </c>
+      <c r="O95" s="146" t="n"/>
+      <c r="P95" s="2" t="inlineStr">
         <is>
           <t>≈ 21 dégâts  (2 cartes/6 visées)</t>
         </is>
@@ -18878,13 +20257,18 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E96" s="146" t="inlineStr">
-        <is>
-          <t>Iron Wall×2</t>
-        </is>
-      </c>
-      <c r="F96" s="146" t="n"/>
-      <c r="G96" s="2" t="inlineStr">
+      <c r="E96" s="143" t="inlineStr">
+        <is>
+          <t>Iron Wall</t>
+        </is>
+      </c>
+      <c r="F96" s="143" t="inlineStr">
+        <is>
+          <t>Iron Wall</t>
+        </is>
+      </c>
+      <c r="O96" s="146" t="n"/>
+      <c r="P96" s="2" t="inlineStr">
         <is>
           <t>≈ 8 armure  (2 cartes/6 visées)</t>
         </is>
@@ -18911,13 +20295,18 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E97" s="146" t="inlineStr">
-        <is>
-          <t>Empower×1, Flex×1</t>
-        </is>
-      </c>
-      <c r="F97" s="146" t="n"/>
-      <c r="G97" s="2" t="inlineStr">
+      <c r="E97" s="143" t="inlineStr">
+        <is>
+          <t>Empower</t>
+        </is>
+      </c>
+      <c r="F97" s="143" t="inlineStr">
+        <is>
+          <t>Flex</t>
+        </is>
+      </c>
+      <c r="O97" s="146" t="n"/>
+      <c r="P97" s="2" t="inlineStr">
         <is>
           <t>aucun dégât/armure  (2 cartes/6 visées · 2 buff)</t>
         </is>
@@ -18944,13 +20333,18 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E98" s="146" t="inlineStr">
-        <is>
-          <t>Venom Nova×1, Poison Dart×1</t>
-        </is>
-      </c>
-      <c r="F98" s="146" t="n"/>
-      <c r="G98" s="2" t="inlineStr">
+      <c r="E98" s="143" t="inlineStr">
+        <is>
+          <t>Venom Nova</t>
+        </is>
+      </c>
+      <c r="F98" s="143" t="inlineStr">
+        <is>
+          <t>Poison Dart</t>
+        </is>
+      </c>
+      <c r="O98" s="146" t="n"/>
+      <c r="P98" s="2" t="inlineStr">
         <is>
           <t>≈ 21 dégâts  (2 cartes/6 visées)</t>
         </is>
@@ -18977,13 +20371,18 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="E99" s="149" t="inlineStr">
-        <is>
-          <t>Frost Cascade×2</t>
-        </is>
-      </c>
-      <c r="F99" s="149" t="n"/>
-      <c r="G99" s="2" t="inlineStr">
+      <c r="E99" s="143" t="inlineStr">
+        <is>
+          <t>Frost Cascade</t>
+        </is>
+      </c>
+      <c r="F99" s="143" t="inlineStr">
+        <is>
+          <t>Frost Cascade</t>
+        </is>
+      </c>
+      <c r="O99" s="149" t="n"/>
+      <c r="P99" s="2" t="inlineStr">
         <is>
           <t>≈ 48 dégâts  (2 cartes/6 visées)</t>
         </is>
@@ -19010,17 +20409,13 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="E100" s="149" t="inlineStr">
-        <is>
-          <t>(cartes à venir)</t>
-        </is>
-      </c>
-      <c r="F100" s="149" t="inlineStr">
+      <c r="E100" s="149" t="n"/>
+      <c r="O100" s="149" t="inlineStr">
         <is>
           <t>50% de doubler le butin d'un coup de minage (souterrains)</t>
         </is>
       </c>
-      <c r="G100" s="2" t="n"/>
+      <c r="P100" s="2" t="n"/>
     </row>
     <row r="101" ht="15" customHeight="1" s="140">
       <c r="A101" s="47" t="inlineStr">
@@ -19032,7 +20427,7 @@
       <c r="C101" s="48" t="n"/>
       <c r="D101" s="48" t="n"/>
       <c r="E101" s="48" t="n"/>
-      <c r="F101" s="48" t="n"/>
+      <c r="O101" s="48" t="n"/>
     </row>
     <row r="102" ht="15" customHeight="1" s="140">
       <c r="A102" s="142" t="inlineStr">
@@ -19057,11 +20452,16 @@
       </c>
       <c r="E102" s="143" t="inlineStr">
         <is>
-          <t>Nimble Hands×2</t>
-        </is>
-      </c>
-      <c r="F102" s="143" t="n"/>
-      <c r="G102" s="2" t="inlineStr">
+          <t>Nimble Hands</t>
+        </is>
+      </c>
+      <c r="F102" s="143" t="inlineStr">
+        <is>
+          <t>Nimble Hands</t>
+        </is>
+      </c>
+      <c r="O102" s="143" t="n"/>
+      <c r="P102" s="2" t="inlineStr">
         <is>
           <t>aucun dégât/armure  (2 cartes/5 visées · 2 buff)</t>
         </is>
@@ -19090,11 +20490,16 @@
       </c>
       <c r="E103" s="143" t="inlineStr">
         <is>
-          <t>Nimble Hands×1, Guard×1</t>
-        </is>
-      </c>
-      <c r="F103" s="143" t="n"/>
-      <c r="G103" s="2" t="inlineStr">
+          <t>Nimble Hands</t>
+        </is>
+      </c>
+      <c r="F103" s="143" t="inlineStr">
+        <is>
+          <t>Guard</t>
+        </is>
+      </c>
+      <c r="O103" s="143" t="n"/>
+      <c r="P103" s="2" t="inlineStr">
         <is>
           <t>≈ 4 armure  (2 cartes/5 visées · 1 buff)</t>
         </is>
@@ -19123,11 +20528,16 @@
       </c>
       <c r="E104" s="143" t="inlineStr">
         <is>
-          <t>Master's Hand×2</t>
-        </is>
-      </c>
-      <c r="F104" s="143" t="n"/>
-      <c r="G104" s="2" t="inlineStr">
+          <t>Master's Hand</t>
+        </is>
+      </c>
+      <c r="F104" s="143" t="inlineStr">
+        <is>
+          <t>Master's Hand</t>
+        </is>
+      </c>
+      <c r="O104" s="143" t="n"/>
+      <c r="P104" s="2" t="inlineStr">
         <is>
           <t>aucun dégât/armure  (2 cartes/5 visées · 2 buff)</t>
         </is>
@@ -19156,11 +20566,16 @@
       </c>
       <c r="E105" s="143" t="inlineStr">
         <is>
-          <t>Strike×1, Gash×1</t>
-        </is>
-      </c>
-      <c r="F105" s="143" t="n"/>
-      <c r="G105" s="2" t="inlineStr">
+          <t>Strike</t>
+        </is>
+      </c>
+      <c r="F105" s="143" t="inlineStr">
+        <is>
+          <t>Gash</t>
+        </is>
+      </c>
+      <c r="O105" s="143" t="n"/>
+      <c r="P105" s="2" t="inlineStr">
         <is>
           <t>≈ 10 dégâts  (2 cartes/5 visées)</t>
         </is>
@@ -19189,11 +20604,16 @@
       </c>
       <c r="E106" s="143" t="inlineStr">
         <is>
-          <t>Master's Hand×1, Strike×1</t>
-        </is>
-      </c>
-      <c r="F106" s="143" t="n"/>
-      <c r="G106" s="2" t="inlineStr">
+          <t>Master's Hand</t>
+        </is>
+      </c>
+      <c r="F106" s="143" t="inlineStr">
+        <is>
+          <t>Strike</t>
+        </is>
+      </c>
+      <c r="O106" s="143" t="n"/>
+      <c r="P106" s="2" t="inlineStr">
         <is>
           <t>≈ 5 dégâts  (2 cartes/5 visées · 1 buff)</t>
         </is>
@@ -19220,13 +20640,18 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E107" s="146" t="inlineStr">
-        <is>
-          <t>Power Strike×1, Guard×1</t>
-        </is>
-      </c>
-      <c r="F107" s="146" t="n"/>
-      <c r="G107" s="2" t="inlineStr">
+      <c r="E107" s="143" t="inlineStr">
+        <is>
+          <t>Power Strike</t>
+        </is>
+      </c>
+      <c r="F107" s="143" t="inlineStr">
+        <is>
+          <t>Guard</t>
+        </is>
+      </c>
+      <c r="O107" s="146" t="n"/>
+      <c r="P107" s="2" t="inlineStr">
         <is>
           <t>≈ 16 dégâts  ·  ≈ 4 armure  (2 cartes/6 visées)</t>
         </is>
@@ -19253,13 +20678,23 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E108" s="146" t="inlineStr">
-        <is>
-          <t>Roll 1 Dice×1, Roll 2 Dice×1, Lucky Draw×1</t>
-        </is>
-      </c>
-      <c r="F108" s="146" t="n"/>
-      <c r="G108" s="2" t="inlineStr">
+      <c r="E108" s="143" t="inlineStr">
+        <is>
+          <t>Roll 1 Dice</t>
+        </is>
+      </c>
+      <c r="F108" s="143" t="inlineStr">
+        <is>
+          <t>Roll 2 Dice</t>
+        </is>
+      </c>
+      <c r="G108" s="143" t="inlineStr">
+        <is>
+          <t>Lucky Draw</t>
+        </is>
+      </c>
+      <c r="O108" s="146" t="n"/>
+      <c r="P108" s="2" t="inlineStr">
         <is>
           <t>aucun dégât/armure  (3 cartes/6 visées · 3 buff)</t>
         </is>
@@ -19286,17 +20721,37 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E109" s="146" t="inlineStr">
-        <is>
-          <t>Stone×3, Many Stone×1, Pebble Sale×1</t>
-        </is>
-      </c>
-      <c r="F109" s="146" t="inlineStr">
+      <c r="E109" s="143" t="inlineStr">
+        <is>
+          <t>Stone</t>
+        </is>
+      </c>
+      <c r="F109" s="143" t="inlineStr">
+        <is>
+          <t>Stone</t>
+        </is>
+      </c>
+      <c r="G109" s="143" t="inlineStr">
+        <is>
+          <t>Stone</t>
+        </is>
+      </c>
+      <c r="H109" s="143" t="inlineStr">
+        <is>
+          <t>Many Stone</t>
+        </is>
+      </c>
+      <c r="I109" s="143" t="inlineStr">
+        <is>
+          <t>Pebble Sale</t>
+        </is>
+      </c>
+      <c r="O109" s="146" t="inlineStr">
         <is>
           <t>Set: Stone Age Set</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr">
+      <c r="P109" s="2" t="inlineStr">
         <is>
           <t>≈ 36 armure  (5 cartes/6 visées · 1 buff)</t>
         </is>
@@ -19323,13 +20778,18 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E110" s="146" t="inlineStr">
-        <is>
-          <t>Sleight×1, Gimme That×1</t>
-        </is>
-      </c>
-      <c r="F110" s="146" t="n"/>
-      <c r="G110" s="2" t="inlineStr">
+      <c r="E110" s="143" t="inlineStr">
+        <is>
+          <t>Sleight</t>
+        </is>
+      </c>
+      <c r="F110" s="143" t="inlineStr">
+        <is>
+          <t>Gimme That</t>
+        </is>
+      </c>
+      <c r="O110" s="146" t="n"/>
+      <c r="P110" s="2" t="inlineStr">
         <is>
           <t>aucun dégât/armure  (2 cartes/6 visées · 2 buff)</t>
         </is>
@@ -19356,13 +20816,18 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E111" s="146" t="inlineStr">
-        <is>
-          <t>Poison Coat×1, Poison Dart×1</t>
-        </is>
-      </c>
-      <c r="F111" s="146" t="n"/>
-      <c r="G111" s="2" t="inlineStr">
+      <c r="E111" s="143" t="inlineStr">
+        <is>
+          <t>Poison Coat</t>
+        </is>
+      </c>
+      <c r="F111" s="143" t="inlineStr">
+        <is>
+          <t>Poison Dart</t>
+        </is>
+      </c>
+      <c r="O111" s="146" t="n"/>
+      <c r="P111" s="2" t="inlineStr">
         <is>
           <t>≈ 10 dégâts  (2 cartes/6 visées)</t>
         </is>
@@ -19389,17 +20854,37 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="E112" s="149" t="inlineStr">
-        <is>
-          <t>Open Veins×2, Contagion×2, Blood Absorption×1</t>
-        </is>
-      </c>
-      <c r="F112" s="149" t="inlineStr">
+      <c r="E112" s="143" t="inlineStr">
+        <is>
+          <t>Open Veins</t>
+        </is>
+      </c>
+      <c r="F112" s="143" t="inlineStr">
+        <is>
+          <t>Open Veins</t>
+        </is>
+      </c>
+      <c r="G112" s="143" t="inlineStr">
+        <is>
+          <t>Contagion</t>
+        </is>
+      </c>
+      <c r="H112" s="143" t="inlineStr">
+        <is>
+          <t>Contagion</t>
+        </is>
+      </c>
+      <c r="I112" s="143" t="inlineStr">
+        <is>
+          <t>Blood Absorption</t>
+        </is>
+      </c>
+      <c r="O112" s="149" t="inlineStr">
         <is>
           <t>Set: Blood Set</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr">
+      <c r="P112" s="2" t="inlineStr">
         <is>
           <t>≈ 72 dégâts  (5 cartes/6 visées · 1 buff)</t>
         </is>
@@ -19426,17 +20911,37 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="E113" s="149" t="inlineStr">
-        <is>
-          <t>Master's Hand×2, Halo Burst×1, Lay on Hands×2</t>
-        </is>
-      </c>
-      <c r="F113" s="149" t="inlineStr">
+      <c r="E113" s="143" t="inlineStr">
+        <is>
+          <t>Master's Hand</t>
+        </is>
+      </c>
+      <c r="F113" s="143" t="inlineStr">
+        <is>
+          <t>Master's Hand</t>
+        </is>
+      </c>
+      <c r="G113" s="143" t="inlineStr">
+        <is>
+          <t>Halo Burst</t>
+        </is>
+      </c>
+      <c r="H113" s="143" t="inlineStr">
+        <is>
+          <t>Lay on Hands</t>
+        </is>
+      </c>
+      <c r="I113" s="143" t="inlineStr">
+        <is>
+          <t>Lay on Hands</t>
+        </is>
+      </c>
+      <c r="O113" s="149" t="inlineStr">
         <is>
           <t>Set: Crusader Set</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr">
+      <c r="P113" s="2" t="inlineStr">
         <is>
           <t>≈ 12 dégâts  (5 cartes/6 visées · 4 buff)</t>
         </is>
@@ -19463,17 +20968,42 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="E114" s="149" t="inlineStr">
-        <is>
-          <t>Maul Swing×2, Whirlwind×2, Bloodlust×2</t>
-        </is>
-      </c>
-      <c r="F114" s="149" t="inlineStr">
+      <c r="E114" s="143" t="inlineStr">
+        <is>
+          <t>Maul Swing</t>
+        </is>
+      </c>
+      <c r="F114" s="143" t="inlineStr">
+        <is>
+          <t>Maul Swing</t>
+        </is>
+      </c>
+      <c r="G114" s="143" t="inlineStr">
+        <is>
+          <t>Whirlwind</t>
+        </is>
+      </c>
+      <c r="H114" s="143" t="inlineStr">
+        <is>
+          <t>Whirlwind</t>
+        </is>
+      </c>
+      <c r="I114" s="143" t="inlineStr">
+        <is>
+          <t>Bloodlust</t>
+        </is>
+      </c>
+      <c r="J114" s="143" t="inlineStr">
+        <is>
+          <t>Bloodlust</t>
+        </is>
+      </c>
+      <c r="O114" s="149" t="inlineStr">
         <is>
           <t>Set: Barbarian Set</t>
         </is>
       </c>
-      <c r="G114" s="2" t="n"/>
+      <c r="P114" s="2" t="n"/>
     </row>
     <row r="115" ht="15" customHeight="1" s="140">
       <c r="A115" s="148" t="inlineStr">
@@ -19496,17 +21026,37 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="E115" s="149" t="inlineStr">
-        <is>
-          <t>Master's Hand×2, Outnumbered×2, Mail Advantage×1</t>
-        </is>
-      </c>
-      <c r="F115" s="149" t="inlineStr">
+      <c r="E115" s="143" t="inlineStr">
+        <is>
+          <t>Master's Hand</t>
+        </is>
+      </c>
+      <c r="F115" s="143" t="inlineStr">
+        <is>
+          <t>Master's Hand</t>
+        </is>
+      </c>
+      <c r="G115" s="143" t="inlineStr">
+        <is>
+          <t>Outnumbered</t>
+        </is>
+      </c>
+      <c r="H115" s="143" t="inlineStr">
+        <is>
+          <t>Outnumbered</t>
+        </is>
+      </c>
+      <c r="I115" s="143" t="inlineStr">
+        <is>
+          <t>Mail Advantage</t>
+        </is>
+      </c>
+      <c r="O115" s="149" t="inlineStr">
         <is>
           <t>Set: Mail Set</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr">
+      <c r="P115" s="2" t="inlineStr">
         <is>
           <t>aucun dégât/armure  (5 cartes/6 visées · 5 buff)</t>
         </is>
@@ -19533,17 +21083,47 @@
           <t>Épique</t>
         </is>
       </c>
-      <c r="E116" s="152" t="inlineStr">
-        <is>
-          <t>Judgement×2, Hammer of Light×2, Sentence×2, Skyfall Hammer×1</t>
-        </is>
-      </c>
-      <c r="F116" s="152" t="inlineStr">
+      <c r="E116" s="143" t="inlineStr">
+        <is>
+          <t>Judgement</t>
+        </is>
+      </c>
+      <c r="F116" s="143" t="inlineStr">
+        <is>
+          <t>Judgement</t>
+        </is>
+      </c>
+      <c r="G116" s="143" t="inlineStr">
+        <is>
+          <t>Hammer of Light</t>
+        </is>
+      </c>
+      <c r="H116" s="143" t="inlineStr">
+        <is>
+          <t>Hammer of Light</t>
+        </is>
+      </c>
+      <c r="I116" s="143" t="inlineStr">
+        <is>
+          <t>Sentence</t>
+        </is>
+      </c>
+      <c r="J116" s="143" t="inlineStr">
+        <is>
+          <t>Sentence</t>
+        </is>
+      </c>
+      <c r="K116" s="143" t="inlineStr">
+        <is>
+          <t>Skyfall Hammer</t>
+        </is>
+      </c>
+      <c r="O116" s="152" t="inlineStr">
         <is>
           <t>Craft: pierre solaire + or + mithril  ·  Set: Dunir's Blessing</t>
         </is>
       </c>
-      <c r="G116" s="2" t="n"/>
+      <c r="P116" s="2" t="n"/>
     </row>
     <row r="117" ht="17.1" customHeight="1" s="140">
       <c r="A117" s="151" t="inlineStr">
@@ -19566,17 +21146,42 @@
           <t>Epic</t>
         </is>
       </c>
-      <c r="E117" s="152" t="inlineStr">
-        <is>
-          <t>Burning Hand×2, Onyx Fist×2, Forge from Ashes×2</t>
-        </is>
-      </c>
-      <c r="F117" s="152" t="inlineStr">
+      <c r="E117" s="143" t="inlineStr">
+        <is>
+          <t>Burning Hand</t>
+        </is>
+      </c>
+      <c r="F117" s="143" t="inlineStr">
+        <is>
+          <t>Burning Hand</t>
+        </is>
+      </c>
+      <c r="G117" s="143" t="inlineStr">
+        <is>
+          <t>Onyx Fist</t>
+        </is>
+      </c>
+      <c r="H117" s="143" t="inlineStr">
+        <is>
+          <t>Onyx Fist</t>
+        </is>
+      </c>
+      <c r="I117" s="143" t="inlineStr">
+        <is>
+          <t>Forge from Ashes</t>
+        </is>
+      </c>
+      <c r="J117" s="143" t="inlineStr">
+        <is>
+          <t>Forge from Ashes</t>
+        </is>
+      </c>
+      <c r="O117" s="152" t="inlineStr">
         <is>
           <t>Set: Onyx Set</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr">
+      <c r="P117" s="2" t="inlineStr">
         <is>
           <t>≈ 34 dégâts  (6 cartes/7 visées · 4 buff)</t>
         </is>
@@ -19592,7 +21197,7 @@
       <c r="C118" s="48" t="n"/>
       <c r="D118" s="48" t="n"/>
       <c r="E118" s="48" t="n"/>
-      <c r="F118" s="48" t="n"/>
+      <c r="O118" s="48" t="n"/>
     </row>
     <row r="119" ht="15" customHeight="1" s="140">
       <c r="A119" s="142" t="inlineStr">
@@ -19617,15 +21222,20 @@
       </c>
       <c r="E119" s="143" t="inlineStr">
         <is>
-          <t>Acceleration×2</t>
-        </is>
-      </c>
-      <c r="F119" s="144" t="inlineStr">
+          <t>Acceleration</t>
+        </is>
+      </c>
+      <c r="F119" s="143" t="inlineStr">
+        <is>
+          <t>Acceleration</t>
+        </is>
+      </c>
+      <c r="O119" s="144" t="inlineStr">
         <is>
           <t>+30 Agilité  ·  +10% déplacement</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr">
+      <c r="P119" s="2" t="inlineStr">
         <is>
           <t>aucun dégât/armure  (2 cartes/5 visées · 2 buff)</t>
         </is>
@@ -19654,15 +21264,20 @@
       </c>
       <c r="E120" s="143" t="inlineStr">
         <is>
-          <t>Acceleration×1, Fresh Wind×1</t>
-        </is>
-      </c>
-      <c r="F120" s="144" t="inlineStr">
+          <t>Acceleration</t>
+        </is>
+      </c>
+      <c r="F120" s="143" t="inlineStr">
+        <is>
+          <t>Fresh Wind</t>
+        </is>
+      </c>
+      <c r="O120" s="144" t="inlineStr">
         <is>
           <t>+20 Agilité  ·  +8% déplacement</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr">
+      <c r="P120" s="2" t="inlineStr">
         <is>
           <t>aucun dégât/armure  (2 cartes/5 visées · 2 buff)</t>
         </is>
@@ -19691,15 +21306,20 @@
       </c>
       <c r="E121" s="143" t="inlineStr">
         <is>
-          <t>Acceleration×1, Long Run×1</t>
-        </is>
-      </c>
-      <c r="F121" s="144" t="inlineStr">
+          <t>Acceleration</t>
+        </is>
+      </c>
+      <c r="F121" s="143" t="inlineStr">
+        <is>
+          <t>Long Run</t>
+        </is>
+      </c>
+      <c r="O121" s="144" t="inlineStr">
         <is>
           <t>+30 Agilité  ·  +15% déplacement</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr">
+      <c r="P121" s="2" t="inlineStr">
         <is>
           <t>aucun dégât/armure  (2 cartes/5 visées · 2 buff)</t>
         </is>
@@ -19728,15 +21348,15 @@
       </c>
       <c r="E122" s="143" t="inlineStr">
         <is>
-          <t>Acceleration×1</t>
-        </is>
-      </c>
-      <c r="F122" s="144" t="inlineStr">
+          <t>Acceleration</t>
+        </is>
+      </c>
+      <c r="O122" s="144" t="inlineStr">
         <is>
           <t>+10 Agilité  ·  +5% déplacement</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr">
+      <c r="P122" s="2" t="inlineStr">
         <is>
           <t>aucun dégât/armure  (1 carte/5 visées · 1 buff)</t>
         </is>
@@ -19763,17 +21383,22 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E123" s="146" t="inlineStr">
-        <is>
-          <t>Ember×1, Quicken×1</t>
-        </is>
-      </c>
-      <c r="F123" s="147" t="inlineStr">
+      <c r="E123" s="143" t="inlineStr">
+        <is>
+          <t>Ember</t>
+        </is>
+      </c>
+      <c r="F123" s="143" t="inlineStr">
+        <is>
+          <t>Quicken</t>
+        </is>
+      </c>
+      <c r="O123" s="147" t="inlineStr">
         <is>
           <t>+60 Agilité  ·  +15% déplacement</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr">
+      <c r="P123" s="2" t="inlineStr">
         <is>
           <t>≈ 5 dégâts  (2 cartes/6 visées · 1 buff)</t>
         </is>
@@ -19800,17 +21425,37 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E124" s="146" t="inlineStr">
-        <is>
-          <t>Stone×3, Many Stone×1, Melt Stones×1</t>
-        </is>
-      </c>
-      <c r="F124" s="147" t="inlineStr">
+      <c r="E124" s="143" t="inlineStr">
+        <is>
+          <t>Stone</t>
+        </is>
+      </c>
+      <c r="F124" s="143" t="inlineStr">
+        <is>
+          <t>Stone</t>
+        </is>
+      </c>
+      <c r="G124" s="143" t="inlineStr">
+        <is>
+          <t>Stone</t>
+        </is>
+      </c>
+      <c r="H124" s="143" t="inlineStr">
+        <is>
+          <t>Many Stone</t>
+        </is>
+      </c>
+      <c r="I124" s="143" t="inlineStr">
+        <is>
+          <t>Melt Stones</t>
+        </is>
+      </c>
+      <c r="O124" s="147" t="inlineStr">
         <is>
           <t>+30 Agilité  ·  +6% déplacement  ·  Set: Stone Age Set</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr">
+      <c r="P124" s="2" t="inlineStr">
         <is>
           <t>≈ 36 armure  (5 cartes/6 visées · 1 buff)</t>
         </is>
@@ -19837,17 +21482,22 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E125" s="146" t="inlineStr">
-        <is>
-          <t>Stone Fist×1, Guard×1</t>
-        </is>
-      </c>
-      <c r="F125" s="147" t="inlineStr">
+      <c r="E125" s="143" t="inlineStr">
+        <is>
+          <t>Stone Fist</t>
+        </is>
+      </c>
+      <c r="F125" s="143" t="inlineStr">
+        <is>
+          <t>Guard</t>
+        </is>
+      </c>
+      <c r="O125" s="147" t="inlineStr">
         <is>
           <t>+50 Agilité  ·  +8% déplacement</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr">
+      <c r="P125" s="2" t="inlineStr">
         <is>
           <t>≈ 24 dégâts  ·  ≈ 4 armure  (2 cartes/6 visées)</t>
         </is>
@@ -19874,17 +21524,32 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E126" s="146" t="inlineStr">
-        <is>
-          <t>Quicken×3, Second breath×1</t>
-        </is>
-      </c>
-      <c r="F126" s="147" t="inlineStr">
+      <c r="E126" s="143" t="inlineStr">
+        <is>
+          <t>Quicken</t>
+        </is>
+      </c>
+      <c r="F126" s="143" t="inlineStr">
+        <is>
+          <t>Quicken</t>
+        </is>
+      </c>
+      <c r="G126" s="143" t="inlineStr">
+        <is>
+          <t>Quicken</t>
+        </is>
+      </c>
+      <c r="H126" s="143" t="inlineStr">
+        <is>
+          <t>Second breath</t>
+        </is>
+      </c>
+      <c r="O126" s="147" t="inlineStr">
         <is>
           <t>+100 Agilité  ·  +20% déplacement</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr">
+      <c r="P126" s="2" t="inlineStr">
         <is>
           <t>aucun dégât/armure  (4 cartes/6 visées · 4 buff)</t>
         </is>
@@ -19911,17 +21576,22 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E127" s="146" t="inlineStr">
-        <is>
-          <t>Dash×1, Quicken×1</t>
-        </is>
-      </c>
-      <c r="F127" s="147" t="inlineStr">
+      <c r="E127" s="143" t="inlineStr">
+        <is>
+          <t>Dash</t>
+        </is>
+      </c>
+      <c r="F127" s="143" t="inlineStr">
+        <is>
+          <t>Quicken</t>
+        </is>
+      </c>
+      <c r="O127" s="147" t="inlineStr">
         <is>
           <t>+80 Agilité  ·  +30% déplacement</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr">
+      <c r="P127" s="2" t="inlineStr">
         <is>
           <t>aucun dégât/armure  (2 cartes/6 visées · 2 buff)</t>
         </is>
@@ -19948,17 +21618,37 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="E128" s="149" t="inlineStr">
-        <is>
-          <t>Blood Slide×1, Blood Rush×2, Quicken×1, Boost×1</t>
-        </is>
-      </c>
-      <c r="F128" s="150" t="inlineStr">
+      <c r="E128" s="143" t="inlineStr">
+        <is>
+          <t>Blood Slide</t>
+        </is>
+      </c>
+      <c r="F128" s="143" t="inlineStr">
+        <is>
+          <t>Blood Rush</t>
+        </is>
+      </c>
+      <c r="G128" s="143" t="inlineStr">
+        <is>
+          <t>Blood Rush</t>
+        </is>
+      </c>
+      <c r="H128" s="143" t="inlineStr">
+        <is>
+          <t>Quicken</t>
+        </is>
+      </c>
+      <c r="I128" s="143" t="inlineStr">
+        <is>
+          <t>Boost</t>
+        </is>
+      </c>
+      <c r="O128" s="150" t="inlineStr">
         <is>
           <t>+140 Agilité  ·  +25% déplacement  ·  Set: Blood Set</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr">
+      <c r="P128" s="2" t="inlineStr">
         <is>
           <t>≈ 24 dégâts  (5 cartes/6 visées · 4 buff)</t>
         </is>
@@ -19985,17 +21675,37 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="E129" s="149" t="inlineStr">
-        <is>
-          <t>Quicken×1, Kick of light×2, Boost×2</t>
-        </is>
-      </c>
-      <c r="F129" s="150" t="inlineStr">
+      <c r="E129" s="143" t="inlineStr">
+        <is>
+          <t>Quicken</t>
+        </is>
+      </c>
+      <c r="F129" s="143" t="inlineStr">
+        <is>
+          <t>Kick of light</t>
+        </is>
+      </c>
+      <c r="G129" s="143" t="inlineStr">
+        <is>
+          <t>Kick of light</t>
+        </is>
+      </c>
+      <c r="H129" s="143" t="inlineStr">
+        <is>
+          <t>Boost</t>
+        </is>
+      </c>
+      <c r="I129" s="143" t="inlineStr">
+        <is>
+          <t>Boost</t>
+        </is>
+      </c>
+      <c r="O129" s="150" t="inlineStr">
         <is>
           <t>+120 Agilité  ·  +25% déplacement  ·  Set: Crusader Set</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr">
+      <c r="P129" s="2" t="inlineStr">
         <is>
           <t>≈ 24 dégâts  (5 cartes/6 visées · 3 buff)</t>
         </is>
@@ -20022,17 +21732,42 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="E130" s="149" t="inlineStr">
-        <is>
-          <t>Stomp×2, Reckless Charge×2, War Cry×1, Boost×1</t>
-        </is>
-      </c>
-      <c r="F130" s="149" t="inlineStr">
+      <c r="E130" s="143" t="inlineStr">
+        <is>
+          <t>Stomp</t>
+        </is>
+      </c>
+      <c r="F130" s="143" t="inlineStr">
+        <is>
+          <t>Stomp</t>
+        </is>
+      </c>
+      <c r="G130" s="143" t="inlineStr">
+        <is>
+          <t>Reckless Charge</t>
+        </is>
+      </c>
+      <c r="H130" s="143" t="inlineStr">
+        <is>
+          <t>Reckless Charge</t>
+        </is>
+      </c>
+      <c r="I130" s="143" t="inlineStr">
+        <is>
+          <t>War Cry</t>
+        </is>
+      </c>
+      <c r="J130" s="143" t="inlineStr">
+        <is>
+          <t>Boost</t>
+        </is>
+      </c>
+      <c r="O130" s="149" t="inlineStr">
         <is>
           <t>+140 Agilité  ·  +20% déplacement  ·  Set: Barbarian Set</t>
         </is>
       </c>
-      <c r="G130" s="2" t="n"/>
+      <c r="P130" s="2" t="n"/>
     </row>
     <row r="131" ht="15" customHeight="1" s="140">
       <c r="A131" s="148" t="inlineStr">
@@ -20055,17 +21790,37 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="E131" s="149" t="inlineStr">
-        <is>
-          <t>Quicken×2, Mail Advantage×1, Boost×2</t>
-        </is>
-      </c>
-      <c r="F131" s="150" t="inlineStr">
+      <c r="E131" s="143" t="inlineStr">
+        <is>
+          <t>Quicken</t>
+        </is>
+      </c>
+      <c r="F131" s="143" t="inlineStr">
+        <is>
+          <t>Quicken</t>
+        </is>
+      </c>
+      <c r="G131" s="143" t="inlineStr">
+        <is>
+          <t>Mail Advantage</t>
+        </is>
+      </c>
+      <c r="H131" s="143" t="inlineStr">
+        <is>
+          <t>Boost</t>
+        </is>
+      </c>
+      <c r="I131" s="143" t="inlineStr">
+        <is>
+          <t>Boost</t>
+        </is>
+      </c>
+      <c r="O131" s="150" t="inlineStr">
         <is>
           <t>+100 Agilité  ·  +15% déplacement  ·  Set: Mail Set</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr">
+      <c r="P131" s="2" t="inlineStr">
         <is>
           <t>aucun dégât/armure  (5 cartes/6 visées · 5 buff)</t>
         </is>
@@ -20092,17 +21847,47 @@
           <t>Épique</t>
         </is>
       </c>
-      <c r="E132" s="152" t="inlineStr">
-        <is>
-          <t>Golden Dawn×2, Judgement×2, Hammer of Light×1, Gilded Guard×1, Boost×1</t>
-        </is>
-      </c>
-      <c r="F132" s="152" t="inlineStr">
+      <c r="E132" s="143" t="inlineStr">
+        <is>
+          <t>Golden Dawn</t>
+        </is>
+      </c>
+      <c r="F132" s="143" t="inlineStr">
+        <is>
+          <t>Golden Dawn</t>
+        </is>
+      </c>
+      <c r="G132" s="143" t="inlineStr">
+        <is>
+          <t>Judgement</t>
+        </is>
+      </c>
+      <c r="H132" s="143" t="inlineStr">
+        <is>
+          <t>Judgement</t>
+        </is>
+      </c>
+      <c r="I132" s="143" t="inlineStr">
+        <is>
+          <t>Hammer of Light</t>
+        </is>
+      </c>
+      <c r="J132" s="143" t="inlineStr">
+        <is>
+          <t>Gilded Guard</t>
+        </is>
+      </c>
+      <c r="K132" s="143" t="inlineStr">
+        <is>
+          <t>Boost</t>
+        </is>
+      </c>
+      <c r="O132" s="152" t="inlineStr">
         <is>
           <t>+160 Agilité  ·  +30% déplacement  ·  Craft: pierre solaire + or + mithril  ·  Set: Dunir's Blessing</t>
         </is>
       </c>
-      <c r="G132" s="2" t="n"/>
+      <c r="P132" s="2" t="n"/>
     </row>
     <row r="133" ht="17.1" customHeight="1" s="140">
       <c r="A133" s="151" t="inlineStr">
@@ -20125,17 +21910,42 @@
           <t>Epic</t>
         </is>
       </c>
-      <c r="E133" s="152" t="inlineStr">
-        <is>
-          <t>Burning Run×1, Flaming Kick×1, Fire Boost×2, Boost×2</t>
-        </is>
-      </c>
-      <c r="F133" s="153" t="inlineStr">
+      <c r="E133" s="143" t="inlineStr">
+        <is>
+          <t>Burning Run</t>
+        </is>
+      </c>
+      <c r="F133" s="143" t="inlineStr">
+        <is>
+          <t>Flaming Kick</t>
+        </is>
+      </c>
+      <c r="G133" s="143" t="inlineStr">
+        <is>
+          <t>Fire Boost</t>
+        </is>
+      </c>
+      <c r="H133" s="143" t="inlineStr">
+        <is>
+          <t>Fire Boost</t>
+        </is>
+      </c>
+      <c r="I133" s="143" t="inlineStr">
+        <is>
+          <t>Boost</t>
+        </is>
+      </c>
+      <c r="J133" s="143" t="inlineStr">
+        <is>
+          <t>Boost</t>
+        </is>
+      </c>
+      <c r="O133" s="153" t="inlineStr">
         <is>
           <t>+200 Agilité  ·  +40% déplacement  ·  Set: Onyx Set</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr">
+      <c r="P133" s="2" t="inlineStr">
         <is>
           <t>aucun dégât/armure  (6 cartes/7 visées · 6 buff)</t>
         </is>
@@ -20151,7 +21961,7 @@
       <c r="C134" s="48" t="n"/>
       <c r="D134" s="48" t="n"/>
       <c r="E134" s="48" t="n"/>
-      <c r="F134" s="48" t="n"/>
+      <c r="O134" s="48" t="n"/>
     </row>
     <row r="135" ht="15" customHeight="1" s="140">
       <c r="A135" s="142" t="inlineStr">
@@ -20174,17 +21984,13 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="E135" s="143" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F135" s="143" t="inlineStr">
+      <c r="E135" s="143" t="n"/>
+      <c r="O135" s="143" t="inlineStr">
         <is>
           <t>+1 rangées de sac</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr">
+      <c r="P135" s="2" t="inlineStr">
         <is>
           <t>aucun dégât/armure  (0 carte/5 visées)</t>
         </is>
@@ -20211,17 +22017,13 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E136" s="146" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F136" s="146" t="inlineStr">
+      <c r="E136" s="146" t="n"/>
+      <c r="O136" s="146" t="inlineStr">
         <is>
           <t>+2 rangées de sac</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr">
+      <c r="P136" s="2" t="inlineStr">
         <is>
           <t>aucun dégât/armure  (0 carte/6 visées)</t>
         </is>
@@ -20248,17 +22050,13 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="E137" s="149" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F137" s="149" t="inlineStr">
+      <c r="E137" s="149" t="n"/>
+      <c r="O137" s="149" t="inlineStr">
         <is>
           <t>+4 rangées de sac</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr">
+      <c r="P137" s="2" t="inlineStr">
         <is>
           <t>aucun dégât/armure  (0 carte/6 visées)</t>
         </is>
@@ -20285,17 +22083,13 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="E138" s="149" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F138" s="149" t="inlineStr">
+      <c r="E138" s="149" t="n"/>
+      <c r="O138" s="149" t="inlineStr">
         <is>
           <t>+3 rangées de sac</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr">
+      <c r="P138" s="2" t="inlineStr">
         <is>
           <t>aucun dégât/armure  (0 carte/6 visées)</t>
         </is>
@@ -20322,17 +22116,13 @@
           <t>Epic</t>
         </is>
       </c>
-      <c r="E139" s="152" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F139" s="152" t="inlineStr">
+      <c r="E139" s="152" t="n"/>
+      <c r="O139" s="152" t="inlineStr">
         <is>
           <t>+6 rangées de sac</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr">
+      <c r="P139" s="2" t="inlineStr">
         <is>
           <t>aucun dégât/armure  (0 carte/7 visées)</t>
         </is>
@@ -20359,17 +22149,13 @@
           <t>Legendary</t>
         </is>
       </c>
-      <c r="E140" s="155" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F140" s="155" t="inlineStr">
+      <c r="E140" s="155" t="n"/>
+      <c r="O140" s="155" t="inlineStr">
         <is>
           <t>+10 rangées de sac</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr">
+      <c r="P140" s="2" t="inlineStr">
         <is>
           <t>aucun dégât/armure  (0 carte/8 visées)</t>
         </is>
@@ -20381,28 +22167,28 @@
       <c r="C141" s="51" t="n"/>
       <c r="D141" s="51" t="n"/>
       <c r="E141" s="51" t="n"/>
-      <c r="F141" s="51" t="n"/>
+      <c r="O141" s="51" t="n"/>
     </row>
     <row r="142" ht="15" customHeight="1" s="140"/>
     <row r="143" ht="15" customHeight="1" s="140">
-      <c r="G143" s="2" t="n"/>
+      <c r="P143" s="2" t="n"/>
     </row>
     <row r="144" ht="15" customHeight="1" s="140">
-      <c r="G144" s="2" t="n"/>
+      <c r="P144" s="2" t="n"/>
     </row>
     <row r="145" ht="15" customHeight="1" s="140">
-      <c r="G145" s="2" t="n"/>
+      <c r="P145" s="2" t="n"/>
     </row>
     <row r="146" ht="15" customHeight="1" s="140"/>
     <row r="147" ht="15" customHeight="1" s="140"/>
     <row r="148">
-      <c r="G148" s="2" t="n"/>
+      <c r="P148" s="2" t="n"/>
     </row>
     <row r="149">
-      <c r="G149" s="2" t="n"/>
+      <c r="P149" s="2" t="n"/>
     </row>
     <row r="150">
-      <c r="G150" s="2" t="n"/>
+      <c r="P150" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -25536,7 +27322,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="56" t="inlineStr">
         <is>
@@ -25790,7 +27575,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="75" t="inlineStr">
         <is>
@@ -25853,7 +27637,6 @@
       </c>
       <c r="D18" s="77" t="n"/>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="A20" s="75" t="inlineStr">
         <is>
@@ -25913,7 +27696,6 @@
         </is>
       </c>
     </row>
-    <row r="24"/>
     <row r="25">
       <c r="A25" s="75" t="inlineStr">
         <is>
@@ -25977,7 +27759,6 @@
       </c>
       <c r="D29" s="77" t="n"/>
     </row>
-    <row r="30"/>
     <row r="31">
       <c r="A31" s="75" t="inlineStr">
         <is>
@@ -26037,7 +27818,6 @@
         </is>
       </c>
     </row>
-    <row r="35"/>
     <row r="36">
       <c r="A36" s="75" t="inlineStr">
         <is>
@@ -26100,7 +27880,6 @@
       </c>
       <c r="D39" s="77" t="n"/>
     </row>
-    <row r="40"/>
     <row r="41">
       <c r="A41" s="75" t="inlineStr">
         <is>
@@ -26149,7 +27928,6 @@
         </is>
       </c>
     </row>
-    <row r="45"/>
     <row r="46">
       <c r="A46" s="75" t="inlineStr">
         <is>
@@ -26201,7 +27979,6 @@
       </c>
       <c r="C49" s="77" t="n"/>
     </row>
-    <row r="50"/>
     <row r="51">
       <c r="A51" s="75" t="inlineStr">
         <is>
@@ -26255,7 +28032,6 @@
       </c>
       <c r="D53" s="77" t="n"/>
     </row>
-    <row r="54"/>
     <row r="55">
       <c r="A55" s="75" t="inlineStr">
         <is>
@@ -26304,7 +28080,6 @@
         </is>
       </c>
     </row>
-    <row r="59"/>
     <row r="60">
       <c r="A60" s="75" t="inlineStr">
         <is>
@@ -26364,7 +28139,6 @@
         </is>
       </c>
     </row>
-    <row r="64"/>
     <row r="65">
       <c r="A65" s="75" t="inlineStr">
         <is>
@@ -26424,7 +28198,6 @@
         </is>
       </c>
     </row>
-    <row r="69"/>
     <row r="70">
       <c r="A70" s="75" t="inlineStr">
         <is>
@@ -26487,7 +28260,6 @@
       </c>
       <c r="D73" s="77" t="n"/>
     </row>
-    <row r="74"/>
     <row r="75">
       <c r="A75" s="75" t="inlineStr">
         <is>
@@ -26543,7 +28315,6 @@
         </is>
       </c>
     </row>
-    <row r="80"/>
     <row r="81">
       <c r="A81" s="75" t="inlineStr">
         <is>
@@ -26606,7 +28377,6 @@
       </c>
       <c r="D84" s="77" t="n"/>
     </row>
-    <row r="85"/>
     <row r="86">
       <c r="A86" s="75" t="inlineStr">
         <is>
@@ -26674,7 +28444,6 @@
         </is>
       </c>
     </row>
-    <row r="91"/>
     <row r="92">
       <c r="A92" s="75" t="inlineStr">
         <is>
@@ -26737,7 +28506,6 @@
       </c>
       <c r="D95" s="77" t="n"/>
     </row>
-    <row r="96"/>
     <row r="97">
       <c r="A97" s="75" t="inlineStr">
         <is>
@@ -26808,7 +28576,6 @@
       </c>
       <c r="D100" s="77" t="n"/>
     </row>
-    <row r="101"/>
     <row r="102">
       <c r="A102" s="75" t="inlineStr">
         <is>
@@ -26889,7 +28656,6 @@
       </c>
       <c r="D107" s="77" t="n"/>
     </row>
-    <row r="108"/>
     <row r="109">
       <c r="A109" s="75" t="inlineStr">
         <is>
@@ -26970,7 +28736,6 @@
       </c>
       <c r="D114" s="77" t="n"/>
     </row>
-    <row r="115"/>
     <row r="116">
       <c r="A116" s="75" t="inlineStr">
         <is>
@@ -27026,7 +28791,6 @@
         </is>
       </c>
     </row>
-    <row r="121"/>
     <row r="122">
       <c r="A122" s="75" t="inlineStr">
         <is>
@@ -27098,7 +28862,6 @@
       </c>
       <c r="D126" s="77" t="n"/>
     </row>
-    <row r="127"/>
     <row r="128">
       <c r="A128" s="75" t="inlineStr">
         <is>
@@ -27166,7 +28929,6 @@
       </c>
       <c r="D132" s="77" t="n"/>
     </row>
-    <row r="133"/>
     <row r="134">
       <c r="A134" s="75" t="inlineStr">
         <is>
@@ -27233,7 +28995,6 @@
       </c>
       <c r="D137" s="77" t="n"/>
     </row>
-    <row r="138"/>
     <row r="139">
       <c r="A139" s="75" t="inlineStr">
         <is>
@@ -27309,7 +29070,6 @@
       </c>
       <c r="D143" s="77" t="n"/>
     </row>
-    <row r="144"/>
     <row r="145">
       <c r="A145" s="75" t="inlineStr">
         <is>
@@ -27380,7 +29140,6 @@
       </c>
       <c r="D148" s="77" t="n"/>
     </row>
-    <row r="149"/>
     <row r="150">
       <c r="A150" s="75" t="inlineStr">
         <is>
@@ -27447,7 +29206,6 @@
         </is>
       </c>
     </row>
-    <row r="154"/>
     <row r="155">
       <c r="A155" s="75" t="inlineStr">
         <is>
@@ -27519,7 +29277,6 @@
       </c>
       <c r="D159" s="77" t="n"/>
     </row>
-    <row r="160"/>
     <row r="161">
       <c r="A161" s="75" t="inlineStr">
         <is>
@@ -27575,7 +29332,6 @@
         </is>
       </c>
     </row>
-    <row r="165"/>
     <row r="166">
       <c r="A166" s="75" t="inlineStr">
         <is>
@@ -27643,7 +29399,6 @@
         </is>
       </c>
     </row>
-    <row r="171"/>
     <row r="172">
       <c r="A172" s="75" t="inlineStr">
         <is>
@@ -27714,7 +29469,6 @@
       </c>
       <c r="D175" s="77" t="n"/>
     </row>
-    <row r="176"/>
     <row r="177">
       <c r="A177" s="75" t="inlineStr">
         <is>
@@ -27786,7 +29540,6 @@
       </c>
       <c r="D181" s="77" t="n"/>
     </row>
-    <row r="182"/>
     <row r="183">
       <c r="A183" s="75" t="inlineStr">
         <is>
@@ -27850,7 +29603,6 @@
         </is>
       </c>
     </row>
-    <row r="188"/>
     <row r="189">
       <c r="A189" s="75" t="inlineStr">
         <is>
@@ -27939,7 +29691,6 @@
       </c>
       <c r="D194" s="77" t="n"/>
     </row>
-    <row r="195"/>
     <row r="196">
       <c r="A196" s="75" t="inlineStr">
         <is>
@@ -28019,7 +29770,6 @@
       </c>
       <c r="D200" s="77" t="n"/>
     </row>
-    <row r="201"/>
     <row r="202">
       <c r="A202" s="75" t="inlineStr">
         <is>
@@ -28090,7 +29840,6 @@
       </c>
       <c r="D205" s="77" t="n"/>
     </row>
-    <row r="206"/>
     <row r="207">
       <c r="A207" s="75" t="inlineStr">
         <is>
@@ -28171,7 +29920,6 @@
       </c>
       <c r="D212" s="77" t="n"/>
     </row>
-    <row r="213"/>
     <row r="214">
       <c r="A214" s="75" t="inlineStr">
         <is>
@@ -28252,7 +30000,6 @@
       <c r="C219" s="77" t="n"/>
       <c r="D219" s="77" t="n"/>
     </row>
-    <row r="220"/>
     <row r="221">
       <c r="A221" s="75" t="inlineStr">
         <is>
@@ -28314,7 +30061,6 @@
         </is>
       </c>
     </row>
-    <row r="224"/>
     <row r="225">
       <c r="A225" s="75" t="inlineStr">
         <is>
@@ -28376,7 +30122,6 @@
         </is>
       </c>
     </row>
-    <row r="228"/>
     <row r="229">
       <c r="A229" s="75" t="inlineStr">
         <is>
@@ -28438,7 +30183,6 @@
         </is>
       </c>
     </row>
-    <row r="232"/>
     <row r="233">
       <c r="A233" s="75" t="inlineStr">
         <is>
@@ -28500,7 +30244,6 @@
         </is>
       </c>
     </row>
-    <row r="236"/>
     <row r="237">
       <c r="A237" s="75" t="inlineStr">
         <is>
@@ -28562,7 +30305,6 @@
         </is>
       </c>
     </row>
-    <row r="240"/>
     <row r="241">
       <c r="A241" s="75" t="inlineStr">
         <is>
@@ -28641,7 +30383,6 @@
         </is>
       </c>
     </row>
-    <row r="245"/>
     <row r="246">
       <c r="A246" s="75" t="inlineStr">
         <is>
@@ -28720,7 +30461,6 @@
         </is>
       </c>
     </row>
-    <row r="250"/>
     <row r="251">
       <c r="A251" s="75" t="inlineStr">
         <is>
@@ -28782,7 +30522,6 @@
         </is>
       </c>
     </row>
-    <row r="254"/>
     <row r="255">
       <c r="A255" s="75" t="inlineStr">
         <is>
@@ -28844,7 +30583,6 @@
         </is>
       </c>
     </row>
-    <row r="258"/>
     <row r="259">
       <c r="A259" s="75" t="inlineStr">
         <is>
@@ -28923,7 +30661,6 @@
         </is>
       </c>
     </row>
-    <row r="263"/>
     <row r="264">
       <c r="A264" s="75" t="inlineStr">
         <is>
@@ -29002,7 +30739,6 @@
         </is>
       </c>
     </row>
-    <row r="268"/>
     <row r="269">
       <c r="A269" s="75" t="inlineStr">
         <is>
@@ -29081,7 +30817,6 @@
         </is>
       </c>
     </row>
-    <row r="273"/>
     <row r="274">
       <c r="A274" s="75" t="inlineStr">
         <is>
@@ -29160,7 +30895,6 @@
         </is>
       </c>
     </row>
-    <row r="278"/>
     <row r="279">
       <c r="A279" s="75" t="inlineStr">
         <is>
@@ -29283,7 +31017,6 @@
         </is>
       </c>
     </row>
-    <row r="285"/>
     <row r="286">
       <c r="A286" s="75" t="inlineStr">
         <is>
@@ -29406,7 +31139,6 @@
         </is>
       </c>
     </row>
-    <row r="292"/>
     <row r="293">
       <c r="A293" s="75" t="inlineStr">
         <is>
@@ -29454,7 +31186,6 @@
         </is>
       </c>
     </row>
-    <row r="296"/>
     <row r="297">
       <c r="A297" s="75" t="inlineStr">
         <is>
@@ -29510,7 +31241,6 @@
         </is>
       </c>
     </row>
-    <row r="301"/>
     <row r="302">
       <c r="A302" s="75" t="inlineStr">
         <is>
@@ -29558,7 +31288,6 @@
         </is>
       </c>
     </row>
-    <row r="305"/>
     <row r="306">
       <c r="A306" s="75" t="inlineStr">
         <is>
@@ -29598,7 +31327,6 @@
         </is>
       </c>
     </row>
-    <row r="308"/>
     <row r="309">
       <c r="A309" s="75" t="inlineStr">
         <is>
@@ -29646,7 +31374,6 @@
         </is>
       </c>
     </row>
-    <row r="312"/>
     <row r="313">
       <c r="A313" s="75" t="inlineStr">
         <is>
@@ -29694,7 +31421,6 @@
         </is>
       </c>
     </row>
-    <row r="316"/>
     <row r="317">
       <c r="A317" s="75" t="inlineStr">
         <is>
@@ -29742,7 +31468,6 @@
         </is>
       </c>
     </row>
-    <row r="320"/>
     <row r="321">
       <c r="A321" s="75" t="inlineStr">
         <is>
@@ -29790,7 +31515,6 @@
       </c>
       <c r="C323" s="77" t="n"/>
     </row>
-    <row r="324"/>
     <row r="325">
       <c r="A325" s="75" t="inlineStr">
         <is>
@@ -29838,7 +31562,6 @@
       </c>
       <c r="C327" s="77" t="n"/>
     </row>
-    <row r="328"/>
     <row r="329">
       <c r="A329" s="75" t="inlineStr">
         <is>
@@ -29894,7 +31617,6 @@
       </c>
       <c r="C332" s="77" t="n"/>
     </row>
-    <row r="333"/>
     <row r="334">
       <c r="A334" s="75" t="inlineStr">
         <is>
@@ -29950,7 +31672,6 @@
       </c>
       <c r="C337" s="77" t="n"/>
     </row>
-    <row r="338"/>
     <row r="339">
       <c r="A339" s="75" t="inlineStr">
         <is>
@@ -30006,7 +31727,6 @@
       </c>
       <c r="C342" s="77" t="n"/>
     </row>
-    <row r="343"/>
     <row r="344">
       <c r="A344" s="75" t="inlineStr">
         <is>
@@ -30062,7 +31782,6 @@
       </c>
       <c r="C347" s="77" t="n"/>
     </row>
-    <row r="348"/>
     <row r="349">
       <c r="A349" s="75" t="inlineStr">
         <is>
@@ -30152,7 +31871,6 @@
         </is>
       </c>
     </row>
-    <row r="353"/>
     <row r="354">
       <c r="A354" s="75" t="inlineStr">
         <is>
@@ -30242,7 +31960,6 @@
         </is>
       </c>
     </row>
-    <row r="358"/>
     <row r="359">
       <c r="A359" s="75" t="inlineStr">
         <is>
@@ -30290,7 +32007,6 @@
         </is>
       </c>
     </row>
-    <row r="362"/>
     <row r="363">
       <c r="A363" s="75" t="inlineStr">
         <is>
@@ -30338,7 +32054,6 @@
       </c>
       <c r="C365" s="77" t="n"/>
     </row>
-    <row r="366"/>
     <row r="367">
       <c r="A367" s="75" t="inlineStr">
         <is>
@@ -30386,7 +32101,6 @@
         </is>
       </c>
     </row>
-    <row r="370"/>
     <row r="371">
       <c r="A371" s="75" t="inlineStr">
         <is>
@@ -30434,7 +32148,6 @@
       </c>
       <c r="C373" s="77" t="n"/>
     </row>
-    <row r="374"/>
     <row r="375">
       <c r="A375" s="75" t="inlineStr">
         <is>
@@ -30482,7 +32195,6 @@
         </is>
       </c>
     </row>
-    <row r="378"/>
     <row r="379">
       <c r="A379" s="75" t="inlineStr">
         <is>
@@ -30530,7 +32242,6 @@
       </c>
       <c r="C381" s="77" t="n"/>
     </row>
-    <row r="382"/>
     <row r="383">
       <c r="A383" s="75" t="inlineStr">
         <is>
@@ -30582,7 +32293,6 @@
         </is>
       </c>
     </row>
-    <row r="386"/>
     <row r="387">
       <c r="A387" s="75" t="inlineStr">
         <is>
@@ -30630,7 +32340,6 @@
       </c>
       <c r="C389" s="77" t="n"/>
     </row>
-    <row r="390"/>
     <row r="391">
       <c r="A391" s="75" t="inlineStr">
         <is>
@@ -30682,7 +32391,6 @@
         </is>
       </c>
     </row>
-    <row r="394"/>
     <row r="395">
       <c r="A395" s="75" t="inlineStr">
         <is>
@@ -30730,7 +32438,6 @@
         </is>
       </c>
     </row>
-    <row r="398"/>
     <row r="399">
       <c r="A399" s="75" t="inlineStr">
         <is>
@@ -30778,7 +32485,6 @@
       </c>
       <c r="C401" s="77" t="n"/>
     </row>
-    <row r="402"/>
     <row r="403">
       <c r="A403" s="75" t="inlineStr">
         <is>
@@ -30830,7 +32536,6 @@
         </is>
       </c>
     </row>
-    <row r="406"/>
     <row r="407">
       <c r="A407" s="75" t="inlineStr">
         <is>
@@ -30882,7 +32587,6 @@
         </is>
       </c>
     </row>
-    <row r="410"/>
     <row r="411">
       <c r="A411" s="75" t="inlineStr">
         <is>
@@ -30930,7 +32634,6 @@
       </c>
       <c r="C413" s="77" t="n"/>
     </row>
-    <row r="414"/>
     <row r="415">
       <c r="A415" s="75" t="inlineStr">
         <is>
@@ -31011,7 +32714,6 @@
         </is>
       </c>
     </row>
-    <row r="419"/>
     <row r="420">
       <c r="A420" s="75" t="inlineStr">
         <is>
@@ -31097,7 +32799,6 @@
         </is>
       </c>
     </row>
-    <row r="424"/>
     <row r="425">
       <c r="A425" s="75" t="inlineStr">
         <is>
@@ -31137,7 +32838,6 @@
         </is>
       </c>
     </row>
-    <row r="427"/>
     <row r="428">
       <c r="A428" s="75" t="inlineStr">
         <is>
@@ -31177,7 +32877,6 @@
         </is>
       </c>
     </row>
-    <row r="430"/>
     <row r="431">
       <c r="A431" s="75" t="inlineStr">
         <is>
@@ -31219,7 +32918,6 @@
         </is>
       </c>
     </row>
-    <row r="434"/>
     <row r="435">
       <c r="A435" s="75" t="inlineStr">
         <is>
@@ -31261,7 +32959,6 @@
         </is>
       </c>
     </row>
-    <row r="438"/>
     <row r="439">
       <c r="A439" s="75" t="inlineStr">
         <is>
@@ -31301,7 +32998,6 @@
         </is>
       </c>
     </row>
-    <row r="441"/>
     <row r="442">
       <c r="A442" s="75" t="inlineStr">
         <is>
@@ -31341,7 +33037,6 @@
         </is>
       </c>
     </row>
-    <row r="444"/>
     <row r="445">
       <c r="A445" s="75" t="inlineStr">
         <is>
@@ -31381,7 +33076,6 @@
         </is>
       </c>
     </row>
-    <row r="447"/>
     <row r="448">
       <c r="A448" s="75" t="inlineStr">
         <is>
@@ -31423,7 +33117,6 @@
         </is>
       </c>
     </row>
-    <row r="451"/>
     <row r="452">
       <c r="A452" s="75" t="inlineStr">
         <is>
@@ -31463,7 +33156,6 @@
         </is>
       </c>
     </row>
-    <row r="454"/>
     <row r="455">
       <c r="A455" s="75" t="inlineStr">
         <is>
@@ -31511,7 +33203,6 @@
       </c>
       <c r="C457" s="77" t="n"/>
     </row>
-    <row r="458"/>
     <row r="459">
       <c r="A459" s="75" t="inlineStr">
         <is>
@@ -31559,7 +33250,6 @@
       </c>
       <c r="C461" s="77" t="n"/>
     </row>
-    <row r="462"/>
     <row r="463">
       <c r="A463" s="75" t="inlineStr">
         <is>
@@ -31608,7 +33298,6 @@
         </is>
       </c>
     </row>
-    <row r="467"/>
     <row r="468">
       <c r="A468" s="75" t="inlineStr">
         <is>
@@ -31657,7 +33346,6 @@
         </is>
       </c>
     </row>
-    <row r="472"/>
     <row r="473">
       <c r="A473" s="75" t="inlineStr">
         <is>
@@ -31705,7 +33393,6 @@
       </c>
       <c r="C475" s="77" t="n"/>
     </row>
-    <row r="476"/>
     <row r="477">
       <c r="A477" s="75" t="inlineStr">
         <is>
@@ -31753,7 +33440,6 @@
         </is>
       </c>
     </row>
-    <row r="480"/>
     <row r="481">
       <c r="A481" s="75" t="inlineStr">
         <is>
@@ -31801,7 +33487,6 @@
         </is>
       </c>
     </row>
-    <row r="484"/>
     <row r="485">
       <c r="A485" s="75" t="inlineStr">
         <is>
@@ -31849,7 +33534,6 @@
       </c>
       <c r="C487" s="77" t="n"/>
     </row>
-    <row r="488"/>
     <row r="489">
       <c r="A489" s="75" t="inlineStr">
         <is>
@@ -31901,7 +33585,6 @@
         </is>
       </c>
     </row>
-    <row r="492"/>
     <row r="493">
       <c r="A493" s="75" t="inlineStr">
         <is>
@@ -31955,7 +33638,6 @@
       </c>
       <c r="D495" s="77" t="n"/>
     </row>
-    <row r="496"/>
     <row r="497">
       <c r="A497" s="75" t="inlineStr">
         <is>
@@ -32003,7 +33685,6 @@
         </is>
       </c>
     </row>
-    <row r="500"/>
     <row r="501">
       <c r="A501" s="75" t="inlineStr">
         <is>
@@ -32051,7 +33732,6 @@
       </c>
       <c r="C503" s="77" t="n"/>
     </row>
-    <row r="504"/>
     <row r="505">
       <c r="A505" s="75" t="inlineStr">
         <is>
@@ -32100,7 +33780,6 @@
         </is>
       </c>
     </row>
-    <row r="509"/>
     <row r="510">
       <c r="A510" s="75" t="inlineStr">
         <is>
@@ -32145,7 +33824,6 @@
         </is>
       </c>
     </row>
-    <row r="512"/>
     <row r="513">
       <c r="A513" s="75" t="inlineStr">
         <is>
@@ -32199,7 +33877,6 @@
       </c>
       <c r="D515" s="77" t="n"/>
     </row>
-    <row r="516"/>
     <row r="517">
       <c r="A517" s="75" t="inlineStr">
         <is>
@@ -32247,7 +33924,6 @@
         </is>
       </c>
     </row>
-    <row r="520"/>
     <row r="521">
       <c r="A521" s="75" t="inlineStr">
         <is>
@@ -32296,7 +33972,6 @@
         </is>
       </c>
     </row>
-    <row r="525"/>
     <row r="526">
       <c r="A526" s="75" t="inlineStr">
         <is>
@@ -32341,7 +34016,6 @@
         </is>
       </c>
     </row>
-    <row r="528"/>
     <row r="529">
       <c r="A529" s="75" t="inlineStr">
         <is>
@@ -32386,7 +34060,6 @@
         </is>
       </c>
     </row>
-    <row r="531"/>
     <row r="532">
       <c r="A532" s="75" t="inlineStr">
         <is>
@@ -32440,7 +34113,6 @@
       </c>
       <c r="D534" s="77" t="n"/>
     </row>
-    <row r="535"/>
     <row r="536">
       <c r="A536" s="75" t="inlineStr">
         <is>
@@ -32504,7 +34176,6 @@
         </is>
       </c>
     </row>
-    <row r="540"/>
     <row r="541">
       <c r="A541" s="75" t="inlineStr">
         <is>
@@ -32556,7 +34227,6 @@
         </is>
       </c>
     </row>
-    <row r="544"/>
     <row r="545">
       <c r="A545" s="75" t="inlineStr">
         <is>
@@ -32608,7 +34278,6 @@
         </is>
       </c>
     </row>
-    <row r="548"/>
     <row r="549">
       <c r="A549" s="75" t="inlineStr">
         <is>
@@ -32657,7 +34326,6 @@
         </is>
       </c>
     </row>
-    <row r="553"/>
     <row r="554">
       <c r="A554" s="75" t="inlineStr">
         <is>
@@ -32706,7 +34374,6 @@
         </is>
       </c>
     </row>
-    <row r="558"/>
     <row r="559">
       <c r="A559" s="75" t="inlineStr">
         <is>
@@ -32758,7 +34425,6 @@
         </is>
       </c>
     </row>
-    <row r="562"/>
     <row r="563">
       <c r="A563" s="75" t="inlineStr">
         <is>
@@ -32822,7 +34488,6 @@
         </is>
       </c>
     </row>
-    <row r="567"/>
     <row r="568">
       <c r="A568" s="75" t="inlineStr">
         <is>
@@ -32874,7 +34539,6 @@
         </is>
       </c>
     </row>
-    <row r="571"/>
     <row r="572">
       <c r="A572" s="75" t="inlineStr">
         <is>
@@ -32923,7 +34587,6 @@
         </is>
       </c>
     </row>
-    <row r="576"/>
     <row r="577">
       <c r="A577" s="75" t="inlineStr">
         <is>
@@ -32987,7 +34650,6 @@
         </is>
       </c>
     </row>
-    <row r="581"/>
     <row r="582">
       <c r="A582" s="75" t="inlineStr">
         <is>
@@ -33039,7 +34701,6 @@
         </is>
       </c>
     </row>
-    <row r="585"/>
     <row r="586">
       <c r="A586" s="75" t="inlineStr">
         <is>

--- a/docs/BRUTAL-items-et-cartes.xlsx
+++ b/docs/BRUTAL-items-et-cartes.xlsx
@@ -21,7 +21,12 @@
     <sheet name="Héros" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="Général" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Cartes'!$A$2:$L$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Items'!$A$1:$P$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Valeurs'!$A$6:$D$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Ressources'!$A$6:$D$6</definedName>
+  </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -1550,7 +1555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:F94"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" style="140" min="1" max="1"/>
@@ -1669,7 +1674,7 @@
     <row r="19">
       <c r="A19" s="2" t="n"/>
     </row>
-    <row r="20">
+    <row r="20" s="140">
       <c r="A20" s="3" t="inlineStr">
         <is>
           <t>Lignes surlignées en JAUNE</t>
@@ -1683,162 +1688,180 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+    <row r="22" s="140">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Vérifier que le classeur et le jeu disent la même chose</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1" s="140">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Une commande relit TOUT le classeur et le compare au contenu réel du jeu :  python3 outils/auditer_excel.py  — elle signale les noms qui divergent, les prix manquants, les cartes oubliées d'un côté ou de l'autre, les lignes/colonnes fantômes. Elle ne modifie RIEN : elle dit juste ce qui cloche. À lancer après chaque série de modifications.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1" s="140">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Conventions que l'audit fait respecter : colonne « Type » = Attaque / Défense / Buff (avec l'accent) · colonne « AOE » = « Oui » UNIQUEMENT si la carte frappe TOUS les ennemis d'un coup (une carte qui n'éclabousse que les voisins n'est pas de l'AOE) · colonne « Donnée par » = les noms d'objets séparés par une virgule, suivis de « ×N » quand un objet donne la carte plusieurs fois · onglet « Valeurs » trié par rareté puis par nom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>Légende des raretés</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  Common  (commun)</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  Uncommon  (uncommon)</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">  Rare  (rare)</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Epic  (epique)</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="8" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">  Legendary  (legendaire)</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="9" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
         <is>
           <t>Tableau de référence pour garder une certaine balance</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>Rareté</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>Nb de cartes</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>Dégât / énergie</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>Armure / énergie</t>
         </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="C32" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="D32" s="2" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="C33" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="D33" s="2" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="C34" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="D34" s="2" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Legendary</t>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C36" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="C36" s="2" t="n">
-        <v>25</v>
-      </c>
       <c r="D36" s="2" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" ht="30" customHeight="1" s="140">
       <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>Armes à deux mains : ×1,5 sur dégât et armure/énergie (moins de cartes), souvent via des sorts chers en énergie.</t>
         </is>
@@ -1854,8 +1877,7 @@
       <c r="C43" s="137" t="n"/>
       <c r="D43" s="137" t="n"/>
       <c r="E43" s="137" t="n"/>
-      <c r="F43" s="137" t="n"/>
-      <c r="G43" s="138" t="n"/>
+      <c r="F43" s="138" t="n"/>
     </row>
     <row r="44" ht="15.75" customHeight="1" s="140" thickBot="1">
       <c r="B44" s="128" t="inlineStr">
@@ -1883,7 +1905,6 @@
           <t>XP estimé</t>
         </is>
       </c>
-      <c r="G44" s="119" t="n"/>
     </row>
     <row r="45">
       <c r="B45" s="130" t="n">
@@ -1901,7 +1922,6 @@
       <c r="F45" s="126" t="n">
         <v>20</v>
       </c>
-      <c r="G45" s="125" t="n"/>
     </row>
     <row r="46">
       <c r="B46" s="131" t="n">
@@ -1919,7 +1939,6 @@
       <c r="F46" s="127" t="n">
         <v>30</v>
       </c>
-      <c r="G46" s="121" t="n"/>
     </row>
     <row r="47">
       <c r="B47" s="131" t="n">
@@ -1937,7 +1956,6 @@
       <c r="F47" s="127" t="n">
         <v>50</v>
       </c>
-      <c r="G47" s="121" t="n"/>
     </row>
     <row r="48">
       <c r="B48" s="131" t="n">
@@ -1955,7 +1973,6 @@
       <c r="F48" s="127" t="n">
         <v>90</v>
       </c>
-      <c r="G48" s="121" t="n"/>
     </row>
     <row r="49">
       <c r="B49" s="131" t="n">
@@ -1973,7 +1990,6 @@
       <c r="F49" s="127" t="n">
         <v>140</v>
       </c>
-      <c r="G49" s="121" t="n"/>
     </row>
     <row r="50">
       <c r="B50" s="131" t="n">
@@ -1991,7 +2007,6 @@
       <c r="F50" s="127" t="n">
         <v>200</v>
       </c>
-      <c r="G50" s="121" t="n"/>
     </row>
     <row r="51">
       <c r="B51" s="131" t="n">
@@ -2009,7 +2024,6 @@
       <c r="F51" s="127" t="n">
         <v>280</v>
       </c>
-      <c r="G51" s="121" t="n"/>
     </row>
     <row r="52">
       <c r="B52" s="131" t="n">
@@ -2027,7 +2041,6 @@
       <c r="F52" s="127" t="n">
         <v>380</v>
       </c>
-      <c r="G52" s="121" t="n"/>
     </row>
     <row r="53">
       <c r="B53" s="131" t="n">
@@ -2045,7 +2058,6 @@
       <c r="F53" s="127" t="n">
         <v>500</v>
       </c>
-      <c r="G53" s="121" t="n"/>
     </row>
     <row r="54">
       <c r="B54" s="131" t="n">
@@ -2063,7 +2075,6 @@
       <c r="F54" s="127" t="n">
         <v>650</v>
       </c>
-      <c r="G54" s="121" t="n"/>
     </row>
     <row r="55">
       <c r="B55" s="131" t="n">
@@ -2081,7 +2092,6 @@
       <c r="F55" s="127" t="n">
         <v>800</v>
       </c>
-      <c r="G55" s="121" t="n"/>
     </row>
     <row r="56">
       <c r="B56" s="131" t="n">
@@ -2099,7 +2109,6 @@
       <c r="F56" s="127" t="n">
         <v>1000</v>
       </c>
-      <c r="G56" s="121" t="n"/>
     </row>
     <row r="57">
       <c r="B57" s="131" t="n">
@@ -2117,7 +2126,6 @@
       <c r="F57" s="127" t="n">
         <v>1200</v>
       </c>
-      <c r="G57" s="121" t="n"/>
     </row>
     <row r="58">
       <c r="B58" s="131" t="n">
@@ -2135,7 +2143,6 @@
       <c r="F58" s="127" t="n">
         <v>1500</v>
       </c>
-      <c r="G58" s="121" t="n"/>
     </row>
     <row r="59">
       <c r="B59" s="131" t="n">
@@ -2153,7 +2160,6 @@
       <c r="F59" s="127" t="n">
         <v>1800</v>
       </c>
-      <c r="G59" s="121" t="n"/>
     </row>
     <row r="60">
       <c r="B60" s="131" t="n">
@@ -2171,7 +2177,6 @@
       <c r="F60" s="127" t="n">
         <v>2300</v>
       </c>
-      <c r="G60" s="121" t="n"/>
     </row>
     <row r="61">
       <c r="B61" s="131" t="n">
@@ -2189,7 +2194,6 @@
       <c r="F61" s="127" t="n">
         <v>2800</v>
       </c>
-      <c r="G61" s="121" t="n"/>
     </row>
     <row r="62">
       <c r="B62" s="131" t="n">
@@ -2207,7 +2211,6 @@
       <c r="F62" s="127" t="n">
         <v>3500</v>
       </c>
-      <c r="G62" s="121" t="n"/>
     </row>
     <row r="63">
       <c r="B63" s="131" t="n">
@@ -2225,7 +2228,6 @@
       <c r="F63" s="127" t="n">
         <v>4500</v>
       </c>
-      <c r="G63" s="121" t="n"/>
     </row>
     <row r="64">
       <c r="B64" s="131" t="n">
@@ -2243,7 +2245,6 @@
       <c r="F64" s="127" t="n">
         <v>6000</v>
       </c>
-      <c r="G64" s="121" t="n"/>
     </row>
     <row r="65">
       <c r="B65" s="131" t="n">
@@ -2261,7 +2262,6 @@
       <c r="F65" s="127" t="n">
         <v>8000</v>
       </c>
-      <c r="G65" s="121" t="n"/>
     </row>
     <row r="66">
       <c r="B66" s="131" t="n">
@@ -2279,7 +2279,6 @@
       <c r="F66" s="127" t="n">
         <v>10000</v>
       </c>
-      <c r="G66" s="121" t="n"/>
     </row>
     <row r="67">
       <c r="B67" s="131" t="n">
@@ -2297,7 +2296,6 @@
       <c r="F67" s="127" t="n">
         <v>15000</v>
       </c>
-      <c r="G67" s="121" t="n"/>
     </row>
     <row r="68">
       <c r="B68" s="131" t="n">
@@ -2315,7 +2313,6 @@
       <c r="F68" s="127" t="n">
         <v>20000</v>
       </c>
-      <c r="G68" s="121" t="n"/>
     </row>
     <row r="69">
       <c r="B69" s="131" t="n">
@@ -2333,7 +2330,6 @@
       <c r="F69" s="127" t="n">
         <v>30000</v>
       </c>
-      <c r="G69" s="121" t="n"/>
     </row>
     <row r="70">
       <c r="B70" s="131" t="n">
@@ -2351,7 +2347,6 @@
       <c r="F70" s="127" t="n">
         <v>40000</v>
       </c>
-      <c r="G70" s="121" t="n"/>
     </row>
     <row r="71">
       <c r="B71" s="131" t="n">
@@ -2369,7 +2364,6 @@
       <c r="F71" s="127" t="n">
         <v>50000</v>
       </c>
-      <c r="G71" s="121" t="n"/>
     </row>
     <row r="72">
       <c r="B72" s="131" t="n">
@@ -2387,7 +2381,6 @@
       <c r="F72" s="127" t="n">
         <v>50000</v>
       </c>
-      <c r="G72" s="121" t="n"/>
     </row>
     <row r="73">
       <c r="B73" s="131" t="n">
@@ -2405,7 +2398,6 @@
       <c r="F73" s="127" t="n">
         <v>50000</v>
       </c>
-      <c r="G73" s="121" t="n"/>
     </row>
     <row r="74">
       <c r="B74" s="131" t="n">
@@ -2423,7 +2415,6 @@
       <c r="F74" s="127" t="n">
         <v>50000</v>
       </c>
-      <c r="G74" s="121" t="n"/>
     </row>
     <row r="75">
       <c r="B75" s="131" t="n">
@@ -2441,7 +2432,6 @@
       <c r="F75" s="127" t="n">
         <v>50000</v>
       </c>
-      <c r="G75" s="121" t="n"/>
     </row>
     <row r="76">
       <c r="B76" s="131" t="n">
@@ -2459,7 +2449,6 @@
       <c r="F76" s="127" t="n">
         <v>50000</v>
       </c>
-      <c r="G76" s="121" t="n"/>
     </row>
     <row r="77">
       <c r="B77" s="131" t="n">
@@ -2477,7 +2466,6 @@
       <c r="F77" s="127" t="n">
         <v>50000</v>
       </c>
-      <c r="G77" s="121" t="n"/>
     </row>
     <row r="78">
       <c r="B78" s="131" t="n">
@@ -2495,7 +2483,6 @@
       <c r="F78" s="127" t="n">
         <v>50000</v>
       </c>
-      <c r="G78" s="121" t="n"/>
     </row>
     <row r="79">
       <c r="B79" s="131" t="n">
@@ -2513,7 +2500,6 @@
       <c r="F79" s="127" t="n">
         <v>50000</v>
       </c>
-      <c r="G79" s="121" t="n"/>
     </row>
     <row r="80">
       <c r="B80" s="131" t="n">
@@ -2531,7 +2517,6 @@
       <c r="F80" s="127" t="n">
         <v>50000</v>
       </c>
-      <c r="G80" s="121" t="n"/>
     </row>
     <row r="81">
       <c r="B81" s="131" t="n">
@@ -2549,7 +2534,6 @@
       <c r="F81" s="127" t="n">
         <v>50000</v>
       </c>
-      <c r="G81" s="121" t="n"/>
     </row>
     <row r="82">
       <c r="B82" s="131" t="n">
@@ -2567,7 +2551,6 @@
       <c r="F82" s="127" t="n">
         <v>50000</v>
       </c>
-      <c r="G82" s="121" t="n"/>
     </row>
     <row r="83">
       <c r="B83" s="131" t="n">
@@ -2585,7 +2568,6 @@
       <c r="F83" s="127" t="n">
         <v>50000</v>
       </c>
-      <c r="G83" s="121" t="n"/>
     </row>
     <row r="84">
       <c r="B84" s="131" t="n">
@@ -2603,7 +2585,6 @@
       <c r="F84" s="127" t="n">
         <v>50000</v>
       </c>
-      <c r="G84" s="121" t="n"/>
     </row>
     <row r="85">
       <c r="B85" s="131" t="n">
@@ -2621,7 +2602,6 @@
       <c r="F85" s="127" t="n">
         <v>50000</v>
       </c>
-      <c r="G85" s="121" t="n"/>
     </row>
     <row r="86">
       <c r="B86" s="131" t="n">
@@ -2639,7 +2619,6 @@
       <c r="F86" s="127" t="n">
         <v>50000</v>
       </c>
-      <c r="G86" s="121" t="n"/>
     </row>
     <row r="87">
       <c r="B87" s="131" t="n">
@@ -2657,7 +2636,6 @@
       <c r="F87" s="127" t="n">
         <v>50000</v>
       </c>
-      <c r="G87" s="121" t="n"/>
     </row>
     <row r="88">
       <c r="B88" s="131" t="n">
@@ -2675,7 +2653,6 @@
       <c r="F88" s="127" t="n">
         <v>50000</v>
       </c>
-      <c r="G88" s="121" t="n"/>
     </row>
     <row r="89">
       <c r="B89" s="131" t="n">
@@ -2693,7 +2670,6 @@
       <c r="F89" s="127" t="n">
         <v>50000</v>
       </c>
-      <c r="G89" s="121" t="n"/>
     </row>
     <row r="90">
       <c r="B90" s="131" t="n">
@@ -2711,7 +2687,6 @@
       <c r="F90" s="127" t="n">
         <v>50000</v>
       </c>
-      <c r="G90" s="121" t="n"/>
     </row>
     <row r="91">
       <c r="B91" s="131" t="n">
@@ -2729,7 +2704,6 @@
       <c r="F91" s="127" t="n">
         <v>50000</v>
       </c>
-      <c r="G91" s="121" t="n"/>
     </row>
     <row r="92">
       <c r="B92" s="131" t="n">
@@ -2747,7 +2721,6 @@
       <c r="F92" s="127" t="n">
         <v>50000</v>
       </c>
-      <c r="G92" s="121" t="n"/>
     </row>
     <row r="93">
       <c r="B93" s="131" t="n">
@@ -2765,7 +2738,6 @@
       <c r="F93" s="127" t="n">
         <v>50000</v>
       </c>
-      <c r="G93" s="121" t="n"/>
     </row>
     <row r="94" ht="15.75" customHeight="1" s="140" thickBot="1">
       <c r="B94" s="132" t="n">
@@ -2783,11 +2755,12 @@
       <c r="F94" s="129" t="n">
         <v>50000</v>
       </c>
-      <c r="G94" s="123" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B43:G43"/>
+  <mergeCells count="3">
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="A23:F23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2866,7 +2839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W47"/>
+  <dimension ref="A1:L47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="140" min="1" max="1"/>
@@ -3024,7 +2997,6 @@
       <c r="J3" s="106" t="n"/>
       <c r="K3" s="106" t="n"/>
       <c r="L3" s="106" t="n"/>
-      <c r="R3" s="141" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="107" t="inlineStr">
@@ -4731,9 +4703,6 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="R3:W3"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4900,7 +4869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" style="140" min="1" max="1"/>
@@ -5412,7 +5381,7 @@
       </c>
       <c r="E23" s="101" t="inlineStr">
         <is>
-          <t>data/items.js + inventaire.js</t>
+          <t>data/items.js + systems/inventaire.js</t>
         </is>
       </c>
     </row>
@@ -5907,69 +5876,6 @@
           <t>systems/combat.js</t>
         </is>
       </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="134" t="n"/>
-      <c r="B44" s="135" t="n"/>
-      <c r="C44" s="135" t="n"/>
-      <c r="D44" s="135" t="n"/>
-      <c r="E44" s="135" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="101" t="n"/>
-      <c r="B45" s="101" t="n"/>
-      <c r="C45" s="102" t="n"/>
-      <c r="D45" s="101" t="n"/>
-      <c r="E45" s="101" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="101" t="n"/>
-      <c r="B46" s="101" t="n"/>
-      <c r="C46" s="102" t="n"/>
-      <c r="D46" s="101" t="n"/>
-      <c r="E46" s="101" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="101" t="n"/>
-      <c r="B47" s="101" t="n"/>
-      <c r="C47" s="102" t="n"/>
-      <c r="D47" s="101" t="n"/>
-      <c r="E47" s="101" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="134" t="n"/>
-      <c r="B48" s="135" t="n"/>
-      <c r="C48" s="135" t="n"/>
-      <c r="D48" s="135" t="n"/>
-      <c r="E48" s="135" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="101" t="n"/>
-      <c r="B49" s="101" t="n"/>
-      <c r="C49" s="102" t="n"/>
-      <c r="D49" s="101" t="n"/>
-      <c r="E49" s="101" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="101" t="n"/>
-      <c r="B50" s="101" t="n"/>
-      <c r="C50" s="102" t="n"/>
-      <c r="D50" s="101" t="n"/>
-      <c r="E50" s="101" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="101" t="n"/>
-      <c r="B51" s="101" t="n"/>
-      <c r="C51" s="102" t="n"/>
-      <c r="D51" s="101" t="n"/>
-      <c r="E51" s="101" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="101" t="n"/>
-      <c r="B52" s="101" t="n"/>
-      <c r="C52" s="102" t="n"/>
-      <c r="D52" s="101" t="n"/>
-      <c r="E52" s="101" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6178,7 +6084,7 @@
       <c r="H5" s="13" t="n"/>
       <c r="I5" s="14" t="inlineStr">
         <is>
-          <t>Hatchet, Twin Daggers</t>
+          <t>Hatchet ×2, Twin Daggers</t>
         </is>
       </c>
       <c r="J5" s="14" t="inlineStr">
@@ -6234,7 +6140,7 @@
       <c r="H6" s="13" t="n"/>
       <c r="I6" s="14" t="inlineStr">
         <is>
-          <t>Wooden Club, Mace, Cleaver, Executioner's Blade</t>
+          <t>Wooden Club, Mace ×2, Cleaver, Executioner's Blade</t>
         </is>
       </c>
       <c r="J6" s="14" t="inlineStr">
@@ -6290,7 +6196,7 @@
       <c r="H7" s="13" t="n"/>
       <c r="I7" s="14" t="inlineStr">
         <is>
-          <t>Miner's Pick</t>
+          <t>Miner's Pick ×2</t>
         </is>
       </c>
       <c r="J7" s="14" t="inlineStr">
@@ -6346,7 +6252,7 @@
       <c r="H8" s="13" t="n"/>
       <c r="I8" s="14" t="inlineStr">
         <is>
-          <t>Spear, Pitchfork</t>
+          <t>Spear ×2, Pitchfork ×2</t>
         </is>
       </c>
       <c r="J8" s="14" t="inlineStr">
@@ -6402,7 +6308,7 @@
       <c r="H9" s="13" t="n"/>
       <c r="I9" s="14" t="inlineStr">
         <is>
-          <t>Rusty Axe</t>
+          <t>Rusty Axe ×2</t>
         </is>
       </c>
       <c r="J9" s="14" t="inlineStr">
@@ -6458,7 +6364,7 @@
       <c r="H10" s="13" t="n"/>
       <c r="I10" s="14" t="inlineStr">
         <is>
-          <t>Short Sword, Spear, Serpent Knife, Venomfang Dagger, Frostbrand, Emberblade, Reaver Axe, Berserker Axe, Executioner's Blade, Holy Sword</t>
+          <t>Short Sword ×2, Spear, Serpent Knife, Venomfang Dagger, Frostbrand, Emberblade, Reaver Axe, Berserker Axe, Executioner's Blade, Holy Sword ×2</t>
         </is>
       </c>
       <c r="J10" s="14" t="inlineStr">
@@ -6570,7 +6476,7 @@
       <c r="H12" s="13" t="n"/>
       <c r="I12" s="14" t="inlineStr">
         <is>
-          <t>Rusty Axe, Forge Hammer, Miner's Pick, Short Sword, Wooden Club, Spear, Hatchet, Rusty Dagger, Ice Pick, Torch, Serrated Knife, Cleaver, Training Sword, Quarterstaff, Work Gloves, Studded Gloves</t>
+          <t>Rusty Axe ×3, Forge Hammer ×2, Miner's Pick ×3, Short Sword ×3, Wooden Club ×3, Spear ×2, Hatchet ×2, Rusty Dagger ×2, Ice Pick ×2, Torch ×2, Serrated Knife ×2, Cleaver ×2, Training Sword ×3, Quarterstaff ×2, Work Gloves, Studded Gloves</t>
         </is>
       </c>
       <c r="J12" s="14" t="inlineStr">
@@ -6682,7 +6588,7 @@
       <c r="H14" s="15" t="n"/>
       <c r="I14" s="16" t="inlineStr">
         <is>
-          <t>Stone Hammer, Berserker Axe, Warhammer, Twin Daggers, Executioner's Blade, Crystal Wand, Spiked Flail</t>
+          <t>Stone Hammer ×2, Berserker Axe, Warhammer, Twin Daggers ×2, Executioner's Blade, Crystal Wand, Spiked Flail ×2</t>
         </is>
       </c>
       <c r="J14" s="16" t="inlineStr">
@@ -6794,7 +6700,7 @@
       <c r="H16" s="15" t="n"/>
       <c r="I16" s="16" t="inlineStr">
         <is>
-          <t>Executioner's Blade</t>
+          <t>Executioner's Blade ×2</t>
         </is>
       </c>
       <c r="J16" s="16" t="inlineStr">
@@ -6850,7 +6756,7 @@
       <c r="H17" s="15" t="n"/>
       <c r="I17" s="16" t="inlineStr">
         <is>
-          <t>Twin Daggers</t>
+          <t>Twin Daggers ×2</t>
         </is>
       </c>
       <c r="J17" s="16" t="inlineStr">
@@ -6906,7 +6812,7 @@
       <c r="H18" s="15" t="n"/>
       <c r="I18" s="16" t="inlineStr">
         <is>
-          <t>Halberd</t>
+          <t>Halberd ×2</t>
         </is>
       </c>
       <c r="J18" s="16" t="inlineStr">
@@ -6962,7 +6868,7 @@
       <c r="H19" s="15" t="n"/>
       <c r="I19" s="16" t="inlineStr">
         <is>
-          <t>Berserker Axe</t>
+          <t>Berserker Axe ×2</t>
         </is>
       </c>
       <c r="J19" s="16" t="inlineStr">
@@ -7018,7 +6924,7 @@
       <c r="H20" s="15" t="n"/>
       <c r="I20" s="15" t="inlineStr">
         <is>
-          <t>Claymore</t>
+          <t>Claymore ×2</t>
         </is>
       </c>
       <c r="J20" s="15" t="inlineStr">
@@ -7074,7 +6980,7 @@
       <c r="H21" s="15" t="n"/>
       <c r="I21" s="15" t="inlineStr">
         <is>
-          <t>Claymore</t>
+          <t>Claymore ×2</t>
         </is>
       </c>
       <c r="J21" s="15" t="inlineStr">
@@ -7134,7 +7040,7 @@
       </c>
       <c r="I22" s="15" t="inlineStr">
         <is>
-          <t>Halberd</t>
+          <t>Halberd ×2</t>
         </is>
       </c>
       <c r="J22" s="15" t="inlineStr">
@@ -7161,7 +7067,7 @@
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>Cleave in half</t>
+          <t>Cleave</t>
         </is>
       </c>
       <c r="C23" s="17" t="inlineStr">
@@ -7190,7 +7096,7 @@
       <c r="H23" s="17" t="n"/>
       <c r="I23" s="18" t="inlineStr">
         <is>
-          <t>War Axe</t>
+          <t>War Axe ×2</t>
         </is>
       </c>
       <c r="J23" s="18" t="inlineStr">
@@ -7375,7 +7281,7 @@
       <c r="H27" s="13" t="n"/>
       <c r="I27" s="14" t="inlineStr">
         <is>
-          <t>Torch, Emberblade, Ember Striders, Ember Ring, Spark Pendant, Hand Torch, Grimoire of Flames</t>
+          <t>Torch ×2, Emberblade ×2, Ember Striders, Ember Ring ×2, Spark Pendant, Hand Torch ×2, Grimoire of Flames ×2</t>
         </is>
       </c>
       <c r="J27" s="14" t="inlineStr">
@@ -7779,7 +7685,7 @@
       <c r="H34" s="21" t="n"/>
       <c r="I34" s="22" t="inlineStr">
         <is>
-          <t>Onyx Glove</t>
+          <t>Onyx Glove ×2</t>
         </is>
       </c>
       <c r="J34" s="22" t="inlineStr">
@@ -7951,7 +7857,7 @@
       <c r="H37" s="21" t="n"/>
       <c r="I37" s="22" t="inlineStr">
         <is>
-          <t>Onyx Boots</t>
+          <t>Onyx Boots ×2</t>
         </is>
       </c>
       <c r="J37" s="22" t="inlineStr">
@@ -8007,7 +7913,7 @@
       <c r="H38" s="21" t="n"/>
       <c r="I38" s="22" t="inlineStr">
         <is>
-          <t>Magma Hammer</t>
+          <t>Magma Hammer ×2</t>
         </is>
       </c>
       <c r="J38" s="22" t="inlineStr">
@@ -8179,7 +8085,7 @@
       <c r="H41" s="21" t="n"/>
       <c r="I41" s="22" t="inlineStr">
         <is>
-          <t>Magma Hammer</t>
+          <t>Magma Hammer ×3</t>
         </is>
       </c>
       <c r="J41" s="22" t="inlineStr">
@@ -8239,7 +8145,7 @@
       </c>
       <c r="I42" s="22" t="inlineStr">
         <is>
-          <t>Onyx Guard Plate</t>
+          <t>Onyx Guard Plate ×2</t>
         </is>
       </c>
       <c r="J42" s="22" t="inlineStr">
@@ -8295,7 +8201,7 @@
       <c r="H43" s="21" t="n"/>
       <c r="I43" s="22" t="inlineStr">
         <is>
-          <t>Onyx Glove</t>
+          <t>Onyx Glove ×2</t>
         </is>
       </c>
       <c r="J43" s="22" t="inlineStr">
@@ -8355,7 +8261,7 @@
       </c>
       <c r="I44" s="22" t="inlineStr">
         <is>
-          <t>Big Onyx Sword</t>
+          <t>Big Onyx Sword ×2</t>
         </is>
       </c>
       <c r="J44" s="22" t="inlineStr">
@@ -8411,7 +8317,7 @@
       <c r="H45" s="21" t="n"/>
       <c r="I45" s="22" t="inlineStr">
         <is>
-          <t>Big Onyx Sword</t>
+          <t>Big Onyx Sword ×3</t>
         </is>
       </c>
       <c r="J45" s="22" t="inlineStr">
@@ -8544,7 +8450,7 @@
       <c r="H48" s="13" t="n"/>
       <c r="I48" s="14" t="inlineStr">
         <is>
-          <t>Rusty Dagger, Serpent Knife, Venomfang Dagger, Venom Gloves, Venom Ring, Toxic Ring</t>
+          <t>Rusty Dagger ×2, Serpent Knife ×3, Venomfang Dagger ×2, Venom Gloves, Venom Ring ×2, Toxic Ring</t>
         </is>
       </c>
       <c r="J48" s="14" t="inlineStr">
@@ -8720,7 +8626,7 @@
       </c>
       <c r="I51" s="18" t="inlineStr">
         <is>
-          <t>Basilisk Fang</t>
+          <t>Basilisk Fang ×2</t>
         </is>
       </c>
       <c r="J51" s="18" t="inlineStr">
@@ -8832,7 +8738,7 @@
       <c r="H53" s="17" t="n"/>
       <c r="I53" s="18" t="inlineStr">
         <is>
-          <t>Basilisk Fang</t>
+          <t>Basilisk Fang ×6</t>
         </is>
       </c>
       <c r="J53" s="18" t="inlineStr">
@@ -8905,7 +8811,7 @@
       <c r="H55" s="13" t="n"/>
       <c r="I55" s="14" t="inlineStr">
         <is>
-          <t>Serrated Knife, Cleaver, Pitchfork, Reaver Axe, Spiked Flail, Studded Gloves, Bleeding Ring, Bloodthirst Ring, Bone Charm, Vampiric Pendant</t>
+          <t>Serrated Knife ×2, Cleaver, Pitchfork, Reaver Axe ×2, Spiked Flail, Studded Gloves, Bleeding Ring ×2, Bloodthirst Ring, Bone Charm, Vampiric Pendant</t>
         </is>
       </c>
       <c r="J55" s="14" t="inlineStr">
@@ -8961,7 +8867,7 @@
       <c r="H56" s="15" t="n"/>
       <c r="I56" s="16" t="inlineStr">
         <is>
-          <t>Blood Ring</t>
+          <t>Blood Ring ×2</t>
         </is>
       </c>
       <c r="J56" s="16" t="inlineStr">
@@ -9189,7 +9095,7 @@
       </c>
       <c r="I60" s="16" t="inlineStr">
         <is>
-          <t>Spiked Flail</t>
+          <t>Spiked Flail ×2</t>
         </is>
       </c>
       <c r="J60" s="16" t="inlineStr">
@@ -9301,7 +9207,7 @@
       <c r="H62" s="17" t="n"/>
       <c r="I62" s="18" t="inlineStr">
         <is>
-          <t>Blood Greaves</t>
+          <t>Blood Greaves ×2</t>
         </is>
       </c>
       <c r="J62" s="18" t="inlineStr">
@@ -9477,7 +9383,7 @@
       <c r="H65" s="17" t="n"/>
       <c r="I65" s="18" t="inlineStr">
         <is>
-          <t>Blood Gauntlets</t>
+          <t>Blood Gauntlets ×2</t>
         </is>
       </c>
       <c r="J65" s="18" t="inlineStr">
@@ -9597,7 +9503,7 @@
       </c>
       <c r="I67" s="18" t="inlineStr">
         <is>
-          <t>War Axe</t>
+          <t>War Axe ×2</t>
         </is>
       </c>
       <c r="J67" s="18" t="inlineStr">
@@ -9653,7 +9559,7 @@
       <c r="H68" s="17" t="n"/>
       <c r="I68" s="18" t="inlineStr">
         <is>
-          <t>Blood Gauntlets</t>
+          <t>Blood Gauntlets ×2</t>
         </is>
       </c>
       <c r="J68" s="18" t="inlineStr">
@@ -9693,7 +9599,7 @@
       </c>
       <c r="E69" s="17" t="inlineStr">
         <is>
-          <t>Defense</t>
+          <t>Défense</t>
         </is>
       </c>
       <c r="F69" s="17" t="inlineStr">
@@ -9709,7 +9615,7 @@
       <c r="H69" s="17" t="n"/>
       <c r="I69" s="18" t="inlineStr">
         <is>
-          <t>Blood Plate</t>
+          <t>Blood Plate ×2</t>
         </is>
       </c>
       <c r="J69" s="18" t="inlineStr">
@@ -9765,7 +9671,7 @@
       <c r="H70" s="21" t="n"/>
       <c r="I70" s="21" t="inlineStr">
         <is>
-          <t>Great Scythe</t>
+          <t>Great Scythe ×3</t>
         </is>
       </c>
       <c r="J70" s="21" t="inlineStr">
@@ -9825,7 +9731,7 @@
       </c>
       <c r="I71" s="21" t="inlineStr">
         <is>
-          <t>Great Scythe</t>
+          <t>Great Scythe ×2</t>
         </is>
       </c>
       <c r="J71" s="21" t="inlineStr">
@@ -9898,7 +9804,7 @@
       <c r="H73" s="13" t="n"/>
       <c r="I73" s="14" t="inlineStr">
         <is>
-          <t>Ice Pick, Frostbrand, Frost Band, Frost Signet</t>
+          <t>Ice Pick ×2, Frostbrand ×2, Frost Band ×2, Frost Signet</t>
         </is>
       </c>
       <c r="J73" s="14" t="inlineStr">
@@ -10014,7 +9920,7 @@
       <c r="H75" s="15" t="n"/>
       <c r="I75" s="16" t="inlineStr">
         <is>
-          <t>Frost Ring</t>
+          <t>Frost Ring ×2</t>
         </is>
       </c>
       <c r="J75" s="16" t="inlineStr">
@@ -10070,7 +9976,7 @@
       <c r="H76" s="16" t="n"/>
       <c r="I76" s="16" t="inlineStr">
         <is>
-          <t>Halberd</t>
+          <t>Halberd ×2</t>
         </is>
       </c>
       <c r="J76" s="16" t="inlineStr">
@@ -10182,7 +10088,7 @@
       <c r="H78" s="17" t="n"/>
       <c r="I78" s="18" t="inlineStr">
         <is>
-          <t>Perfect Frost Ring</t>
+          <t>Perfect Frost Ring ×2</t>
         </is>
       </c>
       <c r="J78" s="18" t="inlineStr">
@@ -10407,7 +10313,7 @@
       </c>
       <c r="E83" s="17" t="inlineStr">
         <is>
-          <t>Defense</t>
+          <t>Défense</t>
         </is>
       </c>
       <c r="F83" s="17" t="inlineStr">
@@ -10423,7 +10329,7 @@
       <c r="H83" s="17" t="n"/>
       <c r="I83" s="18" t="inlineStr">
         <is>
-          <t>Crusader Plate</t>
+          <t>Crusader Plate ×3</t>
         </is>
       </c>
       <c r="J83" s="18" t="inlineStr">
@@ -10599,7 +10505,7 @@
       <c r="H86" s="17" t="n"/>
       <c r="I86" s="18" t="inlineStr">
         <is>
-          <t>Crusader Greaves</t>
+          <t>Crusader Greaves ×2</t>
         </is>
       </c>
       <c r="J86" s="18" t="inlineStr">
@@ -10655,7 +10561,7 @@
       <c r="H87" s="17" t="n"/>
       <c r="I87" s="18" t="inlineStr">
         <is>
-          <t>War Axe</t>
+          <t>War Axe ×2</t>
         </is>
       </c>
       <c r="J87" s="18" t="inlineStr">
@@ -10711,7 +10617,7 @@
       <c r="H88" s="17" t="n"/>
       <c r="I88" s="18" t="inlineStr">
         <is>
-          <t>Siege Maul</t>
+          <t>Siege Maul ×2</t>
         </is>
       </c>
       <c r="J88" s="18" t="inlineStr">
@@ -10767,7 +10673,7 @@
       <c r="H89" s="17" t="n"/>
       <c r="I89" s="18" t="inlineStr">
         <is>
-          <t>Tower Shield</t>
+          <t>Tower Shield ×2</t>
         </is>
       </c>
       <c r="J89" s="18" t="inlineStr">
@@ -10884,7 +10790,7 @@
       </c>
       <c r="E92" s="13" t="inlineStr">
         <is>
-          <t>Defense</t>
+          <t>Défense</t>
         </is>
       </c>
       <c r="F92" s="13" t="inlineStr">
@@ -10940,7 +10846,7 @@
       </c>
       <c r="E93" s="13" t="inlineStr">
         <is>
-          <t>Defense</t>
+          <t>Défense</t>
         </is>
       </c>
       <c r="F93" s="13" t="inlineStr">
@@ -10956,7 +10862,7 @@
       <c r="H93" s="13" t="n"/>
       <c r="I93" s="14" t="inlineStr">
         <is>
-          <t>Wooden Club, Mace, Quarterstaff, Pitchfork, Leather Armor, Hide Armor, Stonetread Boots, Leather Gloves, Gauntlets, Vigor Ring, Wooden Shield, Buckler, Warding Shield</t>
+          <t>Wooden Club, Mace ×2, Quarterstaff ×2, Pitchfork, Leather Armor ×2, Hide Armor, Stonetread Boots, Leather Gloves, Gauntlets, Vigor Ring, Wooden Shield ×2, Buckler, Warding Shield</t>
         </is>
       </c>
       <c r="J93" s="14" t="inlineStr">
@@ -10996,7 +10902,7 @@
       </c>
       <c r="E94" s="13" t="inlineStr">
         <is>
-          <t>Defense</t>
+          <t>Défense</t>
         </is>
       </c>
       <c r="F94" s="13" t="inlineStr">
@@ -11012,7 +10918,7 @@
       <c r="H94" s="13" t="n"/>
       <c r="I94" s="14" t="inlineStr">
         <is>
-          <t>Stone Hammer, Warhammer, Leather Armor, Iron Ring, Stone Ring, Wooden Shield, Reinforced Shield, Warding Shield</t>
+          <t>Stone Hammer ×2, Warhammer ×2, Leather Armor, Iron Ring ×2, Stone Ring ×2, Wooden Shield, Reinforced Shield ×3, Warding Shield</t>
         </is>
       </c>
       <c r="J94" s="14" t="inlineStr">
@@ -11052,7 +10958,7 @@
       </c>
       <c r="E95" s="13" t="inlineStr">
         <is>
-          <t>Defense</t>
+          <t>Défense</t>
         </is>
       </c>
       <c r="F95" s="13" t="inlineStr">
@@ -11068,7 +10974,7 @@
       <c r="H95" s="13" t="n"/>
       <c r="I95" s="14" t="inlineStr">
         <is>
-          <t>Traveler's Garb, Padded Vest, Chainmail</t>
+          <t>Traveler's Garb ×3, Padded Vest ×2, Chainmail ×3</t>
         </is>
       </c>
       <c r="J95" s="14" t="inlineStr">
@@ -11108,7 +11014,7 @@
       </c>
       <c r="E96" s="13" t="inlineStr">
         <is>
-          <t>Defense</t>
+          <t>Défense</t>
         </is>
       </c>
       <c r="F96" s="13" t="inlineStr">
@@ -11124,7 +11030,7 @@
       <c r="H96" s="13" t="n"/>
       <c r="I96" s="14" t="inlineStr">
         <is>
-          <t>Chainmail, Basic Iron Plate, Spiked Armor, Berserker Hide</t>
+          <t>Chainmail, Basic Iron Plate ×2, Spiked Armor ×3, Berserker Hide</t>
         </is>
       </c>
       <c r="J96" s="14" t="inlineStr">
@@ -11164,7 +11070,7 @@
       </c>
       <c r="E97" s="15" t="inlineStr">
         <is>
-          <t>Defense</t>
+          <t>Défense</t>
         </is>
       </c>
       <c r="F97" s="15" t="inlineStr">
@@ -11220,7 +11126,7 @@
       </c>
       <c r="E98" s="15" t="inlineStr">
         <is>
-          <t>Defense</t>
+          <t>Défense</t>
         </is>
       </c>
       <c r="F98" s="15" t="inlineStr">
@@ -11348,7 +11254,7 @@
       <c r="H100" s="15" t="n"/>
       <c r="I100" s="16" t="inlineStr">
         <is>
-          <t>Forge Hammer</t>
+          <t>Forge Hammer ×3</t>
         </is>
       </c>
       <c r="J100" s="16" t="inlineStr">
@@ -11388,7 +11294,7 @@
       </c>
       <c r="E101" s="15" t="inlineStr">
         <is>
-          <t>Defense</t>
+          <t>Défense</t>
         </is>
       </c>
       <c r="F101" s="15" t="inlineStr">
@@ -11444,7 +11350,7 @@
       </c>
       <c r="E102" s="15" t="inlineStr">
         <is>
-          <t>Defense</t>
+          <t>Défense</t>
         </is>
       </c>
       <c r="F102" s="15" t="inlineStr">
@@ -11460,7 +11366,7 @@
       <c r="H102" s="15" t="n"/>
       <c r="I102" s="16" t="inlineStr">
         <is>
-          <t>Stone Armor, Stone Glove, Stone Boots</t>
+          <t>Stone Armor ×3, Stone Glove, Stone Boots</t>
         </is>
       </c>
       <c r="J102" s="16" t="inlineStr">
@@ -11500,7 +11406,7 @@
       </c>
       <c r="E103" s="15" t="inlineStr">
         <is>
-          <t>Defense</t>
+          <t>Défense</t>
         </is>
       </c>
       <c r="F103" s="15" t="inlineStr">
@@ -11556,7 +11462,7 @@
       </c>
       <c r="E104" s="15" t="inlineStr">
         <is>
-          <t>Defense</t>
+          <t>Défense</t>
         </is>
       </c>
       <c r="F104" s="15" t="inlineStr">
@@ -11572,7 +11478,7 @@
       <c r="H104" s="15" t="n"/>
       <c r="I104" s="16" t="inlineStr">
         <is>
-          <t>Tower Shield, Reinforced Shield</t>
+          <t>Tower Shield ×3, Reinforced Shield</t>
         </is>
       </c>
       <c r="J104" s="16" t="inlineStr">
@@ -11612,7 +11518,7 @@
       </c>
       <c r="E105" s="15" t="inlineStr">
         <is>
-          <t>Defense</t>
+          <t>Défense</t>
         </is>
       </c>
       <c r="F105" s="15" t="inlineStr">
@@ -11628,7 +11534,7 @@
       <c r="H105" s="15" t="n"/>
       <c r="I105" s="16" t="inlineStr">
         <is>
-          <t>Stone Armor, Stone Glove, Stone Boots</t>
+          <t>Stone Armor ×6, Stone Glove ×3, Stone Boots ×3</t>
         </is>
       </c>
       <c r="J105" s="16" t="inlineStr">
@@ -11668,7 +11574,7 @@
       </c>
       <c r="E106" s="15" t="inlineStr">
         <is>
-          <t>Defense</t>
+          <t>Défense</t>
         </is>
       </c>
       <c r="F106" s="15" t="inlineStr">
@@ -11780,7 +11686,7 @@
       </c>
       <c r="E108" s="15" t="inlineStr">
         <is>
-          <t>Defense</t>
+          <t>Défense</t>
         </is>
       </c>
       <c r="F108" s="15" t="inlineStr">
@@ -11796,7 +11702,7 @@
       <c r="H108" s="15" t="n"/>
       <c r="I108" s="16" t="inlineStr">
         <is>
-          <t>Siege Maul</t>
+          <t>Siege Maul ×2</t>
         </is>
       </c>
       <c r="J108" s="16" t="inlineStr">
@@ -11836,7 +11742,7 @@
       </c>
       <c r="E109" s="17" t="inlineStr">
         <is>
-          <t>Defense</t>
+          <t>Défense</t>
         </is>
       </c>
       <c r="F109" s="17" t="inlineStr">
@@ -11852,7 +11758,7 @@
       <c r="H109" s="17" t="n"/>
       <c r="I109" s="18" t="inlineStr">
         <is>
-          <t>Forgemaster's Mail, Crusader Plate, Blood Plate</t>
+          <t>Forgemaster's Mail ×2, Crusader Plate, Blood Plate ×2</t>
         </is>
       </c>
       <c r="J109" s="18" t="inlineStr">
@@ -11948,7 +11854,7 @@
       </c>
       <c r="E111" s="17" t="inlineStr">
         <is>
-          <t>Defense</t>
+          <t>Défense</t>
         </is>
       </c>
       <c r="F111" s="17" t="inlineStr">
@@ -11964,7 +11870,7 @@
       <c r="H111" s="17" t="n"/>
       <c r="I111" s="18" t="inlineStr">
         <is>
-          <t>Forgemaster's Mail</t>
+          <t>Forgemaster's Mail ×3</t>
         </is>
       </c>
       <c r="J111" s="18" t="inlineStr">
@@ -12004,7 +11910,7 @@
       </c>
       <c r="E112" s="17" t="inlineStr">
         <is>
-          <t>Defense</t>
+          <t>Défense</t>
         </is>
       </c>
       <c r="F112" s="17" t="inlineStr">
@@ -12060,7 +11966,7 @@
       </c>
       <c r="E113" s="17" t="inlineStr">
         <is>
-          <t>Defense</t>
+          <t>Défense</t>
         </is>
       </c>
       <c r="F113" s="17" t="inlineStr">
@@ -12132,7 +12038,7 @@
       <c r="H114" s="17" t="n"/>
       <c r="I114" s="18" t="inlineStr">
         <is>
-          <t>Siege Maul</t>
+          <t>Siege Maul ×2</t>
         </is>
       </c>
       <c r="J114" s="18" t="inlineStr">
@@ -12172,7 +12078,7 @@
       </c>
       <c r="E115" s="21" t="inlineStr">
         <is>
-          <t>Defense</t>
+          <t>Défense</t>
         </is>
       </c>
       <c r="F115" s="21" t="inlineStr">
@@ -12188,7 +12094,7 @@
       <c r="H115" s="21" t="n"/>
       <c r="I115" s="22" t="inlineStr">
         <is>
-          <t>Onyx Guard Plate</t>
+          <t>Onyx Guard Plate ×3</t>
         </is>
       </c>
       <c r="J115" s="22" t="inlineStr">
@@ -12228,7 +12134,7 @@
       </c>
       <c r="E116" s="13" t="inlineStr">
         <is>
-          <t>Defense</t>
+          <t>Défense</t>
         </is>
       </c>
       <c r="F116" s="13" t="inlineStr">
@@ -12317,7 +12223,7 @@
       <c r="H118" s="13" t="n"/>
       <c r="I118" s="14" t="inlineStr">
         <is>
-          <t>Hide Armor, Vigor Ring, Healing Book, Holy Sword</t>
+          <t>Hide Armor, Vigor Ring, Healing Book ×2, Holy Sword</t>
         </is>
       </c>
       <c r="J118" s="14" t="inlineStr">
@@ -12529,7 +12435,7 @@
       </c>
       <c r="E122" s="17" t="inlineStr">
         <is>
-          <t>Defense</t>
+          <t>Défense</t>
         </is>
       </c>
       <c r="F122" s="17" t="inlineStr">
@@ -12601,7 +12507,7 @@
       <c r="H123" s="17" t="n"/>
       <c r="I123" s="18" t="inlineStr">
         <is>
-          <t>Crusader Gauntlets</t>
+          <t>Crusader Gauntlets ×2</t>
         </is>
       </c>
       <c r="J123" s="18" t="inlineStr">
@@ -12842,7 +12748,7 @@
       <c r="H128" s="13" t="n"/>
       <c r="I128" s="14" t="inlineStr">
         <is>
-          <t>Crystal Wand, Spark Ring, Forge Ring, Copper Amulet, Quartz Pendant, Spark Pendant, Energizing Pendant, Spellbook, Apprentice Scepter, Tome of Power</t>
+          <t>Crystal Wand, Spark Ring ×2, Forge Ring, Copper Amulet, Quartz Pendant, Spark Pendant, Energizing Pendant, Spellbook, Apprentice Scepter, Tome of Power</t>
         </is>
       </c>
       <c r="J128" s="14" t="inlineStr">
@@ -12898,7 +12804,7 @@
       <c r="H129" s="15" t="n"/>
       <c r="I129" s="16" t="inlineStr">
         <is>
-          <t>Crystal Wand</t>
+          <t>Crystal Wand ×2</t>
         </is>
       </c>
       <c r="J129" s="16" t="inlineStr">
@@ -13014,7 +12920,7 @@
       <c r="H131" s="15" t="n"/>
       <c r="I131" s="16" t="inlineStr">
         <is>
-          <t>Onyx Boots, Mail Boots, Crusader Greaves, Blood Greaves, Energizing Pendant</t>
+          <t>Onyx Boots ×2, Mail Boots ×2, Crusader Greaves ×2, Dunir's Blessed Sabatons, Barbarian Boots, Blood Greaves, Energizing Pendant</t>
         </is>
       </c>
       <c r="J131" s="16" t="inlineStr">
@@ -13294,7 +13200,7 @@
       <c r="H136" s="15" t="n"/>
       <c r="I136" s="16" t="inlineStr">
         <is>
-          <t>Sapphire Amulet, Nice Sapphire Amulet</t>
+          <t>Sapphire Amulet, Nice Sapphire Amulet ×2</t>
         </is>
       </c>
       <c r="J136" s="16" t="inlineStr">
@@ -13462,7 +13368,7 @@
       <c r="H139" s="21" t="n"/>
       <c r="I139" s="22" t="inlineStr">
         <is>
-          <t>Perfect Sapphire Amulet</t>
+          <t>Perfect Sapphire Amulet ×3</t>
         </is>
       </c>
       <c r="J139" s="22" t="inlineStr">
@@ -13535,7 +13441,7 @@
       <c r="H141" s="13" t="n"/>
       <c r="I141" s="14" t="inlineStr">
         <is>
-          <t>Worn Boots, Leather Boots, Traveler Boots, Sandals</t>
+          <t>Worn Boots, Leather Boots ×2, Traveler Boots, Sandals</t>
         </is>
       </c>
       <c r="J141" s="14" t="inlineStr">
@@ -13759,7 +13665,7 @@
       <c r="H145" s="15" t="n"/>
       <c r="I145" s="16" t="inlineStr">
         <is>
-          <t>Swift Boots, Mail Boots, Crusader Greaves, Blood Greaves, Swift Striders, Ember Striders</t>
+          <t>Swift Boots ×3, Mail Boots ×2, Crusader Greaves, Blood Greaves, Swift Striders, Ember Striders</t>
         </is>
       </c>
       <c r="J145" s="16" t="inlineStr">
@@ -14000,7 +13906,7 @@
       <c r="H150" s="13" t="n"/>
       <c r="I150" s="14" t="inlineStr">
         <is>
-          <t>Training Sword, Berserker Axe, Padded Vest, Power Ring, Ring of Might, Apprentice Scepter, Scepter of Command</t>
+          <t>Training Sword, Berserker Axe, Padded Vest, Power Ring ×2, Ring of Might, Apprentice Scepter, Scepter of Command</t>
         </is>
       </c>
       <c r="J150" s="14" t="inlineStr">
@@ -14353,7 +14259,7 @@
       <c r="H157" s="13" t="n"/>
       <c r="I157" s="14" t="inlineStr">
         <is>
-          <t>Miner's Gloves, Mail Glove, Crusader Gauntlets, Work Gloves</t>
+          <t>Miner's Gloves ×2, Mail Glove ×2, Crusader Gauntlets ×2, Work Gloves</t>
         </is>
       </c>
       <c r="J157" s="14" t="inlineStr">
@@ -14409,7 +14315,7 @@
       <c r="H158" s="13" t="n"/>
       <c r="I158" s="14" t="inlineStr">
         <is>
-          <t>Quarterstaff, Cloth Gloves, Leather Gloves, Nimble Ring, Quartz Pendant, Lucky Charm, Amulet of Focus, Buckler, Spellbook, Healing Book, Tome of Power</t>
+          <t>Quarterstaff, Cloth Gloves ×2, Leather Gloves, Nimble Ring ×2, Quartz Pendant, Lucky Charm, Amulet of Focus, Buckler, Spellbook, Healing Book, Tome of Power</t>
         </is>
       </c>
       <c r="J158" s="14" t="inlineStr">
@@ -14633,7 +14539,7 @@
       <c r="H162" s="17" t="n"/>
       <c r="I162" s="18" t="inlineStr">
         <is>
-          <t>Mail Glove</t>
+          <t>Mail Glove ×2</t>
         </is>
       </c>
       <c r="J162" s="18" t="inlineStr">
@@ -14689,7 +14595,7 @@
       <c r="H163" s="21" t="n"/>
       <c r="I163" s="22" t="inlineStr">
         <is>
-          <t>Onyx Glove</t>
+          <t>Onyx Glove ×2</t>
         </is>
       </c>
       <c r="J163" s="22" t="inlineStr">
@@ -14829,7 +14735,7 @@
       <c r="H167" s="13" t="n"/>
       <c r="I167" s="14" t="inlineStr">
         <is>
-          <t>Barbarian Harness ×2, Barbarian Boots ×1</t>
+          <t>Barbarian Harness ×2, Barbarian Boots</t>
         </is>
       </c>
       <c r="J167" s="14" t="inlineStr">
@@ -14933,7 +14839,7 @@
       <c r="H169" s="13" t="n"/>
       <c r="I169" s="14" t="inlineStr">
         <is>
-          <t>Barbarian Harness ×1, Barbarian Boots ×2</t>
+          <t>Barbarian Harness, Barbarian Boots ×2</t>
         </is>
       </c>
       <c r="J169" s="14" t="inlineStr">
@@ -14985,7 +14891,7 @@
       <c r="H170" s="13" t="n"/>
       <c r="I170" s="14" t="inlineStr">
         <is>
-          <t>Barbarian Harness ×1</t>
+          <t>Barbarian Harness</t>
         </is>
       </c>
       <c r="J170" s="14" t="inlineStr">
@@ -15086,11 +14992,7 @@
           <t>Mêlée</t>
         </is>
       </c>
-      <c r="H172" s="13" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="H172" s="13" t="n"/>
       <c r="I172" s="14" t="inlineStr">
         <is>
           <t>Barbarian Bracers ×2</t>
@@ -15256,7 +15158,7 @@
       <c r="H177" s="13" t="n"/>
       <c r="I177" s="14" t="inlineStr">
         <is>
-          <t>Plate ×1, Gauntlets ×2, Sabatons ×2</t>
+          <t>Dunir's Blessed Plate, Dunir's Blessed Gauntlets ×2, Dunir's Blessed Sabatons ×2</t>
         </is>
       </c>
       <c r="J177" s="14" t="inlineStr">
@@ -15307,12 +15209,12 @@
       </c>
       <c r="H178" s="13" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="I178" s="14" t="inlineStr">
         <is>
-          <t>Plate ×1</t>
+          <t>Dunir's Blessed Plate</t>
         </is>
       </c>
       <c r="J178" s="14" t="inlineStr">
@@ -15366,7 +15268,7 @@
       <c r="H179" s="13" t="n"/>
       <c r="I179" s="14" t="inlineStr">
         <is>
-          <t>Gauntlets ×2, Sabatons ×1</t>
+          <t>Dunir's Blessed Gauntlets ×2, Dunir's Blessed Sabatons</t>
         </is>
       </c>
       <c r="J179" s="14" t="inlineStr">
@@ -15418,7 +15320,7 @@
       <c r="H180" s="13" t="n"/>
       <c r="I180" s="14" t="inlineStr">
         <is>
-          <t>Plate ×1</t>
+          <t>Dunir's Blessed Plate</t>
         </is>
       </c>
       <c r="J180" s="14" t="inlineStr">
@@ -15470,7 +15372,7 @@
       <c r="H181" s="13" t="n"/>
       <c r="I181" s="14" t="inlineStr">
         <is>
-          <t>Gauntlets ×2</t>
+          <t>Dunir's Blessed Gauntlets ×2</t>
         </is>
       </c>
       <c r="J181" s="14" t="inlineStr">
@@ -15522,7 +15424,7 @@
       <c r="H182" s="13" t="n"/>
       <c r="I182" s="14" t="inlineStr">
         <is>
-          <t>Plate ×2, Sabatons ×1</t>
+          <t>Dunir's Blessed Plate ×2, Dunir's Blessed Sabatons</t>
         </is>
       </c>
       <c r="J182" s="14" t="inlineStr">
@@ -15574,7 +15476,7 @@
       <c r="H183" s="13" t="n"/>
       <c r="I183" s="14" t="inlineStr">
         <is>
-          <t>Plate ×2</t>
+          <t>Dunir's Blessed Plate ×2</t>
         </is>
       </c>
       <c r="J183" s="14" t="inlineStr">
@@ -15625,12 +15527,12 @@
       </c>
       <c r="H184" s="13" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="I184" s="14" t="inlineStr">
         <is>
-          <t>Sabatons ×2</t>
+          <t>Dunir's Blessed Sabatons ×2</t>
         </is>
       </c>
       <c r="J184" s="14" t="inlineStr">
@@ -15679,14 +15581,10 @@
           <t>Mêlée</t>
         </is>
       </c>
-      <c r="H185" s="13" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="H185" s="13" t="n"/>
       <c r="I185" s="14" t="inlineStr">
         <is>
-          <t>Gauntlets ×1</t>
+          <t>Dunir's Blessed Gauntlets</t>
         </is>
       </c>
       <c r="J185" s="14" t="inlineStr">
@@ -15702,6 +15600,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A2:L2"/>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
   </mergeCells>
@@ -15716,7 +15615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P150"/>
+  <dimension ref="A1:P140"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" style="140" min="1" max="1"/>
@@ -19151,7 +19050,7 @@
       </c>
       <c r="D67" s="151" t="inlineStr">
         <is>
-          <t>Épique</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="E67" s="143" t="inlineStr">
@@ -21080,7 +20979,7 @@
       </c>
       <c r="D116" s="151" t="inlineStr">
         <is>
-          <t>Épique</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="E116" s="143" t="inlineStr">
@@ -21844,7 +21743,7 @@
       </c>
       <c r="D132" s="151" t="inlineStr">
         <is>
-          <t>Épique</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="E132" s="143" t="inlineStr">
@@ -22161,36 +22060,15 @@
         </is>
       </c>
     </row>
-    <row r="141" ht="15" customHeight="1" s="140">
-      <c r="A141" s="51" t="n"/>
-      <c r="B141" s="51" t="n"/>
-      <c r="C141" s="51" t="n"/>
-      <c r="D141" s="51" t="n"/>
-      <c r="E141" s="51" t="n"/>
-      <c r="O141" s="51" t="n"/>
-    </row>
+    <row r="141" ht="15" customHeight="1" s="140"/>
     <row r="142" ht="15" customHeight="1" s="140"/>
-    <row r="143" ht="15" customHeight="1" s="140">
-      <c r="P143" s="2" t="n"/>
-    </row>
-    <row r="144" ht="15" customHeight="1" s="140">
-      <c r="P144" s="2" t="n"/>
-    </row>
-    <row r="145" ht="15" customHeight="1" s="140">
-      <c r="P145" s="2" t="n"/>
-    </row>
+    <row r="143" ht="15" customHeight="1" s="140"/>
+    <row r="144" ht="15" customHeight="1" s="140"/>
+    <row r="145" ht="15" customHeight="1" s="140"/>
     <row r="146" ht="15" customHeight="1" s="140"/>
     <row r="147" ht="15" customHeight="1" s="140"/>
-    <row r="148">
-      <c r="P148" s="2" t="n"/>
-    </row>
-    <row r="149">
-      <c r="P149" s="2" t="n"/>
-    </row>
-    <row r="150">
-      <c r="P150" s="2" t="n"/>
-    </row>
   </sheetData>
+  <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
@@ -22412,7 +22290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D88"/>
+  <dimension ref="A1:D95"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="140" min="1" max="1"/>
@@ -23092,51 +22970,51 @@
       </c>
     </row>
     <row r="36" ht="24" customHeight="1" s="140">
-      <c r="A36" s="46" t="inlineStr">
+      <c r="A36" s="44" t="inlineStr">
+        <is>
+          <t>defausser-piocher</t>
+        </is>
+      </c>
+      <c r="B36" s="44" t="inlineStr">
+        <is>
+          <t>Échanger des cartes</t>
+        </is>
+      </c>
+      <c r="C36" s="44" t="inlineStr">
+        <is>
+          <t>Défausse N carte(s) au hasard de la main, puis en repioche autant (échange sec). Rien ne se passe si la main est vide.</t>
+        </is>
+      </c>
+      <c r="D36" s="44" t="inlineStr">
+        <is>
+          <t>valeur: N</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1" s="140">
+      <c r="A37" s="46" t="inlineStr">
         <is>
           <t>── EFFETS SPÉCIAUX OFFENSIFS ──</t>
         </is>
       </c>
-      <c r="B36" s="46" t="n"/>
-      <c r="C36" s="46" t="n"/>
-      <c r="D36" s="46" t="n"/>
-    </row>
-    <row r="37" ht="30" customHeight="1" s="140">
-      <c r="A37" s="44" t="inlineStr">
-        <is>
-          <t>cleave-adjacent</t>
-        </is>
-      </c>
-      <c r="B37" s="44" t="inlineStr">
-        <is>
-          <t>Cleave adjacent</t>
-        </is>
-      </c>
-      <c r="C37" s="44" t="inlineStr">
-        <is>
-          <t>N dégâts à chaque ennemi adjacent à la cible.</t>
-        </is>
-      </c>
-      <c r="D37" s="44" t="inlineStr">
-        <is>
-          <t>valeur: N</t>
-        </is>
-      </c>
+      <c r="B37" s="46" t="n"/>
+      <c r="C37" s="46" t="n"/>
+      <c r="D37" s="46" t="n"/>
     </row>
     <row r="38" ht="30" customHeight="1" s="140">
       <c r="A38" s="44" t="inlineStr">
         <is>
-          <t>coup-de-grace</t>
+          <t>cleave-adjacent</t>
         </is>
       </c>
       <c r="B38" s="44" t="inlineStr">
         <is>
-          <t>Coup de grâce</t>
+          <t>Cleave adjacent</t>
         </is>
       </c>
       <c r="C38" s="44" t="inlineStr">
         <is>
-          <t>Si la cible meurt : N dégâts à un ennemi aléatoire.</t>
+          <t>N dégâts à chaque ennemi adjacent à la cible.</t>
         </is>
       </c>
       <c r="D38" s="44" t="inlineStr">
@@ -23148,17 +23026,17 @@
     <row r="39" ht="30" customHeight="1" s="140">
       <c r="A39" s="44" t="inlineStr">
         <is>
-          <t>rebond</t>
+          <t>coup-de-grace</t>
         </is>
       </c>
       <c r="B39" s="44" t="inlineStr">
         <is>
-          <t>Rebond (kill)</t>
+          <t>Coup de grâce</t>
         </is>
       </c>
       <c r="C39" s="44" t="inlineStr">
         <is>
-          <t>Si la cible meurt : N dégâts à l'ennemi suivant.</t>
+          <t>Si la cible meurt : N dégâts à un ennemi aléatoire.</t>
         </is>
       </c>
       <c r="D39" s="44" t="inlineStr">
@@ -23170,17 +23048,17 @@
     <row r="40" ht="30" customHeight="1" s="140">
       <c r="A40" s="44" t="inlineStr">
         <is>
-          <t>pierre-par-ennemi</t>
+          <t>rebond</t>
         </is>
       </c>
       <c r="B40" s="44" t="inlineStr">
         <is>
-          <t>Pierre par ennemi</t>
+          <t>Rebond (kill)</t>
         </is>
       </c>
       <c r="C40" s="44" t="inlineStr">
         <is>
-          <t>N Pierre par ennemi vivant.</t>
+          <t>Si la cible meurt : N dégâts à l'ennemi suivant.</t>
         </is>
       </c>
       <c r="D40" s="44" t="inlineStr">
@@ -23192,203 +23070,203 @@
     <row r="41" ht="30" customHeight="1" s="140">
       <c r="A41" s="44" t="inlineStr">
         <is>
-          <t>degats-si-gel</t>
+          <t>pierre-par-ennemi</t>
         </is>
       </c>
       <c r="B41" s="44" t="inlineStr">
         <is>
-          <t>Dégâts si gelé</t>
+          <t>Pierre par ennemi</t>
         </is>
       </c>
       <c r="C41" s="44" t="inlineStr">
         <is>
-          <t>N dégâts + bonus si la cible est gelée.</t>
+          <t>N Pierre par ennemi vivant.</t>
         </is>
       </c>
       <c r="D41" s="44" t="inlineStr">
         <is>
-          <t>valeur: N, bonus: X</t>
+          <t>valeur: N</t>
         </is>
       </c>
     </row>
     <row r="42" ht="30" customHeight="1" s="140">
       <c r="A42" s="44" t="inlineStr">
         <is>
-          <t>degats-si-faible</t>
+          <t>degats-si-gel</t>
         </is>
       </c>
       <c r="B42" s="44" t="inlineStr">
         <is>
-          <t>Dégâts si PV bas</t>
+          <t>Dégâts si gelé</t>
         </is>
       </c>
       <c r="C42" s="44" t="inlineStr">
         <is>
-          <t>N dégâts, doublés sous le seuil de PV.</t>
+          <t>N dégâts + bonus si la cible est gelée.</t>
         </is>
       </c>
       <c r="D42" s="44" t="inlineStr">
         <is>
-          <t>valeur: N, seuil: %</t>
+          <t>valeur: N, bonus: X</t>
         </is>
       </c>
     </row>
     <row r="43" ht="30" customHeight="1" s="140">
       <c r="A43" s="44" t="inlineStr">
         <is>
-          <t>degats-execution</t>
+          <t>degats-si-faible</t>
         </is>
       </c>
       <c r="B43" s="44" t="inlineStr">
         <is>
-          <t>Exécution</t>
+          <t>Dégâts si PV bas</t>
         </is>
       </c>
       <c r="C43" s="44" t="inlineStr">
         <is>
-          <t>N dégâts, doublés si la cible a un statut négatif.</t>
+          <t>N dégâts, doublés sous le seuil de PV.</t>
         </is>
       </c>
       <c r="D43" s="44" t="inlineStr">
         <is>
-          <t>valeur: N</t>
+          <t>valeur: N, seuil: %</t>
         </is>
       </c>
     </row>
     <row r="44" ht="30" customHeight="1" s="140">
       <c r="A44" s="44" t="inlineStr">
         <is>
-          <t>danse-poison</t>
+          <t>degats-execution</t>
         </is>
       </c>
       <c r="B44" s="44" t="inlineStr">
         <is>
-          <t>Danse du Poison</t>
+          <t>Exécution</t>
         </is>
       </c>
       <c r="C44" s="44" t="inlineStr">
         <is>
-          <t>Frappe tous les ennemis X fois ; +1 Poison/hit (2 si déjà empoisonné).</t>
+          <t>N dégâts, doublés si la cible a un statut négatif.</t>
         </is>
       </c>
       <c r="D44" s="44" t="inlineStr">
         <is>
-          <t>hits: X, degats: N</t>
+          <t>valeur: N</t>
         </is>
       </c>
     </row>
     <row r="45" ht="30" customHeight="1" s="140">
       <c r="A45" s="44" t="inlineStr">
         <is>
-          <t>brulure-adjacent</t>
+          <t>danse-poison</t>
         </is>
       </c>
       <c r="B45" s="44" t="inlineStr">
         <is>
-          <t>Brûlure adjacente</t>
+          <t>Danse du Poison</t>
         </is>
       </c>
       <c r="C45" s="44" t="inlineStr">
         <is>
-          <t>Chaque voisin a X% de chance de recevoir N Feu.</t>
+          <t>Frappe tous les ennemis X fois ; +1 Poison/hit (2 si déjà empoisonné).</t>
         </is>
       </c>
       <c r="D45" s="44" t="inlineStr">
         <is>
-          <t>feu: N, proba: X</t>
+          <t>hits: X, degats: N</t>
         </is>
       </c>
     </row>
     <row r="46" ht="30" customHeight="1" s="140">
       <c r="A46" s="44" t="inlineStr">
         <is>
+          <t>brulure-adjacent</t>
+        </is>
+      </c>
+      <c r="B46" s="44" t="inlineStr">
+        <is>
+          <t>Brûlure adjacente</t>
+        </is>
+      </c>
+      <c r="C46" s="44" t="inlineStr">
+        <is>
+          <t>Chaque voisin a X% de chance de recevoir N Feu.</t>
+        </is>
+      </c>
+      <c r="D46" s="44" t="inlineStr">
+        <is>
+          <t>feu: N, proba: X</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="24" customHeight="1" s="140">
+      <c r="A47" s="44" t="inlineStr">
+        <is>
           <t>eclaboussure</t>
         </is>
       </c>
-      <c r="B46" s="44" t="inlineStr">
+      <c r="B47" s="44" t="inlineStr">
         <is>
           <t>Éclaboussure</t>
         </is>
       </c>
-      <c r="C46" s="44" t="inlineStr">
+      <c r="C47" s="44" t="inlineStr">
         <is>
           <t>L'ennemi derrière prend N dégâts et N Feu.</t>
         </is>
       </c>
-      <c r="D46" s="44" t="inlineStr">
+      <c r="D47" s="44" t="inlineStr">
         <is>
           <t>degats: N, feu: N</t>
         </is>
       </c>
-    </row>
-    <row r="47" ht="24" customHeight="1" s="140">
-      <c r="A47" s="46" t="inlineStr">
-        <is>
-          <t>── MÉCANIQUES SAIGNEMENT ──</t>
-        </is>
-      </c>
-      <c r="B47" s="46" t="n"/>
-      <c r="C47" s="46" t="n"/>
-      <c r="D47" s="46" t="n"/>
     </row>
     <row r="48" ht="30" customHeight="1" s="140">
       <c r="A48" s="44" t="inlineStr">
         <is>
-          <t>pierre-par-sang</t>
+          <t>explosion-poison</t>
         </is>
       </c>
       <c r="B48" s="44" t="inlineStr">
         <is>
-          <t>Pierre par Saignement</t>
+          <t>Explosion de poison</t>
         </is>
       </c>
       <c r="C48" s="44" t="inlineStr">
         <is>
-          <t>N Pierre par tick de Saignement total.</t>
+          <t>Détonateur qui NE consomme PAS le poison : la cible ET ses deux voisins prennent autant de dégâts que la cible a de doses de poison, puis chacun gagne N poison. Répétable.</t>
         </is>
       </c>
       <c r="D48" s="44" t="inlineStr">
         <is>
-          <t>valeur: N</t>
+          <t>poison: N</t>
         </is>
       </c>
     </row>
     <row r="49" ht="30" customHeight="1" s="140">
-      <c r="A49" s="44" t="inlineStr">
-        <is>
-          <t>soin-par-sang</t>
-        </is>
-      </c>
-      <c r="B49" s="44" t="inlineStr">
-        <is>
-          <t>Soin par Saignement</t>
-        </is>
-      </c>
-      <c r="C49" s="44" t="inlineStr">
-        <is>
-          <t>N PV par tick de Saignement total.</t>
-        </is>
-      </c>
-      <c r="D49" s="44" t="inlineStr">
-        <is>
-          <t>valeur: N</t>
-        </is>
-      </c>
+      <c r="A49" s="46" t="inlineStr">
+        <is>
+          <t>── MÉCANIQUES SAIGNEMENT ──</t>
+        </is>
+      </c>
+      <c r="B49" s="46" t="n"/>
+      <c r="C49" s="46" t="n"/>
+      <c r="D49" s="46" t="n"/>
     </row>
     <row r="50" ht="30" customHeight="1" s="140">
       <c r="A50" s="44" t="inlineStr">
         <is>
-          <t>absorption-sang</t>
+          <t>pierre-par-sang</t>
         </is>
       </c>
       <c r="B50" s="44" t="inlineStr">
         <is>
-          <t>Absorption de sang</t>
+          <t>Pierre par Saignement</t>
         </is>
       </c>
       <c r="C50" s="44" t="inlineStr">
         <is>
-          <t>N PV par tick total, puis efface tout le Saignement.</t>
+          <t>N Pierre par tick de Saignement total.</t>
         </is>
       </c>
       <c r="D50" s="44" t="inlineStr">
@@ -23400,39 +23278,39 @@
     <row r="51" ht="30" customHeight="1" s="140">
       <c r="A51" s="44" t="inlineStr">
         <is>
-          <t>chaleur-par-sang</t>
+          <t>soin-par-sang</t>
         </is>
       </c>
       <c r="B51" s="44" t="inlineStr">
         <is>
-          <t>Chaleur par Saignement</t>
+          <t>Soin par Saignement</t>
         </is>
       </c>
       <c r="C51" s="44" t="inlineStr">
         <is>
-          <t>1 Chaleur par N ticks de Saignement total.</t>
+          <t>N PV par tick de Saignement total.</t>
         </is>
       </c>
       <c r="D51" s="44" t="inlineStr">
         <is>
-          <t>par: N</t>
+          <t>valeur: N</t>
         </is>
       </c>
     </row>
     <row r="52" ht="30" customHeight="1" s="140">
       <c r="A52" s="44" t="inlineStr">
         <is>
-          <t>stun-si-sang</t>
+          <t>soin-par-sang-cible</t>
         </is>
       </c>
       <c r="B52" s="44" t="inlineStr">
         <is>
-          <t>Stun si Saignement</t>
+          <t>Soin par saignement de la cible</t>
         </is>
       </c>
       <c r="C52" s="44" t="inlineStr">
         <is>
-          <t>Étourdit N tours les ennemis qui saignent.</t>
+          <t>Soigne le héros de N PV par tick de Saignement porté par LA CIBLE (≠ soin-par-sang, qui compte le saignement de tous les ennemis).</t>
         </is>
       </c>
       <c r="D52" s="44" t="inlineStr">
@@ -23444,71 +23322,83 @@
     <row r="53" ht="30" customHeight="1" s="140">
       <c r="A53" s="44" t="inlineStr">
         <is>
-          <t>contagion</t>
+          <t>absorption-sang</t>
         </is>
       </c>
       <c r="B53" s="44" t="inlineStr">
         <is>
-          <t>Contagion</t>
+          <t>Absorption de sang</t>
         </is>
       </c>
       <c r="C53" s="44" t="inlineStr">
         <is>
-          <t>Les voisins de la cible copient son niveau de Saignement.</t>
+          <t>N PV par tick total, puis efface tout le Saignement.</t>
         </is>
       </c>
       <c r="D53" s="44" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>valeur: N</t>
         </is>
       </c>
     </row>
     <row r="54" ht="30" customHeight="1" s="140">
       <c r="A54" s="44" t="inlineStr">
         <is>
-          <t>boire-le-sang</t>
+          <t>chaleur-par-sang</t>
         </is>
       </c>
       <c r="B54" s="44" t="inlineStr">
         <is>
-          <t>Vampire</t>
+          <t>Chaleur par Saignement</t>
         </is>
       </c>
       <c r="C54" s="44" t="inlineStr">
         <is>
-          <t>Perd N PV ; X dégâts + Saignement à tous ; soigne par kill.</t>
+          <t>1 Chaleur par N ticks de Saignement total.</t>
         </is>
       </c>
       <c r="D54" s="44" t="inlineStr">
         <is>
-          <t>hp,degats,sang,soinMort</t>
+          <t>par: N</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="46" t="inlineStr">
-        <is>
-          <t>── MÉCANIQUES FEU ──</t>
-        </is>
-      </c>
-      <c r="B55" s="46" t="n"/>
-      <c r="C55" s="46" t="n"/>
-      <c r="D55" s="46" t="n"/>
+      <c r="A55" s="44" t="inlineStr">
+        <is>
+          <t>stun-si-sang</t>
+        </is>
+      </c>
+      <c r="B55" s="44" t="inlineStr">
+        <is>
+          <t>Stun si Saignement</t>
+        </is>
+      </c>
+      <c r="C55" s="44" t="inlineStr">
+        <is>
+          <t>Étourdit N tours les ennemis qui saignent.</t>
+        </is>
+      </c>
+      <c r="D55" s="44" t="inlineStr">
+        <is>
+          <t>valeur: N</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="30" customHeight="1" s="140">
       <c r="A56" s="44" t="inlineStr">
         <is>
-          <t>tout-en-feu</t>
+          <t>contagion</t>
         </is>
       </c>
       <c r="B56" s="44" t="inlineStr">
         <is>
-          <t>Tout en Feu</t>
+          <t>Contagion</t>
         </is>
       </c>
       <c r="C56" s="44" t="inlineStr">
         <is>
-          <t>Convertit tous les statuts ennemis en Feu, puis le double.</t>
+          <t>Les voisins de la cible copient son niveau de Saignement.</t>
         </is>
       </c>
       <c r="D56" s="44" t="inlineStr">
@@ -23520,159 +23410,181 @@
     <row r="57" ht="30" customHeight="1" s="140">
       <c r="A57" s="44" t="inlineStr">
         <is>
-          <t>transfert-feu</t>
+          <t>boire-le-sang</t>
         </is>
       </c>
       <c r="B57" s="44" t="inlineStr">
         <is>
-          <t>Transfert de Feu</t>
+          <t>Vampire</t>
         </is>
       </c>
       <c r="C57" s="44" t="inlineStr">
         <is>
-          <t>Déplace tout le Feu de la cible vers l'ennemi derrière.</t>
+          <t>Perd N PV ; X dégâts + Saignement à tous ; soigne par kill.</t>
         </is>
       </c>
       <c r="D57" s="44" t="inlineStr">
         <is>
+          <t>hp,degats,sang,soinMort</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="30" customHeight="1" s="140">
+      <c r="A58" s="46" t="inlineStr">
+        <is>
+          <t>── MÉCANIQUES FEU ──</t>
+        </is>
+      </c>
+      <c r="B58" s="46" t="n"/>
+      <c r="C58" s="46" t="n"/>
+      <c r="D58" s="46" t="n"/>
+    </row>
+    <row r="59" ht="24" customHeight="1" s="140">
+      <c r="A59" s="44" t="inlineStr">
+        <is>
+          <t>tout-en-feu</t>
+        </is>
+      </c>
+      <c r="B59" s="44" t="inlineStr">
+        <is>
+          <t>Tout en Feu</t>
+        </is>
+      </c>
+      <c r="C59" s="44" t="inlineStr">
+        <is>
+          <t>Convertit tous les statuts ennemis en Feu, puis le double.</t>
+        </is>
+      </c>
+      <c r="D59" s="44" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-    </row>
-    <row r="58" ht="30" customHeight="1" s="140">
-      <c r="A58" s="44" t="inlineStr">
-        <is>
-          <t>forgeage</t>
-        </is>
-      </c>
-      <c r="B58" s="44" t="inlineStr">
-        <is>
-          <t>Forgeage d'armure</t>
-        </is>
-      </c>
-      <c r="C58" s="44" t="inlineStr">
-        <is>
-          <t>N Feu AOE ; déjà enflammés = double, puis Feu → Pierre pour le héros.</t>
-        </is>
-      </c>
-      <c r="D58" s="44" t="inlineStr">
-        <is>
-          <t>feu: N</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="24" customHeight="1" s="140">
-      <c r="A59" s="46" t="inlineStr">
-        <is>
-          <t>── MÉCANIQUES CONFUSION ──</t>
-        </is>
-      </c>
-      <c r="B59" s="46" t="n"/>
-      <c r="C59" s="46" t="n"/>
-      <c r="D59" s="46" t="n"/>
     </row>
     <row r="60" ht="30" customHeight="1" s="140">
       <c r="A60" s="44" t="inlineStr">
         <is>
-          <t>confusion-proche</t>
+          <t>transfert-feu</t>
         </is>
       </c>
       <c r="B60" s="44" t="inlineStr">
         <is>
-          <t>Confusion proche</t>
+          <t>Transfert de Feu</t>
         </is>
       </c>
       <c r="C60" s="44" t="inlineStr">
         <is>
-          <t>N Confusion à l'ennemi le plus proche.</t>
+          <t>Déplace tout le Feu de la cible vers l'ennemi derrière.</t>
         </is>
       </c>
       <c r="D60" s="44" t="inlineStr">
         <is>
-          <t>valeur: N</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="61" ht="30" customHeight="1" s="140">
       <c r="A61" s="44" t="inlineStr">
         <is>
-          <t>confusion-si-confus</t>
+          <t>forgeage</t>
         </is>
       </c>
       <c r="B61" s="44" t="inlineStr">
         <is>
-          <t>Confusion amplifiée</t>
+          <t>Forgeage d'armure</t>
         </is>
       </c>
       <c r="C61" s="44" t="inlineStr">
         <is>
-          <t>+N Confusion à chaque ennemi déjà confus.</t>
+          <t>N Feu AOE ; déjà enflammés = double, puis Feu → Pierre pour le héros.</t>
         </is>
       </c>
       <c r="D61" s="44" t="inlineStr">
         <is>
+          <t>feu: N</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="30" customHeight="1" s="140">
+      <c r="A62" s="46" t="inlineStr">
+        <is>
+          <t>── MÉCANIQUES CONFUSION ──</t>
+        </is>
+      </c>
+      <c r="B62" s="46" t="n"/>
+      <c r="C62" s="46" t="n"/>
+      <c r="D62" s="46" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="44" t="inlineStr">
+        <is>
+          <t>confusion-proche</t>
+        </is>
+      </c>
+      <c r="B63" s="44" t="inlineStr">
+        <is>
+          <t>Confusion proche</t>
+        </is>
+      </c>
+      <c r="C63" s="44" t="inlineStr">
+        <is>
+          <t>N Confusion à l'ennemi le plus proche.</t>
+        </is>
+      </c>
+      <c r="D63" s="44" t="inlineStr">
+        <is>
           <t>valeur: N</t>
         </is>
       </c>
-    </row>
-    <row r="62" ht="30" customHeight="1" s="140">
-      <c r="A62" s="44" t="inlineStr">
-        <is>
-          <t>purifier-hero</t>
-        </is>
-      </c>
-      <c r="B62" s="44" t="inlineStr">
-        <is>
-          <t>Purifier le héros</t>
-        </is>
-      </c>
-      <c r="C62" s="44" t="inlineStr">
-        <is>
-          <t>Retire un statut négatif aléatoire du héros.</t>
-        </is>
-      </c>
-      <c r="D62" s="44" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="46" t="inlineStr">
-        <is>
-          <t>── MÉCANIQUES GEL ──</t>
-        </is>
-      </c>
-      <c r="B63" s="46" t="n"/>
-      <c r="C63" s="46" t="n"/>
-      <c r="D63" s="46" t="n"/>
     </row>
     <row r="64" ht="30" customHeight="1" s="140">
       <c r="A64" s="44" t="inlineStr">
         <is>
-          <t>gel-cascade</t>
+          <t>confusion-si-confus</t>
         </is>
       </c>
       <c r="B64" s="44" t="inlineStr">
         <is>
-          <t>Cascade de gel</t>
+          <t>Confusion amplifiée</t>
         </is>
       </c>
       <c r="C64" s="44" t="inlineStr">
         <is>
-          <t>N dégâts + N Gel ; rebondit si la cible était déjà gelée.</t>
+          <t>+N Confusion à chaque ennemi déjà confus.</t>
         </is>
       </c>
       <c r="D64" s="44" t="inlineStr">
         <is>
-          <t>degats: N, gel: N</t>
+          <t>valeur: N</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="44" t="inlineStr">
+        <is>
+          <t>purifier-hero</t>
+        </is>
+      </c>
+      <c r="B65" s="44" t="inlineStr">
+        <is>
+          <t>Purifier le héros</t>
+        </is>
+      </c>
+      <c r="C65" s="44" t="inlineStr">
+        <is>
+          <t>Retire un statut négatif aléatoire du héros.</t>
+        </is>
+      </c>
+      <c r="D65" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="66" ht="24" customHeight="1" s="140">
       <c r="A66" s="46" t="inlineStr">
         <is>
-          <t>── NOUVELLES MÉCANIQUES (révision Excel juin) ──</t>
+          <t>── MÉCANIQUES GEL ──</t>
         </is>
       </c>
       <c r="B66" s="46" t="n"/>
@@ -23682,259 +23594,226 @@
     <row r="67" ht="30" customHeight="1" s="140">
       <c r="A67" s="44" t="inlineStr">
         <is>
-          <t>drain-sang</t>
+          <t>gel-cascade</t>
         </is>
       </c>
       <c r="B67" s="44" t="inlineStr">
         <is>
-          <t>Drain</t>
+          <t>Cascade de gel</t>
         </is>
       </c>
       <c r="C67" s="44" t="inlineStr">
         <is>
-          <t>Consomme tout le Saignement de la cible, soigne le héros d'autant, +`energie` Chaleur.</t>
+          <t>N dégâts + N Gel ; rebondit si la cible était déjà gelée.</t>
         </is>
       </c>
       <c r="D67" s="44" t="inlineStr">
         <is>
-          <t>energie: N</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="30" customHeight="1" s="140">
-      <c r="A68" s="44" t="inlineStr">
-        <is>
-          <t>supprimer-bonus</t>
-        </is>
-      </c>
-      <c r="B68" s="44" t="inlineStr">
-        <is>
-          <t>Dissiper un bonus</t>
-        </is>
-      </c>
-      <c r="C68" s="44" t="inlineStr">
-        <is>
-          <t>Retire un bonus (statut positif) au hasard de la cible ; si réussi, +`regen` Regen au héros.</t>
-        </is>
-      </c>
-      <c r="D68" s="44" t="inlineStr">
-        <is>
-          <t>regen: N</t>
-        </is>
-      </c>
-    </row>
+          <t>degats: N, gel: N</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="30" customHeight="1" s="140"/>
     <row r="69" ht="30" customHeight="1" s="140">
-      <c r="A69" s="44" t="inlineStr">
-        <is>
-          <t>voler-bonus</t>
-        </is>
-      </c>
-      <c r="B69" s="44" t="inlineStr">
-        <is>
-          <t>Voler un bonus</t>
-        </is>
-      </c>
-      <c r="C69" s="44" t="inlineStr">
-        <is>
-          <t>Vole un bonus au hasard de la cible et l'applique au héros (Hâte alliée → célérité).</t>
-        </is>
-      </c>
-      <c r="D69" s="44" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="A69" s="46" t="inlineStr">
+        <is>
+          <t>── NOUVELLES MÉCANIQUES (révision Excel juin) ──</t>
+        </is>
+      </c>
+      <c r="B69" s="46" t="n"/>
+      <c r="C69" s="46" t="n"/>
+      <c r="D69" s="46" t="n"/>
     </row>
     <row r="70" ht="30" customHeight="1" s="140">
       <c r="A70" s="44" t="inlineStr">
         <is>
-          <t>piocher-pierre</t>
+          <t>drain-sang</t>
         </is>
       </c>
       <c r="B70" s="44" t="inlineStr">
         <is>
-          <t>Pioche + Pierre</t>
+          <t>Drain</t>
         </is>
       </c>
       <c r="C70" s="44" t="inlineStr">
         <is>
-          <t>Pioche `valeur` carte(s) ; gagne `mult`× leur coût en Pierre.</t>
+          <t>Consomme tout le Saignement de la cible, soigne le héros d'autant, +`energie` Chaleur.</t>
         </is>
       </c>
       <c r="D70" s="44" t="inlineStr">
         <is>
-          <t>valeur: N, mult: X</t>
+          <t>energie: N</t>
         </is>
       </c>
     </row>
     <row r="71" ht="30" customHeight="1" s="140">
       <c r="A71" s="44" t="inlineStr">
         <is>
-          <t>retirer-feu-hero</t>
+          <t>supprimer-bonus</t>
         </is>
       </c>
       <c r="B71" s="44" t="inlineStr">
         <is>
-          <t>Anti-feu (héros)</t>
+          <t>Dissiper un bonus</t>
         </is>
       </c>
       <c r="C71" s="44" t="inlineStr">
         <is>
-          <t>Retire `valeur` ticks de brûlure DU HÉROS.</t>
+          <t>Retire un bonus (statut positif) au hasard de la cible ; si réussi, +`regen` Regen au héros.</t>
         </is>
       </c>
       <c r="D71" s="44" t="inlineStr">
         <is>
-          <t>valeur: N</t>
+          <t>regen: N</t>
         </is>
       </c>
     </row>
     <row r="72" ht="30" customHeight="1" s="140">
       <c r="A72" s="44" t="inlineStr">
         <is>
-          <t>chaleur-aleatoire</t>
+          <t>voler-bonus</t>
         </is>
       </c>
       <c r="B72" s="44" t="inlineStr">
         <is>
-          <t>Énergie aléatoire</t>
+          <t>Voler un bonus</t>
         </is>
       </c>
       <c r="C72" s="44" t="inlineStr">
         <is>
-          <t>Gagne une Chaleur ALÉATOIRE entre `min` et `max` (inclus).</t>
+          <t>Vole un bonus au hasard de la cible et l'applique au héros (Hâte alliée → célérité).</t>
         </is>
       </c>
       <c r="D72" s="44" t="inlineStr">
         <is>
-          <t>min, max</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="73" ht="30" customHeight="1" s="140">
       <c r="A73" s="44" t="inlineStr">
         <is>
-          <t>pioche-filtre</t>
+          <t>piocher-pierre</t>
         </is>
       </c>
       <c r="B73" s="44" t="inlineStr">
         <is>
-          <t>Pioche filtrée</t>
+          <t>Pioche + Pierre</t>
         </is>
       </c>
       <c r="C73" s="44" t="inlineStr">
         <is>
-          <t>Pioche `valeur` cartes, garde celles de coût &lt; `coutMax`, défausse les autres.</t>
+          <t>Pioche `valeur` carte(s) ; gagne `mult`× leur coût en Pierre.</t>
         </is>
       </c>
       <c r="D73" s="44" t="inlineStr">
         <is>
-          <t>valeur: N, coutMax: X</t>
+          <t>valeur: N, mult: X</t>
         </is>
       </c>
     </row>
     <row r="74" ht="30" customHeight="1" s="140">
       <c r="A74" s="44" t="inlineStr">
         <is>
-          <t>degats-soin-cible</t>
+          <t>retirer-feu-hero</t>
         </is>
       </c>
       <c r="B74" s="44" t="inlineStr">
         <is>
-          <t>Dégâts + soin/cible</t>
+          <t>Anti-feu (héros)</t>
         </is>
       </c>
       <c r="C74" s="44" t="inlineStr">
         <is>
-          <t>Dégâts AOE `degats` ; soigne `soin` PV par ennemi touché.</t>
+          <t>Retire `valeur` ticks de brûlure DU HÉROS.</t>
         </is>
       </c>
       <c r="D74" s="44" t="inlineStr">
         <is>
-          <t>degats, soin</t>
+          <t>valeur: N</t>
         </is>
       </c>
     </row>
     <row r="75" ht="30" customHeight="1" s="140">
       <c r="A75" s="44" t="inlineStr">
         <is>
-          <t>celerite-par-tour</t>
+          <t>chaleur-aleatoire</t>
         </is>
       </c>
       <c r="B75" s="44" t="inlineStr">
         <is>
-          <t>Hâte permanente/tour</t>
+          <t>Énergie aléatoire</t>
         </is>
       </c>
       <c r="C75" s="44" t="inlineStr">
         <is>
-          <t>Long run : +`valeur` Hâte PERMANENTE (hatePerm, ne s'écoule pas) au début de chaque tour.</t>
+          <t>Gagne une Chaleur ALÉATOIRE entre `min` et `max` (inclus).</t>
         </is>
       </c>
       <c r="D75" s="44" t="inlineStr">
         <is>
-          <t>valeur: N</t>
+          <t>min, max</t>
         </is>
       </c>
     </row>
     <row r="76" ht="30" customHeight="1" s="140">
       <c r="A76" s="44" t="inlineStr">
         <is>
-          <t>riposte</t>
+          <t>pioche-filtre</t>
         </is>
       </c>
       <c r="B76" s="44" t="inlineStr">
         <is>
-          <t>Riposte</t>
+          <t>Pioche filtrée</t>
         </is>
       </c>
       <c r="C76" s="44" t="inlineStr">
         <is>
-          <t>Gagne `valeur` ticks de Riposte : renvoie les dégâts de MÊLÉE reçus, −1 tick/renvoi.</t>
+          <t>Pioche `valeur` cartes, garde celles de coût &lt; `coutMax`, défausse les autres.</t>
         </is>
       </c>
       <c r="D76" s="44" t="inlineStr">
         <is>
-          <t>valeur: N</t>
+          <t>valeur: N, coutMax: X</t>
         </is>
       </c>
     </row>
     <row r="77" ht="30" customHeight="1" s="140">
       <c r="A77" s="44" t="inlineStr">
         <is>
-          <t>tour-bonus</t>
+          <t>degats-soin-cible</t>
         </is>
       </c>
       <c r="B77" s="44" t="inlineStr">
         <is>
-          <t>Tour bonus</t>
+          <t>Dégâts + soin/cible</t>
         </is>
       </c>
       <c r="C77" s="44" t="inlineStr">
         <is>
-          <t>Le héros enchaîne `valeur` tour(s) de plus (jauge d'init remplie en fin de tour).</t>
+          <t>Dégâts AOE `degats` ; soigne `soin` PV par ennemi touché.</t>
         </is>
       </c>
       <c r="D77" s="44" t="inlineStr">
         <is>
-          <t>valeur: N</t>
+          <t>degats, soin</t>
         </is>
       </c>
     </row>
     <row r="78" ht="30" customHeight="1" s="140">
       <c r="A78" s="44" t="inlineStr">
         <is>
-          <t>compteur-pierre</t>
+          <t>celerite-par-tour</t>
         </is>
       </c>
       <c r="B78" s="44" t="inlineStr">
         <is>
-          <t>Compteur pierre</t>
+          <t>Hâte permanente/tour</t>
         </is>
       </c>
       <c r="C78" s="44" t="inlineStr">
         <is>
-          <t>Set Stone Age : marque `valeur` carte(s) pierre jouée(s) ; déclenche le set par paliers de 10.</t>
+          <t>Long run : +`valeur` Hâte PERMANENTE (hatePerm, ne s'écoule pas) au début de chaque tour.</t>
         </is>
       </c>
       <c r="D78" s="44" t="inlineStr">
@@ -23946,17 +23825,17 @@
     <row r="79" ht="30" customHeight="1" s="140">
       <c r="A79" s="44" t="inlineStr">
         <is>
-          <t>pierre-par-compteur</t>
+          <t>riposte</t>
         </is>
       </c>
       <c r="B79" s="44" t="inlineStr">
         <is>
-          <t>Pierre par compteur</t>
+          <t>Riposte</t>
         </is>
       </c>
       <c r="C79" s="44" t="inlineStr">
         <is>
-          <t>Gagne `valeur` Pierre par carte pierre déjà jouée (cartesPierre).</t>
+          <t>Gagne `valeur` ticks de Riposte : renvoie les dégâts de MÊLÉE reçus, −1 tick/renvoi.</t>
         </is>
       </c>
       <c r="D79" s="44" t="inlineStr">
@@ -23968,162 +23847,289 @@
     <row r="80" ht="30" customHeight="1" s="140">
       <c r="A80" s="44" t="inlineStr">
         <is>
-          <t>piocher-par-compteur</t>
+          <t>tour-bonus</t>
         </is>
       </c>
       <c r="B80" s="44" t="inlineStr">
         <is>
-          <t>Pioche par compteur</t>
+          <t>Tour bonus</t>
         </is>
       </c>
       <c r="C80" s="44" t="inlineStr">
         <is>
-          <t>Pioche cartesPierre/`div` cartes, borné [min, max].</t>
+          <t>Le héros enchaîne `valeur` tour(s) de plus (jauge d'init remplie en fin de tour).</t>
         </is>
       </c>
       <c r="D80" s="44" t="inlineStr">
         <is>
-          <t>div, min, max</t>
+          <t>valeur: N</t>
         </is>
       </c>
     </row>
     <row r="81" ht="30" customHeight="1" s="140">
       <c r="A81" s="44" t="inlineStr">
         <is>
-          <t>chaleur-par-compteur</t>
+          <t>compteur-pierre</t>
         </is>
       </c>
       <c r="B81" s="44" t="inlineStr">
         <is>
-          <t>Énergie par compteur</t>
+          <t>Compteur pierre</t>
         </is>
       </c>
       <c r="C81" s="44" t="inlineStr">
         <is>
-          <t>Gagne cartesPierre/`div` Chaleur, borné [min, max].</t>
+          <t>Set Stone Age : marque `valeur` carte(s) pierre jouée(s) ; déclenche le set par paliers de 10.</t>
         </is>
       </c>
       <c r="D81" s="44" t="inlineStr">
         <is>
+          <t>valeur: N</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="44" t="inlineStr">
+        <is>
+          <t>pierre-par-compteur</t>
+        </is>
+      </c>
+      <c r="B82" s="44" t="inlineStr">
+        <is>
+          <t>Pierre par compteur</t>
+        </is>
+      </c>
+      <c r="C82" s="44" t="inlineStr">
+        <is>
+          <t>Gagne `valeur` Pierre par carte pierre déjà jouée (cartesPierre).</t>
+        </is>
+      </c>
+      <c r="D82" s="44" t="inlineStr">
+        <is>
+          <t>valeur: N</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="24" customHeight="1" s="140">
+      <c r="A83" s="44" t="inlineStr">
+        <is>
+          <t>piocher-par-compteur</t>
+        </is>
+      </c>
+      <c r="B83" s="44" t="inlineStr">
+        <is>
+          <t>Pioche par compteur</t>
+        </is>
+      </c>
+      <c r="C83" s="44" t="inlineStr">
+        <is>
+          <t>Pioche cartesPierre/`div` cartes, borné [min, max].</t>
+        </is>
+      </c>
+      <c r="D83" s="44" t="inlineStr">
+        <is>
           <t>div, min, max</t>
         </is>
       </c>
-    </row>
-    <row r="83" ht="24" customHeight="1" s="140">
-      <c r="A83" s="46" t="inlineStr">
-        <is>
-          <t>── COMBOS ARMES 2 MAINS ──</t>
-        </is>
-      </c>
-      <c r="B83" s="46" t="n"/>
-      <c r="C83" s="46" t="n"/>
-      <c r="D83" s="46" t="n"/>
     </row>
     <row r="84" ht="30" customHeight="1" s="140">
       <c r="A84" s="44" t="inlineStr">
         <is>
-          <t>degats-si-force</t>
+          <t>chaleur-par-compteur</t>
         </is>
       </c>
       <c r="B84" s="44" t="inlineStr">
         <is>
-          <t>Frappe décisive</t>
+          <t>Énergie par compteur</t>
         </is>
       </c>
       <c r="C84" s="44" t="inlineStr">
         <is>
-          <t>Dégâts (Force incluse) DOUBLÉS si la Force totale ≥ `seuil`.</t>
+          <t>Gagne cartesPierre/`div` Chaleur, borné [min, max].</t>
         </is>
       </c>
       <c r="D84" s="44" t="inlineStr">
         <is>
-          <t>valeur, seuil</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="30" customHeight="1" s="140">
-      <c r="A85" s="44" t="inlineStr">
-        <is>
-          <t>stun-si-pierre</t>
-        </is>
-      </c>
-      <c r="B85" s="44" t="inlineStr">
-        <is>
-          <t>Étourdir si Pierre</t>
-        </is>
-      </c>
-      <c r="C85" s="44" t="inlineStr">
-        <is>
-          <t>Étourdit la cible `valeur` tour(s) seulement si la Pierre du héros ≥ `seuil`.</t>
-        </is>
-      </c>
-      <c r="D85" s="44" t="inlineStr">
-        <is>
-          <t>valeur, seuil</t>
-        </is>
-      </c>
-    </row>
+          <t>div, min, max</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="30" customHeight="1" s="140"/>
     <row r="86" ht="30" customHeight="1" s="140">
-      <c r="A86" s="44" t="inlineStr">
-        <is>
-          <t>soin-par-ennemi-saignant</t>
-        </is>
-      </c>
-      <c r="B86" s="44" t="inlineStr">
-        <is>
-          <t>Récolte</t>
-        </is>
-      </c>
-      <c r="C86" s="44" t="inlineStr">
-        <is>
-          <t>Soigne `valeur` PV par ennemi vivant qui SAIGNE.</t>
-        </is>
-      </c>
-      <c r="D86" s="44" t="inlineStr">
-        <is>
-          <t>valeur</t>
-        </is>
-      </c>
+      <c r="A86" s="46" t="inlineStr">
+        <is>
+          <t>── COMBOS ARMES 2 MAINS ──</t>
+        </is>
+      </c>
+      <c r="B86" s="46" t="n"/>
+      <c r="C86" s="46" t="n"/>
+      <c r="D86" s="46" t="n"/>
     </row>
     <row r="87" ht="30" customHeight="1" s="140">
       <c r="A87" s="44" t="inlineStr">
         <is>
-          <t>recompense-mort</t>
+          <t>degats-si-force</t>
         </is>
       </c>
       <c r="B87" s="44" t="inlineStr">
         <is>
-          <t>Récolte d'âme</t>
+          <t>Frappe décisive</t>
         </is>
       </c>
       <c r="C87" s="44" t="inlineStr">
         <is>
-          <t>Si la cible meurt du coup : +`force` Force et +`soin` PV au héros.</t>
+          <t>Dégâts (Force incluse) DOUBLÉS si la Force totale ≥ `seuil`.</t>
         </is>
       </c>
       <c r="D87" s="44" t="inlineStr">
         <is>
-          <t>force, soin</t>
+          <t>valeur, seuil</t>
         </is>
       </c>
     </row>
     <row r="88" ht="36" customHeight="1" s="140">
       <c r="A88" s="44" t="inlineStr">
         <is>
+          <t>stun-si-pierre</t>
+        </is>
+      </c>
+      <c r="B88" s="44" t="inlineStr">
+        <is>
+          <t>Étourdir si Pierre</t>
+        </is>
+      </c>
+      <c r="C88" s="44" t="inlineStr">
+        <is>
+          <t>Étourdit la cible `valeur` tour(s) seulement si la Pierre du héros ≥ `seuil`.</t>
+        </is>
+      </c>
+      <c r="D88" s="44" t="inlineStr">
+        <is>
+          <t>valeur, seuil</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="44" t="inlineStr">
+        <is>
+          <t>soin-par-ennemi-saignant</t>
+        </is>
+      </c>
+      <c r="B89" s="44" t="inlineStr">
+        <is>
+          <t>Récolte</t>
+        </is>
+      </c>
+      <c r="C89" s="44" t="inlineStr">
+        <is>
+          <t>Soigne `valeur` PV par ennemi vivant qui SAIGNE.</t>
+        </is>
+      </c>
+      <c r="D89" s="44" t="inlineStr">
+        <is>
+          <t>valeur</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="44" t="inlineStr">
+        <is>
+          <t>recompense-mort</t>
+        </is>
+      </c>
+      <c r="B90" s="44" t="inlineStr">
+        <is>
+          <t>Récolte d'âme</t>
+        </is>
+      </c>
+      <c r="C90" s="44" t="inlineStr">
+        <is>
+          <t>Si la cible meurt du coup : +`force` Force et +`soin` PV au héros.</t>
+        </is>
+      </c>
+      <c r="D90" s="44" t="inlineStr">
+        <is>
+          <t>force, soin</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="44" t="n"/>
+      <c r="B91" s="44" t="n"/>
+      <c r="C91" s="44" t="n"/>
+      <c r="D91" s="44" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="46" t="inlineStr">
+        <is>
+          <t>── JUGEMENT (set béni par Dunïr) ──</t>
+        </is>
+      </c>
+      <c r="B92" s="46" t="n"/>
+      <c r="C92" s="46" t="n"/>
+      <c r="D92" s="46" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="44" t="inlineStr">
+        <is>
           <t>jugement</t>
         </is>
       </c>
-      <c r="B88" s="44" t="inlineStr">
+      <c r="B93" s="44" t="inlineStr">
         <is>
           <t>Jugement (⚖)</t>
         </is>
       </c>
-      <c r="C88" s="44" t="inlineStr">
-        <is>
-          <t>Posé sur un ennemi. Ne fait AUCUN dégât et ne s'écoule JAMAIS : il augmente de N chaque blessure que cet ennemi subit (toute source). Set béni par Dunïr : à la mort d'un ennemi jugé, son Jugement se DISPERSE au hasard entre les survivants (total conservé).</t>
-        </is>
-      </c>
-      <c r="D88" s="44" t="inlineStr">
+      <c r="C93" s="44" t="inlineStr">
+        <is>
+          <t>Posé sur un ennemi. Ne fait AUCUN dégât et ne s'écoule JAMAIS : il augmente de N TOUTES les blessures suivantes de cette cible. À sa mort, ses piles se dispersent au hasard sur les survivants.</t>
+        </is>
+      </c>
+      <c r="D93" s="44" t="inlineStr">
+        <is>
+          <t>valeur: N</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="44" t="inlineStr">
+        <is>
+          <t>jugement-tous</t>
+        </is>
+      </c>
+      <c r="B94" s="44" t="inlineStr">
+        <is>
+          <t>Jugement de masse</t>
+        </is>
+      </c>
+      <c r="C94" s="44" t="inlineStr">
+        <is>
+          <t>Pose N Jugement sur TOUS les ennemis vivants d'un coup (Sceau de Dunïr, Aube dorée).</t>
+        </is>
+      </c>
+      <c r="D94" s="44" t="inlineStr">
+        <is>
+          <t>valeur: N</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="44" t="inlineStr">
+        <is>
+          <t>degats-par-jugement</t>
+        </is>
+      </c>
+      <c r="B95" s="44" t="inlineStr">
+        <is>
+          <t>Dégâts par Jugement</t>
+        </is>
+      </c>
+      <c r="C95" s="44" t="inlineStr">
+        <is>
+          <t>Inflige N dégâts PAR pile de Jugement déjà posée sur la cible — l'amplification normale du Jugement s'y ajoute ensuite (Sentence).</t>
+        </is>
+      </c>
+      <c r="D95" s="44" t="inlineStr">
         <is>
           <t>valeur: N</t>
         </is>
@@ -24140,7 +24146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D137"/>
+  <dimension ref="A1:D143"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="140" min="1" max="1"/>
@@ -24199,2626 +24205,2747 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="79" t="inlineStr">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>sceptre-apprenti</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Apprentice Scepter</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>pioche-basique</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Basic Pickaxe</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>anneau-saignant</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Bleeding Ring</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>charme-os</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Bone Charm</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>targe</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Buckler</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>cotte-mailles</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Chainmail</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>couperet</t>
         </is>
       </c>
-      <c r="B7" s="80" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Cleaver</t>
         </is>
       </c>
-      <c r="C7" s="81" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="D7" s="78" t="n">
+      <c r="D13" t="n">
         <v>440</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="79" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>gants-tissu</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Cloth Gloves</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>collier-cuivre</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Copper Amulet</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>anneau-braise</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ember Ring</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>anneau-frimas</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Frost Band</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>fanal</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Hand Torch</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>hachette</t>
         </is>
       </c>
-      <c r="B8" s="80" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Hatchet</t>
         </is>
       </c>
-      <c r="C8" s="81" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="D8" s="78" t="n">
+      <c r="D19" t="n">
         <v>430</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="79" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>grimoire-soin</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Healing Book</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>armure-peau</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Hide Armor</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>pic-de-glace</t>
         </is>
       </c>
-      <c r="B9" s="80" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Ice Pick</t>
         </is>
       </c>
-      <c r="C9" s="81" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="D9" s="78" t="n">
+      <c r="D22" t="n">
         <v>360</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="79" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>armure-cuir</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Leather Armor</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>bottes-cuir</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Leather Boots</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>gants-cuir</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Leather Gloves</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>sac-en-cuir</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Leather Pouch</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>porte-bonheur</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Lucky Charm</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>masse</t>
         </is>
       </c>
-      <c r="B10" s="80" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>Mace</t>
         </is>
       </c>
-      <c r="C10" s="81" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="D10" s="78" t="n">
+      <c r="D28" t="n">
         <v>400</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="79" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>gants-de-mineur</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Miner's Gloves</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>pioche-de-mineur</t>
         </is>
       </c>
-      <c r="B11" s="80" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>Miner's Pick</t>
         </is>
       </c>
-      <c r="C11" s="81" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="D11" s="78" t="n">
+      <c r="D30" t="n">
         <v>460</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="79" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>anneau-agile</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nimble Ring</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>gilet-rembourre</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Padded Vest</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>fourche</t>
         </is>
       </c>
-      <c r="B12" s="80" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>Pitchfork</t>
         </is>
       </c>
-      <c r="C12" s="81" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="D12" s="78" t="n">
+      <c r="D33" t="n">
         <v>330</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="79" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>anneau-force</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Power Ring</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>baton</t>
         </is>
       </c>
-      <c r="B13" s="80" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>Quarterstaff</t>
         </is>
       </c>
-      <c r="C13" s="81" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="D13" s="78" t="n">
+      <c r="D35" t="n">
         <v>330</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="79" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>pendentif-quartz</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Quartz Pendant</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>hache-rouillee</t>
         </is>
       </c>
-      <c r="B14" s="80" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>Rusty Axe</t>
         </is>
       </c>
-      <c r="C14" s="81" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="D14" s="78" t="n">
+      <c r="D37" t="n">
         <v>370</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="79" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>dague-rouillee</t>
         </is>
       </c>
-      <c r="B15" s="80" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>Rusty Dagger</t>
         </is>
       </c>
-      <c r="C15" s="81" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="D15" s="78" t="n">
+      <c r="D38" t="n">
         <v>430</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="79" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>sandales</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Sandals</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>couteau-serpent</t>
         </is>
       </c>
-      <c r="B16" s="80" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>Serpent Knife</t>
         </is>
       </c>
-      <c r="C16" s="81" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="D16" s="78" t="n">
+      <c r="D40" t="n">
         <v>380</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="79" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>couteau-dentele</t>
         </is>
       </c>
-      <c r="B17" s="80" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>Serrated Knife</t>
         </is>
       </c>
-      <c r="C17" s="81" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="D17" s="78" t="n">
+      <c r="D41" t="n">
         <v>370</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="79" t="inlineStr">
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>epee-courte</t>
         </is>
       </c>
-      <c r="B18" s="80" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>Short Sword</t>
         </is>
       </c>
-      <c r="C18" s="81" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="D18" s="78" t="n">
+      <c r="D42" t="n">
         <v>330</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="79" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>pendentif-chaud</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Spark Pendant</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>anneau-etincelle</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Spark Ring</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>lance</t>
         </is>
       </c>
-      <c r="B19" s="80" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>Spear</t>
         </is>
       </c>
-      <c r="C19" s="81" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="D19" s="78" t="n">
+      <c r="D45" t="n">
         <v>340</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="79" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>grimoire</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Spellbook</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>anneau-pierre</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Stone Ring</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>gants-cloutes</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Studded Gloves</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t>torche</t>
         </is>
       </c>
-      <c r="B20" s="80" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>Torch</t>
         </is>
       </c>
-      <c r="C20" s="81" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="D20" s="78" t="n">
+      <c r="D49" t="n">
         <v>360</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="79" t="inlineStr">
+    <row r="50">
+      <c r="A50" t="inlineStr">
         <is>
           <t>epee-entrainement</t>
         </is>
       </c>
-      <c r="B21" s="80" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>Training Sword</t>
         </is>
       </c>
-      <c r="C21" s="81" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="D21" s="78" t="n">
+      <c r="D50" t="n">
         <v>350</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="79" t="inlineStr">
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>bottes-voyage</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Traveler Boots</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>tenue-de-voyageur</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Traveler's Garb</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>anneau-venin</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Venom Ring</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>anneau-vigueur</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Vigor Ring</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
         <is>
           <t>gourdin</t>
         </is>
       </c>
-      <c r="B22" s="80" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>Wooden Club</t>
         </is>
       </c>
-      <c r="C22" s="81" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="D22" s="78" t="n">
+      <c r="D55" t="n">
         <v>420</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="79" t="inlineStr">
-        <is>
-          <t>cotte-mailles</t>
-        </is>
-      </c>
-      <c r="B23" s="80" t="inlineStr">
-        <is>
-          <t>Chainmail</t>
-        </is>
-      </c>
-      <c r="C23" s="81" t="inlineStr">
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>bouclier-bois</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Wooden Shield</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="D23" s="78" t="n">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="79" t="inlineStr">
-        <is>
-          <t>armure-peau</t>
-        </is>
-      </c>
-      <c r="B24" s="80" t="inlineStr">
-        <is>
-          <t>Hide Armor</t>
-        </is>
-      </c>
-      <c r="C24" s="81" t="inlineStr">
+      <c r="D56" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>gants-travail</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Work Gloves</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="D24" s="78" t="n">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="79" t="inlineStr">
-        <is>
-          <t>armure-cuir</t>
-        </is>
-      </c>
-      <c r="B25" s="80" t="inlineStr">
-        <is>
-          <t>Leather Armor</t>
-        </is>
-      </c>
-      <c r="C25" s="81" t="inlineStr">
+      <c r="D57" t="n">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>bottes-usees</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Worn Boots</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="D25" s="78" t="n">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="79" t="inlineStr">
-        <is>
-          <t>gilet-rembourre</t>
-        </is>
-      </c>
-      <c r="B26" s="80" t="inlineStr">
-        <is>
-          <t>Padded Vest</t>
-        </is>
-      </c>
-      <c r="C26" s="81" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="D26" s="78" t="n">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="79" t="inlineStr">
-        <is>
-          <t>tenue-de-voyageur</t>
-        </is>
-      </c>
-      <c r="B27" s="80" t="inlineStr">
-        <is>
-          <t>Traveler's Garb</t>
-        </is>
-      </c>
-      <c r="C27" s="81" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="D27" s="78" t="n">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="79" t="inlineStr">
-        <is>
-          <t>anneau-saignant</t>
-        </is>
-      </c>
-      <c r="B28" s="80" t="inlineStr">
-        <is>
-          <t>Bleeding Ring</t>
-        </is>
-      </c>
-      <c r="C28" s="81" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="D28" s="78" t="n">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="79" t="inlineStr">
-        <is>
-          <t>anneau-braise</t>
-        </is>
-      </c>
-      <c r="B29" s="80" t="inlineStr">
-        <is>
-          <t>Ember Ring</t>
-        </is>
-      </c>
-      <c r="C29" s="81" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="D29" s="78" t="n">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="79" t="inlineStr">
-        <is>
-          <t>anneau-frimas</t>
-        </is>
-      </c>
-      <c r="B30" s="80" t="inlineStr">
-        <is>
-          <t>Frost Band</t>
-        </is>
-      </c>
-      <c r="C30" s="81" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="D30" s="78" t="n">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="79" t="inlineStr">
-        <is>
-          <t>anneau-agile</t>
-        </is>
-      </c>
-      <c r="B31" s="80" t="inlineStr">
-        <is>
-          <t>Nimble Ring</t>
-        </is>
-      </c>
-      <c r="C31" s="81" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="D31" s="78" t="n">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="79" t="inlineStr">
-        <is>
-          <t>anneau-force</t>
-        </is>
-      </c>
-      <c r="B32" s="80" t="inlineStr">
-        <is>
-          <t>Power Ring</t>
-        </is>
-      </c>
-      <c r="C32" s="81" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="D32" s="78" t="n">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="79" t="inlineStr">
-        <is>
-          <t>anneau-etincelle</t>
-        </is>
-      </c>
-      <c r="B33" s="80" t="inlineStr">
-        <is>
-          <t>Spark Ring</t>
-        </is>
-      </c>
-      <c r="C33" s="81" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="D33" s="78" t="n">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="79" t="inlineStr">
-        <is>
-          <t>anneau-pierre</t>
-        </is>
-      </c>
-      <c r="B34" s="80" t="inlineStr">
-        <is>
-          <t>Stone Ring</t>
-        </is>
-      </c>
-      <c r="C34" s="81" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="D34" s="78" t="n">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="79" t="inlineStr">
-        <is>
-          <t>anneau-venin</t>
-        </is>
-      </c>
-      <c r="B35" s="80" t="inlineStr">
-        <is>
-          <t>Venom Ring</t>
-        </is>
-      </c>
-      <c r="C35" s="81" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="D35" s="78" t="n">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="79" t="inlineStr">
-        <is>
-          <t>anneau-vigueur</t>
-        </is>
-      </c>
-      <c r="B36" s="80" t="inlineStr">
-        <is>
-          <t>Vigor Ring</t>
-        </is>
-      </c>
-      <c r="C36" s="81" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="D36" s="78" t="n">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="79" t="inlineStr">
-        <is>
-          <t>bottes-cuir</t>
-        </is>
-      </c>
-      <c r="B37" s="80" t="inlineStr">
-        <is>
-          <t>Leather Boots</t>
-        </is>
-      </c>
-      <c r="C37" s="81" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="D37" s="78" t="n">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="79" t="inlineStr">
-        <is>
-          <t>sandales</t>
-        </is>
-      </c>
-      <c r="B38" s="80" t="inlineStr">
-        <is>
-          <t>Sandals</t>
-        </is>
-      </c>
-      <c r="C38" s="81" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="D38" s="78" t="n">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="79" t="inlineStr">
-        <is>
-          <t>bottes-voyage</t>
-        </is>
-      </c>
-      <c r="B39" s="80" t="inlineStr">
-        <is>
-          <t>Traveler Boots</t>
-        </is>
-      </c>
-      <c r="C39" s="81" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="D39" s="78" t="n">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="79" t="inlineStr">
-        <is>
-          <t>bottes-usees</t>
-        </is>
-      </c>
-      <c r="B40" s="80" t="inlineStr">
-        <is>
-          <t>Worn Boots</t>
-        </is>
-      </c>
-      <c r="C40" s="81" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="D40" s="78" t="n">
+      <c r="D58" t="n">
         <v>480</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="79" t="inlineStr">
-        <is>
-          <t>sceptre-apprenti</t>
-        </is>
-      </c>
-      <c r="B41" s="80" t="inlineStr">
-        <is>
-          <t>Apprentice Scepter</t>
-        </is>
-      </c>
-      <c r="C41" s="81" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="D41" s="78" t="n">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="79" t="inlineStr">
-        <is>
-          <t>targe</t>
-        </is>
-      </c>
-      <c r="B42" s="80" t="inlineStr">
-        <is>
-          <t>Buckler</t>
-        </is>
-      </c>
-      <c r="C42" s="81" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="D42" s="78" t="n">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="79" t="inlineStr">
-        <is>
-          <t>fanal</t>
-        </is>
-      </c>
-      <c r="B43" s="80" t="inlineStr">
-        <is>
-          <t>Hand Torch</t>
-        </is>
-      </c>
-      <c r="C43" s="81" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="D43" s="78" t="n">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="79" t="inlineStr">
-        <is>
-          <t>grimoire-soin</t>
-        </is>
-      </c>
-      <c r="B44" s="80" t="inlineStr">
-        <is>
-          <t>Healing Book</t>
-        </is>
-      </c>
-      <c r="C44" s="81" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="D44" s="78" t="n">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="79" t="inlineStr">
-        <is>
-          <t>grimoire</t>
-        </is>
-      </c>
-      <c r="B45" s="80" t="inlineStr">
-        <is>
-          <t>Spellbook</t>
-        </is>
-      </c>
-      <c r="C45" s="81" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="D45" s="78" t="n">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="79" t="inlineStr">
-        <is>
-          <t>bouclier-bois</t>
-        </is>
-      </c>
-      <c r="B46" s="80" t="inlineStr">
-        <is>
-          <t>Wooden Shield</t>
-        </is>
-      </c>
-      <c r="C46" s="81" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="D46" s="78" t="n">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="79" t="inlineStr">
-        <is>
-          <t>charme-os</t>
-        </is>
-      </c>
-      <c r="B47" s="80" t="inlineStr">
-        <is>
-          <t>Bone Charm</t>
-        </is>
-      </c>
-      <c r="C47" s="81" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="D47" s="78" t="n">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="79" t="inlineStr">
-        <is>
-          <t>collier-cuivre</t>
-        </is>
-      </c>
-      <c r="B48" s="80" t="inlineStr">
-        <is>
-          <t>Copper Amulet</t>
-        </is>
-      </c>
-      <c r="C48" s="81" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="D48" s="78" t="n">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="79" t="inlineStr">
-        <is>
-          <t>porte-bonheur</t>
-        </is>
-      </c>
-      <c r="B49" s="80" t="inlineStr">
-        <is>
-          <t>Lucky Charm</t>
-        </is>
-      </c>
-      <c r="C49" s="81" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="D49" s="78" t="n">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="79" t="inlineStr">
-        <is>
-          <t>pendentif-quartz</t>
-        </is>
-      </c>
-      <c r="B50" s="80" t="inlineStr">
-        <is>
-          <t>Quartz Pendant</t>
-        </is>
-      </c>
-      <c r="C50" s="81" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="D50" s="78" t="n">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="79" t="inlineStr">
-        <is>
-          <t>pendentif-chaud</t>
-        </is>
-      </c>
-      <c r="B51" s="80" t="inlineStr">
-        <is>
-          <t>Spark Pendant</t>
-        </is>
-      </c>
-      <c r="C51" s="81" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="D51" s="78" t="n">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="79" t="inlineStr">
-        <is>
-          <t>gants-tissu</t>
-        </is>
-      </c>
-      <c r="B52" s="80" t="inlineStr">
-        <is>
-          <t>Cloth Gloves</t>
-        </is>
-      </c>
-      <c r="C52" s="81" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="D52" s="78" t="n">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="79" t="inlineStr">
-        <is>
-          <t>gants-cuir</t>
-        </is>
-      </c>
-      <c r="B53" s="80" t="inlineStr">
-        <is>
-          <t>Leather Gloves</t>
-        </is>
-      </c>
-      <c r="C53" s="81" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="D53" s="78" t="n">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="79" t="inlineStr">
-        <is>
-          <t>gants-de-mineur</t>
-        </is>
-      </c>
-      <c r="B54" s="80" t="inlineStr">
-        <is>
-          <t>Miner's Gloves</t>
-        </is>
-      </c>
-      <c r="C54" s="81" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="D54" s="78" t="n">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="79" t="inlineStr">
-        <is>
-          <t>gants-cloutes</t>
-        </is>
-      </c>
-      <c r="B55" s="80" t="inlineStr">
-        <is>
-          <t>Studded Gloves</t>
-        </is>
-      </c>
-      <c r="C55" s="81" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="D55" s="78" t="n">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="79" t="inlineStr">
-        <is>
-          <t>gants-travail</t>
-        </is>
-      </c>
-      <c r="B56" s="80" t="inlineStr">
-        <is>
-          <t>Work Gloves</t>
-        </is>
-      </c>
-      <c r="C56" s="81" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="D56" s="78" t="n">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="79" t="inlineStr">
-        <is>
-          <t>sac-en-cuir</t>
-        </is>
-      </c>
-      <c r="B57" s="80" t="inlineStr">
-        <is>
-          <t>Leather Pouch</t>
-        </is>
-      </c>
-      <c r="C57" s="81" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="D57" s="78" t="n">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="79" t="inlineStr">
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>collier-concentration</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Amulet of Focus</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>plaque-de-fer</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Basic Iron Plate</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
         <is>
           <t>hache-berserk</t>
         </is>
       </c>
-      <c r="B58" s="80" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>Berserker Axe</t>
         </is>
       </c>
-      <c r="C58" s="82" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="D58" s="78" t="n">
+      <c r="D61" t="n">
         <v>1900</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="79" t="inlineStr">
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>peau-berserk</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Berserker Hide</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>grand-sac-en-cuir</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Big Leather Pouch</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>bague-de-sang</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Blood Ring</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>anneau-soif-sang</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Bloodthirst Ring</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
         <is>
           <t>epee-large</t>
         </is>
       </c>
-      <c r="B59" s="80" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>Claymore</t>
         </is>
       </c>
-      <c r="C59" s="82" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="D59" s="78" t="n">
+      <c r="D66" t="n">
         <v>1700</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="79" t="inlineStr">
+    <row r="67">
+      <c r="A67" t="inlineStr">
         <is>
           <t>baguette-cristal</t>
         </is>
       </c>
-      <c r="B60" s="80" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>Crystal Wand</t>
         </is>
       </c>
-      <c r="C60" s="82" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="D60" s="78" t="n">
+      <c r="D67" t="n">
         <v>2300</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="79" t="inlineStr">
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>bottes-braise</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Ember Striders</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
         <is>
           <t>lame-de-braise</t>
         </is>
       </c>
-      <c r="B61" s="80" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>Emberblade</t>
         </is>
       </c>
-      <c r="C61" s="82" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="D61" s="78" t="n">
+      <c r="D69" t="n">
         <v>1900</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="79" t="inlineStr">
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>pendentif-energie</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Energizing Pendant</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
         <is>
           <t>lame-bourreau</t>
         </is>
       </c>
-      <c r="B62" s="80" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>Executioner's Blade</t>
         </is>
       </c>
-      <c r="C62" s="82" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="D62" s="78" t="n">
+      <c r="D71" t="n">
         <v>2300</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="79" t="inlineStr">
+    <row r="72">
+      <c r="A72" t="inlineStr">
         <is>
           <t>marteau-de-forge</t>
         </is>
       </c>
-      <c r="B63" s="80" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>Forge Hammer</t>
         </is>
       </c>
-      <c r="C63" s="82" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="D63" s="78" t="n">
+      <c r="D72" t="n">
         <v>1900</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="79" t="inlineStr">
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>anneau-forge</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Forge Ring</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>anneau-de-givre</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Frost Ring</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>sceau-givre</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Frost Signet</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
         <is>
           <t>lame-de-givre</t>
         </is>
       </c>
-      <c r="B64" s="80" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t>Frostbrand</t>
         </is>
       </c>
-      <c r="C64" s="82" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="D64" s="78" t="n">
+      <c r="D76" t="n">
         <v>2300</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="79" t="inlineStr">
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>gantelets</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Gauntlets</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>grimoire-flammes</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Grimoire of Flames</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
         <is>
           <t>hallebarde</t>
         </is>
       </c>
-      <c r="B65" s="80" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>Halberd</t>
         </is>
       </c>
-      <c r="C65" s="82" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="D65" s="78" t="n">
+      <c r="D79" t="n">
         <v>2200</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="79" t="inlineStr">
+    <row r="80">
+      <c r="A80" t="inlineStr">
         <is>
           <t>epee-sacree</t>
         </is>
       </c>
-      <c r="B66" s="80" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>Holy Sword</t>
         </is>
       </c>
-      <c r="C66" s="82" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="D66" s="78" t="n">
+      <c r="D80" t="n">
         <v>2000</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="79" t="inlineStr">
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>anneau-de-fer</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Iron Ring</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>gants-chance</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Lucky Glove</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
         <is>
           <t>hache-faucheuse</t>
         </is>
       </c>
-      <c r="B67" s="80" t="inlineStr">
+      <c r="B83" t="inlineStr">
         <is>
           <t>Reaver Axe</t>
         </is>
       </c>
-      <c r="C67" s="82" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="D67" s="78" t="n">
+      <c r="D83" t="n">
         <v>2100</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="79" t="inlineStr">
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>bouclier-renforce</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Reinforced Shield</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>anneau-puissance</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Ring of Might</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>collier-de-saphir</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Sapphire Amulet</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>sceptre-commandement</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Scepter of Command</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>armure-cloutee</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Spiked Armor</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
         <is>
           <t>fleau-cloute</t>
         </is>
       </c>
-      <c r="B68" s="80" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>Spiked Flail</t>
         </is>
       </c>
-      <c r="C68" s="82" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="D68" s="78" t="n">
+      <c r="D89" t="n">
         <v>2200</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="79" t="inlineStr">
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>armure-stone-age</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Stone Armor</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>bottes-stone-age</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Stone Boots</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>gants-stone-age</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Stone Glove</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
         <is>
           <t>marteau-de-pierre</t>
         </is>
       </c>
-      <c r="B69" s="80" t="inlineStr">
+      <c r="B93" t="inlineStr">
         <is>
           <t>Stone Hammer</t>
         </is>
       </c>
-      <c r="C69" s="82" t="inlineStr">
+      <c r="C93" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="D69" s="78" t="n">
+      <c r="D93" t="n">
         <v>2200</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="79" t="inlineStr">
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>bottes-pierre</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Stonetread Boots</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>bottes-vives</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Swift Boots</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>bottes-rapides</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Swift Striders</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>gants-voleur</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Thief's Gloves</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>grimoire-puissance</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Tome of Power</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>anneau-toxique</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Toxic Ring</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
         <is>
           <t>dagues-jumelles</t>
         </is>
       </c>
-      <c r="B70" s="80" t="inlineStr">
+      <c r="B100" t="inlineStr">
         <is>
           <t>Twin Daggers</t>
         </is>
       </c>
-      <c r="C70" s="82" t="inlineStr">
+      <c r="C100" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="D70" s="78" t="n">
+      <c r="D100" t="n">
         <v>2300</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="79" t="inlineStr">
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>pendentif-vampire</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Vampiric Pendant</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>gants-venin</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Venom Gloves</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
         <is>
           <t>dague-venin</t>
         </is>
       </c>
-      <c r="B71" s="80" t="inlineStr">
+      <c r="B103" t="inlineStr">
         <is>
           <t>Venomfang Dagger</t>
         </is>
       </c>
-      <c r="C71" s="82" t="inlineStr">
+      <c r="C103" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="D71" s="78" t="n">
+      <c r="D103" t="n">
         <v>2200</v>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="79" t="inlineStr">
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>bouclier-protecteur</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Warding Shield</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
         <is>
           <t>marteau-guerre</t>
         </is>
       </c>
-      <c r="B72" s="80" t="inlineStr">
+      <c r="B105" t="inlineStr">
         <is>
           <t>Warhammer</t>
         </is>
       </c>
-      <c r="C72" s="82" t="inlineStr">
+      <c r="C105" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="D72" s="78" t="n">
+      <c r="D105" t="n">
         <v>2300</v>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="79" t="inlineStr">
-        <is>
-          <t>plaque-de-fer</t>
-        </is>
-      </c>
-      <c r="B73" s="80" t="inlineStr">
-        <is>
-          <t>Basic Iron Plate</t>
-        </is>
-      </c>
-      <c r="C73" s="82" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="D73" s="78" t="n">
-        <v>1700</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="79" t="inlineStr">
-        <is>
-          <t>peau-berserk</t>
-        </is>
-      </c>
-      <c r="B74" s="80" t="inlineStr">
-        <is>
-          <t>Berserker Hide</t>
-        </is>
-      </c>
-      <c r="C74" s="82" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="D74" s="78" t="n">
-        <v>1800</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="79" t="inlineStr">
-        <is>
-          <t>armure-stone-age</t>
-        </is>
-      </c>
-      <c r="B75" s="80" t="inlineStr">
-        <is>
-          <t>Stone Armor</t>
-        </is>
-      </c>
-      <c r="C75" s="82" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="D75" s="78" t="n">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="79" t="inlineStr">
-        <is>
-          <t>bague-de-sang</t>
-        </is>
-      </c>
-      <c r="B76" s="80" t="inlineStr">
-        <is>
-          <t>Blood Ring</t>
-        </is>
-      </c>
-      <c r="C76" s="82" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="D76" s="78" t="n">
-        <v>1700</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="79" t="inlineStr">
-        <is>
-          <t>anneau-soif-sang</t>
-        </is>
-      </c>
-      <c r="B77" s="80" t="inlineStr">
-        <is>
-          <t>Bloodthirst Ring</t>
-        </is>
-      </c>
-      <c r="C77" s="82" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="D77" s="78" t="n">
-        <v>2100</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="79" t="inlineStr">
-        <is>
-          <t>anneau-forge</t>
-        </is>
-      </c>
-      <c r="B78" s="80" t="inlineStr">
-        <is>
-          <t>Forge Ring</t>
-        </is>
-      </c>
-      <c r="C78" s="82" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="D78" s="78" t="n">
-        <v>2200</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="79" t="inlineStr">
-        <is>
-          <t>anneau-de-givre</t>
-        </is>
-      </c>
-      <c r="B79" s="80" t="inlineStr">
-        <is>
-          <t>Frost Ring</t>
-        </is>
-      </c>
-      <c r="C79" s="82" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="D79" s="78" t="n">
-        <v>2100</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="79" t="inlineStr">
-        <is>
-          <t>sceau-givre</t>
-        </is>
-      </c>
-      <c r="B80" s="80" t="inlineStr">
-        <is>
-          <t>Frost Signet</t>
-        </is>
-      </c>
-      <c r="C80" s="82" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="D80" s="78" t="n">
-        <v>1900</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="79" t="inlineStr">
-        <is>
-          <t>anneau-de-fer</t>
-        </is>
-      </c>
-      <c r="B81" s="80" t="inlineStr">
-        <is>
-          <t>Iron Ring</t>
-        </is>
-      </c>
-      <c r="C81" s="82" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="D81" s="78" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="79" t="inlineStr">
-        <is>
-          <t>anneau-puissance</t>
-        </is>
-      </c>
-      <c r="B82" s="80" t="inlineStr">
-        <is>
-          <t>Ring of Might</t>
-        </is>
-      </c>
-      <c r="C82" s="82" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="D82" s="78" t="n">
-        <v>2300</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="79" t="inlineStr">
-        <is>
-          <t>anneau-toxique</t>
-        </is>
-      </c>
-      <c r="B83" s="80" t="inlineStr">
-        <is>
-          <t>Toxic Ring</t>
-        </is>
-      </c>
-      <c r="C83" s="82" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="D83" s="78" t="n">
-        <v>1900</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="79" t="inlineStr">
-        <is>
-          <t>bottes-braise</t>
-        </is>
-      </c>
-      <c r="B84" s="80" t="inlineStr">
-        <is>
-          <t>Ember Striders</t>
-        </is>
-      </c>
-      <c r="C84" s="82" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="D84" s="78" t="n">
-        <v>2100</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="79" t="inlineStr">
-        <is>
-          <t>bottes-stone-age</t>
-        </is>
-      </c>
-      <c r="B85" s="80" t="inlineStr">
-        <is>
-          <t>Stone Boots</t>
-        </is>
-      </c>
-      <c r="C85" s="82" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="D85" s="78" t="n">
-        <v>1800</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="79" t="inlineStr">
-        <is>
-          <t>bottes-pierre</t>
-        </is>
-      </c>
-      <c r="B86" s="80" t="inlineStr">
-        <is>
-          <t>Stonetread Boots</t>
-        </is>
-      </c>
-      <c r="C86" s="82" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="D86" s="78" t="n">
-        <v>2100</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="79" t="inlineStr">
-        <is>
-          <t>bottes-vives</t>
-        </is>
-      </c>
-      <c r="B87" s="80" t="inlineStr">
-        <is>
-          <t>Swift Boots</t>
-        </is>
-      </c>
-      <c r="C87" s="82" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="D87" s="78" t="n">
-        <v>2400</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="79" t="inlineStr">
-        <is>
-          <t>bottes-rapides</t>
-        </is>
-      </c>
-      <c r="B88" s="80" t="inlineStr">
-        <is>
-          <t>Swift Striders</t>
-        </is>
-      </c>
-      <c r="C88" s="82" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="D88" s="78" t="n">
-        <v>1900</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="79" t="inlineStr">
-        <is>
-          <t>grimoire-flammes</t>
-        </is>
-      </c>
-      <c r="B89" s="80" t="inlineStr">
-        <is>
-          <t>Grimoire of Flames</t>
-        </is>
-      </c>
-      <c r="C89" s="82" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="D89" s="78" t="n">
-        <v>2200</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="79" t="inlineStr">
-        <is>
-          <t>bouclier-renforce</t>
-        </is>
-      </c>
-      <c r="B90" s="80" t="inlineStr">
-        <is>
-          <t>Reinforced Shield</t>
-        </is>
-      </c>
-      <c r="C90" s="82" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="D90" s="78" t="n">
-        <v>2400</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="79" t="inlineStr">
-        <is>
-          <t>sceptre-commandement</t>
-        </is>
-      </c>
-      <c r="B91" s="80" t="inlineStr">
-        <is>
-          <t>Scepter of Command</t>
-        </is>
-      </c>
-      <c r="C91" s="82" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="D91" s="78" t="n">
-        <v>1800</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="79" t="inlineStr">
-        <is>
-          <t>grimoire-puissance</t>
-        </is>
-      </c>
-      <c r="B92" s="80" t="inlineStr">
-        <is>
-          <t>Tome of Power</t>
-        </is>
-      </c>
-      <c r="C92" s="82" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="D92" s="78" t="n">
-        <v>2100</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="79" t="inlineStr">
-        <is>
-          <t>collier-concentration</t>
-        </is>
-      </c>
-      <c r="B93" s="80" t="inlineStr">
-        <is>
-          <t>Amulet of Focus</t>
-        </is>
-      </c>
-      <c r="C93" s="82" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="D93" s="78" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="79" t="inlineStr">
-        <is>
-          <t>pendentif-energie</t>
-        </is>
-      </c>
-      <c r="B94" s="80" t="inlineStr">
-        <is>
-          <t>Energizing Pendant</t>
-        </is>
-      </c>
-      <c r="C94" s="82" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="D94" s="78" t="n">
-        <v>2300</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="79" t="inlineStr">
-        <is>
-          <t>collier-de-saphir</t>
-        </is>
-      </c>
-      <c r="B95" s="80" t="inlineStr">
-        <is>
-          <t>Sapphire Amulet</t>
-        </is>
-      </c>
-      <c r="C95" s="82" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="D95" s="78" t="n">
-        <v>1700</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="79" t="inlineStr">
-        <is>
-          <t>pendentif-vampire</t>
-        </is>
-      </c>
-      <c r="B96" s="80" t="inlineStr">
-        <is>
-          <t>Vampiric Pendant</t>
-        </is>
-      </c>
-      <c r="C96" s="82" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="D96" s="78" t="n">
-        <v>2100</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="79" t="inlineStr">
-        <is>
-          <t>gantelets</t>
-        </is>
-      </c>
-      <c r="B97" s="80" t="inlineStr">
-        <is>
-          <t>Gauntlets</t>
-        </is>
-      </c>
-      <c r="C97" s="82" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="D97" s="78" t="n">
-        <v>2200</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="79" t="inlineStr">
-        <is>
-          <t>gants-chance</t>
-        </is>
-      </c>
-      <c r="B98" s="80" t="inlineStr">
-        <is>
-          <t>Lucky Glove</t>
-        </is>
-      </c>
-      <c r="C98" s="82" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="D98" s="78" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="79" t="inlineStr">
-        <is>
-          <t>gants-stone-age</t>
-        </is>
-      </c>
-      <c r="B99" s="80" t="inlineStr">
-        <is>
-          <t>Stone Glove</t>
-        </is>
-      </c>
-      <c r="C99" s="82" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="D99" s="78" t="n">
-        <v>2100</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="79" t="inlineStr">
-        <is>
-          <t>gants-voleur</t>
-        </is>
-      </c>
-      <c r="B100" s="80" t="inlineStr">
-        <is>
-          <t>Thief's Gloves</t>
-        </is>
-      </c>
-      <c r="C100" s="82" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="D100" s="78" t="n">
-        <v>2200</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="79" t="inlineStr">
-        <is>
-          <t>gants-venin</t>
-        </is>
-      </c>
-      <c r="B101" s="80" t="inlineStr">
-        <is>
-          <t>Venom Gloves</t>
-        </is>
-      </c>
-      <c r="C101" s="82" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="D101" s="78" t="n">
-        <v>1900</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="79" t="inlineStr">
-        <is>
-          <t>grand-sac-en-cuir</t>
-        </is>
-      </c>
-      <c r="B102" s="80" t="inlineStr">
-        <is>
-          <t>Big Leather Pouch</t>
-        </is>
-      </c>
-      <c r="C102" s="82" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="D102" s="78" t="n">
-        <v>2100</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="79" t="inlineStr">
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>chevaliere-ancienne</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Ancient Signet</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>sac-a-dos</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Backpack</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>bottes-barbare</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Barbarian Boots</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10100</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>brassards-barbare</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Barbarian Bracers</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>9800</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>plastron-barbare</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Barbarian Harness</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10400</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
         <is>
           <t>croc-de-basilic</t>
         </is>
       </c>
-      <c r="B103" s="80" t="inlineStr">
+      <c r="B111" t="inlineStr">
         <is>
           <t>Basilisk Fang</t>
         </is>
       </c>
-      <c r="C103" s="83" t="inlineStr">
+      <c r="C111" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="D103" s="78" t="n">
+      <c r="D111" t="n">
         <v>9000</v>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="79" t="inlineStr">
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>gants-sang</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Blood Gauntlets</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>9200</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>bottes-sang</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Blood Greaves</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>plate-sang</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Blood Plate</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>gants-croise</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Crusader Gauntlets</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>8400</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>bottes-croise</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Crusader Greaves</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>9900</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>plate-croise</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Crusader Plate</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>calice-cristal</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Crystal Chalice</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>9900</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>remede-vieillesse</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Elixir of Youth</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>10500</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>caillou-flottant</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Floating Pebble</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>maille-de-forge</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Forgemaster's Mail</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>8100</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>idole-doree</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Gilded Idol</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>enorme-sac-en-cuir</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Huge Leather Pouch</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>9400</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>bottes-de-maille</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Mail Boots</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>8900</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>gants-de-maille</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Mail Glove</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>collier-de-saphir-fin</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Nice Sapphire Amulet</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>8600</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>anneau-de-givre-parfait</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Perfect Frost Ring</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>8300</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>ring-of-luck</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Ring of Luck</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
         <is>
           <t>marteau-de-siege</t>
         </is>
       </c>
-      <c r="B104" s="80" t="inlineStr">
+      <c r="B129" t="inlineStr">
         <is>
           <t>Siege Maul</t>
         </is>
       </c>
-      <c r="C104" s="83" t="inlineStr">
+      <c r="C129" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="D104" s="78" t="n">
+      <c r="D129" t="n">
         <v>11000</v>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="79" t="inlineStr">
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>bouclier-tour</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Tower Shield</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>9200</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
         <is>
           <t>hache-de-guerre</t>
         </is>
       </c>
-      <c r="B105" s="80" t="inlineStr">
+      <c r="B131" t="inlineStr">
         <is>
           <t>War Axe</t>
         </is>
       </c>
-      <c r="C105" s="83" t="inlineStr">
+      <c r="C131" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="D105" s="78" t="n">
+      <c r="D131" t="n">
         <v>8100</v>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="79" t="inlineStr">
-        <is>
-          <t>plate-sang</t>
-        </is>
-      </c>
-      <c r="B106" s="80" t="inlineStr">
-        <is>
-          <t>Blood Plate</t>
-        </is>
-      </c>
-      <c r="C106" s="83" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="D106" s="78" t="n">
-        <v>11000</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="79" t="inlineStr">
-        <is>
-          <t>plate-croise</t>
-        </is>
-      </c>
-      <c r="B107" s="80" t="inlineStr">
-        <is>
-          <t>Crusader Plate</t>
-        </is>
-      </c>
-      <c r="C107" s="83" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="D107" s="78" t="n">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="79" t="inlineStr">
-        <is>
-          <t>maille-de-forge</t>
-        </is>
-      </c>
-      <c r="B108" s="80" t="inlineStr">
-        <is>
-          <t>Forgemaster's Mail</t>
-        </is>
-      </c>
-      <c r="C108" s="83" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="D108" s="78" t="n">
-        <v>8100</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="79" t="inlineStr">
-        <is>
-          <t>anneau-de-givre-parfait</t>
-        </is>
-      </c>
-      <c r="B109" s="80" t="inlineStr">
-        <is>
-          <t>Perfect Frost Ring</t>
-        </is>
-      </c>
-      <c r="C109" s="83" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="D109" s="78" t="n">
-        <v>8300</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="79" t="inlineStr">
-        <is>
-          <t>ring-of-luck</t>
-        </is>
-      </c>
-      <c r="B110" s="80" t="inlineStr">
-        <is>
-          <t>Ring of Luck</t>
-        </is>
-      </c>
-      <c r="C110" s="83" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="D110" s="95" t="n">
-        <v>11000</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="79" t="inlineStr">
-        <is>
-          <t>bottes-sang</t>
-        </is>
-      </c>
-      <c r="B111" s="80" t="inlineStr">
-        <is>
-          <t>Blood Greaves</t>
-        </is>
-      </c>
-      <c r="C111" s="83" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="D111" s="78" t="n">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="79" t="inlineStr">
-        <is>
-          <t>bottes-croise</t>
-        </is>
-      </c>
-      <c r="B112" s="80" t="inlineStr">
-        <is>
-          <t>Crusader Greaves</t>
-        </is>
-      </c>
-      <c r="C112" s="83" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="D112" s="78" t="n">
-        <v>9900</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="79" t="inlineStr">
-        <is>
-          <t>bottes-de-maille</t>
-        </is>
-      </c>
-      <c r="B113" s="80" t="inlineStr">
-        <is>
-          <t>Mail Boots</t>
-        </is>
-      </c>
-      <c r="C113" s="83" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="D113" s="78" t="n">
-        <v>8900</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="79" t="inlineStr">
-        <is>
-          <t>collier-de-saphir-fin</t>
-        </is>
-      </c>
-      <c r="B114" s="80" t="inlineStr">
-        <is>
-          <t>Nice Sapphire Amulet</t>
-        </is>
-      </c>
-      <c r="C114" s="83" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="D114" s="78" t="n">
-        <v>8600</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="79" t="inlineStr">
-        <is>
-          <t>gants-sang</t>
-        </is>
-      </c>
-      <c r="B115" s="80" t="inlineStr">
-        <is>
-          <t>Blood Gauntlets</t>
-        </is>
-      </c>
-      <c r="C115" s="83" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="D115" s="78" t="n">
-        <v>9200</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="79" t="inlineStr">
-        <is>
-          <t>gants-croise</t>
-        </is>
-      </c>
-      <c r="B116" s="80" t="inlineStr">
-        <is>
-          <t>Crusader Gauntlets</t>
-        </is>
-      </c>
-      <c r="C116" s="83" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="D116" s="78" t="n">
-        <v>8400</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="79" t="inlineStr">
-        <is>
-          <t>gants-de-maille</t>
-        </is>
-      </c>
-      <c r="B117" s="80" t="inlineStr">
-        <is>
-          <t>Mail Glove</t>
-        </is>
-      </c>
-      <c r="C117" s="83" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="D117" s="78" t="n">
-        <v>9000</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="79" t="inlineStr">
-        <is>
-          <t>sac-a-dos</t>
-        </is>
-      </c>
-      <c r="B118" s="80" t="inlineStr">
-        <is>
-          <t>Backpack</t>
-        </is>
-      </c>
-      <c r="C118" s="83" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="D118" s="78" t="n">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="79" t="inlineStr">
-        <is>
-          <t>enorme-sac-en-cuir</t>
-        </is>
-      </c>
-      <c r="B119" s="80" t="inlineStr">
-        <is>
-          <t>Huge Leather Pouch</t>
-        </is>
-      </c>
-      <c r="C119" s="83" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="D119" s="78" t="n">
-        <v>9400</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="79" t="inlineStr">
-        <is>
-          <t>chevaliere-ancienne</t>
-        </is>
-      </c>
-      <c r="B120" s="80" t="inlineStr">
-        <is>
-          <t>Ancient Signet</t>
-        </is>
-      </c>
-      <c r="C120" s="83" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="D120" s="78" t="n">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="79" t="inlineStr">
-        <is>
-          <t>calice-cristal</t>
-        </is>
-      </c>
-      <c r="B121" s="80" t="inlineStr">
-        <is>
-          <t>Crystal Chalice</t>
-        </is>
-      </c>
-      <c r="C121" s="83" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="D121" s="78" t="n">
-        <v>9900</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="79" t="inlineStr">
-        <is>
-          <t>idole-doree</t>
-        </is>
-      </c>
-      <c r="B122" s="80" t="inlineStr">
-        <is>
-          <t>Gilded Idol</t>
-        </is>
-      </c>
-      <c r="C122" s="83" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="D122" s="78" t="n">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="79" t="inlineStr">
+    <row r="132">
+      <c r="A132" t="inlineStr">
         <is>
           <t>epee-onyx</t>
         </is>
       </c>
-      <c r="B123" s="80" t="inlineStr">
+      <c r="B132" t="inlineStr">
         <is>
           <t>Big Onyx Sword</t>
         </is>
       </c>
-      <c r="C123" s="84" t="inlineStr">
+      <c r="C132" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="D123" s="78" t="n">
+      <c r="D132" t="n">
         <v>64000</v>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="79" t="inlineStr">
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>sac-sans-fond</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Bottomless Bag</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>94000</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>gantelets-dunir</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Dunir's Blessed Gauntlets</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>79000</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>plastron-dunir</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Dunir's Blessed Plate</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>83000</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>solerets-dunir</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Dunir's Blessed Sabatons</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>80500</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
         <is>
           <t>grande-faux</t>
         </is>
       </c>
-      <c r="B124" s="80" t="inlineStr">
+      <c r="B137" t="inlineStr">
         <is>
           <t>Great Scythe</t>
         </is>
       </c>
-      <c r="C124" s="84" t="inlineStr">
+      <c r="C137" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="D124" s="78" t="n">
+      <c r="D137" t="n">
         <v>88000</v>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="79" t="inlineStr">
+    <row r="138">
+      <c r="A138" t="inlineStr">
         <is>
           <t>marteau-de-lave</t>
         </is>
       </c>
-      <c r="B125" s="80" t="inlineStr">
+      <c r="B138" t="inlineStr">
         <is>
           <t>Magma Hammer</t>
         </is>
       </c>
-      <c r="C125" s="84" t="inlineStr">
+      <c r="C138" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="D125" s="78" t="n">
+      <c r="D138" t="n">
         <v>80000</v>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="79" t="inlineStr">
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>bottes-onyx</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Onyx Boots</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>gants-onyx</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Onyx Glove</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>82000</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
         <is>
           <t>plate-onyx</t>
         </is>
       </c>
-      <c r="B126" s="80" t="inlineStr">
+      <c r="B141" t="inlineStr">
         <is>
           <t>Onyx Guard Plate</t>
         </is>
       </c>
-      <c r="C126" s="84" t="inlineStr">
+      <c r="C141" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="D126" s="78" t="n">
+      <c r="D141" t="n">
         <v>65000</v>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="79" t="inlineStr">
-        <is>
-          <t>bottes-onyx</t>
-        </is>
-      </c>
-      <c r="B127" s="80" t="inlineStr">
-        <is>
-          <t>Onyx Boots</t>
-        </is>
-      </c>
-      <c r="C127" s="84" t="inlineStr">
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>collier-de-saphir-parfait</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Perfect Sapphire Amulet</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="D127" s="78" t="n">
-        <v>70000</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="79" t="inlineStr">
-        <is>
-          <t>collier-de-saphir-parfait</t>
-        </is>
-      </c>
-      <c r="B128" s="80" t="inlineStr">
-        <is>
-          <t>Perfect Sapphire Amulet</t>
-        </is>
-      </c>
-      <c r="C128" s="84" t="inlineStr">
-        <is>
-          <t>Epic</t>
-        </is>
-      </c>
-      <c r="D128" s="78" t="n">
+      <c r="D142" t="n">
         <v>84000</v>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="79" t="inlineStr">
-        <is>
-          <t>gants-onyx</t>
-        </is>
-      </c>
-      <c r="B129" s="80" t="inlineStr">
-        <is>
-          <t>Onyx Glove</t>
-        </is>
-      </c>
-      <c r="C129" s="84" t="inlineStr">
-        <is>
-          <t>Epic</t>
-        </is>
-      </c>
-      <c r="D129" s="78" t="n">
-        <v>82000</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="79" t="inlineStr">
-        <is>
-          <t>sac-sans-fond</t>
-        </is>
-      </c>
-      <c r="B130" s="80" t="inlineStr">
-        <is>
-          <t>Bottomless Bag</t>
-        </is>
-      </c>
-      <c r="C130" s="84" t="inlineStr">
-        <is>
-          <t>Epic</t>
-        </is>
-      </c>
-      <c r="D130" s="78" t="n">
-        <v>94000</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="79" t="inlineStr">
+    <row r="143">
+      <c r="A143" t="inlineStr">
         <is>
           <t>sac-maitre-mineur</t>
         </is>
       </c>
-      <c r="B131" s="80" t="inlineStr">
+      <c r="B143" t="inlineStr">
         <is>
           <t>Master Miner's Bag</t>
         </is>
       </c>
-      <c r="C131" s="85" t="inlineStr">
+      <c r="C143" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="D131" s="78" t="n">
+      <c r="D143" t="n">
         <v>290000</v>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="79" t="inlineStr">
-        <is>
-          <t>plastron-barbare</t>
-        </is>
-      </c>
-      <c r="B132" s="80" t="inlineStr">
-        <is>
-          <t>Barbarian Harness</t>
-        </is>
-      </c>
-      <c r="C132" s="85" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="D132" s="78" t="n">
-        <v>10400</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="79" t="inlineStr">
-        <is>
-          <t>brassards-barbare</t>
-        </is>
-      </c>
-      <c r="B133" s="80" t="inlineStr">
-        <is>
-          <t>Barbarian Bracers</t>
-        </is>
-      </c>
-      <c r="C133" s="85" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="D133" s="78" t="n">
-        <v>9800</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="79" t="inlineStr">
-        <is>
-          <t>bottes-barbare</t>
-        </is>
-      </c>
-      <c r="B134" s="80" t="inlineStr">
-        <is>
-          <t>Barbarian Boots</t>
-        </is>
-      </c>
-      <c r="C134" s="85" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="D134" s="78" t="n">
-        <v>10100</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="79" t="inlineStr">
-        <is>
-          <t>plastron-dunir</t>
-        </is>
-      </c>
-      <c r="B135" s="80" t="inlineStr">
-        <is>
-          <t>Dunir's Blessed Plate</t>
-        </is>
-      </c>
-      <c r="C135" s="85" t="inlineStr">
-        <is>
-          <t>Epic</t>
-        </is>
-      </c>
-      <c r="D135" s="78" t="n">
-        <v>83000</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="79" t="inlineStr">
-        <is>
-          <t>gantelets-dunir</t>
-        </is>
-      </c>
-      <c r="B136" s="80" t="inlineStr">
-        <is>
-          <t>Dunir's Blessed Gauntlets</t>
-        </is>
-      </c>
-      <c r="C136" s="85" t="inlineStr">
-        <is>
-          <t>Epic</t>
-        </is>
-      </c>
-      <c r="D136" s="78" t="n">
-        <v>79000</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="79" t="inlineStr">
-        <is>
-          <t>solerets-dunir</t>
-        </is>
-      </c>
-      <c r="B137" s="80" t="inlineStr">
-        <is>
-          <t>Dunir's Blessed Sabatons</t>
-        </is>
-      </c>
-      <c r="C137" s="85" t="inlineStr">
-        <is>
-          <t>Epic</t>
-        </is>
-      </c>
-      <c r="D137" s="78" t="n">
-        <v>80500</v>
-      </c>
-    </row>
   </sheetData>
+  <autoFilter ref="A6:D6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -27284,6 +27411,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A6:D6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -34848,6 +34976,11 @@
           <t>Épique</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -34919,12 +35052,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Celerity Stone</t>
+          <t>Agility Stone</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>agilité</t>
+          <t>agilite</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -35016,12 +35149,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Onde de tranquilité</t>
+          <t>onde-tranquilite</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Wave of Calm</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
           <t>pop-monstre</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>#a8e0d0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -35046,12 +35189,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>poussière de rubis</t>
+          <t>poussiere-rubis</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ruby Dust</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Soigne</t>
+          <t>soin</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>#e0555f</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -35072,12 +35225,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Lucky stone</t>
+          <t>pierre-chance</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Lucky Stone</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>% de chance augmenté</t>
+          <t>chance-minerais</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>#7ed957</t>
         </is>
       </c>
       <c r="E14" t="n">

--- a/docs/BRUTAL-items-et-cartes.xlsx
+++ b/docs/BRUTAL-items-et-cartes.xlsx
@@ -24146,7 +24146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D143"/>
+  <dimension ref="A1:D148"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="140" min="1" max="1"/>
@@ -24227,12 +24227,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pioche-basique</t>
+          <t>anneau-saignant</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Basic Pickaxe</t>
+          <t>Bleeding Ring</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -24241,18 +24241,18 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>350</v>
+        <v>440</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>anneau-saignant</t>
+          <t>charme-os</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bleeding Ring</t>
+          <t>Bone Charm</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -24261,18 +24261,18 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>440</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>charme-os</t>
+          <t>targe</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bone Charm</t>
+          <t>Buckler</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -24287,12 +24287,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>targe</t>
+          <t>cotte-mailles</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Buckler</t>
+          <t>Chainmail</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -24301,18 +24301,18 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>380</v>
+        <v>460</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>cotte-mailles</t>
+          <t>couperet</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Chainmail</t>
+          <t>Cleaver</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -24321,18 +24321,18 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>460</v>
+        <v>440</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>couperet</t>
+          <t>gants-tissu</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cleaver</t>
+          <t>Cloth Gloves</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -24341,18 +24341,18 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>440</v>
+        <v>340</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>gants-tissu</t>
+          <t>collier-cuivre</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cloth Gloves</t>
+          <t>Copper Amulet</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -24361,18 +24361,18 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>340</v>
+        <v>410</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>collier-cuivre</t>
+          <t>anneau-braise</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Copper Amulet</t>
+          <t>Ember Ring</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -24381,18 +24381,18 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>410</v>
+        <v>340</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>anneau-braise</t>
+          <t>anneau-frimas</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ember Ring</t>
+          <t>Frost Band</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -24401,18 +24401,18 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>340</v>
+        <v>370</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>anneau-frimas</t>
+          <t>fanal</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Frost Band</t>
+          <t>Hand Torch</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -24421,18 +24421,18 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>370</v>
+        <v>380</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>fanal</t>
+          <t>hachette</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Hand Torch</t>
+          <t>Hatchet</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -24441,18 +24441,18 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>380</v>
+        <v>430</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>hachette</t>
+          <t>grimoire-soin</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Hatchet</t>
+          <t>Healing Book</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -24461,18 +24461,18 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>430</v>
+        <v>470</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>grimoire-soin</t>
+          <t>armure-peau</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Healing Book</t>
+          <t>Hide Armor</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -24487,12 +24487,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>armure-peau</t>
+          <t>pic-de-glace</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Hide Armor</t>
+          <t>Ice Pick</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -24501,18 +24501,18 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>470</v>
+        <v>360</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>pic-de-glace</t>
+          <t>pioche-fer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ice Pick</t>
+          <t>Iron Pickaxe</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -24521,7 +24521,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>360</v>
+        <v>450</v>
       </c>
     </row>
     <row r="23">
@@ -24707,12 +24707,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>gilet-rembourre</t>
+          <t>vieille-pioche</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Padded Vest</t>
+          <t>Old Pickaxe</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -24721,18 +24721,18 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>420</v>
+        <v>320</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>fourche</t>
+          <t>gilet-rembourre</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Pitchfork</t>
+          <t>Padded Vest</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -24741,18 +24741,18 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>330</v>
+        <v>420</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>anneau-force</t>
+          <t>fourche</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Power Ring</t>
+          <t>Pitchfork</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -24761,18 +24761,18 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>340</v>
+        <v>330</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>baton</t>
+          <t>anneau-force</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Quarterstaff</t>
+          <t>Power Ring</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -24781,18 +24781,18 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>330</v>
+        <v>340</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>pendentif-quartz</t>
+          <t>baton</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Quartz Pendant</t>
+          <t>Quarterstaff</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -24807,12 +24807,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>hache-rouillee</t>
+          <t>pendentif-quartz</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Rusty Axe</t>
+          <t>Quartz Pendant</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -24821,18 +24821,18 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>370</v>
+        <v>330</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>dague-rouillee</t>
+          <t>hache-rouillee</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Rusty Dagger</t>
+          <t>Rusty Axe</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -24841,18 +24841,18 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>430</v>
+        <v>370</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>sandales</t>
+          <t>dague-rouillee</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Sandals</t>
+          <t>Rusty Dagger</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -24861,18 +24861,18 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>410</v>
+        <v>430</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>couteau-serpent</t>
+          <t>sandales</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Serpent Knife</t>
+          <t>Sandals</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -24881,18 +24881,18 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>380</v>
+        <v>410</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>couteau-dentele</t>
+          <t>couteau-serpent</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Serrated Knife</t>
+          <t>Serpent Knife</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -24901,18 +24901,18 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>370</v>
+        <v>380</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>epee-courte</t>
+          <t>couteau-dentele</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Short Sword</t>
+          <t>Serrated Knife</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -24921,18 +24921,18 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>330</v>
+        <v>370</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>pendentif-chaud</t>
+          <t>epee-courte</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Spark Pendant</t>
+          <t>Short Sword</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -24941,18 +24941,18 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>400</v>
+        <v>330</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>anneau-etincelle</t>
+          <t>pendentif-chaud</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Spark Ring</t>
+          <t>Spark Pendant</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -24961,18 +24961,18 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>460</v>
+        <v>400</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>lance</t>
+          <t>anneau-etincelle</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Spear</t>
+          <t>Spark Ring</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -24981,18 +24981,18 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>340</v>
+        <v>460</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>grimoire</t>
+          <t>lance</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Spellbook</t>
+          <t>Spear</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -25001,18 +25001,18 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>480</v>
+        <v>340</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>anneau-pierre</t>
+          <t>grimoire</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Stone Ring</t>
+          <t>Spellbook</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -25021,18 +25021,18 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>390</v>
+        <v>480</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>gants-cloutes</t>
+          <t>anneau-pierre</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Studded Gloves</t>
+          <t>Stone Ring</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -25041,18 +25041,18 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>450</v>
+        <v>390</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>torche</t>
+          <t>gants-cloutes</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Torch</t>
+          <t>Studded Gloves</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -25061,18 +25061,18 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>360</v>
+        <v>450</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>epee-entrainement</t>
+          <t>torche</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Training Sword</t>
+          <t>Torch</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -25081,18 +25081,18 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>350</v>
+        <v>360</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bottes-voyage</t>
+          <t>epee-entrainement</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Traveler Boots</t>
+          <t>Training Sword</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -25101,18 +25101,18 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>430</v>
+        <v>350</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>tenue-de-voyageur</t>
+          <t>bottes-voyage</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Traveler's Garb</t>
+          <t>Traveler Boots</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -25121,18 +25121,18 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>370</v>
+        <v>430</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>anneau-venin</t>
+          <t>tenue-de-voyageur</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Venom Ring</t>
+          <t>Traveler's Garb</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -25141,18 +25141,18 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>330</v>
+        <v>370</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>anneau-vigueur</t>
+          <t>anneau-venin</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Vigor Ring</t>
+          <t>Venom Ring</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -25161,18 +25161,18 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>460</v>
+        <v>330</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>gourdin</t>
+          <t>anneau-vigueur</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Wooden Club</t>
+          <t>Vigor Ring</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -25181,18 +25181,18 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>420</v>
+        <v>460</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bouclier-bois</t>
+          <t>gourdin</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Wooden Shield</t>
+          <t>Wooden Club</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -25201,18 +25201,18 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>400</v>
+        <v>420</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>gants-travail</t>
+          <t>bouclier-bois</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Work Gloves</t>
+          <t>Wooden Shield</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -25221,18 +25221,18 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>370</v>
+        <v>400</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bottes-usees</t>
+          <t>gants-travail</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Worn Boots</t>
+          <t>Work Gloves</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -25241,38 +25241,38 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>480</v>
+        <v>370</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>collier-concentration</t>
+          <t>bottes-usees</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Amulet of Focus</t>
+          <t>Worn Boots</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>2000</v>
+        <v>480</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>plaque-de-fer</t>
+          <t>collier-concentration</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Basic Iron Plate</t>
+          <t>Amulet of Focus</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -25281,18 +25281,18 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1700</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>hache-berserk</t>
+          <t>plaque-de-fer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Berserker Axe</t>
+          <t>Basic Iron Plate</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -25301,18 +25301,18 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1900</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>peau-berserk</t>
+          <t>hache-berserk</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Berserker Hide</t>
+          <t>Berserker Axe</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -25321,18 +25321,18 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1800</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>grand-sac-en-cuir</t>
+          <t>peau-berserk</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Big Leather Pouch</t>
+          <t>Berserker Hide</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -25341,18 +25341,18 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>2100</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>bague-de-sang</t>
+          <t>grand-sac-en-cuir</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Blood Ring</t>
+          <t>Big Leather Pouch</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -25361,18 +25361,18 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1700</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>anneau-soif-sang</t>
+          <t>bague-de-sang</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Bloodthirst Ring</t>
+          <t>Blood Ring</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -25381,18 +25381,18 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>2100</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>epee-large</t>
+          <t>anneau-soif-sang</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Claymore</t>
+          <t>Bloodthirst Ring</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -25401,18 +25401,18 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1700</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>baguette-cristal</t>
+          <t>epee-large</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Crystal Wand</t>
+          <t>Claymore</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -25421,18 +25421,18 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>2300</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>bottes-braise</t>
+          <t>baguette-cristal</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Ember Striders</t>
+          <t>Crystal Wand</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -25441,18 +25441,18 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>2100</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>lame-de-braise</t>
+          <t>bottes-braise</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Emberblade</t>
+          <t>Ember Striders</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -25461,18 +25461,18 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1900</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>pendentif-energie</t>
+          <t>lame-de-braise</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Energizing Pendant</t>
+          <t>Emberblade</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -25481,18 +25481,18 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>2300</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>lame-bourreau</t>
+          <t>pendentif-energie</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Executioner's Blade</t>
+          <t>Energizing Pendant</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -25507,12 +25507,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>marteau-de-forge</t>
+          <t>lame-bourreau</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Forge Hammer</t>
+          <t>Executioner's Blade</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -25521,18 +25521,18 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1900</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>anneau-forge</t>
+          <t>marteau-de-forge</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Forge Ring</t>
+          <t>Forge Hammer</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -25541,18 +25541,18 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>2200</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>anneau-de-givre</t>
+          <t>anneau-forge</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Frost Ring</t>
+          <t>Forge Ring</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -25561,18 +25561,18 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>2100</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>sceau-givre</t>
+          <t>anneau-de-givre</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Frost Signet</t>
+          <t>Frost Ring</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -25581,18 +25581,18 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1900</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>lame-de-givre</t>
+          <t>sceau-givre</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Frostbrand</t>
+          <t>Frost Signet</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -25601,18 +25601,18 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>2300</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>gantelets</t>
+          <t>lame-de-givre</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Gauntlets</t>
+          <t>Frostbrand</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -25621,18 +25621,18 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>2200</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>grimoire-flammes</t>
+          <t>gantelets</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Grimoire of Flames</t>
+          <t>Gauntlets</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -25647,12 +25647,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>hallebarde</t>
+          <t>grimoire-flammes</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Halberd</t>
+          <t>Grimoire of Flames</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -25667,12 +25667,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>epee-sacree</t>
+          <t>hallebarde</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Holy Sword</t>
+          <t>Halberd</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -25681,18 +25681,18 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>2000</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>anneau-de-fer</t>
+          <t>epee-sacree</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Iron Ring</t>
+          <t>Holy Sword</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -25707,12 +25707,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>gants-chance</t>
+          <t>anneau-de-fer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Lucky Glove</t>
+          <t>Iron Ring</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -25727,12 +25727,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>hache-faucheuse</t>
+          <t>gants-chance</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Reaver Axe</t>
+          <t>Lucky Glove</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -25741,18 +25741,18 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>bouclier-renforce</t>
+          <t>hache-faucheuse</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Reinforced Shield</t>
+          <t>Reaver Axe</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -25761,18 +25761,18 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>2400</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>anneau-puissance</t>
+          <t>pioche-fer-renforcee</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Ring of Might</t>
+          <t>Reinforced Iron Pickaxe</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -25781,18 +25781,18 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>2300</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>collier-de-saphir</t>
+          <t>bouclier-renforce</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Sapphire Amulet</t>
+          <t>Reinforced Shield</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -25801,18 +25801,18 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1700</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>sceptre-commandement</t>
+          <t>anneau-puissance</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Scepter of Command</t>
+          <t>Ring of Might</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -25821,18 +25821,18 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1800</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>armure-cloutee</t>
+          <t>collier-de-saphir</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Spiked Armor</t>
+          <t>Sapphire Amulet</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -25841,18 +25841,18 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1900</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>fleau-cloute</t>
+          <t>sceptre-commandement</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Spiked Flail</t>
+          <t>Scepter of Command</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -25861,18 +25861,18 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>2200</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>armure-stone-age</t>
+          <t>armure-cloutee</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Stone Armor</t>
+          <t>Spiked Armor</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -25881,18 +25881,18 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1600</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>bottes-stone-age</t>
+          <t>fleau-cloute</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Stone Boots</t>
+          <t>Spiked Flail</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -25901,18 +25901,18 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1800</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>gants-stone-age</t>
+          <t>armure-stone-age</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Stone Glove</t>
+          <t>Stone Armor</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -25921,18 +25921,18 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>2100</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>marteau-de-pierre</t>
+          <t>bottes-stone-age</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Stone Hammer</t>
+          <t>Stone Boots</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -25941,18 +25941,18 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>2200</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>bottes-pierre</t>
+          <t>gants-stone-age</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Stonetread Boots</t>
+          <t>Stone Glove</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -25967,12 +25967,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>bottes-vives</t>
+          <t>marteau-de-pierre</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Swift Boots</t>
+          <t>Stone Hammer</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -25981,18 +25981,18 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>2400</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>bottes-rapides</t>
+          <t>bottes-pierre</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Swift Striders</t>
+          <t>Stonetread Boots</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -26001,18 +26001,18 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1900</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>gants-voleur</t>
+          <t>bottes-vives</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Thief's Gloves</t>
+          <t>Swift Boots</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -26021,18 +26021,18 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>2200</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>grimoire-puissance</t>
+          <t>bottes-rapides</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Tome of Power</t>
+          <t>Swift Striders</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -26041,18 +26041,18 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>2100</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>anneau-toxique</t>
+          <t>gants-voleur</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Toxic Ring</t>
+          <t>Thief's Gloves</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -26061,18 +26061,18 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1900</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>dagues-jumelles</t>
+          <t>grimoire-puissance</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Twin Daggers</t>
+          <t>Tome of Power</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -26081,18 +26081,18 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>2300</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>pendentif-vampire</t>
+          <t>anneau-toxique</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Vampiric Pendant</t>
+          <t>Toxic Ring</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -26101,18 +26101,18 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>2100</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>gants-venin</t>
+          <t>dagues-jumelles</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Venom Gloves</t>
+          <t>Twin Daggers</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -26121,18 +26121,18 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1900</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>dague-venin</t>
+          <t>pendentif-vampire</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Venomfang Dagger</t>
+          <t>Vampiric Pendant</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -26141,18 +26141,18 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>2200</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>bouclier-protecteur</t>
+          <t>gants-venin</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Warding Shield</t>
+          <t>Venom Gloves</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -26161,18 +26161,18 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>2200</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>marteau-guerre</t>
+          <t>dague-venin</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Warhammer</t>
+          <t>Venomfang Dagger</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -26181,58 +26181,58 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>2300</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>chevaliere-ancienne</t>
+          <t>bouclier-protecteur</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Ancient Signet</t>
+          <t>Warding Shield</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>12000</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>sac-a-dos</t>
+          <t>marteau-guerre</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Backpack</t>
+          <t>Warhammer</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>10000</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>bottes-barbare</t>
+          <t>chevaliere-ancienne</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Barbarian Boots</t>
+          <t>Ancient Signet</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -26241,18 +26241,18 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>10100</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>brassards-barbare</t>
+          <t>sac-a-dos</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Barbarian Bracers</t>
+          <t>Backpack</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -26261,18 +26261,18 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>9800</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>plastron-barbare</t>
+          <t>bottes-barbare</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Barbarian Harness</t>
+          <t>Barbarian Boots</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -26281,18 +26281,18 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>10400</v>
+        <v>10100</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>croc-de-basilic</t>
+          <t>brassards-barbare</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Basilisk Fang</t>
+          <t>Barbarian Bracers</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -26301,18 +26301,18 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>9000</v>
+        <v>9800</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>gants-sang</t>
+          <t>plastron-barbare</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Blood Gauntlets</t>
+          <t>Barbarian Harness</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -26321,18 +26321,18 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>9200</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>bottes-sang</t>
+          <t>croc-de-basilic</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Blood Greaves</t>
+          <t>Basilisk Fang</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -26341,18 +26341,18 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>10000</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>plate-sang</t>
+          <t>gants-sang</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Blood Plate</t>
+          <t>Blood Gauntlets</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -26361,18 +26361,18 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11000</v>
+        <v>9200</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>gants-croise</t>
+          <t>bottes-sang</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Crusader Gauntlets</t>
+          <t>Blood Greaves</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -26381,18 +26381,18 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>8400</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>bottes-croise</t>
+          <t>plate-sang</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Crusader Greaves</t>
+          <t>Blood Plate</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -26401,18 +26401,18 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>9900</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>plate-croise</t>
+          <t>gants-croise</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Crusader Plate</t>
+          <t>Crusader Gauntlets</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -26421,18 +26421,18 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>10000</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>calice-cristal</t>
+          <t>bottes-croise</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Crystal Chalice</t>
+          <t>Crusader Greaves</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -26447,12 +26447,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>remede-vieillesse</t>
+          <t>plate-croise</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Elixir of Youth</t>
+          <t>Crusader Plate</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -26461,18 +26461,18 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>10500</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>caillou-flottant</t>
+          <t>calice-cristal</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Floating Pebble</t>
+          <t>Crystal Chalice</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -26481,18 +26481,18 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>11000</v>
+        <v>9900</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>maille-de-forge</t>
+          <t>remede-vieillesse</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Forgemaster's Mail</t>
+          <t>Elixir of Youth</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -26501,18 +26501,18 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>8100</v>
+        <v>10500</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>idole-doree</t>
+          <t>caillou-flottant</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Gilded Idol</t>
+          <t>Floating Pebble</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -26521,18 +26521,18 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>10000</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>enorme-sac-en-cuir</t>
+          <t>maille-de-forge</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Huge Leather Pouch</t>
+          <t>Forgemaster's Mail</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -26541,18 +26541,18 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>9400</v>
+        <v>8100</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>bottes-de-maille</t>
+          <t>idole-doree</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Mail Boots</t>
+          <t>Gilded Idol</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -26561,18 +26561,18 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>8900</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>gants-de-maille</t>
+          <t>enorme-sac-en-cuir</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Mail Glove</t>
+          <t>Huge Leather Pouch</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -26581,18 +26581,18 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>9000</v>
+        <v>9400</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>collier-de-saphir-fin</t>
+          <t>bottes-de-maille</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Nice Sapphire Amulet</t>
+          <t>Mail Boots</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -26601,18 +26601,18 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>8600</v>
+        <v>8900</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>anneau-de-givre-parfait</t>
+          <t>gants-de-maille</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Perfect Frost Ring</t>
+          <t>Mail Glove</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -26621,18 +26621,18 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>8300</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ring-of-luck</t>
+          <t>collier-de-saphir-fin</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Ring of Luck</t>
+          <t>Nice Sapphire Amulet</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -26641,18 +26641,18 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>11000</v>
+        <v>8600</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>marteau-de-siege</t>
+          <t>anneau-de-givre-parfait</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Siege Maul</t>
+          <t>Perfect Frost Ring</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -26661,18 +26661,18 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>11000</v>
+        <v>8300</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>bouclier-tour</t>
+          <t>ring-of-luck</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Tower Shield</t>
+          <t>Ring of Luck</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -26681,18 +26681,18 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>9200</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>hache-de-guerre</t>
+          <t>marteau-de-siege</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>War Axe</t>
+          <t>Siege Maul</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -26701,78 +26701,78 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>8100</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>epee-onyx</t>
+          <t>pioche-titane</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Big Onyx Sword</t>
+          <t>Titanium Pickaxe</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>64000</v>
+        <v>10500</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>sac-sans-fond</t>
+          <t>bouclier-tour</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Bottomless Bag</t>
+          <t>Tower Shield</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>94000</v>
+        <v>9200</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>gantelets-dunir</t>
+          <t>hache-de-guerre</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Dunir's Blessed Gauntlets</t>
+          <t>War Axe</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>79000</v>
+        <v>8100</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>plastron-dunir</t>
+          <t>epee-onyx</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Dunir's Blessed Plate</t>
+          <t>Big Onyx Sword</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -26781,18 +26781,18 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>83000</v>
+        <v>64000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>solerets-dunir</t>
+          <t>sac-sans-fond</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Dunir's Blessed Sabatons</t>
+          <t>Bottomless Bag</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -26801,18 +26801,18 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>80500</v>
+        <v>94000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>grande-faux</t>
+          <t>pioche-diamant</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Great Scythe</t>
+          <t>Diamond Pickaxe</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -26821,18 +26821,18 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>88000</v>
+        <v>82000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>marteau-de-lave</t>
+          <t>gantelets-dunir</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Magma Hammer</t>
+          <t>Dunir's Blessed Gauntlets</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -26841,18 +26841,18 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>80000</v>
+        <v>79000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>bottes-onyx</t>
+          <t>plastron-dunir</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Onyx Boots</t>
+          <t>Dunir's Blessed Plate</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -26861,18 +26861,18 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>70000</v>
+        <v>83000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>gants-onyx</t>
+          <t>solerets-dunir</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Onyx Glove</t>
+          <t>Dunir's Blessed Sabatons</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -26881,18 +26881,18 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>82000</v>
+        <v>80500</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>plate-onyx</t>
+          <t>grande-faux</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Onyx Guard Plate</t>
+          <t>Great Scythe</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -26901,18 +26901,18 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>65000</v>
+        <v>88000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>collier-de-saphir-parfait</t>
+          <t>marteau-de-lave</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Perfect Sapphire Amulet</t>
+          <t>Magma Hammer</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -26921,26 +26921,126 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>84000</v>
+        <v>80000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
+          <t>bottes-onyx</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Onyx Boots</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>gants-onyx</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Onyx Glove</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>82000</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>plate-onyx</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Onyx Guard Plate</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>65000</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>pioche-onyx</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Onyx Pickaxe</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>88000</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>collier-de-saphir-parfait</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Perfect Sapphire Amulet</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>84000</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
           <t>sac-maitre-mineur</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr">
+      <c r="B148" t="inlineStr">
         <is>
           <t>Master Miner's Bag</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr">
+      <c r="C148" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="D143" t="n">
+      <c r="D148" t="n">
         <v>290000</v>
       </c>
     </row>
@@ -27422,7 +27522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F589"/>
+  <dimension ref="A1:F619"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="140" min="1" max="1"/>
@@ -27765,6 +27865,7 @@
       </c>
       <c r="D18" s="77" t="n"/>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="75" t="inlineStr">
         <is>
@@ -27824,6 +27925,7 @@
         </is>
       </c>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="75" t="inlineStr">
         <is>
@@ -27887,6 +27989,7 @@
       </c>
       <c r="D29" s="77" t="n"/>
     </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="75" t="inlineStr">
         <is>
@@ -27946,6 +28049,7 @@
         </is>
       </c>
     </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" s="75" t="inlineStr">
         <is>
@@ -28008,6 +28112,7 @@
       </c>
       <c r="D39" s="77" t="n"/>
     </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" s="75" t="inlineStr">
         <is>
@@ -28056,6 +28161,7 @@
         </is>
       </c>
     </row>
+    <row r="45"/>
     <row r="46">
       <c r="A46" s="75" t="inlineStr">
         <is>
@@ -28107,6 +28213,7 @@
       </c>
       <c r="C49" s="77" t="n"/>
     </row>
+    <row r="50"/>
     <row r="51">
       <c r="A51" s="75" t="inlineStr">
         <is>
@@ -28160,6 +28267,7 @@
       </c>
       <c r="D53" s="77" t="n"/>
     </row>
+    <row r="54"/>
     <row r="55">
       <c r="A55" s="75" t="inlineStr">
         <is>
@@ -28208,6 +28316,7 @@
         </is>
       </c>
     </row>
+    <row r="59"/>
     <row r="60">
       <c r="A60" s="75" t="inlineStr">
         <is>
@@ -28267,6 +28376,7 @@
         </is>
       </c>
     </row>
+    <row r="64"/>
     <row r="65">
       <c r="A65" s="75" t="inlineStr">
         <is>
@@ -28326,6 +28436,7 @@
         </is>
       </c>
     </row>
+    <row r="69"/>
     <row r="70">
       <c r="A70" s="75" t="inlineStr">
         <is>
@@ -28388,6 +28499,7 @@
       </c>
       <c r="D73" s="77" t="n"/>
     </row>
+    <row r="74"/>
     <row r="75">
       <c r="A75" s="75" t="inlineStr">
         <is>
@@ -28443,6 +28555,7 @@
         </is>
       </c>
     </row>
+    <row r="80"/>
     <row r="81">
       <c r="A81" s="75" t="inlineStr">
         <is>
@@ -28505,6 +28618,7 @@
       </c>
       <c r="D84" s="77" t="n"/>
     </row>
+    <row r="85"/>
     <row r="86">
       <c r="A86" s="75" t="inlineStr">
         <is>
@@ -28572,6 +28686,7 @@
         </is>
       </c>
     </row>
+    <row r="91"/>
     <row r="92">
       <c r="A92" s="75" t="inlineStr">
         <is>
@@ -28634,6 +28749,7 @@
       </c>
       <c r="D95" s="77" t="n"/>
     </row>
+    <row r="96"/>
     <row r="97">
       <c r="A97" s="75" t="inlineStr">
         <is>
@@ -28704,6 +28820,7 @@
       </c>
       <c r="D100" s="77" t="n"/>
     </row>
+    <row r="101"/>
     <row r="102">
       <c r="A102" s="75" t="inlineStr">
         <is>
@@ -28784,6 +28901,7 @@
       </c>
       <c r="D107" s="77" t="n"/>
     </row>
+    <row r="108"/>
     <row r="109">
       <c r="A109" s="75" t="inlineStr">
         <is>
@@ -28864,6 +28982,7 @@
       </c>
       <c r="D114" s="77" t="n"/>
     </row>
+    <row r="115"/>
     <row r="116">
       <c r="A116" s="75" t="inlineStr">
         <is>
@@ -28919,6 +29038,7 @@
         </is>
       </c>
     </row>
+    <row r="121"/>
     <row r="122">
       <c r="A122" s="75" t="inlineStr">
         <is>
@@ -28990,6 +29110,7 @@
       </c>
       <c r="D126" s="77" t="n"/>
     </row>
+    <row r="127"/>
     <row r="128">
       <c r="A128" s="75" t="inlineStr">
         <is>
@@ -29057,6 +29178,7 @@
       </c>
       <c r="D132" s="77" t="n"/>
     </row>
+    <row r="133"/>
     <row r="134">
       <c r="A134" s="75" t="inlineStr">
         <is>
@@ -29123,6 +29245,7 @@
       </c>
       <c r="D137" s="77" t="n"/>
     </row>
+    <row r="138"/>
     <row r="139">
       <c r="A139" s="75" t="inlineStr">
         <is>
@@ -29198,6 +29321,7 @@
       </c>
       <c r="D143" s="77" t="n"/>
     </row>
+    <row r="144"/>
     <row r="145">
       <c r="A145" s="75" t="inlineStr">
         <is>
@@ -29268,6 +29392,7 @@
       </c>
       <c r="D148" s="77" t="n"/>
     </row>
+    <row r="149"/>
     <row r="150">
       <c r="A150" s="75" t="inlineStr">
         <is>
@@ -29334,6 +29459,7 @@
         </is>
       </c>
     </row>
+    <row r="154"/>
     <row r="155">
       <c r="A155" s="75" t="inlineStr">
         <is>
@@ -29405,6 +29531,7 @@
       </c>
       <c r="D159" s="77" t="n"/>
     </row>
+    <row r="160"/>
     <row r="161">
       <c r="A161" s="75" t="inlineStr">
         <is>
@@ -29460,6 +29587,7 @@
         </is>
       </c>
     </row>
+    <row r="165"/>
     <row r="166">
       <c r="A166" s="75" t="inlineStr">
         <is>
@@ -29527,6 +29655,7 @@
         </is>
       </c>
     </row>
+    <row r="171"/>
     <row r="172">
       <c r="A172" s="75" t="inlineStr">
         <is>
@@ -29597,6 +29726,7 @@
       </c>
       <c r="D175" s="77" t="n"/>
     </row>
+    <row r="176"/>
     <row r="177">
       <c r="A177" s="75" t="inlineStr">
         <is>
@@ -29668,6 +29798,7 @@
       </c>
       <c r="D181" s="77" t="n"/>
     </row>
+    <row r="182"/>
     <row r="183">
       <c r="A183" s="75" t="inlineStr">
         <is>
@@ -29731,6 +29862,7 @@
         </is>
       </c>
     </row>
+    <row r="188"/>
     <row r="189">
       <c r="A189" s="75" t="inlineStr">
         <is>
@@ -29819,6 +29951,7 @@
       </c>
       <c r="D194" s="77" t="n"/>
     </row>
+    <row r="195"/>
     <row r="196">
       <c r="A196" s="75" t="inlineStr">
         <is>
@@ -29898,6 +30031,7 @@
       </c>
       <c r="D200" s="77" t="n"/>
     </row>
+    <row r="201"/>
     <row r="202">
       <c r="A202" s="75" t="inlineStr">
         <is>
@@ -29968,6 +30102,7 @@
       </c>
       <c r="D205" s="77" t="n"/>
     </row>
+    <row r="206"/>
     <row r="207">
       <c r="A207" s="75" t="inlineStr">
         <is>
@@ -30048,6 +30183,7 @@
       </c>
       <c r="D212" s="77" t="n"/>
     </row>
+    <row r="213"/>
     <row r="214">
       <c r="A214" s="75" t="inlineStr">
         <is>
@@ -30128,6 +30264,7 @@
       <c r="C219" s="77" t="n"/>
       <c r="D219" s="77" t="n"/>
     </row>
+    <row r="220"/>
     <row r="221">
       <c r="A221" s="75" t="inlineStr">
         <is>
@@ -30189,6 +30326,7 @@
         </is>
       </c>
     </row>
+    <row r="224"/>
     <row r="225">
       <c r="A225" s="75" t="inlineStr">
         <is>
@@ -30250,6 +30388,7 @@
         </is>
       </c>
     </row>
+    <row r="228"/>
     <row r="229">
       <c r="A229" s="75" t="inlineStr">
         <is>
@@ -30311,6 +30450,7 @@
         </is>
       </c>
     </row>
+    <row r="232"/>
     <row r="233">
       <c r="A233" s="75" t="inlineStr">
         <is>
@@ -30372,6 +30512,7 @@
         </is>
       </c>
     </row>
+    <row r="236"/>
     <row r="237">
       <c r="A237" s="75" t="inlineStr">
         <is>
@@ -30433,6 +30574,7 @@
         </is>
       </c>
     </row>
+    <row r="240"/>
     <row r="241">
       <c r="A241" s="75" t="inlineStr">
         <is>
@@ -30511,6 +30653,7 @@
         </is>
       </c>
     </row>
+    <row r="245"/>
     <row r="246">
       <c r="A246" s="75" t="inlineStr">
         <is>
@@ -30589,6 +30732,7 @@
         </is>
       </c>
     </row>
+    <row r="250"/>
     <row r="251">
       <c r="A251" s="75" t="inlineStr">
         <is>
@@ -30650,6 +30794,7 @@
         </is>
       </c>
     </row>
+    <row r="254"/>
     <row r="255">
       <c r="A255" s="75" t="inlineStr">
         <is>
@@ -30711,6 +30856,7 @@
         </is>
       </c>
     </row>
+    <row r="258"/>
     <row r="259">
       <c r="A259" s="75" t="inlineStr">
         <is>
@@ -30789,6 +30935,7 @@
         </is>
       </c>
     </row>
+    <row r="263"/>
     <row r="264">
       <c r="A264" s="75" t="inlineStr">
         <is>
@@ -30867,6 +31014,7 @@
         </is>
       </c>
     </row>
+    <row r="268"/>
     <row r="269">
       <c r="A269" s="75" t="inlineStr">
         <is>
@@ -30945,6 +31093,7 @@
         </is>
       </c>
     </row>
+    <row r="273"/>
     <row r="274">
       <c r="A274" s="75" t="inlineStr">
         <is>
@@ -31023,6 +31172,7 @@
         </is>
       </c>
     </row>
+    <row r="278"/>
     <row r="279">
       <c r="A279" s="75" t="inlineStr">
         <is>
@@ -31145,6 +31295,7 @@
         </is>
       </c>
     </row>
+    <row r="285"/>
     <row r="286">
       <c r="A286" s="75" t="inlineStr">
         <is>
@@ -31267,6 +31418,7 @@
         </is>
       </c>
     </row>
+    <row r="292"/>
     <row r="293">
       <c r="A293" s="75" t="inlineStr">
         <is>
@@ -31314,6 +31466,7 @@
         </is>
       </c>
     </row>
+    <row r="296"/>
     <row r="297">
       <c r="A297" s="75" t="inlineStr">
         <is>
@@ -31369,6 +31522,7 @@
         </is>
       </c>
     </row>
+    <row r="301"/>
     <row r="302">
       <c r="A302" s="75" t="inlineStr">
         <is>
@@ -31416,6 +31570,7 @@
         </is>
       </c>
     </row>
+    <row r="305"/>
     <row r="306">
       <c r="A306" s="75" t="inlineStr">
         <is>
@@ -31455,6 +31610,7 @@
         </is>
       </c>
     </row>
+    <row r="308"/>
     <row r="309">
       <c r="A309" s="75" t="inlineStr">
         <is>
@@ -31502,6 +31658,7 @@
         </is>
       </c>
     </row>
+    <row r="312"/>
     <row r="313">
       <c r="A313" s="75" t="inlineStr">
         <is>
@@ -31549,6 +31706,7 @@
         </is>
       </c>
     </row>
+    <row r="316"/>
     <row r="317">
       <c r="A317" s="75" t="inlineStr">
         <is>
@@ -31596,6 +31754,7 @@
         </is>
       </c>
     </row>
+    <row r="320"/>
     <row r="321">
       <c r="A321" s="75" t="inlineStr">
         <is>
@@ -31643,6 +31802,7 @@
       </c>
       <c r="C323" s="77" t="n"/>
     </row>
+    <row r="324"/>
     <row r="325">
       <c r="A325" s="75" t="inlineStr">
         <is>
@@ -31690,6 +31850,7 @@
       </c>
       <c r="C327" s="77" t="n"/>
     </row>
+    <row r="328"/>
     <row r="329">
       <c r="A329" s="75" t="inlineStr">
         <is>
@@ -31745,6 +31906,7 @@
       </c>
       <c r="C332" s="77" t="n"/>
     </row>
+    <row r="333"/>
     <row r="334">
       <c r="A334" s="75" t="inlineStr">
         <is>
@@ -31800,6 +31962,7 @@
       </c>
       <c r="C337" s="77" t="n"/>
     </row>
+    <row r="338"/>
     <row r="339">
       <c r="A339" s="75" t="inlineStr">
         <is>
@@ -31855,6 +32018,7 @@
       </c>
       <c r="C342" s="77" t="n"/>
     </row>
+    <row r="343"/>
     <row r="344">
       <c r="A344" s="75" t="inlineStr">
         <is>
@@ -31910,6 +32074,7 @@
       </c>
       <c r="C347" s="77" t="n"/>
     </row>
+    <row r="348"/>
     <row r="349">
       <c r="A349" s="75" t="inlineStr">
         <is>
@@ -31999,6 +32164,7 @@
         </is>
       </c>
     </row>
+    <row r="353"/>
     <row r="354">
       <c r="A354" s="75" t="inlineStr">
         <is>
@@ -32088,6 +32254,7 @@
         </is>
       </c>
     </row>
+    <row r="358"/>
     <row r="359">
       <c r="A359" s="75" t="inlineStr">
         <is>
@@ -32135,6 +32302,7 @@
         </is>
       </c>
     </row>
+    <row r="362"/>
     <row r="363">
       <c r="A363" s="75" t="inlineStr">
         <is>
@@ -32182,6 +32350,7 @@
       </c>
       <c r="C365" s="77" t="n"/>
     </row>
+    <row r="366"/>
     <row r="367">
       <c r="A367" s="75" t="inlineStr">
         <is>
@@ -32229,6 +32398,7 @@
         </is>
       </c>
     </row>
+    <row r="370"/>
     <row r="371">
       <c r="A371" s="75" t="inlineStr">
         <is>
@@ -32276,6 +32446,7 @@
       </c>
       <c r="C373" s="77" t="n"/>
     </row>
+    <row r="374"/>
     <row r="375">
       <c r="A375" s="75" t="inlineStr">
         <is>
@@ -32323,6 +32494,7 @@
         </is>
       </c>
     </row>
+    <row r="378"/>
     <row r="379">
       <c r="A379" s="75" t="inlineStr">
         <is>
@@ -32370,6 +32542,7 @@
       </c>
       <c r="C381" s="77" t="n"/>
     </row>
+    <row r="382"/>
     <row r="383">
       <c r="A383" s="75" t="inlineStr">
         <is>
@@ -32421,6 +32594,7 @@
         </is>
       </c>
     </row>
+    <row r="386"/>
     <row r="387">
       <c r="A387" s="75" t="inlineStr">
         <is>
@@ -32468,6 +32642,7 @@
       </c>
       <c r="C389" s="77" t="n"/>
     </row>
+    <row r="390"/>
     <row r="391">
       <c r="A391" s="75" t="inlineStr">
         <is>
@@ -32519,6 +32694,7 @@
         </is>
       </c>
     </row>
+    <row r="394"/>
     <row r="395">
       <c r="A395" s="75" t="inlineStr">
         <is>
@@ -32566,6 +32742,7 @@
         </is>
       </c>
     </row>
+    <row r="398"/>
     <row r="399">
       <c r="A399" s="75" t="inlineStr">
         <is>
@@ -32613,6 +32790,7 @@
       </c>
       <c r="C401" s="77" t="n"/>
     </row>
+    <row r="402"/>
     <row r="403">
       <c r="A403" s="75" t="inlineStr">
         <is>
@@ -32664,6 +32842,7 @@
         </is>
       </c>
     </row>
+    <row r="406"/>
     <row r="407">
       <c r="A407" s="75" t="inlineStr">
         <is>
@@ -32715,6 +32894,7 @@
         </is>
       </c>
     </row>
+    <row r="410"/>
     <row r="411">
       <c r="A411" s="75" t="inlineStr">
         <is>
@@ -32762,6 +32942,7 @@
       </c>
       <c r="C413" s="77" t="n"/>
     </row>
+    <row r="414"/>
     <row r="415">
       <c r="A415" s="75" t="inlineStr">
         <is>
@@ -32842,6 +33023,7 @@
         </is>
       </c>
     </row>
+    <row r="419"/>
     <row r="420">
       <c r="A420" s="75" t="inlineStr">
         <is>
@@ -32927,6 +33109,7 @@
         </is>
       </c>
     </row>
+    <row r="424"/>
     <row r="425">
       <c r="A425" s="75" t="inlineStr">
         <is>
@@ -32966,6 +33149,7 @@
         </is>
       </c>
     </row>
+    <row r="427"/>
     <row r="428">
       <c r="A428" s="75" t="inlineStr">
         <is>
@@ -33005,6 +33189,7 @@
         </is>
       </c>
     </row>
+    <row r="430"/>
     <row r="431">
       <c r="A431" s="75" t="inlineStr">
         <is>
@@ -33046,6 +33231,7 @@
         </is>
       </c>
     </row>
+    <row r="434"/>
     <row r="435">
       <c r="A435" s="75" t="inlineStr">
         <is>
@@ -33087,6 +33273,7 @@
         </is>
       </c>
     </row>
+    <row r="438"/>
     <row r="439">
       <c r="A439" s="75" t="inlineStr">
         <is>
@@ -33126,6 +33313,7 @@
         </is>
       </c>
     </row>
+    <row r="441"/>
     <row r="442">
       <c r="A442" s="75" t="inlineStr">
         <is>
@@ -33165,6 +33353,7 @@
         </is>
       </c>
     </row>
+    <row r="444"/>
     <row r="445">
       <c r="A445" s="75" t="inlineStr">
         <is>
@@ -33204,6 +33393,7 @@
         </is>
       </c>
     </row>
+    <row r="447"/>
     <row r="448">
       <c r="A448" s="75" t="inlineStr">
         <is>
@@ -33245,6 +33435,7 @@
         </is>
       </c>
     </row>
+    <row r="451"/>
     <row r="452">
       <c r="A452" s="75" t="inlineStr">
         <is>
@@ -33284,6 +33475,7 @@
         </is>
       </c>
     </row>
+    <row r="454"/>
     <row r="455">
       <c r="A455" s="75" t="inlineStr">
         <is>
@@ -33331,6 +33523,7 @@
       </c>
       <c r="C457" s="77" t="n"/>
     </row>
+    <row r="458"/>
     <row r="459">
       <c r="A459" s="75" t="inlineStr">
         <is>
@@ -33378,6 +33571,7 @@
       </c>
       <c r="C461" s="77" t="n"/>
     </row>
+    <row r="462"/>
     <row r="463">
       <c r="A463" s="75" t="inlineStr">
         <is>
@@ -33426,6 +33620,7 @@
         </is>
       </c>
     </row>
+    <row r="467"/>
     <row r="468">
       <c r="A468" s="75" t="inlineStr">
         <is>
@@ -33474,6 +33669,7 @@
         </is>
       </c>
     </row>
+    <row r="472"/>
     <row r="473">
       <c r="A473" s="75" t="inlineStr">
         <is>
@@ -33521,6 +33717,7 @@
       </c>
       <c r="C475" s="77" t="n"/>
     </row>
+    <row r="476"/>
     <row r="477">
       <c r="A477" s="75" t="inlineStr">
         <is>
@@ -33568,6 +33765,7 @@
         </is>
       </c>
     </row>
+    <row r="480"/>
     <row r="481">
       <c r="A481" s="75" t="inlineStr">
         <is>
@@ -33615,6 +33813,7 @@
         </is>
       </c>
     </row>
+    <row r="484"/>
     <row r="485">
       <c r="A485" s="75" t="inlineStr">
         <is>
@@ -33662,6 +33861,7 @@
       </c>
       <c r="C487" s="77" t="n"/>
     </row>
+    <row r="488"/>
     <row r="489">
       <c r="A489" s="75" t="inlineStr">
         <is>
@@ -33713,6 +33913,7 @@
         </is>
       </c>
     </row>
+    <row r="492"/>
     <row r="493">
       <c r="A493" s="75" t="inlineStr">
         <is>
@@ -33766,6 +33967,7 @@
       </c>
       <c r="D495" s="77" t="n"/>
     </row>
+    <row r="496"/>
     <row r="497">
       <c r="A497" s="75" t="inlineStr">
         <is>
@@ -33813,6 +34015,7 @@
         </is>
       </c>
     </row>
+    <row r="500"/>
     <row r="501">
       <c r="A501" s="75" t="inlineStr">
         <is>
@@ -33860,6 +34063,7 @@
       </c>
       <c r="C503" s="77" t="n"/>
     </row>
+    <row r="504"/>
     <row r="505">
       <c r="A505" s="75" t="inlineStr">
         <is>
@@ -33908,6 +34112,7 @@
         </is>
       </c>
     </row>
+    <row r="509"/>
     <row r="510">
       <c r="A510" s="75" t="inlineStr">
         <is>
@@ -33952,6 +34157,7 @@
         </is>
       </c>
     </row>
+    <row r="512"/>
     <row r="513">
       <c r="A513" s="75" t="inlineStr">
         <is>
@@ -34005,6 +34211,7 @@
       </c>
       <c r="D515" s="77" t="n"/>
     </row>
+    <row r="516"/>
     <row r="517">
       <c r="A517" s="75" t="inlineStr">
         <is>
@@ -34052,6 +34259,7 @@
         </is>
       </c>
     </row>
+    <row r="520"/>
     <row r="521">
       <c r="A521" s="75" t="inlineStr">
         <is>
@@ -34100,6 +34308,7 @@
         </is>
       </c>
     </row>
+    <row r="525"/>
     <row r="526">
       <c r="A526" s="75" t="inlineStr">
         <is>
@@ -34144,6 +34353,7 @@
         </is>
       </c>
     </row>
+    <row r="528"/>
     <row r="529">
       <c r="A529" s="75" t="inlineStr">
         <is>
@@ -34188,6 +34398,7 @@
         </is>
       </c>
     </row>
+    <row r="531"/>
     <row r="532">
       <c r="A532" s="75" t="inlineStr">
         <is>
@@ -34241,6 +34452,7 @@
       </c>
       <c r="D534" s="77" t="n"/>
     </row>
+    <row r="535"/>
     <row r="536">
       <c r="A536" s="75" t="inlineStr">
         <is>
@@ -34304,6 +34516,7 @@
         </is>
       </c>
     </row>
+    <row r="540"/>
     <row r="541">
       <c r="A541" s="75" t="inlineStr">
         <is>
@@ -34355,6 +34568,7 @@
         </is>
       </c>
     </row>
+    <row r="544"/>
     <row r="545">
       <c r="A545" s="75" t="inlineStr">
         <is>
@@ -34406,6 +34620,7 @@
         </is>
       </c>
     </row>
+    <row r="548"/>
     <row r="549">
       <c r="A549" s="75" t="inlineStr">
         <is>
@@ -34454,6 +34669,7 @@
         </is>
       </c>
     </row>
+    <row r="553"/>
     <row r="554">
       <c r="A554" s="75" t="inlineStr">
         <is>
@@ -34502,6 +34718,7 @@
         </is>
       </c>
     </row>
+    <row r="558"/>
     <row r="559">
       <c r="A559" s="75" t="inlineStr">
         <is>
@@ -34553,6 +34770,7 @@
         </is>
       </c>
     </row>
+    <row r="562"/>
     <row r="563">
       <c r="A563" s="75" t="inlineStr">
         <is>
@@ -34616,6 +34834,7 @@
         </is>
       </c>
     </row>
+    <row r="567"/>
     <row r="568">
       <c r="A568" s="75" t="inlineStr">
         <is>
@@ -34667,6 +34886,7 @@
         </is>
       </c>
     </row>
+    <row r="571"/>
     <row r="572">
       <c r="A572" s="75" t="inlineStr">
         <is>
@@ -34715,6 +34935,7 @@
         </is>
       </c>
     </row>
+    <row r="576"/>
     <row r="577">
       <c r="A577" s="75" t="inlineStr">
         <is>
@@ -34778,6 +34999,7 @@
         </is>
       </c>
     </row>
+    <row r="581"/>
     <row r="582">
       <c r="A582" s="75" t="inlineStr">
         <is>
@@ -34829,6 +35051,7 @@
         </is>
       </c>
     </row>
+    <row r="585"/>
     <row r="586">
       <c r="A586" s="75" t="inlineStr">
         <is>
@@ -34889,6 +35112,408 @@
       <c r="C589" s="62" t="inlineStr">
         <is>
           <t>Ag</t>
+        </is>
+      </c>
+    </row>
+    <row r="590"/>
+    <row r="591">
+      <c r="A591" s="75" t="inlineStr">
+        <is>
+          <t>Pioche</t>
+        </is>
+      </c>
+      <c r="B591" s="75" t="inlineStr">
+        <is>
+          <t>vieille-pioche</t>
+        </is>
+      </c>
+      <c r="C591" s="76" t="inlineStr">
+        <is>
+          <t>Old Pickaxe</t>
+        </is>
+      </c>
+      <c r="D591" s="76" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="E591" s="76" t="inlineStr">
+        <is>
+          <t>tête usée, manche de bois</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="B592" s="67" t="inlineStr">
+        <is>
+          <t>St</t>
+        </is>
+      </c>
+      <c r="C592" s="67" t="inlineStr">
+        <is>
+          <t>St</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>St</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="B593" s="67" t="n"/>
+      <c r="C593" s="67" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="B594" s="67" t="n"/>
+      <c r="C594" s="67" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+    </row>
+    <row r="595"/>
+    <row r="596">
+      <c r="A596" s="75" t="inlineStr">
+        <is>
+          <t>Pioche</t>
+        </is>
+      </c>
+      <c r="B596" s="75" t="inlineStr">
+        <is>
+          <t>pioche-fer</t>
+        </is>
+      </c>
+      <c r="C596" s="76" t="inlineStr">
+        <is>
+          <t>Iron Pickaxe</t>
+        </is>
+      </c>
+      <c r="D596" s="76" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="E596" s="76" t="inlineStr">
+        <is>
+          <t>tête de fer, manche renforcé</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="B597" s="67" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="C597" s="67" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="B598" s="67" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="C598" s="67" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="B599" s="67" t="n"/>
+      <c r="C599" s="67" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="75" t="inlineStr">
+        <is>
+          <t>Pioche</t>
+        </is>
+      </c>
+      <c r="B601" s="75" t="inlineStr">
+        <is>
+          <t>pioche-fer-renforcee</t>
+        </is>
+      </c>
+      <c r="C601" s="76" t="inlineStr">
+        <is>
+          <t>Reinforced Iron Pickaxe</t>
+        </is>
+      </c>
+      <c r="D601" s="76" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="E601" s="76" t="inlineStr">
+        <is>
+          <t>fer trempé au charbon</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="B602" s="67" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="C602" s="67" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="B603" s="67" t="inlineStr">
+        <is>
+          <t>Co</t>
+        </is>
+      </c>
+      <c r="C603" s="67" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>Co</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="B604" s="67" t="n"/>
+      <c r="C604" s="67" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="75" t="inlineStr">
+        <is>
+          <t>Pioche</t>
+        </is>
+      </c>
+      <c r="B606" s="75" t="inlineStr">
+        <is>
+          <t>pioche-titane</t>
+        </is>
+      </c>
+      <c r="C606" s="76" t="inlineStr">
+        <is>
+          <t>Titanium Pickaxe</t>
+        </is>
+      </c>
+      <c r="D606" s="76" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="E606" s="76" t="inlineStr">
+        <is>
+          <t>titane, renforts d'argent</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="B607" s="67" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+      <c r="C607" s="67" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="B608" s="67" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="C608" s="67" t="inlineStr">
+        <is>
+          <t>Wd</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="B609" s="67" t="n"/>
+      <c r="C609" s="67" t="inlineStr">
+        <is>
+          <t>Ws</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="75" t="inlineStr">
+        <is>
+          <t>Pioche</t>
+        </is>
+      </c>
+      <c r="B611" s="75" t="inlineStr">
+        <is>
+          <t>pioche-diamant</t>
+        </is>
+      </c>
+      <c r="C611" s="76" t="inlineStr">
+        <is>
+          <t>Diamond Pickaxe</t>
+        </is>
+      </c>
+      <c r="D611" s="76" t="inlineStr">
+        <is>
+          <t>epique</t>
+        </is>
+      </c>
+      <c r="E611" s="76" t="inlineStr">
+        <is>
+          <t>pointes de diamant — creuse vite</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="B612" s="67" t="inlineStr">
+        <is>
+          <t>Di</t>
+        </is>
+      </c>
+      <c r="C612" s="67" t="inlineStr">
+        <is>
+          <t>Di</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>Di</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="B613" s="67" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+      <c r="C613" s="67" t="inlineStr">
+        <is>
+          <t>We</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="B614" s="67" t="n"/>
+      <c r="C614" s="67" t="inlineStr">
+        <is>
+          <t>We</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="75" t="inlineStr">
+        <is>
+          <t>Pioche</t>
+        </is>
+      </c>
+      <c r="B616" s="75" t="inlineStr">
+        <is>
+          <t>pioche-onyx</t>
+        </is>
+      </c>
+      <c r="C616" s="76" t="inlineStr">
+        <is>
+          <t>Onyx Pickaxe</t>
+        </is>
+      </c>
+      <c r="D616" s="76" t="inlineStr">
+        <is>
+          <t>epique</t>
+        </is>
+      </c>
+      <c r="E616" s="76" t="inlineStr">
+        <is>
+          <t>onyx et mithril — ramène le plus</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="B617" s="67" t="inlineStr">
+        <is>
+          <t>On</t>
+        </is>
+      </c>
+      <c r="C617" s="67" t="inlineStr">
+        <is>
+          <t>On</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>On</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="B618" s="67" t="inlineStr">
+        <is>
+          <t>Mi</t>
+        </is>
+      </c>
+      <c r="C618" s="67" t="inlineStr">
+        <is>
+          <t>We</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>Mi</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="B619" s="67" t="n"/>
+      <c r="C619" s="67" t="inlineStr">
+        <is>
+          <t>We</t>
         </is>
       </c>
     </row>

--- a/docs/BRUTAL-items-et-cartes.xlsx
+++ b/docs/BRUTAL-items-et-cartes.xlsx
@@ -10,22 +10,23 @@
     <sheet name="Lisez-moi" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Cartes" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Items" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Sets" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Effets" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Valeurs" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Ressources" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Recettes" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Profondeurs" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Profondeurs-chances" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Monstres" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Héros" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Général" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Pioches" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Sets" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Effets" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Valeurs" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Ressources" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Recettes" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Profondeurs" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Profondeurs-chances" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Monstres" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Héros" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Général" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Cartes'!$A$2:$L$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Items'!$A$1:$P$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Valeurs'!$A$6:$D$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Ressources'!$A$6:$D$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Valeurs'!$A$6:$D$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Ressources'!$A$6:$D$6</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -34,7 +35,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="28">
+  <fonts count="31">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -191,6 +192,20 @@
       <name val="Calibri"/>
       <family val="2"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFE0B64E"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <color rgb="FFB9C2CC"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF14121A"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="72">
@@ -831,7 +846,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="158">
+  <cellXfs count="161">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1154,6 +1169,9 @@
     <xf numFmtId="0" fontId="27" fillId="70" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="25" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2772,6 +2790,372 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" style="140" min="1" max="2"/>
+    <col width="12" customWidth="1" style="140" min="3" max="4"/>
+    <col width="10" customWidth="1" style="140" min="5" max="5"/>
+    <col width="8" customWidth="1" style="140" min="6" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="17.25" customHeight="1" s="140">
+      <c r="A1" s="91" t="inlineStr">
+        <is>
+          <t>LOOTS DE PROFONDEUR — buffs de « run » (SOURCE ÉDITABLE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>À chaque étage des profondeurs, on choisit UN loot parmi 2 (ou +). Les buffs s'accumulent</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>toute la descente et sont perdus en ressortant. Édite les valeurs, puis : python3 outils/importer_profondeur.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Effets reconnus : force (dégâts perm. en combat) · gold (or versé si on sort VIVANT) · celerite (% vitesse combat) · armure (armure au début du combat)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="92" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B6" s="92" t="inlineStr">
+        <is>
+          <t>Nom</t>
+        </is>
+      </c>
+      <c r="C6" s="92" t="inlineStr">
+        <is>
+          <t>Effet</t>
+        </is>
+      </c>
+      <c r="D6" s="92" t="inlineStr">
+        <is>
+          <t>Icône (hex)</t>
+        </is>
+      </c>
+      <c r="E6" s="92" t="inlineStr">
+        <is>
+          <t>Normale</t>
+        </is>
+      </c>
+      <c r="F6" s="92" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="G6" s="92" t="inlineStr">
+        <is>
+          <t>Épique</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>pierre-force</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Strength Stone</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>force</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>#d9542a</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>tresor-gold</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Gold Hoard</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>gold</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>#e0b64e</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100</v>
+      </c>
+      <c r="F8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G8" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>pierre-celerite</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Agility Stone</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>agilite</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>#5fb0e8</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Augmente l'agilité</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>plaque-renforcement</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Reinforcement Plate</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>armure</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>#9cd3ff</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" t="n">
+        <v>20</v>
+      </c>
+      <c r="G10" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>portail-profondeur</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Depth Portal</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>porte</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>#5fd08a</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>onde-tranquilite</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Wave of Calm</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>pop-monstre</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>#a8e0d0</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Si choisis il n'y a pas de pop de monstre a cette étage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>poussiere-rubis</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ruby Dust</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>soin</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>#e0555f</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>20</v>
+      </c>
+      <c r="F13" t="n">
+        <v>40</v>
+      </c>
+      <c r="G13" t="n">
+        <v>80</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Soigne d'autant de hp directement</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>pierre-chance</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Lucky Stone</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>chance-minerais</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>#7ed957</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" t="n">
+        <v>6</v>
+      </c>
+      <c r="G14" t="n">
+        <v>12</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Ca augmente le % de minerais a l'étage actuel.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
@@ -2833,7 +3217,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4707,7 +5091,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4863,7 +5247,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -22080,6 +22464,379 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" style="140" min="1" max="1"/>
+    <col width="26" customWidth="1" style="140" min="2" max="2"/>
+    <col width="12" customWidth="1" style="140" min="3" max="3"/>
+    <col width="19" customWidth="1" style="140" min="4" max="4"/>
+    <col width="16" customWidth="1" style="140" min="5" max="5"/>
+    <col width="20" customWidth="1" style="140" min="6" max="6"/>
+    <col width="42" customWidth="1" style="140" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="158" t="inlineStr">
+        <is>
+          <t>LES PIOCHES DE MINAGE — SOURCE ÉDITABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="159" t="inlineStr">
+        <is>
+          <t>Édite les colonnes Rareté / Vitesse / Efficacité, puis lance :  python3 outils/importer_pioches.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="159" t="inlineStr">
+        <is>
+          <t>VITESSE DE MINAGE (%) : 100 = référence. Plus c'est haut, plus la barre de minage va vite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="159" t="inlineStr">
+        <is>
+          <t>EFFICACITÉ (%) : chance de minerai SUPPLÉMENTAIRE par coup. 0 = toujours 1 seul minerai ·</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   100 = un 2e garanti · 150 = un 2e garanti et 50 % d'en avoir un 3e.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="159" t="inlineStr">
+        <is>
+          <t>RARETÉ : décide AUSSI de ce que la pioche peut casser — sa rareté et UNE au-dessus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   (une pioche commune s'arrête donc à l'uncommon). C'est la progression du mineur.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="159" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="160" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B9" s="160" t="inlineStr">
+        <is>
+          <t>Nom</t>
+        </is>
+      </c>
+      <c r="C9" s="160" t="inlineStr">
+        <is>
+          <t>Rareté</t>
+        </is>
+      </c>
+      <c r="D9" s="160" t="inlineStr">
+        <is>
+          <t>Vitesse minage (%)</t>
+        </is>
+      </c>
+      <c r="E9" s="160" t="inlineStr">
+        <is>
+          <t>Efficacité (%)</t>
+        </is>
+      </c>
+      <c r="F9" s="160" t="inlineStr">
+        <is>
+          <t>Mine jusqu'à (info)</t>
+        </is>
+      </c>
+      <c r="G9" s="160" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>vieille-pioche</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Old Pickaxe</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>80</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>commun + uncommon</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>l'outil de départ : lent, aucun bonus</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>pioche-fer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Iron Pickaxe</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>100</v>
+      </c>
+      <c r="E11" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>commun + uncommon</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>la première vraie pioche</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>pioche-fer-renforcee</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Reinforced Iron Pickaxe</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>125</v>
+      </c>
+      <c r="E12" t="n">
+        <v>30</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>+ rare</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ouvre les minerais rares</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>pioche-titane</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Titanium Pickaxe</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>155</v>
+      </c>
+      <c r="E13" t="n">
+        <v>60</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>+ épique</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ouvre les minerais épiques</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>pioche-diamant</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Diamond Pickaxe</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>epique</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>210</v>
+      </c>
+      <c r="E14" t="n">
+        <v>90</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>tout</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ÉPIQUE VITESSE : creuse le plus vite</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>pioche-onyx</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Onyx Pickaxe</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>epique</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>175</v>
+      </c>
+      <c r="E15" t="n">
+        <v>130</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>tout</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ÉPIQUE RENDEMENT : ramène le plus</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="158" t="inlineStr">
+        <is>
+          <t>BONUS DE FORGE D'UNE PIOCHE (réussir le mini-jeu)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="159" t="inlineStr">
+        <is>
+          <t>Sur une ARME la réussite donne de la Force ; sur une PIOCHE elle donne de l'EFFICACITÉ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="159" t="inlineStr">
+        <is>
+          <t>Valeurs plates, indépendantes de la rareté (data/recettes.js → EFFICACITE_QUALITE).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="160" t="inlineStr">
+        <is>
+          <t>Qualité obtenue</t>
+        </is>
+      </c>
+      <c r="B21" s="160" t="inlineStr">
+        <is>
+          <t>Bonus d'efficacité</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Artisan</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Maître (Master)</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Exceptionnel (Exceptional)</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
@@ -22284,7 +23041,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -24140,7 +24897,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -27050,7 +27807,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -27516,7 +28273,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -27865,7 +28622,6 @@
       </c>
       <c r="D18" s="77" t="n"/>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="A20" s="75" t="inlineStr">
         <is>
@@ -27925,7 +28681,6 @@
         </is>
       </c>
     </row>
-    <row r="24"/>
     <row r="25">
       <c r="A25" s="75" t="inlineStr">
         <is>
@@ -27989,7 +28744,6 @@
       </c>
       <c r="D29" s="77" t="n"/>
     </row>
-    <row r="30"/>
     <row r="31">
       <c r="A31" s="75" t="inlineStr">
         <is>
@@ -28049,7 +28803,6 @@
         </is>
       </c>
     </row>
-    <row r="35"/>
     <row r="36">
       <c r="A36" s="75" t="inlineStr">
         <is>
@@ -28112,7 +28865,6 @@
       </c>
       <c r="D39" s="77" t="n"/>
     </row>
-    <row r="40"/>
     <row r="41">
       <c r="A41" s="75" t="inlineStr">
         <is>
@@ -28161,7 +28913,6 @@
         </is>
       </c>
     </row>
-    <row r="45"/>
     <row r="46">
       <c r="A46" s="75" t="inlineStr">
         <is>
@@ -28213,7 +28964,6 @@
       </c>
       <c r="C49" s="77" t="n"/>
     </row>
-    <row r="50"/>
     <row r="51">
       <c r="A51" s="75" t="inlineStr">
         <is>
@@ -28267,7 +29017,6 @@
       </c>
       <c r="D53" s="77" t="n"/>
     </row>
-    <row r="54"/>
     <row r="55">
       <c r="A55" s="75" t="inlineStr">
         <is>
@@ -28316,7 +29065,6 @@
         </is>
       </c>
     </row>
-    <row r="59"/>
     <row r="60">
       <c r="A60" s="75" t="inlineStr">
         <is>
@@ -28376,7 +29124,6 @@
         </is>
       </c>
     </row>
-    <row r="64"/>
     <row r="65">
       <c r="A65" s="75" t="inlineStr">
         <is>
@@ -28436,7 +29183,6 @@
         </is>
       </c>
     </row>
-    <row r="69"/>
     <row r="70">
       <c r="A70" s="75" t="inlineStr">
         <is>
@@ -28499,7 +29245,6 @@
       </c>
       <c r="D73" s="77" t="n"/>
     </row>
-    <row r="74"/>
     <row r="75">
       <c r="A75" s="75" t="inlineStr">
         <is>
@@ -28555,7 +29300,6 @@
         </is>
       </c>
     </row>
-    <row r="80"/>
     <row r="81">
       <c r="A81" s="75" t="inlineStr">
         <is>
@@ -28618,7 +29362,6 @@
       </c>
       <c r="D84" s="77" t="n"/>
     </row>
-    <row r="85"/>
     <row r="86">
       <c r="A86" s="75" t="inlineStr">
         <is>
@@ -28686,7 +29429,6 @@
         </is>
       </c>
     </row>
-    <row r="91"/>
     <row r="92">
       <c r="A92" s="75" t="inlineStr">
         <is>
@@ -28749,7 +29491,6 @@
       </c>
       <c r="D95" s="77" t="n"/>
     </row>
-    <row r="96"/>
     <row r="97">
       <c r="A97" s="75" t="inlineStr">
         <is>
@@ -28820,7 +29561,6 @@
       </c>
       <c r="D100" s="77" t="n"/>
     </row>
-    <row r="101"/>
     <row r="102">
       <c r="A102" s="75" t="inlineStr">
         <is>
@@ -28901,7 +29641,6 @@
       </c>
       <c r="D107" s="77" t="n"/>
     </row>
-    <row r="108"/>
     <row r="109">
       <c r="A109" s="75" t="inlineStr">
         <is>
@@ -28982,7 +29721,6 @@
       </c>
       <c r="D114" s="77" t="n"/>
     </row>
-    <row r="115"/>
     <row r="116">
       <c r="A116" s="75" t="inlineStr">
         <is>
@@ -29038,7 +29776,6 @@
         </is>
       </c>
     </row>
-    <row r="121"/>
     <row r="122">
       <c r="A122" s="75" t="inlineStr">
         <is>
@@ -29110,7 +29847,6 @@
       </c>
       <c r="D126" s="77" t="n"/>
     </row>
-    <row r="127"/>
     <row r="128">
       <c r="A128" s="75" t="inlineStr">
         <is>
@@ -29178,7 +29914,6 @@
       </c>
       <c r="D132" s="77" t="n"/>
     </row>
-    <row r="133"/>
     <row r="134">
       <c r="A134" s="75" t="inlineStr">
         <is>
@@ -29245,7 +29980,6 @@
       </c>
       <c r="D137" s="77" t="n"/>
     </row>
-    <row r="138"/>
     <row r="139">
       <c r="A139" s="75" t="inlineStr">
         <is>
@@ -29321,7 +30055,6 @@
       </c>
       <c r="D143" s="77" t="n"/>
     </row>
-    <row r="144"/>
     <row r="145">
       <c r="A145" s="75" t="inlineStr">
         <is>
@@ -29392,7 +30125,6 @@
       </c>
       <c r="D148" s="77" t="n"/>
     </row>
-    <row r="149"/>
     <row r="150">
       <c r="A150" s="75" t="inlineStr">
         <is>
@@ -29459,7 +30191,6 @@
         </is>
       </c>
     </row>
-    <row r="154"/>
     <row r="155">
       <c r="A155" s="75" t="inlineStr">
         <is>
@@ -29531,7 +30262,6 @@
       </c>
       <c r="D159" s="77" t="n"/>
     </row>
-    <row r="160"/>
     <row r="161">
       <c r="A161" s="75" t="inlineStr">
         <is>
@@ -29587,7 +30317,6 @@
         </is>
       </c>
     </row>
-    <row r="165"/>
     <row r="166">
       <c r="A166" s="75" t="inlineStr">
         <is>
@@ -29655,7 +30384,6 @@
         </is>
       </c>
     </row>
-    <row r="171"/>
     <row r="172">
       <c r="A172" s="75" t="inlineStr">
         <is>
@@ -29726,7 +30454,6 @@
       </c>
       <c r="D175" s="77" t="n"/>
     </row>
-    <row r="176"/>
     <row r="177">
       <c r="A177" s="75" t="inlineStr">
         <is>
@@ -29798,7 +30525,6 @@
       </c>
       <c r="D181" s="77" t="n"/>
     </row>
-    <row r="182"/>
     <row r="183">
       <c r="A183" s="75" t="inlineStr">
         <is>
@@ -29862,7 +30588,6 @@
         </is>
       </c>
     </row>
-    <row r="188"/>
     <row r="189">
       <c r="A189" s="75" t="inlineStr">
         <is>
@@ -29951,7 +30676,6 @@
       </c>
       <c r="D194" s="77" t="n"/>
     </row>
-    <row r="195"/>
     <row r="196">
       <c r="A196" s="75" t="inlineStr">
         <is>
@@ -30031,7 +30755,6 @@
       </c>
       <c r="D200" s="77" t="n"/>
     </row>
-    <row r="201"/>
     <row r="202">
       <c r="A202" s="75" t="inlineStr">
         <is>
@@ -30102,7 +30825,6 @@
       </c>
       <c r="D205" s="77" t="n"/>
     </row>
-    <row r="206"/>
     <row r="207">
       <c r="A207" s="75" t="inlineStr">
         <is>
@@ -30183,7 +30905,6 @@
       </c>
       <c r="D212" s="77" t="n"/>
     </row>
-    <row r="213"/>
     <row r="214">
       <c r="A214" s="75" t="inlineStr">
         <is>
@@ -30264,7 +30985,6 @@
       <c r="C219" s="77" t="n"/>
       <c r="D219" s="77" t="n"/>
     </row>
-    <row r="220"/>
     <row r="221">
       <c r="A221" s="75" t="inlineStr">
         <is>
@@ -30326,7 +31046,6 @@
         </is>
       </c>
     </row>
-    <row r="224"/>
     <row r="225">
       <c r="A225" s="75" t="inlineStr">
         <is>
@@ -30388,7 +31107,6 @@
         </is>
       </c>
     </row>
-    <row r="228"/>
     <row r="229">
       <c r="A229" s="75" t="inlineStr">
         <is>
@@ -30450,7 +31168,6 @@
         </is>
       </c>
     </row>
-    <row r="232"/>
     <row r="233">
       <c r="A233" s="75" t="inlineStr">
         <is>
@@ -30512,7 +31229,6 @@
         </is>
       </c>
     </row>
-    <row r="236"/>
     <row r="237">
       <c r="A237" s="75" t="inlineStr">
         <is>
@@ -30574,7 +31290,6 @@
         </is>
       </c>
     </row>
-    <row r="240"/>
     <row r="241">
       <c r="A241" s="75" t="inlineStr">
         <is>
@@ -30653,7 +31368,6 @@
         </is>
       </c>
     </row>
-    <row r="245"/>
     <row r="246">
       <c r="A246" s="75" t="inlineStr">
         <is>
@@ -30732,7 +31446,6 @@
         </is>
       </c>
     </row>
-    <row r="250"/>
     <row r="251">
       <c r="A251" s="75" t="inlineStr">
         <is>
@@ -30794,7 +31507,6 @@
         </is>
       </c>
     </row>
-    <row r="254"/>
     <row r="255">
       <c r="A255" s="75" t="inlineStr">
         <is>
@@ -30856,7 +31568,6 @@
         </is>
       </c>
     </row>
-    <row r="258"/>
     <row r="259">
       <c r="A259" s="75" t="inlineStr">
         <is>
@@ -30935,7 +31646,6 @@
         </is>
       </c>
     </row>
-    <row r="263"/>
     <row r="264">
       <c r="A264" s="75" t="inlineStr">
         <is>
@@ -31014,7 +31724,6 @@
         </is>
       </c>
     </row>
-    <row r="268"/>
     <row r="269">
       <c r="A269" s="75" t="inlineStr">
         <is>
@@ -31093,7 +31802,6 @@
         </is>
       </c>
     </row>
-    <row r="273"/>
     <row r="274">
       <c r="A274" s="75" t="inlineStr">
         <is>
@@ -31172,7 +31880,6 @@
         </is>
       </c>
     </row>
-    <row r="278"/>
     <row r="279">
       <c r="A279" s="75" t="inlineStr">
         <is>
@@ -31295,7 +32002,6 @@
         </is>
       </c>
     </row>
-    <row r="285"/>
     <row r="286">
       <c r="A286" s="75" t="inlineStr">
         <is>
@@ -31418,7 +32124,6 @@
         </is>
       </c>
     </row>
-    <row r="292"/>
     <row r="293">
       <c r="A293" s="75" t="inlineStr">
         <is>
@@ -31466,7 +32171,6 @@
         </is>
       </c>
     </row>
-    <row r="296"/>
     <row r="297">
       <c r="A297" s="75" t="inlineStr">
         <is>
@@ -31522,7 +32226,6 @@
         </is>
       </c>
     </row>
-    <row r="301"/>
     <row r="302">
       <c r="A302" s="75" t="inlineStr">
         <is>
@@ -31570,7 +32273,6 @@
         </is>
       </c>
     </row>
-    <row r="305"/>
     <row r="306">
       <c r="A306" s="75" t="inlineStr">
         <is>
@@ -31610,7 +32312,6 @@
         </is>
       </c>
     </row>
-    <row r="308"/>
     <row r="309">
       <c r="A309" s="75" t="inlineStr">
         <is>
@@ -31658,7 +32359,6 @@
         </is>
       </c>
     </row>
-    <row r="312"/>
     <row r="313">
       <c r="A313" s="75" t="inlineStr">
         <is>
@@ -31706,7 +32406,6 @@
         </is>
       </c>
     </row>
-    <row r="316"/>
     <row r="317">
       <c r="A317" s="75" t="inlineStr">
         <is>
@@ -31754,7 +32453,6 @@
         </is>
       </c>
     </row>
-    <row r="320"/>
     <row r="321">
       <c r="A321" s="75" t="inlineStr">
         <is>
@@ -31802,7 +32500,6 @@
       </c>
       <c r="C323" s="77" t="n"/>
     </row>
-    <row r="324"/>
     <row r="325">
       <c r="A325" s="75" t="inlineStr">
         <is>
@@ -31850,7 +32547,6 @@
       </c>
       <c r="C327" s="77" t="n"/>
     </row>
-    <row r="328"/>
     <row r="329">
       <c r="A329" s="75" t="inlineStr">
         <is>
@@ -31906,7 +32602,6 @@
       </c>
       <c r="C332" s="77" t="n"/>
     </row>
-    <row r="333"/>
     <row r="334">
       <c r="A334" s="75" t="inlineStr">
         <is>
@@ -31962,7 +32657,6 @@
       </c>
       <c r="C337" s="77" t="n"/>
     </row>
-    <row r="338"/>
     <row r="339">
       <c r="A339" s="75" t="inlineStr">
         <is>
@@ -32018,7 +32712,6 @@
       </c>
       <c r="C342" s="77" t="n"/>
     </row>
-    <row r="343"/>
     <row r="344">
       <c r="A344" s="75" t="inlineStr">
         <is>
@@ -32074,7 +32767,6 @@
       </c>
       <c r="C347" s="77" t="n"/>
     </row>
-    <row r="348"/>
     <row r="349">
       <c r="A349" s="75" t="inlineStr">
         <is>
@@ -32164,7 +32856,6 @@
         </is>
       </c>
     </row>
-    <row r="353"/>
     <row r="354">
       <c r="A354" s="75" t="inlineStr">
         <is>
@@ -32254,7 +32945,6 @@
         </is>
       </c>
     </row>
-    <row r="358"/>
     <row r="359">
       <c r="A359" s="75" t="inlineStr">
         <is>
@@ -32302,7 +32992,6 @@
         </is>
       </c>
     </row>
-    <row r="362"/>
     <row r="363">
       <c r="A363" s="75" t="inlineStr">
         <is>
@@ -32350,7 +33039,6 @@
       </c>
       <c r="C365" s="77" t="n"/>
     </row>
-    <row r="366"/>
     <row r="367">
       <c r="A367" s="75" t="inlineStr">
         <is>
@@ -32398,7 +33086,6 @@
         </is>
       </c>
     </row>
-    <row r="370"/>
     <row r="371">
       <c r="A371" s="75" t="inlineStr">
         <is>
@@ -32446,7 +33133,6 @@
       </c>
       <c r="C373" s="77" t="n"/>
     </row>
-    <row r="374"/>
     <row r="375">
       <c r="A375" s="75" t="inlineStr">
         <is>
@@ -32494,7 +33180,6 @@
         </is>
       </c>
     </row>
-    <row r="378"/>
     <row r="379">
       <c r="A379" s="75" t="inlineStr">
         <is>
@@ -32542,7 +33227,6 @@
       </c>
       <c r="C381" s="77" t="n"/>
     </row>
-    <row r="382"/>
     <row r="383">
       <c r="A383" s="75" t="inlineStr">
         <is>
@@ -32594,7 +33278,6 @@
         </is>
       </c>
     </row>
-    <row r="386"/>
     <row r="387">
       <c r="A387" s="75" t="inlineStr">
         <is>
@@ -32642,7 +33325,6 @@
       </c>
       <c r="C389" s="77" t="n"/>
     </row>
-    <row r="390"/>
     <row r="391">
       <c r="A391" s="75" t="inlineStr">
         <is>
@@ -32694,7 +33376,6 @@
         </is>
       </c>
     </row>
-    <row r="394"/>
     <row r="395">
       <c r="A395" s="75" t="inlineStr">
         <is>
@@ -32742,7 +33423,6 @@
         </is>
       </c>
     </row>
-    <row r="398"/>
     <row r="399">
       <c r="A399" s="75" t="inlineStr">
         <is>
@@ -32790,7 +33470,6 @@
       </c>
       <c r="C401" s="77" t="n"/>
     </row>
-    <row r="402"/>
     <row r="403">
       <c r="A403" s="75" t="inlineStr">
         <is>
@@ -32842,7 +33521,6 @@
         </is>
       </c>
     </row>
-    <row r="406"/>
     <row r="407">
       <c r="A407" s="75" t="inlineStr">
         <is>
@@ -32894,7 +33572,6 @@
         </is>
       </c>
     </row>
-    <row r="410"/>
     <row r="411">
       <c r="A411" s="75" t="inlineStr">
         <is>
@@ -32942,7 +33619,6 @@
       </c>
       <c r="C413" s="77" t="n"/>
     </row>
-    <row r="414"/>
     <row r="415">
       <c r="A415" s="75" t="inlineStr">
         <is>
@@ -33023,7 +33699,6 @@
         </is>
       </c>
     </row>
-    <row r="419"/>
     <row r="420">
       <c r="A420" s="75" t="inlineStr">
         <is>
@@ -33109,7 +33784,6 @@
         </is>
       </c>
     </row>
-    <row r="424"/>
     <row r="425">
       <c r="A425" s="75" t="inlineStr">
         <is>
@@ -33149,7 +33823,6 @@
         </is>
       </c>
     </row>
-    <row r="427"/>
     <row r="428">
       <c r="A428" s="75" t="inlineStr">
         <is>
@@ -33189,7 +33862,6 @@
         </is>
       </c>
     </row>
-    <row r="430"/>
     <row r="431">
       <c r="A431" s="75" t="inlineStr">
         <is>
@@ -33231,7 +33903,6 @@
         </is>
       </c>
     </row>
-    <row r="434"/>
     <row r="435">
       <c r="A435" s="75" t="inlineStr">
         <is>
@@ -33273,7 +33944,6 @@
         </is>
       </c>
     </row>
-    <row r="438"/>
     <row r="439">
       <c r="A439" s="75" t="inlineStr">
         <is>
@@ -33313,7 +33983,6 @@
         </is>
       </c>
     </row>
-    <row r="441"/>
     <row r="442">
       <c r="A442" s="75" t="inlineStr">
         <is>
@@ -33353,7 +34022,6 @@
         </is>
       </c>
     </row>
-    <row r="444"/>
     <row r="445">
       <c r="A445" s="75" t="inlineStr">
         <is>
@@ -33393,7 +34061,6 @@
         </is>
       </c>
     </row>
-    <row r="447"/>
     <row r="448">
       <c r="A448" s="75" t="inlineStr">
         <is>
@@ -33435,7 +34102,6 @@
         </is>
       </c>
     </row>
-    <row r="451"/>
     <row r="452">
       <c r="A452" s="75" t="inlineStr">
         <is>
@@ -33475,7 +34141,6 @@
         </is>
       </c>
     </row>
-    <row r="454"/>
     <row r="455">
       <c r="A455" s="75" t="inlineStr">
         <is>
@@ -33523,7 +34188,6 @@
       </c>
       <c r="C457" s="77" t="n"/>
     </row>
-    <row r="458"/>
     <row r="459">
       <c r="A459" s="75" t="inlineStr">
         <is>
@@ -33571,7 +34235,6 @@
       </c>
       <c r="C461" s="77" t="n"/>
     </row>
-    <row r="462"/>
     <row r="463">
       <c r="A463" s="75" t="inlineStr">
         <is>
@@ -33620,7 +34283,6 @@
         </is>
       </c>
     </row>
-    <row r="467"/>
     <row r="468">
       <c r="A468" s="75" t="inlineStr">
         <is>
@@ -33669,7 +34331,6 @@
         </is>
       </c>
     </row>
-    <row r="472"/>
     <row r="473">
       <c r="A473" s="75" t="inlineStr">
         <is>
@@ -33717,7 +34378,6 @@
       </c>
       <c r="C475" s="77" t="n"/>
     </row>
-    <row r="476"/>
     <row r="477">
       <c r="A477" s="75" t="inlineStr">
         <is>
@@ -33765,7 +34425,6 @@
         </is>
       </c>
     </row>
-    <row r="480"/>
     <row r="481">
       <c r="A481" s="75" t="inlineStr">
         <is>
@@ -33813,7 +34472,6 @@
         </is>
       </c>
     </row>
-    <row r="484"/>
     <row r="485">
       <c r="A485" s="75" t="inlineStr">
         <is>
@@ -33861,7 +34519,6 @@
       </c>
       <c r="C487" s="77" t="n"/>
     </row>
-    <row r="488"/>
     <row r="489">
       <c r="A489" s="75" t="inlineStr">
         <is>
@@ -33913,7 +34570,6 @@
         </is>
       </c>
     </row>
-    <row r="492"/>
     <row r="493">
       <c r="A493" s="75" t="inlineStr">
         <is>
@@ -33967,7 +34623,6 @@
       </c>
       <c r="D495" s="77" t="n"/>
     </row>
-    <row r="496"/>
     <row r="497">
       <c r="A497" s="75" t="inlineStr">
         <is>
@@ -34015,7 +34670,6 @@
         </is>
       </c>
     </row>
-    <row r="500"/>
     <row r="501">
       <c r="A501" s="75" t="inlineStr">
         <is>
@@ -34063,7 +34717,6 @@
       </c>
       <c r="C503" s="77" t="n"/>
     </row>
-    <row r="504"/>
     <row r="505">
       <c r="A505" s="75" t="inlineStr">
         <is>
@@ -34112,7 +34765,6 @@
         </is>
       </c>
     </row>
-    <row r="509"/>
     <row r="510">
       <c r="A510" s="75" t="inlineStr">
         <is>
@@ -34157,7 +34809,6 @@
         </is>
       </c>
     </row>
-    <row r="512"/>
     <row r="513">
       <c r="A513" s="75" t="inlineStr">
         <is>
@@ -34211,7 +34862,6 @@
       </c>
       <c r="D515" s="77" t="n"/>
     </row>
-    <row r="516"/>
     <row r="517">
       <c r="A517" s="75" t="inlineStr">
         <is>
@@ -34259,7 +34909,6 @@
         </is>
       </c>
     </row>
-    <row r="520"/>
     <row r="521">
       <c r="A521" s="75" t="inlineStr">
         <is>
@@ -34308,7 +34957,6 @@
         </is>
       </c>
     </row>
-    <row r="525"/>
     <row r="526">
       <c r="A526" s="75" t="inlineStr">
         <is>
@@ -34353,7 +35001,6 @@
         </is>
       </c>
     </row>
-    <row r="528"/>
     <row r="529">
       <c r="A529" s="75" t="inlineStr">
         <is>
@@ -34398,7 +35045,6 @@
         </is>
       </c>
     </row>
-    <row r="531"/>
     <row r="532">
       <c r="A532" s="75" t="inlineStr">
         <is>
@@ -34452,7 +35098,6 @@
       </c>
       <c r="D534" s="77" t="n"/>
     </row>
-    <row r="535"/>
     <row r="536">
       <c r="A536" s="75" t="inlineStr">
         <is>
@@ -34516,7 +35161,6 @@
         </is>
       </c>
     </row>
-    <row r="540"/>
     <row r="541">
       <c r="A541" s="75" t="inlineStr">
         <is>
@@ -34568,7 +35212,6 @@
         </is>
       </c>
     </row>
-    <row r="544"/>
     <row r="545">
       <c r="A545" s="75" t="inlineStr">
         <is>
@@ -34620,7 +35263,6 @@
         </is>
       </c>
     </row>
-    <row r="548"/>
     <row r="549">
       <c r="A549" s="75" t="inlineStr">
         <is>
@@ -34669,7 +35311,6 @@
         </is>
       </c>
     </row>
-    <row r="553"/>
     <row r="554">
       <c r="A554" s="75" t="inlineStr">
         <is>
@@ -34718,7 +35359,6 @@
         </is>
       </c>
     </row>
-    <row r="558"/>
     <row r="559">
       <c r="A559" s="75" t="inlineStr">
         <is>
@@ -34770,7 +35410,6 @@
         </is>
       </c>
     </row>
-    <row r="562"/>
     <row r="563">
       <c r="A563" s="75" t="inlineStr">
         <is>
@@ -34834,7 +35473,6 @@
         </is>
       </c>
     </row>
-    <row r="567"/>
     <row r="568">
       <c r="A568" s="75" t="inlineStr">
         <is>
@@ -34886,7 +35524,6 @@
         </is>
       </c>
     </row>
-    <row r="571"/>
     <row r="572">
       <c r="A572" s="75" t="inlineStr">
         <is>
@@ -34935,7 +35572,6 @@
         </is>
       </c>
     </row>
-    <row r="576"/>
     <row r="577">
       <c r="A577" s="75" t="inlineStr">
         <is>
@@ -34999,7 +35635,6 @@
         </is>
       </c>
     </row>
-    <row r="581"/>
     <row r="582">
       <c r="A582" s="75" t="inlineStr">
         <is>
@@ -35051,7 +35686,6 @@
         </is>
       </c>
     </row>
-    <row r="585"/>
     <row r="586">
       <c r="A586" s="75" t="inlineStr">
         <is>
@@ -35115,7 +35749,6 @@
         </is>
       </c>
     </row>
-    <row r="590"/>
     <row r="591">
       <c r="A591" s="75" t="inlineStr">
         <is>
@@ -35176,7 +35809,6 @@
         </is>
       </c>
     </row>
-    <row r="595"/>
     <row r="596">
       <c r="A596" s="75" t="inlineStr">
         <is>
@@ -35514,372 +36146,6 @@
       <c r="C619" s="67" t="inlineStr">
         <is>
           <t>We</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" style="140" min="1" max="2"/>
-    <col width="12" customWidth="1" style="140" min="3" max="4"/>
-    <col width="10" customWidth="1" style="140" min="5" max="5"/>
-    <col width="8" customWidth="1" style="140" min="6" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="17.25" customHeight="1" s="140">
-      <c r="A1" s="91" t="inlineStr">
-        <is>
-          <t>LOOTS DE PROFONDEUR — buffs de « run » (SOURCE ÉDITABLE)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>À chaque étage des profondeurs, on choisit UN loot parmi 2 (ou +). Les buffs s'accumulent</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>toute la descente et sont perdus en ressortant. Édite les valeurs, puis : python3 outils/importer_profondeur.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Effets reconnus : force (dégâts perm. en combat) · gold (or versé si on sort VIVANT) · celerite (% vitesse combat) · armure (armure au début du combat)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="92" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B6" s="92" t="inlineStr">
-        <is>
-          <t>Nom</t>
-        </is>
-      </c>
-      <c r="C6" s="92" t="inlineStr">
-        <is>
-          <t>Effet</t>
-        </is>
-      </c>
-      <c r="D6" s="92" t="inlineStr">
-        <is>
-          <t>Icône (hex)</t>
-        </is>
-      </c>
-      <c r="E6" s="92" t="inlineStr">
-        <is>
-          <t>Normale</t>
-        </is>
-      </c>
-      <c r="F6" s="92" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="G6" s="92" t="inlineStr">
-        <is>
-          <t>Épique</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>pierre-force</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Strength Stone</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>force</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>#d9542a</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G7" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>tresor-gold</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Gold Hoard</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>gold</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>#e0b64e</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>100</v>
-      </c>
-      <c r="F8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G8" t="n">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>pierre-celerite</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Agility Stone</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>agilite</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>#5fb0e8</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Augmente l'agilité</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>plaque-renforcement</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Reinforcement Plate</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>armure</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>#9cd3ff</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>10</v>
-      </c>
-      <c r="F10" t="n">
-        <v>20</v>
-      </c>
-      <c r="G10" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>portail-profondeur</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Depth Portal</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>porte</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>#5fd08a</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>onde-tranquilite</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Wave of Calm</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>pop-monstre</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>#a8e0d0</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Si choisis il n'y a pas de pop de monstre a cette étage.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>poussiere-rubis</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Ruby Dust</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>soin</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>#e0555f</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>20</v>
-      </c>
-      <c r="F13" t="n">
-        <v>40</v>
-      </c>
-      <c r="G13" t="n">
-        <v>80</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Soigne d'autant de hp directement</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>pierre-chance</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Lucky Stone</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>chance-minerais</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>#7ed957</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>3</v>
-      </c>
-      <c r="F14" t="n">
-        <v>6</v>
-      </c>
-      <c r="G14" t="n">
-        <v>12</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Ca augmente le % de minerais a l'étage actuel.</t>
         </is>
       </c>
     </row>

--- a/docs/BRUTAL-items-et-cartes.xlsx
+++ b/docs/BRUTAL-items-et-cartes.xlsx
@@ -5253,7 +5253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" style="140" min="1" max="1"/>
@@ -5642,17 +5642,17 @@
       </c>
       <c r="B19" s="101" t="inlineStr">
         <is>
-          <t>Ring of Luck : double butin</t>
+          <t>Anneau de chance — efficacité</t>
         </is>
       </c>
       <c r="C19" s="102" t="inlineStr">
         <is>
-          <t>50 %</t>
+          <t>+50</t>
         </is>
       </c>
       <c r="D19" s="101" t="inlineStr">
         <is>
-          <t>Chance de DOUBLER le minerai d'un coup de pioche (item Ring of Luck).</t>
+          <t>Efficacité de minage donnée par l'Anneau de chance (butin du Lapin blanc). S'additionne à celle de la pioche.</t>
         </is>
       </c>
       <c r="E19" s="101" t="inlineStr">
@@ -5669,22 +5669,22 @@
       </c>
       <c r="B20" s="101" t="inlineStr">
         <is>
-          <t>Bonus minerai par rareté</t>
+          <t>Efficacité — comment ça marche</t>
         </is>
       </c>
       <c r="C20" s="102" t="inlineStr">
         <is>
-          <t>10 / 15 / 20 / 25 / 35 %</t>
+          <t>0 = 1 minerai · 100 = 2 · 150 = 2 et 50 % d'un 3e</t>
         </is>
       </c>
       <c r="D20" s="101" t="inlineStr">
         <is>
-          <t>Chance d'un minerai bonus par coup selon la rareté (commun → légendaire).</t>
+          <t>Chance de minerai SUPPLÉMENTAIRE par coup. Remplace l'ancien « bonus par rareté » (10 à 35 % offerts à tout le monde) : le rendement dépend maintenant de la PIOCHE. Réglage par pioche dans l'onglet « Pioches ».</t>
         </is>
       </c>
       <c r="E20" s="101" t="inlineStr">
         <is>
-          <t>principal.js</t>
+          <t>systems/minage.js</t>
         </is>
       </c>
     </row>
@@ -5706,12 +5706,12 @@
       </c>
       <c r="D21" s="101" t="inlineStr">
         <is>
-          <t>Temps de base d'un coup (divisé par la vitesse de la pioche équipée).</t>
+          <t>Temps de base d'un coup. Multiplié par la DURETÉ du minerai (×1 commun, ×1,25 uncommon, ×1,55 rare, ×1,9 épique, ×2,3 légendaire) puis divisé par la vitesse de la pioche.</t>
         </is>
       </c>
       <c r="E21" s="101" t="inlineStr">
         <is>
-          <t>principal.js</t>
+          <t>principal.js + systems/minage.js</t>
         </is>
       </c>
     </row>
@@ -5723,22 +5723,22 @@
       </c>
       <c r="B22" s="101" t="inlineStr">
         <is>
-          <t>Veines par étage</t>
+          <t>Verrou de rareté des pioches</t>
         </is>
       </c>
       <c r="C22" s="102" t="inlineStr">
         <is>
-          <t>3 à 6</t>
+          <t>sa rareté + 1</t>
         </is>
       </c>
       <c r="D22" s="101" t="inlineStr">
         <is>
-          <t>Nombre de filons posés dans les salles d'un étage de mine.</t>
+          <t>Une pioche ne casse que les minerais de SA rareté et d'UNE au-dessus (pioche commune → commun + uncommon). C'est ce qui oblige à en forger de meilleures.</t>
         </is>
       </c>
       <c r="E22" s="101" t="inlineStr">
         <is>
-          <t>world/mine.js</t>
+          <t>systems/minage.js</t>
         </is>
       </c>
     </row>
@@ -5750,22 +5750,22 @@
       </c>
       <c r="B23" s="101" t="inlineStr">
         <is>
-          <t>Taille de pile de base</t>
+          <t>Veines par étage</t>
         </is>
       </c>
       <c r="C23" s="102" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3 à 6</t>
         </is>
       </c>
       <c r="D23" s="101" t="inlineStr">
         <is>
-          <t>Nombre max de minerais par pile SANS talent (avant : 10).</t>
+          <t>Nombre de filons posés dans les salles d'un étage de mine.</t>
         </is>
       </c>
       <c r="E23" s="101" t="inlineStr">
         <is>
-          <t>data/items.js + systems/inventaire.js</t>
+          <t>world/mine.js</t>
         </is>
       </c>
     </row>
@@ -5777,62 +5777,62 @@
       </c>
       <c r="B24" s="101" t="inlineStr">
         <is>
+          <t>Taille de pile de base</t>
+        </is>
+      </c>
+      <c r="C24" s="102" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D24" s="101" t="inlineStr">
+        <is>
+          <t>Nombre max de minerais par pile SANS talent (avant : 10).</t>
+        </is>
+      </c>
+      <c r="E24" s="101" t="inlineStr">
+        <is>
+          <t>data/items.js + systems/inventaire.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="101" t="inlineStr">
+        <is>
+          <t>Minage</t>
+        </is>
+      </c>
+      <c r="B25" s="101" t="inlineStr">
+        <is>
           <t>Talent « Ore Hauler » (par rang)</t>
         </is>
       </c>
-      <c r="C24" s="102" t="inlineStr">
+      <c r="C25" s="102" t="inlineStr">
         <is>
           <t>+5 (×5 rangs → 30)</t>
         </is>
       </c>
-      <c r="D24" s="101" t="inlineStr">
+      <c r="D25" s="101" t="inlineStr">
         <is>
           <t>Chaque rang du talent forge agrandit les piles de +5 (5 rangs → 30/pile).</t>
         </is>
       </c>
-      <c r="E24" s="101" t="inlineStr">
+      <c r="E25" s="101" t="inlineStr">
         <is>
           <t>data/talents.js</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="99" t="inlineStr">
+    <row r="26" ht="30" customHeight="1" s="140">
+      <c r="A26" s="99" t="inlineStr">
         <is>
           <t>LUCKY DELVER (talent forge — caverne de chance)</t>
         </is>
       </c>
-      <c r="B25" s="100" t="n"/>
-      <c r="C25" s="100" t="n"/>
-      <c r="D25" s="100" t="n"/>
-      <c r="E25" s="100" t="n"/>
-    </row>
-    <row r="26" ht="30" customHeight="1" s="140">
-      <c r="A26" s="101" t="inlineStr">
-        <is>
-          <t>Caverne</t>
-        </is>
-      </c>
-      <c r="B26" s="101" t="inlineStr">
-        <is>
-          <t>Chance d'apparition</t>
-        </is>
-      </c>
-      <c r="C26" s="102" t="inlineStr">
-        <is>
-          <t>22 %</t>
-        </is>
-      </c>
-      <c r="D26" s="101" t="inlineStr">
-        <is>
-          <t>Proba, par descente éligible (étage 3+), de tomber sur une caverne de chance.</t>
-        </is>
-      </c>
-      <c r="E26" s="101" t="inlineStr">
-        <is>
-          <t>principal.js</t>
-        </is>
-      </c>
+      <c r="B26" s="100" t="n"/>
+      <c r="C26" s="100" t="n"/>
+      <c r="D26" s="100" t="n"/>
+      <c r="E26" s="100" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="101" t="inlineStr">
@@ -5842,17 +5842,17 @@
       </c>
       <c r="B27" s="101" t="inlineStr">
         <is>
-          <t>Bonus de minerais</t>
+          <t>Chance d'apparition</t>
         </is>
       </c>
       <c r="C27" s="102" t="inlineStr">
         <is>
-          <t>+220 %</t>
+          <t>22 %</t>
         </is>
       </c>
       <c r="D27" s="101" t="inlineStr">
         <is>
-          <t>Boost du nombre de veines dans une caverne de chance.</t>
+          <t>Proba, par descente éligible (étage 3+), de tomber sur une caverne de chance.</t>
         </is>
       </c>
       <c r="E27" s="101" t="inlineStr">
@@ -5869,100 +5869,100 @@
       </c>
       <c r="B28" s="101" t="inlineStr">
         <is>
+          <t>Bonus de minerais</t>
+        </is>
+      </c>
+      <c r="C28" s="102" t="inlineStr">
+        <is>
+          <t>+220 %</t>
+        </is>
+      </c>
+      <c r="D28" s="101" t="inlineStr">
+        <is>
+          <t>Boost du nombre de veines dans une caverne de chance.</t>
+        </is>
+      </c>
+      <c r="E28" s="101" t="inlineStr">
+        <is>
+          <t>principal.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="101" t="inlineStr">
+        <is>
+          <t>Caverne</t>
+        </is>
+      </c>
+      <c r="B29" s="101" t="inlineStr">
+        <is>
           <t>Taux de rencontre</t>
         </is>
       </c>
-      <c r="C28" s="102" t="inlineStr">
+      <c r="C29" s="102" t="inlineStr">
         <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="D28" s="101" t="inlineStr">
+      <c r="D29" s="101" t="inlineStr">
         <is>
           <t>Fréquence des combats dans une caverne (vs 0.3 normal → quasi zéro monstre).</t>
         </is>
       </c>
-      <c r="E28" s="101" t="inlineStr">
+      <c r="E29" s="101" t="inlineStr">
         <is>
           <t>principal.js</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="99" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="99" t="inlineStr">
         <is>
           <t>BANQUE</t>
         </is>
       </c>
-      <c r="B29" s="100" t="n"/>
-      <c r="C29" s="100" t="n"/>
-      <c r="D29" s="100" t="n"/>
-      <c r="E29" s="100" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="101" t="inlineStr">
+      <c r="B30" s="100" t="n"/>
+      <c r="C30" s="100" t="n"/>
+      <c r="D30" s="100" t="n"/>
+      <c r="E30" s="100" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="101" t="inlineStr">
         <is>
           <t>Banque</t>
         </is>
       </c>
-      <c r="B30" s="101" t="inlineStr">
+      <c r="B31" s="101" t="inlineStr">
         <is>
           <t>Rendement du coffre-fort</t>
         </is>
       </c>
-      <c r="C30" s="102" t="inlineStr">
+      <c r="C31" s="102" t="inlineStr">
         <is>
           <t>0.2 % / jour</t>
         </is>
       </c>
-      <c r="D30" s="101" t="inlineStr">
+      <c r="D31" s="101" t="inlineStr">
         <is>
           <t>Intérêt composé du dépôt SÛR (par jour de jeu).</t>
         </is>
       </c>
-      <c r="E30" s="101" t="inlineStr">
+      <c r="E31" s="101" t="inlineStr">
         <is>
           <t>data/banque.js</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="99" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="99" t="inlineStr">
         <is>
           <t>RENCONTRES &amp; GROUPES DE MONSTRES</t>
         </is>
       </c>
-      <c r="B31" s="100" t="n"/>
-      <c r="C31" s="100" t="n"/>
-      <c r="D31" s="100" t="n"/>
-      <c r="E31" s="100" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="101" t="inlineStr">
-        <is>
-          <t>Mine</t>
-        </is>
-      </c>
-      <c r="B32" s="101" t="inlineStr">
-        <is>
-          <t>Taux de rencontre</t>
-        </is>
-      </c>
-      <c r="C32" s="102" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="D32" s="101" t="inlineStr">
-        <is>
-          <t>Fréquence de base des combats en explorant une mine.</t>
-        </is>
-      </c>
-      <c r="E32" s="101" t="inlineStr">
-        <is>
-          <t>world/mine.js</t>
-        </is>
-      </c>
+      <c r="B32" s="100" t="n"/>
+      <c r="C32" s="100" t="n"/>
+      <c r="D32" s="100" t="n"/>
+      <c r="E32" s="100" t="n"/>
     </row>
     <row r="33" ht="30" customHeight="1" s="140">
       <c r="A33" s="101" t="inlineStr">
@@ -5972,17 +5972,17 @@
       </c>
       <c r="B33" s="101" t="inlineStr">
         <is>
-          <t>Étage « monstres profonds »</t>
+          <t>Taux de rencontre</t>
         </is>
       </c>
       <c r="C33" s="102" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="D33" s="101" t="inlineStr">
         <is>
-          <t>Étage mini où apparaissent orcs / blobs / molosses / ours / champignons.</t>
+          <t>Fréquence de base des combats en explorant une mine.</t>
         </is>
       </c>
       <c r="E33" s="101" t="inlineStr">
@@ -5999,17 +5999,17 @@
       </c>
       <c r="B34" s="101" t="inlineStr">
         <is>
-          <t>Chance de biome (thème)</t>
+          <t>Étage « monstres profonds »</t>
         </is>
       </c>
       <c r="C34" s="102" t="inlineStr">
         <is>
-          <t>40 %</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D34" s="101" t="inlineStr">
         <is>
-          <t>Proba qu'un étage éligible soit à thème (cristal / glace / lave…).</t>
+          <t>Étage mini où apparaissent orcs / blobs / molosses / ours / champignons.</t>
         </is>
       </c>
       <c r="E34" s="101" t="inlineStr">
@@ -6021,27 +6021,27 @@
     <row r="35" ht="30" customHeight="1" s="140">
       <c r="A35" s="101" t="inlineStr">
         <is>
-          <t>Groupes</t>
+          <t>Mine</t>
         </is>
       </c>
       <c r="B35" s="101" t="inlineStr">
         <is>
-          <t>Taille des groupes</t>
+          <t>Chance de biome (thème)</t>
         </is>
       </c>
       <c r="C35" s="102" t="inlineStr">
         <is>
-          <t>30 / 30 / 20 / 15 / 5 %</t>
+          <t>40 %</t>
         </is>
       </c>
       <c r="D35" s="101" t="inlineStr">
         <is>
-          <t>Proba d'un groupe de 1 / 2 / 3 / 4 / 5 emplacements.</t>
+          <t>Proba qu'un étage éligible soit à thème (cristal / glace / lave…).</t>
         </is>
       </c>
       <c r="E35" s="101" t="inlineStr">
         <is>
-          <t>data/ennemis.js</t>
+          <t>world/mine.js</t>
         </is>
       </c>
     </row>
@@ -6053,17 +6053,17 @@
       </c>
       <c r="B36" s="101" t="inlineStr">
         <is>
-          <t>Facteur de niveau</t>
+          <t>Taille des groupes</t>
         </is>
       </c>
       <c r="C36" s="102" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>30 / 30 / 20 / 15 / 5 %</t>
         </is>
       </c>
       <c r="D36" s="101" t="inlineStr">
         <is>
-          <t>Un niveau de monstre en plus = ~2× plus rare dans le tirage.</t>
+          <t>Proba d'un groupe de 1 / 2 / 3 / 4 / 5 emplacements.</t>
         </is>
       </c>
       <c r="E36" s="101" t="inlineStr">
@@ -6080,17 +6080,17 @@
       </c>
       <c r="B37" s="101" t="inlineStr">
         <is>
-          <t>Rareté d'un « grand » (petit grp)</t>
+          <t>Facteur de niveau</t>
         </is>
       </c>
       <c r="C37" s="102" t="inlineStr">
         <is>
-          <t>×0.5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D37" s="101" t="inlineStr">
         <is>
-          <t>Poids d'un grand monstre dans un petit groupe (plus rare).</t>
+          <t>Un niveau de monstre en plus = ~2× plus rare dans le tirage.</t>
         </is>
       </c>
       <c r="E37" s="101" t="inlineStr">
@@ -6107,17 +6107,17 @@
       </c>
       <c r="B38" s="101" t="inlineStr">
         <is>
-          <t>Bonus d'un « grand » (gros grp)</t>
+          <t>Rareté d'un « grand » (petit grp)</t>
         </is>
       </c>
       <c r="C38" s="102" t="inlineStr">
         <is>
-          <t>×3</t>
+          <t>×0.5</t>
         </is>
       </c>
       <c r="D38" s="101" t="inlineStr">
         <is>
-          <t>Poids d'un grand dans un gros groupe (favorisé).</t>
+          <t>Poids d'un grand monstre dans un petit groupe (plus rare).</t>
         </is>
       </c>
       <c r="E38" s="101" t="inlineStr">
@@ -6134,17 +6134,17 @@
       </c>
       <c r="B39" s="101" t="inlineStr">
         <is>
-          <t>Meneur de la rencontre</t>
+          <t>Bonus d'un « grand » (gros grp)</t>
         </is>
       </c>
       <c r="C39" s="102" t="inlineStr">
         <is>
-          <t>1 monstre du bon niveau</t>
+          <t>×3</t>
         </is>
       </c>
       <c r="D39" s="101" t="inlineStr">
         <is>
-          <t>Chaque rencontre part d'UN monstre tiré dans la fourchette de niveau de l'étage. C'est lui qui fixe la famille du groupe, et il en fait toujours partie.</t>
+          <t>Poids d'un grand dans un gros groupe (favorisé).</t>
         </is>
       </c>
       <c r="E39" s="101" t="inlineStr">
@@ -6161,17 +6161,17 @@
       </c>
       <c r="B40" s="101" t="inlineStr">
         <is>
-          <t>Compagnons : niveau autorisé</t>
+          <t>Meneur de la rencontre</t>
         </is>
       </c>
       <c r="C40" s="102" t="inlineStr">
         <is>
-          <t>≤ haut de la fourchette</t>
+          <t>1 monstre du bon niveau</t>
         </is>
       </c>
       <c r="D40" s="101" t="inlineStr">
         <is>
-          <t>Les compagnons sont de la même famille que le meneur. Jamais au-dessus de la fourchette de l'étage (le combat resterait jouable), mais EN DESSOUS c'est permis — pour la variété. Plus un compagnon est loin du niveau du meneur, plus il est rare (même facteur 2).</t>
+          <t>Chaque rencontre part d'UN monstre tiré dans la fourchette de niveau de l'étage. C'est lui qui fixe la famille du groupe, et il en fait toujours partie.</t>
         </is>
       </c>
       <c r="E40" s="101" t="inlineStr">
@@ -6183,27 +6183,27 @@
     <row r="41" ht="30" customHeight="1" s="140">
       <c r="A41" s="101" t="inlineStr">
         <is>
-          <t>Combat</t>
+          <t>Groupes</t>
         </is>
       </c>
       <c r="B41" s="101" t="inlineStr">
         <is>
-          <t>Fuite selon nb d'ennemis</t>
+          <t>Compagnons : niveau autorisé</t>
         </is>
       </c>
       <c r="C41" s="102" t="inlineStr">
         <is>
-          <t>50 / 33 / 25 / 25 / 20 %</t>
+          <t>≤ haut de la fourchette</t>
         </is>
       </c>
       <c r="D41" s="101" t="inlineStr">
         <is>
-          <t>Chance de fuir un combat normal selon le nombre d'ennemis (1 à 5).</t>
+          <t>Les compagnons sont de la même famille que le meneur. Jamais au-dessus de la fourchette de l'étage (le combat resterait jouable), mais EN DESSOUS c'est permis — pour la variété. Plus un compagnon est loin du niveau du meneur, plus il est rare (même facteur 2).</t>
         </is>
       </c>
       <c r="E41" s="101" t="inlineStr">
         <is>
-          <t>ui/combat.js</t>
+          <t>data/ennemis.js</t>
         </is>
       </c>
     </row>
@@ -6215,22 +6215,22 @@
       </c>
       <c r="B42" s="101" t="inlineStr">
         <is>
-          <t>Hâte : bonus de vitesse</t>
+          <t>Fuite selon nb d'ennemis</t>
         </is>
       </c>
       <c r="C42" s="102" t="inlineStr">
         <is>
-          <t>×1,30</t>
+          <t>50 / 33 / 25 / 25 / 20 %</t>
         </is>
       </c>
       <c r="D42" s="101" t="inlineStr">
         <is>
-          <t>Bonus FIXE tant qu'il reste au moins un tick de Hâte (héros ET monstres). Ne dépend PAS du nombre de ticks : ils ne font que la durée.</t>
+          <t>Chance de fuir un combat normal selon le nombre d'ennemis (1 à 5).</t>
         </is>
       </c>
       <c r="E42" s="101" t="inlineStr">
         <is>
-          <t>systems/combat.js</t>
+          <t>ui/combat.js</t>
         </is>
       </c>
     </row>
@@ -6242,20 +6242,47 @@
       </c>
       <c r="B43" s="101" t="inlineStr">
         <is>
+          <t>Hâte : bonus de vitesse</t>
+        </is>
+      </c>
+      <c r="C43" s="102" t="inlineStr">
+        <is>
+          <t>×1,30</t>
+        </is>
+      </c>
+      <c r="D43" s="101" t="inlineStr">
+        <is>
+          <t>Bonus FIXE tant qu'il reste au moins un tick de Hâte (héros ET monstres). Ne dépend PAS du nombre de ticks : ils ne font que la durée.</t>
+        </is>
+      </c>
+      <c r="E43" s="101" t="inlineStr">
+        <is>
+          <t>systems/combat.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="101" t="inlineStr">
+        <is>
+          <t>Combat</t>
+        </is>
+      </c>
+      <c r="B44" s="101" t="inlineStr">
+        <is>
           <t>Hâte : seuil du tour bonus</t>
         </is>
       </c>
-      <c r="C43" s="102" t="inlineStr">
+      <c r="C44" s="102" t="inlineStr">
         <is>
           <t>8 ticks</t>
         </is>
       </c>
-      <c r="D43" s="101" t="inlineStr">
+      <c r="D44" s="101" t="inlineStr">
         <is>
           <t>À 8 ticks accumulés, le combattant rejoue immédiatement — et ça lui coûte 8 ticks (le surplus reste). Baisser ce seuil = plus de tours d'affilée.</t>
         </is>
       </c>
-      <c r="E43" s="101" t="inlineStr">
+      <c r="E44" s="101" t="inlineStr">
         <is>
           <t>systems/combat.js</t>
         </is>

--- a/docs/BRUTAL-items-et-cartes.xlsx
+++ b/docs/BRUTAL-items-et-cartes.xlsx
@@ -35,7 +35,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="31">
+  <fonts count="34">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -207,8 +207,22 @@
       <color rgb="FF14121A"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF14121A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <color rgb="FFB9C2CC"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFE0B64E"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="72">
+  <fills count="73">
     <fill>
       <patternFill/>
     </fill>
@@ -570,6 +584,11 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8D8C0"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="20">
     <border>
@@ -846,7 +865,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="161">
+  <cellXfs count="164">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1172,6 +1191,9 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="30" fillId="25" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="72" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3223,7 +3245,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L47"/>
+  <dimension ref="A1:Q58"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="140" min="1" max="1"/>
@@ -3238,6 +3260,10 @@
     <col width="8" customWidth="1" style="140" min="10" max="10"/>
     <col width="30" customWidth="1" style="140" min="11" max="11"/>
     <col width="34" customWidth="1" style="140" min="12" max="12"/>
+    <col width="16" customWidth="1" style="140" min="14" max="14"/>
+    <col width="30" customWidth="1" style="140" min="15" max="15"/>
+    <col width="26" customWidth="1" style="140" min="16" max="16"/>
+    <col width="26" customWidth="1" style="140" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3301,6 +3327,26 @@
           <t>passif / note</t>
         </is>
       </c>
+      <c r="N1" s="161" t="inlineStr">
+        <is>
+          <t>Or lâché</t>
+        </is>
+      </c>
+      <c r="O1" s="161" t="inlineStr">
+        <is>
+          <t>Ressource de famille</t>
+        </is>
+      </c>
+      <c r="P1" s="161" t="inlineStr">
+        <is>
+          <t>Recettes (rareté possible)</t>
+        </is>
+      </c>
+      <c r="Q1" s="161" t="inlineStr">
+        <is>
+          <t>Objet spécifique</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="54" customHeight="1" s="140">
       <c r="A2" s="104" t="inlineStr">
@@ -3361,6 +3407,26 @@
       <c r="L2" s="104" t="inlineStr">
         <is>
           <t>passif / mémo (poison, meute…) — NON lu par l'importer, purement informatif</t>
+        </is>
+      </c>
+      <c r="N2" s="162" t="inlineStr">
+        <is>
+          <t>fourchette, par NIVEAU (data/butin.js → OR_PAR_NIVEAU)</t>
+        </is>
+      </c>
+      <c r="O2" s="162" t="inlineStr">
+        <is>
+          <t>par FAMILLE : chance et quantité à chaque kill</t>
+        </is>
+      </c>
+      <c r="P2" s="162" t="inlineStr">
+        <is>
+          <t>selon le NIVEAU (voir le barème sous le tableau)</t>
+        </is>
+      </c>
+      <c r="Q2" s="162" t="inlineStr">
+        <is>
+          <t>réservé aux rencontres uniques (Lapin blanc)</t>
         </is>
       </c>
     </row>
@@ -3427,6 +3493,26 @@
           <t>1 poison par coup</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>15 – 25</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>bois 60% ×1-2</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="107" t="inlineStr">
@@ -3467,6 +3553,26 @@
         </is>
       </c>
       <c r="L5" s="107" t="n"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>15 – 25</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>bois 60% ×1-2</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="59.1" customHeight="1" s="140">
       <c r="A6" s="107" t="inlineStr">
@@ -3513,6 +3619,26 @@
         </is>
       </c>
       <c r="L6" s="107" t="n"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>20 – 30</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>bois 60% ×1-2</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="109" t="inlineStr">
@@ -3573,6 +3699,26 @@
         </is>
       </c>
       <c r="L8" s="107" t="n"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>30 – 45</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="59.1" customHeight="1" s="140">
       <c r="A9" s="107" t="inlineStr">
@@ -3619,6 +3765,26 @@
         </is>
       </c>
       <c r="L9" s="107" t="n"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>40 – 65</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="107" t="inlineStr">
@@ -3659,6 +3825,26 @@
         </is>
       </c>
       <c r="L10" s="107" t="n"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>40 – 65</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="107" t="inlineStr">
@@ -3699,6 +3885,26 @@
         </is>
       </c>
       <c r="L11" s="107" t="n"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>30 – 45</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="107" t="inlineStr">
@@ -3741,6 +3947,26 @@
         </is>
       </c>
       <c r="L12" s="107" t="n"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>60 – 90</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="111" t="inlineStr">
@@ -3803,6 +4029,26 @@
           <t xml:space="preserve">3 poison par coup </t>
         </is>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>30 – 45</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="107" t="inlineStr">
@@ -3847,6 +4093,26 @@
           <t>2 poison par coup</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>40 – 65</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="30" customHeight="1" s="140">
       <c r="A16" s="107" t="inlineStr">
@@ -3891,6 +4157,26 @@
           <t>piquants - à 5 buff riposte en début de combat.</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>60 – 90</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="30" customHeight="1" s="140">
       <c r="A17" s="107" t="inlineStr">
@@ -3933,6 +4219,26 @@
       <c r="L17" s="107" t="inlineStr">
         <is>
           <t>très résistant - commence avec 40 bouclier</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>60 – 90</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -3993,6 +4299,26 @@
         </is>
       </c>
       <c r="L19" s="107" t="n"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>20 – 30</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>cuir 60% ×1-2</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="107" t="inlineStr">
@@ -4035,6 +4361,26 @@
         </is>
       </c>
       <c r="L20" s="107" t="n"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>30 – 45</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>cuir 60% ×1-2</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="107" t="inlineStr">
@@ -4077,6 +4423,26 @@
         </is>
       </c>
       <c r="L21" s="107" t="n"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>30 – 45</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>cuir 60% ×1-2</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="107" t="inlineStr">
@@ -4121,6 +4487,26 @@
           <t>2 brulure par coup</t>
         </is>
       </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>40 – 65</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>cuir 60% ×1-2</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="107" t="inlineStr">
@@ -4161,6 +4547,26 @@
         </is>
       </c>
       <c r="L23" s="107" t="n"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>30 – 45</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>cuir 60% ×1-2</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="107" t="inlineStr">
@@ -4201,6 +4607,26 @@
         </is>
       </c>
       <c r="L24" s="107" t="n"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>40 – 65</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>cuir 60% ×1-2</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="107" t="inlineStr">
@@ -4243,6 +4669,26 @@
         </is>
       </c>
       <c r="L25" s="107" t="n"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>85 – 130</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>cuir 60% ×1-2</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>commun / uncommon</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="115" t="inlineStr">
@@ -4305,6 +4751,26 @@
         </is>
       </c>
       <c r="L27" s="107" t="n"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>60 – 90</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="59.1" customHeight="1" s="140">
       <c r="A28" s="107" t="inlineStr">
@@ -4351,6 +4817,26 @@
         </is>
       </c>
       <c r="L28" s="107" t="n"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>85 – 130</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>commun / uncommon</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="107" t="inlineStr">
@@ -4393,6 +4879,26 @@
         </is>
       </c>
       <c r="L29" s="107" t="n"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>85 – 130</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>commun / uncommon</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="107" t="inlineStr">
@@ -4433,6 +4939,26 @@
         </is>
       </c>
       <c r="L30" s="107" t="n"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>85 – 130</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>commun / uncommon</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="30" customHeight="1" s="140">
       <c r="A31" s="107" t="inlineStr">
@@ -4473,6 +4999,26 @@
         </is>
       </c>
       <c r="L31" s="107" t="n"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>120 – 180</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>commun / uncommon</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="59.1" customHeight="1" s="140">
       <c r="A32" s="107" t="inlineStr">
@@ -4521,6 +5067,26 @@
         </is>
       </c>
       <c r="L32" s="107" t="n"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>120 – 180</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>commun / uncommon</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="117" t="inlineStr">
@@ -4583,6 +5149,26 @@
           <t>stade 1 GENTIL : n'attaque pas ; le tuer le fait ÉVOLUER</t>
         </is>
       </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>120 – 180</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>commun / uncommon</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="107" t="inlineStr">
@@ -4629,6 +5215,26 @@
           <t>stade 2 : évolue en stade 3</t>
         </is>
       </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>120 – 180</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>commun / uncommon</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="30" customHeight="1" s="140">
       <c r="A36" s="107" t="inlineStr">
@@ -4673,6 +5279,26 @@
       <c r="L36" s="107" t="inlineStr">
         <is>
           <t>stade 3 : gros or (niv 10) + 2% Ring of Luck</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>340 – 530</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>commun / uncommon</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>ring-of-luck 2%</t>
         </is>
       </c>
     </row>
@@ -4739,6 +5365,26 @@
           <t>boss unique ; à sa mort se DISLOQUE en son équipage (Kaboom + 3 de siège + porte-étendard)</t>
         </is>
       </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>680 – 1050</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>bois 60% ×1-2</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>uncommon / rare</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="45" customHeight="1" s="140">
       <c r="A39" s="107" t="inlineStr">
@@ -4783,6 +5429,26 @@
           <t>longue mèche (2 tours) puis EXPLOSE pour 100 et meurt — dégâts en code (explose)</t>
         </is>
       </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>85 – 130</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>bois 60% ×1-2</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>commun / uncommon</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="30" customHeight="1" s="140">
       <c r="A40" s="107" t="inlineStr">
@@ -4827,6 +5493,26 @@
           <t>juste son épée ; rapide mais fragile</t>
         </is>
       </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>30 – 45</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>bois 60% ×1-2</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="90" customHeight="1" s="140">
       <c r="A41" s="107" t="inlineStr">
@@ -4876,6 +5562,26 @@
         <is>
           <t>buffe les alliés : +2 Hâte ET +2 force sur tout les alliés. 
 Renfort : appel autant de "gobelin-de-siege" que necessaire pour remplir les espace vide (5 mobs max).</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>85 – 130</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>bois 60% ×1-2</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>commun / uncommon</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -4942,6 +5648,26 @@
           <t>GRAND. Commence avec 50 de BOUCLIER (absorbe avant les PV, cf. Général). À sa mort se disloque en 2 gobelins sur ses 2 places : bouclier à GAUCHE, masse à DROITE.</t>
         </is>
       </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>170 – 260</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>bois 60% ×1-2</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>commun / uncommon</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="30" customHeight="1" s="140">
       <c r="A44" s="107" t="inlineStr">
@@ -4982,6 +5708,26 @@
         </is>
       </c>
       <c r="L44" s="107" t="n"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>60 – 90</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>bois 60% ×1-2</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="30" customHeight="1" s="140">
       <c r="A45" s="107" t="inlineStr">
@@ -5030,6 +5776,26 @@
           <t>Commence avec 15 bouclier</t>
         </is>
       </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>60 – 90</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>bois 60% ×1-2</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="133" t="inlineStr">
@@ -5083,6 +5849,149 @@
       <c r="L47" s="107" t="inlineStr">
         <is>
           <t>Rencontre-énigme : ne frappe JAMAIS tant qu'il marchande (il fuit avant). SEULE exception, la rancune (rencontre d'après le cadeau) : il reste et attaque à 60. Tué = butin garanti (5000 🪙 + 10 rubis/émeraude/saphir/diamant + 1 onyx + 1 sunstone) et ne revient plus. 3e paiement = cadeau (50000 XP, 10 onyx, 10 sunstone, 20 bois enchanté, 20 cuir étrange).</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>340 – 530</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>commun / uncommon</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="163" t="inlineStr">
+        <is>
+          <t>BARÈME DES RECETTES LÂCHÉES — le seul « équipement » qu'un monstre donne encore</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="162" t="inlineStr">
+        <is>
+          <t>Un monstre ne lâche PLUS d'objets tout faits (décision 28/07/2026) : seulement des RECETTES, et rarement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="162" t="inlineStr">
+        <is>
+          <t>La chance MONTE avec le niveau à l'intérieur d'un palier. Les recettes ÉPIQUES et LÉGENDAIRES ne tombent</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="162" t="inlineStr">
+        <is>
+          <t>d'aucun monstre : elles sont réservées aux boss et aux futures quêtes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="162" t="inlineStr">
+        <is>
+          <t>Réglage : data/butin.js → RECETTES_PAR_NIVEAU (pas d'importer, report à la main).</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="161" t="inlineStr">
+        <is>
+          <t>Niveau du monstre</t>
+        </is>
+      </c>
+      <c r="B55" s="161" t="inlineStr">
+        <is>
+          <t>Chance (début → fin du palier)</t>
+        </is>
+      </c>
+      <c r="C55" s="161" t="inlineStr">
+        <is>
+          <t>Raretés possibles</t>
+        </is>
+      </c>
+      <c r="D55" s="161" t="inlineStr">
+        <is>
+          <t>≈ 1 recette tous les</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>1 à 5</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2 % → 5 %</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>commun (poids 1)</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>20 à 50 kills</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>6 à 10</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>5 % → 9 %</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>commun (poids 2) / uncommon (poids 1)</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>11 à 20 kills</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>11 et plus</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>9 % → 14 %</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>uncommon (poids 2) / rare (poids 1)</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>7 à 11 kills</t>
         </is>
       </c>
     </row>

--- a/docs/BRUTAL-items-et-cartes.xlsx
+++ b/docs/BRUTAL-items-et-cartes.xlsx
@@ -3253,7 +3253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q58"/>
+  <dimension ref="A1:Q68"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="140" min="1" max="1"/>
@@ -5099,7 +5099,7 @@
     <row r="33">
       <c r="A33" s="117" t="inlineStr">
         <is>
-          <t>▸ LAPIN BLANC (rencontre spéciale, évolutif)</t>
+          <t>▸ KOBOLDS (le peuple de la cire — mineurs des galeries profondes)</t>
         </is>
       </c>
       <c r="B33" s="118" t="n"/>
@@ -5117,54 +5117,56 @@
     <row r="34" ht="30" customHeight="1" s="140">
       <c r="A34" s="107" t="inlineStr">
         <is>
-          <t>lapin-stage1</t>
+          <t>kobolds-miner</t>
         </is>
       </c>
       <c r="B34" s="107" t="inlineStr">
         <is>
-          <t>White Rabbit</t>
+          <t>Candle Kobold</t>
         </is>
       </c>
       <c r="C34" s="108" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D34" s="107" t="inlineStr">
         <is>
-          <t>lapin</t>
+          <t>kobold</t>
         </is>
       </c>
       <c r="E34" s="108" t="n">
-        <v>1</v>
-      </c>
-      <c r="F34" s="108" t="n">
-        <v>0</v>
+        <v>45</v>
+      </c>
+      <c r="F34" s="108" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="G34" s="108" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H34" s="108" t="n">
-        <v>100</v>
-      </c>
-      <c r="I34" s="107" t="n"/>
-      <c r="J34" s="108" t="n"/>
+        <v>110</v>
+      </c>
+      <c r="I34" s="107" t="inlineStr"/>
+      <c r="J34" s="108" t="inlineStr"/>
       <c r="K34" s="107" t="inlineStr">
         <is>
-          <t>Rencontre spéciale rare (mine, étage 4+, seul/entre lapins)</t>
+          <t>Profondeur</t>
         </is>
       </c>
       <c r="L34" s="107" t="inlineStr">
         <is>
-          <t>stade 1 GENTIL : n'attaque pas ; le tuer le fait ÉVOLUER</t>
+          <t>troupier de base du clan</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>120 – 180</t>
+          <t>85 – 130</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>charbon 50% ×1-2 / pierre taillée 25% ×1</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -5181,12 +5183,12 @@
     <row r="35">
       <c r="A35" s="107" t="inlineStr">
         <is>
-          <t>lapin-stage2</t>
+          <t>kobolds-miner-2</t>
         </is>
       </c>
       <c r="B35" s="107" t="inlineStr">
         <is>
-          <t>Feral Hare</t>
+          <t>Kobold Hammerhand</t>
         </is>
       </c>
       <c r="C35" s="108" t="n">
@@ -5194,33 +5196,33 @@
       </c>
       <c r="D35" s="107" t="inlineStr">
         <is>
-          <t>lapin</t>
+          <t>kobold</t>
         </is>
       </c>
       <c r="E35" s="108" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="F35" s="108" t="inlineStr">
         <is>
-          <t>10x2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G35" s="108" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H35" s="108" t="n">
-        <v>220</v>
-      </c>
-      <c r="I35" s="107" t="n"/>
-      <c r="J35" s="108" t="n"/>
+        <v>90</v>
+      </c>
+      <c r="I35" s="107" t="inlineStr"/>
+      <c r="J35" s="108" t="inlineStr"/>
       <c r="K35" s="107" t="inlineStr">
         <is>
-          <t>Rencontre spéciale (évolution)</t>
+          <t>Profondeur</t>
         </is>
       </c>
       <c r="L35" s="107" t="inlineStr">
         <is>
-          <t>stade 2 : évolue en stade 3</t>
+          <t>maillet à deux mains : lent, mais lourd</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -5230,7 +5232,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>charbon 50% ×1-2 / pierre taillée 25% ×1</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -5247,145 +5249,201 @@
     <row r="36" ht="30" customHeight="1" s="140">
       <c r="A36" s="107" t="inlineStr">
         <is>
-          <t>lapin-stage3</t>
+          <t>kobolds-poison</t>
         </is>
       </c>
       <c r="B36" s="107" t="inlineStr">
         <is>
-          <t>Bloodfang Horror</t>
+          <t>Kobold Venomshot</t>
         </is>
       </c>
       <c r="C36" s="108" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D36" s="107" t="inlineStr">
         <is>
-          <t>lapin</t>
+          <t>kobold</t>
         </is>
       </c>
       <c r="E36" s="108" t="n">
-        <v>250</v>
+        <v>40</v>
       </c>
       <c r="F36" s="108" t="inlineStr">
         <is>
-          <t>10x4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G36" s="108" t="n">
-        <v>2000</v>
+        <v>55</v>
       </c>
       <c r="H36" s="108" t="n">
-        <v>350</v>
-      </c>
-      <c r="I36" s="107" t="n"/>
-      <c r="J36" s="108" t="n"/>
+        <v>140</v>
+      </c>
+      <c r="I36" s="107" t="inlineStr"/>
+      <c r="J36" s="108" t="inlineStr"/>
       <c r="K36" s="107" t="inlineStr">
         <is>
-          <t>Rencontre spéciale (stade final)</t>
+          <t>Profondeur</t>
         </is>
       </c>
       <c r="L36" s="107" t="inlineStr">
         <is>
-          <t>stade 3 : gros or (niv 10) + 2% Ring of Luck</t>
+          <t>arbalète : n'apparaît qu'en groupe de 3+</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>340 – 530</t>
+          <t>120 – 180</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
+          <t>charbon 50% ×1-2 / pierre taillée 25% ×1</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>commun / uncommon</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
+    </row>
+    <row r="37">
+      <c r="A37" s="107" t="inlineStr">
+        <is>
+          <t>big-kobolds-miner</t>
+        </is>
+      </c>
+      <c r="B37" s="107" t="inlineStr">
+        <is>
+          <t>Kobold Deepbreaker</t>
+        </is>
+      </c>
+      <c r="C37" s="108" t="n">
+        <v>9</v>
+      </c>
+      <c r="D37" s="107" t="inlineStr">
+        <is>
+          <t>kobold</t>
+        </is>
+      </c>
+      <c r="E37" s="108" t="n">
+        <v>130</v>
+      </c>
+      <c r="F37" s="108" t="inlineStr">
+        <is>
+          <t>13x2</t>
+        </is>
+      </c>
+      <c r="G37" s="108" t="n">
+        <v>140</v>
+      </c>
+      <c r="H37" s="108" t="n">
+        <v>90</v>
+      </c>
+      <c r="I37" s="107" t="inlineStr"/>
+      <c r="J37" s="108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K37" s="107" t="inlineStr">
+        <is>
+          <t>Profondeur</t>
+        </is>
+      </c>
+      <c r="L37" s="107" t="inlineStr">
+        <is>
+          <t>GRAND. Deux pioches = deux coups par attaque</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>240 – 370</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>charbon 50% ×1-2 / pierre taillée 25% ×1</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
         <is>
           <t>commun / uncommon</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>ring-of-luck 2%</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="117" t="inlineStr">
-        <is>
-          <t>▸ TOUR DE SIÈGE (boss unique + son équipage, spawnOnly)</t>
-        </is>
-      </c>
-      <c r="B37" s="118" t="n"/>
-      <c r="C37" s="118" t="n"/>
-      <c r="D37" s="118" t="n"/>
-      <c r="E37" s="118" t="n"/>
-      <c r="F37" s="118" t="n"/>
-      <c r="G37" s="118" t="n"/>
-      <c r="H37" s="118" t="n"/>
-      <c r="I37" s="118" t="n"/>
-      <c r="J37" s="118" t="n"/>
-      <c r="K37" s="118" t="n"/>
-      <c r="L37" s="118" t="n"/>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="45" customHeight="1" s="140">
       <c r="A38" s="107" t="inlineStr">
         <is>
-          <t>tour-de-siege-gobeline</t>
+          <t>fat-kobolds</t>
         </is>
       </c>
       <c r="B38" s="107" t="inlineStr">
         <is>
-          <t>Goblin Siege Tower</t>
+          <t>Kobold War-Cart</t>
         </is>
       </c>
       <c r="C38" s="108" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D38" s="107" t="inlineStr">
         <is>
-          <t>gobelin</t>
+          <t>kobold</t>
         </is>
       </c>
       <c r="E38" s="108" t="n">
-        <v>150</v>
-      </c>
-      <c r="F38" s="108" t="n">
-        <v>50</v>
+        <v>120</v>
+      </c>
+      <c r="F38" s="108" t="inlineStr">
+        <is>
+          <t>9x3</t>
+        </is>
       </c>
       <c r="G38" s="108" t="n">
-        <v>4000</v>
+        <v>200</v>
       </c>
       <c r="H38" s="108" t="n">
         <v>150</v>
       </c>
-      <c r="I38" s="107" t="n"/>
-      <c r="J38" s="108" t="n">
-        <v>1</v>
+      <c r="I38" s="107" t="inlineStr"/>
+      <c r="J38" s="108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="K38" s="107" t="inlineStr">
         <is>
-          <t>Rencontre spéciale (mine, étage 5+, TOUJOURS seule)</t>
+          <t>Profondeur</t>
         </is>
       </c>
       <c r="L38" s="107" t="inlineStr">
         <is>
-          <t>boss unique ; à sa mort se DISLOQUE en son équipage (Kaboom + 3 de siège + porte-étendard)</t>
+          <t>GRAND. Mitraille : trois coups à distance</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>680 – 1050</t>
+          <t>340 – 530</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>bois 60% ×1-2</t>
+          <t>charbon 50% ×1-2 / pierre taillée 25% ×1</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>uncommon / rare</t>
+          <t>commun / uncommon</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -5397,54 +5455,61 @@
     <row r="39" ht="45" customHeight="1" s="140">
       <c r="A39" s="107" t="inlineStr">
         <is>
-          <t>gobelin-kaboom</t>
+          <t>kobolds-slave-king-1</t>
         </is>
       </c>
       <c r="B39" s="107" t="inlineStr">
         <is>
-          <t>Goblin Kaboom</t>
+          <t>Wax Bearer</t>
         </is>
       </c>
       <c r="C39" s="108" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D39" s="107" t="inlineStr">
         <is>
-          <t>gobelin</t>
+          <t>kobold</t>
         </is>
       </c>
       <c r="E39" s="108" t="n">
-        <v>80</v>
-      </c>
-      <c r="F39" s="108" t="n">
-        <v>0</v>
+        <v>45</v>
+      </c>
+      <c r="F39" s="108" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="G39" s="108" t="n">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="H39" s="108" t="n">
-        <v>150</v>
-      </c>
-      <c r="I39" s="107" t="n"/>
-      <c r="J39" s="108" t="n"/>
+        <v>130</v>
+      </c>
+      <c r="I39" s="107" t="inlineStr">
+        <is>
+          <t>Bouclier alliés +18 (65%)
+Attaque (35%)</t>
+        </is>
+      </c>
+      <c r="J39" s="108" t="inlineStr"/>
       <c r="K39" s="107" t="inlineStr">
         <is>
-          <t>Équipage de la tour (n'apparaît QUE de sa mort)</t>
+          <t>Escorte du Roi de cire</t>
         </is>
       </c>
       <c r="L39" s="107" t="inlineStr">
         <is>
-          <t>longue mèche (2 tours) puis EXPLOSE pour 100 et meurt — dégâts en code (explose)</t>
+          <t>n'apparaît JAMAIS sans le Roi</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>85 – 130</t>
+          <t>340 – 530</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>bois 60% ×1-2</t>
+          <t>charbon 50% ×1-2 / pierre taillée 25% ×1</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5461,59 +5526,67 @@
     <row r="40" ht="30" customHeight="1" s="140">
       <c r="A40" s="107" t="inlineStr">
         <is>
-          <t>gobelin-de-siege</t>
+          <t>kobolds-slave-king-2</t>
         </is>
       </c>
       <c r="B40" s="107" t="inlineStr">
         <is>
-          <t>Siege Goblin</t>
+          <t>Candle Servant</t>
         </is>
       </c>
       <c r="C40" s="108" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D40" s="107" t="inlineStr">
         <is>
-          <t>gobelin</t>
+          <t>kobold</t>
         </is>
       </c>
       <c r="E40" s="108" t="n">
-        <v>30</v>
-      </c>
-      <c r="F40" s="108" t="n">
-        <v>8</v>
+        <v>45</v>
+      </c>
+      <c r="F40" s="108" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="G40" s="108" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H40" s="108" t="n">
-        <v>120</v>
-      </c>
-      <c r="I40" s="107" t="n"/>
-      <c r="J40" s="108" t="n"/>
+        <v>140</v>
+      </c>
+      <c r="I40" s="107" t="inlineStr">
+        <is>
+          <t>Soin 28 (45%)
+Hâte alliés 3 (30%)
+Attaque (25%)</t>
+        </is>
+      </c>
+      <c r="J40" s="108" t="inlineStr"/>
       <c r="K40" s="107" t="inlineStr">
         <is>
-          <t>Équipage de la tour (n'apparaît QUE de sa mort)</t>
+          <t>Escorte du Roi de cire</t>
         </is>
       </c>
       <c r="L40" s="107" t="inlineStr">
         <is>
-          <t>juste son épée ; rapide mais fragile</t>
+          <t>n'apparaît JAMAIS sans le Roi</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>30 – 45</t>
+          <t>340 – 530</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>bois 60% ×1-2</t>
+          <t>charbon 50% ×1-2 / pierre taillée 25% ×1</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>commun</t>
+          <t>commun / uncommon</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -5525,479 +5598,979 @@
     <row r="41" ht="90" customHeight="1" s="140">
       <c r="A41" s="107" t="inlineStr">
         <is>
+          <t>kobolds-king</t>
+        </is>
+      </c>
+      <c r="B41" s="107" t="inlineStr">
+        <is>
+          <t>The Wax King</t>
+        </is>
+      </c>
+      <c r="C41" s="108" t="n">
+        <v>11</v>
+      </c>
+      <c r="D41" s="107" t="inlineStr">
+        <is>
+          <t>kobold</t>
+        </is>
+      </c>
+      <c r="E41" s="108" t="n">
+        <v>220</v>
+      </c>
+      <c r="F41" s="108" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="G41" s="108" t="n">
+        <v>450</v>
+      </c>
+      <c r="H41" s="108" t="n">
+        <v>110</v>
+      </c>
+      <c r="I41" s="107" t="inlineStr">
+        <is>
+          <t>Bouclier alliés +20 (25%)
+Attaque (75%)</t>
+        </is>
+      </c>
+      <c r="J41" s="108" t="inlineStr"/>
+      <c r="K41" s="107" t="inlineStr">
+        <is>
+          <t>Profondeur</t>
+        </is>
+      </c>
+      <c r="L41" s="107" t="inlineStr">
+        <is>
+          <t>Chef du clan. Vient TOUJOURS avec ses deux porte-cire : la rencontre occupe 3 places d'un coup.</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>480 – 750</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>charbon 50% ×1-2 / pierre taillée 25% ×1</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>uncommon / rare</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="42"/>
+    <row r="43" ht="75" customHeight="1" s="140">
+      <c r="A43" s="117" t="inlineStr">
+        <is>
+          <t>▸ LAPIN BLANC (rencontre spéciale, évolutif)</t>
+        </is>
+      </c>
+      <c r="B43" s="118" t="n"/>
+      <c r="C43" s="118" t="n"/>
+      <c r="D43" s="118" t="n"/>
+      <c r="E43" s="118" t="n"/>
+      <c r="F43" s="118" t="n"/>
+      <c r="G43" s="118" t="n"/>
+      <c r="H43" s="118" t="n"/>
+      <c r="I43" s="118" t="n"/>
+      <c r="J43" s="118" t="n"/>
+      <c r="K43" s="118" t="n"/>
+      <c r="L43" s="118" t="n"/>
+    </row>
+    <row r="44" ht="30" customHeight="1" s="140">
+      <c r="A44" s="107" t="inlineStr">
+        <is>
+          <t>lapin-stage1</t>
+        </is>
+      </c>
+      <c r="B44" s="107" t="inlineStr">
+        <is>
+          <t>White Rabbit</t>
+        </is>
+      </c>
+      <c r="C44" s="108" t="n">
+        <v>7</v>
+      </c>
+      <c r="D44" s="107" t="inlineStr">
+        <is>
+          <t>lapin</t>
+        </is>
+      </c>
+      <c r="E44" s="108" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" s="108" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="108" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="108" t="n">
+        <v>100</v>
+      </c>
+      <c r="I44" s="107" t="n"/>
+      <c r="J44" s="108" t="n"/>
+      <c r="K44" s="107" t="inlineStr">
+        <is>
+          <t>Rencontre spéciale rare (mine, étage 4+, seul/entre lapins)</t>
+        </is>
+      </c>
+      <c r="L44" s="107" t="inlineStr">
+        <is>
+          <t>stade 1 GENTIL : n'attaque pas ; le tuer le fait ÉVOLUER</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>120 – 180</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>commun / uncommon</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="30" customHeight="1" s="140">
+      <c r="A45" s="107" t="inlineStr">
+        <is>
+          <t>lapin-stage2</t>
+        </is>
+      </c>
+      <c r="B45" s="107" t="inlineStr">
+        <is>
+          <t>Feral Hare</t>
+        </is>
+      </c>
+      <c r="C45" s="108" t="n">
+        <v>7</v>
+      </c>
+      <c r="D45" s="107" t="inlineStr">
+        <is>
+          <t>lapin</t>
+        </is>
+      </c>
+      <c r="E45" s="108" t="n">
+        <v>50</v>
+      </c>
+      <c r="F45" s="108" t="inlineStr">
+        <is>
+          <t>10x2</t>
+        </is>
+      </c>
+      <c r="G45" s="108" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="108" t="n">
+        <v>220</v>
+      </c>
+      <c r="I45" s="107" t="n"/>
+      <c r="J45" s="108" t="n"/>
+      <c r="K45" s="107" t="inlineStr">
+        <is>
+          <t>Rencontre spéciale (évolution)</t>
+        </is>
+      </c>
+      <c r="L45" s="107" t="inlineStr">
+        <is>
+          <t>stade 2 : évolue en stade 3</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>120 – 180</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>commun / uncommon</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="107" t="inlineStr">
+        <is>
+          <t>lapin-stage3</t>
+        </is>
+      </c>
+      <c r="B46" s="107" t="inlineStr">
+        <is>
+          <t>Bloodfang Horror</t>
+        </is>
+      </c>
+      <c r="C46" s="108" t="n">
+        <v>10</v>
+      </c>
+      <c r="D46" s="107" t="inlineStr">
+        <is>
+          <t>lapin</t>
+        </is>
+      </c>
+      <c r="E46" s="108" t="n">
+        <v>250</v>
+      </c>
+      <c r="F46" s="108" t="inlineStr">
+        <is>
+          <t>10x4</t>
+        </is>
+      </c>
+      <c r="G46" s="108" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H46" s="108" t="n">
+        <v>350</v>
+      </c>
+      <c r="I46" s="107" t="n"/>
+      <c r="J46" s="108" t="n"/>
+      <c r="K46" s="107" t="inlineStr">
+        <is>
+          <t>Rencontre spéciale (stade final)</t>
+        </is>
+      </c>
+      <c r="L46" s="107" t="inlineStr">
+        <is>
+          <t>stade 3 : gros or (niv 10) + 2% Ring of Luck</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>340 – 530</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>commun / uncommon</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>ring-of-luck 2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="165" customHeight="1" s="140">
+      <c r="A47" s="117" t="inlineStr">
+        <is>
+          <t>▸ TOUR DE SIÈGE (boss unique + son équipage, spawnOnly)</t>
+        </is>
+      </c>
+      <c r="B47" s="118" t="n"/>
+      <c r="C47" s="118" t="n"/>
+      <c r="D47" s="118" t="n"/>
+      <c r="E47" s="118" t="n"/>
+      <c r="F47" s="118" t="n"/>
+      <c r="G47" s="118" t="n"/>
+      <c r="H47" s="118" t="n"/>
+      <c r="I47" s="118" t="n"/>
+      <c r="J47" s="118" t="n"/>
+      <c r="K47" s="118" t="n"/>
+      <c r="L47" s="118" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="107" t="inlineStr">
+        <is>
+          <t>tour-de-siege-gobeline</t>
+        </is>
+      </c>
+      <c r="B48" s="107" t="inlineStr">
+        <is>
+          <t>Goblin Siege Tower</t>
+        </is>
+      </c>
+      <c r="C48" s="108" t="n">
+        <v>12</v>
+      </c>
+      <c r="D48" s="107" t="inlineStr">
+        <is>
+          <t>gobelin</t>
+        </is>
+      </c>
+      <c r="E48" s="108" t="n">
+        <v>150</v>
+      </c>
+      <c r="F48" s="108" t="n">
+        <v>50</v>
+      </c>
+      <c r="G48" s="108" t="n">
+        <v>4000</v>
+      </c>
+      <c r="H48" s="108" t="n">
+        <v>150</v>
+      </c>
+      <c r="I48" s="107" t="n"/>
+      <c r="J48" s="108" t="n">
+        <v>1</v>
+      </c>
+      <c r="K48" s="107" t="inlineStr">
+        <is>
+          <t>Rencontre spéciale (mine, étage 5+, TOUJOURS seule)</t>
+        </is>
+      </c>
+      <c r="L48" s="107" t="inlineStr">
+        <is>
+          <t>boss unique ; à sa mort se DISLOQUE en son équipage (Kaboom + 3 de siège + porte-étendard)</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>680 – 1050</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>bois 60% ×1-2</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>uncommon / rare</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="107" t="inlineStr">
+        <is>
+          <t>gobelin-kaboom</t>
+        </is>
+      </c>
+      <c r="B49" s="107" t="inlineStr">
+        <is>
+          <t>Goblin Kaboom</t>
+        </is>
+      </c>
+      <c r="C49" s="108" t="n">
+        <v>6</v>
+      </c>
+      <c r="D49" s="107" t="inlineStr">
+        <is>
+          <t>gobelin</t>
+        </is>
+      </c>
+      <c r="E49" s="108" t="n">
+        <v>80</v>
+      </c>
+      <c r="F49" s="108" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="108" t="n">
+        <v>200</v>
+      </c>
+      <c r="H49" s="108" t="n">
+        <v>150</v>
+      </c>
+      <c r="I49" s="107" t="n"/>
+      <c r="J49" s="108" t="n"/>
+      <c r="K49" s="107" t="inlineStr">
+        <is>
+          <t>Équipage de la tour (n'apparaît QUE de sa mort)</t>
+        </is>
+      </c>
+      <c r="L49" s="107" t="inlineStr">
+        <is>
+          <t>longue mèche (2 tours) puis EXPLOSE pour 100 et meurt — dégâts en code (explose)</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>85 – 130</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>bois 60% ×1-2</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>commun / uncommon</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="107" t="inlineStr">
+        <is>
+          <t>gobelin-de-siege</t>
+        </is>
+      </c>
+      <c r="B50" s="107" t="inlineStr">
+        <is>
+          <t>Siege Goblin</t>
+        </is>
+      </c>
+      <c r="C50" s="108" t="n">
+        <v>3</v>
+      </c>
+      <c r="D50" s="107" t="inlineStr">
+        <is>
+          <t>gobelin</t>
+        </is>
+      </c>
+      <c r="E50" s="108" t="n">
+        <v>30</v>
+      </c>
+      <c r="F50" s="108" t="n">
+        <v>8</v>
+      </c>
+      <c r="G50" s="108" t="n">
+        <v>50</v>
+      </c>
+      <c r="H50" s="108" t="n">
+        <v>120</v>
+      </c>
+      <c r="I50" s="107" t="n"/>
+      <c r="J50" s="108" t="n"/>
+      <c r="K50" s="107" t="inlineStr">
+        <is>
+          <t>Équipage de la tour (n'apparaît QUE de sa mort)</t>
+        </is>
+      </c>
+      <c r="L50" s="107" t="inlineStr">
+        <is>
+          <t>juste son épée ; rapide mais fragile</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>30 – 45</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>bois 60% ×1-2</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>commun</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="107" t="inlineStr">
+        <is>
           <t>gobelin-de-siege-etandart</t>
         </is>
       </c>
-      <c r="B41" s="107" t="inlineStr">
+      <c r="B51" s="107" t="inlineStr">
         <is>
           <t>Siege Standard-Bearer</t>
         </is>
       </c>
-      <c r="C41" s="108" t="n">
+      <c r="C51" s="108" t="n">
         <v>6</v>
       </c>
-      <c r="D41" s="107" t="inlineStr">
+      <c r="D51" s="107" t="inlineStr">
         <is>
           <t>gobelin</t>
         </is>
       </c>
-      <c r="E41" s="108" t="n">
+      <c r="E51" s="108" t="n">
         <v>50</v>
       </c>
-      <c r="F41" s="108" t="n">
+      <c r="F51" s="108" t="n">
         <v>25</v>
       </c>
-      <c r="G41" s="108" t="n">
+      <c r="G51" s="108" t="n">
         <v>200</v>
       </c>
-      <c r="H41" s="108" t="n">
+      <c r="H51" s="108" t="n">
         <v>160</v>
       </c>
-      <c r="I41" s="107" t="inlineStr">
+      <c r="I51" s="107" t="inlineStr">
         <is>
           <t>2 de fore + 2 de hate (60%)
 attaque (30%)
 Renforts (10%)</t>
         </is>
       </c>
-      <c r="J41" s="108" t="n"/>
-      <c r="K41" s="107" t="inlineStr">
+      <c r="J51" s="108" t="n"/>
+      <c r="K51" s="107" t="inlineStr">
         <is>
           <t>Équipage de la tour (n'apparaît QUE de sa mort)</t>
         </is>
       </c>
-      <c r="L41" s="107" t="inlineStr">
+      <c r="L51" s="107" t="inlineStr">
         <is>
           <t>buffe les alliés : +2 Hâte ET +2 force sur tout les alliés. 
 Renfort : appel autant de "gobelin-de-siege" que necessaire pour remplir les espace vide (5 mobs max).</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="N51" t="inlineStr">
         <is>
           <t>85 – 130</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t>bois 60% ×1-2</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="P51" t="inlineStr">
         <is>
           <t>commun / uncommon</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr">
+      <c r="Q51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="133" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="133" t="inlineStr">
         <is>
           <t>▸ GOBELIN BLINDÉ (grand + son duo)</t>
         </is>
       </c>
-      <c r="B42" s="118" t="n"/>
-      <c r="C42" s="118" t="n"/>
-      <c r="D42" s="118" t="n"/>
-      <c r="E42" s="118" t="n"/>
-      <c r="F42" s="118" t="n"/>
-      <c r="G42" s="118" t="n"/>
-      <c r="H42" s="118" t="n"/>
-      <c r="I42" s="118" t="n"/>
-      <c r="J42" s="118" t="n"/>
-      <c r="K42" s="118" t="n"/>
-      <c r="L42" s="118" t="n"/>
-    </row>
-    <row r="43" ht="75" customHeight="1" s="140">
-      <c r="A43" s="107" t="inlineStr">
+      <c r="B52" s="118" t="n"/>
+      <c r="C52" s="118" t="n"/>
+      <c r="D52" s="118" t="n"/>
+      <c r="E52" s="118" t="n"/>
+      <c r="F52" s="118" t="n"/>
+      <c r="G52" s="118" t="n"/>
+      <c r="H52" s="118" t="n"/>
+      <c r="I52" s="118" t="n"/>
+      <c r="J52" s="118" t="n"/>
+      <c r="K52" s="118" t="n"/>
+      <c r="L52" s="118" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="107" t="inlineStr">
         <is>
           <t>gobelin-blinde</t>
         </is>
       </c>
-      <c r="B43" s="107" t="inlineStr">
+      <c r="B53" s="107" t="inlineStr">
         <is>
           <t>Armored Goblin</t>
         </is>
       </c>
-      <c r="C43" s="108" t="n">
+      <c r="C53" s="108" t="n">
         <v>8</v>
       </c>
-      <c r="D43" s="107" t="inlineStr">
+      <c r="D53" s="107" t="inlineStr">
         <is>
           <t>gobelin</t>
         </is>
       </c>
-      <c r="E43" s="108" t="n">
+      <c r="E53" s="108" t="n">
         <v>120</v>
       </c>
-      <c r="F43" s="108" t="n">
+      <c r="F53" s="108" t="n">
         <v>20</v>
       </c>
-      <c r="G43" s="108" t="n">
+      <c r="G53" s="108" t="n">
         <v>500</v>
       </c>
-      <c r="H43" s="108" t="n">
+      <c r="H53" s="108" t="n">
         <v>160</v>
       </c>
-      <c r="I43" s="107" t="n"/>
-      <c r="J43" s="108" t="n">
+      <c r="I53" s="107" t="n"/>
+      <c r="J53" s="108" t="n">
         <v>1</v>
       </c>
-      <c r="K43" s="107" t="inlineStr">
+      <c r="K53" s="107" t="inlineStr">
         <is>
           <t>Eastern + profondeur</t>
         </is>
       </c>
-      <c r="L43" s="107" t="inlineStr">
+      <c r="L53" s="107" t="inlineStr">
         <is>
           <t>GRAND. Commence avec 50 de BOUCLIER (absorbe avant les PV, cf. Général). À sa mort se disloque en 2 gobelins sur ses 2 places : bouclier à GAUCHE, masse à DROITE.</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t>170 – 260</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t>bois 60% ×1-2</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="P53" t="inlineStr">
         <is>
           <t>commun / uncommon</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="Q53" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="30" customHeight="1" s="140">
-      <c r="A44" s="107" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="107" t="inlineStr">
         <is>
           <t>gobelin-sans-blindage1</t>
         </is>
       </c>
-      <c r="B44" s="107" t="inlineStr">
+      <c r="B54" s="107" t="inlineStr">
         <is>
           <t>Mace Goblin</t>
         </is>
       </c>
-      <c r="C44" s="108" t="n">
+      <c r="C54" s="108" t="n">
         <v>5</v>
       </c>
-      <c r="D44" s="107" t="inlineStr">
+      <c r="D54" s="107" t="inlineStr">
         <is>
           <t>gobelin</t>
         </is>
       </c>
-      <c r="E44" s="108" t="n">
+      <c r="E54" s="108" t="n">
         <v>40</v>
       </c>
-      <c r="F44" s="108" t="n">
+      <c r="F54" s="108" t="n">
         <v>15</v>
       </c>
-      <c r="G44" s="108" t="n">
+      <c r="G54" s="108" t="n">
         <v>140</v>
       </c>
-      <c r="H44" s="108" t="n">
+      <c r="H54" s="108" t="n">
         <v>150</v>
       </c>
-      <c r="I44" s="107" t="n"/>
-      <c r="J44" s="108" t="n"/>
-      <c r="K44" s="107" t="inlineStr">
+      <c r="I54" s="107" t="n"/>
+      <c r="J54" s="108" t="n"/>
+      <c r="K54" s="107" t="inlineStr">
         <is>
           <t>Duo du Gobelin blindé (n'apparaît QUE de sa mort)</t>
         </is>
       </c>
-      <c r="L44" s="107" t="n"/>
-      <c r="N44" t="inlineStr">
+      <c r="L54" s="107" t="n"/>
+      <c r="N54" t="inlineStr">
         <is>
           <t>60 – 90</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t>bois 60% ×1-2</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="P54" t="inlineStr">
         <is>
           <t>commun</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr">
+      <c r="Q54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="30" customHeight="1" s="140">
-      <c r="A45" s="107" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="107" t="inlineStr">
         <is>
           <t>gobelin-sans-blindage2</t>
         </is>
       </c>
-      <c r="B45" s="107" t="inlineStr">
+      <c r="B55" s="107" t="inlineStr">
         <is>
           <t>Shield Goblin</t>
         </is>
       </c>
-      <c r="C45" s="108" t="n">
+      <c r="C55" s="108" t="n">
         <v>5</v>
       </c>
-      <c r="D45" s="107" t="inlineStr">
+      <c r="D55" s="107" t="inlineStr">
         <is>
           <t>gobelin</t>
         </is>
       </c>
-      <c r="E45" s="108" t="n">
+      <c r="E55" s="108" t="n">
         <v>60</v>
       </c>
-      <c r="F45" s="108" t="n">
+      <c r="F55" s="108" t="n">
         <v>5</v>
       </c>
-      <c r="G45" s="108" t="n">
+      <c r="G55" s="108" t="n">
         <v>140</v>
       </c>
-      <c r="H45" s="108" t="n">
+      <c r="H55" s="108" t="n">
         <v>120</v>
       </c>
-      <c r="I45" s="107" t="inlineStr">
+      <c r="I55" s="107" t="inlineStr">
         <is>
           <t>Bouclier alliés +15 (100%)</t>
         </is>
       </c>
-      <c r="J45" s="108" t="n"/>
-      <c r="K45" s="107" t="inlineStr">
+      <c r="J55" s="108" t="n"/>
+      <c r="K55" s="107" t="inlineStr">
         <is>
           <t>Duo du Gobelin blindé (n'apparaît QUE de sa mort)</t>
         </is>
       </c>
-      <c r="L45" s="107" t="inlineStr">
+      <c r="L55" s="107" t="inlineStr">
         <is>
           <t>Commence avec 15 bouclier</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t>60 – 90</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t>bois 60% ×1-2</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
+      <c r="P55" t="inlineStr">
         <is>
           <t>commun</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="Q55" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="133" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="133" t="inlineStr">
         <is>
           <t>▸ LE FOU DU ROI (rencontre-énigme)</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="165" customHeight="1" s="140">
-      <c r="A47" s="107" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="107" t="inlineStr">
         <is>
           <t>fou-du-roi</t>
         </is>
       </c>
-      <c r="B47" s="107" t="inlineStr">
+      <c r="B57" s="107" t="inlineStr">
         <is>
           <t>The King's Fool</t>
         </is>
       </c>
-      <c r="C47" s="108" t="n">
+      <c r="C57" s="108" t="n">
         <v>10</v>
       </c>
-      <c r="D47" s="107" t="inlineStr">
+      <c r="D57" s="107" t="inlineStr">
         <is>
           <t>fou</t>
         </is>
       </c>
-      <c r="E47" s="108" t="n">
+      <c r="E57" s="108" t="n">
         <v>100</v>
       </c>
-      <c r="F47" s="108" t="n">
+      <c r="F57" s="108" t="n">
         <v>0</v>
       </c>
-      <c r="G47" s="108" t="n">
+      <c r="G57" s="108" t="n">
         <v>200</v>
       </c>
-      <c r="H47" s="108" t="n">
+      <c r="H57" s="108" t="n">
         <v>200</v>
       </c>
-      <c r="I47" s="107" t="inlineStr">
+      <c r="I57" s="107" t="inlineStr">
         <is>
           <t>Marché (500/2000/10000 🪙) ; fuit après 1 tour du héros ; vol 200 🪙 si touché ; RANCUNE (après cadeau) : ne fuit plus et frappe à 60</t>
         </is>
       </c>
-      <c r="J47" s="108" t="n"/>
-      <c r="K47" s="107" t="inlineStr">
+      <c r="J57" s="108" t="n"/>
+      <c r="K57" s="107" t="inlineStr">
         <is>
           <t>TOUTES les profondeurs — 0,1 % par rencontre (tirage dédié, hors pool de zone)</t>
         </is>
       </c>
-      <c r="L47" s="107" t="inlineStr">
+      <c r="L57" s="107" t="inlineStr">
         <is>
           <t>Rencontre-énigme : ne frappe JAMAIS tant qu'il marchande (il fuit avant). SEULE exception, la rancune (rencontre d'après le cadeau) : il reste et attaque à 60. Tué = butin garanti (5000 🪙 + 10 rubis/émeraude/saphir/diamant + 1 onyx + 1 sunstone) et ne revient plus. 3e paiement = cadeau (50000 XP, 10 onyx, 10 sunstone, 20 bois enchanté, 20 cuir étrange).</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="N57" t="inlineStr">
         <is>
           <t>340 – 530</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="O57" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="P57" t="inlineStr">
         <is>
           <t>commun / uncommon</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr">
+      <c r="Q57" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="163" t="inlineStr">
+    <row r="58"/>
+    <row r="59">
+      <c r="A59" s="163" t="inlineStr">
         <is>
           <t>BARÈME DES RECETTES LÂCHÉES — le seul « équipement » qu'un monstre donne encore</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="162" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="162" t="inlineStr">
         <is>
           <t>Un monstre ne lâche PLUS d'objets tout faits (décision 28/07/2026) : seulement des RECETTES, et rarement.</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="162" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="162" t="inlineStr">
         <is>
           <t>La chance MONTE avec le niveau à l'intérieur d'un palier. Les recettes ÉPIQUES et LÉGENDAIRES ne tombent</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="162" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="162" t="inlineStr">
         <is>
           <t>d'aucun monstre : elles sont réservées aux boss et aux futures quêtes.</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="162" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="162" t="inlineStr">
         <is>
           <t>Réglage : data/butin.js → RECETTES_PAR_NIVEAU (pas d'importer, report à la main).</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="161" t="inlineStr">
+    <row r="64"/>
+    <row r="65">
+      <c r="A65" s="161" t="inlineStr">
         <is>
           <t>Niveau du monstre</t>
         </is>
       </c>
-      <c r="B55" s="161" t="inlineStr">
+      <c r="B65" s="161" t="inlineStr">
         <is>
           <t>Chance (début → fin du palier)</t>
         </is>
       </c>
-      <c r="C55" s="161" t="inlineStr">
+      <c r="C65" s="161" t="inlineStr">
         <is>
           <t>Raretés possibles</t>
         </is>
       </c>
-      <c r="D55" s="161" t="inlineStr">
+      <c r="D65" s="161" t="inlineStr">
         <is>
           <t>≈ 1 recette tous les</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
+    <row r="66">
+      <c r="A66" t="inlineStr">
         <is>
           <t>1 à 5</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>2 % → 5 %</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>commun (poids 1)</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>20 à 50 kills</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
+    <row r="67">
+      <c r="A67" t="inlineStr">
         <is>
           <t>6 à 10</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>5 % → 9 %</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>commun (poids 2) / uncommon (poids 1)</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>11 à 20 kills</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
+    <row r="68">
+      <c r="A68" t="inlineStr">
         <is>
           <t>11 et plus</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>9 % → 14 %</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>uncommon (poids 2) / rare (poids 1)</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>7 à 11 kills</t>
         </is>
